--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -529,16 +529,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>渝中区</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>渝中区</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PVC管,PE管,袖阀管</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管 材询比采购公告 中铁十一局集团有限公司建安分公司招标采购中心就中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房 及配套综合交通枢纽工程CQZSG-2标段项目经理部管材组织询比采购，诚邀有意向的合格供应商参与报价。 一、项目概况及询比采购内容 1.1项目概况 网 （1）新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程位于重庆市中心渝中区中部，具体位置为菜园 坝立交桥以西，龙家湾隧道以东，菜袁路以北，王家坡以南。正在建设的地铁18号线贴临站房北侧，地铁26/27 号线从站区地下通过。项目共划分为4个施工标段，CQZSG-1标段：为国铁站房、地铁站台区域；站北路密不可 分的边坡及场坪工程，包含土石方工程和边坡支护工程，不含机电工程，由中铁建设承建。CQZSG-2标段：为 务 枢纽配套工程，地铁区间、西广场、成都局剩余还建，由中铁十一局承建。CQZSG-3标段：地铁区间、CTC、 站场、东广场，由中铁建工承建。CQZSG-4标段：人防车库、铁路自营车场、综合开发生产配套房屋等，由中 铁二局承建。 （2）标段概况：我方负责新建重庆至黔江铁路重庆站站商房及配套综合交通枢纽工程CQZSG-2标段全部施工内容 （简称B区），主要包含：（1）B区投影范围内盖板以下27号线、26号线明挖区间基坑支护、土石方、区间主体 结构及配套防水、综合接地工程（不含砌筑墙体、装饰装修和机电安装工程），以及承轨层以下市政排水 涵DK1+196（196m）和行包通道；（2）轨道交通26号线暗挖隧道预留工程，其中26左线487m，26号右线408m； （3）站北路E、F、H连接匝道工程，其中E匝道道247m、F匝道285.5m、H匝道174m；（4）B区盖板及以上还建房 屋，其中西侧盖板约3.56万㎡，还建房屋等总建筑面积约3.50万㎡。 1.2询比内容 详见拟采购货物一览表 管 二、供应商资格要求 2.1供应商必须是“中国铁建云链平台”注册并通过审核的供应商。 2.2本次询比采购不接受国被列入“《2026年中国铁建合作方警示名录》、《中铁十一局集团有限公司不良行为供 应商名录》、《JD采购网失信名单》（此项核查针对JMRH项目）”中的供应商,不接受近一年内在铁路建设工程 网公布有违法行为记录及物资供应不良记录、被中国铁路总公司限制投标或已清退出铁路市场的供货商（此项 核查针对铁路站房项目），不接受在铁建云链平台被标记的不良行为供应商。 中 2.3供应商在报价时，如是法定代表人签字的需提供法定代表人身份证复印件、如是法人授权代理人签字的需提 供授权委托书及被授权人身份证复印件。 2.4询比响应供应商需提供营业执照复印件。 2.5其它要求：提供样品、每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌 等质量证明文件，甲方凭此报告检验质量。 2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 三、拟采购物资及相关要求 3.1拟采购物资一览表 交 序 物资 型号 单 项目 货 交货日 数量 备注 号 名称 规格 位 名称 地 期 址 重 直 庆 径6:0mm 市 包含车 PVC 批次交 壁 渝 丝、黑 1 （袖 米 7100 货与零 厚4:-45.mm 中 色胶布、 阀管） 星交货 单节 新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 区 管筛、 （具体 长4m CQZSG-2 标段项目经理部 菜 管箍、 以项目 园 堵头等 通知为 坝 一切相 准） 直 网 重 关费用 2 PE管 米 7100 径2:5mm 庆 站 合计 14200 务 3.2技术规格书： 按询比文件第二章项目技术规格书执行 商 3.3结算和付款 3.3.1采购物资报价规则： 道 固定价格。 3.3.2付款方式 （1）货款支付方式：支付方式包管括但不限于银行转账、银行汇票、银行本票、支票、银行承兑汇票、商业承兑 汇票、财务公司票据、供应链票据、其他数字化信用凭证，票据贴息费用由 供货单位 承担。 （2）付款周期：本合同无预付款。甲方在收到乙方提交的合规增值税专用发票，并经税务机关认证通过后次月 支付乙方上月供应期所国供合格物资70%货款，全部货物供应完毕后三个月内付至95%，剩余货款暂时扣留作为质 量保证金，供货完毕后，由乙方提交结算确认单，经甲方审核通过后做最终结算，待所有物资验收合格后12个月 内无息付清。 （3）逾期付款约定：如甲方付款逾期，双方秉持“长期合作，友好往来”原则，在逾期付款行为发生后一年内 中 乙方不向甲方收取逾期付款利息。若一年甲方仍未支付款项，需向乙方支付逾期付款利息，逾期付款利息起算 时间为全部款项到期之日一年后至付清之日，逾期利息的利率为合同订立时中国人民银行授权全国银行间同业 拆借中心公布的一年期贷款市场报价利率(LPR)1倍。 3.4拟采购物资相关的要求 3.4.1本次询比为整体采购，询比响应供应商报价时须写明单价、到站价和运距，报价包含货物制造、运输、装卸、 售后服务等交付采购人使用前所有可能发生的费用，收到报价后不再增补任何费用。 3.4.2交货期：按照采购人规定的期限内分批次运抵交付。 3.4.3供货地点：甲方指定的甲方所属 中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通 枢纽工程CQZSG-2标段项目施工现场。 3.4.4询比响应供应商必须保证产品的质量及售后服务。询比响应供应商提供的货物制造标准及技术规范等，必须 符合最新相关国家标准、部颁标准相关标准和规范的要求，进场提供相关检验检测报告。 3.4.5采购方在确定成交供应商后有权对成交产品的结构、规格做适当调整，调整内容将以工作联系函形式提前发 至供应商。 3.4.6售后服务：本批采购货物若在验收阶段出现不符合规格或质量标准，供应商必须接受退货要求，并在采购人 规定期限内等量补运合格产品，若未按时交付影响采购人使用，供应商必须承担由此给采购单位造成的后续经 济损失。 3.4.7报价方不得虚报各项技术指标，所供货物若不能符合技术要求，成交供应商必须接受全额退还货款，并承担 由此给采购单位造成的经济损失。 3.4.8验收方法及标准 （1）验收依据：询比采购文件、厂家货物技术标准说明及国家有关的质量标准规定，均为验收依据。 （2）货物验收：货物运抵采购人指定交货处后由双方对照采购清单及技术要求进行验收。 （3）其它要求：每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌等质量证 明文件，甲方凭此报告检验质量。 网 （4）2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 四、报价文件递交 务 4.1此次报价供应商需制作电子报价文件，在递交截止时间前线上递交报价文件。 4.2报价文件递交截止时间：2026年08月24日15时00分。 商 4.3报价文件递交地点：中国铁建云链平台（www.crccep.cn），供应商须登录该平台，在报价文件递交截止时间 前完成所有报价文件资料的上传。 五、发布公告的媒介 道 本次询比公告发布媒体:中国招标投标公共服务平台(www.cebpubservice.com)、中国铁建云链平台（www.crccep.cn） 上同时发布。 管 六、联系方式 1.采购组织单位：中铁十一局集团有限公司建安分公司招标采购中心 地 址：湖北省武汉市国武昌区丁字桥路47号 联 系 人：张先生 联系电话：027-87258521 中 电子邮件：2454774350@qq.com 2.采购人：中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 CQZSG-2 标段项 目经理部 地 址：重庆市渝中区菜袁路59号 联 系 人：金先生 联系电话：16607273445 电子邮件：2285445503@qq.com 2026年08月21日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3077066.html cqdingjiu 2026.08.21 10:06:40</t>
@@ -550,9 +566,13 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 询比采购</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -585,16 +605,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>本项目位于璧山区，建设范围为双龙大道以北，璧铜线以东、渝蓉高速以南、玉泉湖（璧南河）以西区域，用地面积约6平方公里。项目建设遵循循序渐进、分期、分块实施原则，采用“总体开发、分步实施”的方式进行建设开发，合作期限8年，包含建设期和运营期（缺陷责任期），其中建设期6年，共分三期实施。第一期实施玉泉湖以西，第二期实施璧南河以西，第三期实施渝蓉高速下道口。项目总投资44亿元，其中建安费28.6亿元，含市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。项目开发建设内容包括片区范围内的基础设施、人才教育基地、水系生态整治、绿化及广场、公共交通场等。本次采购的内容为本项目一期实施的市政道路所需的钢筋混凝土管及管件，预计供货时间为2026年8月至2027年4月。</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>项目总投资44亿元，其中建安费28.6亿元，含市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>钢筋混凝土管及管件</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>璧山项目钢筋混凝土管询价公告 本项目位于璧山区，建设范围为双龙大道以北，璧铜线以东、渝蓉高速以南、玉泉湖（璧南河）以西区域，用 地面积约6平方公里。项目建设遵循循序渐进、分期、分块实施原则，采用“总体开发、分步实施”的方式进行 建设开发，合作期限8年，包含建设期和运营期（缺陷责任期），其中建设期6年，共分三期实施。第一期实施玉 泉湖以西，第二期实施璧南河以西，第三期实施渝蓉高速下道口。项目总投资44亿元，其中建安费28.6亿元，含 市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。项目开发建设内容包括片区范 围内的基础设施、人才教育基地、水系生态整治、绿化及广场、公共交通场等。本次采购的内容为本项目一期 实施的市政道路所需的钢筋混凝土管及管件，预计供货时间为2026年8月至2027年4月。 网 登录地 mhem&amp;cNh6e0&amp;ce2C2m3s1e71=a64so0d9FAe=0903%e08005206E%6772dm6=%82he29&amp;=cI8p9eeyAs%7t?E%5lB%1iB%a1DetE%c9eweNAi%1iotvB%n/9cE%7.cBe9%ccAiE%p.E%s9%/29址/A%2:：psE%7tAhtD%B8%E%6B%7B%7E%5%78D9%E%5C9%F%9E%7AE%A%1E%9%78%78E%8B%4AD%N&amp;8E%6m657optUa3%6=6290%e3ni51B%5917E%443d6=E%862B%I8eAc%A1iD&amp;88no%tE%4BA%A%4E%7AC%AC%E%4BA%C8%E%8%88AA%E%5A8%A%1E%5B%7A%5E%7A%8B8%E%5B%1%08E%6C9%%98E%9%99%09E%5%58AC%E%5F%8B%8E%8A%5BF%E%9%38A%8EF%BC%%88E%5B9%BD%E%9%99%58EF%BC%%98E%6%59B%0E%5AD%%79E%7BB%F%8E%6B%5E8%E%4BA%A%7E%4B%8A9%E%5B9%AD%E%5C8%BA%E%9%58D8%E%5A%5%79E%9A%1B%9E%7B9%AE%EF%BC%%88E%8A%5BF%E%7%98%78E%5C8%BA%EF%BC%%98E%9A%1B%9E%7B9%AE%E%7=BgB&amp;upC%a=sod&amp;euF%pN=8Flk&amp;cmsusheaE%c7=te%0a9m%6he=8tT&amp;cpS7eeyeE%s9sha%&amp;3c2845d5=pur5A6I&amp;8optUni 信息来源:https://www.chinapipe.net/project/d3077008.html 务 cqdingjiu 2026.08.21 10:06:40 商 道 管 国 中</t>
@@ -606,9 +634,13 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -641,16 +673,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>沙坪坝区</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>沙坪坝区</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>临水临电材料采购</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>采购概算金额：135万元（含税）</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>临水临电材料</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购公告 物资采购 【招标公告】中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购 招标编号：cscec2026081900001246027 项目：重庆市第四人民医院科学城院区建设项目（二期） 发布时间：2026-08-20 17:52:30 报名截止：None 区域：重庆市市辖区沙坪坝区 招标品类：其他类 招标（资格预审）公告 网 中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料采购 采 购 文 件 务 采 购 人： 中国建筑第七工程局有限公司 日 期： 2026年8月 商 目 录 一、响应须知 道 二、评审办法 三、响应注意事项 管 四、响应文件的上传 五．响应文件 六、物资设备合同 国 一、响应须知 【公司总部供应链中心业务监督电话：17516461564】 中 1、工程概况： 工程名称：临水临电材料采购 采购名称： 中国建筑第七工程局有限公司重庆区域暨重庆市第四人民医院科学城院区建设项目 (二期)临水临电 材料采购 采购编号： cscec2026081900001246027 项目地址： 重庆市 工程内容：重庆市第四人民医院科学城院区建设项目 (二期)建筑总用地面积15214.5平方米；总建筑面积65020平 方米，其中住院楼22229.9平方米，实验教学楼8103.6平方米，院内生活楼5830.59平方米，高压氧舱315.53平方米， 地下车库28540.38平方米，以及给排水工程、强电工程、弱电工程、消防工程、暖通工程、总图工程等。为参考。 （说明：描述本工程概况）。最终工程规模及内容以上级部门及采购人确定为准。 采购概算金额：135万元（含税）【采购概算金额视为最高采购限价，响应人响应报价高于最高采购限价的，作 无效响应处理】。 2、采购范围及相关要求： （1）资格审查方式： 资格后审 （2）采购联系人：项目联系人： 修经理 ，电话： 17838218888 ，地址：重庆市 公司联系人： 苟经理 ，电话： 19828530610 ，地址：四川省青白江国际贸易产业园10幢 （3）采购内容： 临水临电材料 （4）工程价款支付： 月结方式，即每月20日结算（遇节假日顺延），次月25日前（结算日后35日历天内），乙 方提供与结算等额增值税专用发票后，支付至前月结算额的70%（遇节假日顺延），最终结算办理完毕6个月后 付至最终结算价款的 97%，剩余3%质保金在质保期满后30日内无息支付。（质保期自全部货物供货完毕且验收 合格日起1年计算）（支付工程款时均应扣除根据采购合同应予扣除的其它金额。） 网 3、响应方式： （1）响应保证金缴纳方式 务 响应保证金采用保证金现金或购买保证金保险（二选一）两种支付方式，支付成功后点击页面【去响应】按钮， 响应人方可正常响应。 方式一：保证金现金缴纳： 商 1、本次采购的响应保证金为/元。 2、保证金收款账户信息请参见云筑网保证金支付页面信息。 道 页面显示账户只对公办理，不接受个人汇款，响应人以响应人基本账户或对公账号转账；响应人转账时务必备注 “交易识别码”（具体操作详见附件《供应商保证金操作手册》或可拨打云筑客服电话：4006-818-555） 方式二：保证金保险缴纳： 管 1、保证金保险可替代保证金，购买后无需再缴纳保证金，响应人可通过“云筑网”购买，响应保险费不退 还；(具体操作详见云筑网上传附件《供应商保证金操作手册》） 2、如发生扣除保证金国情况，保险公司按照保险合同约定向采购单位赔偿相关款项后，保险公司代位取得向响应 单位追偿的权利，响应单位应在规定时间内向保险公司支付相应追偿款。 以下情况可免缴本采购项响应保证金： 中 ①工程局A级分供商。 发生以下情况，响应保证金不予退还： ①响应截止后响应人撤销响应文件的，采购人可以不退还响应保证金。 ②成交人无正当理由不与采购人订立合同，在签订合同时向采购人提出附加条件，或者不按照采购文件要求提 交履约保证金的，取消其成交资格。 （2）采购文件领取事宜：响应人根据采购公告内容领取采购文件，然后根据采购文件要求，进行响应，一经报 价即认为响应人对采购文件已作出实质性响应。 （3）采购文件的澄清与修改 ①采购文件的答疑：如响应人发现采购文件有不清楚的地方或对内容有疑问，要求澄清和解答的，均应在距响 应截止时间2天前向采购人提出答疑，采购人应解答响应人提出的问题。 ②采购人允许响应人在响应截止日期之前对云筑网响应进行修改，但必须在响应截止时间之前完成云筑网响应， 逾期未响应的，则视为无效响应。 （4）（4）响应文件递交事宜 采用云筑网电子响应。 4、评审： （1）评审方法：本次采购拟选出 1 名成交人，区段划分：（如选2个及以上，应明确划分各成交人分供范围及工 程量，成交人按照最终排名顺序享有优先选择权）。采用经评审的（原则上应选择合理低价法），在响应文件 能够满足采购文件实质性要求的响应人中，评审出响应价格合理低价的响应人，但响应价格低于其成本的除外， 具体由采购评审小组在评审会上商定。 （2）响应人有下列情形之一的，取消成交资格： ①成交人在成交后拒签合同； 网 ②成交人未按约定缴纳履约保证金。 采购人： 中国建筑第七工程局有限公司 务 采购时间：2026年8月 二、评 审 办 法 （一）、评审依据 商 1、采购文件 2、响应文件 道 3、评审办法 （二）、评审小组 管 1、评审小组成员：（评审小组应由5人及以上单数评审专家组成，项目负责人必须参与评审。与分供商存在利害 关系的应回避。） 2、小组成员负责根据国评审办法及标准开展评审工作。 3、与响应人有利害关系的，不得进入评审小组。 （三）、评审原则 中 （1）采取经评审的合理低价法：从满足采购文件实质性要求的响应人中，选择合理报价中最低者（不合理低价 除外）为成交分供商。 （四）、初步评审 有效分供商（资审通过并参与有效报价的分供商）数量不少于N（拟选分供商数量）+2家。（询比采购和竞价采 购要求，其他采购方式参照采购管理办法，下同） 出现以下情形的，响应无效。 1、未按要求缴纳响应保证金的。 2、未按要求完成线上响应的。 3、未响应采购文件的实质性要求和条件的。 4、响应人提供虚假资料、隐瞒误导采购的。 5、响应人以他人名义响应或者以其他方式弄虚作假，骗取成交的。 6、响应人ip重复、涉嫌弄虚作假或串通交易行为的。 7、采购文件或法律规定的其它情形。 （五）、详细评审 1、评审：以云筑网填报数据为准。 2、排名：对进入详细评审的响应人响应报价进行汇总后，按响应报价由低到高进行综合排名。 若出现响应人响应报价相同时，按其年度供应商考评评级高低优先排序，若仍相同，可再选用以下进行情况排序 （根据情况自行排序）。 网 ①近三年工抵房金额； ②具有绿色节能环保材料设备； 务 ③云筑网显示的该响应人响应时间等。 1）、采购概算金额（见采购公告）视为最高采购限价，响应人响应报价高于采购概算金额的，作无效响应处理。 响应人响应报价低于成本的，经评审小组评审确定后，作无效响应处理。 商 2）、在评审过程中，评审小组可以要求响应人对所提交的响应文件中含义不明确、表述不一致或者有明显笔误、 文字和计算错误的内容作出必要的澄清、说明或者补正，该澄清、说明和补正属于响应文件的组成部分，须经 采购授权代表书面署名确认，不得改变响应文件的实质性内容，且须经评审小组一致同意。评审小组不接受响 应人主动提出的澄清、说明或补正。 道 3）、经以上评审，有效响应人数量仍须满足“有效分供商（资审通过并参与有效报价的分供商）数量不少于N （拟选分供商数量）+2家”，否则本次采购按废止处理（成交单位数量为“N”）。 管 4）、废止后重新发起采购，需经调查核实后，视具体调查核实结果决定是否准予原响应人参与新发起的采购响 应。 （六）、确定成交候选单位 国 多轮次公开竞争报价：（说明：如需要(应视采购标的物及响应报价情况)进行多轮次公开竞争报价的，应按详细 评审的排名顺序确定一定比例(首轮最高价不得进入二次报价)的有效响应人进行后续轮次报价，总轮次不超过3轮 （竞价采购）。 中 报价规则：响应人提交的首轮报价作为后续报价基准；后续轮次总报价不得高于前轮报价，若设置参考价，单 项报价不得高于参考单价。否则该轮报价无效；最终轮次报价提交后不得撤回或修改（以系统记录为准）。 晋级规则：每轮报价截止后，采购人按报价从低到高排序；出现相同报价时，依次比较：（1）资源库等级；（2） （参考上述第五条第2点，以优质优价为原则，优先选用具备相应能力的本级及上级A级分供商） 成交机制：最终按末轮有效报价的从低到高排序；当最低报价出现多家时，可自主决定成交人。 最终按照排名顺序拟定有效响应人作为成交候选单位，具体成交候选单位数量由评审小组根据采购文件确定。 成交候选单位经审批后作为最终成交单位。 成交候选人放弃成交、因不可抗力不能履行合同、不按照采购文件要求提交履约保证金，或者被查实存在影响 成交结果的违法行为等情形，不符合成交条件的，采购人可以按照评审小组提出的成交候选人名单排序依次确 定其他成交候选人为成交人，也可以重新采购。 （七）、其他事项 1、因响应人原因造成其自身未响应采购要求及未能成交等情况，由响应人自行承担相应责任及损失，与采购人 无关。 2、本采购文件中的合同范本即实际签约合同范本，双方均不允许以任何理由更改合同内容。 三、响应注意事项 1、若响应人对采购文件中之任何内容有不理解之处，须立即联系采购人，以便在响应截止日期之前能予以解释。 2、采购人不保证一定要接受最低价成交，不论响应结果如何响应人的响应文件均不退回，且不对未成交单位做 任何解释。 3、响应人在响应之前，对本采购项的分包条件均已了解，响应即认为已详细了解。 4、采购人对响应人进行考察时，响应人应提供便利条件。 5、本次采购的最终解释权在采购人。 网 四、响应文件的上传 1需上传的响应附件（未上传视为不响应采购文件）有： 务 1.1.《响应函》 1.2.《响应承诺函》 1.3.法定代表人身份证明（格式）； 商 1.4.授权委托书（格式）（若若为法定代表人响应则可不提供）； 1.5.报价清单明细（盖章版） 道 1.6金融工具支付方式及优惠措施 1.7.响应保证金汇款凭证扫描件或免缴证明（云筑网平台缴纳的无须提供）（若需） 管 六、响应文件格式 一、封面（格式） 国 中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料采购响应文件 响应内容：临水临电材料采购 中 （编号：cscec2026081900001246027） 响应人：（盖章） 法定代表人 或授权代理人（签字盖章）： 响 应 函 致：中国建筑第七工程局有限公司 1、经勘察了本工程现场,并仔细研究了响应须知、合同协议条款、合同条件、采购图纸、工程规范、地质勘察报 告、工程量清单、响应答疑、及其他有关采购文件后，我公司愿以我公司云筑网所上传的含税综合单价，并按 采购文件所要求的条件承包在规定工期内完成重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料的施 工、竣工并补充其任何缺陷。 2、我公司保证本工程质量必须：达到符合工程所需材料质量验收标准、设计、合同及有关工程施工及验收规范 的要求标准。 3、一旦我公司的云筑网响应内容被接纳，我公司将在收到成交通知书后按贵公司的要求开始施工，我公司保证 于承诺的工期内或双方议定的工期内完成并交付本合同中规定的整项工程。 4、我公司同意在本区段的正式建设工程施工合同签署之前，云筑网响应将始终对我公司具有约束力，并可随时 被贵公司接受。 5、我公司知道：云筑网报价及云筑网响应的其他部分构成我公司向贵公司的要约，贵公司如发出成交通知书则 成交通知书及云筑网响应、采购文件将构成约束我们双方的合同，如果我公司在接到成交通知书后，没有按贵 公司要求的时间签署正式合同或坚持提出附加条件，那么我公司同意贵公司有权另选成交单位并向我公司追讨 有关损失。 6、我公司知道，贵公司并无义务必须接受所收到的价格最低的或其他任何响应书。 7、云筑网响应内容已考虑了贵公司向我公司发出的关于采购文件的相关答疑，网补充通知（如有的话） 8、云筑网响应效力优先于同时提交的任何响应文件的其他组成部分。 响应人： （盖章） 务 日 期： 年 月 日 响应承诺书 商 致：中国建筑第七工程局有限公司 我系有幸参与贵公司 重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料的响应，我公司经研究决定， 在此郑重承诺： 道 1、我公司在响应过程中已完全了解并掌握了采购内容、合同条件及施工现场等情况。确保云筑网响应报价操作 为本公司自己操作，如响应后发生非本公司操作的情形，本公司承担相应违约责任。 管 2、我公司已经详细阅读该采购文件所有内容，充分领会并完全接受采购文件所述响应人应尽的实质性的权利与 义务。我公司保证不会对采购文件产生不利于双方友好合作关系和将增加贵公司采购范围内经济支出的重大误 解。 3、我公司确认，贵公国司发出的采购文件所有内容为不可割裂的整体。 4、我公司保证成交后不会对成交价格提出任何异议，更不会以任何理由要求贵公司针对成交范围的价款要求额 外补偿。不会以不了解采购文件、合同文件为由或曲解、片面理解采购文件、合同文件或割裂采购文件、合同 文件，断章取义，向贵公司提出任何补偿要求。 中 5、在本合同的履约过程中，如因我公司的供货或质量原因导致贵司损失，我公司保证承担因此而给贵公司带来 的所有经济上的损失。 6、我公司将本工程作为重点项目对待，保证不会出现供货能力不能满足施工需要的现象。为满足本工程业主及 贵公司在质量、进度、安全、环保上的要求，我公司将采取一切措施保证物资设备生产、供应、租赁，运输等 均满足贵公司的要求，并保证不会因此而向贵公司提出增加任何补偿要求。 7、我公司承诺无论本工程最终的成本状况如何，将不会违背合同基本原则而向贵公司要求增加或补偿合同文件 约定以外的任何费用。 8、我公司认为，贵公司可以就物资设备采购数量或租赁时长进行调整，并且此种调整不构成我公司的索赔理由。 响应人：（盖章） 法定代表人或 其授权代理人：（签字或盖章） 日 期： 年 月 日 响应人名称：【全称】 单位性质： 地 址： 成立时间：年月日 经营期限： 姓名：性别：年龄：职务：系（响应人名称）的法定代表人。 网 特此证明。 响应人：（盖单位章） 务 年月日 授权委托书 商 本人（姓名）系（响应人名称）的法定代表人，现委托（姓名）为我方代理人。代理人根据授权，以我方名义 签署、澄清、说明、补正、递交、撤回、修改中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建 设项目 (二期)临水临电材料采购（采购项目名称）响应文件、签订合同和处理有关事宜，其法律后果由我方承担。 道 委托期限：本授权书于年月日签字生效，至本次采购期结束为止。授权期限内无特殊情况不变更合法授权代理 人。 代理人无权转委托。 管 特此声明。 响应人：（盖章） 国 法定代表人：（签字） 身份证号： 中 授权代理人：（签字） 身份证号： 联系方式： 日期： 年 月 日 备注：法定代表人和委托代理人必须在授权书上亲笔签名，不得使用印章、签名章或其他电子制版签名,同时附 法定代表人和授权代理人身份证复印件（正反面，加盖公章） 报价清单明细 不 含 含 不含 计量单 税 税 含税 备 序号 材料名称 规格型号 数量 税 税合 税额 位 率 单 合价 注 单 价 价 价 1 镀锌钢管 DN100*4.0 米 500 2 镀锌钢管 DN150*4.5 米 250 3 镀锌钢管 DN65*3.25 米 650 4 镀锌钢管 DN50*3.25 米 800 5 PE管 DN100*1.6MPA 米 450 6 PPR管 DN50*1.6MPA 米 400 7 闸阀 DN100 个 22 8 闸阀 DN250 个 10 9 截止阀 DN50 个 42 网 10 截止阀 DN25 个 60 11 蝶阀 DN100 个 6 12 消防箱 800×1000×250mm 台 20 务 功率30kw,扬程144m，流 13 加压泵（变频控制） 台 1 量55m/h 14 橡塑保温材料 DN100*20mm 米 620 商 15 橡塑保温材料 DN150*30mm 米 280 16 橡塑保温材料 DN65*20mm 米 700 17 压线钳 CO-1000 个 1 道 18 污水泵 380V4KW=25米 台 12 19 污水泵 380V5KW=30米 台 7 20 热熔机 63-160 台 1 管 21 电工胶布 / 卷 200 22 高压自粘带 / 卷 120 23 水泵控制箱 / 个 8 国 24 PE聚乙烯管 DE110*1.6MPA m 560 25 PE聚乙烯管 DE75*1.6MPA m 420 26 PE聚乙烯管 DE63*1.6MPA m 480 中 27 PE聚乙烯管 DE32*1.6MPA m 750 28 PE球阀 DN25 个 6 29 PE球阀 DN50 个 6 30 PE球阀 DN100 个 5 31 镀锌桥架 200*100*1.2mm 米 1200 32 PVC排水管 DE300*5.0 m 180 33 PVC排水管 DE200*5.0 m 380 34 PVC排水管 DE160*4.0 m 486 35 PVC排水管 De110*4.0 米 560 36 PVC排水管 DE75*3.0 m 420 37 PVC排水管 DE50*2.0 m 660 38 PVC排水管 DE32*2.0 m 380 39 PPR给水管 De90*1.6MPA 米 440 40 PPR给水管 DE75*1.6MPA 米 360 41 PPR给水管 DE63*1.6MPA 米 450 42 PPR给水管 De50*1.6MPA 米 435 43 PPR给水管 De40*1.6MPA 米 315 44 PPR给水管 DE32*1.6MPA 米 520 45 PPR给水管 De25*1.6MPA 米 680 46 PPR给水管 De20*1.6MPA 米 370 47 橡塑保温板 平板×20mm m 15 48 橡塑保温板 平板×30mm m 28 49 保温胶 3公斤/桶 桶 25 网 50 PPR给水管接头 De75 个 30 51 PPR给水管弯头 De75 个 20 52 PPR给水管三通 De75 个 22 务 53 PPR给水管接头 De63 个 20 54 PPR给水管弯头 De63 个 15 55 PPR给水管三通 De63 个 15 商 56 PPR给水管接头 De50 个 17 57 PPR给水管弯头 De50 个 22 58 PPR给水管三通 De50 个 17 道 59 PPR给水管接头 De40 个 14 60 PPR给水管弯头 De40 个 22 61 PPR给水管三通 De40 个 17 管 62 PPR给水管接头 De32 个 14 63 PPR给水管弯头 De32 个 14 64 PPR给水管三通 De32 个 17 国 65 PPR给水管接头 De25 个 22 66 PPR给水管弯头 De25 个 17 67 PPR给水管三通 De25 个 14 中 68 PPR给水管接头 De20 个 25 69 PPR给水管弯头 De20 个 17 70 PPR给水管三通 De20 个 22 71 PPR内丝直接 De25 个 17 72 PPR内丝直接 De20 个 84 73 球墨铸铁井盖 700*800*40T 套 22 74 球墨铸铁井盖 1000*1000*20T 套 20 75 球墨铸铁雨箅子 400*600*30 块 1750 76 球墨铸铁雨箅子 350*500*30 块 1200 77 高分子成品排水沟 300*300*1000 米 850 78 高压洗车机 380v/3KW 套 5 79 高压洗车机 380v/5.5KW 套 3 80 HDPE双壁波纹管 DN300 米 360 81 HDPE双壁波纹管 DN200 米 410 82 HDPE双壁波纹管 DN400 米 340 83 HDPE双壁波纹管 DN800 米 260 84 玻璃钢化粪池 20m 个 1 85 玻璃钢化粪池 50m 个 1 86 不锈钢消防水箱 12m 个 1 87 一级配电柜 2000*1200*500*630A 台 1 88 二级配电柜 800*600*210*250A 台 8 89 铜芯电缆线 YC3*16+2*10 米 60 90 铜芯电缆线 YC3*10+2*6 米 70 网 91 铜芯电缆线 YC3*6+2*4 米 70 92 铜芯电缆线 YC3*10 米 100 93 铜芯电缆线 YC3*6 米 100 务 94 铜芯电缆线 YC3*4 米 100 95 铜芯电缆线 YC3*2.5+2*1.5 米 100 96 聚录乙烯铝芯电缆 YJLV-22-4*185+1*95 米 50 商 97 聚录乙烯铝芯电缆 YJLY-4*25+1*16 米 90 98 聚录乙烯铝芯电缆 YJLY-4*35+1*16 米 100 99 聚录乙烯铝芯电缆 YJY-4*50+1*25 米 90 道 100 聚录乙烯铝芯电缆 YJLY-4*70+1*35 米 72 101 网线 Cat5e 米 100 102 铜芯电线 BV-2.5 米 400 管 103 铜芯电线 BV-4 米 300 104 铜芯电线 BV-6 米 200 105 铝芯电缆线 YJLV3*10 米 100 国 106 透明塑壳断路器 3P32A 米 34 107 透明塑壳断路器 3P63A 米 28 108 透明塑壳断路器 4P100A 米 26 中 109 透明塑壳断路器 4P160A 米 22 110 透明塑壳断路器 4P250A 米 20 111 透明塑壳断路器 4P400A 米 8 112 低压铝芯电缆 YJLV-4*300+1 米 20 113 低压铝芯电缆 YJLV-4*150+1 米 50 114 铝芯铠装电缆 YJLV-22-4*95+1*50 米 60 115 铜铝线鼻 300mm2 个 20 116 铜铝线鼻 150mm2 个 36 117 铜铝线鼻 95mm2 个 24 118 铜铝线鼻 50mm2 个 20 合计 0.00 0.00 0.00 1、综合单价：包括但不限于材料费、保险费、风险费、包装费、装车费、过桥过路费、管理费、检验费、技术 指导费、货到工地负责卸货堆入至指定地点等所有费用。本合同单价一次包死，在合同履行过程中不再做任何 调整。本合同的总价为暂估价，用方有权调整合同中材料计划或材料数量，材料数量和规格的调整，不影响本 合同单价及其他条款的执行。 2、计量方式：查看检测报告合格证，以实际验收通过数量计量。 3、付款比例：月结方式，即每月20日结算（遇节假日顺延），次月25日前（结算日后35日历天内），乙方提供 与结算等额增值税专用发票后，支付前月结算额的70%（遇节假日顺延）；供货完毕，验收合格，材料相关资料 （包括不限于合格证、质检报告等）移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%；剩余3% 质保金在质保期满后30日内无息支付。质保期自全部货物供货完毕且竣工验收合格日起1年计算，支付工程款时 均应扣除根据采购合同应予扣除的其它金额。 4、付款方式： （1）现金支付:采用现金转账的模式支付； （2）非现金支付:包括不限于(1)金融工具支付:银行承兑汇票，商业承兑汇票，网应付账款保理，银行信用证，中 建财务公司承兑汇票。(2)工抵房支付。 5、响应报价表中所列数量的变动，丝毫不会降低或影响合同条款的效力。 务 6、整个合同执行期内，若遇市场价格下行，甲方有权做出价格调整，乙方应接受并重新签订补充协议确认价格。 若乙方无法接受新的低价，甲方有权重新选择其他能够响应该价格的供应商进行供货，乙方无条件同意。 响应人（加盖公章）： 商 法定代表人或授权代理人（签字）： 日 期：年月 道 金融工具支付方式及优惠措施 管 1、金融工具支付： 可接受金融工具支付比例累计为%，其中： ① 可接受的国银行承兑汇票比例%；贴息响应人自行承担。 ② 可接受的商业承兑汇票比例%；贴息响应人自行承担。 金融支付 ③ 可接受的应付账款保理比例 %；贴息响应人自行承担。 中④ 可接受的银行信用证比例%；贴息响应人自行承担。 ⑤ 可接受的中建财务公司承兑汇票比例为%；贴息响应人自行承担。 2、资产支付 资产支付 可接受比例为合同额的%。 3、优惠付款比例：按按照采购文件的付款比例，我方可优惠%。 4、如响应人提供其他由于采购条件的承诺，请逐项列示。 响应人（加盖公章）： 法定代表人或授权代理人（签字）： 日 期：年月 响应保证金汇款凭证扫描件或免缴证明（若需） 响应人（加盖公章）： 法定代表人或授权代理人（签字）： 日 期：年月 六、物资设备采购合同 合同编号：______________________ 物资采购与供应合同 （通用） 项目名称：【 重庆市第四人民医院科学城院区建设项目 (二期) 】 网 甲 方：【 】 乙 方：【 】 务 签订时间：【 】 签订地点：【 】 商 目录 1. 工程概况及供货范围 道 2. 企业性质 3. 合同价款 2 管 4. 质量要求 5. 供货时间及地点 6. 交货与验收 国 7. 结算方式及时间 8. 支付 中 9. 发票 10. 双方责任 11. 不可抗力 12. 权利瑕疵 13. 保密 14. 违约与赔偿 15. 联络与送达 16. 争议解决 17. 补充条款 18. 其他 物资采购与供应合同 甲方（买受人）：【中建七局安装工程有限公司 】 乙方（出卖人）：【 】 根据《中华人民共和国民法典》及有关规定，为明确双方权利、义务和责任，经双方协商一致，就甲方承包的 【高新LIVE（咸阳高新区租赁住房）建设项目】工程所用【 水电管材】采购与供应事宜签订本合同条款，愿共 同遵守。 1. 网 1.1 工程名称：【高新LIVE（咸阳高新区租赁住房）建设项目 】 1.2 工程地点：【陕西省咸阳市星火大道】 务 本合同供货范围为：【高新LIVE（咸阳高新区租赁住房）建设项目 】的【水电管材】供应（以下简称为“本合 同标的物”）。 1.3本合同标的物的数量为暂定量，乙方按附件1《计划采商购与供应物资清单》所列品种和规格供货，最终以经甲 方验收合格的实际数量为准。 2. 企业性质 道 乙方企业规模：大型 □中型 □小型 □微型企业 以上企业规模由乙方根据（1）工信部官网：“中小企业规模类型测试网址https://baosong.miit.gov.cn/ScaleTest。 （2）工信部微信小程序：“中小企业规模类型自测”两种渠道自测确定。 管 乙方应保证其企业规模的真实性。如乙方提供信息不实，经甲方查证后，将按照《中国建筑股份有限公司分供 商资源管理办法》中的《不良行为分供商禁用处理标准》第19项对乙方严格实施禁用管理。 合同价款 国 3.1 本合同采用第【 】种价格形式： （1）固定综合单价包干，价格不可调整。 中 3.2 本合同价款为各项货款之和，合同价款（含增值税）暂定：（大写）【 】（￥【 】元），其中不含税价款为 （大写）【 】（￥【 】元），增值税为（大写）【 】（￥【 】元），税率为【 】%。最终甲乙双方以实际验收 的数量结算。 3.3 本合同约定的不含税价款不因国家税率变化而变化，在合同履行期间，如遇国家的税率调整，则价税合计的 合同价款或货款相应调整，以开具发票时间为准。 3.4 本合同不含税价款仅指不包含增值税，除增值税外的其他全部税费（包括但不限于城市建设维护税、教育费 附加及地方教育费附加、个人所得税、合同印花税、企业所得税、车船使用税以及国家和地方规定的所有税费） 均包含在不含税价款中。 3.5 本合同标的物的计价、结算和支付货币均为人民币。 3.6 本合同标的物的计量单位为中华人民共和国法定公制计量单位（除技术规范标准另有规定外）。 3.7 本合同标的物的不含税单价，指运抵本工程施工现场甲方指定交货地点的综合单价，包括但不限于货物费、 加工费、包装费、人工搬运费（由乙方自行协调，甲方只进行指定场地和材料验收工作）、运输费、出厂检测费 （包括但不限于到场后的第三方检测费用）、装卸费、码放费、现场倒运费用，保险费、仓储费、驻厂监造费、 运输造成的道路污染的清理及维修费用、除增值税以外的税金、乙方合理的利润、管理费、市场价格波动带来 的风险、向有关部门缴纳的各项费用以及政策性文件所规定的各项应有费用等乙方履行本合同规定义务的全部 价款与费税。除本合同第3.1条约定的因素外，不含税单价不因政府政策变动、市场环境改变、税率调整等而调 整。 3.8 除合同条款另有约定外，本合同标的物的不含税单价已包含专利、专有技术以及技术秘密的使用费。 质量要求 4.1 乙方应在交货同时向甲方提供本合同标的物制造商出具的书面质量保证书。 4.2 本合同所采购与供应的物资，应符合现行中华人民共和国国家标准及行业或地方标准，行业标准或地方标准 高于国家标准的，执行行业标准或地方标准。各项技术性能指标经本工程所在地具有相应检测资质的专业机构 或单位检测中心检验必须符合相关标准要求。合同执行过程中，若出现新的国家标准、行业标准、地方标准， 则以更新后的标准为准。 网 4.3 乙方的物资供应与管理应符合国家有关环保法律、法规和甲方ISO14001环境体系及OHSMS18001职业安全健康 管理体系标准。 4.4 本合同标的物的质量保证期为最后一批货物验收合格之日起满【180】日。 务 4.5在合同履行期及质量保证期内，乙方无条件地向甲方提供缺陷产品的免费维修、更换等服务。针对甲方提出 的书面要求，乙方必须在3日内给予书面答复。如有必要，乙方在3日内指派专人到现场解决，因此产生的所有费 用均由乙方承担。 商 4.6 如缺陷产品经乙方进行免费维修和更换后仍无法达到甲方要求的质量标准时，甲方有权终止合同。终止合同 后，乙方需向甲方赔偿由于乙方问题造成的损失及其连带损失。如乙方借故推脱或拒绝甲方提出的维修、更换 等服务请求，甲方有权自行采购同等货物替代或委托第三方维修，实际发生的更换等或维修费用，从应支付给 乙方的任一期货款中扣除，并保留进一步索赔道的权利，乙方不得提出异议。维修或更换物资的质量保证期相应 延长6个月。 4.7 如因乙方产品质量导致工程出现质量问题，由此给甲方造成的一切损失由乙方承担。 管 4.8 其他质量要求：/。 供货时间及地点 5.1 供货方式：□按批次国供货 □一次性供货 5.2 通知方式：供货时间及数量以甲方书面通知为准，甲方可以选择通过电子邮件、微信、QQ等方式将物资采购 订单发送至乙方。紧急情况下，甲方可口头通知乙方发货，手续后补，乙方应予以确认。 中 5.3 供货地点：乙方负责送货至施工现场，卸至甲方指定的卸货地点【高新LIVE（咸阳高新区租赁住房）建设项 目】。乙方不得雇佣甲方在班人员及设备装卸货物。运输、装卸过程中发生的安全事故责任，乙方自行承担。 5.4 根据工程项目施工需要，甲方对所采购物资的数量和送货时间如有变更，应及时书面通知乙方，乙方按变更 后的数量和送货时间供货，货物单价不因货物数量和送货时间的变更而变化。 5.5 乙方应确保已经知悉货物运输的交通状况、交货卸车环境以及政府的交通管制政策措施，不得以此等理由要 求增加费用、减免责任、提出索赔、要求延长或变更供货期限。 交货与验收 6.1交货 6.1.1 除另有规定和协议要求外，乙方提供的全部货物须采用国家、企业、行业标准要求包装，具有足够的强度 及安全起吊标识，保证货物能够经受多次搬运、装卸、长途及短途运输的要求，并采取良好的防潮、防震、防 腐蚀、防爆及防止其它损坏的必要保措施。包装物的回收按以下第【 2】项方式执行：（1）不回收；（2）包装 物由乙方在交货时回收；（3）其它方式：【 /】。 6.1.2 装箱单应注明货物的名称、规格、型号、数量、质量、生产商、发货地、供货人、收货人、交货地、承运 人等，并在显著位置标明装卸警示标志。 6.1.3 乙方运抵甲方指定现场的物资，交货单据上应详细列明当次供应物资的名称、品牌、产地、生产厂家、规 格型号、计量单位、数量。 6.1.4 乙方应向甲方提交本合同标的物的技术文件，包括材质报告（物资质量检验报告）和出厂检验报告（合格 证），以及按照工程竣工验收规定及甲方要求，提供所有相关符合要求的资料。 6.1.5 乙方在首次供货前需提供样品，乙方须在样品和样品资料上加盖单位公章，样品经双方指定人员签字确认 后予以封存，在提交文件上注明与合同文件约定不同之处。 6.2.1 乙方须随货提供载有数量、规格等内容的送货单，否则，甲方有权对本批次货物不予验收确认，由此导致 的违约责任由乙方承担。乙方送货到交货地点后，甲方指定验收人员对产品的规格、尺寸偏差、外观、数量及 质量证明资料等进行查验。若产品的以上各项符合合同约定，则双方人员共同在收领单上签字确认。 6.2.2 甲乙双方在交货现场以 【 点数】方式进行数量验收。乙方应对在甲方工地网现场的验收数据进行确认。 6.2.3 进行数量验收的同时，甲方可以按照封存样品标准进行尺寸、外观质量验收，尺寸和外观质量符合要求方 可卸车，否则不得卸车。 务 6.2.4 外观质量符合要求的， 甲方可打开包装进行质量、性能检验或及时按规定取样送本工程所在地具有相应检 测资质的专业机构或单位进行检测。抽检未发现不合格产品不视为乙方供应产品全部合格，甲方有权随时将乙 方所供货物送到有检测资质的第三方进行检测。如检测合格，检测费用由甲方承担；如检测不合格，甲方可全 部退货，检测费用由乙方承担，并承担由此给甲方造成的一切损失。 商 6.2.5 甲方及工程监理（业主）的收货验收仅作为感观合格的依据，不能免除乙方对货物品牌真实性、内在质量 及使用功能所负的责任。如甲方、本工程建设单位或监理单位提出异议，乙方需参照有关标准规范，结合现场 情况解决。 道 6.2.6 若发现不合格产品，乙方必须及时（接到甲方通知后【 3】小时内），从甲方项目现场运走不合格品，甲方 不负有保管义务，不对不合格产品的损毁灭失承担人和责任，若超过【 12】小时乙方仍未运走的，甲方收取场 地租赁费（根据货物合理确定）【 1.0】万元/天，且不合格品的储存、装卸、运输等所有相关费用及风险由乙方 承担。 管 6.2.7 如因乙方产品问题造成甲方工期、质量、劳务等损失，全部责任均由乙方承担。乙方对甲方所提出的质量 问题有不同意见的，双方可送至双方共同选定的具有法定资质的检测机构检测，所产生的费用及责任由责任方 承担。 国 6.2.8 本合同的标的物所有权自【卸货完毕且经甲方验收合格】起转移。 结算方式及时间 中 7.1 过程结算：甲乙双方按以下第【 1】条约定的时间办理过程结算。 （1）每月20日结算（遇节假日顺延），每季度最后一个月的25日后支付当期货款额的70%（遇节假日顺延，乙 方提供与结算等额增值税专用发票），供货完毕，验收合格，材料相关资料（包括不限于合格证、质检报告等） 移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%，余款3%（不计息）待质保期满无质量问题后 无息付清。（质保期为供货完毕且验收合格后2年）（支付工程款时均应扣除根据采购合同应予扣除的其它金额。 ）； （2）按节点结算，具体结算节点为：【 】。 7.2 最终结算：全部供货完毕后【 6个月后】日内，乙方应向甲方提供完整的结算资料，甲方在收到完整的结算 资料后【 5 】日内进行审核。 7.3 结算依据：包括但不限于物资采购与供应合同、乙方合法等额有效增值税发票（含税务机关代开）、产品合 格报告、项目授权人员验收单、送货单等有效材料。 7.4 乙方未按照约定的期限和甲方要求提供结算资料，或未委派专人与甲方办理结算，或提供的结算资料不齐全、 提供虚假资料的，经甲方催告后10个工作日内，乙方仍未按要求提供结算资料的，甲方有权不予办理结算并暂停 支付材料款，同时甲方可根据本合同、现有结算资料及乙方实际履约情况单方办理结算，确定结算价格，结算 对甲乙双方具有法律约束力。 支付 支付/√不支付预付款 8.1.1 预付款金额（或占合同价款的比例）：【 /】。 8.1.2 预付款的支付时间：【 /】，在乙方提交等额银行保函及增值税专用发票后，甲方向乙方支付预付款。 8.1.3 扣回预付款的时间、比例：【 /】。 8.1.4 乙方提交的银行保函有效期至预付款抵扣完为止，若预付款保函到期日前，预付款无法抵扣完毕，则乙方 应于预付款保函到期日前不少于10日及时办理保函延期，否则甲方有权暂停支付未抵扣完部分的货款。 网 / 8.2.1 货款支付，按以下第【 3】条约定的时间和比例支付。 务 （1）月度付款：甲方在次月的25日支付上月月度结算货款的【 / 】%。双方办理完毕最终结算后【 / 】（条款说 明：建议不超过60日，如超过60日，应当按照行业规范、交易习惯合理约定付款期限并及时支付款项）个日历天 内付至总结算货款（且不超含税合同价款）的【 / 】%。余款【 /】%作为质保金，在质保期届满后28日内付清； 或由乙方提供等同余款金额的质保保函（仅接受金融机构出具的无条件见索即付保函，质保保函格式以开函金 融机构标准格式为准），则双方办理完毕最终结算后【 /商】（条款说明：建议不超过60日，如超过60日，应当按 照行业规范、交易习惯合理约定付款期限并及时支付款项）个日历天内付清。 （2）节点付款：按节点支付（条款说明：此处需具体罗列每个付款节点及各节点对应的付款比例，节点结算完 成后约定支付期限应在60日内，如超过60日，道应当按照行业规范、交易习惯合理约定付款期限并及时支付款项）， 余款【 /】作为质保金，在质保期满后28日内付清，或由乙方提供等同余款金额的质保保函（仅接受金融机构出 具的无条件见索即付保函，质保保函格式以开函金融机构标准格式为准），则在最后一个付款节点付清。每次 付款前乙方应提供结算值【100%】的发票，否则甲方可拒绝付款。 管 （3）其他支付方式【每月20日结算（遇节假日顺延），每季度最后一个月的25日后支付当期货款额的70%（遇 节假日顺延，乙方提供与结算等额增值税专用发票），供货完毕，验收合格，材料相关资料（包括不限于合格 证、质检报告等）移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%，余款3%（不计息）待质保 期满无质量问题后无息付清。（质保期为供货完毕且验收合格后2年）（支付工程款时均应扣除根据采购合同应 予扣除的其它金额。）国】 （4）甲方依合同约定确认的进度款仅为中期付款依据，不作为竣工结算的依据，且不视为对因变更调整的合同 价款、索赔的价款或费用以及其他约定的追加合同价款的确认。 中 8.2.2 甲乙双方协商一致同意本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保理、商业承兑汇票、 国内信用证、应收账款电子凭证、抵房抵款及其他】常规支付方式的付款方式。付款过程中产生的贴息费用及 手续费由【乙方】承担。乙方委托专职收款人办理收付款业务，收款人必须取得授权 8.3 乙方指定以下帐户为收款帐户，甲方所有款项均需通过该帐户支付。如乙方变更收款帐户，应提前十五天以 上书面通知甲方，否则造成资金的损失由乙方自行承担，与甲方无关。 账户名：【 】 开户行：【 】 账 号：【 】 发票 9.1 乙方在向甲方请款时，应根据甲方确认的应支付金额开具合法、有效、完整、准确的增值税（请勾选：□专 用□普通）发票，计税方法为【□一般计税方法 □简易计税方法】，双方发票信息如下： 名 称 纳税人身份 □一般纳税人 □小规模纳税人（请勾选） 甲方 纳税人识别号 地 址、电 话 开户行及账号 名 称 纳税人身份 □一般纳税人 □小规模纳税人（请勾选） 网 纳税人识别号 乙方 地 址、电 话 开户行及账号 务 联 行 号 该开户行为乙方在税务局已备案的乙方单位账户。 9.2 任何一方如上述信息发生变更，应提前10日以书面方商式通知另一方。如一方未按本合同规定通知而使另一方 遭受损失的，应予以赔偿。 9.3 每次乙方在甲方付款前必须提供符合国家现行税法规定的合法有效等额增值税发票，甲乙双方一致确认提供 发票为主合同义务而非附随义务，若乙方未按要求提供发票，甲方有权暂停付款。乙方应在开票之日起7天内将 道 发票送达甲方指定人员【 刘磊】，甲方指定人员签收发票的日期为发票的送达日期。 9.4 乙方开具的增值税专用发票应保证信息完整、内容规范，如乙方未提供发票或提供的发票不合规、不及时、 无法认证，甲方有权拒绝付款，且不视为甲方付款逾期，乙方无权要求甲方支付利息、违约金或赔偿损失，也 管 不得以此为由中止履行合同约定的义务。 9.5若乙方由一般纳税人身份变为小规模纳税人身份的，或者计税方法发生变化的，或者政策法规等规范性文件 发生变化的，并导致甲方可抵扣的进项税额减少或被税务机关要求补缴税款的，则减少的进项税额或补缴的税 款应由乙方承担，甲方国有权从将支付的任何一笔款项中扣除。 9.6 增值税税率变化：合同执行过程中如果遇到国家税务政策调整，增值税税率发生变化的，按新的税率执行， 不含税价不变，仅调整增值税税率的原则进行相应调整。 中 若乙方提供的发票不符合要求的，发包人有权拒收增值税发票，并有权暂停支付相应款项，乙方不得以此为由 中止履行合同的义务。如因乙方不能按期提供发票或提供的发票不符合要求而导致付款延期的，由其自行承担 后果，发包人不承担任何责任。 9.8若乙方迟延提供发票的，每日应按暂定合同总价的0.05%向甲方支付违约金，但迟延违约金累计支付不超过90 日；若乙方迟延提供发票超过90日且已跨年的，视为乙方未提供发票，乙方除应支付前述迟延违约金外，还应另 行向甲方支付以下款项： （1）相当于合同暂定总价1%的违约金； （2）甲方因未收到发票所产生的税款损失， 损失金额按以下公式计算：赔偿损失金额=未提供发票对应的增值税税额*（1+增值税附加税率）+未提供发票金额 *甲方企业所得税税率。 9.9乙方保证开具的发票已经依法足额纳税，支付每笔款项前，乙方需提供发票对应税期的增值税纳税申报表和 完税证明。 9.10乙方承诺其提供的发票真实合法，若发包人认证后出现走逃失联、被列为异常纳税人等违规行为，导致发包 人不能认证抵扣或者认证抵扣后被税务机关要求进项转出情形，应在72小时内补开合规发票，否则按以下方法计 算应赔偿发包人损失，应赔偿损失金额=进项转出税额*（1+增值税附率)+不合规发票金额*发包人企业所得税税 率，逾期未赔偿的，甲方有权从结算金额或者履约保证金中扣除。 9.11乙方主张已开具发票的，应提供：①税务系统发票开具记录 ；②采购方签收凭证或者发票邮寄物流凭证。无 法完整提供两项证据的视为未开票。 10.双方责任 10.1 双方现场代表 10.1.1甲方现场代表为【 】，其职务为【 】 ，其授权签署文件的范围为：【签发监管项目的各类文函、工程变更 指令、索赔文件的报出、违约处罚决定文件等】。 10.1.2甲方收货代表：【 】，联系电话【 】。甲方指定收货代表仅有对乙方送货单中货物的数量及乙方提供的单 据是否齐全子以确认的权利，对货物单价、质量、货款以及总结算单没有确认的权利。 10.1.3乙方应将物资按合同约定时间运至甲方指定地点，并经甲方指定收货代表和甲方工程项目所属其他1人及以 上在甲方指定的收领单上签字验收确认后有效。 网 10.1.4 甲方未经授权的任何人员和项目印章均无权从事下列行为：【（1）签订本合同的补充协议或签署其他合 同类文件，包括但不限于采购合同、分包合同、租赁合同；（2）签署任何借贷、担保性质的文件，包括但不限 于借条、保函、保证书、承诺书；（3）签署代他人清偿债务的文件，签署任何放弃债权的文件；（4）签署任何 对总承包合同进行修改和补充的文件;（5）收取现金及任何款项；（6）签署合同价款的变更、结算及支付确认 务 文件；（7）签署任何劳动关系确认文件、工资发放承诺文件。】 10.1.5 甲方授权人员的职权/职责范围、授权签署文件范围均不可转授权，任何形式的转授权、代签行为，甲方均 不予认可且不承担任何法律责任。 商 10.1.6 乙方确认已完全明白和理解甲方对甲方人员及项目印章的上述授权范围，超出甲方授权范围的行为属于无 权代理行为，对甲方无效，甲方不承担任何法律责任。乙方应谨慎审查相关文件的签署主体资格和权限，对于 无权代理人签署的相关文件，乙方应及时与甲方核实。 道 10.1.7 乙方现场代表为【 】，其职务为【 】，其授权范围为：【全面代表乙方履行本合同，并有权代表乙方签署、 确认履约过程中形成的工程变更、价款确认、经济索赔、违约处罚决定及物资丢失损坏赔偿文件；签署确权文 件及结算书；签收甲方发出的各类文函、工程变更及其他文件等。】 管 10.1.8 双方更换各自代表时，应及时书面通知对方，以确保物资顺利交接。 10.1.9 甲方禁止项目部及任何人员以甲方、甲方分公司、甲方项目部的名义对外借款或者支取任何款项，如乙方 或乙方有关人员以任何形式将款项出借或支付或返还给甲方项目部及任何人员，则不论该等款项是否实际用于 甲方工程，均与甲方无国关，该行为均属于乙方与相关人员个人之间的经济关系，乙方无权向甲方主张任何权利。 10.1.10 未经甲方书面授权不得擅自与建设方及有关部门发生工作上的联系，严禁在对外任何事务中签署甲方单 位名称或带有甲方简称中任何“【中国建筑】”“【中建】”“【中建XX局】”“【XX局】”等字样的落款， 每发现一次中乙方承担2万元的违约金并赔偿所有直接或间接损失。 10.2卫生、环境与安全保护 10.2.1 甲乙双方须贯彻执行国家、地方政府相关部门发布的有关卫生法律、法规，以及甲方发布的规章制度，积 极配合政府部门的检查，对于提出的要求按所属责任立刻整改，确保瘟疫和传染疾病防控的管理落实到位。 10.2.2 乙方保证在运输和卸货过程中应采取相应的环保措施，符合国家环保要求。车辆在进入项目现场要保证不 沾泥土和脏物，车辆出入项目现场必须在项目大门内现场洗车。乙方在卸货过程中保证噪声不超过以下标准 （白天小于或等于【 】dB、夜间小于或等于【 】dB）。乙方保证乙方人员以及车辆进入本工地现场，应遵守现 场的一切卫生环保、文明施工的规定，因违反环保要求所造成的一切罚款由乙方承担。 10.2.3 甲乙双方必须贯彻执行国家和政府、行业主管部门颁布实施的有关安全生产的法律、法规及有关规定。乙 方车辆及人员进出工地现场时必须接受甲方安全检查。乙方因供货造成安全生产责任事故的，责任由乙方承担。 乙方必须对自身出入工地现场的人员进行安全交底，并为其配备安全防护用品，因乙方原因造成的各种人员伤 害及经济损失由乙方自行承担，并赔偿甲方及其它方因此造成的一切损失。 10.3 售后服务 10.3.1 如所供货物为专业性较高的产品，乙方应免费为甲方或工程业主提供操作及维修人员的培训服务，培训内 容应包括：基本原理、操作使用、维修保养等。 10.3.2 对于工程中的剩余或未使用到的货物在不严重影响外观、质量和功能的情况下甲方有权退货，退货原则上 以合同约定的含税单价为准，确因商品特殊的（比如定制等），价格由双方协商，协商不一致的，按照附件1 《计划采购与供应物资清单》中的含税单价（考虑甲方已支付费用、乙方承担运费等情况下，原则上不低于【 】%）【 】%退货，退货数量以实际数量为准。 不可抗力 11.1 不可抗力是指合同当事人在签订合同时不可预见，在合同履行过程中不可避免且不能克服的自然灾害和社会 性突发事件，包括地震、海啸、瘟疫、骚乱、戒严、暴动、战争等情形。 11.2 不可抗力事件发生后，乙方应立即通知甲方现场代表并迅速采取措施，尽量减少损失，并在24小时内向甲方 通报受害情况，提供必要证明。不可抗力持续发生，乙方应每日报告一次受害情况，直到不可抗力结束。甲方 应对受害处理提供必要的条件，并负责处理工作的组织、指挥。不可抗力发生后网，乙方未采取有效措施控制灾 害而发生的损失由乙方承担。 11.3 不可抗力引起的后果，由甲乙双方应各自承担其人员伤亡及财产损失，履行合同的期限相应延长。 务 不可抗力发生后，双方均应采取措施尽量避免和减少损失的扩大，任何一方没有采取有效措施导致损失扩大的， 应对扩大的损失承担责任。 因一方迟延履行合同义务，在迟延履行期间遭遇不可抗力的，不能免除迟延履行方的违约责任。 商 11.4 因单次不可抗力导致合同无法履行连续超过【30】天或累计超过【60】天的，甲方有权解除合同。合同解除 后，双方应就合同履行情况及结算与付款等善后事宜达成补充协议。 权利瑕疵 道 12.1 涉及到知识产权（专利权）标记的产品，乙方应提供知识产权（或专利权）及其权属的有效证明材料。乙方 承诺其提供的物资不侵犯他人的知识产权（或专利权），若乙方提供物资侵犯他人知识产权（或专利权）导致 他人向甲方索赔的，乙方承担由此给甲方造成的一切损失，包括但不限于甲方处理此纠纷发生的律师费、诉讼 管 费、仲裁费、差旅费等一切损失。此外，乙方应向甲方支付合同价款【5】%的违约金。甲方针对上述一切损失 有权从乙方结算货款中扣除或依法追索。 12.2 乙方所供物资应不存在任何权属纠纷及抵押、查封等权利限制情形，如乙方所供物资存在权属纠纷或任何权 利限制情形导致甲方遭国受损失，乙方应赔偿甲方全部损失。 保密 13.1 除法律规定或合同另有约定外，未经乙方同意，甲方不得将乙方提供的技术秘密及声明需要保密的资料信息 中 等商业秘密泄露给第三方。 13.2 除法律规定或合同条款另有约定外，未经甲方书面同意，乙方不得将甲方提供的图纸、文件以及声明需要保 密的资料信息等商业秘密泄露给第三方。 13.3 任何一方违反上述约定，应负责赔偿守约方因此造成的一切损失。 违约与赔偿14.1甲方应按照合同约定及时向乙方支付合同价款，若因甲方资金不到位，乙方同意给予甲方【 30 】 日的宽限期，宽限期内不视为甲方违约。超过宽限期仍未支付的，乙方可向甲方主张自宽限期结束后的违约金； 违约金以逾期支付的价款为基数，自宽限期结束之日起至甲方支付逾期价款之日止，按照中国人民银行同期活 期存款利率向乙方计付，向乙方计付，逾期支付违约金的上限为逾期支付金额的【 / 】%（不超过3%）。在我方 支付逾期付款利息后，分供商不可就此向我方再主张逾期付款的违约责任。（条款说明：乙方为中小企业时， 甲方前述条款支付期限+本条宽限期整体不得超过60日）。14.2 除本合同中规定的不可抗力外，其他不论任何原 因，乙方若不能按约定期限足额足量送至甲方指定现场存货地点，甲方向乙方收取逾期运达物资货款（含增值 税）每日【3】％的违约金，自逾期之日起计算至乙方实际送达之日止，延迟或供货不足超过【3】日时，甲方有 权单方面终止合同。14.3 未经甲方书面同意自行停止供应本合同约定的货物，均视为乙方违约，乙方除承担因此 给甲方造成的一切损失外，乙方另支付合同价款的【5】%作为违约金。 14.4若乙方提供的货物为非合同约定的厂家或品牌的产品，或提供的是假冒他人品牌的产品，甲方有权立即终止 合同，乙方必须支付合同价款【2】倍的违约金给甲方，如乙方所供产品已安装至工程项目，则乙方除承担违约 金外，还必须承担拆除、工程维修、工作面清理和重新安装产生的所有费用等，如违约金不足以弥补因此给甲 方造成的所有损失，包括一切直接损失和间接损失，则超出部分，甲方有权向乙方追偿。乙方提供的货物为合 同约定的厂家及品牌产品，但货物质量不合格或不符合约定的技术要求时，可由乙方负责更换质量合格和符合 约定技术要求的产品，同时承担合同价款【5】%的违约金，并承担因违约造成的各项损失，甲方也可直接要求 解除合同，乙方承担因此给甲方造成的所有损失。乙方提供的合同标的物因品牌、质量等原因导致甲方被项目 业主或总包方罚款或追究违约责任，乙方应向甲方相应承担赔偿责任。 14.5 本合同履行过程中，如果乙方不能按时交货，应在交货前48小时内以书面形式通报甲方，甲方视情况确定是 否同意变更供货时间。如甲方不同意变更供货时间，可自行采购部分或全部货物。甲方在自行采购和接收该违 约部分货物时实际发生的所有额外费用及因此给甲方造成的损失，从甲方应支付给乙方的任一期货款中扣除， 甲方同时保留进一步索赔的权利。 14.6甲方提出索赔通知后，乙方应在【28】日内答复，如果在【28】日内未答复，视为乙方已接受该索赔，同时 甲方保留进一步要求赔偿的权利。 网 14.7 乙方在进出场时乙方不得私自运送甲方现场物资出场，一经发现，乙方向甲方支付所涉及物资原值【2】倍 的违约金，情节严重的交由司法机关处理。 务 14.8 由于乙方自身原因（如：不按约定开立银行账户、未及时提交报量资料或不按合同配合甲方进行款项支付 等），导致货款或工程款延期支付，甲方不承担延期付款利息及违约金，乙方不得因此停止供货；乙方擅自停 供的视为乙方违约，乙方承担因此给甲方造成的所有责任及损失。 14.9 如果出现合同为可调价合同，甲乙双方调价达不成一致商情形；或者出现合同为不可调价合同，乙方提出调价， 甲乙双方达不成一致情形，则甲方有权选择其他供应商，甲方不承担任何违约责任。 14.10 若乙方因14.5和14.9款原因停止供货，或未完成全部供货、或主张解除合同等不履行合同的情形，乙方剩余 款项的支付不适用本合同8.2条款，甲乙双方应道就剩余款项的支付签订书面补充协议，重新明确支付条款，甲方 不承担任何违约责任。 14.11 其他违约与赔偿要求：【 /】。 管 联络与送达 甲方：收件人【 】，联系电话【 】，电子邮箱【 】，地址【 】。 乙方：收件人【 】，联国系电话【 】，电子邮箱【 】，地址【 】。 15.2 一方通过电子邮箱发送文件的，文件到达对方邮箱即视为送达，送达时间为电子邮件到达对方邮箱地址时间； 一方通过信函邮寄送达的，则信函寄出后的第三个工作日或收件人实际签收日（以先到的时间为准）视为送达； 一方选择直中接送达的，则递交时视为送达。 15.3 邮件邮寄至上述地址被拒收或无人签收，亦视为已经送达，由此增加的费用和（或）延误的期限由拒绝接收 一方承担。 15.4 双方承诺，因本协议的履行或争议解决，上述联系人和联系方式为有效的联系方式，各项通知均应当向上述 联系人、联系方式送达。在诉讼、仲裁中，上述联系人、联系方式亦为有效的送达地址，向上述地址的送达即 为有效送达，即使发生拒收、退信等事件。 上述联系信息发生变更的，变更方应当即时通知对方；在对方收到变更通知之前，对方当事人或者仲裁、司法 机构已经向原联系人、联系方式进行的通知，视为有效通知。 争议解决 16.1 因本合同引起或与之相关的任何争议、纠纷或权利主张，则必须先行向对方发出书面和解申请书，并告知对 方争议、纠纷或权利主张之事实及依据、联系人及联系方式，在对方收到上述通知之日起 3 个月为双方和解期限。 在和解期限内，若双方达成和解协议的，双方的权利义务按照和解协议履行；若未达成和解协议的，任何一方 采用下列第【 】种争议解决方式，并自行承担本方发生的律师费、差旅费、保函费等相关费用∶ （1）向仲裁委员会申请仲裁 周口仲裁委员会（开庭地点：郑州） 郑州仲裁委员会 武汉仲裁委员会 北京仲裁委员会 上海仲裁委员会 中国国际经济贸易仲裁委员会 R成都仲裁委 （2）向【 】人民法院提起诉讼。 网 1.因本合同引起的或与本合同有关的任何争议，如仲裁委员会，则按照其仲裁规则进行仲裁。仲裁裁决是终局的， 对双方均有约束力。 务 2.双方承诺：任何一方向仲裁委员会申请仲裁的，双方均自愿放弃向对方主张仲裁费用和实际发生的其他费用， 包括但不限于鉴定费用、评估费用、审计费用等；双方均自愿放弃向对方主张补偿因办理案件支出的合理费用， 包括但不限于律师费、保全费、差旅费、公证费等。 3.双方约定：仲裁案件无论标的额大小、复杂程度如何，商均适用普通程序，即由三名仲裁员组成仲裁庭审理，以 确保案件公正审理。 4.调解期限：争议应先行和解协商解决，设定3-6个月和解期（可根据情况调整），且和解期限不计入仲裁审理 期限。任何一方若未履行上述和解程序而直接道提请至争议解决机构的，则需要向对方承担签约合同价【10】%的 违约金；如一方出现上述情形，另一方提起反诉或反请求，则提起反诉或反请求的一方不承担违约金。 17.禁止债权转让条款甲乙双方确认，若发生下列任一情形，即视为乙方重大违约，乙方需向甲方支付合同总价 （建议10%） %的违约金，且甲方有权视违约程度单方解除本合同，同时乙方应赔偿甲方因此遭受的全部损失 管 （包括但不限于直接损失、间接损失、维权产生的律师费、诉讼费、保全费等）。具体情形如下： （1）未经甲 方事先书面同意，乙方擅自将其在本合同项下对甲方享有的全部或部分债权进行转让、质押或以其他方式处分 给任何第三方的； （2）因乙方与乙方债权人存在债务纠纷，导致该乙方债权人以甲方为被告或被申请人提起代 位权诉讼、仲裁或采取其他司法/仲裁手段的； （3）未经甲方事先书面同意，乙方以自身名义或委托任何第三 方，就本合同相关事项国对甲方的关联单位（包括但不限于业主单位、建设单位、 发包方）提起代位权诉讼、仲 裁或采取其他司法/仲裁手段的； （4）其他性质同上述条款规定的情形。18.补充条款 /】 中 其他 19.1 本合同采用下列第【 2 】种签订方式： （1）本合同自双方签字并盖章后生效，一式【叁】份，甲方执 【贰】份，乙方执【壹】份，每份具有同等法律 效力。 （2）本合同采用电子签章签署生效。根据《中华人民共和国民法典》、《电子签名法》等相关法律、法规，双 方一致认可在【 】平台（网址：【 】）使用电子印章签署合同为其真实意思表示，且确保在该平台注册时，使 用的企业信息和个人相关信息真实有效，并且自觉遵守国家法律法规和甲方在该平台的合同签约流程。甲乙双 方使用电子签章方式签署的合同，只有通过验证生效的电子原件具有法律效力，未经电子印章服务平台公司提 供书面证明材料的电子合同打印版不能作为法律依据。如因乙方使用不当给甲方造成损失，乙方愿自行承担由 此造成的全部经济损失和法律责任。 19.2未尽事宜经双方协商一致后，可签订补充协议，与本合同具有同等法律效力。 19.3对于因本合同产生的任何争议或投诉，乙方可通过【 】（条款说明：根据各公司情况填写投诉平台或者联系 方式）进行提交。甲方将在收到乙方的投诉后，对乙方的投诉进行初步审查，并尽快与乙方取得联系以进一步 了解详情。因不可抗力或第三方原因导致无法按时处理投诉的情况，甲方将尽快通知乙方，并尽力协调解决问 题。 19.4本合同条款（包括但不���于免责条款、责任限制条款等）均经双方充分协商，双方已就全部条款内容达成一 致意见，不存在单方预先拟定且未予协商的情形。 附件： 附件1：《计划采购与供应物资清单》 附件2：《法人授权委托书》 附件3：《廉政合同书》 （以下无正文） 甲 方：【盖章】 乙 方：【盖章】 网 法定代表人：【签字】 法定代表人：【签字】 委托代理人：【签字】 委托代理人：【签字】 务 地 址：【 】 地 址：【 】 电 话：【 】 电 话：【 】 商 电子信箱：【 】 电子信箱：【 】 附件1 道 计划采购与供应物资清单 人民币：元 管 计量 暂定 单价 暂定含税 序号 物资名称 规格型号 品牌/产地 生产厂家 备注 单位 数量 不含税单价 增值税 含税单价 货款金额 价税合计 暂定合同价款人民币大写： 国 以上数量为暂定项目，最终以双方签字确认的采购结算单为准 中 附件2 中国建筑 项目管理表格 表格编号 法人授权委托书 CSCEC-WZ-HN003 （甲方）： 本授权委托书声明：本的法定代表人，授权委托我公司的 为我公司代理人，代表我公司与贵公司工程对涉及投标报价，物资合同、补充协议的签订、履行，物资结算、收款等业务进行签字确认，由在上述授权范围签字的所有文书，我公 司均予认可，由此产生的一切经济法律责任由我公司承担。 代理期限为前述代理人对上述业务发生第一次签字确认之日起至本工程结算完成之日止。代理人无转委托权。 特此委托。 代理人（签字/按指纹）：身份证号码： （供应商）法定代表人签字： （供应商盖章）： 日期： 附件3 廉政合同书 甲方：【 】 乙方：【 】 为确保甲方对业主的承诺，高效、优质共同完成施工任务，争创优质工程，保证合同双方能够高效廉洁地履行， 维护双方合法权益，经双方协商，特订立如下廉政合同书。 第一条 甲乙双方的权利和义务 1.甲乙双方应本着“公开、公平、公正、诚信、透明”的原则开展工作，自觉遵守党和国家、工程项目所在省、 市、区工程建设有关法律法规以及廉政建设的各项规定。 2.甲乙双方应建立健全廉政教育制度，开展经常性教育活动，积极宣贯“合规诚信 自律清正”的廉洁从业核心理 念，加强廉政教育。 3.加强相互监督，发现对方有违反廉政合同书规定的行为，应及时提醒对方纠正。 第二条 甲方的责任 网 甲方工作人员不得有以下行为： （1）为乙方多结算工程量、多签证、多付工程款等，并向乙方索要或接受贿赂、回扣、礼金、有价证券（卡）、 务 贵重物品和好处费等; （2）在乙方报销任何应由甲方或个人支付的费用; （3）参加有可能影响公正执行公务的超标准宴请和娱乐商、健身等活动; （4）接受乙方提供的通讯工具、交通工具和高档办公用品; （5）要求、暗示或接受乙方为个人住房装修道、婚丧嫁娶、配偶子女工作的安排以及出国（境）、旅游提供的方 便; （6）向乙方介绍或推荐配偶、子女、亲属参与的工程施工合同有关的设备、材料、工程分包、劳务等; 管 （7）向乙方推荐分包单位或要求乙方购买合同规定以外的材料、机具设备等; （8）因乙方拒绝本人的不合理要求，而故意刁难乙方。 第三条 乙方的责任 国 乙方应当通过正常途径开展业务，不得有以下行为： （1）为多结算工程量、多签证、多收工程款等，向甲方及其管理人员行贿或馈赠礼金、有价证券（卡）、贵重 中 礼品; （2）为甲方及其工作人员报销应由甲方单位或个人支付的任何费用; （3）安排甲方人员参加超标准宴请、娱乐活动及带有黄、赌性质的娱乐活动; （4）为甲方人员购置或提供通讯工具、交通工具和高档办公用品等; （5）乙方向甲方工作人员及其家属或者亲友介绍从事与甲乙双方工程有关的工程分包及材料设备、周转工具的 供应、租赁等经营活动。 第四条 违约责任 1.如甲方工作人员有违反本廉政合同书的行为，由甲方纪委查处，追究相应的党纪、政务责任，涉嫌犯罪的，移 交司法机关追究刑事责任；对实名举报的，甲方要立即调查，并采取有效措施保障乙方的合法权益，防止报复 事件发生。 2.如乙方单位或个人有违反本廉政合同书的行为，甲方视情节对乙方处以合同额0.5%—1%的罚款，情节较重并给 甲方造成损失的，乙方另需赔偿甲方直接经济损失，并取消乙方工程分包资格。 第五条 甲方接受举报的途径 1. 受理电话：【 】 2. 受理地址：【 】 3. 受理部门：【 】 4. 受理邮箱：【 】 第六条 本廉政合同书作为采购合同的一部分，具有同等法律效力，本协议与采购合同同日生效，至甲乙双方工 程合同履约完止。 甲方： 乙方： 网 法定代表人： 法定代表人： 授权委托人： 授权委托人： 务 签订时间： 年 月 日 请查看报价网 商 址：https://xy.yzw.cn/sj/bid-detail?tenderId=&amp;source=3&amp;tenderCode=cscec2026081900001246027&amp;tenantId=cscec 信息来源:https://www.chinapipe.net/project/d3076919.html cqdingjiu 2026.08.21 10:06:42 道 管 国 中</t>
@@ -664,7 +712,11 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -697,16 +749,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>忠县</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>忠县</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(三标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>本项目工程总投资金额：约3140万元；本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>高标准农田建设工程</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(三标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 网 2.项目概况与招标范围 务 2.1 建设地点： 忠县花桥镇、新立镇、石宝镇、兴峰乡。 商 2.2 项目概况与建设规模①忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）：田块整治 工程：旱地区域撂荒地整治278.95亩；灌溉与排水工程：新建200m蓄水池6座、PE75管道967m、新建1.2*1.2m箱 涵16m、新建2*2m箱涵8m；田间道路工程：新建2.5m混凝土生产路15114m、改建2.5m混凝土生产路1078m、新 建2.5m泥结碎石生产路910m、改建2.5m泥结碎道石生产路279m、新建3.0m混凝土生产路601m、改建3.5m混凝土机 耕路4587m；地力提升工程：施有机肥278.95亩；其他工程：工号牌124块。 管 ②忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）：田块整治工程：旱地区域撂荒地 整治195.54亩；灌溉与排水工程：新建100m蓄水池4座、新建200m蓄水池6座、PE75管道5258m、PE90管 道1375m、PE110管道2156m、改建0.5*0.6m混凝土排水沟740m、改建0.6*0.8m混凝土排水沟109m、改建0.8*1.0m混 凝土排水沟296m、改建1*1.5m混凝土排水沟262m、新建3*2m盖板涵1座；田间道路工程：新建2.5m混凝土生产 路11359m、改建2.5m混国凝土生产路3430m、新建2.5m泥结碎石生产路1834m、新建3.0m混凝土生产路350m；农田 防护工程：新建1.0m高挡土墙39m；地力提升工程：施有机肥195.54亩；其他工程：工号牌142块。 中 2.3 本项目工程总投资金额：约3140万元； 本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）施工图所示范围的所 有内容为准，详见发布的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分： 标段划分情况、建设规模及标段合同估算金额等内容如下： 合同估算金额 序号 项目名称 建设地点 （万元） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二 1 花桥镇、新立镇 1022 标段） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三 2 石宝镇、兴峰乡 735 标段） 网 本项目共分为2个标段，每家投标单位仅对2个标段中的任意1个标段进行投标，若同时参与2个及以上标段投标的， 其投标文件无效。 务 2.7 其他： / 商 3.政府采购工程 道 3.1 是否属于政府采购工程：是 □否 管 3.2 是否专门面向中小企业预留：是 国 专门面向中小企业预留的实施方式： 中 方式一：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（忠县）下载招标文件、工 程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字 证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责 任自负。 5.2投标人可在重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要网提问”栏提出疑问，提问时间从 本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-10-12 09:30，投标人应当在投标截止时间前，通过互 务 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 商 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 道 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 管 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 国 开户银行: 开户银行: 账 号: 账 号: 中 监督部门: 忠县发展和改革委员会 电 话: 023-54456078 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段） 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005499 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421353 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891814619 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082001038 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00385 信息来源:https://www.chinapipe.net/project/d3076880.html cqdingjiu 2026.08.21 10:06:45</t>
@@ -718,9 +786,13 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>重庆, 高标准农田建设工程, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -735,7 +807,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -753,16 +825,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)，包括田块整治、灌溉与排水、田间道路、地力提升和其他工程。</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>本项目总投资金额约3140万元，其中二标段1022万元，三标段735万元。</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>主要产品包括混凝土生产路、泥结碎石生产路、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点： 忠县花桥镇、新立镇、石宝镇、兴峰乡。 2.2 项目概况与建设规模①忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）：田块整治 务 工程：旱地区域撂荒地整治278.95亩；灌溉与排水工程：新建200m蓄水池6座、PE75管道967m、新建1.2*1.2m箱 涵16m、新建2*2m箱涵8m；田间道路工程：新建2.5m混凝土生产路15114m、改建2.5m混凝土生产路1078m、新 建2.5m泥结碎石生产路910m、改建2.5m泥结碎石生产路279m、新建3.0m混凝土生产路601m、改建3.5m混凝土机 耕路4587m；地力提升工程：施有机肥278.95亩；其他工程：工号牌124块。 商 ②忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）：田块整治工程：旱地区域撂荒地 整治195.54亩；灌溉与排水工程：新建100m蓄水池4座、新建200m蓄水池6座、PE75管道5258m、PE90管 道1375m、PE110管道2156m、改建0.5*0.6m混凝土排水沟740m、改建0.6*0.8m混凝土排水沟109m、改建0.8*1.0m混 凝土排水沟296m、改建1*1.5m混凝土排水沟2道62m、新建3*2m盖板涵1座；田间道路工程：新建2.5m混凝土生产 路11359m、改建2.5m混凝土生产路3430m、新建2.5m泥结碎石生产路1834m、新建3.0m混凝土生产路350m；农田 防护工程：新建1.0m高挡土墙39m；地力提升工程：施有机肥195.54亩；其他工程：工号牌142块。 2.3 本项目工程总投资金额：约3140万元； 管 本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）施工图所示范围的所 有内容为准，详见发布国的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分中： 标段划分情况、建设规模及标段合同估算金额等内容如下： 合同估算金额 序号 项目名称 建设地点 （万元） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二 1 花桥镇、新立镇 1022 标段） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三 2 石宝镇、兴峰乡 735 标段） 本项目共分为2个标段，每家投标单位仅对2个标段中的任意1个标段进行投标，若同时参与2个及以上标段投标的， 其投标文件无效。 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 方式一：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 网 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 .技术成果经济补偿 务 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （忠县）下载招标文件、工程量清单、电子图纸等资料。商参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（忠县）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源 交易监督网、重庆市公共资源交易网（忠县）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数字证 书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的，责任 自负。 道 5.2投标人可在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要提 问”栏提出疑问，提问时间从本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 管 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-10-12 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 国 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 中忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 忠县发展和改革委员会 电 话: 023-54450483 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段） 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421361 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00386 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005423 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891832091 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082001039 信息来源:https://www.chinapipe.net/project/d3076879.html 网 cqdingjiu 2026.08.21 10:06:45 务 商 道 管 国 中</t>
@@ -776,7 +856,11 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -809,16 +893,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>忠县</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>忠县</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>田块整治工程、灌溉与排水工程、田间道路工程、地力提升工程、其他工程</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>项目总投资金额约3140万元，本次招标项目合同估算金额一标段1167万元</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>高标准农田建设工程</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(一标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）已由 忠县发展和改革委 员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来 自 业主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具 备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 网 务 2.项目概况与招标范围 商 2.1 建设地点： 忠县马灌镇、三汇镇、永丰镇。 道 2.2 项目概况与建设规模：忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）：田块整治 工程：水田整治50.67亩、水田区域撂荒地整治79亩、旱地区域撂荒地整治62.83亩；灌溉与排水工程：新 建200m蓄水池5座、新建500m蓄水池1座、泵站1座；田间道路工程：新建2.5m混凝土生产路12325m、改 建2.5m混凝土生产路8549m、新建2.5m泥结碎石生产路1223m、新建3.0m混凝土生产路576m、改建3.0m混凝土生 管 产路648m、改建3.0m混凝土生产路（拆除原1.5m宽路）266m、改建3.5m混凝土机耕路1662m；地力提升工程：施 有机肥136.48亩；其他工程：公示牌1座、工号牌213块。 国 2.3 本项目工程总投资金额：约3140万元； 中 本次招标项目合同估算金额：一标段1167万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）施工图所示范围的所 有内容为准，详见发布的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 网 方式一：本项目整体面向中小企业。 务 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 商 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 道 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 管 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 国 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 中 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（忠县）下载招标文件、工 程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及CA数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 5.2投标人可在重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从 本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-10 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 网 监督部门: 忠县发展和改革委员会 电 话: 023-54456078 务 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段） 商 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082000104 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005469 道 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421379 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00387 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891884496 管 信息来源:https://www.chinapipe.net/project/d3076876.html cqdingjiu 2026.08.21 10:06:46 国 中</t>
@@ -830,9 +930,13 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>重庆, 高标准农田建设工程, 投资金额, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -865,16 +969,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>永川区</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>永川区</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>农村供水管网巩固提升改造工程</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>供水管网</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>永川区农村供水管网巩固提升改造工程(东部片区)答疑补遗文件 永川区农村供水管网巩固提升改造工程（东部片区） 补遗文件（01） 各潜在投标人： 现将“永川区农村供水管网巩固提升改造工程（东部片区）”招标文件补遗通知如下，本次发布的补遗文件中 的所有内容与招标文件具有同等法律效力，如与招标文件、答疑补遗文件（01）网不一致时，以本补遗文件为准。 请各潜在投标人自行下载本补遗文件，不管下载与否，都视为全部知晓其全部内容。 一、本招标项目招标文件第二章投标人须知前附表第1.4.1项第1条第（3）款中“具备建设行政主管部门颁发的有 效的安全生产许可证，企业主要负责人、拟派项目经理具备相应的由建设行政主管部门颁发的有效的安全生产 务 考核合格证书。”修改为： “（3）具备建设行政主管部门颁发的有效的安全生产许可证，企业主要负责人、拟派项目经理具备相应的由水 行政主管部门颁发的有效的安全生产考核合格证书”。 商 二、本招标项目招标文件第二章投标人须知前附表第1.4.1项中第3条“业绩要求”修改为： “投标人自2023年1月1日起至投标截止日止（以合同工程完工日期或工程竣工日期为准），完成过1个单项合同 输配水管网长度不少于100km的水利工程施工道业绩。 提供：供该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴 定书）的证明材料。若提供的上述业绩证明材料不能体现上述业绩指标的，应补充提供业主证明。 管 注：（1）当上述业绩证明材料中针对同一指标存在不一致时，以合同工程完工证书（或合同工程验收鉴定书或 工程竣工证书副本或竣工验收鉴定书）的证明材料为准。（2）投标人提供的业绩为联合体业绩的，其在该业绩 中的工作分工应与本项目承担的工作一致。” 三、本招标项目招标文国件第二章投标人须知前附表第1.4.1项中第5条中的“5.3项目经理业绩要求”修改为： “投标人拟派的项目经理自2023年1月1日起至投标截止日止（以合同工程完工日期或工程竣工日期为准），完成 过1个单项合同输配水管网长度不少于100km的水利工程施工业绩，并在该业绩中担任项目经理。 中 提供：供该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴 定书）的证明材料。若提供的上述业绩证明材料不能体现上述业绩指标的，应补充提供业主证明。 注：（1）当上述业绩证明材料中针对同一指标存在不一致时，以合同工程完工证书（或合同工程验收鉴定书或 工程竣工证书副本或竣工验收鉴定书）的证明材料为准。（2）投标人提供的业绩为联合体业绩的，其在该业绩 中的工作分工应与本项目承担的工作一致。” 四、本招标项目的投标文件递交的截止时间（投标截止时间）调整为2026年9月4日9时30分（北京时间），开标 时间及投标保证金递交截止时间相应顺延。 招标人：重庆市永川区惠永水务有限公司 招标代理机构：重庆永川政鑫综合能源有限公司 2026年8月20日 信息来源:https://www.chinapipe.net/project/d3076870.html cqdingjiu 2026.08.21 10:06:46</t>
@@ -886,9 +1006,13 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>重庆, 农村供水管网, 巩固提升改造, 东部片区, 管材招标</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -921,16 +1045,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>长寿区</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>长寿区</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>新改建及修复DN300mm-DN1200mm排水管道20.187公里，其中新改建管道15.21公里，修复管道4.977公里，Ⅲ、Ⅳ级结构性及功能性缺陷修复453处。</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>项目业主为重庆市长寿区住房和城乡建设服务中心，建设资金来自财政资金，项目出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DN300mm-DN1200mm排水管道</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>长寿区海棠、石堰、龙河片区污水管网建设项目(二期)招标公告 长寿区海棠、石堰、龙河片区污水管网建设项目（二期）招标公告 1.招标条件 本招标项目长寿区海棠、石堰、龙河片区污水管网建设项目已由重庆市长寿区发展和改革委员会以长改发投 〔2024〕169号文批准建设，项目业主为重庆市长寿区住房和城乡建设服务中心，建设资金来自财政资金，项目 出资比例为100%，招标人为重庆长寿乡村建设集团有限公司。项目已具备招标条件，现对该项目的施工进行公 开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：长寿区海棠镇、龙河镇、新市街道、云台镇。 2.2 项目概况与建设规模：新改建及修复DN300mm-DN1200mm排水管道20.187公里，其中新改建管道15.21公里， 务 修复管道4.977公里，Ⅲ、Ⅳ级结构性及功能性缺陷修复453处。 2.3 本次招标项目合同估算金额：4139.45万元。 2.4 招标范围：详见招标人提供的本工程的施工图图纸、图商说、设计变更以及工程量清单所明确的全部工程内容。 2.5 工期要求：270日历天。 缺陷责任期要求：24个月。 道 3.政府采购工程 3.投标人资格要求 管 3.1 本次招标要求投标人须具备以下条件： 3.1.1 本次招标要求投标人具备的资质条件：建设行政主管部门颁发的有效的市政公用工程施工总承包三级及以 上资质； 国 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 中 3.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需 在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网 导航栏“主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登 记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公 告发布至2026-08-25 15:00:00前。 4.3招标人应于2026-08-28 18:00:00前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交 易网（长寿区）（https://www.cqggzy.com/changshouweb/）发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-14 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源 交易监督网上发布。] 7.联系方式 招 标 人: 重庆长寿乡村建设集团有限公司 代理机构: 中新创达咨询有限公司 地 址: 重庆市长寿区桃源大道3号一号商务楼5-6楼 地 址: 邮 编: 邮 编: 项目负责人: 刘老师 项目负责人: 钟亮 网 电 话: 023-40233279 电 话: 19132912275 传 真: 传 真: 电子邮箱: 电子邮箱务: 开户银行: 开户银行: 账 号: 账 号: 商 监督部门: 重庆市长寿区发展和改革委员会 电 话: 023-40245080 2026年08月20日 长寿区海棠、石堰、龙河片区污水管网建设道项目（二期） 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公 中国农业银行股份有限公司重庆自由贸易 312601010400083780000033561 司 管试验区分行 重庆联合产权交易所集团股份有限公 中国建设银行股份有限公司重庆渝中支行 6232813760003317764 司 重庆联合产权交易所集国团股份有限公 重庆银行股份有限公司七星岗支行 15010202900420146632392 司 信息来源:https://www.chinapipe.net/project/d3076848.html cqdingjiu 20中26.08.21 10:06:46</t>
@@ -944,7 +1084,11 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -977,16 +1121,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>渝万高铁站前1标位于重庆市万州区和忠县境内,起止里程DK14+233.2~D1K47+550.4，正线长度33.01km，中标造价31.73亿元。管区内共有隧道8座/22.36km，斜井2座/1.76km;桥梁15座/8.97km，其中，预制及架设梁301孔，(40+64+40)m和(45+100+45)m连续梁各1联;区间路基22段/1.68km，土石方约67万方，负责DK0+000~DK57+136段小型构件预制。</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>中标造价31.73亿元</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>刺丝滚笼,塑钢模板,泄水管</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部刺丝滚笼、塑钢模板、泄水管询价采购公告 中铁十一局集团有限公司重庆至万州高铁站前 1标项目经理部 刺丝滚笼、塑钢模板、泄水管询价采购公告 询价编号： ZT1105-XJ-2026-590 尊敬的 各潜 在供应商 : 网 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与 中铁十一局集团有限公司重庆至万州高铁站 前 1标项目经理部 ZT1105-XJ-2026-590， 刺丝滚笼、塑钢模板、泄水管 的报价。 一、 项目概况 务 渝万高铁站前 1标位于重庆市万州区和忠县境内,起止里程DK14+233.2~ D1K47+550.4，正线长度 33.01km，中标造 价 31.73 亿元。管区内共有隧道8座/22.36km，斜井2座/1.76km;桥梁15座/8.97km，其中，预制及架设梁 301 孔，(40+64+40)m和(45+100+45)m连续梁各1联;区间路基22段/1.68km，土石方约67万方，负 责DK0+000~DK57+136段小型构件预制。合同工期54.7月商，开工日期为2022年11月01日，竣工日期为2027 年04 月30日。 二、 询价内容 道 本次 计划对刺丝滚笼、塑钢模板、泄水管 进行询价，询价内容如下： 询价物资一览表 管 计 序 物资 量 包件号 规格型号 数量 备注 号 名称 单 位 国 刺丝 1 GL-01 2.5mm 6m0.5m 米 6500 半径 ≥225mm，包括刀片刺绳、挂丝、连接卡、支架 滚笼 防护 中 栅栏 2 GL-01 用立 50X30X765X2.5mm 套 500 含抱箍、螺栓等配件 柱支 架 平 塑钢 3 MB-01 350X300mm 方 19.2 400*400,1个挡水沿，配固定手柄 模板 米 平 塑钢 4 MB-01 350X300mm 方 19.2 400*400,2个挡水沿，配固定手柄 模板 米 平 塑钢 5 MB-01 300X300mm 方 75.6 2个挡水沿，配固定手柄 模板 米 平 塑钢 6 MB-01 300X300mm 方 75.6 1个挡水沿，配固定手柄 模板 米 7 SSG-01 管篦 PVC250X200x10mm 个 220 材质硬聚氯乙烯 PVC，详见附图 PVC 8 SSG-01 泄水 135X38mm 块 220 材质硬聚氯乙烯 PVC，详见附图 管盖 U型 9 SSG-01 125mm 个 900 详见附图 管卡 UPV 材质硬聚氯乙烯 PVC，两端接头采用阴阳螺纹连接详见 10 SSG-01 C排 125X8mm螺纹 米 2870 附图 水管 UPV 11 SSG-01 C弯 DN125X8mm90° 个 240 材质硬聚氯乙烯 PVC，详见附图 管 UPV 网 125X125X110mm弹性密 12 SSG-01 C三 个 120 材质硬聚氯乙烯 PVC，详见附图 封圈异径斜三通 通 无压 埋地 务 排污 排水 用硬 13 SSG-01 DN125 个 150 材质硬聚氯乙烯 PVC，详见附图 聚氯 商 乙烯 管 T 型接 头 道 合 计 管 说明： 1. 表中数量为计划数量，实际 采购 过程中可能有所调整，最终结算按照实际 采购 数量结算。 2.收货地点：中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部 三、 技术质量 及报价国 要求 1. 此次 询价物资 各项技术性能要 符合 甲方 的要求，质量满足甲方项目部正常使用的要求，保证 产品 的质量合 格。 具体要求或图纸见询价文件技术规格书。 。 中 2 .报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、 结算及付款方式 每个月 15 日为双方价款结算日期（即上月 16 日至当月 15 日内），结算前双方要在对帐确认单上签字认可，乙 方按双方确认的金额开具增值税专用发票，并自发票开具之日起 7日内传递给甲方。甲乙双方在增值税专用发票 传递过程中必须留取相应的交接签证手续。自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发 票认证完成之日起第6个月，支付至本次结算金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内， 累计支付总额不超结算总金额的75%，剩余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理 末次结算后第二年，支付金额应大于等于尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总 额的15%；办理末次结算后第四年，全部付清）。 五、 报价 人资格要求 1.营业范围要求：在中华人民共和国境内依法注册，具有询价物资生产或供应经验的生产商或代理商，并且具有 合法有效的营业执照。 2.生产能力要求： 生产商须具备 询价 物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定 。 代理商需出具制造厂出具签字盖章的授权函。 3.财务能力要求：报价人为增值税一般纳税人或小规模纳税人，有依法纳税的良好记录。 4.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8月至今） 国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；每种物资全指标技术参数性能满足 国家和行业最新标准的各项规定。 5.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年8月至今）企业或企业法定代表人有人民法院生效判决、裁定 认定的行贿犯罪记录的。④ 对纳入国家铁路局“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接受 通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合作 方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 网 6.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 务 ★7 .下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 六、 报价人需要提供的资料 1. 营业执照复印件、 法人身份证复印件、 开户许可证、商授权委托书 、 报价表 和报价人资格要求中所需的证明资 料， 所有资料需加盖公司鲜章。 2. 产品质量检测报告等质量证明文件。 道 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、 询价 报名截止 时间 管 有意参加本次询价采购的报价人 须在铁建云链平台 （ https:// www.crccep. cn） 完成供应商注册，并 于 202 6 年 8 月 20 日 9时 00 分 至 202 6 年 8 月 24 日 9时 00 分在网上 完成报名工作。 八、 询价 截止 时间 国 凡有意参加本次询价采购的报价人，请于 202 6 年 8 月 24 日 14 时 00分 前 提交报价。截止时间前未完成 报价 文 件传输的，视为放弃 报价 。 供应商报价必须严格按照《 报价表 》格式进行报价。 中 九、 联系方式 采购 组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村 71号 联系人：胡先生 联系电话： 13983336494 （提供平台服务支持） 采购人名称：中铁十一局集团有限公司重庆至万州高铁站前 1标项目经理部 地址： 重庆市万州区双河口街道檬兴路万州现代综合物流中心信息交易大厅（中铁十一局） 联系人： 唐大伟 联系电话： 18323391938（提供采购服务支持、保证金退还） 中铁十一局集团有限公司物资设备集中采购管理中心 第五分中心 2026 年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3076805.html cqdingjiu 2026.08.21 10:06:47 网 务 商 道 管 国 中</t>
@@ -998,9 +1158,13 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>重庆, 万州, 高铁站前, 刺丝滚笼, 塑钢模板, 泄水管, 询价采购</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1033,16 +1197,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>垫江县</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>垫江县</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目，主要内容包括河堤护岸岸线整治2100m；产业路扩宽及油化改造775.3m；新建污水管网450m，化粪池2座；产业基地水肥一体化改造45亩等。</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>项目总投资金额为642.89万元，本次招标项目合同估算金额约为5014864.52元。</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>水利水电工程施工</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告 1.招标条件 本招标项目 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目 已由 垫江县发展和 改革委员会 以 垫江发改委发〔2026〕20号 文批准建设，项目业主为 垫江县太平镇人民政府，建设资金来 自 大中型后扶资金及自筹资金 ，项目出资比例为 100% ，招标人为垫江县太平镇人民政府。项目已具备招 标条件，现对本项目施工进行公开招标，评标办法采用经评审的最低投标价法。网 务 2.项目概况与招标范围 商 2.1 建设地点：垫江县太平镇桂花村 道 2.2 项目概况与建设规模：主要为河堤护岸岸线整治2100m；产业路扩宽及油化改造775.3m；新建污水管网450m， 化粪池2座；产业基地水肥一体化改造45亩等。 管 2.3 本项目工程总投资金额：642.89万元 国 本次招标项目合同估算金额：约5014864.52元 中 2.4 招标范围：本工程施工图纸所含全部的施工内容，具体以招标人发布的工程量清单为准。 2.5 工期要求：工期为360日历天 ，缺陷责任期为24个月。 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：□是 否，因专门面向中小企业预留无法确保充分供应、充分竞争，根据 《政府采购促进中小企业发展管理办法》第六条第(三)“按本办法规定预留采购份额无法确保充分供应、充分竞 争，或者存在可能影响政府采购目标实现的情形”的规定，本项目不专门面向中小企业预留。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 网 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的水利水电工程施工总承包三级 务 及以上资质。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相商应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 道 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 管 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com国/dianjiangweb/)、重庆市公共资源交易监督网下载招标文件、工程量清单、电子图纸等资 料。参与投标的投标人需在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共 资源交易监督网完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交易监督网导航栏“主体信息”页面中“市场主体信息 登记”、“中CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流 程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交易监督 网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-24 17:00:00前。 5.3招标人应于2026-08-28 17:00:00前在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重 庆市公共资源交易监督网发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-28 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交 易监督网发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 垫江县太平镇人民政府 代理机构: 重庆皓辰建设工程咨询有限公司 重庆市渝北区金开大道1228号大雅金开国际1 地 址: 重庆市垫江县太平镇牡丹路191号 地 址: 栋9-2 邮 编: 邮 编: 项目负责人: 余老师 项目负责人: 雷雨得 电 话: 13996889839 电 话: 023-86018770 18580880860 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 垫江县发展和改革委员会 电 话: 023-74517161 网 2026年08月19日 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目 务 户名 开户行 投标保证金账号 垫江县公共资源交易中心 中国农业银行重庆垫江支行 316301010400077950000005966 垫江县公共资源交易中心 中国银行重庆垫江支行 111616885778VA00139 商 垫江县公共资源交易中心 重庆农村商业银行垫江支行 2501010120010009065000128 垫江县公共资源交易中心 工商银行重庆垫江支行营业部 9558853100016843371 垫江县公共资源交易中心 重庆银行垫江支行 820101040000584-101195 道 附件：垫江县2026年度大中型水库移民后期扶持项目-.zip https://www.cqggzy.com/trade/014001/dac54522-3264-4eac-ae47-f434567ce374?categoryNum=014001001007 信息来源:https://www.chinapipe.net管/project/d3076788.html cqdingjiu 2026.08.21 10:06:47 国 中</t>
@@ -1054,9 +1234,13 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标, 水利, 移民, 后期扶持</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1089,16 +1273,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>新建水厂1座（新建2000m³茨竹水厂），输、配水管道改造与新建，管道总长约226.127km，管径DN20~DN250，管材为涂塑钢管。</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>合同预估金额：5000万元</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>涂塑钢管</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>万州区新田等6个镇乡农村饮水质量提升项目招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区新田等6个镇乡农村饮水质量提升项目 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 及文号 务 新建水厂1座（新建2000m3茨竹水厂），输、配水管道改造与新建，管道总长约226.127km，管 主要建设内容 径DN20~DN250，管材为涂塑钢管。 招标项目名 招标方 招标文件计划 拟交易场 合同预估金 序号 招标内容 备注 称 式 发布时间 所 额(万元) 商 万州区新田 万州区新田 重庆市万 招标项目 等6个镇乡农 等6个镇乡农 公开招 州区公共 1 村饮水质量提 2026-08 5000.00 村饮水质量 标 资源交易 升项目道施工总 提升项目 中心 承包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076721.html 管 cqdingjiu 2026.08.21 10:06:48 国 中</t>
@@ -1110,9 +1310,13 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标, 商机</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1145,16 +1349,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>新建50m³蓄水池4口、取水池2座；新建50m³/d-100m³/d水厂2座；改造100m³/d-300m³/d水厂5座；铺设DN25-DN250涂塑钢管约86km；新建提水泵站8座；配套阀井、电磁流量计等有关设施。</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>合同预估金额：3000万元</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>DN25-DN250涂塑钢管</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>万州区大周等4个镇乡街道农村饮水质量提升项目招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区大周等4个镇乡街道农村饮水质量提升项目 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 及文号 务 新建50m3蓄水池4口、取水池2座；新建50m3/d-100m3/d水厂2座；改造100m3/d-300m3/d水厂5 主要建设内容 座；铺设DN25-DN250涂塑钢管约86km；新建提水泵站8座；配套阀井、电磁流量计等有关设 施。 招标项目名 招标方 招标文件计划 拟交易场 合同预估金 序号 招标内容 商 备注 称 式 发布时间 所 额(万元) 万州区大周 万州区大周 重庆市万 招标项目 等4个镇乡街 等4个镇乡街 公开招 州区公共 1 道农村饮水 道农村饮道水质 2026-08 3000.00 标 资源交易 质量提升项 量提升项目施 中心 目 工总承包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3076720.html cqdingjiu 2026.08.21 10:06:49 国 中</t>
@@ -1166,9 +1378,13 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>重庆, 农村饮水质量提升项目, 管材招标, 合同预估金额</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1201,16 +1417,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>本项目西起太阳岗立交(不含太阳岗立交)，往东穿越铜锣山，止于内环南泉立交(不含南泉立交)。项目全长约6.8km，其中二标段长约3.62公里，采用主干路标准，设计车速60km/h，标准路幅为双向6车道，主要工程包括长隧道1座(新燕尾山隧道，长2542m)，简易立交1座(花溪立交),互通式立交2座(南温泉立交、苦竹坝立交)。</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>采购项目资金为企业自筹。</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>纤维编绕拉挤电缆保护套管(BWFRP100/2.0，79158米)</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>二航科工新燕尾山项目纤维编绕拉挤电缆保护套管采购询价通知公告 中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程项目询比采购 公告 中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程项目已具备采 购条件，现公开邀请供应商参加询比采购活动。 网 1. 采购项目简介 1.1 采购项目名称：中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机 电工程项目。 务 1.2采购方案编号：FA00000674478。 1.3 采购人：中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程 项目经理部。 商 1.4 采购代理机构：中交二航局科工（武汉）有限公司。 1.5 采购项目资金：企业自筹。 道 1.6 采购项目概况：新燕尾山隧道工程位于重庆市内环吉庆隧道北侧，四横线分流道鹿角隧道南侧，西接白居 寺大桥，东接内环快速路，并向东延伸接渝黔复线高速，其所在的道路系统呈东西布置，为主城区南部片区重 要干道。本项目西起太阳岗立交(不含太阳岗立交)，往东穿越铜锣山，止于内环南泉立交(不含南泉立交)。项目 管 全长约6.8km，其中二标段长约3.62公里，采用主干路标准，设计车速60km/h，标准路幅为双向6车道，主要工程 包括长隧道1座(新燕尾山隧道，长2542m)，简易立交1座(花溪立交),互通式立交2座(南温泉立交、苦竹坝立交)。 2.采购范围及相关要求 国 2.1 采购范围：纤维编绕拉挤电缆保护套管（BWFRP100/2.0，79158米）。 2.2 交货期：以甲方实际订单要求为准。 中 2.3 交货地点：重庆市巴南区新燕尾山项目甲方指定位置。 2.4 物资质量标准：满足国家法律法规、标准、规范、设计参数及技术规格书要求。 3.供应商资格要求 3.1 供应商应依法设立且满足如下要求： （1）资质要求：在中华人民共和国境内依法注册，具有独立法人资格、具有采购物资生产或供应经验的企业， 并且具有合法、有效的“三证合一”的营业执照,代理商需提供制造商授权委托书。 （2）财务要求：必须是经税务部门注册登记核准的一般纳税人，有依法纳税的良好记录，提供近三年的财务报 告。 （3）业绩要求：同类产品销售业绩不少于2个，并具备与本招标项目需求相适应的供货能力。 （4）信誉要求：本项目投标截止期前未被“信用中国”、“中国政府采购网”、中国交建物资采购管理信息系 统网站列入失信被执行人、违法案件当事人、违法失信行为记录名单。 （5）其他要求：提供运输方案及生产周期。 3.2 供应商不得存在下列情形之一： （1）处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； （2）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （3）已列入黑名单，且未解除限制期限； （4）其他： / 。 4.供应商报名 4.1有意参加询比采购活动的单位，请于2026年 8 月 20 日 11 时 00 分至2026 网 年 8 月 25 日 11 时 00 分（北京时间、下同），登录“中交招采网”（网 址：https://zjzcw.iccec.cn）进行报名并下载采购文件。 4.2 已在网并且已通过采购人层级供应商或已增加采购人为合作单位的供应商、上级供应商可直接参与询比采 务 购。在网平级单位供应商未增加采购人为合作单位需进行合作意向申请通过后参与询比采购。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择采购人，审核通过后方可参与询比 采购。 商 5. 供应商报价 5.1 报价结束（递交响应文件截止）时间：2026年 8 月 25 日 11 时 00 分。 道 5.2 供应商应在报价结束时间前，登录“中交招采网”进行线上报价并上传电子响应文件。逾期未完成上传的 电子响应文件，采购人将拒收。 5.3电子采购的供应商报价文件由线上电子报价表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 管 子报价表的数据为准。 6. 开标 6.1开标时间：与报价结国束时间相同。 6.2开标地点：本次采购在“中交招采网”平台线上开标，不举办现场开标，现场开标地点/。 7. 发布公告的媒介 中 本询比采购公告在中交招采网上发布。 8. 评审办法 本项目评审办法采用 经评审的最低价法 。 9. 合同主要条款 9.1 付款条件：无预付款，到货后办理结算，双方办理完结算手续、卖方提供符合合同要求的正式发票给买方 后60天，买方支付该批材料价值80%的货款，完工结算后支付至97%，剩余3%为质保金，质保期2年，两年后供 应方申请返还3%（无息）；银行转账、承兑、18个月供应链金融混合支付方式。 9.2履约保证金的递交： （1）□不要求递交 （2）要求递交 保证金金额：2万元 ； 保证金形式：银行转账、银行保函等电子保函；其他形式：无 。 10. 成交供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”（网址：https://zjzcw.iccec.cn）发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联 系4006765885中标服务费请按7咨询。 10.1收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： 网 （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； 务 （3）在1000万元（含）至3000万元之间的，每次收取1000元； （4）在3000万元（含）至1亿元之间的，每次收取3000元； （5）在1亿元（含）以上的，每次收取5000元。 商 10.2支付流程 （1）通知推送：中标结果发布后，系统自动道推送缴费通知（含应缴金额及支付链接）； （2）费用查询：供应商登录“中交招采网-服务管理”模块查看待支付费用； （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 管 （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网- 服务管理－发票下载”模块获取。 11.监督机构 国 监督机构名称：中交二航局科工（武汉）有限公司纪委监察部 举报电话：中027-82796466 举报邮箱：sneb_kggs@ccccltd.cn 12.其他 投标保证金采用银行转账形式的需转至中交二航局科工（武汉）有限公司账户（账 号：42001186108053006379-0006开户行：建行武汉长江支行，行号：105521000053），并备注二航科工燕尾山机 电照明项目纤维编绕管投标保证金。 13.联系方式 采购 人：中交二航局科工（武汉）有限公司 采购代理机构：中交二航局科工（武汉）有限公司 地 址：武汉市新洲区双柳街星谷大道158号地 址：武汉市新洲区双柳街星谷大道158号 邮政编码：430400 邮政编 码：430400 联系人：李鑫 联系人：毕明 月 电 话：18186145302 电 话：17853118573 电子邮件：18186145302@ccccltd.cn 电子邮件：bimingyue@ccccltd.cn 2026年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3076715.html cqdingjiu 2026.08.21 10:06:50 网 务 商 道 管 国 中</t>
@@ -1222,9 +1446,13 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 光纤电缆保护套管</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1257,16 +1485,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>巴南区</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>巴南区</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程变更公告</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>天然气表后管道安装工程</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程变更公告 重庆巴南天然气有限责任公司 重庆国际生物城配套公寓项目天然气表后管道安装工程 变更公 告 公告编号： RQBGGG202608200006 本公司于2026年08月19日发布的重庆国际生物城配套公寓项目天然气表后管道安装工程公告（编 号：RQCGXY202608170010），现做出如下变更： 网 1、对采购文件第一卷“采购需求“中墙体管道暗埋的具体内容进行明确。墙体管道暗埋应包含墙体开槽，输送 用不锈钢波纹管及钢制槽板的安装，墙体恢复，暗埋管道视频记录。 2、对由响应供应商提供的钢制槽板的规格进行明确。钢制槽板为U型开口槽，采用热镀锌Q235B钢板，钢板厚度 务 不得小于1.2mm，尺寸不得小于U40*30*1.2（宽40mm,高30mm,壁厚1.2mm热镀锌） 3、对由响应供应商提供的F型不锈钢三通，材质可以选用黄铜进行替代。 4、采购文件第二卷“技术规范及要求“中增加T/CECS633-2019 《燃气用户工程不锈钢波纹软管技术规程》。 以上内容在合同中也同步进行调整。 商 除上述变更外，原公告其余内容仍有效。 道 重庆巴南天然气有限责任公司 管 2026-08-20 信息来源:https://www.chinapipe.net/project/d3076704.html cqdingjiu 2026.08.21 10:国06:50 中</t>
@@ -1278,9 +1522,13 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>重庆, 天然气表后管道安装工程, 变更公告</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1313,16 +1561,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>合川区</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>合川区</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300-D800管道130米，新增检查井11座，新建D300排水管道38米；紫外光修复 D300-D800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米，螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米，不锈钢快速锁修复 D1000管道42米；完成 D300-D1000管道清障189米、清淤2627米。</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>合同预估金额为1708.44万元</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>排水管道、检查井、紫外线修复设备、螺旋缠绕修复材料、树脂修复材料、不锈钢快速锁修复设备</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>合川区中南片区污水管网工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目 合川区中南片区污水管网工程（一期） 名称 招标 网 法人 或招 标人 重庆市合川区住房和城乡建设委员会 名称 （盖 务 章） 项目 批准 文件 合川发改投〔2025〕19 号 商 及文 号 主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300-D800管道130米，新增检查井11座，新 主要 建D300排水管道38米；紫外光修复 D300-D道800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米， 建设 螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米，不锈钢快速锁修复 D1000管道42 内容 米；完成 D300-D1000管道清障189米、清淤2627米。 拟 招 招标文 合同预 招标 管 交 序 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 所 国 重 庆 市 合川 合 招标 区中 主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300- 川 项目 中 南片 D800管道130米，新增检查井11座，新建D300排水管道38米；紫外光修复 公 区 区污 D300-D800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米， 开 公 1 2026-09 1708.44 水管 螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米， 招 共 网工程 不锈钢快速锁修复 D1000管道42米；完成 D300-D1000管道清障189米、清 标 资 （一 淤2627米。 源 期） 交 易 中 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076543.html cqdingjiu 2026.08.21 10:06:50</t>
@@ -1334,9 +1598,13 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>重庆, 污水管网工程, 管网修复, 新建工程, 排水管道, 检查井, 紫外线修复, 螺旋缠绕修复, 树脂修复, 不锈钢快速锁修复</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1369,16 +1637,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>本次采购项目涉及球墨铸铁管及管件的供应，具体包括样品的规格和数量要求。</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>球墨铸铁管及管件</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>重庆市自来水有限公司球墨铸铁管及管件2026-2027(2年)采购项目(第二次)答疑补遗文件 重庆市自来水有限公司球墨铸铁管及管件2026-2027（2年）采购项目（第二次）答疑 提问1：样品20CM长含承口吗？如果含承口20CM那就太短，标识LOGO无法体现完整建议≥20CM 答1：球墨铸铁管样品含承口，样品长度≥20CM 网 务 招标人：重庆市自来水有限公司 招标代理机构：重庆水务集团公用工程咨询有限公司 商 2026年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d30道76446.html cqdingjiu 2026.08.21 10:06:50 管 国 中</t>
@@ -1390,9 +1666,13 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>重庆, 球墨铸铁管, 管件, 采购项目</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1425,16 +1705,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>大足区</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>大足区</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>大足区中心城区和龙水镇市政公共排水设施的运维(材料)。</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>大足区中心城区和龙水镇市政公共排水设施运维(材料)更正一号公告 一、更正项 更正项 更正子项 更正前内容 更正后内容 网上投标 网上投标截止时间 2026-08-20 15:00:00 2026-08-25 15:00:00 递交投标响应文件 线下递交投标（响应）文件开始时间 2026-08-20 14:30:00 2026-08-25 14:30:00 递交投标响应文件 线下递交投标（响应）文件截止时间 2026-08-20 15:00:00 2026-08-25 15:00:00 网 开标 开标时间 2026-08-20 15:00:00 2026-08-25 15:00:00 招标采购（附件） 附件 务 二、补遗更正说明 清单限价重新做调整，开标时间已更正，详见更正文件内容 商 三、联系方式 采购执行方： 道 单位名称：重庆誉双项目管理有限公司 联系人：陈老师 联系电话：13996336872 采购需求方： 管 单位名称：重庆市大足区茂泰市政工程有限公司 联系人：谢老师 联系电话：18523539371 信息来源:https://www.chinapipe.net/project/d3076319.html 国 cqdingjiu 2026.08.21 10:06:50 中</t>
@@ -1446,9 +1742,13 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1481,16 +1781,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>璧山区</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>璧山区</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>项目主要建设内容包括：1.新建茄果类智能种植温室11256平方米；2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、二氧化碳补施系统1套、智能环境控制系统1套、作业物流装备1套；3.项目后勤及仓储配套（含装修）5000平方米；4.土方回填及场地平整53000平方米；5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米；6.都市农文旅配套建设1000平方米。</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>合同预估金额为9182.25万元</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>温度调控系统、水肥一体化设备、人工补光系统、二氧化碳补施系统、智能环境控制系统、作业物流装备</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>璧山区2026年大路街道三台村智慧设施农业建设项目招标计划表 重庆市工程建设项目招标计划表 项目 璧山区2026年大路街道三台村智慧设施农业建设项目 名称 招标 法人 或招 网 标人 中农良品（重庆）生态农业有限公司 名称 （盖 章） 项目 批准 务 文件 及文 号 主要 1.新建茄果类智能种植温室11256平方米；2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、二氧化碳补施系统1套、智能环境控制系统1套、作业物流 建设 装备1套；3.项目后勤及仓储配套（含装修）5000平方米；4.土方回填及场地平整53000平方米；5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米；6. 内容 都市农文旅配套建设1000平方米。 商 招 拟 标 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 称 道 璧 山 区2026 重 年 庆 大 市 路 公 招标 街 管 共 项目 道 资 三 公 源 台 项目主要建设内容包括：1.新建茄果类智能种植温室11256平方米； 2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、 开 交 1 村 二氧化碳补施系统1套、智能环境控制系统1套、作业物流装备1套； 3.项目后勤及仓储配套（含装修）5000平方米； 4.土方回填及场地平整53000平 2026-09 9182.25 招 易 智 方米； 5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米； 6.都市农文旅配套建设1000平方米。 标 中 慧 心 设 国 璧 施 山 农 分 业 中 建 心 设 项 目 中 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076777.html cqdingjiu 2026.08.21 10:06:51</t>
@@ -1502,9 +1818,13 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>重庆, 智慧设施农业, 招标计划, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1537,16 +1857,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>长寿区</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>长寿区</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>本项目包括但不限于新建混凝池-三沉池，还建格栅池，厌氧池新增搅拌机，好氧池联通孔短流整改、拆除填料及底部曝气盘，增设可提升曝气系统，原斜管沉淀池改造为二沉池（新增中心筒、改造成多斗排泥、提高液位，更换三角堰），拆除原有污泥池，新增临时污泥储罐务并还建污泥池，污泥堆场临时改建及恢复，实施技改期间的临时排放工程，进行基础的自控改造。</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>企业自筹，出资比例为100%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>污水处理设备</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>长寿区江南街道污水处理厂更新改造工程项目公告 长寿区江南街道污水处理厂更新改造工程比选公告 1. 比选条件 本比选项目长寿区江南街道污水处理厂更新改造工程，比选人为重庆环保投资集团有限公司，资金来源为企业 自筹，出资比例为100%。现对该项目进行公开比选，诚邀有兴趣的潜在参选人参与比选。 2. 项目概况与比选范围 网 2.1项目概况：长寿区江南街道污水处理厂更新改造工程包括但不限于以下内容新建混凝池-三沉池；还建格栅池； 厌氧池新增搅拌机，好氧池联通孔短流整改、拆除填料及底部曝气盘，增设可提升曝气系统；原斜管沉淀池改 造为二沉池（新增中心筒、改造成多斗排泥、提高液位，更换三角堰）。拆除原有污泥池，新增临时污泥储罐 务 并还建污泥池；污泥堆场临时改建及恢复；实施技改期间的临时排放工程；进行基础的自控改造。 2.2 比选范围：长寿区江南街道污水处理厂更新改造工程施工图范围中的所有工作内容，包括但不限于土建工 程、设备及安装工程、工艺管道工程、电气工程、临排工程等内容，具体以比选人提供的图纸、技术规范、设 备需求清单、答疑资料、澄清资料、其他补遗资料等相关商内容为准。 2.3 建设地点：重庆市长寿区江南街道。 2.4 工期：110日历天（实际开工日期以监理工道程师签发的工程开工通知明确的开工日期为准），缺陷责任期24 个月。 3. 参选人资格要求 管 3.1 本次比选要求参选人具备以下条件： （1）独立法人资格； （2）建设行政主管部国门颁发的有效的市政公用工程施工总承包二级及以上资质； 3.2 参选人还应在资质、业绩、资金、人员等方面具有相应的服务能力，详见比选文件第二章参选人须知前附 表第1.4.1项内容。 中 3.3本次比选不接受联合体参选。 4. 比选文件的获取 4.1 参选人于2026年8月19日起可自行在重庆水务集团电子商务平台（https://www.cqswjt.cn）上下载比选文件电 子版，以及答疑、补遗等比选截止时间前公布的所有相关资料，不管参选人下载与否，比选人和代理机构都视 为参选人收到以上资料并全部知晓有关比选过程和事宜，如因参选人自身原因未能下载相关资料由此产生的一 切后果由参选人自行负责。各参选单位应随时关注网上（https://www.cqswjt.cn）发布的比选文件及相关修改内容。 4.2 参选人须在重庆水务集团电子商务平台（https://www.cqswjt.cn）进行供应商注册，填写相关信息，审批过后 成为平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标（仍须同时提交纸质版参选文件）。参选 人需提前在重庆水务集团电子商务平台（https://www.cqswjt.cn）上注册、报名，下载比选文件，上传参选文件电 子档并报价。在比选截止时间前未按时报名、报价并上传参选文件电子档、递交纸质版参选文件者，将被否决 参选。 5. 比选文件的递交 5.1 参选文件递交时间：2026年8月 27 日09时00分至09时30分，地点：重庆市两江新区嘉华路36号重庆水务 大厦5楼。 5.2 比选截止时间：2026年8月 27 日09时30分（北京时间）。 5.3 逾期送达的或者未送达指定地点的参选文件，比选人不予受理。 6. 发布比选公告的媒介 本次比选公告在重庆水务集团电子商务平台（https：//www.cqswjt.cn）上发布。 7. 联系方式 比选人：重庆环保投资集团有限公司 地 址：重庆市两江新区礼环南路102号 网 联系人：曹老师 电话：023-71618725 务 代理机构：重庆招标采购（集团）有限责任公司 地址：重庆市江北区五简路2号重庆咨询大厦A座2004室 商 联系人：高老师 电话：023-67706841 道 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 管 信息来源:https://www.chinapipe.net/project/d3076456.html cqdingjiu 2026.08.21 10:06:51 国 中</t>
@@ -1558,9 +1894,13 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 污水处理厂</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1593,16 +1933,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>潼南区</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>潼南区</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>本项目包括两个子项目：一是潼南区新胜镇污水处理厂的更新改造，主要内容是新增一体化污水处理设备基础，更新现有污水处理系统设备，升级处理系统，新建风机房-配电室防尘防渗地坪；二是潼南区双江镇污水处理厂的更新改造，内容包括将原有斜管沉淀池改建为好氧池，新建竖流沉淀池，更新老旧及故障设备，新建储药加药区和一体化危废储存间，完善污水处理配套设施。</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>本项目资金来源为企业自筹，出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>污水处理设备、一体化设备、沉淀池、好氧池、竖流沉淀池、储药加药区、一体化危废储存间、污水处理配套设施</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>潼南区新胜镇、双江镇污水处理厂更新改造工程项目项目公告 潼南区新胜镇、双江镇污水处理厂更新改造工程比选公告 1. 比选条件 本比选项目潼南区新胜镇、双江镇污水处理厂更新改造工程，比选人为重庆环保投资集团有限公司，资金来源 为企业自筹，出资比例为100%。现对该项目进行公开比选，诚邀有兴趣的潜在参选人参与比选。 2. 项目概况与比选范围 网 2.1项目概况：潼南区新胜镇污水处理厂更新改造工程，主要建设内容为新增200m?/d一体化污水处理设备基础； 更新现有污水处理系统设备，提高现有沉淀池二沉池、三沉池液位；升级处理系统（干化池改建为污泥池，新 增叠螺脱水机，改建污泥堆场及雨棚）；新建风机房－配电室防尘防渗地坪。潼南区双江镇污水处理厂更新改 务 造工程，主要建设内容为将原有斜管沉淀池改建为好氧池，新建3座竖流沉淀池，配套安装相关设备；更新污水 处理系统中老旧及故障设备；新建储药加药区与一体化危废储存间，完善污水处理配套设施。 2.2 比选范围：潼南区新胜镇、双江镇污水处理厂更新改造工程施工图范围中的工作内容（一体化设备采购及 相关安装工作除外），包括但不限于土建工程、附属工程商（包括但不限于绿化工程、工艺管线工程、电气及自 控工程、临排清淤工程等）、一体化污水处理设备基础、标准化建设、配套设备材料采购及安装工程等内容， 其中一体化设备采购及相关安装工作不在本次比选范围内；具体以比选人提供的图纸、技术规范、工程量清单、 答疑资料、澄清资料、其他补遗资料等相关内容为准。 道 2.3 建设地点：潼南区新胜镇、双江镇。 2.4 工期：120日历天（实际开工日期以监理工程师签发的工程开工通知明确的开工日期为准），缺陷责任期24 个月。 管 3. 参选人资格要求 3.1 本次比选要求参选人具备以下条件： 国 （1）独立法人资格； （2）建设行政主管部门颁发的有效的市政公用工程施工总承包二级及以上资质； 中 3.2 参选人还应在资质、业绩、资金、人员等方面具有相应的服务能力，详见比选文件第二章参选人须知前附 表第1.4.1项内容。 3.3本次比选不接受联合体参选。 4. 比选文件的获取 4.1 参选人于2026年8月19日起可自行在重庆水务集团电子商务平台（https://www.cqswjt.cn）上下载比选文件电 子版，以及答疑、补遗等比选截止时间前公布的所有相关资料，不管参选人下载与否，比选人和代理机构都视 为参选人收到以上资料并全部知晓有关比选过程和事宜，如因参选人自身原因未能下载相关资料由此产生的一 切后果由参选人自行负责。各参选单位应随时关注网上（https://www.cqswjt.cn）发布的比选文件及相关修改内容。 4.2 参选人须在重庆水务集团电子商务平台（https://www.cqswjt.cn）进行供应商注册，填写相关信息，审批过后 成为平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标（仍须同时提交纸质版参选文件）。参选 人需提前在重庆水务集团电子商务平台（https://www.cqswjt.cn）上注册、报名，下载比选文件，上传参选文件电 子档并报价。在比选截止时间前未按时报名、报价并上传参选文件电子档、递交纸质版参选文件者，将被否决 参选。 5. 比选文件的递交 5.1 参选文件递交时间：2026年8月27日09时00分至09时30分，地点：重庆市两江新区嘉华路36号重庆水务大厦5 楼。 5.2 比选截止时间：2026年8月27日09时30分（北京时间）。 5.3 逾期送达的或者未送达指定地点的参选文件，比选人不予受理。 6. 发布比选公告的媒介 本次比选公告在重庆水务集团电子商务平台（https：//www.cqswjt.cn）上发布。 7. 联系方式 网 比选人：重庆环保投资集团有限公司 地 址：重庆市两江新区礼环南路102号 务 联系人：陈老师 电话：023-42756696 商 代理机构：重庆招标采购（集团）有限责任公司 道 地址：重庆市江北区五简路2号重庆咨询大厦A座2004室 联系人：高老师 管 电话：023-67706841 重庆水务电子商务平台国咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3076454.html cqdingjiu 2026.08.21 10:06:51 中</t>
@@ -1614,9 +1970,13 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 污水处理厂更新改造</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1631,7 +1991,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>房建</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1649,16 +2009,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>给重庆医科大学附属第二医院医疗教学配套业务用房配置第二市政水源</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>采购预算 409674.71元</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>市政水源</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表 重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表 采购需求单位(全称) 重庆医科大学附属第二医院总务科 项目名称 重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程 项目内容 给重庆医科大学附属第二医院医疗教学配套业务用房配置第二市政水源 采购预算 409674.71元 网 拟采购供应商全称 东部自来水分公司 配套业务用房第二市政水源从重庆水资源产业股份有限公司东部自来水分公司管辖范围 单一来源采购理由 的管网具体接入，属于市政管网施工，具有特殊要求。 务 公示时间 2026年8月19日-2026年8月25日 联系人及联系电话 刘老师 023-63693215 注：1.以上陈述是否真实，欢迎社会各界监督，公示时间商至少5个工作日； 2.公示期内无异议的，采购管理处将进行该项目采购；有异议请将意见反映采购人。 信息来源:https://www.chinapipe.net/project/d30道76334.html cqdingjiu 2026.08.21 10:06:51 管 国 中</t>
@@ -1670,9 +2038,13 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1705,16 +2077,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>黔江区</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>黔江区</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>本项目服务内容为G319黔江区正阳至城西段改建工程管线探测工作。</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>管线探测工作</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>中铁二院工程集团有限责任公司G319黔江区正阳至城西段改建工程管线探测工作线上询价采购公告 中铁二院工程集团有限责任公司G319黔江区正阳至城西 段改建工程管线探测工作线上询价采购 ZTEYCQ-XJ-2026-019 网 采购单位: 中铁二院工程集团有限责任公司 发布时间: 2026-08-19 16:10 报价截止时间: 务 2026-08-21 17:00 招标方联系人: 杨先生 招标方联系电话: 商 13883021521 招标方邮箱: 监督方联系人: 李先生 道 监督方联系电话: 15823237919 监督方邮箱: 保证金: 0元 管 结算与发票信息: 详情 交货信息: 详情 国 其他说明事项: 标的明细 流水号：询2026081900304 中 计量单 技术标准及要 序号 标的名称 数量 交货期 送货地址 位 求 G319黔江区正阳至城西段 合同签订后5天内完成 西南区-重庆市-市辖 1 1 项 详见询价文件 改建工程管线探测工作 本项目服务内容。 区-黔江区-项目地点 信息来源:https://www.chinapipe.net/project/d3076309.html cqdingjiu 2026.08.21 10:06:51</t>
@@ -1726,9 +2114,13 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类, 匹配程度, 匹配关键词</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1761,16 +2153,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>本项目主要涉及室外蒸汽管道φ219x6mm的安装，管道材质为20#，地上敷设，蒸汽管道运行压力1.08MPa，管道设计压力1.2MPa。蒸汽管道系统包括从锅炉房分汽缸到6#和8#车间分汽缸的所有蒸汽管道、管件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸等的采购、运输、安装、保温工作。还包括钢结构桁架工程的采购、运输、制作、安装、防腐工作，以及管道附件及控制系统的采购、运输、安装、接线等工作。此外，还需要进行调试与验收，确保蒸汽管道系统能够正常使用并备案。</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>项目总投资额为580.643717万元，全部为企业自筹资金。</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>蒸汽管道、管件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸、钢结构桁架、阀门、压力表、温度表、流量计、电动/气动执行机构、配套仪表电缆、桥架、保护管</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告 乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告 1.招标条件 本招标项目乌江涪陵榨菜绿色智能化生产基地(一期)已由重庆市涪陵区发展和改革委员会以重庆市企业投资项目 备案证2020-500102-13-03-000003 批准建设，项目业主为重庆市涪陵榨菜集团股份有限公司，建设资金来自企业 自筹，项目出资比例为100% ，招标人为重庆市涪陵榨菜集团股份有限公司。项目已具备招标条件，现对乌江 涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 2.1 建设地点： 重庆市涪陵区马鞍街道人和社区 。 网 2.2 项目概况与建设规模：建筑面积约369384.27㎡。本项目蒸汽管道主要为室外蒸汽管道φ219x6mm，管道材质： 20#地上敷设，由14#锅炉房分汽缸分别接至6#和8#智能化车间分汽缸，蒸汽管道运行压力1.08MPa，管道设计压 力1.2MPa。 务 2.3 本次招标项目合同估算金额：580.643717万元。 2.4 招标范围： 商 （1）蒸汽管道系统本体：从锅炉房分汽缸后（含分气缸阀门）至6#车间、8#车间分气缸处，所有蒸汽管道、管 件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸等的采购、运输、安装、保温（含保温层及保 护层）工作。 道 （2）钢结构桁架工程：负责本项目范围内所有钢结构架空桁架（管廊）的采购、运输、制作、安装、防腐工作。 （3）管道附件及控制系统：负责本工程范围内所有阀门、压力表、温度表、流量计、电动/气动执行机构以及配 套仪表电缆、桥架、保护管的采购、运输、安装、接线。负责与DCS/PLC系统接口的接线与联动调试。 管 （4）调试与验收：组织并确保整个蒸汽管道系统（含分气缸后段末端管道、桁架及其安全附件）通过项目所在 地特种设备安全监察管理部门实施的安装监督检验。负责报检、配合现场检验、整改、出具深化图纸并由设计 单位审核盖章、特种设备法定报检取证的全部费用，包括但不限于：施工前办理安装告知，设计院盖章审核， 施工中接受并通过安装国监督检验，最终负责取得《压力管道安装监督检验证书》与《特种设备使用登记证》， 确保蒸汽管道投入使用并备案，提交全套法定检验报告。 （5）土建工作部分 中 1）管架和桁架基础的施工，包括但不限于钢结构桁架的混凝土独立基础的土方开挖、浇筑、养护及回填恢复。 2）管道穿墙/板孔洞的开挖、封堵与修复。 3）室内外地面的开挖（包括但不限于疏水井、沟槽开挖、通行地沟、设备基础开挖）与恢复（包括但不限于土 方回填、渣土弃运、地面硬化）。 4）桁架及设备接地线的施工，包括但不限于接地极制作、接地干线敷设，并与厂区主接地网可靠连接，接地电 阻测试合格。 具体详见施工图、招标文件、工程量清单、答疑补遗等资料。 2.5 工期要求： 60 日历天 缺陷责任期要求： 24 个月 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：投标人应同时具备以下(1)、(2)项资质： （1）具备建设行政主管部门颁发的有效的建筑工程施工总承包二级及以上资质； （2）具备有效的《中华人民共和国特种设备生产许可证》（许可子项目：工业管道安装GC2级及以上）。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 网 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 务 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（涪陵区） （https://www.cqggzy.com/fulingweb/）下载招标文件、工程商量清单、电子图纸等资料。参与投标的投标人需在重 庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏 “主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网（涪陵区道）（https://www.cqggzy.com/fulingweb/）本项目招标公告网页下 方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-23 17:00:00前。 4.3招标人应于2026-08-24 18:00:00前在重庆市公共资源交易网（涪陵区）（https://www.cqggzy.com/fulingweb/）发 布澄清。 5.投标文件递交的内容 管 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-09 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 国 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（涪陵区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 中重庆市涪陵榨菜集团股份有限公司 代理机构: 中招国际招标有限公司 重庆两江新区黄山大道中段53号5-1（双 地 址: 重庆市涪陵区江北街道办事处二渡村一组 地 址: 鱼座A栋5楼） 邮 编: 408000 邮 编: 项目负责人: 徐老师 项目负责人: 寿云凤 电 话: 13212467016 电 话: 023-68881331-9032 传 真: 传 真: 电子邮箱: bsd2me@126.com 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市涪陵区发展和改革委员会 电 话: 023-72203687 2026年08月19日 乌江 涪陵 榨菜 绿色 智能 化生 产基地 (一 期)6#、 8#车 网 间蒸 汽管 道安 装工 务 程 中 中 国 国 重 银 重 商民 重 庆 行 庆 生 庆 涪 股 涪 银 涪 陵 份 陵 行 陵 重 投 公 有 道公 股 公 庆 标 共 限 共 份 共 银 开 保 户 资 公 资 有 资 行 户 证 110292140553VA00154 9902001860445897 430102029007791845-275 名 源 司 源 限 源 涪 行 金 交 重 交 公 交 陵 账 管 易 庆 易 司 易 支 号 有 涪 有 重 有 行 限 陵 限 庆 限 公 马 公 涪 公 国 司 鞍 司 陵 司 支 支 行 行 中 信息来源:https://www.chinapipe.net/project/d3076300.html cqdingjiu 2026.08.21 10:06:51</t>
@@ -1782,9 +2182,13 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>重庆, 蒸汽管道, 安装工程, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1817,16 +2221,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>完成重庆国际生物城配套公寓项目（民用1020户）天然气表后管道定制化服务。（含安装燃气输送用不锈钢波纹管RSB-IF-13—12240米（预估）、双外螺纹球阀DN15-1020个、燃气管道自闭阀DN15-1020个，其它配套管件及辅材，墙体管道暗埋等）</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>天然气表后管道定制化服务</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程询比采购公告 采购公告 公告编号： RQXYGG202608190057 一、采购项目基本情况 采购人：重庆巴南天然气有限责任公司 网 采购项目编号：RQCGXY202608170010 采购项目名称：重庆国际生物城配套公寓项目天然气表后管道安装工程 务 采购内容和范围：完成重庆国际生物城配套公寓项目 （民用1020户）天然气表后管道定制化服务。（含安装燃 气输送用不锈钢波纹管RSB-IF-13—12240米（预估）、双外螺纹球阀DN15-1020个、燃气管道自闭阀DN15-1020个， 其它配套管件及辅材，墙体管道暗埋等） 二、供应商资格要求 商 1. 资质要求:资质要求： 1.响应供应商为中华人民共和国境内合法注册的独立法人或其他组织，具有独立承担民事责任能力，具有独立订 立合同的权利。 道 2.响应供应商应具备市政公用工程施工总承包三级及以上资质、具备有效的安全生产许可证。 3.响应供应商应为本项目配备项目负责人一名，持有市政公用工程或机电工程专业二级建造师及以上资质，且为 本单位在职人员并提供社保证明。 4.响应供应商应为本项目配备专职安全员一名，持有安全生产考核合格C证，且为本单位在职人员并提供社保证 管 明。 5.项目负责人及专职安全员社保证明期限须包含2026年5月至2026年7月。提供的社保证明，须体现上述人员的姓 名、身份证号（或社保号）、单位名称、本单位参保时间（或起始参保时间），并带有社保部门公章或社保部 门的有效电子印章。 2. 信用要求:6.信用要求国： （1）响应供应商（含联合体响应的成员单位）未被“国家企业信用信息公示系统” 网站（www.gsxt.gov.cn）列 入严重违法失信企业名单（如：提供网站查询界面截图）； （2）响应供应商（含联合体响应的成员单位）未被 “信用中国”网站（www.creditchina.gov.cn）列入严重失信 主体名单（中如：提供网站查询界面截图）。 三、采购文件的获取 采购文件在 华润守正采购交易平台 发布，不再另行线下提供纸质采购文件，凡有意参与者请自行登录守正平台 查看和下载采购文件。 四、响应文件的提交 响应文件提交 / 报价截止时间： 2026-08-25 08:00:00 （北京时间，若有变化另行通知）。 响应文件提交 / 报价方式：在响应文件提交 / 报价截止时间前，通过 华润守正采购交易平台 提交电子响应文件或 报价，逾期提交将被拒收。 五、采购人联系方式 联系人：何俊 电话：15178855716 邮箱：1460553040@qq.com 六、采购明细 行号 采购内容 需求数量 单位 补充说明 1 重庆国际生物城配套公寓项目天然气表后管道定制化服务 1 元/次 具体内容详见采购文件 七、答疑澄清、通知 答疑澄清、通知等文件一经在 华润守正采购交易平台 发布，视为已发放给相应供应商（发放时间即为发出时 间），请随时关注 华润守正采购交易平台 发布的相关信息，并及时查阅和处理。 八、服务费交纳 网 本项目向成交人收取服务费,供应商收到预成交通知书和服务费交款通知书10日内,向平台运营方(华润守正招标有 限公司)支付服务费,经确认无误后由采购人发送成交通知书。平台运营方在收到服务费后向成交人开具服务费发 票。 收费标准：项目总成交金额＜50万元的采购项目，免收服务费。项目总成交金额≥50万元的采购项目，按成交金 务 额的0.15%向成交人收取（金额四舍五入，精确到分）。单项目总收费封顶100000元。其他说明：（1）总价采购， 收费基数为成交金额；单价、费率采购，收费基数为预算金额。（2）单项目存在多个成交人情形的，按总成交 金额计算收费总额，各成交人按成交比例分摊；项目总成交金额50万以上，但单个成交人成交金额少于50万仍按 比例收取服务费。 商 退款说明：成交通知书发布后,平台提供相关服务已完成,成交人已交纳服务费不予退还。 多成交人服务费收取示例： 以某项目总成交金额100万为例,A、B、C多成交人情形,总服务费为0.15万, 供应商A成交金额为50万,A服务费为0.075万; 供应商B成交金额为30万,B服务费为0.045万; 道 供应商C成交金额为20万,C服务费为0.03万。 九、其它事项 管 1.本公告在 华润守正采购交易平台 ( https://www.szecp.com.cn/ )上公开发布。 2.本项目采购通过守正平台线上进行，供应商需注册 华润守正采购交易平台 ，通过平台进行响应文件的递交或 报价，具体操作步骤可查阅网站首页帮助中心的操作手册，也可以联系守正客服。 国 3.如对采购项目有异议，请登录 华润守正采购交易平台 ,通过异议菜单提出。 2026年08月19日 中 信息来源:https://www.chinapipe.net/project/d3076125.html cqdingjiu 2026.08.21 10:06:52</t>
@@ -1838,9 +2250,13 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>重庆, 天然气表后管道安装工程, 管材招标</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1873,16 +2289,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>重庆市映天辉氯碱化工有限公司拟开展废盐综合利用联产20万吨/年离子膜烧碱项目(一期12万吨/年)建设。</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>项目资金来自业主自筹，项目出资比例为100%。本次招标项目货物采购估算金额约为330万元。</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>非金属管道管件阀门</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)非金属管道管件阀门采购招标公告 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采购招标公告 1、招标条件 本招标项目废盐综合利用联产20万吨/年离子膜烧碱项目已由重庆市长寿区发展和改革委员会以 重庆市企业投 资项目备案证（2207-500115-04-05-168305）批准建设，项目业主为重庆市映天辉氯碱化工有限公司，建设资金来 自业主自筹，项目出资比例为100%，招标人为重庆市映天辉氯碱化工有限公司。项目已具备招标条件，现对本 项目的（一期12万吨/年）非金属管道管件阀门采购进行公开招标。 网 2、项目概况 2.1 建设地点：重庆长寿经济技术开发区化北路2号。 务 2.2、项目概况与建设规模： 重庆市映天辉氯碱化工有限公司（以下简称“映天辉”）位于重庆长寿经济技术开发区化北路2号，始建于2004 年5月，占地430亩，注册资本34800万元。现为国有控股企商业，是一家集氯碱生产经营、新材料研发经营于一体 的专业型、科技型综合企业，系国家级高新技术企业。 映天辉作为长寿经开区氯碱产业基础平台的龙头化工企业，现有一条氯碱生产线，生产规模为20万吨/年烧碱 （折100%NaOH计）。为建设并贯通氯碱化工道循环经济产业链，保障下游产业链装置氯气需求，实现氯碱产品的 升级和高端化发展，增加产品附加值，降低成本，提高竞争力，映天辉公司经过充分调研和反复论证后，拟开 展废盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）建设。装置在正常运行情况下，按照每年 8000 小时操作。具体要求及参数以第五章货物需求一览表及技术规格标准和要求为准。 管 2.3 本次招标项目货物采购估算金额： 约 330 万元。 2.4招标范围： 本次招标项目为：“废国盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采 购”包括不限于非金属管道管件阀门所含设计、制造、试验、出厂检验、防腐、运输（含保护、包装及运输、 货到现场车板交货）、保险（交货验收前）、指导安装、调试、备件及专用工具、税费、技术资料和图纸及质 保期内的各种备品、备件的供应及相关的技术服务、产品质量证明书及原材料检测报告等。（详见“第五章货 物需求一览中表及技术规格标准和要求”）。 2.5 交货地点：货物运送至买方指定地点； 2.6 交货期： 2.6.1合同签订后3个月内，所有货物运送招标人现场并具备安装条件。 2.6.2 中标方应于合同签订之日起7天内，向买方提交完整的技术资料，以供设计院开展相关设计工作。 3、投标人资格要求 3.1 投标人应符合以下要求： （1）投标人具备有效的营业执照。 注：不得将投标人营业执照记载的经营范围作为评审因素。 （2）投标人具备有效的《中华人民共和国特种设备生产许可证》压力管道管子-B级及以上资质、压力管道管 件B2级及以上资质； （3）投标人具备塑料管道管子、管件的型式试验证书。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3本次招标不接受代理商投标，不接受联合体投标。 4. 招标文件的获取 4.1 凡愿意参加的潜在投标人，从2026年 8 月19 日起至投标截止时间前，均可登录重庆市公共资源交易网 （www.cqggzy.com）直接下载获取招标文件、答疑等开标前的有关资料。在公告期间，各投标人应随时关注网上 发布的招标文件答疑、补遗、澄清等文件内容，不管投标人是否下载，均视为已知晓招标文件的全部内容和有 关事宜。本项目不需要报名，直接投标。 网 5.投标文件的递交 5.1 投标文件递交的截止时间为 2026年 9 月10 日上午09时30分，地点在重庆市公共资源交易中心开标厅（地 址：重庆市两江新区青枫北路6号渝兴广场B10栋2层），具体开标地点详见一、二楼大厅显示屏。 务 5.2逾期送达的或者未送达指定地点的，或者未按照招标文件要求密封的投标文件，招标人将拒收。 6、发布公告的媒介 商 本次招标公告在中国招标投标公共服务平台、重庆市公共资源交易网上发布。 7、联系方式 道 招 标 人：重庆市映天辉氯碱化工有限公司 地 址：重庆长寿经济技术开发区化北路二号 管 联 系 人：张先生 电 话：023-40717888 国 招标代理机构： 重庆招标采购（集团）有限责任公司 地 址：重庆市两江新区五里店五简路2号重庆咨询大厦A栋20楼2001室 中 项目负责人：彭文婷 电 话： 023-67703002 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采购 户名 开户行 投标保证金账号 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000631258 支行 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051303372 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630010400 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000002549 贸易试验区分行 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835014652 坝支行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146619529 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764260665 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020038958 信息来源:https://www.chinapipe.net/project/d3076119.html cqdingjiu 2026.08.21 10:06:52 网 务 商 道 管 国 中</t>
@@ -1894,9 +2318,13 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标, 资金, 产品</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1929,16 +2357,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>重庆市映天辉氯碱化工有限公司拟开展废盐综合利用联产20万吨/年离子膜烧碱项目(一期12万吨/年)，包括衬氟管道及管件的采购。</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>项目资金来自业主自筹，项目出资比例为100%。货物采购估算金额约为225万元。</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>衬氟管道及管件</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)衬氟管道及管件采购招标公告 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）衬氟管道及管件采购招标公告 1、招标条件 本招标项目废盐综合利用联产20万吨/年离子膜烧碱项目已由重庆市长寿区发展和改革委员会以 重庆市企业投 资项目备案证（2207-500115-04-05-168305）批准建设，项目业主为重庆市映天辉氯碱化工有限公司，建设资金来 自业主自筹，项目出资比例为100%，招标人为重庆市映天辉氯碱化工有限公司。项目已具备招标条件，现对本 项目的（一期12万吨/年）衬氟管道及管件采购进行公开招标。 网 2、项目概况 2.1 建设地点：重庆长寿经济技术开发区化北路2号。 务 2.2、项目概况与建设规模： 重庆市映天辉氯碱化工有限公司（以下简称“映天辉”）位于重庆长寿经济技术开发区化北路2号，始建于2004 年5月，占地430亩，注册资本34800万元。现为国有控股企商业，是一家集氯碱生产经营、新材料研发经营于一体 的专业型、科技型综合企业，系国家级高新技术企业。 映天辉作为长寿经开区氯碱产业基础平台的龙头化工企业，现有一条氯碱生产线，生产规模为20万吨/年烧碱 （折100%NaOH计）。为建设并贯通氯碱化工道循环经济产业链，保障下游产业链装置氯气需求，实现氯碱产品的 升级和高端化发展，增加产品附加值，降低成本，提高竞争力，映天辉公司经过充分调研和反复论证后，拟开 展废盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）建设。装置在正常运行情况下，按照每年 8000 小时操作。具体要求及参数以第五章货物需求一览表及技术规格标准和要求为准。 管 2.3 本次招标项目货物采购估算金额： 约225万元。 2.4招标范围： 本次招标项目为：“废国盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）衬氟管道及管件采购一批” 包括但不限于制造、涂漆、包装、运输、配合验收工作、检验检测、产品质量证明书等。（详见“第五章货物 （材料）需求一览表及技术规格标准和要求”）。 2.5 交货地点：货物运送至买方指定地点； 中 2.6 交货期： 2.6.1合同签订后 3个月内，所有货物运送招标人现场并具备安装条件。 2.6.2 中标方应于合同签订之日起7天内，向招标方提交完整的技术资料，以供设计院开展设备相关设计工作。 3、投标人资格要求 3.1 投标人应符合以下要求： （1）投标人具备有效的营业执照。 注：不得将投标人营业执照记载的经营范围作为评审因素。 （2）具备有效的《中华人民共和国特种设备生产许可证》-压力管道元件制造-元件组合装置。 （3）具有防腐管道元件特种设备型式试验证书。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3本次招标不接受代理商投标，不接受联合体投标。 4、招标文件的获取 4.1 凡愿意参加的潜在投标人，从2026年8 月 19 日起至投标截止时间前，均可登录重庆市公共资源交易网 （www.cqggzy.com）直接下载获取招标文件、答疑等开标前的有关资料。在公告期间，各投标人应随时关注网上 发布的招标文件答疑、补遗、澄清等文件内容，不管投标人是否下载，均视为已知晓招标文件的全部内容和有 关事宜。本项目不需要报名，直接投标。 5、投标文件的递交 5.1 投标文件递交的截止时间为 2026年 9 月 10 日上午09时30分，地点在重庆市公共资源交易中心开标厅 （地址：重庆市两江新区青枫北路6号渝兴广场B10栋2层），具体开标地点详见网一、二楼大厅显示屏。 5.2逾期送达的或者未送达指定地点的，或者未按照招标文件要求密封的投标文件，招标人将拒收。 6、发布公告的媒介 务 本次招标公告在 中国招标投标公共服务平台、重庆市公共资源交易网上发布。 7、联系方式 商 招 标 人：重庆市映天辉氯碱化工有限公司 地 址：重庆长寿经济技术开发区化北路二号 道 联 系 人：张先生 电 话：023-40717888 管 招标代理机构： 重庆招标采购（集团）有限责任公司 地 址：重庆市两江新区国五里店五简路2号重庆咨询大厦A栋20楼2001室 项目负责人：彭文婷 电 话： 023-67703002 中 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）衬氟管道及管件采购 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630011190 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835003139 坝支行 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000000834 贸易试验区分行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146638621 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051302432 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000620855 支行 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020013554 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764235261 信息来源:https://www.chinapipe.net/project/d3076111.html cqdingjiu 2026.08.21 10:06:52</t>
@@ -1950,9 +2386,13 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>重庆, 废盐综合利用, 离子膜烧碱, 衬氟管道, 管件采购</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1985,16 +2425,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>蒸汽管道改造</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>蒸汽管道</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>重庆市益康环保工程有限公司永川分公司蒸汽管道改造项目询价采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3076108.html cqdingjiu 2026.08.21 10:06:52 网 务 商 道 管 国 中</t>
@@ -2006,9 +2454,13 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>重庆, 蒸汽管道, 改造项目, 询价采购</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2041,16 +2493,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>南岸区</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>南岸区</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>包括改造市政混接点194个，改造管网8582米，缺陷管网开挖修复1355米，非开挖修复8679米。</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>总投资概算未明确具体金额，但合同预估金额为6600万元。</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>排水管网改造</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>南岸区融侨大道、江南大道片区2023年排水管网改造项目(三标段)招标计划表 重庆市工程建设项目招标计划表 项目名 南岸区融侨大道、江南大道片区 2023年排水管网改造项目（三标段） 称 网 招标法 人或招 重庆市南岸区城市建设发展（集团）有限公司 标人名称 （盖章） 务 项目批 准文件 南岸发改〔2024〕304《南岸区融侨大道、江南大道片区2023年排水管网改造项目总投资概算的批复》 及文号 主要建 包括改造市政混接点194个，改造管网8582米，商管径d300~d1500;缺陷管网开挖修复1355米，管 设内容 径d300~d600;非开挖修复8679米，管径d300~d1200。 招标文件 拟交 合同预估 招标内 招标 序号 招标项目名称 计划发布 易场 金额(万 备注 道容 方式 时间 所 元) 51处雨 污混错 重庆 招标项 接点位 管 市公 目 改 南岸区融侨大道、江南大道片区 2023年排 公开 共资 1 造，1082 2026-08 6600.00 水管网改造项目（三标段） 招标 源交 个管网 易中 三四级 国 心 缺陷修 复。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 中 信息来源:https://www.chinapipe.net/project/d3076097.html cqdingjiu 2026.08.21 10:06:52</t>
@@ -2062,9 +2530,13 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>重庆, 排水管网改造, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2097,16 +2569,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>永川区</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>永川区</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>项目位于永川区三教镇，项目占地面积41673.42㎡（62.51亩），总建筑面积6078.71㎡，新建净水厂1座，规模5万吨/天，新建厂外管网4.6km（DN200～DN1000），配套建设净水处理系统、排泥水处理系统、综合楼、生产建（构）筑物以及附属建筑物等。</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>项目合同额1.7亿元</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>钢筋混凝土排水管</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购公告 永川三教水厂项目 已具备采购条件，现公开邀请供应商参加询比采购活动。 1.采购项目简介 1.1 采购项目名称：中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购。 1.2 采购方案编号：FA00000663117。 网 1.3 采购人：中交一公局重庆工程有限公司。 1.4 采购代理机构：/。 务 1.5 采购项目资金：已落实 1.6 采购项目概况： 商 永川三教水厂项目：项目位于永川区三教镇，项目占地面积41673.42㎡（62.51亩），总建筑面积6078.71㎡，新建 净水厂1座，规模5万吨/天，新建厂外管网4.6km（DN200～DN1000），配套建设净水处理系统、排泥水处理系统、 综合楼、生产建（构）筑物以及附属建筑物等。项目合同额1.7亿元，工期450天。 道 项目地址：重庆市永川区。 2.采购范围及相关要求 管 2.1 采购范围：钢筋混凝土排水管。 2.2 交货期：2026年9月-2026年12月。 2.3 交货地点：重庆市永国川区项目指定地点。 2.4 物资质量标准：满足《混凝土和钢筋混凝土排水管》（GB/T 11836-2023）的相关要求。 3.供应商资格要求 中 3.1 供应商应依法设立且满足如下要求： （1）资质要求：本次询比采购要求供应商须是在中华人民共和国境内依法注册，具有合法有效的营业执照、税 务登记、组织机构代码等证件，具有独立法人资格、具有采购物资生产经营范围的生产商或代理商（销售商）。 （2）财务要求：供应商必须是经税务部门注册登记核准的纳税人，有依法纳税的良好记录。 （3）业绩要求：无。 （4）信誉要求：无不良履约记录、未列入工程所在地质量监督部门和中国交建、中交一公局集团企业黑名单。 因质量原因被交通部质监站通报，正在进行整改的生产厂家和产品不得参与投标。生产商或代理商（销售商） 具有良好的社会信誉，近3年内没有与骗取合同有关的犯罪或严重违法行为而引起的诉讼和仲裁；近3年不曾在合 同中严重违约或被逐；财产未被接管或冻结，企业未处于禁止或取消投标状态；在最高人民法院、信用中国 （www.creditchina.gov.cn）或各级信用信息共享平台查询拟入库单位无不良行为记录。 （5）其他要求：无。 3.2 供应商不得存在下列情形之一： （1）处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； （2）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （3）已列入黑名单，且未解除限制期限； （4）其他：无。 4.供应商报名 4.1 有意参加询比采购活动的单位，请于2026年8月19日15时00分至2026年8月26日17时00分（北京时间，下同，法 定公休日、节假日不休），登录“中交招采网”（网址：https://zjzcw.iccec.cn）进行报名并下载采购文件。 4.2 已在网并且已通过采购人层级供应商或已增加采购人为合作单位的供应商、上级供应商可直接参与询比采 网 购。在网平级单位供应商未增加采购人为合作单位需进行合作意向申请通过后参与询比采购。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择采购人，审核通过后方可参与询比 采购。 务 5.供应商报价 5.1 报价结束（递交响应文件截止）时间为2026年8月26日17时00分。 商 5.2 供应商应在报价结束时间前，登录“中交招采网”进行线上报价并上传电子响应文件。逾期未完成上传的电 子响应文件，采购人将拒收。 5.3电子采购的供应商响应文件由线上电子报价道表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 子报价表的数据为准。 6.开标 管 6.1 开标时间：与报价结束时间相同。 6.2 开标地点：本次采购在“中交招采网”平台线上开标，不举办现场开标。 国 7.发布公告的媒介 本询比采购公告在 “中交招采网” 上发布。 中 8.评审办法 本项目评审办法采用 经评审的最低价法 。 9.合同主要条款 9.1 付款条件：按月结算，上月11日至本月10日为一个结算对账期，乙方必须按照甲方要求开具合规的增值税专 用发票，无发票不予付款。结算完成后1个月内支付已结算金额的70%，剩余30%货款在结算完成后3个月内支付。 付款方式为银行转账，甲方有权采用票据支付或者供应链支付的方式支付货款，因此产生的费用包含在综合单 价中，乙方不得因此调价和索赔。如遇业主支付不及时，乙方应予理解。 9.2 履约保证金的递交： （1）R不要求递交 （2）要求递交，保证金金额：/，保证金形式：/，其他形式：/ 。 10.监督机构 监督机构名称： 中交一公局重庆工程有限公司审计部 11.成交供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联系400-676-5885，中标服务费请按7咨询。 11.1 收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： 网 （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； （3）在1000万元（含）至3000万元之间的，每次收取1000元； 务 （4）在3000万元（含）至1亿元之间的，每次收取3000元； （5）在1亿元（含）以上的，每次收取5000元。 商 11.2 支付流程 （1）通知推送：中标结果发布后，系统自动推送缴费通知（含应缴金额及支付链接）； 道 （2）费用查询：供应商登录“中交招采网—供应商协同—服务费”模块查看待支付费用； （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 管 （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网— 供应商协同—服务费—发票查询”模块获取。 12.其他 国 / 。 13.联系方式 中 采 购 人：中交一公局重庆工程有限公司 地 址：重庆市江北区创富路5号 邮 编：361021 联 系 人：汪仁宽 电 话：13527572392 电子邮件：1176245792@qq.com 项目联系人及电话： 序号 项目名称 联系人 联系电话 1 永川三教水厂项目 高博 17788661005 中交一公局重庆工程有限公司 2026年8月19日 物资信息 序号 设备物资名称 设备物资说明 税率 单位 网 1 钢筋混凝土排水管 2000mm Ⅲ级 承插口 13% 米 信息来源:https://www.chinapipe.net/project/d3076078.html 务 cqdingjiu 2026.08.21 10:06:52 商 道 管 国 中</t>
@@ -2118,9 +2606,13 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 钢筋混泥土排水管, 永川三教水厂项目</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2153,16 +2645,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标。</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>项目出资比例为100%，资金已落实。</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>施工劳务</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>中国铁路成都局集团有限公司重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施 工劳务招标招标公告 重庆市大渡口区萤石及配套企业 35 千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标公告 招标编号：DXNZBCQ-GC-2026-13 1. 招标条件 本建设项目重庆市大渡口区萤石及配套企业 35 千伏专用变电站项目穿越渝贵等网铁路防护工程施工劳务招标已由 《中国铁路成都局集团有限公司关于重庆市大渡 口 区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防 护工程施工图设计的复函》（科信技审〔2025 〕115号）批准建设，建设单位为重庆建桥置业有限公司，建设资 金使用外委资金，项 目出资比例为100%，资金已落实。招标人为中国铁路成都局集团有限公司重庆工务段。本 项目已具备法定招标条件，现进行公开招标，特邀请有意向的投标人参加投标。 务 2. 项目概况与招标范围 2.1 项目概况 商 2.1.1建设地点：渝贵线K38+838、南疏Ⅰ线K10+808、川黔线K1+622、川黔线K3+781、兴珞上行线K38+619、兴珞 下行线K38+635、小西线K1+633、南疏Ⅱ线K11+257。 2.1.2建设规模：重庆市大渡 口区萤石及配套企道业35千伏专用变电站项目穿越渝贵等铁 路防护工程，本项目工分为5个交叉工点。工点一采用明挖直埋方式下穿渝贵铁路新白沙沱长江多线特大桥第14孔 （渝贵线K38+838）；工点二采用顶进套管方式下穿南疏 Ⅰ 线K10+808（ 已停用）、川黔线K3+781（ 已停用 ）； 工点三采用明挖直埋方式下穿兴珞线陈家湾双线特大桥（上行线K38+619、下行线K38+635）；工点四采用顶进 管 套管方式下穿。 2.2 招标范围：重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标。 即涉铁部分第第三章桥涵，第六章通信、信号、信息及灾害监测，第十章大型临时设施和过渡工程，第十一章 其他费用中的安全生产国费以及非涉铁部分。 2.3标段划分：本项目施工招标划分为1个标段。 2.4计划工期：240日历天，计划开工日期：2026年10月8日，计划竣工日期：2027年6月4日。 中 2.5 其他说明：___/___。 3. 投标人资格要求 3.1本次招标要求投标人为在中华人民共和国境内合法注册的独立法人，具备有效的营业执照、施工企业资质和 安全生产许可证等，并在人员、设备、资金等方面具备相应的施工能力。资格要求如下： 3.1.1 标段编号：全标段 （1）资质要求：施工劳务企业资质。 （2）业绩要求：近3年内完成过铁路营业线类似项目业绩。 （3）项目负责人要求:具有工程师及以上职称，2 年及以上类似铁路营业线项目管理工作经验， 良好的职业道德， 且未在其他在建工程项目任职。 （4）本标段不接受联合体投标申请。 （投标人资格要求详见招标公告附件） 3.2 各投标人可就上述标段中的 1 个标段进行投标。 3.3投标人未在“信用中国”网站（www.creditchina.gov.cn）中被列入失信被执行人名单，投标人未在国家企业信 用信息公示系统（www.gsxt.gov.cn）中被列入严重违法失信企业名单，投标人未被列入铁路工程建设失信行 为“黑名单”，投标人及其法定代表人、拟委派的项目经理在近3年不曾有行贿犯罪记录； 其他信誉要求：未被取消或暂停投标资格、不存在辖内失信的情形、不存在最近一期国铁集团施工企业评价为D 级且在整改期内的情形。 4. 招标文件的获取 4.1凡有意参加投标者，请于2026年08月20日00时00分至2026年08月25日00时00，在重庆龙头寺旅游集散中心（重 庆市两江新区天宫殿街道昆仑大道56号附1号5楼办公室）持单位介绍信获取招标网文件。 4.2招标文件每套售价0元，售后不退。 4.3其他：凡有意参加投标者可通过网上登记获取招标文件，将获取招标文件材料扫描件（PDF格式）发送 务 至dxncq_bgs@163.com邮箱登记，由招标代理人通过电子邮件方式向有意参加投标者发送招标文件。 5. 投标文件的递交 5.1投标文件递交时间为2026年09 月10 日08时30分至2026年商09月10 日09时00分，递交比选申请文件的截止时间（比 选截止时间，下同）为2026年09月10日09时00分，地点为重庆龙头寺旅游集散中心（重庆市两江新区天宫殿街道 昆仑大道56号附1号5楼开标室）。 5.2逾期送达的或者未送达指定地点或者不按照道招标文件要求密封的投标文件，招标代理人不予受理。 6. 发布公告的媒介 本次招标公告在国铁采购平台（https://cg.95306.cn）发布。 管 7. 联系方式 招 标 人：中国铁路成都局集团有限公司 招标代理机构：成都大西南铁路监理 国 重庆工务段 有限公司 地 址：重庆市九龙坡区黄桷坪街道铁 地 址：成都市金牛区站西桥西街305 中 路3村161号 号府河路苑9栋14楼 邮 编： / 邮 编：610081 法定代表人： 法定代表人 或其委托代理人： 或其委托代理人： 联 系 人： 任女士 联 系 人：汤女士 电 话： 17393148353 电 话：023-61896910 传 真： / 传 真： / 电子邮箱： / 电子邮箱：dxncq_bgs@163.com 网 址： / 网 址： / 开户银行： / 开户银行： / 账 号： / 账 号： / 2026年08月19日 附件： 获取招标文件信息表 申请人名称： （加盖公章） 项目名称：（按公告名称填写） 获取招标文件起止时间：（按照公告时间填写） 项目编号：（按照公告填写） 单位名称 经办人 联系电话 电子邮箱 标段 资料提交时间 备注 网 注：须附经办人介绍信、身份证复印件、单位营业执照复印件。 信息来源:https://www.chinapipe.net/project/d3075989.html cqdingjiu 2026.08.21 10:06:53 务 商 道 管 国 中</t>
@@ -2176,7 +2676,11 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2209,16 +2713,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>云阳县</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>云阳县</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>新建污水管网55.5千米，其中DN200管网12千米、DN300管网24千米、DN400管网19.5千米等。</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>合同预估金额：9100.00万元</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>污水管网</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>长江流域云阳青龙段污水管网一体化建设项目招标计划表 重庆市工程建设项目招标计划表 项目名称 长江流域云阳青龙段污水管网一体化建设项目 招标法人或 招标人名称 云阳县青江环境综合整治有限公司 网 （盖章） 项目批准文 云阳发改资环【2025】55号 件及文号 务 主要建设内 新建污水管网55.5千米，其中DN200管网12千米、DN300管网24千米、DN400管网19.5千米等。 容 招标方 招标文件计 拟交易场 合同预估金额 序号 招标项目名称 招标内容 备注 式 划发布时间 所 (万元) 商 长江流域云阳 新建污水管网55.5千米， 重庆市公 青龙段污水管 其中DN200管网12千 公开招 共资源交 1 网一体化建设 米、DN300管网24千 2026-08 9100.00 标 易中心云 项目EPC总承 米、DN40道0管网19.5千 招标项目 阳分中心 包 米等。 新建污水管网55.5千米， 长江流域云阳 重庆市公 其中DN200管网12千 青龙段污水管 公开招 共资源交 2 管米、DN300管网24千 2026-08 140.00 网一体化建设 标 易中心云 米、DN400管网19.5千 项目监理 阳分中心 米等监理。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 国 信息来源:https://www.chinapipe.net/project/d3075867.html cqdingjiu 2026.08.21 10:06:53 中</t>
@@ -2230,9 +2750,13 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 污水管网, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2265,16 +2789,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>重庆轨道交通17号线一期5标段包含金凤北站（不含）～终点（3站5区间的土建）：高龙大道站、斑竹林站、石家院子站、金凤北站～高龙大道站区间、高龙大道站～斑竹林站区间、斑竹林站～石家院子站区间、石家院子站～终点区间、7/17号线联络线区间。采购范围为雨污水排水迁改工程。</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>建设资金来源已落实，但具体资金数额未明确。</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>雨污水排水迁改工程</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>中国电建水电四局华中公司重庆轨道交通17号线一期5标项目雨污水排水迁改工程施工劳务分包采购项目公开询 比采购公告 询比采购公告 采购编号： PC-0104-26J6-FP0895 一、采购条件 受中国水利水电第四工程局有限公司重庆轨道交通17号线一期5标项目委托，中水电四局华中（武汉）工程有限 公司以公开询比方式采购重庆轨道交通17号线一期5标雨污水排水迁改工程项目网，建设资金来源已落实。目前项 目已具备采购条件，现进行公开询比采购。 二、项目概况、采购范围 务 1、项目概况：重庆轨道交通17号线一期5标段包含金凤北站（不含）～终点（3 站5 区间的土建）：高龙大道 站、斑竹林站、石家院子站、金凤北站～高龙大道站区间、高龙大道站～斑竹林站区间、斑竹林站～石家院子 站区间、石家院子站～终点区间、7/17号线联络线区间。 2、采购范围： 商 （1）雨污水排水迁改工程 （2）工程招标范围工作内容：17号线一期5标道中高龙大道站、斑竹林站及高斑竖井位于城市既有道路下方，设计 采用明挖法施工。为保证市政排水管网的正常使用，在明挖施工前需对既有管网进行临时迁改，车站结构施工 后进行恢复。施工PE钢带管长度2387米、B型排水管长度2799m、钢筋混凝土管127米，检查井239座劳务部分。 （3）施工内容详见工程量清单，以及为完成此项工程而做的一切工作。 管 3、计划工期:计划开工日期：2026年9月25日（具体时间以采购人通知为准），计划完工日期：2027年 12 月25 日； 合同工期总日历天数为457天。 4、质量要求：符合《国给水排水管道工程施工及验收规范》（GB 50268）、《混凝土结构工程施工质量验收规范》 （GB 50204）、《城镇道路工程施工与质量验收规范》（CJJ 1-2008）以及项目所在地最新的相关法规、标准和 图集。工程质量全面达到设计要求和标准，其中：验收合格率 100%，优良率达 90%以上，工程综合验收质量评 定达优良标准。 中 5、付款方式：采用银行转账/支票支付工程价款，月度结算完成具备付款条件后30天内工程进度款支付比例约定 为扣除各项保证金及费用后应付价款不低于65%；清算完成并签订《退场协议》后30天内工程进度款支付比例约 定为扣除各项保证金及费用后应付价款不低于80%；清算完成并签订《退场协议》后一年内工程进度款支付比例 约定为扣除响应人缺陷责任等相关费用后应付价款不低于90%；清算完成并签订《退场协议》，办理完成保证金 退还手续后两年内，工程进度款支付比例约定为扣除响应人缺陷责任等相关费用后应付价款的100%。 6、其他：无。 三、响应人资格要求 响应人必须满足以下全部资格要求： （1）资质要求：施工劳务不分等级 （2）主要人员要求:授权委托人（如有）及项目经理、专职安全员应提供社保和劳动合同。其中劳动合同至少提 供首、末两页，并且包含有关人员的详细信息;社保证明应提供响应截止时间前三个月的社保缴纳记录。 （3）安全三类人员要求:应提供企业主要负责人安全A证、项目经理B证、专职安全员C证。 （4）响应人具有良好的银行资信和商业信誉，没有处于被责令停业，财产被接管、冻结、破产状态。 （5）响应人应具有 雨污水排水迁改 工程的施工业绩，在近 5年内(2021年7月-2026年7月内签订)的施工合同不少 于 1 个，且签订单项合同金额均在 100 万元以上（应附成交通知书和（或）合同扫描件）。 （6）其它要求:无。 （7）本次采购不接受联合体响应。 四、采购文件的获取 凡满足本公告规定资格要求并有意参加的响应人，请于2026年8月22日10时00分前在中国电建采购招标数智化平台 （https://bid.powerchina.cn/bidweb/#/login，以下简称“数智化平台”）获取采购文件，采购文件免费提供。 五、响应文件的递交 1、响应文件递交的截止时间（响应截止时间，下同）为2026年8月26日10时30分网（北京时间），响应人应在截止 时间前通过数智化平台递交电子响应文件。 2、本次采购将通过数智化平台全程在线开展，电子响应文件的加密、提交等流程须响应人在线进行操作。响应 人须提前办理数字证书用于在线递交响应文件，办理方式详见数智化平台首页，并严格按照要求进行在线操作， 务 因操作流程失误造成的递交失败将由响应人自行承担后果。 3、开启由“数智化平台”在响应截止时间后自动对响应文件进行解密，响应人及时关注开启结果。 4、响应截止时间如有变动，采购人将及时通知已获取采商购文件的响应人。 六、发布公告的媒介 本次询比采购公告同时在中国电建阳光采购网道（https://bid-zb.powerchina.cn）上发布。 七、评审办法 采用综合评估法。 管 八、联系方式 采 购 人： 中水电四局华中（武汉）工程有限公司 国 地 址： 湖北省武汉市江岸区塔子湖东路健美街30号立城中心商务楼13、14层 邮 编： 430014 中 联 系 人： 王飞 电 话： 15827222587 电子邮箱： 107830343@qq.com 九、提出异议的渠道和方式 单位名称： 中水电四局华中（武汉）工程有限公司 电 话： 17708178186 电子邮箱： sjhzgsjw@163.com 十、纪检监督机构 响应人或者其他利害关系人认为本次采购活动存在违规违纪行为的，可以书面形式向中国水利水电第四工程局 有限公司中水电四局华中（武汉）工程有限公司纪委办公室（联系方式：17708178186）提出投诉。 2026年8月 19 日 报价网址:https://bid.powerchina.cn/notice/detail?id=2409510708 信息来源:https://www.chinapipe.net/project/d3075750.html cqdingjiu 2026.08.21 10:06:53 网 务 商 道 管 国 中</t>
@@ -2286,9 +2818,13 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>重庆, 轨道交通, 雨污水排水迁改, 施工劳务分包</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2321,16 +2857,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>本项目涉及预制钢筋砼管、成品混凝土仿木栏杆等材料的采购。</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>建设资金为国债资金，项目出资比例为100%。具体预算金额未在文本中明确列出。</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>预制钢筋砼管,成品混凝土仿木栏杆</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>万州区2026年超长期特别国债高标准农田建设项目拟进行预制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜的 信息公告 1.采购条件 1.1本项目万州区2026年超长期特别国债高标准农田建设项目工程已由 重庆市万州路桥建设有限公司承建，项目 业主为重庆市万州区农业技术与机械推广中心，代建业主为重庆市万州区农业发展有限公司，建设资金为国债 资金，项目出资比例为 100% ，承包人为重庆市万州路桥建设有限公司。项目已具备施工条件，现对该项目的预 制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜发布信息公告。 网 2.项目概况与采购范围 2.1建设地点：重庆市万州区走马镇、瀼渡镇、罗田镇、余家镇、高梁镇、分水镇、柱山乡等7个镇乡。 务 2.2本项目材料采购拟进行比选情况如下： 罗田镇谷山片区材料采购费暂定金额约： 17.5万元； 余家镇桥亭片区材料采购费暂定金额约： 17.99万元； 商 柱山乡山田片区材料采购费暂定金额约： 26.32 万元； 走马镇凉风片区材料采购费暂定金额约： 15.道66万元； 瀼渡镇高村片区材料采购费暂定金额约： 17.72 万元； 分水镇大冲片区材料采购费暂定金额约： 47.12 万元； 管 高梁镇茨坪片区材料采购费暂定金额约： 10.7万元； （以上片区片区金额为暂定金额，最终比选限价金额以比选文件为准）。 国 2.3计划采购周期： 以合同签订为准 日历天。 2.4采购范围：本项目各片区所包含的预制钢筋砼管、成品混凝土仿木栏杆等材料。 中 3.供应商资格要求 3.1本次材料采购要求供应商具备独立企业法人，具有本次所需材料生产能力的厂家或经销商等，其经营范围和 权限应满足本次所需材料的要求，并依法取得国家行政主管部门颁发的有效工商营业执照(建筑材料销售或水泥 制品制造、水泥制品销售等相关营业资格），所提供产品必须满足各项检测要求，达到国家现行标准规定的合 格标准。具有良好的商业信誉和充分的供应保障能力，具备相应售后服务能力。要求竞选人为一般纳税人，可 开具13%税率增值税专用发票，提供一般纳税人认定证明。 3.2本次供应商单位优先选择万州本地企业。 3.3本次 不接受 联合体竞选。 4. 报名要求 4.1报名时间：2026年8月 19日9:00起至 8月21日17:00止。 4.2报名地点：重庆市万州路桥建设有限公司经营部（重庆市万州区天城东路278号）。 4.3报名时，须提交有效的营业执照(有效工商营业执照((建筑材料销售或水泥制品制造、水泥制品销售等相关营 业资格）)，前述证书均为复印件并加盖单位公章。法定代表人参加报名的不需要授权委托书，只需要提供法定 代表人身份证明；非法定代表人参加报名的除提供法定代表人身份证明外还须提供授权委托书、委托代理人身 份证明。 4.4 本项目材料采购需提前报名。经资格预审合格后，通知资格预审合格的供应商，到承包人单位领取相关文件。 4.5本项目材料采购设七个片区进行比选，为保证比选公平、公正、有效，规定同一参选单位报名片区上限为2个， 且最终仅限中选一个片区。 5.联系方式 承包人：重庆市万州路桥建设有限公司 地 址：重庆市万州区天城东路278号 网 联系人： 张红娟 电 话：15923491915 务 邮 箱： 商 重庆市万州路桥建设有限公司 2026年8月19日 道 信息来源:https://www.chinapipe.net/project/d3075512.html cqdingjiu 2026.08.21 10:06:53 管 国 中</t>
@@ -2342,9 +2894,13 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>重庆, 预制钢筋砼管, 成品混凝土仿木栏杆, 国债资金, 高标准农田建设</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2377,16 +2933,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>酉阳土家族苗族自治县</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>酉阳土家族苗族自治县</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资(污水管道)公开招标采购。</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>污水管道</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资(污水 管道)招标采购流标公告 发布单位：中国铁建/中铁十一局/六公司 发布时间：2026-08-19 10:40:49 投标截至时间：2026-08-18 10:00:00 内容： 各投标人： 网 中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资（污水 管道）公开招标采购（采购编号： CR1106-JC-2026-26-02）评标工作，已于北京时间2026年08月18日10:00整，在 铁建云链（https://www.crccep.com）线上平台公开开标。评审委员会根据招标文件载明的评审办法完成评审工作， 现将评审结果公示如下： 务 一、招标公告发布日期及媒体 招标公告发布日期：2026年07月27日至2026年08月01日 商 招标公告媒体：铁建云链（https://www.crccep.com） 二、拟中标信息 道 公开招标采购编号：CR1106-JC-2026-26-02 包件号：WSGD-01 序号 供应商名称 推荐排序 管 1 无 1 国 以上包件有效投标不足三家，本次招标做流标处理。 三、公示时间 中 自2026年08月19日始，至2026年08月22日止。在公示期间，所有竞标人和其他利害关系人如对公示的评审结果有 异议，可以向相关监督部门举报，逾期将不再受理。举报人必须由其法定代表人或者授权代表签字并盖章，其 他组织或者个人举报的，必须由其主要负责人或者本人签字，并附有效身份证明复印件。举报人如实反映情况 受法律保护。 公示期满，如无异议，即时生效。 监督竞诉受理部门： 中铁十一局集团第六工程有限公司招采中心 联系电话：18671041790 信息来源:https://www.chinapipe.net/project/d3075461.html cqdingjiu 2026.08.21 10:06:53</t>
@@ -2398,9 +2970,13 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 酉阳县, 污水管网, 新建改造工程</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2433,16 +3009,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>详见附件。</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>镀锌管件</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>协同创新区-四期房建三标段镀锌管件物资竞价采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3075420.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
@@ -2454,9 +3038,13 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 商机</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2489,16 +3077,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>渝北区</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>渝北区</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>长江一级支流溉澜溪流域(新华水库混流箱涵)污水收集效能提升工程(渝北区)施工答疑补遗文件</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>长江一级支流溉澜溪流域(新华水库混流箱涵)污水收集效能提升工程(渝北区)施工答疑补遗文件 长江一级支流溉澜溪流域（新华水库混流箱涵）污水收集效能提升工程（渝北区）施工答疑文件 各潜在投标人： 现将“长江一级支流溉澜溪流域（新华水库混流箱涵）污水收集效能提升工程（渝北区）施工”公开招标项目 答疑文件发布。本答疑文件是在招标文件的基础上作出的澄清、说明或补正，与招标文件具有同等法律效力， 若相关内容与原招标文件不一致时，一律以本答疑文件内容为准。 网 一、答疑部分： 问题一：1、我公司于2026年进行了优势合并整合，现准备使用合并前公司项目业绩作为本次我司投标的投标人 业绩证明，并提供上级主管单位出具的相关吸收合并文件或两家公司签订的吸收合并协议，请问是否可视为满 务 足招标业绩要求？ 2、我单位为中型企业，其控股股东为大企业，但我单位不属于大企业的分支机构，也不存在与大企业的负责人 为同一人的情形。鉴于此种情况，我单位应提供《中小企业声明函（工程类）》还是《中小企业承担合同份额 承诺函》？ 商 回复：1. 满足，但还需满足招标文件对业绩的其他要求。最终由评标委员会根据投标人提供的证明材料并结合 招标文件要求进行评审； 道 2. 贵司其控股股东为大企业，故需提供中小企业承担合同份额承诺函。 问题二：本项目有无业主专家参与评标？ 管 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 问题三：请明确是否有业主专家 是否异地评标 回复：1. 该项目评标委国员会由招标人按法律法规及相关规定依法组建。 2.本项目是异地评标。 问题四：1、财务报告可以不提供财务报表附注吗? 中 2、投标函附录中，工期、分包、工程质量、缺陷责任期等要求可以统一填写"达到招标文件要求"吗? 3、招标文件第八章投标文件格式中(二)承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要提供其 他格式之外的其他承诺? 4、是否有业代专家参与评标，不要模糊的回答什么依法组建评标委员会。请明确回复有或者没有。 5、本项目是否异地评标？ 6、业绩竣工验收证明材料中有单位盖的项目部章是否认可呢？ 回复：1. 可以不提供财务报表附注。 2. 可以统一填写"达到招标文件要求"。 3. 投标人自行核实招标文件要求提供的承诺要求，如有需要，还需补充提供招标文件第八章投标文件格式中 （二）承诺部分之外的其他承诺。 4. 该项目评标委员会由招标人按法律法规及相关规定依法组建。 5. 本项目是异地评标。 6. 不认可。 问题五：请问**公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，因为不能履行保函的见索即 付，拒绝赔付。 相关业主方在招标文件补遗通知中直接将**公司列入担保公司回避名单，拒绝**公司所出具的保函。由此可 见**公司的信用资质、履约能力、根本无能力是存在很大问题的。请问以**公司目前的被执行和不履行投标担保 责任的情况是否符合招标文件的要求? 回复：纸质投标保函的开立人应当是具有相应资格的银行、保险机构、融资担保公司，其信用资质、履约能力、 担保能力、赔付流程、安全保密等应符合工程保函业务条件。纸质投标保函应合网法合规，符合招投标行政监督 部门、行业主管部门和金融监管部门的相关规定，满足招标文件约定要求。投标人应选择在渝依法设立总部或 者设有分支机构的金融机构开具纸质投标保函。投标人对所提交的纸质投标保函的真实性、合法性、有效性负 责。以纸质投标保函形式交纳投标保证金是否符合招标文件要求，由评标委员会评标时，根据招标文件要求进 行独立评审，并作出相应评审判断。 务 问题六：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 回复：经核实，招标文件（PDF签章版）中投标文件格式商与重庆市电子招投标系统投标文件制作软件中格式一致。 可能因重庆市电子招投标系统投标文件制作软件中的格式页边距与招标文件（PDF签章版）不一致的原因导致格 式显示不一致，该情形不影响投标人编制投标文件。若重庆市电子招投标系统投标文件制作软件导出的投标文 件格式与招标文件（PDF签章版）的投标文件格式不一致，以重庆市电子招投标系统投标文件制作软件导出的投 标文件格式为准。 道 问题七：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖 章，请问需要提供联合体协议书吗？ 管 回复：若投标人提供的公司业绩为epc业绩，且合同协议书或工程竣工验收合格的证明材料或业主证明能证明该 投标人承担的工作为施工任务的，则不需要提供联合体协议书；若投标人提供的公司业绩为epc业绩，但合同协 议书或工程竣工验收合格的证明材料或业主证明不能证明该投标人承担的工作为施工任务的，则需要提供联合 体协议书。 国 问题八：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可 以不填(空白)，对此有无要求？ 回复：投标中文件中下划线上、空格处、表格中无需要填写或无法填写内容的，填“/”或“无”均可。 问题九：公园施工业绩符合吗？ 回复：公园概念太宽泛，无法判定该施工业绩是否属市政工程，请投标人自行核实，并按招标文件要求提供施 工业绩证明材料，其是否满足要求应由评标委员会根据证明材料具体内容进行判定。 问题十：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需 要提供其他格式之外的其他承诺？ 回复：投标人自行核实招标文件要求提供的承诺要求，如有需要，还需补充提供招标文件第八章投标文件格式中 （二）承诺部分之外的其他承诺。 问题十一：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收， 请问我公司业绩满足业绩要求吗？ 回复：不满足。 问题十二：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗？ 回复：投标人投标总报价低于招标文件规定的对应的异常低价警戒线的，应提供报价合理性说明，并提供必要 的证明材料。证明材料由投标人自行提供，但提供的说明不得降低或者改变原设计方案、技术工艺、施工标准， 不得影响项目的质量、安全、工期、结算等正常履约。 问题十三：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 回复：按照招标文件要求“提供：会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表，财务 报表须至少包括现金流量表、资产负债表、利润表”。 问题十四：业绩要求的竣工时间是指竣工验收时间吗？ 回复：本项目业绩要求所指竣工时间，即为工程竣工验收合格证明载明的竣工验收时间。 问题十五：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知 书发出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面网通知相关金融机构本项目准 予提前注销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 回复：纸质投标保函原件上未加盖“正本”字样的，不因此否决投标，但投标人应确保提交的保函为唯一正本。 若因保函真伪问题导致的一切不利后果由投标人自行承担。 务 问题十六：燃气管道安装施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 商 问题十七：请问招标人是否委派业主专家参与评标吗？ 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 道 问题十八：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 回复：根据招标文件“投标人的工程量清单单项报价不得为零报价（招标人提供的工程量清单单项最高限价中 金额为零的除外）或者负数报价”，招标人提供的工程量清单单项最高限价中金额为零的，该项清单综合单价 管 报价可以为0。 问题十九：自来水厂或者净水厂施工业绩满足业绩要求吗？ 回复：满足，但还需满国足招标文件对业绩的其他要求。 问题二十：财务报告可以不提供财务报表附注吗？ 回复：可以不提供财务报表附注。 中 问题二十一：老旧小区室外环境改造施工业绩符合吗？ 回复：不满足。 问题二十二：有人提出一个无关问题。 回复：无关问题不予回复。 问题二十三：任一清单的综合单价低于警戒线，就要提供说明吗？ 回复：本招标项目单项报价未设置异常低价警戒线。 问题二十四：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题二十五：本项目是异地评标吗？ 回复：本项目是异地评标。 问题二十六：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、 注册证及在本单位注册的证明文件替代？ 回复：不满足。 问题二十七：污水处理厂提标改造施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题二十八：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 回复：可以填“达到招标文件的要求”。 问题二十九：财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加网强审计报告查验工作的通知》 中要求会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第十四条规定审计业务出具的报告 （以下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标 人提供的财务报告需要赋码和提供深度查询截图吗？ 务 回复：投标人提供的财务报告不需要赋码和提供深度查询截图。 问题三十：有人提出一个无关问题。 回复：无关问题不予回复。 商 问题三十一：我公司业绩合同金额3600万元及以上，但是竣工报告业绩金额小于3600万元，请问是否满足业绩要 求？ 道 回复：按招标文件执行。“当上述业绩证明材料中针对同一指标存在不一致时，以工程竣工验收合格的证明材 料为准”。 问题三十二：专业分包业绩满足业绩要求吗？ 管 回复：专业分包业绩可满足业绩要求，但还需满足招标文件对业绩的其他要求。 问题三十三：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养 老保险证明材料复印件国递交吗？ 回复：不需要。 问题三十四：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要 中 求”吗？ 回复：可以统一填写“达到招标文件要求”。 问题三十五：市政桥梁施工业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题三十六：有人提出一个无关问题。 回复：无关问题不予回复。 问题三十七：本项目委派业主专家吗？ 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 特别提示：本通知与招标文件具有同等法律效力，若招标文件与本通知不一致时，一律以本通知为准。 招标人：重庆水务环境控股集团管网有限公司 招标代理机构：重庆市工程管理有限公司 2026年8月19日 信息来源:https://www.chinapipe.net/project/d3075975.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
@@ -2512,7 +3116,11 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2545,16 +3153,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>新建一体化提升泵站及管道约5000m，投资约800万元。</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>投资约800万元</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>施工</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>中化重庆涪陵化工搬迁后污水处理厂建设项目招标计划表 重庆市工程建设项目招标计划表 项目名称 中化重庆涪陵化工搬迁后污水处理厂建设项目 招标法人或 招标人名称 重庆市涪陵交通旅游建设投资集团有限公司 网 （盖章） 项目批准文 涪发改委发[2019] 505号 件及文号 务 主要建设内 新建一体化提升泵站及管道约5000m，投资约800万元。 容 招标 招标 招标文件计 拟交易 合同预估 序号 招标项目名称 备注 内容 方式 划发布时间 场所 金额(万元) 商 本招标计划与2026年5 月25日发布的招标项目 中化重庆涪陵 重庆市 名称为“中化重庆涪陵 招标项目 化工搬迁后污 涪陵区 公道开 化工搬迁后污水处理厂 1 水处理厂建设 施工 2026-09 公共资 800.00 招标 建设项目（场外连接管 项目（场外干 源交易 网）”的招标计划，除 管部分） 中心 招标项目名称调整外， 其余内容完全一致。 管 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075591.html cqdingjiu 2026.08.21 10:国06:54 中</t>
@@ -2566,9 +3190,13 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标, 商机</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2601,16 +3229,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>綦江区</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>綦江区</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>对三江污水处理站、綦齿园污水处理厂、信家岩污水处理站的设施设备进行更新改造，包括配电柜、风机、污水提升泵、在线监测等设备的更新更换，以及对工艺落后的污水厂完成工艺技改；北渡污水厂、赶水污水处理厂、工业园区污水厂、食品园污水厂零星设施更新等。</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>上级补助和业主自筹，项目出资比例为100%，本项目工程总投资金额约1327.40万元</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>污水处理设施设备</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>綦江区污水处理厂设施设备更新改造工程(二期)招标公告 1.招标条件 本招标项目 綦江区污水处理厂设施设备更新改造工程（二期） 已由 重庆市綦江区发展和改革委员会 以 重庆市企业投资备案证（项目代码：2502-500110-04-01-844057） 批准建设，项目业主为 重庆南州城市管 理服务有限公司 ，建设资金来自 上级补助和业主自筹 ，项目出资比例为 100% ，招标人为 重庆南州 城市管理服务有限公司。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用经评审的最低 投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 綦江区 2.2 项目概况与建设规模：对三江污水处理站、綦齿园污水处理厂、信家岩污水处理站的设施设备进行更新改造， 务 包括配电柜、风机、污水提升泵、在线监测等设备更新更换，以及对工艺落后的污水厂完成工艺技改；北渡污 水厂、赶水污水处理厂、工业园区污水厂、食品园污水厂零星设施更新等。 2.3 本项目工程总投资金额： 约1327.40万元 商 2.4 招标范围： 本项目设计施工图和招标文件、答疑、补遗、工程量清单等资料所涉及的全部内容。 2.5 工期要求： 180日历天 道 缺陷责任期要求： 24个月 2.6 标段划分（如有）： / 管 2.7 其他： / 3.政府采购工程 国 3.1 是否属于政府采购工程：否 4.投标人资格要求 中 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（綦江区） （https://www.cqggzy.com/qijiangweb/）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重 庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏 “主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网（綦江区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-22 18:00:00前。 5.3招标人应于2026-09-11 18:00:00前在重庆市公共资源交易网（綦江区）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-28 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（綦江区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆南州城市管理服务有限公司 代理机构: 永卓国际工程技术有限公司 地 址: 重庆市綦江区红星美凯龙生活广场3幢19-3 地 址: 两江新区网泰山大道东段98号2幢10-12号 邮 编: 邮 编: 项目负责人: 赵老师 项目负责人: 廖淼 电 话: 023-48690537 电 话: 务023-60391733 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 商开户银行: 账 号: 账 号: 监督部门: 道 电 话: 2026年08月18日 綦江区污水处理厂设施设备更新改造工程（二期） 管 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051287453 中国农业银行股份有限公司重庆自由贸 重庆联合产权交易所集国团股份有限公司 312601010400083780000031123 易试验区分行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146631326 信息来源:https://www.chinapipe.net/project/d3075589.html 中 cqdingjiu 2026.08.21 10:06:54</t>
@@ -2622,9 +3266,13 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>重庆, 綦江区, 污水处理厂, 设施设备更新改造, 管材招标</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2657,16 +3305,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>南岸区</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>南岸区</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>本工程主要内容包括新（改）建峡口、道迎龙片区4个乡镇DN20～DN300农村供水管网81km，新建3座一体化智慧加压泵站。对朱家岩水厂进行升级改造：更换陈旧、老化的工艺、电气设备及自控、仪表系统，对全厂进行智能化、标准化改造，增加高级工艺控制系统，建设智能化、标准化的农村供水区级管理平台。</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>概算批复工程建安费2975.27万元。</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>农村供水管网、智慧加压泵站、水厂升级改造、智能控制系统、加药系统、金属防腐工程、入户管道、入户水表、监测计量基础设施。</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>南岸区峡口、迎龙片区农村供水保障提升工程招标计划表 重庆市工程建设项目招标计划表 项目 南岸区峡口、迎龙片区农村供水保障提升工程 名称 招标 网 法人 或招 标人 重庆市江南城市建设发展（集团）有限公司 名称 务 （盖 章） 项目 批准 商 文件 南岸发改﹝2026﹞156号 及文 号 本工程主要内容包括新（改）建峡口、道迎龙片区4个乡镇DN20～DN300农村供水管网81km，新建3座一体 主要 化智慧加压泵站。对朱家岩水厂进行升级改造：更换陈旧、老化的工艺、电气设备及自控、仪表系统， 建设 对全厂进行智能化、标准化改造，增加高级工艺控制系统，建设智能化、标准化的农村供水区级管理平 内容 台。概算批复工程建安费2975.27万元。 管 拟 招 招标文 合同预 招标 交 序 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 国 所 南岸 重 区峡 庆 口、 中 市 迎龙 朱家岩水厂升级改造工程：对全厂老旧设备进行设备更新；对全 公 片区 公 厂进行智慧化改造，增加高级工艺控制系统；对厂区建筑和构筑 共 农村 开 1 物修缮；优化加药系统投加模式，增加精确加药系统；对全厂部 2026-08 资 1600.00 供水 招 分老旧管道进行更换；金属防腐工程，对金属设备和管道的防锈 源 保障 标 刷漆工作。 交 提升 招标 易 工程 项目 中 （一 心 标段） 南岸 重 区峡 庆 口、 市 迎龙 公 片区 管网工程：延伸、改造峡口镇、迎龙镇等4个乡镇 46 公里 公 共 农村 DN40~DN300 配水主支管，36公里 DN20入户管道，新建3座一体 开 2 2026-08 资 1300.00 供水 化智慧加压泵房，入户水表改造 1752 户，并配套建设监测计量 招 源 保障 基础设施。 标 交 提升 易 工程 中 （二 心 标段） 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075572.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
@@ -2678,9 +3342,13 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>重庆, 农村供水保障提升工程, 管材招标, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2713,16 +3381,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>北碚区</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>北碚区</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>工程建设区域为东阳及天府片区，主要建设内容包含改造供水管网437千米，其中DN200供水主要建设内容管网35千米，DN100~DN150供水管网82千米，DN100以下供水管网320千米，并配套建设管网附属设施。</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>合同预估金额为8457万元</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>供水管网</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>北碚区东阳天府片区农村供水提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 北碚区东阳天府片区农村供水提升工程 招标法人或招 标人名称（盖 重庆北碚文旅产业发展有限公司 网 章） 项目批准文件 及文号 务 工程建设区域为东阳及天府片区，主要建设内容包含改造供水管网437千米，其中DN200供水 主要建设内容 管网35千米，DN100~DN150供水管网82千米，DN100以下供水管网320千米，并配套建设管网 附属设施。 招标项目名 招标内 招标方 招标文件计划 拟交易场 合同预估金 序号 商 备注 称 容 式 发布时间 所 额(万元) 北碚区东阳 招标项目 重庆市公 天府片区农 施工招 公开招 1 2026-08 共资源交 8457.00 村供水提升 标 道标 易中心 工程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075569.html 管 cqdingjiu 2026.08.21 10:06:55 国 中</t>
@@ -2734,9 +3418,13 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 农村供水提升工程, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2769,16 +3457,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>改造取水泵站一座，改造DN600供水管网2.9km，DN50~DN300供水管网88.863km，DN25供水管网68.5km及其附属设施。</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>合同预估金额：8741.00万元</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>供水管网及相关附属设施</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>北碚区澄江片区农村供水提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 北碚区澄江片区农村供水提升工程 招标法人或招标 重庆北碚文旅产业发展有限公司 人名称（盖章） 网 项目批准文件及 文号 改造取水泵站一座，改造DN600供水管网2.9km，DN50~DN300供水管网88.863km，DN25供 主要建设内容 务 水管网68.5km及其附属设施。 招标项目名 招标文件计划 合同预估金 序号 招标内容 招标方式 拟交易场所 备注 称 发布时间 额(万元) 招标项目 北碚区澄江 商重庆市公共 1 片区农村供 施工招标 公开招标 2026-08 资源交易中 8741.00 水提升工程 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 道 信息来源:https://www.chinapipe.net/project/d3075568.html cqdingjiu 2026.08.21 10:06:55 管 国 中</t>
@@ -2790,9 +3486,13 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标, 商机</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2807,7 +3507,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2825,16 +3525,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>主要改造及延伸配水管188.2千米，新建加压泵站4座，新建计量监测设施建设以及配套电气工程。</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>预算金额为3137.22万元</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>管道、加压泵站、计量监测设施、电气设备</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>涪陵区江东街道农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区江东街道农村供水保障能力提升工程（二期） 名称 招标 法人 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 项目 网 批准 文件 涪陵发改〔2026〕471号 及文 号 主要 改造及延伸配水管 188.2千米，新建加压泵站4座，新建计量监测设施 建设 以及配套电气工程。 务 内容 招 标 合 文 同 招 件 预 招标 标 招标方 计 拟交易 备 序号 招标项目名商称 估 项目 内 式 划 场所 注 金额 容 发 (万 布 元) 时 间 重 道 庆 市 涪 陵 公 区 改造及延伸配水管 188.2千米，新建加压泵站4座，新建计量监测设施 开 公 1 涪陵区江东街道农村供水保障能力提升工程（二期） 2026-09 3137.22 管以及配套电气工程。 招 共 标 资 源 交 易 中 心 国 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075558.html cqdingjiu 2026.08.21 10:06:55 中</t>
@@ -2846,9 +3562,13 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2863,7 +3583,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2881,16 +3601,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>改造荣桂水厂老化、破损、生锈的输水管道7.36公里。马武水厂增设废水回收及污泥浓缩系统1套。荣桂水厂增设废水回收及污泥浓缩系统1套。新建配水管道总长0.74公里；改造配水管道总长139.42公里。新建1座微型集成泵房及改造1座泵站(原牌坊泵站)。新增管网监测设施40套。</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>预估合同金额为3236.36万元人民币</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>输水管道、废水回收及污泥浓缩系统、配水管道、微型集成泵房、泵站、管网监测设施</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>涪陵区龙桥街道农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 涪陵区龙桥街道农村供水保障能力 项目名称 提升工程 招标法人 或招标人 重庆水务环境控股集团渝东自来水 名称（盖 有限公司 章） 网 项目批准 文件及文 涪陵发改〔2026〕466号 号 改造荣桂水厂老化、破损、生锈的 务 输水管道7.36公里。马武水厂增设 废水回收及污泥浓缩系统1套。荣 桂水厂增设废水回收及污泥浓缩系 主要建设 统1套。新建配水管道总长0.74公里； 商 内容 改造配水管道总长139.42公里。新 建1座微型集成泵房及改造1座泵 站(原牌坊泵站)。新增管网监测设 施40套。 道 招标 合同 招 文件 预估 标 招标方 拟交易 备 招标项目 序号 招标项目名称 计划 金 内 式 场所 注 管 发布 额(万 容 时间 元) 改造荣桂水厂老化、 破损、生锈的输水管 国 道7.36公里。马武水厂 增设废水回收及污泥 重庆 浓缩系统1套。荣桂水 市涪 厂增设废水回收及污 公 陵区 中 涪陵区龙桥街道农村供水保障能力 泥浓缩系统1套。新建 开 1 2026-09 公共 3236.36 提升工程 配水管道总长0.74公里； 招 资源 改造配水管道总 标 交易 长139.42公里。新建1 中心 座微型集成泵房及改 造1座泵站(原牌坊泵 站)。新增管网监测设 施40套。 本计划表所列招标项目信息均为暂 备注 定，最终以实际招标时的信 信息来源:https://www.chinapipe.net/project/d3075556.html cqdingjiu 2026.08.21 10:06:55</t>
@@ -2902,9 +3638,13 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>涪陵区龙桥街道, 农村供水保障能力提升工程, 输水管道, 废水回收及污泥浓缩系统, 配水管道, 微型集成泵房, 泵站, 管网监测设施</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2919,7 +3659,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2937,16 +3677,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>整治De315原水管长1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1套及配套电气工程。</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>合同金额1489.90万元</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>管材、水泵、加压泵站、废水处理系统、电气工程</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>涪陵区百胜镇农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区百胜镇农村供水保障能力提升工程 名称 招标 法人 或招 标人重庆水务环境控股集团渝东自来水有限公司 名称 网 （盖 章） 项目 批准 文件涪陵发改〔2026〕465号 及文 号 务 主要 建设整治 De315原水管长 1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1套及配套电气工程。 内容 招 拟 标 招招标文 合同预 交 序项 标件计划 估金 备 招标内容 易 号目 方发布时 额(万 注 场 名 商 式间 所 元) 称 涪 陵 区 重 百 庆 胜 市 招标 镇 涪 项目 农 道 陵 村 公 区 供整治 De315原水管长 1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1开 公 1 2026-09 1489.90 水套及配套电气工程。 招 共 保 标 资 障 源 能 交 力 易 提 中 管 升 心 工 程 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075553.html 国 cqdingjiu 2026.08.21 10:06:55 中</t>
@@ -2958,9 +3706,13 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>涪陵区百胜镇, 农村供水保障能力提升工程, 管材招标, 重庆</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2993,16 +3745,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>对清溪水厂原取水口进行改造。改造清溪厂输水管道长6.38公里。清溪水厂新建3000m³/d集成水厂1套，增设废水回收及污泥浓缩系统1套。新建配水管道总长2.46公里。改造配水管道总长145.04公里。四合村泵站增加1套备用加压泵。新增管网监测设施35套。</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>合同预估金额：2888.89万元</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>集成水厂、输水管道、配水管道、加压泵、管网监测设施</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>涪陵区清溪镇农村供水保障能力提升工程招标计划 重庆市工程建设项目招标计划表 项目名称 涪陵区清溪镇农村供水保障能力提升工程 招标法人 或招标人 重庆水务环境控股集团渝东自来水有限公司 网 名称（盖 章） 项目批准 文件及文 涪陵发改〔2026〕467号 务 号 对清溪水厂原取水口进行改造。改造清溪水厂输水管道长6.38公里。清溪水厂新建3000m3/d集成水 主要建设 厂1套，增设废水回收及污泥浓缩系统1套。新建配水管道总长2.46公里。改造配水管道总长145.04 内容 公里。四合村泵站增加1套备用加压泵。新商增管网监测设施35套。 招标项目 招标方 招标文件计 拟交易场 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 所 (万元) 对清溪水厂原道取水口进行 改造。改造清溪水厂输水 管道长6.38公里。清溪水厂 涪陵区清 新建3000m3/d集成水厂1套， 重庆市涪 招标项目 溪镇农村 增设废水回收及污泥浓缩 公开招 陵区公共 管 1 供水保障 2026-09 2888.89 系统1套。新建配水管道总 标 资源交易 能力提升 长2.46公里。改造配水管道 中心 工程 总长145.04公里。四合村泵 站增加1套备用加压泵。新 国 增管网监测设施35套。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075552.html 中 cqdingjiu 2026.08.21 10:06:55</t>
@@ -3014,9 +3782,13 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3031,7 +3803,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3049,16 +3821,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>改造11000m³/d(旺水垭6000m³/d和二水厂5000m³/d)原水处理系统及辅助设施，主要包括加氯系统、加药系统、清水池、絮凝池、重力无阀滤池、污水处理回收池、二水厂泵房设备等及其他辅助设施。更换旺水垭水厂至张家塘配水管13.5km，张家塘至滴水配水管长3.3km，全长16.8km；滴水至洪湖配水管长0.3km；更换八一水库至旺水垭水厂引水管1.7km，更换珍溪二水厂至珍溪大桥配水管5km，新建应急泵站至百汇大桥配水管9km；百汇至观将泵站4.5km；共计37.3km。</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>合同预估金额3427.27万元</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>管材</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>涪陵区珍溪镇农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目名 涪陵区珍溪镇农村供水保障能力提升工程（一期） 称 招标法 网 人或招 重庆水务环境控股集团渝东自来水有限公司 标人名称 （盖章） 项目批 务 准文件 涪陵发改〔2026〕476号 及文号 (一)改造11000m3/d(旺水垭6000m3/d和二水厂5000m3/d)原水处理系统及辅助设施，主要有加氯系统、 加药系统、清水池、絮凝池、重力无阀滤池、商污水处理回收池、二水厂泵房设备等及其他辅助设施。 主要建 (二)更换旺水垭水厂至张家塘配水管13.5km，张家塘至滴水配水管长3.3km，全长16.8km；滴水至洪 设内容 湖配水管长0.3km；更换八一水库至旺水垭水厂引水管1.7km，更换珍溪二水厂至珍溪大桥配水管5km， 新建应急泵站至百汇大桥配水管9km：百汇至观将泵站4.5km；共计37.3km。 道 招标项目 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 场所 (万元) (一)改造11000m3/d(旺水 垭6000m3/d和二水厂5000m3/d) 管 原水处理系统及辅助设施，主 要有加氯系统、加药系统、清 水池、絮凝池、重力无阀滤池、 污水处理回收池、二水厂泵房 涪陵国区珍 设备等及其他辅助设施。(二) 重庆市 招标项 溪镇农村 更换旺水垭水厂至张家塘配水 涪陵区 目 供水保障 公开招 1 管13.5km，张家塘至滴水配水 2026-09 公共资 3427.27 能力提升 标 管长3.3km，全长16.8km；滴水 源交易 中工程（一 至洪湖配水管长0.3km；更换八 中心 期） 一水库至旺水垭水厂引水 管1.7km，更换珍溪二水厂至珍 溪大桥配水管5km，新建应急 泵站至百汇大桥配水管9km： 百汇至观将泵站4.5km；共 计37.3km。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075551.html cqdingjiu 2026.08.21 10:06:56</t>
@@ -3070,9 +3858,13 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标, 供水, 改造</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3087,7 +3879,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3105,16 +3897,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>新建及整治输配水管网总长124.26千米，新建加压泵站5座，新建高位水箱4座（总容积354立方米），武陵山水厂新建废水处理系统1套及配套电气工程等。</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>合同预估金额1861.77万元</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>输配水管网、加压泵站、高位水箱、废水处理系统、电气工程</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>涪陵区武陵山镇农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区武陵山镇农村供水保障能力提升工程 名称 招标 网 法人 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 务 （盖 章） 项目 批准 商 文件 涪陵发改〔2026〕468号 及文 号 主要 道 新建及整治输配水管网总长 124.26千米，新建加压泵站 5座，新建高位水箱4座（总容积 354立方米），武 建设 陵山水厂新建废水处理系统1套及配套电气工程等。 内容 招 管 拟 标 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 国 称 涪 陵 区 中 重 武 庆 陵 市 山 招标 涪 镇 项目 陵 农 公 区 村 新建及整治输配水管网总长 124.26千米，新建加压泵站 5座，新建高 开 公 1 供 位水箱4座（总容积 354立方米），武陵山水厂新建废水处理系统1套 2026-09 1861.77 招 共 水 及配套电气工程等。 标 资 保 源 障 交 能 易 力 中 提 心 升 工 程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075549.html cqdingjiu 2026.08.21 10:06:56</t>
@@ -3126,9 +3934,13 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>涪陵区武陵山镇, 农村供水保障能力提升工程, 重庆, 输配水管网, 加压泵站, 高位水箱, 废水处理系统, 电气工程</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3143,7 +3955,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3161,16 +3973,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>建设配水管网总长34.80km，新建加压泵站2座、改造已成泵站2座、新建加氯加药间1座、新建高位水箱7座、新建计量监测设施以及配套电气工程。</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>合同预估金额3503.77万元</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>配水管网、加压泵站、加氯加药间、高位水箱、计量监测设施、电气工程</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>涪陵区江东街道农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目名 涪陵区江东街道农村供水保障能力提升工程（一期） 称 招标法 网 人或招 重庆水务环境控股集团渝东自来水有限公司 标人名称 （盖章） 项目批 务 准文件 涪陵发改〔2026〕470 号 及文号 主要建 建设配水管网总长 34.80km，新建加压泵站 2 座、改造已成泵站 2 座、新建加氯加药间 1 座、新建高位 设内容 水箱 7 座、新建计量监测设施以及配套电气工程商。 招 招标文件 拟交 合同预估 序 招标项 标 备 招标内容 计划发布 易场 金额(万 号 目名称 方 注 道 时间 所 元) 式 涪陵区 重庆 招标项 江东街 市涪 目 建设配水管网总长 34.80km，新建加压泵站 2 座、 公 道农村 陵区 管 改造已成泵站 2 座、新建加氯加药间 1 座、新建高 开 1 供水保 2026-09 公共 3503.77 位水箱 7 座、新建计量监测设施以及配套电气工 招 障能力 资源 程。 标 提升工程 交易 （一期） 中心 国 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075548.html cqdingjiu 20中26.08.21 10:06:56</t>
@@ -3182,9 +4010,13 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>重庆, 农村供水保障能力提升工程, 配水管网, 加压泵站, 加氯加药间, 高位水箱, 计量监测设施, 电气工程</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3217,16 +4049,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>详见附件。</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>内外涂环氧消防复合钢管管件</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>中国电建水电五局二公司重庆轨道交通17号线一期7标内外涂环氧消防复合钢管管件采购项目公开竞价采购(二次 挂网)变更公告(一) 详见附件。 信息来源:https://www.chinapipe.net/project/d3075376.html cqdingjiu 2026.08.21 10:06:56 网 务 商 道 管 国 中</t>
@@ -3238,9 +4078,13 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3273,16 +4117,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>本次修复选择开挖换管：开挖约80米，2孔110波纹管、2孔蜂窝管，新建两通信手控井。</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>项目资金已落实。</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>通信管道</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>2026年石柱分公司黄水镇黄连大道通信管道建设招标公告 ZB_ZHAOBIAOGONGGAO_START 本询比项目为 2026年石柱分公司黄水镇黄连大道通信管道建设 （标段 编号： CQBBFA202604170051 ），采购人为 中国电信股份有限公司石柱分公司 ，采购代理机构为 。项目 资金已落实。 具备采购条件，现进行公开询比，特邀请有意向的且具有提供标的物能力的潜在供应商（以下简 称供应商）参加询比响应。 1.项目概况与采购内容 1.1项目概况： 2026年石柱分公司黄水黄连大道通信管道修复项目主要针对黄水网黄连大道受损通信管道进行修 复80米 本次集中询比合同有效期为： 2026.9-2026.12 1.2采购内容 及标包划分情况： 务 1.2.1 本次询比的规模、货物名称、数量及主要技术参数、交货期及交货地点具体如下：黄水镇黄连大道80米通 信管道修复。 序号 标包名称 产品名称 规格型号 数量 交货地点 交货期 商 2026年石柱分公司黄水 黄水镇黄连 1 镇黄连大道通信管道建 管道建设 新建2孔110波纹管、 新建2孔蜂窝管 80 2026.12.20 大道 设 道 本项目 不划分标包 。 ${ } ${ 本项目允许供应商同时成交的最多标包数为 0 个。 } 本项目将按照最新的《中国电信供应商不良行为管 理规则》执行供应商不良行为处理结果，请重点关注处理结果适用的供应商主体、被处理产品、处理范围、禁 限期、处理措施等关键内容，请务必登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）查阅《中国 管 电信供应商不良行为管理规则》。 本项目根据《中国电信供应商不良行为管理规则》选择适用备选处理措施 （但涉及生产安全责任事故的处理结果不适用备选措施）。 1.2.2成交供应商数量： 1 个，每个成交供应商对应的份额如下 ： [请在此处自行编辑与采购方案相同的成交原则] 国 ${ 1.2.2成交供应商数量如下： [ 请在此处自行编辑与采购方案相同的有效供应商及成交供应商数量原则相关表格 ] 每个成交供应商对应的份额如下: [请在此处自行编辑与采购方案相同的份额分配原则] } 1.3本项目 设置最高 响应限价 。 设置最高响应限价，最高响应限价为不含税31000元人民币/计算方法，供应商响应报价高于最高 响应限价的，其响应将被否决 供应商响应报价高于最高响应限价的，其响应 将被否决。 ${ } 2.供应商中资格要求 2.1供应商基本资格要求 2.1.1 供应商 应为 中华人民共和国境内 法律上和财务上独立的法人或依法登记注册的其他组织，合法运作并 独立于采购人和采购代理机构。 供应商应具有良好的银行资信和商业信誉。法人下属不具备法人资格的分支机 构参与响应的，应提供所属法人针对本项目或覆盖本项目的经营事项的有效授权。 2.1.2 供应商 的法定代表人或负责人为同一人或者存在控股、管理关系的不同 供应商 ，不得参加同一标包响应或 者未划分标包的同一询比项目响应。 ${ 2.1.3 } ${ 2.1.3 } 2.1.4 本次询比 不接受 联合体响应。 ${如 供应商 为联合体，应满足下列要求： （1） 联合体各方必须按询比文件提供的格式签订联合体协议书，明确联合体牵头人和各方的权利义务； （2）由同一 专业的单位组成的联合体，按照资质等级较低的单位确定资质等级； （3）联合体各方不得再以自己名义单独或 加入其他联合体在同一标包或者未划分标包的同一询比项目中响应。 ${ （4） 。} } 2.1.5 本次询比 不接受代理商响应。 ${ （1）产品制造商注册地在中华人民共和国境外（与中华人民共和国有正常贸易与往来的国家或地区）及香港、 澳门、台湾地区且必须使用代理商响应和签订销售合同的；（2）产品制造商为注册地在中华人民共和国境内的 外资企业（包括香港、澳门、台湾地区资本）或者由外国投资者（包括香港、澳门、台湾地区）享有绝对控制权 （最大或最多表决权）的企业且必须使用代理商响应和签订销售合同的。代理商响应的，应满足下列要求 ： } ${ （1） ${ （2） 供应商与产品制造商 的代理合作关系迄今为止应已持续 0 年（含）以上。 } ${ （3） } } ${ 2.1.6 与供应商有产品代工制造关系的制造商不得参加同一标包响应或者未划分标包的同一询比项目响 应。 } 2.1.7 供应商须提供2022年1月1日至本项目发布公告之日的同类项目（通信管道施工类）证明材料， 合同累计金额不低于3万元（含税） 2.2供应商不得存在下列情形之一 （1） 为采购人不具有独立法人资格的附属机构（单位）； （2） 被依法暂停或取消 投标/ 响应资格的； （3） 被责令停产停业、暂扣或者吊销许可证、暂扣或者吊销执照； （4） 进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （5） 在最近三年内（自 2022年04月01日 起）被相关行业主管部门或司法机关认定有骗取 中标/成交 、严重 违约、重大工程质量或者安全问题的； 网 （6） 在最近五年内（自 2022年06月01日 起）被判处单位行贿罪，且行贿行为与采购活动相关的（以“中国 裁判文书网”的生效判决为准）； （7） 在最近五年内（自 2022年06月01日 起）被判处合同诈骗罪的（以“中国裁判文书网”的生效判决为 务 准）； （8） 被最高人民法院在“信用中国”网站（www.creditchina.gov.cn）或各级信用信息共享平台中列入失信被执 行人名单，已执行完毕或不再执行的除外； 商 （9） 为本询比项目提供过设计、编制技术规范和其他文件的咨询服务 ； （10） 为本工程项目的相关监理人，或者与本工程项目的相关监理人存在隶属关系或者其他利害关系； 道 （11） 为本询比项目的代建人 ； （12） 为本询比项目的采购代理机构 ； 管 （13） 与本询比项目的监理人或代建人或采购代理机构同为一个法定代表人 ； （14） 与本询比项目的监理人或代建人或采购代理机构存在控股或参股关系 ； （15） 被工商行政管理国机关在国家企业信用信息公示系统中列入严重违法失信企业名单的； （16） 中国电信在职员工违规担任供应商法定代表人并参与采购活动的； （17） 中国电信集团有限公司/中国电信股份有限公司中层及以上管理人员违反有关领导人员配偶、子女及其配 中 偶经商办企业行为管理规定，其配偶、子女及其配偶经商办企业参与采购活动的； （18） 中国电信领导人员离职或退休后三年内违反《国有企业领导人员廉洁从业若干规定》等相关规定任职、 投资入股的私营企业、外资企业和中介机构，参与其原任职单位采购活动的； ${ （19） } （19） 其他按照中国电信供应商不良行为处理结果及《中国电信供应商不良行为管理规则》的结 果执行规则，应对供应商及其响应产品在本项目中执行禁止采购处理措施的； （20） 法律法规、询比文件限定的其他情形。 ${ 供应商 是代理商的，本条所指的 供应商 也包括其所代理的制造商。 } ${ 联合体响应的，联合体成员均不得 存在上述任一情形。 } 2.3产品资格要求 2.3.1 产品 应是来自中华人民共和国 ${或是与中华人民共和国有正常贸易与往来的国家或地区} 的 成熟稳定的 产品 。 ${ 2.3.2 产品 。 } ${ 2.3.3 产品 。 } ${ 2.3.4 。 } ${ 2.3.5 。 } 2.3.6 产品应符合中国电信相关技术要求， 并满足以下关键技术指标： （1） 序号 技术指标 具体要求 1 开挖深度 埋深≥0.8m（道路≥1.2m） 2 施工规格 本次修复选择开挖换管：开挖约80米，2孔110波纹管、2孔蜂窝管，新建两通信手控井 ${ 2.3.7 产品 业绩要求： 。 } ${ 2.3.8 。 } ${ 2.4 产品制造商资格要求 2.4.1 制造商应提供合法有效的登记 （或注册）证明文件，应具有良好的银行资信和商业信誉。 } ${ 2.4.2 } ${ 2.4.2 } ${ 2.4.3 } ${ 2.4.4 } ${ 2.4.5 } ${ 2.5现场考察 } ${ 2.6评价检测 } 2.7 法律法规规定的其他要求。 3.资格审查方法 本项目将进行资格后审，资格审查标准和内容见询比文件第三章“评审办法”，凡未通过资格后审的供应商， 其响应将被否决 。 网 4.询比文件的获取 4.1询比文件获取时间: 2026年08月25日 00时00分00秒 至 2026年09月01日 00时00分00秒 （北京时间，下同）。 4.2询比文件获取方式：登录“中国电信阳光采购网（https://caigou.c务hinatelecom.com.cn）”后，通过“招投标-采 购文件领取”模块或通过“电子采购入口”跳转中国电信电子采购系统，进入本项目进行询比文件登记申领， 未在系统注册的供应商须先进行注册，注册方法详见本公告“ 7 供应商注册”。 4.3询比文件费用： 本项目不收取文件费用。 ${每套售价商 0 元人民币，售后不退。支付要求： } 5.响应文件的递交 5.1响应文件递交截止时间（即响应截止时间）为： 2026年09月02日 00时00分00秒 道 5.2 电子响应文件的提交方式：登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投 标-我的项目”模块或通过“电子采购入口”跳转中国电信电子采购系统，选择本项目进行响应文件提交，供应 商应在响应文件提交截止时间之前通过电子采购系统完成加密电子响应文件的上传。供应商未在电子采购系统 进行询比文件申领登记或电子响应管文件未按照要求加密的，将无法通过电子采购系统提交电子响应文件 。 5.3 本项目将于响应文件提交截止同一时间通过中国电信电子采购系统开启响应文件， 采购人/采购代理机构 邀 请响应供应商的法定代表人或者其委托代理人准时参加 。 国 ${ 6.样品的递交 6.1样品递交的时间、地点：于 递交至 。 } 7. 供应商注册 7.1 中国电信阳光采购网注册 未注册过的潜在供应商，须通过中国电信阳光采购网（https://caigou.chinatelecom.com.cn）首页“立即注册”模 中 块完成注册后，方可申领本项目询比文件。 7.2 CA证书办理 参加询比响应的潜在供应商须提前办理CA证书，并确保CA证书在使用时有效。CA证书办理流程详见中国电信 阳光采购网首页“操作指引-CA办理”。 7.3 技术支撑联系方式 服务热线：4000111884 服务邮箱：zb_support@chinatelecom.cn（电子采购系统技术支撑） ctsc@chinatelecom.cn（CA证书办理技术支撑） 8. 发布公告的媒介 本询比公告在 中国电信阳光采购网（https://caigou.chinatelecom.com.cn） 、中国招标投标公共服务平台 （http://www.cebpubservice.com/） 上发布，其他媒介转载无效。 9. 联系及异议接收方式 9.1 联系方式 采 购 人: 中国电信股份有限公司石柱分公司 采购代理机构: 地 址： 重庆市石柱县城南路6号 地 址： 无 邮 编： 邮 编： 无 联 系 人： 马卫平 联 系 人： 无 电 话： 17365204567 电 话： 无 电子邮件： 17365204567@189.cn 电子邮件： 无 网 址： www.chinatelecom.com.cn或“/” 网 址： 无 网 开户银行： 无 账 号： 无 9.2 异议接收方式 务 登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投标-采购异议-提出异议”模块提出。 采购代理机构： 商 2026年08月25日 信息来源:https://www.chinapipe.net/project/d30道75344.html cqdingjiu 2026.08.21 10:06:56 管 国 中</t>
@@ -3296,7 +4148,11 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="P51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3329,16 +4185,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>重庆站站房CQZSG-4标项目蓝色PVC袖阀管(外径60mm)询价采购公告</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>蓝色PVC袖阀管，外径60mm，壁厚4.5-5mm PVC管</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>重庆站站房CQZSG-4标项目蓝色PVC袖阀管(外径60mm)询价采购公告 ZTEJWZ-JZ-2026-询027（一） 采购单位:重庆站站房CQZSG-4标段项目经理部 发布时间:2026-08-18 19:06 报价截止时间:2026-08-21 10:00 招标方联系人:刘健 网 招标方联系电话:13540650091 招标方邮箱: 务 监督方联系人:纪委 监督方联系电话:028-87653066 商 监督方邮箱: 保证金:0.0元 道 结算与发票信息: 结算方式：上月21日至本月的20日为一个结算周期，当月20日为本月的结算截止日期。结算时根据甲方检验合格 及双方共同签认的凭证计算当月实际收货数量。 管 支付条件：结算完成后，甲方在收到乙方开具的正式的增值税专用发票后第1个月支付该批物资结算金额的70%， 第12个月支付20%，剩余10%在第18-24月内按月均衡支付。 发票种类：增值税专用国发票 发票抬头：中铁二局集团有限公司 税号：9151中0100MA61RKR7X3 其他要求： 交货信息: 交货方式:点数验收 收货人:刘健 收货人联系方式:13540650091 其他说明事项: 流水号：询2026081800458 交 标的 规格 计量 标的编号 数量 技术标准及要求 货 送货地址 名称 型号 单位 期 蓝色PVC袖阀管，外 西南区-重庆市-市辖区-渝中区-重 袖阀 径60mm，壁 庆市菜园坝立交以西，龙家湾隧道 0950999183764 - 23188.0 米 管 厚4.5-5mm PVC管，承压 以东，菜袁路以北，王家坡以南的 不小于5MPa,节长4m 地块内，原重庆站。 报价网址:http://www.crecgec.com 信息来源:https://www.chinapipe.net/project/d3075317.html cqdingjiu 2026.08.21 10:06:56 网 务 商 道 管 国 中</t>
@@ -3350,9 +4214,13 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3385,16 +4253,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>新建、更换配水管网396.72km（dn20-dn160PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收及污泥浓缩处理系统。</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>合同金额：3611.91万元</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>dn20-dn160PE管、DN40-DN250抗菌耐磨涂塑钢管</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>涪陵区蔺市街道农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区蔺市街道农村供水保障能力提升工程（一期） 名称 招标 法人 或招 标人重庆水务环境控股集团渝东自来水有限公司 名称 网 （盖 章） 项目 批准 文件涪陵发改〔2026〕474号 及文 号 主要 务 建设新建、更换配水管网 396.72km（dn20-dnl60PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收及污泥浓缩处理系统。 内容 拟 招招标文 合同预 招标 交 序 标件计划 估金 备 项目招标内容 易 号 方发布时 额(万 注 名称 场 式间 元) 所 商 重 庆 涪陵 市 区蔺 招标 市街 涪 项目 道农 陵 公 区 村供 新建、更换配水管网 396.72km（dn20-dnl60PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收 开 公 1 水保 2026-09 3611.91 及污泥浓缩处理系统。 招 共 障能 道 标 资 力提 源 升工程 交 （一 易 期） 中 心 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075278.html 管 cqdingjiu 2026.08.21 10:06:57 国 中</t>
@@ -3406,9 +4290,13 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标, 商机</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3441,16 +4329,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>改造李渡街道15个村（社区）配水主支管道，更换配水主管网193.71千米（DN250-DN40抗菌耐磨涂塑钢管、dn40-dn25PE管）及配套附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治3座，新建测控井78座。</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>项目批准文件：涪陵发改[2026]469号</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>DN250-DN40抗菌耐磨涂塑钢管、dn40-dn25PE管</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>涪陵区李渡街道农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区李渡街道农村供水保障能力提升工程 名称 招标 法人 网 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 务 项目 批准 文件 涪陵发改〔2026〕469号 及文 号 商 主要 改造李渡街道 15个村（社区）配水主支管道，更换配水主管网 193.71 千米（DN250-DN40 抗菌耐磨涂塑钢管、dn40-dn25PE管）及配套 建设 附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治 3座，新建测控井78座。 内容 招 拟 标 道 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 称 管 涪 陵 区 重 李 庆 渡 市 街 国 招标 涪 道 项目 陵 农 公 区 村 改造李渡街道 15个村（社区）配水主支管道，更换配水主管网 193.71 千米（DN250-DN40 抗菌耐磨涂 开 公 1 供 塑钢管、dn40-dn25PE管）及配套附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治 3座，新建 2026-09 2372.74 招 共 水中测控井78座。 标 资 保 源 障 交 能 易 力 中 提 心 升 工 程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075277.html cqdingjiu 2026.08.21 10:06:57</t>
@@ -3462,9 +4366,13 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 改造, 配水主支管道, 更换配水主管网, 抗菌耐磨涂塑钢管, PE管, 泵站改造, 集成泵站, 蓄水池整治, 测控井</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3497,16 +4405,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>本项目对珍溪镇23个村(社区)安装配水管网660km及配套附属设施，其中：1.De160~De40的PE管主要建设有232km；2.连接各村社的De32~De20的PE管有381km；3.219~32的衬塑钢管47km。(二)购置安装泵站14座(一用一备共计28台水泵)，其中新建泵商站10座、更换泵站4座及配套电力设施;新建不锈钢水箱2座等。(三)购置安装(0~25kg)减压阀61个;排污阀(25kg）3个。</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>合同预估金额为2182.77万元</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>PE管、衬塑钢管、水泵、不锈钢水箱、减压阀、排污阀</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>涪陵区珍溪镇农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目名称 涪陵区珍溪镇农村供水保障能力提升工程（二期） 招标法人 或招标人 重庆水务环境控股集团渝东自来水有限公司 网 名称（盖 章） 项目批准 文件及文 涪陵发改〔2026〕477号 务 号 (一)本项目对珍溪镇23个村(社区)安装配水管网660km及配套附属设施，其中：1.De160~De40的PE管 主要建设 有232km；2.连接各村社的De32~De20的PE管有381km；3.219~32的衬塑钢管47km。(二)购置安装泵 内容 站14座(一用一备共计28台水泵)，其中新建泵商站10座、更换泵站4座及配套电力设施;新建不锈钢水 箱2座等。(三)购置安装(0~25kg)减压阀61个;排污阀(25kg）3个。 招标项目名 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 称 式 划发布时间 场所 (万元) 道 (一)本项目对珍溪镇23个 村(社区)安装配水管网660km 及配套附属设施，其 中：1.De160~De40的PE管 管 有232km；2.连接各村社 涪陵区珍溪 重庆市 的De32~De20的PE管有381km； 招标项目 镇农村供水 涪陵区 3.219~32的衬塑钢 公开招 1 保障能力提 2026-09 公共资 2182.77 管47km。(二)购置安装泵 标 升工国程（二 源交易 站14座(一用一备共计28台水 期） 中心 泵)，其中新建泵站10座、更 换泵站4座及配套电力设施; 新建不锈钢水箱2座等。(三) 中 购置安装(0~25kg)减压阀61 个;排污阀(25kg）3个。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075275.html cqdingjiu 2026.08.21 10:06:57</t>
@@ -3518,9 +4442,13 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>涪陵区, 珍溪镇, 农村供水, 提升工程, PE管, 衬塑钢管, 水泵, 不锈钢水箱, 减压阀, 排污阀</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3553,16 +4481,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长105.307km（dn20-dn40PE管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建1座改造3座；新建测控井52座。</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>合同预估金额：2652.89万元</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>净水设备、PE管、抗菌耐磨涂塑钢管</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>涪陵区蔺市街道农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区蔺市街道农村供水保障能力提升工程（二期） 名称 招标 法人 网 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 务 项目 批准 文件 涪陵发改〔2026〕475号 及文 号 商 主要 八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长 105.307km（dn20-dn40PE 建设 管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建 1座改造3座；新建测控井 52座。 内容 拟 招 招标文 合同预 招标 交 序 道 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 所 重 庆 涪陵 管 市 区蔺 涪 招标 市街 陵 项目 道农 公 区 村供 八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长 开 公 1 水保 105.307km（dn20-dn40PE 管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建 1座改造3座； 2026-09 2652.89 国 招 共 障能 新建测控井 52座。 标 资 力提 源 升工程 交 （二 易 期） 中 中 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075274.html cqdingjiu 2026.08.21 10:06:57</t>
@@ -3574,9 +4518,13 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3609,16 +4557,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>本项目涉及管道为鱼洞污水处理厂专件厂线管网，管道编号为WD4-WD8+1，该管道为自流管道，位于鱼轻桥至河嘴倒虹井段，主要用于收集输送鱼洞大江商至华熙片区的生活污水。该段管道管径为DN600，管道为混凝土管，主要采用架空明敷的方式沿河敷设。该管道自建成投运以来已有20余年，管道及污水井老化严重现象十分明显，容易出现破损从而造成污水溢流，造成环保风险。为规避环保风险且保障该段管道以及鱼洞污水厂的正常收水及运行，需对该段管道进行改造。</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>项目资金来自企业自筹</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>DN600混凝土管，检查井</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目项目公告 重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目（项目名称）比选公告 1.比选条件 本比选项目重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目（项目名称），比选人为重庆市排 网 水有限公司，比选项目资金来自企业自筹（资金来源），项目已具备比选条件。中标后合同与重庆市豪洋水务 建设管理有限公司签订。现对本项目进行公开比选，诚邀有兴趣的潜在投标人参与投标。 2.项目概况与比选范围 务 2.1 建设地点：重庆市巴南区 2.2 项目概况：本项目涉及管道为鱼洞污水处理厂专件厂线管网，管道编号为WD4-WD8+1,该管道为自流管道， 位于鱼轻桥至河嘴倒虹井段，主要用于收集输送鱼洞大江商至华熙片区的生活污水。该段管道管径为DN600，管道 为混凝土管，主要采用架空明敷的方式沿河敷设。该管道自建成投运以来已有20余年，管道及污水井老化严重现 象十分明显，容易出现破损从而造成污水溢流，造成环保风险。为规避环保风险且保障该段管道以及鱼洞污水 厂的正常收水及运行，需对该段管道进行改造。 道 2.3 比选范围：拆除现状管道为DN600混凝土管，同时需拆除并新建9座检查井。 2.4 工期要求：30日历天，以甲方通知进场时间为准。 管 2.5缺陷责任期要求：24个月 3.投标人资格要求 国 3.1 本次比选要求投标人须具备以下条件： 3.1.1 本次比选要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰级 及以上资质。 中 3.1.2 投标人还应在人员、设备、资金等方面具有相应的施工能力，详见比选文件第二章投标人须知前附表第1.4.1 项内容。 3.2 本次比选接受不联合体投标。 4.比选文件的获取 4.1 投标人于2026年8月 18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子 版，以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都 视为投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的 一切后果由投标人自行负责。各投标单位应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行供应商注册，填写相关信息，审批过后成为 平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价、递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，将被否决投标。 4.4 比选文件每份售价800元，售后不退。投标单位在递交纸质投标文件时扫描支付，否则比选人拒绝接收其投标 文件。 5.投标文件的递交 5.1 电子投标文件递交时间：2026年8月24日14时30分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年8月24日14时00分至14时30分（北京时间），地点：重庆水务招标采购中心 （重庆市两江新区嘉华路36号重庆水务大厦5楼）。 5.3 投标截止时间：2026年 8月24日14时30分（北京时间）。 网 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 务 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 商 比 选 人：重庆市排水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝中区长江滨江路126号 地 址：重庆市两江新区嘉华路36号重庆水务大厦 道 联 系 人： 黄老师 联 系 人： 黄晓华 电 话： 023-67767416 电 话： 18523396416 管 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3075272.html 国 cqdingjiu 2026.08.21 10:06:57 中</t>
@@ -3630,9 +4586,13 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>重庆, 排水公司, 污水处理厂, 管网改造, DN600混凝土管, 检查井</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3665,16 +4625,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>潼南区</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>潼南区</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>改建潼南城区输水主管网约39.63km及配套相应阀门阀件等，对城区供水管网上商老旧阀门阀件、设施设备进行更换，合理增设部分计量及压力监控、水质监控等。</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>合同预估金额：918.00万元</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>城区配套阀门阀件改造工程</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>重庆市潼南城区老旧供水管网改造工程招标计划 重庆市工程建设项目招标计划表 项目名称 重庆市潼南城区老旧供水管网改造工程 招标法人或招 标人名称（盖 重庆市潼南自来水有限公司 网 章） 项目批准文件 及文号 务 主要建设内容 改建潼南城区输水主管网约39.63km及配套相应阀门阀件等 招标方 招标文件计 拟交易场 合同预估 序号 招标项目名称 招标内容 备注 式 划发布时间 所 金额(万元) 对城区供水管网上商 重庆市潼南城 老旧阀门阀件、设 区老旧供水管 重庆市潼 招标项目 施设备进行更换， 网改造工程 公开招 南区公共 1 保障供水管网稳定 2026-09 918.00 （城区配套阀 标 资源交易 运行合道理增设部分 门阀件改造工 中心 计量及压力监控、 程） 水质监控等。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3075266.html cqdingjiu 2026.08.21 10:06:58 国 中</t>
@@ -3686,9 +4662,13 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3721,16 +4701,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>开州区</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>开州区</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>该项目涉及硬化生产便道、建设防旱池和蓄水池、建造育苗大棚和小棚、安装水源处理和水肥一体化设施、新建设备管理房以及完善蔬菜基地配套设施等内容。</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>工程总投资335万元。</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>工程设计服务</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>关于为【重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购】公开选取【工程设计】 机构的公告 我单位在重庆市网上中介超市公开选取工程设计中介服务机构，现将相关事项公告如下： 该项目为直接选取项目，由采购人从报名的中介服务机构中直接选定一家中介服务机构进行项目服务。 项目 重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购 名称 网 采购 重庆市开州区河堰镇人民政府 人 投资 审批 否 务 项目 是否 破产 商 业务 否 服务 项目 采购 道 所需 中介 其他 服务 事项 管 所需 服务 工程设计 类型 项目实施地点为国河堰镇清泉社区，项目建设内容为：硬化2米宽生产便道5.5千米，100方防旱池1口，50方 服务 蓄水池1口，标准自动化育苗大棚1个，蔬菜小棚20个，水源处理设施1套，水肥一体化配套设施1套，新 内容 建50平方米设备管理房，完善蔬菜基地配套设施等。工程总投资335万元。选取此项目设计单位（含预算 编制服务）。 中 中介 机构 资质（资格）要求 要求 资质 （资 1、报名单位提供有效的营业执照，资质证书（资质丙级或丙级以上），具备从事项目设计服务工作； 2、 格） 具有独立承担民事责任的能力； 3、具有良好的商业信誉和健全的财务会计制度； 4、具有履行合同所必 要求 需的专业技术能力； 5、有依法缴纳税收和社会保障资金的良好记录。 说明 其他 要求 无 说明 服务 时限 无要求，按照合同双方自行约定 说明 服务 3.1%费率 金额 金额 按文件要求执行 说明 选取 直接选取 方式 需规 避机 构 规避 原因 选取 2026-08-20 16:00:00 （选取时间到达后不接受报名，建议中介机构至少在选取开始半小时前完成报名。） 时间 采购 人业 网 务咨 重庆市开州区河堰镇人民政府（18716685679） 询电 话 采购 务 需求 26清泉社区项目设计服务采购说明.pdf 书下 载 商 2026-08-18 信息来源:https://www.chinapipe.net/project/d3075198.html 道 cqdingjiu 2026.08.21 10:06:58 管 国 中</t>
@@ -3742,9 +4738,13 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3777,16 +4777,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>开州区</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>开州区</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1.建设果园水肥一体化系统1套，对示范柑桔果园建设水肥一体智能化系统;2.果园运输线4000米(含轨道主机、叉车、周转箱、三轮车等配套设施设备);3.建设排灌站一处;4.建设1.8米宽生产便道2000米，务周转场300平方米;5.配备载重无人机1台、小型挖机1台、电子控制屏1个;6.建设智慧平台与监测系统软硬件系统等。</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>项目总投资金额：500万元，本次招标项目合同估算金额：446.278921万元</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>柑橘基地改造提升项目</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目招标公告 1.招标条件 本招标项目重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目已由重庆市开州区发展和改革委员会以开州 发改审〔2026〕357号批准建设，项目业主为重庆市开州区长沙镇人民政府，建设资金来自开州区2026年中央和 市级提前批财政衔接推进乡村振兴补助资金，项目出资比例为 100% ，招标人为重庆市开州区长沙镇人民 政府。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：开州区长沙镇桔香村 2.2 项目概况与建设规模：1.建设果园水肥一体化系统1套，对示范柑桔果园建设水肥一体智能化系统;2.果园运输 线4000米(含轨道主机、叉车、周转箱、三轮车等配套设施设备);3.建设排灌站一处;4.建设1.8米宽生产便道2000米， 务 周转场300平方米;5.配备载重无人机1台、小型挖机1台、电子控制屏1个;6.建设智慧平台与监测系统软硬件系统等。 2.3 本项目工程总投资金额： 500万元 本次招标项目合同估算金额： 446.278921万元 商 2.4 招标范围：招标人发布的由重庆中煜华资工程技术有限公司设计的《重庆市开州区2026年长沙镇桔香村柑橘 基地改造提升项目》施工图及图纸说明、招标文件(含补遗)及工程量清单、答疑资料、澄清资料范围内所涉及的 工作内容，具体以招标人发布的工程量清单及道施工图为准。 2.5 工期要求： 150日历天 缺陷责任期要求： 12个月 管 2.6 标段划分（如有）： / 2.7 其他： / 国 3.政府采购工程 3.1 是否属于政府采购工程：是 中 3.2 是否专门面向中小企业预留：否，按照《政府采购促进中小企业发展管理办法》第六条第(三)“按照本办法 规定预留采购份额 无法确保充分供应、充分竞争，或者存在可能影响政府采购目标实现的情形”的规定，故本 项目不专门面向中小企业预留。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包叁级及以 上资质或市政公用工程施工总承包叁级及以上资质或水利水电工程施工总承包叁级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在 重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）下载招 标文件、工程量清单、电子图纸等资料。参与投标的投标人需在 重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）完成市 场主体信息登记以及CA数字证书办理，办理方式请参见 重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、 重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）导航栏“主体信息”页面中“市场主 体信息登记”、“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完 成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区） （https://www.cqggzy.com/kaizhouweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告 发布至2026-08-21 17:00:00前。 5.3招标人应于2026-08-25 23:59:59前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源 交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）发布澄清。 6.投标文件递交的内容 网 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-21 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 务 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区） （https://www.cqggzy.com/kaizhouweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交 易监督网上发布。] 商 8.联系方式 招 标 人: 重庆市开州区长沙镇人民政府 代理机构: 重庆毅仁建设项目管理有限公司 重庆市开州区文峰街道天鹅湖社区富厚街158号附10 地 址: 重庆市开州区长沙镇山花街1号 地 址: 道号 邮 编: 邮 编: 项目负责人: 丁敬余 项目负责人: 谭毅 电 话: 15826368887 管电 话: 13452653126 传 真: 传 真: 电子邮箱: 1415705480@qq.com 电子邮箱: 开户银行: 国 开户银行: 账 号: 账 号: 监督部门:中重庆市开州区公共资源交易管理局 电 话: 023-52218977 2026年08月17日 重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目 户名 开户行 投标保证金账号 重庆市开州区公共资源交易中心 重庆农村商业银行股份有限公司开州支行 3401010120010012772000200 中国农业银行股份有限公司重庆开州支行营 重庆市开州区公共资源交易中心 314401010400104500000006031 业部 中国工商银行股份有限公司重庆开州支行营 重庆市开州区公共资源交易中心 9558853100005824176 业部 重庆市开州区公共资源交易中心 重庆银行股份有限公司开州支行 680101040007547-100984 重庆市开州区公共资源交易中心 中国银行股份有限公司重庆开州支行 108865555576VA00149 信息来源:https://www.chinapipe.net/project/d3075199.html cqdingjiu 2026.08.21 10:06:58</t>
@@ -3798,9 +4814,13 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>重庆, 柑橘基地改造, 水肥一体化系统, 运输线, 排灌站, 生产便道, 无人机, 小型挖机, 智慧平台</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3833,16 +4853,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>万盛区</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>万盛区</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>万盛城区老旧供水管网更新改造工程答疑及补遗。</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>供水管网</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>万盛城区老旧供水管网更新改造工程答疑及补遗(一) 万盛城区老旧供水管网更新改造工程 答疑及补遗（一） 各潜在投标人： 现将万盛城区老旧供水管网更新改造工程答疑及补遗（一）相关条款通知如下： 网 一、答疑 问题1：请问招标人是否委派业主专家参与评标吗？ 务 答：是，本项目评标委员会共7人，其中在重庆市综合评标专家库随机抽取5人，招标人代表2人。? 问题2：本项目是否采用异地评标方式？ 答：是 。 商 问题3：本项目是否有业主代表，如有，请明确业主代表数量。 答：是，本项目评标委员会共7人，其中在重道庆市综合评标专家库随机抽取5人，招标人代表2人 。 问题4：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 答：可以。 管 问题5：污水处理厂提标改造及附属管道施工业绩满足吗？ 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 国 问题6：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可以 不填(空白)，对此有无要求？ 答：无要求。? 中 问题7：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖章， 请问需要提供联合体协议书吗？ 。 答： 根据招标文件第二章“投标人须知前附表”1.4.1 第3条业绩要求中：“注：（2）投标人提供的业绩为联 合体业绩的，其在该业绩中的工作分工应与本项目承担的工作一致。”要求，故需要提供联合体协议书。 问题8：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要求”吗？ 答：填写“达到招标文件的要求”或按照招标文件相关条款填写具体内容均可 。 问题9：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 答：投标人的工程量清单单项报价不得为零报价(招标人提供的工程量清单单项最高限价中金额为零的除外)或者 负数报价，否则由评标委员会作否决投标处理。 问题10：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知书发 出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予提前注 销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 答：需要。但不将加盖正本作为评审因素。 问题11：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收，请 问我公司业绩满足业绩要求吗？ 答：不满足。? 问题12：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 答：可以 。 问题13：业绩要求的竣工时间是指竣工验收时间吗？ 答：是的。 网 问题14：重庆市电子招投标系统投标文件-报价部分“己标价工程量清单”-“投标总价”页面招标人名称需要填 写吗？ 务 答：由投标人自行决定是否填写，是否填写不作为评审因素。 问题15：请问招标人是否委派业主专家参与评标吗？ 答：是，本项目评标委员会共7人，其中在重庆市综合评商标专家库随机抽取5人，招标人代表2人。 问题16：自来水厂或者净水厂含管道施工业绩满足业绩要求吗？ 答：投标人提供的业绩合同规模和工程类别需道满足招标文件要求。? 问题17：有没有人行贿专家，有的话我们就不参加了。 答：本项目评标委员会由招标人按法律法规及相关规定依法组建。 管 问题18：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要 提供其他格式之外的其他承诺？ 答：请各潜在投标人仔国细阅读招标文件，并按招标文件要求提供相应承诺。 问题19：财务报告可以不提供财务报表附注吗？ 答：可以。 中 问题20：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 问题21：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、注册证 及在本单位注册的证明文件替代？ 答：退休证等材料不能替代养老保险证明，按招标文件执行。? 问题22：本项目是异地评标吗？ 答：是。 问题23：现在除了没有警戒线和技术方案的低价项目评标专家不被围猎，哪个项目不围猎评标专家，请问招标人 如何保证公平？ 答：本项目招标文件严格按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本（2026年版）》编制， 且本项目评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 问题24：没有低价警戒线怎么保证中高价呢？ 答：本项目未设置低价警戒线，通过综合评估法对各潜在投标人进行评审。分值由技术、商务、报价组成，综 合实力优良的投标人合理中高价可依靠综合得分优势参与竞争，同时招标文件履约追责条款约束投标人理性报 价，保障合理报价竞争环境。 问题25：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗？ 答：现场递交纸质保函原件的人员不作要求 。 问题26：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 网 答：电子投标系统中锁定不可修改的格式（如封面、投标函）直接填空即可，其他投标文件格式以加盖公章的 招标文件PDF文件为准。? 问题27：专业分包业绩满足业绩要求吗？ 务 答：不满足。 问题28： 市政道路包含给水管网施工业绩满足业绩要求吗？ 商 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 问题29：技术负责人在资格审查部分中提供了工程类高级及以上职称证后，在商务部分中再提供工程类高级及以 上职称证可以加分吗？ 道 答：可以。 问题30：万盛的项目挂綦江来投这样都还控制不了还全是你们万盛公司中的？是有啥猫腻是吧？参考之前的项目 管 全是万盛的公司中的！业主、专家全是你们自己人吧？ 答：本项目招标文件严格按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本（2026年版）》编制， 且本项目评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 国 二、补遗 1、本次重新发布本项目的工程量清单，在《重庆市公共资源交易网》(綦江区) （https://www.cqggzy.com/qijiangweb/）网上发布，请投标人自行下载。 中 招 标 人：重庆市万盛经济技术开发区城市管理局 招标代理机构：重庆力圣建设工程咨询有限公司 2026年8月18日 信息来源:https://www.chinapipe.net/project/d3074975.html cqdingjiu 2026.08.21 10:06:58</t>
@@ -3854,9 +4890,13 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>重庆, 供水管网, 更新改造</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3871,7 +4911,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3889,16 +4929,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>巴南区</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>巴南区</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>为解决片区内涝问题，在李家沱街道、花溪街道改建d400-d800雨水管网9665m，管材采用高密度聚乙烯(HDPE)缠绕结构壁管B型管；改建d1000-d1400雨水管网664m，管材采用高密度聚乙烯(HDPE)缠绕结构壁管B型管、III级钢筋混凝土管；改建d1500-d2000雨水管网426m，管材采用III级钢筋混凝土管；改建d2100-d2600雨水管网1000m，管材采用III级钢筋混凝土管；修复雨水管网5345m，增加智能感知设备6套。</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>本次招标项目工程费估算金额：11061.83万元，勘察设计合同估算金额：334.544万元。</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>雨水管网、高密度聚乙烯(HDPE)缠绕结构壁管B型管、III级钢筋混凝土管、智能感知设备</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告 重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告 1.招标条件 本招标项目 重庆市巴南区土桥片区内涝积水整治工程已由重庆市巴南区发展和改革委员会以巴南发改审 发[2025]33号文批准建设，项目业主为重庆市巴南区住房和城乡建设委员会，代建业主为重庆市巴南公路建设有 限公司，建设资金来自区级财政资金统筹，项目出资比例为 100%，招标人为重庆市巴南公路建设有限公司。 项目已具备招标条件，现对该工程的勘察设计进行公开招标，评标办法采用综合评估法。 网 2.项目概况与招标范围 2.1 建设地点：重庆市巴南区花溪街道、李家沱街道 务 2.2 项目概况与建设规模：为解决片区内涝问题，在李家沱街道、花溪街道改建 d400-d800 雨水管网 9665m，管材 采用高密度聚乙烯(HDPE)缠绕结构壁管 B型管；改建 d1商000-d1400雨水管网 664m，管材采用高密度聚乙 烯(HDPE)缠绕结构壁管 B 型管、III 级钢筋混凝土管；改建 d1500-d2000 雨水管网 426m，管材采用III 级钢筋混凝 土管;改建 d2100-d2600 雨水管网 1000m，管材采用 III 级钢筋混凝土管；修复雨水管网 5345m，增加智能感知设 备6 套。 道 2.3 本项目工程总投资金额：13477.10万元 管 本次招标项目工程费估算金额：11061.83万元 国 本次招标项目勘察设计合同估算金额：334.544万元 中 2.4 招标范围：主要包括勘察、施工图设计（包含高边坡、深基坑）和相应阶段的勘察工作，以及提供施工现场 全过程技术服务，并配合业主办理相关手续等，具体范围为： （1）勘察部分：完成本项目范围内的勘察工作，包括但不限于排水管网排查、1:500地形图测量、地质钻勘、管 线内窥、物探、综合管线测量，市政管网错混接点测量及调查等工作，解决区域地下空间臭气问题，勘察成果 需达到重庆市城市建成区排水管网排查技术导则的要求，并配合业主完成对应的成果审查等事宜。 （2）设计部分：包括不限于完成本项目的施工图设计、施工期间交通组织设计、桥梁（涉轨）安全论证方案及 施工期间至竣工验收阶段，质量保修阶段的设计配合服务，配合办理施工图审查相关手续及竣工验收阶段、质 量保修阶段的设计服务等工作以及协助招标人完成各项审批手续办理等工作。 2.5 勘察设计服务期限：30日历天 2.6 标段划分（如有）：/ 2.7 其他：/ 3.政府采购工程 3.投标人资格要求 3.1 本次招标要求投标人须具备以下条件： 网 3.1.1 本次招标要求投标人具备的资质条件： 务 投标人应同时具有建设行政主管部门颁发的下列勘察和设计两类资质： 商 I、投标人应具备下列勘察资质之一： 道 ①工程勘察综合甲级资质。 管 ②工程勘察专业类（岩土工程）专业甲级资质和工程勘察专业类（工程测量）甲级资质； 国 II、投标人应具备下列设计资质之一： 中 ①工程设计综合甲级资质； ②工程设计市政行业甲级资质； ③工程设计市政行业(燃气工程、轨道交通工程除外)甲级资质； ④工程设计市政行业(排水工程)甲级资质。 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的勘察设计能力，详见招标文件第二章投标人须知 前附表第1.4.1项内容。 3.2 本次招标接受联合体投标。联合体投标的，应满足下列要求：联合体组成单位数量不超过2家，由负责设计 任务的单位作为联合体牵头人。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件及其附件、澄 清、修改、补充通知、最高限价通知等资料。参与投标的投标人需在重庆市公共网资源交易网完成市场主体信息 登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息 登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程 电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 务 布至2026-08-23 12:00:00前。 4.3招标人应于2026-08-26 17:00:00前在重庆市公共资源交易网发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-24 09:30，投标人应当在投标截止时间前，通过互 商 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督道网、重庆市公共资源交易网、重庆市公共资源交易网（巴南区） 发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 重庆市巴南公路建设有限公司 代理机构: 重庆云远项目管理有限公司 管 地 址: 重庆市巴南区龙洲大道265号 地 址: 重庆市九龙坡区渝隆大厦28楼 邮 编: 邮 编: 项目负责人: 牟老师 项目负责人: 李强 国 电 话: 023-66238079 电 话: 023-68434996 传 真: 传 真: 电子邮箱: 电子邮箱: 中 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市巴南区发展和改革委员会 电 话: 023-66221670 2026年08月18日 重庆市巴南区土桥片区内涝积水整治工程勘察设计 户名 开户行 投标保证金账号 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000001675 贸易试验区分行 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051304894 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020041267 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764210157 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000682897 支行 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835000509 坝支行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146639123 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630018252 信息来源:https://www.chinapipe.net/project/d3074953.html cqdingjiu 2026.08.21 10:06:58 网 务 商 道 管 国 中</t>
@@ -3910,9 +4966,13 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标, 雨水管网, 高密度聚乙烯, HDPE, 钢筋混凝土管</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3945,16 +5005,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>涪陵作业区涪陵压气站空压机、阀门等设备、消防泵房消防管道、循环水管道油漆出现锈蚀情况，为保证设施安全运行，对站场设备、消防管道及附属钢结构进行打磨除锈、油漆防腐。</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>管道、设备防腐</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>重庆管道公司2026年涪陵压气站管道、设备防腐项目-非招标公告 公告发布时间: 2026年08月18日09时02分19秒 一、概述 1.2.1项目概况：涪陵作业区涪陵压气站空压机、阀门等设备、消防泵房消防管道、循环水管道油漆出现锈蚀情况， 为保证设施安全运行，对站场设备、消防管道及附属钢结构进行打磨除锈、油漆防腐。 二、采购项目与标段 交货期限: 开工之日起90日内完工 网 质保期限(月): 标段 序号 标段名称 标段描述 编号 重庆管道公司2026年涪陵 涪陵作业区涪陵压气站空压务机、阀门等设备、消防泵房消防管道、循 1 1 压气站管道、设备防腐项 环水管道油漆出现锈蚀情况，为保证设施安全运行，对站场设备、消 目 防管道及附属钢结构进行打磨除锈、油漆防腐。 三、供应商资格要求 商 *1、响应人资质要求（1）响应人必须是依照中华人民共和国法律在国内注册，具备合格有效的营业执照的法人、 其他组织；与采购人存在利害关系可能影响询比采购公正性的法人、其他组织或者个人，不得参加响应。单位 负责人为同一人或者存在控股、管理关系的不同单位，不得参加同一标段响应或者未划分标段的同一询比项目 响应。（2）响应人须具备防水防腐保温工程专业承包二级及以上资质。*2、信誉要求响应人在响应文件提交截 止当日不存在以下情况：（1）响应人被“国道家企业信用信息公示系统”网站（www.gsxt.gov.cn）列入严重违法 失信企业名单（响应文件提交截止时间前已移出的除外）。（2）响应人被“信用中国”网站 （www.creditchina.gov.cn）列入严重失信主体名单（响应文件提交截止时间前已移出的除外）。（3）响应人或其 法定代表人、负责人、拟委任的项目经理被“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）列入失信 被执行人名单（响应文件提交截止时间前已移出的除外），响应文件中需提供有效身份证号供查询。（4）响应 管 人、拟委任的项目经理被“全国建筑市场监管公共服务平台”网站（https://jzsc.mohurd.gov.cn/home）列入黑名单 （响应文件提交截止时间前已移出的除外）。上述（1）-（4）条以评审当日评审小组从官网查询信息为准。（5） 被国家管网集团或西南管道公司暂停、取消投标资格或业务承揽资格。（6）法律、行政法规规定的其他不允许 参与投标的情况。 国 四、询比文件的获取 4.1 有意向参加项目者，于2026年08月20日09时05分22秒前，登录数字供应链平台进行项目报名。 中 4.2 报名成功后于2026年08月18日09时01分42秒至2026年08月24日09时05分22秒，登录数字供应链平台进行项目下 载询比文件。 五、响应文件的递交 5.1 请于2026年08月24日11时00分00秒前，登录数字供应链平台递交项目响应文件。 5.2 逾期将无法进行递交响应文件，采购人将不予受理。 5.3 供应商在递交响应文件前，应按照有关规定提供人民币0万元项目保证金。 六、响应文件的开启 6.1 响应文件的开启时间2026年08月24日11时06分00秒 6.1 响应文件的开启地点供应链系统上 七、采购人信息 地址： 邮编： 联系人：舒建华 联系电话：18581824001 电子邮件：shujh@pipechina.com.cn 传真： 开户银行： 账户名： 账号： 信息来源:https://www.chinapipe.net/project/d3074904.html cqdingjiu 2026.08.21 10:06:59 网 务 商 道 管 国 中</t>
@@ -3968,7 +5044,11 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="P63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3983,7 +5063,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4001,16 +5081,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>安装部分包括材料验收、运输及履带式挖掘机及人工布管、管道管件安装、新旧管道的碰口、安装DN400直埋球阀1座、管道和商焊口的除锈及防腐、管道下沟后15KV电火花检测、管道的清管、强度及严密性试验、警示带敷设和线路标志桩（砖）安装、监检手续等。土建部分包括清表、扫线、平整场地、沟槽、基坑、阀井砌筑、回填土方、余方弃置、人工开挖人行道（花台）、公路及路面恢复、其他线缆穿跨越工道程施工、交通组织、水工保护等。</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>燃气管线工程</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>重庆燃气集团股份有限公司输配分公司大渡口调压站至二郎调压站次高压燃气管线工程(大渡口段)公告 采购 公告 公告编号： RQXYGG202608130064 一、采购项目基本情况 网 采购人：重庆燃气集团股份有限公司输配分公司 采购项目编号：RQCGXY202608130040 务 采购项目名称：大渡口调压站至二郎调压站次高压燃气管线工程（大渡口段） 采购内容或范围：安装部分： ①材料验收（甲供材料：阀门、管材、弯头、标志桩等）、运输及履带式挖掘机及人工布管； ②管道管件安装， 新旧管道的碰口；③安装DN400直埋球阀1座； ④管道和商焊口的除锈及防腐； ⑤管道下沟后15KV电火花检测； ⑥管道的清管，强度及严密性试验；⑦警示带敷设和线路标志桩（砖）安装； ⑧监检手续等。 土建部分： ①清表； ②扫线、平整场地； ③沟槽、基坑、阀井砌筑； ④回填土方； ⑤余方弃置； ⑥人工开挖人行道（花 台），公路及路面恢复； ⑦其他线缆穿跨越工道程施工，交通组织； ⑧水工保护等。 （具体内容详见施工图纸和 工程量清单） 公告发布时间 ：2026-08-18 14:39:10 管 二、采购人联系方式 联系人：王瑶 电话：023-67502265 国 邮箱：wangyao232@crcgas.com 三、采购明细 中 行号 采购内容 需求数量 单位 补充说明 拟邀请单位 大渡口调压站至二郎调压站次高压燃气管线 重庆燃气安装工程有限责任公 1 1 项目 无 工程(大渡口段) 司 四、服务费交纳 本项目不收取服务费。 五、 其他 事项 1.本公告在华润守正 采购交易 平 台（ https://www.szecp.com.cn/ ）上公开 发布。 2. 本项目采购通过守正平台线上进行，供应商需注册华润守正 采购交易 平台，通过平台进行响应文件的递交或 报价，具体操作步骤可查阅网站首页帮助中心的操作手册，也可以联系守正客服。 3 .答疑澄清、通知等文件一经在华润守正 采购交易 平台发布，视为已发放给相应供应商（发放时间即为发出时 间），请随时关注华润守正 采购交易 平台发布的相关信息，并及时查阅和处理。 4 .若有参与意向 ， 请于 2026-08-22 00:00:00前联系采购人 （联系方式见公示内容）反馈。 5 .若有异议 ， 请于 2026-08-22 00:00:00前提出异议 。 信息来源:https://www.chinapipe.net/project/d3074793.html cqdingjiu 2026.08.21 10:06:59 网 务 商 道 管 国 中</t>
@@ -4022,9 +5110,13 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4057,16 +5149,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-2027年度用户供水管道安装及管网抢（维）修服务</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>项目资金来自企业自筹，合同估算金额约280万元</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>供水管道安装及管网抢（维）修服务</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>石柱公司2026-2027年度用户供水管道安装及管网抢(维)修工程(第二次)项目公告 石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程（第二次）（比选公告 1.比选条件 本比选项目石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程（第二次）（项目名称），比选人 为重庆石柱水利水电实业开发有限公司，比选项目资金来自企业自筹（资金来源），项目已具备比选条件。现 对本项目进行公开比选，诚邀有兴趣的潜在投标人参与投标。 网 2.项目概况与比选范围 2.1 建设地点：比选人指定地点 务 2.2 项目概况与建设规模：2026-2027年度用户供水管道安装及管网抢（维）修服务 2.3 本次比选项目合同估算金额：约280万元 商 2.4 比选范围：完成石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程包括公司供水范围内用户 各类管道及管件安装、水表安装及更换、阀门安装等、并完成配套土建工程、零星签证等工程量清单所列项目、 管网抢维修和公司所属生产单元零星项目，具体内容详见第五章 工程量清单。 道 2.5 工期要求：1年 缺陷责任期要求：24个月 管 3.投标人资格要求 3.1 本次比选要求投标人须具备以下条件： 国 3.1.1 本次比选要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰级 及以上资质； 3.1.2 投标人还应在人员、设备、资金等方面具有相应的施工能力，详见比选文件第二章投标人须知前附表第1.4.1 中 项内容。 3.2 本次比选不接受联合体投标。 4.比选文件的获取 4.1 投标人于2026年08月18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子版， 以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都视为 投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的一切 后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价，递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，被视为无效。 4.4比选文件每份售价1000 元，售后不退。投标人在递交纸质投标文件时支付，否则比选人拒绝接收其投标文 件。 5.投标文件的递交 5.1电子投标文件递交时间：2026年08月24日10时00分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年08月24日09时30分至10时00分，地点：水务集团招标采购中心（重庆市两江新 区嘉华路36号重庆水务大厦五楼）。 5.3 投标截止时间：2026年08月24日10时00分（北京时间）。 网 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 务 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 商 比 选 人：重庆石柱水利水电实业开发有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市石柱土家族自治县都督大道11号 地 址：重庆市两江新区嘉华路36号重庆水务大厦1018 联 系 人：王老师 联 系 人：颜老师 道 电 话：13658292968 电 话：023-67901915 重庆水务电子商务平台咨询电话：管023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3074720.html cqdingjiu 2026.08.21 10:06:59 国 中</t>
@@ -4078,9 +5178,13 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>重庆, 供水管道安装, 管网抢修, 企业自筹, 280万元</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4113,16 +5217,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>万盛城区老旧供水管网更新改造工程涉及3PE防腐钢管的采购，其管道部分壁厚需符合国标标准并达到设计要求。</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>项目详情中未提及具体资金情况。</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>3PE防腐钢管</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>万盛城区老旧供水管网更新改造工程(甲供材料)答疑(一) 万盛城区老旧供水管网更新改造工程（甲供材料） 答疑（一） 各潜在投标人： 现将万盛城区老旧供水管网更新改造工程（甲供材料）答疑（一）相关条款通知如下： 网 一、答疑 问题1：请问招标人是否委派业主专家参与评标吗？ 务 答：是，本项目评标委员会共7人，其中在重庆市综合评标专家库随机抽取5人，招标人代表2人。 问题2：万盛的项目挂綦江来投这样都还控制不了还全是你们万盛公司中的？是有啥猫腻是吧？参考之前的项目 全是万盛的公司中的！业主、专家全是你们自己人吧？ 商 答：本项目招标文件严格按照《重庆市工程建设项目货物采购招标文件示范文本（2026年版）》编制，且本项目 评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 问题3：3PE管道部分壁厚是多少呢？ 道 答：本项目采购的3PE防腐钢管的管道部分壁厚须符合国标标准并达到设计要求。 招 标 人：重庆市万盛经济技术开发区城市管理局 管 招标代理机构：重庆力圣建设工程咨询有限公司 2026年8月18日 国 信息来源:https://www.chinapipe.net/project/d3074712.html cqdingjiu 2026.08.21 10:06:59 中</t>
@@ -4134,9 +5246,13 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 3PE防腐钢管, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4169,16 +5285,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>本项目涉及普通防腐钢管及管件的采购，包括各种规格的钢高频焊管和钢螺旋焊管，以及相应的管件如钢套筒、钢制标准接头等。</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>项目资金来自企业自筹，出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>钢高频焊管,钢螺旋焊管,钢套筒,钢制标准接头,钢制渐缩,钢制三通,钢制双盘短管,钢制弯头</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>重庆中法供水2026年普通防腐钢管及管件采购项目(第三次)项目公告 重庆中法供水2026年普通防腐钢管及管件采购项目（第三次）比选公告 1.比选条件 本比选项目重庆中法供水2026年普通防腐钢管及管件采购项目（第三次），比选人为重庆中法供水有限公司，比 选项目资金来自企业自筹，出资比例为100%，项目已具备比选条件。现对本项目进行公开比选，诚邀有兴趣的 潜在投标人参与投标。 网 2.项目概况与比选范围 2.1 普通防腐钢管及管件采购清单： 务 序号 存货编码 材料名称 规格型号 单位 数量 最高单价限价（元） 1 10400177 钢高频焊管 D89*4 5 米 61.92 2 10400181 钢高频焊管 D108*5 300 米 88.89 商 3 10400182 钢高频焊管 D159*5 5 米 132.18 4 10400206 钢高频焊管 D159*6 5 米 152.13 5 10400290 钢螺旋焊管 DN219*6 5 米 196.68 道 6 10400291 钢螺旋焊管 DN219*8 5 米 244.80 7 10400292 钢螺旋焊管 DN325*8 5 米 361.28 8 10400293 钢螺旋焊管 DN377*8 5 米 423.12 管 9 10400294 钢螺旋焊管 DN426*8 5 米 475.89 10 10400295 钢螺旋焊管 DN426*10 5 米 574.29 11 10400297 钢螺旋焊管 DN529*8 5 米 595.76 国 12 10400298 钢螺旋焊管 DN529*10 5 米 718.91 13 10400299 钢螺旋焊管 DN630*10 5 米 861.50 14 10400300 钢螺旋焊管 DN720*10 5 米 987.95 中 15 10400301 钢螺旋焊管 DN820*10 5 米 1133.08 16 10400302 钢螺旋焊管 DN920*10 5 米 1279.51 17 10400304 钢螺旋焊管 DN1020*10 5 米 1424.64 18 10400305 钢螺旋焊管 DN1020*12 5 米 1652.24 19 10400306 钢螺旋焊管 DN1220*10 5 米 1709.70 20 10400307 钢螺旋焊管 DN1220*12 5 米 1982.83 21 10400308 钢螺旋焊管 DN1420*12 5 米 2375.96 22 10400309 钢螺旋焊管 DN1420*14 5 米 2697.83 23 10400332 钢螺旋焊管 DN1120*10 5 米 1574.96 24 10400342 钢螺旋焊管 DN1020*14 5 米 1879.02 25 10400322 钢螺旋焊管（特加强） DN820*10 5 米 1133.08 26 10200490 钢套筒 D159*500cm 5 个 159.00 27 10200491 钢套筒 D219*500cm 5 个 240.00 28 10200492 钢套筒 D273*500cm 5 个 300.00 29 10200493 钢套筒 D325*500cm 5 个 361.00 30 10200494 钢套筒 D377*500cm 5 个 436.00 31 10200495 钢套筒 D426*500cm 5 个 482.00 32 10200589 钢套筒 D159*1000cm 5 个 226.00 33 10200590 钢套筒 D219*1000cm 5 个 1627.00 34 10200591 钢套筒 D273*1000cm 5 个 2501.00 35 10200592 钢套筒 D325*1000cm 5 个 488.00 36 10200593 钢套筒 D377*1000cm 5 个 591.00 网 37 10200598 钢套筒 D426*1000cm 5 个 833.00 38 10200155 钢制标准接头 D108 5 个 91.00 39 10200156 钢制标准接头 D159 5 个 160.06 务 40 10200157 钢制标准接头 D219 5 个 319.41 41 10200158 钢制标准接头 D273 5 个 396.63 42 10200159 钢制标准接头 D325 5 个 475.96 商 43 10200160 钢制标准接头 D426 5 个 619.87 44 10200161 钢制标准接头 D529 5 个 779.22 45 10200162 钢制标准接头 D630 5 个 1068.44 道 46 10200163 钢制标准接头 D720 5 个 1214.46 47 10200164 钢制标准接头 D820 5 个 1428.34 48 10200165 钢制标准接头 D920 5 个 1600.14 管 49 10200169 钢制标准接头 D1220 5 个 2297.57 50 10200170 钢制标准接头 D1420 5 个 3027.02 51 10200171 钢制标准接头 D1020 5 个 2194.19 国 52 10300309 钢制大小头 DN65*DN50 5 个 14.74 53 10200667 钢制渐缩 D108＞57 3 个 21.06 54 10200668 钢制渐缩 D108＞89 3 个 26.00 中 55 10200695 钢制渐缩 D159＞108 3 个 40.72 56 10200671 钢制渐缩 D219＞159 3 个 68.09 57 10200672 钢制渐缩 D219＞108 3 个 80.03 58 10201605 钢制渐缩 219*125 3 个 75.82 59 10200694 钢制渐缩 D273＞108 3 个 129.87 60 10200673 钢制渐缩 D273＞159 3 个 94.07 61 10200674 钢制渐缩 D273＞219 3 个 84.94 62 10200675 钢制渐缩 D325＞108 3 个 184.63 63 10200676 钢制渐缩 D325＞159 3 个 143.91 64 10200680 钢制渐缩 D325＞219 3 个 131.98 65 10200677 钢制渐缩 D325＞273 3 个 124.25 66 10200684 钢制渐缩 D426＞325 3 个 285.01 67 10200685 钢制渐缩 D529＞325 3 个 617.76 68 10200679 钢制渐缩 D529＞426 3 个 547.56 69 10200659 钢制渐缩 D630＞325 3 个 756.00 70 10200687 钢制渐缩 D630＞426 3 个 728.00 71 10201539 钢制渐缩 D630＞529 3 个 722.00 72 10200690 钢制渐缩 D720＞630 3 个 848.00 73 10200691 钢制渐缩 D720＞529 3 个 842.00 74 10200682 钢制渐缩 D820＞720 3 个 913.00 75 10200692 钢制渐缩 D920＞720 3 个 1053.00 76 10201519 钢制渐缩 D920*820 3 个 1064.00 77 10200652 钢制渐缩 D1020＞820 3 个 1305.00 网 78 10200693 钢制渐缩 D1020＞920 3 个 1322.00 79 10201738 钢制渐缩 1220*820 3 个 1806.00 80 10201507 钢制渐缩 1220＞1020 3 个 1834.00 务 81 10201624 钢制三盘三通 D108⊥108 3 个 224.64 82 10200371 钢制三盘三通 DN200⊥100 3 个 435.24 83 10200373 钢制三盘三通 DN200⊥200 3 个 599.51 商 84 10201531 钢制三通 108*108 3 个 58.97 85 10200285 钢制三通 219*108 3 个 187.43 86 10201341 钢制双盘短管 89*400mm 3 个 139.00 道 87 10201342 钢制双盘短管 89*800mm 3 个 178.31 88 10201340 钢制双盘短管 108*300mm 3 个 158.65 89 10201299 钢制双盘短管 DN108*500mm 3 个 185.33 管 90 10201300 钢制双盘短管 DN108*1000mm 3 个 258.34 91 10201301 钢制双盘短管 DN108*1500mm 3 个 329.94 92 10201332 钢制双盘短管 159*300mm 3 个 251.32 国 93 10201339 钢制双盘短管 159*750mm 3 个 348.19 94 10201303 钢制双盘短管 DN159*1000mm 3 个 402.95 95 10201304 钢制双盘短管 DN159*1500mm 3 个 508.25 中 96 10201305 钢制双盘短管 DN219*500mm 3 个 463.32 97 10201306 钢制双盘短管 DN219*1000mm 3 个 672.52 98 10201307 钢制双盘短管 DN219*1500mm 3 个 876.00 99 10201312 钢制双盘短管 DN219*750mm 3 个 581.26 100 10201338 钢制双盘短管 273*1250mm 3 个 1010.88 101 10201458 钢制双盘渐缩 108*57 3 个 109.51 102 10201469 钢制双盘渐缩 108*89 3 个 117.94 103 10201514 钢制双盘渐缩 159*108 3 个 185.33 104 10201748 钢制双盘渐缩 200*80 3 个 294.84 105 10201462 钢制双盘渐缩 219*108 3 个 256.93 106 10201513 钢制双盘渐缩 219*159 3 个 280.80 107 10201465 钢制双盘渐缩 D273＞108 3 个 339.77 108 10201467 钢制双盘渐缩 D273＞219 3 个 388.91 109 10201770 钢制双盘渐缩 D273＞159 3 个 365.04 110 10201461 钢制双盘渐缩 325*219 3 个 477.36 111 10301108 钢制弯头 89*90° 3 个 28.78 112 10200702 钢制弯头 D108×90° 100 个 43.52 113 10200701 钢制弯头 D159×90° 3 个 84.24 114 10200705 钢制弯头 D219*90° 3 个 231.66 115 10200706 钢制弯头 D273*90° 3 个 300.46 116 10200709 钢制弯头 D325*90° 3 个 418.39 117 10200711 钢制弯头 D426*90° 3 个 744.12 118 10200712 钢制弯头 D529*90° 3 个 1352.05 网 119 10200764 钢制弯头 D570*90° 3 个 1474.20 120 10200714 钢制弯头 D630*90° 3 个 1535.98 121 10200715 钢制弯头 D720*90° 3 个 1742.36 务 122 10200717 钢制弯头 DN720*90°*12mm 3 个 1989.47 123 10200720 钢制弯头 D920*90° 3 个 2935.30 124 10200722 钢制弯头 D820*90° 3 个 2325.23 商 125 10200762 钢制弯头 D1020*90° 3 个 4829.55 126 10200723 钢制弯头 D1220*90° 3 个 6039.80 127 10200724 钢制弯头 D1420*90° 3 个 8297.00 道 注：管材按照米数进行报价，管件按照件数进行报价。 2.2 供货数量、时间和批次：根据工程实际进度与比选人的要求进行供货，以实际供货量为准，供货时间达到商 务条款的规定。 管 2.3 交货地点：比选人指定的施工现场。 2.4 供货期：两年。 国 3.投标人资格要求 3.1 本次比选允许投标人以投标货物的下列身份参加投标： 中 ?制造商 3.1.1 投标人为制造商应符合以下要求： 投标人必须是依法设立的，并在中国注册的，具有独立法人地位的企业。 【提供有效的营业执照】 3.2 投标人2025年的年度财务状况不亏损。 【提供由会计师事务所或审计机构出具的无保留意见的财务审计报告及会计报表，财务报表至少包括现金流量 表、资产负债表、利润表】 3.3 投标产品的制造商须通过质量ISO9001、环境ISO14001、职业健康体系ISO45001认证。 【提供有效的证书】 3.4 投标人须提供2023年1月1日至投标截止日止（以合同签订时间为准）,签订的30万元及以上的钢管及管件产品 购销合同至少1个。 【提供采购合同、不低于前述金额50％的发票，合同与发票的项目名称须一致】 注：①若投标人开具的发票上未能体现具体项目，需附上税务出具的发票清单（清单上需显示采购项目为钢管 及管件产品）。 ②若提供的合同为年度合同未体现具体金额，但实际供货金额达到30万元及以上，应提供与该合同对应的30万元 及以上的钢管及管件产品发票作为佐证。 3.5 投标人须为所投投标产品制造商，此次所提供的普通防腐钢管及管件必须是自己工厂所制造的产品，不得外 购他人产品。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函及工商部门出具的本产品商标或品牌证明文件】 3.6 投标产品过水部分涉及的涂料须提供行政主管部门出具的有效的“卫生许可网批件”及卫生疾控中心出具的卫 生检测报告。 【提供行政主管部门出具的有效的“卫生许可批件”及卫生疾控中心出具的卫生检测报告】 务 3.5 根据本次采购清单及技术规范的要求，投标人须承诺具备相关的技术手段和措施、保证产品设计使用寿命 20 年以上。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 商 3.6 投标人须承诺保证5年内不得停产同型号的投标产品。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 道 3.7 办事机构和库房【比选人有权对中标人的办事机构及库房进行实地核查，若发现与提供资料不符，将视为提 供虚假资料，按相关规定取消其中标资格，其投标保证金不予退还。】 投标人承诺：收到中标通知书后30日内提供租赁合同或产权证明，并提供重庆库房卫星定位图片。 管 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 【卫星定位图片：手机打开地图，搜索该地址、进行标注，然后截图或者电脑打开地图（地图软件不限），搜 索该地址、选择卫星模国式、进行标注、然后截图均可。】 3.8 符合第五章“技术要求”普通防腐钢管及管件技术要求。 【根据技术要求提供技术响应表，并根据技术条款要求提供对应的检测报告等。】 中 3.9 售后服务承诺【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】： 1）货物交付及付款方式要求，满足第四部分合同协议书第3条及第10条；供货单位应确保产品的及时供应，承诺 因产品供应不及时造成的一切损失均由供货单位负责赔偿。 2）有完整的售后服务方案、培训计划并在合同签订后为比选人免费提供培训服务。 3）售后服务承诺书，满足第四部分合同协议书第11条；承诺质保期后提供2年及以上定期免费巡查、保养计划。 4）承诺接到分派的工单1小时内联系用户约定维修时间，在24小时内处理完毕工单，且让用户满意。若工单超时、 未在规定时间内告知比选人维修时间或工单处理未让用户满意造成返单的，按比选人制度进行处罚。 3.10 投标人承诺不得存在下列情形之一： 1）被人民法院列入失信被执行人名单且在被执行期内； 2）被国家、重庆市（含市或任意区县）有关行政部门行政处罚，且在处罚期限内； 3）投标截止日前两年内（指2024年1月1日至投标截止日止），投标人或其法定代表人被人民法院判定犯行贿罪 的； 4）投标截止日前五年内（指2021年1月1日至投标截止日止），投标人与重庆中法供水有限公司有违约情况或终 止合同情况的。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 3.11 投标截止日前五年内（指2021年1月1日至投标截止日止），投标人无在我司因产品及服务等对公司生产、经 营、安全造成不良影响的记录；若投标人出现过供水通报事项，因产品质量问题对生产、安全造成影响，存在 合同违约等问题，不予参加本次项目投标。 【按照第六章 三、资格审查部分“无不良记录承诺函”提供承诺函，若经验证承诺函不属实，将对中标人作否 决投标处理。】 网 3.12 投标样品要求： 3.12.1 投标人需提供以下规格型号数量的样品： 务 【①钢螺旋焊管 DN219*8 壹件 ②钢制弯头 D108*90°壹件】，提供的样品应满足第五章技术要求规定。样品为 投标人免费提供，管材样品不低于20CM，不计入采购清单内。 3.12.2 投标样品同投标文件一并递交。每件样品上分别标明样品的投标人、生产厂家、品牌、名称、规格、型号等 （格式自拟），投标样品必须密封装箱，且在密封包装外商贴样品一览表（格式自拟），注明提供样品的投标人、 生产厂家、品牌、名称、规格、型号、数量等。 3.12.3 投标人的样品在开标当日递交至样品区（样品区地点：开标当日咨询比选代理机构），中标人的投标样品 不退还，其余投标人的样品在中标公示期满后道5个工作日内退还，如不领取，投标样品按废品处理。 3.12.4 上述对投标样品的密封和标识要求是为便于评标，请投标人积极配合，未按上述要求对投标样品进行密封 和标识的，不作否决投标处理，但由此造成的其他后果由投标人自行承担。 管 3.13 若投标人违反重庆中法供水有限公司《供应商负面清单管理办法》规定且在处罚期内的，按否决投标处理 （评标委员会根据比选公告后附“供应商负面清单”进行评审）。 3.14 本次比选不接受联合体投标。 国 特别说明： （1） 本比选文件要求提供的所有检测报告须为近2年内的检测报告（2024年1月1日-投标截止日），此要求不包 括卫生许可批件及其检测报告。 中 （2） 上述所须提交的相关证明材料复印件均应加盖投标单位法人章并装入投标文件资格审查部分中。上述有一 条不满足则投标文件由评标委员会作否决投标处理。 （3） 比选人有权对投标人提供的以上资料进行核实，若发现存在弄虚作假，取消其投标、中标资格，投标人承 担因此造成的相关责任并赔偿相应损失。 4.比选文件的获取 4.1 投标人于2026年8月18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子版， 以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都视为 投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的一切 后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价，递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，被视为无效。 4.4比选文件每份售价 500 元，售后不退。投标人在递交纸质投标文件时扫描支付，否则比选人拒绝接收其投标文 件。 5.投标文件的递交 5.1电子投标文件递交时间：2026年8月26日14时30分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年8月26日14时00分至14时30分，地点：水务集团招标采购中心（重庆市两江新 区嘉华路36号重庆水务大厦五楼。导航：重庆水务大厦东门）。 5.3 投标截止时间：2026年8月26日14时30分（北京时间）。 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 网 6.发布公告的媒介 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 务 7.联系方式 比 选 人：重庆中法供水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝北区悦来镇悦来水厂 地 址：重庆市两商江新区嘉华路36号重庆水务大厦10楼1018 联 系 人：陈老师 联 系 人：周洲 电 话：023-67585971 电 话：18602396399 道 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3074673.html 管 cqdingjiu 2026.08.21 10:06:59 国 中</t>
@@ -4192,7 +5316,11 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="P67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4225,16 +5353,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>南岸区</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>南岸区</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>本项目比选范围修改为：在项目动工前完成水土保持方案审批程序，项目建设过程开展水土保持监管测工作。</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>供水管网</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>南岸区茶园片区乡镇老旧供水管网更新改造工程更正公告 南岸区茶园片区乡镇老旧供水管网更新改造工程更正公 告 发布日期： 2026年8月18日 网 首次公示日期： 2026年8月14日 更正日期： 2026年8月18日 采购人名称： 重庆市江南城市建设发展（集团）有限公司务 采购人地址： 重庆市南岸区米兰路51号电子信息标准化厂房2号楼 联系人： 赵老师 商 电话： 023-62820331 采购代理机构名称： 重庆多杰数字科技咨询服务有限公司 采购代理机构地址： 重庆市重庆市经开区重庆市经开区长生桥镇江峡路8号13-1幢1楼 道 经办人名称： 李佩奇、戴沛轩、李倩 联系电话： 023-67648437 本项目比选范围修改为：在项目动工前完成水土保持方案审批程序，项目建设过程开展 更正事项： 水土保持监管测工作。 https://www.gec123.com/notices/detail/1665701682723590144 信息来源:https://www.c国hinapipe.net/project/d3074669.html cqdingjiu 2026.08.21 10:07:01 中</t>
@@ -4246,9 +5390,13 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>重庆, 管材招标, 商机</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4281,16 +5429,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>中铁十一局集团宜涪高铁3标项目，位于重庆市石柱土家族自治县。合同金额28.01亿元，合同工期73个月，主要工程包括新方斗山隧道、石板坡隧道、城北隧道、刘家坪隧道、刘家店子1号大桥工程、刘家店子2号大桥、城北大桥、冉家湾大桥，采用移动模架和支商架法现浇施工，正线铺无砟道床43.808Km。</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>合同金额28.01亿元</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>排水钢管Φ200*6m</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部排水钢管询价采购公告 中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 排水钢管询价采购公告 询价编号：ZT1105-XJ-2026-561-1 尊敬的各潜在供应商: 网 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与中铁十一局集团有限公司宜涪高铁重庆段站 前3标项目经理ZT1105-XJ-2026-561-1，排水钢管材料的报价。 一、项目概况 务 中铁十一局集团宜涪高铁3标项目，位于重庆市石柱土家族自治（县）。合同金额28.01亿元，合同工期73个月， 开工日期：2024年12月，竣工日期：2030年12月。主要工程：新方斗山隧道(10660m)、石板坡隧道(4148m)、城北 隧道(3228m)、刘家坪隧道(2077m);刘家店子1号大桥工程(224.096m)、刘家店子2号大桥(232.099m)、城北大 桥(330.241m)、冉家湾大桥(355.245m),采用移动模架和支商架法现浇施工，其中24米移动模架施工6孔；32米支架法 施工5孔，移动模架施工28孔;正线铺无砟道床43.808Km。 二、询价内容 道 本次计划对排水钢管、GG-01材料进行询价，询价内容如下： 询价物资一览表 管 序号 包件号 物资名称 规格型号 计量单位 数量 备注 1 GG-01 排水钢管 Φ200*6m 米 3000 Q235B，壁厚6mm 合计 3000 国 说明：1.表中数量为计划数量，实际采购过程中可能有所调整，最终结算按照实际采购数量结算。 2.收货地点：中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 中 三、技术质量及报价要求 1. 此次排水钢管、GG-01各项技术性能：Q235B 碳素结构钢无缝钢管，符合 GB/T8163 标准。质量需满足甲方项 目部正常使用的要求，保证产品的质量合格，满足试验室检测所有要求，详见技术规格书。 2.报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、结算及付款方式 自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发票认证完成之日起第6个月，支付至本次结算 金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内，累计支付总额不超结算总金额的75%，剩 余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理末次结算后第二年，支付金额应大于等于 尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总额的15%；办理末次结算后第四年，全部 付清）。 五、报价人资格要求 1.营业范围要求：在中华人民共和国境内依法注册、符合项目经营范围，具有询价物资生产或供应经验 的生产商或代理商，并且具有合法有效的营业执照。 2.生产能力要求：生产商须具备询价物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定。代 理商需出具制造厂出具签字盖章的授权函。 3.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8 月至今）国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；需满足排水钢管的相关所 有要求。 4.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年12月至今）企业或企业法定代表人有人民法院生效判决、裁 定认定的行贿犯罪记录的。④ 对纳入国家铁路局“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接 受通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合 作方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 网 5.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 务 ★6.下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 六、报价人需要提供的资料 1.营业执照复印件、法人身份证复印件、开户许可证、授商权委托书、报价表和报价人资格要求中所需的证明资料， 所有资料需加盖公司鲜章。 2.生产厂家资质，产品质量检测报告等质量证明文件。 道 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、询价报名截止时间 管 有意参加本次询价采购的报价人须在铁建云链平台（https://www.crccep.cn）完成供应商注册，并于2026年8月18 日9时00分至2026年8月21日9时00分在网上完成报名工作。 八、询价截止时间 国 凡有意参加本次询价采购的报价人，请于 2026年8月21日14时00分 前提交报价。截止时间前未完成报价文件传 输的，视为放弃报价。 供应商报价必须严格按照《报价表》格式进行报价。 中 九、联系方式 采购组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村71号 采购人名称：中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 地址：重庆市石柱土家族自治县金彰工业园区C区中铁十一局项目部 联系人：罗先生 联系电话：18580400001（提供采购服务支持） 中铁十一局集团有限公司 物资设备集中采购管理中心第五分中心 2026年8月18日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3074654.html cqdingjiu 2026.08.21 10:07:01 网 务 商 道 管 国 中</t>
@@ -4302,9 +5458,13 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>重庆, 排水钢管, 询价采购</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4337,16 +5497,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>重庆协同创新区供冷供热能源站及配套系统工程冷却塔、分集水器、水板式热交换机组采购。</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>冷却塔、分集水器、水板式热交换机组</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>中铁建设集团(重庆)建设有限公司重庆协同创新区供冷供热能源站及配套系统工程冷却塔、分集水器、水板式热 交换机组采购竞价补遗公告二 各 投标单位 ： 根据参加报名的潜在投标单位数量不满足招标方充分竞价要求的情况，此次重庆协同创新区供冷供热能源站及 配套系统工程冷却塔、分集水器、水板式热交换机组采购竞价资格预审报名截止日期将延期至 8月19日（周三） 上午9:00。 特此说明。 网 中铁建设集团（重庆）建设有限公司 2026年8月17日 务 信息来源:https://www.chinapipe.net/project/d3074650.html cqdingjiu 2026.08.21 10:07:01 商 道 管 国 中</t>
@@ -4358,9 +5526,13 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>重庆协同创新区, 供冷供热能源站, 冷却塔, 分集水器, 水板式热交换机组, 采购竞价</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4393,16 +5565,32 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>城口县</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>城口县</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>在城口县东安镇新建一座污水处理站，铺设不同直径的污水管道共计29.3公里，包括dn110、dn160、dn200、DN300、DN400等规格的污水管道，以及DN200压力管道7.4公里，建设配套泵站2座和化粪池56座、隔油池32座。</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>合同预估金额为3400万元人民币。</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>污水管网、泵站、化粪池、隔油池</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>城口县东安及河鱼片区污水管网建设项目(一期)招标计划表 重庆市工程建设项目招标计划表 项 名 目 称城口县东安及河鱼片区污水管网建设项目（一期） 招标 法人 或招 标人城口县生态环境局 名称 （盖 网 章） 项目 批准 文件 及文 号 主 建 内 要 设 容 在 污 城 水 口 处 县 理 东 站 安 1座 镇 ， 等 改 片 建 区 后 新 设 建 计 污 规 水 模 管 20 网 0m 29 3 . / 0 d 0 。 km，其中新建dn110污水管5.80km，dn160污水管2.75km，dn200污水管0.57km，DN300污水干管4.36km，D 务 N400污水干管8.12km，DN200压力管7.4km,以及建设配套泵站2座,化粪池56座，隔油池32座。改扩建 序号 招标项目名称 招标内容 招标方式 招标文件计划发布时间 拟交易场所 合同预估金额(万元) 备注 招 项 标 目1 城 建 口 设 县 项 东 目 安 （ 及 一 河 期 鱼 ） 片区污水管网 工程施工 公开招标 2026-09 城 易 口 中 县 心 公共资源交 3400.00 本 暂 为 计 定 准 划 ， 。 表 最 所 终 列 以 招 实 标 际 项 招 目 标 信 时 息 的 均 信 为 息 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3074602.html 商 cqdingjiu 2026.08.21 10:07:01 道 管 国 中</t>
@@ -4414,9 +5602,13 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>重庆, 管材, 招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4449,16 +5641,24 @@
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>场平面积800亩；新建厂房10000平方米，并完善相关基础配套设施等；新建道路长4000米，包括道路、综合管网等基础配套设施等。</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>本项目工程总投资金额：55000万元 本次招标项目合同估算金额：184.669075万元</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>土石方开挖回填、砼支墩、污水管道安装、检查井砌筑、河堤修复等</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>阀门产业园(管网改造)项目招标公告 阀门产业园（管网改造）项目招标公告 1.招标条件 本招标项目 阀门产业园（管网改造）项目已由垫江县发展和改革委员会以垫江发改委发【2022】459 号（批文 名称及编号）批准建设，项目业主为 垫江县丹香建设有限公司，建设资金来自 自筹资金 （资金来源）， 项目出资比例为 100% ，招标人为 垫江县丹香建设有限公司。项目已具备招标条件，现对该项目的施工进 行公开招标，评标办法采用经评审的最低投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 重庆市垫江县高新区县城组团 2.2 项目概况与建设规模： 场平面积800亩；新建厂房10000平方米，并完善相关基础配套设施等；新建道路 务 长4000米，包括道路、综合管网等基础配套设施等。 2.3 本项目工程总投资金额：55000万元 本次招标项目合同估算金额：184.669075万元 商 2.4 招标范围： 包括土石方开挖回填、砼支墩、污水管道安装、检查井砌筑、河堤修复等。具体详见施工图和 工程量清单。 道 2.5 工期要求：建设工期180日历天 缺陷责任期要求：24个月 管 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 国 3.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 中 4.1.1 本次招标要求投标人具备的资质条件： 具备建设行政主管部门颁发的有效的市政公用工程施工总承包叁 级及以上资质 ； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标 不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （垫江县）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（垫江县）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资 源交易监督网、重庆市公共资源交易网（垫江县）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 4.2投标人可在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）本项目招标公告网页下方“我要 提问”栏提出疑问，提问时间从本公告发布至2026-08-24 09:00:00前。 4.3招标人应于2026-08-24 23:59:59前在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-18 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 垫江县丹香建设有限公司 代理机构: 重庆博钰大数据科技有限公司 地 址: 地 址: 重庆市垫江县桂溪街道南内街88号 网 邮 编: 邮 编: 项目负责人: 熊老师 项目负责人: 郭威 电 话: 023-74630098 电 话: 023-74692498 务 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 商 账 号: 账 号: 监督部门: 垫江县发展和改革委员会 电 话: 023-74517161 道 2026年08月18日 信息来源:https://www.chinapipe.net/project/d3074578.html cqdingjiu 2026.08.21 10:07:02 管 国 中</t>
@@ -4470,9 +5670,13 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>重庆, 管网改造, 投资金额, 产品种类</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -606,8 +606,16 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>璧山区</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>璧山区</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>本项目位于璧山区，建设范围为双龙大道以北，璧铜线以东、渝蓉高速以南、玉泉湖（璧南河）以西区域，用地面积约6平方公里。项目建设遵循循序渐进、分期、分块实施原则，采用“总体开发、分步实施”的方式进行建设开发，合作期限8年，包含建设期和运营期（缺陷责任期），其中建设期6年，共分三期实施。第一期实施玉泉湖以西，第二期实施璧南河以西，第三期实施渝蓉高速下道口。项目总投资44亿元，其中建安费28.6亿元，含市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。项目开发建设内容包括片区范围内的基础设施、人才教育基地、水系生态整治、绿化及广场、公共交通场等。本次采购的内容为本项目一期实施的市政道路所需的钢筋混凝土管及管件，预计供货时间为2026年8月至2027年4月。</t>
@@ -826,8 +834,16 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>忠县</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>忠县</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)，包括田块整治、灌溉与排水、田间道路、地力提升和其他工程。</t>
@@ -1350,8 +1366,16 @@
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>新建50m³蓄水池4口、取水池2座；新建50m³/d-100m³/d水厂2座；改造100m³/d-300m³/d水厂5座；铺设DN25-DN250涂塑钢管约86km；新建提水泵站8座；配套阀井、电磁流量计等有关设施。</t>
@@ -2154,8 +2178,16 @@
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>本项目主要涉及室外蒸汽管道φ219x6mm的安装，管道材质为20#，地上敷设，蒸汽管道运行压力1.08MPa，管道设计压力1.2MPa。蒸汽管道系统包括从锅炉房分汽缸到6#和8#车间分汽缸的所有蒸汽管道、管件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸等的采购、运输、安装、保温工作。还包括钢结构桁架工程的采购、运输、制作、安装、防腐工作，以及管道附件及控制系统的采购、运输、安装、接线等工作。此外，还需要进行调试与验收，确保蒸汽管道系统能够正常使用并备案。</t>
@@ -2222,8 +2254,16 @@
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>巴南区</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>巴南区</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>完成重庆国际生物城配套公寓项目（民用1020户）天然气表后管道定制化服务。（含安装燃气输送用不锈钢波纹管RSB-IF-13—12240米（预估）、双外螺纹球阀DN15-1020个、燃气管道自闭阀DN15-1020个，其它配套管件及辅材，墙体管道暗埋等）</t>
@@ -2426,8 +2466,16 @@
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>永川区</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>永川区</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>蒸汽管道改造</t>
@@ -2646,8 +2694,16 @@
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>大渡口区</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>大渡口区</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标。</t>
@@ -3458,8 +3514,16 @@
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>北碚区</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>北碚区</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>改造取水泵站一座，改造DN600供水管网2.9km，DN50~DN300供水管网88.863km，DN25供水管网68.5km及其附属设施。</t>
@@ -3678,8 +3742,16 @@
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>整治De315原水管长1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1套及配套电气工程。</t>
@@ -4118,8 +4190,16 @@
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>石柱土家族自治县</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>石柱土家族自治县</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>本次修复选择开挖换管：开挖约80米，2孔110波纹管、2孔蜂窝管，新建两通信手控井。</t>
@@ -5082,8 +5162,16 @@
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>大渡口区</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>大渡口区</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>安装部分包括材料验收、运输及履带式挖掘机及人工布管、管道管件安装、新旧管道的碰口、安装DN400直埋球阀1座、管道和商焊口的除锈及防腐、管道下沟后15KV电火花检测、管道的清管、强度及严密性试验、警示带敷设和线路标志桩（砖）安装、监检手续等。土建部分包括清表、扫线、平整场地、沟槽、基坑、阀井砌筑、回填土方、余方弃置、人工开挖人行道（花台）、公路及路面恢复、其他线缆穿跨越工道程施工、交通组织、水工保护等。</t>
@@ -5150,8 +5238,16 @@
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>石柱土家族自治县</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>石柱土家族自治县</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>2026-2027年度用户供水管道安装及管网抢（维）修服务</t>

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -566,11 +566,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>重庆, 管材, 询比采购</t>
+          <t>塑料管不计匹配分</t>
         </is>
       </c>
     </row>
@@ -4294,11 +4294,11 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标</t>
+          <t>塑料管不计匹配分</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 改造, 配水主支管道, 更换配水主管网, 抗菌耐磨涂塑钢管, PE管, 泵站改造, 集成泵站, 蓄水池整治, 测控井</t>
+          <t>重庆, 管材招标, 改造, 配水主支管道, 更换配水主管网, 抗菌耐磨涂塑钢管, 泵站改造, 集成泵站, 蓄水池整治, 测控井</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>涪陵区, 珍溪镇, 农村供水, 提升工程, PE管, 衬塑钢管, 水泵, 不锈钢水箱, 减压阀, 排污阀</t>
+          <t>涪陵区, 珍溪镇, 农村供水, 提升工程, 衬塑钢管, 水泵, 不锈钢水箱, 减压阀, 排污阀</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 雨水管网, 高密度聚乙烯, HDPE, 钢筋混凝土管</t>
+          <t>重庆, 管材, 招标, 雨水管网, 高密度聚乙烯, 钢筋混凝土管</t>
         </is>
       </c>
     </row>

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>PDF来源网页链接</t>
+          <t>产品用量</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
@@ -560,11 +560,7 @@
           <t>中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管 材询比采购公告 中铁十一局集团有限公司建安分公司招标采购中心就中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房 及配套综合交通枢纽工程CQZSG-2标段项目经理部管材组织询比采购，诚邀有意向的合格供应商参与报价。 一、项目概况及询比采购内容 1.1项目概况 网 （1）新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程位于重庆市中心渝中区中部，具体位置为菜园 坝立交桥以西，龙家湾隧道以东，菜袁路以北，王家坡以南。正在建设的地铁18号线贴临站房北侧，地铁26/27 号线从站区地下通过。项目共划分为4个施工标段，CQZSG-1标段：为国铁站房、地铁站台区域；站北路密不可 分的边坡及场坪工程，包含土石方工程和边坡支护工程，不含机电工程，由中铁建设承建。CQZSG-2标段：为 务 枢纽配套工程，地铁区间、西广场、成都局剩余还建，由中铁十一局承建。CQZSG-3标段：地铁区间、CTC、 站场、东广场，由中铁建工承建。CQZSG-4标段：人防车库、铁路自营车场、综合开发生产配套房屋等，由中 铁二局承建。 （2）标段概况：我方负责新建重庆至黔江铁路重庆站站商房及配套综合交通枢纽工程CQZSG-2标段全部施工内容 （简称B区），主要包含：（1）B区投影范围内盖板以下27号线、26号线明挖区间基坑支护、土石方、区间主体 结构及配套防水、综合接地工程（不含砌筑墙体、装饰装修和机电安装工程），以及承轨层以下市政排水 涵DK1+196（196m）和行包通道；（2）轨道交通26号线暗挖隧道预留工程，其中26左线487m，26号右线408m； （3）站北路E、F、H连接匝道工程，其中E匝道道247m、F匝道285.5m、H匝道174m；（4）B区盖板及以上还建房 屋，其中西侧盖板约3.56万㎡，还建房屋等总建筑面积约3.50万㎡。 1.2询比内容 详见拟采购货物一览表 管 二、供应商资格要求 2.1供应商必须是“中国铁建云链平台”注册并通过审核的供应商。 2.2本次询比采购不接受国被列入“《2026年中国铁建合作方警示名录》、《中铁十一局集团有限公司不良行为供 应商名录》、《JD采购网失信名单》（此项核查针对JMRH项目）”中的供应商,不接受近一年内在铁路建设工程 网公布有违法行为记录及物资供应不良记录、被中国铁路总公司限制投标或已清退出铁路市场的供货商（此项 核查针对铁路站房项目），不接受在铁建云链平台被标记的不良行为供应商。 中 2.3供应商在报价时，如是法定代表人签字的需提供法定代表人身份证复印件、如是法人授权代理人签字的需提 供授权委托书及被授权人身份证复印件。 2.4询比响应供应商需提供营业执照复印件。 2.5其它要求：提供样品、每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌 等质量证明文件，甲方凭此报告检验质量。 2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 三、拟采购物资及相关要求 3.1拟采购物资一览表 交 序 物资 型号 单 项目 货 交货日 数量 备注 号 名称 规格 位 名称 地 期 址 重 直 庆 径6:0mm 市 包含车 PVC 批次交 壁 渝 丝、黑 1 （袖 米 7100 货与零 厚4:-45.mm 中 色胶布、 阀管） 星交货 单节 新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 区 管筛、 （具体 长4m CQZSG-2 标段项目经理部 菜 管箍、 以项目 园 堵头等 通知为 坝 一切相 准） 直 网 重 关费用 2 PE管 米 7100 径2:5mm 庆 站 合计 14200 务 3.2技术规格书： 按询比文件第二章项目技术规格书执行 商 3.3结算和付款 3.3.1采购物资报价规则： 道 固定价格。 3.3.2付款方式 （1）货款支付方式：支付方式包管括但不限于银行转账、银行汇票、银行本票、支票、银行承兑汇票、商业承兑 汇票、财务公司票据、供应链票据、其他数字化信用凭证，票据贴息费用由 供货单位 承担。 （2）付款周期：本合同无预付款。甲方在收到乙方提交的合规增值税专用发票，并经税务机关认证通过后次月 支付乙方上月供应期所国供合格物资70%货款，全部货物供应完毕后三个月内付至95%，剩余货款暂时扣留作为质 量保证金，供货完毕后，由乙方提交结算确认单，经甲方审核通过后做最终结算，待所有物资验收合格后12个月 内无息付清。 （3）逾期付款约定：如甲方付款逾期，双方秉持“长期合作，友好往来”原则，在逾期付款行为发生后一年内 中 乙方不向甲方收取逾期付款利息。若一年甲方仍未支付款项，需向乙方支付逾期付款利息，逾期付款利息起算 时间为全部款项到期之日一年后至付清之日，逾期利息的利率为合同订立时中国人民银行授权全国银行间同业 拆借中心公布的一年期贷款市场报价利率(LPR)1倍。 3.4拟采购物资相关的要求 3.4.1本次询比为整体采购，询比响应供应商报价时须写明单价、到站价和运距，报价包含货物制造、运输、装卸、 售后服务等交付采购人使用前所有可能发生的费用，收到报价后不再增补任何费用。 3.4.2交货期：按照采购人规定的期限内分批次运抵交付。 3.4.3供货地点：甲方指定的甲方所属 中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通 枢纽工程CQZSG-2标段项目施工现场。 3.4.4询比响应供应商必须保证产品的质量及售后服务。询比响应供应商提供的货物制造标准及技术规范等，必须 符合最新相关国家标准、部颁标准相关标准和规范的要求，进场提供相关检验检测报告。 3.4.5采购方在确定成交供应商后有权对成交产品的结构、规格做适当调整，调整内容将以工作联系函形式提前发 至供应商。 3.4.6售后服务：本批采购货物若在验收阶段出现不符合规格或质量标准，供应商必须接受退货要求，并在采购人 规定期限内等量补运合格产品，若未按时交付影响采购人使用，供应商必须承担由此给采购单位造成的后续经 济损失。 3.4.7报价方不得虚报各项技术指标，所供货物若不能符合技术要求，成交供应商必须接受全额退还货款，并承担 由此给采购单位造成的经济损失。 3.4.8验收方法及标准 （1）验收依据：询比采购文件、厂家货物技术标准说明及国家有关的质量标准规定，均为验收依据。 （2）货物验收：货物运抵采购人指定交货处后由双方对照采购清单及技术要求进行验收。 （3）其它要求：每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌等质量证 明文件，甲方凭此报告检验质量。 网 （4）2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 四、报价文件递交 务 4.1此次报价供应商需制作电子报价文件，在递交截止时间前线上递交报价文件。 4.2报价文件递交截止时间：2026年08月24日15时00分。 商 4.3报价文件递交地点：中国铁建云链平台（www.crccep.cn），供应商须登录该平台，在报价文件递交截止时间 前完成所有报价文件资料的上传。 五、发布公告的媒介 道 本次询比公告发布媒体:中国招标投标公共服务平台(www.cebpubservice.com)、中国铁建云链平台（www.crccep.cn） 上同时发布。 管 六、联系方式 1.采购组织单位：中铁十一局集团有限公司建安分公司招标采购中心 地 址：湖北省武汉市国武昌区丁字桥路47号 联 系 人：张先生 联系电话：027-87258521 中 电子邮件：2454774350@qq.com 2.采购人：中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 CQZSG-2 标段项 目经理部 地 址：重庆市渝中区菜袁路59号 联 系 人：金先生 联系电话：16607273445 电子邮件：2285445503@qq.com 2026年08月21日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3077066.html cqdingjiu 2026.08.21 10:06:40</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3077066.html</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
         <v>0</v>
       </c>
@@ -636,11 +632,7 @@
           <t>璧山项目钢筋混凝土管询价公告 本项目位于璧山区，建设范围为双龙大道以北，璧铜线以东、渝蓉高速以南、玉泉湖（璧南河）以西区域，用 地面积约6平方公里。项目建设遵循循序渐进、分期、分块实施原则，采用“总体开发、分步实施”的方式进行 建设开发，合作期限8年，包含建设期和运营期（缺陷责任期），其中建设期6年，共分三期实施。第一期实施玉 泉湖以西，第二期实施璧南河以西，第三期实施渝蓉高速下道口。项目总投资44亿元，其中建安费28.6亿元，含 市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。项目开发建设内容包括片区范 围内的基础设施、人才教育基地、水系生态整治、绿化及广场、公共交通场等。本次采购的内容为本项目一期 实施的市政道路所需的钢筋混凝土管及管件，预计供货时间为2026年8月至2027年4月。 网 登录地 mhem&amp;cNh6e0&amp;ce2C2m3s1e71=a64so0d9FAe=0903%e08005206E%6772dm6=%82he29&amp;=cI8p9eeyAs%7t?E%5lB%1iB%a1DetE%c9eweNAi%1iotvB%n/9cE%7.cBe9%ccAiE%p.E%s9%/29址/A%2:：psE%7tAhtD%B8%E%6B%7B%7E%5%78D9%E%5C9%F%9E%7AE%A%1E%9%78%78E%8B%4AD%N&amp;8E%6m657optUa3%6=6290%e3ni51B%5917E%443d6=E%862B%I8eAc%A1iD&amp;88no%tE%4BA%A%4E%7AC%AC%E%4BA%C8%E%8%88AA%E%5A8%A%1E%5B%7A%5E%7A%8B8%E%5B%1%08E%6C9%%98E%9%99%09E%5%58AC%E%5F%8B%8E%8A%5BF%E%9%38A%8EF%BC%%88E%5B9%BD%E%9%99%58EF%BC%%98E%6%59B%0E%5AD%%79E%7BB%F%8E%6B%5E8%E%4BA%A%7E%4B%8A9%E%5B9%AD%E%5C8%BA%E%9%58D8%E%5A%5%79E%9A%1B%9E%7B9%AE%EF%BC%%88E%8A%5BF%E%7%98%78E%5C8%BA%EF%BC%%98E%9A%1B%9E%7B9%AE%E%7=BgB&amp;upC%a=sod&amp;euF%pN=8Flk&amp;cmsusheaE%c7=te%0a9m%6he=8tT&amp;cpS7eeyeE%s9sha%&amp;3c2845d5=pur5A6I&amp;8optUni 信息来源:https://www.chinapipe.net/project/d3077008.html 务 cqdingjiu 2026.08.21 10:06:40 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3077008.html</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>70</v>
       </c>
@@ -712,11 +704,7 @@
           <t>中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购公告 物资采购 【招标公告】中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购 招标编号：cscec2026081900001246027 项目：重庆市第四人民医院科学城院区建设项目（二期） 发布时间：2026-08-20 17:52:30 报名截止：None 区域：重庆市市辖区沙坪坝区 招标品类：其他类 招标（资格预审）公告 网 中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料采购 采 购 文 件 务 采 购 人： 中国建筑第七工程局有限公司 日 期： 2026年8月 商 目 录 一、响应须知 道 二、评审办法 三、响应注意事项 管 四、响应文件的上传 五．响应文件 六、物资设备合同 国 一、响应须知 【公司总部供应链中心业务监督电话：17516461564】 中 1、工程概况： 工程名称：临水临电材料采购 采购名称： 中国建筑第七工程局有限公司重庆区域暨重庆市第四人民医院科学城院区建设项目 (二期)临水临电 材料采购 采购编号： cscec2026081900001246027 项目地址： 重庆市 工程内容：重庆市第四人民医院科学城院区建设项目 (二期)建筑总用地面积15214.5平方米；总建筑面积65020平 方米，其中住院楼22229.9平方米，实验教学楼8103.6平方米，院内生活楼5830.59平方米，高压氧舱315.53平方米， 地下车库28540.38平方米，以及给排水工程、强电工程、弱电工程、消防工程、暖通工程、总图工程等。为参考。 （说明：描述本工程概况）。最终工程规模及内容以上级部门及采购人确定为准。 采购概算金额：135万元（含税）【采购概算金额视为最高采购限价，响应人响应报价高于最高采购限价的，作 无效响应处理】。 2、采购范围及相关要求： （1）资格审查方式： 资格后审 （2）采购联系人：项目联系人： 修经理 ，电话： 17838218888 ，地址：重庆市 公司联系人： 苟经理 ，电话： 19828530610 ，地址：四川省青白江国际贸易产业园10幢 （3）采购内容： 临水临电材料 （4）工程价款支付： 月结方式，即每月20日结算（遇节假日顺延），次月25日前（结算日后35日历天内），乙 方提供与结算等额增值税专用发票后，支付至前月结算额的70%（遇节假日顺延），最终结算办理完毕6个月后 付至最终结算价款的 97%，剩余3%质保金在质保期满后30日内无息支付。（质保期自全部货物供货完毕且验收 合格日起1年计算）（支付工程款时均应扣除根据采购合同应予扣除的其它金额。） 网 3、响应方式： （1）响应保证金缴纳方式 务 响应保证金采用保证金现金或购买保证金保险（二选一）两种支付方式，支付成功后点击页面【去响应】按钮， 响应人方可正常响应。 方式一：保证金现金缴纳： 商 1、本次采购的响应保证金为/元。 2、保证金收款账户信息请参见云筑网保证金支付页面信息。 道 页面显示账户只对公办理，不接受个人汇款，响应人以响应人基本账户或对公账号转账；响应人转账时务必备注 “交易识别码”（具体操作详见附件《供应商保证金操作手册》或可拨打云筑客服电话：4006-818-555） 方式二：保证金保险缴纳： 管 1、保证金保险可替代保证金，购买后无需再缴纳保证金，响应人可通过“云筑网”购买，响应保险费不退 还；(具体操作详见云筑网上传附件《供应商保证金操作手册》） 2、如发生扣除保证金国情况，保险公司按照保险合同约定向采购单位赔偿相关款项后，保险公司代位取得向响应 单位追偿的权利，响应单位应在规定时间内向保险公司支付相应追偿款。 以下情况可免缴本采购项响应保证金： 中 ①工程局A级分供商。 发生以下情况，响应保证金不予退还： ①响应截止后响应人撤销响应文件的，采购人可以不退还响应保证金。 ②成交人无正当理由不与采购人订立合同，在签订合同时向采购人提出附加条件，或者不按照采购文件要求提 交履约保证金的，取消其成交资格。 （2）采购文件领取事宜：响应人根据采购公告内容领取采购文件，然后根据采购文件要求，进行响应，一经报 价即认为响应人对采购文件已作出实质性响应。 （3）采购文件的澄清与修改 ①采购文件的答疑：如响应人发现采购文件有不清楚的地方或对内容有疑问，要求澄清和解答的，均应在距响 应截止时间2天前向采购人提出答疑，采购人应解答响应人提出的问题。 ②采购人允许响应人在响应截止日期之前对云筑网响应进行修改，但必须在响应截止时间之前完成云筑网响应， 逾期未响应的，则视为无效响应。 （4）（4）响应文件递交事宜 采用云筑网电子响应。 4、评审： （1）评审方法：本次采购拟选出 1 名成交人，区段划分：（如选2个及以上，应明确划分各成交人分供范围及工 程量，成交人按照最终排名顺序享有优先选择权）。采用经评审的（原则上应选择合理低价法），在响应文件 能够满足采购文件实质性要求的响应人中，评审出响应价格合理低价的响应人，但响应价格低于其成本的除外， 具体由采购评审小组在评审会上商定。 （2）响应人有下列情形之一的，取消成交资格： ①成交人在成交后拒签合同； 网 ②成交人未按约定缴纳履约保证金。 采购人： 中国建筑第七工程局有限公司 务 采购时间：2026年8月 二、评 审 办 法 （一）、评审依据 商 1、采购文件 2、响应文件 道 3、评审办法 （二）、评审小组 管 1、评审小组成员：（评审小组应由5人及以上单数评审专家组成，项目负责人必须参与评审。与分供商存在利害 关系的应回避。） 2、小组成员负责根据国评审办法及标准开展评审工作。 3、与响应人有利害关系的，不得进入评审小组。 （三）、评审原则 中 （1）采取经评审的合理低价法：从满足采购文件实质性要求的响应人中，选择合理报价中最低者（不合理低价 除外）为成交分供商。 （四）、初步评审 有效分供商（资审通过并参与有效报价的分供商）数量不少于N（拟选分供商数量）+2家。（询比采购和竞价采 购要求，其他采购方式参照采购管理办法，下同） 出现以下情形的，响应无效。 1、未按要求缴纳响应保证金的。 2、未按要求完成线上响应的。 3、未响应采购文件的实质性要求和条件的。 4、响应人提供虚假资料、隐瞒误导采购的。 5、响应人以他人名义响应或者以其他方式弄虚作假，骗取成交的。 6、响应人ip重复、涉嫌弄虚作假或串通交易行为的。 7、采购文件或法律规定的其它情形。 （五）、详细评审 1、评审：以云筑网填报数据为准。 2、排名：对进入详细评审的响应人响应报价进行汇总后，按响应报价由低到高进行综合排名。 若出现响应人响应报价相同时，按其年度供应商考评评级高低优先排序，若仍相同，可再选用以下进行情况排序 （根据情况自行排序）。 网 ①近三年工抵房金额； ②具有绿色节能环保材料设备； 务 ③云筑网显示的该响应人响应时间等。 1）、采购概算金额（见采购公告）视为最高采购限价，响应人响应报价高于采购概算金额的，作无效响应处理。 响应人响应报价低于成本的，经评审小组评审确定后，作无效响应处理。 商 2）、在评审过程中，评审小组可以要求响应人对所提交的响应文件中含义不明确、表述不一致或者有明显笔误、 文字和计算错误的内容作出必要的澄清、说明或者补正，该澄清、说明和补正属于响应文件的组成部分，须经 采购授权代表书面署名确认，不得改变响应文件的实质性内容，且须经评审小组一致同意。评审小组不接受响 应人主动提出的澄清、说明或补正。 道 3）、经以上评审，有效响应人数量仍须满足“有效分供商（资审通过并参与有效报价的分供商）数量不少于N （拟选分供商数量）+2家”，否则本次采购按废止处理（成交单位数量为“N”）。 管 4）、废止后重新发起采购，需经调查核实后，视具体调查核实结果决定是否准予原响应人参与新发起的采购响 应。 （六）、确定成交候选单位 国 多轮次公开竞争报价：（说明：如需要(应视采购标的物及响应报价情况)进行多轮次公开竞争报价的，应按详细 评审的排名顺序确定一定比例(首轮最高价不得进入二次报价)的有效响应人进行后续轮次报价，总轮次不超过3轮 （竞价采购）。 中 报价规则：响应人提交的首轮报价作为后续报价基准；后续轮次总报价不得高于前轮报价，若设置参考价，单 项报价不得高于参考单价。否则该轮报价无效；最终轮次报价提交后不得撤回或修改（以系统记录为准）。 晋级规则：每轮报价截止后，采购人按报价从低到高排序；出现相同报价时，依次比较：（1）资源库等级；（2） （参考上述第五条第2点，以优质优价为原则，优先选用具备相应能力的本级及上级A级分供商） 成交机制：最终按末轮有效报价的从低到高排序；当最低报价出现多家时，可自主决定成交人。 最终按照排名顺序拟定有效响应人作为成交候选单位，具体成交候选单位数量由评审小组根据采购文件确定。 成交候选单位经审批后作为最终成交单位。 成交候选人放弃成交、因不可抗力不能履行合同、不按照采购文件要求提交履约保证金，或者被查实存在影响 成交结果的违法行为等情形，不符合成交条件的，采购人可以按照评审小组提出的成交候选人名单排序依次确 定其他成交候选人为成交人，也可以重新采购。 （七）、其他事项 1、因响应人原因造成其自身未响应采购要求及未能成交等情况，由响应人自行承担相应责任及损失，与采购人 无关。 2、本采购文件中的合同范本即实际签约合同范本，双方均不允许以任何理由更改合同内容。 三、响应注意事项 1、若响应人对采购文件中之任何内容有不理解之处，须立即联系采购人，以便在响应截止日期之前能予以解释。 2、采购人不保证一定要接受最低价成交，不论响应结果如何响应人的响应文件均不退回，且不对未成交单位做 任何解释。 3、响应人在响应之前，对本采购项的分包条件均已了解，响应即认为已详细了解。 4、采购人对响应人进行考察时，响应人应提供便利条件。 5、本次采购的最终解释权在采购人。 网 四、响应文件的上传 1需上传的响应附件（未上传视为不响应采购文件）有： 务 1.1.《响应函》 1.2.《响应承诺函》 1.3.法定代表人身份证明（格式）； 商 1.4.授权委托书（格式）（若若为法定代表人响应则可不提供）； 1.5.报价清单明细（盖章版） 道 1.6金融工具支付方式及优惠措施 1.7.响应保证金汇款凭证扫描件或免缴证明（云筑网平台缴纳的无须提供）（若需） 管 六、响应文件格式 一、封面（格式） 国 中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料采购响应文件 响应内容：临水临电材料采购 中 （编号：cscec2026081900001246027） 响应人：（盖章） 法定代表人 或授权代理人（签字盖章）： 响 应 函 致：中国建筑第七工程局有限公司 1、经勘察了本工程现场,并仔细研究了响应须知、合同协议条款、合同条件、采购图纸、工程规范、地质勘察报 告、工程量清单、响应答疑、及其他有关采购文件后，我公司愿以我公司云筑网所上传的含税综合单价，并按 采购文件所要求的条件承包在规定工期内完成重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料的施 工、竣工并补充其任何缺陷。 2、我公司保证本工程质量必须：达到符合工程所需材料质量验收标准、设计、合同及有关工程施工及验收规范 的要求标准。 3、一旦我公司的云筑网响应内容被接纳，我公司将在收到成交通知书后按贵公司的要求开始施工，我公司保证 于承诺的工期内或双方议定的工期内完成并交付本合同中规定的整项工程。 4、我公司同意在本区段的正式建设工程施工合同签署之前，云筑网响应将始终对我公司具有约束力，并可随时 被贵公司接受。 5、我公司知道：云筑网报价及云筑网响应的其他部分构成我公司向贵公司的要约，贵公司如发出成交通知书则 成交通知书及云筑网响应、采购文件将构成约束我们双方的合同，如果我公司在接到成交通知书后，没有按贵 公司要求的时间签署正式合同或坚持提出附加条件，那么我公司同意贵公司有权另选成交单位并向我公司追讨 有关损失。 6、我公司知道，贵公司并无义务必须接受所收到的价格最低的或其他任何响应书。 7、云筑网响应内容已考虑了贵公司向我公司发出的关于采购文件的相关答疑，网补充通知（如有的话） 8、云筑网响应效力优先于同时提交的任何响应文件的其他组成部分。 响应人： （盖章） 务 日 期： 年 月 日 响应承诺书 商 致：中国建筑第七工程局有限公司 我系有幸参与贵公司 重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料的响应，我公司经研究决定， 在此郑重承诺： 道 1、我公司在响应过程中已完全了解并掌握了采购内容、合同条件及施工现场等情况。确保云筑网响应报价操作 为本公司自己操作，如响应后发生非本公司操作的情形，本公司承担相应违约责任。 管 2、我公司已经详细阅读该采购文件所有内容，充分领会并完全接受采购文件所述响应人应尽的实质性的权利与 义务。我公司保证不会对采购文件产生不利于双方友好合作关系和将增加贵公司采购范围内经济支出的重大误 解。 3、我公司确认，贵公国司发出的采购文件所有内容为不可割裂的整体。 4、我公司保证成交后不会对成交价格提出任何异议，更不会以任何理由要求贵公司针对成交范围的价款要求额 外补偿。不会以不了解采购文件、合同文件为由或曲解、片面理解采购文件、合同文件或割裂采购文件、合同 文件，断章取义，向贵公司提出任何补偿要求。 中 5、在本合同的履约过程中，如因我公司的供货或质量原因导致贵司损失，我公司保证承担因此而给贵公司带来 的所有经济上的损失。 6、我公司将本工程作为重点项目对待，保证不会出现供货能力不能满足施工需要的现象。为满足本工程业主及 贵公司在质量、进度、安全、环保上的要求，我公司将采取一切措施保证物资设备生产、供应、租赁，运输等 均满足贵公司的要求，并保证不会因此而向贵公司提出增加任何补偿要求。 7、我公司承诺无论本工程最终的成本状况如何，将不会违背合同基本原则而向贵公司要求增加或补偿合同文件 约定以外的任何费用。 8、我公司认为，贵公司可以就物资设备采购数量或租赁时长进行调整，并且此种调整不构成我公司的索赔理由。 响应人：（盖章） 法定代表人或 其授权代理人：（签字或盖章） 日 期： 年 月 日 响应人名称：【全称】 单位性质： 地 址： 成立时间：年月日 经营期限： 姓名：性别：年龄：职务：系（响应人名称）的法定代表人。 网 特此证明。 响应人：（盖单位章） 务 年月日 授权委托书 商 本人（姓名）系（响应人名称）的法定代表人，现委托（姓名）为我方代理人。代理人根据授权，以我方名义 签署、澄清、说明、补正、递交、撤回、修改中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建 设项目 (二期)临水临电材料采购（采购项目名称）响应文件、签订合同和处理有关事宜，其法律后果由我方承担。 道 委托期限：本授权书于年月日签字生效，至本次采购期结束为止。授权期限内无特殊情况不变更合法授权代理 人。 代理人无权转委托。 管 特此声明。 响应人：（盖章） 国 法定代表人：（签字） 身份证号： 中 授权代理人：（签字） 身份证号： 联系方式： 日期： 年 月 日 备注：法定代表人和委托代理人必须在授权书上亲笔签名，不得使用印章、签名章或其他电子制版签名,同时附 法定代表人和授权代理人身份证复印件（正反面，加盖公章） 报价清单明细 不 含 含 不含 计量单 税 税 含税 备 序号 材料名称 规格型号 数量 税 税合 税额 位 率 单 合价 注 单 价 价 价 1 镀锌钢管 DN100*4.0 米 500 2 镀锌钢管 DN150*4.5 米 250 3 镀锌钢管 DN65*3.25 米 650 4 镀锌钢管 DN50*3.25 米 800 5 PE管 DN100*1.6MPA 米 450 6 PPR管 DN50*1.6MPA 米 400 7 闸阀 DN100 个 22 8 闸阀 DN250 个 10 9 截止阀 DN50 个 42 网 10 截止阀 DN25 个 60 11 蝶阀 DN100 个 6 12 消防箱 800×1000×250mm 台 20 务 功率30kw,扬程144m，流 13 加压泵（变频控制） 台 1 量55m/h 14 橡塑保温材料 DN100*20mm 米 620 商 15 橡塑保温材料 DN150*30mm 米 280 16 橡塑保温材料 DN65*20mm 米 700 17 压线钳 CO-1000 个 1 道 18 污水泵 380V4KW=25米 台 12 19 污水泵 380V5KW=30米 台 7 20 热熔机 63-160 台 1 管 21 电工胶布 / 卷 200 22 高压自粘带 / 卷 120 23 水泵控制箱 / 个 8 国 24 PE聚乙烯管 DE110*1.6MPA m 560 25 PE聚乙烯管 DE75*1.6MPA m 420 26 PE聚乙烯管 DE63*1.6MPA m 480 中 27 PE聚乙烯管 DE32*1.6MPA m 750 28 PE球阀 DN25 个 6 29 PE球阀 DN50 个 6 30 PE球阀 DN100 个 5 31 镀锌桥架 200*100*1.2mm 米 1200 32 PVC排水管 DE300*5.0 m 180 33 PVC排水管 DE200*5.0 m 380 34 PVC排水管 DE160*4.0 m 486 35 PVC排水管 De110*4.0 米 560 36 PVC排水管 DE75*3.0 m 420 37 PVC排水管 DE50*2.0 m 660 38 PVC排水管 DE32*2.0 m 380 39 PPR给水管 De90*1.6MPA 米 440 40 PPR给水管 DE75*1.6MPA 米 360 41 PPR给水管 DE63*1.6MPA 米 450 42 PPR给水管 De50*1.6MPA 米 435 43 PPR给水管 De40*1.6MPA 米 315 44 PPR给水管 DE32*1.6MPA 米 520 45 PPR给水管 De25*1.6MPA 米 680 46 PPR给水管 De20*1.6MPA 米 370 47 橡塑保温板 平板×20mm m 15 48 橡塑保温板 平板×30mm m 28 49 保温胶 3公斤/桶 桶 25 网 50 PPR给水管接头 De75 个 30 51 PPR给水管弯头 De75 个 20 52 PPR给水管三通 De75 个 22 务 53 PPR给水管接头 De63 个 20 54 PPR给水管弯头 De63 个 15 55 PPR给水管三通 De63 个 15 商 56 PPR给水管接头 De50 个 17 57 PPR给水管弯头 De50 个 22 58 PPR给水管三通 De50 个 17 道 59 PPR给水管接头 De40 个 14 60 PPR给水管弯头 De40 个 22 61 PPR给水管三通 De40 个 17 管 62 PPR给水管接头 De32 个 14 63 PPR给水管弯头 De32 个 14 64 PPR给水管三通 De32 个 17 国 65 PPR给水管接头 De25 个 22 66 PPR给水管弯头 De25 个 17 67 PPR给水管三通 De25 个 14 中 68 PPR给水管接头 De20 个 25 69 PPR给水管弯头 De20 个 17 70 PPR给水管三通 De20 个 22 71 PPR内丝直接 De25 个 17 72 PPR内丝直接 De20 个 84 73 球墨铸铁井盖 700*800*40T 套 22 74 球墨铸铁井盖 1000*1000*20T 套 20 75 球墨铸铁雨箅子 400*600*30 块 1750 76 球墨铸铁雨箅子 350*500*30 块 1200 77 高分子成品排水沟 300*300*1000 米 850 78 高压洗车机 380v/3KW 套 5 79 高压洗车机 380v/5.5KW 套 3 80 HDPE双壁波纹管 DN300 米 360 81 HDPE双壁波纹管 DN200 米 410 82 HDPE双壁波纹管 DN400 米 340 83 HDPE双壁波纹管 DN800 米 260 84 玻璃钢化粪池 20m 个 1 85 玻璃钢化粪池 50m 个 1 86 不锈钢消防水箱 12m 个 1 87 一级配电柜 2000*1200*500*630A 台 1 88 二级配电柜 800*600*210*250A 台 8 89 铜芯电缆线 YC3*16+2*10 米 60 90 铜芯电缆线 YC3*10+2*6 米 70 网 91 铜芯电缆线 YC3*6+2*4 米 70 92 铜芯电缆线 YC3*10 米 100 93 铜芯电缆线 YC3*6 米 100 务 94 铜芯电缆线 YC3*4 米 100 95 铜芯电缆线 YC3*2.5+2*1.5 米 100 96 聚录乙烯铝芯电缆 YJLV-22-4*185+1*95 米 50 商 97 聚录乙烯铝芯电缆 YJLY-4*25+1*16 米 90 98 聚录乙烯铝芯电缆 YJLY-4*35+1*16 米 100 99 聚录乙烯铝芯电缆 YJY-4*50+1*25 米 90 道 100 聚录乙烯铝芯电缆 YJLY-4*70+1*35 米 72 101 网线 Cat5e 米 100 102 铜芯电线 BV-2.5 米 400 管 103 铜芯电线 BV-4 米 300 104 铜芯电线 BV-6 米 200 105 铝芯电缆线 YJLV3*10 米 100 国 106 透明塑壳断路器 3P32A 米 34 107 透明塑壳断路器 3P63A 米 28 108 透明塑壳断路器 4P100A 米 26 中 109 透明塑壳断路器 4P160A 米 22 110 透明塑壳断路器 4P250A 米 20 111 透明塑壳断路器 4P400A 米 8 112 低压铝芯电缆 YJLV-4*300+1 米 20 113 低压铝芯电缆 YJLV-4*150+1 米 50 114 铝芯铠装电缆 YJLV-22-4*95+1*50 米 60 115 铜铝线鼻 300mm2 个 20 116 铜铝线鼻 150mm2 个 36 117 铜铝线鼻 95mm2 个 24 118 铜铝线鼻 50mm2 个 20 合计 0.00 0.00 0.00 1、综合单价：包括但不限于材料费、保险费、风险费、包装费、装车费、过桥过路费、管理费、检验费、技术 指导费、货到工地负责卸货堆入至指定地点等所有费用。本合同单价一次包死，在合同履行过程中不再做任何 调整。本合同的总价为暂估价，用方有权调整合同中材料计划或材料数量，材料数量和规格的调整，不影响本 合同单价及其他条款的执行。 2、计量方式：查看检测报告合格证，以实际验收通过数量计量。 3、付款比例：月结方式，即每月20日结算（遇节假日顺延），次月25日前（结算日后35日历天内），乙方提供 与结算等额增值税专用发票后，支付前月结算额的70%（遇节假日顺延）；供货完毕，验收合格，材料相关资料 （包括不限于合格证、质检报告等）移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%；剩余3% 质保金在质保期满后30日内无息支付。质保期自全部货物供货完毕且竣工验收合格日起1年计算，支付工程款时 均应扣除根据采购合同应予扣除的其它金额。 4、付款方式： （1）现金支付:采用现金转账的模式支付； （2）非现金支付:包括不限于(1)金融工具支付:银行承兑汇票，商业承兑汇票，网应付账款保理，银行信用证，中 建财务公司承兑汇票。(2)工抵房支付。 5、响应报价表中所列数量的变动，丝毫不会降低或影响合同条款的效力。 务 6、整个合同执行期内，若遇市场价格下行，甲方有权做出价格调整，乙方应接受并重新签订补充协议确认价格。 若乙方无法接受新的低价，甲方有权重新选择其他能够响应该价格的供应商进行供货，乙方无条件同意。 响应人（加盖公章）： 商 法定代表人或授权代理人（签字）： 日 期：年月 道 金融工具支付方式及优惠措施 管 1、金融工具支付： 可接受金融工具支付比例累计为%，其中： ① 可接受的国银行承兑汇票比例%；贴息响应人自行承担。 ② 可接受的商业承兑汇票比例%；贴息响应人自行承担。 金融支付 ③ 可接受的应付账款保理比例 %；贴息响应人自行承担。 中④ 可接受的银行信用证比例%；贴息响应人自行承担。 ⑤ 可接受的中建财务公司承兑汇票比例为%；贴息响应人自行承担。 2、资产支付 资产支付 可接受比例为合同额的%。 3、优惠付款比例：按按照采购文件的付款比例，我方可优惠%。 4、如响应人提供其他由于采购条件的承诺，请逐项列示。 响应人（加盖公章）： 法定代表人或授权代理人（签字）： 日 期：年月 响应保证金汇款凭证扫描件或免缴证明（若需） 响应人（加盖公章）： 法定代表人或授权代理人（签字）： 日 期：年月 六、物资设备采购合同 合同编号：______________________ 物资采购与供应合同 （通用） 项目名称：【 重庆市第四人民医院科学城院区建设项目 (二期) 】 网 甲 方：【 】 乙 方：【 】 务 签订时间：【 】 签订地点：【 】 商 目录 1. 工程概况及供货范围 道 2. 企业性质 3. 合同价款 2 管 4. 质量要求 5. 供货时间及地点 6. 交货与验收 国 7. 结算方式及时间 8. 支付 中 9. 发票 10. 双方责任 11. 不可抗力 12. 权利瑕疵 13. 保密 14. 违约与赔偿 15. 联络与送达 16. 争议解决 17. 补充条款 18. 其他 物资采购与供应合同 甲方（买受人）：【中建七局安装工程有限公司 】 乙方（出卖人）：【 】 根据《中华人民共和国民法典》及有关规定，为明确双方权利、义务和责任，经双方协商一致，就甲方承包的 【高新LIVE（咸阳高新区租赁住房）建设项目】工程所用【 水电管材】采购与供应事宜签订本合同条款，愿共 同遵守。 1. 网 1.1 工程名称：【高新LIVE（咸阳高新区租赁住房）建设项目 】 1.2 工程地点：【陕西省咸阳市星火大道】 务 本合同供货范围为：【高新LIVE（咸阳高新区租赁住房）建设项目 】的【水电管材】供应（以下简称为“本合 同标的物”）。 1.3本合同标的物的数量为暂定量，乙方按附件1《计划采商购与供应物资清单》所列品种和规格供货，最终以经甲 方验收合格的实际数量为准。 2. 企业性质 道 乙方企业规模：大型 □中型 □小型 □微型企业 以上企业规模由乙方根据（1）工信部官网：“中小企业规模类型测试网址https://baosong.miit.gov.cn/ScaleTest。 （2）工信部微信小程序：“中小企业规模类型自测”两种渠道自测确定。 管 乙方应保证其企业规模的真实性。如乙方提供信息不实，经甲方查证后，将按照《中国建筑股份有限公司分供 商资源管理办法》中的《不良行为分供商禁用处理标准》第19项对乙方严格实施禁用管理。 合同价款 国 3.1 本合同采用第【 】种价格形式： （1）固定综合单价包干，价格不可调整。 中 3.2 本合同价款为各项货款之和，合同价款（含增值税）暂定：（大写）【 】（￥【 】元），其中不含税价款为 （大写）【 】（￥【 】元），增值税为（大写）【 】（￥【 】元），税率为【 】%。最终甲乙双方以实际验收 的数量结算。 3.3 本合同约定的不含税价款不因国家税率变化而变化，在合同履行期间，如遇国家的税率调整，则价税合计的 合同价款或货款相应调整，以开具发票时间为准。 3.4 本合同不含税价款仅指不包含增值税，除增值税外的其他全部税费（包括但不限于城市建设维护税、教育费 附加及地方教育费附加、个人所得税、合同印花税、企业所得税、车船使用税以及国家和地方规定的所有税费） 均包含在不含税价款中。 3.5 本合同标的物的计价、结算和支付货币均为人民币。 3.6 本合同标的物的计量单位为中华人民共和国法定公制计量单位（除技术规范标准另有规定外）。 3.7 本合同标的物的不含税单价，指运抵本工程施工现场甲方指定交货地点的综合单价，包括但不限于货物费、 加工费、包装费、人工搬运费（由乙方自行协调，甲方只进行指定场地和材料验收工作）、运输费、出厂检测费 （包括但不限于到场后的第三方检测费用）、装卸费、码放费、现场倒运费用，保险费、仓储费、驻厂监造费、 运输造成的道路污染的清理及维修费用、除增值税以外的税金、乙方合理的利润、管理费、市场价格波动带来 的风险、向有关部门缴纳的各项费用以及政策性文件所规定的各项应有费用等乙方履行本合同规定义务的全部 价款与费税。除本合同第3.1条约定的因素外，不含税单价不因政府政策变动、市场环境改变、税率调整等而调 整。 3.8 除合同条款另有约定外，本合同标的物的不含税单价已包含专利、专有技术以及技术秘密的使用费。 质量要求 4.1 乙方应在交货同时向甲方提供本合同标的物制造商出具的书面质量保证书。 4.2 本合同所采购与供应的物资，应符合现行中华人民共和国国家标准及行业或地方标准，行业标准或地方标准 高于国家标准的，执行行业标准或地方标准。各项技术性能指标经本工程所在地具有相应检测资质的专业机构 或单位检测中心检验必须符合相关标准要求。合同执行过程中，若出现新的国家标准、行业标准、地方标准， 则以更新后的标准为准。 网 4.3 乙方的物资供应与管理应符合国家有关环保法律、法规和甲方ISO14001环境体系及OHSMS18001职业安全健康 管理体系标准。 4.4 本合同标的物的质量保证期为最后一批货物验收合格之日起满【180】日。 务 4.5在合同履行期及质量保证期内，乙方无条件地向甲方提供缺陷产品的免费维修、更换等服务。针对甲方提出 的书面要求，乙方必须在3日内给予书面答复。如有必要，乙方在3日内指派专人到现场解决，因此产生的所有费 用均由乙方承担。 商 4.6 如缺陷产品经乙方进行免费维修和更换后仍无法达到甲方要求的质量标准时，甲方有权终止合同。终止合同 后，乙方需向甲方赔偿由于乙方问题造成的损失及其连带损失。如乙方借故推脱或拒绝甲方提出的维修、更换 等服务请求，甲方有权自行采购同等货物替代或委托第三方维修，实际发生的更换等或维修费用，从应支付给 乙方的任一期货款中扣除，并保留进一步索赔道的权利，乙方不得提出异议。维修或更换物资的质量保证期相应 延长6个月。 4.7 如因乙方产品质量导致工程出现质量问题，由此给甲方造成的一切损失由乙方承担。 管 4.8 其他质量要求：/。 供货时间及地点 5.1 供货方式：□按批次国供货 □一次性供货 5.2 通知方式：供货时间及数量以甲方书面通知为准，甲方可以选择通过电子邮件、微信、QQ等方式将物资采购 订单发送至乙方。紧急情况下，甲方可口头通知乙方发货，手续后补，乙方应予以确认。 中 5.3 供货地点：乙方负责送货至施工现场，卸至甲方指定的卸货地点【高新LIVE（咸阳高新区租赁住房）建设项 目】。乙方不得雇佣甲方在班人员及设备装卸货物。运输、装卸过程中发生的安全事故责任，乙方自行承担。 5.4 根据工程项目施工需要，甲方对所采购物资的数量和送货时间如有变更，应及时书面通知乙方，乙方按变更 后的数量和送货时间供货，货物单价不因货物数量和送货时间的变更而变化。 5.5 乙方应确保已经知悉货物运输的交通状况、交货卸车环境以及政府的交通管制政策措施，不得以此等理由要 求增加费用、减免责任、提出索赔、要求延长或变更供货期限。 交货与验收 6.1交货 6.1.1 除另有规定和协议要求外，乙方提供的全部货物须采用国家、企业、行业标准要求包装，具有足够的强度 及安全起吊标识，保证货物能够经受多次搬运、装卸、长途及短途运输的要求，并采取良好的防潮、防震、防 腐蚀、防爆及防止其它损坏的必要保措施。包装物的回收按以下第【 2】项方式执行：（1）不回收；（2）包装 物由乙方在交货时回收；（3）其它方式：【 /】。 6.1.2 装箱单应注明货物的名称、规格、型号、数量、质量、生产商、发货地、供货人、收货人、交货地、承运 人等，并在显著位置标明装卸警示标志。 6.1.3 乙方运抵甲方指定现场的物资，交货单据上应详细列明当次供应物资的名称、品牌、产地、生产厂家、规 格型号、计量单位、数量。 6.1.4 乙方应向甲方提交本合同标的物的技术文件，包括材质报告（物资质量检验报告）和出厂检验报告（合格 证），以及按照工程竣工验收规定及甲方要求，提供所有相关符合要求的资料。 6.1.5 乙方在首次供货前需提供样品，乙方须在样品和样品资料上加盖单位公章，样品经双方指定人员签字确认 后予以封存，在提交文件上注明与合同文件约定不同之处。 6.2.1 乙方须随货提供载有数量、规格等内容的送货单，否则，甲方有权对本批次货物不予验收确认，由此导致 的违约责任由乙方承担。乙方送货到交货地点后，甲方指定验收人员对产品的规格、尺寸偏差、外观、数量及 质量证明资料等进行查验。若产品的以上各项符合合同约定，则双方人员共同在收领单上签字确认。 6.2.2 甲乙双方在交货现场以 【 点数】方式进行数量验收。乙方应对在甲方工地网现场的验收数据进行确认。 6.2.3 进行数量验收的同时，甲方可以按照封存样品标准进行尺寸、外观质量验收，尺寸和外观质量符合要求方 可卸车，否则不得卸车。 务 6.2.4 外观质量符合要求的， 甲方可打开包装进行质量、性能检验或及时按规定取样送本工程所在地具有相应检 测资质的专业机构或单位进行检测。抽检未发现不合格产品不视为乙方供应产品全部合格，甲方有权随时将乙 方所供货物送到有检测资质的第三方进行检测。如检测合格，检测费用由甲方承担；如检测不合格，甲方可全 部退货，检测费用由乙方承担，并承担由此给甲方造成的一切损失。 商 6.2.5 甲方及工程监理（业主）的收货验收仅作为感观合格的依据，不能免除乙方对货物品牌真实性、内在质量 及使用功能所负的责任。如甲方、本工程建设单位或监理单位提出异议，乙方需参照有关标准规范，结合现场 情况解决。 道 6.2.6 若发现不合格产品，乙方必须及时（接到甲方通知后【 3】小时内），从甲方项目现场运走不合格品，甲方 不负有保管义务，不对不合格产品的损毁灭失承担人和责任，若超过【 12】小时乙方仍未运走的，甲方收取场 地租赁费（根据货物合理确定）【 1.0】万元/天，且不合格品的储存、装卸、运输等所有相关费用及风险由乙方 承担。 管 6.2.7 如因乙方产品问题造成甲方工期、质量、劳务等损失，全部责任均由乙方承担。乙方对甲方所提出的质量 问题有不同意见的，双方可送至双方共同选定的具有法定资质的检测机构检测，所产生的费用及责任由责任方 承担。 国 6.2.8 本合同的标的物所有权自【卸货完毕且经甲方验收合格】起转移。 结算方式及时间 中 7.1 过程结算：甲乙双方按以下第【 1】条约定的时间办理过程结算。 （1）每月20日结算（遇节假日顺延），每季度最后一个月的25日后支付当期货款额的70%（遇节假日顺延，乙 方提供与结算等额增值税专用发票），供货完毕，验收合格，材料相关资料（包括不限于合格证、质检报告等） 移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%，余款3%（不计息）待质保期满无质量问题后 无息付清。（质保期为供货完毕且验收合格后2年）（支付工程款时均应扣除根据采购合同应予扣除的其它金额。 ）； （2）按节点结算，具体结算节点为：【 】。 7.2 最终结算：全部供货完毕后【 6个月后】日内，乙方应向甲方提供完整的结算资料，甲方在收到完整的结算 资料后【 5 】日内进行审核。 7.3 结算依据：包括但不限于物资采购与供应合同、乙方合法等额有效增值税发票（含税务机关代开）、产品合 格报告、项目授权人员验收单、送货单等有效材料。 7.4 乙方未按照约定的期限和甲方要求提供结算资料，或未委派专人与甲方办理结算，或提供的结算资料不齐全、 提供虚假资料的，经甲方催告后10个工作日内，乙方仍未按要求提供结算资料的，甲方有权不予办理结算并暂停 支付材料款，同时甲方可根据本合同、现有结算资料及乙方实际履约情况单方办理结算，确定结算价格，结算 对甲乙双方具有法律约束力。 支付 支付/√不支付预付款 8.1.1 预付款金额（或占合同价款的比例）：【 /】。 8.1.2 预付款的支付时间：【 /】，在乙方提交等额银行保函及增值税专用发票后，甲方向乙方支付预付款。 8.1.3 扣回预付款的时间、比例：【 /】。 8.1.4 乙方提交的银行保函有效期至预付款抵扣完为止，若预付款保函到期日前，预付款无法抵扣完毕，则乙方 应于预付款保函到期日前不少于10日及时办理保函延期，否则甲方有权暂停支付未抵扣完部分的货款。 网 / 8.2.1 货款支付，按以下第【 3】条约定的时间和比例支付。 务 （1）月度付款：甲方在次月的25日支付上月月度结算货款的【 / 】%。双方办理完毕最终结算后【 / 】（条款说 明：建议不超过60日，如超过60日，应当按照行业规范、交易习惯合理约定付款期限并及时支付款项）个日历天 内付至总结算货款（且不超含税合同价款）的【 / 】%。余款【 /】%作为质保金，在质保期届满后28日内付清； 或由乙方提供等同余款金额的质保保函（仅接受金融机构出具的无条件见索即付保函，质保保函格式以开函金 融机构标准格式为准），则双方办理完毕最终结算后【 /商】（条款说明：建议不超过60日，如超过60日，应当按 照行业规范、交易习惯合理约定付款期限并及时支付款项）个日历天内付清。 （2）节点付款：按节点支付（条款说明：此处需具体罗列每个付款节点及各节点对应的付款比例，节点结算完 成后约定支付期限应在60日内，如超过60日，道应当按照行业规范、交易习惯合理约定付款期限并及时支付款项）， 余款【 /】作为质保金，在质保期满后28日内付清，或由乙方提供等同余款金额的质保保函（仅接受金融机构出 具的无条件见索即付保函，质保保函格式以开函金融机构标准格式为准），则在最后一个付款节点付清。每次 付款前乙方应提供结算值【100%】的发票，否则甲方可拒绝付款。 管 （3）其他支付方式【每月20日结算（遇节假日顺延），每季度最后一个月的25日后支付当期货款额的70%（遇 节假日顺延，乙方提供与结算等额增值税专用发票），供货完毕，验收合格，材料相关资料（包括不限于合格 证、质检报告等）移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%，余款3%（不计息）待质保 期满无质量问题后无息付清。（质保期为供货完毕且验收合格后2年）（支付工程款时均应扣除根据采购合同应 予扣除的其它金额。）国】 （4）甲方依合同约定确认的进度款仅为中期付款依据，不作为竣工结算的依据，且不视为对因变更调整的合同 价款、索赔的价款或费用以及其他约定的追加合同价款的确认。 中 8.2.2 甲乙双方协商一致同意本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保理、商业承兑汇票、 国内信用证、应收账款电子凭证、抵房抵款及其他】常规支付方式的付款方式。付款过程中产生的贴息费用及 手续费由【乙方】承担。乙方委托专职收款人办理收付款业务，收款人必须取得授权 8.3 乙方指定以下帐户为收款帐户，甲方所有款项均需通过该帐户支付。如乙方变更收款帐户，应提前十五天以 上书面通知甲方，否则造成资金的损失由乙方自行承担，与甲方无关。 账户名：【 】 开户行：【 】 账 号：【 】 发票 9.1 乙方在向甲方请款时，应根据甲方确认的应支付金额开具合法、有效、完整、准确的增值税（请勾选：□专 用□普通）发票，计税方法为【□一般计税方法 □简易计税方法】，双方发票信息如下： 名 称 纳税人身份 □一般纳税人 □小规模纳税人（请勾选） 甲方 纳税人识别号 地 址、电 话 开户行及账号 名 称 纳税人身份 □一般纳税人 □小规模纳税人（请勾选） 网 纳税人识别号 乙方 地 址、电 话 开户行及账号 务 联 行 号 该开户行为乙方在税务局已备案的乙方单位账户。 9.2 任何一方如上述信息发生变更，应提前10日以书面方商式通知另一方。如一方未按本合同规定通知而使另一方 遭受损失的，应予以赔偿。 9.3 每次乙方在甲方付款前必须提供符合国家现行税法规定的合法有效等额增值税发票，甲乙双方一致确认提供 发票为主合同义务而非附随义务，若乙方未按要求提供发票，甲方有权暂停付款。乙方应在开票之日起7天内将 道 发票送达甲方指定人员【 刘磊】，甲方指定人员签收发票的日期为发票的送达日期。 9.4 乙方开具的增值税专用发票应保证信息完整、内容规范，如乙方未提供发票或提供的发票不合规、不及时、 无法认证，甲方有权拒绝付款，且不视为甲方付款逾期，乙方无权要求甲方支付利息、违约金或赔偿损失，也 管 不得以此为由中止履行合同约定的义务。 9.5若乙方由一般纳税人身份变为小规模纳税人身份的，或者计税方法发生变化的，或者政策法规等规范性文件 发生变化的，并导致甲方可抵扣的进项税额减少或被税务机关要求补缴税款的，则减少的进项税额或补缴的税 款应由乙方承担，甲方国有权从将支付的任何一笔款项中扣除。 9.6 增值税税率变化：合同执行过程中如果遇到国家税务政策调整，增值税税率发生变化的，按新的税率执行， 不含税价不变，仅调整增值税税率的原则进行相应调整。 中 若乙方提供的发票不符合要求的，发包人有权拒收增值税发票，并有权暂停支付相应款项，乙方不得以此为由 中止履行合同的义务。如因乙方不能按期提供发票或提供的发票不符合要求而导致付款延期的，由其自行承担 后果，发包人不承担任何责任。 9.8若乙方迟延提供发票的，每日应按暂定合同总价的0.05%向甲方支付违约金，但迟延违约金累计支付不超过90 日；若乙方迟延提供发票超过90日且已跨年的，视为乙方未提供发票，乙方除应支付前述迟延违约金外，还应另 行向甲方支付以下款项： （1）相当于合同暂定总价1%的违约金； （2）甲方因未收到发票所产生的税款损失， 损失金额按以下公式计算：赔偿损失金额=未提供发票对应的增值税税额*（1+增值税附加税率）+未提供发票金额 *甲方企业所得税税率。 9.9乙方保证开具的发票已经依法足额纳税，支付每笔款项前，乙方需提供发票对应税期的增值税纳税申报表和 完税证明。 9.10乙方承诺其提供的发票真实合法，若发包人认证后出现走逃失联、被列为异常纳税人等违规行为，导致发包 人不能认证抵扣或者认证抵扣后被税务机关要求进项转出情形，应在72小时内补开合规发票，否则按以下方法计 算应赔偿发包人损失，应赔偿损失金额=进项转出税额*（1+增值税附率)+不合规发票金额*发包人企业所得税税 率，逾期未赔偿的，甲方有权从结算金额或者履约保证金中扣除。 9.11乙方主张已开具发票的，应提供：①税务系统发票开具记录 ；②采购方签收凭证或者发票邮寄物流凭证。无 法完整提供两项证据的视为未开票。 10.双方责任 10.1 双方现场代表 10.1.1甲方现场代表为【 】，其职务为【 】 ，其授权签署文件的范围为：【签发监管项目的各类文函、工程变更 指令、索赔文件的报出、违约处罚决定文件等】。 10.1.2甲方收货代表：【 】，联系电话【 】。甲方指定收货代表仅有对乙方送货单中货物的数量及乙方提供的单 据是否齐全子以确认的权利，对货物单价、质量、货款以及总结算单没有确认的权利。 10.1.3乙方应将物资按合同约定时间运至甲方指定地点，并经甲方指定收货代表和甲方工程项目所属其他1人及以 上在甲方指定的收领单上签字验收确认后有效。 网 10.1.4 甲方未经授权的任何人员和项目印章均无权从事下列行为：【（1）签订本合同的补充协议或签署其他合 同类文件，包括但不限于采购合同、分包合同、租赁合同；（2）签署任何借贷、担保性质的文件，包括但不限 于借条、保函、保证书、承诺书；（3）签署代他人清偿债务的文件，签署任何放弃债权的文件；（4）签署任何 对总承包合同进行修改和补充的文件;（5）收取现金及任何款项；（6）签署合同价款的变更、结算及支付确认 务 文件；（7）签署任何劳动关系确认文件、工资发放承诺文件。】 10.1.5 甲方授权人员的职权/职责范围、授权签署文件范围均不可转授权，任何形式的转授权、代签行为，甲方均 不予认可且不承担任何法律责任。 商 10.1.6 乙方确认已完全明白和理解甲方对甲方人员及项目印章的上述授权范围，超出甲方授权范围的行为属于无 权代理行为，对甲方无效，甲方不承担任何法律责任。乙方应谨慎审查相关文件的签署主体资格和权限，对于 无权代理人签署的相关文件，乙方应及时与甲方核实。 道 10.1.7 乙方现场代表为【 】，其职务为【 】，其授权范围为：【全面代表乙方履行本合同，并有权代表乙方签署、 确认履约过程中形成的工程变更、价款确认、经济索赔、违约处罚决定及物资丢失损坏赔偿文件；签署确权文 件及结算书；签收甲方发出的各类文函、工程变更及其他文件等。】 管 10.1.8 双方更换各自代表时，应及时书面通知对方，以确保物资顺利交接。 10.1.9 甲方禁止项目部及任何人员以甲方、甲方分公司、甲方项目部的名义对外借款或者支取任何款项，如乙方 或乙方有关人员以任何形式将款项出借或支付或返还给甲方项目部及任何人员，则不论该等款项是否实际用于 甲方工程，均与甲方无国关，该行为均属于乙方与相关人员个人之间的经济关系，乙方无权向甲方主张任何权利。 10.1.10 未经甲方书面授权不得擅自与建设方及有关部门发生工作上的联系，严禁在对外任何事务中签署甲方单 位名称或带有甲方简称中任何“【中国建筑】”“【中建】”“【中建XX局】”“【XX局】”等字样的落款， 每发现一次中乙方承担2万元的违约金并赔偿所有直接或间接损失。 10.2卫生、环境与安全保护 10.2.1 甲乙双方须贯彻执行国家、地方政府相关部门发布的有关卫生法律、法规，以及甲方发布的规章制度，积 极配合政府部门的检查，对于提出的要求按所属责任立刻整改，确保瘟疫和传染疾病防控的管理落实到位。 10.2.2 乙方保证在运输和卸货过程中应采取相应的环保措施，符合国家环保要求。车辆在进入项目现场要保证不 沾泥土和脏物，车辆出入项目现场必须在项目大门内现场洗车。乙方在卸货过程中保证噪声不超过以下标准 （白天小于或等于【 】dB、夜间小于或等于【 】dB）。乙方保证乙方人员以及车辆进入本工地现场，应遵守现 场的一切卫生环保、文明施工的规定，因违反环保要求所造成的一切罚款由乙方承担。 10.2.3 甲乙双方必须贯彻执行国家和政府、行业主管部门颁布实施的有关安全生产的法律、法规及有关规定。乙 方车辆及人员进出工地现场时必须接受甲方安全检查。乙方因供货造成安全生产责任事故的，责任由乙方承担。 乙方必须对自身出入工地现场的人员进行安全交底，并为其配备安全防护用品，因乙方原因造成的各种人员伤 害及经济损失由乙方自行承担，并赔偿甲方及其它方因此造成的一切损失。 10.3 售后服务 10.3.1 如所供货物为专业性较高的产品，乙方应免费为甲方或工程业主提供操作及维修人员的培训服务，培训内 容应包括：基本原理、操作使用、维修保养等。 10.3.2 对于工程中的剩余或未使用到的货物在不严重影响外观、质量和功能的情况下甲方有权退货，退货原则上 以合同约定的含税单价为准，确因商品特殊的（比如定制等），价格由双方协商，协商不一致的，按照附件1 《计划采购与供应物资清单》中的含税单价（考虑甲方已支付费用、乙方承担运费等情况下，原则上不低于【 】%）【 】%退货，退货数量以实际数量为准。 不可抗力 11.1 不可抗力是指合同当事人在签订合同时不可预见，在合同履行过程中不可避免且不能克服的自然灾害和社会 性突发事件，包括地震、海啸、瘟疫、骚乱、戒严、暴动、战争等情形。 11.2 不可抗力事件发生后，乙方应立即通知甲方现场代表并迅速采取措施，尽量减少损失，并在24小时内向甲方 通报受害情况，提供必要证明。不可抗力持续发生，乙方应每日报告一次受害情况，直到不可抗力结束。甲方 应对受害处理提供必要的条件，并负责处理工作的组织、指挥。不可抗力发生后网，乙方未采取有效措施控制灾 害而发生的损失由乙方承担。 11.3 不可抗力引起的后果，由甲乙双方应各自承担其人员伤亡及财产损失，履行合同的期限相应延长。 务 不可抗力发生后，双方均应采取措施尽量避免和减少损失的扩大，任何一方没有采取有效措施导致损失扩大的， 应对扩大的损失承担责任。 因一方迟延履行合同义务，在迟延履行期间遭遇不可抗力的，不能免除迟延履行方的违约责任。 商 11.4 因单次不可抗力导致合同无法履行连续超过【30】天或累计超过【60】天的，甲方有权解除合同。合同解除 后，双方应就合同履行情况及结算与付款等善后事宜达成补充协议。 权利瑕疵 道 12.1 涉及到知识产权（专利权）标记的产品，乙方应提供知识产权（或专利权）及其权属的有效证明材料。乙方 承诺其提供的物资不侵犯他人的知识产权（或专利权），若乙方提供物资侵犯他人知识产权（或专利权）导致 他人向甲方索赔的，乙方承担由此给甲方造成的一切损失，包括但不限于甲方处理此纠纷发生的律师费、诉讼 管 费、仲裁费、差旅费等一切损失。此外，乙方应向甲方支付合同价款【5】%的违约金。甲方针对上述一切损失 有权从乙方结算货款中扣除或依法追索。 12.2 乙方所供物资应不存在任何权属纠纷及抵押、查封等权利限制情形，如乙方所供物资存在权属纠纷或任何权 利限制情形导致甲方遭国受损失，乙方应赔偿甲方全部损失。 保密 13.1 除法律规定或合同另有约定外，未经乙方同意，甲方不得将乙方提供的技术秘密及声明需要保密的资料信息 中 等商业秘密泄露给第三方。 13.2 除法律规定或合同条款另有约定外，未经甲方书面同意，乙方不得将甲方提供的图纸、文件以及声明需要保 密的资料信息等商业秘密泄露给第三方。 13.3 任何一方违反上述约定，应负责赔偿守约方因此造成的一切损失。 违约与赔偿14.1甲方应按照合同约定及时向乙方支付合同价款，若因甲方资金不到位，乙方同意给予甲方【 30 】 日的宽限期，宽限期内不视为甲方违约。超过宽限期仍未支付的，乙方可向甲方主张自宽限期结束后的违约金； 违约金以逾期支付的价款为基数，自宽限期结束之日起至甲方支付逾期价款之日止，按照中国人民银行同期活 期存款利率向乙方计付，向乙方计付，逾期支付违约金的上限为逾期支付金额的【 / 】%（不超过3%）。在我方 支付逾期付款利息后，分供商不可就此向我方再主张逾期付款的违约责任。（条款说明：乙方为中小企业时， 甲方前述条款支付期限+本条宽限期整体不得超过60日）。14.2 除本合同中规定的不可抗力外，其他不论任何原 因，乙方若不能按约定期限足额足量送至甲方指定现场存货地点，甲方向乙方收取逾期运达物资货款（含增值 税）每日【3】％的违约金，自逾期之日起计算至乙方实际送达之日止，延迟或供货不足超过【3】日时，甲方有 权单方面终止合同。14.3 未经甲方书面同意自行停止供应本合同约定的货物，均视为乙方违约，乙方除承担因此 给甲方造成的一切损失外，乙方另支付合同价款的【5】%作为违约金。 14.4若乙方提供的货物为非合同约定的厂家或品牌的产品，或提供的是假冒他人品牌的产品，甲方有权立即终止 合同，乙方必须支付合同价款【2】倍的违约金给甲方，如乙方所供产品已安装至工程项目，则乙方除承担违约 金外，还必须承担拆除、工程维修、工作面清理和重新安装产生的所有费用等，如违约金不足以弥补因此给甲 方造成的所有损失，包括一切直接损失和间接损失，则超出部分，甲方有权向乙方追偿。乙方提供的货物为合 同约定的厂家及品牌产品，但货物质量不合格或不符合约定的技术要求时，可由乙方负责更换质量合格和符合 约定技术要求的产品，同时承担合同价款【5】%的违约金，并承担因违约造成的各项损失，甲方也可直接要求 解除合同，乙方承担因此给甲方造成的所有损失。乙方提供的合同标的物因品牌、质量等原因导致甲方被项目 业主或总包方罚款或追究违约责任，乙方应向甲方相应承担赔偿责任。 14.5 本合同履行过程中，如果乙方不能按时交货，应在交货前48小时内以书面形式通报甲方，甲方视情况确定是 否同意变更供货时间。如甲方不同意变更供货时间，可自行采购部分或全部货物。甲方在自行采购和接收该违 约部分货物时实际发生的所有额外费用及因此给甲方造成的损失，从甲方应支付给乙方的任一期货款中扣除， 甲方同时保留进一步索赔的权利。 14.6甲方提出索赔通知后，乙方应在【28】日内答复，如果在【28】日内未答复，视为乙方已接受该索赔，同时 甲方保留进一步要求赔偿的权利。 网 14.7 乙方在进出场时乙方不得私自运送甲方现场物资出场，一经发现，乙方向甲方支付所涉及物资原值【2】倍 的违约金，情节严重的交由司法机关处理。 务 14.8 由于乙方自身原因（如：不按约定开立银行账户、未及时提交报量资料或不按合同配合甲方进行款项支付 等），导致货款或工程款延期支付，甲方不承担延期付款利息及违约金，乙方不得因此停止供货；乙方擅自停 供的视为乙方违约，乙方承担因此给甲方造成的所有责任及损失。 14.9 如果出现合同为可调价合同，甲乙双方调价达不成一致商情形；或者出现合同为不可调价合同，乙方提出调价， 甲乙双方达不成一致情形，则甲方有权选择其他供应商，甲方不承担任何违约责任。 14.10 若乙方因14.5和14.9款原因停止供货，或未完成全部供货、或主张解除合同等不履行合同的情形，乙方剩余 款项的支付不适用本合同8.2条款，甲乙双方应道就剩余款项的支付签订书面补充协议，重新明确支付条款，甲方 不承担任何违约责任。 14.11 其他违约与赔偿要求：【 /】。 管 联络与送达 甲方：收件人【 】，联系电话【 】，电子邮箱【 】，地址【 】。 乙方：收件人【 】，联国系电话【 】，电子邮箱【 】，地址【 】。 15.2 一方通过电子邮箱发送文件的，文件到达对方邮箱即视为送达，送达时间为电子邮件到达对方邮箱地址时间； 一方通过信函邮寄送达的，则信函寄出后的第三个工作日或收件人实际签收日（以先到的时间为准）视为送达； 一方选择直中接送达的，则递交时视为送达。 15.3 邮件邮寄至上述地址被拒收或无人签收，亦视为已经送达，由此增加的费用和（或）延误的期限由拒绝接收 一方承担。 15.4 双方承诺，因本协议的履行或争议解决，上述联系人和联系方式为有效的联系方式，各项通知均应当向上述 联系人、联系方式送达。在诉讼、仲裁中，上述联系人、联系方式亦为有效的送达地址，向上述地址的送达即 为有效送达，即使发生拒收、退信等事件。 上述联系信息发生变更的，变更方应当即时通知对方；在对方收到变更通知之前，对方当事人或者仲裁、司法 机构已经向原联系人、联系方式进行的通知，视为有效通知。 争议解决 16.1 因本合同引起或与之相关的任何争议、纠纷或权利主张，则必须先行向对方发出书面和解申请书，并告知对 方争议、纠纷或权利主张之事实及依据、联系人及联系方式，在对方收到上述通知之日起 3 个月为双方和解期限。 在和解期限内，若双方达成和解协议的，双方的权利义务按照和解协议履行；若未达成和解协议的，任何一方 采用下列第【 】种争议解决方式，并自行承担本方发生的律师费、差旅费、保函费等相关费用∶ （1）向仲裁委员会申请仲裁 周口仲裁委员会（开庭地点：郑州） 郑州仲裁委员会 武汉仲裁委员会 北京仲裁委员会 上海仲裁委员会 中国国际经济贸易仲裁委员会 R成都仲裁委 （2）向【 】人民法院提起诉讼。 网 1.因本合同引起的或与本合同有关的任何争议，如仲裁委员会，则按照其仲裁规则进行仲裁。仲裁裁决是终局的， 对双方均有约束力。 务 2.双方承诺：任何一方向仲裁委员会申请仲裁的，双方均自愿放弃向对方主张仲裁费用和实际发生的其他费用， 包括但不限于鉴定费用、评估费用、审计费用等；双方均自愿放弃向对方主张补偿因办理案件支出的合理费用， 包括但不限于律师费、保全费、差旅费、公证费等。 3.双方约定：仲裁案件无论标的额大小、复杂程度如何，商均适用普通程序，即由三名仲裁员组成仲裁庭审理，以 确保案件公正审理。 4.调解期限：争议应先行和解协商解决，设定3-6个月和解期（可根据情况调整），且和解期限不计入仲裁审理 期限。任何一方若未履行上述和解程序而直接道提请至争议解决机构的，则需要向对方承担签约合同价【10】%的 违约金；如一方出现上述情形，另一方提起反诉或反请求，则提起反诉或反请求的一方不承担违约金。 17.禁止债权转让条款甲乙双方确认，若发生下列任一情形，即视为乙方重大违约，乙方需向甲方支付合同总价 （建议10%） %的违约金，且甲方有权视违约程度单方解除本合同，同时乙方应赔偿甲方因此遭受的全部损失 管 （包括但不限于直接损失、间接损失、维权产生的律师费、诉讼费、保全费等）。具体情形如下： （1）未经甲 方事先书面同意，乙方擅自将其在本合同项下对甲方享有的全部或部分债权进行转让、质押或以其他方式处分 给任何第三方的； （2）因乙方与乙方债权人存在债务纠纷，导致该乙方债权人以甲方为被告或被申请人提起代 位权诉讼、仲裁或采取其他司法/仲裁手段的； （3）未经甲方事先书面同意，乙方以自身名义或委托任何第三 方，就本合同相关事项国对甲方的关联单位（包括但不限于业主单位、建设单位、 发包方）提起代位权诉讼、仲 裁或采取其他司法/仲裁手段的； （4）其他性质同上述条款规定的情形。18.补充条款 /】 中 其他 19.1 本合同采用下列第【 2 】种签订方式： （1）本合同自双方签字并盖章后生效，一式【叁】份，甲方执 【贰】份，乙方执【壹】份，每份具有同等法律 效力。 （2）本合同采用电子签章签署生效。根据《中华人民共和国民法典》、《电子签名法》等相关法律、法规，双 方一致认可在【 】平台（网址：【 】）使用电子印章签署合同为其真实意思表示，且确保在该平台注册时，使 用的企业信息和个人相关信息真实有效，并且自觉遵守国家法律法规和甲方在该平台的合同签约流程。甲乙双 方使用电子签章方式签署的合同，只有通过验证生效的电子原件具有法律效力，未经电子印章服务平台公司提 供书面证明材料的电子合同打印版不能作为法律依据。如因乙方使用不当给甲方造成损失，乙方愿自行承担由 此造成的全部经济损失和法律责任。 19.2未尽事宜经双方协商一致后，可签订补充协议，与本合同具有同等法律效力。 19.3对于因本合同产生的任何争议或投诉，乙方可通过【 】（条款说明：根据各公司情况填写投诉平台或者联系 方式）进行提交。甲方将在收到乙方的投诉后，对乙方的投诉进行初步审查，并尽快与乙方取得联系以进一步 了解详情。因不可抗力或第三方原因导致无法按时处理投诉的情况，甲方将尽快通知乙方，并尽力协调解决问 题。 19.4本合同条款（包括但不���于免责条款、责任限制条款等）均经双方充分协商，双方已就全部条款内容达成一 致意见，不存在单方预先拟定且未予协商的情形。 附件： 附件1：《计划采购与供应物资清单》 附件2：《法人授权委托书》 附件3：《廉政合同书》 （以下无正文） 甲 方：【盖章】 乙 方：【盖章】 网 法定代表人：【签字】 法定代表人：【签字】 委托代理人：【签字】 委托代理人：【签字】 务 地 址：【 】 地 址：【 】 电 话：【 】 电 话：【 】 商 电子信箱：【 】 电子信箱：【 】 附件1 道 计划采购与供应物资清单 人民币：元 管 计量 暂定 单价 暂定含税 序号 物资名称 规格型号 品牌/产地 生产厂家 备注 单位 数量 不含税单价 增值税 含税单价 货款金额 价税合计 暂定合同价款人民币大写： 国 以上数量为暂定项目，最终以双方签字确认的采购结算单为准 中 附件2 中国建筑 项目管理表格 表格编号 法人授权委托书 CSCEC-WZ-HN003 （甲方）： 本授权委托书声明：本的法定代表人，授权委托我公司的 为我公司代理人，代表我公司与贵公司工程对涉及投标报价，物资合同、补充协议的签订、履行，物资结算、收款等业务进行签字确认，由在上述授权范围签字的所有文书，我公 司均予认可，由此产生的一切经济法律责任由我公司承担。 代理期限为前述代理人对上述业务发生第一次签字确认之日起至本工程结算完成之日止。代理人无转委托权。 特此委托。 代理人（签字/按指纹）：身份证号码： （供应商）法定代表人签字： （供应商盖章）： 日期： 附件3 廉政合同书 甲方：【 】 乙方：【 】 为确保甲方对业主的承诺，高效、优质共同完成施工任务，争创优质工程，保证合同双方能够高效廉洁地履行， 维护双方合法权益，经双方协商，特订立如下廉政合同书。 第一条 甲乙双方的权利和义务 1.甲乙双方应本着“公开、公平、公正、诚信、透明”的原则开展工作，自觉遵守党和国家、工程项目所在省、 市、区工程建设有关法律法规以及廉政建设的各项规定。 2.甲乙双方应建立健全廉政教育制度，开展经常性教育活动，积极宣贯“合规诚信 自律清正”的廉洁从业核心理 念，加强廉政教育。 3.加强相互监督，发现对方有违反廉政合同书规定的行为，应及时提醒对方纠正。 第二条 甲方的责任 网 甲方工作人员不得有以下行为： （1）为乙方多结算工程量、多签证、多付工程款等，并向乙方索要或接受贿赂、回扣、礼金、有价证券（卡）、 务 贵重物品和好处费等; （2）在乙方报销任何应由甲方或个人支付的费用; （3）参加有可能影响公正执行公务的超标准宴请和娱乐商、健身等活动; （4）接受乙方提供的通讯工具、交通工具和高档办公用品; （5）要求、暗示或接受乙方为个人住房装修道、婚丧嫁娶、配偶子女工作的安排以及出国（境）、旅游提供的方 便; （6）向乙方介绍或推荐配偶、子女、亲属参与的工程施工合同有关的设备、材料、工程分包、劳务等; 管 （7）向乙方推荐分包单位或要求乙方购买合同规定以外的材料、机具设备等; （8）因乙方拒绝本人的不合理要求，而故意刁难乙方。 第三条 乙方的责任 国 乙方应当通过正常途径开展业务，不得有以下行为： （1）为多结算工程量、多签证、多收工程款等，向甲方及其管理人员行贿或馈赠礼金、有价证券（卡）、贵重 中 礼品; （2）为甲方及其工作人员报销应由甲方单位或个人支付的任何费用; （3）安排甲方人员参加超标准宴请、娱乐活动及带有黄、赌性质的娱乐活动; （4）为甲方人员购置或提供通讯工具、交通工具和高档办公用品等; （5）乙方向甲方工作人员及其家属或者亲友介绍从事与甲乙双方工程有关的工程分包及材料设备、周转工具的 供应、租赁等经营活动。 第四条 违约责任 1.如甲方工作人员有违反本廉政合同书的行为，由甲方纪委查处，追究相应的党纪、政务责任，涉嫌犯罪的，移 交司法机关追究刑事责任；对实名举报的，甲方要立即调查，并采取有效措施保障乙方的合法权益，防止报复 事件发生。 2.如乙方单位或个人有违反本廉政合同书的行为，甲方视情节对乙方处以合同额0.5%—1%的罚款，情节较重并给 甲方造成损失的，乙方另需赔偿甲方直接经济损失，并取消乙方工程分包资格。 第五条 甲方接受举报的途径 1. 受理电话：【 】 2. 受理地址：【 】 3. 受理部门：【 】 4. 受理邮箱：【 】 第六条 本廉政合同书作为采购合同的一部分，具有同等法律效力，本协议与采购合同同日生效，至甲乙双方工 程合同履约完止。 甲方： 乙方： 网 法定代表人： 法定代表人： 授权委托人： 授权委托人： 务 签订时间： 年 月 日 请查看报价网 商 址：https://xy.yzw.cn/sj/bid-detail?tenderId=&amp;source=3&amp;tenderCode=cscec2026081900001246027&amp;tenantId=cscec 信息来源:https://www.chinapipe.net/project/d3076919.html cqdingjiu 2026.08.21 10:06:42 道 管 国 中</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076919.html</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>0</v>
       </c>
@@ -788,11 +776,7 @@
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(三标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 网 2.项目概况与招标范围 务 2.1 建设地点： 忠县花桥镇、新立镇、石宝镇、兴峰乡。 商 2.2 项目概况与建设规模①忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）：田块整治 工程：旱地区域撂荒地整治278.95亩；灌溉与排水工程：新建200m蓄水池6座、PE75管道967m、新建1.2*1.2m箱 涵16m、新建2*2m箱涵8m；田间道路工程：新建2.5m混凝土生产路15114m、改建2.5m混凝土生产路1078m、新 建2.5m泥结碎石生产路910m、改建2.5m泥结碎道石生产路279m、新建3.0m混凝土生产路601m、改建3.5m混凝土机 耕路4587m；地力提升工程：施有机肥278.95亩；其他工程：工号牌124块。 管 ②忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）：田块整治工程：旱地区域撂荒地 整治195.54亩；灌溉与排水工程：新建100m蓄水池4座、新建200m蓄水池6座、PE75管道5258m、PE90管 道1375m、PE110管道2156m、改建0.5*0.6m混凝土排水沟740m、改建0.6*0.8m混凝土排水沟109m、改建0.8*1.0m混 凝土排水沟296m、改建1*1.5m混凝土排水沟262m、新建3*2m盖板涵1座；田间道路工程：新建2.5m混凝土生产 路11359m、改建2.5m混国凝土生产路3430m、新建2.5m泥结碎石生产路1834m、新建3.0m混凝土生产路350m；农田 防护工程：新建1.0m高挡土墙39m；地力提升工程：施有机肥195.54亩；其他工程：工号牌142块。 中 2.3 本项目工程总投资金额：约3140万元； 本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）施工图所示范围的所 有内容为准，详见发布的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分： 标段划分情况、建设规模及标段合同估算金额等内容如下： 合同估算金额 序号 项目名称 建设地点 （万元） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二 1 花桥镇、新立镇 1022 标段） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三 2 石宝镇、兴峰乡 735 标段） 网 本项目共分为2个标段，每家投标单位仅对2个标段中的任意1个标段进行投标，若同时参与2个及以上标段投标的， 其投标文件无效。 务 2.7 其他： / 商 3.政府采购工程 道 3.1 是否属于政府采购工程：是 □否 管 3.2 是否专门面向中小企业预留：是 国 专门面向中小企业预留的实施方式： 中 方式一：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（忠县）下载招标文件、工 程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字 证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责 任自负。 5.2投标人可在重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要网提问”栏提出疑问，提问时间从 本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-10-12 09:30，投标人应当在投标截止时间前，通过互 务 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 商 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 道 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 管 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 国 开户银行: 开户银行: 账 号: 账 号: 中 监督部门: 忠县发展和改革委员会 电 话: 023-54456078 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段） 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005499 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421353 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891814619 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082001038 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00385 信息来源:https://www.chinapipe.net/project/d3076880.html cqdingjiu 2026.08.21 10:06:45</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076880.html</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>90</v>
       </c>
@@ -864,11 +848,7 @@
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点： 忠县花桥镇、新立镇、石宝镇、兴峰乡。 2.2 项目概况与建设规模①忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）：田块整治 务 工程：旱地区域撂荒地整治278.95亩；灌溉与排水工程：新建200m蓄水池6座、PE75管道967m、新建1.2*1.2m箱 涵16m、新建2*2m箱涵8m；田间道路工程：新建2.5m混凝土生产路15114m、改建2.5m混凝土生产路1078m、新 建2.5m泥结碎石生产路910m、改建2.5m泥结碎石生产路279m、新建3.0m混凝土生产路601m、改建3.5m混凝土机 耕路4587m；地力提升工程：施有机肥278.95亩；其他工程：工号牌124块。 商 ②忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）：田块整治工程：旱地区域撂荒地 整治195.54亩；灌溉与排水工程：新建100m蓄水池4座、新建200m蓄水池6座、PE75管道5258m、PE90管 道1375m、PE110管道2156m、改建0.5*0.6m混凝土排水沟740m、改建0.6*0.8m混凝土排水沟109m、改建0.8*1.0m混 凝土排水沟296m、改建1*1.5m混凝土排水沟2道62m、新建3*2m盖板涵1座；田间道路工程：新建2.5m混凝土生产 路11359m、改建2.5m混凝土生产路3430m、新建2.5m泥结碎石生产路1834m、新建3.0m混凝土生产路350m；农田 防护工程：新建1.0m高挡土墙39m；地力提升工程：施有机肥195.54亩；其他工程：工号牌142块。 2.3 本项目工程总投资金额：约3140万元； 管 本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）施工图所示范围的所 有内容为准，详见发布国的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分中： 标段划分情况、建设规模及标段合同估算金额等内容如下： 合同估算金额 序号 项目名称 建设地点 （万元） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二 1 花桥镇、新立镇 1022 标段） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三 2 石宝镇、兴峰乡 735 标段） 本项目共分为2个标段，每家投标单位仅对2个标段中的任意1个标段进行投标，若同时参与2个及以上标段投标的， 其投标文件无效。 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 方式一：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 网 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 .技术成果经济补偿 务 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （忠县）下载招标文件、工程量清单、电子图纸等资料。商参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（忠县）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源 交易监督网、重庆市公共资源交易网（忠县）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数字证 书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的，责任 自负。 道 5.2投标人可在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要提 问”栏提出疑问，提问时间从本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 管 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-10-12 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 国 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 中忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 忠县发展和改革委员会 电 话: 023-54450483 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段） 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421361 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00386 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005423 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891832091 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082001039 信息来源:https://www.chinapipe.net/project/d3076879.html 网 cqdingjiu 2026.08.21 10:06:45 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076879.html</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
         <v>0</v>
       </c>
@@ -940,11 +920,7 @@
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(一标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）已由 忠县发展和改革委 员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来 自 业主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具 备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 网 务 2.项目概况与招标范围 商 2.1 建设地点： 忠县马灌镇、三汇镇、永丰镇。 道 2.2 项目概况与建设规模：忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）：田块整治 工程：水田整治50.67亩、水田区域撂荒地整治79亩、旱地区域撂荒地整治62.83亩；灌溉与排水工程：新 建200m蓄水池5座、新建500m蓄水池1座、泵站1座；田间道路工程：新建2.5m混凝土生产路12325m、改 建2.5m混凝土生产路8549m、新建2.5m泥结碎石生产路1223m、新建3.0m混凝土生产路576m、改建3.0m混凝土生 管 产路648m、改建3.0m混凝土生产路（拆除原1.5m宽路）266m、改建3.5m混凝土机耕路1662m；地力提升工程：施 有机肥136.48亩；其他工程：公示牌1座、工号牌213块。 国 2.3 本项目工程总投资金额：约3140万元； 中 本次招标项目合同估算金额：一标段1167万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）施工图所示范围的所 有内容为准，详见发布的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 网 方式一：本项目整体面向中小企业。 务 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 商 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 道 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 管 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 国 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 中 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（忠县）下载招标文件、工 程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及CA数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 5.2投标人可在重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从 本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-10 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 网 监督部门: 忠县发展和改革委员会 电 话: 023-54456078 务 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段） 商 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082000104 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005469 道 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421379 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00387 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891884496 管 信息来源:https://www.chinapipe.net/project/d3076876.html cqdingjiu 2026.08.21 10:06:46 国 中</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076876.html</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
         <v>95</v>
       </c>
@@ -1016,11 +992,7 @@
           <t>永川区农村供水管网巩固提升改造工程(东部片区)答疑补遗文件 永川区农村供水管网巩固提升改造工程（东部片区） 补遗文件（01） 各潜在投标人： 现将“永川区农村供水管网巩固提升改造工程（东部片区）”招标文件补遗通知如下，本次发布的补遗文件中 的所有内容与招标文件具有同等法律效力，如与招标文件、答疑补遗文件（01）网不一致时，以本补遗文件为准。 请各潜在投标人自行下载本补遗文件，不管下载与否，都视为全部知晓其全部内容。 一、本招标项目招标文件第二章投标人须知前附表第1.4.1项第1条第（3）款中“具备建设行政主管部门颁发的有 效的安全生产许可证，企业主要负责人、拟派项目经理具备相应的由建设行政主管部门颁发的有效的安全生产 务 考核合格证书。”修改为： “（3）具备建设行政主管部门颁发的有效的安全生产许可证，企业主要负责人、拟派项目经理具备相应的由水 行政主管部门颁发的有效的安全生产考核合格证书”。 商 二、本招标项目招标文件第二章投标人须知前附表第1.4.1项中第3条“业绩要求”修改为： “投标人自2023年1月1日起至投标截止日止（以合同工程完工日期或工程竣工日期为准），完成过1个单项合同 输配水管网长度不少于100km的水利工程施工道业绩。 提供：供该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴 定书）的证明材料。若提供的上述业绩证明材料不能体现上述业绩指标的，应补充提供业主证明。 管 注：（1）当上述业绩证明材料中针对同一指标存在不一致时，以合同工程完工证书（或合同工程验收鉴定书或 工程竣工证书副本或竣工验收鉴定书）的证明材料为准。（2）投标人提供的业绩为联合体业绩的，其在该业绩 中的工作分工应与本项目承担的工作一致。” 三、本招标项目招标文国件第二章投标人须知前附表第1.4.1项中第5条中的“5.3项目经理业绩要求”修改为： “投标人拟派的项目经理自2023年1月1日起至投标截止日止（以合同工程完工日期或工程竣工日期为准），完成 过1个单项合同输配水管网长度不少于100km的水利工程施工业绩，并在该业绩中担任项目经理。 中 提供：供该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴 定书）的证明材料。若提供的上述业绩证明材料不能体现上述业绩指标的，应补充提供业主证明。 注：（1）当上述业绩证明材料中针对同一指标存在不一致时，以合同工程完工证书（或合同工程验收鉴定书或 工程竣工证书副本或竣工验收鉴定书）的证明材料为准。（2）投标人提供的业绩为联合体业绩的，其在该业绩 中的工作分工应与本项目承担的工作一致。” 四、本招标项目的投标文件递交的截止时间（投标截止时间）调整为2026年9月4日9时30分（北京时间），开标 时间及投标保证金递交截止时间相应顺延。 招标人：重庆市永川区惠永水务有限公司 招标代理机构：重庆永川政鑫综合能源有限公司 2026年8月20日 信息来源:https://www.chinapipe.net/project/d3076870.html cqdingjiu 2026.08.21 10:06:46</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076870.html</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
         <v>80</v>
       </c>
@@ -1092,11 +1064,7 @@
           <t>长寿区海棠、石堰、龙河片区污水管网建设项目(二期)招标公告 长寿区海棠、石堰、龙河片区污水管网建设项目（二期）招标公告 1.招标条件 本招标项目长寿区海棠、石堰、龙河片区污水管网建设项目已由重庆市长寿区发展和改革委员会以长改发投 〔2024〕169号文批准建设，项目业主为重庆市长寿区住房和城乡建设服务中心，建设资金来自财政资金，项目 出资比例为100%，招标人为重庆长寿乡村建设集团有限公司。项目已具备招标条件，现对该项目的施工进行公 开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：长寿区海棠镇、龙河镇、新市街道、云台镇。 2.2 项目概况与建设规模：新改建及修复DN300mm-DN1200mm排水管道20.187公里，其中新改建管道15.21公里， 务 修复管道4.977公里，Ⅲ、Ⅳ级结构性及功能性缺陷修复453处。 2.3 本次招标项目合同估算金额：4139.45万元。 2.4 招标范围：详见招标人提供的本工程的施工图图纸、图商说、设计变更以及工程量清单所明确的全部工程内容。 2.5 工期要求：270日历天。 缺陷责任期要求：24个月。 道 3.政府采购工程 3.投标人资格要求 管 3.1 本次招标要求投标人须具备以下条件： 3.1.1 本次招标要求投标人具备的资质条件：建设行政主管部门颁发的有效的市政公用工程施工总承包三级及以 上资质； 国 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 中 3.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需 在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网 导航栏“主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登 记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公 告发布至2026-08-25 15:00:00前。 4.3招标人应于2026-08-28 18:00:00前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交 易网（长寿区）（https://www.cqggzy.com/changshouweb/）发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-14 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源 交易监督网上发布。] 7.联系方式 招 标 人: 重庆长寿乡村建设集团有限公司 代理机构: 中新创达咨询有限公司 地 址: 重庆市长寿区桃源大道3号一号商务楼5-6楼 地 址: 邮 编: 邮 编: 项目负责人: 刘老师 项目负责人: 钟亮 网 电 话: 023-40233279 电 话: 19132912275 传 真: 传 真: 电子邮箱: 电子邮箱务: 开户银行: 开户银行: 账 号: 账 号: 商 监督部门: 重庆市长寿区发展和改革委员会 电 话: 023-40245080 2026年08月20日 长寿区海棠、石堰、龙河片区污水管网建设道项目（二期） 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公 中国农业银行股份有限公司重庆自由贸易 312601010400083780000033561 司 管试验区分行 重庆联合产权交易所集团股份有限公 中国建设银行股份有限公司重庆渝中支行 6232813760003317764 司 重庆联合产权交易所集国团股份有限公 重庆银行股份有限公司七星岗支行 15010202900420146632392 司 信息来源:https://www.chinapipe.net/project/d3076848.html cqdingjiu 20中26.08.21 10:06:46</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076848.html</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
         <v>0</v>
       </c>
@@ -1168,11 +1136,7 @@
           <t>中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部刺丝滚笼、塑钢模板、泄水管询价采购公告 中铁十一局集团有限公司重庆至万州高铁站前 1标项目经理部 刺丝滚笼、塑钢模板、泄水管询价采购公告 询价编号： ZT1105-XJ-2026-590 尊敬的 各潜 在供应商 : 网 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与 中铁十一局集团有限公司重庆至万州高铁站 前 1标项目经理部 ZT1105-XJ-2026-590， 刺丝滚笼、塑钢模板、泄水管 的报价。 一、 项目概况 务 渝万高铁站前 1标位于重庆市万州区和忠县境内,起止里程DK14+233.2~ D1K47+550.4，正线长度 33.01km，中标造 价 31.73 亿元。管区内共有隧道8座/22.36km，斜井2座/1.76km;桥梁15座/8.97km，其中，预制及架设梁 301 孔，(40+64+40)m和(45+100+45)m连续梁各1联;区间路基22段/1.68km，土石方约67万方，负 责DK0+000~DK57+136段小型构件预制。合同工期54.7月商，开工日期为2022年11月01日，竣工日期为2027 年04 月30日。 二、 询价内容 道 本次 计划对刺丝滚笼、塑钢模板、泄水管 进行询价，询价内容如下： 询价物资一览表 管 计 序 物资 量 包件号 规格型号 数量 备注 号 名称 单 位 国 刺丝 1 GL-01 2.5mm 6m0.5m 米 6500 半径 ≥225mm，包括刀片刺绳、挂丝、连接卡、支架 滚笼 防护 中 栅栏 2 GL-01 用立 50X30X765X2.5mm 套 500 含抱箍、螺栓等配件 柱支 架 平 塑钢 3 MB-01 350X300mm 方 19.2 400*400,1个挡水沿，配固定手柄 模板 米 平 塑钢 4 MB-01 350X300mm 方 19.2 400*400,2个挡水沿，配固定手柄 模板 米 平 塑钢 5 MB-01 300X300mm 方 75.6 2个挡水沿，配固定手柄 模板 米 平 塑钢 6 MB-01 300X300mm 方 75.6 1个挡水沿，配固定手柄 模板 米 7 SSG-01 管篦 PVC250X200x10mm 个 220 材质硬聚氯乙烯 PVC，详见附图 PVC 8 SSG-01 泄水 135X38mm 块 220 材质硬聚氯乙烯 PVC，详见附图 管盖 U型 9 SSG-01 125mm 个 900 详见附图 管卡 UPV 材质硬聚氯乙烯 PVC，两端接头采用阴阳螺纹连接详见 10 SSG-01 C排 125X8mm螺纹 米 2870 附图 水管 UPV 11 SSG-01 C弯 DN125X8mm90° 个 240 材质硬聚氯乙烯 PVC，详见附图 管 UPV 网 125X125X110mm弹性密 12 SSG-01 C三 个 120 材质硬聚氯乙烯 PVC，详见附图 封圈异径斜三通 通 无压 埋地 务 排污 排水 用硬 13 SSG-01 DN125 个 150 材质硬聚氯乙烯 PVC，详见附图 聚氯 商 乙烯 管 T 型接 头 道 合 计 管 说明： 1. 表中数量为计划数量，实际 采购 过程中可能有所调整，最终结算按照实际 采购 数量结算。 2.收货地点：中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部 三、 技术质量 及报价国 要求 1. 此次 询价物资 各项技术性能要 符合 甲方 的要求，质量满足甲方项目部正常使用的要求，保证 产品 的质量合 格。 具体要求或图纸见询价文件技术规格书。 。 中 2 .报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、 结算及付款方式 每个月 15 日为双方价款结算日期（即上月 16 日至当月 15 日内），结算前双方要在对帐确认单上签字认可，乙 方按双方确认的金额开具增值税专用发票，并自发票开具之日起 7日内传递给甲方。甲乙双方在增值税专用发票 传递过程中必须留取相应的交接签证手续。自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发 票认证完成之日起第6个月，支付至本次结算金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内， 累计支付总额不超结算总金额的75%，剩余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理 末次结算后第二年，支付金额应大于等于尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总 额的15%；办理末次结算后第四年，全部付清）。 五、 报价 人资格要求 1.营业范围要求：在中华人民共和国境内依法注册，具有询价物资生产或供应经验的生产商或代理商，并且具有 合法有效的营业执照。 2.生产能力要求： 生产商须具备 询价 物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定 。 代理商需出具制造厂出具签字盖章的授权函。 3.财务能力要求：报价人为增值税一般纳税人或小规模纳税人，有依法纳税的良好记录。 4.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8月至今） 国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；每种物资全指标技术参数性能满足 国家和行业最新标准的各项规定。 5.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年8月至今）企业或企业法定代表人有人民法院生效判决、裁定 认定的行贿犯罪记录的。④ 对纳入国家铁路局“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接受 通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合作 方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 网 6.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 务 ★7 .下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 六、 报价人需要提供的资料 1. 营业执照复印件、 法人身份证复印件、 开户许可证、商授权委托书 、 报价表 和报价人资格要求中所需的证明资 料， 所有资料需加盖公司鲜章。 2. 产品质量检测报告等质量证明文件。 道 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、 询价 报名截止 时间 管 有意参加本次询价采购的报价人 须在铁建云链平台 （ https:// www.crccep. cn） 完成供应商注册，并 于 202 6 年 8 月 20 日 9时 00 分 至 202 6 年 8 月 24 日 9时 00 分在网上 完成报名工作。 八、 询价 截止 时间 国 凡有意参加本次询价采购的报价人，请于 202 6 年 8 月 24 日 14 时 00分 前 提交报价。截止时间前未完成 报价 文 件传输的，视为放弃 报价 。 供应商报价必须严格按照《 报价表 》格式进行报价。 中 九、 联系方式 采购 组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村 71号 联系人：胡先生 联系电话： 13983336494 （提供平台服务支持） 采购人名称：中铁十一局集团有限公司重庆至万州高铁站前 1标项目经理部 地址： 重庆市万州区双河口街道檬兴路万州现代综合物流中心信息交易大厅（中铁十一局） 联系人： 唐大伟 联系电话： 18323391938（提供采购服务支持、保证金退还） 中铁十一局集团有限公司物资设备集中采购管理中心 第五分中心 2026 年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3076805.html cqdingjiu 2026.08.21 10:06:47 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076805.html</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>85</v>
       </c>
@@ -1244,11 +1208,7 @@
           <t>垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告 1.招标条件 本招标项目 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目 已由 垫江县发展和 改革委员会 以 垫江发改委发〔2026〕20号 文批准建设，项目业主为 垫江县太平镇人民政府，建设资金来 自 大中型后扶资金及自筹资金 ，项目出资比例为 100% ，招标人为垫江县太平镇人民政府。项目已具备招 标条件，现对本项目施工进行公开招标，评标办法采用经评审的最低投标价法。网 务 2.项目概况与招标范围 商 2.1 建设地点：垫江县太平镇桂花村 道 2.2 项目概况与建设规模：主要为河堤护岸岸线整治2100m；产业路扩宽及油化改造775.3m；新建污水管网450m， 化粪池2座；产业基地水肥一体化改造45亩等。 管 2.3 本项目工程总投资金额：642.89万元 国 本次招标项目合同估算金额：约5014864.52元 中 2.4 招标范围：本工程施工图纸所含全部的施工内容，具体以招标人发布的工程量清单为准。 2.5 工期要求：工期为360日历天 ，缺陷责任期为24个月。 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：□是 否，因专门面向中小企业预留无法确保充分供应、充分竞争，根据 《政府采购促进中小企业发展管理办法》第六条第(三)“按本办法规定预留采购份额无法确保充分供应、充分竞 争，或者存在可能影响政府采购目标实现的情形”的规定，本项目不专门面向中小企业预留。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 网 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的水利水电工程施工总承包三级 务 及以上资质。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相商应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 道 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 管 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com国/dianjiangweb/)、重庆市公共资源交易监督网下载招标文件、工程量清单、电子图纸等资 料。参与投标的投标人需在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共 资源交易监督网完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交易监督网导航栏“主体信息”页面中“市场主体信息 登记”、“中CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流 程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交易监督 网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-24 17:00:00前。 5.3招标人应于2026-08-28 17:00:00前在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重 庆市公共资源交易监督网发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-28 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交 易监督网发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 垫江县太平镇人民政府 代理机构: 重庆皓辰建设工程咨询有限公司 重庆市渝北区金开大道1228号大雅金开国际1 地 址: 重庆市垫江县太平镇牡丹路191号 地 址: 栋9-2 邮 编: 邮 编: 项目负责人: 余老师 项目负责人: 雷雨得 电 话: 13996889839 电 话: 023-86018770 18580880860 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 垫江县发展和改革委员会 电 话: 023-74517161 网 2026年08月19日 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目 务 户名 开户行 投标保证金账号 垫江县公共资源交易中心 中国农业银行重庆垫江支行 316301010400077950000005966 垫江县公共资源交易中心 中国银行重庆垫江支行 111616885778VA00139 商 垫江县公共资源交易中心 重庆农村商业银行垫江支行 2501010120010009065000128 垫江县公共资源交易中心 工商银行重庆垫江支行营业部 9558853100016843371 垫江县公共资源交易中心 重庆银行垫江支行 820101040000584-101195 道 附件：垫江县2026年度大中型水库移民后期扶持项目-.zip https://www.cqggzy.com/trade/014001/dac54522-3264-4eac-ae47-f434567ce374?categoryNum=014001001007 信息来源:https://www.chinapipe.net管/project/d3076788.html cqdingjiu 2026.08.21 10:06:47 国 中</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076788.html</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
         <v>85</v>
       </c>
@@ -1320,11 +1280,7 @@
           <t>万州区新田等6个镇乡农村饮水质量提升项目招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区新田等6个镇乡农村饮水质量提升项目 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 及文号 务 新建水厂1座（新建2000m3茨竹水厂），输、配水管道改造与新建，管道总长约226.127km，管 主要建设内容 径DN20~DN250，管材为涂塑钢管。 招标项目名 招标方 招标文件计划 拟交易场 合同预估金 序号 招标内容 备注 称 式 发布时间 所 额(万元) 商 万州区新田 万州区新田 重庆市万 招标项目 等6个镇乡农 等6个镇乡农 公开招 州区公共 1 村饮水质量提 2026-08 5000.00 村饮水质量 标 资源交易 升项目道施工总 提升项目 中心 承包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076721.html 管 cqdingjiu 2026.08.21 10:06:48 国 中</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076721.html</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
         <v>80</v>
       </c>
@@ -1396,11 +1352,7 @@
           <t>万州区大周等4个镇乡街道农村饮水质量提升项目招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区大周等4个镇乡街道农村饮水质量提升项目 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 及文号 务 新建50m3蓄水池4口、取水池2座；新建50m3/d-100m3/d水厂2座；改造100m3/d-300m3/d水厂5 主要建设内容 座；铺设DN25-DN250涂塑钢管约86km；新建提水泵站8座；配套阀井、电磁流量计等有关设 施。 招标项目名 招标方 招标文件计划 拟交易场 合同预估金 序号 招标内容 商 备注 称 式 发布时间 所 额(万元) 万州区大周 万州区大周 重庆市万 招标项目 等4个镇乡街 等4个镇乡街 公开招 州区公共 1 道农村饮水 道农村饮道水质 2026-08 3000.00 标 资源交易 质量提升项 量提升项目施 中心 目 工总承包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3076720.html cqdingjiu 2026.08.21 10:06:49 国 中</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076720.html</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
         <v>80</v>
       </c>
@@ -1464,11 +1416,7 @@
           <t>二航科工新燕尾山项目纤维编绕拉挤电缆保护套管采购询价通知公告 中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程项目询比采购 公告 中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程项目已具备采 购条件，现公开邀请供应商参加询比采购活动。 网 1. 采购项目简介 1.1 采购项目名称：中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机 电工程项目。 务 1.2采购方案编号：FA00000674478。 1.3 采购人：中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程 项目经理部。 商 1.4 采购代理机构：中交二航局科工（武汉）有限公司。 1.5 采购项目资金：企业自筹。 道 1.6 采购项目概况：新燕尾山隧道工程位于重庆市内环吉庆隧道北侧，四横线分流道鹿角隧道南侧，西接白居 寺大桥，东接内环快速路，并向东延伸接渝黔复线高速，其所在的道路系统呈东西布置，为主城区南部片区重 要干道。本项目西起太阳岗立交(不含太阳岗立交)，往东穿越铜锣山，止于内环南泉立交(不含南泉立交)。项目 管 全长约6.8km，其中二标段长约3.62公里，采用主干路标准，设计车速60km/h，标准路幅为双向6车道，主要工程 包括长隧道1座(新燕尾山隧道，长2542m)，简易立交1座(花溪立交),互通式立交2座(南温泉立交、苦竹坝立交)。 2.采购范围及相关要求 国 2.1 采购范围：纤维编绕拉挤电缆保护套管（BWFRP100/2.0，79158米）。 2.2 交货期：以甲方实际订单要求为准。 中 2.3 交货地点：重庆市巴南区新燕尾山项目甲方指定位置。 2.4 物资质量标准：满足国家法律法规、标准、规范、设计参数及技术规格书要求。 3.供应商资格要求 3.1 供应商应依法设立且满足如下要求： （1）资质要求：在中华人民共和国境内依法注册，具有独立法人资格、具有采购物资生产或供应经验的企业， 并且具有合法、有效的“三证合一”的营业执照,代理商需提供制造商授权委托书。 （2）财务要求：必须是经税务部门注册登记核准的一般纳税人，有依法纳税的良好记录，提供近三年的财务报 告。 （3）业绩要求：同类产品销售业绩不少于2个，并具备与本招标项目需求相适应的供货能力。 （4）信誉要求：本项目投标截止期前未被“信用中国”、“中国政府采购网”、中国交建物资采购管理信息系 统网站列入失信被执行人、违法案件当事人、违法失信行为记录名单。 （5）其他要求：提供运输方案及生产周期。 3.2 供应商不得存在下列情形之一： （1）处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； （2）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （3）已列入黑名单，且未解除限制期限； （4）其他： / 。 4.供应商报名 4.1有意参加询比采购活动的单位，请于2026年 8 月 20 日 11 时 00 分至2026 网 年 8 月 25 日 11 时 00 分（北京时间、下同），登录“中交招采网”（网 址：https://zjzcw.iccec.cn）进行报名并下载采购文件。 4.2 已在网并且已通过采购人层级供应商或已增加采购人为合作单位的供应商、上级供应商可直接参与询比采 务 购。在网平级单位供应商未增加采购人为合作单位需进行合作意向申请通过后参与询比采购。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择采购人，审核通过后方可参与询比 采购。 商 5. 供应商报价 5.1 报价结束（递交响应文件截止）时间：2026年 8 月 25 日 11 时 00 分。 道 5.2 供应商应在报价结束时间前，登录“中交招采网”进行线上报价并上传电子响应文件。逾期未完成上传的 电子响应文件，采购人将拒收。 5.3电子采购的供应商报价文件由线上电子报价表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 管 子报价表的数据为准。 6. 开标 6.1开标时间：与报价结国束时间相同。 6.2开标地点：本次采购在“中交招采网”平台线上开标，不举办现场开标，现场开标地点/。 7. 发布公告的媒介 中 本询比采购公告在中交招采网上发布。 8. 评审办法 本项目评审办法采用 经评审的最低价法 。 9. 合同主要条款 9.1 付款条件：无预付款，到货后办理结算，双方办理完结算手续、卖方提供符合合同要求的正式发票给买方 后60天，买方支付该批材料价值80%的货款，完工结算后支付至97%，剩余3%为质保金，质保期2年，两年后供 应方申请返还3%（无息）；银行转账、承兑、18个月供应链金融混合支付方式。 9.2履约保证金的递交： （1）□不要求递交 （2）要求递交 保证金金额：2万元 ； 保证金形式：银行转账、银行保函等电子保函；其他形式：无 。 10. 成交供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”（网址：https://zjzcw.iccec.cn）发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联 系4006765885中标服务费请按7咨询。 10.1收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： 网 （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； 务 （3）在1000万元（含）至3000万元之间的，每次收取1000元； （4）在3000万元（含）至1亿元之间的，每次收取3000元； （5）在1亿元（含）以上的，每次收取5000元。 商 10.2支付流程 （1）通知推送：中标结果发布后，系统自动道推送缴费通知（含应缴金额及支付链接）； （2）费用查询：供应商登录“中交招采网-服务管理”模块查看待支付费用； （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 管 （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网- 服务管理－发票下载”模块获取。 11.监督机构 国 监督机构名称：中交二航局科工（武汉）有限公司纪委监察部 举报电话：中027-82796466 举报邮箱：sneb_kggs@ccccltd.cn 12.其他 投标保证金采用银行转账形式的需转至中交二航局科工（武汉）有限公司账户（账 号：42001186108053006379-0006开户行：建行武汉长江支行，行号：105521000053），并备注二航科工燕尾山机 电照明项目纤维编绕管投标保证金。 13.联系方式 采购 人：中交二航局科工（武汉）有限公司 采购代理机构：中交二航局科工（武汉）有限公司 地 址：武汉市新洲区双柳街星谷大道158号地 址：武汉市新洲区双柳街星谷大道158号 邮政编码：430400 邮政编 码：430400 联系人：李鑫 联系人：毕明 月 电 话：18186145302 电 话：17853118573 电子邮件：18186145302@ccccltd.cn 电子邮件：bimingyue@ccccltd.cn 2026年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3076715.html cqdingjiu 2026.08.21 10:06:50 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076715.html</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
         <v>90</v>
       </c>
@@ -1540,11 +1488,7 @@
           <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程变更公告 重庆巴南天然气有限责任公司 重庆国际生物城配套公寓项目天然气表后管道安装工程 变更公 告 公告编号： RQBGGG202608200006 本公司于2026年08月19日发布的重庆国际生物城配套公寓项目天然气表后管道安装工程公告（编 号：RQCGXY202608170010），现做出如下变更： 网 1、对采购文件第一卷“采购需求“中墙体管道暗埋的具体内容进行明确。墙体管道暗埋应包含墙体开槽，输送 用不锈钢波纹管及钢制槽板的安装，墙体恢复，暗埋管道视频记录。 2、对由响应供应商提供的钢制槽板的规格进行明确。钢制槽板为U型开口槽，采用热镀锌Q235B钢板，钢板厚度 务 不得小于1.2mm，尺寸不得小于U40*30*1.2（宽40mm,高30mm,壁厚1.2mm热镀锌） 3、对由响应供应商提供的F型不锈钢三通，材质可以选用黄铜进行替代。 4、采购文件第二卷“技术规范及要求“中增加T/CECS633-2019 《燃气用户工程不锈钢波纹软管技术规程》。 以上内容在合同中也同步进行调整。 商 除上述变更外，原公告其余内容仍有效。 道 重庆巴南天然气有限责任公司 管 2026-08-20 信息来源:https://www.chinapipe.net/project/d3076704.html cqdingjiu 2026.08.21 10:国06:50 中</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076704.html</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
         <v>80</v>
       </c>
@@ -1616,11 +1560,7 @@
           <t>合川区中南片区污水管网工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目 合川区中南片区污水管网工程（一期） 名称 招标 网 法人 或招 标人 重庆市合川区住房和城乡建设委员会 名称 （盖 务 章） 项目 批准 文件 合川发改投〔2025〕19 号 商 及文 号 主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300-D800管道130米，新增检查井11座，新 主要 建D300排水管道38米；紫外光修复 D300-D道800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米， 建设 螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米，不锈钢快速锁修复 D1000管道42 内容 米；完成 D300-D1000管道清障189米、清淤2627米。 拟 招 招标文 合同预 招标 管 交 序 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 所 国 重 庆 市 合川 合 招标 区中 主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300- 川 项目 中 南片 D800管道130米，新增检查井11座，新建D300排水管道38米；紫外光修复 公 区 区污 D300-D800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米， 开 公 1 2026-09 1708.44 水管 螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米， 招 共 网工程 不锈钢快速锁修复 D1000管道42米；完成 D300-D1000管道清障189米、清 标 资 （一 淤2627米。 源 期） 交 易 中 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076543.html cqdingjiu 2026.08.21 10:06:50</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076543.html</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>90</v>
       </c>
@@ -1684,11 +1624,7 @@
           <t>重庆市自来水有限公司球墨铸铁管及管件2026-2027(2年)采购项目(第二次)答疑补遗文件 重庆市自来水有限公司球墨铸铁管及管件2026-2027（2年）采购项目（第二次）答疑 提问1：样品20CM长含承口吗？如果含承口20CM那就太短，标识LOGO无法体现完整建议≥20CM 答1：球墨铸铁管样品含承口，样品长度≥20CM 网 务 招标人：重庆市自来水有限公司 招标代理机构：重庆水务集团公用工程咨询有限公司 商 2026年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d30道76446.html cqdingjiu 2026.08.21 10:06:50 管 国 中</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076446.html</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
         <v>80</v>
       </c>
@@ -1760,11 +1696,7 @@
           <t>大足区中心城区和龙水镇市政公共排水设施运维(材料)更正一号公告 一、更正项 更正项 更正子项 更正前内容 更正后内容 网上投标 网上投标截止时间 2026-08-20 15:00:00 2026-08-25 15:00:00 递交投标响应文件 线下递交投标（响应）文件开始时间 2026-08-20 14:30:00 2026-08-25 14:30:00 递交投标响应文件 线下递交投标（响应）文件截止时间 2026-08-20 15:00:00 2026-08-25 15:00:00 网 开标 开标时间 2026-08-20 15:00:00 2026-08-25 15:00:00 招标采购（附件） 附件 务 二、补遗更正说明 清单限价重新做调整，开标时间已更正，详见更正文件内容 商 三、联系方式 采购执行方： 道 单位名称：重庆誉双项目管理有限公司 联系人：陈老师 联系电话：13996336872 采购需求方： 管 单位名称：重庆市大足区茂泰市政工程有限公司 联系人：谢老师 联系电话：18523539371 信息来源:https://www.chinapipe.net/project/d3076319.html 国 cqdingjiu 2026.08.21 10:06:50 中</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076319.html</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
         <v>80</v>
       </c>
@@ -1836,11 +1768,7 @@
           <t>璧山区2026年大路街道三台村智慧设施农业建设项目招标计划表 重庆市工程建设项目招标计划表 项目 璧山区2026年大路街道三台村智慧设施农业建设项目 名称 招标 法人 或招 网 标人 中农良品（重庆）生态农业有限公司 名称 （盖 章） 项目 批准 务 文件 及文 号 主要 1.新建茄果类智能种植温室11256平方米；2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、二氧化碳补施系统1套、智能环境控制系统1套、作业物流 建设 装备1套；3.项目后勤及仓储配套（含装修）5000平方米；4.土方回填及场地平整53000平方米；5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米；6. 内容 都市农文旅配套建设1000平方米。 商 招 拟 标 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 称 道 璧 山 区2026 重 年 庆 大 市 路 公 招标 街 管 共 项目 道 资 三 公 源 台 项目主要建设内容包括：1.新建茄果类智能种植温室11256平方米； 2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、 开 交 1 村 二氧化碳补施系统1套、智能环境控制系统1套、作业物流装备1套； 3.项目后勤及仓储配套（含装修）5000平方米； 4.土方回填及场地平整53000平 2026-09 9182.25 招 易 智 方米； 5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米； 6.都市农文旅配套建设1000平方米。 标 中 慧 心 设 国 璧 施 山 农 分 业 中 建 心 设 项 目 中 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076777.html cqdingjiu 2026.08.21 10:06:51</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076777.html</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
         <v>80</v>
       </c>
@@ -1912,11 +1840,7 @@
           <t>长寿区江南街道污水处理厂更新改造工程项目公告 长寿区江南街道污水处理厂更新改造工程比选公告 1. 比选条件 本比选项目长寿区江南街道污水处理厂更新改造工程，比选人为重庆环保投资集团有限公司，资金来源为企业 自筹，出资比例为100%。现对该项目进行公开比选，诚邀有兴趣的潜在参选人参与比选。 2. 项目概况与比选范围 网 2.1项目概况：长寿区江南街道污水处理厂更新改造工程包括但不限于以下内容新建混凝池-三沉池；还建格栅池； 厌氧池新增搅拌机，好氧池联通孔短流整改、拆除填料及底部曝气盘，增设可提升曝气系统；原斜管沉淀池改 造为二沉池（新增中心筒、改造成多斗排泥、提高液位，更换三角堰）。拆除原有污泥池，新增临时污泥储罐 务 并还建污泥池；污泥堆场临时改建及恢复；实施技改期间的临时排放工程；进行基础的自控改造。 2.2 比选范围：长寿区江南街道污水处理厂更新改造工程施工图范围中的所有工作内容，包括但不限于土建工 程、设备及安装工程、工艺管道工程、电气工程、临排工程等内容，具体以比选人提供的图纸、技术规范、设 备需求清单、答疑资料、澄清资料、其他补遗资料等相关商内容为准。 2.3 建设地点：重庆市长寿区江南街道。 2.4 工期：110日历天（实际开工日期以监理工道程师签发的工程开工通知明确的开工日期为准），缺陷责任期24 个月。 3. 参选人资格要求 管 3.1 本次比选要求参选人具备以下条件： （1）独立法人资格； （2）建设行政主管部国门颁发的有效的市政公用工程施工总承包二级及以上资质； 3.2 参选人还应在资质、业绩、资金、人员等方面具有相应的服务能力，详见比选文件第二章参选人须知前附 表第1.4.1项内容。 中 3.3本次比选不接受联合体参选。 4. 比选文件的获取 4.1 参选人于2026年8月19日起可自行在重庆水务集团电子商务平台（https://www.cqswjt.cn）上下载比选文件电 子版，以及答疑、补遗等比选截止时间前公布的所有相关资料，不管参选人下载与否，比选人和代理机构都视 为参选人收到以上资料并全部知晓有关比选过程和事宜，如因参选人自身原因未能下载相关资料由此产生的一 切后果由参选人自行负责。各参选单位应随时关注网上（https://www.cqswjt.cn）发布的比选文件及相关修改内容。 4.2 参选人须在重庆水务集团电子商务平台（https://www.cqswjt.cn）进行供应商注册，填写相关信息，审批过后 成为平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标（仍须同时提交纸质版参选文件）。参选 人需提前在重庆水务集团电子商务平台（https://www.cqswjt.cn）上注册、报名，下载比选文件，上传参选文件电 子档并报价。在比选截止时间前未按时报名、报价并上传参选文件电子档、递交纸质版参选文件者，将被否决 参选。 5. 比选文件的递交 5.1 参选文件递交时间：2026年8月 27 日09时00分至09时30分，地点：重庆市两江新区嘉华路36号重庆水务 大厦5楼。 5.2 比选截止时间：2026年8月 27 日09时30分（北京时间）。 5.3 逾期送达的或者未送达指定地点的参选文件，比选人不予受理。 6. 发布比选公告的媒介 本次比选公告在重庆水务集团电子商务平台（https：//www.cqswjt.cn）上发布。 7. 联系方式 比选人：重庆环保投资集团有限公司 地 址：重庆市两江新区礼环南路102号 网 联系人：曹老师 电话：023-71618725 务 代理机构：重庆招标采购（集团）有限责任公司 地址：重庆市江北区五简路2号重庆咨询大厦A座2004室 商 联系人：高老师 电话：023-67706841 道 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 管 信息来源:https://www.chinapipe.net/project/d3076456.html cqdingjiu 2026.08.21 10:06:51 国 中</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076456.html</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
         <v>90</v>
       </c>
@@ -1988,11 +1912,7 @@
           <t>潼南区新胜镇、双江镇污水处理厂更新改造工程项目项目公告 潼南区新胜镇、双江镇污水处理厂更新改造工程比选公告 1. 比选条件 本比选项目潼南区新胜镇、双江镇污水处理厂更新改造工程，比选人为重庆环保投资集团有限公司，资金来源 为企业自筹，出资比例为100%。现对该项目进行公开比选，诚邀有兴趣的潜在参选人参与比选。 2. 项目概况与比选范围 网 2.1项目概况：潼南区新胜镇污水处理厂更新改造工程，主要建设内容为新增200m?/d一体化污水处理设备基础； 更新现有污水处理系统设备，提高现有沉淀池二沉池、三沉池液位；升级处理系统（干化池改建为污泥池，新 增叠螺脱水机，改建污泥堆场及雨棚）；新建风机房－配电室防尘防渗地坪。潼南区双江镇污水处理厂更新改 务 造工程，主要建设内容为将原有斜管沉淀池改建为好氧池，新建3座竖流沉淀池，配套安装相关设备；更新污水 处理系统中老旧及故障设备；新建储药加药区与一体化危废储存间，完善污水处理配套设施。 2.2 比选范围：潼南区新胜镇、双江镇污水处理厂更新改造工程施工图范围中的工作内容（一体化设备采购及 相关安装工作除外），包括但不限于土建工程、附属工程商（包括但不限于绿化工程、工艺管线工程、电气及自 控工程、临排清淤工程等）、一体化污水处理设备基础、标准化建设、配套设备材料采购及安装工程等内容， 其中一体化设备采购及相关安装工作不在本次比选范围内；具体以比选人提供的图纸、技术规范、工程量清单、 答疑资料、澄清资料、其他补遗资料等相关内容为准。 道 2.3 建设地点：潼南区新胜镇、双江镇。 2.4 工期：120日历天（实际开工日期以监理工程师签发的工程开工通知明确的开工日期为准），缺陷责任期24 个月。 管 3. 参选人资格要求 3.1 本次比选要求参选人具备以下条件： 国 （1）独立法人资格； （2）建设行政主管部门颁发的有效的市政公用工程施工总承包二级及以上资质； 中 3.2 参选人还应在资质、业绩、资金、人员等方面具有相应的服务能力，详见比选文件第二章参选人须知前附 表第1.4.1项内容。 3.3本次比选不接受联合体参选。 4. 比选文件的获取 4.1 参选人于2026年8月19日起可自行在重庆水务集团电子商务平台（https://www.cqswjt.cn）上下载比选文件电 子版，以及答疑、补遗等比选截止时间前公布的所有相关资料，不管参选人下载与否，比选人和代理机构都视 为参选人收到以上资料并全部知晓有关比选过程和事宜，如因参选人自身原因未能下载相关资料由此产生的一 切后果由参选人自行负责。各参选单位应随时关注网上（https://www.cqswjt.cn）发布的比选文件及相关修改内容。 4.2 参选人须在重庆水务集团电子商务平台（https://www.cqswjt.cn）进行供应商注册，填写相关信息，审批过后 成为平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标（仍须同时提交纸质版参选文件）。参选 人需提前在重庆水务集团电子商务平台（https://www.cqswjt.cn）上注册、报名，下载比选文件，上传参选文件电 子档并报价。在比选截止时间前未按时报名、报价并上传参选文件电子档、递交纸质版参选文件者，将被否决 参选。 5. 比选文件的递交 5.1 参选文件递交时间：2026年8月27日09时00分至09时30分，地点：重庆市两江新区嘉华路36号重庆水务大厦5 楼。 5.2 比选截止时间：2026年8月27日09时30分（北京时间）。 5.3 逾期送达的或者未送达指定地点的参选文件，比选人不予受理。 6. 发布比选公告的媒介 本次比选公告在重庆水务集团电子商务平台（https：//www.cqswjt.cn）上发布。 7. 联系方式 网 比选人：重庆环保投资集团有限公司 地 址：重庆市两江新区礼环南路102号 务 联系人：陈老师 电话：023-42756696 商 代理机构：重庆招标采购（集团）有限责任公司 道 地址：重庆市江北区五简路2号重庆咨询大厦A座2004室 联系人：高老师 管 电话：023-67706841 重庆水务电子商务平台国咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3076454.html cqdingjiu 2026.08.21 10:06:51 中</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076454.html</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
         <v>90</v>
       </c>
@@ -2056,11 +1976,7 @@
           <t>重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表 重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表 采购需求单位(全称) 重庆医科大学附属第二医院总务科 项目名称 重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程 项目内容 给重庆医科大学附属第二医院医疗教学配套业务用房配置第二市政水源 采购预算 409674.71元 网 拟采购供应商全称 东部自来水分公司 配套业务用房第二市政水源从重庆水资源产业股份有限公司东部自来水分公司管辖范围 单一来源采购理由 的管网具体接入，属于市政管网施工，具有特殊要求。 务 公示时间 2026年8月19日-2026年8月25日 联系人及联系电话 刘老师 023-63693215 注：1.以上陈述是否真实，欢迎社会各界监督，公示时间商至少5个工作日； 2.公示期内无异议的，采购管理处将进行该项目采购；有异议请将意见反映采购人。 信息来源:https://www.chinapipe.net/project/d30道76334.html cqdingjiu 2026.08.21 10:06:51 管 国 中</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076334.html</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
         <v>80</v>
       </c>
@@ -2132,11 +2048,7 @@
           <t>中铁二院工程集团有限责任公司G319黔江区正阳至城西段改建工程管线探测工作线上询价采购公告 中铁二院工程集团有限责任公司G319黔江区正阳至城西 段改建工程管线探测工作线上询价采购 ZTEYCQ-XJ-2026-019 网 采购单位: 中铁二院工程集团有限责任公司 发布时间: 2026-08-19 16:10 报价截止时间: 务 2026-08-21 17:00 招标方联系人: 杨先生 招标方联系电话: 商 13883021521 招标方邮箱: 监督方联系人: 李先生 道 监督方联系电话: 15823237919 监督方邮箱: 保证金: 0元 管 结算与发票信息: 详情 交货信息: 详情 国 其他说明事项: 标的明细 流水号：询2026081900304 中 计量单 技术标准及要 序号 标的名称 数量 交货期 送货地址 位 求 G319黔江区正阳至城西段 合同签订后5天内完成 西南区-重庆市-市辖 1 1 项 详见询价文件 改建工程管线探测工作 本项目服务内容。 区-黔江区-项目地点 信息来源:https://www.chinapipe.net/project/d3076309.html cqdingjiu 2026.08.21 10:06:51</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076309.html</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
         <v>80</v>
       </c>
@@ -2208,11 +2120,7 @@
           <t>乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告 乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告 1.招标条件 本招标项目乌江涪陵榨菜绿色智能化生产基地(一期)已由重庆市涪陵区发展和改革委员会以重庆市企业投资项目 备案证2020-500102-13-03-000003 批准建设，项目业主为重庆市涪陵榨菜集团股份有限公司，建设资金来自企业 自筹，项目出资比例为100% ，招标人为重庆市涪陵榨菜集团股份有限公司。项目已具备招标条件，现对乌江 涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 2.1 建设地点： 重庆市涪陵区马鞍街道人和社区 。 网 2.2 项目概况与建设规模：建筑面积约369384.27㎡。本项目蒸汽管道主要为室外蒸汽管道φ219x6mm，管道材质： 20#地上敷设，由14#锅炉房分汽缸分别接至6#和8#智能化车间分汽缸，蒸汽管道运行压力1.08MPa，管道设计压 力1.2MPa。 务 2.3 本次招标项目合同估算金额：580.643717万元。 2.4 招标范围： 商 （1）蒸汽管道系统本体：从锅炉房分汽缸后（含分气缸阀门）至6#车间、8#车间分气缸处，所有蒸汽管道、管 件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸等的采购、运输、安装、保温（含保温层及保 护层）工作。 道 （2）钢结构桁架工程：负责本项目范围内所有钢结构架空桁架（管廊）的采购、运输、制作、安装、防腐工作。 （3）管道附件及控制系统：负责本工程范围内所有阀门、压力表、温度表、流量计、电动/气动执行机构以及配 套仪表电缆、桥架、保护管的采购、运输、安装、接线。负责与DCS/PLC系统接口的接线与联动调试。 管 （4）调试与验收：组织并确保整个蒸汽管道系统（含分气缸后段末端管道、桁架及其安全附件）通过项目所在 地特种设备安全监察管理部门实施的安装监督检验。负责报检、配合现场检验、整改、出具深化图纸并由设计 单位审核盖章、特种设备法定报检取证的全部费用，包括但不限于：施工前办理安装告知，设计院盖章审核， 施工中接受并通过安装国监督检验，最终负责取得《压力管道安装监督检验证书》与《特种设备使用登记证》， 确保蒸汽管道投入使用并备案，提交全套法定检验报告。 （5）土建工作部分 中 1）管架和桁架基础的施工，包括但不限于钢结构桁架的混凝土独立基础的土方开挖、浇筑、养护及回填恢复。 2）管道穿墙/板孔洞的开挖、封堵与修复。 3）室内外地面的开挖（包括但不限于疏水井、沟槽开挖、通行地沟、设备基础开挖）与恢复（包括但不限于土 方回填、渣土弃运、地面硬化）。 4）桁架及设备接地线的施工，包括但不限于接地极制作、接地干线敷设，并与厂区主接地网可靠连接，接地电 阻测试合格。 具体详见施工图、招标文件、工程量清单、答疑补遗等资料。 2.5 工期要求： 60 日历天 缺陷责任期要求： 24 个月 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：投标人应同时具备以下(1)、(2)项资质： （1）具备建设行政主管部门颁发的有效的建筑工程施工总承包二级及以上资质； （2）具备有效的《中华人民共和国特种设备生产许可证》（许可子项目：工业管道安装GC2级及以上）。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 网 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 务 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（涪陵区） （https://www.cqggzy.com/fulingweb/）下载招标文件、工程商量清单、电子图纸等资料。参与投标的投标人需在重 庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏 “主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网（涪陵区道）（https://www.cqggzy.com/fulingweb/）本项目招标公告网页下 方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-23 17:00:00前。 4.3招标人应于2026-08-24 18:00:00前在重庆市公共资源交易网（涪陵区）（https://www.cqggzy.com/fulingweb/）发 布澄清。 5.投标文件递交的内容 管 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-09 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 国 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（涪陵区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 中重庆市涪陵榨菜集团股份有限公司 代理机构: 中招国际招标有限公司 重庆两江新区黄山大道中段53号5-1（双 地 址: 重庆市涪陵区江北街道办事处二渡村一组 地 址: 鱼座A栋5楼） 邮 编: 408000 邮 编: 项目负责人: 徐老师 项目负责人: 寿云凤 电 话: 13212467016 电 话: 023-68881331-9032 传 真: 传 真: 电子邮箱: bsd2me@126.com 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市涪陵区发展和改革委员会 电 话: 023-72203687 2026年08月19日 乌江 涪陵 榨菜 绿色 智能 化生 产基地 (一 期)6#、 8#车 网 间蒸 汽管 道安 装工 务 程 中 中 国 国 重 银 重 商民 重 庆 行 庆 生 庆 涪 股 涪 银 涪 陵 份 陵 行 陵 重 投 公 有 道公 股 公 庆 标 共 限 共 份 共 银 开 保 户 资 公 资 有 资 行 户 证 110292140553VA00154 9902001860445897 430102029007791845-275 名 源 司 源 限 源 涪 行 金 交 重 交 公 交 陵 账 管 易 庆 易 司 易 支 号 有 涪 有 重 有 行 限 陵 限 庆 限 公 马 公 涪 公 国 司 鞍 司 陵 司 支 支 行 行 中 信息来源:https://www.chinapipe.net/project/d3076300.html cqdingjiu 2026.08.21 10:06:51</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076300.html</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
         <v>95</v>
       </c>
@@ -2284,11 +2192,7 @@
           <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程询比采购公告 采购公告 公告编号： RQXYGG202608190057 一、采购项目基本情况 采购人：重庆巴南天然气有限责任公司 网 采购项目编号：RQCGXY202608170010 采购项目名称：重庆国际生物城配套公寓项目天然气表后管道安装工程 务 采购内容和范围：完成重庆国际生物城配套公寓项目 （民用1020户）天然气表后管道定制化服务。（含安装燃 气输送用不锈钢波纹管RSB-IF-13—12240米（预估）、双外螺纹球阀DN15-1020个、燃气管道自闭阀DN15-1020个， 其它配套管件及辅材，墙体管道暗埋等） 二、供应商资格要求 商 1. 资质要求:资质要求： 1.响应供应商为中华人民共和国境内合法注册的独立法人或其他组织，具有独立承担民事责任能力，具有独立订 立合同的权利。 道 2.响应供应商应具备市政公用工程施工总承包三级及以上资质、具备有效的安全生产许可证。 3.响应供应商应为本项目配备项目负责人一名，持有市政公用工程或机电工程专业二级建造师及以上资质，且为 本单位在职人员并提供社保证明。 4.响应供应商应为本项目配备专职安全员一名，持有安全生产考核合格C证，且为本单位在职人员并提供社保证 管 明。 5.项目负责人及专职安全员社保证明期限须包含2026年5月至2026年7月。提供的社保证明，须体现上述人员的姓 名、身份证号（或社保号）、单位名称、本单位参保时间（或起始参保时间），并带有社保部门公章或社保部 门的有效电子印章。 2. 信用要求:6.信用要求国： （1）响应供应商（含联合体响应的成员单位）未被“国家企业信用信息公示系统” 网站（www.gsxt.gov.cn）列 入严重违法失信企业名单（如：提供网站查询界面截图）； （2）响应供应商（含联合体响应的成员单位）未被 “信用中国”网站（www.creditchina.gov.cn）列入严重失信 主体名单（中如：提供网站查询界面截图）。 三、采购文件的获取 采购文件在 华润守正采购交易平台 发布，不再另行线下提供纸质采购文件，凡有意参与者请自行登录守正平台 查看和下载采购文件。 四、响应文件的提交 响应文件提交 / 报价截止时间： 2026-08-25 08:00:00 （北京时间，若有变化另行通知）。 响应文件提交 / 报价方式：在响应文件提交 / 报价截止时间前，通过 华润守正采购交易平台 提交电子响应文件或 报价，逾期提交将被拒收。 五、采购人联系方式 联系人：何俊 电话：15178855716 邮箱：1460553040@qq.com 六、采购明细 行号 采购内容 需求数量 单位 补充说明 1 重庆国际生物城配套公寓项目天然气表后管道定制化服务 1 元/次 具体内容详见采购文件 七、答疑澄清、通知 答疑澄清、通知等文件一经在 华润守正采购交易平台 发布，视为已发放给相应供应商（发放时间即为发出时 间），请随时关注 华润守正采购交易平台 发布的相关信息，并及时查阅和处理。 八、服务费交纳 网 本项目向成交人收取服务费,供应商收到预成交通知书和服务费交款通知书10日内,向平台运营方(华润守正招标有 限公司)支付服务费,经确认无误后由采购人发送成交通知书。平台运营方在收到服务费后向成交人开具服务费发 票。 收费标准：项目总成交金额＜50万元的采购项目，免收服务费。项目总成交金额≥50万元的采购项目，按成交金 务 额的0.15%向成交人收取（金额四舍五入，精确到分）。单项目总收费封顶100000元。其他说明：（1）总价采购， 收费基数为成交金额；单价、费率采购，收费基数为预算金额。（2）单项目存在多个成交人情形的，按总成交 金额计算收费总额，各成交人按成交比例分摊；项目总成交金额50万以上，但单个成交人成交金额少于50万仍按 比例收取服务费。 商 退款说明：成交通知书发布后,平台提供相关服务已完成,成交人已交纳服务费不予退还。 多成交人服务费收取示例： 以某项目总成交金额100万为例,A、B、C多成交人情形,总服务费为0.15万, 供应商A成交金额为50万,A服务费为0.075万; 供应商B成交金额为30万,B服务费为0.045万; 道 供应商C成交金额为20万,C服务费为0.03万。 九、其它事项 管 1.本公告在 华润守正采购交易平台 ( https://www.szecp.com.cn/ )上公开发布。 2.本项目采购通过守正平台线上进行，供应商需注册 华润守正采购交易平台 ，通过平台进行响应文件的递交或 报价，具体操作步骤可查阅网站首页帮助中心的操作手册，也可以联系守正客服。 国 3.如对采购项目有异议，请登录 华润守正采购交易平台 ,通过异议菜单提出。 2026年08月19日 中 信息来源:https://www.chinapipe.net/project/d3076125.html cqdingjiu 2026.08.21 10:06:52</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076125.html</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
         <v>80</v>
       </c>
@@ -2352,11 +2256,7 @@
           <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)非金属管道管件阀门采购招标公告 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采购招标公告 1、招标条件 本招标项目废盐综合利用联产20万吨/年离子膜烧碱项目已由重庆市长寿区发展和改革委员会以 重庆市企业投 资项目备案证（2207-500115-04-05-168305）批准建设，项目业主为重庆市映天辉氯碱化工有限公司，建设资金来 自业主自筹，项目出资比例为100%，招标人为重庆市映天辉氯碱化工有限公司。项目已具备招标条件，现对本 项目的（一期12万吨/年）非金属管道管件阀门采购进行公开招标。 网 2、项目概况 2.1 建设地点：重庆长寿经济技术开发区化北路2号。 务 2.2、项目概况与建设规模： 重庆市映天辉氯碱化工有限公司（以下简称“映天辉”）位于重庆长寿经济技术开发区化北路2号，始建于2004 年5月，占地430亩，注册资本34800万元。现为国有控股企商业，是一家集氯碱生产经营、新材料研发经营于一体 的专业型、科技型综合企业，系国家级高新技术企业。 映天辉作为长寿经开区氯碱产业基础平台的龙头化工企业，现有一条氯碱生产线，生产规模为20万吨/年烧碱 （折100%NaOH计）。为建设并贯通氯碱化工道循环经济产业链，保障下游产业链装置氯气需求，实现氯碱产品的 升级和高端化发展，增加产品附加值，降低成本，提高竞争力，映天辉公司经过充分调研和反复论证后，拟开 展废盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）建设。装置在正常运行情况下，按照每年 8000 小时操作。具体要求及参数以第五章货物需求一览表及技术规格标准和要求为准。 管 2.3 本次招标项目货物采购估算金额： 约 330 万元。 2.4招标范围： 本次招标项目为：“废国盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采 购”包括不限于非金属管道管件阀门所含设计、制造、试验、出厂检验、防腐、运输（含保护、包装及运输、 货到现场车板交货）、保险（交货验收前）、指导安装、调试、备件及专用工具、税费、技术资料和图纸及质 保期内的各种备品、备件的供应及相关的技术服务、产品质量证明书及原材料检测报告等。（详见“第五章货 物需求一览中表及技术规格标准和要求”）。 2.5 交货地点：货物运送至买方指定地点； 2.6 交货期： 2.6.1合同签订后3个月内，所有货物运送招标人现场并具备安装条件。 2.6.2 中标方应于合同签订之日起7天内，向买方提交完整的技术资料，以供设计院开展相关设计工作。 3、投标人资格要求 3.1 投标人应符合以下要求： （1）投标人具备有效的营业执照。 注：不得将投标人营业执照记载的经营范围作为评审因素。 （2）投标人具备有效的《中华人民共和国特种设备生产许可证》压力管道管子-B级及以上资质、压力管道管 件B2级及以上资质； （3）投标人具备塑料管道管子、管件的型式试验证书。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3本次招标不接受代理商投标，不接受联合体投标。 4. 招标文件的获取 4.1 凡愿意参加的潜在投标人，从2026年 8 月19 日起至投标截止时间前，均可登录重庆市公共资源交易网 （www.cqggzy.com）直接下载获取招标文件、答疑等开标前的有关资料。在公告期间，各投标人应随时关注网上 发布的招标文件答疑、补遗、澄清等文件内容，不管投标人是否下载，均视为已知晓招标文件的全部内容和有 关事宜。本项目不需要报名，直接投标。 网 5.投标文件的递交 5.1 投标文件递交的截止时间为 2026年 9 月10 日上午09时30分，地点在重庆市公共资源交易中心开标厅（地 址：重庆市两江新区青枫北路6号渝兴广场B10栋2层），具体开标地点详见一、二楼大厅显示屏。 务 5.2逾期送达的或者未送达指定地点的，或者未按照招标文件要求密封的投标文件，招标人将拒收。 6、发布公告的媒介 商 本次招标公告在中国招标投标公共服务平台、重庆市公共资源交易网上发布。 7、联系方式 道 招 标 人：重庆市映天辉氯碱化工有限公司 地 址：重庆长寿经济技术开发区化北路二号 管 联 系 人：张先生 电 话：023-40717888 国 招标代理机构： 重庆招标采购（集团）有限责任公司 地 址：重庆市两江新区五里店五简路2号重庆咨询大厦A栋20楼2001室 中 项目负责人：彭文婷 电 话： 023-67703002 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采购 户名 开户行 投标保证金账号 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000631258 支行 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051303372 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630010400 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000002549 贸易试验区分行 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835014652 坝支行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146619529 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764260665 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020038958 信息来源:https://www.chinapipe.net/project/d3076119.html cqdingjiu 2026.08.21 10:06:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076119.html</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
         <v>85</v>
       </c>
@@ -2420,11 +2320,7 @@
           <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)衬氟管道及管件采购招标公告 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）衬氟管道及管件采购招标公告 1、招标条件 本招标项目废盐综合利用联产20万吨/年离子膜烧碱项目已由重庆市长寿区发展和改革委员会以 重庆市企业投 资项目备案证（2207-500115-04-05-168305）批准建设，项目业主为重庆市映天辉氯碱化工有限公司，建设资金来 自业主自筹，项目出资比例为100%，招标人为重庆市映天辉氯碱化工有限公司。项目已具备招标条件，现对本 项目的（一期12万吨/年）衬氟管道及管件采购进行公开招标。 网 2、项目概况 2.1 建设地点：重庆长寿经济技术开发区化北路2号。 务 2.2、项目概况与建设规模： 重庆市映天辉氯碱化工有限公司（以下简称“映天辉”）位于重庆长寿经济技术开发区化北路2号，始建于2004 年5月，占地430亩，注册资本34800万元。现为国有控股企商业，是一家集氯碱生产经营、新材料研发经营于一体 的专业型、科技型综合企业，系国家级高新技术企业。 映天辉作为长寿经开区氯碱产业基础平台的龙头化工企业，现有一条氯碱生产线，生产规模为20万吨/年烧碱 （折100%NaOH计）。为建设并贯通氯碱化工道循环经济产业链，保障下游产业链装置氯气需求，实现氯碱产品的 升级和高端化发展，增加产品附加值，降低成本，提高竞争力，映天辉公司经过充分调研和反复论证后，拟开 展废盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）建设。装置在正常运行情况下，按照每年 8000 小时操作。具体要求及参数以第五章货物需求一览表及技术规格标准和要求为准。 管 2.3 本次招标项目货物采购估算金额： 约225万元。 2.4招标范围： 本次招标项目为：“废国盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）衬氟管道及管件采购一批” 包括但不限于制造、涂漆、包装、运输、配合验收工作、检验检测、产品质量证明书等。（详见“第五章货物 （材料）需求一览表及技术规格标准和要求”）。 2.5 交货地点：货物运送至买方指定地点； 中 2.6 交货期： 2.6.1合同签订后 3个月内，所有货物运送招标人现场并具备安装条件。 2.6.2 中标方应于合同签订之日起7天内，向招标方提交完整的技术资料，以供设计院开展设备相关设计工作。 3、投标人资格要求 3.1 投标人应符合以下要求： （1）投标人具备有效的营业执照。 注：不得将投标人营业执照记载的经营范围作为评审因素。 （2）具备有效的《中华人民共和国特种设备生产许可证》-压力管道元件制造-元件组合装置。 （3）具有防腐管道元件特种设备型式试验证书。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3本次招标不接受代理商投标，不接受联合体投标。 4、招标文件的获取 4.1 凡愿意参加的潜在投标人，从2026年8 月 19 日起至投标截止时间前，均可登录重庆市公共资源交易网 （www.cqggzy.com）直接下载获取招标文件、答疑等开标前的有关资料。在公告期间，各投标人应随时关注网上 发布的招标文件答疑、补遗、澄清等文件内容，不管投标人是否下载，均视为已知晓招标文件的全部内容和有 关事宜。本项目不需要报名，直接投标。 5、投标文件的递交 5.1 投标文件递交的截止时间为 2026年 9 月 10 日上午09时30分，地点在重庆市公共资源交易中心开标厅 （地址：重庆市两江新区青枫北路6号渝兴广场B10栋2层），具体开标地点详见网一、二楼大厅显示屏。 5.2逾期送达的或者未送达指定地点的，或者未按照招标文件要求密封的投标文件，招标人将拒收。 6、发布公告的媒介 务 本次招标公告在 中国招标投标公共服务平台、重庆市公共资源交易网上发布。 7、联系方式 商 招 标 人：重庆市映天辉氯碱化工有限公司 地 址：重庆长寿经济技术开发区化北路二号 道 联 系 人：张先生 电 话：023-40717888 管 招标代理机构： 重庆招标采购（集团）有限责任公司 地 址：重庆市两江新区国五里店五简路2号重庆咨询大厦A栋20楼2001室 项目负责人：彭文婷 电 话： 023-67703002 中 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）衬氟管道及管件采购 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630011190 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835003139 坝支行 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000000834 贸易试验区分行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146638621 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051302432 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000620855 支行 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020013554 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764235261 信息来源:https://www.chinapipe.net/project/d3076111.html cqdingjiu 2026.08.21 10:06:52</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076111.html</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
         <v>85</v>
       </c>
@@ -2496,11 +2392,7 @@
           <t>重庆市益康环保工程有限公司永川分公司蒸汽管道改造项目询价采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3076108.html cqdingjiu 2026.08.21 10:06:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076108.html</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
         <v>60</v>
       </c>
@@ -2572,11 +2464,7 @@
           <t>南岸区融侨大道、江南大道片区2023年排水管网改造项目(三标段)招标计划表 重庆市工程建设项目招标计划表 项目名 南岸区融侨大道、江南大道片区 2023年排水管网改造项目（三标段） 称 网 招标法 人或招 重庆市南岸区城市建设发展（集团）有限公司 标人名称 （盖章） 务 项目批 准文件 南岸发改〔2024〕304《南岸区融侨大道、江南大道片区2023年排水管网改造项目总投资概算的批复》 及文号 主要建 包括改造市政混接点194个，改造管网8582米，商管径d300~d1500;缺陷管网开挖修复1355米，管 设内容 径d300~d600;非开挖修复8679米，管径d300~d1200。 招标文件 拟交 合同预估 招标内 招标 序号 招标项目名称 计划发布 易场 金额(万 备注 道容 方式 时间 所 元) 51处雨 污混错 重庆 招标项 接点位 管 市公 目 改 南岸区融侨大道、江南大道片区 2023年排 公开 共资 1 造，1082 2026-08 6600.00 水管网改造项目（三标段） 招标 源交 个管网 易中 三四级 国 心 缺陷修 复。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 中 信息来源:https://www.chinapipe.net/project/d3076097.html cqdingjiu 2026.08.21 10:06:52</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076097.html</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
         <v>80</v>
       </c>
@@ -2648,11 +2536,7 @@
           <t>中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购公告 永川三教水厂项目 已具备采购条件，现公开邀请供应商参加询比采购活动。 1.采购项目简介 1.1 采购项目名称：中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购。 1.2 采购方案编号：FA00000663117。 网 1.3 采购人：中交一公局重庆工程有限公司。 1.4 采购代理机构：/。 务 1.5 采购项目资金：已落实 1.6 采购项目概况： 商 永川三教水厂项目：项目位于永川区三教镇，项目占地面积41673.42㎡（62.51亩），总建筑面积6078.71㎡，新建 净水厂1座，规模5万吨/天，新建厂外管网4.6km（DN200～DN1000），配套建设净水处理系统、排泥水处理系统、 综合楼、生产建（构）筑物以及附属建筑物等。项目合同额1.7亿元，工期450天。 道 项目地址：重庆市永川区。 2.采购范围及相关要求 管 2.1 采购范围：钢筋混凝土排水管。 2.2 交货期：2026年9月-2026年12月。 2.3 交货地点：重庆市永国川区项目指定地点。 2.4 物资质量标准：满足《混凝土和钢筋混凝土排水管》（GB/T 11836-2023）的相关要求。 3.供应商资格要求 中 3.1 供应商应依法设立且满足如下要求： （1）资质要求：本次询比采购要求供应商须是在中华人民共和国境内依法注册，具有合法有效的营业执照、税 务登记、组织机构代码等证件，具有独立法人资格、具有采购物资生产经营范围的生产商或代理商（销售商）。 （2）财务要求：供应商必须是经税务部门注册登记核准的纳税人，有依法纳税的良好记录。 （3）业绩要求：无。 （4）信誉要求：无不良履约记录、未列入工程所在地质量监督部门和中国交建、中交一公局集团企业黑名单。 因质量原因被交通部质监站通报，正在进行整改的生产厂家和产品不得参与投标。生产商或代理商（销售商） 具有良好的社会信誉，近3年内没有与骗取合同有关的犯罪或严重违法行为而引起的诉讼和仲裁；近3年不曾在合 同中严重违约或被逐；财产未被接管或冻结，企业未处于禁止或取消投标状态；在最高人民法院、信用中国 （www.creditchina.gov.cn）或各级信用信息共享平台查询拟入库单位无不良行为记录。 （5）其他要求：无。 3.2 供应商不得存在下列情形之一： （1）处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； （2）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （3）已列入黑名单，且未解除限制期限； （4）其他：无。 4.供应商报名 4.1 有意参加询比采购活动的单位，请于2026年8月19日15时00分至2026年8月26日17时00分（北京时间，下同，法 定公休日、节假日不休），登录“中交招采网”（网址：https://zjzcw.iccec.cn）进行报名并下载采购文件。 4.2 已在网并且已通过采购人层级供应商或已增加采购人为合作单位的供应商、上级供应商可直接参与询比采 网 购。在网平级单位供应商未增加采购人为合作单位需进行合作意向申请通过后参与询比采购。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择采购人，审核通过后方可参与询比 采购。 务 5.供应商报价 5.1 报价结束（递交响应文件截止）时间为2026年8月26日17时00分。 商 5.2 供应商应在报价结束时间前，登录“中交招采网”进行线上报价并上传电子响应文件。逾期未完成上传的电 子响应文件，采购人将拒收。 5.3电子采购的供应商响应文件由线上电子报价道表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 子报价表的数据为准。 6.开标 管 6.1 开标时间：与报价结束时间相同。 6.2 开标地点：本次采购在“中交招采网”平台线上开标，不举办现场开标。 国 7.发布公告的媒介 本询比采购公告在 “中交招采网” 上发布。 中 8.评审办法 本项目评审办法采用 经评审的最低价法 。 9.合同主要条款 9.1 付款条件：按月结算，上月11日至本月10日为一个结算对账期，乙方必须按照甲方要求开具合规的增值税专 用发票，无发票不予付款。结算完成后1个月内支付已结算金额的70%，剩余30%货款在结算完成后3个月内支付。 付款方式为银行转账，甲方有权采用票据支付或者供应链支付的方式支付货款，因此产生的费用包含在综合单 价中，乙方不得因此调价和索赔。如遇业主支付不及时，乙方应予理解。 9.2 履约保证金的递交： （1）R不要求递交 （2）要求递交，保证金金额：/，保证金形式：/，其他形式：/ 。 10.监督机构 监督机构名称： 中交一公局重庆工程有限公司审计部 11.成交供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联系400-676-5885，中标服务费请按7咨询。 11.1 收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： 网 （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； （3）在1000万元（含）至3000万元之间的，每次收取1000元； 务 （4）在3000万元（含）至1亿元之间的，每次收取3000元； （5）在1亿元（含）以上的，每次收取5000元。 商 11.2 支付流程 （1）通知推送：中标结果发布后，系统自动推送缴费通知（含应缴金额及支付链接）； 道 （2）费用查询：供应商登录“中交招采网—供应商协同—服务费”模块查看待支付费用； （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 管 （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网— 供应商协同—服务费—发票查询”模块获取。 12.其他 国 / 。 13.联系方式 中 采 购 人：中交一公局重庆工程有限公司 地 址：重庆市江北区创富路5号 邮 编：361021 联 系 人：汪仁宽 电 话：13527572392 电子邮件：1176245792@qq.com 项目联系人及电话： 序号 项目名称 联系人 联系电话 1 永川三教水厂项目 高博 17788661005 中交一公局重庆工程有限公司 2026年8月19日 物资信息 序号 设备物资名称 设备物资说明 税率 单位 网 1 钢筋混凝土排水管 2000mm Ⅲ级 承插口 13% 米 信息来源:https://www.chinapipe.net/project/d3076078.html 务 cqdingjiu 2026.08.21 10:06:52 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3076078.html</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
         <v>90</v>
       </c>
@@ -2724,11 +2608,7 @@
           <t>中国铁路成都局集团有限公司重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施 工劳务招标招标公告 重庆市大渡口区萤石及配套企业 35 千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标公告 招标编号：DXNZBCQ-GC-2026-13 1. 招标条件 本建设项目重庆市大渡口区萤石及配套企业 35 千伏专用变电站项目穿越渝贵等网铁路防护工程施工劳务招标已由 《中国铁路成都局集团有限公司关于重庆市大渡 口 区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防 护工程施工图设计的复函》（科信技审〔2025 〕115号）批准建设，建设单位为重庆建桥置业有限公司，建设资 金使用外委资金，项 目出资比例为100%，资金已落实。招标人为中国铁路成都局集团有限公司重庆工务段。本 项目已具备法定招标条件，现进行公开招标，特邀请有意向的投标人参加投标。 务 2. 项目概况与招标范围 2.1 项目概况 商 2.1.1建设地点：渝贵线K38+838、南疏Ⅰ线K10+808、川黔线K1+622、川黔线K3+781、兴珞上行线K38+619、兴珞 下行线K38+635、小西线K1+633、南疏Ⅱ线K11+257。 2.1.2建设规模：重庆市大渡 口区萤石及配套企道业35千伏专用变电站项目穿越渝贵等铁 路防护工程，本项目工分为5个交叉工点。工点一采用明挖直埋方式下穿渝贵铁路新白沙沱长江多线特大桥第14孔 （渝贵线K38+838）；工点二采用顶进套管方式下穿南疏 Ⅰ 线K10+808（ 已停用）、川黔线K3+781（ 已停用 ）； 工点三采用明挖直埋方式下穿兴珞线陈家湾双线特大桥（上行线K38+619、下行线K38+635）；工点四采用顶进 管 套管方式下穿。 2.2 招标范围：重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标。 即涉铁部分第第三章桥涵，第六章通信、信号、信息及灾害监测，第十章大型临时设施和过渡工程，第十一章 其他费用中的安全生产国费以及非涉铁部分。 2.3标段划分：本项目施工招标划分为1个标段。 2.4计划工期：240日历天，计划开工日期：2026年10月8日，计划竣工日期：2027年6月4日。 中 2.5 其他说明：___/___。 3. 投标人资格要求 3.1本次招标要求投标人为在中华人民共和国境内合法注册的独立法人，具备有效的营业执照、施工企业资质和 安全生产许可证等，并在人员、设备、资金等方面具备相应的施工能力。资格要求如下： 3.1.1 标段编号：全标段 （1）资质要求：施工劳务企业资质。 （2）业绩要求：近3年内完成过铁路营业线类似项目业绩。 （3）项目负责人要求:具有工程师及以上职称，2 年及以上类似铁路营业线项目管理工作经验， 良好的职业道德， 且未在其他在建工程项目任职。 （4）本标段不接受联合体投标申请。 （投标人资格要求详见招标公告附件） 3.2 各投标人可就上述标段中的 1 个标段进行投标。 3.3投标人未在“信用中国”网站（www.creditchina.gov.cn）中被列入失信被执行人名单，投标人未在国家企业信 用信息公示系统（www.gsxt.gov.cn）中被列入严重违法失信企业名单，投标人未被列入铁路工程建设失信行 为“黑名单”，投标人及其法定代表人、拟委派的项目经理在近3年不曾有行贿犯罪记录； 其他信誉要求：未被取消或暂停投标资格、不存在辖内失信的情形、不存在最近一期国铁集团施工企业评价为D 级且在整改期内的情形。 4. 招标文件的获取 4.1凡有意参加投标者，请于2026年08月20日00时00分至2026年08月25日00时00，在重庆龙头寺旅游集散中心（重 庆市两江新区天宫殿街道昆仑大道56号附1号5楼办公室）持单位介绍信获取招标网文件。 4.2招标文件每套售价0元，售后不退。 4.3其他：凡有意参加投标者可通过网上登记获取招标文件，将获取招标文件材料扫描件（PDF格式）发送 务 至dxncq_bgs@163.com邮箱登记，由招标代理人通过电子邮件方式向有意参加投标者发送招标文件。 5. 投标文件的递交 5.1投标文件递交时间为2026年09 月10 日08时30分至2026年商09月10 日09时00分，递交比选申请文件的截止时间（比 选截止时间，下同）为2026年09月10日09时00分，地点为重庆龙头寺旅游集散中心（重庆市两江新区天宫殿街道 昆仑大道56号附1号5楼开标室）。 5.2逾期送达的或者未送达指定地点或者不按照道招标文件要求密封的投标文件，招标代理人不予受理。 6. 发布公告的媒介 本次招标公告在国铁采购平台（https://cg.95306.cn）发布。 管 7. 联系方式 招 标 人：中国铁路成都局集团有限公司 招标代理机构：成都大西南铁路监理 国 重庆工务段 有限公司 地 址：重庆市九龙坡区黄桷坪街道铁 地 址：成都市金牛区站西桥西街305 中 路3村161号 号府河路苑9栋14楼 邮 编： / 邮 编：610081 法定代表人： 法定代表人 或其委托代理人： 或其委托代理人： 联 系 人： 任女士 联 系 人：汤女士 电 话： 17393148353 电 话：023-61896910 传 真： / 传 真： / 电子邮箱： / 电子邮箱：dxncq_bgs@163.com 网 址： / 网 址： / 开户银行： / 开户银行： / 账 号： / 账 号： / 2026年08月19日 附件： 获取招标文件信息表 申请人名称： （加盖公章） 项目名称：（按公告名称填写） 获取招标文件起止时间：（按照公告时间填写） 项目编号：（按照公告填写） 单位名称 经办人 联系电话 电子邮箱 标段 资料提交时间 备注 网 注：须附经办人介绍信、身份证复印件、单位营业执照复印件。 信息来源:https://www.chinapipe.net/project/d3075989.html cqdingjiu 2026.08.21 10:06:53 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075989.html</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
         <v>0</v>
       </c>
@@ -2800,11 +2680,7 @@
           <t>长江流域云阳青龙段污水管网一体化建设项目招标计划表 重庆市工程建设项目招标计划表 项目名称 长江流域云阳青龙段污水管网一体化建设项目 招标法人或 招标人名称 云阳县青江环境综合整治有限公司 网 （盖章） 项目批准文 云阳发改资环【2025】55号 件及文号 务 主要建设内 新建污水管网55.5千米，其中DN200管网12千米、DN300管网24千米、DN400管网19.5千米等。 容 招标方 招标文件计 拟交易场 合同预估金额 序号 招标项目名称 招标内容 备注 式 划发布时间 所 (万元) 商 长江流域云阳 新建污水管网55.5千米， 重庆市公 青龙段污水管 其中DN200管网12千 公开招 共资源交 1 网一体化建设 米、DN300管网24千 2026-08 9100.00 标 易中心云 项目EPC总承 米、DN40道0管网19.5千 招标项目 阳分中心 包 米等。 新建污水管网55.5千米， 长江流域云阳 重庆市公 其中DN200管网12千 青龙段污水管 公开招 共资源交 2 管米、DN300管网24千 2026-08 140.00 网一体化建设 标 易中心云 米、DN400管网19.5千 项目监理 阳分中心 米等监理。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 国 信息来源:https://www.chinapipe.net/project/d3075867.html cqdingjiu 2026.08.21 10:06:53 中</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075867.html</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
         <v>80</v>
       </c>
@@ -2868,11 +2744,7 @@
           <t>中国电建水电四局华中公司重庆轨道交通17号线一期5标项目雨污水排水迁改工程施工劳务分包采购项目公开询 比采购公告 询比采购公告 采购编号： PC-0104-26J6-FP0895 一、采购条件 受中国水利水电第四工程局有限公司重庆轨道交通17号线一期5标项目委托，中水电四局华中（武汉）工程有限 公司以公开询比方式采购重庆轨道交通17号线一期5标雨污水排水迁改工程项目网，建设资金来源已落实。目前项 目已具备采购条件，现进行公开询比采购。 二、项目概况、采购范围 务 1、项目概况：重庆轨道交通17号线一期5标段包含金凤北站（不含）～终点（3 站5 区间的土建）：高龙大道 站、斑竹林站、石家院子站、金凤北站～高龙大道站区间、高龙大道站～斑竹林站区间、斑竹林站～石家院子 站区间、石家院子站～终点区间、7/17号线联络线区间。 2、采购范围： 商 （1）雨污水排水迁改工程 （2）工程招标范围工作内容：17号线一期5标道中高龙大道站、斑竹林站及高斑竖井位于城市既有道路下方，设计 采用明挖法施工。为保证市政排水管网的正常使用，在明挖施工前需对既有管网进行临时迁改，车站结构施工 后进行恢复。施工PE钢带管长度2387米、B型排水管长度2799m、钢筋混凝土管127米，检查井239座劳务部分。 （3）施工内容详见工程量清单，以及为完成此项工程而做的一切工作。 管 3、计划工期:计划开工日期：2026年9月25日（具体时间以采购人通知为准），计划完工日期：2027年 12 月25 日； 合同工期总日历天数为457天。 4、质量要求：符合《国给水排水管道工程施工及验收规范》（GB 50268）、《混凝土结构工程施工质量验收规范》 （GB 50204）、《城镇道路工程施工与质量验收规范》（CJJ 1-2008）以及项目所在地最新的相关法规、标准和 图集。工程质量全面达到设计要求和标准，其中：验收合格率 100%，优良率达 90%以上，工程综合验收质量评 定达优良标准。 中 5、付款方式：采用银行转账/支票支付工程价款，月度结算完成具备付款条件后30天内工程进度款支付比例约定 为扣除各项保证金及费用后应付价款不低于65%；清算完成并签订《退场协议》后30天内工程进度款支付比例约 定为扣除各项保证金及费用后应付价款不低于80%；清算完成并签订《退场协议》后一年内工程进度款支付比例 约定为扣除响应人缺陷责任等相关费用后应付价款不低于90%；清算完成并签订《退场协议》，办理完成保证金 退还手续后两年内，工程进度款支付比例约定为扣除响应人缺陷责任等相关费用后应付价款的100%。 6、其他：无。 三、响应人资格要求 响应人必须满足以下全部资格要求： （1）资质要求：施工劳务不分等级 （2）主要人员要求:授权委托人（如有）及项目经理、专职安全员应提供社保和劳动合同。其中劳动合同至少提 供首、末两页，并且包含有关人员的详细信息;社保证明应提供响应截止时间前三个月的社保缴纳记录。 （3）安全三类人员要求:应提供企业主要负责人安全A证、项目经理B证、专职安全员C证。 （4）响应人具有良好的银行资信和商业信誉，没有处于被责令停业，财产被接管、冻结、破产状态。 （5）响应人应具有 雨污水排水迁改 工程的施工业绩，在近 5年内(2021年7月-2026年7月内签订)的施工合同不少 于 1 个，且签订单项合同金额均在 100 万元以上（应附成交通知书和（或）合同扫描件）。 （6）其它要求:无。 （7）本次采购不接受联合体响应。 四、采购文件的获取 凡满足本公告规定资格要求并有意参加的响应人，请于2026年8月22日10时00分前在中国电建采购招标数智化平台 （https://bid.powerchina.cn/bidweb/#/login，以下简称“数智化平台”）获取采购文件，采购文件免费提供。 五、响应文件的递交 1、响应文件递交的截止时间（响应截止时间，下同）为2026年8月26日10时30分网（北京时间），响应人应在截止 时间前通过数智化平台递交电子响应文件。 2、本次采购将通过数智化平台全程在线开展，电子响应文件的加密、提交等流程须响应人在线进行操作。响应 人须提前办理数字证书用于在线递交响应文件，办理方式详见数智化平台首页，并严格按照要求进行在线操作， 务 因操作流程失误造成的递交失败将由响应人自行承担后果。 3、开启由“数智化平台”在响应截止时间后自动对响应文件进行解密，响应人及时关注开启结果。 4、响应截止时间如有变动，采购人将及时通知已获取采商购文件的响应人。 六、发布公告的媒介 本次询比采购公告同时在中国电建阳光采购网道（https://bid-zb.powerchina.cn）上发布。 七、评审办法 采用综合评估法。 管 八、联系方式 采 购 人： 中水电四局华中（武汉）工程有限公司 国 地 址： 湖北省武汉市江岸区塔子湖东路健美街30号立城中心商务楼13、14层 邮 编： 430014 中 联 系 人： 王飞 电 话： 15827222587 电子邮箱： 107830343@qq.com 九、提出异议的渠道和方式 单位名称： 中水电四局华中（武汉）工程有限公司 电 话： 17708178186 电子邮箱： sjhzgsjw@163.com 十、纪检监督机构 响应人或者其他利害关系人认为本次采购活动存在违规违纪行为的，可以书面形式向中国水利水电第四工程局 有限公司中水电四局华中（武汉）工程有限公司纪委办公室（联系方式：17708178186）提出投诉。 2026年8月 19 日 报价网址:https://bid.powerchina.cn/notice/detail?id=2409510708 信息来源:https://www.chinapipe.net/project/d3075750.html cqdingjiu 2026.08.21 10:06:53 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075750.html</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
         <v>85</v>
       </c>
@@ -2944,11 +2816,7 @@
           <t>万州区2026年超长期特别国债高标准农田建设项目拟进行预制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜的 信息公告 1.采购条件 1.1本项目万州区2026年超长期特别国债高标准农田建设项目工程已由 重庆市万州路桥建设有限公司承建，项目 业主为重庆市万州区农业技术与机械推广中心，代建业主为重庆市万州区农业发展有限公司，建设资金为国债 资金，项目出资比例为 100% ，承包人为重庆市万州路桥建设有限公司。项目已具备施工条件，现对该项目的预 制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜发布信息公告。 网 2.项目概况与采购范围 2.1建设地点：重庆市万州区走马镇、瀼渡镇、罗田镇、余家镇、高梁镇、分水镇、柱山乡等7个镇乡。 务 2.2本项目材料采购拟进行比选情况如下： 罗田镇谷山片区材料采购费暂定金额约： 17.5万元； 余家镇桥亭片区材料采购费暂定金额约： 17.99万元； 商 柱山乡山田片区材料采购费暂定金额约： 26.32 万元； 走马镇凉风片区材料采购费暂定金额约： 15.道66万元； 瀼渡镇高村片区材料采购费暂定金额约： 17.72 万元； 分水镇大冲片区材料采购费暂定金额约： 47.12 万元； 管 高梁镇茨坪片区材料采购费暂定金额约： 10.7万元； （以上片区片区金额为暂定金额，最终比选限价金额以比选文件为准）。 国 2.3计划采购周期： 以合同签订为准 日历天。 2.4采购范围：本项目各片区所包含的预制钢筋砼管、成品混凝土仿木栏杆等材料。 中 3.供应商资格要求 3.1本次材料采购要求供应商具备独立企业法人，具有本次所需材料生产能力的厂家或经销商等，其经营范围和 权限应满足本次所需材料的要求，并依法取得国家行政主管部门颁发的有效工商营业执照(建筑材料销售或水泥 制品制造、水泥制品销售等相关营业资格），所提供产品必须满足各项检测要求，达到国家现行标准规定的合 格标准。具有良好的商业信誉和充分的供应保障能力，具备相应售后服务能力。要求竞选人为一般纳税人，可 开具13%税率增值税专用发票，提供一般纳税人认定证明。 3.2本次供应商单位优先选择万州本地企业。 3.3本次 不接受 联合体竞选。 4. 报名要求 4.1报名时间：2026年8月 19日9:00起至 8月21日17:00止。 4.2报名地点：重庆市万州路桥建设有限公司经营部（重庆市万州区天城东路278号）。 4.3报名时，须提交有效的营业执照(有效工商营业执照((建筑材料销售或水泥制品制造、水泥制品销售等相关营 业资格）)，前述证书均为复印件并加盖单位公章。法定代表人参加报名的不需要授权委托书，只需要提供法定 代表人身份证明；非法定代表人参加报名的除提供法定代表人身份证明外还须提供授权委托书、委托代理人身 份证明。 4.4 本项目材料采购需提前报名。经资格预审合格后，通知资格预审合格的供应商，到承包人单位领取相关文件。 4.5本项目材料采购设七个片区进行比选，为保证比选公平、公正、有效，规定同一参选单位报名片区上限为2个， 且最终仅限中选一个片区。 5.联系方式 承包人：重庆市万州路桥建设有限公司 地 址：重庆市万州区天城东路278号 网 联系人： 张红娟 电 话：15923491915 务 邮 箱： 商 重庆市万州路桥建设有限公司 2026年8月19日 道 信息来源:https://www.chinapipe.net/project/d3075512.html cqdingjiu 2026.08.21 10:06:53 管 国 中</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075512.html</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
         <v>80</v>
       </c>
@@ -3020,11 +2888,7 @@
           <t>中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资(污水 管道)招标采购流标公告 发布单位：中国铁建/中铁十一局/六公司 发布时间：2026-08-19 10:40:49 投标截至时间：2026-08-18 10:00:00 内容： 各投标人： 网 中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资（污水 管道）公开招标采购（采购编号： CR1106-JC-2026-26-02）评标工作，已于北京时间2026年08月18日10:00整，在 铁建云链（https://www.crccep.com）线上平台公开开标。评审委员会根据招标文件载明的评审办法完成评审工作， 现将评审结果公示如下： 务 一、招标公告发布日期及媒体 招标公告发布日期：2026年07月27日至2026年08月01日 商 招标公告媒体：铁建云链（https://www.crccep.com） 二、拟中标信息 道 公开招标采购编号：CR1106-JC-2026-26-02 包件号：WSGD-01 序号 供应商名称 推荐排序 管 1 无 1 国 以上包件有效投标不足三家，本次招标做流标处理。 三、公示时间 中 自2026年08月19日始，至2026年08月22日止。在公示期间，所有竞标人和其他利害关系人如对公示的评审结果有 异议，可以向相关监督部门举报，逾期将不再受理。举报人必须由其法定代表人或者授权代表签字并盖章，其 他组织或者个人举报的，必须由其主要负责人或者本人签字，并附有效身份证明复印件。举报人如实反映情况 受法律保护。 公示期满，如无异议，即时生效。 监督竞诉受理部门： 中铁十一局集团第六工程有限公司招采中心 联系电话：18671041790 信息来源:https://www.chinapipe.net/project/d3075461.html cqdingjiu 2026.08.21 10:06:53</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075461.html</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
         <v>80</v>
       </c>
@@ -3088,11 +2952,7 @@
           <t>协同创新区-四期房建三标段镀锌管件物资竞价采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3075420.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075420.html</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
         <v>60</v>
       </c>
@@ -3164,11 +3024,7 @@
           <t>长江一级支流溉澜溪流域(新华水库混流箱涵)污水收集效能提升工程(渝北区)施工答疑补遗文件 长江一级支流溉澜溪流域（新华水库混流箱涵）污水收集效能提升工程（渝北区）施工答疑文件 各潜在投标人： 现将“长江一级支流溉澜溪流域（新华水库混流箱涵）污水收集效能提升工程（渝北区）施工”公开招标项目 答疑文件发布。本答疑文件是在招标文件的基础上作出的澄清、说明或补正，与招标文件具有同等法律效力， 若相关内容与原招标文件不一致时，一律以本答疑文件内容为准。 网 一、答疑部分： 问题一：1、我公司于2026年进行了优势合并整合，现准备使用合并前公司项目业绩作为本次我司投标的投标人 业绩证明，并提供上级主管单位出具的相关吸收合并文件或两家公司签订的吸收合并协议，请问是否可视为满 务 足招标业绩要求？ 2、我单位为中型企业，其控股股东为大企业，但我单位不属于大企业的分支机构，也不存在与大企业的负责人 为同一人的情形。鉴于此种情况，我单位应提供《中小企业声明函（工程类）》还是《中小企业承担合同份额 承诺函》？ 商 回复：1. 满足，但还需满足招标文件对业绩的其他要求。最终由评标委员会根据投标人提供的证明材料并结合 招标文件要求进行评审； 道 2. 贵司其控股股东为大企业，故需提供中小企业承担合同份额承诺函。 问题二：本项目有无业主专家参与评标？ 管 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 问题三：请明确是否有业主专家 是否异地评标 回复：1. 该项目评标委国员会由招标人按法律法规及相关规定依法组建。 2.本项目是异地评标。 问题四：1、财务报告可以不提供财务报表附注吗? 中 2、投标函附录中，工期、分包、工程质量、缺陷责任期等要求可以统一填写"达到招标文件要求"吗? 3、招标文件第八章投标文件格式中(二)承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要提供其 他格式之外的其他承诺? 4、是否有业代专家参与评标，不要模糊的回答什么依法组建评标委员会。请明确回复有或者没有。 5、本项目是否异地评标？ 6、业绩竣工验收证明材料中有单位盖的项目部章是否认可呢？ 回复：1. 可以不提供财务报表附注。 2. 可以统一填写"达到招标文件要求"。 3. 投标人自行核实招标文件要求提供的承诺要求，如有需要，还需补充提供招标文件第八章投标文件格式中 （二）承诺部分之外的其他承诺。 4. 该项目评标委员会由招标人按法律法规及相关规定依法组建。 5. 本项目是异地评标。 6. 不认可。 问题五：请问**公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，因为不能履行保函的见索即 付，拒绝赔付。 相关业主方在招标文件补遗通知中直接将**公司列入担保公司回避名单，拒绝**公司所出具的保函。由此可 见**公司的信用资质、履约能力、根本无能力是存在很大问题的。请问以**公司目前的被执行和不履行投标担保 责任的情况是否符合招标文件的要求? 回复：纸质投标保函的开立人应当是具有相应资格的银行、保险机构、融资担保公司，其信用资质、履约能力、 担保能力、赔付流程、安全保密等应符合工程保函业务条件。纸质投标保函应合网法合规，符合招投标行政监督 部门、行业主管部门和金融监管部门的相关规定，满足招标文件约定要求。投标人应选择在渝依法设立总部或 者设有分支机构的金融机构开具纸质投标保函。投标人对所提交的纸质投标保函的真实性、合法性、有效性负 责。以纸质投标保函形式交纳投标保证金是否符合招标文件要求，由评标委员会评标时，根据招标文件要求进 行独立评审，并作出相应评审判断。 务 问题六：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 回复：经核实，招标文件（PDF签章版）中投标文件格式商与重庆市电子招投标系统投标文件制作软件中格式一致。 可能因重庆市电子招投标系统投标文件制作软件中的格式页边距与招标文件（PDF签章版）不一致的原因导致格 式显示不一致，该情形不影响投标人编制投标文件。若重庆市电子招投标系统投标文件制作软件导出的投标文 件格式与招标文件（PDF签章版）的投标文件格式不一致，以重庆市电子招投标系统投标文件制作软件导出的投 标文件格式为准。 道 问题七：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖 章，请问需要提供联合体协议书吗？ 管 回复：若投标人提供的公司业绩为epc业绩，且合同协议书或工程竣工验收合格的证明材料或业主证明能证明该 投标人承担的工作为施工任务的，则不需要提供联合体协议书；若投标人提供的公司业绩为epc业绩，但合同协 议书或工程竣工验收合格的证明材料或业主证明不能证明该投标人承担的工作为施工任务的，则需要提供联合 体协议书。 国 问题八：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可 以不填(空白)，对此有无要求？ 回复：投标中文件中下划线上、空格处、表格中无需要填写或无法填写内容的，填“/”或“无”均可。 问题九：公园施工业绩符合吗？ 回复：公园概念太宽泛，无法判定该施工业绩是否属市政工程，请投标人自行核实，并按招标文件要求提供施 工业绩证明材料，其是否满足要求应由评标委员会根据证明材料具体内容进行判定。 问题十：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需 要提供其他格式之外的其他承诺？ 回复：投标人自行核实招标文件要求提供的承诺要求，如有需要，还需补充提供招标文件第八章投标文件格式中 （二）承诺部分之外的其他承诺。 问题十一：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收， 请问我公司业绩满足业绩要求吗？ 回复：不满足。 问题十二：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗？ 回复：投标人投标总报价低于招标文件规定的对应的异常低价警戒线的，应提供报价合理性说明，并提供必要 的证明材料。证明材料由投标人自行提供，但提供的说明不得降低或者改变原设计方案、技术工艺、施工标准， 不得影响项目的质量、安全、工期、结算等正常履约。 问题十三：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 回复：按照招标文件要求“提供：会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表，财务 报表须至少包括现金流量表、资产负债表、利润表”。 问题十四：业绩要求的竣工时间是指竣工验收时间吗？ 回复：本项目业绩要求所指竣工时间，即为工程竣工验收合格证明载明的竣工验收时间。 问题十五：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知 书发出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面网通知相关金融机构本项目准 予提前注销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 回复：纸质投标保函原件上未加盖“正本”字样的，不因此否决投标，但投标人应确保提交的保函为唯一正本。 若因保函真伪问题导致的一切不利后果由投标人自行承担。 务 问题十六：燃气管道安装施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 商 问题十七：请问招标人是否委派业主专家参与评标吗？ 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 道 问题十八：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 回复：根据招标文件“投标人的工程量清单单项报价不得为零报价（招标人提供的工程量清单单项最高限价中 金额为零的除外）或者负数报价”，招标人提供的工程量清单单项最高限价中金额为零的，该项清单综合单价 管 报价可以为0。 问题十九：自来水厂或者净水厂施工业绩满足业绩要求吗？ 回复：满足，但还需满国足招标文件对业绩的其他要求。 问题二十：财务报告可以不提供财务报表附注吗？ 回复：可以不提供财务报表附注。 中 问题二十一：老旧小区室外环境改造施工业绩符合吗？ 回复：不满足。 问题二十二：有人提出一个无关问题。 回复：无关问题不予回复。 问题二十三：任一清单的综合单价低于警戒线，就要提供说明吗？ 回复：本招标项目单项报价未设置异常低价警戒线。 问题二十四：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题二十五：本项目是异地评标吗？ 回复：本项目是异地评标。 问题二十六：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、 注册证及在本单位注册的证明文件替代？ 回复：不满足。 问题二十七：污水处理厂提标改造施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题二十八：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 回复：可以填“达到招标文件的要求”。 问题二十九：财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加网强审计报告查验工作的通知》 中要求会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第十四条规定审计业务出具的报告 （以下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标 人提供的财务报告需要赋码和提供深度查询截图吗？ 务 回复：投标人提供的财务报告不需要赋码和提供深度查询截图。 问题三十：有人提出一个无关问题。 回复：无关问题不予回复。 商 问题三十一：我公司业绩合同金额3600万元及以上，但是竣工报告业绩金额小于3600万元，请问是否满足业绩要 求？ 道 回复：按招标文件执行。“当上述业绩证明材料中针对同一指标存在不一致时，以工程竣工验收合格的证明材 料为准”。 问题三十二：专业分包业绩满足业绩要求吗？ 管 回复：专业分包业绩可满足业绩要求，但还需满足招标文件对业绩的其他要求。 问题三十三：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养 老保险证明材料复印件国递交吗？ 回复：不需要。 问题三十四：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要 中 求”吗？ 回复：可以统一填写“达到招标文件要求”。 问题三十五：市政桥梁施工业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题三十六：有人提出一个无关问题。 回复：无关问题不予回复。 问题三十七：本项目委派业主专家吗？ 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 特别提示：本通知与招标文件具有同等法律效力，若招标文件与本通知不一致时，一律以本通知为准。 招标人：重庆水务环境控股集团管网有限公司 招标代理机构：重庆市工程管理有限公司 2026年8月19日 信息来源:https://www.chinapipe.net/project/d3075975.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075975.html</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -3240,11 +3096,7 @@
           <t>中化重庆涪陵化工搬迁后污水处理厂建设项目招标计划表 重庆市工程建设项目招标计划表 项目名称 中化重庆涪陵化工搬迁后污水处理厂建设项目 招标法人或 招标人名称 重庆市涪陵交通旅游建设投资集团有限公司 网 （盖章） 项目批准文 涪发改委发[2019] 505号 件及文号 务 主要建设内 新建一体化提升泵站及管道约5000m，投资约800万元。 容 招标 招标 招标文件计 拟交易 合同预估 序号 招标项目名称 备注 内容 方式 划发布时间 场所 金额(万元) 商 本招标计划与2026年5 月25日发布的招标项目 中化重庆涪陵 重庆市 名称为“中化重庆涪陵 招标项目 化工搬迁后污 涪陵区 公道开 化工搬迁后污水处理厂 1 水处理厂建设 施工 2026-09 公共资 800.00 招标 建设项目（场外连接管 项目（场外干 源交易 网）”的招标计划，除 管部分） 中心 招标项目名称调整外， 其余内容完全一致。 管 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075591.html cqdingjiu 2026.08.21 10:国06:54 中</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075591.html</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
         <v>80</v>
       </c>
@@ -3316,11 +3168,7 @@
           <t>綦江区污水处理厂设施设备更新改造工程(二期)招标公告 1.招标条件 本招标项目 綦江区污水处理厂设施设备更新改造工程（二期） 已由 重庆市綦江区发展和改革委员会 以 重庆市企业投资备案证（项目代码：2502-500110-04-01-844057） 批准建设，项目业主为 重庆南州城市管 理服务有限公司 ，建设资金来自 上级补助和业主自筹 ，项目出资比例为 100% ，招标人为 重庆南州 城市管理服务有限公司。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用经评审的最低 投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 綦江区 2.2 项目概况与建设规模：对三江污水处理站、綦齿园污水处理厂、信家岩污水处理站的设施设备进行更新改造， 务 包括配电柜、风机、污水提升泵、在线监测等设备更新更换，以及对工艺落后的污水厂完成工艺技改；北渡污 水厂、赶水污水处理厂、工业园区污水厂、食品园污水厂零星设施更新等。 2.3 本项目工程总投资金额： 约1327.40万元 商 2.4 招标范围： 本项目设计施工图和招标文件、答疑、补遗、工程量清单等资料所涉及的全部内容。 2.5 工期要求： 180日历天 道 缺陷责任期要求： 24个月 2.6 标段划分（如有）： / 管 2.7 其他： / 3.政府采购工程 国 3.1 是否属于政府采购工程：否 4.投标人资格要求 中 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（綦江区） （https://www.cqggzy.com/qijiangweb/）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重 庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏 “主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网（綦江区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-22 18:00:00前。 5.3招标人应于2026-09-11 18:00:00前在重庆市公共资源交易网（綦江区）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-28 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（綦江区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆南州城市管理服务有限公司 代理机构: 永卓国际工程技术有限公司 地 址: 重庆市綦江区红星美凯龙生活广场3幢19-3 地 址: 两江新区网泰山大道东段98号2幢10-12号 邮 编: 邮 编: 项目负责人: 赵老师 项目负责人: 廖淼 电 话: 023-48690537 电 话: 务023-60391733 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 商开户银行: 账 号: 账 号: 监督部门: 道 电 话: 2026年08月18日 綦江区污水处理厂设施设备更新改造工程（二期） 管 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051287453 中国农业银行股份有限公司重庆自由贸 重庆联合产权交易所集国团股份有限公司 312601010400083780000031123 易试验区分行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146631326 信息来源:https://www.chinapipe.net/project/d3075589.html 中 cqdingjiu 2026.08.21 10:06:54</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075589.html</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
         <v>90</v>
       </c>
@@ -3392,11 +3240,7 @@
           <t>南岸区峡口、迎龙片区农村供水保障提升工程招标计划表 重庆市工程建设项目招标计划表 项目 南岸区峡口、迎龙片区农村供水保障提升工程 名称 招标 网 法人 或招 标人 重庆市江南城市建设发展（集团）有限公司 名称 务 （盖 章） 项目 批准 商 文件 南岸发改﹝2026﹞156号 及文 号 本工程主要内容包括新（改）建峡口、道迎龙片区4个乡镇DN20～DN300农村供水管网81km，新建3座一体 主要 化智慧加压泵站。对朱家岩水厂进行升级改造：更换陈旧、老化的工艺、电气设备及自控、仪表系统， 建设 对全厂进行智能化、标准化改造，增加高级工艺控制系统，建设智能化、标准化的农村供水区级管理平 内容 台。概算批复工程建安费2975.27万元。 管 拟 招 招标文 合同预 招标 交 序 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 国 所 南岸 重 区峡 庆 口、 中 市 迎龙 朱家岩水厂升级改造工程：对全厂老旧设备进行设备更新；对全 公 片区 公 厂进行智慧化改造，增加高级工艺控制系统；对厂区建筑和构筑 共 农村 开 1 物修缮；优化加药系统投加模式，增加精确加药系统；对全厂部 2026-08 资 1600.00 供水 招 分老旧管道进行更换；金属防腐工程，对金属设备和管道的防锈 源 保障 标 刷漆工作。 交 提升 招标 易 工程 项目 中 （一 心 标段） 南岸 重 区峡 庆 口、 市 迎龙 公 片区 管网工程：延伸、改造峡口镇、迎龙镇等4个乡镇 46 公里 公 共 农村 DN40~DN300 配水主支管，36公里 DN20入户管道，新建3座一体 开 2 2026-08 资 1300.00 供水 化智慧加压泵房，入户水表改造 1752 户，并配套建设监测计量 招 源 保障 基础设施。 标 交 提升 易 工程 中 （二 心 标段） 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075572.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075572.html</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
         <v>90</v>
       </c>
@@ -3468,11 +3312,7 @@
           <t>北碚区东阳天府片区农村供水提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 北碚区东阳天府片区农村供水提升工程 招标法人或招 标人名称（盖 重庆北碚文旅产业发展有限公司 网 章） 项目批准文件 及文号 务 工程建设区域为东阳及天府片区，主要建设内容包含改造供水管网437千米，其中DN200供水 主要建设内容 管网35千米，DN100~DN150供水管网82千米，DN100以下供水管网320千米，并配套建设管网 附属设施。 招标项目名 招标内 招标方 招标文件计划 拟交易场 合同预估金 序号 商 备注 称 容 式 发布时间 所 额(万元) 北碚区东阳 招标项目 重庆市公 天府片区农 施工招 公开招 1 2026-08 共资源交 8457.00 村供水提升 标 道标 易中心 工程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075569.html 管 cqdingjiu 2026.08.21 10:06:55 国 中</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075569.html</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
         <v>80</v>
       </c>
@@ -3544,11 +3384,7 @@
           <t>北碚区澄江片区农村供水提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 北碚区澄江片区农村供水提升工程 招标法人或招标 重庆北碚文旅产业发展有限公司 人名称（盖章） 网 项目批准文件及 文号 改造取水泵站一座，改造DN600供水管网2.9km，DN50~DN300供水管网88.863km，DN25供 主要建设内容 务 水管网68.5km及其附属设施。 招标项目名 招标文件计划 合同预估金 序号 招标内容 招标方式 拟交易场所 备注 称 发布时间 额(万元) 招标项目 北碚区澄江 商重庆市公共 1 片区农村供 施工招标 公开招标 2026-08 资源交易中 8741.00 水提升工程 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 道 信息来源:https://www.chinapipe.net/project/d3075568.html cqdingjiu 2026.08.21 10:06:55 管 国 中</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075568.html</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
         <v>80</v>
       </c>
@@ -3620,11 +3456,7 @@
           <t>涪陵区江东街道农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区江东街道农村供水保障能力提升工程（二期） 名称 招标 法人 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 项目 网 批准 文件 涪陵发改〔2026〕471号 及文 号 主要 改造及延伸配水管 188.2千米，新建加压泵站4座，新建计量监测设施 建设 以及配套电气工程。 务 内容 招 标 合 文 同 招 件 预 招标 标 招标方 计 拟交易 备 序号 招标项目名商称 估 项目 内 式 划 场所 注 金额 容 发 (万 布 元) 时 间 重 道 庆 市 涪 陵 公 区 改造及延伸配水管 188.2千米，新建加压泵站4座，新建计量监测设施 开 公 1 涪陵区江东街道农村供水保障能力提升工程（二期） 2026-09 3137.22 管以及配套电气工程。 招 共 标 资 源 交 易 中 心 国 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075558.html cqdingjiu 2026.08.21 10:06:55 中</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075558.html</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
         <v>80</v>
       </c>
@@ -3696,11 +3528,7 @@
           <t>涪陵区龙桥街道农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 涪陵区龙桥街道农村供水保障能力 项目名称 提升工程 招标法人 或招标人 重庆水务环境控股集团渝东自来水 名称（盖 有限公司 章） 网 项目批准 文件及文 涪陵发改〔2026〕466号 号 改造荣桂水厂老化、破损、生锈的 务 输水管道7.36公里。马武水厂增设 废水回收及污泥浓缩系统1套。荣 桂水厂增设废水回收及污泥浓缩系 主要建设 统1套。新建配水管道总长0.74公里； 商 内容 改造配水管道总长139.42公里。新 建1座微型集成泵房及改造1座泵 站(原牌坊泵站)。新增管网监测设 施40套。 道 招标 合同 招 文件 预估 标 招标方 拟交易 备 招标项目 序号 招标项目名称 计划 金 内 式 场所 注 管 发布 额(万 容 时间 元) 改造荣桂水厂老化、 破损、生锈的输水管 国 道7.36公里。马武水厂 增设废水回收及污泥 重庆 浓缩系统1套。荣桂水 市涪 厂增设废水回收及污 公 陵区 中 涪陵区龙桥街道农村供水保障能力 泥浓缩系统1套。新建 开 1 2026-09 公共 3236.36 提升工程 配水管道总长0.74公里； 招 资源 改造配水管道总 标 交易 长139.42公里。新建1 中心 座微型集成泵房及改 造1座泵站(原牌坊泵 站)。新增管网监测设 施40套。 本计划表所列招标项目信息均为暂 备注 定，最终以实际招标时的信 信息来源:https://www.chinapipe.net/project/d3075556.html cqdingjiu 2026.08.21 10:06:55</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075556.html</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
         <v>90</v>
       </c>
@@ -3772,11 +3600,7 @@
           <t>涪陵区百胜镇农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区百胜镇农村供水保障能力提升工程 名称 招标 法人 或招 标人重庆水务环境控股集团渝东自来水有限公司 名称 网 （盖 章） 项目 批准 文件涪陵发改〔2026〕465号 及文 号 务 主要 建设整治 De315原水管长 1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1套及配套电气工程。 内容 招 拟 标 招招标文 合同预 交 序项 标件计划 估金 备 招标内容 易 号目 方发布时 额(万 注 场 名 商 式间 所 元) 称 涪 陵 区 重 百 庆 胜 市 招标 镇 涪 项目 农 道 陵 村 公 区 供整治 De315原水管长 1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1开 公 1 2026-09 1489.90 水套及配套电气工程。 招 共 保 标 资 障 源 能 交 力 易 提 中 管 升 心 工 程 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075553.html 国 cqdingjiu 2026.08.21 10:06:55 中</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075553.html</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
         <v>80</v>
       </c>
@@ -3848,11 +3672,7 @@
           <t>涪陵区清溪镇农村供水保障能力提升工程招标计划 重庆市工程建设项目招标计划表 项目名称 涪陵区清溪镇农村供水保障能力提升工程 招标法人 或招标人 重庆水务环境控股集团渝东自来水有限公司 网 名称（盖 章） 项目批准 文件及文 涪陵发改〔2026〕467号 务 号 对清溪水厂原取水口进行改造。改造清溪水厂输水管道长6.38公里。清溪水厂新建3000m3/d集成水 主要建设 厂1套，增设废水回收及污泥浓缩系统1套。新建配水管道总长2.46公里。改造配水管道总长145.04 内容 公里。四合村泵站增加1套备用加压泵。新商增管网监测设施35套。 招标项目 招标方 招标文件计 拟交易场 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 所 (万元) 对清溪水厂原道取水口进行 改造。改造清溪水厂输水 管道长6.38公里。清溪水厂 涪陵区清 新建3000m3/d集成水厂1套， 重庆市涪 招标项目 溪镇农村 增设废水回收及污泥浓缩 公开招 陵区公共 管 1 供水保障 2026-09 2888.89 系统1套。新建配水管道总 标 资源交易 能力提升 长2.46公里。改造配水管道 中心 工程 总长145.04公里。四合村泵 站增加1套备用加压泵。新 国 增管网监测设施35套。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075552.html 中 cqdingjiu 2026.08.21 10:06:55</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075552.html</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
         <v>80</v>
       </c>
@@ -3924,11 +3744,7 @@
           <t>涪陵区珍溪镇农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目名 涪陵区珍溪镇农村供水保障能力提升工程（一期） 称 招标法 网 人或招 重庆水务环境控股集团渝东自来水有限公司 标人名称 （盖章） 项目批 务 准文件 涪陵发改〔2026〕476号 及文号 (一)改造11000m3/d(旺水垭6000m3/d和二水厂5000m3/d)原水处理系统及辅助设施，主要有加氯系统、 加药系统、清水池、絮凝池、重力无阀滤池、商污水处理回收池、二水厂泵房设备等及其他辅助设施。 主要建 (二)更换旺水垭水厂至张家塘配水管13.5km，张家塘至滴水配水管长3.3km，全长16.8km；滴水至洪 设内容 湖配水管长0.3km；更换八一水库至旺水垭水厂引水管1.7km，更换珍溪二水厂至珍溪大桥配水管5km， 新建应急泵站至百汇大桥配水管9km：百汇至观将泵站4.5km；共计37.3km。 道 招标项目 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 场所 (万元) (一)改造11000m3/d(旺水 垭6000m3/d和二水厂5000m3/d) 管 原水处理系统及辅助设施，主 要有加氯系统、加药系统、清 水池、絮凝池、重力无阀滤池、 污水处理回收池、二水厂泵房 涪陵国区珍 设备等及其他辅助设施。(二) 重庆市 招标项 溪镇农村 更换旺水垭水厂至张家塘配水 涪陵区 目 供水保障 公开招 1 管13.5km，张家塘至滴水配水 2026-09 公共资 3427.27 能力提升 标 管长3.3km，全长16.8km；滴水 源交易 中工程（一 至洪湖配水管长0.3km；更换八 中心 期） 一水库至旺水垭水厂引水 管1.7km，更换珍溪二水厂至珍 溪大桥配水管5km，新建应急 泵站至百汇大桥配水管9km： 百汇至观将泵站4.5km；共 计37.3km。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075551.html cqdingjiu 2026.08.21 10:06:56</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075551.html</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
         <v>80</v>
       </c>
@@ -4000,11 +3816,7 @@
           <t>涪陵区武陵山镇农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区武陵山镇农村供水保障能力提升工程 名称 招标 网 法人 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 务 （盖 章） 项目 批准 商 文件 涪陵发改〔2026〕468号 及文 号 主要 道 新建及整治输配水管网总长 124.26千米，新建加压泵站 5座，新建高位水箱4座（总容积 354立方米），武 建设 陵山水厂新建废水处理系统1套及配套电气工程等。 内容 招 管 拟 标 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 国 称 涪 陵 区 中 重 武 庆 陵 市 山 招标 涪 镇 项目 陵 农 公 区 村 新建及整治输配水管网总长 124.26千米，新建加压泵站 5座，新建高 开 公 1 供 位水箱4座（总容积 354立方米），武陵山水厂新建废水处理系统1套 2026-09 1861.77 招 共 水 及配套电气工程等。 标 资 保 源 障 交 能 易 力 中 提 心 升 工 程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075549.html cqdingjiu 2026.08.21 10:06:56</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075549.html</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
         <v>80</v>
       </c>
@@ -4076,11 +3888,7 @@
           <t>涪陵区江东街道农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目名 涪陵区江东街道农村供水保障能力提升工程（一期） 称 招标法 网 人或招 重庆水务环境控股集团渝东自来水有限公司 标人名称 （盖章） 项目批 务 准文件 涪陵发改〔2026〕470 号 及文号 主要建 建设配水管网总长 34.80km，新建加压泵站 2 座、改造已成泵站 2 座、新建加氯加药间 1 座、新建高位 设内容 水箱 7 座、新建计量监测设施以及配套电气工程商。 招 招标文件 拟交 合同预估 序 招标项 标 备 招标内容 计划发布 易场 金额(万 号 目名称 方 注 道 时间 所 元) 式 涪陵区 重庆 招标项 江东街 市涪 目 建设配水管网总长 34.80km，新建加压泵站 2 座、 公 道农村 陵区 管 改造已成泵站 2 座、新建加氯加药间 1 座、新建高 开 1 供水保 2026-09 公共 3503.77 位水箱 7 座、新建计量监测设施以及配套电气工 招 障能力 资源 程。 标 提升工程 交易 （一期） 中心 国 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075548.html cqdingjiu 20中26.08.21 10:06:56</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075548.html</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
         <v>90</v>
       </c>
@@ -4144,11 +3952,7 @@
           <t>中国电建水电五局二公司重庆轨道交通17号线一期7标内外涂环氧消防复合钢管管件采购项目公开竞价采购(二次 挂网)变更公告(一) 详见附件。 信息来源:https://www.chinapipe.net/project/d3075376.html cqdingjiu 2026.08.21 10:06:56 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075376.html</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
         <v>60</v>
       </c>
@@ -4220,11 +4024,7 @@
           <t>2026年石柱分公司黄水镇黄连大道通信管道建设招标公告 ZB_ZHAOBIAOGONGGAO_START 本询比项目为 2026年石柱分公司黄水镇黄连大道通信管道建设 （标段 编号： CQBBFA202604170051 ），采购人为 中国电信股份有限公司石柱分公司 ，采购代理机构为 。项目 资金已落实。 具备采购条件，现进行公开询比，特邀请有意向的且具有提供标的物能力的潜在供应商（以下简 称供应商）参加询比响应。 1.项目概况与采购内容 1.1项目概况： 2026年石柱分公司黄水黄连大道通信管道修复项目主要针对黄水网黄连大道受损通信管道进行修 复80米 本次集中询比合同有效期为： 2026.9-2026.12 1.2采购内容 及标包划分情况： 务 1.2.1 本次询比的规模、货物名称、数量及主要技术参数、交货期及交货地点具体如下：黄水镇黄连大道80米通 信管道修复。 序号 标包名称 产品名称 规格型号 数量 交货地点 交货期 商 2026年石柱分公司黄水 黄水镇黄连 1 镇黄连大道通信管道建 管道建设 新建2孔110波纹管、 新建2孔蜂窝管 80 2026.12.20 大道 设 道 本项目 不划分标包 。 ${ } ${ 本项目允许供应商同时成交的最多标包数为 0 个。 } 本项目将按照最新的《中国电信供应商不良行为管 理规则》执行供应商不良行为处理结果，请重点关注处理结果适用的供应商主体、被处理产品、处理范围、禁 限期、处理措施等关键内容，请务必登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）查阅《中国 管 电信供应商不良行为管理规则》。 本项目根据《中国电信供应商不良行为管理规则》选择适用备选处理措施 （但涉及生产安全责任事故的处理结果不适用备选措施）。 1.2.2成交供应商数量： 1 个，每个成交供应商对应的份额如下 ： [请在此处自行编辑与采购方案相同的成交原则] 国 ${ 1.2.2成交供应商数量如下： [ 请在此处自行编辑与采购方案相同的有效供应商及成交供应商数量原则相关表格 ] 每个成交供应商对应的份额如下: [请在此处自行编辑与采购方案相同的份额分配原则] } 1.3本项目 设置最高 响应限价 。 设置最高响应限价，最高响应限价为不含税31000元人民币/计算方法，供应商响应报价高于最高 响应限价的，其响应将被否决 供应商响应报价高于最高响应限价的，其响应 将被否决。 ${ } 2.供应商中资格要求 2.1供应商基本资格要求 2.1.1 供应商 应为 中华人民共和国境内 法律上和财务上独立的法人或依法登记注册的其他组织，合法运作并 独立于采购人和采购代理机构。 供应商应具有良好的银行资信和商业信誉。法人下属不具备法人资格的分支机 构参与响应的，应提供所属法人针对本项目或覆盖本项目的经营事项的有效授权。 2.1.2 供应商 的法定代表人或负责人为同一人或者存在控股、管理关系的不同 供应商 ，不得参加同一标包响应或 者未划分标包的同一询比项目响应。 ${ 2.1.3 } ${ 2.1.3 } 2.1.4 本次询比 不接受 联合体响应。 ${如 供应商 为联合体，应满足下列要求： （1） 联合体各方必须按询比文件提供的格式签订联合体协议书，明确联合体牵头人和各方的权利义务； （2）由同一 专业的单位组成的联合体，按照资质等级较低的单位确定资质等级； （3）联合体各方不得再以自己名义单独或 加入其他联合体在同一标包或者未划分标包的同一询比项目中响应。 ${ （4） 。} } 2.1.5 本次询比 不接受代理商响应。 ${ （1）产品制造商注册地在中华人民共和国境外（与中华人民共和国有正常贸易与往来的国家或地区）及香港、 澳门、台湾地区且必须使用代理商响应和签订销售合同的；（2）产品制造商为注册地在中华人民共和国境内的 外资企业（包括香港、澳门、台湾地区资本）或者由外国投资者（包括香港、澳门、台湾地区）享有绝对控制权 （最大或最多表决权）的企业且必须使用代理商响应和签订销售合同的。代理商响应的，应满足下列要求 ： } ${ （1） ${ （2） 供应商与产品制造商 的代理合作关系迄今为止应已持续 0 年（含）以上。 } ${ （3） } } ${ 2.1.6 与供应商有产品代工制造关系的制造商不得参加同一标包响应或者未划分标包的同一询比项目响 应。 } 2.1.7 供应商须提供2022年1月1日至本项目发布公告之日的同类项目（通信管道施工类）证明材料， 合同累计金额不低于3万元（含税） 2.2供应商不得存在下列情形之一 （1） 为采购人不具有独立法人资格的附属机构（单位）； （2） 被依法暂停或取消 投标/ 响应资格的； （3） 被责令停产停业、暂扣或者吊销许可证、暂扣或者吊销执照； （4） 进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （5） 在最近三年内（自 2022年04月01日 起）被相关行业主管部门或司法机关认定有骗取 中标/成交 、严重 违约、重大工程质量或者安全问题的； 网 （6） 在最近五年内（自 2022年06月01日 起）被判处单位行贿罪，且行贿行为与采购活动相关的（以“中国 裁判文书网”的生效判决为准）； （7） 在最近五年内（自 2022年06月01日 起）被判处合同诈骗罪的（以“中国裁判文书网”的生效判决为 务 准）； （8） 被最高人民法院在“信用中国”网站（www.creditchina.gov.cn）或各级信用信息共享平台中列入失信被执 行人名单，已执行完毕或不再执行的除外； 商 （9） 为本询比项目提供过设计、编制技术规范和其他文件的咨询服务 ； （10） 为本工程项目的相关监理人，或者与本工程项目的相关监理人存在隶属关系或者其他利害关系； 道 （11） 为本询比项目的代建人 ； （12） 为本询比项目的采购代理机构 ； 管 （13） 与本询比项目的监理人或代建人或采购代理机构同为一个法定代表人 ； （14） 与本询比项目的监理人或代建人或采购代理机构存在控股或参股关系 ； （15） 被工商行政管理国机关在国家企业信用信息公示系统中列入严重违法失信企业名单的； （16） 中国电信在职员工违规担任供应商法定代表人并参与采购活动的； （17） 中国电信集团有限公司/中国电信股份有限公司中层及以上管理人员违反有关领导人员配偶、子女及其配 中 偶经商办企业行为管理规定，其配偶、子女及其配偶经商办企业参与采购活动的； （18） 中国电信领导人员离职或退休后三年内违反《国有企业领导人员廉洁从业若干规定》等相关规定任职、 投资入股的私营企业、外资企业和中介机构，参与其原任职单位采购活动的； ${ （19） } （19） 其他按照中国电信供应商不良行为处理结果及《中国电信供应商不良行为管理规则》的结 果执行规则，应对供应商及其响应产品在本项目中执行禁止采购处理措施的； （20） 法律法规、询比文件限定的其他情形。 ${ 供应商 是代理商的，本条所指的 供应商 也包括其所代理的制造商。 } ${ 联合体响应的，联合体成员均不得 存在上述任一情形。 } 2.3产品资格要求 2.3.1 产品 应是来自中华人民共和国 ${或是与中华人民共和国有正常贸易与往来的国家或地区} 的 成熟稳定的 产品 。 ${ 2.3.2 产品 。 } ${ 2.3.3 产品 。 } ${ 2.3.4 。 } ${ 2.3.5 。 } 2.3.6 产品应符合中国电信相关技术要求， 并满足以下关键技术指标： （1） 序号 技术指标 具体要求 1 开挖深度 埋深≥0.8m（道路≥1.2m） 2 施工规格 本次修复选择开挖换管：开挖约80米，2孔110波纹管、2孔蜂窝管，新建两通信手控井 ${ 2.3.7 产品 业绩要求： 。 } ${ 2.3.8 。 } ${ 2.4 产品制造商资格要求 2.4.1 制造商应提供合法有效的登记 （或注册）证明文件，应具有良好的银行资信和商业信誉。 } ${ 2.4.2 } ${ 2.4.2 } ${ 2.4.3 } ${ 2.4.4 } ${ 2.4.5 } ${ 2.5现场考察 } ${ 2.6评价检测 } 2.7 法律法规规定的其他要求。 3.资格审查方法 本项目将进行资格后审，资格审查标准和内容见询比文件第三章“评审办法”，凡未通过资格后审的供应商， 其响应将被否决 。 网 4.询比文件的获取 4.1询比文件获取时间: 2026年08月25日 00时00分00秒 至 2026年09月01日 00时00分00秒 （北京时间，下同）。 4.2询比文件获取方式：登录“中国电信阳光采购网（https://caigou.c务hinatelecom.com.cn）”后，通过“招投标-采 购文件领取”模块或通过“电子采购入口”跳转中国电信电子采购系统，进入本项目进行询比文件登记申领， 未在系统注册的供应商须先进行注册，注册方法详见本公告“ 7 供应商注册”。 4.3询比文件费用： 本项目不收取文件费用。 ${每套售价商 0 元人民币，售后不退。支付要求： } 5.响应文件的递交 5.1响应文件递交截止时间（即响应截止时间）为： 2026年09月02日 00时00分00秒 道 5.2 电子响应文件的提交方式：登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投 标-我的项目”模块或通过“电子采购入口”跳转中国电信电子采购系统，选择本项目进行响应文件提交，供应 商应在响应文件提交截止时间之前通过电子采购系统完成加密电子响应文件的上传。供应商未在电子采购系统 进行询比文件申领登记或电子响应管文件未按照要求加密的，将无法通过电子采购系统提交电子响应文件 。 5.3 本项目将于响应文件提交截止同一时间通过中国电信电子采购系统开启响应文件， 采购人/采购代理机构 邀 请响应供应商的法定代表人或者其委托代理人准时参加 。 国 ${ 6.样品的递交 6.1样品递交的时间、地点：于 递交至 。 } 7. 供应商注册 7.1 中国电信阳光采购网注册 未注册过的潜在供应商，须通过中国电信阳光采购网（https://caigou.chinatelecom.com.cn）首页“立即注册”模 中 块完成注册后，方可申领本项目询比文件。 7.2 CA证书办理 参加询比响应的潜在供应商须提前办理CA证书，并确保CA证书在使用时有效。CA证书办理流程详见中国电信 阳光采购网首页“操作指引-CA办理”。 7.3 技术支撑联系方式 服务热线：4000111884 服务邮箱：zb_support@chinatelecom.cn（电子采购系统技术支撑） ctsc@chinatelecom.cn（CA证书办理技术支撑） 8. 发布公告的媒介 本询比公告在 中国电信阳光采购网（https://caigou.chinatelecom.com.cn） 、中国招标投标公共服务平台 （http://www.cebpubservice.com/） 上发布，其他媒介转载无效。 9. 联系及异议接收方式 9.1 联系方式 采 购 人: 中国电信股份有限公司石柱分公司 采购代理机构: 地 址： 重庆市石柱县城南路6号 地 址： 无 邮 编： 邮 编： 无 联 系 人： 马卫平 联 系 人： 无 电 话： 17365204567 电 话： 无 电子邮件： 17365204567@189.cn 电子邮件： 无 网 址： www.chinatelecom.com.cn或“/” 网 址： 无 网 开户银行： 无 账 号： 无 9.2 异议接收方式 务 登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投标-采购异议-提出异议”模块提出。 采购代理机构： 商 2026年08月25日 信息来源:https://www.chinapipe.net/project/d30道75344.html cqdingjiu 2026.08.21 10:06:56 管 国 中</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075344.html</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
         <v>0</v>
       </c>
@@ -4288,11 +4088,7 @@
           <t>重庆站站房CQZSG-4标项目蓝色PVC袖阀管(外径60mm)询价采购公告 ZTEJWZ-JZ-2026-询027（一） 采购单位:重庆站站房CQZSG-4标段项目经理部 发布时间:2026-08-18 19:06 报价截止时间:2026-08-21 10:00 招标方联系人:刘健 网 招标方联系电话:13540650091 招标方邮箱: 务 监督方联系人:纪委 监督方联系电话:028-87653066 商 监督方邮箱: 保证金:0.0元 道 结算与发票信息: 结算方式：上月21日至本月的20日为一个结算周期，当月20日为本月的结算截止日期。结算时根据甲方检验合格 及双方共同签认的凭证计算当月实际收货数量。 管 支付条件：结算完成后，甲方在收到乙方开具的正式的增值税专用发票后第1个月支付该批物资结算金额的70%， 第12个月支付20%，剩余10%在第18-24月内按月均衡支付。 发票种类：增值税专用国发票 发票抬头：中铁二局集团有限公司 税号：9151中0100MA61RKR7X3 其他要求： 交货信息: 交货方式:点数验收 收货人:刘健 收货人联系方式:13540650091 其他说明事项: 流水号：询2026081800458 交 标的 规格 计量 标的编号 数量 技术标准及要求 货 送货地址 名称 型号 单位 期 蓝色PVC袖阀管，外 西南区-重庆市-市辖区-渝中区-重 袖阀 径60mm，壁 庆市菜园坝立交以西，龙家湾隧道 0950999183764 - 23188.0 米 管 厚4.5-5mm PVC管，承压 以东，菜袁路以北，王家坡以南的 不小于5MPa,节长4m 地块内，原重庆站。 报价网址:http://www.crecgec.com 信息来源:https://www.chinapipe.net/project/d3075317.html cqdingjiu 2026.08.21 10:06:56 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075317.html</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
         <v>0</v>
       </c>
@@ -4364,11 +4160,7 @@
           <t>涪陵区蔺市街道农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区蔺市街道农村供水保障能力提升工程（一期） 名称 招标 法人 或招 标人重庆水务环境控股集团渝东自来水有限公司 名称 网 （盖 章） 项目 批准 文件涪陵发改〔2026〕474号 及文 号 主要 务 建设新建、更换配水管网 396.72km（dn20-dnl60PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收及污泥浓缩处理系统。 内容 拟 招招标文 合同预 招标 交 序 标件计划 估金 备 项目招标内容 易 号 方发布时 额(万 注 名称 场 式间 元) 所 商 重 庆 涪陵 市 区蔺 招标 市街 涪 项目 道农 陵 公 区 村供 新建、更换配水管网 396.72km（dn20-dnl60PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收 开 公 1 水保 2026-09 3611.91 及污泥浓缩处理系统。 招 共 障能 道 标 资 力提 源 升工程 交 （一 易 期） 中 心 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075278.html 管 cqdingjiu 2026.08.21 10:06:57 国 中</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075278.html</t>
-        </is>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
         <v>80</v>
       </c>
@@ -4440,11 +4232,7 @@
           <t>涪陵区李渡街道农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区李渡街道农村供水保障能力提升工程 名称 招标 法人 网 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 务 项目 批准 文件 涪陵发改〔2026〕469号 及文 号 商 主要 改造李渡街道 15个村（社区）配水主支管道，更换配水主管网 193.71 千米（DN250-DN40 抗菌耐磨涂塑钢管、dn40-dn25PE管）及配套 建设 附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治 3座，新建测控井78座。 内容 招 拟 标 道 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 称 管 涪 陵 区 重 李 庆 渡 市 街 国 招标 涪 道 项目 陵 农 公 区 村 改造李渡街道 15个村（社区）配水主支管道，更换配水主管网 193.71 千米（DN250-DN40 抗菌耐磨涂 开 公 1 供 塑钢管、dn40-dn25PE管）及配套附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治 3座，新建 2026-09 2372.74 招 共 水中测控井78座。 标 资 保 源 障 交 能 易 力 中 提 心 升 工 程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075277.html cqdingjiu 2026.08.21 10:06:57</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075277.html</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
         <v>80</v>
       </c>
@@ -4516,11 +4304,7 @@
           <t>涪陵区珍溪镇农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目名称 涪陵区珍溪镇农村供水保障能力提升工程（二期） 招标法人 或招标人 重庆水务环境控股集团渝东自来水有限公司 网 名称（盖 章） 项目批准 文件及文 涪陵发改〔2026〕477号 务 号 (一)本项目对珍溪镇23个村(社区)安装配水管网660km及配套附属设施，其中：1.De160~De40的PE管 主要建设 有232km；2.连接各村社的De32~De20的PE管有381km；3.219~32的衬塑钢管47km。(二)购置安装泵 内容 站14座(一用一备共计28台水泵)，其中新建泵商站10座、更换泵站4座及配套电力设施;新建不锈钢水 箱2座等。(三)购置安装(0~25kg)减压阀61个;排污阀(25kg）3个。 招标项目名 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 称 式 划发布时间 场所 (万元) 道 (一)本项目对珍溪镇23个 村(社区)安装配水管网660km 及配套附属设施，其 中：1.De160~De40的PE管 管 有232km；2.连接各村社 涪陵区珍溪 重庆市 的De32~De20的PE管有381km； 招标项目 镇农村供水 涪陵区 3.219~32的衬塑钢 公开招 1 保障能力提 2026-09 公共资 2182.77 管47km。(二)购置安装泵 标 升工国程（二 源交易 站14座(一用一备共计28台水 期） 中心 泵)，其中新建泵站10座、更 换泵站4座及配套电力设施; 新建不锈钢水箱2座等。(三) 中 购置安装(0~25kg)减压阀61 个;排污阀(25kg）3个。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075275.html cqdingjiu 2026.08.21 10:06:57</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075275.html</t>
-        </is>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
         <v>90</v>
       </c>
@@ -4592,11 +4376,7 @@
           <t>涪陵区蔺市街道农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区蔺市街道农村供水保障能力提升工程（二期） 名称 招标 法人 网 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 务 项目 批准 文件 涪陵发改〔2026〕475号 及文 号 商 主要 八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长 105.307km（dn20-dn40PE 建设 管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建 1座改造3座；新建测控井 52座。 内容 拟 招 招标文 合同预 招标 交 序 道 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 所 重 庆 涪陵 管 市 区蔺 涪 招标 市街 陵 项目 道农 公 区 村供 八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长 开 公 1 水保 105.307km（dn20-dn40PE 管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建 1座改造3座； 2026-09 2652.89 国 招 共 障能 新建测控井 52座。 标 资 力提 源 升工程 交 （二 易 期） 中 中 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075274.html cqdingjiu 2026.08.21 10:06:57</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075274.html</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>80</v>
       </c>
@@ -4660,11 +4440,7 @@
           <t>重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目项目公告 重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目（项目名称）比选公告 1.比选条件 本比选项目重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目（项目名称），比选人为重庆市排 网 水有限公司，比选项目资金来自企业自筹（资金来源），项目已具备比选条件。中标后合同与重庆市豪洋水务 建设管理有限公司签订。现对本项目进行公开比选，诚邀有兴趣的潜在投标人参与投标。 2.项目概况与比选范围 务 2.1 建设地点：重庆市巴南区 2.2 项目概况：本项目涉及管道为鱼洞污水处理厂专件厂线管网，管道编号为WD4-WD8+1,该管道为自流管道， 位于鱼轻桥至河嘴倒虹井段，主要用于收集输送鱼洞大江商至华熙片区的生活污水。该段管道管径为DN600，管道 为混凝土管，主要采用架空明敷的方式沿河敷设。该管道自建成投运以来已有20余年，管道及污水井老化严重现 象十分明显，容易出现破损从而造成污水溢流，造成环保风险。为规避环保风险且保障该段管道以及鱼洞污水 厂的正常收水及运行，需对该段管道进行改造。 道 2.3 比选范围：拆除现状管道为DN600混凝土管，同时需拆除并新建9座检查井。 2.4 工期要求：30日历天，以甲方通知进场时间为准。 管 2.5缺陷责任期要求：24个月 3.投标人资格要求 国 3.1 本次比选要求投标人须具备以下条件： 3.1.1 本次比选要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰级 及以上资质。 中 3.1.2 投标人还应在人员、设备、资金等方面具有相应的施工能力，详见比选文件第二章投标人须知前附表第1.4.1 项内容。 3.2 本次比选接受不联合体投标。 4.比选文件的获取 4.1 投标人于2026年8月 18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子 版，以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都 视为投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的 一切后果由投标人自行负责。各投标单位应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行供应商注册，填写相关信息，审批过后成为 平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价、递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，将被否决投标。 4.4 比选文件每份售价800元，售后不退。投标单位在递交纸质投标文件时扫描支付，否则比选人拒绝接收其投标 文件。 5.投标文件的递交 5.1 电子投标文件递交时间：2026年8月24日14时30分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年8月24日14时00分至14时30分（北京时间），地点：重庆水务招标采购中心 （重庆市两江新区嘉华路36号重庆水务大厦5楼）。 5.3 投标截止时间：2026年 8月24日14时30分（北京时间）。 网 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 务 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 商 比 选 人：重庆市排水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝中区长江滨江路126号 地 址：重庆市两江新区嘉华路36号重庆水务大厦 道 联 系 人： 黄老师 联 系 人： 黄晓华 电 话： 023-67767416 电 话： 18523396416 管 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3075272.html 国 cqdingjiu 2026.08.21 10:06:57 中</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075272.html</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>90</v>
       </c>
@@ -4736,11 +4512,7 @@
           <t>重庆市潼南城区老旧供水管网改造工程招标计划 重庆市工程建设项目招标计划表 项目名称 重庆市潼南城区老旧供水管网改造工程 招标法人或招 标人名称（盖 重庆市潼南自来水有限公司 网 章） 项目批准文件 及文号 务 主要建设内容 改建潼南城区输水主管网约39.63km及配套相应阀门阀件等 招标方 招标文件计 拟交易场 合同预估 序号 招标项目名称 招标内容 备注 式 划发布时间 所 金额(万元) 对城区供水管网上商 重庆市潼南城 老旧阀门阀件、设 区老旧供水管 重庆市潼 招标项目 施设备进行更换， 网改造工程 公开招 南区公共 1 保障供水管网稳定 2026-09 918.00 （城区配套阀 标 资源交易 运行合道理增设部分 门阀件改造工 中心 计量及压力监控、 程） 水质监控等。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3075266.html cqdingjiu 2026.08.21 10:06:58 国 中</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075266.html</t>
-        </is>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
         <v>80</v>
       </c>
@@ -4812,11 +4584,7 @@
           <t>关于为【重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购】公开选取【工程设计】 机构的公告 我单位在重庆市网上中介超市公开选取工程设计中介服务机构，现将相关事项公告如下： 该项目为直接选取项目，由采购人从报名的中介服务机构中直接选定一家中介服务机构进行项目服务。 项目 重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购 名称 网 采购 重庆市开州区河堰镇人民政府 人 投资 审批 否 务 项目 是否 破产 商 业务 否 服务 项目 采购 道 所需 中介 其他 服务 事项 管 所需 服务 工程设计 类型 项目实施地点为国河堰镇清泉社区，项目建设内容为：硬化2米宽生产便道5.5千米，100方防旱池1口，50方 服务 蓄水池1口，标准自动化育苗大棚1个，蔬菜小棚20个，水源处理设施1套，水肥一体化配套设施1套，新 内容 建50平方米设备管理房，完善蔬菜基地配套设施等。工程总投资335万元。选取此项目设计单位（含预算 编制服务）。 中 中介 机构 资质（资格）要求 要求 资质 （资 1、报名单位提供有效的营业执照，资质证书（资质丙级或丙级以上），具备从事项目设计服务工作； 2、 格） 具有独立承担民事责任的能力； 3、具有良好的商业信誉和健全的财务会计制度； 4、具有履行合同所必 要求 需的专业技术能力； 5、有依法缴纳税收和社会保障资金的良好记录。 说明 其他 要求 无 说明 服务 时限 无要求，按照合同双方自行约定 说明 服务 3.1%费率 金额 金额 按文件要求执行 说明 选取 直接选取 方式 需规 避机 构 规避 原因 选取 2026-08-20 16:00:00 （选取时间到达后不接受报名，建议中介机构至少在选取开始半小时前完成报名。） 时间 采购 人业 网 务咨 重庆市开州区河堰镇人民政府（18716685679） 询电 话 采购 务 需求 26清泉社区项目设计服务采购说明.pdf 书下 载 商 2026-08-18 信息来源:https://www.chinapipe.net/project/d3075198.html 道 cqdingjiu 2026.08.21 10:06:58 管 国 中</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075198.html</t>
-        </is>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
         <v>90</v>
       </c>
@@ -4888,11 +4656,7 @@
           <t>重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目招标公告 1.招标条件 本招标项目重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目已由重庆市开州区发展和改革委员会以开州 发改审〔2026〕357号批准建设，项目业主为重庆市开州区长沙镇人民政府，建设资金来自开州区2026年中央和 市级提前批财政衔接推进乡村振兴补助资金，项目出资比例为 100% ，招标人为重庆市开州区长沙镇人民 政府。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：开州区长沙镇桔香村 2.2 项目概况与建设规模：1.建设果园水肥一体化系统1套，对示范柑桔果园建设水肥一体智能化系统;2.果园运输 线4000米(含轨道主机、叉车、周转箱、三轮车等配套设施设备);3.建设排灌站一处;4.建设1.8米宽生产便道2000米， 务 周转场300平方米;5.配备载重无人机1台、小型挖机1台、电子控制屏1个;6.建设智慧平台与监测系统软硬件系统等。 2.3 本项目工程总投资金额： 500万元 本次招标项目合同估算金额： 446.278921万元 商 2.4 招标范围：招标人发布的由重庆中煜华资工程技术有限公司设计的《重庆市开州区2026年长沙镇桔香村柑橘 基地改造提升项目》施工图及图纸说明、招标文件(含补遗)及工程量清单、答疑资料、澄清资料范围内所涉及的 工作内容，具体以招标人发布的工程量清单及道施工图为准。 2.5 工期要求： 150日历天 缺陷责任期要求： 12个月 管 2.6 标段划分（如有）： / 2.7 其他： / 国 3.政府采购工程 3.1 是否属于政府采购工程：是 中 3.2 是否专门面向中小企业预留：否，按照《政府采购促进中小企业发展管理办法》第六条第(三)“按照本办法 规定预留采购份额 无法确保充分供应、充分竞争，或者存在可能影响政府采购目标实现的情形”的规定，故本 项目不专门面向中小企业预留。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包叁级及以 上资质或市政公用工程施工总承包叁级及以上资质或水利水电工程施工总承包叁级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在 重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）下载招 标文件、工程量清单、电子图纸等资料。参与投标的投标人需在 重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）完成市 场主体信息登记以及CA数字证书办理，办理方式请参见 重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、 重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）导航栏“主体信息”页面中“市场主 体信息登记”、“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完 成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区） （https://www.cqggzy.com/kaizhouweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告 发布至2026-08-21 17:00:00前。 5.3招标人应于2026-08-25 23:59:59前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源 交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）发布澄清。 6.投标文件递交的内容 网 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-21 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 务 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区） （https://www.cqggzy.com/kaizhouweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交 易监督网上发布。] 商 8.联系方式 招 标 人: 重庆市开州区长沙镇人民政府 代理机构: 重庆毅仁建设项目管理有限公司 重庆市开州区文峰街道天鹅湖社区富厚街158号附10 地 址: 重庆市开州区长沙镇山花街1号 地 址: 道号 邮 编: 邮 编: 项目负责人: 丁敬余 项目负责人: 谭毅 电 话: 15826368887 管电 话: 13452653126 传 真: 传 真: 电子邮箱: 1415705480@qq.com 电子邮箱: 开户银行: 国 开户银行: 账 号: 账 号: 监督部门:中重庆市开州区公共资源交易管理局 电 话: 023-52218977 2026年08月17日 重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目 户名 开户行 投标保证金账号 重庆市开州区公共资源交易中心 重庆农村商业银行股份有限公司开州支行 3401010120010012772000200 中国农业银行股份有限公司重庆开州支行营 重庆市开州区公共资源交易中心 314401010400104500000006031 业部 中国工商银行股份有限公司重庆开州支行营 重庆市开州区公共资源交易中心 9558853100005824176 业部 重庆市开州区公共资源交易中心 重庆银行股份有限公司开州支行 680101040007547-100984 重庆市开州区公共资源交易中心 中国银行股份有限公司重庆开州支行 108865555576VA00149 信息来源:https://www.chinapipe.net/project/d3075199.html cqdingjiu 2026.08.21 10:06:58</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3075199.html</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="n">
         <v>90</v>
       </c>
@@ -4964,11 +4728,7 @@
           <t>万盛城区老旧供水管网更新改造工程答疑及补遗(一) 万盛城区老旧供水管网更新改造工程 答疑及补遗（一） 各潜在投标人： 现将万盛城区老旧供水管网更新改造工程答疑及补遗（一）相关条款通知如下： 网 一、答疑 问题1：请问招标人是否委派业主专家参与评标吗？ 务 答：是，本项目评标委员会共7人，其中在重庆市综合评标专家库随机抽取5人，招标人代表2人。? 问题2：本项目是否采用异地评标方式？ 答：是 。 商 问题3：本项目是否有业主代表，如有，请明确业主代表数量。 答：是，本项目评标委员会共7人，其中在重道庆市综合评标专家库随机抽取5人，招标人代表2人 。 问题4：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 答：可以。 管 问题5：污水处理厂提标改造及附属管道施工业绩满足吗？ 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 国 问题6：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可以 不填(空白)，对此有无要求？ 答：无要求。? 中 问题7：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖章， 请问需要提供联合体协议书吗？ 。 答： 根据招标文件第二章“投标人须知前附表”1.4.1 第3条业绩要求中：“注：（2）投标人提供的业绩为联 合体业绩的，其在该业绩中的工作分工应与本项目承担的工作一致。”要求，故需要提供联合体协议书。 问题8：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要求”吗？ 答：填写“达到招标文件的要求”或按照招标文件相关条款填写具体内容均可 。 问题9：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 答：投标人的工程量清单单项报价不得为零报价(招标人提供的工程量清单单项最高限价中金额为零的除外)或者 负数报价，否则由评标委员会作否决投标处理。 问题10：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知书发 出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予提前注 销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 答：需要。但不将加盖正本作为评审因素。 问题11：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收，请 问我公司业绩满足业绩要求吗？ 答：不满足。? 问题12：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 答：可以 。 问题13：业绩要求的竣工时间是指竣工验收时间吗？ 答：是的。 网 问题14：重庆市电子招投标系统投标文件-报价部分“己标价工程量清单”-“投标总价”页面招标人名称需要填 写吗？ 务 答：由投标人自行决定是否填写，是否填写不作为评审因素。 问题15：请问招标人是否委派业主专家参与评标吗？ 答：是，本项目评标委员会共7人，其中在重庆市综合评商标专家库随机抽取5人，招标人代表2人。 问题16：自来水厂或者净水厂含管道施工业绩满足业绩要求吗？ 答：投标人提供的业绩合同规模和工程类别需道满足招标文件要求。? 问题17：有没有人行贿专家，有的话我们就不参加了。 答：本项目评标委员会由招标人按法律法规及相关规定依法组建。 管 问题18：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要 提供其他格式之外的其他承诺？ 答：请各潜在投标人仔国细阅读招标文件，并按招标文件要求提供相应承诺。 问题19：财务报告可以不提供财务报表附注吗？ 答：可以。 中 问题20：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 问题21：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、注册证 及在本单位注册的证明文件替代？ 答：退休证等材料不能替代养老保险证明，按招标文件执行。? 问题22：本项目是异地评标吗？ 答：是。 问题23：现在除了没有警戒线和技术方案的低价项目评标专家不被围猎，哪个项目不围猎评标专家，请问招标人 如何保证公平？ 答：本项目招标文件严格按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本（2026年版）》编制， 且本项目评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 问题24：没有低价警戒线怎么保证中高价呢？ 答：本项目未设置低价警戒线，通过综合评估法对各潜在投标人进行评审。分值由技术、商务、报价组成，综 合实力优良的投标人合理中高价可依靠综合得分优势参与竞争，同时招标文件履约追责条款约束投标人理性报 价，保障合理报价竞争环境。 问题25：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗？ 答：现场递交纸质保函原件的人员不作要求 。 问题26：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 网 答：电子投标系统中锁定不可修改的格式（如封面、投标函）直接填空即可，其他投标文件格式以加盖公章的 招标文件PDF文件为准。? 问题27：专业分包业绩满足业绩要求吗？ 务 答：不满足。 问题28： 市政道路包含给水管网施工业绩满足业绩要求吗？ 商 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 问题29：技术负责人在资格审查部分中提供了工程类高级及以上职称证后，在商务部分中再提供工程类高级及以 上职称证可以加分吗？ 道 答：可以。 问题30：万盛的项目挂綦江来投这样都还控制不了还全是你们万盛公司中的？是有啥猫腻是吧？参考之前的项目 管 全是万盛的公司中的！业主、专家全是你们自己人吧？ 答：本项目招标文件严格按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本（2026年版）》编制， 且本项目评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 国 二、补遗 1、本次重新发布本项目的工程量清单，在《重庆市公共资源交易网》(綦江区) （https://www.cqggzy.com/qijiangweb/）网上发布，请投标人自行下载。 中 招 标 人：重庆市万盛经济技术开发区城市管理局 招标代理机构：重庆力圣建设工程咨询有限公司 2026年8月18日 信息来源:https://www.chinapipe.net/project/d3074975.html cqdingjiu 2026.08.21 10:06:58</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074975.html</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
         <v>80</v>
       </c>
@@ -5040,11 +4800,7 @@
           <t>重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告 重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告 1.招标条件 本招标项目 重庆市巴南区土桥片区内涝积水整治工程已由重庆市巴南区发展和改革委员会以巴南发改审 发[2025]33号文批准建设，项目业主为重庆市巴南区住房和城乡建设委员会，代建业主为重庆市巴南公路建设有 限公司，建设资金来自区级财政资金统筹，项目出资比例为 100%，招标人为重庆市巴南公路建设有限公司。 项目已具备招标条件，现对该工程的勘察设计进行公开招标，评标办法采用综合评估法。 网 2.项目概况与招标范围 2.1 建设地点：重庆市巴南区花溪街道、李家沱街道 务 2.2 项目概况与建设规模：为解决片区内涝问题，在李家沱街道、花溪街道改建 d400-d800 雨水管网 9665m，管材 采用高密度聚乙烯(HDPE)缠绕结构壁管 B型管；改建 d1商000-d1400雨水管网 664m，管材采用高密度聚乙 烯(HDPE)缠绕结构壁管 B 型管、III 级钢筋混凝土管；改建 d1500-d2000 雨水管网 426m，管材采用III 级钢筋混凝 土管;改建 d2100-d2600 雨水管网 1000m，管材采用 III 级钢筋混凝土管；修复雨水管网 5345m，增加智能感知设 备6 套。 道 2.3 本项目工程总投资金额：13477.10万元 管 本次招标项目工程费估算金额：11061.83万元 国 本次招标项目勘察设计合同估算金额：334.544万元 中 2.4 招标范围：主要包括勘察、施工图设计（包含高边坡、深基坑）和相应阶段的勘察工作，以及提供施工现场 全过程技术服务，并配合业主办理相关手续等，具体范围为： （1）勘察部分：完成本项目范围内的勘察工作，包括但不限于排水管网排查、1:500地形图测量、地质钻勘、管 线内窥、物探、综合管线测量，市政管网错混接点测量及调查等工作，解决区域地下空间臭气问题，勘察成果 需达到重庆市城市建成区排水管网排查技术导则的要求，并配合业主完成对应的成果审查等事宜。 （2）设计部分：包括不限于完成本项目的施工图设计、施工期间交通组织设计、桥梁（涉轨）安全论证方案及 施工期间至竣工验收阶段，质量保修阶段的设计配合服务，配合办理施工图审查相关手续及竣工验收阶段、质 量保修阶段的设计服务等工作以及协助招标人完成各项审批手续办理等工作。 2.5 勘察设计服务期限：30日历天 2.6 标段划分（如有）：/ 2.7 其他：/ 3.政府采购工程 3.投标人资格要求 3.1 本次招标要求投标人须具备以下条件： 网 3.1.1 本次招标要求投标人具备的资质条件： 务 投标人应同时具有建设行政主管部门颁发的下列勘察和设计两类资质： 商 I、投标人应具备下列勘察资质之一： 道 ①工程勘察综合甲级资质。 管 ②工程勘察专业类（岩土工程）专业甲级资质和工程勘察专业类（工程测量）甲级资质； 国 II、投标人应具备下列设计资质之一： 中 ①工程设计综合甲级资质； ②工程设计市政行业甲级资质； ③工程设计市政行业(燃气工程、轨道交通工程除外)甲级资质； ④工程设计市政行业(排水工程)甲级资质。 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的勘察设计能力，详见招标文件第二章投标人须知 前附表第1.4.1项内容。 3.2 本次招标接受联合体投标。联合体投标的，应满足下列要求：联合体组成单位数量不超过2家，由负责设计 任务的单位作为联合体牵头人。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件及其附件、澄 清、修改、补充通知、最高限价通知等资料。参与投标的投标人需在重庆市公共网资源交易网完成市场主体信息 登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息 登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程 电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 务 布至2026-08-23 12:00:00前。 4.3招标人应于2026-08-26 17:00:00前在重庆市公共资源交易网发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-24 09:30，投标人应当在投标截止时间前，通过互 商 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督道网、重庆市公共资源交易网、重庆市公共资源交易网（巴南区） 发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 重庆市巴南公路建设有限公司 代理机构: 重庆云远项目管理有限公司 管 地 址: 重庆市巴南区龙洲大道265号 地 址: 重庆市九龙坡区渝隆大厦28楼 邮 编: 邮 编: 项目负责人: 牟老师 项目负责人: 李强 国 电 话: 023-66238079 电 话: 023-68434996 传 真: 传 真: 电子邮箱: 电子邮箱: 中 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市巴南区发展和改革委员会 电 话: 023-66221670 2026年08月18日 重庆市巴南区土桥片区内涝积水整治工程勘察设计 户名 开户行 投标保证金账号 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000001675 贸易试验区分行 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051304894 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020041267 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764210157 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000682897 支行 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835000509 坝支行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146639123 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630018252 信息来源:https://www.chinapipe.net/project/d3074953.html cqdingjiu 2026.08.21 10:06:58 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074953.html</t>
-        </is>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
         <v>95</v>
       </c>
@@ -5116,11 +4872,7 @@
           <t>重庆管道公司2026年涪陵压气站管道、设备防腐项目-非招标公告 公告发布时间: 2026年08月18日09时02分19秒 一、概述 1.2.1项目概况：涪陵作业区涪陵压气站空压机、阀门等设备、消防泵房消防管道、循环水管道油漆出现锈蚀情况， 为保证设施安全运行，对站场设备、消防管道及附属钢结构进行打磨除锈、油漆防腐。 二、采购项目与标段 交货期限: 开工之日起90日内完工 网 质保期限(月): 标段 序号 标段名称 标段描述 编号 重庆管道公司2026年涪陵 涪陵作业区涪陵压气站空压务机、阀门等设备、消防泵房消防管道、循 1 1 压气站管道、设备防腐项 环水管道油漆出现锈蚀情况，为保证设施安全运行，对站场设备、消 目 防管道及附属钢结构进行打磨除锈、油漆防腐。 三、供应商资格要求 商 *1、响应人资质要求（1）响应人必须是依照中华人民共和国法律在国内注册，具备合格有效的营业执照的法人、 其他组织；与采购人存在利害关系可能影响询比采购公正性的法人、其他组织或者个人，不得参加响应。单位 负责人为同一人或者存在控股、管理关系的不同单位，不得参加同一标段响应或者未划分标段的同一询比项目 响应。（2）响应人须具备防水防腐保温工程专业承包二级及以上资质。*2、信誉要求响应人在响应文件提交截 止当日不存在以下情况：（1）响应人被“国道家企业信用信息公示系统”网站（www.gsxt.gov.cn）列入严重违法 失信企业名单（响应文件提交截止时间前已移出的除外）。（2）响应人被“信用中国”网站 （www.creditchina.gov.cn）列入严重失信主体名单（响应文件提交截止时间前已移出的除外）。（3）响应人或其 法定代表人、负责人、拟委任的项目经理被“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）列入失信 被执行人名单（响应文件提交截止时间前已移出的除外），响应文件中需提供有效身份证号供查询。（4）响应 管 人、拟委任的项目经理被“全国建筑市场监管公共服务平台”网站（https://jzsc.mohurd.gov.cn/home）列入黑名单 （响应文件提交截止时间前已移出的除外）。上述（1）-（4）条以评审当日评审小组从官网查询信息为准。（5） 被国家管网集团或西南管道公司暂停、取消投标资格或业务承揽资格。（6）法律、行政法规规定的其他不允许 参与投标的情况。 国 四、询比文件的获取 4.1 有意向参加项目者，于2026年08月20日09时05分22秒前，登录数字供应链平台进行项目报名。 中 4.2 报名成功后于2026年08月18日09时01分42秒至2026年08月24日09时05分22秒，登录数字供应链平台进行项目下 载询比文件。 五、响应文件的递交 5.1 请于2026年08月24日11时00分00秒前，登录数字供应链平台递交项目响应文件。 5.2 逾期将无法进行递交响应文件，采购人将不予受理。 5.3 供应商在递交响应文件前，应按照有关规定提供人民币0万元项目保证金。 六、响应文件的开启 6.1 响应文件的开启时间2026年08月24日11时06分00秒 6.1 响应文件的开启地点供应链系统上 七、采购人信息 地址： 邮编： 联系人：舒建华 联系电话：18581824001 电子邮件：shujh@pipechina.com.cn 传真： 开户银行： 账户名： 账号： 信息来源:https://www.chinapipe.net/project/d3074904.html cqdingjiu 2026.08.21 10:06:59 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074904.html</t>
-        </is>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
         <v>0</v>
       </c>
@@ -5192,11 +4944,7 @@
           <t>重庆燃气集团股份有限公司输配分公司大渡口调压站至二郎调压站次高压燃气管线工程(大渡口段)公告 采购 公告 公告编号： RQXYGG202608130064 一、采购项目基本情况 网 采购人：重庆燃气集团股份有限公司输配分公司 采购项目编号：RQCGXY202608130040 务 采购项目名称：大渡口调压站至二郎调压站次高压燃气管线工程（大渡口段） 采购内容或范围：安装部分： ①材料验收（甲供材料：阀门、管材、弯头、标志桩等）、运输及履带式挖掘机及人工布管； ②管道管件安装， 新旧管道的碰口；③安装DN400直埋球阀1座； ④管道和商焊口的除锈及防腐； ⑤管道下沟后15KV电火花检测； ⑥管道的清管，强度及严密性试验；⑦警示带敷设和线路标志桩（砖）安装； ⑧监检手续等。 土建部分： ①清表； ②扫线、平整场地； ③沟槽、基坑、阀井砌筑； ④回填土方； ⑤余方弃置； ⑥人工开挖人行道（花 台），公路及路面恢复； ⑦其他线缆穿跨越工道程施工，交通组织； ⑧水工保护等。 （具体内容详见施工图纸和 工程量清单） 公告发布时间 ：2026-08-18 14:39:10 管 二、采购人联系方式 联系人：王瑶 电话：023-67502265 国 邮箱：wangyao232@crcgas.com 三、采购明细 中 行号 采购内容 需求数量 单位 补充说明 拟邀请单位 大渡口调压站至二郎调压站次高压燃气管线 重庆燃气安装工程有限责任公 1 1 项目 无 工程(大渡口段) 司 四、服务费交纳 本项目不收取服务费。 五、 其他 事项 1.本公告在华润守正 采购交易 平 台（ https://www.szecp.com.cn/ ）上公开 发布。 2. 本项目采购通过守正平台线上进行，供应商需注册华润守正 采购交易 平台，通过平台进行响应文件的递交或 报价，具体操作步骤可查阅网站首页帮助中心的操作手册，也可以联系守正客服。 3 .答疑澄清、通知等文件一经在华润守正 采购交易 平台发布，视为已发放给相应供应商（发放时间即为发出时 间），请随时关注华润守正 采购交易 平台发布的相关信息，并及时查阅和处理。 4 .若有参与意向 ， 请于 2026-08-22 00:00:00前联系采购人 （联系方式见公示内容）反馈。 5 .若有异议 ， 请于 2026-08-22 00:00:00前提出异议 。 信息来源:https://www.chinapipe.net/project/d3074793.html cqdingjiu 2026.08.21 10:06:59 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074793.html</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
         <v>80</v>
       </c>
@@ -5268,11 +5016,7 @@
           <t>石柱公司2026-2027年度用户供水管道安装及管网抢(维)修工程(第二次)项目公告 石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程（第二次）（比选公告 1.比选条件 本比选项目石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程（第二次）（项目名称），比选人 为重庆石柱水利水电实业开发有限公司，比选项目资金来自企业自筹（资金来源），项目已具备比选条件。现 对本项目进行公开比选，诚邀有兴趣的潜在投标人参与投标。 网 2.项目概况与比选范围 2.1 建设地点：比选人指定地点 务 2.2 项目概况与建设规模：2026-2027年度用户供水管道安装及管网抢（维）修服务 2.3 本次比选项目合同估算金额：约280万元 商 2.4 比选范围：完成石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程包括公司供水范围内用户 各类管道及管件安装、水表安装及更换、阀门安装等、并完成配套土建工程、零星签证等工程量清单所列项目、 管网抢维修和公司所属生产单元零星项目，具体内容详见第五章 工程量清单。 道 2.5 工期要求：1年 缺陷责任期要求：24个月 管 3.投标人资格要求 3.1 本次比选要求投标人须具备以下条件： 国 3.1.1 本次比选要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰级 及以上资质； 3.1.2 投标人还应在人员、设备、资金等方面具有相应的施工能力，详见比选文件第二章投标人须知前附表第1.4.1 中 项内容。 3.2 本次比选不接受联合体投标。 4.比选文件的获取 4.1 投标人于2026年08月18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子版， 以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都视为 投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的一切 后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价，递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，被视为无效。 4.4比选文件每份售价1000 元，售后不退。投标人在递交纸质投标文件时支付，否则比选人拒绝接收其投标文 件。 5.投标文件的递交 5.1电子投标文件递交时间：2026年08月24日10时00分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年08月24日09时30分至10时00分，地点：水务集团招标采购中心（重庆市两江新 区嘉华路36号重庆水务大厦五楼）。 5.3 投标截止时间：2026年08月24日10时00分（北京时间）。 网 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 务 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 商 比 选 人：重庆石柱水利水电实业开发有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市石柱土家族自治县都督大道11号 地 址：重庆市两江新区嘉华路36号重庆水务大厦1018 联 系 人：王老师 联 系 人：颜老师 道 电 话：13658292968 电 话：023-67901915 重庆水务电子商务平台咨询电话：管023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3074720.html cqdingjiu 2026.08.21 10:06:59 国 中</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074720.html</t>
-        </is>
-      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
         <v>90</v>
       </c>
@@ -5336,11 +5080,7 @@
           <t>万盛城区老旧供水管网更新改造工程(甲供材料)答疑(一) 万盛城区老旧供水管网更新改造工程（甲供材料） 答疑（一） 各潜在投标人： 现将万盛城区老旧供水管网更新改造工程（甲供材料）答疑（一）相关条款通知如下： 网 一、答疑 问题1：请问招标人是否委派业主专家参与评标吗？ 务 答：是，本项目评标委员会共7人，其中在重庆市综合评标专家库随机抽取5人，招标人代表2人。 问题2：万盛的项目挂綦江来投这样都还控制不了还全是你们万盛公司中的？是有啥猫腻是吧？参考之前的项目 全是万盛的公司中的！业主、专家全是你们自己人吧？ 商 答：本项目招标文件严格按照《重庆市工程建设项目货物采购招标文件示范文本（2026年版）》编制，且本项目 评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 问题3：3PE管道部分壁厚是多少呢？ 道 答：本项目采购的3PE防腐钢管的管道部分壁厚须符合国标标准并达到设计要求。 招 标 人：重庆市万盛经济技术开发区城市管理局 管 招标代理机构：重庆力圣建设工程咨询有限公司 2026年8月18日 国 信息来源:https://www.chinapipe.net/project/d3074712.html cqdingjiu 2026.08.21 10:06:59 中</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074712.html</t>
-        </is>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
         <v>80</v>
       </c>
@@ -5404,11 +5144,7 @@
           <t>重庆中法供水2026年普通防腐钢管及管件采购项目(第三次)项目公告 重庆中法供水2026年普通防腐钢管及管件采购项目（第三次）比选公告 1.比选条件 本比选项目重庆中法供水2026年普通防腐钢管及管件采购项目（第三次），比选人为重庆中法供水有限公司，比 选项目资金来自企业自筹，出资比例为100%，项目已具备比选条件。现对本项目进行公开比选，诚邀有兴趣的 潜在投标人参与投标。 网 2.项目概况与比选范围 2.1 普通防腐钢管及管件采购清单： 务 序号 存货编码 材料名称 规格型号 单位 数量 最高单价限价（元） 1 10400177 钢高频焊管 D89*4 5 米 61.92 2 10400181 钢高频焊管 D108*5 300 米 88.89 商 3 10400182 钢高频焊管 D159*5 5 米 132.18 4 10400206 钢高频焊管 D159*6 5 米 152.13 5 10400290 钢螺旋焊管 DN219*6 5 米 196.68 道 6 10400291 钢螺旋焊管 DN219*8 5 米 244.80 7 10400292 钢螺旋焊管 DN325*8 5 米 361.28 8 10400293 钢螺旋焊管 DN377*8 5 米 423.12 管 9 10400294 钢螺旋焊管 DN426*8 5 米 475.89 10 10400295 钢螺旋焊管 DN426*10 5 米 574.29 11 10400297 钢螺旋焊管 DN529*8 5 米 595.76 国 12 10400298 钢螺旋焊管 DN529*10 5 米 718.91 13 10400299 钢螺旋焊管 DN630*10 5 米 861.50 14 10400300 钢螺旋焊管 DN720*10 5 米 987.95 中 15 10400301 钢螺旋焊管 DN820*10 5 米 1133.08 16 10400302 钢螺旋焊管 DN920*10 5 米 1279.51 17 10400304 钢螺旋焊管 DN1020*10 5 米 1424.64 18 10400305 钢螺旋焊管 DN1020*12 5 米 1652.24 19 10400306 钢螺旋焊管 DN1220*10 5 米 1709.70 20 10400307 钢螺旋焊管 DN1220*12 5 米 1982.83 21 10400308 钢螺旋焊管 DN1420*12 5 米 2375.96 22 10400309 钢螺旋焊管 DN1420*14 5 米 2697.83 23 10400332 钢螺旋焊管 DN1120*10 5 米 1574.96 24 10400342 钢螺旋焊管 DN1020*14 5 米 1879.02 25 10400322 钢螺旋焊管（特加强） DN820*10 5 米 1133.08 26 10200490 钢套筒 D159*500cm 5 个 159.00 27 10200491 钢套筒 D219*500cm 5 个 240.00 28 10200492 钢套筒 D273*500cm 5 个 300.00 29 10200493 钢套筒 D325*500cm 5 个 361.00 30 10200494 钢套筒 D377*500cm 5 个 436.00 31 10200495 钢套筒 D426*500cm 5 个 482.00 32 10200589 钢套筒 D159*1000cm 5 个 226.00 33 10200590 钢套筒 D219*1000cm 5 个 1627.00 34 10200591 钢套筒 D273*1000cm 5 个 2501.00 35 10200592 钢套筒 D325*1000cm 5 个 488.00 36 10200593 钢套筒 D377*1000cm 5 个 591.00 网 37 10200598 钢套筒 D426*1000cm 5 个 833.00 38 10200155 钢制标准接头 D108 5 个 91.00 39 10200156 钢制标准接头 D159 5 个 160.06 务 40 10200157 钢制标准接头 D219 5 个 319.41 41 10200158 钢制标准接头 D273 5 个 396.63 42 10200159 钢制标准接头 D325 5 个 475.96 商 43 10200160 钢制标准接头 D426 5 个 619.87 44 10200161 钢制标准接头 D529 5 个 779.22 45 10200162 钢制标准接头 D630 5 个 1068.44 道 46 10200163 钢制标准接头 D720 5 个 1214.46 47 10200164 钢制标准接头 D820 5 个 1428.34 48 10200165 钢制标准接头 D920 5 个 1600.14 管 49 10200169 钢制标准接头 D1220 5 个 2297.57 50 10200170 钢制标准接头 D1420 5 个 3027.02 51 10200171 钢制标准接头 D1020 5 个 2194.19 国 52 10300309 钢制大小头 DN65*DN50 5 个 14.74 53 10200667 钢制渐缩 D108＞57 3 个 21.06 54 10200668 钢制渐缩 D108＞89 3 个 26.00 中 55 10200695 钢制渐缩 D159＞108 3 个 40.72 56 10200671 钢制渐缩 D219＞159 3 个 68.09 57 10200672 钢制渐缩 D219＞108 3 个 80.03 58 10201605 钢制渐缩 219*125 3 个 75.82 59 10200694 钢制渐缩 D273＞108 3 个 129.87 60 10200673 钢制渐缩 D273＞159 3 个 94.07 61 10200674 钢制渐缩 D273＞219 3 个 84.94 62 10200675 钢制渐缩 D325＞108 3 个 184.63 63 10200676 钢制渐缩 D325＞159 3 个 143.91 64 10200680 钢制渐缩 D325＞219 3 个 131.98 65 10200677 钢制渐缩 D325＞273 3 个 124.25 66 10200684 钢制渐缩 D426＞325 3 个 285.01 67 10200685 钢制渐缩 D529＞325 3 个 617.76 68 10200679 钢制渐缩 D529＞426 3 个 547.56 69 10200659 钢制渐缩 D630＞325 3 个 756.00 70 10200687 钢制渐缩 D630＞426 3 个 728.00 71 10201539 钢制渐缩 D630＞529 3 个 722.00 72 10200690 钢制渐缩 D720＞630 3 个 848.00 73 10200691 钢制渐缩 D720＞529 3 个 842.00 74 10200682 钢制渐缩 D820＞720 3 个 913.00 75 10200692 钢制渐缩 D920＞720 3 个 1053.00 76 10201519 钢制渐缩 D920*820 3 个 1064.00 77 10200652 钢制渐缩 D1020＞820 3 个 1305.00 网 78 10200693 钢制渐缩 D1020＞920 3 个 1322.00 79 10201738 钢制渐缩 1220*820 3 个 1806.00 80 10201507 钢制渐缩 1220＞1020 3 个 1834.00 务 81 10201624 钢制三盘三通 D108⊥108 3 个 224.64 82 10200371 钢制三盘三通 DN200⊥100 3 个 435.24 83 10200373 钢制三盘三通 DN200⊥200 3 个 599.51 商 84 10201531 钢制三通 108*108 3 个 58.97 85 10200285 钢制三通 219*108 3 个 187.43 86 10201341 钢制双盘短管 89*400mm 3 个 139.00 道 87 10201342 钢制双盘短管 89*800mm 3 个 178.31 88 10201340 钢制双盘短管 108*300mm 3 个 158.65 89 10201299 钢制双盘短管 DN108*500mm 3 个 185.33 管 90 10201300 钢制双盘短管 DN108*1000mm 3 个 258.34 91 10201301 钢制双盘短管 DN108*1500mm 3 个 329.94 92 10201332 钢制双盘短管 159*300mm 3 个 251.32 国 93 10201339 钢制双盘短管 159*750mm 3 个 348.19 94 10201303 钢制双盘短管 DN159*1000mm 3 个 402.95 95 10201304 钢制双盘短管 DN159*1500mm 3 个 508.25 中 96 10201305 钢制双盘短管 DN219*500mm 3 个 463.32 97 10201306 钢制双盘短管 DN219*1000mm 3 个 672.52 98 10201307 钢制双盘短管 DN219*1500mm 3 个 876.00 99 10201312 钢制双盘短管 DN219*750mm 3 个 581.26 100 10201338 钢制双盘短管 273*1250mm 3 个 1010.88 101 10201458 钢制双盘渐缩 108*57 3 个 109.51 102 10201469 钢制双盘渐缩 108*89 3 个 117.94 103 10201514 钢制双盘渐缩 159*108 3 个 185.33 104 10201748 钢制双盘渐缩 200*80 3 个 294.84 105 10201462 钢制双盘渐缩 219*108 3 个 256.93 106 10201513 钢制双盘渐缩 219*159 3 个 280.80 107 10201465 钢制双盘渐缩 D273＞108 3 个 339.77 108 10201467 钢制双盘渐缩 D273＞219 3 个 388.91 109 10201770 钢制双盘渐缩 D273＞159 3 个 365.04 110 10201461 钢制双盘渐缩 325*219 3 个 477.36 111 10301108 钢制弯头 89*90° 3 个 28.78 112 10200702 钢制弯头 D108×90° 100 个 43.52 113 10200701 钢制弯头 D159×90° 3 个 84.24 114 10200705 钢制弯头 D219*90° 3 个 231.66 115 10200706 钢制弯头 D273*90° 3 个 300.46 116 10200709 钢制弯头 D325*90° 3 个 418.39 117 10200711 钢制弯头 D426*90° 3 个 744.12 118 10200712 钢制弯头 D529*90° 3 个 1352.05 网 119 10200764 钢制弯头 D570*90° 3 个 1474.20 120 10200714 钢制弯头 D630*90° 3 个 1535.98 121 10200715 钢制弯头 D720*90° 3 个 1742.36 务 122 10200717 钢制弯头 DN720*90°*12mm 3 个 1989.47 123 10200720 钢制弯头 D920*90° 3 个 2935.30 124 10200722 钢制弯头 D820*90° 3 个 2325.23 商 125 10200762 钢制弯头 D1020*90° 3 个 4829.55 126 10200723 钢制弯头 D1220*90° 3 个 6039.80 127 10200724 钢制弯头 D1420*90° 3 个 8297.00 道 注：管材按照米数进行报价，管件按照件数进行报价。 2.2 供货数量、时间和批次：根据工程实际进度与比选人的要求进行供货，以实际供货量为准，供货时间达到商 务条款的规定。 管 2.3 交货地点：比选人指定的施工现场。 2.4 供货期：两年。 国 3.投标人资格要求 3.1 本次比选允许投标人以投标货物的下列身份参加投标： 中 ?制造商 3.1.1 投标人为制造商应符合以下要求： 投标人必须是依法设立的，并在中国注册的，具有独立法人地位的企业。 【提供有效的营业执照】 3.2 投标人2025年的年度财务状况不亏损。 【提供由会计师事务所或审计机构出具的无保留意见的财务审计报告及会计报表，财务报表至少包括现金流量 表、资产负债表、利润表】 3.3 投标产品的制造商须通过质量ISO9001、环境ISO14001、职业健康体系ISO45001认证。 【提供有效的证书】 3.4 投标人须提供2023年1月1日至投标截止日止（以合同签订时间为准）,签订的30万元及以上的钢管及管件产品 购销合同至少1个。 【提供采购合同、不低于前述金额50％的发票，合同与发票的项目名称须一致】 注：①若投标人开具的发票上未能体现具体项目，需附上税务出具的发票清单（清单上需显示采购项目为钢管 及管件产品）。 ②若提供的合同为年度合同未体现具体金额，但实际供货金额达到30万元及以上，应提供与该合同对应的30万元 及以上的钢管及管件产品发票作为佐证。 3.5 投标人须为所投投标产品制造商，此次所提供的普通防腐钢管及管件必须是自己工厂所制造的产品，不得外 购他人产品。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函及工商部门出具的本产品商标或品牌证明文件】 3.6 投标产品过水部分涉及的涂料须提供行政主管部门出具的有效的“卫生许可网批件”及卫生疾控中心出具的卫 生检测报告。 【提供行政主管部门出具的有效的“卫生许可批件”及卫生疾控中心出具的卫生检测报告】 务 3.5 根据本次采购清单及技术规范的要求，投标人须承诺具备相关的技术手段和措施、保证产品设计使用寿命 20 年以上。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 商 3.6 投标人须承诺保证5年内不得停产同型号的投标产品。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 道 3.7 办事机构和库房【比选人有权对中标人的办事机构及库房进行实地核查，若发现与提供资料不符，将视为提 供虚假资料，按相关规定取消其中标资格，其投标保证金不予退还。】 投标人承诺：收到中标通知书后30日内提供租赁合同或产权证明，并提供重庆库房卫星定位图片。 管 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 【卫星定位图片：手机打开地图，搜索该地址、进行标注，然后截图或者电脑打开地图（地图软件不限），搜 索该地址、选择卫星模国式、进行标注、然后截图均可。】 3.8 符合第五章“技术要求”普通防腐钢管及管件技术要求。 【根据技术要求提供技术响应表，并根据技术条款要求提供对应的检测报告等。】 中 3.9 售后服务承诺【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】： 1）货物交付及付款方式要求，满足第四部分合同协议书第3条及第10条；供货单位应确保产品的及时供应，承诺 因产品供应不及时造成的一切损失均由供货单位负责赔偿。 2）有完整的售后服务方案、培训计划并在合同签订后为比选人免费提供培训服务。 3）售后服务承诺书，满足第四部分合同协议书第11条；承诺质保期后提供2年及以上定期免费巡查、保养计划。 4）承诺接到分派的工单1小时内联系用户约定维修时间，在24小时内处理完毕工单，且让用户满意。若工单超时、 未在规定时间内告知比选人维修时间或工单处理未让用户满意造成返单的，按比选人制度进行处罚。 3.10 投标人承诺不得存在下列情形之一： 1）被人民法院列入失信被执行人名单且在被执行期内； 2）被国家、重庆市（含市或任意区县）有关行政部门行政处罚，且在处罚期限内； 3）投标截止日前两年内（指2024年1月1日至投标截止日止），投标人或其法定代表人被人民法院判定犯行贿罪 的； 4）投标截止日前五年内（指2021年1月1日至投标截止日止），投标人与重庆中法供水有限公司有违约情况或终 止合同情况的。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 3.11 投标截止日前五年内（指2021年1月1日至投标截止日止），投标人无在我司因产品及服务等对公司生产、经 营、安全造成不良影响的记录；若投标人出现过供水通报事项，因产品质量问题对生产、安全造成影响，存在 合同违约等问题，不予参加本次项目投标。 【按照第六章 三、资格审查部分“无不良记录承诺函”提供承诺函，若经验证承诺函不属实，将对中标人作否 决投标处理。】 网 3.12 投标样品要求： 3.12.1 投标人需提供以下规格型号数量的样品： 务 【①钢螺旋焊管 DN219*8 壹件 ②钢制弯头 D108*90°壹件】，提供的样品应满足第五章技术要求规定。样品为 投标人免费提供，管材样品不低于20CM，不计入采购清单内。 3.12.2 投标样品同投标文件一并递交。每件样品上分别标明样品的投标人、生产厂家、品牌、名称、规格、型号等 （格式自拟），投标样品必须密封装箱，且在密封包装外商贴样品一览表（格式自拟），注明提供样品的投标人、 生产厂家、品牌、名称、规格、型号、数量等。 3.12.3 投标人的样品在开标当日递交至样品区（样品区地点：开标当日咨询比选代理机构），中标人的投标样品 不退还，其余投标人的样品在中标公示期满后道5个工作日内退还，如不领取，投标样品按废品处理。 3.12.4 上述对投标样品的密封和标识要求是为便于评标，请投标人积极配合，未按上述要求对投标样品进行密封 和标识的，不作否决投标处理，但由此造成的其他后果由投标人自行承担。 管 3.13 若投标人违反重庆中法供水有限公司《供应商负面清单管理办法》规定且在处罚期内的，按否决投标处理 （评标委员会根据比选公告后附“供应商负面清单”进行评审）。 3.14 本次比选不接受联合体投标。 国 特别说明： （1） 本比选文件要求提供的所有检测报告须为近2年内的检测报告（2024年1月1日-投标截止日），此要求不包 括卫生许可批件及其检测报告。 中 （2） 上述所须提交的相关证明材料复印件均应加盖投标单位法人章并装入投标文件资格审查部分中。上述有一 条不满足则投标文件由评标委员会作否决投标处理。 （3） 比选人有权对投标人提供的以上资料进行核实，若发现存在弄虚作假，取消其投标、中标资格，投标人承 担因此造成的相关责任并赔偿相应损失。 4.比选文件的获取 4.1 投标人于2026年8月18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子版， 以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都视为 投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的一切 后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价，递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，被视为无效。 4.4比选文件每份售价 500 元，售后不退。投标人在递交纸质投标文件时扫描支付，否则比选人拒绝接收其投标文 件。 5.投标文件的递交 5.1电子投标文件递交时间：2026年8月26日14时30分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年8月26日14时00分至14时30分，地点：水务集团招标采购中心（重庆市两江新 区嘉华路36号重庆水务大厦五楼。导航：重庆水务大厦东门）。 5.3 投标截止时间：2026年8月26日14时30分（北京时间）。 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 网 6.发布公告的媒介 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 务 7.联系方式 比 选 人：重庆中法供水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝北区悦来镇悦来水厂 地 址：重庆市两商江新区嘉华路36号重庆水务大厦10楼1018 联 系 人：陈老师 联 系 人：周洲 电 话：023-67585971 电 话：18602396399 道 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3074673.html 管 cqdingjiu 2026.08.21 10:06:59 国 中</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074673.html</t>
-        </is>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
         <v>0</v>
       </c>
@@ -5480,11 +5216,7 @@
           <t>南岸区茶园片区乡镇老旧供水管网更新改造工程更正公告 南岸区茶园片区乡镇老旧供水管网更新改造工程更正公 告 发布日期： 2026年8月18日 网 首次公示日期： 2026年8月14日 更正日期： 2026年8月18日 采购人名称： 重庆市江南城市建设发展（集团）有限公司务 采购人地址： 重庆市南岸区米兰路51号电子信息标准化厂房2号楼 联系人： 赵老师 商 电话： 023-62820331 采购代理机构名称： 重庆多杰数字科技咨询服务有限公司 采购代理机构地址： 重庆市重庆市经开区重庆市经开区长生桥镇江峡路8号13-1幢1楼 道 经办人名称： 李佩奇、戴沛轩、李倩 联系电话： 023-67648437 本项目比选范围修改为：在项目动工前完成水土保持方案审批程序，项目建设过程开展 更正事项： 水土保持监管测工作。 https://www.gec123.com/notices/detail/1665701682723590144 信息来源:https://www.c国hinapipe.net/project/d3074669.html cqdingjiu 2026.08.21 10:07:01 中</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074669.html</t>
-        </is>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
         <v>80</v>
       </c>
@@ -5548,11 +5280,7 @@
           <t>中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部排水钢管询价采购公告 中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 排水钢管询价采购公告 询价编号：ZT1105-XJ-2026-561-1 尊敬的各潜在供应商: 网 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与中铁十一局集团有限公司宜涪高铁重庆段站 前3标项目经理ZT1105-XJ-2026-561-1，排水钢管材料的报价。 一、项目概况 务 中铁十一局集团宜涪高铁3标项目，位于重庆市石柱土家族自治（县）。合同金额28.01亿元，合同工期73个月， 开工日期：2024年12月，竣工日期：2030年12月。主要工程：新方斗山隧道(10660m)、石板坡隧道(4148m)、城北 隧道(3228m)、刘家坪隧道(2077m);刘家店子1号大桥工程(224.096m)、刘家店子2号大桥(232.099m)、城北大 桥(330.241m)、冉家湾大桥(355.245m),采用移动模架和支商架法现浇施工，其中24米移动模架施工6孔；32米支架法 施工5孔，移动模架施工28孔;正线铺无砟道床43.808Km。 二、询价内容 道 本次计划对排水钢管、GG-01材料进行询价，询价内容如下： 询价物资一览表 管 序号 包件号 物资名称 规格型号 计量单位 数量 备注 1 GG-01 排水钢管 Φ200*6m 米 3000 Q235B，壁厚6mm 合计 3000 国 说明：1.表中数量为计划数量，实际采购过程中可能有所调整，最终结算按照实际采购数量结算。 2.收货地点：中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 中 三、技术质量及报价要求 1. 此次排水钢管、GG-01各项技术性能：Q235B 碳素结构钢无缝钢管，符合 GB/T8163 标准。质量需满足甲方项 目部正常使用的要求，保证产品的质量合格，满足试验室检测所有要求，详见技术规格书。 2.报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、结算及付款方式 自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发票认证完成之日起第6个月，支付至本次结算 金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内，累计支付总额不超结算总金额的75%，剩 余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理末次结算后第二年，支付金额应大于等于 尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总额的15%；办理末次结算后第四年，全部 付清）。 五、报价人资格要求 1.营业范围要求：在中华人民共和国境内依法注册、符合项目经营范围，具有询价物资生产或供应经验 的生产商或代理商，并且具有合法有效的营业执照。 2.生产能力要求：生产商须具备询价物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定。代 理商需出具制造厂出具签字盖章的授权函。 3.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8 月至今）国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；需满足排水钢管的相关所 有要求。 4.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年12月至今）企业或企业法定代表人有人民法院生效判决、裁 定认定的行贿犯罪记录的。④ 对纳入国家铁路局“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接 受通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合 作方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 网 5.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 务 ★6.下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 六、报价人需要提供的资料 1.营业执照复印件、法人身份证复印件、开户许可证、授商权委托书、报价表和报价人资格要求中所需的证明资料， 所有资料需加盖公司鲜章。 2.生产厂家资质，产品质量检测报告等质量证明文件。 道 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、询价报名截止时间 管 有意参加本次询价采购的报价人须在铁建云链平台（https://www.crccep.cn）完成供应商注册，并于2026年8月18 日9时00分至2026年8月21日9时00分在网上完成报名工作。 八、询价截止时间 国 凡有意参加本次询价采购的报价人，请于 2026年8月21日14时00分 前提交报价。截止时间前未完成报价文件传 输的，视为放弃报价。 供应商报价必须严格按照《报价表》格式进行报价。 中 九、联系方式 采购组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村71号 采购人名称：中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 地址：重庆市石柱土家族自治县金彰工业园区C区中铁十一局项目部 联系人：罗先生 联系电话：18580400001（提供采购服务支持） 中铁十一局集团有限公司 物资设备集中采购管理中心第五分中心 2026年8月18日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3074654.html cqdingjiu 2026.08.21 10:07:01 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074654.html</t>
-        </is>
-      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
         <v>90</v>
       </c>
@@ -5616,11 +5344,7 @@
           <t>中铁建设集团(重庆)建设有限公司重庆协同创新区供冷供热能源站及配套系统工程冷却塔、分集水器、水板式热 交换机组采购竞价补遗公告二 各 投标单位 ： 根据参加报名的潜在投标单位数量不满足招标方充分竞价要求的情况，此次重庆协同创新区供冷供热能源站及 配套系统工程冷却塔、分集水器、水板式热交换机组采购竞价资格预审报名截止日期将延期至 8月19日（周三） 上午9:00。 特此说明。 网 中铁建设集团（重庆）建设有限公司 2026年8月17日 务 信息来源:https://www.chinapipe.net/project/d3074650.html cqdingjiu 2026.08.21 10:07:01 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074650.html</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
         <v>80</v>
       </c>
@@ -5692,11 +5416,7 @@
           <t>城口县东安及河鱼片区污水管网建设项目(一期)招标计划表 重庆市工程建设项目招标计划表 项 名 目 称城口县东安及河鱼片区污水管网建设项目（一期） 招标 法人 或招 标人城口县生态环境局 名称 （盖 网 章） 项目 批准 文件 及文 号 主 建 内 要 设 容 在 污 城 水 口 处 县 理 东 站 安 1座 镇 ， 等 改 片 建 区 后 新 设 建 计 污 规 水 模 管 20 网 0m 29 3 . / 0 d 0 。 km，其中新建dn110污水管5.80km，dn160污水管2.75km，dn200污水管0.57km，DN300污水干管4.36km，D 务 N400污水干管8.12km，DN200压力管7.4km,以及建设配套泵站2座,化粪池56座，隔油池32座。改扩建 序号 招标项目名称 招标内容 招标方式 招标文件计划发布时间 拟交易场所 合同预估金额(万元) 备注 招 项 标 目1 城 建 口 设 县 项 东 目 安 （ 及 一 河 期 鱼 ） 片区污水管网 工程施工 公开招标 2026-09 城 易 口 中 县 心 公共资源交 3400.00 本 暂 为 计 定 准 划 ， 。 表 最 所 终 列 以 招 实 标 际 项 招 目 标 信 时 息 的 均 信 为 息 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3074602.html 商 cqdingjiu 2026.08.21 10:07:01 道 管 国 中</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074602.html</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
         <v>90</v>
       </c>
@@ -5760,11 +5480,7 @@
           <t>阀门产业园(管网改造)项目招标公告 阀门产业园（管网改造）项目招标公告 1.招标条件 本招标项目 阀门产业园（管网改造）项目已由垫江县发展和改革委员会以垫江发改委发【2022】459 号（批文 名称及编号）批准建设，项目业主为 垫江县丹香建设有限公司，建设资金来自 自筹资金 （资金来源）， 项目出资比例为 100% ，招标人为 垫江县丹香建设有限公司。项目已具备招标条件，现对该项目的施工进 行公开招标，评标办法采用经评审的最低投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 重庆市垫江县高新区县城组团 2.2 项目概况与建设规模： 场平面积800亩；新建厂房10000平方米，并完善相关基础配套设施等；新建道路 务 长4000米，包括道路、综合管网等基础配套设施等。 2.3 本项目工程总投资金额：55000万元 本次招标项目合同估算金额：184.669075万元 商 2.4 招标范围： 包括土石方开挖回填、砼支墩、污水管道安装、检查井砌筑、河堤修复等。具体详见施工图和 工程量清单。 道 2.5 工期要求：建设工期180日历天 缺陷责任期要求：24个月 管 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 国 3.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 中 4.1.1 本次招标要求投标人具备的资质条件： 具备建设行政主管部门颁发的有效的市政公用工程施工总承包叁 级及以上资质 ； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标 不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （垫江县）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（垫江县）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资 源交易监督网、重庆市公共资源交易网（垫江县）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 4.2投标人可在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）本项目招标公告网页下方“我要 提问”栏提出疑问，提问时间从本公告发布至2026-08-24 09:00:00前。 4.3招标人应于2026-08-24 23:59:59前在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-18 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 垫江县丹香建设有限公司 代理机构: 重庆博钰大数据科技有限公司 地 址: 地 址: 重庆市垫江县桂溪街道南内街88号 网 邮 编: 邮 编: 项目负责人: 熊老师 项目负责人: 郭威 电 话: 023-74630098 电 话: 023-74692498 务 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 商 账 号: 账 号: 监督部门: 垫江县发展和改革委员会 电 话: 023-74517161 道 2026年08月18日 信息来源:https://www.chinapipe.net/project/d3074578.html cqdingjiu 2026.08.21 10:07:02 管 国 中</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>https://www.chinapipe.net/project/d3074578.html</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
         <v>90</v>
       </c>

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>省级行政区</t>
+          <t>省份</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -454,45 +454,40 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>县级市</t>
+          <t>城市</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>次级行政区</t>
+          <t>项目内容</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>项目内容</t>
+          <t>合计金额（元）</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>资金情况</t>
+          <t>产品种类</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>产品种类</t>
+          <t>项目详细内容</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>项目详细内容</t>
+          <t>产品用量</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>产品用量</t>
+          <t>匹配程度</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
-        <is>
-          <t>匹配程度</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>匹配关键词</t>
         </is>
@@ -537,34 +532,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>渝中区</t>
+          <t>新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>PVC管,PE管,袖阀管</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PVC管,PE管,袖阀管</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
           <t>中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管 材询比采购公告 中铁十一局集团有限公司建安分公司招标采购中心就中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房 及配套综合交通枢纽工程CQZSG-2标段项目经理部管材组织询比采购，诚邀有意向的合格供应商参与报价。 一、项目概况及询比采购内容 1.1项目概况 网 （1）新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程位于重庆市中心渝中区中部，具体位置为菜园 坝立交桥以西，龙家湾隧道以东，菜袁路以北，王家坡以南。正在建设的地铁18号线贴临站房北侧，地铁26/27 号线从站区地下通过。项目共划分为4个施工标段，CQZSG-1标段：为国铁站房、地铁站台区域；站北路密不可 分的边坡及场坪工程，包含土石方工程和边坡支护工程，不含机电工程，由中铁建设承建。CQZSG-2标段：为 务 枢纽配套工程，地铁区间、西广场、成都局剩余还建，由中铁十一局承建。CQZSG-3标段：地铁区间、CTC、 站场、东广场，由中铁建工承建。CQZSG-4标段：人防车库、铁路自营车场、综合开发生产配套房屋等，由中 铁二局承建。 （2）标段概况：我方负责新建重庆至黔江铁路重庆站站商房及配套综合交通枢纽工程CQZSG-2标段全部施工内容 （简称B区），主要包含：（1）B区投影范围内盖板以下27号线、26号线明挖区间基坑支护、土石方、区间主体 结构及配套防水、综合接地工程（不含砌筑墙体、装饰装修和机电安装工程），以及承轨层以下市政排水 涵DK1+196（196m）和行包通道；（2）轨道交通26号线暗挖隧道预留工程，其中26左线487m，26号右线408m； （3）站北路E、F、H连接匝道工程，其中E匝道道247m、F匝道285.5m、H匝道174m；（4）B区盖板及以上还建房 屋，其中西侧盖板约3.56万㎡，还建房屋等总建筑面积约3.50万㎡。 1.2询比内容 详见拟采购货物一览表 管 二、供应商资格要求 2.1供应商必须是“中国铁建云链平台”注册并通过审核的供应商。 2.2本次询比采购不接受国被列入“《2026年中国铁建合作方警示名录》、《中铁十一局集团有限公司不良行为供 应商名录》、《JD采购网失信名单》（此项核查针对JMRH项目）”中的供应商,不接受近一年内在铁路建设工程 网公布有违法行为记录及物资供应不良记录、被中国铁路总公司限制投标或已清退出铁路市场的供货商（此项 核查针对铁路站房项目），不接受在铁建云链平台被标记的不良行为供应商。 中 2.3供应商在报价时，如是法定代表人签字的需提供法定代表人身份证复印件、如是法人授权代理人签字的需提 供授权委托书及被授权人身份证复印件。 2.4询比响应供应商需提供营业执照复印件。 2.5其它要求：提供样品、每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌 等质量证明文件，甲方凭此报告检验质量。 2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 三、拟采购物资及相关要求 3.1拟采购物资一览表 交 序 物资 型号 单 项目 货 交货日 数量 备注 号 名称 规格 位 名称 地 期 址 重 直 庆 径6:0mm 市 包含车 PVC 批次交 壁 渝 丝、黑 1 （袖 米 7100 货与零 厚4:-45.mm 中 色胶布、 阀管） 星交货 单节 新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 区 管筛、 （具体 长4m CQZSG-2 标段项目经理部 菜 管箍、 以项目 园 堵头等 通知为 坝 一切相 准） 直 网 重 关费用 2 PE管 米 7100 径2:5mm 庆 站 合计 14200 务 3.2技术规格书： 按询比文件第二章项目技术规格书执行 商 3.3结算和付款 3.3.1采购物资报价规则： 道 固定价格。 3.3.2付款方式 （1）货款支付方式：支付方式包管括但不限于银行转账、银行汇票、银行本票、支票、银行承兑汇票、商业承兑 汇票、财务公司票据、供应链票据、其他数字化信用凭证，票据贴息费用由 供货单位 承担。 （2）付款周期：本合同无预付款。甲方在收到乙方提交的合规增值税专用发票，并经税务机关认证通过后次月 支付乙方上月供应期所国供合格物资70%货款，全部货物供应完毕后三个月内付至95%，剩余货款暂时扣留作为质 量保证金，供货完毕后，由乙方提交结算确认单，经甲方审核通过后做最终结算，待所有物资验收合格后12个月 内无息付清。 （3）逾期付款约定：如甲方付款逾期，双方秉持“长期合作，友好往来”原则，在逾期付款行为发生后一年内 中 乙方不向甲方收取逾期付款利息。若一年甲方仍未支付款项，需向乙方支付逾期付款利息，逾期付款利息起算 时间为全部款项到期之日一年后至付清之日，逾期利息的利率为合同订立时中国人民银行授权全国银行间同业 拆借中心公布的一年期贷款市场报价利率(LPR)1倍。 3.4拟采购物资相关的要求 3.4.1本次询比为整体采购，询比响应供应商报价时须写明单价、到站价和运距，报价包含货物制造、运输、装卸、 售后服务等交付采购人使用前所有可能发生的费用，收到报价后不再增补任何费用。 3.4.2交货期：按照采购人规定的期限内分批次运抵交付。 3.4.3供货地点：甲方指定的甲方所属 中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通 枢纽工程CQZSG-2标段项目施工现场。 3.4.4询比响应供应商必须保证产品的质量及售后服务。询比响应供应商提供的货物制造标准及技术规范等，必须 符合最新相关国家标准、部颁标准相关标准和规范的要求，进场提供相关检验检测报告。 3.4.5采购方在确定成交供应商后有权对成交产品的结构、规格做适当调整，调整内容将以工作联系函形式提前发 至供应商。 3.4.6售后服务：本批采购货物若在验收阶段出现不符合规格或质量标准，供应商必须接受退货要求，并在采购人 规定期限内等量补运合格产品，若未按时交付影响采购人使用，供应商必须承担由此给采购单位造成的后续经 济损失。 3.4.7报价方不得虚报各项技术指标，所供货物若不能符合技术要求，成交供应商必须接受全额退还货款，并承担 由此给采购单位造成的经济损失。 3.4.8验收方法及标准 （1）验收依据：询比采购文件、厂家货物技术标准说明及国家有关的质量标准规定，均为验收依据。 （2）货物验收：货物运抵采购人指定交货处后由双方对照采购清单及技术要求进行验收。 （3）其它要求：每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌等质量证 明文件，甲方凭此报告检验质量。 网 （4）2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 四、报价文件递交 务 4.1此次报价供应商需制作电子报价文件，在递交截止时间前线上递交报价文件。 4.2报价文件递交截止时间：2026年08月24日15时00分。 商 4.3报价文件递交地点：中国铁建云链平台（www.crccep.cn），供应商须登录该平台，在报价文件递交截止时间 前完成所有报价文件资料的上传。 五、发布公告的媒介 道 本次询比公告发布媒体:中国招标投标公共服务平台(www.cebpubservice.com)、中国铁建云链平台（www.crccep.cn） 上同时发布。 管 六、联系方式 1.采购组织单位：中铁十一局集团有限公司建安分公司招标采购中心 地 址：湖北省武汉市国武昌区丁字桥路47号 联 系 人：张先生 联系电话：027-87258521 中 电子邮件：2454774350@qq.com 2.采购人：中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 CQZSG-2 标段项 目经理部 地 址：重庆市渝中区菜袁路59号 联 系 人：金先生 联系电话：16607273445 电子邮件：2285445503@qq.com 2026年08月21日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3077066.html cqdingjiu 2026.08.21 10:06:40</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>塑料管不计匹配分</t>
         </is>
@@ -609,34 +599,29 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>璧山区</t>
+          <t>本项目位于璧山区，建设范围为双龙大道以北，璧铜线以东、渝蓉高速以南、玉泉湖（璧南河）以西区域，用地面积约6平方公里。项目建设遵循循序渐进、分期、分块实施原则，采用“总体开发、分步实施”的方式进行建设开发，合作期限8年，包含建设期和运营期（缺陷责任期），其中建设期6年，共分三期实施。第一期实施玉泉湖以西，第二期实施璧南河以西，第三期实施渝蓉高速下道口。项目总投资44亿元，其中建安费28.6亿元，含市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。项目开发建设内容包括片区范围内的基础设施、人才教育基地、水系生态整治、绿化及广场、公共交通场等。本次采购的内容为本项目一期实施的市政道路所需的钢筋混凝土管及管件，预计供货时间为2026年8月至2027年4月。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>本项目位于璧山区，建设范围为双龙大道以北，璧铜线以东、渝蓉高速以南、玉泉湖（璧南河）以西区域，用地面积约6平方公里。项目建设遵循循序渐进、分期、分块实施原则，采用“总体开发、分步实施”的方式进行建设开发，合作期限8年，包含建设期和运营期（缺陷责任期），其中建设期6年，共分三期实施。第一期实施玉泉湖以西，第二期实施璧南河以西，第三期实施渝蓉高速下道口。项目总投资44亿元，其中建安费28.6亿元，含市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。项目开发建设内容包括片区范围内的基础设施、人才教育基地、水系生态整治、绿化及广场、公共交通场等。本次采购的内容为本项目一期实施的市政道路所需的钢筋混凝土管及管件，预计供货时间为2026年8月至2027年4月。</t>
+          <t>项目总投资44亿元，其中建安费28.6亿元，含市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>项目总投资44亿元，其中建安费28.6亿元，含市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。</t>
+          <t>钢筋混凝土管及管件</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>钢筋混凝土管及管件</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>璧山项目钢筋混凝土管询价公告 本项目位于璧山区，建设范围为双龙大道以北，璧铜线以东、渝蓉高速以南、玉泉湖（璧南河）以西区域，用 地面积约6平方公里。项目建设遵循循序渐进、分期、分块实施原则，采用“总体开发、分步实施”的方式进行 建设开发，合作期限8年，包含建设期和运营期（缺陷责任期），其中建设期6年，共分三期实施。第一期实施玉 泉湖以西，第二期实施璧南河以西，第三期实施渝蓉高速下道口。项目总投资44亿元，其中建安费28.6亿元，含 市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。项目开发建设内容包括片区范 围内的基础设施、人才教育基地、水系生态整治、绿化及广场、公共交通场等。本次采购的内容为本项目一期 实施的市政道路所需的钢筋混凝土管及管件，预计供货时间为2026年8月至2027年4月。 网 登录地 mhem&amp;cNh6e0&amp;ce2C2m3s1e71=a64so0d9FAe=0903%e08005206E%6772dm6=%82he29&amp;=cI8p9eeyAs%7t?E%5lB%1iB%a1DetE%c9eweNAi%1iotvB%n/9cE%7.cBe9%ccAiE%p.E%s9%/29址/A%2:：psE%7tAhtD%B8%E%6B%7B%7E%5%78D9%E%5C9%F%9E%7AE%A%1E%9%78%78E%8B%4AD%N&amp;8E%6m657optUa3%6=6290%e3ni51B%5917E%443d6=E%862B%I8eAc%A1iD&amp;88no%tE%4BA%A%4E%7AC%AC%E%4BA%C8%E%8%88AA%E%5A8%A%1E%5B%7A%5E%7A%8B8%E%5B%1%08E%6C9%%98E%9%99%09E%5%58AC%E%5F%8B%8E%8A%5BF%E%9%38A%8EF%BC%%88E%5B9%BD%E%9%99%58EF%BC%%98E%6%59B%0E%5AD%%79E%7BB%F%8E%6B%5E8%E%4BA%A%7E%4B%8A9%E%5B9%AD%E%5C8%BA%E%9%58D8%E%5A%5%79E%9A%1B%9E%7B9%AE%EF%BC%%88E%8A%5BF%E%7%98%78E%5C8%BA%EF%BC%%98E%9A%1B%9E%7B9%AE%E%7=BgB&amp;upC%a=sod&amp;euF%pN=8Flk&amp;cmsusheaE%c7=te%0a9m%6he=8tT&amp;cpS7eeyeE%s9sha%&amp;3c2845d5=pur5A6I&amp;8optUni 信息来源:https://www.chinapipe.net/project/d3077008.html 务 cqdingjiu 2026.08.21 10:06:40 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
         <v>70</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -681,34 +666,29 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>沙坪坝区</t>
+          <t>临水临电材料采购</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>临水临电材料采购</t>
+          <t>采购概算金额：135万元（含税）</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>采购概算金额：135万元（含税）</t>
+          <t>临水临电材料</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>临水临电材料</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
           <t>中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购公告 物资采购 【招标公告】中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购 招标编号：cscec2026081900001246027 项目：重庆市第四人民医院科学城院区建设项目（二期） 发布时间：2026-08-20 17:52:30 报名截止：None 区域：重庆市市辖区沙坪坝区 招标品类：其他类 招标（资格预审）公告 网 中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料采购 采 购 文 件 务 采 购 人： 中国建筑第七工程局有限公司 日 期： 2026年8月 商 目 录 一、响应须知 道 二、评审办法 三、响应注意事项 管 四、响应文件的上传 五．响应文件 六、物资设备合同 国 一、响应须知 【公司总部供应链中心业务监督电话：17516461564】 中 1、工程概况： 工程名称：临水临电材料采购 采购名称： 中国建筑第七工程局有限公司重庆区域暨重庆市第四人民医院科学城院区建设项目 (二期)临水临电 材料采购 采购编号： cscec2026081900001246027 项目地址： 重庆市 工程内容：重庆市第四人民医院科学城院区建设项目 (二期)建筑总用地面积15214.5平方米；总建筑面积65020平 方米，其中住院楼22229.9平方米，实验教学楼8103.6平方米，院内生活楼5830.59平方米，高压氧舱315.53平方米， 地下车库28540.38平方米，以及给排水工程、强电工程、弱电工程、消防工程、暖通工程、总图工程等。为参考。 （说明：描述本工程概况）。最终工程规模及内容以上级部门及采购人确定为准。 采购概算金额：135万元（含税）【采购概算金额视为最高采购限价，响应人响应报价高于最高采购限价的，作 无效响应处理】。 2、采购范围及相关要求： （1）资格审查方式： 资格后审 （2）采购联系人：项目联系人： 修经理 ，电话： 17838218888 ，地址：重庆市 公司联系人： 苟经理 ，电话： 19828530610 ，地址：四川省青白江国际贸易产业园10幢 （3）采购内容： 临水临电材料 （4）工程价款支付： 月结方式，即每月20日结算（遇节假日顺延），次月25日前（结算日后35日历天内），乙 方提供与结算等额增值税专用发票后，支付至前月结算额的70%（遇节假日顺延），最终结算办理完毕6个月后 付至最终结算价款的 97%，剩余3%质保金在质保期满后30日内无息支付。（质保期自全部货物供货完毕且验收 合格日起1年计算）（支付工程款时均应扣除根据采购合同应予扣除的其它金额。） 网 3、响应方式： （1）响应保证金缴纳方式 务 响应保证金采用保证金现金或购买保证金保险（二选一）两种支付方式，支付成功后点击页面【去响应】按钮， 响应人方可正常响应。 方式一：保证金现金缴纳： 商 1、本次采购的响应保证金为/元。 2、保证金收款账户信息请参见云筑网保证金支付页面信息。 道 页面显示账户只对公办理，不接受个人汇款，响应人以响应人基本账户或对公账号转账；响应人转账时务必备注 “交易识别码”（具体操作详见附件《供应商保证金操作手册》或可拨打云筑客服电话：4006-818-555） 方式二：保证金保险缴纳： 管 1、保证金保险可替代保证金，购买后无需再缴纳保证金，响应人可通过“云筑网”购买，响应保险费不退 还；(具体操作详见云筑网上传附件《供应商保证金操作手册》） 2、如发生扣除保证金国情况，保险公司按照保险合同约定向采购单位赔偿相关款项后，保险公司代位取得向响应 单位追偿的权利，响应单位应在规定时间内向保险公司支付相应追偿款。 以下情况可免缴本采购项响应保证金： 中 ①工程局A级分供商。 发生以下情况，响应保证金不予退还： ①响应截止后响应人撤销响应文件的，采购人可以不退还响应保证金。 ②成交人无正当理由不与采购人订立合同，在签订合同时向采购人提出附加条件，或者不按照采购文件要求提 交履约保证金的，取消其成交资格。 （2）采购文件领取事宜：响应人根据采购公告内容领取采购文件，然后根据采购文件要求，进行响应，一经报 价即认为响应人对采购文件已作出实质性响应。 （3）采购文件的澄清与修改 ①采购文件的答疑：如响应人发现采购文件有不清楚的地方或对内容有疑问，要求澄清和解答的，均应在距响 应截止时间2天前向采购人提出答疑，采购人应解答响应人提出的问题。 ②采购人允许响应人在响应截止日期之前对云筑网响应进行修改，但必须在响应截止时间之前完成云筑网响应， 逾期未响应的，则视为无效响应。 （4）（4）响应文件递交事宜 采用云筑网电子响应。 4、评审： （1）评审方法：本次采购拟选出 1 名成交人，区段划分：（如选2个及以上，应明确划分各成交人分供范围及工 程量，成交人按照最终排名顺序享有优先选择权）。采用经评审的（原则上应选择合理低价法），在响应文件 能够满足采购文件实质性要求的响应人中，评审出响应价格合理低价的响应人，但响应价格低于其成本的除外， 具体由采购评审小组在评审会上商定。 （2）响应人有下列情形之一的，取消成交资格： ①成交人在成交后拒签合同； 网 ②成交人未按约定缴纳履约保证金。 采购人： 中国建筑第七工程局有限公司 务 采购时间：2026年8月 二、评 审 办 法 （一）、评审依据 商 1、采购文件 2、响应文件 道 3、评审办法 （二）、评审小组 管 1、评审小组成员：（评审小组应由5人及以上单数评审专家组成，项目负责人必须参与评审。与分供商存在利害 关系的应回避。） 2、小组成员负责根据国评审办法及标准开展评审工作。 3、与响应人有利害关系的，不得进入评审小组。 （三）、评审原则 中 （1）采取经评审的合理低价法：从满足采购文件实质性要求的响应人中，选择合理报价中最低者（不合理低价 除外）为成交分供商。 （四）、初步评审 有效分供商（资审通过并参与有效报价的分供商）数量不少于N（拟选分供商数量）+2家。（询比采购和竞价采 购要求，其他采购方式参照采购管理办法，下同） 出现以下情形的，响应无效。 1、未按要求缴纳响应保证金的。 2、未按要求完成线上响应的。 3、未响应采购文件的实质性要求和条件的。 4、响应人提供虚假资料、隐瞒误导采购的。 5、响应人以他人名义响应或者以其他方式弄虚作假，骗取成交的。 6、响应人ip重复、涉嫌弄虚作假或串通交易行为的。 7、采购文件或法律规定的其它情形。 （五）、详细评审 1、评审：以云筑网填报数据为准。 2、排名：对进入详细评审的响应人响应报价进行汇总后，按响应报价由低到高进行综合排名。 若出现响应人响应报价相同时，按其年度供应商考评评级高低优先排序，若仍相同，可再选用以下进行情况排序 （根据情况自行排序）。 网 ①近三年工抵房金额； ②具有绿色节能环保材料设备； 务 ③云筑网显示的该响应人响应时间等。 1）、采购概算金额（见采购公告）视为最高采购限价，响应人响应报价高于采购概算金额的，作无效响应处理。 响应人响应报价低于成本的，经评审小组评审确定后，作无效响应处理。 商 2）、在评审过程中，评审小组可以要求响应人对所提交的响应文件中含义不明确、表述不一致或者有明显笔误、 文字和计算错误的内容作出必要的澄清、说明或者补正，该澄清、说明和补正属于响应文件的组成部分，须经 采购授权代表书面署名确认，不得改变响应文件的实质性内容，且须经评审小组一致同意。评审小组不接受响 应人主动提出的澄清、说明或补正。 道 3）、经以上评审，有效响应人数量仍须满足“有效分供商（资审通过并参与有效报价的分供商）数量不少于N （拟选分供商数量）+2家”，否则本次采购按废止处理（成交单位数量为“N”）。 管 4）、废止后重新发起采购，需经调查核实后，视具体调查核实结果决定是否准予原响应人参与新发起的采购响 应。 （六）、确定成交候选单位 国 多轮次公开竞争报价：（说明：如需要(应视采购标的物及响应报价情况)进行多轮次公开竞争报价的，应按详细 评审的排名顺序确定一定比例(首轮最高价不得进入二次报价)的有效响应人进行后续轮次报价，总轮次不超过3轮 （竞价采购）。 中 报价规则：响应人提交的首轮报价作为后续报价基准；后续轮次总报价不得高于前轮报价，若设置参考价，单 项报价不得高于参考单价。否则该轮报价无效；最终轮次报价提交后不得撤回或修改（以系统记录为准）。 晋级规则：每轮报价截止后，采购人按报价从低到高排序；出现相同报价时，依次比较：（1）资源库等级；（2） （参考上述第五条第2点，以优质优价为原则，优先选用具备相应能力的本级及上级A级分供商） 成交机制：最终按末轮有效报价的从低到高排序；当最低报价出现多家时，可自主决定成交人。 最终按照排名顺序拟定有效响应人作为成交候选单位，具体成交候选单位数量由评审小组根据采购文件确定。 成交候选单位经审批后作为最终成交单位。 成交候选人放弃成交、因不可抗力不能履行合同、不按照采购文件要求提交履约保证金，或者被查实存在影响 成交结果的违法行为等情形，不符合成交条件的，采购人可以按照评审小组提出的成交候选人名单排序依次确 定其他成交候选人为成交人，也可以重新采购。 （七）、其他事项 1、因响应人原因造成其自身未响应采购要求及未能成交等情况，由响应人自行承担相应责任及损失，与采购人 无关。 2、本采购文件中的合同范本即实际签约合同范本，双方均不允许以任何理由更改合同内容。 三、响应注意事项 1、若响应人对采购文件中之任何内容有不理解之处，须立即联系采购人，以便在响应截止日期之前能予以解释。 2、采购人不保证一定要接受最低价成交，不论响应结果如何响应人的响应文件均不退回，且不对未成交单位做 任何解释。 3、响应人在响应之前，对本采购项的分包条件均已了解，响应即认为已详细了解。 4、采购人对响应人进行考察时，响应人应提供便利条件。 5、本次采购的最终解释权在采购人。 网 四、响应文件的上传 1需上传的响应附件（未上传视为不响应采购文件）有： 务 1.1.《响应函》 1.2.《响应承诺函》 1.3.法定代表人身份证明（格式）； 商 1.4.授权委托书（格式）（若若为法定代表人响应则可不提供）； 1.5.报价清单明细（盖章版） 道 1.6金融工具支付方式及优惠措施 1.7.响应保证金汇款凭证扫描件或免缴证明（云筑网平台缴纳的无须提供）（若需） 管 六、响应文件格式 一、封面（格式） 国 中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料采购响应文件 响应内容：临水临电材料采购 中 （编号：cscec2026081900001246027） 响应人：（盖章） 法定代表人 或授权代理人（签字盖章）： 响 应 函 致：中国建筑第七工程局有限公司 1、经勘察了本工程现场,并仔细研究了响应须知、合同协议条款、合同条件、采购图纸、工程规范、地质勘察报 告、工程量清单、响应答疑、及其他有关采购文件后，我公司愿以我公司云筑网所上传的含税综合单价，并按 采购文件所要求的条件承包在规定工期内完成重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料的施 工、竣工并补充其任何缺陷。 2、我公司保证本工程质量必须：达到符合工程所需材料质量验收标准、设计、合同及有关工程施工及验收规范 的要求标准。 3、一旦我公司的云筑网响应内容被接纳，我公司将在收到成交通知书后按贵公司的要求开始施工，我公司保证 于承诺的工期内或双方议定的工期内完成并交付本合同中规定的整项工程。 4、我公司同意在本区段的正式建设工程施工合同签署之前，云筑网响应将始终对我公司具有约束力，并可随时 被贵公司接受。 5、我公司知道：云筑网报价及云筑网响应的其他部分构成我公司向贵公司的要约，贵公司如发出成交通知书则 成交通知书及云筑网响应、采购文件将构成约束我们双方的合同，如果我公司在接到成交通知书后，没有按贵 公司要求的时间签署正式合同或坚持提出附加条件，那么我公司同意贵公司有权另选成交单位并向我公司追讨 有关损失。 6、我公司知道，贵公司并无义务必须接受所收到的价格最低的或其他任何响应书。 7、云筑网响应内容已考虑了贵公司向我公司发出的关于采购文件的相关答疑，网补充通知（如有的话） 8、云筑网响应效力优先于同时提交的任何响应文件的其他组成部分。 响应人： （盖章） 务 日 期： 年 月 日 响应承诺书 商 致：中国建筑第七工程局有限公司 我系有幸参与贵公司 重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料的响应，我公司经研究决定， 在此郑重承诺： 道 1、我公司在响应过程中已完全了解并掌握了采购内容、合同条件及施工现场等情况。确保云筑网响应报价操作 为本公司自己操作，如响应后发生非本公司操作的情形，本公司承担相应违约责任。 管 2、我公司已经详细阅读该采购文件所有内容，充分领会并完全接受采购文件所述响应人应尽的实质性的权利与 义务。我公司保证不会对采购文件产生不利于双方友好合作关系和将增加贵公司采购范围内经济支出的重大误 解。 3、我公司确认，贵公国司发出的采购文件所有内容为不可割裂的整体。 4、我公司保证成交后不会对成交价格提出任何异议，更不会以任何理由要求贵公司针对成交范围的价款要求额 外补偿。不会以不了解采购文件、合同文件为由或曲解、片面理解采购文件、合同文件或割裂采购文件、合同 文件，断章取义，向贵公司提出任何补偿要求。 中 5、在本合同的履约过程中，如因我公司的供货或质量原因导致贵司损失，我公司保证承担因此而给贵公司带来 的所有经济上的损失。 6、我公司将本工程作为重点项目对待，保证不会出现供货能力不能满足施工需要的现象。为满足本工程业主及 贵公司在质量、进度、安全、环保上的要求，我公司将采取一切措施保证物资设备生产、供应、租赁，运输等 均满足贵公司的要求，并保证不会因此而向贵公司提出增加任何补偿要求。 7、我公司承诺无论本工程最终的成本状况如何，将不会违背合同基本原则而向贵公司要求增加或补偿合同文件 约定以外的任何费用。 8、我公司认为，贵公司可以就物资设备采购数量或租赁时长进行调整，并且此种调整不构成我公司的索赔理由。 响应人：（盖章） 法定代表人或 其授权代理人：（签字或盖章） 日 期： 年 月 日 响应人名称：【全称】 单位性质： 地 址： 成立时间：年月日 经营期限： 姓名：性别：年龄：职务：系（响应人名称）的法定代表人。 网 特此证明。 响应人：（盖单位章） 务 年月日 授权委托书 商 本人（姓名）系（响应人名称）的法定代表人，现委托（姓名）为我方代理人。代理人根据授权，以我方名义 签署、澄清、说明、补正、递交、撤回、修改中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建 设项目 (二期)临水临电材料采购（采购项目名称）响应文件、签订合同和处理有关事宜，其法律后果由我方承担。 道 委托期限：本授权书于年月日签字生效，至本次采购期结束为止。授权期限内无特殊情况不变更合法授权代理 人。 代理人无权转委托。 管 特此声明。 响应人：（盖章） 国 法定代表人：（签字） 身份证号： 中 授权代理人：（签字） 身份证号： 联系方式： 日期： 年 月 日 备注：法定代表人和委托代理人必须在授权书上亲笔签名，不得使用印章、签名章或其他电子制版签名,同时附 法定代表人和授权代理人身份证复印件（正反面，加盖公章） 报价清单明细 不 含 含 不含 计量单 税 税 含税 备 序号 材料名称 规格型号 数量 税 税合 税额 位 率 单 合价 注 单 价 价 价 1 镀锌钢管 DN100*4.0 米 500 2 镀锌钢管 DN150*4.5 米 250 3 镀锌钢管 DN65*3.25 米 650 4 镀锌钢管 DN50*3.25 米 800 5 PE管 DN100*1.6MPA 米 450 6 PPR管 DN50*1.6MPA 米 400 7 闸阀 DN100 个 22 8 闸阀 DN250 个 10 9 截止阀 DN50 个 42 网 10 截止阀 DN25 个 60 11 蝶阀 DN100 个 6 12 消防箱 800×1000×250mm 台 20 务 功率30kw,扬程144m，流 13 加压泵（变频控制） 台 1 量55m/h 14 橡塑保温材料 DN100*20mm 米 620 商 15 橡塑保温材料 DN150*30mm 米 280 16 橡塑保温材料 DN65*20mm 米 700 17 压线钳 CO-1000 个 1 道 18 污水泵 380V4KW=25米 台 12 19 污水泵 380V5KW=30米 台 7 20 热熔机 63-160 台 1 管 21 电工胶布 / 卷 200 22 高压自粘带 / 卷 120 23 水泵控制箱 / 个 8 国 24 PE聚乙烯管 DE110*1.6MPA m 560 25 PE聚乙烯管 DE75*1.6MPA m 420 26 PE聚乙烯管 DE63*1.6MPA m 480 中 27 PE聚乙烯管 DE32*1.6MPA m 750 28 PE球阀 DN25 个 6 29 PE球阀 DN50 个 6 30 PE球阀 DN100 个 5 31 镀锌桥架 200*100*1.2mm 米 1200 32 PVC排水管 DE300*5.0 m 180 33 PVC排水管 DE200*5.0 m 380 34 PVC排水管 DE160*4.0 m 486 35 PVC排水管 De110*4.0 米 560 36 PVC排水管 DE75*3.0 m 420 37 PVC排水管 DE50*2.0 m 660 38 PVC排水管 DE32*2.0 m 380 39 PPR给水管 De90*1.6MPA 米 440 40 PPR给水管 DE75*1.6MPA 米 360 41 PPR给水管 DE63*1.6MPA 米 450 42 PPR给水管 De50*1.6MPA 米 435 43 PPR给水管 De40*1.6MPA 米 315 44 PPR给水管 DE32*1.6MPA 米 520 45 PPR给水管 De25*1.6MPA 米 680 46 PPR给水管 De20*1.6MPA 米 370 47 橡塑保温板 平板×20mm m 15 48 橡塑保温板 平板×30mm m 28 49 保温胶 3公斤/桶 桶 25 网 50 PPR给水管接头 De75 个 30 51 PPR给水管弯头 De75 个 20 52 PPR给水管三通 De75 个 22 务 53 PPR给水管接头 De63 个 20 54 PPR给水管弯头 De63 个 15 55 PPR给水管三通 De63 个 15 商 56 PPR给水管接头 De50 个 17 57 PPR给水管弯头 De50 个 22 58 PPR给水管三通 De50 个 17 道 59 PPR给水管接头 De40 个 14 60 PPR给水管弯头 De40 个 22 61 PPR给水管三通 De40 个 17 管 62 PPR给水管接头 De32 个 14 63 PPR给水管弯头 De32 个 14 64 PPR给水管三通 De32 个 17 国 65 PPR给水管接头 De25 个 22 66 PPR给水管弯头 De25 个 17 67 PPR给水管三通 De25 个 14 中 68 PPR给水管接头 De20 个 25 69 PPR给水管弯头 De20 个 17 70 PPR给水管三通 De20 个 22 71 PPR内丝直接 De25 个 17 72 PPR内丝直接 De20 个 84 73 球墨铸铁井盖 700*800*40T 套 22 74 球墨铸铁井盖 1000*1000*20T 套 20 75 球墨铸铁雨箅子 400*600*30 块 1750 76 球墨铸铁雨箅子 350*500*30 块 1200 77 高分子成品排水沟 300*300*1000 米 850 78 高压洗车机 380v/3KW 套 5 79 高压洗车机 380v/5.5KW 套 3 80 HDPE双壁波纹管 DN300 米 360 81 HDPE双壁波纹管 DN200 米 410 82 HDPE双壁波纹管 DN400 米 340 83 HDPE双壁波纹管 DN800 米 260 84 玻璃钢化粪池 20m 个 1 85 玻璃钢化粪池 50m 个 1 86 不锈钢消防水箱 12m 个 1 87 一级配电柜 2000*1200*500*630A 台 1 88 二级配电柜 800*600*210*250A 台 8 89 铜芯电缆线 YC3*16+2*10 米 60 90 铜芯电缆线 YC3*10+2*6 米 70 网 91 铜芯电缆线 YC3*6+2*4 米 70 92 铜芯电缆线 YC3*10 米 100 93 铜芯电缆线 YC3*6 米 100 务 94 铜芯电缆线 YC3*4 米 100 95 铜芯电缆线 YC3*2.5+2*1.5 米 100 96 聚录乙烯铝芯电缆 YJLV-22-4*185+1*95 米 50 商 97 聚录乙烯铝芯电缆 YJLY-4*25+1*16 米 90 98 聚录乙烯铝芯电缆 YJLY-4*35+1*16 米 100 99 聚录乙烯铝芯电缆 YJY-4*50+1*25 米 90 道 100 聚录乙烯铝芯电缆 YJLY-4*70+1*35 米 72 101 网线 Cat5e 米 100 102 铜芯电线 BV-2.5 米 400 管 103 铜芯电线 BV-4 米 300 104 铜芯电线 BV-6 米 200 105 铝芯电缆线 YJLV3*10 米 100 国 106 透明塑壳断路器 3P32A 米 34 107 透明塑壳断路器 3P63A 米 28 108 透明塑壳断路器 4P100A 米 26 中 109 透明塑壳断路器 4P160A 米 22 110 透明塑壳断路器 4P250A 米 20 111 透明塑壳断路器 4P400A 米 8 112 低压铝芯电缆 YJLV-4*300+1 米 20 113 低压铝芯电缆 YJLV-4*150+1 米 50 114 铝芯铠装电缆 YJLV-22-4*95+1*50 米 60 115 铜铝线鼻 300mm2 个 20 116 铜铝线鼻 150mm2 个 36 117 铜铝线鼻 95mm2 个 24 118 铜铝线鼻 50mm2 个 20 合计 0.00 0.00 0.00 1、综合单价：包括但不限于材料费、保险费、风险费、包装费、装车费、过桥过路费、管理费、检验费、技术 指导费、货到工地负责卸货堆入至指定地点等所有费用。本合同单价一次包死，在合同履行过程中不再做任何 调整。本合同的总价为暂估价，用方有权调整合同中材料计划或材料数量，材料数量和规格的调整，不影响本 合同单价及其他条款的执行。 2、计量方式：查看检测报告合格证，以实际验收通过数量计量。 3、付款比例：月结方式，即每月20日结算（遇节假日顺延），次月25日前（结算日后35日历天内），乙方提供 与结算等额增值税专用发票后，支付前月结算额的70%（遇节假日顺延）；供货完毕，验收合格，材料相关资料 （包括不限于合格证、质检报告等）移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%；剩余3% 质保金在质保期满后30日内无息支付。质保期自全部货物供货完毕且竣工验收合格日起1年计算，支付工程款时 均应扣除根据采购合同应予扣除的其它金额。 4、付款方式： （1）现金支付:采用现金转账的模式支付； （2）非现金支付:包括不限于(1)金融工具支付:银行承兑汇票，商业承兑汇票，网应付账款保理，银行信用证，中 建财务公司承兑汇票。(2)工抵房支付。 5、响应报价表中所列数量的变动，丝毫不会降低或影响合同条款的效力。 务 6、整个合同执行期内，若遇市场价格下行，甲方有权做出价格调整，乙方应接受并重新签订补充协议确认价格。 若乙方无法接受新的低价，甲方有权重新选择其他能够响应该价格的供应商进行供货，乙方无条件同意。 响应人（加盖公章）： 商 法定代表人或授权代理人（签字）： 日 期：年月 道 金融工具支付方式及优惠措施 管 1、金融工具支付： 可接受金融工具支付比例累计为%，其中： ① 可接受的国银行承兑汇票比例%；贴息响应人自行承担。 ② 可接受的商业承兑汇票比例%；贴息响应人自行承担。 金融支付 ③ 可接受的应付账款保理比例 %；贴息响应人自行承担。 中④ 可接受的银行信用证比例%；贴息响应人自行承担。 ⑤ 可接受的中建财务公司承兑汇票比例为%；贴息响应人自行承担。 2、资产支付 资产支付 可接受比例为合同额的%。 3、优惠付款比例：按按照采购文件的付款比例，我方可优惠%。 4、如响应人提供其他由于采购条件的承诺，请逐项列示。 响应人（加盖公章）： 法定代表人或授权代理人（签字）： 日 期：年月 响应保证金汇款凭证扫描件或免缴证明（若需） 响应人（加盖公章）： 法定代表人或授权代理人（签字）： 日 期：年月 六、物资设备采购合同 合同编号：______________________ 物资采购与供应合同 （通用） 项目名称：【 重庆市第四人民医院科学城院区建设项目 (二期) 】 网 甲 方：【 】 乙 方：【 】 务 签订时间：【 】 签订地点：【 】 商 目录 1. 工程概况及供货范围 道 2. 企业性质 3. 合同价款 2 管 4. 质量要求 5. 供货时间及地点 6. 交货与验收 国 7. 结算方式及时间 8. 支付 中 9. 发票 10. 双方责任 11. 不可抗力 12. 权利瑕疵 13. 保密 14. 违约与赔偿 15. 联络与送达 16. 争议解决 17. 补充条款 18. 其他 物资采购与供应合同 甲方（买受人）：【中建七局安装工程有限公司 】 乙方（出卖人）：【 】 根据《中华人民共和国民法典》及有关规定，为明确双方权利、义务和责任，经双方协商一致，就甲方承包的 【高新LIVE（咸阳高新区租赁住房）建设项目】工程所用【 水电管材】采购与供应事宜签订本合同条款，愿共 同遵守。 1. 网 1.1 工程名称：【高新LIVE（咸阳高新区租赁住房）建设项目 】 1.2 工程地点：【陕西省咸阳市星火大道】 务 本合同供货范围为：【高新LIVE（咸阳高新区租赁住房）建设项目 】的【水电管材】供应（以下简称为“本合 同标的物”）。 1.3本合同标的物的数量为暂定量，乙方按附件1《计划采商购与供应物资清单》所列品种和规格供货，最终以经甲 方验收合格的实际数量为准。 2. 企业性质 道 乙方企业规模：大型 □中型 □小型 □微型企业 以上企业规模由乙方根据（1）工信部官网：“中小企业规模类型测试网址https://baosong.miit.gov.cn/ScaleTest。 （2）工信部微信小程序：“中小企业规模类型自测”两种渠道自测确定。 管 乙方应保证其企业规模的真实性。如乙方提供信息不实，经甲方查证后，将按照《中国建筑股份有限公司分供 商资源管理办法》中的《不良行为分供商禁用处理标准》第19项对乙方严格实施禁用管理。 合同价款 国 3.1 本合同采用第【 】种价格形式： （1）固定综合单价包干，价格不可调整。 中 3.2 本合同价款为各项货款之和，合同价款（含增值税）暂定：（大写）【 】（￥【 】元），其中不含税价款为 （大写）【 】（￥【 】元），增值税为（大写）【 】（￥【 】元），税率为【 】%。最终甲乙双方以实际验收 的数量结算。 3.3 本合同约定的不含税价款不因国家税率变化而变化，在合同履行期间，如遇国家的税率调整，则价税合计的 合同价款或货款相应调整，以开具发票时间为准。 3.4 本合同不含税价款仅指不包含增值税，除增值税外的其他全部税费（包括但不限于城市建设维护税、教育费 附加及地方教育费附加、个人所得税、合同印花税、企业所得税、车船使用税以及国家和地方规定的所有税费） 均包含在不含税价款中。 3.5 本合同标的物的计价、结算和支付货币均为人民币。 3.6 本合同标的物的计量单位为中华人民共和国法定公制计量单位（除技术规范标准另有规定外）。 3.7 本合同标的物的不含税单价，指运抵本工程施工现场甲方指定交货地点的综合单价，包括但不限于货物费、 加工费、包装费、人工搬运费（由乙方自行协调，甲方只进行指定场地和材料验收工作）、运输费、出厂检测费 （包括但不限于到场后的第三方检测费用）、装卸费、码放费、现场倒运费用，保险费、仓储费、驻厂监造费、 运输造成的道路污染的清理及维修费用、除增值税以外的税金、乙方合理的利润、管理费、市场价格波动带来 的风险、向有关部门缴纳的各项费用以及政策性文件所规定的各项应有费用等乙方履行本合同规定义务的全部 价款与费税。除本合同第3.1条约定的因素外，不含税单价不因政府政策变动、市场环境改变、税率调整等而调 整。 3.8 除合同条款另有约定外，本合同标的物的不含税单价已包含专利、专有技术以及技术秘密的使用费。 质量要求 4.1 乙方应在交货同时向甲方提供本合同标的物制造商出具的书面质量保证书。 4.2 本合同所采购与供应的物资，应符合现行中华人民共和国国家标准及行业或地方标准，行业标准或地方标准 高于国家标准的，执行行业标准或地方标准。各项技术性能指标经本工程所在地具有相应检测资质的专业机构 或单位检测中心检验必须符合相关标准要求。合同执行过程中，若出现新的国家标准、行业标准、地方标准， 则以更新后的标准为准。 网 4.3 乙方的物资供应与管理应符合国家有关环保法律、法规和甲方ISO14001环境体系及OHSMS18001职业安全健康 管理体系标准。 4.4 本合同标的物的质量保证期为最后一批货物验收合格之日起满【180】日。 务 4.5在合同履行期及质量保证期内，乙方无条件地向甲方提供缺陷产品的免费维修、更换等服务。针对甲方提出 的书面要求，乙方必须在3日内给予书面答复。如有必要，乙方在3日内指派专人到现场解决，因此产生的所有费 用均由乙方承担。 商 4.6 如缺陷产品经乙方进行免费维修和更换后仍无法达到甲方要求的质量标准时，甲方有权终止合同。终止合同 后，乙方需向甲方赔偿由于乙方问题造成的损失及其连带损失。如乙方借故推脱或拒绝甲方提出的维修、更换 等服务请求，甲方有权自行采购同等货物替代或委托第三方维修，实际发生的更换等或维修费用，从应支付给 乙方的任一期货款中扣除，并保留进一步索赔道的权利，乙方不得提出异议。维修或更换物资的质量保证期相应 延长6个月。 4.7 如因乙方产品质量导致工程出现质量问题，由此给甲方造成的一切损失由乙方承担。 管 4.8 其他质量要求：/。 供货时间及地点 5.1 供货方式：□按批次国供货 □一次性供货 5.2 通知方式：供货时间及数量以甲方书面通知为准，甲方可以选择通过电子邮件、微信、QQ等方式将物资采购 订单发送至乙方。紧急情况下，甲方可口头通知乙方发货，手续后补，乙方应予以确认。 中 5.3 供货地点：乙方负责送货至施工现场，卸至甲方指定的卸货地点【高新LIVE（咸阳高新区租赁住房）建设项 目】。乙方不得雇佣甲方在班人员及设备装卸货物。运输、装卸过程中发生的安全事故责任，乙方自行承担。 5.4 根据工程项目施工需要，甲方对所采购物资的数量和送货时间如有变更，应及时书面通知乙方，乙方按变更 后的数量和送货时间供货，货物单价不因货物数量和送货时间的变更而变化。 5.5 乙方应确保已经知悉货物运输的交通状况、交货卸车环境以及政府的交通管制政策措施，不得以此等理由要 求增加费用、减免责任、提出索赔、要求延长或变更供货期限。 交货与验收 6.1交货 6.1.1 除另有规定和协议要求外，乙方提供的全部货物须采用国家、企业、行业标准要求包装，具有足够的强度 及安全起吊标识，保证货物能够经受多次搬运、装卸、长途及短途运输的要求，并采取良好的防潮、防震、防 腐蚀、防爆及防止其它损坏的必要保措施。包装物的回收按以下第【 2】项方式执行：（1）不回收；（2）包装 物由乙方在交货时回收；（3）其它方式：【 /】。 6.1.2 装箱单应注明货物的名称、规格、型号、数量、质量、生产商、发货地、供货人、收货人、交货地、承运 人等，并在显著位置标明装卸警示标志。 6.1.3 乙方运抵甲方指定现场的物资，交货单据上应详细列明当次供应物资的名称、品牌、产地、生产厂家、规 格型号、计量单位、数量。 6.1.4 乙方应向甲方提交本合同标的物的技术文件，包括材质报告（物资质量检验报告）和出厂检验报告（合格 证），以及按照工程竣工验收规定及甲方要求，提供所有相关符合要求的资料。 6.1.5 乙方在首次供货前需提供样品，乙方须在样品和样品资料上加盖单位公章，样品经双方指定人员签字确认 后予以封存，在提交文件上注明与合同文件约定不同之处。 6.2.1 乙方须随货提供载有数量、规格等内容的送货单，否则，甲方有权对本批次货物不予验收确认，由此导致 的违约责任由乙方承担。乙方送货到交货地点后，甲方指定验收人员对产品的规格、尺寸偏差、外观、数量及 质量证明资料等进行查验。若产品的以上各项符合合同约定，则双方人员共同在收领单上签字确认。 6.2.2 甲乙双方在交货现场以 【 点数】方式进行数量验收。乙方应对在甲方工地网现场的验收数据进行确认。 6.2.3 进行数量验收的同时，甲方可以按照封存样品标准进行尺寸、外观质量验收，尺寸和外观质量符合要求方 可卸车，否则不得卸车。 务 6.2.4 外观质量符合要求的， 甲方可打开包装进行质量、性能检验或及时按规定取样送本工程所在地具有相应检 测资质的专业机构或单位进行检测。抽检未发现不合格产品不视为乙方供应产品全部合格，甲方有权随时将乙 方所供货物送到有检测资质的第三方进行检测。如检测合格，检测费用由甲方承担；如检测不合格，甲方可全 部退货，检测费用由乙方承担，并承担由此给甲方造成的一切损失。 商 6.2.5 甲方及工程监理（业主）的收货验收仅作为感观合格的依据，不能免除乙方对货物品牌真实性、内在质量 及使用功能所负的责任。如甲方、本工程建设单位或监理单位提出异议，乙方需参照有关标准规范，结合现场 情况解决。 道 6.2.6 若发现不合格产品，乙方必须及时（接到甲方通知后【 3】小时内），从甲方项目现场运走不合格品，甲方 不负有保管义务，不对不合格产品的损毁灭失承担人和责任，若超过【 12】小时乙方仍未运走的，甲方收取场 地租赁费（根据货物合理确定）【 1.0】万元/天，且不合格品的储存、装卸、运输等所有相关费用及风险由乙方 承担。 管 6.2.7 如因乙方产品问题造成甲方工期、质量、劳务等损失，全部责任均由乙方承担。乙方对甲方所提出的质量 问题有不同意见的，双方可送至双方共同选定的具有法定资质的检测机构检测，所产生的费用及责任由责任方 承担。 国 6.2.8 本合同的标的物所有权自【卸货完毕且经甲方验收合格】起转移。 结算方式及时间 中 7.1 过程结算：甲乙双方按以下第【 1】条约定的时间办理过程结算。 （1）每月20日结算（遇节假日顺延），每季度最后一个月的25日后支付当期货款额的70%（遇节假日顺延，乙 方提供与结算等额增值税专用发票），供货完毕，验收合格，材料相关资料（包括不限于合格证、质检报告等） 移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%，余款3%（不计息）待质保期满无质量问题后 无息付清。（质保期为供货完毕且验收合格后2年）（支付工程款时均应扣除根据采购合同应予扣除的其它金额。 ）； （2）按节点结算，具体结算节点为：【 】。 7.2 最终结算：全部供货完毕后【 6个月后】日内，乙方应向甲方提供完整的结算资料，甲方在收到完整的结算 资料后【 5 】日内进行审核。 7.3 结算依据：包括但不限于物资采购与供应合同、乙方合法等额有效增值税发票（含税务机关代开）、产品合 格报告、项目授权人员验收单、送货单等有效材料。 7.4 乙方未按照约定的期限和甲方要求提供结算资料，或未委派专人与甲方办理结算，或提供的结算资料不齐全、 提供虚假资料的，经甲方催告后10个工作日内，乙方仍未按要求提供结算资料的，甲方有权不予办理结算并暂停 支付材料款，同时甲方可根据本合同、现有结算资料及乙方实际履约情况单方办理结算，确定结算价格，结算 对甲乙双方具有法律约束力。 支付 支付/√不支付预付款 8.1.1 预付款金额（或占合同价款的比例）：【 /】。 8.1.2 预付款的支付时间：【 /】，在乙方提交等额银行保函及增值税专用发票后，甲方向乙方支付预付款。 8.1.3 扣回预付款的时间、比例：【 /】。 8.1.4 乙方提交的银行保函有效期至预付款抵扣完为止，若预付款保函到期日前，预付款无法抵扣完毕，则乙方 应于预付款保函到期日前不少于10日及时办理保函延期，否则甲方有权暂停支付未抵扣完部分的货款。 网 / 8.2.1 货款支付，按以下第【 3】条约定的时间和比例支付。 务 （1）月度付款：甲方在次月的25日支付上月月度结算货款的【 / 】%。双方办理完毕最终结算后【 / 】（条款说 明：建议不超过60日，如超过60日，应当按照行业规范、交易习惯合理约定付款期限并及时支付款项）个日历天 内付至总结算货款（且不超含税合同价款）的【 / 】%。余款【 /】%作为质保金，在质保期届满后28日内付清； 或由乙方提供等同余款金额的质保保函（仅接受金融机构出具的无条件见索即付保函，质保保函格式以开函金 融机构标准格式为准），则双方办理完毕最终结算后【 /商】（条款说明：建议不超过60日，如超过60日，应当按 照行业规范、交易习惯合理约定付款期限并及时支付款项）个日历天内付清。 （2）节点付款：按节点支付（条款说明：此处需具体罗列每个付款节点及各节点对应的付款比例，节点结算完 成后约定支付期限应在60日内，如超过60日，道应当按照行业规范、交易习惯合理约定付款期限并及时支付款项）， 余款【 /】作为质保金，在质保期满后28日内付清，或由乙方提供等同余款金额的质保保函（仅接受金融机构出 具的无条件见索即付保函，质保保函格式以开函金融机构标准格式为准），则在最后一个付款节点付清。每次 付款前乙方应提供结算值【100%】的发票，否则甲方可拒绝付款。 管 （3）其他支付方式【每月20日结算（遇节假日顺延），每季度最后一个月的25日后支付当期货款额的70%（遇 节假日顺延，乙方提供与结算等额增值税专用发票），供货完毕，验收合格，材料相关资料（包括不限于合格 证、质检报告等）移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%，余款3%（不计息）待质保 期满无质量问题后无息付清。（质保期为供货完毕且验收合格后2年）（支付工程款时均应扣除根据采购合同应 予扣除的其它金额。）国】 （4）甲方依合同约定确认的进度款仅为中期付款依据，不作为竣工结算的依据，且不视为对因变更调整的合同 价款、索赔的价款或费用以及其他约定的追加合同价款的确认。 中 8.2.2 甲乙双方协商一致同意本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保理、商业承兑汇票、 国内信用证、应收账款电子凭证、抵房抵款及其他】常规支付方式的付款方式。付款过程中产生的贴息费用及 手续费由【乙方】承担。乙方委托专职收款人办理收付款业务，收款人必须取得授权 8.3 乙方指定以下帐户为收款帐户，甲方所有款项均需通过该帐户支付。如乙方变更收款帐户，应提前十五天以 上书面通知甲方，否则造成资金的损失由乙方自行承担，与甲方无关。 账户名：【 】 开户行：【 】 账 号：【 】 发票 9.1 乙方在向甲方请款时，应根据甲方确认的应支付金额开具合法、有效、完整、准确的增值税（请勾选：□专 用□普通）发票，计税方法为【□一般计税方法 □简易计税方法】，双方发票信息如下： 名 称 纳税人身份 □一般纳税人 □小规模纳税人（请勾选） 甲方 纳税人识别号 地 址、电 话 开户行及账号 名 称 纳税人身份 □一般纳税人 □小规模纳税人（请勾选） 网 纳税人识别号 乙方 地 址、电 话 开户行及账号 务 联 行 号 该开户行为乙方在税务局已备案的乙方单位账户。 9.2 任何一方如上述信息发生变更，应提前10日以书面方商式通知另一方。如一方未按本合同规定通知而使另一方 遭受损失的，应予以赔偿。 9.3 每次乙方在甲方付款前必须提供符合国家现行税法规定的合法有效等额增值税发票，甲乙双方一致确认提供 发票为主合同义务而非附随义务，若乙方未按要求提供发票，甲方有权暂停付款。乙方应在开票之日起7天内将 道 发票送达甲方指定人员【 刘磊】，甲方指定人员签收发票的日期为发票的送达日期。 9.4 乙方开具的增值税专用发票应保证信息完整、内容规范，如乙方未提供发票或提供的发票不合规、不及时、 无法认证，甲方有权拒绝付款，且不视为甲方付款逾期，乙方无权要求甲方支付利息、违约金或赔偿损失，也 管 不得以此为由中止履行合同约定的义务。 9.5若乙方由一般纳税人身份变为小规模纳税人身份的，或者计税方法发生变化的，或者政策法规等规范性文件 发生变化的，并导致甲方可抵扣的进项税额减少或被税务机关要求补缴税款的，则减少的进项税额或补缴的税 款应由乙方承担，甲方国有权从将支付的任何一笔款项中扣除。 9.6 增值税税率变化：合同执行过程中如果遇到国家税务政策调整，增值税税率发生变化的，按新的税率执行， 不含税价不变，仅调整增值税税率的原则进行相应调整。 中 若乙方提供的发票不符合要求的，发包人有权拒收增值税发票，并有权暂停支付相应款项，乙方不得以此为由 中止履行合同的义务。如因乙方不能按期提供发票或提供的发票不符合要求而导致付款延期的，由其自行承担 后果，发包人不承担任何责任。 9.8若乙方迟延提供发票的，每日应按暂定合同总价的0.05%向甲方支付违约金，但迟延违约金累计支付不超过90 日；若乙方迟延提供发票超过90日且已跨年的，视为乙方未提供发票，乙方除应支付前述迟延违约金外，还应另 行向甲方支付以下款项： （1）相当于合同暂定总价1%的违约金； （2）甲方因未收到发票所产生的税款损失， 损失金额按以下公式计算：赔偿损失金额=未提供发票对应的增值税税额*（1+增值税附加税率）+未提供发票金额 *甲方企业所得税税率。 9.9乙方保证开具的发票已经依法足额纳税，支付每笔款项前，乙方需提供发票对应税期的增值税纳税申报表和 完税证明。 9.10乙方承诺其提供的发票真实合法，若发包人认证后出现走逃失联、被列为异常纳税人等违规行为，导致发包 人不能认证抵扣或者认证抵扣后被税务机关要求进项转出情形，应在72小时内补开合规发票，否则按以下方法计 算应赔偿发包人损失，应赔偿损失金额=进项转出税额*（1+增值税附率)+不合规发票金额*发包人企业所得税税 率，逾期未赔偿的，甲方有权从结算金额或者履约保证金中扣除。 9.11乙方主张已开具发票的，应提供：①税务系统发票开具记录 ；②采购方签收凭证或者发票邮寄物流凭证。无 法完整提供两项证据的视为未开票。 10.双方责任 10.1 双方现场代表 10.1.1甲方现场代表为【 】，其职务为【 】 ，其授权签署文件的范围为：【签发监管项目的各类文函、工程变更 指令、索赔文件的报出、违约处罚决定文件等】。 10.1.2甲方收货代表：【 】，联系电话【 】。甲方指定收货代表仅有对乙方送货单中货物的数量及乙方提供的单 据是否齐全子以确认的权利，对货物单价、质量、货款以及总结算单没有确认的权利。 10.1.3乙方应将物资按合同约定时间运至甲方指定地点，并经甲方指定收货代表和甲方工程项目所属其他1人及以 上在甲方指定的收领单上签字验收确认后有效。 网 10.1.4 甲方未经授权的任何人员和项目印章均无权从事下列行为：【（1）签订本合同的补充协议或签署其他合 同类文件，包括但不限于采购合同、分包合同、租赁合同；（2）签署任何借贷、担保性质的文件，包括但不限 于借条、保函、保证书、承诺书；（3）签署代他人清偿债务的文件，签署任何放弃债权的文件；（4）签署任何 对总承包合同进行修改和补充的文件;（5）收取现金及任何款项；（6）签署合同价款的变更、结算及支付确认 务 文件；（7）签署任何劳动关系确认文件、工资发放承诺文件。】 10.1.5 甲方授权人员的职权/职责范围、授权签署文件范围均不可转授权，任何形式的转授权、代签行为，甲方均 不予认可且不承担任何法律责任。 商 10.1.6 乙方确认已完全明白和理解甲方对甲方人员及项目印章的上述授权范围，超出甲方授权范围的行为属于无 权代理行为，对甲方无效，甲方不承担任何法律责任。乙方应谨慎审查相关文件的签署主体资格和权限，对于 无权代理人签署的相关文件，乙方应及时与甲方核实。 道 10.1.7 乙方现场代表为【 】，其职务为【 】，其授权范围为：【全面代表乙方履行本合同，并有权代表乙方签署、 确认履约过程中形成的工程变更、价款确认、经济索赔、违约处罚决定及物资丢失损坏赔偿文件；签署确权文 件及结算书；签收甲方发出的各类文函、工程变更及其他文件等。】 管 10.1.8 双方更换各自代表时，应及时书面通知对方，以确保物资顺利交接。 10.1.9 甲方禁止项目部及任何人员以甲方、甲方分公司、甲方项目部的名义对外借款或者支取任何款项，如乙方 或乙方有关人员以任何形式将款项出借或支付或返还给甲方项目部及任何人员，则不论该等款项是否实际用于 甲方工程，均与甲方无国关，该行为均属于乙方与相关人员个人之间的经济关系，乙方无权向甲方主张任何权利。 10.1.10 未经甲方书面授权不得擅自与建设方及有关部门发生工作上的联系，严禁在对外任何事务中签署甲方单 位名称或带有甲方简称中任何“【中国建筑】”“【中建】”“【中建XX局】”“【XX局】”等字样的落款， 每发现一次中乙方承担2万元的违约金并赔偿所有直接或间接损失。 10.2卫生、环境与安全保护 10.2.1 甲乙双方须贯彻执行国家、地方政府相关部门发布的有关卫生法律、法规，以及甲方发布的规章制度，积 极配合政府部门的检查，对于提出的要求按所属责任立刻整改，确保瘟疫和传染疾病防控的管理落实到位。 10.2.2 乙方保证在运输和卸货过程中应采取相应的环保措施，符合国家环保要求。车辆在进入项目现场要保证不 沾泥土和脏物，车辆出入项目现场必须在项目大门内现场洗车。乙方在卸货过程中保证噪声不超过以下标准 （白天小于或等于【 】dB、夜间小于或等于【 】dB）。乙方保证乙方人员以及车辆进入本工地现场，应遵守现 场的一切卫生环保、文明施工的规定，因违反环保要求所造成的一切罚款由乙方承担。 10.2.3 甲乙双方必须贯彻执行国家和政府、行业主管部门颁布实施的有关安全生产的法律、法规及有关规定。乙 方车辆及人员进出工地现场时必须接受甲方安全检查。乙方因供货造成安全生产责任事故的，责任由乙方承担。 乙方必须对自身出入工地现场的人员进行安全交底，并为其配备安全防护用品，因乙方原因造成的各种人员伤 害及经济损失由乙方自行承担，并赔偿甲方及其它方因此造成的一切损失。 10.3 售后服务 10.3.1 如所供货物为专业性较高的产品，乙方应免费为甲方或工程业主提供操作及维修人员的培训服务，培训内 容应包括：基本原理、操作使用、维修保养等。 10.3.2 对于工程中的剩余或未使用到的货物在不严重影响外观、质量和功能的情况下甲方有权退货，退货原则上 以合同约定的含税单价为准，确因商品特殊的（比如定制等），价格由双方协商，协商不一致的，按照附件1 《计划采购与供应物资清单》中的含税单价（考虑甲方已支付费用、乙方承担运费等情况下，原则上不低于【 】%）【 】%退货，退货数量以实际数量为准。 不可抗力 11.1 不可抗力是指合同当事人在签订合同时不可预见，在合同履行过程中不可避免且不能克服的自然灾害和社会 性突发事件，包括地震、海啸、瘟疫、骚乱、戒严、暴动、战争等情形。 11.2 不可抗力事件发生后，乙方应立即通知甲方现场代表并迅速采取措施，尽量减少损失，并在24小时内向甲方 通报受害情况，提供必要证明。不可抗力持续发生，乙方应每日报告一次受害情况，直到不可抗力结束。甲方 应对受害处理提供必要的条件，并负责处理工作的组织、指挥。不可抗力发生后网，乙方未采取有效措施控制灾 害而发生的损失由乙方承担。 11.3 不可抗力引起的后果，由甲乙双方应各自承担其人员伤亡及财产损失，履行合同的期限相应延长。 务 不可抗力发生后，双方均应采取措施尽量避免和减少损失的扩大，任何一方没有采取有效措施导致损失扩大的， 应对扩大的损失承担责任。 因一方迟延履行合同义务，在迟延履行期间遭遇不可抗力的，不能免除迟延履行方的违约责任。 商 11.4 因单次不可抗力导致合同无法履行连续超过【30】天或累计超过【60】天的，甲方有权解除合同。合同解除 后，双方应就合同履行情况及结算与付款等善后事宜达成补充协议。 权利瑕疵 道 12.1 涉及到知识产权（专利权）标记的产品，乙方应提供知识产权（或专利权）及其权属的有效证明材料。乙方 承诺其提供的物资不侵犯他人的知识产权（或专利权），若乙方提供物资侵犯他人知识产权（或专利权）导致 他人向甲方索赔的，乙方承担由此给甲方造成的一切损失，包括但不限于甲方处理此纠纷发生的律师费、诉讼 管 费、仲裁费、差旅费等一切损失。此外，乙方应向甲方支付合同价款【5】%的违约金。甲方针对上述一切损失 有权从乙方结算货款中扣除或依法追索。 12.2 乙方所供物资应不存在任何权属纠纷及抵押、查封等权利限制情形，如乙方所供物资存在权属纠纷或任何权 利限制情形导致甲方遭国受损失，乙方应赔偿甲方全部损失。 保密 13.1 除法律规定或合同另有约定外，未经乙方同意，甲方不得将乙方提供的技术秘密及声明需要保密的资料信息 中 等商业秘密泄露给第三方。 13.2 除法律规定或合同条款另有约定外，未经甲方书面同意，乙方不得将甲方提供的图纸、文件以及声明需要保 密的资料信息等商业秘密泄露给第三方。 13.3 任何一方违反上述约定，应负责赔偿守约方因此造成的一切损失。 违约与赔偿14.1甲方应按照合同约定及时向乙方支付合同价款，若因甲方资金不到位，乙方同意给予甲方【 30 】 日的宽限期，宽限期内不视为甲方违约。超过宽限期仍未支付的，乙方可向甲方主张自宽限期结束后的违约金； 违约金以逾期支付的价款为基数，自宽限期结束之日起至甲方支付逾期价款之日止，按照中国人民银行同期活 期存款利率向乙方计付，向乙方计付，逾期支付违约金的上限为逾期支付金额的【 / 】%（不超过3%）。在我方 支付逾期付款利息后，分供商不可就此向我方再主张逾期付款的违约责任。（条款说明：乙方为中小企业时， 甲方前述条款支付期限+本条宽限期整体不得超过60日）。14.2 除本合同中规定的不可抗力外，其他不论任何原 因，乙方若不能按约定期限足额足量送至甲方指定现场存货地点，甲方向乙方收取逾期运达物资货款（含增值 税）每日【3】％的违约金，自逾期之日起计算至乙方实际送达之日止，延迟或供货不足超过【3】日时，甲方有 权单方面终止合同。14.3 未经甲方书面同意自行停止供应本合同约定的货物，均视为乙方违约，乙方除承担因此 给甲方造成的一切损失外，乙方另支付合同价款的【5】%作为违约金。 14.4若乙方提供的货物为非合同约定的厂家或品牌的产品，或提供的是假冒他人品牌的产品，甲方有权立即终止 合同，乙方必须支付合同价款【2】倍的违约金给甲方，如乙方所供产品已安装至工程项目，则乙方除承担违约 金外，还必须承担拆除、工程维修、工作面清理和重新安装产生的所有费用等，如违约金不足以弥补因此给甲 方造成的所有损失，包括一切直接损失和间接损失，则超出部分，甲方有权向乙方追偿。乙方提供的货物为合 同约定的厂家及品牌产品，但货物质量不合格或不符合约定的技术要求时，可由乙方负责更换质量合格和符合 约定技术要求的产品，同时承担合同价款【5】%的违约金，并承担因违约造成的各项损失，甲方也可直接要求 解除合同，乙方承担因此给甲方造成的所有损失。乙方提供的合同标的物因品牌、质量等原因导致甲方被项目 业主或总包方罚款或追究违约责任，乙方应向甲方相应承担赔偿责任。 14.5 本合同履行过程中，如果乙方不能按时交货，应在交货前48小时内以书面形式通报甲方，甲方视情况确定是 否同意变更供货时间。如甲方不同意变更供货时间，可自行采购部分或全部货物。甲方在自行采购和接收该违 约部分货物时实际发生的所有额外费用及因此给甲方造成的损失，从甲方应支付给乙方的任一期货款中扣除， 甲方同时保留进一步索赔的权利。 14.6甲方提出索赔通知后，乙方应在【28】日内答复，如果在【28】日内未答复，视为乙方已接受该索赔，同时 甲方保留进一步要求赔偿的权利。 网 14.7 乙方在进出场时乙方不得私自运送甲方现场物资出场，一经发现，乙方向甲方支付所涉及物资原值【2】倍 的违约金，情节严重的交由司法机关处理。 务 14.8 由于乙方自身原因（如：不按约定开立银行账户、未及时提交报量资料或不按合同配合甲方进行款项支付 等），导致货款或工程款延期支付，甲方不承担延期付款利息及违约金，乙方不得因此停止供货；乙方擅自停 供的视为乙方违约，乙方承担因此给甲方造成的所有责任及损失。 14.9 如果出现合同为可调价合同，甲乙双方调价达不成一致商情形；或者出现合同为不可调价合同，乙方提出调价， 甲乙双方达不成一致情形，则甲方有权选择其他供应商，甲方不承担任何违约责任。 14.10 若乙方因14.5和14.9款原因停止供货，或未完成全部供货、或主张解除合同等不履行合同的情形，乙方剩余 款项的支付不适用本合同8.2条款，甲乙双方应道就剩余款项的支付签订书面补充协议，重新明确支付条款，甲方 不承担任何违约责任。 14.11 其他违约与赔偿要求：【 /】。 管 联络与送达 甲方：收件人【 】，联系电话【 】，电子邮箱【 】，地址【 】。 乙方：收件人【 】，联国系电话【 】，电子邮箱【 】，地址【 】。 15.2 一方通过电子邮箱发送文件的，文件到达对方邮箱即视为送达，送达时间为电子邮件到达对方邮箱地址时间； 一方通过信函邮寄送达的，则信函寄出后的第三个工作日或收件人实际签收日（以先到的时间为准）视为送达； 一方选择直中接送达的，则递交时视为送达。 15.3 邮件邮寄至上述地址被拒收或无人签收，亦视为已经送达，由此增加的费用和（或）延误的期限由拒绝接收 一方承担。 15.4 双方承诺，因本协议的履行或争议解决，上述联系人和联系方式为有效的联系方式，各项通知均应当向上述 联系人、联系方式送达。在诉讼、仲裁中，上述联系人、联系方式亦为有效的送达地址，向上述地址的送达即 为有效送达，即使发生拒收、退信等事件。 上述联系信息发生变更的，变更方应当即时通知对方；在对方收到变更通知之前，对方当事人或者仲裁、司法 机构已经向原联系人、联系方式进行的通知，视为有效通知。 争议解决 16.1 因本合同引起或与之相关的任何争议、纠纷或权利主张，则必须先行向对方发出书面和解申请书，并告知对 方争议、纠纷或权利主张之事实及依据、联系人及联系方式，在对方收到上述通知之日起 3 个月为双方和解期限。 在和解期限内，若双方达成和解协议的，双方的权利义务按照和解协议履行；若未达成和解协议的，任何一方 采用下列第【 】种争议解决方式，并自行承担本方发生的律师费、差旅费、保函费等相关费用∶ （1）向仲裁委员会申请仲裁 周口仲裁委员会（开庭地点：郑州） 郑州仲裁委员会 武汉仲裁委员会 北京仲裁委员会 上海仲裁委员会 中国国际经济贸易仲裁委员会 R成都仲裁委 （2）向【 】人民法院提起诉讼。 网 1.因本合同引起的或与本合同有关的任何争议，如仲裁委员会，则按照其仲裁规则进行仲裁。仲裁裁决是终局的， 对双方均有约束力。 务 2.双方承诺：任何一方向仲裁委员会申请仲裁的，双方均自愿放弃向对方主张仲裁费用和实际发生的其他费用， 包括但不限于鉴定费用、评估费用、审计费用等；双方均自愿放弃向对方主张补偿因办理案件支出的合理费用， 包括但不限于律师费、保全费、差旅费、公证费等。 3.双方约定：仲裁案件无论标的额大小、复杂程度如何，商均适用普通程序，即由三名仲裁员组成仲裁庭审理，以 确保案件公正审理。 4.调解期限：争议应先行和解协商解决，设定3-6个月和解期（可根据情况调整），且和解期限不计入仲裁审理 期限。任何一方若未履行上述和解程序而直接道提请至争议解决机构的，则需要向对方承担签约合同价【10】%的 违约金；如一方出现上述情形，另一方提起反诉或反请求，则提起反诉或反请求的一方不承担违约金。 17.禁止债权转让条款甲乙双方确认，若发生下列任一情形，即视为乙方重大违约，乙方需向甲方支付合同总价 （建议10%） %的违约金，且甲方有权视违约程度单方解除本合同，同时乙方应赔偿甲方因此遭受的全部损失 管 （包括但不限于直接损失、间接损失、维权产生的律师费、诉讼费、保全费等）。具体情形如下： （1）未经甲 方事先书面同意，乙方擅自将其在本合同项下对甲方享有的全部或部分债权进行转让、质押或以其他方式处分 给任何第三方的； （2）因乙方与乙方债权人存在债务纠纷，导致该乙方债权人以甲方为被告或被申请人提起代 位权诉讼、仲裁或采取其他司法/仲裁手段的； （3）未经甲方事先书面同意，乙方以自身名义或委托任何第三 方，就本合同相关事项国对甲方的关联单位（包括但不限于业主单位、建设单位、 发包方）提起代位权诉讼、仲 裁或采取其他司法/仲裁手段的； （4）其他性质同上述条款规定的情形。18.补充条款 /】 中 其他 19.1 本合同采用下列第【 2 】种签订方式： （1）本合同自双方签字并盖章后生效，一式【叁】份，甲方执 【贰】份，乙方执【壹】份，每份具有同等法律 效力。 （2）本合同采用电子签章签署生效。根据《中华人民共和国民法典》、《电子签名法》等相关法律、法规，双 方一致认可在【 】平台（网址：【 】）使用电子印章签署合同为其真实意思表示，且确保在该平台注册时，使 用的企业信息和个人相关信息真实有效，并且自觉遵守国家法律法规和甲方在该平台的合同签约流程。甲乙双 方使用电子签章方式签署的合同，只有通过验证生效的电子原件具有法律效力，未经电子印章服务平台公司提 供书面证明材料的电子合同打印版不能作为法律依据。如因乙方使用不当给甲方造成损失，乙方愿自行承担由 此造成的全部经济损失和法律责任。 19.2未尽事宜经双方协商一致后，可签订补充协议，与本合同具有同等法律效力。 19.3对于因本合同产生的任何争议或投诉，乙方可通过【 】（条款说明：根据各公司情况填写投诉平台或者联系 方式）进行提交。甲方将在收到乙方的投诉后，对乙方的投诉进行初步审查，并尽快与乙方取得联系以进一步 了解详情。因不可抗力或第三方原因导致无法按时处理投诉的情况，甲方将尽快通知乙方，并尽力协调解决问 题。 19.4本合同条款（包括但不���于免责条款、责任限制条款等）均经双方充分协商，双方已就全部条款内容达成一 致意见，不存在单方预先拟定且未予协商的情形。 附件： 附件1：《计划采购与供应物资清单》 附件2：《法人授权委托书》 附件3：《廉政合同书》 （以下无正文） 甲 方：【盖章】 乙 方：【盖章】 网 法定代表人：【签字】 法定代表人：【签字】 委托代理人：【签字】 委托代理人：【签字】 务 地 址：【 】 地 址：【 】 电 话：【 】 电 话：【 】 商 电子信箱：【 】 电子信箱：【 】 附件1 道 计划采购与供应物资清单 人民币：元 管 计量 暂定 单价 暂定含税 序号 物资名称 规格型号 品牌/产地 生产厂家 备注 单位 数量 不含税单价 增值税 含税单价 货款金额 价税合计 暂定合同价款人民币大写： 国 以上数量为暂定项目，最终以双方签字确认的采购结算单为准 中 附件2 中国建筑 项目管理表格 表格编号 法人授权委托书 CSCEC-WZ-HN003 （甲方）： 本授权委托书声明：本的法定代表人，授权委托我公司的 为我公司代理人，代表我公司与贵公司工程对涉及投标报价，物资合同、补充协议的签订、履行，物资结算、收款等业务进行签字确认，由在上述授权范围签字的所有文书，我公 司均予认可，由此产生的一切经济法律责任由我公司承担。 代理期限为前述代理人对上述业务发生第一次签字确认之日起至本工程结算完成之日止。代理人无转委托权。 特此委托。 代理人（签字/按指纹）：身份证号码： （供应商）法定代表人签字： （供应商盖章）： 日期： 附件3 廉政合同书 甲方：【 】 乙方：【 】 为确保甲方对业主的承诺，高效、优质共同完成施工任务，争创优质工程，保证合同双方能够高效廉洁地履行， 维护双方合法权益，经双方协商，特订立如下廉政合同书。 第一条 甲乙双方的权利和义务 1.甲乙双方应本着“公开、公平、公正、诚信、透明”的原则开展工作，自觉遵守党和国家、工程项目所在省、 市、区工程建设有关法律法规以及廉政建设的各项规定。 2.甲乙双方应建立健全廉政教育制度，开展经常性教育活动，积极宣贯“合规诚信 自律清正”的廉洁从业核心理 念，加强廉政教育。 3.加强相互监督，发现对方有违反廉政合同书规定的行为，应及时提醒对方纠正。 第二条 甲方的责任 网 甲方工作人员不得有以下行为： （1）为乙方多结算工程量、多签证、多付工程款等，并向乙方索要或接受贿赂、回扣、礼金、有价证券（卡）、 务 贵重物品和好处费等; （2）在乙方报销任何应由甲方或个人支付的费用; （3）参加有可能影响公正执行公务的超标准宴请和娱乐商、健身等活动; （4）接受乙方提供的通讯工具、交通工具和高档办公用品; （5）要求、暗示或接受乙方为个人住房装修道、婚丧嫁娶、配偶子女工作的安排以及出国（境）、旅游提供的方 便; （6）向乙方介绍或推荐配偶、子女、亲属参与的工程施工合同有关的设备、材料、工程分包、劳务等; 管 （7）向乙方推荐分包单位或要求乙方购买合同规定以外的材料、机具设备等; （8）因乙方拒绝本人的不合理要求，而故意刁难乙方。 第三条 乙方的责任 国 乙方应当通过正常途径开展业务，不得有以下行为： （1）为多结算工程量、多签证、多收工程款等，向甲方及其管理人员行贿或馈赠礼金、有价证券（卡）、贵重 中 礼品; （2）为甲方及其工作人员报销应由甲方单位或个人支付的任何费用; （3）安排甲方人员参加超标准宴请、娱乐活动及带有黄、赌性质的娱乐活动; （4）为甲方人员购置或提供通讯工具、交通工具和高档办公用品等; （5）乙方向甲方工作人员及其家属或者亲友介绍从事与甲乙双方工程有关的工程分包及材料设备、周转工具的 供应、租赁等经营活动。 第四条 违约责任 1.如甲方工作人员有违反本廉政合同书的行为，由甲方纪委查处，追究相应的党纪、政务责任，涉嫌犯罪的，移 交司法机关追究刑事责任；对实名举报的，甲方要立即调查，并采取有效措施保障乙方的合法权益，防止报复 事件发生。 2.如乙方单位或个人有违反本廉政合同书的行为，甲方视情节对乙方处以合同额0.5%—1%的罚款，情节较重并给 甲方造成损失的，乙方另需赔偿甲方直接经济损失，并取消乙方工程分包资格。 第五条 甲方接受举报的途径 1. 受理电话：【 】 2. 受理地址：【 】 3. 受理部门：【 】 4. 受理邮箱：【 】 第六条 本廉政合同书作为采购合同的一部分，具有同等法律效力，本协议与采购合同同日生效，至甲乙双方工 程合同履约完止。 甲方： 乙方： 网 法定代表人： 法定代表人： 授权委托人： 授权委托人： 务 签订时间： 年 月 日 请查看报价网 商 址：https://xy.yzw.cn/sj/bid-detail?tenderId=&amp;source=3&amp;tenderCode=cscec2026081900001246027&amp;tenantId=cscec 信息来源:https://www.chinapipe.net/project/d3076919.html cqdingjiu 2026.08.21 10:06:42 道 管 国 中</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>未识别到明确匹配关键词</t>
         </is>
@@ -753,34 +733,29 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>忠县</t>
+          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(三标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(三标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。</t>
+          <t>本项目工程总投资金额：约3140万元；本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>本项目工程总投资金额：约3140万元；本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。</t>
+          <t>高标准农田建设工程</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>高标准农田建设工程</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(三标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 网 2.项目概况与招标范围 务 2.1 建设地点： 忠县花桥镇、新立镇、石宝镇、兴峰乡。 商 2.2 项目概况与建设规模①忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）：田块整治 工程：旱地区域撂荒地整治278.95亩；灌溉与排水工程：新建200m蓄水池6座、PE75管道967m、新建1.2*1.2m箱 涵16m、新建2*2m箱涵8m；田间道路工程：新建2.5m混凝土生产路15114m、改建2.5m混凝土生产路1078m、新 建2.5m泥结碎石生产路910m、改建2.5m泥结碎道石生产路279m、新建3.0m混凝土生产路601m、改建3.5m混凝土机 耕路4587m；地力提升工程：施有机肥278.95亩；其他工程：工号牌124块。 管 ②忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）：田块整治工程：旱地区域撂荒地 整治195.54亩；灌溉与排水工程：新建100m蓄水池4座、新建200m蓄水池6座、PE75管道5258m、PE90管 道1375m、PE110管道2156m、改建0.5*0.6m混凝土排水沟740m、改建0.6*0.8m混凝土排水沟109m、改建0.8*1.0m混 凝土排水沟296m、改建1*1.5m混凝土排水沟262m、新建3*2m盖板涵1座；田间道路工程：新建2.5m混凝土生产 路11359m、改建2.5m混国凝土生产路3430m、新建2.5m泥结碎石生产路1834m、新建3.0m混凝土生产路350m；农田 防护工程：新建1.0m高挡土墙39m；地力提升工程：施有机肥195.54亩；其他工程：工号牌142块。 中 2.3 本项目工程总投资金额：约3140万元； 本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）施工图所示范围的所 有内容为准，详见发布的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分： 标段划分情况、建设规模及标段合同估算金额等内容如下： 合同估算金额 序号 项目名称 建设地点 （万元） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二 1 花桥镇、新立镇 1022 标段） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三 2 石宝镇、兴峰乡 735 标段） 网 本项目共分为2个标段，每家投标单位仅对2个标段中的任意1个标段进行投标，若同时参与2个及以上标段投标的， 其投标文件无效。 务 2.7 其他： / 商 3.政府采购工程 道 3.1 是否属于政府采购工程：是 □否 管 3.2 是否专门面向中小企业预留：是 国 专门面向中小企业预留的实施方式： 中 方式一：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（忠县）下载招标文件、工 程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字 证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责 任自负。 5.2投标人可在重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要网提问”栏提出疑问，提问时间从 本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-10-12 09:30，投标人应当在投标截止时间前，通过互 务 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 商 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 道 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 管 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 国 开户银行: 开户银行: 账 号: 账 号: 中 监督部门: 忠县发展和改革委员会 电 话: 023-54456078 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段） 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005499 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421353 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891814619 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082001038 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00385 信息来源:https://www.chinapipe.net/project/d3076880.html cqdingjiu 2026.08.21 10:06:45</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
         <v>90</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>重庆, 高标准农田建设工程, 资金情况, 产品种类</t>
         </is>
@@ -825,34 +800,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>忠县</t>
+          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)，包括田块整治、灌溉与排水、田间道路、地力提升和其他工程。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)，包括田块整治、灌溉与排水、田间道路、地力提升和其他工程。</t>
+          <t>本项目总投资金额约3140万元，其中二标段1022万元，三标段735万元。</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>本项目总投资金额约3140万元，其中二标段1022万元，三标段735万元。</t>
+          <t>主要产品包括混凝土生产路、泥结碎石生产路、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>主要产品包括混凝土生产路、泥结碎石生产路、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点： 忠县花桥镇、新立镇、石宝镇、兴峰乡。 2.2 项目概况与建设规模①忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）：田块整治 务 工程：旱地区域撂荒地整治278.95亩；灌溉与排水工程：新建200m蓄水池6座、PE75管道967m、新建1.2*1.2m箱 涵16m、新建2*2m箱涵8m；田间道路工程：新建2.5m混凝土生产路15114m、改建2.5m混凝土生产路1078m、新 建2.5m泥结碎石生产路910m、改建2.5m泥结碎石生产路279m、新建3.0m混凝土生产路601m、改建3.5m混凝土机 耕路4587m；地力提升工程：施有机肥278.95亩；其他工程：工号牌124块。 商 ②忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）：田块整治工程：旱地区域撂荒地 整治195.54亩；灌溉与排水工程：新建100m蓄水池4座、新建200m蓄水池6座、PE75管道5258m、PE90管 道1375m、PE110管道2156m、改建0.5*0.6m混凝土排水沟740m、改建0.6*0.8m混凝土排水沟109m、改建0.8*1.0m混 凝土排水沟296m、改建1*1.5m混凝土排水沟2道62m、新建3*2m盖板涵1座；田间道路工程：新建2.5m混凝土生产 路11359m、改建2.5m混凝土生产路3430m、新建2.5m泥结碎石生产路1834m、新建3.0m混凝土生产路350m；农田 防护工程：新建1.0m高挡土墙39m；地力提升工程：施有机肥195.54亩；其他工程：工号牌142块。 2.3 本项目工程总投资金额：约3140万元； 管 本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）施工图所示范围的所 有内容为准，详见发布国的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分中： 标段划分情况、建设规模及标段合同估算金额等内容如下： 合同估算金额 序号 项目名称 建设地点 （万元） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二 1 花桥镇、新立镇 1022 标段） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三 2 石宝镇、兴峰乡 735 标段） 本项目共分为2个标段，每家投标单位仅对2个标段中的任意1个标段进行投标，若同时参与2个及以上标段投标的， 其投标文件无效。 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 方式一：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 网 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 .技术成果经济补偿 务 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （忠县）下载招标文件、工程量清单、电子图纸等资料。商参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（忠县）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源 交易监督网、重庆市公共资源交易网（忠县）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数字证 书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的，责任 自负。 道 5.2投标人可在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要提 问”栏提出疑问，提问时间从本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 管 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-10-12 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 国 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 中忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 忠县发展和改革委员会 电 话: 023-54450483 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段） 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421361 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00386 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005423 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891832091 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082001039 信息来源:https://www.chinapipe.net/project/d3076879.html 网 cqdingjiu 2026.08.21 10:06:45 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>未识别到明确匹配关键词</t>
         </is>
@@ -897,34 +867,29 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>忠县</t>
+          <t>田块整治工程、灌溉与排水工程、田间道路工程、地力提升工程、其他工程</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>田块整治工程、灌溉与排水工程、田间道路工程、地力提升工程、其他工程</t>
+          <t>项目总投资金额约3140万元，本次招标项目合同估算金额一标段1167万元</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>项目总投资金额约3140万元，本次招标项目合同估算金额一标段1167万元</t>
+          <t>高标准农田建设工程</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>高标准农田建设工程</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(一标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）已由 忠县发展和改革委 员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来 自 业主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具 备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 网 务 2.项目概况与招标范围 商 2.1 建设地点： 忠县马灌镇、三汇镇、永丰镇。 道 2.2 项目概况与建设规模：忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）：田块整治 工程：水田整治50.67亩、水田区域撂荒地整治79亩、旱地区域撂荒地整治62.83亩；灌溉与排水工程：新 建200m蓄水池5座、新建500m蓄水池1座、泵站1座；田间道路工程：新建2.5m混凝土生产路12325m、改 建2.5m混凝土生产路8549m、新建2.5m泥结碎石生产路1223m、新建3.0m混凝土生产路576m、改建3.0m混凝土生 管 产路648m、改建3.0m混凝土生产路（拆除原1.5m宽路）266m、改建3.5m混凝土机耕路1662m；地力提升工程：施 有机肥136.48亩；其他工程：公示牌1座、工号牌213块。 国 2.3 本项目工程总投资金额：约3140万元； 中 本次招标项目合同估算金额：一标段1167万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）施工图所示范围的所 有内容为准，详见发布的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 网 方式一：本项目整体面向中小企业。 务 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 商 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 道 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 管 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 国 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 中 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（忠县）下载招标文件、工 程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及CA数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 5.2投标人可在重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从 本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-10 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 网 监督部门: 忠县发展和改革委员会 电 话: 023-54456078 务 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段） 商 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082000104 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005469 道 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421379 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00387 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891884496 管 信息来源:https://www.chinapipe.net/project/d3076876.html cqdingjiu 2026.08.21 10:06:46 国 中</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
         <v>95</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>重庆, 高标准农田建设工程, 投资金额, 产品种类</t>
         </is>
@@ -969,34 +934,29 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>永川区</t>
+          <t>农村供水管网巩固提升改造工程</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>农村供水管网巩固提升改造工程</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>供水管网</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>供水管网</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
           <t>永川区农村供水管网巩固提升改造工程(东部片区)答疑补遗文件 永川区农村供水管网巩固提升改造工程（东部片区） 补遗文件（01） 各潜在投标人： 现将“永川区农村供水管网巩固提升改造工程（东部片区）”招标文件补遗通知如下，本次发布的补遗文件中 的所有内容与招标文件具有同等法律效力，如与招标文件、答疑补遗文件（01）网不一致时，以本补遗文件为准。 请各潜在投标人自行下载本补遗文件，不管下载与否，都视为全部知晓其全部内容。 一、本招标项目招标文件第二章投标人须知前附表第1.4.1项第1条第（3）款中“具备建设行政主管部门颁发的有 效的安全生产许可证，企业主要负责人、拟派项目经理具备相应的由建设行政主管部门颁发的有效的安全生产 务 考核合格证书。”修改为： “（3）具备建设行政主管部门颁发的有效的安全生产许可证，企业主要负责人、拟派项目经理具备相应的由水 行政主管部门颁发的有效的安全生产考核合格证书”。 商 二、本招标项目招标文件第二章投标人须知前附表第1.4.1项中第3条“业绩要求”修改为： “投标人自2023年1月1日起至投标截止日止（以合同工程完工日期或工程竣工日期为准），完成过1个单项合同 输配水管网长度不少于100km的水利工程施工道业绩。 提供：供该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴 定书）的证明材料。若提供的上述业绩证明材料不能体现上述业绩指标的，应补充提供业主证明。 管 注：（1）当上述业绩证明材料中针对同一指标存在不一致时，以合同工程完工证书（或合同工程验收鉴定书或 工程竣工证书副本或竣工验收鉴定书）的证明材料为准。（2）投标人提供的业绩为联合体业绩的，其在该业绩 中的工作分工应与本项目承担的工作一致。” 三、本招标项目招标文国件第二章投标人须知前附表第1.4.1项中第5条中的“5.3项目经理业绩要求”修改为： “投标人拟派的项目经理自2023年1月1日起至投标截止日止（以合同工程完工日期或工程竣工日期为准），完成 过1个单项合同输配水管网长度不少于100km的水利工程施工业绩，并在该业绩中担任项目经理。 中 提供：供该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴 定书）的证明材料。若提供的上述业绩证明材料不能体现上述业绩指标的，应补充提供业主证明。 注：（1）当上述业绩证明材料中针对同一指标存在不一致时，以合同工程完工证书（或合同工程验收鉴定书或 工程竣工证书副本或竣工验收鉴定书）的证明材料为准。（2）投标人提供的业绩为联合体业绩的，其在该业绩 中的工作分工应与本项目承担的工作一致。” 四、本招标项目的投标文件递交的截止时间（投标截止时间）调整为2026年9月4日9时30分（北京时间），开标 时间及投标保证金递交截止时间相应顺延。 招标人：重庆市永川区惠永水务有限公司 招标代理机构：重庆永川政鑫综合能源有限公司 2026年8月20日 信息来源:https://www.chinapipe.net/project/d3076870.html cqdingjiu 2026.08.21 10:06:46</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
         <v>80</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>重庆, 农村供水管网, 巩固提升改造, 东部片区, 管材招标</t>
         </is>
@@ -1041,34 +1001,29 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>长寿区</t>
+          <t>新改建及修复DN300mm-DN1200mm排水管道20.187公里，其中新改建管道15.21公里，修复管道4.977公里，Ⅲ、Ⅳ级结构性及功能性缺陷修复453处。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>新改建及修复DN300mm-DN1200mm排水管道20.187公里，其中新改建管道15.21公里，修复管道4.977公里，Ⅲ、Ⅳ级结构性及功能性缺陷修复453处。</t>
+          <t>项目业主为重庆市长寿区住房和城乡建设服务中心，建设资金来自财政资金，项目出资比例为100%。</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>项目业主为重庆市长寿区住房和城乡建设服务中心，建设资金来自财政资金，项目出资比例为100%。</t>
+          <t>DN300mm-DN1200mm排水管道</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DN300mm-DN1200mm排水管道</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
           <t>长寿区海棠、石堰、龙河片区污水管网建设项目(二期)招标公告 长寿区海棠、石堰、龙河片区污水管网建设项目（二期）招标公告 1.招标条件 本招标项目长寿区海棠、石堰、龙河片区污水管网建设项目已由重庆市长寿区发展和改革委员会以长改发投 〔2024〕169号文批准建设，项目业主为重庆市长寿区住房和城乡建设服务中心，建设资金来自财政资金，项目 出资比例为100%，招标人为重庆长寿乡村建设集团有限公司。项目已具备招标条件，现对该项目的施工进行公 开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：长寿区海棠镇、龙河镇、新市街道、云台镇。 2.2 项目概况与建设规模：新改建及修复DN300mm-DN1200mm排水管道20.187公里，其中新改建管道15.21公里， 务 修复管道4.977公里，Ⅲ、Ⅳ级结构性及功能性缺陷修复453处。 2.3 本次招标项目合同估算金额：4139.45万元。 2.4 招标范围：详见招标人提供的本工程的施工图图纸、图商说、设计变更以及工程量清单所明确的全部工程内容。 2.5 工期要求：270日历天。 缺陷责任期要求：24个月。 道 3.政府采购工程 3.投标人资格要求 管 3.1 本次招标要求投标人须具备以下条件： 3.1.1 本次招标要求投标人具备的资质条件：建设行政主管部门颁发的有效的市政公用工程施工总承包三级及以 上资质； 国 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 中 3.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需 在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网 导航栏“主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登 记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公 告发布至2026-08-25 15:00:00前。 4.3招标人应于2026-08-28 18:00:00前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交 易网（长寿区）（https://www.cqggzy.com/changshouweb/）发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-14 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源 交易监督网上发布。] 7.联系方式 招 标 人: 重庆长寿乡村建设集团有限公司 代理机构: 中新创达咨询有限公司 地 址: 重庆市长寿区桃源大道3号一号商务楼5-6楼 地 址: 邮 编: 邮 编: 项目负责人: 刘老师 项目负责人: 钟亮 网 电 话: 023-40233279 电 话: 19132912275 传 真: 传 真: 电子邮箱: 电子邮箱务: 开户银行: 开户银行: 账 号: 账 号: 商 监督部门: 重庆市长寿区发展和改革委员会 电 话: 023-40245080 2026年08月20日 长寿区海棠、石堰、龙河片区污水管网建设道项目（二期） 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公 中国农业银行股份有限公司重庆自由贸易 312601010400083780000033561 司 管试验区分行 重庆联合产权交易所集团股份有限公 中国建设银行股份有限公司重庆渝中支行 6232813760003317764 司 重庆联合产权交易所集国团股份有限公 重庆银行股份有限公司七星岗支行 15010202900420146632392 司 信息来源:https://www.chinapipe.net/project/d3076848.html cqdingjiu 20中26.08.21 10:06:46</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>未识别到明确匹配关键词</t>
         </is>
@@ -1113,34 +1068,29 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>万州区</t>
+          <t>渝万高铁站前1标位于重庆市万州区和忠县境内,起止里程DK14+233.2~D1K47+550.4，正线长度33.01km，中标造价31.73亿元。管区内共有隧道8座/22.36km，斜井2座/1.76km;桥梁15座/8.97km，其中，预制及架设梁301孔，(40+64+40)m和(45+100+45)m连续梁各1联;区间路基22段/1.68km，土石方约67万方，负责DK0+000~DK57+136段小型构件预制。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>渝万高铁站前1标位于重庆市万州区和忠县境内,起止里程DK14+233.2~D1K47+550.4，正线长度33.01km，中标造价31.73亿元。管区内共有隧道8座/22.36km，斜井2座/1.76km;桥梁15座/8.97km，其中，预制及架设梁301孔，(40+64+40)m和(45+100+45)m连续梁各1联;区间路基22段/1.68km，土石方约67万方，负责DK0+000~DK57+136段小型构件预制。</t>
+          <t>中标造价31.73亿元</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>中标造价31.73亿元</t>
+          <t>刺丝滚笼,塑钢模板,泄水管</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>刺丝滚笼,塑钢模板,泄水管</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
           <t>中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部刺丝滚笼、塑钢模板、泄水管询价采购公告 中铁十一局集团有限公司重庆至万州高铁站前 1标项目经理部 刺丝滚笼、塑钢模板、泄水管询价采购公告 询价编号： ZT1105-XJ-2026-590 尊敬的 各潜 在供应商 : 网 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与 中铁十一局集团有限公司重庆至万州高铁站 前 1标项目经理部 ZT1105-XJ-2026-590， 刺丝滚笼、塑钢模板、泄水管 的报价。 一、 项目概况 务 渝万高铁站前 1标位于重庆市万州区和忠县境内,起止里程DK14+233.2~ D1K47+550.4，正线长度 33.01km，中标造 价 31.73 亿元。管区内共有隧道8座/22.36km，斜井2座/1.76km;桥梁15座/8.97km，其中，预制及架设梁 301 孔，(40+64+40)m和(45+100+45)m连续梁各1联;区间路基22段/1.68km，土石方约67万方，负 责DK0+000~DK57+136段小型构件预制。合同工期54.7月商，开工日期为2022年11月01日，竣工日期为2027 年04 月30日。 二、 询价内容 道 本次 计划对刺丝滚笼、塑钢模板、泄水管 进行询价，询价内容如下： 询价物资一览表 管 计 序 物资 量 包件号 规格型号 数量 备注 号 名称 单 位 国 刺丝 1 GL-01 2.5mm 6m0.5m 米 6500 半径 ≥225mm，包括刀片刺绳、挂丝、连接卡、支架 滚笼 防护 中 栅栏 2 GL-01 用立 50X30X765X2.5mm 套 500 含抱箍、螺栓等配件 柱支 架 平 塑钢 3 MB-01 350X300mm 方 19.2 400*400,1个挡水沿，配固定手柄 模板 米 平 塑钢 4 MB-01 350X300mm 方 19.2 400*400,2个挡水沿，配固定手柄 模板 米 平 塑钢 5 MB-01 300X300mm 方 75.6 2个挡水沿，配固定手柄 模板 米 平 塑钢 6 MB-01 300X300mm 方 75.6 1个挡水沿，配固定手柄 模板 米 7 SSG-01 管篦 PVC250X200x10mm 个 220 材质硬聚氯乙烯 PVC，详见附图 PVC 8 SSG-01 泄水 135X38mm 块 220 材质硬聚氯乙烯 PVC，详见附图 管盖 U型 9 SSG-01 125mm 个 900 详见附图 管卡 UPV 材质硬聚氯乙烯 PVC，两端接头采用阴阳螺纹连接详见 10 SSG-01 C排 125X8mm螺纹 米 2870 附图 水管 UPV 11 SSG-01 C弯 DN125X8mm90° 个 240 材质硬聚氯乙烯 PVC，详见附图 管 UPV 网 125X125X110mm弹性密 12 SSG-01 C三 个 120 材质硬聚氯乙烯 PVC，详见附图 封圈异径斜三通 通 无压 埋地 务 排污 排水 用硬 13 SSG-01 DN125 个 150 材质硬聚氯乙烯 PVC，详见附图 聚氯 商 乙烯 管 T 型接 头 道 合 计 管 说明： 1. 表中数量为计划数量，实际 采购 过程中可能有所调整，最终结算按照实际 采购 数量结算。 2.收货地点：中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部 三、 技术质量 及报价国 要求 1. 此次 询价物资 各项技术性能要 符合 甲方 的要求，质量满足甲方项目部正常使用的要求，保证 产品 的质量合 格。 具体要求或图纸见询价文件技术规格书。 。 中 2 .报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、 结算及付款方式 每个月 15 日为双方价款结算日期（即上月 16 日至当月 15 日内），结算前双方要在对帐确认单上签字认可，乙 方按双方确认的金额开具增值税专用发票，并自发票开具之日起 7日内传递给甲方。甲乙双方在增值税专用发票 传递过程中必须留取相应的交接签证手续。自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发 票认证完成之日起第6个月，支付至本次结算金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内， 累计支付总额不超结算总金额的75%，剩余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理 末次结算后第二年，支付金额应大于等于尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总 额的15%；办理末次结算后第四年，全部付清）。 五、 报价 人资格要求 1.营业范围要求：在中华人民共和国境内依法注册，具有询价物资生产或供应经验的生产商或代理商，并且具有 合法有效的营业执照。 2.生产能力要求： 生产商须具备 询价 物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定 。 代理商需出具制造厂出具签字盖章的授权函。 3.财务能力要求：报价人为增值税一般纳税人或小规模纳税人，有依法纳税的良好记录。 4.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8月至今） 国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；每种物资全指标技术参数性能满足 国家和行业最新标准的各项规定。 5.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年8月至今）企业或企业法定代表人有人民法院生效判决、裁定 认定的行贿犯罪记录的。④ 对纳入国家铁路局“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接受 通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合作 方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 网 6.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 务 ★7 .下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 六、 报价人需要提供的资料 1. 营业执照复印件、 法人身份证复印件、 开户许可证、商授权委托书 、 报价表 和报价人资格要求中所需的证明资 料， 所有资料需加盖公司鲜章。 2. 产品质量检测报告等质量证明文件。 道 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、 询价 报名截止 时间 管 有意参加本次询价采购的报价人 须在铁建云链平台 （ https:// www.crccep. cn） 完成供应商注册，并 于 202 6 年 8 月 20 日 9时 00 分 至 202 6 年 8 月 24 日 9时 00 分在网上 完成报名工作。 八、 询价 截止 时间 国 凡有意参加本次询价采购的报价人，请于 202 6 年 8 月 24 日 14 时 00分 前 提交报价。截止时间前未完成 报价 文 件传输的，视为放弃 报价 。 供应商报价必须严格按照《 报价表 》格式进行报价。 中 九、 联系方式 采购 组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村 71号 联系人：胡先生 联系电话： 13983336494 （提供平台服务支持） 采购人名称：中铁十一局集团有限公司重庆至万州高铁站前 1标项目经理部 地址： 重庆市万州区双河口街道檬兴路万州现代综合物流中心信息交易大厅（中铁十一局） 联系人： 唐大伟 联系电话： 18323391938（提供采购服务支持、保证金退还） 中铁十一局集团有限公司物资设备集中采购管理中心 第五分中心 2026 年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3076805.html cqdingjiu 2026.08.21 10:06:47 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
         <v>85</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>重庆, 万州, 高铁站前, 刺丝滚笼, 塑钢模板, 泄水管, 询价采购</t>
         </is>
@@ -1185,34 +1135,29 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>垫江县</t>
+          <t>垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目，主要内容包括河堤护岸岸线整治2100m；产业路扩宽及油化改造775.3m；新建污水管网450m，化粪池2座；产业基地水肥一体化改造45亩等。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目，主要内容包括河堤护岸岸线整治2100m；产业路扩宽及油化改造775.3m；新建污水管网450m，化粪池2座；产业基地水肥一体化改造45亩等。</t>
+          <t>项目总投资金额为642.89万元，本次招标项目合同估算金额约为5014864.52元。</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>项目总投资金额为642.89万元，本次招标项目合同估算金额约为5014864.52元。</t>
+          <t>水利水电工程施工</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>水利水电工程施工</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
           <t>垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告 1.招标条件 本招标项目 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目 已由 垫江县发展和 改革委员会 以 垫江发改委发〔2026〕20号 文批准建设，项目业主为 垫江县太平镇人民政府，建设资金来 自 大中型后扶资金及自筹资金 ，项目出资比例为 100% ，招标人为垫江县太平镇人民政府。项目已具备招 标条件，现对本项目施工进行公开招标，评标办法采用经评审的最低投标价法。网 务 2.项目概况与招标范围 商 2.1 建设地点：垫江县太平镇桂花村 道 2.2 项目概况与建设规模：主要为河堤护岸岸线整治2100m；产业路扩宽及油化改造775.3m；新建污水管网450m， 化粪池2座；产业基地水肥一体化改造45亩等。 管 2.3 本项目工程总投资金额：642.89万元 国 本次招标项目合同估算金额：约5014864.52元 中 2.4 招标范围：本工程施工图纸所含全部的施工内容，具体以招标人发布的工程量清单为准。 2.5 工期要求：工期为360日历天 ，缺陷责任期为24个月。 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：□是 否，因专门面向中小企业预留无法确保充分供应、充分竞争，根据 《政府采购促进中小企业发展管理办法》第六条第(三)“按本办法规定预留采购份额无法确保充分供应、充分竞 争，或者存在可能影响政府采购目标实现的情形”的规定，本项目不专门面向中小企业预留。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 网 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的水利水电工程施工总承包三级 务 及以上资质。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相商应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 道 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 管 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com国/dianjiangweb/)、重庆市公共资源交易监督网下载招标文件、工程量清单、电子图纸等资 料。参与投标的投标人需在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共 资源交易监督网完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交易监督网导航栏“主体信息”页面中“市场主体信息 登记”、“中CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流 程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交易监督 网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-24 17:00:00前。 5.3招标人应于2026-08-28 17:00:00前在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重 庆市公共资源交易监督网发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-28 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交 易监督网发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 垫江县太平镇人民政府 代理机构: 重庆皓辰建设工程咨询有限公司 重庆市渝北区金开大道1228号大雅金开国际1 地 址: 重庆市垫江县太平镇牡丹路191号 地 址: 栋9-2 邮 编: 邮 编: 项目负责人: 余老师 项目负责人: 雷雨得 电 话: 13996889839 电 话: 023-86018770 18580880860 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 垫江县发展和改革委员会 电 话: 023-74517161 网 2026年08月19日 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目 务 户名 开户行 投标保证金账号 垫江县公共资源交易中心 中国农业银行重庆垫江支行 316301010400077950000005966 垫江县公共资源交易中心 中国银行重庆垫江支行 111616885778VA00139 商 垫江县公共资源交易中心 重庆农村商业银行垫江支行 2501010120010009065000128 垫江县公共资源交易中心 工商银行重庆垫江支行营业部 9558853100016843371 垫江县公共资源交易中心 重庆银行垫江支行 820101040000584-101195 道 附件：垫江县2026年度大中型水库移民后期扶持项目-.zip https://www.cqggzy.com/trade/014001/dac54522-3264-4eac-ae47-f434567ce374?categoryNum=014001001007 信息来源:https://www.chinapipe.net管/project/d3076788.html cqdingjiu 2026.08.21 10:06:47 国 中</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
         <v>85</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标, 水利, 移民, 后期扶持</t>
         </is>
@@ -1257,34 +1202,29 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>万州区</t>
+          <t>新建水厂1座（新建2000m³茨竹水厂），输、配水管道改造与新建，管道总长约226.127km，管径DN20~DN250，管材为涂塑钢管。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>新建水厂1座（新建2000m³茨竹水厂），输、配水管道改造与新建，管道总长约226.127km，管径DN20~DN250，管材为涂塑钢管。</t>
+          <t>合同预估金额：5000万元</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>合同预估金额：5000万元</t>
+          <t>涂塑钢管</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>涂塑钢管</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
           <t>万州区新田等6个镇乡农村饮水质量提升项目招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区新田等6个镇乡农村饮水质量提升项目 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 及文号 务 新建水厂1座（新建2000m3茨竹水厂），输、配水管道改造与新建，管道总长约226.127km，管 主要建设内容 径DN20~DN250，管材为涂塑钢管。 招标项目名 招标方 招标文件计划 拟交易场 合同预估金 序号 招标内容 备注 称 式 发布时间 所 额(万元) 商 万州区新田 万州区新田 重庆市万 招标项目 等6个镇乡农 等6个镇乡农 公开招 州区公共 1 村饮水质量提 2026-08 5000.00 村饮水质量 标 资源交易 升项目道施工总 提升项目 中心 承包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076721.html 管 cqdingjiu 2026.08.21 10:06:48 国 中</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
         <v>80</v>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标, 商机</t>
         </is>
@@ -1329,34 +1269,29 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>万州区</t>
+          <t>新建50m³蓄水池4口、取水池2座；新建50m³/d-100m³/d水厂2座；改造100m³/d-300m³/d水厂5座；铺设DN25-DN250涂塑钢管约86km；新建提水泵站8座；配套阀井、电磁流量计等有关设施。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>新建50m³蓄水池4口、取水池2座；新建50m³/d-100m³/d水厂2座；改造100m³/d-300m³/d水厂5座；铺设DN25-DN250涂塑钢管约86km；新建提水泵站8座；配套阀井、电磁流量计等有关设施。</t>
+          <t>合同预估金额：3000万元</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>合同预估金额：3000万元</t>
+          <t>DN25-DN250涂塑钢管</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>DN25-DN250涂塑钢管</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
           <t>万州区大周等4个镇乡街道农村饮水质量提升项目招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区大周等4个镇乡街道农村饮水质量提升项目 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 及文号 务 新建50m3蓄水池4口、取水池2座；新建50m3/d-100m3/d水厂2座；改造100m3/d-300m3/d水厂5 主要建设内容 座；铺设DN25-DN250涂塑钢管约86km；新建提水泵站8座；配套阀井、电磁流量计等有关设 施。 招标项目名 招标方 招标文件计划 拟交易场 合同预估金 序号 招标内容 商 备注 称 式 发布时间 所 额(万元) 万州区大周 万州区大周 重庆市万 招标项目 等4个镇乡街 等4个镇乡街 公开招 州区公共 1 道农村饮水 道农村饮道水质 2026-08 3000.00 标 资源交易 质量提升项 量提升项目施 中心 目 工总承包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3076720.html cqdingjiu 2026.08.21 10:06:49 国 中</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
         <v>80</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>重庆, 农村饮水质量提升项目, 管材招标, 合同预估金额</t>
         </is>
@@ -1395,32 +1330,31 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>本项目西起太阳岗立交(不含太阳岗立交)，往东穿越铜锣山，止于内环南泉立交(不含南泉立交)。项目全长约6.8km，其中二标段长约3.62公里，采用主干路标准，设计车速60km/h，标准路幅为双向6车道，主要工程包括长隧道1座(新燕尾山隧道，长2542m)，简易立交1座(花溪立交),互通式立交2座(南温泉立交、苦竹坝立交)。</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>本项目西起太阳岗立交(不含太阳岗立交)，往东穿越铜锣山，止于内环南泉立交(不含南泉立交)。项目全长约6.8km，其中二标段长约3.62公里，采用主干路标准，设计车速60km/h，标准路幅为双向6车道，主要工程包括长隧道1座(新燕尾山隧道，长2542m)，简易立交1座(花溪立交),互通式立交2座(南温泉立交、苦竹坝立交)。</t>
+          <t>采购项目资金为企业自筹。</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>采购项目资金为企业自筹。</t>
+          <t>纤维编绕拉挤电缆保护套管(BWFRP100/2.0，79158米)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>纤维编绕拉挤电缆保护套管(BWFRP100/2.0，79158米)</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
           <t>二航科工新燕尾山项目纤维编绕拉挤电缆保护套管采购询价通知公告 中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程项目询比采购 公告 中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程项目已具备采 购条件，现公开邀请供应商参加询比采购活动。 网 1. 采购项目简介 1.1 采购项目名称：中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机 电工程项目。 务 1.2采购方案编号：FA00000674478。 1.3 采购人：中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程 项目经理部。 商 1.4 采购代理机构：中交二航局科工（武汉）有限公司。 1.5 采购项目资金：企业自筹。 道 1.6 采购项目概况：新燕尾山隧道工程位于重庆市内环吉庆隧道北侧，四横线分流道鹿角隧道南侧，西接白居 寺大桥，东接内环快速路，并向东延伸接渝黔复线高速，其所在的道路系统呈东西布置，为主城区南部片区重 要干道。本项目西起太阳岗立交(不含太阳岗立交)，往东穿越铜锣山，止于内环南泉立交(不含南泉立交)。项目 管 全长约6.8km，其中二标段长约3.62公里，采用主干路标准，设计车速60km/h，标准路幅为双向6车道，主要工程 包括长隧道1座(新燕尾山隧道，长2542m)，简易立交1座(花溪立交),互通式立交2座(南温泉立交、苦竹坝立交)。 2.采购范围及相关要求 国 2.1 采购范围：纤维编绕拉挤电缆保护套管（BWFRP100/2.0，79158米）。 2.2 交货期：以甲方实际订单要求为准。 中 2.3 交货地点：重庆市巴南区新燕尾山项目甲方指定位置。 2.4 物资质量标准：满足国家法律法规、标准、规范、设计参数及技术规格书要求。 3.供应商资格要求 3.1 供应商应依法设立且满足如下要求： （1）资质要求：在中华人民共和国境内依法注册，具有独立法人资格、具有采购物资生产或供应经验的企业， 并且具有合法、有效的“三证合一”的营业执照,代理商需提供制造商授权委托书。 （2）财务要求：必须是经税务部门注册登记核准的一般纳税人，有依法纳税的良好记录，提供近三年的财务报 告。 （3）业绩要求：同类产品销售业绩不少于2个，并具备与本招标项目需求相适应的供货能力。 （4）信誉要求：本项目投标截止期前未被“信用中国”、“中国政府采购网”、中国交建物资采购管理信息系 统网站列入失信被执行人、违法案件当事人、违法失信行为记录名单。 （5）其他要求：提供运输方案及生产周期。 3.2 供应商不得存在下列情形之一： （1）处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； （2）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （3）已列入黑名单，且未解除限制期限； （4）其他： / 。 4.供应商报名 4.1有意参加询比采购活动的单位，请于2026年 8 月 20 日 11 时 00 分至2026 网 年 8 月 25 日 11 时 00 分（北京时间、下同），登录“中交招采网”（网 址：https://zjzcw.iccec.cn）进行报名并下载采购文件。 4.2 已在网并且已通过采购人层级供应商或已增加采购人为合作单位的供应商、上级供应商可直接参与询比采 务 购。在网平级单位供应商未增加采购人为合作单位需进行合作意向申请通过后参与询比采购。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择采购人，审核通过后方可参与询比 采购。 商 5. 供应商报价 5.1 报价结束（递交响应文件截止）时间：2026年 8 月 25 日 11 时 00 分。 道 5.2 供应商应在报价结束时间前，登录“中交招采网”进行线上报价并上传电子响应文件。逾期未完成上传的 电子响应文件，采购人将拒收。 5.3电子采购的供应商报价文件由线上电子报价表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 管 子报价表的数据为准。 6. 开标 6.1开标时间：与报价结国束时间相同。 6.2开标地点：本次采购在“中交招采网”平台线上开标，不举办现场开标，现场开标地点/。 7. 发布公告的媒介 中 本询比采购公告在中交招采网上发布。 8. 评审办法 本项目评审办法采用 经评审的最低价法 。 9. 合同主要条款 9.1 付款条件：无预付款，到货后办理结算，双方办理完结算手续、卖方提供符合合同要求的正式发票给买方 后60天，买方支付该批材料价值80%的货款，完工结算后支付至97%，剩余3%为质保金，质保期2年，两年后供 应方申请返还3%（无息）；银行转账、承兑、18个月供应链金融混合支付方式。 9.2履约保证金的递交： （1）□不要求递交 （2）要求递交 保证金金额：2万元 ； 保证金形式：银行转账、银行保函等电子保函；其他形式：无 。 10. 成交供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”（网址：https://zjzcw.iccec.cn）发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联 系4006765885中标服务费请按7咨询。 10.1收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： 网 （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； 务 （3）在1000万元（含）至3000万元之间的，每次收取1000元； （4）在3000万元（含）至1亿元之间的，每次收取3000元； （5）在1亿元（含）以上的，每次收取5000元。 商 10.2支付流程 （1）通知推送：中标结果发布后，系统自动道推送缴费通知（含应缴金额及支付链接）； （2）费用查询：供应商登录“中交招采网-服务管理”模块查看待支付费用； （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 管 （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网- 服务管理－发票下载”模块获取。 11.监督机构 国 监督机构名称：中交二航局科工（武汉）有限公司纪委监察部 举报电话：中027-82796466 举报邮箱：sneb_kggs@ccccltd.cn 12.其他 投标保证金采用银行转账形式的需转至中交二航局科工（武汉）有限公司账户（账 号：42001186108053006379-0006开户行：建行武汉长江支行，行号：105521000053），并备注二航科工燕尾山机 电照明项目纤维编绕管投标保证金。 13.联系方式 采购 人：中交二航局科工（武汉）有限公司 采购代理机构：中交二航局科工（武汉）有限公司 地 址：武汉市新洲区双柳街星谷大道158号地 址：武汉市新洲区双柳街星谷大道158号 邮政编码：430400 邮政编 码：430400 联系人：李鑫 联系人：毕明 月 电 话：18186145302 电 话：17853118573 电子邮件：18186145302@ccccltd.cn 电子邮件：bimingyue@ccccltd.cn 2026年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3076715.html cqdingjiu 2026.08.21 10:06:50 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
         <v>90</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 光纤电缆保护套管</t>
         </is>
@@ -1465,34 +1399,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>巴南区</t>
+          <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程变更公告</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程变更公告</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>天然气表后管道安装工程</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>天然气表后管道安装工程</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
           <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程变更公告 重庆巴南天然气有限责任公司 重庆国际生物城配套公寓项目天然气表后管道安装工程 变更公 告 公告编号： RQBGGG202608200006 本公司于2026年08月19日发布的重庆国际生物城配套公寓项目天然气表后管道安装工程公告（编 号：RQCGXY202608170010），现做出如下变更： 网 1、对采购文件第一卷“采购需求“中墙体管道暗埋的具体内容进行明确。墙体管道暗埋应包含墙体开槽，输送 用不锈钢波纹管及钢制槽板的安装，墙体恢复，暗埋管道视频记录。 2、对由响应供应商提供的钢制槽板的规格进行明确。钢制槽板为U型开口槽，采用热镀锌Q235B钢板，钢板厚度 务 不得小于1.2mm，尺寸不得小于U40*30*1.2（宽40mm,高30mm,壁厚1.2mm热镀锌） 3、对由响应供应商提供的F型不锈钢三通，材质可以选用黄铜进行替代。 4、采购文件第二卷“技术规范及要求“中增加T/CECS633-2019 《燃气用户工程不锈钢波纹软管技术规程》。 以上内容在合同中也同步进行调整。 商 除上述变更外，原公告其余内容仍有效。 道 重庆巴南天然气有限责任公司 管 2026-08-20 信息来源:https://www.chinapipe.net/project/d3076704.html cqdingjiu 2026.08.21 10:国06:50 中</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
         <v>80</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>重庆, 天然气表后管道安装工程, 变更公告</t>
         </is>
@@ -1537,34 +1466,29 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>合川区</t>
+          <t>主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300-D800管道130米，新增检查井11座，新建D300排水管道38米；紫外光修复 D300-D800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米，螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米，不锈钢快速锁修复 D1000管道42米；完成 D300-D1000管道清障189米、清淤2627米。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300-D800管道130米，新增检查井11座，新建D300排水管道38米；紫外光修复 D300-D800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米，螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米，不锈钢快速锁修复 D1000管道42米；完成 D300-D1000管道清障189米、清淤2627米。</t>
+          <t>合同预估金额为1708.44万元</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>合同预估金额为1708.44万元</t>
+          <t>排水管道、检查井、紫外线修复设备、螺旋缠绕修复材料、树脂修复材料、不锈钢快速锁修复设备</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>排水管道、检查井、紫外线修复设备、螺旋缠绕修复材料、树脂修复材料、不锈钢快速锁修复设备</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
           <t>合川区中南片区污水管网工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目 合川区中南片区污水管网工程（一期） 名称 招标 网 法人 或招 标人 重庆市合川区住房和城乡建设委员会 名称 （盖 务 章） 项目 批准 文件 合川发改投〔2025〕19 号 商 及文 号 主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300-D800管道130米，新增检查井11座，新 主要 建D300排水管道38米；紫外光修复 D300-D道800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米， 建设 螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米，不锈钢快速锁修复 D1000管道42 内容 米；完成 D300-D1000管道清障189米、清淤2627米。 拟 招 招标文 合同预 招标 管 交 序 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 所 国 重 庆 市 合川 合 招标 区中 主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300- 川 项目 中 南片 D800管道130米，新增检查井11座，新建D300排水管道38米；紫外光修复 公 区 区污 D300-D800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米， 开 公 1 2026-09 1708.44 水管 螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米， 招 共 网工程 不锈钢快速锁修复 D1000管道42米；完成 D300-D1000管道清障189米、清 标 资 （一 淤2627米。 源 期） 交 易 中 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076543.html cqdingjiu 2026.08.21 10:06:50</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
         <v>90</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>重庆, 污水管网工程, 管网修复, 新建工程, 排水管道, 检查井, 紫外线修复, 螺旋缠绕修复, 树脂修复, 不锈钢快速锁修复</t>
         </is>
@@ -1603,32 +1527,31 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>本次采购项目涉及球墨铸铁管及管件的供应，具体包括样品的规格和数量要求。</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>本次采购项目涉及球墨铸铁管及管件的供应，具体包括样品的规格和数量要求。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>球墨铸铁管及管件</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>球墨铸铁管及管件</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
           <t>重庆市自来水有限公司球墨铸铁管及管件2026-2027(2年)采购项目(第二次)答疑补遗文件 重庆市自来水有限公司球墨铸铁管及管件2026-2027（2年）采购项目（第二次）答疑 提问1：样品20CM长含承口吗？如果含承口20CM那就太短，标识LOGO无法体现完整建议≥20CM 答1：球墨铸铁管样品含承口，样品长度≥20CM 网 务 招标人：重庆市自来水有限公司 招标代理机构：重庆水务集团公用工程咨询有限公司 商 2026年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d30道76446.html cqdingjiu 2026.08.21 10:06:50 管 国 中</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
         <v>80</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>重庆, 球墨铸铁管, 管件, 采购项目</t>
         </is>
@@ -1673,12 +1596,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>大足区</t>
+          <t>大足区中心城区和龙水镇市政公共排水设施的运维(材料)。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>大足区中心城区和龙水镇市政公共排水设施的运维(材料)。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1688,19 +1611,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
           <t>大足区中心城区和龙水镇市政公共排水设施运维(材料)更正一号公告 一、更正项 更正项 更正子项 更正前内容 更正后内容 网上投标 网上投标截止时间 2026-08-20 15:00:00 2026-08-25 15:00:00 递交投标响应文件 线下递交投标（响应）文件开始时间 2026-08-20 14:30:00 2026-08-25 14:30:00 递交投标响应文件 线下递交投标（响应）文件截止时间 2026-08-20 15:00:00 2026-08-25 15:00:00 网 开标 开标时间 2026-08-20 15:00:00 2026-08-25 15:00:00 招标采购（附件） 附件 务 二、补遗更正说明 清单限价重新做调整，开标时间已更正，详见更正文件内容 商 三、联系方式 采购执行方： 道 单位名称：重庆誉双项目管理有限公司 联系人：陈老师 联系电话：13996336872 采购需求方： 管 单位名称：重庆市大足区茂泰市政工程有限公司 联系人：谢老师 联系电话：18523539371 信息来源:https://www.chinapipe.net/project/d3076319.html 国 cqdingjiu 2026.08.21 10:06:50 中</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
         <v>80</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>重庆, 管材招标</t>
         </is>
@@ -1745,34 +1663,29 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>璧山区</t>
+          <t>项目主要建设内容包括：1.新建茄果类智能种植温室11256平方米；2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、二氧化碳补施系统1套、智能环境控制系统1套、作业物流装备1套；3.项目后勤及仓储配套（含装修）5000平方米；4.土方回填及场地平整53000平方米；5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米；6.都市农文旅配套建设1000平方米。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>项目主要建设内容包括：1.新建茄果类智能种植温室11256平方米；2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、二氧化碳补施系统1套、智能环境控制系统1套、作业物流装备1套；3.项目后勤及仓储配套（含装修）5000平方米；4.土方回填及场地平整53000平方米；5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米；6.都市农文旅配套建设1000平方米。</t>
+          <t>合同预估金额为9182.25万元</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>合同预估金额为9182.25万元</t>
+          <t>温度调控系统、水肥一体化设备、人工补光系统、二氧化碳补施系统、智能环境控制系统、作业物流装备</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>温度调控系统、水肥一体化设备、人工补光系统、二氧化碳补施系统、智能环境控制系统、作业物流装备</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
           <t>璧山区2026年大路街道三台村智慧设施农业建设项目招标计划表 重庆市工程建设项目招标计划表 项目 璧山区2026年大路街道三台村智慧设施农业建设项目 名称 招标 法人 或招 网 标人 中农良品（重庆）生态农业有限公司 名称 （盖 章） 项目 批准 务 文件 及文 号 主要 1.新建茄果类智能种植温室11256平方米；2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、二氧化碳补施系统1套、智能环境控制系统1套、作业物流 建设 装备1套；3.项目后勤及仓储配套（含装修）5000平方米；4.土方回填及场地平整53000平方米；5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米；6. 内容 都市农文旅配套建设1000平方米。 商 招 拟 标 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 称 道 璧 山 区2026 重 年 庆 大 市 路 公 招标 街 管 共 项目 道 资 三 公 源 台 项目主要建设内容包括：1.新建茄果类智能种植温室11256平方米； 2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、 开 交 1 村 二氧化碳补施系统1套、智能环境控制系统1套、作业物流装备1套； 3.项目后勤及仓储配套（含装修）5000平方米； 4.土方回填及场地平整53000平 2026-09 9182.25 招 易 智 方米； 5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米； 6.都市农文旅配套建设1000平方米。 标 中 慧 心 设 国 璧 施 山 农 分 业 中 建 心 设 项 目 中 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076777.html cqdingjiu 2026.08.21 10:06:51</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
         <v>80</v>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>重庆, 智慧设施农业, 招标计划, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -1817,34 +1730,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>长寿区</t>
+          <t>本项目包括但不限于新建混凝池-三沉池，还建格栅池，厌氧池新增搅拌机，好氧池联通孔短流整改、拆除填料及底部曝气盘，增设可提升曝气系统，原斜管沉淀池改造为二沉池（新增中心筒、改造成多斗排泥、提高液位，更换三角堰），拆除原有污泥池，新增临时污泥储罐务并还建污泥池，污泥堆场临时改建及恢复，实施技改期间的临时排放工程，进行基础的自控改造。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>本项目包括但不限于新建混凝池-三沉池，还建格栅池，厌氧池新增搅拌机，好氧池联通孔短流整改、拆除填料及底部曝气盘，增设可提升曝气系统，原斜管沉淀池改造为二沉池（新增中心筒、改造成多斗排泥、提高液位，更换三角堰），拆除原有污泥池，新增临时污泥储罐务并还建污泥池，污泥堆场临时改建及恢复，实施技改期间的临时排放工程，进行基础的自控改造。</t>
+          <t>企业自筹，出资比例为100%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>企业自筹，出资比例为100%</t>
+          <t>污水处理设备</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>污水处理设备</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
           <t>长寿区江南街道污水处理厂更新改造工程项目公告 长寿区江南街道污水处理厂更新改造工程比选公告 1. 比选条件 本比选项目长寿区江南街道污水处理厂更新改造工程，比选人为重庆环保投资集团有限公司，资金来源为企业 自筹，出资比例为100%。现对该项目进行公开比选，诚邀有兴趣的潜在参选人参与比选。 2. 项目概况与比选范围 网 2.1项目概况：长寿区江南街道污水处理厂更新改造工程包括但不限于以下内容新建混凝池-三沉池；还建格栅池； 厌氧池新增搅拌机，好氧池联通孔短流整改、拆除填料及底部曝气盘，增设可提升曝气系统；原斜管沉淀池改 造为二沉池（新增中心筒、改造成多斗排泥、提高液位，更换三角堰）。拆除原有污泥池，新增临时污泥储罐 务 并还建污泥池；污泥堆场临时改建及恢复；实施技改期间的临时排放工程；进行基础的自控改造。 2.2 比选范围：长寿区江南街道污水处理厂更新改造工程施工图范围中的所有工作内容，包括但不限于土建工 程、设备及安装工程、工艺管道工程、电气工程、临排工程等内容，具体以比选人提供的图纸、技术规范、设 备需求清单、答疑资料、澄清资料、其他补遗资料等相关商内容为准。 2.3 建设地点：重庆市长寿区江南街道。 2.4 工期：110日历天（实际开工日期以监理工道程师签发的工程开工通知明确的开工日期为准），缺陷责任期24 个月。 3. 参选人资格要求 管 3.1 本次比选要求参选人具备以下条件： （1）独立法人资格； （2）建设行政主管部国门颁发的有效的市政公用工程施工总承包二级及以上资质； 3.2 参选人还应在资质、业绩、资金、人员等方面具有相应的服务能力，详见比选文件第二章参选人须知前附 表第1.4.1项内容。 中 3.3本次比选不接受联合体参选。 4. 比选文件的获取 4.1 参选人于2026年8月19日起可自行在重庆水务集团电子商务平台（https://www.cqswjt.cn）上下载比选文件电 子版，以及答疑、补遗等比选截止时间前公布的所有相关资料，不管参选人下载与否，比选人和代理机构都视 为参选人收到以上资料并全部知晓有关比选过程和事宜，如因参选人自身原因未能下载相关资料由此产生的一 切后果由参选人自行负责。各参选单位应随时关注网上（https://www.cqswjt.cn）发布的比选文件及相关修改内容。 4.2 参选人须在重庆水务集团电子商务平台（https://www.cqswjt.cn）进行供应商注册，填写相关信息，审批过后 成为平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标（仍须同时提交纸质版参选文件）。参选 人需提前在重庆水务集团电子商务平台（https://www.cqswjt.cn）上注册、报名，下载比选文件，上传参选文件电 子档并报价。在比选截止时间前未按时报名、报价并上传参选文件电子档、递交纸质版参选文件者，将被否决 参选。 5. 比选文件的递交 5.1 参选文件递交时间：2026年8月 27 日09时00分至09时30分，地点：重庆市两江新区嘉华路36号重庆水务 大厦5楼。 5.2 比选截止时间：2026年8月 27 日09时30分（北京时间）。 5.3 逾期送达的或者未送达指定地点的参选文件，比选人不予受理。 6. 发布比选公告的媒介 本次比选公告在重庆水务集团电子商务平台（https：//www.cqswjt.cn）上发布。 7. 联系方式 比选人：重庆环保投资集团有限公司 地 址：重庆市两江新区礼环南路102号 网 联系人：曹老师 电话：023-71618725 务 代理机构：重庆招标采购（集团）有限责任公司 地址：重庆市江北区五简路2号重庆咨询大厦A座2004室 商 联系人：高老师 电话：023-67706841 道 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 管 信息来源:https://www.chinapipe.net/project/d3076456.html cqdingjiu 2026.08.21 10:06:51 国 中</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
         <v>90</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 污水处理厂</t>
         </is>
@@ -1889,34 +1797,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>潼南区</t>
+          <t>本项目包括两个子项目：一是潼南区新胜镇污水处理厂的更新改造，主要内容是新增一体化污水处理设备基础，更新现有污水处理系统设备，升级处理系统，新建风机房-配电室防尘防渗地坪；二是潼南区双江镇污水处理厂的更新改造，内容包括将原有斜管沉淀池改建为好氧池，新建竖流沉淀池，更新老旧及故障设备，新建储药加药区和一体化危废储存间，完善污水处理配套设施。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>本项目包括两个子项目：一是潼南区新胜镇污水处理厂的更新改造，主要内容是新增一体化污水处理设备基础，更新现有污水处理系统设备，升级处理系统，新建风机房-配电室防尘防渗地坪；二是潼南区双江镇污水处理厂的更新改造，内容包括将原有斜管沉淀池改建为好氧池，新建竖流沉淀池，更新老旧及故障设备，新建储药加药区和一体化危废储存间，完善污水处理配套设施。</t>
+          <t>本项目资金来源为企业自筹，出资比例为100%。</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>本项目资金来源为企业自筹，出资比例为100%。</t>
+          <t>污水处理设备、一体化设备、沉淀池、好氧池、竖流沉淀池、储药加药区、一体化危废储存间、污水处理配套设施</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>污水处理设备、一体化设备、沉淀池、好氧池、竖流沉淀池、储药加药区、一体化危废储存间、污水处理配套设施</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
           <t>潼南区新胜镇、双江镇污水处理厂更新改造工程项目项目公告 潼南区新胜镇、双江镇污水处理厂更新改造工程比选公告 1. 比选条件 本比选项目潼南区新胜镇、双江镇污水处理厂更新改造工程，比选人为重庆环保投资集团有限公司，资金来源 为企业自筹，出资比例为100%。现对该项目进行公开比选，诚邀有兴趣的潜在参选人参与比选。 2. 项目概况与比选范围 网 2.1项目概况：潼南区新胜镇污水处理厂更新改造工程，主要建设内容为新增200m?/d一体化污水处理设备基础； 更新现有污水处理系统设备，提高现有沉淀池二沉池、三沉池液位；升级处理系统（干化池改建为污泥池，新 增叠螺脱水机，改建污泥堆场及雨棚）；新建风机房－配电室防尘防渗地坪。潼南区双江镇污水处理厂更新改 务 造工程，主要建设内容为将原有斜管沉淀池改建为好氧池，新建3座竖流沉淀池，配套安装相关设备；更新污水 处理系统中老旧及故障设备；新建储药加药区与一体化危废储存间，完善污水处理配套设施。 2.2 比选范围：潼南区新胜镇、双江镇污水处理厂更新改造工程施工图范围中的工作内容（一体化设备采购及 相关安装工作除外），包括但不限于土建工程、附属工程商（包括但不限于绿化工程、工艺管线工程、电气及自 控工程、临排清淤工程等）、一体化污水处理设备基础、标准化建设、配套设备材料采购及安装工程等内容， 其中一体化设备采购及相关安装工作不在本次比选范围内；具体以比选人提供的图纸、技术规范、工程量清单、 答疑资料、澄清资料、其他补遗资料等相关内容为准。 道 2.3 建设地点：潼南区新胜镇、双江镇。 2.4 工期：120日历天（实际开工日期以监理工程师签发的工程开工通知明确的开工日期为准），缺陷责任期24 个月。 管 3. 参选人资格要求 3.1 本次比选要求参选人具备以下条件： 国 （1）独立法人资格； （2）建设行政主管部门颁发的有效的市政公用工程施工总承包二级及以上资质； 中 3.2 参选人还应在资质、业绩、资金、人员等方面具有相应的服务能力，详见比选文件第二章参选人须知前附 表第1.4.1项内容。 3.3本次比选不接受联合体参选。 4. 比选文件的获取 4.1 参选人于2026年8月19日起可自行在重庆水务集团电子商务平台（https://www.cqswjt.cn）上下载比选文件电 子版，以及答疑、补遗等比选截止时间前公布的所有相关资料，不管参选人下载与否，比选人和代理机构都视 为参选人收到以上资料并全部知晓有关比选过程和事宜，如因参选人自身原因未能下载相关资料由此产生的一 切后果由参选人自行负责。各参选单位应随时关注网上（https://www.cqswjt.cn）发布的比选文件及相关修改内容。 4.2 参选人须在重庆水务集团电子商务平台（https://www.cqswjt.cn）进行供应商注册，填写相关信息，审批过后 成为平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标（仍须同时提交纸质版参选文件）。参选 人需提前在重庆水务集团电子商务平台（https://www.cqswjt.cn）上注册、报名，下载比选文件，上传参选文件电 子档并报价。在比选截止时间前未按时报名、报价并上传参选文件电子档、递交纸质版参选文件者，将被否决 参选。 5. 比选文件的递交 5.1 参选文件递交时间：2026年8月27日09时00分至09时30分，地点：重庆市两江新区嘉华路36号重庆水务大厦5 楼。 5.2 比选截止时间：2026年8月27日09时30分（北京时间）。 5.3 逾期送达的或者未送达指定地点的参选文件，比选人不予受理。 6. 发布比选公告的媒介 本次比选公告在重庆水务集团电子商务平台（https：//www.cqswjt.cn）上发布。 7. 联系方式 网 比选人：重庆环保投资集团有限公司 地 址：重庆市两江新区礼环南路102号 务 联系人：陈老师 电话：023-42756696 商 代理机构：重庆招标采购（集团）有限责任公司 道 地址：重庆市江北区五简路2号重庆咨询大厦A座2004室 联系人：高老师 管 电话：023-67706841 重庆水务电子商务平台国咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3076454.html cqdingjiu 2026.08.21 10:06:51 中</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
         <v>90</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 污水处理厂更新改造</t>
         </is>
@@ -1955,32 +1858,31 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>给重庆医科大学附属第二医院医疗教学配套业务用房配置第二市政水源</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>给重庆医科大学附属第二医院医疗教学配套业务用房配置第二市政水源</t>
+          <t>采购预算 409674.71元</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>采购预算 409674.71元</t>
+          <t>市政水源</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>市政水源</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
           <t>重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表 重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表 采购需求单位(全称) 重庆医科大学附属第二医院总务科 项目名称 重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程 项目内容 给重庆医科大学附属第二医院医疗教学配套业务用房配置第二市政水源 采购预算 409674.71元 网 拟采购供应商全称 东部自来水分公司 配套业务用房第二市政水源从重庆水资源产业股份有限公司东部自来水分公司管辖范围 单一来源采购理由 的管网具体接入，属于市政管网施工，具有特殊要求。 务 公示时间 2026年8月19日-2026年8月25日 联系人及联系电话 刘老师 023-63693215 注：1.以上陈述是否真实，欢迎社会各界监督，公示时间商至少5个工作日； 2.公示期内无异议的，采购管理处将进行该项目采购；有异议请将意见反映采购人。 信息来源:https://www.chinapipe.net/project/d30道76334.html cqdingjiu 2026.08.21 10:06:51 管 国 中</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
         <v>80</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -2025,34 +1927,29 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>黔江区</t>
+          <t>本项目服务内容为G319黔江区正阳至城西段改建工程管线探测工作。</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>本项目服务内容为G319黔江区正阳至城西段改建工程管线探测工作。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>管线探测工作</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>管线探测工作</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
           <t>中铁二院工程集团有限责任公司G319黔江区正阳至城西段改建工程管线探测工作线上询价采购公告 中铁二院工程集团有限责任公司G319黔江区正阳至城西 段改建工程管线探测工作线上询价采购 ZTEYCQ-XJ-2026-019 网 采购单位: 中铁二院工程集团有限责任公司 发布时间: 2026-08-19 16:10 报价截止时间: 务 2026-08-21 17:00 招标方联系人: 杨先生 招标方联系电话: 商 13883021521 招标方邮箱: 监督方联系人: 李先生 道 监督方联系电话: 15823237919 监督方邮箱: 保证金: 0元 管 结算与发票信息: 详情 交货信息: 详情 国 其他说明事项: 标的明细 流水号：询2026081900304 中 计量单 技术标准及要 序号 标的名称 数量 交货期 送货地址 位 求 G319黔江区正阳至城西段 合同签订后5天内完成 西南区-重庆市-市辖 1 1 项 详见询价文件 改建工程管线探测工作 本项目服务内容。 区-黔江区-项目地点 信息来源:https://www.chinapipe.net/project/d3076309.html cqdingjiu 2026.08.21 10:06:51</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
         <v>80</v>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类, 匹配程度, 匹配关键词</t>
         </is>
@@ -2097,34 +1994,29 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>本项目主要涉及室外蒸汽管道φ219x6mm的安装，管道材质为20#，地上敷设，蒸汽管道运行压力1.08MPa，管道设计压力1.2MPa。蒸汽管道系统包括从锅炉房分汽缸到6#和8#车间分汽缸的所有蒸汽管道、管件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸等的采购、运输、安装、保温工作。还包括钢结构桁架工程的采购、运输、制作、安装、防腐工作，以及管道附件及控制系统的采购、运输、安装、接线等工作。此外，还需要进行调试与验收，确保蒸汽管道系统能够正常使用并备案。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>本项目主要涉及室外蒸汽管道φ219x6mm的安装，管道材质为20#，地上敷设，蒸汽管道运行压力1.08MPa，管道设计压力1.2MPa。蒸汽管道系统包括从锅炉房分汽缸到6#和8#车间分汽缸的所有蒸汽管道、管件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸等的采购、运输、安装、保温工作。还包括钢结构桁架工程的采购、运输、制作、安装、防腐工作，以及管道附件及控制系统的采购、运输、安装、接线等工作。此外，还需要进行调试与验收，确保蒸汽管道系统能够正常使用并备案。</t>
+          <t>项目总投资额为580.643717万元，全部为企业自筹资金。</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>项目总投资额为580.643717万元，全部为企业自筹资金。</t>
+          <t>蒸汽管道、管件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸、钢结构桁架、阀门、压力表、温度表、流量计、电动/气动执行机构、配套仪表电缆、桥架、保护管</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>蒸汽管道、管件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸、钢结构桁架、阀门、压力表、温度表、流量计、电动/气动执行机构、配套仪表电缆、桥架、保护管</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
           <t>乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告 乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告 1.招标条件 本招标项目乌江涪陵榨菜绿色智能化生产基地(一期)已由重庆市涪陵区发展和改革委员会以重庆市企业投资项目 备案证2020-500102-13-03-000003 批准建设，项目业主为重庆市涪陵榨菜集团股份有限公司，建设资金来自企业 自筹，项目出资比例为100% ，招标人为重庆市涪陵榨菜集团股份有限公司。项目已具备招标条件，现对乌江 涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 2.1 建设地点： 重庆市涪陵区马鞍街道人和社区 。 网 2.2 项目概况与建设规模：建筑面积约369384.27㎡。本项目蒸汽管道主要为室外蒸汽管道φ219x6mm，管道材质： 20#地上敷设，由14#锅炉房分汽缸分别接至6#和8#智能化车间分汽缸，蒸汽管道运行压力1.08MPa，管道设计压 力1.2MPa。 务 2.3 本次招标项目合同估算金额：580.643717万元。 2.4 招标范围： 商 （1）蒸汽管道系统本体：从锅炉房分汽缸后（含分气缸阀门）至6#车间、8#车间分气缸处，所有蒸汽管道、管 件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸等的采购、运输、安装、保温（含保温层及保 护层）工作。 道 （2）钢结构桁架工程：负责本项目范围内所有钢结构架空桁架（管廊）的采购、运输、制作、安装、防腐工作。 （3）管道附件及控制系统：负责本工程范围内所有阀门、压力表、温度表、流量计、电动/气动执行机构以及配 套仪表电缆、桥架、保护管的采购、运输、安装、接线。负责与DCS/PLC系统接口的接线与联动调试。 管 （4）调试与验收：组织并确保整个蒸汽管道系统（含分气缸后段末端管道、桁架及其安全附件）通过项目所在 地特种设备安全监察管理部门实施的安装监督检验。负责报检、配合现场检验、整改、出具深化图纸并由设计 单位审核盖章、特种设备法定报检取证的全部费用，包括但不限于：施工前办理安装告知，设计院盖章审核， 施工中接受并通过安装国监督检验，最终负责取得《压力管道安装监督检验证书》与《特种设备使用登记证》， 确保蒸汽管道投入使用并备案，提交全套法定检验报告。 （5）土建工作部分 中 1）管架和桁架基础的施工，包括但不限于钢结构桁架的混凝土独立基础的土方开挖、浇筑、养护及回填恢复。 2）管道穿墙/板孔洞的开挖、封堵与修复。 3）室内外地面的开挖（包括但不限于疏水井、沟槽开挖、通行地沟、设备基础开挖）与恢复（包括但不限于土 方回填、渣土弃运、地面硬化）。 4）桁架及设备接地线的施工，包括但不限于接地极制作、接地干线敷设，并与厂区主接地网可靠连接，接地电 阻测试合格。 具体详见施工图、招标文件、工程量清单、答疑补遗等资料。 2.5 工期要求： 60 日历天 缺陷责任期要求： 24 个月 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：投标人应同时具备以下(1)、(2)项资质： （1）具备建设行政主管部门颁发的有效的建筑工程施工总承包二级及以上资质； （2）具备有效的《中华人民共和国特种设备生产许可证》（许可子项目：工业管道安装GC2级及以上）。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 网 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 务 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（涪陵区） （https://www.cqggzy.com/fulingweb/）下载招标文件、工程商量清单、电子图纸等资料。参与投标的投标人需在重 庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏 “主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网（涪陵区道）（https://www.cqggzy.com/fulingweb/）本项目招标公告网页下 方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-23 17:00:00前。 4.3招标人应于2026-08-24 18:00:00前在重庆市公共资源交易网（涪陵区）（https://www.cqggzy.com/fulingweb/）发 布澄清。 5.投标文件递交的内容 管 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-09 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 国 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（涪陵区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 中重庆市涪陵榨菜集团股份有限公司 代理机构: 中招国际招标有限公司 重庆两江新区黄山大道中段53号5-1（双 地 址: 重庆市涪陵区江北街道办事处二渡村一组 地 址: 鱼座A栋5楼） 邮 编: 408000 邮 编: 项目负责人: 徐老师 项目负责人: 寿云凤 电 话: 13212467016 电 话: 023-68881331-9032 传 真: 传 真: 电子邮箱: bsd2me@126.com 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市涪陵区发展和改革委员会 电 话: 023-72203687 2026年08月19日 乌江 涪陵 榨菜 绿色 智能 化生 产基地 (一 期)6#、 8#车 网 间蒸 汽管 道安 装工 务 程 中 中 国 国 重 银 重 商民 重 庆 行 庆 生 庆 涪 股 涪 银 涪 陵 份 陵 行 陵 重 投 公 有 道公 股 公 庆 标 共 限 共 份 共 银 开 保 户 资 公 资 有 资 行 户 证 110292140553VA00154 9902001860445897 430102029007791845-275 名 源 司 源 限 源 涪 行 金 交 重 交 公 交 陵 账 管 易 庆 易 司 易 支 号 有 涪 有 重 有 行 限 陵 限 庆 限 公 马 公 涪 公 国 司 鞍 司 陵 司 支 支 行 行 中 信息来源:https://www.chinapipe.net/project/d3076300.html cqdingjiu 2026.08.21 10:06:51</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
         <v>95</v>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>重庆, 蒸汽管道, 安装工程, 资金情况, 产品种类</t>
         </is>
@@ -2169,34 +2061,29 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>巴南区</t>
+          <t>完成重庆国际生物城配套公寓项目（民用1020户）天然气表后管道定制化服务。（含安装燃气输送用不锈钢波纹管RSB-IF-13—12240米（预估）、双外螺纹球阀DN15-1020个、燃气管道自闭阀DN15-1020个，其它配套管件及辅材，墙体管道暗埋等）</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>完成重庆国际生物城配套公寓项目（民用1020户）天然气表后管道定制化服务。（含安装燃气输送用不锈钢波纹管RSB-IF-13—12240米（预估）、双外螺纹球阀DN15-1020个、燃气管道自闭阀DN15-1020个，其它配套管件及辅材，墙体管道暗埋等）</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>天然气表后管道定制化服务</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>天然气表后管道定制化服务</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
           <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程询比采购公告 采购公告 公告编号： RQXYGG202608190057 一、采购项目基本情况 采购人：重庆巴南天然气有限责任公司 网 采购项目编号：RQCGXY202608170010 采购项目名称：重庆国际生物城配套公寓项目天然气表后管道安装工程 务 采购内容和范围：完成重庆国际生物城配套公寓项目 （民用1020户）天然气表后管道定制化服务。（含安装燃 气输送用不锈钢波纹管RSB-IF-13—12240米（预估）、双外螺纹球阀DN15-1020个、燃气管道自闭阀DN15-1020个， 其它配套管件及辅材，墙体管道暗埋等） 二、供应商资格要求 商 1. 资质要求:资质要求： 1.响应供应商为中华人民共和国境内合法注册的独立法人或其他组织，具有独立承担民事责任能力，具有独立订 立合同的权利。 道 2.响应供应商应具备市政公用工程施工总承包三级及以上资质、具备有效的安全生产许可证。 3.响应供应商应为本项目配备项目负责人一名，持有市政公用工程或机电工程专业二级建造师及以上资质，且为 本单位在职人员并提供社保证明。 4.响应供应商应为本项目配备专职安全员一名，持有安全生产考核合格C证，且为本单位在职人员并提供社保证 管 明。 5.项目负责人及专职安全员社保证明期限须包含2026年5月至2026年7月。提供的社保证明，须体现上述人员的姓 名、身份证号（或社保号）、单位名称、本单位参保时间（或起始参保时间），并带有社保部门公章或社保部 门的有效电子印章。 2. 信用要求:6.信用要求国： （1）响应供应商（含联合体响应的成员单位）未被“国家企业信用信息公示系统” 网站（www.gsxt.gov.cn）列 入严重违法失信企业名单（如：提供网站查询界面截图）； （2）响应供应商（含联合体响应的成员单位）未被 “信用中国”网站（www.creditchina.gov.cn）列入严重失信 主体名单（中如：提供网站查询界面截图）。 三、采购文件的获取 采购文件在 华润守正采购交易平台 发布，不再另行线下提供纸质采购文件，凡有意参与者请自行登录守正平台 查看和下载采购文件。 四、响应文件的提交 响应文件提交 / 报价截止时间： 2026-08-25 08:00:00 （北京时间，若有变化另行通知）。 响应文件提交 / 报价方式：在响应文件提交 / 报价截止时间前，通过 华润守正采购交易平台 提交电子响应文件或 报价，逾期提交将被拒收。 五、采购人联系方式 联系人：何俊 电话：15178855716 邮箱：1460553040@qq.com 六、采购明细 行号 采购内容 需求数量 单位 补充说明 1 重庆国际生物城配套公寓项目天然气表后管道定制化服务 1 元/次 具体内容详见采购文件 七、答疑澄清、通知 答疑澄清、通知等文件一经在 华润守正采购交易平台 发布，视为已发放给相应供应商（发放时间即为发出时 间），请随时关注 华润守正采购交易平台 发布的相关信息，并及时查阅和处理。 八、服务费交纳 网 本项目向成交人收取服务费,供应商收到预成交通知书和服务费交款通知书10日内,向平台运营方(华润守正招标有 限公司)支付服务费,经确认无误后由采购人发送成交通知书。平台运营方在收到服务费后向成交人开具服务费发 票。 收费标准：项目总成交金额＜50万元的采购项目，免收服务费。项目总成交金额≥50万元的采购项目，按成交金 务 额的0.15%向成交人收取（金额四舍五入，精确到分）。单项目总收费封顶100000元。其他说明：（1）总价采购， 收费基数为成交金额；单价、费率采购，收费基数为预算金额。（2）单项目存在多个成交人情形的，按总成交 金额计算收费总额，各成交人按成交比例分摊；项目总成交金额50万以上，但单个成交人成交金额少于50万仍按 比例收取服务费。 商 退款说明：成交通知书发布后,平台提供相关服务已完成,成交人已交纳服务费不予退还。 多成交人服务费收取示例： 以某项目总成交金额100万为例,A、B、C多成交人情形,总服务费为0.15万, 供应商A成交金额为50万,A服务费为0.075万; 供应商B成交金额为30万,B服务费为0.045万; 道 供应商C成交金额为20万,C服务费为0.03万。 九、其它事项 管 1.本公告在 华润守正采购交易平台 ( https://www.szecp.com.cn/ )上公开发布。 2.本项目采购通过守正平台线上进行，供应商需注册 华润守正采购交易平台 ，通过平台进行响应文件的递交或 报价，具体操作步骤可查阅网站首页帮助中心的操作手册，也可以联系守正客服。 国 3.如对采购项目有异议，请登录 华润守正采购交易平台 ,通过异议菜单提出。 2026年08月19日 中 信息来源:https://www.chinapipe.net/project/d3076125.html cqdingjiu 2026.08.21 10:06:52</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
         <v>80</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>重庆, 天然气表后管道安装工程, 管材招标</t>
         </is>
@@ -2235,32 +2122,31 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>重庆市映天辉氯碱化工有限公司拟开展废盐综合利用联产20万吨/年离子膜烧碱项目(一期12万吨/年)建设。</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>重庆市映天辉氯碱化工有限公司拟开展废盐综合利用联产20万吨/年离子膜烧碱项目(一期12万吨/年)建设。</t>
+          <t>项目资金来自业主自筹，项目出资比例为100%。本次招标项目货物采购估算金额约为330万元。</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>项目资金来自业主自筹，项目出资比例为100%。本次招标项目货物采购估算金额约为330万元。</t>
+          <t>非金属管道管件阀门</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>非金属管道管件阀门</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
           <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)非金属管道管件阀门采购招标公告 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采购招标公告 1、招标条件 本招标项目废盐综合利用联产20万吨/年离子膜烧碱项目已由重庆市长寿区发展和改革委员会以 重庆市企业投 资项目备案证（2207-500115-04-05-168305）批准建设，项目业主为重庆市映天辉氯碱化工有限公司，建设资金来 自业主自筹，项目出资比例为100%，招标人为重庆市映天辉氯碱化工有限公司。项目已具备招标条件，现对本 项目的（一期12万吨/年）非金属管道管件阀门采购进行公开招标。 网 2、项目概况 2.1 建设地点：重庆长寿经济技术开发区化北路2号。 务 2.2、项目概况与建设规模： 重庆市映天辉氯碱化工有限公司（以下简称“映天辉”）位于重庆长寿经济技术开发区化北路2号，始建于2004 年5月，占地430亩，注册资本34800万元。现为国有控股企商业，是一家集氯碱生产经营、新材料研发经营于一体 的专业型、科技型综合企业，系国家级高新技术企业。 映天辉作为长寿经开区氯碱产业基础平台的龙头化工企业，现有一条氯碱生产线，生产规模为20万吨/年烧碱 （折100%NaOH计）。为建设并贯通氯碱化工道循环经济产业链，保障下游产业链装置氯气需求，实现氯碱产品的 升级和高端化发展，增加产品附加值，降低成本，提高竞争力，映天辉公司经过充分调研和反复论证后，拟开 展废盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）建设。装置在正常运行情况下，按照每年 8000 小时操作。具体要求及参数以第五章货物需求一览表及技术规格标准和要求为准。 管 2.3 本次招标项目货物采购估算金额： 约 330 万元。 2.4招标范围： 本次招标项目为：“废国盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采 购”包括不限于非金属管道管件阀门所含设计、制造、试验、出厂检验、防腐、运输（含保护、包装及运输、 货到现场车板交货）、保险（交货验收前）、指导安装、调试、备件及专用工具、税费、技术资料和图纸及质 保期内的各种备品、备件的供应及相关的技术服务、产品质量证明书及原材料检测报告等。（详见“第五章货 物需求一览中表及技术规格标准和要求”）。 2.5 交货地点：货物运送至买方指定地点； 2.6 交货期： 2.6.1合同签订后3个月内，所有货物运送招标人现场并具备安装条件。 2.6.2 中标方应于合同签订之日起7天内，向买方提交完整的技术资料，以供设计院开展相关设计工作。 3、投标人资格要求 3.1 投标人应符合以下要求： （1）投标人具备有效的营业执照。 注：不得将投标人营业执照记载的经营范围作为评审因素。 （2）投标人具备有效的《中华人民共和国特种设备生产许可证》压力管道管子-B级及以上资质、压力管道管 件B2级及以上资质； （3）投标人具备塑料管道管子、管件的型式试验证书。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3本次招标不接受代理商投标，不接受联合体投标。 4. 招标文件的获取 4.1 凡愿意参加的潜在投标人，从2026年 8 月19 日起至投标截止时间前，均可登录重庆市公共资源交易网 （www.cqggzy.com）直接下载获取招标文件、答疑等开标前的有关资料。在公告期间，各投标人应随时关注网上 发布的招标文件答疑、补遗、澄清等文件内容，不管投标人是否下载，均视为已知晓招标文件的全部内容和有 关事宜。本项目不需要报名，直接投标。 网 5.投标文件的递交 5.1 投标文件递交的截止时间为 2026年 9 月10 日上午09时30分，地点在重庆市公共资源交易中心开标厅（地 址：重庆市两江新区青枫北路6号渝兴广场B10栋2层），具体开标地点详见一、二楼大厅显示屏。 务 5.2逾期送达的或者未送达指定地点的，或者未按照招标文件要求密封的投标文件，招标人将拒收。 6、发布公告的媒介 商 本次招标公告在中国招标投标公共服务平台、重庆市公共资源交易网上发布。 7、联系方式 道 招 标 人：重庆市映天辉氯碱化工有限公司 地 址：重庆长寿经济技术开发区化北路二号 管 联 系 人：张先生 电 话：023-40717888 国 招标代理机构： 重庆招标采购（集团）有限责任公司 地 址：重庆市两江新区五里店五简路2号重庆咨询大厦A栋20楼2001室 中 项目负责人：彭文婷 电 话： 023-67703002 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采购 户名 开户行 投标保证金账号 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000631258 支行 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051303372 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630010400 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000002549 贸易试验区分行 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835014652 坝支行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146619529 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764260665 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020038958 信息来源:https://www.chinapipe.net/project/d3076119.html cqdingjiu 2026.08.21 10:06:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
         <v>85</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标, 资金, 产品</t>
         </is>
@@ -2299,32 +2185,31 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>重庆市映天辉氯碱化工有限公司拟开展废盐综合利用联产20万吨/年离子膜烧碱项目(一期12万吨/年)，包括衬氟管道及管件的采购。</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>重庆市映天辉氯碱化工有限公司拟开展废盐综合利用联产20万吨/年离子膜烧碱项目(一期12万吨/年)，包括衬氟管道及管件的采购。</t>
+          <t>项目资金来自业主自筹，项目出资比例为100%。货物采购估算金额约为225万元。</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>项目资金来自业主自筹，项目出资比例为100%。货物采购估算金额约为225万元。</t>
+          <t>衬氟管道及管件</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>衬氟管道及管件</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
           <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)衬氟管道及管件采购招标公告 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）衬氟管道及管件采购招标公告 1、招标条件 本招标项目废盐综合利用联产20万吨/年离子膜烧碱项目已由重庆市长寿区发展和改革委员会以 重庆市企业投 资项目备案证（2207-500115-04-05-168305）批准建设，项目业主为重庆市映天辉氯碱化工有限公司，建设资金来 自业主自筹，项目出资比例为100%，招标人为重庆市映天辉氯碱化工有限公司。项目已具备招标条件，现对本 项目的（一期12万吨/年）衬氟管道及管件采购进行公开招标。 网 2、项目概况 2.1 建设地点：重庆长寿经济技术开发区化北路2号。 务 2.2、项目概况与建设规模： 重庆市映天辉氯碱化工有限公司（以下简称“映天辉”）位于重庆长寿经济技术开发区化北路2号，始建于2004 年5月，占地430亩，注册资本34800万元。现为国有控股企商业，是一家集氯碱生产经营、新材料研发经营于一体 的专业型、科技型综合企业，系国家级高新技术企业。 映天辉作为长寿经开区氯碱产业基础平台的龙头化工企业，现有一条氯碱生产线，生产规模为20万吨/年烧碱 （折100%NaOH计）。为建设并贯通氯碱化工道循环经济产业链，保障下游产业链装置氯气需求，实现氯碱产品的 升级和高端化发展，增加产品附加值，降低成本，提高竞争力，映天辉公司经过充分调研和反复论证后，拟开 展废盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）建设。装置在正常运行情况下，按照每年 8000 小时操作。具体要求及参数以第五章货物需求一览表及技术规格标准和要求为准。 管 2.3 本次招标项目货物采购估算金额： 约225万元。 2.4招标范围： 本次招标项目为：“废国盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）衬氟管道及管件采购一批” 包括但不限于制造、涂漆、包装、运输、配合验收工作、检验检测、产品质量证明书等。（详见“第五章货物 （材料）需求一览表及技术规格标准和要求”）。 2.5 交货地点：货物运送至买方指定地点； 中 2.6 交货期： 2.6.1合同签订后 3个月内，所有货物运送招标人现场并具备安装条件。 2.6.2 中标方应于合同签订之日起7天内，向招标方提交完整的技术资料，以供设计院开展设备相关设计工作。 3、投标人资格要求 3.1 投标人应符合以下要求： （1）投标人具备有效的营业执照。 注：不得将投标人营业执照记载的经营范围作为评审因素。 （2）具备有效的《中华人民共和国特种设备生产许可证》-压力管道元件制造-元件组合装置。 （3）具有防腐管道元件特种设备型式试验证书。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3本次招标不接受代理商投标，不接受联合体投标。 4、招标文件的获取 4.1 凡愿意参加的潜在投标人，从2026年8 月 19 日起至投标截止时间前，均可登录重庆市公共资源交易网 （www.cqggzy.com）直接下载获取招标文件、答疑等开标前的有关资料。在公告期间，各投标人应随时关注网上 发布的招标文件答疑、补遗、澄清等文件内容，不管投标人是否下载，均视为已知晓招标文件的全部内容和有 关事宜。本项目不需要报名，直接投标。 5、投标文件的递交 5.1 投标文件递交的截止时间为 2026年 9 月 10 日上午09时30分，地点在重庆市公共资源交易中心开标厅 （地址：重庆市两江新区青枫北路6号渝兴广场B10栋2层），具体开标地点详见网一、二楼大厅显示屏。 5.2逾期送达的或者未送达指定地点的，或者未按照招标文件要求密封的投标文件，招标人将拒收。 6、发布公告的媒介 务 本次招标公告在 中国招标投标公共服务平台、重庆市公共资源交易网上发布。 7、联系方式 商 招 标 人：重庆市映天辉氯碱化工有限公司 地 址：重庆长寿经济技术开发区化北路二号 道 联 系 人：张先生 电 话：023-40717888 管 招标代理机构： 重庆招标采购（集团）有限责任公司 地 址：重庆市两江新区国五里店五简路2号重庆咨询大厦A栋20楼2001室 项目负责人：彭文婷 电 话： 023-67703002 中 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）衬氟管道及管件采购 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630011190 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835003139 坝支行 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000000834 贸易试验区分行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146638621 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051302432 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000620855 支行 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020013554 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764235261 信息来源:https://www.chinapipe.net/project/d3076111.html cqdingjiu 2026.08.21 10:06:52</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
         <v>85</v>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>重庆, 废盐综合利用, 离子膜烧碱, 衬氟管道, 管件采购</t>
         </is>
@@ -2369,34 +2254,29 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>永川区</t>
+          <t>蒸汽管道改造</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>蒸汽管道改造</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>蒸汽管道</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>蒸汽管道</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
           <t>重庆市益康环保工程有限公司永川分公司蒸汽管道改造项目询价采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3076108.html cqdingjiu 2026.08.21 10:06:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
         <v>60</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>重庆, 蒸汽管道, 改造项目, 询价采购</t>
         </is>
@@ -2441,34 +2321,29 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>南岸区</t>
+          <t>包括改造市政混接点194个，改造管网8582米，缺陷管网开挖修复1355米，非开挖修复8679米。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>包括改造市政混接点194个，改造管网8582米，缺陷管网开挖修复1355米，非开挖修复8679米。</t>
+          <t>总投资概算未明确具体金额，但合同预估金额为6600万元。</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>总投资概算未明确具体金额，但合同预估金额为6600万元。</t>
+          <t>排水管网改造</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>排水管网改造</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
           <t>南岸区融侨大道、江南大道片区2023年排水管网改造项目(三标段)招标计划表 重庆市工程建设项目招标计划表 项目名 南岸区融侨大道、江南大道片区 2023年排水管网改造项目（三标段） 称 网 招标法 人或招 重庆市南岸区城市建设发展（集团）有限公司 标人名称 （盖章） 务 项目批 准文件 南岸发改〔2024〕304《南岸区融侨大道、江南大道片区2023年排水管网改造项目总投资概算的批复》 及文号 主要建 包括改造市政混接点194个，改造管网8582米，商管径d300~d1500;缺陷管网开挖修复1355米，管 设内容 径d300~d600;非开挖修复8679米，管径d300~d1200。 招标文件 拟交 合同预估 招标内 招标 序号 招标项目名称 计划发布 易场 金额(万 备注 道容 方式 时间 所 元) 51处雨 污混错 重庆 招标项 接点位 管 市公 目 改 南岸区融侨大道、江南大道片区 2023年排 公开 共资 1 造，1082 2026-08 6600.00 水管网改造项目（三标段） 招标 源交 个管网 易中 三四级 国 心 缺陷修 复。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 中 信息来源:https://www.chinapipe.net/project/d3076097.html cqdingjiu 2026.08.21 10:06:52</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
         <v>80</v>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>重庆, 排水管网改造, 资金情况, 产品种类</t>
         </is>
@@ -2513,34 +2388,29 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>永川区</t>
+          <t>项目位于永川区三教镇，项目占地面积41673.42㎡（62.51亩），总建筑面积6078.71㎡，新建净水厂1座，规模5万吨/天，新建厂外管网4.6km（DN200～DN1000），配套建设净水处理系统、排泥水处理系统、综合楼、生产建（构）筑物以及附属建筑物等。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>项目位于永川区三教镇，项目占地面积41673.42㎡（62.51亩），总建筑面积6078.71㎡，新建净水厂1座，规模5万吨/天，新建厂外管网4.6km（DN200～DN1000），配套建设净水处理系统、排泥水处理系统、综合楼、生产建（构）筑物以及附属建筑物等。</t>
+          <t>项目合同额1.7亿元</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>项目合同额1.7亿元</t>
+          <t>钢筋混凝土排水管</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>钢筋混凝土排水管</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
           <t>中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购公告 永川三教水厂项目 已具备采购条件，现公开邀请供应商参加询比采购活动。 1.采购项目简介 1.1 采购项目名称：中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购。 1.2 采购方案编号：FA00000663117。 网 1.3 采购人：中交一公局重庆工程有限公司。 1.4 采购代理机构：/。 务 1.5 采购项目资金：已落实 1.6 采购项目概况： 商 永川三教水厂项目：项目位于永川区三教镇，项目占地面积41673.42㎡（62.51亩），总建筑面积6078.71㎡，新建 净水厂1座，规模5万吨/天，新建厂外管网4.6km（DN200～DN1000），配套建设净水处理系统、排泥水处理系统、 综合楼、生产建（构）筑物以及附属建筑物等。项目合同额1.7亿元，工期450天。 道 项目地址：重庆市永川区。 2.采购范围及相关要求 管 2.1 采购范围：钢筋混凝土排水管。 2.2 交货期：2026年9月-2026年12月。 2.3 交货地点：重庆市永国川区项目指定地点。 2.4 物资质量标准：满足《混凝土和钢筋混凝土排水管》（GB/T 11836-2023）的相关要求。 3.供应商资格要求 中 3.1 供应商应依法设立且满足如下要求： （1）资质要求：本次询比采购要求供应商须是在中华人民共和国境内依法注册，具有合法有效的营业执照、税 务登记、组织机构代码等证件，具有独立法人资格、具有采购物资生产经营范围的生产商或代理商（销售商）。 （2）财务要求：供应商必须是经税务部门注册登记核准的纳税人，有依法纳税的良好记录。 （3）业绩要求：无。 （4）信誉要求：无不良履约记录、未列入工程所在地质量监督部门和中国交建、中交一公局集团企业黑名单。 因质量原因被交通部质监站通报，正在进行整改的生产厂家和产品不得参与投标。生产商或代理商（销售商） 具有良好的社会信誉，近3年内没有与骗取合同有关的犯罪或严重违法行为而引起的诉讼和仲裁；近3年不曾在合 同中严重违约或被逐；财产未被接管或冻结，企业未处于禁止或取消投标状态；在最高人民法院、信用中国 （www.creditchina.gov.cn）或各级信用信息共享平台查询拟入库单位无不良行为记录。 （5）其他要求：无。 3.2 供应商不得存在下列情形之一： （1）处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； （2）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （3）已列入黑名单，且未解除限制期限； （4）其他：无。 4.供应商报名 4.1 有意参加询比采购活动的单位，请于2026年8月19日15时00分至2026年8月26日17时00分（北京时间，下同，法 定公休日、节假日不休），登录“中交招采网”（网址：https://zjzcw.iccec.cn）进行报名并下载采购文件。 4.2 已在网并且已通过采购人层级供应商或已增加采购人为合作单位的供应商、上级供应商可直接参与询比采 网 购。在网平级单位供应商未增加采购人为合作单位需进行合作意向申请通过后参与询比采购。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择采购人，审核通过后方可参与询比 采购。 务 5.供应商报价 5.1 报价结束（递交响应文件截止）时间为2026年8月26日17时00分。 商 5.2 供应商应在报价结束时间前，登录“中交招采网”进行线上报价并上传电子响应文件。逾期未完成上传的电 子响应文件，采购人将拒收。 5.3电子采购的供应商响应文件由线上电子报价道表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 子报价表的数据为准。 6.开标 管 6.1 开标时间：与报价结束时间相同。 6.2 开标地点：本次采购在“中交招采网”平台线上开标，不举办现场开标。 国 7.发布公告的媒介 本询比采购公告在 “中交招采网” 上发布。 中 8.评审办法 本项目评审办法采用 经评审的最低价法 。 9.合同主要条款 9.1 付款条件：按月结算，上月11日至本月10日为一个结算对账期，乙方必须按照甲方要求开具合规的增值税专 用发票，无发票不予付款。结算完成后1个月内支付已结算金额的70%，剩余30%货款在结算完成后3个月内支付。 付款方式为银行转账，甲方有权采用票据支付或者供应链支付的方式支付货款，因此产生的费用包含在综合单 价中，乙方不得因此调价和索赔。如遇业主支付不及时，乙方应予理解。 9.2 履约保证金的递交： （1）R不要求递交 （2）要求递交，保证金金额：/，保证金形式：/，其他形式：/ 。 10.监督机构 监督机构名称： 中交一公局重庆工程有限公司审计部 11.成交供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联系400-676-5885，中标服务费请按7咨询。 11.1 收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： 网 （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； （3）在1000万元（含）至3000万元之间的，每次收取1000元； 务 （4）在3000万元（含）至1亿元之间的，每次收取3000元； （5）在1亿元（含）以上的，每次收取5000元。 商 11.2 支付流程 （1）通知推送：中标结果发布后，系统自动推送缴费通知（含应缴金额及支付链接）； 道 （2）费用查询：供应商登录“中交招采网—供应商协同—服务费”模块查看待支付费用； （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 管 （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网— 供应商协同—服务费—发票查询”模块获取。 12.其他 国 / 。 13.联系方式 中 采 购 人：中交一公局重庆工程有限公司 地 址：重庆市江北区创富路5号 邮 编：361021 联 系 人：汪仁宽 电 话：13527572392 电子邮件：1176245792@qq.com 项目联系人及电话： 序号 项目名称 联系人 联系电话 1 永川三教水厂项目 高博 17788661005 中交一公局重庆工程有限公司 2026年8月19日 物资信息 序号 设备物资名称 设备物资说明 税率 单位 网 1 钢筋混凝土排水管 2000mm Ⅲ级 承插口 13% 米 信息来源:https://www.chinapipe.net/project/d3076078.html 务 cqdingjiu 2026.08.21 10:06:52 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
         <v>90</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 钢筋混泥土排水管, 永川三教水厂项目</t>
         </is>
@@ -2585,34 +2455,29 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>大渡口区</t>
+          <t>重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标。</t>
+          <t>项目出资比例为100%，资金已落实。</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>项目出资比例为100%，资金已落实。</t>
+          <t>施工劳务</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>施工劳务</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
           <t>中国铁路成都局集团有限公司重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施 工劳务招标招标公告 重庆市大渡口区萤石及配套企业 35 千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标公告 招标编号：DXNZBCQ-GC-2026-13 1. 招标条件 本建设项目重庆市大渡口区萤石及配套企业 35 千伏专用变电站项目穿越渝贵等网铁路防护工程施工劳务招标已由 《中国铁路成都局集团有限公司关于重庆市大渡 口 区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防 护工程施工图设计的复函》（科信技审〔2025 〕115号）批准建设，建设单位为重庆建桥置业有限公司，建设资 金使用外委资金，项 目出资比例为100%，资金已落实。招标人为中国铁路成都局集团有限公司重庆工务段。本 项目已具备法定招标条件，现进行公开招标，特邀请有意向的投标人参加投标。 务 2. 项目概况与招标范围 2.1 项目概况 商 2.1.1建设地点：渝贵线K38+838、南疏Ⅰ线K10+808、川黔线K1+622、川黔线K3+781、兴珞上行线K38+619、兴珞 下行线K38+635、小西线K1+633、南疏Ⅱ线K11+257。 2.1.2建设规模：重庆市大渡 口区萤石及配套企道业35千伏专用变电站项目穿越渝贵等铁 路防护工程，本项目工分为5个交叉工点。工点一采用明挖直埋方式下穿渝贵铁路新白沙沱长江多线特大桥第14孔 （渝贵线K38+838）；工点二采用顶进套管方式下穿南疏 Ⅰ 线K10+808（ 已停用）、川黔线K3+781（ 已停用 ）； 工点三采用明挖直埋方式下穿兴珞线陈家湾双线特大桥（上行线K38+619、下行线K38+635）；工点四采用顶进 管 套管方式下穿。 2.2 招标范围：重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标。 即涉铁部分第第三章桥涵，第六章通信、信号、信息及灾害监测，第十章大型临时设施和过渡工程，第十一章 其他费用中的安全生产国费以及非涉铁部分。 2.3标段划分：本项目施工招标划分为1个标段。 2.4计划工期：240日历天，计划开工日期：2026年10月8日，计划竣工日期：2027年6月4日。 中 2.5 其他说明：___/___。 3. 投标人资格要求 3.1本次招标要求投标人为在中华人民共和国境内合法注册的独立法人，具备有效的营业执照、施工企业资质和 安全生产许可证等，并在人员、设备、资金等方面具备相应的施工能力。资格要求如下： 3.1.1 标段编号：全标段 （1）资质要求：施工劳务企业资质。 （2）业绩要求：近3年内完成过铁路营业线类似项目业绩。 （3）项目负责人要求:具有工程师及以上职称，2 年及以上类似铁路营业线项目管理工作经验， 良好的职业道德， 且未在其他在建工程项目任职。 （4）本标段不接受联合体投标申请。 （投标人资格要求详见招标公告附件） 3.2 各投标人可就上述标段中的 1 个标段进行投标。 3.3投标人未在“信用中国”网站（www.creditchina.gov.cn）中被列入失信被执行人名单，投标人未在国家企业信 用信息公示系统（www.gsxt.gov.cn）中被列入严重违法失信企业名单，投标人未被列入铁路工程建设失信行 为“黑名单”，投标人及其法定代表人、拟委派的项目经理在近3年不曾有行贿犯罪记录； 其他信誉要求：未被取消或暂停投标资格、不存在辖内失信的情形、不存在最近一期国铁集团施工企业评价为D 级且在整改期内的情形。 4. 招标文件的获取 4.1凡有意参加投标者，请于2026年08月20日00时00分至2026年08月25日00时00，在重庆龙头寺旅游集散中心（重 庆市两江新区天宫殿街道昆仑大道56号附1号5楼办公室）持单位介绍信获取招标网文件。 4.2招标文件每套售价0元，售后不退。 4.3其他：凡有意参加投标者可通过网上登记获取招标文件，将获取招标文件材料扫描件（PDF格式）发送 务 至dxncq_bgs@163.com邮箱登记，由招标代理人通过电子邮件方式向有意参加投标者发送招标文件。 5. 投标文件的递交 5.1投标文件递交时间为2026年09 月10 日08时30分至2026年商09月10 日09时00分，递交比选申请文件的截止时间（比 选截止时间，下同）为2026年09月10日09时00分，地点为重庆龙头寺旅游集散中心（重庆市两江新区天宫殿街道 昆仑大道56号附1号5楼开标室）。 5.2逾期送达的或者未送达指定地点或者不按照道招标文件要求密封的投标文件，招标代理人不予受理。 6. 发布公告的媒介 本次招标公告在国铁采购平台（https://cg.95306.cn）发布。 管 7. 联系方式 招 标 人：中国铁路成都局集团有限公司 招标代理机构：成都大西南铁路监理 国 重庆工务段 有限公司 地 址：重庆市九龙坡区黄桷坪街道铁 地 址：成都市金牛区站西桥西街305 中 路3村161号 号府河路苑9栋14楼 邮 编： / 邮 编：610081 法定代表人： 法定代表人 或其委托代理人： 或其委托代理人： 联 系 人： 任女士 联 系 人：汤女士 电 话： 17393148353 电 话：023-61896910 传 真： / 传 真： / 电子邮箱： / 电子邮箱：dxncq_bgs@163.com 网 址： / 网 址： / 开户银行： / 开户银行： / 账 号： / 账 号： / 2026年08月19日 附件： 获取招标文件信息表 申请人名称： （加盖公章） 项目名称：（按公告名称填写） 获取招标文件起止时间：（按照公告时间填写） 项目编号：（按照公告填写） 单位名称 经办人 联系电话 电子邮箱 标段 资料提交时间 备注 网 注：须附经办人介绍信、身份证复印件、单位营业执照复印件。 信息来源:https://www.chinapipe.net/project/d3075989.html cqdingjiu 2026.08.21 10:06:53 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="n">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>未识别到明确匹配关键词</t>
         </is>
@@ -2657,34 +2522,29 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>云阳县</t>
+          <t>新建污水管网55.5千米，其中DN200管网12千米、DN300管网24千米、DN400管网19.5千米等。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>新建污水管网55.5千米，其中DN200管网12千米、DN300管网24千米、DN400管网19.5千米等。</t>
+          <t>合同预估金额：9100.00万元</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>合同预估金额：9100.00万元</t>
+          <t>污水管网</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>污水管网</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
           <t>长江流域云阳青龙段污水管网一体化建设项目招标计划表 重庆市工程建设项目招标计划表 项目名称 长江流域云阳青龙段污水管网一体化建设项目 招标法人或 招标人名称 云阳县青江环境综合整治有限公司 网 （盖章） 项目批准文 云阳发改资环【2025】55号 件及文号 务 主要建设内 新建污水管网55.5千米，其中DN200管网12千米、DN300管网24千米、DN400管网19.5千米等。 容 招标方 招标文件计 拟交易场 合同预估金额 序号 招标项目名称 招标内容 备注 式 划发布时间 所 (万元) 商 长江流域云阳 新建污水管网55.5千米， 重庆市公 青龙段污水管 其中DN200管网12千 公开招 共资源交 1 网一体化建设 米、DN300管网24千 2026-08 9100.00 标 易中心云 项目EPC总承 米、DN40道0管网19.5千 招标项目 阳分中心 包 米等。 新建污水管网55.5千米， 长江流域云阳 重庆市公 其中DN200管网12千 青龙段污水管 公开招 共资源交 2 管米、DN300管网24千 2026-08 140.00 网一体化建设 标 易中心云 米、DN400管网19.5千 项目监理 阳分中心 米等监理。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 国 信息来源:https://www.chinapipe.net/project/d3075867.html cqdingjiu 2026.08.21 10:06:53 中</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="n">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
         <v>80</v>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 污水管网, 资金情况, 产品种类</t>
         </is>
@@ -2723,32 +2583,31 @@
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>重庆轨道交通17号线一期5标段包含金凤北站（不含）～终点（3站5区间的土建）：高龙大道站、斑竹林站、石家院子站、金凤北站～高龙大道站区间、高龙大道站～斑竹林站区间、斑竹林站～石家院子站区间、石家院子站～终点区间、7/17号线联络线区间。采购范围为雨污水排水迁改工程。</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>重庆轨道交通17号线一期5标段包含金凤北站（不含）～终点（3站5区间的土建）：高龙大道站、斑竹林站、石家院子站、金凤北站～高龙大道站区间、高龙大道站～斑竹林站区间、斑竹林站～石家院子站区间、石家院子站～终点区间、7/17号线联络线区间。采购范围为雨污水排水迁改工程。</t>
+          <t>建设资金来源已落实，但具体资金数额未明确。</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>建设资金来源已落实，但具体资金数额未明确。</t>
+          <t>雨污水排水迁改工程</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>雨污水排水迁改工程</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
           <t>中国电建水电四局华中公司重庆轨道交通17号线一期5标项目雨污水排水迁改工程施工劳务分包采购项目公开询 比采购公告 询比采购公告 采购编号： PC-0104-26J6-FP0895 一、采购条件 受中国水利水电第四工程局有限公司重庆轨道交通17号线一期5标项目委托，中水电四局华中（武汉）工程有限 公司以公开询比方式采购重庆轨道交通17号线一期5标雨污水排水迁改工程项目网，建设资金来源已落实。目前项 目已具备采购条件，现进行公开询比采购。 二、项目概况、采购范围 务 1、项目概况：重庆轨道交通17号线一期5标段包含金凤北站（不含）～终点（3 站5 区间的土建）：高龙大道 站、斑竹林站、石家院子站、金凤北站～高龙大道站区间、高龙大道站～斑竹林站区间、斑竹林站～石家院子 站区间、石家院子站～终点区间、7/17号线联络线区间。 2、采购范围： 商 （1）雨污水排水迁改工程 （2）工程招标范围工作内容：17号线一期5标道中高龙大道站、斑竹林站及高斑竖井位于城市既有道路下方，设计 采用明挖法施工。为保证市政排水管网的正常使用，在明挖施工前需对既有管网进行临时迁改，车站结构施工 后进行恢复。施工PE钢带管长度2387米、B型排水管长度2799m、钢筋混凝土管127米，检查井239座劳务部分。 （3）施工内容详见工程量清单，以及为完成此项工程而做的一切工作。 管 3、计划工期:计划开工日期：2026年9月25日（具体时间以采购人通知为准），计划完工日期：2027年 12 月25 日； 合同工期总日历天数为457天。 4、质量要求：符合《国给水排水管道工程施工及验收规范》（GB 50268）、《混凝土结构工程施工质量验收规范》 （GB 50204）、《城镇道路工程施工与质量验收规范》（CJJ 1-2008）以及项目所在地最新的相关法规、标准和 图集。工程质量全面达到设计要求和标准，其中：验收合格率 100%，优良率达 90%以上，工程综合验收质量评 定达优良标准。 中 5、付款方式：采用银行转账/支票支付工程价款，月度结算完成具备付款条件后30天内工程进度款支付比例约定 为扣除各项保证金及费用后应付价款不低于65%；清算完成并签订《退场协议》后30天内工程进度款支付比例约 定为扣除各项保证金及费用后应付价款不低于80%；清算完成并签订《退场协议》后一年内工程进度款支付比例 约定为扣除响应人缺陷责任等相关费用后应付价款不低于90%；清算完成并签订《退场协议》，办理完成保证金 退还手续后两年内，工程进度款支付比例约定为扣除响应人缺陷责任等相关费用后应付价款的100%。 6、其他：无。 三、响应人资格要求 响应人必须满足以下全部资格要求： （1）资质要求：施工劳务不分等级 （2）主要人员要求:授权委托人（如有）及项目经理、专职安全员应提供社保和劳动合同。其中劳动合同至少提 供首、末两页，并且包含有关人员的详细信息;社保证明应提供响应截止时间前三个月的社保缴纳记录。 （3）安全三类人员要求:应提供企业主要负责人安全A证、项目经理B证、专职安全员C证。 （4）响应人具有良好的银行资信和商业信誉，没有处于被责令停业，财产被接管、冻结、破产状态。 （5）响应人应具有 雨污水排水迁改 工程的施工业绩，在近 5年内(2021年7月-2026年7月内签订)的施工合同不少 于 1 个，且签订单项合同金额均在 100 万元以上（应附成交通知书和（或）合同扫描件）。 （6）其它要求:无。 （7）本次采购不接受联合体响应。 四、采购文件的获取 凡满足本公告规定资格要求并有意参加的响应人，请于2026年8月22日10时00分前在中国电建采购招标数智化平台 （https://bid.powerchina.cn/bidweb/#/login，以下简称“数智化平台”）获取采购文件，采购文件免费提供。 五、响应文件的递交 1、响应文件递交的截止时间（响应截止时间，下同）为2026年8月26日10时30分网（北京时间），响应人应在截止 时间前通过数智化平台递交电子响应文件。 2、本次采购将通过数智化平台全程在线开展，电子响应文件的加密、提交等流程须响应人在线进行操作。响应 人须提前办理数字证书用于在线递交响应文件，办理方式详见数智化平台首页，并严格按照要求进行在线操作， 务 因操作流程失误造成的递交失败将由响应人自行承担后果。 3、开启由“数智化平台”在响应截止时间后自动对响应文件进行解密，响应人及时关注开启结果。 4、响应截止时间如有变动，采购人将及时通知已获取采商购文件的响应人。 六、发布公告的媒介 本次询比采购公告同时在中国电建阳光采购网道（https://bid-zb.powerchina.cn）上发布。 七、评审办法 采用综合评估法。 管 八、联系方式 采 购 人： 中水电四局华中（武汉）工程有限公司 国 地 址： 湖北省武汉市江岸区塔子湖东路健美街30号立城中心商务楼13、14层 邮 编： 430014 中 联 系 人： 王飞 电 话： 15827222587 电子邮箱： 107830343@qq.com 九、提出异议的渠道和方式 单位名称： 中水电四局华中（武汉）工程有限公司 电 话： 17708178186 电子邮箱： sjhzgsjw@163.com 十、纪检监督机构 响应人或者其他利害关系人认为本次采购活动存在违规违纪行为的，可以书面形式向中国水利水电第四工程局 有限公司中水电四局华中（武汉）工程有限公司纪委办公室（联系方式：17708178186）提出投诉。 2026年8月 19 日 报价网址:https://bid.powerchina.cn/notice/detail?id=2409510708 信息来源:https://www.chinapipe.net/project/d3075750.html cqdingjiu 2026.08.21 10:06:53 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="n">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
         <v>85</v>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>重庆, 轨道交通, 雨污水排水迁改, 施工劳务分包</t>
         </is>
@@ -2793,34 +2652,29 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>万州区</t>
+          <t>本项目涉及预制钢筋砼管、成品混凝土仿木栏杆等材料的采购。</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>本项目涉及预制钢筋砼管、成品混凝土仿木栏杆等材料的采购。</t>
+          <t>建设资金为国债资金，项目出资比例为100%。具体预算金额未在文本中明确列出。</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>建设资金为国债资金，项目出资比例为100%。具体预算金额未在文本中明确列出。</t>
+          <t>预制钢筋砼管,成品混凝土仿木栏杆</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>预制钢筋砼管,成品混凝土仿木栏杆</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
           <t>万州区2026年超长期特别国债高标准农田建设项目拟进行预制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜的 信息公告 1.采购条件 1.1本项目万州区2026年超长期特别国债高标准农田建设项目工程已由 重庆市万州路桥建设有限公司承建，项目 业主为重庆市万州区农业技术与机械推广中心，代建业主为重庆市万州区农业发展有限公司，建设资金为国债 资金，项目出资比例为 100% ，承包人为重庆市万州路桥建设有限公司。项目已具备施工条件，现对该项目的预 制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜发布信息公告。 网 2.项目概况与采购范围 2.1建设地点：重庆市万州区走马镇、瀼渡镇、罗田镇、余家镇、高梁镇、分水镇、柱山乡等7个镇乡。 务 2.2本项目材料采购拟进行比选情况如下： 罗田镇谷山片区材料采购费暂定金额约： 17.5万元； 余家镇桥亭片区材料采购费暂定金额约： 17.99万元； 商 柱山乡山田片区材料采购费暂定金额约： 26.32 万元； 走马镇凉风片区材料采购费暂定金额约： 15.道66万元； 瀼渡镇高村片区材料采购费暂定金额约： 17.72 万元； 分水镇大冲片区材料采购费暂定金额约： 47.12 万元； 管 高梁镇茨坪片区材料采购费暂定金额约： 10.7万元； （以上片区片区金额为暂定金额，最终比选限价金额以比选文件为准）。 国 2.3计划采购周期： 以合同签订为准 日历天。 2.4采购范围：本项目各片区所包含的预制钢筋砼管、成品混凝土仿木栏杆等材料。 中 3.供应商资格要求 3.1本次材料采购要求供应商具备独立企业法人，具有本次所需材料生产能力的厂家或经销商等，其经营范围和 权限应满足本次所需材料的要求，并依法取得国家行政主管部门颁发的有效工商营业执照(建筑材料销售或水泥 制品制造、水泥制品销售等相关营业资格），所提供产品必须满足各项检测要求，达到国家现行标准规定的合 格标准。具有良好的商业信誉和充分的供应保障能力，具备相应售后服务能力。要求竞选人为一般纳税人，可 开具13%税率增值税专用发票，提供一般纳税人认定证明。 3.2本次供应商单位优先选择万州本地企业。 3.3本次 不接受 联合体竞选。 4. 报名要求 4.1报名时间：2026年8月 19日9:00起至 8月21日17:00止。 4.2报名地点：重庆市万州路桥建设有限公司经营部（重庆市万州区天城东路278号）。 4.3报名时，须提交有效的营业执照(有效工商营业执照((建筑材料销售或水泥制品制造、水泥制品销售等相关营 业资格）)，前述证书均为复印件并加盖单位公章。法定代表人参加报名的不需要授权委托书，只需要提供法定 代表人身份证明；非法定代表人参加报名的除提供法定代表人身份证明外还须提供授权委托书、委托代理人身 份证明。 4.4 本项目材料采购需提前报名。经资格预审合格后，通知资格预审合格的供应商，到承包人单位领取相关文件。 4.5本项目材料采购设七个片区进行比选，为保证比选公平、公正、有效，规定同一参选单位报名片区上限为2个， 且最终仅限中选一个片区。 5.联系方式 承包人：重庆市万州路桥建设有限公司 地 址：重庆市万州区天城东路278号 网 联系人： 张红娟 电 话：15923491915 务 邮 箱： 商 重庆市万州路桥建设有限公司 2026年8月19日 道 信息来源:https://www.chinapipe.net/project/d3075512.html cqdingjiu 2026.08.21 10:06:53 管 国 中</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
         <v>80</v>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>重庆, 预制钢筋砼管, 成品混凝土仿木栏杆, 国债资金, 高标准农田建设</t>
         </is>
@@ -2865,34 +2719,29 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>酉阳土家族苗族自治县</t>
+          <t>酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资(污水管道)公开招标采购。</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资(污水管道)公开招标采购。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>污水管道</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>污水管道</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
           <t>中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资(污水 管道)招标采购流标公告 发布单位：中国铁建/中铁十一局/六公司 发布时间：2026-08-19 10:40:49 投标截至时间：2026-08-18 10:00:00 内容： 各投标人： 网 中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资（污水 管道）公开招标采购（采购编号： CR1106-JC-2026-26-02）评标工作，已于北京时间2026年08月18日10:00整，在 铁建云链（https://www.crccep.com）线上平台公开开标。评审委员会根据招标文件载明的评审办法完成评审工作， 现将评审结果公示如下： 务 一、招标公告发布日期及媒体 招标公告发布日期：2026年07月27日至2026年08月01日 商 招标公告媒体：铁建云链（https://www.crccep.com） 二、拟中标信息 道 公开招标采购编号：CR1106-JC-2026-26-02 包件号：WSGD-01 序号 供应商名称 推荐排序 管 1 无 1 国 以上包件有效投标不足三家，本次招标做流标处理。 三、公示时间 中 自2026年08月19日始，至2026年08月22日止。在公示期间，所有竞标人和其他利害关系人如对公示的评审结果有 异议，可以向相关监督部门举报，逾期将不再受理。举报人必须由其法定代表人或者授权代表签字并盖章，其 他组织或者个人举报的，必须由其主要负责人或者本人签字，并附有效身份证明复印件。举报人如实反映情况 受法律保护。 公示期满，如无异议，即时生效。 监督竞诉受理部门： 中铁十一局集团第六工程有限公司招采中心 联系电话：18671041790 信息来源:https://www.chinapipe.net/project/d3075461.html cqdingjiu 2026.08.21 10:06:53</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
         <v>80</v>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 酉阳县, 污水管网, 新建改造工程</t>
         </is>
@@ -2931,32 +2780,31 @@
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>详见附件。</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>详见附件。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>镀锌管件</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>镀锌管件</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
           <t>协同创新区-四期房建三标段镀锌管件物资竞价采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3075420.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
         <v>60</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 商机</t>
         </is>
@@ -3001,12 +2849,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>渝北区</t>
+          <t>长江一级支流溉澜溪流域(新华水库混流箱涵)污水收集效能提升工程(渝北区)施工答疑补遗文件</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>长江一级支流溉澜溪流域(新华水库混流箱涵)污水收集效能提升工程(渝北区)施工答疑补遗文件</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3016,19 +2864,14 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
           <t>长江一级支流溉澜溪流域(新华水库混流箱涵)污水收集效能提升工程(渝北区)施工答疑补遗文件 长江一级支流溉澜溪流域（新华水库混流箱涵）污水收集效能提升工程（渝北区）施工答疑文件 各潜在投标人： 现将“长江一级支流溉澜溪流域（新华水库混流箱涵）污水收集效能提升工程（渝北区）施工”公开招标项目 答疑文件发布。本答疑文件是在招标文件的基础上作出的澄清、说明或补正，与招标文件具有同等法律效力， 若相关内容与原招标文件不一致时，一律以本答疑文件内容为准。 网 一、答疑部分： 问题一：1、我公司于2026年进行了优势合并整合，现准备使用合并前公司项目业绩作为本次我司投标的投标人 业绩证明，并提供上级主管单位出具的相关吸收合并文件或两家公司签订的吸收合并协议，请问是否可视为满 务 足招标业绩要求？ 2、我单位为中型企业，其控股股东为大企业，但我单位不属于大企业的分支机构，也不存在与大企业的负责人 为同一人的情形。鉴于此种情况，我单位应提供《中小企业声明函（工程类）》还是《中小企业承担合同份额 承诺函》？ 商 回复：1. 满足，但还需满足招标文件对业绩的其他要求。最终由评标委员会根据投标人提供的证明材料并结合 招标文件要求进行评审； 道 2. 贵司其控股股东为大企业，故需提供中小企业承担合同份额承诺函。 问题二：本项目有无业主专家参与评标？ 管 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 问题三：请明确是否有业主专家 是否异地评标 回复：1. 该项目评标委国员会由招标人按法律法规及相关规定依法组建。 2.本项目是异地评标。 问题四：1、财务报告可以不提供财务报表附注吗? 中 2、投标函附录中，工期、分包、工程质量、缺陷责任期等要求可以统一填写"达到招标文件要求"吗? 3、招标文件第八章投标文件格式中(二)承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要提供其 他格式之外的其他承诺? 4、是否有业代专家参与评标，不要模糊的回答什么依法组建评标委员会。请明确回复有或者没有。 5、本项目是否异地评标？ 6、业绩竣工验收证明材料中有单位盖的项目部章是否认可呢？ 回复：1. 可以不提供财务报表附注。 2. 可以统一填写"达到招标文件要求"。 3. 投标人自行核实招标文件要求提供的承诺要求，如有需要，还需补充提供招标文件第八章投标文件格式中 （二）承诺部分之外的其他承诺。 4. 该项目评标委员会由招标人按法律法规及相关规定依法组建。 5. 本项目是异地评标。 6. 不认可。 问题五：请问**公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，因为不能履行保函的见索即 付，拒绝赔付。 相关业主方在招标文件补遗通知中直接将**公司列入担保公司回避名单，拒绝**公司所出具的保函。由此可 见**公司的信用资质、履约能力、根本无能力是存在很大问题的。请问以**公司目前的被执行和不履行投标担保 责任的情况是否符合招标文件的要求? 回复：纸质投标保函的开立人应当是具有相应资格的银行、保险机构、融资担保公司，其信用资质、履约能力、 担保能力、赔付流程、安全保密等应符合工程保函业务条件。纸质投标保函应合网法合规，符合招投标行政监督 部门、行业主管部门和金融监管部门的相关规定，满足招标文件约定要求。投标人应选择在渝依法设立总部或 者设有分支机构的金融机构开具纸质投标保函。投标人对所提交的纸质投标保函的真实性、合法性、有效性负 责。以纸质投标保函形式交纳投标保证金是否符合招标文件要求，由评标委员会评标时，根据招标文件要求进 行独立评审，并作出相应评审判断。 务 问题六：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 回复：经核实，招标文件（PDF签章版）中投标文件格式商与重庆市电子招投标系统投标文件制作软件中格式一致。 可能因重庆市电子招投标系统投标文件制作软件中的格式页边距与招标文件（PDF签章版）不一致的原因导致格 式显示不一致，该情形不影响投标人编制投标文件。若重庆市电子招投标系统投标文件制作软件导出的投标文 件格式与招标文件（PDF签章版）的投标文件格式不一致，以重庆市电子招投标系统投标文件制作软件导出的投 标文件格式为准。 道 问题七：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖 章，请问需要提供联合体协议书吗？ 管 回复：若投标人提供的公司业绩为epc业绩，且合同协议书或工程竣工验收合格的证明材料或业主证明能证明该 投标人承担的工作为施工任务的，则不需要提供联合体协议书；若投标人提供的公司业绩为epc业绩，但合同协 议书或工程竣工验收合格的证明材料或业主证明不能证明该投标人承担的工作为施工任务的，则需要提供联合 体协议书。 国 问题八：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可 以不填(空白)，对此有无要求？ 回复：投标中文件中下划线上、空格处、表格中无需要填写或无法填写内容的，填“/”或“无”均可。 问题九：公园施工业绩符合吗？ 回复：公园概念太宽泛，无法判定该施工业绩是否属市政工程，请投标人自行核实，并按招标文件要求提供施 工业绩证明材料，其是否满足要求应由评标委员会根据证明材料具体内容进行判定。 问题十：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需 要提供其他格式之外的其他承诺？ 回复：投标人自行核实招标文件要求提供的承诺要求，如有需要，还需补充提供招标文件第八章投标文件格式中 （二）承诺部分之外的其他承诺。 问题十一：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收， 请问我公司业绩满足业绩要求吗？ 回复：不满足。 问题十二：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗？ 回复：投标人投标总报价低于招标文件规定的对应的异常低价警戒线的，应提供报价合理性说明，并提供必要 的证明材料。证明材料由投标人自行提供，但提供的说明不得降低或者改变原设计方案、技术工艺、施工标准， 不得影响项目的质量、安全、工期、结算等正常履约。 问题十三：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 回复：按照招标文件要求“提供：会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表，财务 报表须至少包括现金流量表、资产负债表、利润表”。 问题十四：业绩要求的竣工时间是指竣工验收时间吗？ 回复：本项目业绩要求所指竣工时间，即为工程竣工验收合格证明载明的竣工验收时间。 问题十五：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知 书发出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面网通知相关金融机构本项目准 予提前注销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 回复：纸质投标保函原件上未加盖“正本”字样的，不因此否决投标，但投标人应确保提交的保函为唯一正本。 若因保函真伪问题导致的一切不利后果由投标人自行承担。 务 问题十六：燃气管道安装施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 商 问题十七：请问招标人是否委派业主专家参与评标吗？ 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 道 问题十八：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 回复：根据招标文件“投标人的工程量清单单项报价不得为零报价（招标人提供的工程量清单单项最高限价中 金额为零的除外）或者负数报价”，招标人提供的工程量清单单项最高限价中金额为零的，该项清单综合单价 管 报价可以为0。 问题十九：自来水厂或者净水厂施工业绩满足业绩要求吗？ 回复：满足，但还需满国足招标文件对业绩的其他要求。 问题二十：财务报告可以不提供财务报表附注吗？ 回复：可以不提供财务报表附注。 中 问题二十一：老旧小区室外环境改造施工业绩符合吗？ 回复：不满足。 问题二十二：有人提出一个无关问题。 回复：无关问题不予回复。 问题二十三：任一清单的综合单价低于警戒线，就要提供说明吗？ 回复：本招标项目单项报价未设置异常低价警戒线。 问题二十四：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题二十五：本项目是异地评标吗？ 回复：本项目是异地评标。 问题二十六：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、 注册证及在本单位注册的证明文件替代？ 回复：不满足。 问题二十七：污水处理厂提标改造施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题二十八：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 回复：可以填“达到招标文件的要求”。 问题二十九：财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加网强审计报告查验工作的通知》 中要求会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第十四条规定审计业务出具的报告 （以下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标 人提供的财务报告需要赋码和提供深度查询截图吗？ 务 回复：投标人提供的财务报告不需要赋码和提供深度查询截图。 问题三十：有人提出一个无关问题。 回复：无关问题不予回复。 商 问题三十一：我公司业绩合同金额3600万元及以上，但是竣工报告业绩金额小于3600万元，请问是否满足业绩要 求？ 道 回复：按招标文件执行。“当上述业绩证明材料中针对同一指标存在不一致时，以工程竣工验收合格的证明材 料为准”。 问题三十二：专业分包业绩满足业绩要求吗？ 管 回复：专业分包业绩可满足业绩要求，但还需满足招标文件对业绩的其他要求。 问题三十三：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养 老保险证明材料复印件国递交吗？ 回复：不需要。 问题三十四：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要 中 求”吗？ 回复：可以统一填写“达到招标文件要求”。 问题三十五：市政桥梁施工业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题三十六：有人提出一个无关问题。 回复：无关问题不予回复。 问题三十七：本项目委派业主专家吗？ 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 特别提示：本通知与招标文件具有同等法律效力，若招标文件与本通知不一致时，一律以本通知为准。 招标人：重庆水务环境控股集团管网有限公司 招标代理机构：重庆市工程管理有限公司 2026年8月19日 信息来源:https://www.chinapipe.net/project/d3075975.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标</t>
         </is>
@@ -3073,34 +2916,29 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>新建一体化提升泵站及管道约5000m，投资约800万元。</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>新建一体化提升泵站及管道约5000m，投资约800万元。</t>
+          <t>投资约800万元</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>投资约800万元</t>
+          <t>施工</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>施工</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
           <t>中化重庆涪陵化工搬迁后污水处理厂建设项目招标计划表 重庆市工程建设项目招标计划表 项目名称 中化重庆涪陵化工搬迁后污水处理厂建设项目 招标法人或 招标人名称 重庆市涪陵交通旅游建设投资集团有限公司 网 （盖章） 项目批准文 涪发改委发[2019] 505号 件及文号 务 主要建设内 新建一体化提升泵站及管道约5000m，投资约800万元。 容 招标 招标 招标文件计 拟交易 合同预估 序号 招标项目名称 备注 内容 方式 划发布时间 场所 金额(万元) 商 本招标计划与2026年5 月25日发布的招标项目 中化重庆涪陵 重庆市 名称为“中化重庆涪陵 招标项目 化工搬迁后污 涪陵区 公道开 化工搬迁后污水处理厂 1 水处理厂建设 施工 2026-09 公共资 800.00 招标 建设项目（场外连接管 项目（场外干 源交易 网）”的招标计划，除 管部分） 中心 招标项目名称调整外， 其余内容完全一致。 管 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075591.html cqdingjiu 2026.08.21 10:国06:54 中</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="n">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
         <v>80</v>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标, 商机</t>
         </is>
@@ -3145,34 +2983,29 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>綦江区</t>
+          <t>对三江污水处理站、綦齿园污水处理厂、信家岩污水处理站的设施设备进行更新改造，包括配电柜、风机、污水提升泵、在线监测等设备的更新更换，以及对工艺落后的污水厂完成工艺技改；北渡污水厂、赶水污水处理厂、工业园区污水厂、食品园污水厂零星设施更新等。</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>对三江污水处理站、綦齿园污水处理厂、信家岩污水处理站的设施设备进行更新改造，包括配电柜、风机、污水提升泵、在线监测等设备的更新更换，以及对工艺落后的污水厂完成工艺技改；北渡污水厂、赶水污水处理厂、工业园区污水厂、食品园污水厂零星设施更新等。</t>
+          <t>上级补助和业主自筹，项目出资比例为100%，本项目工程总投资金额约1327.40万元</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>上级补助和业主自筹，项目出资比例为100%，本项目工程总投资金额约1327.40万元</t>
+          <t>污水处理设施设备</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>污水处理设施设备</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
           <t>綦江区污水处理厂设施设备更新改造工程(二期)招标公告 1.招标条件 本招标项目 綦江区污水处理厂设施设备更新改造工程（二期） 已由 重庆市綦江区发展和改革委员会 以 重庆市企业投资备案证（项目代码：2502-500110-04-01-844057） 批准建设，项目业主为 重庆南州城市管 理服务有限公司 ，建设资金来自 上级补助和业主自筹 ，项目出资比例为 100% ，招标人为 重庆南州 城市管理服务有限公司。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用经评审的最低 投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 綦江区 2.2 项目概况与建设规模：对三江污水处理站、綦齿园污水处理厂、信家岩污水处理站的设施设备进行更新改造， 务 包括配电柜、风机、污水提升泵、在线监测等设备更新更换，以及对工艺落后的污水厂完成工艺技改；北渡污 水厂、赶水污水处理厂、工业园区污水厂、食品园污水厂零星设施更新等。 2.3 本项目工程总投资金额： 约1327.40万元 商 2.4 招标范围： 本项目设计施工图和招标文件、答疑、补遗、工程量清单等资料所涉及的全部内容。 2.5 工期要求： 180日历天 道 缺陷责任期要求： 24个月 2.6 标段划分（如有）： / 管 2.7 其他： / 3.政府采购工程 国 3.1 是否属于政府采购工程：否 4.投标人资格要求 中 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（綦江区） （https://www.cqggzy.com/qijiangweb/）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重 庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏 “主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网（綦江区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-22 18:00:00前。 5.3招标人应于2026-09-11 18:00:00前在重庆市公共资源交易网（綦江区）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-28 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（綦江区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆南州城市管理服务有限公司 代理机构: 永卓国际工程技术有限公司 地 址: 重庆市綦江区红星美凯龙生活广场3幢19-3 地 址: 两江新区网泰山大道东段98号2幢10-12号 邮 编: 邮 编: 项目负责人: 赵老师 项目负责人: 廖淼 电 话: 023-48690537 电 话: 务023-60391733 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 商开户银行: 账 号: 账 号: 监督部门: 道 电 话: 2026年08月18日 綦江区污水处理厂设施设备更新改造工程（二期） 管 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051287453 中国农业银行股份有限公司重庆自由贸 重庆联合产权交易所集国团股份有限公司 312601010400083780000031123 易试验区分行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146631326 信息来源:https://www.chinapipe.net/project/d3075589.html 中 cqdingjiu 2026.08.21 10:06:54</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
         <v>90</v>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>重庆, 綦江区, 污水处理厂, 设施设备更新改造, 管材招标</t>
         </is>
@@ -3217,34 +3050,29 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>南岸区</t>
+          <t>本工程主要内容包括新（改）建峡口、道迎龙片区4个乡镇DN20～DN300农村供水管网81km，新建3座一体化智慧加压泵站。对朱家岩水厂进行升级改造：更换陈旧、老化的工艺、电气设备及自控、仪表系统，对全厂进行智能化、标准化改造，增加高级工艺控制系统，建设智能化、标准化的农村供水区级管理平台。</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>本工程主要内容包括新（改）建峡口、道迎龙片区4个乡镇DN20～DN300农村供水管网81km，新建3座一体化智慧加压泵站。对朱家岩水厂进行升级改造：更换陈旧、老化的工艺、电气设备及自控、仪表系统，对全厂进行智能化、标准化改造，增加高级工艺控制系统，建设智能化、标准化的农村供水区级管理平台。</t>
+          <t>概算批复工程建安费2975.27万元。</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>概算批复工程建安费2975.27万元。</t>
+          <t>农村供水管网、智慧加压泵站、水厂升级改造、智能控制系统、加药系统、金属防腐工程、入户管道、入户水表、监测计量基础设施。</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>农村供水管网、智慧加压泵站、水厂升级改造、智能控制系统、加药系统、金属防腐工程、入户管道、入户水表、监测计量基础设施。</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
           <t>南岸区峡口、迎龙片区农村供水保障提升工程招标计划表 重庆市工程建设项目招标计划表 项目 南岸区峡口、迎龙片区农村供水保障提升工程 名称 招标 网 法人 或招 标人 重庆市江南城市建设发展（集团）有限公司 名称 务 （盖 章） 项目 批准 商 文件 南岸发改﹝2026﹞156号 及文 号 本工程主要内容包括新（改）建峡口、道迎龙片区4个乡镇DN20～DN300农村供水管网81km，新建3座一体 主要 化智慧加压泵站。对朱家岩水厂进行升级改造：更换陈旧、老化的工艺、电气设备及自控、仪表系统， 建设 对全厂进行智能化、标准化改造，增加高级工艺控制系统，建设智能化、标准化的农村供水区级管理平 内容 台。概算批复工程建安费2975.27万元。 管 拟 招 招标文 合同预 招标 交 序 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 国 所 南岸 重 区峡 庆 口、 中 市 迎龙 朱家岩水厂升级改造工程：对全厂老旧设备进行设备更新；对全 公 片区 公 厂进行智慧化改造，增加高级工艺控制系统；对厂区建筑和构筑 共 农村 开 1 物修缮；优化加药系统投加模式，增加精确加药系统；对全厂部 2026-08 资 1600.00 供水 招 分老旧管道进行更换；金属防腐工程，对金属设备和管道的防锈 源 保障 标 刷漆工作。 交 提升 招标 易 工程 项目 中 （一 心 标段） 南岸 重 区峡 庆 口、 市 迎龙 公 片区 管网工程：延伸、改造峡口镇、迎龙镇等4个乡镇 46 公里 公 共 农村 DN40~DN300 配水主支管，36公里 DN20入户管道，新建3座一体 开 2 2026-08 资 1300.00 供水 化智慧加压泵房，入户水表改造 1752 户，并配套建设监测计量 招 源 保障 基础设施。 标 交 提升 易 工程 中 （二 心 标段） 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075572.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
         <v>90</v>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>重庆, 农村供水保障提升工程, 管材招标, 资金情况, 产品种类</t>
         </is>
@@ -3289,34 +3117,29 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>北碚区</t>
+          <t>工程建设区域为东阳及天府片区，主要建设内容包含改造供水管网437千米，其中DN200供水主要建设内容管网35千米，DN100~DN150供水管网82千米，DN100以下供水管网320千米，并配套建设管网附属设施。</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>工程建设区域为东阳及天府片区，主要建设内容包含改造供水管网437千米，其中DN200供水主要建设内容管网35千米，DN100~DN150供水管网82千米，DN100以下供水管网320千米，并配套建设管网附属设施。</t>
+          <t>合同预估金额为8457万元</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>合同预估金额为8457万元</t>
+          <t>供水管网</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>供水管网</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
           <t>北碚区东阳天府片区农村供水提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 北碚区东阳天府片区农村供水提升工程 招标法人或招 标人名称（盖 重庆北碚文旅产业发展有限公司 网 章） 项目批准文件 及文号 务 工程建设区域为东阳及天府片区，主要建设内容包含改造供水管网437千米，其中DN200供水 主要建设内容 管网35千米，DN100~DN150供水管网82千米，DN100以下供水管网320千米，并配套建设管网 附属设施。 招标项目名 招标内 招标方 招标文件计划 拟交易场 合同预估金 序号 商 备注 称 容 式 发布时间 所 额(万元) 北碚区东阳 招标项目 重庆市公 天府片区农 施工招 公开招 1 2026-08 共资源交 8457.00 村供水提升 标 道标 易中心 工程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075569.html 管 cqdingjiu 2026.08.21 10:06:55 国 中</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
         <v>80</v>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 农村供水提升工程, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -3361,34 +3184,29 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>北碚区</t>
+          <t>改造取水泵站一座，改造DN600供水管网2.9km，DN50~DN300供水管网88.863km，DN25供水管网68.5km及其附属设施。</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>改造取水泵站一座，改造DN600供水管网2.9km，DN50~DN300供水管网88.863km，DN25供水管网68.5km及其附属设施。</t>
+          <t>合同预估金额：8741.00万元</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>合同预估金额：8741.00万元</t>
+          <t>供水管网及相关附属设施</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>供水管网及相关附属设施</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
           <t>北碚区澄江片区农村供水提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 北碚区澄江片区农村供水提升工程 招标法人或招标 重庆北碚文旅产业发展有限公司 人名称（盖章） 网 项目批准文件及 文号 改造取水泵站一座，改造DN600供水管网2.9km，DN50~DN300供水管网88.863km，DN25供 主要建设内容 务 水管网68.5km及其附属设施。 招标项目名 招标文件计划 合同预估金 序号 招标内容 招标方式 拟交易场所 备注 称 发布时间 额(万元) 招标项目 北碚区澄江 商重庆市公共 1 片区农村供 施工招标 公开招标 2026-08 资源交易中 8741.00 水提升工程 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 道 信息来源:https://www.chinapipe.net/project/d3075568.html cqdingjiu 2026.08.21 10:06:55 管 国 中</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="n">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
         <v>80</v>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标, 商机</t>
         </is>
@@ -3433,34 +3251,29 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>主要改造及延伸配水管188.2千米，新建加压泵站4座，新建计量监测设施建设以及配套电气工程。</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>主要改造及延伸配水管188.2千米，新建加压泵站4座，新建计量监测设施建设以及配套电气工程。</t>
+          <t>预算金额为3137.22万元</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>预算金额为3137.22万元</t>
+          <t>管道、加压泵站、计量监测设施、电气设备</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>管道、加压泵站、计量监测设施、电气设备</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
           <t>涪陵区江东街道农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区江东街道农村供水保障能力提升工程（二期） 名称 招标 法人 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 项目 网 批准 文件 涪陵发改〔2026〕471号 及文 号 主要 改造及延伸配水管 188.2千米，新建加压泵站4座，新建计量监测设施 建设 以及配套电气工程。 务 内容 招 标 合 文 同 招 件 预 招标 标 招标方 计 拟交易 备 序号 招标项目名商称 估 项目 内 式 划 场所 注 金额 容 发 (万 布 元) 时 间 重 道 庆 市 涪 陵 公 区 改造及延伸配水管 188.2千米，新建加压泵站4座，新建计量监测设施 开 公 1 涪陵区江东街道农村供水保障能力提升工程（二期） 2026-09 3137.22 管以及配套电气工程。 招 共 标 资 源 交 易 中 心 国 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075558.html cqdingjiu 2026.08.21 10:06:55 中</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="n">
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
         <v>80</v>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -3505,34 +3318,29 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>改造荣桂水厂老化、破损、生锈的输水管道7.36公里。马武水厂增设废水回收及污泥浓缩系统1套。荣桂水厂增设废水回收及污泥浓缩系统1套。新建配水管道总长0.74公里；改造配水管道总长139.42公里。新建1座微型集成泵房及改造1座泵站(原牌坊泵站)。新增管网监测设施40套。</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>改造荣桂水厂老化、破损、生锈的输水管道7.36公里。马武水厂增设废水回收及污泥浓缩系统1套。荣桂水厂增设废水回收及污泥浓缩系统1套。新建配水管道总长0.74公里；改造配水管道总长139.42公里。新建1座微型集成泵房及改造1座泵站(原牌坊泵站)。新增管网监测设施40套。</t>
+          <t>预估合同金额为3236.36万元人民币</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>预估合同金额为3236.36万元人民币</t>
+          <t>输水管道、废水回收及污泥浓缩系统、配水管道、微型集成泵房、泵站、管网监测设施</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>输水管道、废水回收及污泥浓缩系统、配水管道、微型集成泵房、泵站、管网监测设施</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
           <t>涪陵区龙桥街道农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 涪陵区龙桥街道农村供水保障能力 项目名称 提升工程 招标法人 或招标人 重庆水务环境控股集团渝东自来水 名称（盖 有限公司 章） 网 项目批准 文件及文 涪陵发改〔2026〕466号 号 改造荣桂水厂老化、破损、生锈的 务 输水管道7.36公里。马武水厂增设 废水回收及污泥浓缩系统1套。荣 桂水厂增设废水回收及污泥浓缩系 主要建设 统1套。新建配水管道总长0.74公里； 商 内容 改造配水管道总长139.42公里。新 建1座微型集成泵房及改造1座泵 站(原牌坊泵站)。新增管网监测设 施40套。 道 招标 合同 招 文件 预估 标 招标方 拟交易 备 招标项目 序号 招标项目名称 计划 金 内 式 场所 注 管 发布 额(万 容 时间 元) 改造荣桂水厂老化、 破损、生锈的输水管 国 道7.36公里。马武水厂 增设废水回收及污泥 重庆 浓缩系统1套。荣桂水 市涪 厂增设废水回收及污 公 陵区 中 涪陵区龙桥街道农村供水保障能力 泥浓缩系统1套。新建 开 1 2026-09 公共 3236.36 提升工程 配水管道总长0.74公里； 招 资源 改造配水管道总 标 交易 长139.42公里。新建1 中心 座微型集成泵房及改 造1座泵站(原牌坊泵 站)。新增管网监测设 施40套。 本计划表所列招标项目信息均为暂 备注 定，最终以实际招标时的信 信息来源:https://www.chinapipe.net/project/d3075556.html cqdingjiu 2026.08.21 10:06:55</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
         <v>90</v>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>涪陵区龙桥街道, 农村供水保障能力提升工程, 输水管道, 废水回收及污泥浓缩系统, 配水管道, 微型集成泵房, 泵站, 管网监测设施</t>
         </is>
@@ -3577,34 +3385,29 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>整治De315原水管长1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1套及配套电气工程。</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>整治De315原水管长1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1套及配套电气工程。</t>
+          <t>合同金额1489.90万元</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>合同金额1489.90万元</t>
+          <t>管材、水泵、加压泵站、废水处理系统、电气工程</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>管材、水泵、加压泵站、废水处理系统、电气工程</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
           <t>涪陵区百胜镇农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区百胜镇农村供水保障能力提升工程 名称 招标 法人 或招 标人重庆水务环境控股集团渝东自来水有限公司 名称 网 （盖 章） 项目 批准 文件涪陵发改〔2026〕465号 及文 号 务 主要 建设整治 De315原水管长 1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1套及配套电气工程。 内容 招 拟 标 招招标文 合同预 交 序项 标件计划 估金 备 招标内容 易 号目 方发布时 额(万 注 场 名 商 式间 所 元) 称 涪 陵 区 重 百 庆 胜 市 招标 镇 涪 项目 农 道 陵 村 公 区 供整治 De315原水管长 1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1开 公 1 2026-09 1489.90 水套及配套电气工程。 招 共 保 标 资 障 源 能 交 力 易 提 中 管 升 心 工 程 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075553.html 国 cqdingjiu 2026.08.21 10:06:55 中</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="n">
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
         <v>80</v>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>涪陵区百胜镇, 农村供水保障能力提升工程, 管材招标, 重庆</t>
         </is>
@@ -3649,34 +3452,29 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>对清溪水厂原取水口进行改造。改造清溪厂输水管道长6.38公里。清溪水厂新建3000m³/d集成水厂1套，增设废水回收及污泥浓缩系统1套。新建配水管道总长2.46公里。改造配水管道总长145.04公里。四合村泵站增加1套备用加压泵。新增管网监测设施35套。</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>对清溪水厂原取水口进行改造。改造清溪厂输水管道长6.38公里。清溪水厂新建3000m³/d集成水厂1套，增设废水回收及污泥浓缩系统1套。新建配水管道总长2.46公里。改造配水管道总长145.04公里。四合村泵站增加1套备用加压泵。新增管网监测设施35套。</t>
+          <t>合同预估金额：2888.89万元</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>合同预估金额：2888.89万元</t>
+          <t>集成水厂、输水管道、配水管道、加压泵、管网监测设施</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>集成水厂、输水管道、配水管道、加压泵、管网监测设施</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
           <t>涪陵区清溪镇农村供水保障能力提升工程招标计划 重庆市工程建设项目招标计划表 项目名称 涪陵区清溪镇农村供水保障能力提升工程 招标法人 或招标人 重庆水务环境控股集团渝东自来水有限公司 网 名称（盖 章） 项目批准 文件及文 涪陵发改〔2026〕467号 务 号 对清溪水厂原取水口进行改造。改造清溪水厂输水管道长6.38公里。清溪水厂新建3000m3/d集成水 主要建设 厂1套，增设废水回收及污泥浓缩系统1套。新建配水管道总长2.46公里。改造配水管道总长145.04 内容 公里。四合村泵站增加1套备用加压泵。新商增管网监测设施35套。 招标项目 招标方 招标文件计 拟交易场 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 所 (万元) 对清溪水厂原道取水口进行 改造。改造清溪水厂输水 管道长6.38公里。清溪水厂 涪陵区清 新建3000m3/d集成水厂1套， 重庆市涪 招标项目 溪镇农村 增设废水回收及污泥浓缩 公开招 陵区公共 管 1 供水保障 2026-09 2888.89 系统1套。新建配水管道总 标 资源交易 能力提升 长2.46公里。改造配水管道 中心 工程 总长145.04公里。四合村泵 站增加1套备用加压泵。新 国 增管网监测设施35套。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075552.html 中 cqdingjiu 2026.08.21 10:06:55</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="n">
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
         <v>80</v>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -3721,34 +3519,29 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>改造11000m³/d(旺水垭6000m³/d和二水厂5000m³/d)原水处理系统及辅助设施，主要包括加氯系统、加药系统、清水池、絮凝池、重力无阀滤池、污水处理回收池、二水厂泵房设备等及其他辅助设施。更换旺水垭水厂至张家塘配水管13.5km，张家塘至滴水配水管长3.3km，全长16.8km；滴水至洪湖配水管长0.3km；更换八一水库至旺水垭水厂引水管1.7km，更换珍溪二水厂至珍溪大桥配水管5km，新建应急泵站至百汇大桥配水管9km；百汇至观将泵站4.5km；共计37.3km。</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>改造11000m³/d(旺水垭6000m³/d和二水厂5000m³/d)原水处理系统及辅助设施，主要包括加氯系统、加药系统、清水池、絮凝池、重力无阀滤池、污水处理回收池、二水厂泵房设备等及其他辅助设施。更换旺水垭水厂至张家塘配水管13.5km，张家塘至滴水配水管长3.3km，全长16.8km；滴水至洪湖配水管长0.3km；更换八一水库至旺水垭水厂引水管1.7km，更换珍溪二水厂至珍溪大桥配水管5km，新建应急泵站至百汇大桥配水管9km；百汇至观将泵站4.5km；共计37.3km。</t>
+          <t>合同预估金额3427.27万元</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>合同预估金额3427.27万元</t>
+          <t>管材</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>管材</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
           <t>涪陵区珍溪镇农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目名 涪陵区珍溪镇农村供水保障能力提升工程（一期） 称 招标法 网 人或招 重庆水务环境控股集团渝东自来水有限公司 标人名称 （盖章） 项目批 务 准文件 涪陵发改〔2026〕476号 及文号 (一)改造11000m3/d(旺水垭6000m3/d和二水厂5000m3/d)原水处理系统及辅助设施，主要有加氯系统、 加药系统、清水池、絮凝池、重力无阀滤池、商污水处理回收池、二水厂泵房设备等及其他辅助设施。 主要建 (二)更换旺水垭水厂至张家塘配水管13.5km，张家塘至滴水配水管长3.3km，全长16.8km；滴水至洪 设内容 湖配水管长0.3km；更换八一水库至旺水垭水厂引水管1.7km，更换珍溪二水厂至珍溪大桥配水管5km， 新建应急泵站至百汇大桥配水管9km：百汇至观将泵站4.5km；共计37.3km。 道 招标项目 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 场所 (万元) (一)改造11000m3/d(旺水 垭6000m3/d和二水厂5000m3/d) 管 原水处理系统及辅助设施，主 要有加氯系统、加药系统、清 水池、絮凝池、重力无阀滤池、 污水处理回收池、二水厂泵房 涪陵国区珍 设备等及其他辅助设施。(二) 重庆市 招标项 溪镇农村 更换旺水垭水厂至张家塘配水 涪陵区 目 供水保障 公开招 1 管13.5km，张家塘至滴水配水 2026-09 公共资 3427.27 能力提升 标 管长3.3km，全长16.8km；滴水 源交易 中工程（一 至洪湖配水管长0.3km；更换八 中心 期） 一水库至旺水垭水厂引水 管1.7km，更换珍溪二水厂至珍 溪大桥配水管5km，新建应急 泵站至百汇大桥配水管9km： 百汇至观将泵站4.5km；共 计37.3km。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075551.html cqdingjiu 2026.08.21 10:06:56</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="n">
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
         <v>80</v>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标, 供水, 改造</t>
         </is>
@@ -3793,34 +3586,29 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>新建及整治输配水管网总长124.26千米，新建加压泵站5座，新建高位水箱4座（总容积354立方米），武陵山水厂新建废水处理系统1套及配套电气工程等。</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>新建及整治输配水管网总长124.26千米，新建加压泵站5座，新建高位水箱4座（总容积354立方米），武陵山水厂新建废水处理系统1套及配套电气工程等。</t>
+          <t>合同预估金额1861.77万元</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>合同预估金额1861.77万元</t>
+          <t>输配水管网、加压泵站、高位水箱、废水处理系统、电气工程</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>输配水管网、加压泵站、高位水箱、废水处理系统、电气工程</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
           <t>涪陵区武陵山镇农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区武陵山镇农村供水保障能力提升工程 名称 招标 网 法人 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 务 （盖 章） 项目 批准 商 文件 涪陵发改〔2026〕468号 及文 号 主要 道 新建及整治输配水管网总长 124.26千米，新建加压泵站 5座，新建高位水箱4座（总容积 354立方米），武 建设 陵山水厂新建废水处理系统1套及配套电气工程等。 内容 招 管 拟 标 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 国 称 涪 陵 区 中 重 武 庆 陵 市 山 招标 涪 镇 项目 陵 农 公 区 村 新建及整治输配水管网总长 124.26千米，新建加压泵站 5座，新建高 开 公 1 供 位水箱4座（总容积 354立方米），武陵山水厂新建废水处理系统1套 2026-09 1861.77 招 共 水 及配套电气工程等。 标 资 保 源 障 交 能 易 力 中 提 心 升 工 程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075549.html cqdingjiu 2026.08.21 10:06:56</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="n">
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
         <v>80</v>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>涪陵区武陵山镇, 农村供水保障能力提升工程, 重庆, 输配水管网, 加压泵站, 高位水箱, 废水处理系统, 电气工程</t>
         </is>
@@ -3865,34 +3653,29 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>建设配水管网总长34.80km，新建加压泵站2座、改造已成泵站2座、新建加氯加药间1座、新建高位水箱7座、新建计量监测设施以及配套电气工程。</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>建设配水管网总长34.80km，新建加压泵站2座、改造已成泵站2座、新建加氯加药间1座、新建高位水箱7座、新建计量监测设施以及配套电气工程。</t>
+          <t>合同预估金额3503.77万元</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>合同预估金额3503.77万元</t>
+          <t>配水管网、加压泵站、加氯加药间、高位水箱、计量监测设施、电气工程</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>配水管网、加压泵站、加氯加药间、高位水箱、计量监测设施、电气工程</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
           <t>涪陵区江东街道农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目名 涪陵区江东街道农村供水保障能力提升工程（一期） 称 招标法 网 人或招 重庆水务环境控股集团渝东自来水有限公司 标人名称 （盖章） 项目批 务 准文件 涪陵发改〔2026〕470 号 及文号 主要建 建设配水管网总长 34.80km，新建加压泵站 2 座、改造已成泵站 2 座、新建加氯加药间 1 座、新建高位 设内容 水箱 7 座、新建计量监测设施以及配套电气工程商。 招 招标文件 拟交 合同预估 序 招标项 标 备 招标内容 计划发布 易场 金额(万 号 目名称 方 注 道 时间 所 元) 式 涪陵区 重庆 招标项 江东街 市涪 目 建设配水管网总长 34.80km，新建加压泵站 2 座、 公 道农村 陵区 管 改造已成泵站 2 座、新建加氯加药间 1 座、新建高 开 1 供水保 2026-09 公共 3503.77 位水箱 7 座、新建计量监测设施以及配套电气工 招 障能力 资源 程。 标 提升工程 交易 （一期） 中心 国 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075548.html cqdingjiu 20中26.08.21 10:06:56</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="n">
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
         <v>90</v>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>重庆, 农村供水保障能力提升工程, 配水管网, 加压泵站, 加氯加药间, 高位水箱, 计量监测设施, 电气工程</t>
         </is>
@@ -3931,32 +3714,31 @@
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>详见附件。</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>详见附件。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>内外涂环氧消防复合钢管管件</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>内外涂环氧消防复合钢管管件</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
           <t>中国电建水电五局二公司重庆轨道交通17号线一期7标内外涂环氧消防复合钢管管件采购项目公开竞价采购(二次 挂网)变更公告(一) 详见附件。 信息来源:https://www.chinapipe.net/project/d3075376.html cqdingjiu 2026.08.21 10:06:56 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="n">
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
         <v>60</v>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -4001,34 +3783,29 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>石柱土家族自治县</t>
+          <t>本次修复选择开挖换管：开挖约80米，2孔110波纹管、2孔蜂窝管，新建两通信手控井。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>本次修复选择开挖换管：开挖约80米，2孔110波纹管、2孔蜂窝管，新建两通信手控井。</t>
+          <t>项目资金已落实。</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>项目资金已落实。</t>
+          <t>通信管道</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>通信管道</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
           <t>2026年石柱分公司黄水镇黄连大道通信管道建设招标公告 ZB_ZHAOBIAOGONGGAO_START 本询比项目为 2026年石柱分公司黄水镇黄连大道通信管道建设 （标段 编号： CQBBFA202604170051 ），采购人为 中国电信股份有限公司石柱分公司 ，采购代理机构为 。项目 资金已落实。 具备采购条件，现进行公开询比，特邀请有意向的且具有提供标的物能力的潜在供应商（以下简 称供应商）参加询比响应。 1.项目概况与采购内容 1.1项目概况： 2026年石柱分公司黄水黄连大道通信管道修复项目主要针对黄水网黄连大道受损通信管道进行修 复80米 本次集中询比合同有效期为： 2026.9-2026.12 1.2采购内容 及标包划分情况： 务 1.2.1 本次询比的规模、货物名称、数量及主要技术参数、交货期及交货地点具体如下：黄水镇黄连大道80米通 信管道修复。 序号 标包名称 产品名称 规格型号 数量 交货地点 交货期 商 2026年石柱分公司黄水 黄水镇黄连 1 镇黄连大道通信管道建 管道建设 新建2孔110波纹管、 新建2孔蜂窝管 80 2026.12.20 大道 设 道 本项目 不划分标包 。 ${ } ${ 本项目允许供应商同时成交的最多标包数为 0 个。 } 本项目将按照最新的《中国电信供应商不良行为管 理规则》执行供应商不良行为处理结果，请重点关注处理结果适用的供应商主体、被处理产品、处理范围、禁 限期、处理措施等关键内容，请务必登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）查阅《中国 管 电信供应商不良行为管理规则》。 本项目根据《中国电信供应商不良行为管理规则》选择适用备选处理措施 （但涉及生产安全责任事故的处理结果不适用备选措施）。 1.2.2成交供应商数量： 1 个，每个成交供应商对应的份额如下 ： [请在此处自行编辑与采购方案相同的成交原则] 国 ${ 1.2.2成交供应商数量如下： [ 请在此处自行编辑与采购方案相同的有效供应商及成交供应商数量原则相关表格 ] 每个成交供应商对应的份额如下: [请在此处自行编辑与采购方案相同的份额分配原则] } 1.3本项目 设置最高 响应限价 。 设置最高响应限价，最高响应限价为不含税31000元人民币/计算方法，供应商响应报价高于最高 响应限价的，其响应将被否决 供应商响应报价高于最高响应限价的，其响应 将被否决。 ${ } 2.供应商中资格要求 2.1供应商基本资格要求 2.1.1 供应商 应为 中华人民共和国境内 法律上和财务上独立的法人或依法登记注册的其他组织，合法运作并 独立于采购人和采购代理机构。 供应商应具有良好的银行资信和商业信誉。法人下属不具备法人资格的分支机 构参与响应的，应提供所属法人针对本项目或覆盖本项目的经营事项的有效授权。 2.1.2 供应商 的法定代表人或负责人为同一人或者存在控股、管理关系的不同 供应商 ，不得参加同一标包响应或 者未划分标包的同一询比项目响应。 ${ 2.1.3 } ${ 2.1.3 } 2.1.4 本次询比 不接受 联合体响应。 ${如 供应商 为联合体，应满足下列要求： （1） 联合体各方必须按询比文件提供的格式签订联合体协议书，明确联合体牵头人和各方的权利义务； （2）由同一 专业的单位组成的联合体，按照资质等级较低的单位确定资质等级； （3）联合体各方不得再以自己名义单独或 加入其他联合体在同一标包或者未划分标包的同一询比项目中响应。 ${ （4） 。} } 2.1.5 本次询比 不接受代理商响应。 ${ （1）产品制造商注册地在中华人民共和国境外（与中华人民共和国有正常贸易与往来的国家或地区）及香港、 澳门、台湾地区且必须使用代理商响应和签订销售合同的；（2）产品制造商为注册地在中华人民共和国境内的 外资企业（包括香港、澳门、台湾地区资本）或者由外国投资者（包括香港、澳门、台湾地区）享有绝对控制权 （最大或最多表决权）的企业且必须使用代理商响应和签订销售合同的。代理商响应的，应满足下列要求 ： } ${ （1） ${ （2） 供应商与产品制造商 的代理合作关系迄今为止应已持续 0 年（含）以上。 } ${ （3） } } ${ 2.1.6 与供应商有产品代工制造关系的制造商不得参加同一标包响应或者未划分标包的同一询比项目响 应。 } 2.1.7 供应商须提供2022年1月1日至本项目发布公告之日的同类项目（通信管道施工类）证明材料， 合同累计金额不低于3万元（含税） 2.2供应商不得存在下列情形之一 （1） 为采购人不具有独立法人资格的附属机构（单位）； （2） 被依法暂停或取消 投标/ 响应资格的； （3） 被责令停产停业、暂扣或者吊销许可证、暂扣或者吊销执照； （4） 进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （5） 在最近三年内（自 2022年04月01日 起）被相关行业主管部门或司法机关认定有骗取 中标/成交 、严重 违约、重大工程质量或者安全问题的； 网 （6） 在最近五年内（自 2022年06月01日 起）被判处单位行贿罪，且行贿行为与采购活动相关的（以“中国 裁判文书网”的生效判决为准）； （7） 在最近五年内（自 2022年06月01日 起）被判处合同诈骗罪的（以“中国裁判文书网”的生效判决为 务 准）； （8） 被最高人民法院在“信用中国”网站（www.creditchina.gov.cn）或各级信用信息共享平台中列入失信被执 行人名单，已执行完毕或不再执行的除外； 商 （9） 为本询比项目提供过设计、编制技术规范和其他文件的咨询服务 ； （10） 为本工程项目的相关监理人，或者与本工程项目的相关监理人存在隶属关系或者其他利害关系； 道 （11） 为本询比项目的代建人 ； （12） 为本询比项目的采购代理机构 ； 管 （13） 与本询比项目的监理人或代建人或采购代理机构同为一个法定代表人 ； （14） 与本询比项目的监理人或代建人或采购代理机构存在控股或参股关系 ； （15） 被工商行政管理国机关在国家企业信用信息公示系统中列入严重违法失信企业名单的； （16） 中国电信在职员工违规担任供应商法定代表人并参与采购活动的； （17） 中国电信集团有限公司/中国电信股份有限公司中层及以上管理人员违反有关领导人员配偶、子女及其配 中 偶经商办企业行为管理规定，其配偶、子女及其配偶经商办企业参与采购活动的； （18） 中国电信领导人员离职或退休后三年内违反《国有企业领导人员廉洁从业若干规定》等相关规定任职、 投资入股的私营企业、外资企业和中介机构，参与其原任职单位采购活动的； ${ （19） } （19） 其他按照中国电信供应商不良行为处理结果及《中国电信供应商不良行为管理规则》的结 果执行规则，应对供应商及其响应产品在本项目中执行禁止采购处理措施的； （20） 法律法规、询比文件限定的其他情形。 ${ 供应商 是代理商的，本条所指的 供应商 也包括其所代理的制造商。 } ${ 联合体响应的，联合体成员均不得 存在上述任一情形。 } 2.3产品资格要求 2.3.1 产品 应是来自中华人民共和国 ${或是与中华人民共和国有正常贸易与往来的国家或地区} 的 成熟稳定的 产品 。 ${ 2.3.2 产品 。 } ${ 2.3.3 产品 。 } ${ 2.3.4 。 } ${ 2.3.5 。 } 2.3.6 产品应符合中国电信相关技术要求， 并满足以下关键技术指标： （1） 序号 技术指标 具体要求 1 开挖深度 埋深≥0.8m（道路≥1.2m） 2 施工规格 本次修复选择开挖换管：开挖约80米，2孔110波纹管、2孔蜂窝管，新建两通信手控井 ${ 2.3.7 产品 业绩要求： 。 } ${ 2.3.8 。 } ${ 2.4 产品制造商资格要求 2.4.1 制造商应提供合法有效的登记 （或注册）证明文件，应具有良好的银行资信和商业信誉。 } ${ 2.4.2 } ${ 2.4.2 } ${ 2.4.3 } ${ 2.4.4 } ${ 2.4.5 } ${ 2.5现场考察 } ${ 2.6评价检测 } 2.7 法律法规规定的其他要求。 3.资格审查方法 本项目将进行资格后审，资格审查标准和内容见询比文件第三章“评审办法”，凡未通过资格后审的供应商， 其响应将被否决 。 网 4.询比文件的获取 4.1询比文件获取时间: 2026年08月25日 00时00分00秒 至 2026年09月01日 00时00分00秒 （北京时间，下同）。 4.2询比文件获取方式：登录“中国电信阳光采购网（https://caigou.c务hinatelecom.com.cn）”后，通过“招投标-采 购文件领取”模块或通过“电子采购入口”跳转中国电信电子采购系统，进入本项目进行询比文件登记申领， 未在系统注册的供应商须先进行注册，注册方法详见本公告“ 7 供应商注册”。 4.3询比文件费用： 本项目不收取文件费用。 ${每套售价商 0 元人民币，售后不退。支付要求： } 5.响应文件的递交 5.1响应文件递交截止时间（即响应截止时间）为： 2026年09月02日 00时00分00秒 道 5.2 电子响应文件的提交方式：登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投 标-我的项目”模块或通过“电子采购入口”跳转中国电信电子采购系统，选择本项目进行响应文件提交，供应 商应在响应文件提交截止时间之前通过电子采购系统完成加密电子响应文件的上传。供应商未在电子采购系统 进行询比文件申领登记或电子响应管文件未按照要求加密的，将无法通过电子采购系统提交电子响应文件 。 5.3 本项目将于响应文件提交截止同一时间通过中国电信电子采购系统开启响应文件， 采购人/采购代理机构 邀 请响应供应商的法定代表人或者其委托代理人准时参加 。 国 ${ 6.样品的递交 6.1样品递交的时间、地点：于 递交至 。 } 7. 供应商注册 7.1 中国电信阳光采购网注册 未注册过的潜在供应商，须通过中国电信阳光采购网（https://caigou.chinatelecom.com.cn）首页“立即注册”模 中 块完成注册后，方可申领本项目询比文件。 7.2 CA证书办理 参加询比响应的潜在供应商须提前办理CA证书，并确保CA证书在使用时有效。CA证书办理流程详见中国电信 阳光采购网首页“操作指引-CA办理”。 7.3 技术支撑联系方式 服务热线：4000111884 服务邮箱：zb_support@chinatelecom.cn（电子采购系统技术支撑） ctsc@chinatelecom.cn（CA证书办理技术支撑） 8. 发布公告的媒介 本询比公告在 中国电信阳光采购网（https://caigou.chinatelecom.com.cn） 、中国招标投标公共服务平台 （http://www.cebpubservice.com/） 上发布，其他媒介转载无效。 9. 联系及异议接收方式 9.1 联系方式 采 购 人: 中国电信股份有限公司石柱分公司 采购代理机构: 地 址： 重庆市石柱县城南路6号 地 址： 无 邮 编： 邮 编： 无 联 系 人： 马卫平 联 系 人： 无 电 话： 17365204567 电 话： 无 电子邮件： 17365204567@189.cn 电子邮件： 无 网 址： www.chinatelecom.com.cn或“/” 网 址： 无 网 开户银行： 无 账 号： 无 9.2 异议接收方式 务 登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投标-采购异议-提出异议”模块提出。 采购代理机构： 商 2026年08月25日 信息来源:https://www.chinapipe.net/project/d30道75344.html cqdingjiu 2026.08.21 10:06:56 管 国 中</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="n">
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
         <v>0</v>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>未识别到明确匹配关键词</t>
         </is>
@@ -4067,32 +3844,31 @@
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>重庆站站房CQZSG-4标项目蓝色PVC袖阀管(外径60mm)询价采购公告</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>重庆站站房CQZSG-4标项目蓝色PVC袖阀管(外径60mm)询价采购公告</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>蓝色PVC袖阀管，外径60mm，壁厚4.5-5mm PVC管</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>蓝色PVC袖阀管，外径60mm，壁厚4.5-5mm PVC管</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
           <t>重庆站站房CQZSG-4标项目蓝色PVC袖阀管(外径60mm)询价采购公告 ZTEJWZ-JZ-2026-询027（一） 采购单位:重庆站站房CQZSG-4标段项目经理部 发布时间:2026-08-18 19:06 报价截止时间:2026-08-21 10:00 招标方联系人:刘健 网 招标方联系电话:13540650091 招标方邮箱: 务 监督方联系人:纪委 监督方联系电话:028-87653066 商 监督方邮箱: 保证金:0.0元 道 结算与发票信息: 结算方式：上月21日至本月的20日为一个结算周期，当月20日为本月的结算截止日期。结算时根据甲方检验合格 及双方共同签认的凭证计算当月实际收货数量。 管 支付条件：结算完成后，甲方在收到乙方开具的正式的增值税专用发票后第1个月支付该批物资结算金额的70%， 第12个月支付20%，剩余10%在第18-24月内按月均衡支付。 发票种类：增值税专用国发票 发票抬头：中铁二局集团有限公司 税号：9151中0100MA61RKR7X3 其他要求： 交货信息: 交货方式:点数验收 收货人:刘健 收货人联系方式:13540650091 其他说明事项: 流水号：询2026081800458 交 标的 规格 计量 标的编号 数量 技术标准及要求 货 送货地址 名称 型号 单位 期 蓝色PVC袖阀管，外 西南区-重庆市-市辖区-渝中区-重 袖阀 径60mm，壁 庆市菜园坝立交以西，龙家湾隧道 0950999183764 - 23188.0 米 管 厚4.5-5mm PVC管，承压 以东，菜袁路以北，王家坡以南的 不小于5MPa,节长4m 地块内，原重庆站。 报价网址:http://www.crecgec.com 信息来源:https://www.chinapipe.net/project/d3075317.html cqdingjiu 2026.08.21 10:06:56 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="n">
         <v>0</v>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>塑料管不计匹配分</t>
         </is>
@@ -4137,34 +3913,29 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>新建、更换配水管网396.72km（dn20-dn160PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收及污泥浓缩处理系统。</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>新建、更换配水管网396.72km（dn20-dn160PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收及污泥浓缩处理系统。</t>
+          <t>合同金额：3611.91万元</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>合同金额：3611.91万元</t>
+          <t>dn20-dn160PE管、DN40-DN250抗菌耐磨涂塑钢管</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>dn20-dn160PE管、DN40-DN250抗菌耐磨涂塑钢管</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
           <t>涪陵区蔺市街道农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区蔺市街道农村供水保障能力提升工程（一期） 名称 招标 法人 或招 标人重庆水务环境控股集团渝东自来水有限公司 名称 网 （盖 章） 项目 批准 文件涪陵发改〔2026〕474号 及文 号 主要 务 建设新建、更换配水管网 396.72km（dn20-dnl60PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收及污泥浓缩处理系统。 内容 拟 招招标文 合同预 招标 交 序 标件计划 估金 备 项目招标内容 易 号 方发布时 额(万 注 名称 场 式间 元) 所 商 重 庆 涪陵 市 区蔺 招标 市街 涪 项目 道农 陵 公 区 村供 新建、更换配水管网 396.72km（dn20-dnl60PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收 开 公 1 水保 2026-09 3611.91 及污泥浓缩处理系统。 招 共 障能 道 标 资 力提 源 升工程 交 （一 易 期） 中 心 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075278.html 管 cqdingjiu 2026.08.21 10:06:57 国 中</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="n">
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
         <v>80</v>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标, 商机</t>
         </is>
@@ -4209,34 +3980,29 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>改造李渡街道15个村（社区）配水主支管道，更换配水主管网193.71千米（DN250-DN40抗菌耐磨涂塑钢管、dn40-dn25PE管）及配套附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治3座，新建测控井78座。</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>改造李渡街道15个村（社区）配水主支管道，更换配水主管网193.71千米（DN250-DN40抗菌耐磨涂塑钢管、dn40-dn25PE管）及配套附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治3座，新建测控井78座。</t>
+          <t>项目批准文件：涪陵发改[2026]469号</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>项目批准文件：涪陵发改[2026]469号</t>
+          <t>DN250-DN40抗菌耐磨涂塑钢管、dn40-dn25PE管</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>DN250-DN40抗菌耐磨涂塑钢管、dn40-dn25PE管</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
           <t>涪陵区李渡街道农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区李渡街道农村供水保障能力提升工程 名称 招标 法人 网 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 务 项目 批准 文件 涪陵发改〔2026〕469号 及文 号 商 主要 改造李渡街道 15个村（社区）配水主支管道，更换配水主管网 193.71 千米（DN250-DN40 抗菌耐磨涂塑钢管、dn40-dn25PE管）及配套 建设 附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治 3座，新建测控井78座。 内容 招 拟 标 道 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 称 管 涪 陵 区 重 李 庆 渡 市 街 国 招标 涪 道 项目 陵 农 公 区 村 改造李渡街道 15个村（社区）配水主支管道，更换配水主管网 193.71 千米（DN250-DN40 抗菌耐磨涂 开 公 1 供 塑钢管、dn40-dn25PE管）及配套附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治 3座，新建 2026-09 2372.74 招 共 水中测控井78座。 标 资 保 源 障 交 能 易 力 中 提 心 升 工 程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075277.html cqdingjiu 2026.08.21 10:06:57</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="n">
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
         <v>80</v>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 改造, 配水主支管道, 更换配水主管网, 抗菌耐磨涂塑钢管, 泵站改造, 集成泵站, 蓄水池整治, 测控井</t>
         </is>
@@ -4281,34 +4047,29 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>本项目对珍溪镇23个村(社区)安装配水管网660km及配套附属设施，其中：1.De160~De40的PE管主要建设有232km；2.连接各村社的De32~De20的PE管有381km；3.219~32的衬塑钢管47km。(二)购置安装泵站14座(一用一备共计28台水泵)，其中新建泵商站10座、更换泵站4座及配套电力设施;新建不锈钢水箱2座等。(三)购置安装(0~25kg)减压阀61个;排污阀(25kg）3个。</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>本项目对珍溪镇23个村(社区)安装配水管网660km及配套附属设施，其中：1.De160~De40的PE管主要建设有232km；2.连接各村社的De32~De20的PE管有381km；3.219~32的衬塑钢管47km。(二)购置安装泵站14座(一用一备共计28台水泵)，其中新建泵商站10座、更换泵站4座及配套电力设施;新建不锈钢水箱2座等。(三)购置安装(0~25kg)减压阀61个;排污阀(25kg）3个。</t>
+          <t>合同预估金额为2182.77万元</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>合同预估金额为2182.77万元</t>
+          <t>PE管、衬塑钢管、水泵、不锈钢水箱、减压阀、排污阀</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>PE管、衬塑钢管、水泵、不锈钢水箱、减压阀、排污阀</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
           <t>涪陵区珍溪镇农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目名称 涪陵区珍溪镇农村供水保障能力提升工程（二期） 招标法人 或招标人 重庆水务环境控股集团渝东自来水有限公司 网 名称（盖 章） 项目批准 文件及文 涪陵发改〔2026〕477号 务 号 (一)本项目对珍溪镇23个村(社区)安装配水管网660km及配套附属设施，其中：1.De160~De40的PE管 主要建设 有232km；2.连接各村社的De32~De20的PE管有381km；3.219~32的衬塑钢管47km。(二)购置安装泵 内容 站14座(一用一备共计28台水泵)，其中新建泵商站10座、更换泵站4座及配套电力设施;新建不锈钢水 箱2座等。(三)购置安装(0~25kg)减压阀61个;排污阀(25kg）3个。 招标项目名 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 称 式 划发布时间 场所 (万元) 道 (一)本项目对珍溪镇23个 村(社区)安装配水管网660km 及配套附属设施，其 中：1.De160~De40的PE管 管 有232km；2.连接各村社 涪陵区珍溪 重庆市 的De32~De20的PE管有381km； 招标项目 镇农村供水 涪陵区 3.219~32的衬塑钢 公开招 1 保障能力提 2026-09 公共资 2182.77 管47km。(二)购置安装泵 标 升工国程（二 源交易 站14座(一用一备共计28台水 期） 中心 泵)，其中新建泵站10座、更 换泵站4座及配套电力设施; 新建不锈钢水箱2座等。(三) 中 购置安装(0~25kg)减压阀61 个;排污阀(25kg）3个。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075275.html cqdingjiu 2026.08.21 10:06:57</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="n">
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
         <v>90</v>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>涪陵区, 珍溪镇, 农村供水, 提升工程, 衬塑钢管, 水泵, 不锈钢水箱, 减压阀, 排污阀</t>
         </is>
@@ -4353,34 +4114,29 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长105.307km（dn20-dn40PE管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建1座改造3座；新建测控井52座。</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长105.307km（dn20-dn40PE管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建1座改造3座；新建测控井52座。</t>
+          <t>合同预估金额：2652.89万元</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>合同预估金额：2652.89万元</t>
+          <t>净水设备、PE管、抗菌耐磨涂塑钢管</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>净水设备、PE管、抗菌耐磨涂塑钢管</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
           <t>涪陵区蔺市街道农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区蔺市街道农村供水保障能力提升工程（二期） 名称 招标 法人 网 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 务 项目 批准 文件 涪陵发改〔2026〕475号 及文 号 商 主要 八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长 105.307km（dn20-dn40PE 建设 管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建 1座改造3座；新建测控井 52座。 内容 拟 招 招标文 合同预 招标 交 序 道 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 所 重 庆 涪陵 管 市 区蔺 涪 招标 市街 陵 项目 道农 公 区 村供 八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长 开 公 1 水保 105.307km（dn20-dn40PE 管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建 1座改造3座； 2026-09 2652.89 国 招 共 障能 新建测控井 52座。 标 资 力提 源 升工程 交 （二 易 期） 中 中 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075274.html cqdingjiu 2026.08.21 10:06:57</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="n">
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="n">
         <v>80</v>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -4419,32 +4175,31 @@
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>本项目涉及管道为鱼洞污水处理厂专件厂线管网，管道编号为WD4-WD8+1，该管道为自流管道，位于鱼轻桥至河嘴倒虹井段，主要用于收集输送鱼洞大江商至华熙片区的生活污水。该段管道管径为DN600，管道为混凝土管，主要采用架空明敷的方式沿河敷设。该管道自建成投运以来已有20余年，管道及污水井老化严重现象十分明显，容易出现破损从而造成污水溢流，造成环保风险。为规避环保风险且保障该段管道以及鱼洞污水厂的正常收水及运行，需对该段管道进行改造。</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>本项目涉及管道为鱼洞污水处理厂专件厂线管网，管道编号为WD4-WD8+1，该管道为自流管道，位于鱼轻桥至河嘴倒虹井段，主要用于收集输送鱼洞大江商至华熙片区的生活污水。该段管道管径为DN600，管道为混凝土管，主要采用架空明敷的方式沿河敷设。该管道自建成投运以来已有20余年，管道及污水井老化严重现象十分明显，容易出现破损从而造成污水溢流，造成环保风险。为规避环保风险且保障该段管道以及鱼洞污水厂的正常收水及运行，需对该段管道进行改造。</t>
+          <t>项目资金来自企业自筹</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>项目资金来自企业自筹</t>
+          <t>DN600混凝土管，检查井</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>DN600混凝土管，检查井</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
           <t>重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目项目公告 重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目（项目名称）比选公告 1.比选条件 本比选项目重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目（项目名称），比选人为重庆市排 网 水有限公司，比选项目资金来自企业自筹（资金来源），项目已具备比选条件。中标后合同与重庆市豪洋水务 建设管理有限公司签订。现对本项目进行公开比选，诚邀有兴趣的潜在投标人参与投标。 2.项目概况与比选范围 务 2.1 建设地点：重庆市巴南区 2.2 项目概况：本项目涉及管道为鱼洞污水处理厂专件厂线管网，管道编号为WD4-WD8+1,该管道为自流管道， 位于鱼轻桥至河嘴倒虹井段，主要用于收集输送鱼洞大江商至华熙片区的生活污水。该段管道管径为DN600，管道 为混凝土管，主要采用架空明敷的方式沿河敷设。该管道自建成投运以来已有20余年，管道及污水井老化严重现 象十分明显，容易出现破损从而造成污水溢流，造成环保风险。为规避环保风险且保障该段管道以及鱼洞污水 厂的正常收水及运行，需对该段管道进行改造。 道 2.3 比选范围：拆除现状管道为DN600混凝土管，同时需拆除并新建9座检查井。 2.4 工期要求：30日历天，以甲方通知进场时间为准。 管 2.5缺陷责任期要求：24个月 3.投标人资格要求 国 3.1 本次比选要求投标人须具备以下条件： 3.1.1 本次比选要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰级 及以上资质。 中 3.1.2 投标人还应在人员、设备、资金等方面具有相应的施工能力，详见比选文件第二章投标人须知前附表第1.4.1 项内容。 3.2 本次比选接受不联合体投标。 4.比选文件的获取 4.1 投标人于2026年8月 18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子 版，以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都 视为投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的 一切后果由投标人自行负责。各投标单位应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行供应商注册，填写相关信息，审批过后成为 平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价、递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，将被否决投标。 4.4 比选文件每份售价800元，售后不退。投标单位在递交纸质投标文件时扫描支付，否则比选人拒绝接收其投标 文件。 5.投标文件的递交 5.1 电子投标文件递交时间：2026年8月24日14时30分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年8月24日14时00分至14时30分（北京时间），地点：重庆水务招标采购中心 （重庆市两江新区嘉华路36号重庆水务大厦5楼）。 5.3 投标截止时间：2026年 8月24日14时30分（北京时间）。 网 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 务 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 商 比 选 人：重庆市排水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝中区长江滨江路126号 地 址：重庆市两江新区嘉华路36号重庆水务大厦 道 联 系 人： 黄老师 联 系 人： 黄晓华 电 话： 023-67767416 电 话： 18523396416 管 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3075272.html 国 cqdingjiu 2026.08.21 10:06:57 中</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="n">
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
         <v>90</v>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>重庆, 排水公司, 污水处理厂, 管网改造, DN600混凝土管, 检查井</t>
         </is>
@@ -4489,34 +4244,29 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>潼南区</t>
+          <t>改建潼南城区输水主管网约39.63km及配套相应阀门阀件等，对城区供水管网上商老旧阀门阀件、设施设备进行更换，合理增设部分计量及压力监控、水质监控等。</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>改建潼南城区输水主管网约39.63km及配套相应阀门阀件等，对城区供水管网上商老旧阀门阀件、设施设备进行更换，合理增设部分计量及压力监控、水质监控等。</t>
+          <t>合同预估金额：918.00万元</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>合同预估金额：918.00万元</t>
+          <t>城区配套阀门阀件改造工程</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>城区配套阀门阀件改造工程</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
           <t>重庆市潼南城区老旧供水管网改造工程招标计划 重庆市工程建设项目招标计划表 项目名称 重庆市潼南城区老旧供水管网改造工程 招标法人或招 标人名称（盖 重庆市潼南自来水有限公司 网 章） 项目批准文件 及文号 务 主要建设内容 改建潼南城区输水主管网约39.63km及配套相应阀门阀件等 招标方 招标文件计 拟交易场 合同预估 序号 招标项目名称 招标内容 备注 式 划发布时间 所 金额(万元) 对城区供水管网上商 重庆市潼南城 老旧阀门阀件、设 区老旧供水管 重庆市潼 招标项目 施设备进行更换， 网改造工程 公开招 南区公共 1 保障供水管网稳定 2026-09 918.00 （城区配套阀 标 资源交易 运行合道理增设部分 门阀件改造工 中心 计量及压力监控、 程） 水质监控等。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3075266.html cqdingjiu 2026.08.21 10:06:58 国 中</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="n">
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="n">
         <v>80</v>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -4561,34 +4311,29 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>开州区</t>
+          <t>该项目涉及硬化生产便道、建设防旱池和蓄水池、建造育苗大棚和小棚、安装水源处理和水肥一体化设施、新建设备管理房以及完善蔬菜基地配套设施等内容。</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>该项目涉及硬化生产便道、建设防旱池和蓄水池、建造育苗大棚和小棚、安装水源处理和水肥一体化设施、新建设备管理房以及完善蔬菜基地配套设施等内容。</t>
+          <t>工程总投资335万元。</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>工程总投资335万元。</t>
+          <t>工程设计服务</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>工程设计服务</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
           <t>关于为【重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购】公开选取【工程设计】 机构的公告 我单位在重庆市网上中介超市公开选取工程设计中介服务机构，现将相关事项公告如下： 该项目为直接选取项目，由采购人从报名的中介服务机构中直接选定一家中介服务机构进行项目服务。 项目 重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购 名称 网 采购 重庆市开州区河堰镇人民政府 人 投资 审批 否 务 项目 是否 破产 商 业务 否 服务 项目 采购 道 所需 中介 其他 服务 事项 管 所需 服务 工程设计 类型 项目实施地点为国河堰镇清泉社区，项目建设内容为：硬化2米宽生产便道5.5千米，100方防旱池1口，50方 服务 蓄水池1口，标准自动化育苗大棚1个，蔬菜小棚20个，水源处理设施1套，水肥一体化配套设施1套，新 内容 建50平方米设备管理房，完善蔬菜基地配套设施等。工程总投资335万元。选取此项目设计单位（含预算 编制服务）。 中 中介 机构 资质（资格）要求 要求 资质 （资 1、报名单位提供有效的营业执照，资质证书（资质丙级或丙级以上），具备从事项目设计服务工作； 2、 格） 具有独立承担民事责任的能力； 3、具有良好的商业信誉和健全的财务会计制度； 4、具有履行合同所必 要求 需的专业技术能力； 5、有依法缴纳税收和社会保障资金的良好记录。 说明 其他 要求 无 说明 服务 时限 无要求，按照合同双方自行约定 说明 服务 3.1%费率 金额 金额 按文件要求执行 说明 选取 直接选取 方式 需规 避机 构 规避 原因 选取 2026-08-20 16:00:00 （选取时间到达后不接受报名，建议中介机构至少在选取开始半小时前完成报名。） 时间 采购 人业 网 务咨 重庆市开州区河堰镇人民政府（18716685679） 询电 话 采购 务 需求 26清泉社区项目设计服务采购说明.pdf 书下 载 商 2026-08-18 信息来源:https://www.chinapipe.net/project/d3075198.html 道 cqdingjiu 2026.08.21 10:06:58 管 国 中</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="n">
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
         <v>90</v>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -4633,34 +4378,29 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>开州区</t>
+          <t>1.建设果园水肥一体化系统1套，对示范柑桔果园建设水肥一体智能化系统;2.果园运输线4000米(含轨道主机、叉车、周转箱、三轮车等配套设施设备);3.建设排灌站一处;4.建设1.8米宽生产便道2000米，务周转场300平方米;5.配备载重无人机1台、小型挖机1台、电子控制屏1个;6.建设智慧平台与监测系统软硬件系统等。</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1.建设果园水肥一体化系统1套，对示范柑桔果园建设水肥一体智能化系统;2.果园运输线4000米(含轨道主机、叉车、周转箱、三轮车等配套设施设备);3.建设排灌站一处;4.建设1.8米宽生产便道2000米，务周转场300平方米;5.配备载重无人机1台、小型挖机1台、电子控制屏1个;6.建设智慧平台与监测系统软硬件系统等。</t>
+          <t>项目总投资金额：500万元，本次招标项目合同估算金额：446.278921万元</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>项目总投资金额：500万元，本次招标项目合同估算金额：446.278921万元</t>
+          <t>柑橘基地改造提升项目</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>柑橘基地改造提升项目</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
           <t>重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目招标公告 1.招标条件 本招标项目重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目已由重庆市开州区发展和改革委员会以开州 发改审〔2026〕357号批准建设，项目业主为重庆市开州区长沙镇人民政府，建设资金来自开州区2026年中央和 市级提前批财政衔接推进乡村振兴补助资金，项目出资比例为 100% ，招标人为重庆市开州区长沙镇人民 政府。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：开州区长沙镇桔香村 2.2 项目概况与建设规模：1.建设果园水肥一体化系统1套，对示范柑桔果园建设水肥一体智能化系统;2.果园运输 线4000米(含轨道主机、叉车、周转箱、三轮车等配套设施设备);3.建设排灌站一处;4.建设1.8米宽生产便道2000米， 务 周转场300平方米;5.配备载重无人机1台、小型挖机1台、电子控制屏1个;6.建设智慧平台与监测系统软硬件系统等。 2.3 本项目工程总投资金额： 500万元 本次招标项目合同估算金额： 446.278921万元 商 2.4 招标范围：招标人发布的由重庆中煜华资工程技术有限公司设计的《重庆市开州区2026年长沙镇桔香村柑橘 基地改造提升项目》施工图及图纸说明、招标文件(含补遗)及工程量清单、答疑资料、澄清资料范围内所涉及的 工作内容，具体以招标人发布的工程量清单及道施工图为准。 2.5 工期要求： 150日历天 缺陷责任期要求： 12个月 管 2.6 标段划分（如有）： / 2.7 其他： / 国 3.政府采购工程 3.1 是否属于政府采购工程：是 中 3.2 是否专门面向中小企业预留：否，按照《政府采购促进中小企业发展管理办法》第六条第(三)“按照本办法 规定预留采购份额 无法确保充分供应、充分竞争，或者存在可能影响政府采购目标实现的情形”的规定，故本 项目不专门面向中小企业预留。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包叁级及以 上资质或市政公用工程施工总承包叁级及以上资质或水利水电工程施工总承包叁级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在 重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）下载招 标文件、工程量清单、电子图纸等资料。参与投标的投标人需在 重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）完成市 场主体信息登记以及CA数字证书办理，办理方式请参见 重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、 重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）导航栏“主体信息”页面中“市场主 体信息登记”、“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完 成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区） （https://www.cqggzy.com/kaizhouweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告 发布至2026-08-21 17:00:00前。 5.3招标人应于2026-08-25 23:59:59前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源 交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）发布澄清。 6.投标文件递交的内容 网 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-21 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 务 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区） （https://www.cqggzy.com/kaizhouweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交 易监督网上发布。] 商 8.联系方式 招 标 人: 重庆市开州区长沙镇人民政府 代理机构: 重庆毅仁建设项目管理有限公司 重庆市开州区文峰街道天鹅湖社区富厚街158号附10 地 址: 重庆市开州区长沙镇山花街1号 地 址: 道号 邮 编: 邮 编: 项目负责人: 丁敬余 项目负责人: 谭毅 电 话: 15826368887 管电 话: 13452653126 传 真: 传 真: 电子邮箱: 1415705480@qq.com 电子邮箱: 开户银行: 国 开户银行: 账 号: 账 号: 监督部门:中重庆市开州区公共资源交易管理局 电 话: 023-52218977 2026年08月17日 重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目 户名 开户行 投标保证金账号 重庆市开州区公共资源交易中心 重庆农村商业银行股份有限公司开州支行 3401010120010012772000200 中国农业银行股份有限公司重庆开州支行营 重庆市开州区公共资源交易中心 314401010400104500000006031 业部 中国工商银行股份有限公司重庆开州支行营 重庆市开州区公共资源交易中心 9558853100005824176 业部 重庆市开州区公共资源交易中心 重庆银行股份有限公司开州支行 680101040007547-100984 重庆市开州区公共资源交易中心 中国银行股份有限公司重庆开州支行 108865555576VA00149 信息来源:https://www.chinapipe.net/project/d3075199.html cqdingjiu 2026.08.21 10:06:58</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="n">
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
         <v>90</v>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>重庆, 柑橘基地改造, 水肥一体化系统, 运输线, 排灌站, 生产便道, 无人机, 小型挖机, 智慧平台</t>
         </is>
@@ -4705,34 +4445,29 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>万盛区</t>
+          <t>万盛城区老旧供水管网更新改造工程答疑及补遗。</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>万盛城区老旧供水管网更新改造工程答疑及补遗。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>供水管网</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>供水管网</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
           <t>万盛城区老旧供水管网更新改造工程答疑及补遗(一) 万盛城区老旧供水管网更新改造工程 答疑及补遗（一） 各潜在投标人： 现将万盛城区老旧供水管网更新改造工程答疑及补遗（一）相关条款通知如下： 网 一、答疑 问题1：请问招标人是否委派业主专家参与评标吗？ 务 答：是，本项目评标委员会共7人，其中在重庆市综合评标专家库随机抽取5人，招标人代表2人。? 问题2：本项目是否采用异地评标方式？ 答：是 。 商 问题3：本项目是否有业主代表，如有，请明确业主代表数量。 答：是，本项目评标委员会共7人，其中在重道庆市综合评标专家库随机抽取5人，招标人代表2人 。 问题4：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 答：可以。 管 问题5：污水处理厂提标改造及附属管道施工业绩满足吗？ 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 国 问题6：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可以 不填(空白)，对此有无要求？ 答：无要求。? 中 问题7：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖章， 请问需要提供联合体协议书吗？ 。 答： 根据招标文件第二章“投标人须知前附表”1.4.1 第3条业绩要求中：“注：（2）投标人提供的业绩为联 合体业绩的，其在该业绩中的工作分工应与本项目承担的工作一致。”要求，故需要提供联合体协议书。 问题8：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要求”吗？ 答：填写“达到招标文件的要求”或按照招标文件相关条款填写具体内容均可 。 问题9：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 答：投标人的工程量清单单项报价不得为零报价(招标人提供的工程量清单单项最高限价中金额为零的除外)或者 负数报价，否则由评标委员会作否决投标处理。 问题10：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知书发 出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予提前注 销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 答：需要。但不将加盖正本作为评审因素。 问题11：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收，请 问我公司业绩满足业绩要求吗？ 答：不满足。? 问题12：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 答：可以 。 问题13：业绩要求的竣工时间是指竣工验收时间吗？ 答：是的。 网 问题14：重庆市电子招投标系统投标文件-报价部分“己标价工程量清单”-“投标总价”页面招标人名称需要填 写吗？ 务 答：由投标人自行决定是否填写，是否填写不作为评审因素。 问题15：请问招标人是否委派业主专家参与评标吗？ 答：是，本项目评标委员会共7人，其中在重庆市综合评商标专家库随机抽取5人，招标人代表2人。 问题16：自来水厂或者净水厂含管道施工业绩满足业绩要求吗？ 答：投标人提供的业绩合同规模和工程类别需道满足招标文件要求。? 问题17：有没有人行贿专家，有的话我们就不参加了。 答：本项目评标委员会由招标人按法律法规及相关规定依法组建。 管 问题18：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要 提供其他格式之外的其他承诺？ 答：请各潜在投标人仔国细阅读招标文件，并按招标文件要求提供相应承诺。 问题19：财务报告可以不提供财务报表附注吗？ 答：可以。 中 问题20：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 问题21：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、注册证 及在本单位注册的证明文件替代？ 答：退休证等材料不能替代养老保险证明，按招标文件执行。? 问题22：本项目是异地评标吗？ 答：是。 问题23：现在除了没有警戒线和技术方案的低价项目评标专家不被围猎，哪个项目不围猎评标专家，请问招标人 如何保证公平？ 答：本项目招标文件严格按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本（2026年版）》编制， 且本项目评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 问题24：没有低价警戒线怎么保证中高价呢？ 答：本项目未设置低价警戒线，通过综合评估法对各潜在投标人进行评审。分值由技术、商务、报价组成，综 合实力优良的投标人合理中高价可依靠综合得分优势参与竞争，同时招标文件履约追责条款约束投标人理性报 价，保障合理报价竞争环境。 问题25：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗？ 答：现场递交纸质保函原件的人员不作要求 。 问题26：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 网 答：电子投标系统中锁定不可修改的格式（如封面、投标函）直接填空即可，其他投标文件格式以加盖公章的 招标文件PDF文件为准。? 问题27：专业分包业绩满足业绩要求吗？ 务 答：不满足。 问题28： 市政道路包含给水管网施工业绩满足业绩要求吗？ 商 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 问题29：技术负责人在资格审查部分中提供了工程类高级及以上职称证后，在商务部分中再提供工程类高级及以 上职称证可以加分吗？ 道 答：可以。 问题30：万盛的项目挂綦江来投这样都还控制不了还全是你们万盛公司中的？是有啥猫腻是吧？参考之前的项目 管 全是万盛的公司中的！业主、专家全是你们自己人吧？ 答：本项目招标文件严格按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本（2026年版）》编制， 且本项目评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 国 二、补遗 1、本次重新发布本项目的工程量清单，在《重庆市公共资源交易网》(綦江区) （https://www.cqggzy.com/qijiangweb/）网上发布，请投标人自行下载。 中 招 标 人：重庆市万盛经济技术开发区城市管理局 招标代理机构：重庆力圣建设工程咨询有限公司 2026年8月18日 信息来源:https://www.chinapipe.net/project/d3074975.html cqdingjiu 2026.08.21 10:06:58</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="n">
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
         <v>80</v>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>重庆, 供水管网, 更新改造</t>
         </is>
@@ -4777,34 +4512,29 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>巴南区</t>
+          <t>为解决片区内涝问题，在李家沱街道、花溪街道改建d400-d800雨水管网9665m，管材采用高密度聚乙烯(HDPE)缠绕结构壁管B型管；改建d1000-d1400雨水管网664m，管材采用高密度聚乙烯(HDPE)缠绕结构壁管B型管、III级钢筋混凝土管；改建d1500-d2000雨水管网426m，管材采用III级钢筋混凝土管；改建d2100-d2600雨水管网1000m，管材采用III级钢筋混凝土管；修复雨水管网5345m，增加智能感知设备6套。</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>为解决片区内涝问题，在李家沱街道、花溪街道改建d400-d800雨水管网9665m，管材采用高密度聚乙烯(HDPE)缠绕结构壁管B型管；改建d1000-d1400雨水管网664m，管材采用高密度聚乙烯(HDPE)缠绕结构壁管B型管、III级钢筋混凝土管；改建d1500-d2000雨水管网426m，管材采用III级钢筋混凝土管；改建d2100-d2600雨水管网1000m，管材采用III级钢筋混凝土管；修复雨水管网5345m，增加智能感知设备6套。</t>
+          <t>本次招标项目工程费估算金额：11061.83万元，勘察设计合同估算金额：334.544万元。</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>本次招标项目工程费估算金额：11061.83万元，勘察设计合同估算金额：334.544万元。</t>
+          <t>雨水管网、高密度聚乙烯(HDPE)缠绕结构壁管B型管、III级钢筋混凝土管、智能感知设备</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>雨水管网、高密度聚乙烯(HDPE)缠绕结构壁管B型管、III级钢筋混凝土管、智能感知设备</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
           <t>重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告 重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告 1.招标条件 本招标项目 重庆市巴南区土桥片区内涝积水整治工程已由重庆市巴南区发展和改革委员会以巴南发改审 发[2025]33号文批准建设，项目业主为重庆市巴南区住房和城乡建设委员会，代建业主为重庆市巴南公路建设有 限公司，建设资金来自区级财政资金统筹，项目出资比例为 100%，招标人为重庆市巴南公路建设有限公司。 项目已具备招标条件，现对该工程的勘察设计进行公开招标，评标办法采用综合评估法。 网 2.项目概况与招标范围 2.1 建设地点：重庆市巴南区花溪街道、李家沱街道 务 2.2 项目概况与建设规模：为解决片区内涝问题，在李家沱街道、花溪街道改建 d400-d800 雨水管网 9665m，管材 采用高密度聚乙烯(HDPE)缠绕结构壁管 B型管；改建 d1商000-d1400雨水管网 664m，管材采用高密度聚乙 烯(HDPE)缠绕结构壁管 B 型管、III 级钢筋混凝土管；改建 d1500-d2000 雨水管网 426m，管材采用III 级钢筋混凝 土管;改建 d2100-d2600 雨水管网 1000m，管材采用 III 级钢筋混凝土管；修复雨水管网 5345m，增加智能感知设 备6 套。 道 2.3 本项目工程总投资金额：13477.10万元 管 本次招标项目工程费估算金额：11061.83万元 国 本次招标项目勘察设计合同估算金额：334.544万元 中 2.4 招标范围：主要包括勘察、施工图设计（包含高边坡、深基坑）和相应阶段的勘察工作，以及提供施工现场 全过程技术服务，并配合业主办理相关手续等，具体范围为： （1）勘察部分：完成本项目范围内的勘察工作，包括但不限于排水管网排查、1:500地形图测量、地质钻勘、管 线内窥、物探、综合管线测量，市政管网错混接点测量及调查等工作，解决区域地下空间臭气问题，勘察成果 需达到重庆市城市建成区排水管网排查技术导则的要求，并配合业主完成对应的成果审查等事宜。 （2）设计部分：包括不限于完成本项目的施工图设计、施工期间交通组织设计、桥梁（涉轨）安全论证方案及 施工期间至竣工验收阶段，质量保修阶段的设计配合服务，配合办理施工图审查相关手续及竣工验收阶段、质 量保修阶段的设计服务等工作以及协助招标人完成各项审批手续办理等工作。 2.5 勘察设计服务期限：30日历天 2.6 标段划分（如有）：/ 2.7 其他：/ 3.政府采购工程 3.投标人资格要求 3.1 本次招标要求投标人须具备以下条件： 网 3.1.1 本次招标要求投标人具备的资质条件： 务 投标人应同时具有建设行政主管部门颁发的下列勘察和设计两类资质： 商 I、投标人应具备下列勘察资质之一： 道 ①工程勘察综合甲级资质。 管 ②工程勘察专业类（岩土工程）专业甲级资质和工程勘察专业类（工程测量）甲级资质； 国 II、投标人应具备下列设计资质之一： 中 ①工程设计综合甲级资质； ②工程设计市政行业甲级资质； ③工程设计市政行业(燃气工程、轨道交通工程除外)甲级资质； ④工程设计市政行业(排水工程)甲级资质。 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的勘察设计能力，详见招标文件第二章投标人须知 前附表第1.4.1项内容。 3.2 本次招标接受联合体投标。联合体投标的，应满足下列要求：联合体组成单位数量不超过2家，由负责设计 任务的单位作为联合体牵头人。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件及其附件、澄 清、修改、补充通知、最高限价通知等资料。参与投标的投标人需在重庆市公共网资源交易网完成市场主体信息 登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息 登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程 电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 务 布至2026-08-23 12:00:00前。 4.3招标人应于2026-08-26 17:00:00前在重庆市公共资源交易网发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-24 09:30，投标人应当在投标截止时间前，通过互 商 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督道网、重庆市公共资源交易网、重庆市公共资源交易网（巴南区） 发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 重庆市巴南公路建设有限公司 代理机构: 重庆云远项目管理有限公司 管 地 址: 重庆市巴南区龙洲大道265号 地 址: 重庆市九龙坡区渝隆大厦28楼 邮 编: 邮 编: 项目负责人: 牟老师 项目负责人: 李强 国 电 话: 023-66238079 电 话: 023-68434996 传 真: 传 真: 电子邮箱: 电子邮箱: 中 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市巴南区发展和改革委员会 电 话: 023-66221670 2026年08月18日 重庆市巴南区土桥片区内涝积水整治工程勘察设计 户名 开户行 投标保证金账号 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000001675 贸易试验区分行 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051304894 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020041267 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764210157 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000682897 支行 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835000509 坝支行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146639123 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630018252 信息来源:https://www.chinapipe.net/project/d3074953.html cqdingjiu 2026.08.21 10:06:58 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="n">
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="n">
         <v>95</v>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标, 雨水管网, 高密度聚乙烯, 钢筋混凝土管</t>
         </is>
@@ -4849,34 +4579,29 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>涪陵作业区涪陵压气站空压机、阀门等设备、消防泵房消防管道、循环水管道油漆出现锈蚀情况，为保证设施安全运行，对站场设备、消防管道及附属钢结构进行打磨除锈、油漆防腐。</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>涪陵作业区涪陵压气站空压机、阀门等设备、消防泵房消防管道、循环水管道油漆出现锈蚀情况，为保证设施安全运行，对站场设备、消防管道及附属钢结构进行打磨除锈、油漆防腐。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>管道、设备防腐</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>管道、设备防腐</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
           <t>重庆管道公司2026年涪陵压气站管道、设备防腐项目-非招标公告 公告发布时间: 2026年08月18日09时02分19秒 一、概述 1.2.1项目概况：涪陵作业区涪陵压气站空压机、阀门等设备、消防泵房消防管道、循环水管道油漆出现锈蚀情况， 为保证设施安全运行，对站场设备、消防管道及附属钢结构进行打磨除锈、油漆防腐。 二、采购项目与标段 交货期限: 开工之日起90日内完工 网 质保期限(月): 标段 序号 标段名称 标段描述 编号 重庆管道公司2026年涪陵 涪陵作业区涪陵压气站空压务机、阀门等设备、消防泵房消防管道、循 1 1 压气站管道、设备防腐项 环水管道油漆出现锈蚀情况，为保证设施安全运行，对站场设备、消 目 防管道及附属钢结构进行打磨除锈、油漆防腐。 三、供应商资格要求 商 *1、响应人资质要求（1）响应人必须是依照中华人民共和国法律在国内注册，具备合格有效的营业执照的法人、 其他组织；与采购人存在利害关系可能影响询比采购公正性的法人、其他组织或者个人，不得参加响应。单位 负责人为同一人或者存在控股、管理关系的不同单位，不得参加同一标段响应或者未划分标段的同一询比项目 响应。（2）响应人须具备防水防腐保温工程专业承包二级及以上资质。*2、信誉要求响应人在响应文件提交截 止当日不存在以下情况：（1）响应人被“国道家企业信用信息公示系统”网站（www.gsxt.gov.cn）列入严重违法 失信企业名单（响应文件提交截止时间前已移出的除外）。（2）响应人被“信用中国”网站 （www.creditchina.gov.cn）列入严重失信主体名单（响应文件提交截止时间前已移出的除外）。（3）响应人或其 法定代表人、负责人、拟委任的项目经理被“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）列入失信 被执行人名单（响应文件提交截止时间前已移出的除外），响应文件中需提供有效身份证号供查询。（4）响应 管 人、拟委任的项目经理被“全国建筑市场监管公共服务平台”网站（https://jzsc.mohurd.gov.cn/home）列入黑名单 （响应文件提交截止时间前已移出的除外）。上述（1）-（4）条以评审当日评审小组从官网查询信息为准。（5） 被国家管网集团或西南管道公司暂停、取消投标资格或业务承揽资格。（6）法律、行政法规规定的其他不允许 参与投标的情况。 国 四、询比文件的获取 4.1 有意向参加项目者，于2026年08月20日09时05分22秒前，登录数字供应链平台进行项目报名。 中 4.2 报名成功后于2026年08月18日09时01分42秒至2026年08月24日09时05分22秒，登录数字供应链平台进行项目下 载询比文件。 五、响应文件的递交 5.1 请于2026年08月24日11时00分00秒前，登录数字供应链平台递交项目响应文件。 5.2 逾期将无法进行递交响应文件，采购人将不予受理。 5.3 供应商在递交响应文件前，应按照有关规定提供人民币0万元项目保证金。 六、响应文件的开启 6.1 响应文件的开启时间2026年08月24日11时06分00秒 6.1 响应文件的开启地点供应链系统上 七、采购人信息 地址： 邮编： 联系人：舒建华 联系电话：18581824001 电子邮件：shujh@pipechina.com.cn 传真： 开户银行： 账户名： 账号： 信息来源:https://www.chinapipe.net/project/d3074904.html cqdingjiu 2026.08.21 10:06:59 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="n">
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="n">
         <v>0</v>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>未识别到明确匹配关键词</t>
         </is>
@@ -4921,34 +4646,29 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>大渡口区</t>
+          <t>安装部分包括材料验收、运输及履带式挖掘机及人工布管、管道管件安装、新旧管道的碰口、安装DN400直埋球阀1座、管道和商焊口的除锈及防腐、管道下沟后15KV电火花检测、管道的清管、强度及严密性试验、警示带敷设和线路标志桩（砖）安装、监检手续等。土建部分包括清表、扫线、平整场地、沟槽、基坑、阀井砌筑、回填土方、余方弃置、人工开挖人行道（花台）、公路及路面恢复、其他线缆穿跨越工道程施工、交通组织、水工保护等。</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>安装部分包括材料验收、运输及履带式挖掘机及人工布管、管道管件安装、新旧管道的碰口、安装DN400直埋球阀1座、管道和商焊口的除锈及防腐、管道下沟后15KV电火花检测、管道的清管、强度及严密性试验、警示带敷设和线路标志桩（砖）安装、监检手续等。土建部分包括清表、扫线、平整场地、沟槽、基坑、阀井砌筑、回填土方、余方弃置、人工开挖人行道（花台）、公路及路面恢复、其他线缆穿跨越工道程施工、交通组织、水工保护等。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>燃气管线工程</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>燃气管线工程</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
           <t>重庆燃气集团股份有限公司输配分公司大渡口调压站至二郎调压站次高压燃气管线工程(大渡口段)公告 采购 公告 公告编号： RQXYGG202608130064 一、采购项目基本情况 网 采购人：重庆燃气集团股份有限公司输配分公司 采购项目编号：RQCGXY202608130040 务 采购项目名称：大渡口调压站至二郎调压站次高压燃气管线工程（大渡口段） 采购内容或范围：安装部分： ①材料验收（甲供材料：阀门、管材、弯头、标志桩等）、运输及履带式挖掘机及人工布管； ②管道管件安装， 新旧管道的碰口；③安装DN400直埋球阀1座； ④管道和商焊口的除锈及防腐； ⑤管道下沟后15KV电火花检测； ⑥管道的清管，强度及严密性试验；⑦警示带敷设和线路标志桩（砖）安装； ⑧监检手续等。 土建部分： ①清表； ②扫线、平整场地； ③沟槽、基坑、阀井砌筑； ④回填土方； ⑤余方弃置； ⑥人工开挖人行道（花 台），公路及路面恢复； ⑦其他线缆穿跨越工道程施工，交通组织； ⑧水工保护等。 （具体内容详见施工图纸和 工程量清单） 公告发布时间 ：2026-08-18 14:39:10 管 二、采购人联系方式 联系人：王瑶 电话：023-67502265 国 邮箱：wangyao232@crcgas.com 三、采购明细 中 行号 采购内容 需求数量 单位 补充说明 拟邀请单位 大渡口调压站至二郎调压站次高压燃气管线 重庆燃气安装工程有限责任公 1 1 项目 无 工程(大渡口段) 司 四、服务费交纳 本项目不收取服务费。 五、 其他 事项 1.本公告在华润守正 采购交易 平 台（ https://www.szecp.com.cn/ ）上公开 发布。 2. 本项目采购通过守正平台线上进行，供应商需注册华润守正 采购交易 平台，通过平台进行响应文件的递交或 报价，具体操作步骤可查阅网站首页帮助中心的操作手册，也可以联系守正客服。 3 .答疑澄清、通知等文件一经在华润守正 采购交易 平台发布，视为已发放给相应供应商（发放时间即为发出时 间），请随时关注华润守正 采购交易 平台发布的相关信息，并及时查阅和处理。 4 .若有参与意向 ， 请于 2026-08-22 00:00:00前联系采购人 （联系方式见公示内容）反馈。 5 .若有异议 ， 请于 2026-08-22 00:00:00前提出异议 。 信息来源:https://www.chinapipe.net/project/d3074793.html cqdingjiu 2026.08.21 10:06:59 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="n">
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="n">
         <v>80</v>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -4993,34 +4713,29 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>石柱土家族自治县</t>
+          <t>2026-2027年度用户供水管道安装及管网抢（维）修服务</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-2027年度用户供水管道安装及管网抢（维）修服务</t>
+          <t>项目资金来自企业自筹，合同估算金额约280万元</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>项目资金来自企业自筹，合同估算金额约280万元</t>
+          <t>供水管道安装及管网抢（维）修服务</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>供水管道安装及管网抢（维）修服务</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
           <t>石柱公司2026-2027年度用户供水管道安装及管网抢(维)修工程(第二次)项目公告 石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程（第二次）（比选公告 1.比选条件 本比选项目石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程（第二次）（项目名称），比选人 为重庆石柱水利水电实业开发有限公司，比选项目资金来自企业自筹（资金来源），项目已具备比选条件。现 对本项目进行公开比选，诚邀有兴趣的潜在投标人参与投标。 网 2.项目概况与比选范围 2.1 建设地点：比选人指定地点 务 2.2 项目概况与建设规模：2026-2027年度用户供水管道安装及管网抢（维）修服务 2.3 本次比选项目合同估算金额：约280万元 商 2.4 比选范围：完成石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程包括公司供水范围内用户 各类管道及管件安装、水表安装及更换、阀门安装等、并完成配套土建工程、零星签证等工程量清单所列项目、 管网抢维修和公司所属生产单元零星项目，具体内容详见第五章 工程量清单。 道 2.5 工期要求：1年 缺陷责任期要求：24个月 管 3.投标人资格要求 3.1 本次比选要求投标人须具备以下条件： 国 3.1.1 本次比选要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰级 及以上资质； 3.1.2 投标人还应在人员、设备、资金等方面具有相应的施工能力，详见比选文件第二章投标人须知前附表第1.4.1 中 项内容。 3.2 本次比选不接受联合体投标。 4.比选文件的获取 4.1 投标人于2026年08月18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子版， 以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都视为 投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的一切 后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价，递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，被视为无效。 4.4比选文件每份售价1000 元，售后不退。投标人在递交纸质投标文件时支付，否则比选人拒绝接收其投标文 件。 5.投标文件的递交 5.1电子投标文件递交时间：2026年08月24日10时00分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年08月24日09时30分至10时00分，地点：水务集团招标采购中心（重庆市两江新 区嘉华路36号重庆水务大厦五楼）。 5.3 投标截止时间：2026年08月24日10时00分（北京时间）。 网 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 务 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 商 比 选 人：重庆石柱水利水电实业开发有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市石柱土家族自治县都督大道11号 地 址：重庆市两江新区嘉华路36号重庆水务大厦1018 联 系 人：王老师 联 系 人：颜老师 道 电 话：13658292968 电 话：023-67901915 重庆水务电子商务平台咨询电话：管023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3074720.html cqdingjiu 2026.08.21 10:06:59 国 中</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="n">
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="n">
         <v>90</v>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>重庆, 供水管道安装, 管网抢修, 企业自筹, 280万元</t>
         </is>
@@ -5059,32 +4774,31 @@
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>万盛城区老旧供水管网更新改造工程涉及3PE防腐钢管的采购，其管道部分壁厚需符合国标标准并达到设计要求。</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>万盛城区老旧供水管网更新改造工程涉及3PE防腐钢管的采购，其管道部分壁厚需符合国标标准并达到设计要求。</t>
+          <t>项目详情中未提及具体资金情况。</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>项目详情中未提及具体资金情况。</t>
+          <t>3PE防腐钢管</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>3PE防腐钢管</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
           <t>万盛城区老旧供水管网更新改造工程(甲供材料)答疑(一) 万盛城区老旧供水管网更新改造工程（甲供材料） 答疑（一） 各潜在投标人： 现将万盛城区老旧供水管网更新改造工程（甲供材料）答疑（一）相关条款通知如下： 网 一、答疑 问题1：请问招标人是否委派业主专家参与评标吗？ 务 答：是，本项目评标委员会共7人，其中在重庆市综合评标专家库随机抽取5人，招标人代表2人。 问题2：万盛的项目挂綦江来投这样都还控制不了还全是你们万盛公司中的？是有啥猫腻是吧？参考之前的项目 全是万盛的公司中的！业主、专家全是你们自己人吧？ 商 答：本项目招标文件严格按照《重庆市工程建设项目货物采购招标文件示范文本（2026年版）》编制，且本项目 评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 问题3：3PE管道部分壁厚是多少呢？ 道 答：本项目采购的3PE防腐钢管的管道部分壁厚须符合国标标准并达到设计要求。 招 标 人：重庆市万盛经济技术开发区城市管理局 管 招标代理机构：重庆力圣建设工程咨询有限公司 2026年8月18日 国 信息来源:https://www.chinapipe.net/project/d3074712.html cqdingjiu 2026.08.21 10:06:59 中</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="n">
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="n">
         <v>80</v>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 3PE防腐钢管, 资金情况, 产品种类</t>
         </is>
@@ -5123,32 +4837,31 @@
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>本项目涉及普通防腐钢管及管件的采购，包括各种规格的钢高频焊管和钢螺旋焊管，以及相应的管件如钢套筒、钢制标准接头等。</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>本项目涉及普通防腐钢管及管件的采购，包括各种规格的钢高频焊管和钢螺旋焊管，以及相应的管件如钢套筒、钢制标准接头等。</t>
+          <t>项目资金来自企业自筹，出资比例为100%。</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>项目资金来自企业自筹，出资比例为100%。</t>
+          <t>钢高频焊管,钢螺旋焊管,钢套筒,钢制标准接头,钢制渐缩,钢制三通,钢制双盘短管,钢制弯头</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>钢高频焊管,钢螺旋焊管,钢套筒,钢制标准接头,钢制渐缩,钢制三通,钢制双盘短管,钢制弯头</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
           <t>重庆中法供水2026年普通防腐钢管及管件采购项目(第三次)项目公告 重庆中法供水2026年普通防腐钢管及管件采购项目（第三次）比选公告 1.比选条件 本比选项目重庆中法供水2026年普通防腐钢管及管件采购项目（第三次），比选人为重庆中法供水有限公司，比 选项目资金来自企业自筹，出资比例为100%，项目已具备比选条件。现对本项目进行公开比选，诚邀有兴趣的 潜在投标人参与投标。 网 2.项目概况与比选范围 2.1 普通防腐钢管及管件采购清单： 务 序号 存货编码 材料名称 规格型号 单位 数量 最高单价限价（元） 1 10400177 钢高频焊管 D89*4 5 米 61.92 2 10400181 钢高频焊管 D108*5 300 米 88.89 商 3 10400182 钢高频焊管 D159*5 5 米 132.18 4 10400206 钢高频焊管 D159*6 5 米 152.13 5 10400290 钢螺旋焊管 DN219*6 5 米 196.68 道 6 10400291 钢螺旋焊管 DN219*8 5 米 244.80 7 10400292 钢螺旋焊管 DN325*8 5 米 361.28 8 10400293 钢螺旋焊管 DN377*8 5 米 423.12 管 9 10400294 钢螺旋焊管 DN426*8 5 米 475.89 10 10400295 钢螺旋焊管 DN426*10 5 米 574.29 11 10400297 钢螺旋焊管 DN529*8 5 米 595.76 国 12 10400298 钢螺旋焊管 DN529*10 5 米 718.91 13 10400299 钢螺旋焊管 DN630*10 5 米 861.50 14 10400300 钢螺旋焊管 DN720*10 5 米 987.95 中 15 10400301 钢螺旋焊管 DN820*10 5 米 1133.08 16 10400302 钢螺旋焊管 DN920*10 5 米 1279.51 17 10400304 钢螺旋焊管 DN1020*10 5 米 1424.64 18 10400305 钢螺旋焊管 DN1020*12 5 米 1652.24 19 10400306 钢螺旋焊管 DN1220*10 5 米 1709.70 20 10400307 钢螺旋焊管 DN1220*12 5 米 1982.83 21 10400308 钢螺旋焊管 DN1420*12 5 米 2375.96 22 10400309 钢螺旋焊管 DN1420*14 5 米 2697.83 23 10400332 钢螺旋焊管 DN1120*10 5 米 1574.96 24 10400342 钢螺旋焊管 DN1020*14 5 米 1879.02 25 10400322 钢螺旋焊管（特加强） DN820*10 5 米 1133.08 26 10200490 钢套筒 D159*500cm 5 个 159.00 27 10200491 钢套筒 D219*500cm 5 个 240.00 28 10200492 钢套筒 D273*500cm 5 个 300.00 29 10200493 钢套筒 D325*500cm 5 个 361.00 30 10200494 钢套筒 D377*500cm 5 个 436.00 31 10200495 钢套筒 D426*500cm 5 个 482.00 32 10200589 钢套筒 D159*1000cm 5 个 226.00 33 10200590 钢套筒 D219*1000cm 5 个 1627.00 34 10200591 钢套筒 D273*1000cm 5 个 2501.00 35 10200592 钢套筒 D325*1000cm 5 个 488.00 36 10200593 钢套筒 D377*1000cm 5 个 591.00 网 37 10200598 钢套筒 D426*1000cm 5 个 833.00 38 10200155 钢制标准接头 D108 5 个 91.00 39 10200156 钢制标准接头 D159 5 个 160.06 务 40 10200157 钢制标准接头 D219 5 个 319.41 41 10200158 钢制标准接头 D273 5 个 396.63 42 10200159 钢制标准接头 D325 5 个 475.96 商 43 10200160 钢制标准接头 D426 5 个 619.87 44 10200161 钢制标准接头 D529 5 个 779.22 45 10200162 钢制标准接头 D630 5 个 1068.44 道 46 10200163 钢制标准接头 D720 5 个 1214.46 47 10200164 钢制标准接头 D820 5 个 1428.34 48 10200165 钢制标准接头 D920 5 个 1600.14 管 49 10200169 钢制标准接头 D1220 5 个 2297.57 50 10200170 钢制标准接头 D1420 5 个 3027.02 51 10200171 钢制标准接头 D1020 5 个 2194.19 国 52 10300309 钢制大小头 DN65*DN50 5 个 14.74 53 10200667 钢制渐缩 D108＞57 3 个 21.06 54 10200668 钢制渐缩 D108＞89 3 个 26.00 中 55 10200695 钢制渐缩 D159＞108 3 个 40.72 56 10200671 钢制渐缩 D219＞159 3 个 68.09 57 10200672 钢制渐缩 D219＞108 3 个 80.03 58 10201605 钢制渐缩 219*125 3 个 75.82 59 10200694 钢制渐缩 D273＞108 3 个 129.87 60 10200673 钢制渐缩 D273＞159 3 个 94.07 61 10200674 钢制渐缩 D273＞219 3 个 84.94 62 10200675 钢制渐缩 D325＞108 3 个 184.63 63 10200676 钢制渐缩 D325＞159 3 个 143.91 64 10200680 钢制渐缩 D325＞219 3 个 131.98 65 10200677 钢制渐缩 D325＞273 3 个 124.25 66 10200684 钢制渐缩 D426＞325 3 个 285.01 67 10200685 钢制渐缩 D529＞325 3 个 617.76 68 10200679 钢制渐缩 D529＞426 3 个 547.56 69 10200659 钢制渐缩 D630＞325 3 个 756.00 70 10200687 钢制渐缩 D630＞426 3 个 728.00 71 10201539 钢制渐缩 D630＞529 3 个 722.00 72 10200690 钢制渐缩 D720＞630 3 个 848.00 73 10200691 钢制渐缩 D720＞529 3 个 842.00 74 10200682 钢制渐缩 D820＞720 3 个 913.00 75 10200692 钢制渐缩 D920＞720 3 个 1053.00 76 10201519 钢制渐缩 D920*820 3 个 1064.00 77 10200652 钢制渐缩 D1020＞820 3 个 1305.00 网 78 10200693 钢制渐缩 D1020＞920 3 个 1322.00 79 10201738 钢制渐缩 1220*820 3 个 1806.00 80 10201507 钢制渐缩 1220＞1020 3 个 1834.00 务 81 10201624 钢制三盘三通 D108⊥108 3 个 224.64 82 10200371 钢制三盘三通 DN200⊥100 3 个 435.24 83 10200373 钢制三盘三通 DN200⊥200 3 个 599.51 商 84 10201531 钢制三通 108*108 3 个 58.97 85 10200285 钢制三通 219*108 3 个 187.43 86 10201341 钢制双盘短管 89*400mm 3 个 139.00 道 87 10201342 钢制双盘短管 89*800mm 3 个 178.31 88 10201340 钢制双盘短管 108*300mm 3 个 158.65 89 10201299 钢制双盘短管 DN108*500mm 3 个 185.33 管 90 10201300 钢制双盘短管 DN108*1000mm 3 个 258.34 91 10201301 钢制双盘短管 DN108*1500mm 3 个 329.94 92 10201332 钢制双盘短管 159*300mm 3 个 251.32 国 93 10201339 钢制双盘短管 159*750mm 3 个 348.19 94 10201303 钢制双盘短管 DN159*1000mm 3 个 402.95 95 10201304 钢制双盘短管 DN159*1500mm 3 个 508.25 中 96 10201305 钢制双盘短管 DN219*500mm 3 个 463.32 97 10201306 钢制双盘短管 DN219*1000mm 3 个 672.52 98 10201307 钢制双盘短管 DN219*1500mm 3 个 876.00 99 10201312 钢制双盘短管 DN219*750mm 3 个 581.26 100 10201338 钢制双盘短管 273*1250mm 3 个 1010.88 101 10201458 钢制双盘渐缩 108*57 3 个 109.51 102 10201469 钢制双盘渐缩 108*89 3 个 117.94 103 10201514 钢制双盘渐缩 159*108 3 个 185.33 104 10201748 钢制双盘渐缩 200*80 3 个 294.84 105 10201462 钢制双盘渐缩 219*108 3 个 256.93 106 10201513 钢制双盘渐缩 219*159 3 个 280.80 107 10201465 钢制双盘渐缩 D273＞108 3 个 339.77 108 10201467 钢制双盘渐缩 D273＞219 3 个 388.91 109 10201770 钢制双盘渐缩 D273＞159 3 个 365.04 110 10201461 钢制双盘渐缩 325*219 3 个 477.36 111 10301108 钢制弯头 89*90° 3 个 28.78 112 10200702 钢制弯头 D108×90° 100 个 43.52 113 10200701 钢制弯头 D159×90° 3 个 84.24 114 10200705 钢制弯头 D219*90° 3 个 231.66 115 10200706 钢制弯头 D273*90° 3 个 300.46 116 10200709 钢制弯头 D325*90° 3 个 418.39 117 10200711 钢制弯头 D426*90° 3 个 744.12 118 10200712 钢制弯头 D529*90° 3 个 1352.05 网 119 10200764 钢制弯头 D570*90° 3 个 1474.20 120 10200714 钢制弯头 D630*90° 3 个 1535.98 121 10200715 钢制弯头 D720*90° 3 个 1742.36 务 122 10200717 钢制弯头 DN720*90°*12mm 3 个 1989.47 123 10200720 钢制弯头 D920*90° 3 个 2935.30 124 10200722 钢制弯头 D820*90° 3 个 2325.23 商 125 10200762 钢制弯头 D1020*90° 3 个 4829.55 126 10200723 钢制弯头 D1220*90° 3 个 6039.80 127 10200724 钢制弯头 D1420*90° 3 个 8297.00 道 注：管材按照米数进行报价，管件按照件数进行报价。 2.2 供货数量、时间和批次：根据工程实际进度与比选人的要求进行供货，以实际供货量为准，供货时间达到商 务条款的规定。 管 2.3 交货地点：比选人指定的施工现场。 2.4 供货期：两年。 国 3.投标人资格要求 3.1 本次比选允许投标人以投标货物的下列身份参加投标： 中 ?制造商 3.1.1 投标人为制造商应符合以下要求： 投标人必须是依法设立的，并在中国注册的，具有独立法人地位的企业。 【提供有效的营业执照】 3.2 投标人2025年的年度财务状况不亏损。 【提供由会计师事务所或审计机构出具的无保留意见的财务审计报告及会计报表，财务报表至少包括现金流量 表、资产负债表、利润表】 3.3 投标产品的制造商须通过质量ISO9001、环境ISO14001、职业健康体系ISO45001认证。 【提供有效的证书】 3.4 投标人须提供2023年1月1日至投标截止日止（以合同签订时间为准）,签订的30万元及以上的钢管及管件产品 购销合同至少1个。 【提供采购合同、不低于前述金额50％的发票，合同与发票的项目名称须一致】 注：①若投标人开具的发票上未能体现具体项目，需附上税务出具的发票清单（清单上需显示采购项目为钢管 及管件产品）。 ②若提供的合同为年度合同未体现具体金额，但实际供货金额达到30万元及以上，应提供与该合同对应的30万元 及以上的钢管及管件产品发票作为佐证。 3.5 投标人须为所投投标产品制造商，此次所提供的普通防腐钢管及管件必须是自己工厂所制造的产品，不得外 购他人产品。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函及工商部门出具的本产品商标或品牌证明文件】 3.6 投标产品过水部分涉及的涂料须提供行政主管部门出具的有效的“卫生许可网批件”及卫生疾控中心出具的卫 生检测报告。 【提供行政主管部门出具的有效的“卫生许可批件”及卫生疾控中心出具的卫生检测报告】 务 3.5 根据本次采购清单及技术规范的要求，投标人须承诺具备相关的技术手段和措施、保证产品设计使用寿命 20 年以上。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 商 3.6 投标人须承诺保证5年内不得停产同型号的投标产品。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 道 3.7 办事机构和库房【比选人有权对中标人的办事机构及库房进行实地核查，若发现与提供资料不符，将视为提 供虚假资料，按相关规定取消其中标资格，其投标保证金不予退还。】 投标人承诺：收到中标通知书后30日内提供租赁合同或产权证明，并提供重庆库房卫星定位图片。 管 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 【卫星定位图片：手机打开地图，搜索该地址、进行标注，然后截图或者电脑打开地图（地图软件不限），搜 索该地址、选择卫星模国式、进行标注、然后截图均可。】 3.8 符合第五章“技术要求”普通防腐钢管及管件技术要求。 【根据技术要求提供技术响应表，并根据技术条款要求提供对应的检测报告等。】 中 3.9 售后服务承诺【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】： 1）货物交付及付款方式要求，满足第四部分合同协议书第3条及第10条；供货单位应确保产品的及时供应，承诺 因产品供应不及时造成的一切损失均由供货单位负责赔偿。 2）有完整的售后服务方案、培训计划并在合同签订后为比选人免费提供培训服务。 3）售后服务承诺书，满足第四部分合同协议书第11条；承诺质保期后提供2年及以上定期免费巡查、保养计划。 4）承诺接到分派的工单1小时内联系用户约定维修时间，在24小时内处理完毕工单，且让用户满意。若工单超时、 未在规定时间内告知比选人维修时间或工单处理未让用户满意造成返单的，按比选人制度进行处罚。 3.10 投标人承诺不得存在下列情形之一： 1）被人民法院列入失信被执行人名单且在被执行期内； 2）被国家、重庆市（含市或任意区县）有关行政部门行政处罚，且在处罚期限内； 3）投标截止日前两年内（指2024年1月1日至投标截止日止），投标人或其法定代表人被人民法院判定犯行贿罪 的； 4）投标截止日前五年内（指2021年1月1日至投标截止日止），投标人与重庆中法供水有限公司有违约情况或终 止合同情况的。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 3.11 投标截止日前五年内（指2021年1月1日至投标截止日止），投标人无在我司因产品及服务等对公司生产、经 营、安全造成不良影响的记录；若投标人出现过供水通报事项，因产品质量问题对生产、安全造成影响，存在 合同违约等问题，不予参加本次项目投标。 【按照第六章 三、资格审查部分“无不良记录承诺函”提供承诺函，若经验证承诺函不属实，将对中标人作否 决投标处理。】 网 3.12 投标样品要求： 3.12.1 投标人需提供以下规格型号数量的样品： 务 【①钢螺旋焊管 DN219*8 壹件 ②钢制弯头 D108*90°壹件】，提供的样品应满足第五章技术要求规定。样品为 投标人免费提供，管材样品不低于20CM，不计入采购清单内。 3.12.2 投标样品同投标文件一并递交。每件样品上分别标明样品的投标人、生产厂家、品牌、名称、规格、型号等 （格式自拟），投标样品必须密封装箱，且在密封包装外商贴样品一览表（格式自拟），注明提供样品的投标人、 生产厂家、品牌、名称、规格、型号、数量等。 3.12.3 投标人的样品在开标当日递交至样品区（样品区地点：开标当日咨询比选代理机构），中标人的投标样品 不退还，其余投标人的样品在中标公示期满后道5个工作日内退还，如不领取，投标样品按废品处理。 3.12.4 上述对投标样品的密封和标识要求是为便于评标，请投标人积极配合，未按上述要求对投标样品进行密封 和标识的，不作否决投标处理，但由此造成的其他后果由投标人自行承担。 管 3.13 若投标人违反重庆中法供水有限公司《供应商负面清单管理办法》规定且在处罚期内的，按否决投标处理 （评标委员会根据比选公告后附“供应商负面清单”进行评审）。 3.14 本次比选不接受联合体投标。 国 特别说明： （1） 本比选文件要求提供的所有检测报告须为近2年内的检测报告（2024年1月1日-投标截止日），此要求不包 括卫生许可批件及其检测报告。 中 （2） 上述所须提交的相关证明材料复印件均应加盖投标单位法人章并装入投标文件资格审查部分中。上述有一 条不满足则投标文件由评标委员会作否决投标处理。 （3） 比选人有权对投标人提供的以上资料进行核实，若发现存在弄虚作假，取消其投标、中标资格，投标人承 担因此造成的相关责任并赔偿相应损失。 4.比选文件的获取 4.1 投标人于2026年8月18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子版， 以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都视为 投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的一切 后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价，递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，被视为无效。 4.4比选文件每份售价 500 元，售后不退。投标人在递交纸质投标文件时扫描支付，否则比选人拒绝接收其投标文 件。 5.投标文件的递交 5.1电子投标文件递交时间：2026年8月26日14时30分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年8月26日14时00分至14时30分，地点：水务集团招标采购中心（重庆市两江新 区嘉华路36号重庆水务大厦五楼。导航：重庆水务大厦东门）。 5.3 投标截止时间：2026年8月26日14时30分（北京时间）。 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 网 6.发布公告的媒介 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 务 7.联系方式 比 选 人：重庆中法供水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝北区悦来镇悦来水厂 地 址：重庆市两商江新区嘉华路36号重庆水务大厦10楼1018 联 系 人：陈老师 联 系 人：周洲 电 话：023-67585971 电 话：18602396399 道 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3074673.html 管 cqdingjiu 2026.08.21 10:06:59 国 中</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="n">
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="n">
         <v>0</v>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>未识别到明确匹配关键词</t>
         </is>
@@ -5193,34 +4906,29 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>南岸区</t>
+          <t>本项目比选范围修改为：在项目动工前完成水土保持方案审批程序，项目建设过程开展水土保持监管测工作。</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>本项目比选范围修改为：在项目动工前完成水土保持方案审批程序，项目建设过程开展水土保持监管测工作。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>供水管网</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>供水管网</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
           <t>南岸区茶园片区乡镇老旧供水管网更新改造工程更正公告 南岸区茶园片区乡镇老旧供水管网更新改造工程更正公 告 发布日期： 2026年8月18日 网 首次公示日期： 2026年8月14日 更正日期： 2026年8月18日 采购人名称： 重庆市江南城市建设发展（集团）有限公司务 采购人地址： 重庆市南岸区米兰路51号电子信息标准化厂房2号楼 联系人： 赵老师 商 电话： 023-62820331 采购代理机构名称： 重庆多杰数字科技咨询服务有限公司 采购代理机构地址： 重庆市重庆市经开区重庆市经开区长生桥镇江峡路8号13-1幢1楼 道 经办人名称： 李佩奇、戴沛轩、李倩 联系电话： 023-67648437 本项目比选范围修改为：在项目动工前完成水土保持方案审批程序，项目建设过程开展 更正事项： 水土保持监管测工作。 https://www.gec123.com/notices/detail/1665701682723590144 信息来源:https://www.c国hinapipe.net/project/d3074669.html cqdingjiu 2026.08.21 10:07:01 中</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="n">
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="n">
         <v>80</v>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>重庆, 管材招标, 商机</t>
         </is>
@@ -5259,32 +4967,31 @@
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>中铁十一局集团宜涪高铁3标项目，位于重庆市石柱土家族自治县。合同金额28.01亿元，合同工期73个月，主要工程包括新方斗山隧道、石板坡隧道、城北隧道、刘家坪隧道、刘家店子1号大桥工程、刘家店子2号大桥、城北大桥、冉家湾大桥，采用移动模架和支商架法现浇施工，正线铺无砟道床43.808Km。</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>中铁十一局集团宜涪高铁3标项目，位于重庆市石柱土家族自治县。合同金额28.01亿元，合同工期73个月，主要工程包括新方斗山隧道、石板坡隧道、城北隧道、刘家坪隧道、刘家店子1号大桥工程、刘家店子2号大桥、城北大桥、冉家湾大桥，采用移动模架和支商架法现浇施工，正线铺无砟道床43.808Km。</t>
+          <t>合同金额28.01亿元</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>合同金额28.01亿元</t>
+          <t>排水钢管Φ200*6m</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>排水钢管Φ200*6m</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
           <t>中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部排水钢管询价采购公告 中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 排水钢管询价采购公告 询价编号：ZT1105-XJ-2026-561-1 尊敬的各潜在供应商: 网 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与中铁十一局集团有限公司宜涪高铁重庆段站 前3标项目经理ZT1105-XJ-2026-561-1，排水钢管材料的报价。 一、项目概况 务 中铁十一局集团宜涪高铁3标项目，位于重庆市石柱土家族自治（县）。合同金额28.01亿元，合同工期73个月， 开工日期：2024年12月，竣工日期：2030年12月。主要工程：新方斗山隧道(10660m)、石板坡隧道(4148m)、城北 隧道(3228m)、刘家坪隧道(2077m);刘家店子1号大桥工程(224.096m)、刘家店子2号大桥(232.099m)、城北大 桥(330.241m)、冉家湾大桥(355.245m),采用移动模架和支商架法现浇施工，其中24米移动模架施工6孔；32米支架法 施工5孔，移动模架施工28孔;正线铺无砟道床43.808Km。 二、询价内容 道 本次计划对排水钢管、GG-01材料进行询价，询价内容如下： 询价物资一览表 管 序号 包件号 物资名称 规格型号 计量单位 数量 备注 1 GG-01 排水钢管 Φ200*6m 米 3000 Q235B，壁厚6mm 合计 3000 国 说明：1.表中数量为计划数量，实际采购过程中可能有所调整，最终结算按照实际采购数量结算。 2.收货地点：中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 中 三、技术质量及报价要求 1. 此次排水钢管、GG-01各项技术性能：Q235B 碳素结构钢无缝钢管，符合 GB/T8163 标准。质量需满足甲方项 目部正常使用的要求，保证产品的质量合格，满足试验室检测所有要求，详见技术规格书。 2.报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、结算及付款方式 自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发票认证完成之日起第6个月，支付至本次结算 金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内，累计支付总额不超结算总金额的75%，剩 余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理末次结算后第二年，支付金额应大于等于 尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总额的15%；办理末次结算后第四年，全部 付清）。 五、报价人资格要求 1.营业范围要求：在中华人民共和国境内依法注册、符合项目经营范围，具有询价物资生产或供应经验 的生产商或代理商，并且具有合法有效的营业执照。 2.生产能力要求：生产商须具备询价物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定。代 理商需出具制造厂出具签字盖章的授权函。 3.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8 月至今）国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；需满足排水钢管的相关所 有要求。 4.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年12月至今）企业或企业法定代表人有人民法院生效判决、裁 定认定的行贿犯罪记录的。④ 对纳入国家铁路局“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接 受通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合 作方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 网 5.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 务 ★6.下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 六、报价人需要提供的资料 1.营业执照复印件、法人身份证复印件、开户许可证、授商权委托书、报价表和报价人资格要求中所需的证明资料， 所有资料需加盖公司鲜章。 2.生产厂家资质，产品质量检测报告等质量证明文件。 道 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、询价报名截止时间 管 有意参加本次询价采购的报价人须在铁建云链平台（https://www.crccep.cn）完成供应商注册，并于2026年8月18 日9时00分至2026年8月21日9时00分在网上完成报名工作。 八、询价截止时间 国 凡有意参加本次询价采购的报价人，请于 2026年8月21日14时00分 前提交报价。截止时间前未完成报价文件传 输的，视为放弃报价。 供应商报价必须严格按照《报价表》格式进行报价。 中 九、联系方式 采购组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村71号 采购人名称：中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 地址：重庆市石柱土家族自治县金彰工业园区C区中铁十一局项目部 联系人：罗先生 联系电话：18580400001（提供采购服务支持） 中铁十一局集团有限公司 物资设备集中采购管理中心第五分中心 2026年8月18日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3074654.html cqdingjiu 2026.08.21 10:07:01 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="n">
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="n">
         <v>90</v>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>重庆, 排水钢管, 询价采购</t>
         </is>
@@ -5323,32 +5030,31 @@
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>重庆协同创新区供冷供热能源站及配套系统工程冷却塔、分集水器、水板式热交换机组采购。</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>重庆协同创新区供冷供热能源站及配套系统工程冷却塔、分集水器、水板式热交换机组采购。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>冷却塔、分集水器、水板式热交换机组</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>冷却塔、分集水器、水板式热交换机组</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
           <t>中铁建设集团(重庆)建设有限公司重庆协同创新区供冷供热能源站及配套系统工程冷却塔、分集水器、水板式热 交换机组采购竞价补遗公告二 各 投标单位 ： 根据参加报名的潜在投标单位数量不满足招标方充分竞价要求的情况，此次重庆协同创新区供冷供热能源站及 配套系统工程冷却塔、分集水器、水板式热交换机组采购竞价资格预审报名截止日期将延期至 8月19日（周三） 上午9:00。 特此说明。 网 中铁建设集团（重庆）建设有限公司 2026年8月17日 务 信息来源:https://www.chinapipe.net/project/d3074650.html cqdingjiu 2026.08.21 10:07:01 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="n">
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="n">
         <v>80</v>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>重庆协同创新区, 供冷供热能源站, 冷却塔, 分集水器, 水板式热交换机组, 采购竞价</t>
         </is>
@@ -5393,34 +5099,29 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>城口县</t>
+          <t>在城口县东安镇新建一座污水处理站，铺设不同直径的污水管道共计29.3公里，包括dn110、dn160、dn200、DN300、DN400等规格的污水管道，以及DN200压力管道7.4公里，建设配套泵站2座和化粪池56座、隔油池32座。</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>在城口县东安镇新建一座污水处理站，铺设不同直径的污水管道共计29.3公里，包括dn110、dn160、dn200、DN300、DN400等规格的污水管道，以及DN200压力管道7.4公里，建设配套泵站2座和化粪池56座、隔油池32座。</t>
+          <t>合同预估金额为3400万元人民币。</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>合同预估金额为3400万元人民币。</t>
+          <t>污水管网、泵站、化粪池、隔油池</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>污水管网、泵站、化粪池、隔油池</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
           <t>城口县东安及河鱼片区污水管网建设项目(一期)招标计划表 重庆市工程建设项目招标计划表 项 名 目 称城口县东安及河鱼片区污水管网建设项目（一期） 招标 法人 或招 标人城口县生态环境局 名称 （盖 网 章） 项目 批准 文件 及文 号 主 建 内 要 设 容 在 污 城 水 口 处 县 理 东 站 安 1座 镇 ， 等 改 片 建 区 后 新 设 建 计 污 规 水 模 管 20 网 0m 29 3 . / 0 d 0 。 km，其中新建dn110污水管5.80km，dn160污水管2.75km，dn200污水管0.57km，DN300污水干管4.36km，D 务 N400污水干管8.12km，DN200压力管7.4km,以及建设配套泵站2座,化粪池56座，隔油池32座。改扩建 序号 招标项目名称 招标内容 招标方式 招标文件计划发布时间 拟交易场所 合同预估金额(万元) 备注 招 项 标 目1 城 建 口 设 县 项 东 目 安 （ 及 一 河 期 鱼 ） 片区污水管网 工程施工 公开招标 2026-09 城 易 口 中 县 心 公共资源交 3400.00 本 暂 为 计 定 准 划 ， 。 表 最 所 终 列 以 招 实 标 际 项 招 目 标 信 时 息 的 均 信 为 息 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3074602.html 商 cqdingjiu 2026.08.21 10:07:01 道 管 国 中</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="n">
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="n">
         <v>90</v>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>重庆, 管材, 招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
@@ -5459,32 +5160,31 @@
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>场平面积800亩；新建厂房10000平方米，并完善相关基础配套设施等；新建道路长4000米，包括道路、综合管网等基础配套设施等。</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>场平面积800亩；新建厂房10000平方米，并完善相关基础配套设施等；新建道路长4000米，包括道路、综合管网等基础配套设施等。</t>
+          <t>本项目工程总投资金额：55000万元 本次招标项目合同估算金额：184.669075万元</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>本项目工程总投资金额：55000万元 本次招标项目合同估算金额：184.669075万元</t>
+          <t>土石方开挖回填、砼支墩、污水管道安装、检查井砌筑、河堤修复等</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>土石方开挖回填、砼支墩、污水管道安装、检查井砌筑、河堤修复等</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
           <t>阀门产业园(管网改造)项目招标公告 阀门产业园（管网改造）项目招标公告 1.招标条件 本招标项目 阀门产业园（管网改造）项目已由垫江县发展和改革委员会以垫江发改委发【2022】459 号（批文 名称及编号）批准建设，项目业主为 垫江县丹香建设有限公司，建设资金来自 自筹资金 （资金来源）， 项目出资比例为 100% ，招标人为 垫江县丹香建设有限公司。项目已具备招标条件，现对该项目的施工进 行公开招标，评标办法采用经评审的最低投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 重庆市垫江县高新区县城组团 2.2 项目概况与建设规模： 场平面积800亩；新建厂房10000平方米，并完善相关基础配套设施等；新建道路 务 长4000米，包括道路、综合管网等基础配套设施等。 2.3 本项目工程总投资金额：55000万元 本次招标项目合同估算金额：184.669075万元 商 2.4 招标范围： 包括土石方开挖回填、砼支墩、污水管道安装、检查井砌筑、河堤修复等。具体详见施工图和 工程量清单。 道 2.5 工期要求：建设工期180日历天 缺陷责任期要求：24个月 管 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 国 3.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 中 4.1.1 本次招标要求投标人具备的资质条件： 具备建设行政主管部门颁发的有效的市政公用工程施工总承包叁 级及以上资质 ； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标 不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （垫江县）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（垫江县）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资 源交易监督网、重庆市公共资源交易网（垫江县）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 4.2投标人可在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）本项目招标公告网页下方“我要 提问”栏提出疑问，提问时间从本公告发布至2026-08-24 09:00:00前。 4.3招标人应于2026-08-24 23:59:59前在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-18 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 垫江县丹香建设有限公司 代理机构: 重庆博钰大数据科技有限公司 地 址: 地 址: 重庆市垫江县桂溪街道南内街88号 网 邮 编: 邮 编: 项目负责人: 熊老师 项目负责人: 郭威 电 话: 023-74630098 电 话: 023-74692498 务 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 商 账 号: 账 号: 监督部门: 垫江县发展和改革委员会 电 话: 023-74517161 道 2026年08月18日 信息来源:https://www.chinapipe.net/project/d3074578.html cqdingjiu 2026.08.21 10:07:02 管 国 中</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="n">
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="n">
         <v>90</v>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>重庆, 管网改造, 投资金额, 产品种类</t>
         </is>

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -550,7 +550,11 @@
           <t>中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管 材询比采购公告 中铁十一局集团有限公司建安分公司招标采购中心就中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房 及配套综合交通枢纽工程CQZSG-2标段项目经理部管材组织询比采购，诚邀有意向的合格供应商参与报价。 一、项目概况及询比采购内容 1.1项目概况 网 （1）新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程位于重庆市中心渝中区中部，具体位置为菜园 坝立交桥以西，龙家湾隧道以东，菜袁路以北，王家坡以南。正在建设的地铁18号线贴临站房北侧，地铁26/27 号线从站区地下通过。项目共划分为4个施工标段，CQZSG-1标段：为国铁站房、地铁站台区域；站北路密不可 分的边坡及场坪工程，包含土石方工程和边坡支护工程，不含机电工程，由中铁建设承建。CQZSG-2标段：为 务 枢纽配套工程，地铁区间、西广场、成都局剩余还建，由中铁十一局承建。CQZSG-3标段：地铁区间、CTC、 站场、东广场，由中铁建工承建。CQZSG-4标段：人防车库、铁路自营车场、综合开发生产配套房屋等，由中 铁二局承建。 （2）标段概况：我方负责新建重庆至黔江铁路重庆站站商房及配套综合交通枢纽工程CQZSG-2标段全部施工内容 （简称B区），主要包含：（1）B区投影范围内盖板以下27号线、26号线明挖区间基坑支护、土石方、区间主体 结构及配套防水、综合接地工程（不含砌筑墙体、装饰装修和机电安装工程），以及承轨层以下市政排水 涵DK1+196（196m）和行包通道；（2）轨道交通26号线暗挖隧道预留工程，其中26左线487m，26号右线408m； （3）站北路E、F、H连接匝道工程，其中E匝道道247m、F匝道285.5m、H匝道174m；（4）B区盖板及以上还建房 屋，其中西侧盖板约3.56万㎡，还建房屋等总建筑面积约3.50万㎡。 1.2询比内容 详见拟采购货物一览表 管 二、供应商资格要求 2.1供应商必须是“中国铁建云链平台”注册并通过审核的供应商。 2.2本次询比采购不接受国被列入“《2026年中国铁建合作方警示名录》、《中铁十一局集团有限公司不良行为供 应商名录》、《JD采购网失信名单》（此项核查针对JMRH项目）”中的供应商,不接受近一年内在铁路建设工程 网公布有违法行为记录及物资供应不良记录、被中国铁路总公司限制投标或已清退出铁路市场的供货商（此项 核查针对铁路站房项目），不接受在铁建云链平台被标记的不良行为供应商。 中 2.3供应商在报价时，如是法定代表人签字的需提供法定代表人身份证复印件、如是法人授权代理人签字的需提 供授权委托书及被授权人身份证复印件。 2.4询比响应供应商需提供营业执照复印件。 2.5其它要求：提供样品、每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌 等质量证明文件，甲方凭此报告检验质量。 2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 三、拟采购物资及相关要求 3.1拟采购物资一览表 交 序 物资 型号 单 项目 货 交货日 数量 备注 号 名称 规格 位 名称 地 期 址 重 直 庆 径6:0mm 市 包含车 PVC 批次交 壁 渝 丝、黑 1 （袖 米 7100 货与零 厚4:-45.mm 中 色胶布、 阀管） 星交货 单节 新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 区 管筛、 （具体 长4m CQZSG-2 标段项目经理部 菜 管箍、 以项目 园 堵头等 通知为 坝 一切相 准） 直 网 重 关费用 2 PE管 米 7100 径2:5mm 庆 站 合计 14200 务 3.2技术规格书： 按询比文件第二章项目技术规格书执行 商 3.3结算和付款 3.3.1采购物资报价规则： 道 固定价格。 3.3.2付款方式 （1）货款支付方式：支付方式包管括但不限于银行转账、银行汇票、银行本票、支票、银行承兑汇票、商业承兑 汇票、财务公司票据、供应链票据、其他数字化信用凭证，票据贴息费用由 供货单位 承担。 （2）付款周期：本合同无预付款。甲方在收到乙方提交的合规增值税专用发票，并经税务机关认证通过后次月 支付乙方上月供应期所国供合格物资70%货款，全部货物供应完毕后三个月内付至95%，剩余货款暂时扣留作为质 量保证金，供货完毕后，由乙方提交结算确认单，经甲方审核通过后做最终结算，待所有物资验收合格后12个月 内无息付清。 （3）逾期付款约定：如甲方付款逾期，双方秉持“长期合作，友好往来”原则，在逾期付款行为发生后一年内 中 乙方不向甲方收取逾期付款利息。若一年甲方仍未支付款项，需向乙方支付逾期付款利息，逾期付款利息起算 时间为全部款项到期之日一年后至付清之日，逾期利息的利率为合同订立时中国人民银行授权全国银行间同业 拆借中心公布的一年期贷款市场报价利率(LPR)1倍。 3.4拟采购物资相关的要求 3.4.1本次询比为整体采购，询比响应供应商报价时须写明单价、到站价和运距，报价包含货物制造、运输、装卸、 售后服务等交付采购人使用前所有可能发生的费用，收到报价后不再增补任何费用。 3.4.2交货期：按照采购人规定的期限内分批次运抵交付。 3.4.3供货地点：甲方指定的甲方所属 中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通 枢纽工程CQZSG-2标段项目施工现场。 3.4.4询比响应供应商必须保证产品的质量及售后服务。询比响应供应商提供的货物制造标准及技术规范等，必须 符合最新相关国家标准、部颁标准相关标准和规范的要求，进场提供相关检验检测报告。 3.4.5采购方在确定成交供应商后有权对成交产品的结构、规格做适当调整，调整内容将以工作联系函形式提前发 至供应商。 3.4.6售后服务：本批采购货物若在验收阶段出现不符合规格或质量标准，供应商必须接受退货要求，并在采购人 规定期限内等量补运合格产品，若未按时交付影响采购人使用，供应商必须承担由此给采购单位造成的后续经 济损失。 3.4.7报价方不得虚报各项技术指标，所供货物若不能符合技术要求，成交供应商必须接受全额退还货款，并承担 由此给采购单位造成的经济损失。 3.4.8验收方法及标准 （1）验收依据：询比采购文件、厂家货物技术标准说明及国家有关的质量标准规定，均为验收依据。 （2）货物验收：货物运抵采购人指定交货处后由双方对照采购清单及技术要求进行验收。 （3）其它要求：每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌等质量证 明文件，甲方凭此报告检验质量。 网 （4）2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 四、报价文件递交 务 4.1此次报价供应商需制作电子报价文件，在递交截止时间前线上递交报价文件。 4.2报价文件递交截止时间：2026年08月24日15时00分。 商 4.3报价文件递交地点：中国铁建云链平台（www.crccep.cn），供应商须登录该平台，在报价文件递交截止时间 前完成所有报价文件资料的上传。 五、发布公告的媒介 道 本次询比公告发布媒体:中国招标投标公共服务平台(www.cebpubservice.com)、中国铁建云链平台（www.crccep.cn） 上同时发布。 管 六、联系方式 1.采购组织单位：中铁十一局集团有限公司建安分公司招标采购中心 地 址：湖北省武汉市国武昌区丁字桥路47号 联 系 人：张先生 联系电话：027-87258521 中 电子邮件：2454774350@qq.com 2.采购人：中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 CQZSG-2 标段项 目经理部 地 址：重庆市渝中区菜袁路59号 联 系 人：金先生 联系电话：16607273445 电子邮件：2285445503@qq.com 2026年08月21日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3077066.html cqdingjiu 2026.08.21 10:06:40</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>PE管：7100米</t>
+        </is>
+      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
@@ -617,7 +621,11 @@
           <t>璧山项目钢筋混凝土管询价公告 本项目位于璧山区，建设范围为双龙大道以北，璧铜线以东、渝蓉高速以南、玉泉湖（璧南河）以西区域，用 地面积约6平方公里。项目建设遵循循序渐进、分期、分块实施原则，采用“总体开发、分步实施”的方式进行 建设开发，合作期限8年，包含建设期和运营期（缺陷责任期），其中建设期6年，共分三期实施。第一期实施玉 泉湖以西，第二期实施璧南河以西，第三期实施渝蓉高速下道口。项目总投资44亿元，其中建安费28.6亿元，含 市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。项目开发建设内容包括片区范 围内的基础设施、人才教育基地、水系生态整治、绿化及广场、公共交通场等。本次采购的内容为本项目一期 实施的市政道路所需的钢筋混凝土管及管件，预计供货时间为2026年8月至2027年4月。 网 登录地 mhem&amp;cNh6e0&amp;ce2C2m3s1e71=a64so0d9FAe=0903%e08005206E%6772dm6=%82he29&amp;=cI8p9eeyAs%7t?E%5lB%1iB%a1DetE%c9eweNAi%1iotvB%n/9cE%7.cBe9%ccAiE%p.E%s9%/29址/A%2:：psE%7tAhtD%B8%E%6B%7B%7E%5%78D9%E%5C9%F%9E%7AE%A%1E%9%78%78E%8B%4AD%N&amp;8E%6m657optUa3%6=6290%e3ni51B%5917E%443d6=E%862B%I8eAc%A1iD&amp;88no%tE%4BA%A%4E%7AC%AC%E%4BA%C8%E%8%88AA%E%5A8%A%1E%5B%7A%5E%7A%8B8%E%5B%1%08E%6C9%%98E%9%99%09E%5%58AC%E%5F%8B%8E%8A%5BF%E%9%38A%8EF%BC%%88E%5B9%BD%E%9%99%58EF%BC%%98E%6%59B%0E%5AD%%79E%7BB%F%8E%6B%5E8%E%4BA%A%7E%4B%8A9%E%5B9%AD%E%5C8%BA%E%9%58D8%E%5A%5%79E%9A%1B%9E%7B9%AE%EF%BC%%88E%8A%5BF%E%7%98%78E%5C8%BA%EF%BC%%98E%9A%1B%9E%7B9%AE%E%7=BgB&amp;upC%a=sod&amp;euF%pN=8Flk&amp;cmsusheaE%c7=te%0a9m%6he=8tT&amp;cpS7eeyeE%s9sha%&amp;3c2845d5=pur5A6I&amp;8optUni 信息来源:https://www.chinapipe.net/project/d3077008.html 务 cqdingjiu 2026.08.21 10:06:40 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N3" t="n">
         <v>70</v>
       </c>
@@ -684,7 +692,11 @@
           <t>中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购公告 物资采购 【招标公告】中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购 招标编号：cscec2026081900001246027 项目：重庆市第四人民医院科学城院区建设项目（二期） 发布时间：2026-08-20 17:52:30 报名截止：None 区域：重庆市市辖区沙坪坝区 招标品类：其他类 招标（资格预审）公告 网 中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料采购 采 购 文 件 务 采 购 人： 中国建筑第七工程局有限公司 日 期： 2026年8月 商 目 录 一、响应须知 道 二、评审办法 三、响应注意事项 管 四、响应文件的上传 五．响应文件 六、物资设备合同 国 一、响应须知 【公司总部供应链中心业务监督电话：17516461564】 中 1、工程概况： 工程名称：临水临电材料采购 采购名称： 中国建筑第七工程局有限公司重庆区域暨重庆市第四人民医院科学城院区建设项目 (二期)临水临电 材料采购 采购编号： cscec2026081900001246027 项目地址： 重庆市 工程内容：重庆市第四人民医院科学城院区建设项目 (二期)建筑总用地面积15214.5平方米；总建筑面积65020平 方米，其中住院楼22229.9平方米，实验教学楼8103.6平方米，院内生活楼5830.59平方米，高压氧舱315.53平方米， 地下车库28540.38平方米，以及给排水工程、强电工程、弱电工程、消防工程、暖通工程、总图工程等。为参考。 （说明：描述本工程概况）。最终工程规模及内容以上级部门及采购人确定为准。 采购概算金额：135万元（含税）【采购概算金额视为最高采购限价，响应人响应报价高于最高采购限价的，作 无效响应处理】。 2、采购范围及相关要求： （1）资格审查方式： 资格后审 （2）采购联系人：项目联系人： 修经理 ，电话： 17838218888 ，地址：重庆市 公司联系人： 苟经理 ，电话： 19828530610 ，地址：四川省青白江国际贸易产业园10幢 （3）采购内容： 临水临电材料 （4）工程价款支付： 月结方式，即每月20日结算（遇节假日顺延），次月25日前（结算日后35日历天内），乙 方提供与结算等额增值税专用发票后，支付至前月结算额的70%（遇节假日顺延），最终结算办理完毕6个月后 付至最终结算价款的 97%，剩余3%质保金在质保期满后30日内无息支付。（质保期自全部货物供货完毕且验收 合格日起1年计算）（支付工程款时均应扣除根据采购合同应予扣除的其它金额。） 网 3、响应方式： （1）响应保证金缴纳方式 务 响应保证金采用保证金现金或购买保证金保险（二选一）两种支付方式，支付成功后点击页面【去响应】按钮， 响应人方可正常响应。 方式一：保证金现金缴纳： 商 1、本次采购的响应保证金为/元。 2、保证金收款账户信息请参见云筑网保证金支付页面信息。 道 页面显示账户只对公办理，不接受个人汇款，响应人以响应人基本账户或对公账号转账；响应人转账时务必备注 “交易识别码”（具体操作详见附件《供应商保证金操作手册》或可拨打云筑客服电话：4006-818-555） 方式二：保证金保险缴纳： 管 1、保证金保险可替代保证金，购买后无需再缴纳保证金，响应人可通过“云筑网”购买，响应保险费不退 还；(具体操作详见云筑网上传附件《供应商保证金操作手册》） 2、如发生扣除保证金国情况，保险公司按照保险合同约定向采购单位赔偿相关款项后，保险公司代位取得向响应 单位追偿的权利，响应单位应在规定时间内向保险公司支付相应追偿款。 以下情况可免缴本采购项响应保证金： 中 ①工程局A级分供商。 发生以下情况，响应保证金不予退还： ①响应截止后响应人撤销响应文件的，采购人可以不退还响应保证金。 ②成交人无正当理由不与采购人订立合同，在签订合同时向采购人提出附加条件，或者不按照采购文件要求提 交履约保证金的，取消其成交资格。 （2）采购文件领取事宜：响应人根据采购公告内容领取采购文件，然后根据采购文件要求，进行响应，一经报 价即认为响应人对采购文件已作出实质性响应。 （3）采购文件的澄清与修改 ①采购文件的答疑：如响应人发现采购文件有不清楚的地方或对内容有疑问，要求澄清和解答的，均应在距响 应截止时间2天前向采购人提出答疑，采购人应解答响应人提出的问题。 ②采购人允许响应人在响应截止日期之前对云筑网响应进行修改，但必须在响应截止时间之前完成云筑网响应， 逾期未响应的，则视为无效响应。 （4）（4）响应文件递交事宜 采用云筑网电子响应。 4、评审： （1）评审方法：本次采购拟选出 1 名成交人，区段划分：（如选2个及以上，应明确划分各成交人分供范围及工 程量，成交人按照最终排名顺序享有优先选择权）。采用经评审的（原则上应选择合理低价法），在响应文件 能够满足采购文件实质性要求的响应人中，评审出响应价格合理低价的响应人，但响应价格低于其成本的除外， 具体由采购评审小组在评审会上商定。 （2）响应人有下列情形之一的，取消成交资格： ①成交人在成交后拒签合同； 网 ②成交人未按约定缴纳履约保证金。 采购人： 中国建筑第七工程局有限公司 务 采购时间：2026年8月 二、评 审 办 法 （一）、评审依据 商 1、采购文件 2、响应文件 道 3、评审办法 （二）、评审小组 管 1、评审小组成员：（评审小组应由5人及以上单数评审专家组成，项目负责人必须参与评审。与分供商存在利害 关系的应回避。） 2、小组成员负责根据国评审办法及标准开展评审工作。 3、与响应人有利害关系的，不得进入评审小组。 （三）、评审原则 中 （1）采取经评审的合理低价法：从满足采购文件实质性要求的响应人中，选择合理报价中最低者（不合理低价 除外）为成交分供商。 （四）、初步评审 有效分供商（资审通过并参与有效报价的分供商）数量不少于N（拟选分供商数量）+2家。（询比采购和竞价采 购要求，其他采购方式参照采购管理办法，下同） 出现以下情形的，响应无效。 1、未按要求缴纳响应保证金的。 2、未按要求完成线上响应的。 3、未响应采购文件的实质性要求和条件的。 4、响应人提供虚假资料、隐瞒误导采购的。 5、响应人以他人名义响应或者以其他方式弄虚作假，骗取成交的。 6、响应人ip重复、涉嫌弄虚作假或串通交易行为的。 7、采购文件或法律规定的其它情形。 （五）、详细评审 1、评审：以云筑网填报数据为准。 2、排名：对进入详细评审的响应人响应报价进行汇总后，按响应报价由低到高进行综合排名。 若出现响应人响应报价相同时，按其年度供应商考评评级高低优先排序，若仍相同，可再选用以下进行情况排序 （根据情况自行排序）。 网 ①近三年工抵房金额； ②具有绿色节能环保材料设备； 务 ③云筑网显示的该响应人响应时间等。 1）、采购概算金额（见采购公告）视为最高采购限价，响应人响应报价高于采购概算金额的，作无效响应处理。 响应人响应报价低于成本的，经评审小组评审确定后，作无效响应处理。 商 2）、在评审过程中，评审小组可以要求响应人对所提交的响应文件中含义不明确、表述不一致或者有明显笔误、 文字和计算错误的内容作出必要的澄清、说明或者补正，该澄清、说明和补正属于响应文件的组成部分，须经 采购授权代表书面署名确认，不得改变响应文件的实质性内容，且须经评审小组一致同意。评审小组不接受响 应人主动提出的澄清、说明或补正。 道 3）、经以上评审，有效响应人数量仍须满足“有效分供商（资审通过并参与有效报价的分供商）数量不少于N （拟选分供商数量）+2家”，否则本次采购按废止处理（成交单位数量为“N”）。 管 4）、废止后重新发起采购，需经调查核实后，视具体调查核实结果决定是否准予原响应人参与新发起的采购响 应。 （六）、确定成交候选单位 国 多轮次公开竞争报价：（说明：如需要(应视采购标的物及响应报价情况)进行多轮次公开竞争报价的，应按详细 评审的排名顺序确定一定比例(首轮最高价不得进入二次报价)的有效响应人进行后续轮次报价，总轮次不超过3轮 （竞价采购）。 中 报价规则：响应人提交的首轮报价作为后续报价基准；后续轮次总报价不得高于前轮报价，若设置参考价，单 项报价不得高于参考单价。否则该轮报价无效；最终轮次报价提交后不得撤回或修改（以系统记录为准）。 晋级规则：每轮报价截止后，采购人按报价从低到高排序；出现相同报价时，依次比较：（1）资源库等级；（2） （参考上述第五条第2点，以优质优价为原则，优先选用具备相应能力的本级及上级A级分供商） 成交机制：最终按末轮有效报价的从低到高排序；当最低报价出现多家时，可自主决定成交人。 最终按照排名顺序拟定有效响应人作为成交候选单位，具体成交候选单位数量由评审小组根据采购文件确定。 成交候选单位经审批后作为最终成交单位。 成交候选人放弃成交、因不可抗力不能履行合同、不按照采购文件要求提交履约保证金，或者被查实存在影响 成交结果的违法行为等情形，不符合成交条件的，采购人可以按照评审小组提出的成交候选人名单排序依次确 定其他成交候选人为成交人，也可以重新采购。 （七）、其他事项 1、因响应人原因造成其自身未响应采购要求及未能成交等情况，由响应人自行承担相应责任及损失，与采购人 无关。 2、本采购文件中的合同范本即实际签约合同范本，双方均不允许以任何理由更改合同内容。 三、响应注意事项 1、若响应人对采购文件中之任何内容有不理解之处，须立即联系采购人，以便在响应截止日期之前能予以解释。 2、采购人不保证一定要接受最低价成交，不论响应结果如何响应人的响应文件均不退回，且不对未成交单位做 任何解释。 3、响应人在响应之前，对本采购项的分包条件均已了解，响应即认为已详细了解。 4、采购人对响应人进行考察时，响应人应提供便利条件。 5、本次采购的最终解释权在采购人。 网 四、响应文件的上传 1需上传的响应附件（未上传视为不响应采购文件）有： 务 1.1.《响应函》 1.2.《响应承诺函》 1.3.法定代表人身份证明（格式）； 商 1.4.授权委托书（格式）（若若为法定代表人响应则可不提供）； 1.5.报价清单明细（盖章版） 道 1.6金融工具支付方式及优惠措施 1.7.响应保证金汇款凭证扫描件或免缴证明（云筑网平台缴纳的无须提供）（若需） 管 六、响应文件格式 一、封面（格式） 国 中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料采购响应文件 响应内容：临水临电材料采购 中 （编号：cscec2026081900001246027） 响应人：（盖章） 法定代表人 或授权代理人（签字盖章）： 响 应 函 致：中国建筑第七工程局有限公司 1、经勘察了本工程现场,并仔细研究了响应须知、合同协议条款、合同条件、采购图纸、工程规范、地质勘察报 告、工程量清单、响应答疑、及其他有关采购文件后，我公司愿以我公司云筑网所上传的含税综合单价，并按 采购文件所要求的条件承包在规定工期内完成重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料的施 工、竣工并补充其任何缺陷。 2、我公司保证本工程质量必须：达到符合工程所需材料质量验收标准、设计、合同及有关工程施工及验收规范 的要求标准。 3、一旦我公司的云筑网响应内容被接纳，我公司将在收到成交通知书后按贵公司的要求开始施工，我公司保证 于承诺的工期内或双方议定的工期内完成并交付本合同中规定的整项工程。 4、我公司同意在本区段的正式建设工程施工合同签署之前，云筑网响应将始终对我公司具有约束力，并可随时 被贵公司接受。 5、我公司知道：云筑网报价及云筑网响应的其他部分构成我公司向贵公司的要约，贵公司如发出成交通知书则 成交通知书及云筑网响应、采购文件将构成约束我们双方的合同，如果我公司在接到成交通知书后，没有按贵 公司要求的时间签署正式合同或坚持提出附加条件，那么我公司同意贵公司有权另选成交单位并向我公司追讨 有关损失。 6、我公司知道，贵公司并无义务必须接受所收到的价格最低的或其他任何响应书。 7、云筑网响应内容已考虑了贵公司向我公司发出的关于采购文件的相关答疑，网补充通知（如有的话） 8、云筑网响应效力优先于同时提交的任何响应文件的其他组成部分。 响应人： （盖章） 务 日 期： 年 月 日 响应承诺书 商 致：中国建筑第七工程局有限公司 我系有幸参与贵公司 重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料的响应，我公司经研究决定， 在此郑重承诺： 道 1、我公司在响应过程中已完全了解并掌握了采购内容、合同条件及施工现场等情况。确保云筑网响应报价操作 为本公司自己操作，如响应后发生非本公司操作的情形，本公司承担相应违约责任。 管 2、我公司已经详细阅读该采购文件所有内容，充分领会并完全接受采购文件所述响应人应尽的实质性的权利与 义务。我公司保证不会对采购文件产生不利于双方友好合作关系和将增加贵公司采购范围内经济支出的重大误 解。 3、我公司确认，贵公国司发出的采购文件所有内容为不可割裂的整体。 4、我公司保证成交后不会对成交价格提出任何异议，更不会以任何理由要求贵公司针对成交范围的价款要求额 外补偿。不会以不了解采购文件、合同文件为由或曲解、片面理解采购文件、合同文件或割裂采购文件、合同 文件，断章取义，向贵公司提出任何补偿要求。 中 5、在本合同的履约过程中，如因我公司的供货或质量原因导致贵司损失，我公司保证承担因此而给贵公司带来 的所有经济上的损失。 6、我公司将本工程作为重点项目对待，保证不会出现供货能力不能满足施工需要的现象。为满足本工程业主及 贵公司在质量、进度、安全、环保上的要求，我公司将采取一切措施保证物资设备生产、供应、租赁，运输等 均满足贵公司的要求，并保证不会因此而向贵公司提出增加任何补偿要求。 7、我公司承诺无论本工程最终的成本状况如何，将不会违背合同基本原则而向贵公司要求增加或补偿合同文件 约定以外的任何费用。 8、我公司认为，贵公司可以就物资设备采购数量或租赁时长进行调整，并且此种调整不构成我公司的索赔理由。 响应人：（盖章） 法定代表人或 其授权代理人：（签字或盖章） 日 期： 年 月 日 响应人名称：【全称】 单位性质： 地 址： 成立时间：年月日 经营期限： 姓名：性别：年龄：职务：系（响应人名称）的法定代表人。 网 特此证明。 响应人：（盖单位章） 务 年月日 授权委托书 商 本人（姓名）系（响应人名称）的法定代表人，现委托（姓名）为我方代理人。代理人根据授权，以我方名义 签署、澄清、说明、补正、递交、撤回、修改中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建 设项目 (二期)临水临电材料采购（采购项目名称）响应文件、签订合同和处理有关事宜，其法律后果由我方承担。 道 委托期限：本授权书于年月日签字生效，至本次采购期结束为止。授权期限内无特殊情况不变更合法授权代理 人。 代理人无权转委托。 管 特此声明。 响应人：（盖章） 国 法定代表人：（签字） 身份证号： 中 授权代理人：（签字） 身份证号： 联系方式： 日期： 年 月 日 备注：法定代表人和委托代理人必须在授权书上亲笔签名，不得使用印章、签名章或其他电子制版签名,同时附 法定代表人和授权代理人身份证复印件（正反面，加盖公章） 报价清单明细 不 含 含 不含 计量单 税 税 含税 备 序号 材料名称 规格型号 数量 税 税合 税额 位 率 单 合价 注 单 价 价 价 1 镀锌钢管 DN100*4.0 米 500 2 镀锌钢管 DN150*4.5 米 250 3 镀锌钢管 DN65*3.25 米 650 4 镀锌钢管 DN50*3.25 米 800 5 PE管 DN100*1.6MPA 米 450 6 PPR管 DN50*1.6MPA 米 400 7 闸阀 DN100 个 22 8 闸阀 DN250 个 10 9 截止阀 DN50 个 42 网 10 截止阀 DN25 个 60 11 蝶阀 DN100 个 6 12 消防箱 800×1000×250mm 台 20 务 功率30kw,扬程144m，流 13 加压泵（变频控制） 台 1 量55m/h 14 橡塑保温材料 DN100*20mm 米 620 商 15 橡塑保温材料 DN150*30mm 米 280 16 橡塑保温材料 DN65*20mm 米 700 17 压线钳 CO-1000 个 1 道 18 污水泵 380V4KW=25米 台 12 19 污水泵 380V5KW=30米 台 7 20 热熔机 63-160 台 1 管 21 电工胶布 / 卷 200 22 高压自粘带 / 卷 120 23 水泵控制箱 / 个 8 国 24 PE聚乙烯管 DE110*1.6MPA m 560 25 PE聚乙烯管 DE75*1.6MPA m 420 26 PE聚乙烯管 DE63*1.6MPA m 480 中 27 PE聚乙烯管 DE32*1.6MPA m 750 28 PE球阀 DN25 个 6 29 PE球阀 DN50 个 6 30 PE球阀 DN100 个 5 31 镀锌桥架 200*100*1.2mm 米 1200 32 PVC排水管 DE300*5.0 m 180 33 PVC排水管 DE200*5.0 m 380 34 PVC排水管 DE160*4.0 m 486 35 PVC排水管 De110*4.0 米 560 36 PVC排水管 DE75*3.0 m 420 37 PVC排水管 DE50*2.0 m 660 38 PVC排水管 DE32*2.0 m 380 39 PPR给水管 De90*1.6MPA 米 440 40 PPR给水管 DE75*1.6MPA 米 360 41 PPR给水管 DE63*1.6MPA 米 450 42 PPR给水管 De50*1.6MPA 米 435 43 PPR给水管 De40*1.6MPA 米 315 44 PPR给水管 DE32*1.6MPA 米 520 45 PPR给水管 De25*1.6MPA 米 680 46 PPR给水管 De20*1.6MPA 米 370 47 橡塑保温板 平板×20mm m 15 48 橡塑保温板 平板×30mm m 28 49 保温胶 3公斤/桶 桶 25 网 50 PPR给水管接头 De75 个 30 51 PPR给水管弯头 De75 个 20 52 PPR给水管三通 De75 个 22 务 53 PPR给水管接头 De63 个 20 54 PPR给水管弯头 De63 个 15 55 PPR给水管三通 De63 个 15 商 56 PPR给水管接头 De50 个 17 57 PPR给水管弯头 De50 个 22 58 PPR给水管三通 De50 个 17 道 59 PPR给水管接头 De40 个 14 60 PPR给水管弯头 De40 个 22 61 PPR给水管三通 De40 个 17 管 62 PPR给水管接头 De32 个 14 63 PPR给水管弯头 De32 个 14 64 PPR给水管三通 De32 个 17 国 65 PPR给水管接头 De25 个 22 66 PPR给水管弯头 De25 个 17 67 PPR给水管三通 De25 个 14 中 68 PPR给水管接头 De20 个 25 69 PPR给水管弯头 De20 个 17 70 PPR给水管三通 De20 个 22 71 PPR内丝直接 De25 个 17 72 PPR内丝直接 De20 个 84 73 球墨铸铁井盖 700*800*40T 套 22 74 球墨铸铁井盖 1000*1000*20T 套 20 75 球墨铸铁雨箅子 400*600*30 块 1750 76 球墨铸铁雨箅子 350*500*30 块 1200 77 高分子成品排水沟 300*300*1000 米 850 78 高压洗车机 380v/3KW 套 5 79 高压洗车机 380v/5.5KW 套 3 80 HDPE双壁波纹管 DN300 米 360 81 HDPE双壁波纹管 DN200 米 410 82 HDPE双壁波纹管 DN400 米 340 83 HDPE双壁波纹管 DN800 米 260 84 玻璃钢化粪池 20m 个 1 85 玻璃钢化粪池 50m 个 1 86 不锈钢消防水箱 12m 个 1 87 一级配电柜 2000*1200*500*630A 台 1 88 二级配电柜 800*600*210*250A 台 8 89 铜芯电缆线 YC3*16+2*10 米 60 90 铜芯电缆线 YC3*10+2*6 米 70 网 91 铜芯电缆线 YC3*6+2*4 米 70 92 铜芯电缆线 YC3*10 米 100 93 铜芯电缆线 YC3*6 米 100 务 94 铜芯电缆线 YC3*4 米 100 95 铜芯电缆线 YC3*2.5+2*1.5 米 100 96 聚录乙烯铝芯电缆 YJLV-22-4*185+1*95 米 50 商 97 聚录乙烯铝芯电缆 YJLY-4*25+1*16 米 90 98 聚录乙烯铝芯电缆 YJLY-4*35+1*16 米 100 99 聚录乙烯铝芯电缆 YJY-4*50+1*25 米 90 道 100 聚录乙烯铝芯电缆 YJLY-4*70+1*35 米 72 101 网线 Cat5e 米 100 102 铜芯电线 BV-2.5 米 400 管 103 铜芯电线 BV-4 米 300 104 铜芯电线 BV-6 米 200 105 铝芯电缆线 YJLV3*10 米 100 国 106 透明塑壳断路器 3P32A 米 34 107 透明塑壳断路器 3P63A 米 28 108 透明塑壳断路器 4P100A 米 26 中 109 透明塑壳断路器 4P160A 米 22 110 透明塑壳断路器 4P250A 米 20 111 透明塑壳断路器 4P400A 米 8 112 低压铝芯电缆 YJLV-4*300+1 米 20 113 低压铝芯电缆 YJLV-4*150+1 米 50 114 铝芯铠装电缆 YJLV-22-4*95+1*50 米 60 115 铜铝线鼻 300mm2 个 20 116 铜铝线鼻 150mm2 个 36 117 铜铝线鼻 95mm2 个 24 118 铜铝线鼻 50mm2 个 20 合计 0.00 0.00 0.00 1、综合单价：包括但不限于材料费、保险费、风险费、包装费、装车费、过桥过路费、管理费、检验费、技术 指导费、货到工地负责卸货堆入至指定地点等所有费用。本合同单价一次包死，在合同履行过程中不再做任何 调整。本合同的总价为暂估价，用方有权调整合同中材料计划或材料数量，材料数量和规格的调整，不影响本 合同单价及其他条款的执行。 2、计量方式：查看检测报告合格证，以实际验收通过数量计量。 3、付款比例：月结方式，即每月20日结算（遇节假日顺延），次月25日前（结算日后35日历天内），乙方提供 与结算等额增值税专用发票后，支付前月结算额的70%（遇节假日顺延）；供货完毕，验收合格，材料相关资料 （包括不限于合格证、质检报告等）移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%；剩余3% 质保金在质保期满后30日内无息支付。质保期自全部货物供货完毕且竣工验收合格日起1年计算，支付工程款时 均应扣除根据采购合同应予扣除的其它金额。 4、付款方式： （1）现金支付:采用现金转账的模式支付； （2）非现金支付:包括不限于(1)金融工具支付:银行承兑汇票，商业承兑汇票，网应付账款保理，银行信用证，中 建财务公司承兑汇票。(2)工抵房支付。 5、响应报价表中所列数量的变动，丝毫不会降低或影响合同条款的效力。 务 6、整个合同执行期内，若遇市场价格下行，甲方有权做出价格调整，乙方应接受并重新签订补充协议确认价格。 若乙方无法接受新的低价，甲方有权重新选择其他能够响应该价格的供应商进行供货，乙方无条件同意。 响应人（加盖公章）： 商 法定代表人或授权代理人（签字）： 日 期：年月 道 金融工具支付方式及优惠措施 管 1、金融工具支付： 可接受金融工具支付比例累计为%，其中： ① 可接受的国银行承兑汇票比例%；贴息响应人自行承担。 ② 可接受的商业承兑汇票比例%；贴息响应人自行承担。 金融支付 ③ 可接受的应付账款保理比例 %；贴息响应人自行承担。 中④ 可接受的银行信用证比例%；贴息响应人自行承担。 ⑤ 可接受的中建财务公司承兑汇票比例为%；贴息响应人自行承担。 2、资产支付 资产支付 可接受比例为合同额的%。 3、优惠付款比例：按按照采购文件的付款比例，我方可优惠%。 4、如响应人提供其他由于采购条件的承诺，请逐项列示。 响应人（加盖公章）： 法定代表人或授权代理人（签字）： 日 期：年月 响应保证金汇款凭证扫描件或免缴证明（若需） 响应人（加盖公章）： 法定代表人或授权代理人（签字）： 日 期：年月 六、物资设备采购合同 合同编号：______________________ 物资采购与供应合同 （通用） 项目名称：【 重庆市第四人民医院科学城院区建设项目 (二期) 】 网 甲 方：【 】 乙 方：【 】 务 签订时间：【 】 签订地点：【 】 商 目录 1. 工程概况及供货范围 道 2. 企业性质 3. 合同价款 2 管 4. 质量要求 5. 供货时间及地点 6. 交货与验收 国 7. 结算方式及时间 8. 支付 中 9. 发票 10. 双方责任 11. 不可抗力 12. 权利瑕疵 13. 保密 14. 违约与赔偿 15. 联络与送达 16. 争议解决 17. 补充条款 18. 其他 物资采购与供应合同 甲方（买受人）：【中建七局安装工程有限公司 】 乙方（出卖人）：【 】 根据《中华人民共和国民法典》及有关规定，为明确双方权利、义务和责任，经双方协商一致，就甲方承包的 【高新LIVE（咸阳高新区租赁住房）建设项目】工程所用【 水电管材】采购与供应事宜签订本合同条款，愿共 同遵守。 1. 网 1.1 工程名称：【高新LIVE（咸阳高新区租赁住房）建设项目 】 1.2 工程地点：【陕西省咸阳市星火大道】 务 本合同供货范围为：【高新LIVE（咸阳高新区租赁住房）建设项目 】的【水电管材】供应（以下简称为“本合 同标的物”）。 1.3本合同标的物的数量为暂定量，乙方按附件1《计划采商购与供应物资清单》所列品种和规格供货，最终以经甲 方验收合格的实际数量为准。 2. 企业性质 道 乙方企业规模：大型 □中型 □小型 □微型企业 以上企业规模由乙方根据（1）工信部官网：“中小企业规模类型测试网址https://baosong.miit.gov.cn/ScaleTest。 （2）工信部微信小程序：“中小企业规模类型自测”两种渠道自测确定。 管 乙方应保证其企业规模的真实性。如乙方提供信息不实，经甲方查证后，将按照《中国建筑股份有限公司分供 商资源管理办法》中的《不良行为分供商禁用处理标准》第19项对乙方严格实施禁用管理。 合同价款 国 3.1 本合同采用第【 】种价格形式： （1）固定综合单价包干，价格不可调整。 中 3.2 本合同价款为各项货款之和，合同价款（含增值税）暂定：（大写）【 】（￥【 】元），其中不含税价款为 （大写）【 】（￥【 】元），增值税为（大写）【 】（￥【 】元），税率为【 】%。最终甲乙双方以实际验收 的数量结算。 3.3 本合同约定的不含税价款不因国家税率变化而变化，在合同履行期间，如遇国家的税率调整，则价税合计的 合同价款或货款相应调整，以开具发票时间为准。 3.4 本合同不含税价款仅指不包含增值税，除增值税外的其他全部税费（包括但不限于城市建设维护税、教育费 附加及地方教育费附加、个人所得税、合同印花税、企业所得税、车船使用税以及国家和地方规定的所有税费） 均包含在不含税价款中。 3.5 本合同标的物的计价、结算和支付货币均为人民币。 3.6 本合同标的物的计量单位为中华人民共和国法定公制计量单位（除技术规范标准另有规定外）。 3.7 本合同标的物的不含税单价，指运抵本工程施工现场甲方指定交货地点的综合单价，包括但不限于货物费、 加工费、包装费、人工搬运费（由乙方自行协调，甲方只进行指定场地和材料验收工作）、运输费、出厂检测费 （包括但不限于到场后的第三方检测费用）、装卸费、码放费、现场倒运费用，保险费、仓储费、驻厂监造费、 运输造成的道路污染的清理及维修费用、除增值税以外的税金、乙方合理的利润、管理费、市场价格波动带来 的风险、向有关部门缴纳的各项费用以及政策性文件所规定的各项应有费用等乙方履行本合同规定义务的全部 价款与费税。除本合同第3.1条约定的因素外，不含税单价不因政府政策变动、市场环境改变、税率调整等而调 整。 3.8 除合同条款另有约定外，本合同标的物的不含税单价已包含专利、专有技术以及技术秘密的使用费。 质量要求 4.1 乙方应在交货同时向甲方提供本合同标的物制造商出具的书面质量保证书。 4.2 本合同所采购与供应的物资，应符合现行中华人民共和国国家标准及行业或地方标准，行业标准或地方标准 高于国家标准的，执行行业标准或地方标准。各项技术性能指标经本工程所在地具有相应检测资质的专业机构 或单位检测中心检验必须符合相关标准要求。合同执行过程中，若出现新的国家标准、行业标准、地方标准， 则以更新后的标准为准。 网 4.3 乙方的物资供应与管理应符合国家有关环保法律、法规和甲方ISO14001环境体系及OHSMS18001职业安全健康 管理体系标准。 4.4 本合同标的物的质量保证期为最后一批货物验收合格之日起满【180】日。 务 4.5在合同履行期及质量保证期内，乙方无条件地向甲方提供缺陷产品的免费维修、更换等服务。针对甲方提出 的书面要求，乙方必须在3日内给予书面答复。如有必要，乙方在3日内指派专人到现场解决，因此产生的所有费 用均由乙方承担。 商 4.6 如缺陷产品经乙方进行免费维修和更换后仍无法达到甲方要求的质量标准时，甲方有权终止合同。终止合同 后，乙方需向甲方赔偿由于乙方问题造成的损失及其连带损失。如乙方借故推脱或拒绝甲方提出的维修、更换 等服务请求，甲方有权自行采购同等货物替代或委托第三方维修，实际发生的更换等或维修费用，从应支付给 乙方的任一期货款中扣除，并保留进一步索赔道的权利，乙方不得提出异议。维修或更换物资的质量保证期相应 延长6个月。 4.7 如因乙方产品质量导致工程出现质量问题，由此给甲方造成的一切损失由乙方承担。 管 4.8 其他质量要求：/。 供货时间及地点 5.1 供货方式：□按批次国供货 □一次性供货 5.2 通知方式：供货时间及数量以甲方书面通知为准，甲方可以选择通过电子邮件、微信、QQ等方式将物资采购 订单发送至乙方。紧急情况下，甲方可口头通知乙方发货，手续后补，乙方应予以确认。 中 5.3 供货地点：乙方负责送货至施工现场，卸至甲方指定的卸货地点【高新LIVE（咸阳高新区租赁住房）建设项 目】。乙方不得雇佣甲方在班人员及设备装卸货物。运输、装卸过程中发生的安全事故责任，乙方自行承担。 5.4 根据工程项目施工需要，甲方对所采购物资的数量和送货时间如有变更，应及时书面通知乙方，乙方按变更 后的数量和送货时间供货，货物单价不因货物数量和送货时间的变更而变化。 5.5 乙方应确保已经知悉货物运输的交通状况、交货卸车环境以及政府的交通管制政策措施，不得以此等理由要 求增加费用、减免责任、提出索赔、要求延长或变更供货期限。 交货与验收 6.1交货 6.1.1 除另有规定和协议要求外，乙方提供的全部货物须采用国家、企业、行业标准要求包装，具有足够的强度 及安全起吊标识，保证货物能够经受多次搬运、装卸、长途及短途运输的要求，并采取良好的防潮、防震、防 腐蚀、防爆及防止其它损坏的必要保措施。包装物的回收按以下第【 2】项方式执行：（1）不回收；（2）包装 物由乙方在交货时回收；（3）其它方式：【 /】。 6.1.2 装箱单应注明货物的名称、规格、型号、数量、质量、生产商、发货地、供货人、收货人、交货地、承运 人等，并在显著位置标明装卸警示标志。 6.1.3 乙方运抵甲方指定现场的物资，交货单据上应详细列明当次供应物资的名称、品牌、产地、生产厂家、规 格型号、计量单位、数量。 6.1.4 乙方应向甲方提交本合同标的物的技术文件，包括材质报告（物资质量检验报告）和出厂检验报告（合格 证），以及按照工程竣工验收规定及甲方要求，提供所有相关符合要求的资料。 6.1.5 乙方在首次供货前需提供样品，乙方须在样品和样品资料上加盖单位公章，样品经双方指定人员签字确认 后予以封存，在提交文件上注明与合同文件约定不同之处。 6.2.1 乙方须随货提供载有数量、规格等内容的送货单，否则，甲方有权对本批次货物不予验收确认，由此导致 的违约责任由乙方承担。乙方送货到交货地点后，甲方指定验收人员对产品的规格、尺寸偏差、外观、数量及 质量证明资料等进行查验。若产品的以上各项符合合同约定，则双方人员共同在收领单上签字确认。 6.2.2 甲乙双方在交货现场以 【 点数】方式进行数量验收。乙方应对在甲方工地网现场的验收数据进行确认。 6.2.3 进行数量验收的同时，甲方可以按照封存样品标准进行尺寸、外观质量验收，尺寸和外观质量符合要求方 可卸车，否则不得卸车。 务 6.2.4 外观质量符合要求的， 甲方可打开包装进行质量、性能检验或及时按规定取样送本工程所在地具有相应检 测资质的专业机构或单位进行检测。抽检未发现不合格产品不视为乙方供应产品全部合格，甲方有权随时将乙 方所供货物送到有检测资质的第三方进行检测。如检测合格，检测费用由甲方承担；如检测不合格，甲方可全 部退货，检测费用由乙方承担，并承担由此给甲方造成的一切损失。 商 6.2.5 甲方及工程监理（业主）的收货验收仅作为感观合格的依据，不能免除乙方对货物品牌真实性、内在质量 及使用功能所负的责任。如甲方、本工程建设单位或监理单位提出异议，乙方需参照有关标准规范，结合现场 情况解决。 道 6.2.6 若发现不合格产品，乙方必须及时（接到甲方通知后【 3】小时内），从甲方项目现场运走不合格品，甲方 不负有保管义务，不对不合格产品的损毁灭失承担人和责任，若超过【 12】小时乙方仍未运走的，甲方收取场 地租赁费（根据货物合理确定）【 1.0】万元/天，且不合格品的储存、装卸、运输等所有相关费用及风险由乙方 承担。 管 6.2.7 如因乙方产品问题造成甲方工期、质量、劳务等损失，全部责任均由乙方承担。乙方对甲方所提出的质量 问题有不同意见的，双方可送至双方共同选定的具有法定资质的检测机构检测，所产生的费用及责任由责任方 承担。 国 6.2.8 本合同的标的物所有权自【卸货完毕且经甲方验收合格】起转移。 结算方式及时间 中 7.1 过程结算：甲乙双方按以下第【 1】条约定的时间办理过程结算。 （1）每月20日结算（遇节假日顺延），每季度最后一个月的25日后支付当期货款额的70%（遇节假日顺延，乙 方提供与结算等额增值税专用发票），供货完毕，验收合格，材料相关资料（包括不限于合格证、质检报告等） 移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%，余款3%（不计息）待质保期满无质量问题后 无息付清。（质保期为供货完毕且验收合格后2年）（支付工程款时均应扣除根据采购合同应予扣除的其它金额。 ）； （2）按节点结算，具体结算节点为：【 】。 7.2 最终结算：全部供货完毕后【 6个月后】日内，乙方应向甲方提供完整的结算资料，甲方在收到完整的结算 资料后【 5 】日内进行审核。 7.3 结算依据：包括但不限于物资采购与供应合同、乙方合法等额有效增值税发票（含税务机关代开）、产品合 格报告、项目授权人员验收单、送货单等有效材料。 7.4 乙方未按照约定的期限和甲方要求提供结算资料，或未委派专人与甲方办理结算，或提供的结算资料不齐全、 提供虚假资料的，经甲方催告后10个工作日内，乙方仍未按要求提供结算资料的，甲方有权不予办理结算并暂停 支付材料款，同时甲方可根据本合同、现有结算资料及乙方实际履约情况单方办理结算，确定结算价格，结算 对甲乙双方具有法律约束力。 支付 支付/√不支付预付款 8.1.1 预付款金额（或占合同价款的比例）：【 /】。 8.1.2 预付款的支付时间：【 /】，在乙方提交等额银行保函及增值税专用发票后，甲方向乙方支付预付款。 8.1.3 扣回预付款的时间、比例：【 /】。 8.1.4 乙方提交的银行保函有效期至预付款抵扣完为止，若预付款保函到期日前，预付款无法抵扣完毕，则乙方 应于预付款保函到期日前不少于10日及时办理保函延期，否则甲方有权暂停支付未抵扣完部分的货款。 网 / 8.2.1 货款支付，按以下第【 3】条约定的时间和比例支付。 务 （1）月度付款：甲方在次月的25日支付上月月度结算货款的【 / 】%。双方办理完毕最终结算后【 / 】（条款说 明：建议不超过60日，如超过60日，应当按照行业规范、交易习惯合理约定付款期限并及时支付款项）个日历天 内付至总结算货款（且不超含税合同价款）的【 / 】%。余款【 /】%作为质保金，在质保期届满后28日内付清； 或由乙方提供等同余款金额的质保保函（仅接受金融机构出具的无条件见索即付保函，质保保函格式以开函金 融机构标准格式为准），则双方办理完毕最终结算后【 /商】（条款说明：建议不超过60日，如超过60日，应当按 照行业规范、交易习惯合理约定付款期限并及时支付款项）个日历天内付清。 （2）节点付款：按节点支付（条款说明：此处需具体罗列每个付款节点及各节点对应的付款比例，节点结算完 成后约定支付期限应在60日内，如超过60日，道应当按照行业规范、交易习惯合理约定付款期限并及时支付款项）， 余款【 /】作为质保金，在质保期满后28日内付清，或由乙方提供等同余款金额的质保保函（仅接受金融机构出 具的无条件见索即付保函，质保保函格式以开函金融机构标准格式为准），则在最后一个付款节点付清。每次 付款前乙方应提供结算值【100%】的发票，否则甲方可拒绝付款。 管 （3）其他支付方式【每月20日结算（遇节假日顺延），每季度最后一个月的25日后支付当期货款额的70%（遇 节假日顺延，乙方提供与结算等额增值税专用发票），供货完毕，验收合格，材料相关资料（包括不限于合格 证、质检报告等）移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%，余款3%（不计息）待质保 期满无质量问题后无息付清。（质保期为供货完毕且验收合格后2年）（支付工程款时均应扣除根据采购合同应 予扣除的其它金额。）国】 （4）甲方依合同约定确认的进度款仅为中期付款依据，不作为竣工结算的依据，且不视为对因变更调整的合同 价款、索赔的价款或费用以及其他约定的追加合同价款的确认。 中 8.2.2 甲乙双方协商一致同意本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保理、商业承兑汇票、 国内信用证、应收账款电子凭证、抵房抵款及其他】常规支付方式的付款方式。付款过程中产生的贴息费用及 手续费由【乙方】承担。乙方委托专职收款人办理收付款业务，收款人必须取得授权 8.3 乙方指定以下帐户为收款帐户，甲方所有款项均需通过该帐户支付。如乙方变更收款帐户，应提前十五天以 上书面通知甲方，否则造成资金的损失由乙方自行承担，与甲方无关。 账户名：【 】 开户行：【 】 账 号：【 】 发票 9.1 乙方在向甲方请款时，应根据甲方确认的应支付金额开具合法、有效、完整、准确的增值税（请勾选：□专 用□普通）发票，计税方法为【□一般计税方法 □简易计税方法】，双方发票信息如下： 名 称 纳税人身份 □一般纳税人 □小规模纳税人（请勾选） 甲方 纳税人识别号 地 址、电 话 开户行及账号 名 称 纳税人身份 □一般纳税人 □小规模纳税人（请勾选） 网 纳税人识别号 乙方 地 址、电 话 开户行及账号 务 联 行 号 该开户行为乙方在税务局已备案的乙方单位账户。 9.2 任何一方如上述信息发生变更，应提前10日以书面方商式通知另一方。如一方未按本合同规定通知而使另一方 遭受损失的，应予以赔偿。 9.3 每次乙方在甲方付款前必须提供符合国家现行税法规定的合法有效等额增值税发票，甲乙双方一致确认提供 发票为主合同义务而非附随义务，若乙方未按要求提供发票，甲方有权暂停付款。乙方应在开票之日起7天内将 道 发票送达甲方指定人员【 刘磊】，甲方指定人员签收发票的日期为发票的送达日期。 9.4 乙方开具的增值税专用发票应保证信息完整、内容规范，如乙方未提供发票或提供的发票不合规、不及时、 无法认证，甲方有权拒绝付款，且不视为甲方付款逾期，乙方无权要求甲方支付利息、违约金或赔偿损失，也 管 不得以此为由中止履行合同约定的义务。 9.5若乙方由一般纳税人身份变为小规模纳税人身份的，或者计税方法发生变化的，或者政策法规等规范性文件 发生变化的，并导致甲方可抵扣的进项税额减少或被税务机关要求补缴税款的，则减少的进项税额或补缴的税 款应由乙方承担，甲方国有权从将支付的任何一笔款项中扣除。 9.6 增值税税率变化：合同执行过程中如果遇到国家税务政策调整，增值税税率发生变化的，按新的税率执行， 不含税价不变，仅调整增值税税率的原则进行相应调整。 中 若乙方提供的发票不符合要求的，发包人有权拒收增值税发票，并有权暂停支付相应款项，乙方不得以此为由 中止履行合同的义务。如因乙方不能按期提供发票或提供的发票不符合要求而导致付款延期的，由其自行承担 后果，发包人不承担任何责任。 9.8若乙方迟延提供发票的，每日应按暂定合同总价的0.05%向甲方支付违约金，但迟延违约金累计支付不超过90 日；若乙方迟延提供发票超过90日且已跨年的，视为乙方未提供发票，乙方除应支付前述迟延违约金外，还应另 行向甲方支付以下款项： （1）相当于合同暂定总价1%的违约金； （2）甲方因未收到发票所产生的税款损失， 损失金额按以下公式计算：赔偿损失金额=未提供发票对应的增值税税额*（1+增值税附加税率）+未提供发票金额 *甲方企业所得税税率。 9.9乙方保证开具的发票已经依法足额纳税，支付每笔款项前，乙方需提供发票对应税期的增值税纳税申报表和 完税证明。 9.10乙方承诺其提供的发票真实合法，若发包人认证后出现走逃失联、被列为异常纳税人等违规行为，导致发包 人不能认证抵扣或者认证抵扣后被税务机关要求进项转出情形，应在72小时内补开合规发票，否则按以下方法计 算应赔偿发包人损失，应赔偿损失金额=进项转出税额*（1+增值税附率)+不合规发票金额*发包人企业所得税税 率，逾期未赔偿的，甲方有权从结算金额或者履约保证金中扣除。 9.11乙方主张已开具发票的，应提供：①税务系统发票开具记录 ；②采购方签收凭证或者发票邮寄物流凭证。无 法完整提供两项证据的视为未开票。 10.双方责任 10.1 双方现场代表 10.1.1甲方现场代表为【 】，其职务为【 】 ，其授权签署文件的范围为：【签发监管项目的各类文函、工程变更 指令、索赔文件的报出、违约处罚决定文件等】。 10.1.2甲方收货代表：【 】，联系电话【 】。甲方指定收货代表仅有对乙方送货单中货物的数量及乙方提供的单 据是否齐全子以确认的权利，对货物单价、质量、货款以及总结算单没有确认的权利。 10.1.3乙方应将物资按合同约定时间运至甲方指定地点，并经甲方指定收货代表和甲方工程项目所属其他1人及以 上在甲方指定的收领单上签字验收确认后有效。 网 10.1.4 甲方未经授权的任何人员和项目印章均无权从事下列行为：【（1）签订本合同的补充协议或签署其他合 同类文件，包括但不限于采购合同、分包合同、租赁合同；（2）签署任何借贷、担保性质的文件，包括但不限 于借条、保函、保证书、承诺书；（3）签署代他人清偿债务的文件，签署任何放弃债权的文件；（4）签署任何 对总承包合同进行修改和补充的文件;（5）收取现金及任何款项；（6）签署合同价款的变更、结算及支付确认 务 文件；（7）签署任何劳动关系确认文件、工资发放承诺文件。】 10.1.5 甲方授权人员的职权/职责范围、授权签署文件范围均不可转授权，任何形式的转授权、代签行为，甲方均 不予认可且不承担任何法律责任。 商 10.1.6 乙方确认已完全明白和理解甲方对甲方人员及项目印章的上述授权范围，超出甲方授权范围的行为属于无 权代理行为，对甲方无效，甲方不承担任何法律责任。乙方应谨慎审查相关文件的签署主体资格和权限，对于 无权代理人签署的相关文件，乙方应及时与甲方核实。 道 10.1.7 乙方现场代表为【 】，其职务为【 】，其授权范围为：【全面代表乙方履行本合同，并有权代表乙方签署、 确认履约过程中形成的工程变更、价款确认、经济索赔、违约处罚决定及物资丢失损坏赔偿文件；签署确权文 件及结算书；签收甲方发出的各类文函、工程变更及其他文件等。】 管 10.1.8 双方更换各自代表时，应及时书面通知对方，以确保物资顺利交接。 10.1.9 甲方禁止项目部及任何人员以甲方、甲方分公司、甲方项目部的名义对外借款或者支取任何款项，如乙方 或乙方有关人员以任何形式将款项出借或支付或返还给甲方项目部及任何人员，则不论该等款项是否实际用于 甲方工程，均与甲方无国关，该行为均属于乙方与相关人员个人之间的经济关系，乙方无权向甲方主张任何权利。 10.1.10 未经甲方书面授权不得擅自与建设方及有关部门发生工作上的联系，严禁在对外任何事务中签署甲方单 位名称或带有甲方简称中任何“【中国建筑】”“【中建】”“【中建XX局】”“【XX局】”等字样的落款， 每发现一次中乙方承担2万元的违约金并赔偿所有直接或间接损失。 10.2卫生、环境与安全保护 10.2.1 甲乙双方须贯彻执行国家、地方政府相关部门发布的有关卫生法律、法规，以及甲方发布的规章制度，积 极配合政府部门的检查，对于提出的要求按所属责任立刻整改，确保瘟疫和传染疾病防控的管理落实到位。 10.2.2 乙方保证在运输和卸货过程中应采取相应的环保措施，符合国家环保要求。车辆在进入项目现场要保证不 沾泥土和脏物，车辆出入项目现场必须在项目大门内现场洗车。乙方在卸货过程中保证噪声不超过以下标准 （白天小于或等于【 】dB、夜间小于或等于【 】dB）。乙方保证乙方人员以及车辆进入本工地现场，应遵守现 场的一切卫生环保、文明施工的规定，因违反环保要求所造成的一切罚款由乙方承担。 10.2.3 甲乙双方必须贯彻执行国家和政府、行业主管部门颁布实施的有关安全生产的法律、法规及有关规定。乙 方车辆及人员进出工地现场时必须接受甲方安全检查。乙方因供货造成安全生产责任事故的，责任由乙方承担。 乙方必须对自身出入工地现场的人员进行安全交底，并为其配备安全防护用品，因乙方原因造成的各种人员伤 害及经济损失由乙方自行承担，并赔偿甲方及其它方因此造成的一切损失。 10.3 售后服务 10.3.1 如所供货物为专业性较高的产品，乙方应免费为甲方或工程业主提供操作及维修人员的培训服务，培训内 容应包括：基本原理、操作使用、维修保养等。 10.3.2 对于工程中的剩余或未使用到的货物在不严重影响外观、质量和功能的情况下甲方有权退货，退货原则上 以合同约定的含税单价为准，确因商品特殊的（比如定制等），价格由双方协商，协商不一致的，按照附件1 《计划采购与供应物资清单》中的含税单价（考虑甲方已支付费用、乙方承担运费等情况下，原则上不低于【 】%）【 】%退货，退货数量以实际数量为准。 不可抗力 11.1 不可抗力是指合同当事人在签订合同时不可预见，在合同履行过程中不可避免且不能克服的自然灾害和社会 性突发事件，包括地震、海啸、瘟疫、骚乱、戒严、暴动、战争等情形。 11.2 不可抗力事件发生后，乙方应立即通知甲方现场代表并迅速采取措施，尽量减少损失，并在24小时内向甲方 通报受害情况，提供必要证明。不可抗力持续发生，乙方应每日报告一次受害情况，直到不可抗力结束。甲方 应对受害处理提供必要的条件，并负责处理工作的组织、指挥。不可抗力发生后网，乙方未采取有效措施控制灾 害而发生的损失由乙方承担。 11.3 不可抗力引起的后果，由甲乙双方应各自承担其人员伤亡及财产损失，履行合同的期限相应延长。 务 不可抗力发生后，双方均应采取措施尽量避免和减少损失的扩大，任何一方没有采取有效措施导致损失扩大的， 应对扩大的损失承担责任。 因一方迟延履行合同义务，在迟延履行期间遭遇不可抗力的，不能免除迟延履行方的违约责任。 商 11.4 因单次不可抗力导致合同无法履行连续超过【30】天或累计超过【60】天的，甲方有权解除合同。合同解除 后，双方应就合同履行情况及结算与付款等善后事宜达成补充协议。 权利瑕疵 道 12.1 涉及到知识产权（专利权）标记的产品，乙方应提供知识产权（或专利权）及其权属的有效证明材料。乙方 承诺其提供的物资不侵犯他人的知识产权（或专利权），若乙方提供物资侵犯他人知识产权（或专利权）导致 他人向甲方索赔的，乙方承担由此给甲方造成的一切损失，包括但不限于甲方处理此纠纷发生的律师费、诉讼 管 费、仲裁费、差旅费等一切损失。此外，乙方应向甲方支付合同价款【5】%的违约金。甲方针对上述一切损失 有权从乙方结算货款中扣除或依法追索。 12.2 乙方所供物资应不存在任何权属纠纷及抵押、查封等权利限制情形，如乙方所供物资存在权属纠纷或任何权 利限制情形导致甲方遭国受损失，乙方应赔偿甲方全部损失。 保密 13.1 除法律规定或合同另有约定外，未经乙方同意，甲方不得将乙方提供的技术秘密及声明需要保密的资料信息 中 等商业秘密泄露给第三方。 13.2 除法律规定或合同条款另有约定外，未经甲方书面同意，乙方不得将甲方提供的图纸、文件以及声明需要保 密的资料信息等商业秘密泄露给第三方。 13.3 任何一方违反上述约定，应负责赔偿守约方因此造成的一切损失。 违约与赔偿14.1甲方应按照合同约定及时向乙方支付合同价款，若因甲方资金不到位，乙方同意给予甲方【 30 】 日的宽限期，宽限期内不视为甲方违约。超过宽限期仍未支付的，乙方可向甲方主张自宽限期结束后的违约金； 违约金以逾期支付的价款为基数，自宽限期结束之日起至甲方支付逾期价款之日止，按照中国人民银行同期活 期存款利率向乙方计付，向乙方计付，逾期支付违约金的上限为逾期支付金额的【 / 】%（不超过3%）。在我方 支付逾期付款利息后，分供商不可就此向我方再主张逾期付款的违约责任。（条款说明：乙方为中小企业时， 甲方前述条款支付期限+本条宽限期整体不得超过60日）。14.2 除本合同中规定的不可抗力外，其他不论任何原 因，乙方若不能按约定期限足额足量送至甲方指定现场存货地点，甲方向乙方收取逾期运达物资货款（含增值 税）每日【3】％的违约金，自逾期之日起计算至乙方实际送达之日止，延迟或供货不足超过【3】日时，甲方有 权单方面终止合同。14.3 未经甲方书面同意自行停止供应本合同约定的货物，均视为乙方违约，乙方除承担因此 给甲方造成的一切损失外，乙方另支付合同价款的【5】%作为违约金。 14.4若乙方提供的货物为非合同约定的厂家或品牌的产品，或提供的是假冒他人品牌的产品，甲方有权立即终止 合同，乙方必须支付合同价款【2】倍的违约金给甲方，如乙方所供产品已安装至工程项目，则乙方除承担违约 金外，还必须承担拆除、工程维修、工作面清理和重新安装产生的所有费用等，如违约金不足以弥补因此给甲 方造成的所有损失，包括一切直接损失和间接损失，则超出部分，甲方有权向乙方追偿。乙方提供的货物为合 同约定的厂家及品牌产品，但货物质量不合格或不符合约定的技术要求时，可由乙方负责更换质量合格和符合 约定技术要求的产品，同时承担合同价款【5】%的违约金，并承担因违约造成的各项损失，甲方也可直接要求 解除合同，乙方承担因此给甲方造成的所有损失。乙方提供的合同标的物因品牌、质量等原因导致甲方被项目 业主或总包方罚款或追究违约责任，乙方应向甲方相应承担赔偿责任。 14.5 本合同履行过程中，如果乙方不能按时交货，应在交货前48小时内以书面形式通报甲方，甲方视情况确定是 否同意变更供货时间。如甲方不同意变更供货时间，可自行采购部分或全部货物。甲方在自行采购和接收该违 约部分货物时实际发生的所有额外费用及因此给甲方造成的损失，从甲方应支付给乙方的任一期货款中扣除， 甲方同时保留进一步索赔的权利。 14.6甲方提出索赔通知后，乙方应在【28】日内答复，如果在【28】日内未答复，视为乙方已接受该索赔，同时 甲方保留进一步要求赔偿的权利。 网 14.7 乙方在进出场时乙方不得私自运送甲方现场物资出场，一经发现，乙方向甲方支付所涉及物资原值【2】倍 的违约金，情节严重的交由司法机关处理。 务 14.8 由于乙方自身原因（如：不按约定开立银行账户、未及时提交报量资料或不按合同配合甲方进行款项支付 等），导致货款或工程款延期支付，甲方不承担延期付款利息及违约金，乙方不得因此停止供货；乙方擅自停 供的视为乙方违约，乙方承担因此给甲方造成的所有责任及损失。 14.9 如果出现合同为可调价合同，甲乙双方调价达不成一致商情形；或者出现合同为不可调价合同，乙方提出调价， 甲乙双方达不成一致情形，则甲方有权选择其他供应商，甲方不承担任何违约责任。 14.10 若乙方因14.5和14.9款原因停止供货，或未完成全部供货、或主张解除合同等不履行合同的情形，乙方剩余 款项的支付不适用本合同8.2条款，甲乙双方应道就剩余款项的支付签订书面补充协议，重新明确支付条款，甲方 不承担任何违约责任。 14.11 其他违约与赔偿要求：【 /】。 管 联络与送达 甲方：收件人【 】，联系电话【 】，电子邮箱【 】，地址【 】。 乙方：收件人【 】，联国系电话【 】，电子邮箱【 】，地址【 】。 15.2 一方通过电子邮箱发送文件的，文件到达对方邮箱即视为送达，送达时间为电子邮件到达对方邮箱地址时间； 一方通过信函邮寄送达的，则信函寄出后的第三个工作日或收件人实际签收日（以先到的时间为准）视为送达； 一方选择直中接送达的，则递交时视为送达。 15.3 邮件邮寄至上述地址被拒收或无人签收，亦视为已经送达，由此增加的费用和（或）延误的期限由拒绝接收 一方承担。 15.4 双方承诺，因本协议的履行或争议解决，上述联系人和联系方式为有效的联系方式，各项通知均应当向上述 联系人、联系方式送达。在诉讼、仲裁中，上述联系人、联系方式亦为有效的送达地址，向上述地址的送达即 为有效送达，即使发生拒收、退信等事件。 上述联系信息发生变更的，变更方应当即时通知对方；在对方收到变更通知之前，对方当事人或者仲裁、司法 机构已经向原联系人、联系方式进行的通知，视为有效通知。 争议解决 16.1 因本合同引起或与之相关的任何争议、纠纷或权利主张，则必须先行向对方发出书面和解申请书，并告知对 方争议、纠纷或权利主张之事实及依据、联系人及联系方式，在对方收到上述通知之日起 3 个月为双方和解期限。 在和解期限内，若双方达成和解协议的，双方的权利义务按照和解协议履行；若未达成和解协议的，任何一方 采用下列第【 】种争议解决方式，并自行承担本方发生的律师费、差旅费、保函费等相关费用∶ （1）向仲裁委员会申请仲裁 周口仲裁委员会（开庭地点：郑州） 郑州仲裁委员会 武汉仲裁委员会 北京仲裁委员会 上海仲裁委员会 中国国际经济贸易仲裁委员会 R成都仲裁委 （2）向【 】人民法院提起诉讼。 网 1.因本合同引起的或与本合同有关的任何争议，如仲裁委员会，则按照其仲裁规则进行仲裁。仲裁裁决是终局的， 对双方均有约束力。 务 2.双方承诺：任何一方向仲裁委员会申请仲裁的，双方均自愿放弃向对方主张仲裁费用和实际发生的其他费用， 包括但不限于鉴定费用、评估费用、审计费用等；双方均自愿放弃向对方主张补偿因办理案件支出的合理费用， 包括但不限于律师费、保全费、差旅费、公证费等。 3.双方约定：仲裁案件无论标的额大小、复杂程度如何，商均适用普通程序，即由三名仲裁员组成仲裁庭审理，以 确保案件公正审理。 4.调解期限：争议应先行和解协商解决，设定3-6个月和解期（可根据情况调整），且和解期限不计入仲裁审理 期限。任何一方若未履行上述和解程序而直接道提请至争议解决机构的，则需要向对方承担签约合同价【10】%的 违约金；如一方出现上述情形，另一方提起反诉或反请求，则提起反诉或反请求的一方不承担违约金。 17.禁止债权转让条款甲乙双方确认，若发生下列任一情形，即视为乙方重大违约，乙方需向甲方支付合同总价 （建议10%） %的违约金，且甲方有权视违约程度单方解除本合同，同时乙方应赔偿甲方因此遭受的全部损失 管 （包括但不限于直接损失、间接损失、维权产生的律师费、诉讼费、保全费等）。具体情形如下： （1）未经甲 方事先书面同意，乙方擅自将其在本合同项下对甲方享有的全部或部分债权进行转让、质押或以其他方式处分 给任何第三方的； （2）因乙方与乙方债权人存在债务纠纷，导致该乙方债权人以甲方为被告或被申请人提起代 位权诉讼、仲裁或采取其他司法/仲裁手段的； （3）未经甲方事先书面同意，乙方以自身名义或委托任何第三 方，就本合同相关事项国对甲方的关联单位（包括但不限于业主单位、建设单位、 发包方）提起代位权诉讼、仲 裁或采取其他司法/仲裁手段的； （4）其他性质同上述条款规定的情形。18.补充条款 /】 中 其他 19.1 本合同采用下列第【 2 】种签订方式： （1）本合同自双方签字并盖章后生效，一式【叁】份，甲方执 【贰】份，乙方执【壹】份，每份具有同等法律 效力。 （2）本合同采用电子签章签署生效。根据《中华人民共和国民法典》、《电子签名法》等相关法律、法规，双 方一致认可在【 】平台（网址：【 】）使用电子印章签署合同为其真实意思表示，且确保在该平台注册时，使 用的企业信息和个人相关信息真实有效，并且自觉遵守国家法律法规和甲方在该平台的合同签约流程。甲乙双 方使用电子签章方式签署的合同，只有通过验证生效的电子原件具有法律效力，未经电子印章服务平台公司提 供书面证明材料的电子合同打印版不能作为法律依据。如因乙方使用不当给甲方造成损失，乙方愿自行承担由 此造成的全部经济损失和法律责任。 19.2未尽事宜经双方协商一致后，可签订补充协议，与本合同具有同等法律效力。 19.3对于因本合同产生的任何争议或投诉，乙方可通过【 】（条款说明：根据各公司情况填写投诉平台或者联系 方式）进行提交。甲方将在收到乙方的投诉后，对乙方的投诉进行初步审查，并尽快与乙方取得联系以进一步 了解详情。因不可抗力或第三方原因导致无法按时处理投诉的情况，甲方将尽快通知乙方，并尽力协调解决问 题。 19.4本合同条款（包括但不���于免责条款、责任限制条款等）均经双方充分协商，双方已就全部条款内容达成一 致意见，不存在单方预先拟定且未予协商的情形。 附件： 附件1：《计划采购与供应物资清单》 附件2：《法人授权委托书》 附件3：《廉政合同书》 （以下无正文） 甲 方：【盖章】 乙 方：【盖章】 网 法定代表人：【签字】 法定代表人：【签字】 委托代理人：【签字】 委托代理人：【签字】 务 地 址：【 】 地 址：【 】 电 话：【 】 电 话：【 】 商 电子信箱：【 】 电子信箱：【 】 附件1 道 计划采购与供应物资清单 人民币：元 管 计量 暂定 单价 暂定含税 序号 物资名称 规格型号 品牌/产地 生产厂家 备注 单位 数量 不含税单价 增值税 含税单价 货款金额 价税合计 暂定合同价款人民币大写： 国 以上数量为暂定项目，最终以双方签字确认的采购结算单为准 中 附件2 中国建筑 项目管理表格 表格编号 法人授权委托书 CSCEC-WZ-HN003 （甲方）： 本授权委托书声明：本的法定代表人，授权委托我公司的 为我公司代理人，代表我公司与贵公司工程对涉及投标报价，物资合同、补充协议的签订、履行，物资结算、收款等业务进行签字确认，由在上述授权范围签字的所有文书，我公 司均予认可，由此产生的一切经济法律责任由我公司承担。 代理期限为前述代理人对上述业务发生第一次签字确认之日起至本工程结算完成之日止。代理人无转委托权。 特此委托。 代理人（签字/按指纹）：身份证号码： （供应商）法定代表人签字： （供应商盖章）： 日期： 附件3 廉政合同书 甲方：【 】 乙方：【 】 为确保甲方对业主的承诺，高效、优质共同完成施工任务，争创优质工程，保证合同双方能够高效廉洁地履行， 维护双方合法权益，经双方协商，特订立如下廉政合同书。 第一条 甲乙双方的权利和义务 1.甲乙双方应本着“公开、公平、公正、诚信、透明”的原则开展工作，自觉遵守党和国家、工程项目所在省、 市、区工程建设有关法律法规以及廉政建设的各项规定。 2.甲乙双方应建立健全廉政教育制度，开展经常性教育活动，积极宣贯“合规诚信 自律清正”的廉洁从业核心理 念，加强廉政教育。 3.加强相互监督，发现对方有违反廉政合同书规定的行为，应及时提醒对方纠正。 第二条 甲方的责任 网 甲方工作人员不得有以下行为： （1）为乙方多结算工程量、多签证、多付工程款等，并向乙方索要或接受贿赂、回扣、礼金、有价证券（卡）、 务 贵重物品和好处费等; （2）在乙方报销任何应由甲方或个人支付的费用; （3）参加有可能影响公正执行公务的超标准宴请和娱乐商、健身等活动; （4）接受乙方提供的通讯工具、交通工具和高档办公用品; （5）要求、暗示或接受乙方为个人住房装修道、婚丧嫁娶、配偶子女工作的安排以及出国（境）、旅游提供的方 便; （6）向乙方介绍或推荐配偶、子女、亲属参与的工程施工合同有关的设备、材料、工程分包、劳务等; 管 （7）向乙方推荐分包单位或要求乙方购买合同规定以外的材料、机具设备等; （8）因乙方拒绝本人的不合理要求，而故意刁难乙方。 第三条 乙方的责任 国 乙方应当通过正常途径开展业务，不得有以下行为： （1）为多结算工程量、多签证、多收工程款等，向甲方及其管理人员行贿或馈赠礼金、有价证券（卡）、贵重 中 礼品; （2）为甲方及其工作人员报销应由甲方单位或个人支付的任何费用; （3）安排甲方人员参加超标准宴请、娱乐活动及带有黄、赌性质的娱乐活动; （4）为甲方人员购置或提供通讯工具、交通工具和高档办公用品等; （5）乙方向甲方工作人员及其家属或者亲友介绍从事与甲乙双方工程有关的工程分包及材料设备、周转工具的 供应、租赁等经营活动。 第四条 违约责任 1.如甲方工作人员有违反本廉政合同书的行为，由甲方纪委查处，追究相应的党纪、政务责任，涉嫌犯罪的，移 交司法机关追究刑事责任；对实名举报的，甲方要立即调查，并采取有效措施保障乙方的合法权益，防止报复 事件发生。 2.如乙方单位或个人有违反本廉政合同书的行为，甲方视情节对乙方处以合同额0.5%—1%的罚款，情节较重并给 甲方造成损失的，乙方另需赔偿甲方直接经济损失，并取消乙方工程分包资格。 第五条 甲方接受举报的途径 1. 受理电话：【 】 2. 受理地址：【 】 3. 受理部门：【 】 4. 受理邮箱：【 】 第六条 本廉政合同书作为采购合同的一部分，具有同等法律效力，本协议与采购合同同日生效，至甲乙双方工 程合同履约完止。 甲方： 乙方： 网 法定代表人： 法定代表人： 授权委托人： 授权委托人： 务 签订时间： 年 月 日 请查看报价网 商 址：https://xy.yzw.cn/sj/bid-detail?tenderId=&amp;source=3&amp;tenderCode=cscec2026081900001246027&amp;tenantId=cscec 信息来源:https://www.chinapipe.net/project/d3076919.html cqdingjiu 2026.08.21 10:06:42 道 管 国 中</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>镀锌钢管 DN100*4.0：500米；镀锌钢管 DN150*4.5：250米；镀锌钢管 DN65*3.25：650米；镀锌钢管 DN50*3.25：800米</t>
+        </is>
+      </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
@@ -751,7 +763,11 @@
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(三标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 网 2.项目概况与招标范围 务 2.1 建设地点： 忠县花桥镇、新立镇、石宝镇、兴峰乡。 商 2.2 项目概况与建设规模①忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）：田块整治 工程：旱地区域撂荒地整治278.95亩；灌溉与排水工程：新建200m蓄水池6座、PE75管道967m、新建1.2*1.2m箱 涵16m、新建2*2m箱涵8m；田间道路工程：新建2.5m混凝土生产路15114m、改建2.5m混凝土生产路1078m、新 建2.5m泥结碎石生产路910m、改建2.5m泥结碎道石生产路279m、新建3.0m混凝土生产路601m、改建3.5m混凝土机 耕路4587m；地力提升工程：施有机肥278.95亩；其他工程：工号牌124块。 管 ②忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）：田块整治工程：旱地区域撂荒地 整治195.54亩；灌溉与排水工程：新建100m蓄水池4座、新建200m蓄水池6座、PE75管道5258m、PE90管 道1375m、PE110管道2156m、改建0.5*0.6m混凝土排水沟740m、改建0.6*0.8m混凝土排水沟109m、改建0.8*1.0m混 凝土排水沟296m、改建1*1.5m混凝土排水沟262m、新建3*2m盖板涵1座；田间道路工程：新建2.5m混凝土生产 路11359m、改建2.5m混国凝土生产路3430m、新建2.5m泥结碎石生产路1834m、新建3.0m混凝土生产路350m；农田 防护工程：新建1.0m高挡土墙39m；地力提升工程：施有机肥195.54亩；其他工程：工号牌142块。 中 2.3 本项目工程总投资金额：约3140万元； 本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）施工图所示范围的所 有内容为准，详见发布的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分： 标段划分情况、建设规模及标段合同估算金额等内容如下： 合同估算金额 序号 项目名称 建设地点 （万元） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二 1 花桥镇、新立镇 1022 标段） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三 2 石宝镇、兴峰乡 735 标段） 网 本项目共分为2个标段，每家投标单位仅对2个标段中的任意1个标段进行投标，若同时参与2个及以上标段投标的， 其投标文件无效。 务 2.7 其他： / 商 3.政府采购工程 道 3.1 是否属于政府采购工程：是 □否 管 3.2 是否专门面向中小企业预留：是 国 专门面向中小企业预留的实施方式： 中 方式一：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（忠县）下载招标文件、工 程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字 证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责 任自负。 5.2投标人可在重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要网提问”栏提出疑问，提问时间从 本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-10-12 09:30，投标人应当在投标截止时间前，通过互 务 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 商 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 道 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 管 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 国 开户银行: 开户银行: 账 号: 账 号: 中 监督部门: 忠县发展和改革委员会 电 话: 023-54456078 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段） 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005499 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421353 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891814619 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082001038 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00385 信息来源:https://www.chinapipe.net/project/d3076880.html cqdingjiu 2026.08.21 10:06:45</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>管道：967m；管道：5258m；管道：2156m</t>
+        </is>
+      </c>
       <c r="N5" t="n">
         <v>90</v>
       </c>
@@ -818,7 +834,11 @@
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点： 忠县花桥镇、新立镇、石宝镇、兴峰乡。 2.2 项目概况与建设规模①忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）：田块整治 务 工程：旱地区域撂荒地整治278.95亩；灌溉与排水工程：新建200m蓄水池6座、PE75管道967m、新建1.2*1.2m箱 涵16m、新建2*2m箱涵8m；田间道路工程：新建2.5m混凝土生产路15114m、改建2.5m混凝土生产路1078m、新 建2.5m泥结碎石生产路910m、改建2.5m泥结碎石生产路279m、新建3.0m混凝土生产路601m、改建3.5m混凝土机 耕路4587m；地力提升工程：施有机肥278.95亩；其他工程：工号牌124块。 商 ②忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）：田块整治工程：旱地区域撂荒地 整治195.54亩；灌溉与排水工程：新建100m蓄水池4座、新建200m蓄水池6座、PE75管道5258m、PE90管 道1375m、PE110管道2156m、改建0.5*0.6m混凝土排水沟740m、改建0.6*0.8m混凝土排水沟109m、改建0.8*1.0m混 凝土排水沟296m、改建1*1.5m混凝土排水沟2道62m、新建3*2m盖板涵1座；田间道路工程：新建2.5m混凝土生产 路11359m、改建2.5m混凝土生产路3430m、新建2.5m泥结碎石生产路1834m、新建3.0m混凝土生产路350m；农田 防护工程：新建1.0m高挡土墙39m；地力提升工程：施有机肥195.54亩；其他工程：工号牌142块。 2.3 本项目工程总投资金额：约3140万元； 管 本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）施工图所示范围的所 有内容为准，详见发布国的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分中： 标段划分情况、建设规模及标段合同估算金额等内容如下： 合同估算金额 序号 项目名称 建设地点 （万元） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二 1 花桥镇、新立镇 1022 标段） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三 2 石宝镇、兴峰乡 735 标段） 本项目共分为2个标段，每家投标单位仅对2个标段中的任意1个标段进行投标，若同时参与2个及以上标段投标的， 其投标文件无效。 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 方式一：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 网 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 .技术成果经济补偿 务 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （忠县）下载招标文件、工程量清单、电子图纸等资料。商参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（忠县）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源 交易监督网、重庆市公共资源交易网（忠县）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数字证 书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的，责任 自负。 道 5.2投标人可在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要提 问”栏提出疑问，提问时间从本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 管 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-10-12 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 国 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 中忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 忠县发展和改革委员会 电 话: 023-54450483 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段） 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421361 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00386 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005423 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891832091 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082001039 信息来源:https://www.chinapipe.net/project/d3076879.html 网 cqdingjiu 2026.08.21 10:06:45 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>管道：967m；管道：5258m；管道：2156m</t>
+        </is>
+      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -885,7 +905,11 @@
           <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(一标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）已由 忠县发展和改革委 员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来 自 业主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具 备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 网 务 2.项目概况与招标范围 商 2.1 建设地点： 忠县马灌镇、三汇镇、永丰镇。 道 2.2 项目概况与建设规模：忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）：田块整治 工程：水田整治50.67亩、水田区域撂荒地整治79亩、旱地区域撂荒地整治62.83亩；灌溉与排水工程：新 建200m蓄水池5座、新建500m蓄水池1座、泵站1座；田间道路工程：新建2.5m混凝土生产路12325m、改 建2.5m混凝土生产路8549m、新建2.5m泥结碎石生产路1223m、新建3.0m混凝土生产路576m、改建3.0m混凝土生 管 产路648m、改建3.0m混凝土生产路（拆除原1.5m宽路）266m、改建3.5m混凝土机耕路1662m；地力提升工程：施 有机肥136.48亩；其他工程：公示牌1座、工号牌213块。 国 2.3 本项目工程总投资金额：约3140万元； 中 本次招标项目合同估算金额：一标段1167万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）施工图所示范围的所 有内容为准，详见发布的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 网 方式一：本项目整体面向中小企业。 务 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 商 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 道 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 管 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 国 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 中 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（忠县）下载招标文件、工 程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及CA数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 5.2投标人可在重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从 本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-10 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 网 监督部门: 忠县发展和改革委员会 电 话: 023-54456078 务 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段） 商 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082000104 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005469 道 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421379 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00387 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891884496 管 信息来源:https://www.chinapipe.net/project/d3076876.html cqdingjiu 2026.08.21 10:06:46 国 中</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>泵站：1座</t>
+        </is>
+      </c>
       <c r="N7" t="n">
         <v>95</v>
       </c>
@@ -952,7 +976,11 @@
           <t>永川区农村供水管网巩固提升改造工程(东部片区)答疑补遗文件 永川区农村供水管网巩固提升改造工程（东部片区） 补遗文件（01） 各潜在投标人： 现将“永川区农村供水管网巩固提升改造工程（东部片区）”招标文件补遗通知如下，本次发布的补遗文件中 的所有内容与招标文件具有同等法律效力，如与招标文件、答疑补遗文件（01）网不一致时，以本补遗文件为准。 请各潜在投标人自行下载本补遗文件，不管下载与否，都视为全部知晓其全部内容。 一、本招标项目招标文件第二章投标人须知前附表第1.4.1项第1条第（3）款中“具备建设行政主管部门颁发的有 效的安全生产许可证，企业主要负责人、拟派项目经理具备相应的由建设行政主管部门颁发的有效的安全生产 务 考核合格证书。”修改为： “（3）具备建设行政主管部门颁发的有效的安全生产许可证，企业主要负责人、拟派项目经理具备相应的由水 行政主管部门颁发的有效的安全生产考核合格证书”。 商 二、本招标项目招标文件第二章投标人须知前附表第1.4.1项中第3条“业绩要求”修改为： “投标人自2023年1月1日起至投标截止日止（以合同工程完工日期或工程竣工日期为准），完成过1个单项合同 输配水管网长度不少于100km的水利工程施工道业绩。 提供：供该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴 定书）的证明材料。若提供的上述业绩证明材料不能体现上述业绩指标的，应补充提供业主证明。 管 注：（1）当上述业绩证明材料中针对同一指标存在不一致时，以合同工程完工证书（或合同工程验收鉴定书或 工程竣工证书副本或竣工验收鉴定书）的证明材料为准。（2）投标人提供的业绩为联合体业绩的，其在该业绩 中的工作分工应与本项目承担的工作一致。” 三、本招标项目招标文国件第二章投标人须知前附表第1.4.1项中第5条中的“5.3项目经理业绩要求”修改为： “投标人拟派的项目经理自2023年1月1日起至投标截止日止（以合同工程完工日期或工程竣工日期为准），完成 过1个单项合同输配水管网长度不少于100km的水利工程施工业绩，并在该业绩中担任项目经理。 中 提供：供该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴 定书）的证明材料。若提供的上述业绩证明材料不能体现上述业绩指标的，应补充提供业主证明。 注：（1）当上述业绩证明材料中针对同一指标存在不一致时，以合同工程完工证书（或合同工程验收鉴定书或 工程竣工证书副本或竣工验收鉴定书）的证明材料为准。（2）投标人提供的业绩为联合体业绩的，其在该业绩 中的工作分工应与本项目承担的工作一致。” 四、本招标项目的投标文件递交的截止时间（投标截止时间）调整为2026年9月4日9时30分（北京时间），开标 时间及投标保证金递交截止时间相应顺延。 招标人：重庆市永川区惠永水务有限公司 招标代理机构：重庆永川政鑫综合能源有限公司 2026年8月20日 信息来源:https://www.chinapipe.net/project/d3076870.html cqdingjiu 2026.08.21 10:06:46</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>输配水管网：100km</t>
+        </is>
+      </c>
       <c r="N8" t="n">
         <v>80</v>
       </c>
@@ -1019,7 +1047,11 @@
           <t>长寿区海棠、石堰、龙河片区污水管网建设项目(二期)招标公告 长寿区海棠、石堰、龙河片区污水管网建设项目（二期）招标公告 1.招标条件 本招标项目长寿区海棠、石堰、龙河片区污水管网建设项目已由重庆市长寿区发展和改革委员会以长改发投 〔2024〕169号文批准建设，项目业主为重庆市长寿区住房和城乡建设服务中心，建设资金来自财政资金，项目 出资比例为100%，招标人为重庆长寿乡村建设集团有限公司。项目已具备招标条件，现对该项目的施工进行公 开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：长寿区海棠镇、龙河镇、新市街道、云台镇。 2.2 项目概况与建设规模：新改建及修复DN300mm-DN1200mm排水管道20.187公里，其中新改建管道15.21公里， 务 修复管道4.977公里，Ⅲ、Ⅳ级结构性及功能性缺陷修复453处。 2.3 本次招标项目合同估算金额：4139.45万元。 2.4 招标范围：详见招标人提供的本工程的施工图图纸、图商说、设计变更以及工程量清单所明确的全部工程内容。 2.5 工期要求：270日历天。 缺陷责任期要求：24个月。 道 3.政府采购工程 3.投标人资格要求 管 3.1 本次招标要求投标人须具备以下条件： 3.1.1 本次招标要求投标人具备的资质条件：建设行政主管部门颁发的有效的市政公用工程施工总承包三级及以 上资质； 国 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 中 3.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需 在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网 导航栏“主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登 记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公 告发布至2026-08-25 15:00:00前。 4.3招标人应于2026-08-28 18:00:00前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交 易网（长寿区）（https://www.cqggzy.com/changshouweb/）发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-14 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源 交易监督网上发布。] 7.联系方式 招 标 人: 重庆长寿乡村建设集团有限公司 代理机构: 中新创达咨询有限公司 地 址: 重庆市长寿区桃源大道3号一号商务楼5-6楼 地 址: 邮 编: 邮 编: 项目负责人: 刘老师 项目负责人: 钟亮 网 电 话: 023-40233279 电 话: 19132912275 传 真: 传 真: 电子邮箱: 电子邮箱务: 开户银行: 开户银行: 账 号: 账 号: 商 监督部门: 重庆市长寿区发展和改革委员会 电 话: 023-40245080 2026年08月20日 长寿区海棠、石堰、龙河片区污水管网建设道项目（二期） 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公 中国农业银行股份有限公司重庆自由贸易 312601010400083780000033561 司 管试验区分行 重庆联合产权交易所集团股份有限公 中国建设银行股份有限公司重庆渝中支行 6232813760003317764 司 重庆联合产权交易所集国团股份有限公 重庆银行股份有限公司七星岗支行 15010202900420146632392 司 信息来源:https://www.chinapipe.net/project/d3076848.html cqdingjiu 20中26.08.21 10:06:46</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>排水管道：20.187公里；管道：15.21公里；管道：4.977公里</t>
+        </is>
+      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -1086,7 +1118,11 @@
           <t>中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部刺丝滚笼、塑钢模板、泄水管询价采购公告 中铁十一局集团有限公司重庆至万州高铁站前 1标项目经理部 刺丝滚笼、塑钢模板、泄水管询价采购公告 询价编号： ZT1105-XJ-2026-590 尊敬的 各潜 在供应商 : 网 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与 中铁十一局集团有限公司重庆至万州高铁站 前 1标项目经理部 ZT1105-XJ-2026-590， 刺丝滚笼、塑钢模板、泄水管 的报价。 一、 项目概况 务 渝万高铁站前 1标位于重庆市万州区和忠县境内,起止里程DK14+233.2~ D1K47+550.4，正线长度 33.01km，中标造 价 31.73 亿元。管区内共有隧道8座/22.36km，斜井2座/1.76km;桥梁15座/8.97km，其中，预制及架设梁 301 孔，(40+64+40)m和(45+100+45)m连续梁各1联;区间路基22段/1.68km，土石方约67万方，负 责DK0+000~DK57+136段小型构件预制。合同工期54.7月商，开工日期为2022年11月01日，竣工日期为2027 年04 月30日。 二、 询价内容 道 本次 计划对刺丝滚笼、塑钢模板、泄水管 进行询价，询价内容如下： 询价物资一览表 管 计 序 物资 量 包件号 规格型号 数量 备注 号 名称 单 位 国 刺丝 1 GL-01 2.5mm 6m0.5m 米 6500 半径 ≥225mm，包括刀片刺绳、挂丝、连接卡、支架 滚笼 防护 中 栅栏 2 GL-01 用立 50X30X765X2.5mm 套 500 含抱箍、螺栓等配件 柱支 架 平 塑钢 3 MB-01 350X300mm 方 19.2 400*400,1个挡水沿，配固定手柄 模板 米 平 塑钢 4 MB-01 350X300mm 方 19.2 400*400,2个挡水沿，配固定手柄 模板 米 平 塑钢 5 MB-01 300X300mm 方 75.6 2个挡水沿，配固定手柄 模板 米 平 塑钢 6 MB-01 300X300mm 方 75.6 1个挡水沿，配固定手柄 模板 米 7 SSG-01 管篦 PVC250X200x10mm 个 220 材质硬聚氯乙烯 PVC，详见附图 PVC 8 SSG-01 泄水 135X38mm 块 220 材质硬聚氯乙烯 PVC，详见附图 管盖 U型 9 SSG-01 125mm 个 900 详见附图 管卡 UPV 材质硬聚氯乙烯 PVC，两端接头采用阴阳螺纹连接详见 10 SSG-01 C排 125X8mm螺纹 米 2870 附图 水管 UPV 11 SSG-01 C弯 DN125X8mm90° 个 240 材质硬聚氯乙烯 PVC，详见附图 管 UPV 网 125X125X110mm弹性密 12 SSG-01 C三 个 120 材质硬聚氯乙烯 PVC，详见附图 封圈异径斜三通 通 无压 埋地 务 排污 排水 用硬 13 SSG-01 DN125 个 150 材质硬聚氯乙烯 PVC，详见附图 聚氯 商 乙烯 管 T 型接 头 道 合 计 管 说明： 1. 表中数量为计划数量，实际 采购 过程中可能有所调整，最终结算按照实际 采购 数量结算。 2.收货地点：中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部 三、 技术质量 及报价国 要求 1. 此次 询价物资 各项技术性能要 符合 甲方 的要求，质量满足甲方项目部正常使用的要求，保证 产品 的质量合 格。 具体要求或图纸见询价文件技术规格书。 。 中 2 .报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、 结算及付款方式 每个月 15 日为双方价款结算日期（即上月 16 日至当月 15 日内），结算前双方要在对帐确认单上签字认可，乙 方按双方确认的金额开具增值税专用发票，并自发票开具之日起 7日内传递给甲方。甲乙双方在增值税专用发票 传递过程中必须留取相应的交接签证手续。自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发 票认证完成之日起第6个月，支付至本次结算金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内， 累计支付总额不超结算总金额的75%，剩余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理 末次结算后第二年，支付金额应大于等于尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总 额的15%；办理末次结算后第四年，全部付清）。 五、 报价 人资格要求 1.营业范围要求：在中华人民共和国境内依法注册，具有询价物资生产或供应经验的生产商或代理商，并且具有 合法有效的营业执照。 2.生产能力要求： 生产商须具备 询价 物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定 。 代理商需出具制造厂出具签字盖章的授权函。 3.财务能力要求：报价人为增值税一般纳税人或小规模纳税人，有依法纳税的良好记录。 4.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8月至今） 国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；每种物资全指标技术参数性能满足 国家和行业最新标准的各项规定。 5.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年8月至今）企业或企业法定代表人有人民法院生效判决、裁定 认定的行贿犯罪记录的。④ 对纳入国家铁路局“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接受 通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合作 方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 网 6.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 务 ★7 .下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 六、 报价人需要提供的资料 1. 营业执照复印件、 法人身份证复印件、 开户许可证、商授权委托书 、 报价表 和报价人资格要求中所需的证明资 料， 所有资料需加盖公司鲜章。 2. 产品质量检测报告等质量证明文件。 道 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、 询价 报名截止 时间 管 有意参加本次询价采购的报价人 须在铁建云链平台 （ https:// www.crccep. cn） 完成供应商注册，并 于 202 6 年 8 月 20 日 9时 00 分 至 202 6 年 8 月 24 日 9时 00 分在网上 完成报名工作。 八、 询价 截止 时间 国 凡有意参加本次询价采购的报价人，请于 202 6 年 8 月 24 日 14 时 00分 前 提交报价。截止时间前未完成 报价 文 件传输的，视为放弃 报价 。 供应商报价必须严格按照《 报价表 》格式进行报价。 中 九、 联系方式 采购 组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村 71号 联系人：胡先生 联系电话： 13983336494 （提供平台服务支持） 采购人名称：中铁十一局集团有限公司重庆至万州高铁站前 1标项目经理部 地址： 重庆市万州区双河口街道檬兴路万州现代综合物流中心信息交易大厅（中铁十一局） 联系人： 唐大伟 联系电话： 18323391938（提供采购服务支持、保证金退还） 中铁十一局集团有限公司物资设备集中采购管理中心 第五分中心 2026 年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3076805.html cqdingjiu 2026.08.21 10:06:47 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N10" t="n">
         <v>85</v>
       </c>
@@ -1153,7 +1189,11 @@
           <t>垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告 1.招标条件 本招标项目 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目 已由 垫江县发展和 改革委员会 以 垫江发改委发〔2026〕20号 文批准建设，项目业主为 垫江县太平镇人民政府，建设资金来 自 大中型后扶资金及自筹资金 ，项目出资比例为 100% ，招标人为垫江县太平镇人民政府。项目已具备招 标条件，现对本项目施工进行公开招标，评标办法采用经评审的最低投标价法。网 务 2.项目概况与招标范围 商 2.1 建设地点：垫江县太平镇桂花村 道 2.2 项目概况与建设规模：主要为河堤护岸岸线整治2100m；产业路扩宽及油化改造775.3m；新建污水管网450m， 化粪池2座；产业基地水肥一体化改造45亩等。 管 2.3 本项目工程总投资金额：642.89万元 国 本次招标项目合同估算金额：约5014864.52元 中 2.4 招标范围：本工程施工图纸所含全部的施工内容，具体以招标人发布的工程量清单为准。 2.5 工期要求：工期为360日历天 ，缺陷责任期为24个月。 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：□是 否，因专门面向中小企业预留无法确保充分供应、充分竞争，根据 《政府采购促进中小企业发展管理办法》第六条第(三)“按本办法规定预留采购份额无法确保充分供应、充分竞 争，或者存在可能影响政府采购目标实现的情形”的规定，本项目不专门面向中小企业预留。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 网 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的水利水电工程施工总承包三级 务 及以上资质。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相商应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 道 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 管 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com国/dianjiangweb/)、重庆市公共资源交易监督网下载招标文件、工程量清单、电子图纸等资 料。参与投标的投标人需在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共 资源交易监督网完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交易监督网导航栏“主体信息”页面中“市场主体信息 登记”、“中CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流 程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交易监督 网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-24 17:00:00前。 5.3招标人应于2026-08-28 17:00:00前在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重 庆市公共资源交易监督网发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-28 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交 易监督网发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 垫江县太平镇人民政府 代理机构: 重庆皓辰建设工程咨询有限公司 重庆市渝北区金开大道1228号大雅金开国际1 地 址: 重庆市垫江县太平镇牡丹路191号 地 址: 栋9-2 邮 编: 邮 编: 项目负责人: 余老师 项目负责人: 雷雨得 电 话: 13996889839 电 话: 023-86018770 18580880860 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 垫江县发展和改革委员会 电 话: 023-74517161 网 2026年08月19日 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目 务 户名 开户行 投标保证金账号 垫江县公共资源交易中心 中国农业银行重庆垫江支行 316301010400077950000005966 垫江县公共资源交易中心 中国银行重庆垫江支行 111616885778VA00139 商 垫江县公共资源交易中心 重庆农村商业银行垫江支行 2501010120010009065000128 垫江县公共资源交易中心 工商银行重庆垫江支行营业部 9558853100016843371 垫江县公共资源交易中心 重庆银行垫江支行 820101040000584-101195 道 附件：垫江县2026年度大中型水库移民后期扶持项目-.zip https://www.cqggzy.com/trade/014001/dac54522-3264-4eac-ae47-f434567ce374?categoryNum=014001001007 信息来源:https://www.chinapipe.net管/project/d3076788.html cqdingjiu 2026.08.21 10:06:47 国 中</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>污水管网：450m</t>
+        </is>
+      </c>
       <c r="N11" t="n">
         <v>85</v>
       </c>
@@ -1220,7 +1260,11 @@
           <t>万州区新田等6个镇乡农村饮水质量提升项目招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区新田等6个镇乡农村饮水质量提升项目 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 及文号 务 新建水厂1座（新建2000m3茨竹水厂），输、配水管道改造与新建，管道总长约226.127km，管 主要建设内容 径DN20~DN250，管材为涂塑钢管。 招标项目名 招标方 招标文件计划 拟交易场 合同预估金 序号 招标内容 备注 称 式 发布时间 所 额(万元) 商 万州区新田 万州区新田 重庆市万 招标项目 等6个镇乡农 等6个镇乡农 公开招 州区公共 1 村饮水质量提 2026-08 5000.00 村饮水质量 标 资源交易 升项目道施工总 提升项目 中心 承包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076721.html 管 cqdingjiu 2026.08.21 10:06:48 国 中</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>管道：226.127km</t>
+        </is>
+      </c>
       <c r="N12" t="n">
         <v>80</v>
       </c>
@@ -1287,7 +1331,11 @@
           <t>万州区大周等4个镇乡街道农村饮水质量提升项目招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区大周等4个镇乡街道农村饮水质量提升项目 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 及文号 务 新建50m3蓄水池4口、取水池2座；新建50m3/d-100m3/d水厂2座；改造100m3/d-300m3/d水厂5 主要建设内容 座；铺设DN25-DN250涂塑钢管约86km；新建提水泵站8座；配套阀井、电磁流量计等有关设 施。 招标项目名 招标方 招标文件计划 拟交易场 合同预估金 序号 招标内容 商 备注 称 式 发布时间 所 额(万元) 万州区大周 万州区大周 重庆市万 招标项目 等4个镇乡街 等4个镇乡街 公开招 州区公共 1 道农村饮水 道农村饮道水质 2026-08 3000.00 标 资源交易 质量提升项 量提升项目施 中心 目 工总承包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3076720.html cqdingjiu 2026.08.21 10:06:49 国 中</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>涂塑钢管：86km；提水泵站：8座</t>
+        </is>
+      </c>
       <c r="N13" t="n">
         <v>80</v>
       </c>
@@ -1350,7 +1398,11 @@
           <t>二航科工新燕尾山项目纤维编绕拉挤电缆保护套管采购询价通知公告 中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程项目询比采购 公告 中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程项目已具备采 购条件，现公开邀请供应商参加询比采购活动。 网 1. 采购项目简介 1.1 采购项目名称：中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机 电工程项目。 务 1.2采购方案编号：FA00000674478。 1.3 采购人：中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程 项目经理部。 商 1.4 采购代理机构：中交二航局科工（武汉）有限公司。 1.5 采购项目资金：企业自筹。 道 1.6 采购项目概况：新燕尾山隧道工程位于重庆市内环吉庆隧道北侧，四横线分流道鹿角隧道南侧，西接白居 寺大桥，东接内环快速路，并向东延伸接渝黔复线高速，其所在的道路系统呈东西布置，为主城区南部片区重 要干道。本项目西起太阳岗立交(不含太阳岗立交)，往东穿越铜锣山，止于内环南泉立交(不含南泉立交)。项目 管 全长约6.8km，其中二标段长约3.62公里，采用主干路标准，设计车速60km/h，标准路幅为双向6车道，主要工程 包括长隧道1座(新燕尾山隧道，长2542m)，简易立交1座(花溪立交),互通式立交2座(南温泉立交、苦竹坝立交)。 2.采购范围及相关要求 国 2.1 采购范围：纤维编绕拉挤电缆保护套管（BWFRP100/2.0，79158米）。 2.2 交货期：以甲方实际订单要求为准。 中 2.3 交货地点：重庆市巴南区新燕尾山项目甲方指定位置。 2.4 物资质量标准：满足国家法律法规、标准、规范、设计参数及技术规格书要求。 3.供应商资格要求 3.1 供应商应依法设立且满足如下要求： （1）资质要求：在中华人民共和国境内依法注册，具有独立法人资格、具有采购物资生产或供应经验的企业， 并且具有合法、有效的“三证合一”的营业执照,代理商需提供制造商授权委托书。 （2）财务要求：必须是经税务部门注册登记核准的一般纳税人，有依法纳税的良好记录，提供近三年的财务报 告。 （3）业绩要求：同类产品销售业绩不少于2个，并具备与本招标项目需求相适应的供货能力。 （4）信誉要求：本项目投标截止期前未被“信用中国”、“中国政府采购网”、中国交建物资采购管理信息系 统网站列入失信被执行人、违法案件当事人、违法失信行为记录名单。 （5）其他要求：提供运输方案及生产周期。 3.2 供应商不得存在下列情形之一： （1）处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； （2）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （3）已列入黑名单，且未解除限制期限； （4）其他： / 。 4.供应商报名 4.1有意参加询比采购活动的单位，请于2026年 8 月 20 日 11 时 00 分至2026 网 年 8 月 25 日 11 时 00 分（北京时间、下同），登录“中交招采网”（网 址：https://zjzcw.iccec.cn）进行报名并下载采购文件。 4.2 已在网并且已通过采购人层级供应商或已增加采购人为合作单位的供应商、上级供应商可直接参与询比采 务 购。在网平级单位供应商未增加采购人为合作单位需进行合作意向申请通过后参与询比采购。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择采购人，审核通过后方可参与询比 采购。 商 5. 供应商报价 5.1 报价结束（递交响应文件截止）时间：2026年 8 月 25 日 11 时 00 分。 道 5.2 供应商应在报价结束时间前，登录“中交招采网”进行线上报价并上传电子响应文件。逾期未完成上传的 电子响应文件，采购人将拒收。 5.3电子采购的供应商报价文件由线上电子报价表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 管 子报价表的数据为准。 6. 开标 6.1开标时间：与报价结国束时间相同。 6.2开标地点：本次采购在“中交招采网”平台线上开标，不举办现场开标，现场开标地点/。 7. 发布公告的媒介 中 本询比采购公告在中交招采网上发布。 8. 评审办法 本项目评审办法采用 经评审的最低价法 。 9. 合同主要条款 9.1 付款条件：无预付款，到货后办理结算，双方办理完结算手续、卖方提供符合合同要求的正式发票给买方 后60天，买方支付该批材料价值80%的货款，完工结算后支付至97%，剩余3%为质保金，质保期2年，两年后供 应方申请返还3%（无息）；银行转账、承兑、18个月供应链金融混合支付方式。 9.2履约保证金的递交： （1）□不要求递交 （2）要求递交 保证金金额：2万元 ； 保证金形式：银行转账、银行保函等电子保函；其他形式：无 。 10. 成交供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”（网址：https://zjzcw.iccec.cn）发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联 系4006765885中标服务费请按7咨询。 10.1收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： 网 （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； 务 （3）在1000万元（含）至3000万元之间的，每次收取1000元； （4）在3000万元（含）至1亿元之间的，每次收取3000元； （5）在1亿元（含）以上的，每次收取5000元。 商 10.2支付流程 （1）通知推送：中标结果发布后，系统自动道推送缴费通知（含应缴金额及支付链接）； （2）费用查询：供应商登录“中交招采网-服务管理”模块查看待支付费用； （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 管 （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网- 服务管理－发票下载”模块获取。 11.监督机构 国 监督机构名称：中交二航局科工（武汉）有限公司纪委监察部 举报电话：中027-82796466 举报邮箱：sneb_kggs@ccccltd.cn 12.其他 投标保证金采用银行转账形式的需转至中交二航局科工（武汉）有限公司账户（账 号：42001186108053006379-0006开户行：建行武汉长江支行，行号：105521000053），并备注二航科工燕尾山机 电照明项目纤维编绕管投标保证金。 13.联系方式 采购 人：中交二航局科工（武汉）有限公司 采购代理机构：中交二航局科工（武汉）有限公司 地 址：武汉市新洲区双柳街星谷大道158号地 址：武汉市新洲区双柳街星谷大道158号 邮政编码：430400 邮政编 码：430400 联系人：李鑫 联系人：毕明 月 电 话：18186145302 电 话：17853118573 电子邮件：18186145302@ccccltd.cn 电子邮件：bimingyue@ccccltd.cn 2026年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3076715.html cqdingjiu 2026.08.21 10:06:50 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N14" t="n">
         <v>90</v>
       </c>
@@ -1417,7 +1469,11 @@
           <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程变更公告 重庆巴南天然气有限责任公司 重庆国际生物城配套公寓项目天然气表后管道安装工程 变更公 告 公告编号： RQBGGG202608200006 本公司于2026年08月19日发布的重庆国际生物城配套公寓项目天然气表后管道安装工程公告（编 号：RQCGXY202608170010），现做出如下变更： 网 1、对采购文件第一卷“采购需求“中墙体管道暗埋的具体内容进行明确。墙体管道暗埋应包含墙体开槽，输送 用不锈钢波纹管及钢制槽板的安装，墙体恢复，暗埋管道视频记录。 2、对由响应供应商提供的钢制槽板的规格进行明确。钢制槽板为U型开口槽，采用热镀锌Q235B钢板，钢板厚度 务 不得小于1.2mm，尺寸不得小于U40*30*1.2（宽40mm,高30mm,壁厚1.2mm热镀锌） 3、对由响应供应商提供的F型不锈钢三通，材质可以选用黄铜进行替代。 4、采购文件第二卷“技术规范及要求“中增加T/CECS633-2019 《燃气用户工程不锈钢波纹软管技术规程》。 以上内容在合同中也同步进行调整。 商 除上述变更外，原公告其余内容仍有效。 道 重庆巴南天然气有限责任公司 管 2026-08-20 信息来源:https://www.chinapipe.net/project/d3076704.html cqdingjiu 2026.08.21 10:国06:50 中</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N15" t="n">
         <v>80</v>
       </c>
@@ -1484,7 +1540,11 @@
           <t>合川区中南片区污水管网工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目 合川区中南片区污水管网工程（一期） 名称 招标 网 法人 或招 标人 重庆市合川区住房和城乡建设委员会 名称 （盖 务 章） 项目 批准 文件 合川发改投〔2025〕19 号 商 及文 号 主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300-D800管道130米，新增检查井11座，新 主要 建D300排水管道38米；紫外光修复 D300-D道800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米， 建设 螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米，不锈钢快速锁修复 D1000管道42 内容 米；完成 D300-D1000管道清障189米、清淤2627米。 拟 招 招标文 合同预 招标 管 交 序 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 所 国 重 庆 市 合川 合 招标 区中 主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300- 川 项目 中 南片 D800管道130米，新增检查井11座，新建D300排水管道38米；紫外光修复 公 区 区污 D300-D800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米， 开 公 1 2026-09 1708.44 水管 螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米， 招 共 网工程 不锈钢快速锁修复 D1000管道42米；完成 D300-D1000管道清障189米、清 标 资 （一 淤2627米。 源 期） 交 易 中 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076543.html cqdingjiu 2026.08.21 10:06:50</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>D800管道：130米；D300排水管道：38米；D800排水管道：755米；D1600管道：73米；D800排水管道：125米；D800排水管道：712米；D1000管道：42米；检查井：11座；管道：189米</t>
+        </is>
+      </c>
       <c r="N16" t="n">
         <v>90</v>
       </c>
@@ -1547,7 +1607,11 @@
           <t>重庆市自来水有限公司球墨铸铁管及管件2026-2027(2年)采购项目(第二次)答疑补遗文件 重庆市自来水有限公司球墨铸铁管及管件2026-2027（2年）采购项目（第二次）答疑 提问1：样品20CM长含承口吗？如果含承口20CM那就太短，标识LOGO无法体现完整建议≥20CM 答1：球墨铸铁管样品含承口，样品长度≥20CM 网 务 招标人：重庆市自来水有限公司 招标代理机构：重庆水务集团公用工程咨询有限公司 商 2026年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d30道76446.html cqdingjiu 2026.08.21 10:06:50 管 国 中</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N17" t="n">
         <v>80</v>
       </c>
@@ -1614,7 +1678,11 @@
           <t>大足区中心城区和龙水镇市政公共排水设施运维(材料)更正一号公告 一、更正项 更正项 更正子项 更正前内容 更正后内容 网上投标 网上投标截止时间 2026-08-20 15:00:00 2026-08-25 15:00:00 递交投标响应文件 线下递交投标（响应）文件开始时间 2026-08-20 14:30:00 2026-08-25 14:30:00 递交投标响应文件 线下递交投标（响应）文件截止时间 2026-08-20 15:00:00 2026-08-25 15:00:00 网 开标 开标时间 2026-08-20 15:00:00 2026-08-25 15:00:00 招标采购（附件） 附件 务 二、补遗更正说明 清单限价重新做调整，开标时间已更正，详见更正文件内容 商 三、联系方式 采购执行方： 道 单位名称：重庆誉双项目管理有限公司 联系人：陈老师 联系电话：13996336872 采购需求方： 管 单位名称：重庆市大足区茂泰市政工程有限公司 联系人：谢老师 联系电话：18523539371 信息来源:https://www.chinapipe.net/project/d3076319.html 国 cqdingjiu 2026.08.21 10:06:50 中</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N18" t="n">
         <v>80</v>
       </c>
@@ -1681,7 +1749,11 @@
           <t>璧山区2026年大路街道三台村智慧设施农业建设项目招标计划表 重庆市工程建设项目招标计划表 项目 璧山区2026年大路街道三台村智慧设施农业建设项目 名称 招标 法人 或招 网 标人 中农良品（重庆）生态农业有限公司 名称 （盖 章） 项目 批准 务 文件 及文 号 主要 1.新建茄果类智能种植温室11256平方米；2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、二氧化碳补施系统1套、智能环境控制系统1套、作业物流 建设 装备1套；3.项目后勤及仓储配套（含装修）5000平方米；4.土方回填及场地平整53000平方米；5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米；6. 内容 都市农文旅配套建设1000平方米。 商 招 拟 标 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 称 道 璧 山 区2026 重 年 庆 大 市 路 公 招标 街 管 共 项目 道 资 三 公 源 台 项目主要建设内容包括：1.新建茄果类智能种植温室11256平方米； 2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、 开 交 1 村 二氧化碳补施系统1套、智能环境控制系统1套、作业物流装备1套； 3.项目后勤及仓储配套（含装修）5000平方米； 4.土方回填及场地平整53000平 2026-09 9182.25 招 易 智 方米； 5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米； 6.都市农文旅配套建设1000平方米。 标 中 慧 心 设 国 璧 施 山 农 分 业 中 建 心 设 项 目 中 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076777.html cqdingjiu 2026.08.21 10:06:51</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>水渠管网：1387米</t>
+        </is>
+      </c>
       <c r="N19" t="n">
         <v>80</v>
       </c>
@@ -1748,7 +1820,11 @@
           <t>长寿区江南街道污水处理厂更新改造工程项目公告 长寿区江南街道污水处理厂更新改造工程比选公告 1. 比选条件 本比选项目长寿区江南街道污水处理厂更新改造工程，比选人为重庆环保投资集团有限公司，资金来源为企业 自筹，出资比例为100%。现对该项目进行公开比选，诚邀有兴趣的潜在参选人参与比选。 2. 项目概况与比选范围 网 2.1项目概况：长寿区江南街道污水处理厂更新改造工程包括但不限于以下内容新建混凝池-三沉池；还建格栅池； 厌氧池新增搅拌机，好氧池联通孔短流整改、拆除填料及底部曝气盘，增设可提升曝气系统；原斜管沉淀池改 造为二沉池（新增中心筒、改造成多斗排泥、提高液位，更换三角堰）。拆除原有污泥池，新增临时污泥储罐 务 并还建污泥池；污泥堆场临时改建及恢复；实施技改期间的临时排放工程；进行基础的自控改造。 2.2 比选范围：长寿区江南街道污水处理厂更新改造工程施工图范围中的所有工作内容，包括但不限于土建工 程、设备及安装工程、工艺管道工程、电气工程、临排工程等内容，具体以比选人提供的图纸、技术规范、设 备需求清单、答疑资料、澄清资料、其他补遗资料等相关商内容为准。 2.3 建设地点：重庆市长寿区江南街道。 2.4 工期：110日历天（实际开工日期以监理工道程师签发的工程开工通知明确的开工日期为准），缺陷责任期24 个月。 3. 参选人资格要求 管 3.1 本次比选要求参选人具备以下条件： （1）独立法人资格； （2）建设行政主管部国门颁发的有效的市政公用工程施工总承包二级及以上资质； 3.2 参选人还应在资质、业绩、资金、人员等方面具有相应的服务能力，详见比选文件第二章参选人须知前附 表第1.4.1项内容。 中 3.3本次比选不接受联合体参选。 4. 比选文件的获取 4.1 参选人于2026年8月19日起可自行在重庆水务集团电子商务平台（https://www.cqswjt.cn）上下载比选文件电 子版，以及答疑、补遗等比选截止时间前公布的所有相关资料，不管参选人下载与否，比选人和代理机构都视 为参选人收到以上资料并全部知晓有关比选过程和事宜，如因参选人自身原因未能下载相关资料由此产生的一 切后果由参选人自行负责。各参选单位应随时关注网上（https://www.cqswjt.cn）发布的比选文件及相关修改内容。 4.2 参选人须在重庆水务集团电子商务平台（https://www.cqswjt.cn）进行供应商注册，填写相关信息，审批过后 成为平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标（仍须同时提交纸质版参选文件）。参选 人需提前在重庆水务集团电子商务平台（https://www.cqswjt.cn）上注册、报名，下载比选文件，上传参选文件电 子档并报价。在比选截止时间前未按时报名、报价并上传参选文件电子档、递交纸质版参选文件者，将被否决 参选。 5. 比选文件的递交 5.1 参选文件递交时间：2026年8月 27 日09时00分至09时30分，地点：重庆市两江新区嘉华路36号重庆水务 大厦5楼。 5.2 比选截止时间：2026年8月 27 日09时30分（北京时间）。 5.3 逾期送达的或者未送达指定地点的参选文件，比选人不予受理。 6. 发布比选公告的媒介 本次比选公告在重庆水务集团电子商务平台（https：//www.cqswjt.cn）上发布。 7. 联系方式 比选人：重庆环保投资集团有限公司 地 址：重庆市两江新区礼环南路102号 网 联系人：曹老师 电话：023-71618725 务 代理机构：重庆招标采购（集团）有限责任公司 地址：重庆市江北区五简路2号重庆咨询大厦A座2004室 商 联系人：高老师 电话：023-67706841 道 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 管 信息来源:https://www.chinapipe.net/project/d3076456.html cqdingjiu 2026.08.21 10:06:51 国 中</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N20" t="n">
         <v>90</v>
       </c>
@@ -1815,7 +1891,11 @@
           <t>潼南区新胜镇、双江镇污水处理厂更新改造工程项目项目公告 潼南区新胜镇、双江镇污水处理厂更新改造工程比选公告 1. 比选条件 本比选项目潼南区新胜镇、双江镇污水处理厂更新改造工程，比选人为重庆环保投资集团有限公司，资金来源 为企业自筹，出资比例为100%。现对该项目进行公开比选，诚邀有兴趣的潜在参选人参与比选。 2. 项目概况与比选范围 网 2.1项目概况：潼南区新胜镇污水处理厂更新改造工程，主要建设内容为新增200m?/d一体化污水处理设备基础； 更新现有污水处理系统设备，提高现有沉淀池二沉池、三沉池液位；升级处理系统（干化池改建为污泥池，新 增叠螺脱水机，改建污泥堆场及雨棚）；新建风机房－配电室防尘防渗地坪。潼南区双江镇污水处理厂更新改 务 造工程，主要建设内容为将原有斜管沉淀池改建为好氧池，新建3座竖流沉淀池，配套安装相关设备；更新污水 处理系统中老旧及故障设备；新建储药加药区与一体化危废储存间，完善污水处理配套设施。 2.2 比选范围：潼南区新胜镇、双江镇污水处理厂更新改造工程施工图范围中的工作内容（一体化设备采购及 相关安装工作除外），包括但不限于土建工程、附属工程商（包括但不限于绿化工程、工艺管线工程、电气及自 控工程、临排清淤工程等）、一体化污水处理设备基础、标准化建设、配套设备材料采购及安装工程等内容， 其中一体化设备采购及相关安装工作不在本次比选范围内；具体以比选人提供的图纸、技术规范、工程量清单、 答疑资料、澄清资料、其他补遗资料等相关内容为准。 道 2.3 建设地点：潼南区新胜镇、双江镇。 2.4 工期：120日历天（实际开工日期以监理工程师签发的工程开工通知明确的开工日期为准），缺陷责任期24 个月。 管 3. 参选人资格要求 3.1 本次比选要求参选人具备以下条件： 国 （1）独立法人资格； （2）建设行政主管部门颁发的有效的市政公用工程施工总承包二级及以上资质； 中 3.2 参选人还应在资质、业绩、资金、人员等方面具有相应的服务能力，详见比选文件第二章参选人须知前附 表第1.4.1项内容。 3.3本次比选不接受联合体参选。 4. 比选文件的获取 4.1 参选人于2026年8月19日起可自行在重庆水务集团电子商务平台（https://www.cqswjt.cn）上下载比选文件电 子版，以及答疑、补遗等比选截止时间前公布的所有相关资料，不管参选人下载与否，比选人和代理机构都视 为参选人收到以上资料并全部知晓有关比选过程和事宜，如因参选人自身原因未能下载相关资料由此产生的一 切后果由参选人自行负责。各参选单位应随时关注网上（https://www.cqswjt.cn）发布的比选文件及相关修改内容。 4.2 参选人须在重庆水务集团电子商务平台（https://www.cqswjt.cn）进行供应商注册，填写相关信息，审批过后 成为平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标（仍须同时提交纸质版参选文件）。参选 人需提前在重庆水务集团电子商务平台（https://www.cqswjt.cn）上注册、报名，下载比选文件，上传参选文件电 子档并报价。在比选截止时间前未按时报名、报价并上传参选文件电子档、递交纸质版参选文件者，将被否决 参选。 5. 比选文件的递交 5.1 参选文件递交时间：2026年8月27日09时00分至09时30分，地点：重庆市两江新区嘉华路36号重庆水务大厦5 楼。 5.2 比选截止时间：2026年8月27日09时30分（北京时间）。 5.3 逾期送达的或者未送达指定地点的参选文件，比选人不予受理。 6. 发布比选公告的媒介 本次比选公告在重庆水务集团电子商务平台（https：//www.cqswjt.cn）上发布。 7. 联系方式 网 比选人：重庆环保投资集团有限公司 地 址：重庆市两江新区礼环南路102号 务 联系人：陈老师 电话：023-42756696 商 代理机构：重庆招标采购（集团）有限责任公司 道 地址：重庆市江北区五简路2号重庆咨询大厦A座2004室 联系人：高老师 管 电话：023-67706841 重庆水务电子商务平台国咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3076454.html cqdingjiu 2026.08.21 10:06:51 中</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N21" t="n">
         <v>90</v>
       </c>
@@ -1878,7 +1958,11 @@
           <t>重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表 重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表 采购需求单位(全称) 重庆医科大学附属第二医院总务科 项目名称 重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程 项目内容 给重庆医科大学附属第二医院医疗教学配套业务用房配置第二市政水源 采购预算 409674.71元 网 拟采购供应商全称 东部自来水分公司 配套业务用房第二市政水源从重庆水资源产业股份有限公司东部自来水分公司管辖范围 单一来源采购理由 的管网具体接入，属于市政管网施工，具有特殊要求。 务 公示时间 2026年8月19日-2026年8月25日 联系人及联系电话 刘老师 023-63693215 注：1.以上陈述是否真实，欢迎社会各界监督，公示时间商至少5个工作日； 2.公示期内无异议的，采购管理处将进行该项目采购；有异议请将意见反映采购人。 信息来源:https://www.chinapipe.net/project/d30道76334.html cqdingjiu 2026.08.21 10:06:51 管 国 中</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N22" t="n">
         <v>80</v>
       </c>
@@ -1945,7 +2029,11 @@
           <t>中铁二院工程集团有限责任公司G319黔江区正阳至城西段改建工程管线探测工作线上询价采购公告 中铁二院工程集团有限责任公司G319黔江区正阳至城西 段改建工程管线探测工作线上询价采购 ZTEYCQ-XJ-2026-019 网 采购单位: 中铁二院工程集团有限责任公司 发布时间: 2026-08-19 16:10 报价截止时间: 务 2026-08-21 17:00 招标方联系人: 杨先生 招标方联系电话: 商 13883021521 招标方邮箱: 监督方联系人: 李先生 道 监督方联系电话: 15823237919 监督方邮箱: 保证金: 0元 管 结算与发票信息: 详情 交货信息: 详情 国 其他说明事项: 标的明细 流水号：询2026081900304 中 计量单 技术标准及要 序号 标的名称 数量 交货期 送货地址 位 求 G319黔江区正阳至城西段 合同签订后5天内完成 西南区-重庆市-市辖 1 1 项 详见询价文件 改建工程管线探测工作 本项目服务内容。 区-黔江区-项目地点 信息来源:https://www.chinapipe.net/project/d3076309.html cqdingjiu 2026.08.21 10:06:51</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N23" t="n">
         <v>80</v>
       </c>
@@ -2012,7 +2100,11 @@
           <t>乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告 乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告 1.招标条件 本招标项目乌江涪陵榨菜绿色智能化生产基地(一期)已由重庆市涪陵区发展和改革委员会以重庆市企业投资项目 备案证2020-500102-13-03-000003 批准建设，项目业主为重庆市涪陵榨菜集团股份有限公司，建设资金来自企业 自筹，项目出资比例为100% ，招标人为重庆市涪陵榨菜集团股份有限公司。项目已具备招标条件，现对乌江 涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 2.1 建设地点： 重庆市涪陵区马鞍街道人和社区 。 网 2.2 项目概况与建设规模：建筑面积约369384.27㎡。本项目蒸汽管道主要为室外蒸汽管道φ219x6mm，管道材质： 20#地上敷设，由14#锅炉房分汽缸分别接至6#和8#智能化车间分汽缸，蒸汽管道运行压力1.08MPa，管道设计压 力1.2MPa。 务 2.3 本次招标项目合同估算金额：580.643717万元。 2.4 招标范围： 商 （1）蒸汽管道系统本体：从锅炉房分汽缸后（含分气缸阀门）至6#车间、8#车间分气缸处，所有蒸汽管道、管 件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸等的采购、运输、安装、保温（含保温层及保 护层）工作。 道 （2）钢结构桁架工程：负责本项目范围内所有钢结构架空桁架（管廊）的采购、运输、制作、安装、防腐工作。 （3）管道附件及控制系统：负责本工程范围内所有阀门、压力表、温度表、流量计、电动/气动执行机构以及配 套仪表电缆、桥架、保护管的采购、运输、安装、接线。负责与DCS/PLC系统接口的接线与联动调试。 管 （4）调试与验收：组织并确保整个蒸汽管道系统（含分气缸后段末端管道、桁架及其安全附件）通过项目所在 地特种设备安全监察管理部门实施的安装监督检验。负责报检、配合现场检验、整改、出具深化图纸并由设计 单位审核盖章、特种设备法定报检取证的全部费用，包括但不限于：施工前办理安装告知，设计院盖章审核， 施工中接受并通过安装国监督检验，最终负责取得《压力管道安装监督检验证书》与《特种设备使用登记证》， 确保蒸汽管道投入使用并备案，提交全套法定检验报告。 （5）土建工作部分 中 1）管架和桁架基础的施工，包括但不限于钢结构桁架的混凝土独立基础的土方开挖、浇筑、养护及回填恢复。 2）管道穿墙/板孔洞的开挖、封堵与修复。 3）室内外地面的开挖（包括但不限于疏水井、沟槽开挖、通行地沟、设备基础开挖）与恢复（包括但不限于土 方回填、渣土弃运、地面硬化）。 4）桁架及设备接地线的施工，包括但不限于接地极制作、接地干线敷设，并与厂区主接地网可靠连接，接地电 阻测试合格。 具体详见施工图、招标文件、工程量清单、答疑补遗等资料。 2.5 工期要求： 60 日历天 缺陷责任期要求： 24 个月 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：投标人应同时具备以下(1)、(2)项资质： （1）具备建设行政主管部门颁发的有效的建筑工程施工总承包二级及以上资质； （2）具备有效的《中华人民共和国特种设备生产许可证》（许可子项目：工业管道安装GC2级及以上）。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 网 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 务 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（涪陵区） （https://www.cqggzy.com/fulingweb/）下载招标文件、工程商量清单、电子图纸等资料。参与投标的投标人需在重 庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏 “主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网（涪陵区道）（https://www.cqggzy.com/fulingweb/）本项目招标公告网页下 方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-23 17:00:00前。 4.3招标人应于2026-08-24 18:00:00前在重庆市公共资源交易网（涪陵区）（https://www.cqggzy.com/fulingweb/）发 布澄清。 5.投标文件递交的内容 管 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-09 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 国 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（涪陵区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 中重庆市涪陵榨菜集团股份有限公司 代理机构: 中招国际招标有限公司 重庆两江新区黄山大道中段53号5-1（双 地 址: 重庆市涪陵区江北街道办事处二渡村一组 地 址: 鱼座A栋5楼） 邮 编: 408000 邮 编: 项目负责人: 徐老师 项目负责人: 寿云凤 电 话: 13212467016 电 话: 023-68881331-9032 传 真: 传 真: 电子邮箱: bsd2me@126.com 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市涪陵区发展和改革委员会 电 话: 023-72203687 2026年08月19日 乌江 涪陵 榨菜 绿色 智能 化生 产基地 (一 期)6#、 8#车 网 间蒸 汽管 道安 装工 务 程 中 中 国 国 重 银 重 商民 重 庆 行 庆 生 庆 涪 股 涪 银 涪 陵 份 陵 行 陵 重 投 公 有 道公 股 公 庆 标 共 限 共 份 共 银 开 保 户 资 公 资 有 资 行 户 证 110292140553VA00154 9902001860445897 430102029007791845-275 名 源 司 源 限 源 涪 行 金 交 重 交 公 交 陵 账 管 易 庆 易 司 易 支 号 有 涪 有 重 有 行 限 陵 限 庆 限 公 马 公 涪 公 国 司 鞍 司 陵 司 支 支 行 行 中 信息来源:https://www.chinapipe.net/project/d3076300.html cqdingjiu 2026.08.21 10:06:51</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>蒸汽管道：1.08M</t>
+        </is>
+      </c>
       <c r="N24" t="n">
         <v>95</v>
       </c>
@@ -2079,7 +2171,11 @@
           <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程询比采购公告 采购公告 公告编号： RQXYGG202608190057 一、采购项目基本情况 采购人：重庆巴南天然气有限责任公司 网 采购项目编号：RQCGXY202608170010 采购项目名称：重庆国际生物城配套公寓项目天然气表后管道安装工程 务 采购内容和范围：完成重庆国际生物城配套公寓项目 （民用1020户）天然气表后管道定制化服务。（含安装燃 气输送用不锈钢波纹管RSB-IF-13—12240米（预估）、双外螺纹球阀DN15-1020个、燃气管道自闭阀DN15-1020个， 其它配套管件及辅材，墙体管道暗埋等） 二、供应商资格要求 商 1. 资质要求:资质要求： 1.响应供应商为中华人民共和国境内合法注册的独立法人或其他组织，具有独立承担民事责任能力，具有独立订 立合同的权利。 道 2.响应供应商应具备市政公用工程施工总承包三级及以上资质、具备有效的安全生产许可证。 3.响应供应商应为本项目配备项目负责人一名，持有市政公用工程或机电工程专业二级建造师及以上资质，且为 本单位在职人员并提供社保证明。 4.响应供应商应为本项目配备专职安全员一名，持有安全生产考核合格C证，且为本单位在职人员并提供社保证 管 明。 5.项目负责人及专职安全员社保证明期限须包含2026年5月至2026年7月。提供的社保证明，须体现上述人员的姓 名、身份证号（或社保号）、单位名称、本单位参保时间（或起始参保时间），并带有社保部门公章或社保部 门的有效电子印章。 2. 信用要求:6.信用要求国： （1）响应供应商（含联合体响应的成员单位）未被“国家企业信用信息公示系统” 网站（www.gsxt.gov.cn）列 入严重违法失信企业名单（如：提供网站查询界面截图）； （2）响应供应商（含联合体响应的成员单位）未被 “信用中国”网站（www.creditchina.gov.cn）列入严重失信 主体名单（中如：提供网站查询界面截图）。 三、采购文件的获取 采购文件在 华润守正采购交易平台 发布，不再另行线下提供纸质采购文件，凡有意参与者请自行登录守正平台 查看和下载采购文件。 四、响应文件的提交 响应文件提交 / 报价截止时间： 2026-08-25 08:00:00 （北京时间，若有变化另行通知）。 响应文件提交 / 报价方式：在响应文件提交 / 报价截止时间前，通过 华润守正采购交易平台 提交电子响应文件或 报价，逾期提交将被拒收。 五、采购人联系方式 联系人：何俊 电话：15178855716 邮箱：1460553040@qq.com 六、采购明细 行号 采购内容 需求数量 单位 补充说明 1 重庆国际生物城配套公寓项目天然气表后管道定制化服务 1 元/次 具体内容详见采购文件 七、答疑澄清、通知 答疑澄清、通知等文件一经在 华润守正采购交易平台 发布，视为已发放给相应供应商（发放时间即为发出时 间），请随时关注 华润守正采购交易平台 发布的相关信息，并及时查阅和处理。 八、服务费交纳 网 本项目向成交人收取服务费,供应商收到预成交通知书和服务费交款通知书10日内,向平台运营方(华润守正招标有 限公司)支付服务费,经确认无误后由采购人发送成交通知书。平台运营方在收到服务费后向成交人开具服务费发 票。 收费标准：项目总成交金额＜50万元的采购项目，免收服务费。项目总成交金额≥50万元的采购项目，按成交金 务 额的0.15%向成交人收取（金额四舍五入，精确到分）。单项目总收费封顶100000元。其他说明：（1）总价采购， 收费基数为成交金额；单价、费率采购，收费基数为预算金额。（2）单项目存在多个成交人情形的，按总成交 金额计算收费总额，各成交人按成交比例分摊；项目总成交金额50万以上，但单个成交人成交金额少于50万仍按 比例收取服务费。 商 退款说明：成交通知书发布后,平台提供相关服务已完成,成交人已交纳服务费不予退还。 多成交人服务费收取示例： 以某项目总成交金额100万为例,A、B、C多成交人情形,总服务费为0.15万, 供应商A成交金额为50万,A服务费为0.075万; 供应商B成交金额为30万,B服务费为0.045万; 道 供应商C成交金额为20万,C服务费为0.03万。 九、其它事项 管 1.本公告在 华润守正采购交易平台 ( https://www.szecp.com.cn/ )上公开发布。 2.本项目采购通过守正平台线上进行，供应商需注册 华润守正采购交易平台 ，通过平台进行响应文件的递交或 报价，具体操作步骤可查阅网站首页帮助中心的操作手册，也可以联系守正客服。 国 3.如对采购项目有异议，请登录 华润守正采购交易平台 ,通过异议菜单提出。 2026年08月19日 中 信息来源:https://www.chinapipe.net/project/d3076125.html cqdingjiu 2026.08.21 10:06:52</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N25" t="n">
         <v>80</v>
       </c>
@@ -2142,7 +2238,11 @@
           <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)非金属管道管件阀门采购招标公告 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采购招标公告 1、招标条件 本招标项目废盐综合利用联产20万吨/年离子膜烧碱项目已由重庆市长寿区发展和改革委员会以 重庆市企业投 资项目备案证（2207-500115-04-05-168305）批准建设，项目业主为重庆市映天辉氯碱化工有限公司，建设资金来 自业主自筹，项目出资比例为100%，招标人为重庆市映天辉氯碱化工有限公司。项目已具备招标条件，现对本 项目的（一期12万吨/年）非金属管道管件阀门采购进行公开招标。 网 2、项目概况 2.1 建设地点：重庆长寿经济技术开发区化北路2号。 务 2.2、项目概况与建设规模： 重庆市映天辉氯碱化工有限公司（以下简称“映天辉”）位于重庆长寿经济技术开发区化北路2号，始建于2004 年5月，占地430亩，注册资本34800万元。现为国有控股企商业，是一家集氯碱生产经营、新材料研发经营于一体 的专业型、科技型综合企业，系国家级高新技术企业。 映天辉作为长寿经开区氯碱产业基础平台的龙头化工企业，现有一条氯碱生产线，生产规模为20万吨/年烧碱 （折100%NaOH计）。为建设并贯通氯碱化工道循环经济产业链，保障下游产业链装置氯气需求，实现氯碱产品的 升级和高端化发展，增加产品附加值，降低成本，提高竞争力，映天辉公司经过充分调研和反复论证后，拟开 展废盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）建设。装置在正常运行情况下，按照每年 8000 小时操作。具体要求及参数以第五章货物需求一览表及技术规格标准和要求为准。 管 2.3 本次招标项目货物采购估算金额： 约 330 万元。 2.4招标范围： 本次招标项目为：“废国盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采 购”包括不限于非金属管道管件阀门所含设计、制造、试验、出厂检验、防腐、运输（含保护、包装及运输、 货到现场车板交货）、保险（交货验收前）、指导安装、调试、备件及专用工具、税费、技术资料和图纸及质 保期内的各种备品、备件的供应及相关的技术服务、产品质量证明书及原材料检测报告等。（详见“第五章货 物需求一览中表及技术规格标准和要求”）。 2.5 交货地点：货物运送至买方指定地点； 2.6 交货期： 2.6.1合同签订后3个月内，所有货物运送招标人现场并具备安装条件。 2.6.2 中标方应于合同签订之日起7天内，向买方提交完整的技术资料，以供设计院开展相关设计工作。 3、投标人资格要求 3.1 投标人应符合以下要求： （1）投标人具备有效的营业执照。 注：不得将投标人营业执照记载的经营范围作为评审因素。 （2）投标人具备有效的《中华人民共和国特种设备生产许可证》压力管道管子-B级及以上资质、压力管道管 件B2级及以上资质； （3）投标人具备塑料管道管子、管件的型式试验证书。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3本次招标不接受代理商投标，不接受联合体投标。 4. 招标文件的获取 4.1 凡愿意参加的潜在投标人，从2026年 8 月19 日起至投标截止时间前，均可登录重庆市公共资源交易网 （www.cqggzy.com）直接下载获取招标文件、答疑等开标前的有关资料。在公告期间，各投标人应随时关注网上 发布的招标文件答疑、补遗、澄清等文件内容，不管投标人是否下载，均视为已知晓招标文件的全部内容和有 关事宜。本项目不需要报名，直接投标。 网 5.投标文件的递交 5.1 投标文件递交的截止时间为 2026年 9 月10 日上午09时30分，地点在重庆市公共资源交易中心开标厅（地 址：重庆市两江新区青枫北路6号渝兴广场B10栋2层），具体开标地点详见一、二楼大厅显示屏。 务 5.2逾期送达的或者未送达指定地点的，或者未按照招标文件要求密封的投标文件，招标人将拒收。 6、发布公告的媒介 商 本次招标公告在中国招标投标公共服务平台、重庆市公共资源交易网上发布。 7、联系方式 道 招 标 人：重庆市映天辉氯碱化工有限公司 地 址：重庆长寿经济技术开发区化北路二号 管 联 系 人：张先生 电 话：023-40717888 国 招标代理机构： 重庆招标采购（集团）有限责任公司 地 址：重庆市两江新区五里店五简路2号重庆咨询大厦A栋20楼2001室 中 项目负责人：彭文婷 电 话： 023-67703002 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采购 户名 开户行 投标保证金账号 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000631258 支行 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051303372 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630010400 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000002549 贸易试验区分行 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835014652 坝支行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146619529 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764260665 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020038958 信息来源:https://www.chinapipe.net/project/d3076119.html cqdingjiu 2026.08.21 10:06:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N26" t="n">
         <v>85</v>
       </c>
@@ -2205,7 +2305,11 @@
           <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)衬氟管道及管件采购招标公告 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）衬氟管道及管件采购招标公告 1、招标条件 本招标项目废盐综合利用联产20万吨/年离子膜烧碱项目已由重庆市长寿区发展和改革委员会以 重庆市企业投 资项目备案证（2207-500115-04-05-168305）批准建设，项目业主为重庆市映天辉氯碱化工有限公司，建设资金来 自业主自筹，项目出资比例为100%，招标人为重庆市映天辉氯碱化工有限公司。项目已具备招标条件，现对本 项目的（一期12万吨/年）衬氟管道及管件采购进行公开招标。 网 2、项目概况 2.1 建设地点：重庆长寿经济技术开发区化北路2号。 务 2.2、项目概况与建设规模： 重庆市映天辉氯碱化工有限公司（以下简称“映天辉”）位于重庆长寿经济技术开发区化北路2号，始建于2004 年5月，占地430亩，注册资本34800万元。现为国有控股企商业，是一家集氯碱生产经营、新材料研发经营于一体 的专业型、科技型综合企业，系国家级高新技术企业。 映天辉作为长寿经开区氯碱产业基础平台的龙头化工企业，现有一条氯碱生产线，生产规模为20万吨/年烧碱 （折100%NaOH计）。为建设并贯通氯碱化工道循环经济产业链，保障下游产业链装置氯气需求，实现氯碱产品的 升级和高端化发展，增加产品附加值，降低成本，提高竞争力，映天辉公司经过充分调研和反复论证后，拟开 展废盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）建设。装置在正常运行情况下，按照每年 8000 小时操作。具体要求及参数以第五章货物需求一览表及技术规格标准和要求为准。 管 2.3 本次招标项目货物采购估算金额： 约225万元。 2.4招标范围： 本次招标项目为：“废国盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）衬氟管道及管件采购一批” 包括但不限于制造、涂漆、包装、运输、配合验收工作、检验检测、产品质量证明书等。（详见“第五章货物 （材料）需求一览表及技术规格标准和要求”）。 2.5 交货地点：货物运送至买方指定地点； 中 2.6 交货期： 2.6.1合同签订后 3个月内，所有货物运送招标人现场并具备安装条件。 2.6.2 中标方应于合同签订之日起7天内，向招标方提交完整的技术资料，以供设计院开展设备相关设计工作。 3、投标人资格要求 3.1 投标人应符合以下要求： （1）投标人具备有效的营业执照。 注：不得将投标人营业执照记载的经营范围作为评审因素。 （2）具备有效的《中华人民共和国特种设备生产许可证》-压力管道元件制造-元件组合装置。 （3）具有防腐管道元件特种设备型式试验证书。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3本次招标不接受代理商投标，不接受联合体投标。 4、招标文件的获取 4.1 凡愿意参加的潜在投标人，从2026年8 月 19 日起至投标截止时间前，均可登录重庆市公共资源交易网 （www.cqggzy.com）直接下载获取招标文件、答疑等开标前的有关资料。在公告期间，各投标人应随时关注网上 发布的招标文件答疑、补遗、澄清等文件内容，不管投标人是否下载，均视为已知晓招标文件的全部内容和有 关事宜。本项目不需要报名，直接投标。 5、投标文件的递交 5.1 投标文件递交的截止时间为 2026年 9 月 10 日上午09时30分，地点在重庆市公共资源交易中心开标厅 （地址：重庆市两江新区青枫北路6号渝兴广场B10栋2层），具体开标地点详见网一、二楼大厅显示屏。 5.2逾期送达的或者未送达指定地点的，或者未按照招标文件要求密封的投标文件，招标人将拒收。 6、发布公告的媒介 务 本次招标公告在 中国招标投标公共服务平台、重庆市公共资源交易网上发布。 7、联系方式 商 招 标 人：重庆市映天辉氯碱化工有限公司 地 址：重庆长寿经济技术开发区化北路二号 道 联 系 人：张先生 电 话：023-40717888 管 招标代理机构： 重庆招标采购（集团）有限责任公司 地 址：重庆市两江新区国五里店五简路2号重庆咨询大厦A栋20楼2001室 项目负责人：彭文婷 电 话： 023-67703002 中 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）衬氟管道及管件采购 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630011190 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835003139 坝支行 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000000834 贸易试验区分行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146638621 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051302432 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000620855 支行 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020013554 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764235261 信息来源:https://www.chinapipe.net/project/d3076111.html cqdingjiu 2026.08.21 10:06:52</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N27" t="n">
         <v>85</v>
       </c>
@@ -2272,7 +2376,11 @@
           <t>重庆市益康环保工程有限公司永川分公司蒸汽管道改造项目询价采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3076108.html cqdingjiu 2026.08.21 10:06:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N28" t="n">
         <v>60</v>
       </c>
@@ -2339,7 +2447,11 @@
           <t>南岸区融侨大道、江南大道片区2023年排水管网改造项目(三标段)招标计划表 重庆市工程建设项目招标计划表 项目名 南岸区融侨大道、江南大道片区 2023年排水管网改造项目（三标段） 称 网 招标法 人或招 重庆市南岸区城市建设发展（集团）有限公司 标人名称 （盖章） 务 项目批 准文件 南岸发改〔2024〕304《南岸区融侨大道、江南大道片区2023年排水管网改造项目总投资概算的批复》 及文号 主要建 包括改造市政混接点194个，改造管网8582米，商管径d300~d1500;缺陷管网开挖修复1355米，管 设内容 径d300~d600;非开挖修复8679米，管径d300~d1200。 招标文件 拟交 合同预估 招标内 招标 序号 招标项目名称 计划发布 易场 金额(万 备注 道容 方式 时间 所 元) 51处雨 污混错 重庆 招标项 接点位 管 市公 目 改 南岸区融侨大道、江南大道片区 2023年排 公开 共资 1 造，1082 2026-08 6600.00 水管网改造项目（三标段） 招标 源交 个管网 易中 三四级 国 心 缺陷修 复。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 中 信息来源:https://www.chinapipe.net/project/d3076097.html cqdingjiu 2026.08.21 10:06:52</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>管网：8582米；缺陷管网：1355米</t>
+        </is>
+      </c>
       <c r="N29" t="n">
         <v>80</v>
       </c>
@@ -2406,7 +2518,11 @@
           <t>中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购公告 永川三教水厂项目 已具备采购条件，现公开邀请供应商参加询比采购活动。 1.采购项目简介 1.1 采购项目名称：中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购。 1.2 采购方案编号：FA00000663117。 网 1.3 采购人：中交一公局重庆工程有限公司。 1.4 采购代理机构：/。 务 1.5 采购项目资金：已落实 1.6 采购项目概况： 商 永川三教水厂项目：项目位于永川区三教镇，项目占地面积41673.42㎡（62.51亩），总建筑面积6078.71㎡，新建 净水厂1座，规模5万吨/天，新建厂外管网4.6km（DN200～DN1000），配套建设净水处理系统、排泥水处理系统、 综合楼、生产建（构）筑物以及附属建筑物等。项目合同额1.7亿元，工期450天。 道 项目地址：重庆市永川区。 2.采购范围及相关要求 管 2.1 采购范围：钢筋混凝土排水管。 2.2 交货期：2026年9月-2026年12月。 2.3 交货地点：重庆市永国川区项目指定地点。 2.4 物资质量标准：满足《混凝土和钢筋混凝土排水管》（GB/T 11836-2023）的相关要求。 3.供应商资格要求 中 3.1 供应商应依法设立且满足如下要求： （1）资质要求：本次询比采购要求供应商须是在中华人民共和国境内依法注册，具有合法有效的营业执照、税 务登记、组织机构代码等证件，具有独立法人资格、具有采购物资生产经营范围的生产商或代理商（销售商）。 （2）财务要求：供应商必须是经税务部门注册登记核准的纳税人，有依法纳税的良好记录。 （3）业绩要求：无。 （4）信誉要求：无不良履约记录、未列入工程所在地质量监督部门和中国交建、中交一公局集团企业黑名单。 因质量原因被交通部质监站通报，正在进行整改的生产厂家和产品不得参与投标。生产商或代理商（销售商） 具有良好的社会信誉，近3年内没有与骗取合同有关的犯罪或严重违法行为而引起的诉讼和仲裁；近3年不曾在合 同中严重违约或被逐；财产未被接管或冻结，企业未处于禁止或取消投标状态；在最高人民法院、信用中国 （www.creditchina.gov.cn）或各级信用信息共享平台查询拟入库单位无不良行为记录。 （5）其他要求：无。 3.2 供应商不得存在下列情形之一： （1）处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； （2）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （3）已列入黑名单，且未解除限制期限； （4）其他：无。 4.供应商报名 4.1 有意参加询比采购活动的单位，请于2026年8月19日15时00分至2026年8月26日17时00分（北京时间，下同，法 定公休日、节假日不休），登录“中交招采网”（网址：https://zjzcw.iccec.cn）进行报名并下载采购文件。 4.2 已在网并且已通过采购人层级供应商或已增加采购人为合作单位的供应商、上级供应商可直接参与询比采 网 购。在网平级单位供应商未增加采购人为合作单位需进行合作意向申请通过后参与询比采购。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择采购人，审核通过后方可参与询比 采购。 务 5.供应商报价 5.1 报价结束（递交响应文件截止）时间为2026年8月26日17时00分。 商 5.2 供应商应在报价结束时间前，登录“中交招采网”进行线上报价并上传电子响应文件。逾期未完成上传的电 子响应文件，采购人将拒收。 5.3电子采购的供应商响应文件由线上电子报价道表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 子报价表的数据为准。 6.开标 管 6.1 开标时间：与报价结束时间相同。 6.2 开标地点：本次采购在“中交招采网”平台线上开标，不举办现场开标。 国 7.发布公告的媒介 本询比采购公告在 “中交招采网” 上发布。 中 8.评审办法 本项目评审办法采用 经评审的最低价法 。 9.合同主要条款 9.1 付款条件：按月结算，上月11日至本月10日为一个结算对账期，乙方必须按照甲方要求开具合规的增值税专 用发票，无发票不予付款。结算完成后1个月内支付已结算金额的70%，剩余30%货款在结算完成后3个月内支付。 付款方式为银行转账，甲方有权采用票据支付或者供应链支付的方式支付货款，因此产生的费用包含在综合单 价中，乙方不得因此调价和索赔。如遇业主支付不及时，乙方应予理解。 9.2 履约保证金的递交： （1）R不要求递交 （2）要求递交，保证金金额：/，保证金形式：/，其他形式：/ 。 10.监督机构 监督机构名称： 中交一公局重庆工程有限公司审计部 11.成交供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联系400-676-5885，中标服务费请按7咨询。 11.1 收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： 网 （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； （3）在1000万元（含）至3000万元之间的，每次收取1000元； 务 （4）在3000万元（含）至1亿元之间的，每次收取3000元； （5）在1亿元（含）以上的，每次收取5000元。 商 11.2 支付流程 （1）通知推送：中标结果发布后，系统自动推送缴费通知（含应缴金额及支付链接）； 道 （2）费用查询：供应商登录“中交招采网—供应商协同—服务费”模块查看待支付费用； （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 管 （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网— 供应商协同—服务费—发票查询”模块获取。 12.其他 国 / 。 13.联系方式 中 采 购 人：中交一公局重庆工程有限公司 地 址：重庆市江北区创富路5号 邮 编：361021 联 系 人：汪仁宽 电 话：13527572392 电子邮件：1176245792@qq.com 项目联系人及电话： 序号 项目名称 联系人 联系电话 1 永川三教水厂项目 高博 17788661005 中交一公局重庆工程有限公司 2026年8月19日 物资信息 序号 设备物资名称 设备物资说明 税率 单位 网 1 钢筋混凝土排水管 2000mm Ⅲ级 承插口 13% 米 信息来源:https://www.chinapipe.net/project/d3076078.html 务 cqdingjiu 2026.08.21 10:06:52 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>厂外管网：4.6km；钢筋混凝土排水管：2000m</t>
+        </is>
+      </c>
       <c r="N30" t="n">
         <v>90</v>
       </c>
@@ -2473,7 +2589,11 @@
           <t>中国铁路成都局集团有限公司重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施 工劳务招标招标公告 重庆市大渡口区萤石及配套企业 35 千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标公告 招标编号：DXNZBCQ-GC-2026-13 1. 招标条件 本建设项目重庆市大渡口区萤石及配套企业 35 千伏专用变电站项目穿越渝贵等网铁路防护工程施工劳务招标已由 《中国铁路成都局集团有限公司关于重庆市大渡 口 区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防 护工程施工图设计的复函》（科信技审〔2025 〕115号）批准建设，建设单位为重庆建桥置业有限公司，建设资 金使用外委资金，项 目出资比例为100%，资金已落实。招标人为中国铁路成都局集团有限公司重庆工务段。本 项目已具备法定招标条件，现进行公开招标，特邀请有意向的投标人参加投标。 务 2. 项目概况与招标范围 2.1 项目概况 商 2.1.1建设地点：渝贵线K38+838、南疏Ⅰ线K10+808、川黔线K1+622、川黔线K3+781、兴珞上行线K38+619、兴珞 下行线K38+635、小西线K1+633、南疏Ⅱ线K11+257。 2.1.2建设规模：重庆市大渡 口区萤石及配套企道业35千伏专用变电站项目穿越渝贵等铁 路防护工程，本项目工分为5个交叉工点。工点一采用明挖直埋方式下穿渝贵铁路新白沙沱长江多线特大桥第14孔 （渝贵线K38+838）；工点二采用顶进套管方式下穿南疏 Ⅰ 线K10+808（ 已停用）、川黔线K3+781（ 已停用 ）； 工点三采用明挖直埋方式下穿兴珞线陈家湾双线特大桥（上行线K38+619、下行线K38+635）；工点四采用顶进 管 套管方式下穿。 2.2 招标范围：重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标。 即涉铁部分第第三章桥涵，第六章通信、信号、信息及灾害监测，第十章大型临时设施和过渡工程，第十一章 其他费用中的安全生产国费以及非涉铁部分。 2.3标段划分：本项目施工招标划分为1个标段。 2.4计划工期：240日历天，计划开工日期：2026年10月8日，计划竣工日期：2027年6月4日。 中 2.5 其他说明：___/___。 3. 投标人资格要求 3.1本次招标要求投标人为在中华人民共和国境内合法注册的独立法人，具备有效的营业执照、施工企业资质和 安全生产许可证等，并在人员、设备、资金等方面具备相应的施工能力。资格要求如下： 3.1.1 标段编号：全标段 （1）资质要求：施工劳务企业资质。 （2）业绩要求：近3年内完成过铁路营业线类似项目业绩。 （3）项目负责人要求:具有工程师及以上职称，2 年及以上类似铁路营业线项目管理工作经验， 良好的职业道德， 且未在其他在建工程项目任职。 （4）本标段不接受联合体投标申请。 （投标人资格要求详见招标公告附件） 3.2 各投标人可就上述标段中的 1 个标段进行投标。 3.3投标人未在“信用中国”网站（www.creditchina.gov.cn）中被列入失信被执行人名单，投标人未在国家企业信 用信息公示系统（www.gsxt.gov.cn）中被列入严重违法失信企业名单，投标人未被列入铁路工程建设失信行 为“黑名单”，投标人及其法定代表人、拟委派的项目经理在近3年不曾有行贿犯罪记录； 其他信誉要求：未被取消或暂停投标资格、不存在辖内失信的情形、不存在最近一期国铁集团施工企业评价为D 级且在整改期内的情形。 4. 招标文件的获取 4.1凡有意参加投标者，请于2026年08月20日00时00分至2026年08月25日00时00，在重庆龙头寺旅游集散中心（重 庆市两江新区天宫殿街道昆仑大道56号附1号5楼办公室）持单位介绍信获取招标网文件。 4.2招标文件每套售价0元，售后不退。 4.3其他：凡有意参加投标者可通过网上登记获取招标文件，将获取招标文件材料扫描件（PDF格式）发送 务 至dxncq_bgs@163.com邮箱登记，由招标代理人通过电子邮件方式向有意参加投标者发送招标文件。 5. 投标文件的递交 5.1投标文件递交时间为2026年09 月10 日08时30分至2026年商09月10 日09时00分，递交比选申请文件的截止时间（比 选截止时间，下同）为2026年09月10日09时00分，地点为重庆龙头寺旅游集散中心（重庆市两江新区天宫殿街道 昆仑大道56号附1号5楼开标室）。 5.2逾期送达的或者未送达指定地点或者不按照道招标文件要求密封的投标文件，招标代理人不予受理。 6. 发布公告的媒介 本次招标公告在国铁采购平台（https://cg.95306.cn）发布。 管 7. 联系方式 招 标 人：中国铁路成都局集团有限公司 招标代理机构：成都大西南铁路监理 国 重庆工务段 有限公司 地 址：重庆市九龙坡区黄桷坪街道铁 地 址：成都市金牛区站西桥西街305 中 路3村161号 号府河路苑9栋14楼 邮 编： / 邮 编：610081 法定代表人： 法定代表人 或其委托代理人： 或其委托代理人： 联 系 人： 任女士 联 系 人：汤女士 电 话： 17393148353 电 话：023-61896910 传 真： / 传 真： / 电子邮箱： / 电子邮箱：dxncq_bgs@163.com 网 址： / 网 址： / 开户银行： / 开户银行： / 账 号： / 账 号： / 2026年08月19日 附件： 获取招标文件信息表 申请人名称： （加盖公章） 项目名称：（按公告名称填写） 获取招标文件起止时间：（按照公告时间填写） 项目编号：（按照公告填写） 单位名称 经办人 联系电话 电子邮箱 标段 资料提交时间 备注 网 注：须附经办人介绍信、身份证复印件、单位营业执照复印件。 信息来源:https://www.chinapipe.net/project/d3075989.html cqdingjiu 2026.08.21 10:06:53 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -2540,7 +2660,11 @@
           <t>长江流域云阳青龙段污水管网一体化建设项目招标计划表 重庆市工程建设项目招标计划表 项目名称 长江流域云阳青龙段污水管网一体化建设项目 招标法人或 招标人名称 云阳县青江环境综合整治有限公司 网 （盖章） 项目批准文 云阳发改资环【2025】55号 件及文号 务 主要建设内 新建污水管网55.5千米，其中DN200管网12千米、DN300管网24千米、DN400管网19.5千米等。 容 招标方 招标文件计 拟交易场 合同预估金额 序号 招标项目名称 招标内容 备注 式 划发布时间 所 (万元) 商 长江流域云阳 新建污水管网55.5千米， 重庆市公 青龙段污水管 其中DN200管网12千 公开招 共资源交 1 网一体化建设 米、DN300管网24千 2026-08 9100.00 标 易中心云 项目EPC总承 米、DN40道0管网19.5千 招标项目 阳分中心 包 米等。 新建污水管网55.5千米， 长江流域云阳 重庆市公 其中DN200管网12千 青龙段污水管 公开招 共资源交 2 管米、DN300管网24千 2026-08 140.00 网一体化建设 标 易中心云 米、DN400管网19.5千 项目监理 阳分中心 米等监理。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 国 信息来源:https://www.chinapipe.net/project/d3075867.html cqdingjiu 2026.08.21 10:06:53 中</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>DN200管网：12千米；DN300管网：24千米；DN400管网：19.5千米；污水管网：55.5千米</t>
+        </is>
+      </c>
       <c r="N32" t="n">
         <v>80</v>
       </c>
@@ -2603,7 +2727,11 @@
           <t>中国电建水电四局华中公司重庆轨道交通17号线一期5标项目雨污水排水迁改工程施工劳务分包采购项目公开询 比采购公告 询比采购公告 采购编号： PC-0104-26J6-FP0895 一、采购条件 受中国水利水电第四工程局有限公司重庆轨道交通17号线一期5标项目委托，中水电四局华中（武汉）工程有限 公司以公开询比方式采购重庆轨道交通17号线一期5标雨污水排水迁改工程项目网，建设资金来源已落实。目前项 目已具备采购条件，现进行公开询比采购。 二、项目概况、采购范围 务 1、项目概况：重庆轨道交通17号线一期5标段包含金凤北站（不含）～终点（3 站5 区间的土建）：高龙大道 站、斑竹林站、石家院子站、金凤北站～高龙大道站区间、高龙大道站～斑竹林站区间、斑竹林站～石家院子 站区间、石家院子站～终点区间、7/17号线联络线区间。 2、采购范围： 商 （1）雨污水排水迁改工程 （2）工程招标范围工作内容：17号线一期5标道中高龙大道站、斑竹林站及高斑竖井位于城市既有道路下方，设计 采用明挖法施工。为保证市政排水管网的正常使用，在明挖施工前需对既有管网进行临时迁改，车站结构施工 后进行恢复。施工PE钢带管长度2387米、B型排水管长度2799m、钢筋混凝土管127米，检查井239座劳务部分。 （3）施工内容详见工程量清单，以及为完成此项工程而做的一切工作。 管 3、计划工期:计划开工日期：2026年9月25日（具体时间以采购人通知为准），计划完工日期：2027年 12 月25 日； 合同工期总日历天数为457天。 4、质量要求：符合《国给水排水管道工程施工及验收规范》（GB 50268）、《混凝土结构工程施工质量验收规范》 （GB 50204）、《城镇道路工程施工与质量验收规范》（CJJ 1-2008）以及项目所在地最新的相关法规、标准和 图集。工程质量全面达到设计要求和标准，其中：验收合格率 100%，优良率达 90%以上，工程综合验收质量评 定达优良标准。 中 5、付款方式：采用银行转账/支票支付工程价款，月度结算完成具备付款条件后30天内工程进度款支付比例约定 为扣除各项保证金及费用后应付价款不低于65%；清算完成并签订《退场协议》后30天内工程进度款支付比例约 定为扣除各项保证金及费用后应付价款不低于80%；清算完成并签订《退场协议》后一年内工程进度款支付比例 约定为扣除响应人缺陷责任等相关费用后应付价款不低于90%；清算完成并签订《退场协议》，办理完成保证金 退还手续后两年内，工程进度款支付比例约定为扣除响应人缺陷责任等相关费用后应付价款的100%。 6、其他：无。 三、响应人资格要求 响应人必须满足以下全部资格要求： （1）资质要求：施工劳务不分等级 （2）主要人员要求:授权委托人（如有）及项目经理、专职安全员应提供社保和劳动合同。其中劳动合同至少提 供首、末两页，并且包含有关人员的详细信息;社保证明应提供响应截止时间前三个月的社保缴纳记录。 （3）安全三类人员要求:应提供企业主要负责人安全A证、项目经理B证、专职安全员C证。 （4）响应人具有良好的银行资信和商业信誉，没有处于被责令停业，财产被接管、冻结、破产状态。 （5）响应人应具有 雨污水排水迁改 工程的施工业绩，在近 5年内(2021年7月-2026年7月内签订)的施工合同不少 于 1 个，且签订单项合同金额均在 100 万元以上（应附成交通知书和（或）合同扫描件）。 （6）其它要求:无。 （7）本次采购不接受联合体响应。 四、采购文件的获取 凡满足本公告规定资格要求并有意参加的响应人，请于2026年8月22日10时00分前在中国电建采购招标数智化平台 （https://bid.powerchina.cn/bidweb/#/login，以下简称“数智化平台”）获取采购文件，采购文件免费提供。 五、响应文件的递交 1、响应文件递交的截止时间（响应截止时间，下同）为2026年8月26日10时30分网（北京时间），响应人应在截止 时间前通过数智化平台递交电子响应文件。 2、本次采购将通过数智化平台全程在线开展，电子响应文件的加密、提交等流程须响应人在线进行操作。响应 人须提前办理数字证书用于在线递交响应文件，办理方式详见数智化平台首页，并严格按照要求进行在线操作， 务 因操作流程失误造成的递交失败将由响应人自行承担后果。 3、开启由“数智化平台”在响应截止时间后自动对响应文件进行解密，响应人及时关注开启结果。 4、响应截止时间如有变动，采购人将及时通知已获取采商购文件的响应人。 六、发布公告的媒介 本次询比采购公告同时在中国电建阳光采购网道（https://bid-zb.powerchina.cn）上发布。 七、评审办法 采用综合评估法。 管 八、联系方式 采 购 人： 中水电四局华中（武汉）工程有限公司 国 地 址： 湖北省武汉市江岸区塔子湖东路健美街30号立城中心商务楼13、14层 邮 编： 430014 中 联 系 人： 王飞 电 话： 15827222587 电子邮箱： 107830343@qq.com 九、提出异议的渠道和方式 单位名称： 中水电四局华中（武汉）工程有限公司 电 话： 17708178186 电子邮箱： sjhzgsjw@163.com 十、纪检监督机构 响应人或者其他利害关系人认为本次采购活动存在违规违纪行为的，可以书面形式向中国水利水电第四工程局 有限公司中水电四局华中（武汉）工程有限公司纪委办公室（联系方式：17708178186）提出投诉。 2026年8月 19 日 报价网址:https://bid.powerchina.cn/notice/detail?id=2409510708 信息来源:https://www.chinapipe.net/project/d3075750.html cqdingjiu 2026.08.21 10:06:53 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>型排水管：2799m；钢筋混凝土管：127米；检查井：239座</t>
+        </is>
+      </c>
       <c r="N33" t="n">
         <v>85</v>
       </c>
@@ -2670,7 +2798,11 @@
           <t>万州区2026年超长期特别国债高标准农田建设项目拟进行预制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜的 信息公告 1.采购条件 1.1本项目万州区2026年超长期特别国债高标准农田建设项目工程已由 重庆市万州路桥建设有限公司承建，项目 业主为重庆市万州区农业技术与机械推广中心，代建业主为重庆市万州区农业发展有限公司，建设资金为国债 资金，项目出资比例为 100% ，承包人为重庆市万州路桥建设有限公司。项目已具备施工条件，现对该项目的预 制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜发布信息公告。 网 2.项目概况与采购范围 2.1建设地点：重庆市万州区走马镇、瀼渡镇、罗田镇、余家镇、高梁镇、分水镇、柱山乡等7个镇乡。 务 2.2本项目材料采购拟进行比选情况如下： 罗田镇谷山片区材料采购费暂定金额约： 17.5万元； 余家镇桥亭片区材料采购费暂定金额约： 17.99万元； 商 柱山乡山田片区材料采购费暂定金额约： 26.32 万元； 走马镇凉风片区材料采购费暂定金额约： 15.道66万元； 瀼渡镇高村片区材料采购费暂定金额约： 17.72 万元； 分水镇大冲片区材料采购费暂定金额约： 47.12 万元； 管 高梁镇茨坪片区材料采购费暂定金额约： 10.7万元； （以上片区片区金额为暂定金额，最终比选限价金额以比选文件为准）。 国 2.3计划采购周期： 以合同签订为准 日历天。 2.4采购范围：本项目各片区所包含的预制钢筋砼管、成品混凝土仿木栏杆等材料。 中 3.供应商资格要求 3.1本次材料采购要求供应商具备独立企业法人，具有本次所需材料生产能力的厂家或经销商等，其经营范围和 权限应满足本次所需材料的要求，并依法取得国家行政主管部门颁发的有效工商营业执照(建筑材料销售或水泥 制品制造、水泥制品销售等相关营业资格），所提供产品必须满足各项检测要求，达到国家现行标准规定的合 格标准。具有良好的商业信誉和充分的供应保障能力，具备相应售后服务能力。要求竞选人为一般纳税人，可 开具13%税率增值税专用发票，提供一般纳税人认定证明。 3.2本次供应商单位优先选择万州本地企业。 3.3本次 不接受 联合体竞选。 4. 报名要求 4.1报名时间：2026年8月 19日9:00起至 8月21日17:00止。 4.2报名地点：重庆市万州路桥建设有限公司经营部（重庆市万州区天城东路278号）。 4.3报名时，须提交有效的营业执照(有效工商营业执照((建筑材料销售或水泥制品制造、水泥制品销售等相关营 业资格）)，前述证书均为复印件并加盖单位公章。法定代表人参加报名的不需要授权委托书，只需要提供法定 代表人身份证明；非法定代表人参加报名的除提供法定代表人身份证明外还须提供授权委托书、委托代理人身 份证明。 4.4 本项目材料采购需提前报名。经资格预审合格后，通知资格预审合格的供应商，到承包人单位领取相关文件。 4.5本项目材料采购设七个片区进行比选，为保证比选公平、公正、有效，规定同一参选单位报名片区上限为2个， 且最终仅限中选一个片区。 5.联系方式 承包人：重庆市万州路桥建设有限公司 地 址：重庆市万州区天城东路278号 网 联系人： 张红娟 电 话：15923491915 务 邮 箱： 商 重庆市万州路桥建设有限公司 2026年8月19日 道 信息来源:https://www.chinapipe.net/project/d3075512.html cqdingjiu 2026.08.21 10:06:53 管 国 中</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N34" t="n">
         <v>80</v>
       </c>
@@ -2737,7 +2869,11 @@
           <t>中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资(污水 管道)招标采购流标公告 发布单位：中国铁建/中铁十一局/六公司 发布时间：2026-08-19 10:40:49 投标截至时间：2026-08-18 10:00:00 内容： 各投标人： 网 中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资（污水 管道）公开招标采购（采购编号： CR1106-JC-2026-26-02）评标工作，已于北京时间2026年08月18日10:00整，在 铁建云链（https://www.crccep.com）线上平台公开开标。评审委员会根据招标文件载明的评审办法完成评审工作， 现将评审结果公示如下： 务 一、招标公告发布日期及媒体 招标公告发布日期：2026年07月27日至2026年08月01日 商 招标公告媒体：铁建云链（https://www.crccep.com） 二、拟中标信息 道 公开招标采购编号：CR1106-JC-2026-26-02 包件号：WSGD-01 序号 供应商名称 推荐排序 管 1 无 1 国 以上包件有效投标不足三家，本次招标做流标处理。 三、公示时间 中 自2026年08月19日始，至2026年08月22日止。在公示期间，所有竞标人和其他利害关系人如对公示的评审结果有 异议，可以向相关监督部门举报，逾期将不再受理。举报人必须由其法定代表人或者授权代表签字并盖章，其 他组织或者个人举报的，必须由其主要负责人或者本人签字，并附有效身份证明复印件。举报人如实反映情况 受法律保护。 公示期满，如无异议，即时生效。 监督竞诉受理部门： 中铁十一局集团第六工程有限公司招采中心 联系电话：18671041790 信息来源:https://www.chinapipe.net/project/d3075461.html cqdingjiu 2026.08.21 10:06:53</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N35" t="n">
         <v>80</v>
       </c>
@@ -2800,7 +2936,11 @@
           <t>协同创新区-四期房建三标段镀锌管件物资竞价采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3075420.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N36" t="n">
         <v>60</v>
       </c>
@@ -2867,7 +3007,11 @@
           <t>长江一级支流溉澜溪流域(新华水库混流箱涵)污水收集效能提升工程(渝北区)施工答疑补遗文件 长江一级支流溉澜溪流域（新华水库混流箱涵）污水收集效能提升工程（渝北区）施工答疑文件 各潜在投标人： 现将“长江一级支流溉澜溪流域（新华水库混流箱涵）污水收集效能提升工程（渝北区）施工”公开招标项目 答疑文件发布。本答疑文件是在招标文件的基础上作出的澄清、说明或补正，与招标文件具有同等法律效力， 若相关内容与原招标文件不一致时，一律以本答疑文件内容为准。 网 一、答疑部分： 问题一：1、我公司于2026年进行了优势合并整合，现准备使用合并前公司项目业绩作为本次我司投标的投标人 业绩证明，并提供上级主管单位出具的相关吸收合并文件或两家公司签订的吸收合并协议，请问是否可视为满 务 足招标业绩要求？ 2、我单位为中型企业，其控股股东为大企业，但我单位不属于大企业的分支机构，也不存在与大企业的负责人 为同一人的情形。鉴于此种情况，我单位应提供《中小企业声明函（工程类）》还是《中小企业承担合同份额 承诺函》？ 商 回复：1. 满足，但还需满足招标文件对业绩的其他要求。最终由评标委员会根据投标人提供的证明材料并结合 招标文件要求进行评审； 道 2. 贵司其控股股东为大企业，故需提供中小企业承担合同份额承诺函。 问题二：本项目有无业主专家参与评标？ 管 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 问题三：请明确是否有业主专家 是否异地评标 回复：1. 该项目评标委国员会由招标人按法律法规及相关规定依法组建。 2.本项目是异地评标。 问题四：1、财务报告可以不提供财务报表附注吗? 中 2、投标函附录中，工期、分包、工程质量、缺陷责任期等要求可以统一填写"达到招标文件要求"吗? 3、招标文件第八章投标文件格式中(二)承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要提供其 他格式之外的其他承诺? 4、是否有业代专家参与评标，不要模糊的回答什么依法组建评标委员会。请明确回复有或者没有。 5、本项目是否异地评标？ 6、业绩竣工验收证明材料中有单位盖的项目部章是否认可呢？ 回复：1. 可以不提供财务报表附注。 2. 可以统一填写"达到招标文件要求"。 3. 投标人自行核实招标文件要求提供的承诺要求，如有需要，还需补充提供招标文件第八章投标文件格式中 （二）承诺部分之外的其他承诺。 4. 该项目评标委员会由招标人按法律法规及相关规定依法组建。 5. 本项目是异地评标。 6. 不认可。 问题五：请问**公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，因为不能履行保函的见索即 付，拒绝赔付。 相关业主方在招标文件补遗通知中直接将**公司列入担保公司回避名单，拒绝**公司所出具的保函。由此可 见**公司的信用资质、履约能力、根本无能力是存在很大问题的。请问以**公司目前的被执行和不履行投标担保 责任的情况是否符合招标文件的要求? 回复：纸质投标保函的开立人应当是具有相应资格的银行、保险机构、融资担保公司，其信用资质、履约能力、 担保能力、赔付流程、安全保密等应符合工程保函业务条件。纸质投标保函应合网法合规，符合招投标行政监督 部门、行业主管部门和金融监管部门的相关规定，满足招标文件约定要求。投标人应选择在渝依法设立总部或 者设有分支机构的金融机构开具纸质投标保函。投标人对所提交的纸质投标保函的真实性、合法性、有效性负 责。以纸质投标保函形式交纳投标保证金是否符合招标文件要求，由评标委员会评标时，根据招标文件要求进 行独立评审，并作出相应评审判断。 务 问题六：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 回复：经核实，招标文件（PDF签章版）中投标文件格式商与重庆市电子招投标系统投标文件制作软件中格式一致。 可能因重庆市电子招投标系统投标文件制作软件中的格式页边距与招标文件（PDF签章版）不一致的原因导致格 式显示不一致，该情形不影响投标人编制投标文件。若重庆市电子招投标系统投标文件制作软件导出的投标文 件格式与招标文件（PDF签章版）的投标文件格式不一致，以重庆市电子招投标系统投标文件制作软件导出的投 标文件格式为准。 道 问题七：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖 章，请问需要提供联合体协议书吗？ 管 回复：若投标人提供的公司业绩为epc业绩，且合同协议书或工程竣工验收合格的证明材料或业主证明能证明该 投标人承担的工作为施工任务的，则不需要提供联合体协议书；若投标人提供的公司业绩为epc业绩，但合同协 议书或工程竣工验收合格的证明材料或业主证明不能证明该投标人承担的工作为施工任务的，则需要提供联合 体协议书。 国 问题八：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可 以不填(空白)，对此有无要求？ 回复：投标中文件中下划线上、空格处、表格中无需要填写或无法填写内容的，填“/”或“无”均可。 问题九：公园施工业绩符合吗？ 回复：公园概念太宽泛，无法判定该施工业绩是否属市政工程，请投标人自行核实，并按招标文件要求提供施 工业绩证明材料，其是否满足要求应由评标委员会根据证明材料具体内容进行判定。 问题十：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需 要提供其他格式之外的其他承诺？ 回复：投标人自行核实招标文件要求提供的承诺要求，如有需要，还需补充提供招标文件第八章投标文件格式中 （二）承诺部分之外的其他承诺。 问题十一：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收， 请问我公司业绩满足业绩要求吗？ 回复：不满足。 问题十二：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗？ 回复：投标人投标总报价低于招标文件规定的对应的异常低价警戒线的，应提供报价合理性说明，并提供必要 的证明材料。证明材料由投标人自行提供，但提供的说明不得降低或者改变原设计方案、技术工艺、施工标准， 不得影响项目的质量、安全、工期、结算等正常履约。 问题十三：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 回复：按照招标文件要求“提供：会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表，财务 报表须至少包括现金流量表、资产负债表、利润表”。 问题十四：业绩要求的竣工时间是指竣工验收时间吗？ 回复：本项目业绩要求所指竣工时间，即为工程竣工验收合格证明载明的竣工验收时间。 问题十五：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知 书发出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面网通知相关金融机构本项目准 予提前注销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 回复：纸质投标保函原件上未加盖“正本”字样的，不因此否决投标，但投标人应确保提交的保函为唯一正本。 若因保函真伪问题导致的一切不利后果由投标人自行承担。 务 问题十六：燃气管道安装施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 商 问题十七：请问招标人是否委派业主专家参与评标吗？ 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 道 问题十八：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 回复：根据招标文件“投标人的工程量清单单项报价不得为零报价（招标人提供的工程量清单单项最高限价中 金额为零的除外）或者负数报价”，招标人提供的工程量清单单项最高限价中金额为零的，该项清单综合单价 管 报价可以为0。 问题十九：自来水厂或者净水厂施工业绩满足业绩要求吗？ 回复：满足，但还需满国足招标文件对业绩的其他要求。 问题二十：财务报告可以不提供财务报表附注吗？ 回复：可以不提供财务报表附注。 中 问题二十一：老旧小区室外环境改造施工业绩符合吗？ 回复：不满足。 问题二十二：有人提出一个无关问题。 回复：无关问题不予回复。 问题二十三：任一清单的综合单价低于警戒线，就要提供说明吗？ 回复：本招标项目单项报价未设置异常低价警戒线。 问题二十四：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题二十五：本项目是异地评标吗？ 回复：本项目是异地评标。 问题二十六：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、 注册证及在本单位注册的证明文件替代？ 回复：不满足。 问题二十七：污水处理厂提标改造施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题二十八：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 回复：可以填“达到招标文件的要求”。 问题二十九：财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加网强审计报告查验工作的通知》 中要求会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第十四条规定审计业务出具的报告 （以下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标 人提供的财务报告需要赋码和提供深度查询截图吗？ 务 回复：投标人提供的财务报告不需要赋码和提供深度查询截图。 问题三十：有人提出一个无关问题。 回复：无关问题不予回复。 商 问题三十一：我公司业绩合同金额3600万元及以上，但是竣工报告业绩金额小于3600万元，请问是否满足业绩要 求？ 道 回复：按招标文件执行。“当上述业绩证明材料中针对同一指标存在不一致时，以工程竣工验收合格的证明材 料为准”。 问题三十二：专业分包业绩满足业绩要求吗？ 管 回复：专业分包业绩可满足业绩要求，但还需满足招标文件对业绩的其他要求。 问题三十三：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养 老保险证明材料复印件国递交吗？ 回复：不需要。 问题三十四：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要 中 求”吗？ 回复：可以统一填写“达到招标文件要求”。 问题三十五：市政桥梁施工业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题三十六：有人提出一个无关问题。 回复：无关问题不予回复。 问题三十七：本项目委派业主专家吗？ 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 特别提示：本通知与招标文件具有同等法律效力，若招标文件与本通知不一致时，一律以本通知为准。 招标人：重庆水务环境控股集团管网有限公司 招标代理机构：重庆市工程管理有限公司 2026年8月19日 信息来源:https://www.chinapipe.net/project/d3075975.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
@@ -2934,7 +3078,11 @@
           <t>中化重庆涪陵化工搬迁后污水处理厂建设项目招标计划表 重庆市工程建设项目招标计划表 项目名称 中化重庆涪陵化工搬迁后污水处理厂建设项目 招标法人或 招标人名称 重庆市涪陵交通旅游建设投资集团有限公司 网 （盖章） 项目批准文 涪发改委发[2019] 505号 件及文号 务 主要建设内 新建一体化提升泵站及管道约5000m，投资约800万元。 容 招标 招标 招标文件计 拟交易 合同预估 序号 招标项目名称 备注 内容 方式 划发布时间 场所 金额(万元) 商 本招标计划与2026年5 月25日发布的招标项目 中化重庆涪陵 重庆市 名称为“中化重庆涪陵 招标项目 化工搬迁后污 涪陵区 公道开 化工搬迁后污水处理厂 1 水处理厂建设 施工 2026-09 公共资 800.00 招标 建设项目（场外连接管 项目（场外干 源交易 网）”的招标计划，除 管部分） 中心 招标项目名称调整外， 其余内容完全一致。 管 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075591.html cqdingjiu 2026.08.21 10:国06:54 中</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>一体化提升泵站及管道：5000m</t>
+        </is>
+      </c>
       <c r="N38" t="n">
         <v>80</v>
       </c>
@@ -3001,7 +3149,11 @@
           <t>綦江区污水处理厂设施设备更新改造工程(二期)招标公告 1.招标条件 本招标项目 綦江区污水处理厂设施设备更新改造工程（二期） 已由 重庆市綦江区发展和改革委员会 以 重庆市企业投资备案证（项目代码：2502-500110-04-01-844057） 批准建设，项目业主为 重庆南州城市管 理服务有限公司 ，建设资金来自 上级补助和业主自筹 ，项目出资比例为 100% ，招标人为 重庆南州 城市管理服务有限公司。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用经评审的最低 投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 綦江区 2.2 项目概况与建设规模：对三江污水处理站、綦齿园污水处理厂、信家岩污水处理站的设施设备进行更新改造， 务 包括配电柜、风机、污水提升泵、在线监测等设备更新更换，以及对工艺落后的污水厂完成工艺技改；北渡污 水厂、赶水污水处理厂、工业园区污水厂、食品园污水厂零星设施更新等。 2.3 本项目工程总投资金额： 约1327.40万元 商 2.4 招标范围： 本项目设计施工图和招标文件、答疑、补遗、工程量清单等资料所涉及的全部内容。 2.5 工期要求： 180日历天 道 缺陷责任期要求： 24个月 2.6 标段划分（如有）： / 管 2.7 其他： / 3.政府采购工程 国 3.1 是否属于政府采购工程：否 4.投标人资格要求 中 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（綦江区） （https://www.cqggzy.com/qijiangweb/）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重 庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏 “主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网（綦江区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-22 18:00:00前。 5.3招标人应于2026-09-11 18:00:00前在重庆市公共资源交易网（綦江区）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-28 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（綦江区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆南州城市管理服务有限公司 代理机构: 永卓国际工程技术有限公司 地 址: 重庆市綦江区红星美凯龙生活广场3幢19-3 地 址: 两江新区网泰山大道东段98号2幢10-12号 邮 编: 邮 编: 项目负责人: 赵老师 项目负责人: 廖淼 电 话: 023-48690537 电 话: 务023-60391733 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 商开户银行: 账 号: 账 号: 监督部门: 道 电 话: 2026年08月18日 綦江区污水处理厂设施设备更新改造工程（二期） 管 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051287453 中国农业银行股份有限公司重庆自由贸 重庆联合产权交易所集国团股份有限公司 312601010400083780000031123 易试验区分行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146631326 信息来源:https://www.chinapipe.net/project/d3075589.html 中 cqdingjiu 2026.08.21 10:06:54</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N39" t="n">
         <v>90</v>
       </c>
@@ -3068,7 +3220,11 @@
           <t>南岸区峡口、迎龙片区农村供水保障提升工程招标计划表 重庆市工程建设项目招标计划表 项目 南岸区峡口、迎龙片区农村供水保障提升工程 名称 招标 网 法人 或招 标人 重庆市江南城市建设发展（集团）有限公司 名称 务 （盖 章） 项目 批准 商 文件 南岸发改﹝2026﹞156号 及文 号 本工程主要内容包括新（改）建峡口、道迎龙片区4个乡镇DN20～DN300农村供水管网81km，新建3座一体 主要 化智慧加压泵站。对朱家岩水厂进行升级改造：更换陈旧、老化的工艺、电气设备及自控、仪表系统， 建设 对全厂进行智能化、标准化改造，增加高级工艺控制系统，建设智能化、标准化的农村供水区级管理平 内容 台。概算批复工程建安费2975.27万元。 管 拟 招 招标文 合同预 招标 交 序 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 国 所 南岸 重 区峡 庆 口、 中 市 迎龙 朱家岩水厂升级改造工程：对全厂老旧设备进行设备更新；对全 公 片区 公 厂进行智慧化改造，增加高级工艺控制系统；对厂区建筑和构筑 共 农村 开 1 物修缮；优化加药系统投加模式，增加精确加药系统；对全厂部 2026-08 资 1600.00 供水 招 分老旧管道进行更换；金属防腐工程，对金属设备和管道的防锈 源 保障 标 刷漆工作。 交 提升 招标 易 工程 项目 中 （一 心 标段） 南岸 重 区峡 庆 口、 市 迎龙 公 片区 管网工程：延伸、改造峡口镇、迎龙镇等4个乡镇 46 公里 公 共 农村 DN40~DN300 配水主支管，36公里 DN20入户管道，新建3座一体 开 2 2026-08 资 1300.00 供水 化智慧加压泵房，入户水表改造 1752 户，并配套建设监测计量 招 源 保障 基础设施。 标 交 提升 易 工程 中 （二 心 标段） 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075572.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>DN300农村供水管网：81km</t>
+        </is>
+      </c>
       <c r="N40" t="n">
         <v>90</v>
       </c>
@@ -3135,7 +3291,11 @@
           <t>北碚区东阳天府片区农村供水提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 北碚区东阳天府片区农村供水提升工程 招标法人或招 标人名称（盖 重庆北碚文旅产业发展有限公司 网 章） 项目批准文件 及文号 务 工程建设区域为东阳及天府片区，主要建设内容包含改造供水管网437千米，其中DN200供水 主要建设内容 管网35千米，DN100~DN150供水管网82千米，DN100以下供水管网320千米，并配套建设管网 附属设施。 招标项目名 招标内 招标方 招标文件计划 拟交易场 合同预估金 序号 商 备注 称 容 式 发布时间 所 额(万元) 北碚区东阳 招标项目 重庆市公 天府片区农 施工招 公开招 1 2026-08 共资源交 8457.00 村供水提升 标 道标 易中心 工程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075569.html 管 cqdingjiu 2026.08.21 10:06:55 国 中</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>DN150供水管网：82千米；DN100以下供水管网：320千米；主要建设内容包含改造供水管网：437千米；管网：35千米</t>
+        </is>
+      </c>
       <c r="N41" t="n">
         <v>80</v>
       </c>
@@ -3202,7 +3362,11 @@
           <t>北碚区澄江片区农村供水提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 北碚区澄江片区农村供水提升工程 招标法人或招标 重庆北碚文旅产业发展有限公司 人名称（盖章） 网 项目批准文件及 文号 改造取水泵站一座，改造DN600供水管网2.9km，DN50~DN300供水管网88.863km，DN25供 主要建设内容 务 水管网68.5km及其附属设施。 招标项目名 招标文件计划 合同预估金 序号 招标内容 招标方式 拟交易场所 备注 称 发布时间 额(万元) 招标项目 北碚区澄江 商重庆市公共 1 片区农村供 施工招标 公开招标 2026-08 资源交易中 8741.00 水提升工程 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 道 信息来源:https://www.chinapipe.net/project/d3075568.html cqdingjiu 2026.08.21 10:06:55 管 国 中</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>DN600供水管网：2.9km；DN300供水管网：88.863km；水管网：68.5km</t>
+        </is>
+      </c>
       <c r="N42" t="n">
         <v>80</v>
       </c>
@@ -3269,7 +3433,11 @@
           <t>涪陵区江东街道农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区江东街道农村供水保障能力提升工程（二期） 名称 招标 法人 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 项目 网 批准 文件 涪陵发改〔2026〕471号 及文 号 主要 改造及延伸配水管 188.2千米，新建加压泵站4座，新建计量监测设施 建设 以及配套电气工程。 务 内容 招 标 合 文 同 招 件 预 招标 标 招标方 计 拟交易 备 序号 招标项目名商称 估 项目 内 式 划 场所 注 金额 容 发 (万 布 元) 时 间 重 道 庆 市 涪 陵 公 区 改造及延伸配水管 188.2千米，新建加压泵站4座，新建计量监测设施 开 公 1 涪陵区江东街道农村供水保障能力提升工程（二期） 2026-09 3137.22 管以及配套电气工程。 招 共 标 资 源 交 易 中 心 国 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075558.html cqdingjiu 2026.08.21 10:06:55 中</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>加压泵站：4座</t>
+        </is>
+      </c>
       <c r="N43" t="n">
         <v>80</v>
       </c>
@@ -3336,7 +3504,11 @@
           <t>涪陵区龙桥街道农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 涪陵区龙桥街道农村供水保障能力 项目名称 提升工程 招标法人 或招标人 重庆水务环境控股集团渝东自来水 名称（盖 有限公司 章） 网 项目批准 文件及文 涪陵发改〔2026〕466号 号 改造荣桂水厂老化、破损、生锈的 务 输水管道7.36公里。马武水厂增设 废水回收及污泥浓缩系统1套。荣 桂水厂增设废水回收及污泥浓缩系 主要建设 统1套。新建配水管道总长0.74公里； 商 内容 改造配水管道总长139.42公里。新 建1座微型集成泵房及改造1座泵 站(原牌坊泵站)。新增管网监测设 施40套。 道 招标 合同 招 文件 预估 标 招标方 拟交易 备 招标项目 序号 招标项目名称 计划 金 内 式 场所 注 管 发布 额(万 容 时间 元) 改造荣桂水厂老化、 破损、生锈的输水管 国 道7.36公里。马武水厂 增设废水回收及污泥 重庆 浓缩系统1套。荣桂水 市涪 厂增设废水回收及污 公 陵区 中 涪陵区龙桥街道农村供水保障能力 泥浓缩系统1套。新建 开 1 2026-09 公共 3236.36 提升工程 配水管道总长0.74公里； 招 资源 改造配水管道总 标 交易 长139.42公里。新建1 中心 座微型集成泵房及改 造1座泵站(原牌坊泵 站)。新增管网监测设 施40套。 本计划表所列招标项目信息均为暂 备注 定，最终以实际招标时的信 信息来源:https://www.chinapipe.net/project/d3075556.html cqdingjiu 2026.08.21 10:06:55</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>输水管道：7.36公里；配水管道：0.74公里；配水管道：139.42公里</t>
+        </is>
+      </c>
       <c r="N44" t="n">
         <v>90</v>
       </c>
@@ -3403,7 +3575,11 @@
           <t>涪陵区百胜镇农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区百胜镇农村供水保障能力提升工程 名称 招标 法人 或招 标人重庆水务环境控股集团渝东自来水有限公司 名称 网 （盖 章） 项目 批准 文件涪陵发改〔2026〕465号 及文 号 务 主要 建设整治 De315原水管长 1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1套及配套电气工程。 内容 招 拟 标 招招标文 合同预 交 序项 标件计划 估金 备 招标内容 易 号目 方发布时 额(万 注 场 名 商 式间 所 元) 称 涪 陵 区 重 百 庆 胜 市 招标 镇 涪 项目 农 道 陵 村 公 区 供整治 De315原水管长 1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1开 公 1 2026-09 1489.90 水套及配套电气工程。 招 共 保 标 资 障 源 能 交 力 易 提 中 管 升 心 工 程 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075553.html 国 cqdingjiu 2026.08.21 10:06:55 中</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>取水泵站水泵：1套；及整治输配水管网：111.47公里；加压泵站：2座</t>
+        </is>
+      </c>
       <c r="N45" t="n">
         <v>80</v>
       </c>
@@ -3470,7 +3646,11 @@
           <t>涪陵区清溪镇农村供水保障能力提升工程招标计划 重庆市工程建设项目招标计划表 项目名称 涪陵区清溪镇农村供水保障能力提升工程 招标法人 或招标人 重庆水务环境控股集团渝东自来水有限公司 网 名称（盖 章） 项目批准 文件及文 涪陵发改〔2026〕467号 务 号 对清溪水厂原取水口进行改造。改造清溪水厂输水管道长6.38公里。清溪水厂新建3000m3/d集成水 主要建设 厂1套，增设废水回收及污泥浓缩系统1套。新建配水管道总长2.46公里。改造配水管道总长145.04 内容 公里。四合村泵站增加1套备用加压泵。新商增管网监测设施35套。 招标项目 招标方 招标文件计 拟交易场 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 所 (万元) 对清溪水厂原道取水口进行 改造。改造清溪水厂输水 管道长6.38公里。清溪水厂 涪陵区清 新建3000m3/d集成水厂1套， 重庆市涪 招标项目 溪镇农村 增设废水回收及污泥浓缩 公开招 陵区公共 管 1 供水保障 2026-09 2888.89 系统1套。新建配水管道总 标 资源交易 能力提升 长2.46公里。改造配水管道 中心 工程 总长145.04公里。四合村泵 站增加1套备用加压泵。新 国 增管网监测设施35套。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075552.html 中 cqdingjiu 2026.08.21 10:06:55</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>清溪水厂输水管道：6.38公里；配水管道：2.46公里；四合村泵站：1套；新商增管网：35套；管道：6.38公里；增管网：35套</t>
+        </is>
+      </c>
       <c r="N46" t="n">
         <v>80</v>
       </c>
@@ -3537,7 +3717,11 @@
           <t>涪陵区珍溪镇农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目名 涪陵区珍溪镇农村供水保障能力提升工程（一期） 称 招标法 网 人或招 重庆水务环境控股集团渝东自来水有限公司 标人名称 （盖章） 项目批 务 准文件 涪陵发改〔2026〕476号 及文号 (一)改造11000m3/d(旺水垭6000m3/d和二水厂5000m3/d)原水处理系统及辅助设施，主要有加氯系统、 加药系统、清水池、絮凝池、重力无阀滤池、商污水处理回收池、二水厂泵房设备等及其他辅助设施。 主要建 (二)更换旺水垭水厂至张家塘配水管13.5km，张家塘至滴水配水管长3.3km，全长16.8km；滴水至洪 设内容 湖配水管长0.3km；更换八一水库至旺水垭水厂引水管1.7km，更换珍溪二水厂至珍溪大桥配水管5km， 新建应急泵站至百汇大桥配水管9km：百汇至观将泵站4.5km；共计37.3km。 道 招标项目 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 场所 (万元) (一)改造11000m3/d(旺水 垭6000m3/d和二水厂5000m3/d) 管 原水处理系统及辅助设施，主 要有加氯系统、加药系统、清 水池、絮凝池、重力无阀滤池、 污水处理回收池、二水厂泵房 涪陵国区珍 设备等及其他辅助设施。(二) 重庆市 招标项 溪镇农村 更换旺水垭水厂至张家塘配水 涪陵区 目 供水保障 公开招 1 管13.5km，张家塘至滴水配水 2026-09 公共资 3427.27 能力提升 标 管长3.3km，全长16.8km；滴水 源交易 中工程（一 至洪湖配水管长0.3km；更换八 中心 期） 一水库至旺水垭水厂引水 管1.7km，更换珍溪二水厂至珍 溪大桥配水管5km，新建应急 泵站至百汇大桥配水管9km： 百汇至观将泵站4.5km；共 计37.3km。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075551.html cqdingjiu 2026.08.21 10:06:56</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>应急泵站：9km；百汇至观将泵站：4.5km；泵站：9km</t>
+        </is>
+      </c>
       <c r="N47" t="n">
         <v>80</v>
       </c>
@@ -3604,7 +3788,11 @@
           <t>涪陵区武陵山镇农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区武陵山镇农村供水保障能力提升工程 名称 招标 网 法人 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 务 （盖 章） 项目 批准 商 文件 涪陵发改〔2026〕468号 及文 号 主要 道 新建及整治输配水管网总长 124.26千米，新建加压泵站 5座，新建高位水箱4座（总容积 354立方米），武 建设 陵山水厂新建废水处理系统1套及配套电气工程等。 内容 招 管 拟 标 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 国 称 涪 陵 区 中 重 武 庆 陵 市 山 招标 涪 镇 项目 陵 农 公 区 村 新建及整治输配水管网总长 124.26千米，新建加压泵站 5座，新建高 开 公 1 供 位水箱4座（总容积 354立方米），武陵山水厂新建废水处理系统1套 2026-09 1861.77 招 共 水 及配套电气工程等。 标 资 保 源 障 交 能 易 力 中 提 心 升 工 程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075549.html cqdingjiu 2026.08.21 10:06:56</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>及整治输配水管网：124.26千米；加压泵站：5座</t>
+        </is>
+      </c>
       <c r="N48" t="n">
         <v>80</v>
       </c>
@@ -3671,7 +3859,11 @@
           <t>涪陵区江东街道农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目名 涪陵区江东街道农村供水保障能力提升工程（一期） 称 招标法 网 人或招 重庆水务环境控股集团渝东自来水有限公司 标人名称 （盖章） 项目批 务 准文件 涪陵发改〔2026〕470 号 及文号 主要建 建设配水管网总长 34.80km，新建加压泵站 2 座、改造已成泵站 2 座、新建加氯加药间 1 座、新建高位 设内容 水箱 7 座、新建计量监测设施以及配套电气工程商。 招 招标文件 拟交 合同预估 序 招标项 标 备 招标内容 计划发布 易场 金额(万 号 目名称 方 注 道 时间 所 元) 式 涪陵区 重庆 招标项 江东街 市涪 目 建设配水管网总长 34.80km，新建加压泵站 2 座、 公 道农村 陵区 管 改造已成泵站 2 座、新建加氯加药间 1 座、新建高 开 1 供水保 2026-09 公共 3503.77 位水箱 7 座、新建计量监测设施以及配套电气工 招 障能力 资源 程。 标 提升工程 交易 （一期） 中心 国 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075548.html cqdingjiu 20中26.08.21 10:06:56</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>配水管网：34.80km；加压泵站：2座；已成泵站：2座</t>
+        </is>
+      </c>
       <c r="N49" t="n">
         <v>90</v>
       </c>
@@ -3734,7 +3926,11 @@
           <t>中国电建水电五局二公司重庆轨道交通17号线一期7标内外涂环氧消防复合钢管管件采购项目公开竞价采购(二次 挂网)变更公告(一) 详见附件。 信息来源:https://www.chinapipe.net/project/d3075376.html cqdingjiu 2026.08.21 10:06:56 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N50" t="n">
         <v>60</v>
       </c>
@@ -3801,7 +3997,11 @@
           <t>2026年石柱分公司黄水镇黄连大道通信管道建设招标公告 ZB_ZHAOBIAOGONGGAO_START 本询比项目为 2026年石柱分公司黄水镇黄连大道通信管道建设 （标段 编号： CQBBFA202604170051 ），采购人为 中国电信股份有限公司石柱分公司 ，采购代理机构为 。项目 资金已落实。 具备采购条件，现进行公开询比，特邀请有意向的且具有提供标的物能力的潜在供应商（以下简 称供应商）参加询比响应。 1.项目概况与采购内容 1.1项目概况： 2026年石柱分公司黄水黄连大道通信管道修复项目主要针对黄水网黄连大道受损通信管道进行修 复80米 本次集中询比合同有效期为： 2026.9-2026.12 1.2采购内容 及标包划分情况： 务 1.2.1 本次询比的规模、货物名称、数量及主要技术参数、交货期及交货地点具体如下：黄水镇黄连大道80米通 信管道修复。 序号 标包名称 产品名称 规格型号 数量 交货地点 交货期 商 2026年石柱分公司黄水 黄水镇黄连 1 镇黄连大道通信管道建 管道建设 新建2孔110波纹管、 新建2孔蜂窝管 80 2026.12.20 大道 设 道 本项目 不划分标包 。 ${ } ${ 本项目允许供应商同时成交的最多标包数为 0 个。 } 本项目将按照最新的《中国电信供应商不良行为管 理规则》执行供应商不良行为处理结果，请重点关注处理结果适用的供应商主体、被处理产品、处理范围、禁 限期、处理措施等关键内容，请务必登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）查阅《中国 管 电信供应商不良行为管理规则》。 本项目根据《中国电信供应商不良行为管理规则》选择适用备选处理措施 （但涉及生产安全责任事故的处理结果不适用备选措施）。 1.2.2成交供应商数量： 1 个，每个成交供应商对应的份额如下 ： [请在此处自行编辑与采购方案相同的成交原则] 国 ${ 1.2.2成交供应商数量如下： [ 请在此处自行编辑与采购方案相同的有效供应商及成交供应商数量原则相关表格 ] 每个成交供应商对应的份额如下: [请在此处自行编辑与采购方案相同的份额分配原则] } 1.3本项目 设置最高 响应限价 。 设置最高响应限价，最高响应限价为不含税31000元人民币/计算方法，供应商响应报价高于最高 响应限价的，其响应将被否决 供应商响应报价高于最高响应限价的，其响应 将被否决。 ${ } 2.供应商中资格要求 2.1供应商基本资格要求 2.1.1 供应商 应为 中华人民共和国境内 法律上和财务上独立的法人或依法登记注册的其他组织，合法运作并 独立于采购人和采购代理机构。 供应商应具有良好的银行资信和商业信誉。法人下属不具备法人资格的分支机 构参与响应的，应提供所属法人针对本项目或覆盖本项目的经营事项的有效授权。 2.1.2 供应商 的法定代表人或负责人为同一人或者存在控股、管理关系的不同 供应商 ，不得参加同一标包响应或 者未划分标包的同一询比项目响应。 ${ 2.1.3 } ${ 2.1.3 } 2.1.4 本次询比 不接受 联合体响应。 ${如 供应商 为联合体，应满足下列要求： （1） 联合体各方必须按询比文件提供的格式签订联合体协议书，明确联合体牵头人和各方的权利义务； （2）由同一 专业的单位组成的联合体，按照资质等级较低的单位确定资质等级； （3）联合体各方不得再以自己名义单独或 加入其他联合体在同一标包或者未划分标包的同一询比项目中响应。 ${ （4） 。} } 2.1.5 本次询比 不接受代理商响应。 ${ （1）产品制造商注册地在中华人民共和国境外（与中华人民共和国有正常贸易与往来的国家或地区）及香港、 澳门、台湾地区且必须使用代理商响应和签订销售合同的；（2）产品制造商为注册地在中华人民共和国境内的 外资企业（包括香港、澳门、台湾地区资本）或者由外国投资者（包括香港、澳门、台湾地区）享有绝对控制权 （最大或最多表决权）的企业且必须使用代理商响应和签订销售合同的。代理商响应的，应满足下列要求 ： } ${ （1） ${ （2） 供应商与产品制造商 的代理合作关系迄今为止应已持续 0 年（含）以上。 } ${ （3） } } ${ 2.1.6 与供应商有产品代工制造关系的制造商不得参加同一标包响应或者未划分标包的同一询比项目响 应。 } 2.1.7 供应商须提供2022年1月1日至本项目发布公告之日的同类项目（通信管道施工类）证明材料， 合同累计金额不低于3万元（含税） 2.2供应商不得存在下列情形之一 （1） 为采购人不具有独立法人资格的附属机构（单位）； （2） 被依法暂停或取消 投标/ 响应资格的； （3） 被责令停产停业、暂扣或者吊销许可证、暂扣或者吊销执照； （4） 进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （5） 在最近三年内（自 2022年04月01日 起）被相关行业主管部门或司法机关认定有骗取 中标/成交 、严重 违约、重大工程质量或者安全问题的； 网 （6） 在最近五年内（自 2022年06月01日 起）被判处单位行贿罪，且行贿行为与采购活动相关的（以“中国 裁判文书网”的生效判决为准）； （7） 在最近五年内（自 2022年06月01日 起）被判处合同诈骗罪的（以“中国裁判文书网”的生效判决为 务 准）； （8） 被最高人民法院在“信用中国”网站（www.creditchina.gov.cn）或各级信用信息共享平台中列入失信被执 行人名单，已执行完毕或不再执行的除外； 商 （9） 为本询比项目提供过设计、编制技术规范和其他文件的咨询服务 ； （10） 为本工程项目的相关监理人，或者与本工程项目的相关监理人存在隶属关系或者其他利害关系； 道 （11） 为本询比项目的代建人 ； （12） 为本询比项目的采购代理机构 ； 管 （13） 与本询比项目的监理人或代建人或采购代理机构同为一个法定代表人 ； （14） 与本询比项目的监理人或代建人或采购代理机构存在控股或参股关系 ； （15） 被工商行政管理国机关在国家企业信用信息公示系统中列入严重违法失信企业名单的； （16） 中国电信在职员工违规担任供应商法定代表人并参与采购活动的； （17） 中国电信集团有限公司/中国电信股份有限公司中层及以上管理人员违反有关领导人员配偶、子女及其配 中 偶经商办企业行为管理规定，其配偶、子女及其配偶经商办企业参与采购活动的； （18） 中国电信领导人员离职或退休后三年内违反《国有企业领导人员廉洁从业若干规定》等相关规定任职、 投资入股的私营企业、外资企业和中介机构，参与其原任职单位采购活动的； ${ （19） } （19） 其他按照中国电信供应商不良行为处理结果及《中国电信供应商不良行为管理规则》的结 果执行规则，应对供应商及其响应产品在本项目中执行禁止采购处理措施的； （20） 法律法规、询比文件限定的其他情形。 ${ 供应商 是代理商的，本条所指的 供应商 也包括其所代理的制造商。 } ${ 联合体响应的，联合体成员均不得 存在上述任一情形。 } 2.3产品资格要求 2.3.1 产品 应是来自中华人民共和国 ${或是与中华人民共和国有正常贸易与往来的国家或地区} 的 成熟稳定的 产品 。 ${ 2.3.2 产品 。 } ${ 2.3.3 产品 。 } ${ 2.3.4 。 } ${ 2.3.5 。 } 2.3.6 产品应符合中国电信相关技术要求， 并满足以下关键技术指标： （1） 序号 技术指标 具体要求 1 开挖深度 埋深≥0.8m（道路≥1.2m） 2 施工规格 本次修复选择开挖换管：开挖约80米，2孔110波纹管、2孔蜂窝管，新建两通信手控井 ${ 2.3.7 产品 业绩要求： 。 } ${ 2.3.8 。 } ${ 2.4 产品制造商资格要求 2.4.1 制造商应提供合法有效的登记 （或注册）证明文件，应具有良好的银行资信和商业信誉。 } ${ 2.4.2 } ${ 2.4.2 } ${ 2.4.3 } ${ 2.4.4 } ${ 2.4.5 } ${ 2.5现场考察 } ${ 2.6评价检测 } 2.7 法律法规规定的其他要求。 3.资格审查方法 本项目将进行资格后审，资格审查标准和内容见询比文件第三章“评审办法”，凡未通过资格后审的供应商， 其响应将被否决 。 网 4.询比文件的获取 4.1询比文件获取时间: 2026年08月25日 00时00分00秒 至 2026年09月01日 00时00分00秒 （北京时间，下同）。 4.2询比文件获取方式：登录“中国电信阳光采购网（https://caigou.c务hinatelecom.com.cn）”后，通过“招投标-采 购文件领取”模块或通过“电子采购入口”跳转中国电信电子采购系统，进入本项目进行询比文件登记申领， 未在系统注册的供应商须先进行注册，注册方法详见本公告“ 7 供应商注册”。 4.3询比文件费用： 本项目不收取文件费用。 ${每套售价商 0 元人民币，售后不退。支付要求： } 5.响应文件的递交 5.1响应文件递交截止时间（即响应截止时间）为： 2026年09月02日 00时00分00秒 道 5.2 电子响应文件的提交方式：登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投 标-我的项目”模块或通过“电子采购入口”跳转中国电信电子采购系统，选择本项目进行响应文件提交，供应 商应在响应文件提交截止时间之前通过电子采购系统完成加密电子响应文件的上传。供应商未在电子采购系统 进行询比文件申领登记或电子响应管文件未按照要求加密的，将无法通过电子采购系统提交电子响应文件 。 5.3 本项目将于响应文件提交截止同一时间通过中国电信电子采购系统开启响应文件， 采购人/采购代理机构 邀 请响应供应商的法定代表人或者其委托代理人准时参加 。 国 ${ 6.样品的递交 6.1样品递交的时间、地点：于 递交至 。 } 7. 供应商注册 7.1 中国电信阳光采购网注册 未注册过的潜在供应商，须通过中国电信阳光采购网（https://caigou.chinatelecom.com.cn）首页“立即注册”模 中 块完成注册后，方可申领本项目询比文件。 7.2 CA证书办理 参加询比响应的潜在供应商须提前办理CA证书，并确保CA证书在使用时有效。CA证书办理流程详见中国电信 阳光采购网首页“操作指引-CA办理”。 7.3 技术支撑联系方式 服务热线：4000111884 服务邮箱：zb_support@chinatelecom.cn（电子采购系统技术支撑） ctsc@chinatelecom.cn（CA证书办理技术支撑） 8. 发布公告的媒介 本询比公告在 中国电信阳光采购网（https://caigou.chinatelecom.com.cn） 、中国招标投标公共服务平台 （http://www.cebpubservice.com/） 上发布，其他媒介转载无效。 9. 联系及异议接收方式 9.1 联系方式 采 购 人: 中国电信股份有限公司石柱分公司 采购代理机构: 地 址： 重庆市石柱县城南路6号 地 址： 无 邮 编： 邮 编： 无 联 系 人： 马卫平 联 系 人： 无 电 话： 17365204567 电 话： 无 电子邮件： 17365204567@189.cn 电子邮件： 无 网 址： www.chinatelecom.com.cn或“/” 网 址： 无 网 开户银行： 无 账 号： 无 9.2 异议接收方式 务 登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投标-采购异议-提出异议”模块提出。 采购代理机构： 商 2026年08月25日 信息来源:https://www.chinapipe.net/project/d30道75344.html cqdingjiu 2026.08.21 10:06:56 管 国 中</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
@@ -3864,7 +4064,11 @@
           <t>重庆站站房CQZSG-4标项目蓝色PVC袖阀管(外径60mm)询价采购公告 ZTEJWZ-JZ-2026-询027（一） 采购单位:重庆站站房CQZSG-4标段项目经理部 发布时间:2026-08-18 19:06 报价截止时间:2026-08-21 10:00 招标方联系人:刘健 网 招标方联系电话:13540650091 招标方邮箱: 务 监督方联系人:纪委 监督方联系电话:028-87653066 商 监督方邮箱: 保证金:0.0元 道 结算与发票信息: 结算方式：上月21日至本月的20日为一个结算周期，当月20日为本月的结算截止日期。结算时根据甲方检验合格 及双方共同签认的凭证计算当月实际收货数量。 管 支付条件：结算完成后，甲方在收到乙方开具的正式的增值税专用发票后第1个月支付该批物资结算金额的70%， 第12个月支付20%，剩余10%在第18-24月内按月均衡支付。 发票种类：增值税专用国发票 发票抬头：中铁二局集团有限公司 税号：9151中0100MA61RKR7X3 其他要求： 交货信息: 交货方式:点数验收 收货人:刘健 收货人联系方式:13540650091 其他说明事项: 流水号：询2026081800458 交 标的 规格 计量 标的编号 数量 技术标准及要求 货 送货地址 名称 型号 单位 期 蓝色PVC袖阀管，外 西南区-重庆市-市辖区-渝中区-重 袖阀 径60mm，壁 庆市菜园坝立交以西，龙家湾隧道 0950999183764 - 23188.0 米 管 厚4.5-5mm PVC管，承压 以东，菜袁路以北，王家坡以南的 不小于5MPa,节长4m 地块内，原重庆站。 报价网址:http://www.crecgec.com 信息来源:https://www.chinapipe.net/project/d3075317.html cqdingjiu 2026.08.21 10:06:56 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
@@ -3931,7 +4135,11 @@
           <t>涪陵区蔺市街道农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区蔺市街道农村供水保障能力提升工程（一期） 名称 招标 法人 或招 标人重庆水务环境控股集团渝东自来水有限公司 名称 网 （盖 章） 项目 批准 文件涪陵发改〔2026〕474号 及文 号 主要 务 建设新建、更换配水管网 396.72km（dn20-dnl60PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收及污泥浓缩处理系统。 内容 拟 招招标文 合同预 招标 交 序 标件计划 估金 备 项目招标内容 易 号 方发布时 额(万 注 名称 场 式间 元) 所 商 重 庆 涪陵 市 区蔺 招标 市街 涪 项目 道农 陵 公 区 村供 新建、更换配水管网 396.72km（dn20-dnl60PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收 开 公 1 水保 2026-09 3611.91 及污泥浓缩处理系统。 招 共 障能 道 标 资 力提 源 升工程 交 （一 易 期） 中 心 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075278.html 管 cqdingjiu 2026.08.21 10:06:57 国 中</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>配水管网：396.72km</t>
+        </is>
+      </c>
       <c r="N53" t="n">
         <v>80</v>
       </c>
@@ -3998,7 +4206,11 @@
           <t>涪陵区李渡街道农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区李渡街道农村供水保障能力提升工程 名称 招标 法人 网 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 务 项目 批准 文件 涪陵发改〔2026〕469号 及文 号 商 主要 改造李渡街道 15个村（社区）配水主支管道，更换配水主管网 193.71 千米（DN250-DN40 抗菌耐磨涂塑钢管、dn40-dn25PE管）及配套 建设 附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治 3座，新建测控井78座。 内容 招 拟 标 道 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 称 管 涪 陵 区 重 李 庆 渡 市 街 国 招标 涪 道 项目 陵 农 公 区 村 改造李渡街道 15个村（社区）配水主支管道，更换配水主管网 193.71 千米（DN250-DN40 抗菌耐磨涂 开 公 1 供 塑钢管、dn40-dn25PE管）及配套附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治 3座，新建 2026-09 2372.74 招 共 水中测控井78座。 标 资 保 源 障 交 能 易 力 中 提 心 升 工 程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075277.html cqdingjiu 2026.08.21 10:06:57</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>配水主管网：193.71千米；泵站：1座；集成泵站：4座</t>
+        </is>
+      </c>
       <c r="N54" t="n">
         <v>80</v>
       </c>
@@ -4065,7 +4277,11 @@
           <t>涪陵区珍溪镇农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目名称 涪陵区珍溪镇农村供水保障能力提升工程（二期） 招标法人 或招标人 重庆水务环境控股集团渝东自来水有限公司 网 名称（盖 章） 项目批准 文件及文 涪陵发改〔2026〕477号 务 号 (一)本项目对珍溪镇23个村(社区)安装配水管网660km及配套附属设施，其中：1.De160~De40的PE管 主要建设 有232km；2.连接各村社的De32~De20的PE管有381km；3.219~32的衬塑钢管47km。(二)购置安装泵 内容 站14座(一用一备共计28台水泵)，其中新建泵商站10座、更换泵站4座及配套电力设施;新建不锈钢水 箱2座等。(三)购置安装(0~25kg)减压阀61个;排污阀(25kg）3个。 招标项目名 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 称 式 划发布时间 场所 (万元) 道 (一)本项目对珍溪镇23个 村(社区)安装配水管网660km 及配套附属设施，其 中：1.De160~De40的PE管 管 有232km；2.连接各村社 涪陵区珍溪 重庆市 的De32~De20的PE管有381km； 招标项目 镇农村供水 涪陵区 3.219~32的衬塑钢 公开招 1 保障能力提 2026-09 公共资 2182.77 管47km。(二)购置安装泵 标 升工国程（二 源交易 站14座(一用一备共计28台水 期） 中心 泵)，其中新建泵站10座、更 换泵站4座及配套电力设施; 新建不锈钢水箱2座等。(三) 中 购置安装(0~25kg)减压阀61 个;排污阀(25kg）3个。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075275.html cqdingjiu 2026.08.21 10:06:57</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>配水管网：660km；的衬塑钢管：47km；泵站：4座；泵站：10座；换泵站：4座</t>
+        </is>
+      </c>
       <c r="N55" t="n">
         <v>90</v>
       </c>
@@ -4132,7 +4348,11 @@
           <t>涪陵区蔺市街道农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区蔺市街道农村供水保障能力提升工程（二期） 名称 招标 法人 网 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 务 项目 批准 文件 涪陵发改〔2026〕475号 及文 号 商 主要 八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长 105.307km（dn20-dn40PE 建设 管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建 1座改造3座；新建测控井 52座。 内容 拟 招 招标文 合同预 招标 交 序 道 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 所 重 庆 涪陵 管 市 区蔺 涪 招标 市街 陵 项目 道农 公 区 村供 八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长 开 公 1 水保 105.307km（dn20-dn40PE 管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建 1座改造3座； 2026-09 2652.89 国 招 共 障能 新建测控井 52座。 标 资 力提 源 升工程 交 （二 易 期） 中 中 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075274.html cqdingjiu 2026.08.21 10:06:57</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>管网：105.307km；泵站：1座</t>
+        </is>
+      </c>
       <c r="N56" t="n">
         <v>80</v>
       </c>
@@ -4195,7 +4415,11 @@
           <t>重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目项目公告 重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目（项目名称）比选公告 1.比选条件 本比选项目重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目（项目名称），比选人为重庆市排 网 水有限公司，比选项目资金来自企业自筹（资金来源），项目已具备比选条件。中标后合同与重庆市豪洋水务 建设管理有限公司签订。现对本项目进行公开比选，诚邀有兴趣的潜在投标人参与投标。 2.项目概况与比选范围 务 2.1 建设地点：重庆市巴南区 2.2 项目概况：本项目涉及管道为鱼洞污水处理厂专件厂线管网，管道编号为WD4-WD8+1,该管道为自流管道， 位于鱼轻桥至河嘴倒虹井段，主要用于收集输送鱼洞大江商至华熙片区的生活污水。该段管道管径为DN600，管道 为混凝土管，主要采用架空明敷的方式沿河敷设。该管道自建成投运以来已有20余年，管道及污水井老化严重现 象十分明显，容易出现破损从而造成污水溢流，造成环保风险。为规避环保风险且保障该段管道以及鱼洞污水 厂的正常收水及运行，需对该段管道进行改造。 道 2.3 比选范围：拆除现状管道为DN600混凝土管，同时需拆除并新建9座检查井。 2.4 工期要求：30日历天，以甲方通知进场时间为准。 管 2.5缺陷责任期要求：24个月 3.投标人资格要求 国 3.1 本次比选要求投标人须具备以下条件： 3.1.1 本次比选要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰级 及以上资质。 中 3.1.2 投标人还应在人员、设备、资金等方面具有相应的施工能力，详见比选文件第二章投标人须知前附表第1.4.1 项内容。 3.2 本次比选接受不联合体投标。 4.比选文件的获取 4.1 投标人于2026年8月 18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子 版，以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都 视为投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的 一切后果由投标人自行负责。各投标单位应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行供应商注册，填写相关信息，审批过后成为 平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价、递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，将被否决投标。 4.4 比选文件每份售价800元，售后不退。投标单位在递交纸质投标文件时扫描支付，否则比选人拒绝接收其投标 文件。 5.投标文件的递交 5.1 电子投标文件递交时间：2026年8月24日14时30分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年8月24日14时00分至14时30分（北京时间），地点：重庆水务招标采购中心 （重庆市两江新区嘉华路36号重庆水务大厦5楼）。 5.3 投标截止时间：2026年 8月24日14时30分（北京时间）。 网 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 务 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 商 比 选 人：重庆市排水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝中区长江滨江路126号 地 址：重庆市两江新区嘉华路36号重庆水务大厦 道 联 系 人： 黄老师 联 系 人： 黄晓华 电 话： 023-67767416 电 话： 18523396416 管 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3075272.html 国 cqdingjiu 2026.08.21 10:06:57 中</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N57" t="n">
         <v>90</v>
       </c>
@@ -4262,7 +4486,11 @@
           <t>重庆市潼南城区老旧供水管网改造工程招标计划 重庆市工程建设项目招标计划表 项目名称 重庆市潼南城区老旧供水管网改造工程 招标法人或招 标人名称（盖 重庆市潼南自来水有限公司 网 章） 项目批准文件 及文号 务 主要建设内容 改建潼南城区输水主管网约39.63km及配套相应阀门阀件等 招标方 招标文件计 拟交易场 合同预估 序号 招标项目名称 招标内容 备注 式 划发布时间 所 金额(万元) 对城区供水管网上商 重庆市潼南城 老旧阀门阀件、设 区老旧供水管 重庆市潼 招标项目 施设备进行更换， 网改造工程 公开招 南区公共 1 保障供水管网稳定 2026-09 918.00 （城区配套阀 标 资源交易 运行合道理增设部分 门阀件改造工 中心 计量及压力监控、 程） 水质监控等。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3075266.html cqdingjiu 2026.08.21 10:06:58 国 中</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>输水主管网：39.63km</t>
+        </is>
+      </c>
       <c r="N58" t="n">
         <v>80</v>
       </c>
@@ -4329,7 +4557,11 @@
           <t>关于为【重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购】公开选取【工程设计】 机构的公告 我单位在重庆市网上中介超市公开选取工程设计中介服务机构，现将相关事项公告如下： 该项目为直接选取项目，由采购人从报名的中介服务机构中直接选定一家中介服务机构进行项目服务。 项目 重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购 名称 网 采购 重庆市开州区河堰镇人民政府 人 投资 审批 否 务 项目 是否 破产 商 业务 否 服务 项目 采购 道 所需 中介 其他 服务 事项 管 所需 服务 工程设计 类型 项目实施地点为国河堰镇清泉社区，项目建设内容为：硬化2米宽生产便道5.5千米，100方防旱池1口，50方 服务 蓄水池1口，标准自动化育苗大棚1个，蔬菜小棚20个，水源处理设施1套，水肥一体化配套设施1套，新 内容 建50平方米设备管理房，完善蔬菜基地配套设施等。工程总投资335万元。选取此项目设计单位（含预算 编制服务）。 中 中介 机构 资质（资格）要求 要求 资质 （资 1、报名单位提供有效的营业执照，资质证书（资质丙级或丙级以上），具备从事项目设计服务工作； 2、 格） 具有独立承担民事责任的能力； 3、具有良好的商业信誉和健全的财务会计制度； 4、具有履行合同所必 要求 需的专业技术能力； 5、有依法缴纳税收和社会保障资金的良好记录。 说明 其他 要求 无 说明 服务 时限 无要求，按照合同双方自行约定 说明 服务 3.1%费率 金额 金额 按文件要求执行 说明 选取 直接选取 方式 需规 避机 构 规避 原因 选取 2026-08-20 16:00:00 （选取时间到达后不接受报名，建议中介机构至少在选取开始半小时前完成报名。） 时间 采购 人业 网 务咨 重庆市开州区河堰镇人民政府（18716685679） 询电 话 采购 务 需求 26清泉社区项目设计服务采购说明.pdf 书下 载 商 2026-08-18 信息来源:https://www.chinapipe.net/project/d3075198.html 道 cqdingjiu 2026.08.21 10:06:58 管 国 中</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N59" t="n">
         <v>90</v>
       </c>
@@ -4396,7 +4628,11 @@
           <t>重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目招标公告 1.招标条件 本招标项目重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目已由重庆市开州区发展和改革委员会以开州 发改审〔2026〕357号批准建设，项目业主为重庆市开州区长沙镇人民政府，建设资金来自开州区2026年中央和 市级提前批财政衔接推进乡村振兴补助资金，项目出资比例为 100% ，招标人为重庆市开州区长沙镇人民 政府。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：开州区长沙镇桔香村 2.2 项目概况与建设规模：1.建设果园水肥一体化系统1套，对示范柑桔果园建设水肥一体智能化系统;2.果园运输 线4000米(含轨道主机、叉车、周转箱、三轮车等配套设施设备);3.建设排灌站一处;4.建设1.8米宽生产便道2000米， 务 周转场300平方米;5.配备载重无人机1台、小型挖机1台、电子控制屏1个;6.建设智慧平台与监测系统软硬件系统等。 2.3 本项目工程总投资金额： 500万元 本次招标项目合同估算金额： 446.278921万元 商 2.4 招标范围：招标人发布的由重庆中煜华资工程技术有限公司设计的《重庆市开州区2026年长沙镇桔香村柑橘 基地改造提升项目》施工图及图纸说明、招标文件(含补遗)及工程量清单、答疑资料、澄清资料范围内所涉及的 工作内容，具体以招标人发布的工程量清单及道施工图为准。 2.5 工期要求： 150日历天 缺陷责任期要求： 12个月 管 2.6 标段划分（如有）： / 2.7 其他： / 国 3.政府采购工程 3.1 是否属于政府采购工程：是 中 3.2 是否专门面向中小企业预留：否，按照《政府采购促进中小企业发展管理办法》第六条第(三)“按照本办法 规定预留采购份额 无法确保充分供应、充分竞争，或者存在可能影响政府采购目标实现的情形”的规定，故本 项目不专门面向中小企业预留。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包叁级及以 上资质或市政公用工程施工总承包叁级及以上资质或水利水电工程施工总承包叁级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在 重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）下载招 标文件、工程量清单、电子图纸等资料。参与投标的投标人需在 重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）完成市 场主体信息登记以及CA数字证书办理，办理方式请参见 重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、 重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）导航栏“主体信息”页面中“市场主 体信息登记”、“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完 成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区） （https://www.cqggzy.com/kaizhouweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告 发布至2026-08-21 17:00:00前。 5.3招标人应于2026-08-25 23:59:59前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源 交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）发布澄清。 6.投标文件递交的内容 网 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-21 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 务 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区） （https://www.cqggzy.com/kaizhouweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交 易监督网上发布。] 商 8.联系方式 招 标 人: 重庆市开州区长沙镇人民政府 代理机构: 重庆毅仁建设项目管理有限公司 重庆市开州区文峰街道天鹅湖社区富厚街158号附10 地 址: 重庆市开州区长沙镇山花街1号 地 址: 道号 邮 编: 邮 编: 项目负责人: 丁敬余 项目负责人: 谭毅 电 话: 15826368887 管电 话: 13452653126 传 真: 传 真: 电子邮箱: 1415705480@qq.com 电子邮箱: 开户银行: 国 开户银行: 账 号: 账 号: 监督部门:中重庆市开州区公共资源交易管理局 电 话: 023-52218977 2026年08月17日 重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目 户名 开户行 投标保证金账号 重庆市开州区公共资源交易中心 重庆农村商业银行股份有限公司开州支行 3401010120010012772000200 中国农业银行股份有限公司重庆开州支行营 重庆市开州区公共资源交易中心 314401010400104500000006031 业部 中国工商银行股份有限公司重庆开州支行营 重庆市开州区公共资源交易中心 9558853100005824176 业部 重庆市开州区公共资源交易中心 重庆银行股份有限公司开州支行 680101040007547-100984 重庆市开州区公共资源交易中心 中国银行股份有限公司重庆开州支行 108865555576VA00149 信息来源:https://www.chinapipe.net/project/d3075199.html cqdingjiu 2026.08.21 10:06:58</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N60" t="n">
         <v>90</v>
       </c>
@@ -4463,7 +4699,11 @@
           <t>万盛城区老旧供水管网更新改造工程答疑及补遗(一) 万盛城区老旧供水管网更新改造工程 答疑及补遗（一） 各潜在投标人： 现将万盛城区老旧供水管网更新改造工程答疑及补遗（一）相关条款通知如下： 网 一、答疑 问题1：请问招标人是否委派业主专家参与评标吗？ 务 答：是，本项目评标委员会共7人，其中在重庆市综合评标专家库随机抽取5人，招标人代表2人。? 问题2：本项目是否采用异地评标方式？ 答：是 。 商 问题3：本项目是否有业主代表，如有，请明确业主代表数量。 答：是，本项目评标委员会共7人，其中在重道庆市综合评标专家库随机抽取5人，招标人代表2人 。 问题4：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 答：可以。 管 问题5：污水处理厂提标改造及附属管道施工业绩满足吗？ 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 国 问题6：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可以 不填(空白)，对此有无要求？ 答：无要求。? 中 问题7：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖章， 请问需要提供联合体协议书吗？ 。 答： 根据招标文件第二章“投标人须知前附表”1.4.1 第3条业绩要求中：“注：（2）投标人提供的业绩为联 合体业绩的，其在该业绩中的工作分工应与本项目承担的工作一致。”要求，故需要提供联合体协议书。 问题8：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要求”吗？ 答：填写“达到招标文件的要求”或按照招标文件相关条款填写具体内容均可 。 问题9：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 答：投标人的工程量清单单项报价不得为零报价(招标人提供的工程量清单单项最高限价中金额为零的除外)或者 负数报价，否则由评标委员会作否决投标处理。 问题10：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知书发 出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予提前注 销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 答：需要。但不将加盖正本作为评审因素。 问题11：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收，请 问我公司业绩满足业绩要求吗？ 答：不满足。? 问题12：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 答：可以 。 问题13：业绩要求的竣工时间是指竣工验收时间吗？ 答：是的。 网 问题14：重庆市电子招投标系统投标文件-报价部分“己标价工程量清单”-“投标总价”页面招标人名称需要填 写吗？ 务 答：由投标人自行决定是否填写，是否填写不作为评审因素。 问题15：请问招标人是否委派业主专家参与评标吗？ 答：是，本项目评标委员会共7人，其中在重庆市综合评商标专家库随机抽取5人，招标人代表2人。 问题16：自来水厂或者净水厂含管道施工业绩满足业绩要求吗？ 答：投标人提供的业绩合同规模和工程类别需道满足招标文件要求。? 问题17：有没有人行贿专家，有的话我们就不参加了。 答：本项目评标委员会由招标人按法律法规及相关规定依法组建。 管 问题18：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要 提供其他格式之外的其他承诺？ 答：请各潜在投标人仔国细阅读招标文件，并按招标文件要求提供相应承诺。 问题19：财务报告可以不提供财务报表附注吗？ 答：可以。 中 问题20：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 问题21：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、注册证 及在本单位注册的证明文件替代？ 答：退休证等材料不能替代养老保险证明，按招标文件执行。? 问题22：本项目是异地评标吗？ 答：是。 问题23：现在除了没有警戒线和技术方案的低价项目评标专家不被围猎，哪个项目不围猎评标专家，请问招标人 如何保证公平？ 答：本项目招标文件严格按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本（2026年版）》编制， 且本项目评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 问题24：没有低价警戒线怎么保证中高价呢？ 答：本项目未设置低价警戒线，通过综合评估法对各潜在投标人进行评审。分值由技术、商务、报价组成，综 合实力优良的投标人合理中高价可依靠综合得分优势参与竞争，同时招标文件履约追责条款约束投标人理性报 价，保障合理报价竞争环境。 问题25：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗？ 答：现场递交纸质保函原件的人员不作要求 。 问题26：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 网 答：电子投标系统中锁定不可修改的格式（如封面、投标函）直接填空即可，其他投标文件格式以加盖公章的 招标文件PDF文件为准。? 问题27：专业分包业绩满足业绩要求吗？ 务 答：不满足。 问题28： 市政道路包含给水管网施工业绩满足业绩要求吗？ 商 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 问题29：技术负责人在资格审查部分中提供了工程类高级及以上职称证后，在商务部分中再提供工程类高级及以 上职称证可以加分吗？ 道 答：可以。 问题30：万盛的项目挂綦江来投这样都还控制不了还全是你们万盛公司中的？是有啥猫腻是吧？参考之前的项目 管 全是万盛的公司中的！业主、专家全是你们自己人吧？ 答：本项目招标文件严格按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本（2026年版）》编制， 且本项目评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 国 二、补遗 1、本次重新发布本项目的工程量清单，在《重庆市公共资源交易网》(綦江区) （https://www.cqggzy.com/qijiangweb/）网上发布，请投标人自行下载。 中 招 标 人：重庆市万盛经济技术开发区城市管理局 招标代理机构：重庆力圣建设工程咨询有限公司 2026年8月18日 信息来源:https://www.chinapipe.net/project/d3074975.html cqdingjiu 2026.08.21 10:06:58</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N61" t="n">
         <v>80</v>
       </c>
@@ -4530,7 +4770,11 @@
           <t>重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告 重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告 1.招标条件 本招标项目 重庆市巴南区土桥片区内涝积水整治工程已由重庆市巴南区发展和改革委员会以巴南发改审 发[2025]33号文批准建设，项目业主为重庆市巴南区住房和城乡建设委员会，代建业主为重庆市巴南公路建设有 限公司，建设资金来自区级财政资金统筹，项目出资比例为 100%，招标人为重庆市巴南公路建设有限公司。 项目已具备招标条件，现对该工程的勘察设计进行公开招标，评标办法采用综合评估法。 网 2.项目概况与招标范围 2.1 建设地点：重庆市巴南区花溪街道、李家沱街道 务 2.2 项目概况与建设规模：为解决片区内涝问题，在李家沱街道、花溪街道改建 d400-d800 雨水管网 9665m，管材 采用高密度聚乙烯(HDPE)缠绕结构壁管 B型管；改建 d1商000-d1400雨水管网 664m，管材采用高密度聚乙 烯(HDPE)缠绕结构壁管 B 型管、III 级钢筋混凝土管；改建 d1500-d2000 雨水管网 426m，管材采用III 级钢筋混凝 土管;改建 d2100-d2600 雨水管网 1000m，管材采用 III 级钢筋混凝土管；修复雨水管网 5345m，增加智能感知设 备6 套。 道 2.3 本项目工程总投资金额：13477.10万元 管 本次招标项目工程费估算金额：11061.83万元 国 本次招标项目勘察设计合同估算金额：334.544万元 中 2.4 招标范围：主要包括勘察、施工图设计（包含高边坡、深基坑）和相应阶段的勘察工作，以及提供施工现场 全过程技术服务，并配合业主办理相关手续等，具体范围为： （1）勘察部分：完成本项目范围内的勘察工作，包括但不限于排水管网排查、1:500地形图测量、地质钻勘、管 线内窥、物探、综合管线测量，市政管网错混接点测量及调查等工作，解决区域地下空间臭气问题，勘察成果 需达到重庆市城市建成区排水管网排查技术导则的要求，并配合业主完成对应的成果审查等事宜。 （2）设计部分：包括不限于完成本项目的施工图设计、施工期间交通组织设计、桥梁（涉轨）安全论证方案及 施工期间至竣工验收阶段，质量保修阶段的设计配合服务，配合办理施工图审查相关手续及竣工验收阶段、质 量保修阶段的设计服务等工作以及协助招标人完成各项审批手续办理等工作。 2.5 勘察设计服务期限：30日历天 2.6 标段划分（如有）：/ 2.7 其他：/ 3.政府采购工程 3.投标人资格要求 3.1 本次招标要求投标人须具备以下条件： 网 3.1.1 本次招标要求投标人具备的资质条件： 务 投标人应同时具有建设行政主管部门颁发的下列勘察和设计两类资质： 商 I、投标人应具备下列勘察资质之一： 道 ①工程勘察综合甲级资质。 管 ②工程勘察专业类（岩土工程）专业甲级资质和工程勘察专业类（工程测量）甲级资质； 国 II、投标人应具备下列设计资质之一： 中 ①工程设计综合甲级资质； ②工程设计市政行业甲级资质； ③工程设计市政行业(燃气工程、轨道交通工程除外)甲级资质； ④工程设计市政行业(排水工程)甲级资质。 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的勘察设计能力，详见招标文件第二章投标人须知 前附表第1.4.1项内容。 3.2 本次招标接受联合体投标。联合体投标的，应满足下列要求：联合体组成单位数量不超过2家，由负责设计 任务的单位作为联合体牵头人。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件及其附件、澄 清、修改、补充通知、最高限价通知等资料。参与投标的投标人需在重庆市公共网资源交易网完成市场主体信息 登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息 登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程 电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 务 布至2026-08-23 12:00:00前。 4.3招标人应于2026-08-26 17:00:00前在重庆市公共资源交易网发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-24 09:30，投标人应当在投标截止时间前，通过互 商 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督道网、重庆市公共资源交易网、重庆市公共资源交易网（巴南区） 发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 重庆市巴南公路建设有限公司 代理机构: 重庆云远项目管理有限公司 管 地 址: 重庆市巴南区龙洲大道265号 地 址: 重庆市九龙坡区渝隆大厦28楼 邮 编: 邮 编: 项目负责人: 牟老师 项目负责人: 李强 国 电 话: 023-66238079 电 话: 023-68434996 传 真: 传 真: 电子邮箱: 电子邮箱: 中 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市巴南区发展和改革委员会 电 话: 023-66221670 2026年08月18日 重庆市巴南区土桥片区内涝积水整治工程勘察设计 户名 开户行 投标保证金账号 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000001675 贸易试验区分行 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051304894 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020041267 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764210157 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000682897 支行 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835000509 坝支行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146639123 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630018252 信息来源:https://www.chinapipe.net/project/d3074953.html cqdingjiu 2026.08.21 10:06:58 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>d800 雨水管网：9665m；d1400雨水管网：664m；d2000 雨水管网：426m；d2600 雨水管网：1000m；雨水管网：5345m</t>
+        </is>
+      </c>
       <c r="N62" t="n">
         <v>95</v>
       </c>
@@ -4597,7 +4841,11 @@
           <t>重庆管道公司2026年涪陵压气站管道、设备防腐项目-非招标公告 公告发布时间: 2026年08月18日09时02分19秒 一、概述 1.2.1项目概况：涪陵作业区涪陵压气站空压机、阀门等设备、消防泵房消防管道、循环水管道油漆出现锈蚀情况， 为保证设施安全运行，对站场设备、消防管道及附属钢结构进行打磨除锈、油漆防腐。 二、采购项目与标段 交货期限: 开工之日起90日内完工 网 质保期限(月): 标段 序号 标段名称 标段描述 编号 重庆管道公司2026年涪陵 涪陵作业区涪陵压气站空压务机、阀门等设备、消防泵房消防管道、循 1 1 压气站管道、设备防腐项 环水管道油漆出现锈蚀情况，为保证设施安全运行，对站场设备、消 目 防管道及附属钢结构进行打磨除锈、油漆防腐。 三、供应商资格要求 商 *1、响应人资质要求（1）响应人必须是依照中华人民共和国法律在国内注册，具备合格有效的营业执照的法人、 其他组织；与采购人存在利害关系可能影响询比采购公正性的法人、其他组织或者个人，不得参加响应。单位 负责人为同一人或者存在控股、管理关系的不同单位，不得参加同一标段响应或者未划分标段的同一询比项目 响应。（2）响应人须具备防水防腐保温工程专业承包二级及以上资质。*2、信誉要求响应人在响应文件提交截 止当日不存在以下情况：（1）响应人被“国道家企业信用信息公示系统”网站（www.gsxt.gov.cn）列入严重违法 失信企业名单（响应文件提交截止时间前已移出的除外）。（2）响应人被“信用中国”网站 （www.creditchina.gov.cn）列入严重失信主体名单（响应文件提交截止时间前已移出的除外）。（3）响应人或其 法定代表人、负责人、拟委任的项目经理被“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）列入失信 被执行人名单（响应文件提交截止时间前已移出的除外），响应文件中需提供有效身份证号供查询。（4）响应 管 人、拟委任的项目经理被“全国建筑市场监管公共服务平台”网站（https://jzsc.mohurd.gov.cn/home）列入黑名单 （响应文件提交截止时间前已移出的除外）。上述（1）-（4）条以评审当日评审小组从官网查询信息为准。（5） 被国家管网集团或西南管道公司暂停、取消投标资格或业务承揽资格。（6）法律、行政法规规定的其他不允许 参与投标的情况。 国 四、询比文件的获取 4.1 有意向参加项目者，于2026年08月20日09时05分22秒前，登录数字供应链平台进行项目报名。 中 4.2 报名成功后于2026年08月18日09时01分42秒至2026年08月24日09时05分22秒，登录数字供应链平台进行项目下 载询比文件。 五、响应文件的递交 5.1 请于2026年08月24日11时00分00秒前，登录数字供应链平台递交项目响应文件。 5.2 逾期将无法进行递交响应文件，采购人将不予受理。 5.3 供应商在递交响应文件前，应按照有关规定提供人民币0万元项目保证金。 六、响应文件的开启 6.1 响应文件的开启时间2026年08月24日11时06分00秒 6.1 响应文件的开启地点供应链系统上 七、采购人信息 地址： 邮编： 联系人：舒建华 联系电话：18581824001 电子邮件：shujh@pipechina.com.cn 传真： 开户银行： 账户名： 账号： 信息来源:https://www.chinapipe.net/project/d3074904.html cqdingjiu 2026.08.21 10:06:59 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
@@ -4664,7 +4912,11 @@
           <t>重庆燃气集团股份有限公司输配分公司大渡口调压站至二郎调压站次高压燃气管线工程(大渡口段)公告 采购 公告 公告编号： RQXYGG202608130064 一、采购项目基本情况 网 采购人：重庆燃气集团股份有限公司输配分公司 采购项目编号：RQCGXY202608130040 务 采购项目名称：大渡口调压站至二郎调压站次高压燃气管线工程（大渡口段） 采购内容或范围：安装部分： ①材料验收（甲供材料：阀门、管材、弯头、标志桩等）、运输及履带式挖掘机及人工布管； ②管道管件安装， 新旧管道的碰口；③安装DN400直埋球阀1座； ④管道和商焊口的除锈及防腐； ⑤管道下沟后15KV电火花检测； ⑥管道的清管，强度及严密性试验；⑦警示带敷设和线路标志桩（砖）安装； ⑧监检手续等。 土建部分： ①清表； ②扫线、平整场地； ③沟槽、基坑、阀井砌筑； ④回填土方； ⑤余方弃置； ⑥人工开挖人行道（花 台），公路及路面恢复； ⑦其他线缆穿跨越工道程施工，交通组织； ⑧水工保护等。 （具体内容详见施工图纸和 工程量清单） 公告发布时间 ：2026-08-18 14:39:10 管 二、采购人联系方式 联系人：王瑶 电话：023-67502265 国 邮箱：wangyao232@crcgas.com 三、采购明细 中 行号 采购内容 需求数量 单位 补充说明 拟邀请单位 大渡口调压站至二郎调压站次高压燃气管线 重庆燃气安装工程有限责任公 1 1 项目 无 工程(大渡口段) 司 四、服务费交纳 本项目不收取服务费。 五、 其他 事项 1.本公告在华润守正 采购交易 平 台（ https://www.szecp.com.cn/ ）上公开 发布。 2. 本项目采购通过守正平台线上进行，供应商需注册华润守正 采购交易 平台，通过平台进行响应文件的递交或 报价，具体操作步骤可查阅网站首页帮助中心的操作手册，也可以联系守正客服。 3 .答疑澄清、通知等文件一经在华润守正 采购交易 平台发布，视为已发放给相应供应商（发放时间即为发出时 间），请随时关注华润守正 采购交易 平台发布的相关信息，并及时查阅和处理。 4 .若有参与意向 ， 请于 2026-08-22 00:00:00前联系采购人 （联系方式见公示内容）反馈。 5 .若有异议 ， 请于 2026-08-22 00:00:00前提出异议 。 信息来源:https://www.chinapipe.net/project/d3074793.html cqdingjiu 2026.08.21 10:06:59 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N64" t="n">
         <v>80</v>
       </c>
@@ -4731,7 +4983,11 @@
           <t>石柱公司2026-2027年度用户供水管道安装及管网抢(维)修工程(第二次)项目公告 石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程（第二次）（比选公告 1.比选条件 本比选项目石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程（第二次）（项目名称），比选人 为重庆石柱水利水电实业开发有限公司，比选项目资金来自企业自筹（资金来源），项目已具备比选条件。现 对本项目进行公开比选，诚邀有兴趣的潜在投标人参与投标。 网 2.项目概况与比选范围 2.1 建设地点：比选人指定地点 务 2.2 项目概况与建设规模：2026-2027年度用户供水管道安装及管网抢（维）修服务 2.3 本次比选项目合同估算金额：约280万元 商 2.4 比选范围：完成石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程包括公司供水范围内用户 各类管道及管件安装、水表安装及更换、阀门安装等、并完成配套土建工程、零星签证等工程量清单所列项目、 管网抢维修和公司所属生产单元零星项目，具体内容详见第五章 工程量清单。 道 2.5 工期要求：1年 缺陷责任期要求：24个月 管 3.投标人资格要求 3.1 本次比选要求投标人须具备以下条件： 国 3.1.1 本次比选要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰级 及以上资质； 3.1.2 投标人还应在人员、设备、资金等方面具有相应的施工能力，详见比选文件第二章投标人须知前附表第1.4.1 中 项内容。 3.2 本次比选不接受联合体投标。 4.比选文件的获取 4.1 投标人于2026年08月18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子版， 以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都视为 投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的一切 后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价，递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，被视为无效。 4.4比选文件每份售价1000 元，售后不退。投标人在递交纸质投标文件时支付，否则比选人拒绝接收其投标文 件。 5.投标文件的递交 5.1电子投标文件递交时间：2026年08月24日10时00分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年08月24日09时30分至10时00分，地点：水务集团招标采购中心（重庆市两江新 区嘉华路36号重庆水务大厦五楼）。 5.3 投标截止时间：2026年08月24日10时00分（北京时间）。 网 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 务 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 商 比 选 人：重庆石柱水利水电实业开发有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市石柱土家族自治县都督大道11号 地 址：重庆市两江新区嘉华路36号重庆水务大厦1018 联 系 人：王老师 联 系 人：颜老师 道 电 话：13658292968 电 话：023-67901915 重庆水务电子商务平台咨询电话：管023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3074720.html cqdingjiu 2026.08.21 10:06:59 国 中</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N65" t="n">
         <v>90</v>
       </c>
@@ -4794,7 +5050,11 @@
           <t>万盛城区老旧供水管网更新改造工程(甲供材料)答疑(一) 万盛城区老旧供水管网更新改造工程（甲供材料） 答疑（一） 各潜在投标人： 现将万盛城区老旧供水管网更新改造工程（甲供材料）答疑（一）相关条款通知如下： 网 一、答疑 问题1：请问招标人是否委派业主专家参与评标吗？ 务 答：是，本项目评标委员会共7人，其中在重庆市综合评标专家库随机抽取5人，招标人代表2人。 问题2：万盛的项目挂綦江来投这样都还控制不了还全是你们万盛公司中的？是有啥猫腻是吧？参考之前的项目 全是万盛的公司中的！业主、专家全是你们自己人吧？ 商 答：本项目招标文件严格按照《重庆市工程建设项目货物采购招标文件示范文本（2026年版）》编制，且本项目 评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 问题3：3PE管道部分壁厚是多少呢？ 道 答：本项目采购的3PE防腐钢管的管道部分壁厚须符合国标标准并达到设计要求。 招 标 人：重庆市万盛经济技术开发区城市管理局 管 招标代理机构：重庆力圣建设工程咨询有限公司 2026年8月18日 国 信息来源:https://www.chinapipe.net/project/d3074712.html cqdingjiu 2026.08.21 10:06:59 中</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N66" t="n">
         <v>80</v>
       </c>
@@ -4857,7 +5117,11 @@
           <t>重庆中法供水2026年普通防腐钢管及管件采购项目(第三次)项目公告 重庆中法供水2026年普通防腐钢管及管件采购项目（第三次）比选公告 1.比选条件 本比选项目重庆中法供水2026年普通防腐钢管及管件采购项目（第三次），比选人为重庆中法供水有限公司，比 选项目资金来自企业自筹，出资比例为100%，项目已具备比选条件。现对本项目进行公开比选，诚邀有兴趣的 潜在投标人参与投标。 网 2.项目概况与比选范围 2.1 普通防腐钢管及管件采购清单： 务 序号 存货编码 材料名称 规格型号 单位 数量 最高单价限价（元） 1 10400177 钢高频焊管 D89*4 5 米 61.92 2 10400181 钢高频焊管 D108*5 300 米 88.89 商 3 10400182 钢高频焊管 D159*5 5 米 132.18 4 10400206 钢高频焊管 D159*6 5 米 152.13 5 10400290 钢螺旋焊管 DN219*6 5 米 196.68 道 6 10400291 钢螺旋焊管 DN219*8 5 米 244.80 7 10400292 钢螺旋焊管 DN325*8 5 米 361.28 8 10400293 钢螺旋焊管 DN377*8 5 米 423.12 管 9 10400294 钢螺旋焊管 DN426*8 5 米 475.89 10 10400295 钢螺旋焊管 DN426*10 5 米 574.29 11 10400297 钢螺旋焊管 DN529*8 5 米 595.76 国 12 10400298 钢螺旋焊管 DN529*10 5 米 718.91 13 10400299 钢螺旋焊管 DN630*10 5 米 861.50 14 10400300 钢螺旋焊管 DN720*10 5 米 987.95 中 15 10400301 钢螺旋焊管 DN820*10 5 米 1133.08 16 10400302 钢螺旋焊管 DN920*10 5 米 1279.51 17 10400304 钢螺旋焊管 DN1020*10 5 米 1424.64 18 10400305 钢螺旋焊管 DN1020*12 5 米 1652.24 19 10400306 钢螺旋焊管 DN1220*10 5 米 1709.70 20 10400307 钢螺旋焊管 DN1220*12 5 米 1982.83 21 10400308 钢螺旋焊管 DN1420*12 5 米 2375.96 22 10400309 钢螺旋焊管 DN1420*14 5 米 2697.83 23 10400332 钢螺旋焊管 DN1120*10 5 米 1574.96 24 10400342 钢螺旋焊管 DN1020*14 5 米 1879.02 25 10400322 钢螺旋焊管（特加强） DN820*10 5 米 1133.08 26 10200490 钢套筒 D159*500cm 5 个 159.00 27 10200491 钢套筒 D219*500cm 5 个 240.00 28 10200492 钢套筒 D273*500cm 5 个 300.00 29 10200493 钢套筒 D325*500cm 5 个 361.00 30 10200494 钢套筒 D377*500cm 5 个 436.00 31 10200495 钢套筒 D426*500cm 5 个 482.00 32 10200589 钢套筒 D159*1000cm 5 个 226.00 33 10200590 钢套筒 D219*1000cm 5 个 1627.00 34 10200591 钢套筒 D273*1000cm 5 个 2501.00 35 10200592 钢套筒 D325*1000cm 5 个 488.00 36 10200593 钢套筒 D377*1000cm 5 个 591.00 网 37 10200598 钢套筒 D426*1000cm 5 个 833.00 38 10200155 钢制标准接头 D108 5 个 91.00 39 10200156 钢制标准接头 D159 5 个 160.06 务 40 10200157 钢制标准接头 D219 5 个 319.41 41 10200158 钢制标准接头 D273 5 个 396.63 42 10200159 钢制标准接头 D325 5 个 475.96 商 43 10200160 钢制标准接头 D426 5 个 619.87 44 10200161 钢制标准接头 D529 5 个 779.22 45 10200162 钢制标准接头 D630 5 个 1068.44 道 46 10200163 钢制标准接头 D720 5 个 1214.46 47 10200164 钢制标准接头 D820 5 个 1428.34 48 10200165 钢制标准接头 D920 5 个 1600.14 管 49 10200169 钢制标准接头 D1220 5 个 2297.57 50 10200170 钢制标准接头 D1420 5 个 3027.02 51 10200171 钢制标准接头 D1020 5 个 2194.19 国 52 10300309 钢制大小头 DN65*DN50 5 个 14.74 53 10200667 钢制渐缩 D108＞57 3 个 21.06 54 10200668 钢制渐缩 D108＞89 3 个 26.00 中 55 10200695 钢制渐缩 D159＞108 3 个 40.72 56 10200671 钢制渐缩 D219＞159 3 个 68.09 57 10200672 钢制渐缩 D219＞108 3 个 80.03 58 10201605 钢制渐缩 219*125 3 个 75.82 59 10200694 钢制渐缩 D273＞108 3 个 129.87 60 10200673 钢制渐缩 D273＞159 3 个 94.07 61 10200674 钢制渐缩 D273＞219 3 个 84.94 62 10200675 钢制渐缩 D325＞108 3 个 184.63 63 10200676 钢制渐缩 D325＞159 3 个 143.91 64 10200680 钢制渐缩 D325＞219 3 个 131.98 65 10200677 钢制渐缩 D325＞273 3 个 124.25 66 10200684 钢制渐缩 D426＞325 3 个 285.01 67 10200685 钢制渐缩 D529＞325 3 个 617.76 68 10200679 钢制渐缩 D529＞426 3 个 547.56 69 10200659 钢制渐缩 D630＞325 3 个 756.00 70 10200687 钢制渐缩 D630＞426 3 个 728.00 71 10201539 钢制渐缩 D630＞529 3 个 722.00 72 10200690 钢制渐缩 D720＞630 3 个 848.00 73 10200691 钢制渐缩 D720＞529 3 个 842.00 74 10200682 钢制渐缩 D820＞720 3 个 913.00 75 10200692 钢制渐缩 D920＞720 3 个 1053.00 76 10201519 钢制渐缩 D920*820 3 个 1064.00 77 10200652 钢制渐缩 D1020＞820 3 个 1305.00 网 78 10200693 钢制渐缩 D1020＞920 3 个 1322.00 79 10201738 钢制渐缩 1220*820 3 个 1806.00 80 10201507 钢制渐缩 1220＞1020 3 个 1834.00 务 81 10201624 钢制三盘三通 D108⊥108 3 个 224.64 82 10200371 钢制三盘三通 DN200⊥100 3 个 435.24 83 10200373 钢制三盘三通 DN200⊥200 3 个 599.51 商 84 10201531 钢制三通 108*108 3 个 58.97 85 10200285 钢制三通 219*108 3 个 187.43 86 10201341 钢制双盘短管 89*400mm 3 个 139.00 道 87 10201342 钢制双盘短管 89*800mm 3 个 178.31 88 10201340 钢制双盘短管 108*300mm 3 个 158.65 89 10201299 钢制双盘短管 DN108*500mm 3 个 185.33 管 90 10201300 钢制双盘短管 DN108*1000mm 3 个 258.34 91 10201301 钢制双盘短管 DN108*1500mm 3 个 329.94 92 10201332 钢制双盘短管 159*300mm 3 个 251.32 国 93 10201339 钢制双盘短管 159*750mm 3 个 348.19 94 10201303 钢制双盘短管 DN159*1000mm 3 个 402.95 95 10201304 钢制双盘短管 DN159*1500mm 3 个 508.25 中 96 10201305 钢制双盘短管 DN219*500mm 3 个 463.32 97 10201306 钢制双盘短管 DN219*1000mm 3 个 672.52 98 10201307 钢制双盘短管 DN219*1500mm 3 个 876.00 99 10201312 钢制双盘短管 DN219*750mm 3 个 581.26 100 10201338 钢制双盘短管 273*1250mm 3 个 1010.88 101 10201458 钢制双盘渐缩 108*57 3 个 109.51 102 10201469 钢制双盘渐缩 108*89 3 个 117.94 103 10201514 钢制双盘渐缩 159*108 3 个 185.33 104 10201748 钢制双盘渐缩 200*80 3 个 294.84 105 10201462 钢制双盘渐缩 219*108 3 个 256.93 106 10201513 钢制双盘渐缩 219*159 3 个 280.80 107 10201465 钢制双盘渐缩 D273＞108 3 个 339.77 108 10201467 钢制双盘渐缩 D273＞219 3 个 388.91 109 10201770 钢制双盘渐缩 D273＞159 3 个 365.04 110 10201461 钢制双盘渐缩 325*219 3 个 477.36 111 10301108 钢制弯头 89*90° 3 个 28.78 112 10200702 钢制弯头 D108×90° 100 个 43.52 113 10200701 钢制弯头 D159×90° 3 个 84.24 114 10200705 钢制弯头 D219*90° 3 个 231.66 115 10200706 钢制弯头 D273*90° 3 个 300.46 116 10200709 钢制弯头 D325*90° 3 个 418.39 117 10200711 钢制弯头 D426*90° 3 个 744.12 118 10200712 钢制弯头 D529*90° 3 个 1352.05 网 119 10200764 钢制弯头 D570*90° 3 个 1474.20 120 10200714 钢制弯头 D630*90° 3 个 1535.98 121 10200715 钢制弯头 D720*90° 3 个 1742.36 务 122 10200717 钢制弯头 DN720*90°*12mm 3 个 1989.47 123 10200720 钢制弯头 D920*90° 3 个 2935.30 124 10200722 钢制弯头 D820*90° 3 个 2325.23 商 125 10200762 钢制弯头 D1020*90° 3 个 4829.55 126 10200723 钢制弯头 D1220*90° 3 个 6039.80 127 10200724 钢制弯头 D1420*90° 3 个 8297.00 道 注：管材按照米数进行报价，管件按照件数进行报价。 2.2 供货数量、时间和批次：根据工程实际进度与比选人的要求进行供货，以实际供货量为准，供货时间达到商 务条款的规定。 管 2.3 交货地点：比选人指定的施工现场。 2.4 供货期：两年。 国 3.投标人资格要求 3.1 本次比选允许投标人以投标货物的下列身份参加投标： 中 ?制造商 3.1.1 投标人为制造商应符合以下要求： 投标人必须是依法设立的，并在中国注册的，具有独立法人地位的企业。 【提供有效的营业执照】 3.2 投标人2025年的年度财务状况不亏损。 【提供由会计师事务所或审计机构出具的无保留意见的财务审计报告及会计报表，财务报表至少包括现金流量 表、资产负债表、利润表】 3.3 投标产品的制造商须通过质量ISO9001、环境ISO14001、职业健康体系ISO45001认证。 【提供有效的证书】 3.4 投标人须提供2023年1月1日至投标截止日止（以合同签订时间为准）,签订的30万元及以上的钢管及管件产品 购销合同至少1个。 【提供采购合同、不低于前述金额50％的发票，合同与发票的项目名称须一致】 注：①若投标人开具的发票上未能体现具体项目，需附上税务出具的发票清单（清单上需显示采购项目为钢管 及管件产品）。 ②若提供的合同为年度合同未体现具体金额，但实际供货金额达到30万元及以上，应提供与该合同对应的30万元 及以上的钢管及管件产品发票作为佐证。 3.5 投标人须为所投投标产品制造商，此次所提供的普通防腐钢管及管件必须是自己工厂所制造的产品，不得外 购他人产品。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函及工商部门出具的本产品商标或品牌证明文件】 3.6 投标产品过水部分涉及的涂料须提供行政主管部门出具的有效的“卫生许可网批件”及卫生疾控中心出具的卫 生检测报告。 【提供行政主管部门出具的有效的“卫生许可批件”及卫生疾控中心出具的卫生检测报告】 务 3.5 根据本次采购清单及技术规范的要求，投标人须承诺具备相关的技术手段和措施、保证产品设计使用寿命 20 年以上。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 商 3.6 投标人须承诺保证5年内不得停产同型号的投标产品。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 道 3.7 办事机构和库房【比选人有权对中标人的办事机构及库房进行实地核查，若发现与提供资料不符，将视为提 供虚假资料，按相关规定取消其中标资格，其投标保证金不予退还。】 投标人承诺：收到中标通知书后30日内提供租赁合同或产权证明，并提供重庆库房卫星定位图片。 管 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 【卫星定位图片：手机打开地图，搜索该地址、进行标注，然后截图或者电脑打开地图（地图软件不限），搜 索该地址、选择卫星模国式、进行标注、然后截图均可。】 3.8 符合第五章“技术要求”普通防腐钢管及管件技术要求。 【根据技术要求提供技术响应表，并根据技术条款要求提供对应的检测报告等。】 中 3.9 售后服务承诺【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】： 1）货物交付及付款方式要求，满足第四部分合同协议书第3条及第10条；供货单位应确保产品的及时供应，承诺 因产品供应不及时造成的一切损失均由供货单位负责赔偿。 2）有完整的售后服务方案、培训计划并在合同签订后为比选人免费提供培训服务。 3）售后服务承诺书，满足第四部分合同协议书第11条；承诺质保期后提供2年及以上定期免费巡查、保养计划。 4）承诺接到分派的工单1小时内联系用户约定维修时间，在24小时内处理完毕工单，且让用户满意。若工单超时、 未在规定时间内告知比选人维修时间或工单处理未让用户满意造成返单的，按比选人制度进行处罚。 3.10 投标人承诺不得存在下列情形之一： 1）被人民法院列入失信被执行人名单且在被执行期内； 2）被国家、重庆市（含市或任意区县）有关行政部门行政处罚，且在处罚期限内； 3）投标截止日前两年内（指2024年1月1日至投标截止日止），投标人或其法定代表人被人民法院判定犯行贿罪 的； 4）投标截止日前五年内（指2021年1月1日至投标截止日止），投标人与重庆中法供水有限公司有违约情况或终 止合同情况的。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 3.11 投标截止日前五年内（指2021年1月1日至投标截止日止），投标人无在我司因产品及服务等对公司生产、经 营、安全造成不良影响的记录；若投标人出现过供水通报事项，因产品质量问题对生产、安全造成影响，存在 合同违约等问题，不予参加本次项目投标。 【按照第六章 三、资格审查部分“无不良记录承诺函”提供承诺函，若经验证承诺函不属实，将对中标人作否 决投标处理。】 网 3.12 投标样品要求： 3.12.1 投标人需提供以下规格型号数量的样品： 务 【①钢螺旋焊管 DN219*8 壹件 ②钢制弯头 D108*90°壹件】，提供的样品应满足第五章技术要求规定。样品为 投标人免费提供，管材样品不低于20CM，不计入采购清单内。 3.12.2 投标样品同投标文件一并递交。每件样品上分别标明样品的投标人、生产厂家、品牌、名称、规格、型号等 （格式自拟），投标样品必须密封装箱，且在密封包装外商贴样品一览表（格式自拟），注明提供样品的投标人、 生产厂家、品牌、名称、规格、型号、数量等。 3.12.3 投标人的样品在开标当日递交至样品区（样品区地点：开标当日咨询比选代理机构），中标人的投标样品 不退还，其余投标人的样品在中标公示期满后道5个工作日内退还，如不领取，投标样品按废品处理。 3.12.4 上述对投标样品的密封和标识要求是为便于评标，请投标人积极配合，未按上述要求对投标样品进行密封 和标识的，不作否决投标处理，但由此造成的其他后果由投标人自行承担。 管 3.13 若投标人违反重庆中法供水有限公司《供应商负面清单管理办法》规定且在处罚期内的，按否决投标处理 （评标委员会根据比选公告后附“供应商负面清单”进行评审）。 3.14 本次比选不接受联合体投标。 国 特别说明： （1） 本比选文件要求提供的所有检测报告须为近2年内的检测报告（2024年1月1日-投标截止日），此要求不包 括卫生许可批件及其检测报告。 中 （2） 上述所须提交的相关证明材料复印件均应加盖投标单位法人章并装入投标文件资格审查部分中。上述有一 条不满足则投标文件由评标委员会作否决投标处理。 （3） 比选人有权对投标人提供的以上资料进行核实，若发现存在弄虚作假，取消其投标、中标资格，投标人承 担因此造成的相关责任并赔偿相应损失。 4.比选文件的获取 4.1 投标人于2026年8月18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子版， 以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都视为 投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的一切 后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价，递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，被视为无效。 4.4比选文件每份售价 500 元，售后不退。投标人在递交纸质投标文件时扫描支付，否则比选人拒绝接收其投标文 件。 5.投标文件的递交 5.1电子投标文件递交时间：2026年8月26日14时30分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年8月26日14时00分至14时30分，地点：水务集团招标采购中心（重庆市两江新 区嘉华路36号重庆水务大厦五楼。导航：重庆水务大厦东门）。 5.3 投标截止时间：2026年8月26日14时30分（北京时间）。 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 网 6.发布公告的媒介 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 务 7.联系方式 比 选 人：重庆中法供水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝北区悦来镇悦来水厂 地 址：重庆市两商江新区嘉华路36号重庆水务大厦10楼1018 联 系 人：陈老师 联 系 人：周洲 电 话：023-67585971 电 话：18602396399 道 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3074673.html 管 cqdingjiu 2026.08.21 10:06:59 国 中</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
@@ -4924,7 +5188,11 @@
           <t>南岸区茶园片区乡镇老旧供水管网更新改造工程更正公告 南岸区茶园片区乡镇老旧供水管网更新改造工程更正公 告 发布日期： 2026年8月18日 网 首次公示日期： 2026年8月14日 更正日期： 2026年8月18日 采购人名称： 重庆市江南城市建设发展（集团）有限公司务 采购人地址： 重庆市南岸区米兰路51号电子信息标准化厂房2号楼 联系人： 赵老师 商 电话： 023-62820331 采购代理机构名称： 重庆多杰数字科技咨询服务有限公司 采购代理机构地址： 重庆市重庆市经开区重庆市经开区长生桥镇江峡路8号13-1幢1楼 道 经办人名称： 李佩奇、戴沛轩、李倩 联系电话： 023-67648437 本项目比选范围修改为：在项目动工前完成水土保持方案审批程序，项目建设过程开展 更正事项： 水土保持监管测工作。 https://www.gec123.com/notices/detail/1665701682723590144 信息来源:https://www.c国hinapipe.net/project/d3074669.html cqdingjiu 2026.08.21 10:07:01 中</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N68" t="n">
         <v>80</v>
       </c>
@@ -4987,7 +5255,11 @@
           <t>中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部排水钢管询价采购公告 中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 排水钢管询价采购公告 询价编号：ZT1105-XJ-2026-561-1 尊敬的各潜在供应商: 网 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与中铁十一局集团有限公司宜涪高铁重庆段站 前3标项目经理ZT1105-XJ-2026-561-1，排水钢管材料的报价。 一、项目概况 务 中铁十一局集团宜涪高铁3标项目，位于重庆市石柱土家族自治（县）。合同金额28.01亿元，合同工期73个月， 开工日期：2024年12月，竣工日期：2030年12月。主要工程：新方斗山隧道(10660m)、石板坡隧道(4148m)、城北 隧道(3228m)、刘家坪隧道(2077m);刘家店子1号大桥工程(224.096m)、刘家店子2号大桥(232.099m)、城北大 桥(330.241m)、冉家湾大桥(355.245m),采用移动模架和支商架法现浇施工，其中24米移动模架施工6孔；32米支架法 施工5孔，移动模架施工28孔;正线铺无砟道床43.808Km。 二、询价内容 道 本次计划对排水钢管、GG-01材料进行询价，询价内容如下： 询价物资一览表 管 序号 包件号 物资名称 规格型号 计量单位 数量 备注 1 GG-01 排水钢管 Φ200*6m 米 3000 Q235B，壁厚6mm 合计 3000 国 说明：1.表中数量为计划数量，实际采购过程中可能有所调整，最终结算按照实际采购数量结算。 2.收货地点：中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 中 三、技术质量及报价要求 1. 此次排水钢管、GG-01各项技术性能：Q235B 碳素结构钢无缝钢管，符合 GB/T8163 标准。质量需满足甲方项 目部正常使用的要求，保证产品的质量合格，满足试验室检测所有要求，详见技术规格书。 2.报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、结算及付款方式 自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发票认证完成之日起第6个月，支付至本次结算 金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内，累计支付总额不超结算总金额的75%，剩 余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理末次结算后第二年，支付金额应大于等于 尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总额的15%；办理末次结算后第四年，全部 付清）。 五、报价人资格要求 1.营业范围要求：在中华人民共和国境内依法注册、符合项目经营范围，具有询价物资生产或供应经验 的生产商或代理商，并且具有合法有效的营业执照。 2.生产能力要求：生产商须具备询价物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定。代 理商需出具制造厂出具签字盖章的授权函。 3.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8 月至今）国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；需满足排水钢管的相关所 有要求。 4.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年12月至今）企业或企业法定代表人有人民法院生效判决、裁 定认定的行贿犯罪记录的。④ 对纳入国家铁路局“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接 受通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合 作方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 网 5.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 务 ★6.下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 六、报价人需要提供的资料 1.营业执照复印件、法人身份证复印件、开户许可证、授商权委托书、报价表和报价人资格要求中所需的证明资料， 所有资料需加盖公司鲜章。 2.生产厂家资质，产品质量检测报告等质量证明文件。 道 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、询价报名截止时间 管 有意参加本次询价采购的报价人须在铁建云链平台（https://www.crccep.cn）完成供应商注册，并于2026年8月18 日9时00分至2026年8月21日9时00分在网上完成报名工作。 八、询价截止时间 国 凡有意参加本次询价采购的报价人，请于 2026年8月21日14时00分 前提交报价。截止时间前未完成报价文件传 输的，视为放弃报价。 供应商报价必须严格按照《报价表》格式进行报价。 中 九、联系方式 采购组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村71号 采购人名称：中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 地址：重庆市石柱土家族自治县金彰工业园区C区中铁十一局项目部 联系人：罗先生 联系电话：18580400001（提供采购服务支持） 中铁十一局集团有限公司 物资设备集中采购管理中心第五分中心 2026年8月18日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3074654.html cqdingjiu 2026.08.21 10:07:01 网 务 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>排水钢管 Φ200*6m：3000米</t>
+        </is>
+      </c>
       <c r="N69" t="n">
         <v>90</v>
       </c>
@@ -5050,7 +5322,11 @@
           <t>中铁建设集团(重庆)建设有限公司重庆协同创新区供冷供热能源站及配套系统工程冷却塔、分集水器、水板式热 交换机组采购竞价补遗公告二 各 投标单位 ： 根据参加报名的潜在投标单位数量不满足招标方充分竞价要求的情况，此次重庆协同创新区供冷供热能源站及 配套系统工程冷却塔、分集水器、水板式热交换机组采购竞价资格预审报名截止日期将延期至 8月19日（周三） 上午9:00。 特此说明。 网 中铁建设集团（重庆）建设有限公司 2026年8月17日 务 信息来源:https://www.chinapipe.net/project/d3074650.html cqdingjiu 2026.08.21 10:07:01 商 道 管 国 中</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N70" t="n">
         <v>80</v>
       </c>
@@ -5117,7 +5393,11 @@
           <t>城口县东安及河鱼片区污水管网建设项目(一期)招标计划表 重庆市工程建设项目招标计划表 项 名 目 称城口县东安及河鱼片区污水管网建设项目（一期） 招标 法人 或招 标人城口县生态环境局 名称 （盖 网 章） 项目 批准 文件 及文 号 主 建 内 要 设 容 在 污 城 水 口 处 县 理 东 站 安 1座 镇 ， 等 改 片 建 区 后 新 设 建 计 污 规 水 模 管 20 网 0m 29 3 . / 0 d 0 。 km，其中新建dn110污水管5.80km，dn160污水管2.75km，dn200污水管0.57km，DN300污水干管4.36km，D 务 N400污水干管8.12km，DN200压力管7.4km,以及建设配套泵站2座,化粪池56座，隔油池32座。改扩建 序号 招标项目名称 招标内容 招标方式 招标文件计划发布时间 拟交易场所 合同预估金额(万元) 备注 招 项 标 目1 城 建 口 设 县 项 东 目 安 （ 及 一 河 期 鱼 ） 片区污水管网 工程施工 公开招标 2026-09 城 易 口 中 县 心 公共资源交 3400.00 本 暂 为 计 定 准 划 ， 。 表 最 所 终 列 以 招 实 标 际 项 招 目 标 信 时 息 的 均 信 为 息 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3074602.html 商 cqdingjiu 2026.08.21 10:07:01 道 管 国 中</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>dn110污水管：5.80km；dn160污水管：2.75km；dn200污水管：0.57km；DN200压力管：7.4km；泵站：2座</t>
+        </is>
+      </c>
       <c r="N71" t="n">
         <v>90</v>
       </c>
@@ -5180,7 +5460,11 @@
           <t>阀门产业园(管网改造)项目招标公告 阀门产业园（管网改造）项目招标公告 1.招标条件 本招标项目 阀门产业园（管网改造）项目已由垫江县发展和改革委员会以垫江发改委发【2022】459 号（批文 名称及编号）批准建设，项目业主为 垫江县丹香建设有限公司，建设资金来自 自筹资金 （资金来源）， 项目出资比例为 100% ，招标人为 垫江县丹香建设有限公司。项目已具备招标条件，现对该项目的施工进 行公开招标，评标办法采用经评审的最低投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 重庆市垫江县高新区县城组团 2.2 项目概况与建设规模： 场平面积800亩；新建厂房10000平方米，并完善相关基础配套设施等；新建道路 务 长4000米，包括道路、综合管网等基础配套设施等。 2.3 本项目工程总投资金额：55000万元 本次招标项目合同估算金额：184.669075万元 商 2.4 招标范围： 包括土石方开挖回填、砼支墩、污水管道安装、检查井砌筑、河堤修复等。具体详见施工图和 工程量清单。 道 2.5 工期要求：建设工期180日历天 缺陷责任期要求：24个月 管 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 国 3.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 中 4.1.1 本次招标要求投标人具备的资质条件： 具备建设行政主管部门颁发的有效的市政公用工程施工总承包叁 级及以上资质 ； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标 不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （垫江县）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（垫江县）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资 源交易监督网、重庆市公共资源交易网（垫江县）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 4.2投标人可在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）本项目招标公告网页下方“我要 提问”栏提出疑问，提问时间从本公告发布至2026-08-24 09:00:00前。 4.3招标人应于2026-08-24 23:59:59前在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-18 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 垫江县丹香建设有限公司 代理机构: 重庆博钰大数据科技有限公司 地 址: 地 址: 重庆市垫江县桂溪街道南内街88号 网 邮 编: 邮 编: 项目负责人: 熊老师 项目负责人: 郭威 电 话: 023-74630098 电 话: 023-74692498 务 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 商 账 号: 账 号: 监督部门: 垫江县发展和改革委员会 电 话: 023-74517161 道 2026年08月18日 信息来源:https://www.chinapipe.net/project/d3074578.html cqdingjiu 2026.08.21 10:07:02 管 国 中</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
       <c r="N72" t="n">
         <v>90</v>
       </c>

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购公告</t>
+          <t>中建四局(四川)建设有限公司总部重庆交通大学双福校区三期建设项目(图情中心组团)工程总承包(EPC)项目雨水管网工程采购公告</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -527,47 +527,47 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>渝中区</t>
+          <t>江津区</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购</t>
+          <t>包括雨水检查井、钢筋砼承插式雨水管道铺设、中粗砂回填等内容</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PVC管,PE管,袖阀管</t>
+          <t>雨水管网工程</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管 材询比采购公告 中铁十一局集团有限公司建安分公司招标采购中心就中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房 及配套综合交通枢纽工程CQZSG-2标段项目经理部管材组织询比采购，诚邀有意向的合格供应商参与报价。 一、项目概况及询比采购内容 1.1项目概况 网 （1）新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程位于重庆市中心渝中区中部，具体位置为菜园 坝立交桥以西，龙家湾隧道以东，菜袁路以北，王家坡以南。正在建设的地铁18号线贴临站房北侧，地铁26/27 号线从站区地下通过。项目共划分为4个施工标段，CQZSG-1标段：为国铁站房、地铁站台区域；站北路密不可 分的边坡及场坪工程，包含土石方工程和边坡支护工程，不含机电工程，由中铁建设承建。CQZSG-2标段：为 务 枢纽配套工程，地铁区间、西广场、成都局剩余还建，由中铁十一局承建。CQZSG-3标段：地铁区间、CTC、 站场、东广场，由中铁建工承建。CQZSG-4标段：人防车库、铁路自营车场、综合开发生产配套房屋等，由中 铁二局承建。 （2）标段概况：我方负责新建重庆至黔江铁路重庆站站商房及配套综合交通枢纽工程CQZSG-2标段全部施工内容 （简称B区），主要包含：（1）B区投影范围内盖板以下27号线、26号线明挖区间基坑支护、土石方、区间主体 结构及配套防水、综合接地工程（不含砌筑墙体、装饰装修和机电安装工程），以及承轨层以下市政排水 涵DK1+196（196m）和行包通道；（2）轨道交通26号线暗挖隧道预留工程，其中26左线487m，26号右线408m； （3）站北路E、F、H连接匝道工程，其中E匝道道247m、F匝道285.5m、H匝道174m；（4）B区盖板及以上还建房 屋，其中西侧盖板约3.56万㎡，还建房屋等总建筑面积约3.50万㎡。 1.2询比内容 详见拟采购货物一览表 管 二、供应商资格要求 2.1供应商必须是“中国铁建云链平台”注册并通过审核的供应商。 2.2本次询比采购不接受国被列入“《2026年中国铁建合作方警示名录》、《中铁十一局集团有限公司不良行为供 应商名录》、《JD采购网失信名单》（此项核查针对JMRH项目）”中的供应商,不接受近一年内在铁路建设工程 网公布有违法行为记录及物资供应不良记录、被中国铁路总公司限制投标或已清退出铁路市场的供货商（此项 核查针对铁路站房项目），不接受在铁建云链平台被标记的不良行为供应商。 中 2.3供应商在报价时，如是法定代表人签字的需提供法定代表人身份证复印件、如是法人授权代理人签字的需提 供授权委托书及被授权人身份证复印件。 2.4询比响应供应商需提供营业执照复印件。 2.5其它要求：提供样品、每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌 等质量证明文件，甲方凭此报告检验质量。 2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 三、拟采购物资及相关要求 3.1拟采购物资一览表 交 序 物资 型号 单 项目 货 交货日 数量 备注 号 名称 规格 位 名称 地 期 址 重 直 庆 径6:0mm 市 包含车 PVC 批次交 壁 渝 丝、黑 1 （袖 米 7100 货与零 厚4:-45.mm 中 色胶布、 阀管） 星交货 单节 新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 区 管筛、 （具体 长4m CQZSG-2 标段项目经理部 菜 管箍、 以项目 园 堵头等 通知为 坝 一切相 准） 直 网 重 关费用 2 PE管 米 7100 径2:5mm 庆 站 合计 14200 务 3.2技术规格书： 按询比文件第二章项目技术规格书执行 商 3.3结算和付款 3.3.1采购物资报价规则： 道 固定价格。 3.3.2付款方式 （1）货款支付方式：支付方式包管括但不限于银行转账、银行汇票、银行本票、支票、银行承兑汇票、商业承兑 汇票、财务公司票据、供应链票据、其他数字化信用凭证，票据贴息费用由 供货单位 承担。 （2）付款周期：本合同无预付款。甲方在收到乙方提交的合规增值税专用发票，并经税务机关认证通过后次月 支付乙方上月供应期所国供合格物资70%货款，全部货物供应完毕后三个月内付至95%，剩余货款暂时扣留作为质 量保证金，供货完毕后，由乙方提交结算确认单，经甲方审核通过后做最终结算，待所有物资验收合格后12个月 内无息付清。 （3）逾期付款约定：如甲方付款逾期，双方秉持“长期合作，友好往来”原则，在逾期付款行为发生后一年内 中 乙方不向甲方收取逾期付款利息。若一年甲方仍未支付款项，需向乙方支付逾期付款利息，逾期付款利息起算 时间为全部款项到期之日一年后至付清之日，逾期利息的利率为合同订立时中国人民银行授权全国银行间同业 拆借中心公布的一年期贷款市场报价利率(LPR)1倍。 3.4拟采购物资相关的要求 3.4.1本次询比为整体采购，询比响应供应商报价时须写明单价、到站价和运距，报价包含货物制造、运输、装卸、 售后服务等交付采购人使用前所有可能发生的费用，收到报价后不再增补任何费用。 3.4.2交货期：按照采购人规定的期限内分批次运抵交付。 3.4.3供货地点：甲方指定的甲方所属 中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通 枢纽工程CQZSG-2标段项目施工现场。 3.4.4询比响应供应商必须保证产品的质量及售后服务。询比响应供应商提供的货物制造标准及技术规范等，必须 符合最新相关国家标准、部颁标准相关标准和规范的要求，进场提供相关检验检测报告。 3.4.5采购方在确定成交供应商后有权对成交产品的结构、规格做适当调整，调整内容将以工作联系函形式提前发 至供应商。 3.4.6售后服务：本批采购货物若在验收阶段出现不符合规格或质量标准，供应商必须接受退货要求，并在采购人 规定期限内等量补运合格产品，若未按时交付影响采购人使用，供应商必须承担由此给采购单位造成的后续经 济损失。 3.4.7报价方不得虚报各项技术指标，所供货物若不能符合技术要求，成交供应商必须接受全额退还货款，并承担 由此给采购单位造成的经济损失。 3.4.8验收方法及标准 （1）验收依据：询比采购文件、厂家货物技术标准说明及国家有关的质量标准规定，均为验收依据。 （2）货物验收：货物运抵采购人指定交货处后由双方对照采购清单及技术要求进行验收。 （3）其它要求：每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌等质量证 明文件，甲方凭此报告检验质量。 网 （4）2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 四、报价文件递交 务 4.1此次报价供应商需制作电子报价文件，在递交截止时间前线上递交报价文件。 4.2报价文件递交截止时间：2026年08月24日15时00分。 商 4.3报价文件递交地点：中国铁建云链平台（www.crccep.cn），供应商须登录该平台，在报价文件递交截止时间 前完成所有报价文件资料的上传。 五、发布公告的媒介 道 本次询比公告发布媒体:中国招标投标公共服务平台(www.cebpubservice.com)、中国铁建云链平台（www.crccep.cn） 上同时发布。 管 六、联系方式 1.采购组织单位：中铁十一局集团有限公司建安分公司招标采购中心 地 址：湖北省武汉市国武昌区丁字桥路47号 联 系 人：张先生 联系电话：027-87258521 中 电子邮件：2454774350@qq.com 2.采购人：中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 CQZSG-2 标段项 目经理部 地 址：重庆市渝中区菜袁路59号 联 系 人：金先生 联系电话：16607273445 电子邮件：2285445503@qq.com 2026年08月21日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3077066.html cqdingjiu 2026.08.21 10:06:40</t>
+          <t>中建四局(四川)建设有限公司总部重庆交通大学双福校区三期建设项目(图情中心组团)工程总承包(EPC)项目雨 水管网工程采购公告 一、采购概况 1.采购名称：【重庆交通大学双福校区三期建设项目（图情中心组团）工程总承包（EPC）项目雨水管网工程】。 2.工程概况：【1.项目概况：本项目规划用地82876.94㎡，总建筑面积约108691.83㎡，其中9#行政楼建筑层 数6F/-2F，建筑高度为31.5m，10#图书馆建筑层数8F/-2F，建筑高度为57.1m，11#研究生楼建筑层数6F/-1F，建筑 高度为31.5m，12#地下车库建筑层数-2F，建筑高度为-8.7m。2.结构类型：所有楼栋主要结构形式为框架结构3.工 网 程地点: 重庆市江津区福星大道1号】。 3.标段划分：【本工程仅一个标段】。 4.采购内容：【重庆交通大学双福校区三期建设项目（图情中心组团务）工程总承包（EPC）项目雨水管网工程， 包括雨水检查井、钢筋砼承插式雨水管道铺设、中粗砂回填等内容，详见工程量清单】。 5.质量要求：【（1）质量标准：（1）工程施工的质量要求：工程质量应符合强制性质量标准，符合国家和重庆 市现行有关施工质量验收规范要求，并达到合格标准。商 （2）质量创优目标：/ 】。 6.工期要求：【暂定开工日期：2026年9月15日，竣工日期：2027年10月30日，总工期410日历天】。 道 7.文明要求：【（1）安全控制目标：杜绝发生重伤及以上生产安全责任事故，安全轻伤事故率小于1‰；不发生 社会影响较大的其他事故或险肇事件。 （2）安全生产、文明施工达到《管建筑施工安全检查标准（JGJ59-2011）》合格要求。 （3）杜绝机械设备事故、火灾事故和公共安全事故、防止职业病发生；贯彻落实《职业病防治法》、《职业健 康监护技术规范》等国家法律法规要求，关爱员工健康，不发生职业健康损誉事件。 国 （4）创优目标：市级建筑施工安全文明工地】。 8.付款条件：【 中 （1）月进度付款，按照甲方累计确认的已完合格工程量工程价款的【75】%，挂账后于60天内支付应付进度款； （2）乙方完成承包范围内全部工作内容并经甲方经验收合格，挂账后于60天内付款至已完成合格工程量工程价 款的【80】%。 （3）乙方完成承包范围内的全部工作内容并经验收合格及有关部门备案，且双方完成最终结算后，于60天内支 付至合格工程结算总价的【97】%，剩余【3】%作为工程质量保修金。养护期2年，扣除已发生的维护费用后， 甲方无息退还剩余保修金。 （4）本工程采用【银行转账、供应链（一年期以内）、票据（一年期以内）、以物抵债】方式向乙方支付货款。 如涉及贴息费用，贴息费由【甲】方承担。如由甲方承担贴息费，乙方须提供银行出具的贴息相关证明材料， 贴息费甲乙双方通过结算方式办理，乙方根据结算金额开具发票，贴息所产生的增值税税金由【乙方】承担， 甲方按合同中约定的工程进度款支付条件进行支付，贴息费不再产生逾期利息。】。 9.拟选定成交单位数：【1家】。 二、响应人资格 1.响应人报名前需通过“云筑网”（网址：https://jicai.yzw.cn/home）认证并进入中建系统合格分供商资源库，经 采购人资格审查合格后方可参与报价。 2.响应人须具备以下基本条件： （1）具有公司制独立法人主体资格，经营范围有效，时间有效（提供营业执照、法人身份证复印件、授权委托 书、被委托人身份证复印件等证明资料，在本公司本级资源库内分供商可不提供）； （2）办公场所、组织架构：具有固定的办公场所，公司组织架构合理，人员配置充足（提供企业简介、固定办 公地点影像资料、公司组织架构证明等证明资料，在本公司本级资源库内分供商可不提供）； （3）纳税人资格：提供纳税人证明或税务事项通知等证明资料（在本公司本级资源库内分供商可不提供）； （4）诚信经营：经核查政府平台近两年内无、质量事故通报，云筑网无不良记录，不得存在挂靠，必须为法人 直营单位（提供政府平台（中国裁判文书网、中国执行信息公开网、国家企业信用信息公示系统）查询记录截 图、法人直营承诺书等资料证明，在本公司本级资源库内分供商可不提供）； 网 （5）合法经营：遵守国家法律、依法经营、合约期间无违法犯罪记录、无因管理不善、履约不力导致的案件； （6）历史业绩：根据采购物提供对应业绩资料（提供相关合同关键页等资料证明，在本公司本级资源库内分供 商可不提供） 务 （7）资质：本工程无专业承包资质要求】。 3.响应资格审核不通过的情形： 商 1)在云筑网被本上级单位列为“不良行为分供商”或“禁用分供商”； 2)涉嫌围采串采的，如:法人身份证号重复、法人手机号重复、联系人重复、联系人手机号重复、IP地址重 复、MAC地址重复、邮箱地址重复、工商关联道的不同单位; 3)在严重失信或被执行企业名单； 4)分供商(法人)处于被限制高消费状态、司法拍卖影响企业正常运行、破产清算影响企业正常运营； 管 5)“换马甲”的中建股份、中建四局原禁用单位； 6）响应人未上传采购公告要求之资料，或上传资料不符合要求； 国 4.本次采购【不接受】联合体响应。 5.如响应单位提供虚假资料的，任何时候一经发现，取消其响应资格。 中 三、报名响应 1.响应时间：【以“云筑网”平台显示时间为准】，逾期不再接受响应。 2.响应方式：通过“云筑网”进行网上报名，不接受其他方式响应。 3.已在“云筑网”完成分供商注册的响应人，可直接在“云筑网”签收采购公告后响应。 4.响应担保：本次响应担保为【/】元，响应人应于报价截止日24小时前缴纳。 四、资格审查资料清单及格式 响应人报名时需按资格审查要求上传至云筑网，具体要求：按照顺序签字盖章扫描成一个PDF文件以附件形式上 传云筑网，统一命名为：响应报名文件-****单位，不得上传多个附件或压缩文件，不按要求上传资料的资格审 查不通过。 （一）资格审查资料清单（本级库内单位可不提供）： 1)《分供商准入资格预审表》（见附件1）； 2)法定代表人身份证明(见附件2)； 3)法定代表人授权书(见附件3)； 4)被委托人身份证明(见附件4)； 5)企业证明资料(见附件5)； 6)纳税证明或税务事项通知(见附件6)； 7)诚信经营证明(见附件7)； 8)现场拟派人员证书扫描件(见附件8)； 9)近3年施工类似业绩资料（见附件9）； 网 10)响应单位可提供的其他证明企业情况的资料。 五、发放采购文件 务 1.采购人通过“云筑网”对资格审查合格的响应人发放采购文件。 2.发放时间：【以“云筑网”平台显示时间为准 】。 商 3.联系人：【王青松】，联系方式：【18323827265】，联系地址：【四川省成都市双流区金为创新中心19楼】。 4.其他未尽事宜详见采购文件。 道 六、投诉通道 响应人如遇账款、合同、结算、廉洁、安全、环保、禁用等相关问题，可通过云筑网分供商投诉平台 （https://ts.yzw.cn/complaint）提交投诉材料，平台将按规定予以受理和处理。 管 采购人： 中国建筑第四工程局有限公司 国 信息来源:https://www.chinapipe.net/project/d3078437.html cqdingjiu 2026.08.24 12:31:34 中</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PE管：7100米</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>塑料管不计匹配分</t>
+          <t>重庆, 四川, 管材, 招标, 商机</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>璧山项目钢筋混凝土管询价公告</t>
+          <t>五局三西南(重庆)鑫旭达项目室外管材及预制构件采购公告</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>房建</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -596,49 +596,45 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>璧山区</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本项目位于璧山区，建设范围为双龙大道以北，璧铜线以东、渝蓉高速以南、玉泉湖（璧南河）以西区域，用地面积约6平方公里。项目建设遵循循序渐进、分期、分块实施原则，采用“总体开发、分步实施”的方式进行建设开发，合作期限8年，包含建设期和运营期（缺陷责任期），其中建设期6年，共分三期实施。第一期实施玉泉湖以西，第二期实施璧南河以西，第三期实施渝蓉高速下道口。项目总投资44亿元，其中建安费28.6亿元，含市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。项目开发建设内容包括片区范围内的基础设施、人才教育基地、水系生态整治、绿化及广场、公共交通场等。本次采购的内容为本项目一期实施的市政道路所需的钢筋混凝土管及管件，预计供货时间为2026年8月至2027年4月。</t>
+          <t>中建五局第三建设有限公司鑫旭达西南地区生产基地项目室外管材及预制构件采购</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>项目总投资44亿元，其中建安费28.6亿元，含市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。</t>
+          <t>本次采购估价：28万元</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>钢筋混凝土管及管件</t>
+          <t>室外管材及预制构件</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>璧山项目钢筋混凝土管询价公告 本项目位于璧山区，建设范围为双龙大道以北，璧铜线以东、渝蓉高速以南、玉泉湖（璧南河）以西区域，用 地面积约6平方公里。项目建设遵循循序渐进、分期、分块实施原则，采用“总体开发、分步实施”的方式进行 建设开发，合作期限8年，包含建设期和运营期（缺陷责任期），其中建设期6年，共分三期实施。第一期实施玉 泉湖以西，第二期实施璧南河以西，第三期实施渝蓉高速下道口。项目总投资44亿元，其中建安费28.6亿元，含 市政道路26公里，公共服务设施7.4万方，绿化及广场99万方，河道治理11.9公里。项目开发建设内容包括片区范 围内的基础设施、人才教育基地、水系生态整治、绿化及广场、公共交通场等。本次采购的内容为本项目一期 实施的市政道路所需的钢筋混凝土管及管件，预计供货时间为2026年8月至2027年4月。 网 登录地 mhem&amp;cNh6e0&amp;ce2C2m3s1e71=a64so0d9FAe=0903%e08005206E%6772dm6=%82he29&amp;=cI8p9eeyAs%7t?E%5lB%1iB%a1DetE%c9eweNAi%1iotvB%n/9cE%7.cBe9%ccAiE%p.E%s9%/29址/A%2:：psE%7tAhtD%B8%E%6B%7B%7E%5%78D9%E%5C9%F%9E%7AE%A%1E%9%78%78E%8B%4AD%N&amp;8E%6m657optUa3%6=6290%e3ni51B%5917E%443d6=E%862B%I8eAc%A1iD&amp;88no%tE%4BA%A%4E%7AC%AC%E%4BA%C8%E%8%88AA%E%5A8%A%1E%5B%7A%5E%7A%8B8%E%5B%1%08E%6C9%%98E%9%99%09E%5%58AC%E%5F%8B%8E%8A%5BF%E%9%38A%8EF%BC%%88E%5B9%BD%E%9%99%58EF%BC%%98E%6%59B%0E%5AD%%79E%7BB%F%8E%6B%5E8%E%4BA%A%7E%4B%8A9%E%5B9%AD%E%5C8%BA%E%9%58D8%E%5A%5%79E%9A%1B%9E%7B9%AE%EF%BC%%88E%8A%5BF%E%7%98%78E%5C8%BA%EF%BC%%98E%9A%1B%9E%7B9%AE%E%7=BgB&amp;upC%a=sod&amp;euF%pN=8Flk&amp;cmsusheaE%c7=te%0a9m%6he=8tT&amp;cpS7eeyeE%s9sha%&amp;3c2845d5=pur5A6I&amp;8optUni 信息来源:https://www.chinapipe.net/project/d3077008.html 务 cqdingjiu 2026.08.21 10:06:40 商 道 管 国 中</t>
+          <t>五局三西南(重庆)鑫旭达项目室外管材及预制构件采购公告 中建五局第三建设有限公司重庆城市公司 五局三西南（重庆）鑫旭达项目室外管材及预制构件采购 五局三西南（重庆）鑫旭达西南地区生 产基地项目室外管材及预制构件采购公告 网 采购编号:cscecXXX 务 商 道 采购人：中建五局第三建设有限公司 采购日期： 2026 年 08 月 管 鑫旭达西南地区生产基地项目室外管材及预制构件采购公告 国 中建五局第三建设有限公司鑫旭达西南地区生产基地项目室外管材及检查井采购，现面向社会公开采购，诚邀 符合资格条件、能提供优质服务的国内专业公司参加采购合作事宜。 一、基本情况 中 1、采购组织单位：鑫旭达西南地区生产基地项目 2、本次采购内容：室外管材及预制构件 3、工程地点：重庆市涪陵高新区聚业大道北侧 4、合同履约期限：2026年08月-2027年12月 5、本次采购预估数量：管材4802米；预制构件247个 6、本次采购估价：28万元 7、本次采购报价方式：价税分离单价报价 8、计划进场日期：2026年08月28日 9、响应担保：0.28万元（采购完成后若无违规、不诚信操作可立即退还） 10、质量要求：必须符合相应国家标准，若行业标准或地方标准高于国家标准的，执行行业标准或地方标准。材 料尺寸、外管、环刚度、强度以及用料等均国家符合质量验收标准。 11、品牌要求：管材：顾地、中财、利财、联塑、伟星等同等级品牌。 二、付款方式： 1、支付方式：本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保理、商业承兑汇票、国内信用证、 应收账款电子凭证及其他】常规支付方式的付款方式。 2、过程付款方式：甲方在次月的30日支付上月月度结算货款的【70】%，双方办理完毕最终结算后【60】个日 历天内付至总结算货款（且不超含税合同价款）的【97】%，预留质保金【3】%在保修期满且乙方已履行完所 有的保修责任后付清。甲乙双方协商一致同意本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保 理、商业承兑汇票、国内信用证、应收账款电子凭证及其他】常规支付方式的付款方式，付款过程中产生的贴 息费用及手续费由【乙方】承担，每次付款前乙方应提供结算值【100%】的发票，否则甲方可拒绝付款。 网 三、报名条件： 1、报名参与单位必须是独立的法人单位，具备一般纳税人资格供方优先。报名参与单位在近2年内不曾在任何合 同中违约或因报名参与单位的原因而使任何合同被解除、未发生因自身原因造成的诉讼情况。报名参与单位应 务 具备较强的资源组织能力、供货能力、抗风险能力、售后服务能力和资金实力。响应方应随时接受采购方对响 应方设备性能、合格证、保险资料等进行检查。 2、未被列入失信被执行人、重大税收违法案件当事人名单、政府采购严重违法失信行为记录名单； 商 3、未处于被责令停业、响应资格被取消或者财产被接管、冻结和破产状态； 4、不在中建局及公司、分公司不合格名录/黑名单内； 道 5、单位负责人为同一人或者存在直接控股、管理关系的不同响应人，不得同时参加本工程响应； 6、符合《中华人民共和国采购法》、《政府采购法》等法律法规的要求； 管 7、响应单位报名阶段提供与采购标的物规格型号相符的以下证书，可认定为本次采购的绿色建材分供商：绿色 建材产品一星、二星、三星认证证书；中建绿色建材企业认证证书；绿色产品认证证书；中国环境保护标志证 书；中国节能标志证书；中国森林认证证书；入选工信部和省级绿色工厂，享受绿色建材分供商优惠条件。绿 色建材分供商需将认证证书以电子版或扫描件的形式与报名文件一同上传至云筑网。 国 四、响应报名 1、网络报名地点：响应人登录（http://www.yzw.cn），进入平台，填报企业相关资料，进行网络注册认证，通知 我司进行资审通过后，进行网上报名。 中 2、报名所需提交的资料包括： （1）营业执照，建筑业企业资质证书、安全生产标准化证书复印件(正副本均可)、法定代表人授权书证明原件。 （2）参与单位近两年的工作业绩（主要为所招地区业绩）。 （3）参与单位资信等级证书，质量、环境、职业健康安全管理体系认证书原件。 （4）参与单位可提供的其他证明企业情况的资料。 3、采购文件的获取：经资格审查入围的响应人，将对其发放电子版采购文件，登录中建采购网络交易采购平台 （http://www.yzw.cn），网上获取采购文件电子版，并依据文件要求于平台上响应截止日前进行网上响应。 4、严禁报名IP地址重复，IP地址重复者资审均不通过。 五、对本次采购提出询问，请按以下方式联系： 联系人：杨飞 联系电话：16623122372 中建五局第三建设有限公司 2026年08月20日 附件一： 法定代表人授权书 网 致：中建五局第三建设有限公司 务 本授权书声明：位于 （填公司地址） 的 （填公司名称） 的 （填法人 姓名）代表本公司授权 （填被授权人姓名）为本公司的唯一合法代理人，代表本公司参加中建五局第三建设 有限公司 XX项目XX采购采购活动，并在整个采购活动中，以本公司名义全权处理包括递交企业和产品响应资 质材料，确认响应相关信息，响应产品报价、议价，交纳商相关费用，签订采购合同，执行和完成采购周期内的 售后服务等一切与之有关的事务，并保证所提供的资质证明材料真实、合法、完整、有效。 道 本授权书于： 年 月 日签字生效，特此声明。 授权期限为： 年 月 日起至合同终止。授权期限内无特殊情况不变更合法代理人（被授权 人）。 管 法定代表人(签字) 被授权人(签字) 国 授权单位名称（盖章） 联系电话 中 授权人身份证正面 授权人身份证背面 被授权人身份证正面 被授权人身份证背面 点击查看内容 信息来源:https://www.chinapipe.net/project/d3078389.html cqdingjiu 2026.08.24 12:31:34</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>管材4802米；预制构件247个</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>重庆, 管材, 预制构件, 采购</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购公告</t>
+          <t>秀山县2026年龙池镇、雅江镇基地信息化建设项目-第二次询比公告</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -669,32 +665,32 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>沙坪坝区</t>
+          <t>秀山土家族苗族自治县</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>临水临电材料采购</t>
+          <t>项目服务内容自动农业气象监测系统、土壤墒情监测系统、智能虫情测报系统、杀虫控制系统、水肥一体化、宣传片拍摄等。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>采购概算金额：135万元（含税）</t>
+          <t>采购金额：566037.74元（不含税）。</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>临水临电材料</t>
+          <t>信息化建设类</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购公告 物资采购 【招标公告】中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目(二期)临水临电材料采购 招标编号：cscec2026081900001246027 项目：重庆市第四人民医院科学城院区建设项目（二期） 发布时间：2026-08-20 17:52:30 报名截止：None 区域：重庆市市辖区沙坪坝区 招标品类：其他类 招标（资格预审）公告 网 中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料采购 采 购 文 件 务 采 购 人： 中国建筑第七工程局有限公司 日 期： 2026年8月 商 目 录 一、响应须知 道 二、评审办法 三、响应注意事项 管 四、响应文件的上传 五．响应文件 六、物资设备合同 国 一、响应须知 【公司总部供应链中心业务监督电话：17516461564】 中 1、工程概况： 工程名称：临水临电材料采购 采购名称： 中国建筑第七工程局有限公司重庆区域暨重庆市第四人民医院科学城院区建设项目 (二期)临水临电 材料采购 采购编号： cscec2026081900001246027 项目地址： 重庆市 工程内容：重庆市第四人民医院科学城院区建设项目 (二期)建筑总用地面积15214.5平方米；总建筑面积65020平 方米，其中住院楼22229.9平方米，实验教学楼8103.6平方米，院内生活楼5830.59平方米，高压氧舱315.53平方米， 地下车库28540.38平方米，以及给排水工程、强电工程、弱电工程、消防工程、暖通工程、总图工程等。为参考。 （说明：描述本工程概况）。最终工程规模及内容以上级部门及采购人确定为准。 采购概算金额：135万元（含税）【采购概算金额视为最高采购限价，响应人响应报价高于最高采购限价的，作 无效响应处理】。 2、采购范围及相关要求： （1）资格审查方式： 资格后审 （2）采购联系人：项目联系人： 修经理 ，电话： 17838218888 ，地址：重庆市 公司联系人： 苟经理 ，电话： 19828530610 ，地址：四川省青白江国际贸易产业园10幢 （3）采购内容： 临水临电材料 （4）工程价款支付： 月结方式，即每月20日结算（遇节假日顺延），次月25日前（结算日后35日历天内），乙 方提供与结算等额增值税专用发票后，支付至前月结算额的70%（遇节假日顺延），最终结算办理完毕6个月后 付至最终结算价款的 97%，剩余3%质保金在质保期满后30日内无息支付。（质保期自全部货物供货完毕且验收 合格日起1年计算）（支付工程款时均应扣除根据采购合同应予扣除的其它金额。） 网 3、响应方式： （1）响应保证金缴纳方式 务 响应保证金采用保证金现金或购买保证金保险（二选一）两种支付方式，支付成功后点击页面【去响应】按钮， 响应人方可正常响应。 方式一：保证金现金缴纳： 商 1、本次采购的响应保证金为/元。 2、保证金收款账户信息请参见云筑网保证金支付页面信息。 道 页面显示账户只对公办理，不接受个人汇款，响应人以响应人基本账户或对公账号转账；响应人转账时务必备注 “交易识别码”（具体操作详见附件《供应商保证金操作手册》或可拨打云筑客服电话：4006-818-555） 方式二：保证金保险缴纳： 管 1、保证金保险可替代保证金，购买后无需再缴纳保证金，响应人可通过“云筑网”购买，响应保险费不退 还；(具体操作详见云筑网上传附件《供应商保证金操作手册》） 2、如发生扣除保证金国情况，保险公司按照保险合同约定向采购单位赔偿相关款项后，保险公司代位取得向响应 单位追偿的权利，响应单位应在规定时间内向保险公司支付相应追偿款。 以下情况可免缴本采购项响应保证金： 中 ①工程局A级分供商。 发生以下情况，响应保证金不予退还： ①响应截止后响应人撤销响应文件的，采购人可以不退还响应保证金。 ②成交人无正当理由不与采购人订立合同，在签订合同时向采购人提出附加条件，或者不按照采购文件要求提 交履约保证金的，取消其成交资格。 （2）采购文件领取事宜：响应人根据采购公告内容领取采购文件，然后根据采购文件要求，进行响应，一经报 价即认为响应人对采购文件已作出实质性响应。 （3）采购文件的澄清与修改 ①采购文件的答疑：如响应人发现采购文件有不清楚的地方或对内容有疑问，要求澄清和解答的，均应在距响 应截止时间2天前向采购人提出答疑，采购人应解答响应人提出的问题。 ②采购人允许响应人在响应截止日期之前对云筑网响应进行修改，但必须在响应截止时间之前完成云筑网响应， 逾期未响应的，则视为无效响应。 （4）（4）响应文件递交事宜 采用云筑网电子响应。 4、评审： （1）评审方法：本次采购拟选出 1 名成交人，区段划分：（如选2个及以上，应明确划分各成交人分供范围及工 程量，成交人按照最终排名顺序享有优先选择权）。采用经评审的（原则上应选择合理低价法），在响应文件 能够满足采购文件实质性要求的响应人中，评审出响应价格合理低价的响应人，但响应价格低于其成本的除外， 具体由采购评审小组在评审会上商定。 （2）响应人有下列情形之一的，取消成交资格： ①成交人在成交后拒签合同； 网 ②成交人未按约定缴纳履约保证金。 采购人： 中国建筑第七工程局有限公司 务 采购时间：2026年8月 二、评 审 办 法 （一）、评审依据 商 1、采购文件 2、响应文件 道 3、评审办法 （二）、评审小组 管 1、评审小组成员：（评审小组应由5人及以上单数评审专家组成，项目负责人必须参与评审。与分供商存在利害 关系的应回避。） 2、小组成员负责根据国评审办法及标准开展评审工作。 3、与响应人有利害关系的，不得进入评审小组。 （三）、评审原则 中 （1）采取经评审的合理低价法：从满足采购文件实质性要求的响应人中，选择合理报价中最低者（不合理低价 除外）为成交分供商。 （四）、初步评审 有效分供商（资审通过并参与有效报价的分供商）数量不少于N（拟选分供商数量）+2家。（询比采购和竞价采 购要求，其他采购方式参照采购管理办法，下同） 出现以下情形的，响应无效。 1、未按要求缴纳响应保证金的。 2、未按要求完成线上响应的。 3、未响应采购文件的实质性要求和条件的。 4、响应人提供虚假资料、隐瞒误导采购的。 5、响应人以他人名义响应或者以其他方式弄虚作假，骗取成交的。 6、响应人ip重复、涉嫌弄虚作假或串通交易行为的。 7、采购文件或法律规定的其它情形。 （五）、详细评审 1、评审：以云筑网填报数据为准。 2、排名：对进入详细评审的响应人响应报价进行汇总后，按响应报价由低到高进行综合排名。 若出现响应人响应报价相同时，按其年度供应商考评评级高低优先排序，若仍相同，可再选用以下进行情况排序 （根据情况自行排序）。 网 ①近三年工抵房金额； ②具有绿色节能环保材料设备； 务 ③云筑网显示的该响应人响应时间等。 1）、采购概算金额（见采购公告）视为最高采购限价，响应人响应报价高于采购概算金额的，作无效响应处理。 响应人响应报价低于成本的，经评审小组评审确定后，作无效响应处理。 商 2）、在评审过程中，评审小组可以要求响应人对所提交的响应文件中含义不明确、表述不一致或者有明显笔误、 文字和计算错误的内容作出必要的澄清、说明或者补正，该澄清、说明和补正属于响应文件的组成部分，须经 采购授权代表书面署名确认，不得改变响应文件的实质性内容，且须经评审小组一致同意。评审小组不接受响 应人主动提出的澄清、说明或补正。 道 3）、经以上评审，有效响应人数量仍须满足“有效分供商（资审通过并参与有效报价的分供商）数量不少于N （拟选分供商数量）+2家”，否则本次采购按废止处理（成交单位数量为“N”）。 管 4）、废止后重新发起采购，需经调查核实后，视具体调查核实结果决定是否准予原响应人参与新发起的采购响 应。 （六）、确定成交候选单位 国 多轮次公开竞争报价：（说明：如需要(应视采购标的物及响应报价情况)进行多轮次公开竞争报价的，应按详细 评审的排名顺序确定一定比例(首轮最高价不得进入二次报价)的有效响应人进行后续轮次报价，总轮次不超过3轮 （竞价采购）。 中 报价规则：响应人提交的首轮报价作为后续报价基准；后续轮次总报价不得高于前轮报价，若设置参考价，单 项报价不得高于参考单价。否则该轮报价无效；最终轮次报价提交后不得撤回或修改（以系统记录为准）。 晋级规则：每轮报价截止后，采购人按报价从低到高排序；出现相同报价时，依次比较：（1）资源库等级；（2） （参考上述第五条第2点，以优质优价为原则，优先选用具备相应能力的本级及上级A级分供商） 成交机制：最终按末轮有效报价的从低到高排序；当最低报价出现多家时，可自主决定成交人。 最终按照排名顺序拟定有效响应人作为成交候选单位，具体成交候选单位数量由评审小组根据采购文件确定。 成交候选单位经审批后作为最终成交单位。 成交候选人放弃成交、因不可抗力不能履行合同、不按照采购文件要求提交履约保证金，或者被查实存在影响 成交结果的违法行为等情形，不符合成交条件的，采购人可以按照评审小组提出的成交候选人名单排序依次确 定其他成交候选人为成交人，也可以重新采购。 （七）、其他事项 1、因响应人原因造成其自身未响应采购要求及未能成交等情况，由响应人自行承担相应责任及损失，与采购人 无关。 2、本采购文件中的合同范本即实际签约合同范本，双方均不允许以任何理由更改合同内容。 三、响应注意事项 1、若响应人对采购文件中之任何内容有不理解之处，须立即联系采购人，以便在响应截止日期之前能予以解释。 2、采购人不保证一定要接受最低价成交，不论响应结果如何响应人的响应文件均不退回，且不对未成交单位做 任何解释。 3、响应人在响应之前，对本采购项的分包条件均已了解，响应即认为已详细了解。 4、采购人对响应人进行考察时，响应人应提供便利条件。 5、本次采购的最终解释权在采购人。 网 四、响应文件的上传 1需上传的响应附件（未上传视为不响应采购文件）有： 务 1.1.《响应函》 1.2.《响应承诺函》 1.3.法定代表人身份证明（格式）； 商 1.4.授权委托书（格式）（若若为法定代表人响应则可不提供）； 1.5.报价清单明细（盖章版） 道 1.6金融工具支付方式及优惠措施 1.7.响应保证金汇款凭证扫描件或免缴证明（云筑网平台缴纳的无须提供）（若需） 管 六、响应文件格式 一、封面（格式） 国 中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料采购响应文件 响应内容：临水临电材料采购 中 （编号：cscec2026081900001246027） 响应人：（盖章） 法定代表人 或授权代理人（签字盖章）： 响 应 函 致：中国建筑第七工程局有限公司 1、经勘察了本工程现场,并仔细研究了响应须知、合同协议条款、合同条件、采购图纸、工程规范、地质勘察报 告、工程量清单、响应答疑、及其他有关采购文件后，我公司愿以我公司云筑网所上传的含税综合单价，并按 采购文件所要求的条件承包在规定工期内完成重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料的施 工、竣工并补充其任何缺陷。 2、我公司保证本工程质量必须：达到符合工程所需材料质量验收标准、设计、合同及有关工程施工及验收规范 的要求标准。 3、一旦我公司的云筑网响应内容被接纳，我公司将在收到成交通知书后按贵公司的要求开始施工，我公司保证 于承诺的工期内或双方议定的工期内完成并交付本合同中规定的整项工程。 4、我公司同意在本区段的正式建设工程施工合同签署之前，云筑网响应将始终对我公司具有约束力，并可随时 被贵公司接受。 5、我公司知道：云筑网报价及云筑网响应的其他部分构成我公司向贵公司的要约，贵公司如发出成交通知书则 成交通知书及云筑网响应、采购文件将构成约束我们双方的合同，如果我公司在接到成交通知书后，没有按贵 公司要求的时间签署正式合同或坚持提出附加条件，那么我公司同意贵公司有权另选成交单位并向我公司追讨 有关损失。 6、我公司知道，贵公司并无义务必须接受所收到的价格最低的或其他任何响应书。 7、云筑网响应内容已考虑了贵公司向我公司发出的关于采购文件的相关答疑，网补充通知（如有的话） 8、云筑网响应效力优先于同时提交的任何响应文件的其他组成部分。 响应人： （盖章） 务 日 期： 年 月 日 响应承诺书 商 致：中国建筑第七工程局有限公司 我系有幸参与贵公司 重庆市第四人民医院科学城院区建设项目 (二期)临水临电材料的响应，我公司经研究决定， 在此郑重承诺： 道 1、我公司在响应过程中已完全了解并掌握了采购内容、合同条件及施工现场等情况。确保云筑网响应报价操作 为本公司自己操作，如响应后发生非本公司操作的情形，本公司承担相应违约责任。 管 2、我公司已经详细阅读该采购文件所有内容，充分领会并完全接受采购文件所述响应人应尽的实质性的权利与 义务。我公司保证不会对采购文件产生不利于双方友好合作关系和将增加贵公司采购范围内经济支出的重大误 解。 3、我公司确认，贵公国司发出的采购文件所有内容为不可割裂的整体。 4、我公司保证成交后不会对成交价格提出任何异议，更不会以任何理由要求贵公司针对成交范围的价款要求额 外补偿。不会以不了解采购文件、合同文件为由或曲解、片面理解采购文件、合同文件或割裂采购文件、合同 文件，断章取义，向贵公司提出任何补偿要求。 中 5、在本合同的履约过程中，如因我公司的供货或质量原因导致贵司损失，我公司保证承担因此而给贵公司带来 的所有经济上的损失。 6、我公司将本工程作为重点项目对待，保证不会出现供货能力不能满足施工需要的现象。为满足本工程业主及 贵公司在质量、进度、安全、环保上的要求，我公司将采取一切措施保证物资设备生产、供应、租赁，运输等 均满足贵公司的要求，并保证不会因此而向贵公司提出增加任何补偿要求。 7、我公司承诺无论本工程最终的成本状况如何，将不会违背合同基本原则而向贵公司要求增加或补偿合同文件 约定以外的任何费用。 8、我公司认为，贵公司可以就物资设备采购数量或租赁时长进行调整，并且此种调整不构成我公司的索赔理由。 响应人：（盖章） 法定代表人或 其授权代理人：（签字或盖章） 日 期： 年 月 日 响应人名称：【全称】 单位性质： 地 址： 成立时间：年月日 经营期限： 姓名：性别：年龄：职务：系（响应人名称）的法定代表人。 网 特此证明。 响应人：（盖单位章） 务 年月日 授权委托书 商 本人（姓名）系（响应人名称）的法定代表人，现委托（姓名）为我方代理人。代理人根据授权，以我方名义 签署、澄清、说明、补正、递交、撤回、修改中国建筑第七工程局有限公司重庆市第四人民医院科学城院区建 设项目 (二期)临水临电材料采购（采购项目名称）响应文件、签订合同和处理有关事宜，其法律后果由我方承担。 道 委托期限：本授权书于年月日签字生效，至本次采购期结束为止。授权期限内无特殊情况不变更合法授权代理 人。 代理人无权转委托。 管 特此声明。 响应人：（盖章） 国 法定代表人：（签字） 身份证号： 中 授权代理人：（签字） 身份证号： 联系方式： 日期： 年 月 日 备注：法定代表人和委托代理人必须在授权书上亲笔签名，不得使用印章、签名章或其他电子制版签名,同时附 法定代表人和授权代理人身份证复印件（正反面，加盖公章） 报价清单明细 不 含 含 不含 计量单 税 税 含税 备 序号 材料名称 规格型号 数量 税 税合 税额 位 率 单 合价 注 单 价 价 价 1 镀锌钢管 DN100*4.0 米 500 2 镀锌钢管 DN150*4.5 米 250 3 镀锌钢管 DN65*3.25 米 650 4 镀锌钢管 DN50*3.25 米 800 5 PE管 DN100*1.6MPA 米 450 6 PPR管 DN50*1.6MPA 米 400 7 闸阀 DN100 个 22 8 闸阀 DN250 个 10 9 截止阀 DN50 个 42 网 10 截止阀 DN25 个 60 11 蝶阀 DN100 个 6 12 消防箱 800×1000×250mm 台 20 务 功率30kw,扬程144m，流 13 加压泵（变频控制） 台 1 量55m/h 14 橡塑保温材料 DN100*20mm 米 620 商 15 橡塑保温材料 DN150*30mm 米 280 16 橡塑保温材料 DN65*20mm 米 700 17 压线钳 CO-1000 个 1 道 18 污水泵 380V4KW=25米 台 12 19 污水泵 380V5KW=30米 台 7 20 热熔机 63-160 台 1 管 21 电工胶布 / 卷 200 22 高压自粘带 / 卷 120 23 水泵控制箱 / 个 8 国 24 PE聚乙烯管 DE110*1.6MPA m 560 25 PE聚乙烯管 DE75*1.6MPA m 420 26 PE聚乙烯管 DE63*1.6MPA m 480 中 27 PE聚乙烯管 DE32*1.6MPA m 750 28 PE球阀 DN25 个 6 29 PE球阀 DN50 个 6 30 PE球阀 DN100 个 5 31 镀锌桥架 200*100*1.2mm 米 1200 32 PVC排水管 DE300*5.0 m 180 33 PVC排水管 DE200*5.0 m 380 34 PVC排水管 DE160*4.0 m 486 35 PVC排水管 De110*4.0 米 560 36 PVC排水管 DE75*3.0 m 420 37 PVC排水管 DE50*2.0 m 660 38 PVC排水管 DE32*2.0 m 380 39 PPR给水管 De90*1.6MPA 米 440 40 PPR给水管 DE75*1.6MPA 米 360 41 PPR给水管 DE63*1.6MPA 米 450 42 PPR给水管 De50*1.6MPA 米 435 43 PPR给水管 De40*1.6MPA 米 315 44 PPR给水管 DE32*1.6MPA 米 520 45 PPR给水管 De25*1.6MPA 米 680 46 PPR给水管 De20*1.6MPA 米 370 47 橡塑保温板 平板×20mm m 15 48 橡塑保温板 平板×30mm m 28 49 保温胶 3公斤/桶 桶 25 网 50 PPR给水管接头 De75 个 30 51 PPR给水管弯头 De75 个 20 52 PPR给水管三通 De75 个 22 务 53 PPR给水管接头 De63 个 20 54 PPR给水管弯头 De63 个 15 55 PPR给水管三通 De63 个 15 商 56 PPR给水管接头 De50 个 17 57 PPR给水管弯头 De50 个 22 58 PPR给水管三通 De50 个 17 道 59 PPR给水管接头 De40 个 14 60 PPR给水管弯头 De40 个 22 61 PPR给水管三通 De40 个 17 管 62 PPR给水管接头 De32 个 14 63 PPR给水管弯头 De32 个 14 64 PPR给水管三通 De32 个 17 国 65 PPR给水管接头 De25 个 22 66 PPR给水管弯头 De25 个 17 67 PPR给水管三通 De25 个 14 中 68 PPR给水管接头 De20 个 25 69 PPR给水管弯头 De20 个 17 70 PPR给水管三通 De20 个 22 71 PPR内丝直接 De25 个 17 72 PPR内丝直接 De20 个 84 73 球墨铸铁井盖 700*800*40T 套 22 74 球墨铸铁井盖 1000*1000*20T 套 20 75 球墨铸铁雨箅子 400*600*30 块 1750 76 球墨铸铁雨箅子 350*500*30 块 1200 77 高分子成品排水沟 300*300*1000 米 850 78 高压洗车机 380v/3KW 套 5 79 高压洗车机 380v/5.5KW 套 3 80 HDPE双壁波纹管 DN300 米 360 81 HDPE双壁波纹管 DN200 米 410 82 HDPE双壁波纹管 DN400 米 340 83 HDPE双壁波纹管 DN800 米 260 84 玻璃钢化粪池 20m 个 1 85 玻璃钢化粪池 50m 个 1 86 不锈钢消防水箱 12m 个 1 87 一级配电柜 2000*1200*500*630A 台 1 88 二级配电柜 800*600*210*250A 台 8 89 铜芯电缆线 YC3*16+2*10 米 60 90 铜芯电缆线 YC3*10+2*6 米 70 网 91 铜芯电缆线 YC3*6+2*4 米 70 92 铜芯电缆线 YC3*10 米 100 93 铜芯电缆线 YC3*6 米 100 务 94 铜芯电缆线 YC3*4 米 100 95 铜芯电缆线 YC3*2.5+2*1.5 米 100 96 聚录乙烯铝芯电缆 YJLV-22-4*185+1*95 米 50 商 97 聚录乙烯铝芯电缆 YJLY-4*25+1*16 米 90 98 聚录乙烯铝芯电缆 YJLY-4*35+1*16 米 100 99 聚录乙烯铝芯电缆 YJY-4*50+1*25 米 90 道 100 聚录乙烯铝芯电缆 YJLY-4*70+1*35 米 72 101 网线 Cat5e 米 100 102 铜芯电线 BV-2.5 米 400 管 103 铜芯电线 BV-4 米 300 104 铜芯电线 BV-6 米 200 105 铝芯电缆线 YJLV3*10 米 100 国 106 透明塑壳断路器 3P32A 米 34 107 透明塑壳断路器 3P63A 米 28 108 透明塑壳断路器 4P100A 米 26 中 109 透明塑壳断路器 4P160A 米 22 110 透明塑壳断路器 4P250A 米 20 111 透明塑壳断路器 4P400A 米 8 112 低压铝芯电缆 YJLV-4*300+1 米 20 113 低压铝芯电缆 YJLV-4*150+1 米 50 114 铝芯铠装电缆 YJLV-22-4*95+1*50 米 60 115 铜铝线鼻 300mm2 个 20 116 铜铝线鼻 150mm2 个 36 117 铜铝线鼻 95mm2 个 24 118 铜铝线鼻 50mm2 个 20 合计 0.00 0.00 0.00 1、综合单价：包括但不限于材料费、保险费、风险费、包装费、装车费、过桥过路费、管理费、检验费、技术 指导费、货到工地负责卸货堆入至指定地点等所有费用。本合同单价一次包死，在合同履行过程中不再做任何 调整。本合同的总价为暂估价，用方有权调整合同中材料计划或材料数量，材料数量和规格的调整，不影响本 合同单价及其他条款的执行。 2、计量方式：查看检测报告合格证，以实际验收通过数量计量。 3、付款比例：月结方式，即每月20日结算（遇节假日顺延），次月25日前（结算日后35日历天内），乙方提供 与结算等额增值税专用发票后，支付前月结算额的70%（遇节假日顺延）；供货完毕，验收合格，材料相关资料 （包括不限于合格证、质检报告等）移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%；剩余3% 质保金在质保期满后30日内无息支付。质保期自全部货物供货完毕且竣工验收合格日起1年计算，支付工程款时 均应扣除根据采购合同应予扣除的其它金额。 4、付款方式： （1）现金支付:采用现金转账的模式支付； （2）非现金支付:包括不限于(1)金融工具支付:银行承兑汇票，商业承兑汇票，网应付账款保理，银行信用证，中 建财务公司承兑汇票。(2)工抵房支付。 5、响应报价表中所列数量的变动，丝毫不会降低或影响合同条款的效力。 务 6、整个合同执行期内，若遇市场价格下行，甲方有权做出价格调整，乙方应接受并重新签订补充协议确认价格。 若乙方无法接受新的低价，甲方有权重新选择其他能够响应该价格的供应商进行供货，乙方无条件同意。 响应人（加盖公章）： 商 法定代表人或授权代理人（签字）： 日 期：年月 道 金融工具支付方式及优惠措施 管 1、金融工具支付： 可接受金融工具支付比例累计为%，其中： ① 可接受的国银行承兑汇票比例%；贴息响应人自行承担。 ② 可接受的商业承兑汇票比例%；贴息响应人自行承担。 金融支付 ③ 可接受的应付账款保理比例 %；贴息响应人自行承担。 中④ 可接受的银行信用证比例%；贴息响应人自行承担。 ⑤ 可接受的中建财务公司承兑汇票比例为%；贴息响应人自行承担。 2、资产支付 资产支付 可接受比例为合同额的%。 3、优惠付款比例：按按照采购文件的付款比例，我方可优惠%。 4、如响应人提供其他由于采购条件的承诺，请逐项列示。 响应人（加盖公章）： 法定代表人或授权代理人（签字）： 日 期：年月 响应保证金汇款凭证扫描件或免缴证明（若需） 响应人（加盖公章）： 法定代表人或授权代理人（签字）： 日 期：年月 六、物资设备采购合同 合同编号：______________________ 物资采购与供应合同 （通用） 项目名称：【 重庆市第四人民医院科学城院区建设项目 (二期) 】 网 甲 方：【 】 乙 方：【 】 务 签订时间：【 】 签订地点：【 】 商 目录 1. 工程概况及供货范围 道 2. 企业性质 3. 合同价款 2 管 4. 质量要求 5. 供货时间及地点 6. 交货与验收 国 7. 结算方式及时间 8. 支付 中 9. 发票 10. 双方责任 11. 不可抗力 12. 权利瑕疵 13. 保密 14. 违约与赔偿 15. 联络与送达 16. 争议解决 17. 补充条款 18. 其他 物资采购与供应合同 甲方（买受人）：【中建七局安装工程有限公司 】 乙方（出卖人）：【 】 根据《中华人民共和国民法典》及有关规定，为明确双方权利、义务和责任，经双方协商一致，就甲方承包的 【高新LIVE（咸阳高新区租赁住房）建设项目】工程所用【 水电管材】采购与供应事宜签订本合同条款，愿共 同遵守。 1. 网 1.1 工程名称：【高新LIVE（咸阳高新区租赁住房）建设项目 】 1.2 工程地点：【陕西省咸阳市星火大道】 务 本合同供货范围为：【高新LIVE（咸阳高新区租赁住房）建设项目 】的【水电管材】供应（以下简称为“本合 同标的物”）。 1.3本合同标的物的数量为暂定量，乙方按附件1《计划采商购与供应物资清单》所列品种和规格供货，最终以经甲 方验收合格的实际数量为准。 2. 企业性质 道 乙方企业规模：大型 □中型 □小型 □微型企业 以上企业规模由乙方根据（1）工信部官网：“中小企业规模类型测试网址https://baosong.miit.gov.cn/ScaleTest。 （2）工信部微信小程序：“中小企业规模类型自测”两种渠道自测确定。 管 乙方应保证其企业规模的真实性。如乙方提供信息不实，经甲方查证后，将按照《中国建筑股份有限公司分供 商资源管理办法》中的《不良行为分供商禁用处理标准》第19项对乙方严格实施禁用管理。 合同价款 国 3.1 本合同采用第【 】种价格形式： （1）固定综合单价包干，价格不可调整。 中 3.2 本合同价款为各项货款之和，合同价款（含增值税）暂定：（大写）【 】（￥【 】元），其中不含税价款为 （大写）【 】（￥【 】元），增值税为（大写）【 】（￥【 】元），税率为【 】%。最终甲乙双方以实际验收 的数量结算。 3.3 本合同约定的不含税价款不因国家税率变化而变化，在合同履行期间，如遇国家的税率调整，则价税合计的 合同价款或货款相应调整，以开具发票时间为准。 3.4 本合同不含税价款仅指不包含增值税，除增值税外的其他全部税费（包括但不限于城市建设维护税、教育费 附加及地方教育费附加、个人所得税、合同印花税、企业所得税、车船使用税以及国家和地方规定的所有税费） 均包含在不含税价款中。 3.5 本合同标的物的计价、结算和支付货币均为人民币。 3.6 本合同标的物的计量单位为中华人民共和国法定公制计量单位（除技术规范标准另有规定外）。 3.7 本合同标的物的不含税单价，指运抵本工程施工现场甲方指定交货地点的综合单价，包括但不限于货物费、 加工费、包装费、人工搬运费（由乙方自行协调，甲方只进行指定场地和材料验收工作）、运输费、出厂检测费 （包括但不限于到场后的第三方检测费用）、装卸费、码放费、现场倒运费用，保险费、仓储费、驻厂监造费、 运输造成的道路污染的清理及维修费用、除增值税以外的税金、乙方合理的利润、管理费、市场价格波动带来 的风险、向有关部门缴纳的各项费用以及政策性文件所规定的各项应有费用等乙方履行本合同规定义务的全部 价款与费税。除本合同第3.1条约定的因素外，不含税单价不因政府政策变动、市场环境改变、税率调整等而调 整。 3.8 除合同条款另有约定外，本合同标的物的不含税单价已包含专利、专有技术以及技术秘密的使用费。 质量要求 4.1 乙方应在交货同时向甲方提供本合同标的物制造商出具的书面质量保证书。 4.2 本合同所采购与供应的物资，应符合现行中华人民共和国国家标准及行业或地方标准，行业标准或地方标准 高于国家标准的，执行行业标准或地方标准。各项技术性能指标经本工程所在地具有相应检测资质的专业机构 或单位检测中心检验必须符合相关标准要求。合同执行过程中，若出现新的国家标准、行业标准、地方标准， 则以更新后的标准为准。 网 4.3 乙方的物资供应与管理应符合国家有关环保法律、法规和甲方ISO14001环境体系及OHSMS18001职业安全健康 管理体系标准。 4.4 本合同标的物的质量保证期为最后一批货物验收合格之日起满【180】日。 务 4.5在合同履行期及质量保证期内，乙方无条件地向甲方提供缺陷产品的免费维修、更换等服务。针对甲方提出 的书面要求，乙方必须在3日内给予书面答复。如有必要，乙方在3日内指派专人到现场解决，因此产生的所有费 用均由乙方承担。 商 4.6 如缺陷产品经乙方进行免费维修和更换后仍无法达到甲方要求的质量标准时，甲方有权终止合同。终止合同 后，乙方需向甲方赔偿由于乙方问题造成的损失及其连带损失。如乙方借故推脱或拒绝甲方提出的维修、更换 等服务请求，甲方有权自行采购同等货物替代或委托第三方维修，实际发生的更换等或维修费用，从应支付给 乙方的任一期货款中扣除，并保留进一步索赔道的权利，乙方不得提出异议。维修或更换物资的质量保证期相应 延长6个月。 4.7 如因乙方产品质量导致工程出现质量问题，由此给甲方造成的一切损失由乙方承担。 管 4.8 其他质量要求：/。 供货时间及地点 5.1 供货方式：□按批次国供货 □一次性供货 5.2 通知方式：供货时间及数量以甲方书面通知为准，甲方可以选择通过电子邮件、微信、QQ等方式将物资采购 订单发送至乙方。紧急情况下，甲方可口头通知乙方发货，手续后补，乙方应予以确认。 中 5.3 供货地点：乙方负责送货至施工现场，卸至甲方指定的卸货地点【高新LIVE（咸阳高新区租赁住房）建设项 目】。乙方不得雇佣甲方在班人员及设备装卸货物。运输、装卸过程中发生的安全事故责任，乙方自行承担。 5.4 根据工程项目施工需要，甲方对所采购物资的数量和送货时间如有变更，应及时书面通知乙方，乙方按变更 后的数量和送货时间供货，货物单价不因货物数量和送货时间的变更而变化。 5.5 乙方应确保已经知悉货物运输的交通状况、交货卸车环境以及政府的交通管制政策措施，不得以此等理由要 求增加费用、减免责任、提出索赔、要求延长或变更供货期限。 交货与验收 6.1交货 6.1.1 除另有规定和协议要求外，乙方提供的全部货物须采用国家、企业、行业标准要求包装，具有足够的强度 及安全起吊标识，保证货物能够经受多次搬运、装卸、长途及短途运输的要求，并采取良好的防潮、防震、防 腐蚀、防爆及防止其它损坏的必要保措施。包装物的回收按以下第【 2】项方式执行：（1）不回收；（2）包装 物由乙方在交货时回收；（3）其它方式：【 /】。 6.1.2 装箱单应注明货物的名称、规格、型号、数量、质量、生产商、发货地、供货人、收货人、交货地、承运 人等，并在显著位置标明装卸警示标志。 6.1.3 乙方运抵甲方指定现场的物资，交货单据上应详细列明当次供应物资的名称、品牌、产地、生产厂家、规 格型号、计量单位、数量。 6.1.4 乙方应向甲方提交本合同标的物的技术文件，包括材质报告（物资质量检验报告）和出厂检验报告（合格 证），以及按照工程竣工验收规定及甲方要求，提供所有相关符合要求的资料。 6.1.5 乙方在首次供货前需提供样品，乙方须在样品和样品资料上加盖单位公章，样品经双方指定人员签字确认 后予以封存，在提交文件上注明与合同文件约定不同之处。 6.2.1 乙方须随货提供载有数量、规格等内容的送货单，否则，甲方有权对本批次货物不予验收确认，由此导致 的违约责任由乙方承担。乙方送货到交货地点后，甲方指定验收人员对产品的规格、尺寸偏差、外观、数量及 质量证明资料等进行查验。若产品的以上各项符合合同约定，则双方人员共同在收领单上签字确认。 6.2.2 甲乙双方在交货现场以 【 点数】方式进行数量验收。乙方应对在甲方工地网现场的验收数据进行确认。 6.2.3 进行数量验收的同时，甲方可以按照封存样品标准进行尺寸、外观质量验收，尺寸和外观质量符合要求方 可卸车，否则不得卸车。 务 6.2.4 外观质量符合要求的， 甲方可打开包装进行质量、性能检验或及时按规定取样送本工程所在地具有相应检 测资质的专业机构或单位进行检测。抽检未发现不合格产品不视为乙方供应产品全部合格，甲方有权随时将乙 方所供货物送到有检测资质的第三方进行检测。如检测合格，检测费用由甲方承担；如检测不合格，甲方可全 部退货，检测费用由乙方承担，并承担由此给甲方造成的一切损失。 商 6.2.5 甲方及工程监理（业主）的收货验收仅作为感观合格的依据，不能免除乙方对货物品牌真实性、内在质量 及使用功能所负的责任。如甲方、本工程建设单位或监理单位提出异议，乙方需参照有关标准规范，结合现场 情况解决。 道 6.2.6 若发现不合格产品，乙方必须及时（接到甲方通知后【 3】小时内），从甲方项目现场运走不合格品，甲方 不负有保管义务，不对不合格产品的损毁灭失承担人和责任，若超过【 12】小时乙方仍未运走的，甲方收取场 地租赁费（根据货物合理确定）【 1.0】万元/天，且不合格品的储存、装卸、运输等所有相关费用及风险由乙方 承担。 管 6.2.7 如因乙方产品问题造成甲方工期、质量、劳务等损失，全部责任均由乙方承担。乙方对甲方所提出的质量 问题有不同意见的，双方可送至双方共同选定的具有法定资质的检测机构检测，所产生的费用及责任由责任方 承担。 国 6.2.8 本合同的标的物所有权自【卸货完毕且经甲方验收合格】起转移。 结算方式及时间 中 7.1 过程结算：甲乙双方按以下第【 1】条约定的时间办理过程结算。 （1）每月20日结算（遇节假日顺延），每季度最后一个月的25日后支付当期货款额的70%（遇节假日顺延，乙 方提供与结算等额增值税专用发票），供货完毕，验收合格，材料相关资料（包括不限于合格证、质检报告等） 移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%，余款3%（不计息）待质保期满无质量问题后 无息付清。（质保期为供货完毕且验收合格后2年）（支付工程款时均应扣除根据采购合同应予扣除的其它金额。 ）； （2）按节点结算，具体结算节点为：【 】。 7.2 最终结算：全部供货完毕后【 6个月后】日内，乙方应向甲方提供完整的结算资料，甲方在收到完整的结算 资料后【 5 】日内进行审核。 7.3 结算依据：包括但不限于物资采购与供应合同、乙方合法等额有效增值税发票（含税务机关代开）、产品合 格报告、项目授权人员验收单、送货单等有效材料。 7.4 乙方未按照约定的期限和甲方要求提供结算资料，或未委派专人与甲方办理结算，或提供的结算资料不齐全、 提供虚假资料的，经甲方催告后10个工作日内，乙方仍未按要求提供结算资料的，甲方有权不予办理结算并暂停 支付材料款，同时甲方可根据本合同、现有结算资料及乙方实际履约情况单方办理结算，确定结算价格，结算 对甲乙双方具有法律约束力。 支付 支付/√不支付预付款 8.1.1 预付款金额（或占合同价款的比例）：【 /】。 8.1.2 预付款的支付时间：【 /】，在乙方提交等额银行保函及增值税专用发票后，甲方向乙方支付预付款。 8.1.3 扣回预付款的时间、比例：【 /】。 8.1.4 乙方提交的银行保函有效期至预付款抵扣完为止，若预付款保函到期日前，预付款无法抵扣完毕，则乙方 应于预付款保函到期日前不少于10日及时办理保函延期，否则甲方有权暂停支付未抵扣完部分的货款。 网 / 8.2.1 货款支付，按以下第【 3】条约定的时间和比例支付。 务 （1）月度付款：甲方在次月的25日支付上月月度结算货款的【 / 】%。双方办理完毕最终结算后【 / 】（条款说 明：建议不超过60日，如超过60日，应当按照行业规范、交易习惯合理约定付款期限并及时支付款项）个日历天 内付至总结算货款（且不超含税合同价款）的【 / 】%。余款【 /】%作为质保金，在质保期届满后28日内付清； 或由乙方提供等同余款金额的质保保函（仅接受金融机构出具的无条件见索即付保函，质保保函格式以开函金 融机构标准格式为准），则双方办理完毕最终结算后【 /商】（条款说明：建议不超过60日，如超过60日，应当按 照行业规范、交易习惯合理约定付款期限并及时支付款项）个日历天内付清。 （2）节点付款：按节点支付（条款说明：此处需具体罗列每个付款节点及各节点对应的付款比例，节点结算完 成后约定支付期限应在60日内，如超过60日，道应当按照行业规范、交易习惯合理约定付款期限并及时支付款项）， 余款【 /】作为质保金，在质保期满后28日内付清，或由乙方提供等同余款金额的质保保函（仅接受金融机构出 具的无条件见索即付保函，质保保函格式以开函金融机构标准格式为准），则在最后一个付款节点付清。每次 付款前乙方应提供结算值【100%】的发票，否则甲方可拒绝付款。 管 （3）其他支付方式【每月20日结算（遇节假日顺延），每季度最后一个月的25日后支付当期货款额的70%（遇 节假日顺延，乙方提供与结算等额增值税专用发票），供货完毕，验收合格，材料相关资料（包括不限于合格 证、质检报告等）移交甲方，且最终结算办理完毕6个月后付至最终结算价款的 97%，余款3%（不计息）待质保 期满无质量问题后无息付清。（质保期为供货完毕且验收合格后2年）（支付工程款时均应扣除根据采购合同应 予扣除的其它金额。）国】 （4）甲方依合同约定确认的进度款仅为中期付款依据，不作为竣工结算的依据，且不视为对因变更调整的合同 价款、索赔的价款或费用以及其他约定的追加合同价款的确认。 中 8.2.2 甲乙双方协商一致同意本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保理、商业承兑汇票、 国内信用证、应收账款电子凭证、抵房抵款及其他】常规支付方式的付款方式。付款过程中产生的贴息费用及 手续费由【乙方】承担。乙方委托专职收款人办理收付款业务，收款人必须取得授权 8.3 乙方指定以下帐户为收款帐户，甲方所有款项均需通过该帐户支付。如乙方变更收款帐户，应提前十五天以 上书面通知甲方，否则造成资金的损失由乙方自行承担，与甲方无关。 账户名：【 】 开户行：【 】 账 号：【 】 发票 9.1 乙方在向甲方请款时，应根据甲方确认的应支付金额开具合法、有效、完整、准确的增值税（请勾选：□专 用□普通）发票，计税方法为【□一般计税方法 □简易计税方法】，双方发票信息如下： 名 称 纳税人身份 □一般纳税人 □小规模纳税人（请勾选） 甲方 纳税人识别号 地 址、电 话 开户行及账号 名 称 纳税人身份 □一般纳税人 □小规模纳税人（请勾选） 网 纳税人识别号 乙方 地 址、电 话 开户行及账号 务 联 行 号 该开户行为乙方在税务局已备案的乙方单位账户。 9.2 任何一方如上述信息发生变更，应提前10日以书面方商式通知另一方。如一方未按本合同规定通知而使另一方 遭受损失的，应予以赔偿。 9.3 每次乙方在甲方付款前必须提供符合国家现行税法规定的合法有效等额增值税发票，甲乙双方一致确认提供 发票为主合同义务而非附随义务，若乙方未按要求提供发票，甲方有权暂停付款。乙方应在开票之日起7天内将 道 发票送达甲方指定人员【 刘磊】，甲方指定人员签收发票的日期为发票的送达日期。 9.4 乙方开具的增值税专用发票应保证信息完整、内容规范，如乙方未提供发票或提供的发票不合规、不及时、 无法认证，甲方有权拒绝付款，且不视为甲方付款逾期，乙方无权要求甲方支付利息、违约金或赔偿损失，也 管 不得以此为由中止履行合同约定的义务。 9.5若乙方由一般纳税人身份变为小规模纳税人身份的，或者计税方法发生变化的，或者政策法规等规范性文件 发生变化的，并导致甲方可抵扣的进项税额减少或被税务机关要求补缴税款的，则减少的进项税额或补缴的税 款应由乙方承担，甲方国有权从将支付的任何一笔款项中扣除。 9.6 增值税税率变化：合同执行过程中如果遇到国家税务政策调整，增值税税率发生变化的，按新的税率执行， 不含税价不变，仅调整增值税税率的原则进行相应调整。 中 若乙方提供的发票不符合要求的，发包人有权拒收增值税发票，并有权暂停支付相应款项，乙方不得以此为由 中止履行合同的义务。如因乙方不能按期提供发票或提供的发票不符合要求而导致付款延期的，由其自行承担 后果，发包人不承担任何责任。 9.8若乙方迟延提供发票的，每日应按暂定合同总价的0.05%向甲方支付违约金，但迟延违约金累计支付不超过90 日；若乙方迟延提供发票超过90日且已跨年的，视为乙方未提供发票，乙方除应支付前述迟延违约金外，还应另 行向甲方支付以下款项： （1）相当于合同暂定总价1%的违约金； （2）甲方因未收到发票所产生的税款损失， 损失金额按以下公式计算：赔偿损失金额=未提供发票对应的增值税税额*（1+增值税附加税率）+未提供发票金额 *甲方企业所得税税率。 9.9乙方保证开具的发票已经依法足额纳税，支付每笔款项前，乙方需提供发票对应税期的增值税纳税申报表和 完税证明。 9.10乙方承诺其提供的发票真实合法，若发包人认证后出现走逃失联、被列为异常纳税人等违规行为，导致发包 人不能认证抵扣或者认证抵扣后被税务机关要求进项转出情形，应在72小时内补开合规发票，否则按以下方法计 算应赔偿发包人损失，应赔偿损失金额=进项转出税额*（1+增值税附率)+不合规发票金额*发包人企业所得税税 率，逾期未赔偿的，甲方有权从结算金额或者履约保证金中扣除。 9.11乙方主张已开具发票的，应提供：①税务系统发票开具记录 ；②采购方签收凭证或者发票邮寄物流凭证。无 法完整提供两项证据的视为未开票。 10.双方责任 10.1 双方现场代表 10.1.1甲方现场代表为【 】，其职务为【 】 ，其授权签署文件的范围为：【签发监管项目的各类文函、工程变更 指令、索赔文件的报出、违约处罚决定文件等】。 10.1.2甲方收货代表：【 】，联系电话【 】。甲方指定收货代表仅有对乙方送货单中货物的数量及乙方提供的单 据是否齐全子以确认的权利，对货物单价、质量、货款以及总结算单没有确认的权利。 10.1.3乙方应将物资按合同约定时间运至甲方指定地点，并经甲方指定收货代表和甲方工程项目所属其他1人及以 上在甲方指定的收领单上签字验收确认后有效。 网 10.1.4 甲方未经授权的任何人员和项目印章均无权从事下列行为：【（1）签订本合同的补充协议或签署其他合 同类文件，包括但不限于采购合同、分包合同、租赁合同；（2）签署任何借贷、担保性质的文件，包括但不限 于借条、保函、保证书、承诺书；（3）签署代他人清偿债务的文件，签署任何放弃债权的文件；（4）签署任何 对总承包合同进行修改和补充的文件;（5）收取现金及任何款项；（6）签署合同价款的变更、结算及支付确认 务 文件；（7）签署任何劳动关系确认文件、工资发放承诺文件。】 10.1.5 甲方授权人员的职权/职责范围、授权签署文件范围均不可转授权，任何形式的转授权、代签行为，甲方均 不予认可且不承担任何法律责任。 商 10.1.6 乙方确认已完全明白和理解甲方对甲方人员及项目印章的上述授权范围，超出甲方授权范围的行为属于无 权代理行为，对甲方无效，甲方不承担任何法律责任。乙方应谨慎审查相关文件的签署主体资格和权限，对于 无权代理人签署的相关文件，乙方应及时与甲方核实。 道 10.1.7 乙方现场代表为【 】，其职务为【 】，其授权范围为：【全面代表乙方履行本合同，并有权代表乙方签署、 确认履约过程中形成的工程变更、价款确认、经济索赔、违约处罚决定及物资丢失损坏赔偿文件；签署确权文 件及结算书；签收甲方发出的各类文函、工程变更及其他文件等。】 管 10.1.8 双方更换各自代表时，应及时书面通知对方，以确保物资顺利交接。 10.1.9 甲方禁止项目部及任何人员以甲方、甲方分公司、甲方项目部的名义对外借款或者支取任何款项，如乙方 或乙方有关人员以任何形式将款项出借或支付或返还给甲方项目部及任何人员，则不论该等款项是否实际用于 甲方工程，均与甲方无国关，该行为均属于乙方与相关人员个人之间的经济关系，乙方无权向甲方主张任何权利。 10.1.10 未经甲方书面授权不得擅自与建设方及有关部门发生工作上的联系，严禁在对外任何事务中签署甲方单 位名称或带有甲方简称中任何“【中国建筑】”“【中建】”“【中建XX局】”“【XX局】”等字样的落款， 每发现一次中乙方承担2万元的违约金并赔偿所有直接或间接损失。 10.2卫生、环境与安全保护 10.2.1 甲乙双方须贯彻执行国家、地方政府相关部门发布的有关卫生法律、法规，以及甲方发布的规章制度，积 极配合政府部门的检查，对于提出的要求按所属责任立刻整改，确保瘟疫和传染疾病防控的管理落实到位。 10.2.2 乙方保证在运输和卸货过程中应采取相应的环保措施，符合国家环保要求。车辆在进入项目现场要保证不 沾泥土和脏物，车辆出入项目现场必须在项目大门内现场洗车。乙方在卸货过程中保证噪声不超过以下标准 （白天小于或等于【 】dB、夜间小于或等于【 】dB）。乙方保证乙方人员以及车辆进入本工地现场，应遵守现 场的一切卫生环保、文明施工的规定，因违反环保要求所造成的一切罚款由乙方承担。 10.2.3 甲乙双方必须贯彻执行国家和政府、行业主管部门颁布实施的有关安全生产的法律、法规及有关规定。乙 方车辆及人员进出工地现场时必须接受甲方安全检查。乙方因供货造成安全生产责任事故的，责任由乙方承担。 乙方必须对自身出入工地现场的人员进行安全交底，并为其配备安全防护用品，因乙方原因造成的各种人员伤 害及经济损失由乙方自行承担，并赔偿甲方及其它方因此造成的一切损失。 10.3 售后服务 10.3.1 如所供货物为专业性较高的产品，乙方应免费为甲方或工程业主提供操作及维修人员的培训服务，培训内 容应包括：基本原理、操作使用、维修保养等。 10.3.2 对于工程中的剩余或未使用到的货物在不严重影响外观、质量和功能的情况下甲方有权退货，退货原则上 以合同约定的含税单价为准，确因商品特殊的（比如定制等），价格由双方协商，协商不一致的，按照附件1 《计划采购与供应物资清单》中的含税单价（考虑甲方已支付费用、乙方承担运费等情况下，原则上不低于【 】%）【 】%退货，退货数量以实际数量为准。 不可抗力 11.1 不可抗力是指合同当事人在签订合同时不可预见，在合同履行过程中不可避免且不能克服的自然灾害和社会 性突发事件，包括地震、海啸、瘟疫、骚乱、戒严、暴动、战争等情形。 11.2 不可抗力事件发生后，乙方应立即通知甲方现场代表并迅速采取措施，尽量减少损失，并在24小时内向甲方 通报受害情况，提供必要证明。不可抗力持续发生，乙方应每日报告一次受害情况，直到不可抗力结束。甲方 应对受害处理提供必要的条件，并负责处理工作的组织、指挥。不可抗力发生后网，乙方未采取有效措施控制灾 害而发生的损失由乙方承担。 11.3 不可抗力引起的后果，由甲乙双方应各自承担其人员伤亡及财产损失，履行合同的期限相应延长。 务 不可抗力发生后，双方均应采取措施尽量避免和减少损失的扩大，任何一方没有采取有效措施导致损失扩大的， 应对扩大的损失承担责任。 因一方迟延履行合同义务，在迟延履行期间遭遇不可抗力的，不能免除迟延履行方的违约责任。 商 11.4 因单次不可抗力导致合同无法履行连续超过【30】天或累计超过【60】天的，甲方有权解除合同。合同解除 后，双方应就合同履行情况及结算与付款等善后事宜达成补充协议。 权利瑕疵 道 12.1 涉及到知识产权（专利权）标记的产品，乙方应提供知识产权（或专利权）及其权属的有效证明材料。乙方 承诺其提供的物资不侵犯他人的知识产权（或专利权），若乙方提供物资侵犯他人知识产权（或专利权）导致 他人向甲方索赔的，乙方承担由此给甲方造成的一切损失，包括但不限于甲方处理此纠纷发生的律师费、诉讼 管 费、仲裁费、差旅费等一切损失。此外，乙方应向甲方支付合同价款【5】%的违约金。甲方针对上述一切损失 有权从乙方结算货款中扣除或依法追索。 12.2 乙方所供物资应不存在任何权属纠纷及抵押、查封等权利限制情形，如乙方所供物资存在权属纠纷或任何权 利限制情形导致甲方遭国受损失，乙方应赔偿甲方全部损失。 保密 13.1 除法律规定或合同另有约定外，未经乙方同意，甲方不得将乙方提供的技术秘密及声明需要保密的资料信息 中 等商业秘密泄露给第三方。 13.2 除法律规定或合同条款另有约定外，未经甲方书面同意，乙方不得将甲方提供的图纸、文件以及声明需要保 密的资料信息等商业秘密泄露给第三方。 13.3 任何一方违反上述约定，应负责赔偿守约方因此造成的一切损失。 违约与赔偿14.1甲方应按照合同约定及时向乙方支付合同价款，若因甲方资金不到位，乙方同意给予甲方【 30 】 日的宽限期，宽限期内不视为甲方违约。超过宽限期仍未支付的，乙方可向甲方主张自宽限期结束后的违约金； 违约金以逾期支付的价款为基数，自宽限期结束之日起至甲方支付逾期价款之日止，按照中国人民银行同期活 期存款利率向乙方计付，向乙方计付，逾期支付违约金的上限为逾期支付金额的【 / 】%（不超过3%）。在我方 支付逾期付款利息后，分供商不可就此向我方再主张逾期付款的违约责任。（条款说明：乙方为中小企业时， 甲方前述条款支付期限+本条宽限期整体不得超过60日）。14.2 除本合同中规定的不可抗力外，其他不论任何原 因，乙方若不能按约定期限足额足量送至甲方指定现场存货地点，甲方向乙方收取逾期运达物资货款（含增值 税）每日【3】％的违约金，自逾期之日起计算至乙方实际送达之日止，延迟或供货不足超过【3】日时，甲方有 权单方面终止合同。14.3 未经甲方书面同意自行停止供应本合同约定的货物，均视为乙方违约，乙方除承担因此 给甲方造成的一切损失外，乙方另支付合同价款的【5】%作为违约金。 14.4若乙方提供的货物为非合同约定的厂家或品牌的产品，或提供的是假冒他人品牌的产品，甲方有权立即终止 合同，乙方必须支付合同价款【2】倍的违约金给甲方，如乙方所供产品已安装至工程项目，则乙方除承担违约 金外，还必须承担拆除、工程维修、工作面清理和重新安装产生的所有费用等，如违约金不足以弥补因此给甲 方造成的所有损失，包括一切直接损失和间接损失，则超出部分，甲方有权向乙方追偿。乙方提供的货物为合 同约定的厂家及品牌产品，但货物质量不合格或不符合约定的技术要求时，可由乙方负责更换质量合格和符合 约定技术要求的产品，同时承担合同价款【5】%的违约金，并承担因违约造成的各项损失，甲方也可直接要求 解除合同，乙方承担因此给甲方造成的所有损失。乙方提供的合同标的物因品牌、质量等原因导致甲方被项目 业主或总包方罚款或追究违约责任，乙方应向甲方相应承担赔偿责任。 14.5 本合同履行过程中，如果乙方不能按时交货，应在交货前48小时内以书面形式通报甲方，甲方视情况确定是 否同意变更供货时间。如甲方不同意变更供货时间，可自行采购部分或全部货物。甲方在自行采购和接收该违 约部分货物时实际发生的所有额外费用及因此给甲方造成的损失，从甲方应支付给乙方的任一期货款中扣除， 甲方同时保留进一步索赔的权利。 14.6甲方提出索赔通知后，乙方应在【28】日内答复，如果在【28】日内未答复，视为乙方已接受该索赔，同时 甲方保留进一步要求赔偿的权利。 网 14.7 乙方在进出场时乙方不得私自运送甲方现场物资出场，一经发现，乙方向甲方支付所涉及物资原值【2】倍 的违约金，情节严重的交由司法机关处理。 务 14.8 由于乙方自身原因（如：不按约定开立银行账户、未及时提交报量资料或不按合同配合甲方进行款项支付 等），导致货款或工程款延期支付，甲方不承担延期付款利息及违约金，乙方不得因此停止供货；乙方擅自停 供的视为乙方违约，乙方承担因此给甲方造成的所有责任及损失。 14.9 如果出现合同为可调价合同，甲乙双方调价达不成一致商情形；或者出现合同为不可调价合同，乙方提出调价， 甲乙双方达不成一致情形，则甲方有权选择其他供应商，甲方不承担任何违约责任。 14.10 若乙方因14.5和14.9款原因停止供货，或未完成全部供货、或主张解除合同等不履行合同的情形，乙方剩余 款项的支付不适用本合同8.2条款，甲乙双方应道就剩余款项的支付签订书面补充协议，重新明确支付条款，甲方 不承担任何违约责任。 14.11 其他违约与赔偿要求：【 /】。 管 联络与送达 甲方：收件人【 】，联系电话【 】，电子邮箱【 】，地址【 】。 乙方：收件人【 】，联国系电话【 】，电子邮箱【 】，地址【 】。 15.2 一方通过电子邮箱发送文件的，文件到达对方邮箱即视为送达，送达时间为电子邮件到达对方邮箱地址时间； 一方通过信函邮寄送达的，则信函寄出后的第三个工作日或收件人实际签收日（以先到的时间为准）视为送达； 一方选择直中接送达的，则递交时视为送达。 15.3 邮件邮寄至上述地址被拒收或无人签收，亦视为已经送达，由此增加的费用和（或）延误的期限由拒绝接收 一方承担。 15.4 双方承诺，因本协议的履行或争议解决，上述联系人和联系方式为有效的联系方式，各项通知均应当向上述 联系人、联系方式送达。在诉讼、仲裁中，上述联系人、联系方式亦为有效的送达地址，向上述地址的送达即 为有效送达，即使发生拒收、退信等事件。 上述联系信息发生变更的，变更方应当即时通知对方；在对方收到变更通知之前，对方当事人或者仲裁、司法 机构已经向原联系人、联系方式进行的通知，视为有效通知。 争议解决 16.1 因本合同引起或与之相关的任何争议、纠纷或权利主张，则必须先行向对方发出书面和解申请书，并告知对 方争议、纠纷或权利主张之事实及依据、联系人及联系方式，在对方收到上述通知之日起 3 个月为双方和解期限。 在和解期限内，若双方达成和解协议的，双方的权利义务按照和解协议履行；若未达成和解协议的，任何一方 采用下列第【 】种争议解决方式，并自行承担本方发生的律师费、差旅费、保函费等相关费用∶ （1）向仲裁委员会申请仲裁 周口仲裁委员会（开庭地点：郑州） 郑州仲裁委员会 武汉仲裁委员会 北京仲裁委员会 上海仲裁委员会 中国国际经济贸易仲裁委员会 R成都仲裁委 （2）向【 】人民法院提起诉讼。 网 1.因本合同引起的或与本合同有关的任何争议，如仲裁委员会，则按照其仲裁规则进行仲裁。仲裁裁决是终局的， 对双方均有约束力。 务 2.双方承诺：任何一方向仲裁委员会申请仲裁的，双方均自愿放弃向对方主张仲裁费用和实际发生的其他费用， 包括但不限于鉴定费用、评估费用、审计费用等；双方均自愿放弃向对方主张补偿因办理案件支出的合理费用， 包括但不限于律师费、保全费、差旅费、公证费等。 3.双方约定：仲裁案件无论标的额大小、复杂程度如何，商均适用普通程序，即由三名仲裁员组成仲裁庭审理，以 确保案件公正审理。 4.调解期限：争议应先行和解协商解决，设定3-6个月和解期（可根据情况调整），且和解期限不计入仲裁审理 期限。任何一方若未履行上述和解程序而直接道提请至争议解决机构的，则需要向对方承担签约合同价【10】%的 违约金；如一方出现上述情形，另一方提起反诉或反请求，则提起反诉或反请求的一方不承担违约金。 17.禁止债权转让条款甲乙双方确认，若发生下列任一情形，即视为乙方重大违约，乙方需向甲方支付合同总价 （建议10%） %的违约金，且甲方有权视违约程度单方解除本合同，同时乙方应赔偿甲方因此遭受的全部损失 管 （包括但不限于直接损失、间接损失、维权产生的律师费、诉讼费、保全费等）。具体情形如下： （1）未经甲 方事先书面同意，乙方擅自将其在本合同项下对甲方享有的全部或部分债权进行转让、质押或以其他方式处分 给任何第三方的； （2）因乙方与乙方债权人存在债务纠纷，导致该乙方债权人以甲方为被告或被申请人提起代 位权诉讼、仲裁或采取其他司法/仲裁手段的； （3）未经甲方事先书面同意，乙方以自身名义或委托任何第三 方，就本合同相关事项国对甲方的关联单位（包括但不限于业主单位、建设单位、 发包方）提起代位权诉讼、仲 裁或采取其他司法/仲裁手段的； （4）其他性质同上述条款规定的情形。18.补充条款 /】 中 其他 19.1 本合同采用下列第【 2 】种签订方式： （1）本合同自双方签字并盖章后生效，一式【叁】份，甲方执 【贰】份，乙方执【壹】份，每份具有同等法律 效力。 （2）本合同采用电子签章签署生效。根据《中华人民共和国民法典》、《电子签名法》等相关法律、法规，双 方一致认可在【 】平台（网址：【 】）使用电子印章签署合同为其真实意思表示，且确保在该平台注册时，使 用的企业信息和个人相关信息真实有效，并且自觉遵守国家法律法规和甲方在该平台的合同签约流程。甲乙双 方使用电子签章方式签署的合同，只有通过验证生效的电子原件具有法律效力，未经电子印章服务平台公司提 供书面证明材料的电子合同打印版不能作为法律依据。如因乙方使用不当给甲方造成损失，乙方愿自行承担由 此造成的全部经济损失和法律责任。 19.2未尽事宜经双方协商一致后，可签订补充协议，与本合同具有同等法律效力。 19.3对于因本合同产生的任何争议或投诉，乙方可通过【 】（条款说明：根据各公司情况填写投诉平台或者联系 方式）进行提交。甲方将在收到乙方的投诉后，对乙方的投诉进行初步审查，并尽快与乙方取得联系以进一步 了解详情。因不可抗力或第三方原因导致无法按时处理投诉的情况，甲方将尽快通知乙方，并尽力协调解决问 题。 19.4本合同条款（包括但不���于免责条款、责任限制条款等）均经双方充分协商，双方已就全部条款内容达成一 致意见，不存在单方预先拟定且未予协商的情形。 附件： 附件1：《计划采购与供应物资清单》 附件2：《法人授权委托书》 附件3：《廉政合同书》 （以下无正文） 甲 方：【盖章】 乙 方：【盖章】 网 法定代表人：【签字】 法定代表人：【签字】 委托代理人：【签字】 委托代理人：【签字】 务 地 址：【 】 地 址：【 】 电 话：【 】 电 话：【 】 商 电子信箱：【 】 电子信箱：【 】 附件1 道 计划采购与供应物资清单 人民币：元 管 计量 暂定 单价 暂定含税 序号 物资名称 规格型号 品牌/产地 生产厂家 备注 单位 数量 不含税单价 增值税 含税单价 货款金额 价税合计 暂定合同价款人民币大写： 国 以上数量为暂定项目，最终以双方签字确认的采购结算单为准 中 附件2 中国建筑 项目管理表格 表格编号 法人授权委托书 CSCEC-WZ-HN003 （甲方）： 本授权委托书声明：本的法定代表人，授权委托我公司的 为我公司代理人，代表我公司与贵公司工程对涉及投标报价，物资合同、补充协议的签订、履行，物资结算、收款等业务进行签字确认，由在上述授权范围签字的所有文书，我公 司均予认可，由此产生的一切经济法律责任由我公司承担。 代理期限为前述代理人对上述业务发生第一次签字确认之日起至本工程结算完成之日止。代理人无转委托权。 特此委托。 代理人（签字/按指纹）：身份证号码： （供应商）法定代表人签字： （供应商盖章）： 日期： 附件3 廉政合同书 甲方：【 】 乙方：【 】 为确保甲方对业主的承诺，高效、优质共同完成施工任务，争创优质工程，保证合同双方能够高效廉洁地履行， 维护双方合法权益，经双方协商，特订立如下廉政合同书。 第一条 甲乙双方的权利和义务 1.甲乙双方应本着“公开、公平、公正、诚信、透明”的原则开展工作，自觉遵守党和国家、工程项目所在省、 市、区工程建设有关法律法规以及廉政建设的各项规定。 2.甲乙双方应建立健全廉政教育制度，开展经常性教育活动，积极宣贯“合规诚信 自律清正”的廉洁从业核心理 念，加强廉政教育。 3.加强相互监督，发现对方有违反廉政合同书规定的行为，应及时提醒对方纠正。 第二条 甲方的责任 网 甲方工作人员不得有以下行为： （1）为乙方多结算工程量、多签证、多付工程款等，并向乙方索要或接受贿赂、回扣、礼金、有价证券（卡）、 务 贵重物品和好处费等; （2）在乙方报销任何应由甲方或个人支付的费用; （3）参加有可能影响公正执行公务的超标准宴请和娱乐商、健身等活动; （4）接受乙方提供的通讯工具、交通工具和高档办公用品; （5）要求、暗示或接受乙方为个人住房装修道、婚丧嫁娶、配偶子女工作的安排以及出国（境）、旅游提供的方 便; （6）向乙方介绍或推荐配偶、子女、亲属参与的工程施工合同有关的设备、材料、工程分包、劳务等; 管 （7）向乙方推荐分包单位或要求乙方购买合同规定以外的材料、机具设备等; （8）因乙方拒绝本人的不合理要求，而故意刁难乙方。 第三条 乙方的责任 国 乙方应当通过正常途径开展业务，不得有以下行为： （1）为多结算工程量、多签证、多收工程款等，向甲方及其管理人员行贿或馈赠礼金、有价证券（卡）、贵重 中 礼品; （2）为甲方及其工作人员报销应由甲方单位或个人支付的任何费用; （3）安排甲方人员参加超标准宴请、娱乐活动及带有黄、赌性质的娱乐活动; （4）为甲方人员购置或提供通讯工具、交通工具和高档办公用品等; （5）乙方向甲方工作人员及其家属或者亲友介绍从事与甲乙双方工程有关的工程分包及材料设备、周转工具的 供应、租赁等经营活动。 第四条 违约责任 1.如甲方工作人员有违反本廉政合同书的行为，由甲方纪委查处，追究相应的党纪、政务责任，涉嫌犯罪的，移 交司法机关追究刑事责任；对实名举报的，甲方要立即调查，并采取有效措施保障乙方的合法权益，防止报复 事件发生。 2.如乙方单位或个人有违反本廉政合同书的行为，甲方视情节对乙方处以合同额0.5%—1%的罚款，情节较重并给 甲方造成损失的，乙方另需赔偿甲方直接经济损失，并取消乙方工程分包资格。 第五条 甲方接受举报的途径 1. 受理电话：【 】 2. 受理地址：【 】 3. 受理部门：【 】 4. 受理邮箱：【 】 第六条 本廉政合同书作为采购合同的一部分，具有同等法律效力，本协议与采购合同同日生效，至甲乙双方工 程合同履约完止。 甲方： 乙方： 网 法定代表人： 法定代表人： 授权委托人： 授权委托人： 务 签订时间： 年 月 日 请查看报价网 商 址：https://xy.yzw.cn/sj/bid-detail?tenderId=&amp;source=3&amp;tenderCode=cscec2026081900001246027&amp;tenantId=cscec 信息来源:https://www.chinapipe.net/project/d3076919.html cqdingjiu 2026.08.21 10:06:42 道 管 国 中</t>
+          <t>秀山县2026年龙池镇、雅江镇基地信息化建设项目-第二次询比公告 询比公告-秀山县2026年龙池镇、雅江镇基地信息化建设项目-第二次 2026-08-22 ZB_ZHAOBIAOGONGGAO_START 本询比项目为秀山县2026年龙池镇、雅江镇基地信息化建设项目-第二次 （标段编号：CQBBFA2026080700101），采购人为中国电信股份有限公司秀山分公司，采购代理机构为鼎信项目 管理咨询有限公司。项目资金已落实。具备采购条件，现进行公开询比，特邀请有意向的且具有提供标的物能 力的潜在供应商（以下简称供应商）参加询比响应。 网 1.项目概况与采购内容 1.1项目概况：（1）项目地点：重庆市秀山县。 务 （2）采购金额：566037.74元（不含税）。 （3）工作范围：项目服务内容自动农业气象监测系统、土壤墒情监测系统、智能虫情测报系统、杀虫控制系统、 水肥一体化、宣传片拍摄等，具体以技术规范书为准。 商 （4）项目进度要求：整个工期90天。 1.2采购内容及标包划分情况： 1.2.1 道 序号 标包名称 产品名称 规格型号 数量 交货地点 交货期 管 秀山县2026年龙池镇、雅江镇基地信息化建 1 集成服务 - - 重庆市秀山县 整个工期90天 设项目 本项目不划分标包。国 本项目将按照最新的《中国电信供应商不良行为管理规则》执行供应商不良行为处理结果，请重点关注 处理结果适用的供应商主体、被处理产品、处理范围、禁限期、处理措施等关键内容，请务必登录中国电信阳 光采购网（https://caigou.chinatelecom.com.cn）查阅《中国电信供应商不良行为管理规则》。本项目根据《中国 电信供应商中不良行为管理规则》选择适用备选处理措施（但涉及生产安全责任事故的处理结果不适用备选措 施）。 1.2.2成交供应商数量：1个，每个成交供应商对应的份额如下： [第一成交供应商：份额100%] 1.3本项目设置最高响应限价。最高响应限价为566037.74元人民币（不含税），供应商响应报价高于最高 响应限价的，其响应将被否决。 序号 采购内容 最高限价 备注 1 信息化建设类 566037.74 不含税价格 2.供应商资格要求 2.1供应商基本资格要求 2.1.1 供应商应为中华人民共和国境内法律上和财务上独立的法人或依法登记注册的其他组织，合法运作 并独立于采购人和采购代理机构。提供有效的行政管理部门登记的主体资格证件（包括但不限于营业执照、事 业单位法人证书、社会团体法人登记证书等）。法人下属不具备法人资格的分支机构参与响应的，应提供所属 法人针对本项目或覆盖本项目的经营事项的有效授权。 2.1.2 供应商的法定代表人或负责人为同一人或者存在控股、管理关系的不同供应商，不得参加同一标包 响应或者未划分标包的同一询比项目响应。 2.1.3 本次询比不接受联合体响应。} 2.1.4 本次询比不接受代理商响应。 } 2.1.5 供应商须承诺为本项目开具增值税专用发票。 2.1.6资质要求：供应商须具备建设行政主管部门颁发的电子与智能化工程专业承包贰级及以上资质，提供清晰、 完整、有效的行政主管部门颁发的资质证书扫描件。已按照《住房和城乡建设部关于印发建设工程企业资质管 理制度改革方案的通知》（建市〔2020〕94号）规定取得新资质证书的（在2020年11月30日之后），应提供相应 等级的最新资质证书扫描件。 2.1.7安全生产条件：供应商须具有建设行政主管部门颁发的安全生产许可证，企业主要负责人具有相应建设行政 主管部门颁发的安全生产考核合格证A证（企业名称为响应单位名称），提供相应证书扫描件，评委有权对相应 证书进行核验，如存在不实不予认可。 网 2.1.8业绩要求：供应商须提供2024年1月1日至本项目发布公告之日的类似项目（信息化建设类）业绩证明材料至 少一个，且单个合同金额不低于30.00万元（含税）。 注：业绩证明材料包括: 务 1）合同关键页扫描件，合同关键页包括体现合同标的、合同金额（如有）、合同签订时间、合同盖章页，否则 不予认可；合同中能体现合同金额的，以合同金额与合同签订时间为准；如不能体现合同金额，以合同对应订 单的累计金额与订单时间为准。 商 2）该合同对应的其中一张发票扫描件，发票主体名称须与合同双方或其下属分公司名称一致，发票开具时间在 本项目公告发布之日前。评审委员会有权在国家税务总局全国增值税发票查验平台 （https://inv-veri.chinatax.gov.cn/）进行发票查验，如查验结果与提供发票信息不一致则该发票不予认可。 道 如需检查以上相关资料原件，则须在要求时间内提供。 2.1.9项目团队人员要求：供应商须为本项目配备项目经理1人、施工员1人、安全员1人。 管 a）项目经理须具备相应建设行政主管部门颁发的安全生产考核合格证B证（扫描件），项目经理须具备在响应 单位注册的二级及以上注册建造师执业资格（专业为机电工程），提供项目经理有效期内身份证扫描件，相关 建造师资质证书的证明材料（如电子证照或相关官方网站查询截图等）。 b）供应商为本项目配国备的施工员、质量员须附上岗证书、有效期内身份证；安全员须附相应建设行政主管部门 颁发的“安全生产考核合格证C证”、有效期内身份证（扫描件）。 注： 中 ①人员不得兼任，如人员兼任，不予认可。项目经理、安全员须提供社保局出具由响应单位缴纳的2026年4月1日 之后任意一个月的社保证明，其它人员如为第三方公司代缴社保，则还须提供第三方公司与供应商的代缴协议 或类似证明。 ②评委有权通过原件核查或登陆全国建筑市场监管公共服务平台 （https://jzsc.mohurd.gov.cn/home）、全国或当地住房和城乡建设委员会官方网站等网络查验等方式进一步核实 响应文件中的相关信息。若供应商存在任何形式的弄虚作假行为，一经查实，则将否决其响应。 ③以上资料原件备查，如评审时需要核查，接到正式通知后，须在规定时间内提供，否则不予认可。 2.1.10购买保险要求：供应商须符合《安全生产责任保险实施办法》相关要求，购买包含安全生产责任险在内的 人身意外类相关保险（保障范围须覆盖本项目全部实施人员，累计保险赔付额度不低于200万元/人）。供应商须 提供相应的保单证明，或承诺在合同签订前完成购买并达到相应保额。 2.2供应商不得存在下列情形之一 （1） 为采购人不具有独立法人资格的附属机构（单位）； （2） 被依法暂停或取消投标/响应资格的； （3） 被责令停产停业、暂扣或者吊销许可证、暂扣或者吊销执照； （4） 进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （5） 在最近三年内（自2023年09月01日起）被相关行业主管部门或司法机关认定有骗取中标/成交、严重 违约、重大工程质量或者安全问题的； （6） 在最近五年内（自2021年09月01日起）被判处单位行贿罪，且行贿行为与采购活动相关的（以“中 国裁判文书网”的生效判决为准）； （7） 在最近五年内（自2021年09月01日起）被判处合同诈骗罪的（以“中国裁判文书网”的生效判决为 准）； （8） 被最高人民法院在“信用中国”网站（www.creditchina.gov.cn）或各级信用信息共享平台中列入失 信被执行人名单，已执行完毕或不再执行的除外； 网 （9） 为本询比项目提供过设计、编制技术规范和其他文件的咨询服务； （10） 为本工程项目的相关监理人，或者与本工程项目的相关监理人存在隶属关系或者其他利害关系； 务 （11） 为本询比项目的代建人； （12） 为本询比项目的采购代理机构； 商 （13） 与本询比项目的监理人或代建人或采购代理机构同为一个法定代表人； （14） 与本询比项目的监理人或代建人或采购代理机构存在控股或参股关系； 道 （15） 被工商行政管理机关在国家企业信用信息公示系统中列入严重违法失信企业名单的； （16）中国电信在职员工违规担任供应商法定代表人并参与采购活动的； 管 （17）中国电信集团有限公司/中国电信股份有限公司中层及以上管理人员违反有关领导人员配偶、子女 及其配偶经商办企业行为管理规定，其配偶、子女及其配偶经商办企业参与采购活动的； （18）中国电信领导人员离职或退休后三年内违反《国有企业领导人员廉洁从业若干规定》等相关规定 任职、投资入股的私营国企业、外资企业和中介机构，参与其原任职单位采购活动的； （19）其他按照中国电信供应商不良行为处理结果及《中国电信供应商不良行为管理规则》的结果执行 规则，应对供应商及其响应产品在本项目中执行禁止采购处理措施的； （20）法律法规、询比文件限定的其他情形。 中 2.3产品资格要求 2.3.1 产品应是来自中华人民共和国的成熟稳定的产品。 2.4法律法规规定的其他要求。 3.资格审查方法 本项目将进行资格后审，资格审查标准和内容见询比文件第三章“评审办法”，凡未通过资格后审的供应商， 其响应将被否决。 4.询比文件的获取 4.1询比文件获取时间:2026年08月24日 17时00分00秒至2026年08月27日 17时00分00秒（北京时间，下同）。 4.2询比文件获取方式：登录“中国电信阳光采购网（https://caigou.chinatelecom.com.cn）”后，通过“招 投标-采购文件领取”模块或通过“电子采购入口”跳转中国电信电子采购系统，进入本项目进行询比文件登记 申领，未在系统注册的供应商须先进行注册，注册方法详见本公告“7供应商注册”。 4.3询比文件费用：本项目不收取文件费用。 5.响应文件的递交 5.1响应文件递交截止时间（即响应截止时间）为：2026年09月01日 15时00分00秒 5.2电子响应文件的提交方式：登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通 过“招投标-我的项目”模块或通过“电子采购入口”跳转中国电信电子采购系统，选择本项目进行响应文件提 交，供应商应在响应文件提交截止时间之前通过电子采购系统完成加密电子响应文件的上传。供应商未在电子 采购系统进行询比文件申领登记或电子响应文件未按照要求加密的，将无法通过电子采购系统提交电子响应文 件。 5.3本项目将于响应文件提交截止同一时间通过中国电信电子采购系统开启响应文件，采购人/采购代理机 构邀请响应供应商的法定代表人或者其委托代理人准时参加。 网 7.供应商注册 7.1中国电信阳光采购网注册 未注册过的潜在供应商，须通过中国电信阳光采购网（https://caigou.chinatelecom.com.cn）首页“立即注 务 册”模块完成注册后，方可申领本项目询比文件。 7.2 CA证书办理 参加询比响应的潜在供应商须提前办理CA证书，并确保商CA证书在使用时有效。CA证书办理流程详见中 国电信阳光采购网首页“操作指引-CA办理”。 7.3技术支撑联系方式 道 服务热线：4000111884 服务邮箱：zb_support@chinatelecom.cn（电子采购系统技术支撑） 管 ctsc@chinatelecom.cn（CA证书办理技术支撑） 8.发布公告的媒介 本询比公告在 中国电国信阳光采购网（https://caigou.chinatelecom.com.cn）、中国招标投标公共服务平台 （http://www.cebpubservice.com/）上发布，其他媒介转载无效。 9.联系及异议接收方式 中 9.1联系方式 采 购 人: 中国电信股份有限公司秀山分公司 采购代理机构: 鼎信项目管理咨询有限公司 地 址： 地 址： 邮 编： 邮 编： 408000 联 系 人： 谭老师 联 系 人： 姚老师 电 话： 19123814835 电 话： 18183123500 电子邮件： 电子邮件： yufei.cq@chinaccs.cn 网 址： 网 址： 开户银行： 中国工商银行袁家岗支行 账 号： 9558833100007360570 9.2异议接收方式 登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投标-采购异议-提出异议” 模块提出。 采购代理机构：鼎信项目管理咨询有限公司 2026年08月22日 信息来源:https://www.chinapipe.net/project/d3078606.html cqdingjiu 2026.08.24 12:31:35 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>镀锌钢管 DN100*4.0：500米；镀锌钢管 DN150*4.5：250米；镀锌钢管 DN65*3.25：650米；镀锌钢管 DN50*3.25：800米</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -709,7 +705,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(三标段)招标公告</t>
+          <t>中建桥梁有限公司西部(重庆)科学城德感片区污水管网修复完善工程项目(白沙部分新增)市政工程采购公告</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +715,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -738,49 +734,45 @@
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>忠县</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(三标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。</t>
+          <t>西部（重庆）科学城德感片区污水管网修复完善工程项目所需（白沙部分新增）市政工程专业分包工程，包括非开挖紫外光修复、安装前道内部勘测、清淤、封堵气囊、导排水，钢内衬成环回顶，铺设防划垫膜，主物料的拉入、连接充气设备、安装排水软管、物料的充气/紫外光固化、冷却物料、切除管口扎头多余务、抽出内膜、CCTV检测验收、拆除堵通水修复，管道铺设、管件、检查井、完成建筑垃圾清理，路面恢复等主要工序和辅助工序。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>本项目工程总投资金额：约3140万元；本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>高标准农田建设工程</t>
+          <t>市政工程专业分包工程</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(三标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 网 2.项目概况与招标范围 务 2.1 建设地点： 忠县花桥镇、新立镇、石宝镇、兴峰乡。 商 2.2 项目概况与建设规模①忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）：田块整治 工程：旱地区域撂荒地整治278.95亩；灌溉与排水工程：新建200m蓄水池6座、PE75管道967m、新建1.2*1.2m箱 涵16m、新建2*2m箱涵8m；田间道路工程：新建2.5m混凝土生产路15114m、改建2.5m混凝土生产路1078m、新 建2.5m泥结碎石生产路910m、改建2.5m泥结碎道石生产路279m、新建3.0m混凝土生产路601m、改建3.5m混凝土机 耕路4587m；地力提升工程：施有机肥278.95亩；其他工程：工号牌124块。 管 ②忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）：田块整治工程：旱地区域撂荒地 整治195.54亩；灌溉与排水工程：新建100m蓄水池4座、新建200m蓄水池6座、PE75管道5258m、PE90管 道1375m、PE110管道2156m、改建0.5*0.6m混凝土排水沟740m、改建0.6*0.8m混凝土排水沟109m、改建0.8*1.0m混 凝土排水沟296m、改建1*1.5m混凝土排水沟262m、新建3*2m盖板涵1座；田间道路工程：新建2.5m混凝土生产 路11359m、改建2.5m混国凝土生产路3430m、新建2.5m泥结碎石生产路1834m、新建3.0m混凝土生产路350m；农田 防护工程：新建1.0m高挡土墙39m；地力提升工程：施有机肥195.54亩；其他工程：工号牌142块。 中 2.3 本项目工程总投资金额：约3140万元； 本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）施工图所示范围的所 有内容为准，详见发布的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分： 标段划分情况、建设规模及标段合同估算金额等内容如下： 合同估算金额 序号 项目名称 建设地点 （万元） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二 1 花桥镇、新立镇 1022 标段） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三 2 石宝镇、兴峰乡 735 标段） 网 本项目共分为2个标段，每家投标单位仅对2个标段中的任意1个标段进行投标，若同时参与2个及以上标段投标的， 其投标文件无效。 务 2.7 其他： / 商 3.政府采购工程 道 3.1 是否属于政府采购工程：是 □否 管 3.2 是否专门面向中小企业预留：是 国 专门面向中小企业预留的实施方式： 中 方式一：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（忠县）下载招标文件、工 程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字 证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责 任自负。 5.2投标人可在重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要网提问”栏提出疑问，提问时间从 本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-10-12 09:30，投标人应当在投标截止时间前，通过互 务 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 商 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 道 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 管 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 国 开户银行: 开户银行: 账 号: 账 号: 中 监督部门: 忠县发展和改革委员会 电 话: 023-54456078 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段） 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005499 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421353 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891814619 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082001038 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00385 信息来源:https://www.chinapipe.net/project/d3076880.html cqdingjiu 2026.08.21 10:06:45</t>
+          <t>中建桥梁有限公司西部(重庆)科学城德感片区污水管网修复完善工程项目(白沙部分新增)市政工程采购公告 为满足中建桥梁有限公司对中建桥梁有限公司西部（重庆）科学城德感片区污水管网修复完善工程项目生产需 求，现就西部（重庆）科学城德感片区污水管网修复完善工程项目所需（白沙部分新增）市政工程专业分包工 程进行采购，诚邀符合资格要求、能提供优质服务的供应商参与报名。 一、工程概况 1、采购主体：中建桥梁有限公司 网 2、工程地址：重庆市江津区 3、采购内容：非开挖紫外光修复、安装前道内部勘测、清淤、封堵气囊、导排水，钢内衬成环回顶，铺设防划 垫膜，主物料的拉入、连接充气设备、安装排水软管、物料的充气/紫外光固化、冷却物料、切除管口扎头多余 务 废料，抽出内膜、CCTV检测验收、拆除堵通水修复，管道铺设、管件、检查井、完成建筑垃圾清理，路面恢复 等一切所需要的主要工序和上述未明示但实际完成承包项目内容所需的辅助工序所包括的全部工作内容。 二、报名单位资格要求 商 1、具有中华人民共和国企业独立法人资格，持有工商行政管理部门核发并通过最近年检的法人营业执照。代理 人须得到报名单位的授权。 2、资质要求：具备有效的资质证书、安全生道产许可证及相关认证证书，须具备市政公用工程施工总承包资质叁 级及以上资质或具有相关资质成建制单位；具备法律主体资格，具有独立订立及履行合同的能力，可开具增值 税专用发票。 3、业绩要求：在国内有关部门和行业的监督检查中没有不良记录；与中建桥梁有限公司及下属各单位没有不良 管 合作记录； 4、人员、设备、资金、服务、信誉等方面具有相应的能力。 5、成交分供商同意使国用云筑网（http://www.yzw.cn）筑易签电子签章功能完成采购合同签订；鼓励无纸化办公， 推荐分供商使用云筑网电子公章功能完成采购报名和报价工作。 6、存在以下情形的，原则上不得参与本次采购： 中 （1）严重违法失信企业； （2）失信被执行企业； （3）经营异常企业； （4）采购主体本上级单位禁用分供商的“换马甲”企业。 三、报名 1、报名方式 已在云筑网（http://www.yzw.cn）上注册的供应商，并经中建股份本下级任意单位认证“专业分包类”的分供商， 登录后即可报名。 2、报名时间。 公告发布时间： 2026 年8 月20 日（北京时间）。 报名截止时间为： 2026 年 8 月 24日 09 时 00 分（北京时间），具体以云筑网公示时间为准。 3、采购文件的获取 经资格审查入围的报名单位，登录云筑网下载采购文件，并依据采购文件要求于采购文件响应截止日前在云筑 网上递交响应文件。 4、报名及采购文件响应阶段 IP 地址相同的分供商直接淘汰。报名阶段存在信息重叠、工商关联（同一高管或 董监高，或股权关联（四层及以下））的分供商最多允许一家通过资格审查；报价阶段存在信息重叠、工商关联 （同一高管或董监高，或股权关联（四层及以下））的分供商直接淘汰。 5、报名附件格式参照公告附件要求，内容包括： （1）《分包商资质审查表》； 网 （2） 三证合一的营业执照； （3） 资质证书 务 （4） 安全生产许可证 （5） 法定代表人身份证明，授权委托书，授权委托人身份证复印件（正反面）； （6） 其他证明企业情况的资料（如企业荣誉及相关证书商，业绩等，办公场所、生产车间、仓储照片等）； 上述资料（1）至（5）项为必须项，第（6）项为选择项，报名单位可根据公司实际情况选择填写第6（项），所 有报名资料按照以上顺序盖章后扫描成一个 PDF 版电子文件，报名时将 PDF 版电子文件上传至云筑网。 道 四、保证金 报名成功并通过资审的分供商，在签收采购文件前缴纳1万元的采购响应保证金，报名单位可通过云筑网线上缴 纳保证金或购买保证保险（二选一），保证金在采购成交结果公示后30个工作日内退还，保险不予退还。 管 保证金缴纳操作如有问题，请报名单位联系云筑网客服，联系电话：4006-818-555。 若发生下列情况之一，采购人不予退还响应人所缴纳的保证金： 国 （1）响应人在响应截止日至采购人发布成交通知之日期间撤销其响应文件的； （2）提供虚假的材料谋取成交的； 中 （3）成交分供商收到成交通知后在规定的期限内未按采购文件要求签订采购合同的； （4）违反廉政承诺内容的； （5）采购期间发生其它违法、违规行为的。 五、联系方式 联系人：张继涛 电话：13919184919 联系人：游镇华 电话：13212385162 信息来源:https://www.chinapipe.net/project/d3078567.html cqdingjiu 2026.08.24 12:31:34</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>管道：967m；管道：5258m；管道：2156m</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>重庆, 高标准农田建设工程, 资金情况, 产品种类</t>
+          <t>重庆, 市政工程, 污水管网修复</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)招标公告</t>
+          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项目设备材料招标公告</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -811,32 +803,32 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>忠县</t>
+          <t>武隆区</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)，包括田块整治、灌溉与排水、田间道路、地力提升和其他工程。</t>
+          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项目设备材料招标公告</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>本项目总投资金额约3140万元，其中二标段1022万元，三标段735万元。</t>
+          <t>项目资金来自重庆市武隆区提升农村饮水质量专项行动（2025-2027）项目资金，项目出资比例为100%。</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>主要产品包括混凝土生产路、泥结碎石生产路、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土排水沟、混凝土</t>
+          <t>涉及饮用水卫生安全产品的卫生许可批件</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(二标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程已由 忠县发展和改革委员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来自 业 主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具备招标条 件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点： 忠县花桥镇、新立镇、石宝镇、兴峰乡。 2.2 项目概况与建设规模①忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）：田块整治 务 工程：旱地区域撂荒地整治278.95亩；灌溉与排水工程：新建200m蓄水池6座、PE75管道967m、新建1.2*1.2m箱 涵16m、新建2*2m箱涵8m；田间道路工程：新建2.5m混凝土生产路15114m、改建2.5m混凝土生产路1078m、新 建2.5m泥结碎石生产路910m、改建2.5m泥结碎石生产路279m、新建3.0m混凝土生产路601m、改建3.5m混凝土机 耕路4587m；地力提升工程：施有机肥278.95亩；其他工程：工号牌124块。 商 ②忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三标段）：田块整治工程：旱地区域撂荒地 整治195.54亩；灌溉与排水工程：新建100m蓄水池4座、新建200m蓄水池6座、PE75管道5258m、PE90管 道1375m、PE110管道2156m、改建0.5*0.6m混凝土排水沟740m、改建0.6*0.8m混凝土排水沟109m、改建0.8*1.0m混 凝土排水沟296m、改建1*1.5m混凝土排水沟2道62m、新建3*2m盖板涵1座；田间道路工程：新建2.5m混凝土生产 路11359m、改建2.5m混凝土生产路3430m、新建2.5m泥结碎石生产路1834m、新建3.0m混凝土生产路350m；农田 防护工程：新建1.0m高挡土墙39m；地力提升工程：施有机肥195.54亩；其他工程：工号牌142块。 2.3 本项目工程总投资金额：约3140万元； 管 本次招标项目合同估算金额：二标段 1022万元；三标段 735 万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段）施工图所示范围的所 有内容为准，详见发布国的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分中： 标段划分情况、建设规模及标段合同估算金额等内容如下： 合同估算金额 序号 项目名称 建设地点 （万元） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二 1 花桥镇、新立镇 1022 标段） 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（三 2 石宝镇、兴峰乡 735 标段） 本项目共分为2个标段，每家投标单位仅对2个标段中的任意1个标段进行投标，若同时参与2个及以上标段投标的， 其投标文件无效。 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 方式一：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 网 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 .技术成果经济补偿 务 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （忠县）下载招标文件、工程量清单、电子图纸等资料。商参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（忠县）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源 交易监督网、重庆市公共资源交易网（忠县）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数字证 书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的，责任 自负。 道 5.2投标人可在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要提 问”栏提出疑问，提问时间从本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 管 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-10-12 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 国 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 中忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 忠县发展和改革委员会 电 话: 023-54450483 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（二标段） 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421361 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00386 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005423 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891832091 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082001039 信息来源:https://www.chinapipe.net/project/d3076879.html 网 cqdingjiu 2026.08.21 10:06:45 务 商 道 管 国 中</t>
+          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项 目设备材料招标公告 1.招标条件 本招标项目武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水 厂工程已由重庆市武隆区发展和改革委员会以武隆水利发〔2025〕295号、武隆水利发〔2025〕 296号、武隆水 利发〔2025〕311号、武隆水利发〔2025〕313号批准建设，项目业主为重庆市庆祥水资源开发有限公司，招标项 目资金来自重庆市武隆区提升农村饮水质量专项行动（2025-2027）项目资金，项目出资比例为100%，招标人为 重庆武隆城市发展(集团)有限公司。项目已具备招标条件，现对该4个项目设备材料采购进行公开招标，评标办 法采用经评审的最低投标价法。 网 2.项目概况与招标范围 务 2.1 建设地点：武隆区黄莺乡、芙蓉街道、火炉镇、土地乡 商 2.2 项目概况与建设规模 道 （1）武隆区黄莺乡龙洞水厂工程：该工程由取水工程、输水工程、厂区工程和配水工程组成。取水工程新建30 立方米取水井1座 ;输水工程新增DN110PE输水管道0.7公里,DN89x4.5 毫米涂塑无缝钢管 管 5.564 公里，配套减压池1座及配套相应阀门井 ;厂区工程新增日处理规模500立方米一体化净水设备1套，更换消 毒加药设备1套，改造现有厂区管理房厂 :配水工程新建配水管道85.72公里及配套附属设施，新建减压池11 座，100立方米调蓄水池(补氯)1座（本工程的设备材料部分）。 国 （2）武隆区芙蓉街道白杨村集中供水工程：设计供水规模为1256立方米/天，安装管网共计 172.082公里，其 中DN100涂塑钢管15.883公里，DN80 涂塑钢管11.624公里，DN65 涂塑钢管13.336公里，DN50涂塑钢管37.861公里， 中 DN40涂塑钢管93.378公里 ;新建30立方米加氯池及配套加氯设备用房1座 ;新建泵站1座(扬程280米，3.84方/小 时，功率18.5千瓦) ;新建减压池25座 ;管网配套各类阀井共计376座，其中闸阀井245座，泄水阀井65座，排气 阀井 66 座（本工程的设备材料部分）。 （3）武隆区火炉镇万峰水厂工程：改造及延伸供水管道总长71.133 公里，其中：改造供水管道59.085公里，延 伸供水管道 12.048 公里，新建减压池 10 个，新建表井 312 座等（本工程的设备材料部分）。 （4）武隆区土地乡桂花水厂工程：工程供水规模为 500 吨/天。主要建设内容：一是水源引水工程。新增取 水水源点 2 处，安装引水管道总长 12.502 公里；二是供水管道工程41.216 公里；三是厂区围墙改造工程等 （本工程的设备材料部分）。 2.3 本次招标项目货物采购估算金额：1701.27万元。 2.4 招标范围：包含所列货物制造、包装、运输、保险至现场、设备及设备的安装调试(管网不含安装)、检验、 检测、退换货、质保期内售后服务、税费等完成本项目所产生的所有费用。 2.5 交货地点：重庆市武隆区（招标人指定地点）。 2.6 交货期：60日历天，计划开始交货日期：合同签订后10天内开始交货。 3.政府采购工程 网 3.投标人资格要求 3.1 本次招标允许投标人以投标货物的下列身份参加投标： 务 制造商 商 代理商（包括经销商、制造商下属销售子公司） 道 3.1.1 投标人为制造商应符合以下要求： 管 （1）具备独立法人资格； 国 （2）具备有效的《涉及饮用水卫生安全产品卫生许可批件》。 中 3.1.2 投标人为代理商应符合以下要求： （1）具备独立法人资格； （2）投标货物制造商应具备有效的《涉及饮用水卫生安全产品卫生许可批件》。； （3） 涂塑无缝钢管具有制造商授权书。 注：本招标项目同一标段中，一个制造商对同一品牌同一型号的货物，仅能委托一个代理商参加投标，否则各 相关投标均无效； 同一品牌同一型号货物的制造商和代理商不得在本招标项目同一标段中投标，否则各相关 投标均无效。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表 第1.4.1项内容。 3.3 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，网招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件及相关资料。 务 参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重 庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时 完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网（武隆区）（https://www.cqggzy.com/wulongweb）和重庆市公共资源交易监 商 督网（http://ggzyjyjgj.cq.gov.cn/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发布 至2026-08-26 12:00:00前。 4.3招标人应于2026-08-26 12:00:00前在重庆市公共资源交易网（武隆区）（https://www.cqggzy.com/wulongweb）和 重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/）发布澄清。 5.投标文件递交的内容 道 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-11 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 管 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网（武隆区）（https://www.cqggzy.com/wulongweb）和重庆市公共资源 交易监督网（http://ggzyjyjgj.cq.gov.cn/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交 易监督网上发布。] 7.联系方式 国 招 标 人: 重庆武隆城市发展（集团）有限公司 代理机构: 中大宇辰项目管理有限公司 地 址: 重庆市武隆区望江苑1栋 地 址: 渝北区新牌坊二路136号路华苑小区 邮 编: 中 邮 编: 项目负责人: 张老师 项目负责人: 欧朝华 电 话: 023-77721580 电 话: 18996416879 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市武隆区发展和改革委员会 电 话: 023-77765552 2026年08月22日 武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个 项目设备材料 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公 中国建设银行股份有限公司重庆渝中支 6232813760003413621 司 行 重庆联合产权交易所集团股份有限公 中国农业银行股份有限公司重庆自由贸 312601010400083780000031794 司 易试验区分行 重庆联合产权交易所集团股份有限公 重庆银行股份有限公司七星岗支行 15010202900420146631981 司 信息来源:https://www.chinapipe.net/project/d3078450.html cqdingjiu 2026.08.24 12:31:35 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>管道：967m；管道：5258m；管道：2156m</t>
+          <t>排水钢管 Φ200*6m：3000米；DN110PE输水管道0.7公里；DN89x4.5毫米涂塑无缝钢管5.564公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -851,7 +843,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(一标段)招标公告</t>
+          <t>重庆高速巨能建设集团有限公司城开高速城开隧道泄水洞施工项目第一批物资(排水材料)进行优选采购公告</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -861,7 +853,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -880,49 +872,45 @@
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>忠县</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>田块整治工程、灌溉与排水工程、田间道路工程、地力提升工程、其他工程</t>
+          <t>本项目涉及采购钢带增强聚乙烯螺旋波纹管和钢带波纹管密封胶圈，用于重庆高速巨能建设集团有限公司城开高速城开隧道泄水洞施工项目。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>项目总投资金额约3140万元，本次招标项目合同估算金额一标段1167万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>高标准农田建设工程</t>
+          <t>[object Object],[object Object]</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程(一标段)招标公告 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）招标公告 1.招标条件 本招标项目忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）已由 忠县发展和改革委 员会 以 忠发改审批〔2026］753号批准建设，项目业主为 忠县畅达建设投资有限公司 ，建设资金来 自 业主自筹资金，项目出资比例为 100% ，招标人为 忠县畅达建设投资有限公司 。项目已具 备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 网 务 2.项目概况与招标范围 商 2.1 建设地点： 忠县马灌镇、三汇镇、永丰镇。 道 2.2 项目概况与建设规模：忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）：田块整治 工程：水田整治50.67亩、水田区域撂荒地整治79亩、旱地区域撂荒地整治62.83亩；灌溉与排水工程：新 建200m蓄水池5座、新建500m蓄水池1座、泵站1座；田间道路工程：新建2.5m混凝土生产路12325m、改 建2.5m混凝土生产路8549m、新建2.5m泥结碎石生产路1223m、新建3.0m混凝土生产路576m、改建3.0m混凝土生 管 产路648m、改建3.0m混凝土生产路（拆除原1.5m宽路）266m、改建3.5m混凝土机耕路1662m；地力提升工程：施 有机肥136.48亩；其他工程：公示牌1座、工号牌213块。 国 2.3 本项目工程总投资金额：约3140万元； 中 本次招标项目合同估算金额：一标段1167万元。 2.4 招标范围：以忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段）施工图所示范围的所 有内容为准，详见发布的施工图，工程量清单，招标文件及其补充文件。 2.5 工期要求：工期要求：90日历天 ，缺陷责任期为 24个月。 2.6 标段划分： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 网 方式一：本项目整体面向中小企业。 务 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 商 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质或水利水电工程施工总承包三级及以上资质或公路工程施工总承包三级及以上资质； 道 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 管 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 国 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 中 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（忠县）下载招标文件、工 程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及CA数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 5.2投标人可在重庆市公共资源交易网（忠县）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从 本公告发布至2026-08-24 12:00:00前。 5.3招标人应于2026-08-25 18:00:00前在重庆市公共资源交易网（忠县）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-10 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（忠县）发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 忠县畅达建设投资有限公司 代理机构: 重庆市忠资项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 谭超 项目负责人: 张钰枝 电 话: 023-54216300 电 话: 18002358213 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 网 监督部门: 忠县发展和改革委员会 电 话: 023-54456078 务 2026年08月20日 忠县2026年花桥镇大柏村等7个乡镇16个村高标准农田建设工程（一标段） 商 户名 开户行 投标保证金账号 忠县公共资源综合交易中心 重庆农村商业银行股份有限公司忠县支行 3501010120010008082000104 忠县公共资源综合交易中心 中国农业银行股份有限公司重庆忠县支行营业部 314501010400145900000005469 道 忠县公共资源综合交易中心 中国工商银行股份有限公司忠县支行 9558853100005421379 忠县公共资源综合交易中心 中国银行股份有限公司重庆忠县支行 111669494227VA00387 忠县公共资源综合交易中心 中国邮政储蓄银行股份有限公司忠县支行 95000601001203891884496 管 信息来源:https://www.chinapipe.net/project/d3076876.html cqdingjiu 2026.08.21 10:06:46 国 中</t>
+          <t>重庆高速巨能建设集团有限公司城开高速城开隧道泄水洞施工项目第一批物资(排水材料)进行优选采购公告 供应商应当在投标截止时间前，通过注册供应商账号在重庆高速集团物资采购平台 （http://113.250.85.222:8099/merchants/login）上进行报价并将投标文件扫描上传至该平台。 根据《国有企业采购操作规范》、《重庆高速巨能建设集团有限公司采购管理办法》等有关规定，重庆高速巨 能建设集团有限公司城开高速城开隧道泄水洞施工项目第一批物资（排水材料）进行优选采购，现将本次优选 有关事项公告如下： 一、优选项目名称：重庆高速巨能建设集团有限公司城开高速城开隧道泄水洞施网工项目第一批物资（排水材料） 采购项目 二、项目编号：GSJNCK-XSD-WZ-2026-0001 务 三、中选人数： （一）1名 （二）2名 □（供货比例第一名按 / %、第二名 / %） 商 （三）3名 □（供货比例第一名按 / %、第二名 / %、第三名 / %） 四、采购方式：公开优选 道 仅限于重庆高速集团物资采购平台：http://113.250.85.222:8099/merchants/login?redirect=%2F 五、优选范围表 管 序号 材料名称 规格型号 单位 暂定采购量 交货地点 备注 1 钢带增强聚乙烯螺旋波纹管 DN1200(PE)承插式 米 1884 重庆市开州区满月镇 国 2 钢带波纹管密封胶圈 DN1200 个 314 重庆市开州区满月镇 总合计 2198 六、竞选报价 中 （一）竞选报价为物资运送到采购人指定地点的不含税到场价，包括但不限于 材料费、人工费、仓储费、各项 税费、装车费、运输费、下车费、利润等所有一切其他费用。 （二）二次竞选：无。 七、竞选人资格 （一）竞选人必须是在中华人民共和国境内依法注册，具有独立法人资格，具有优选标的物经营范围的生产商 或销售商。 （二）本次优选不接受联合体参选，单位负责人为同一人或者存在控股、管理关系的不同单位，不得同时参加 竞选，否则，相关竞选均被否决。 （三）竞选人必须为巨能集团集采平台内的合格供应商（状态为：可投标，信息维护更新后的缴费年度显示 为2026年），否则视为未参与竞选，（高速集团内部单位除外），供应商注册网 址：http://222.178.219.165:7001/merchants/login。 （四）竞选人已按优选文件要求已缴纳竞选保证金（若有），否则，相关竞选将被否决。 （五）竞选人在国家企业信用信息公示系统中未被列入严重违法失信企业名单，同时必须为三年内与重庆高速 巨能建设集团有限公司无诉讼纠纷的公司，否则，相关竞选将被否决。 八、质量要求 （一）质量技术要求： 1、钢带增强聚乙烯螺旋波纹管：DN1200(PE)承插式，《埋地排水用钢带增强聚乙烯(PE)螺旋波纹管》CJ/T 225-2011。 （二）合同履行过程中中选供应商所供货物被采购人、监理、业主及行业监管部门抽检不合格的，采购人有权 单方面解除合同，并将中选供应商清退出场，所产生的一切损失由中选供应商承担，给采购人造成经济损失费 用采购人可在货款中直接扣除作为经济损失补偿，同时采购人保留诉讼的权利。同时将其列入集团供应商黑名 单，永久不得在集团范围内参与采购竞选。 网 九、付款方式 （一）预付款:无。 务 （二）付款方式：电汇、银行承兑或供应链金融产品（不超过12个月），具体情况根据采购人实际情况确定，中 选供应商不得以任何理由拒绝，若中选供应商接收银行承兑、供应链经融产品后需进行提前兑付时，贴息费用 由中选供应商自行承担； 商 （三）供货周期：以采购人需求时间为准； （四）结算、支付方式：材料进场验收合格后中选供应商与采购方双方每月10日办理结算，中选供应商每 月15-20日前向采购方提供当月结算金额等额的道增值税专用发票，采购方进行线上挂票，达到付款条件后，采购 方60日内支付结算货款的95%，剩余5%货款作为质量保证金，质量保证金在合同履约完成后3个月内无息支付。 （五）在合同履行期间，若因国家税务政策调整导致的税率变更，双方签订补充协议进行变更，合同不含税总 价不变。 管 （六）清单量为暂定数量，最终结算数量以双方共同验收并签字确认的结算验收单为准。 十、优选限价 国 暂定采购 优选限价（不含 序号 材料名称 规格型号 单位 量 税） 单价 总中价（元） （元） 1 钢带增强聚乙烯螺旋波纹管 DN1200(PE)承插式 米 1884 1060.00 1997040.00 2 钢带波纹管密封胶圈 DN1200 个 314 80.00 25120.00 总合计 2198 2022160.00 本次优选采用清单价+总价双限价原则，即竞选人无论清单报价超限价或竞选总价超限价，采购人均作无效竞选 处理 十一、优选文件的获取 由竞选人在重庆高速集团物资采购平台：http://113.250.85.222:8099/merchants/login?redirect=%2F下载优选文件电子 版。 十二、竞选截止时间和地点 （一）电子版竞选文件递交 竞选人须在竞选截止时间 2026年8月27日9时30分前，通过重庆高速集团物资采购平台（网 址：http://113.250.85.222:8099/merchants/login?redirect=%2F）将签章完善的竞选文件扫描件（多页合并成套PDF格 式）进行上传；为方便工作人员统计报价，竞选人须同时上传一份与《竞选报价书》数据一致的Excel电子版报 价清单；竞选人必须在投标页面“投标报价”处填写竞选不含税报价；未上传竞选文件（多页合并成套 PDF 格 式），平台自动拒收，开选现场也不接收。 （二）纸质版竞选文件递交 竞选人须在竞选截止时间2026年8月27日9时30分前将签章完善且装订成册的 贰 份纸质版竞选文件通过现场递 交或邮寄方式提交采购人指定地点（以收到时间为准），逾期拒收。 现场递交地址：重庆市两江新区宝圣东路291号重庆高速巨能建设集团有限公司老办公楼202会议室。 邮寄地址：重庆市两江新区宝圣东路291号重庆高速巨能建设集团有限公司202室； 收件人：王女士，联系电话：15730141615 网 竞选文件须集中装入一个密封袋内，封口处粘贴封条，并在封条的封口处加盖竞选人单位公章（鲜章），“竞 选文件”封袋上写明如下内容： 优选项目名称：重庆高速巨能建设集团有限公司城开高速城开隧道泄水洞施工项目第一批物资（排水材料）采 务 购项目 竞选人名称： 公司 在2026年8月27日9时30分前不得开启（需加盖竞选人单位商公章鲜章）。 （三）竞选人如电子版竞选文件或纸质版竞选文件（缺一项）未提交，则视为未参与竞选。 十三、开选时间及地点 道 本次优选将于2026年8月27日9时30分在重庆市两江新区宝圣东路291号重庆高速巨能建设集团有限公司老办公 楼202会议室开选。 管 十四、竞选保证金：无 重庆高速巨能建设集团有限公司中环分公司 2026年8月19日 国 信息来源:https://www.chinapipe.net/project/d3078467.html cqdingjiu 2026.08.24 12:31:36 中</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>泵站：1座</t>
+          <t>排水材料</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>重庆, 高标准农田建设工程, 投资金额, 产品种类</t>
+          <t>重庆, 管材, 招标, 排水材料</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>永川区农村供水管网巩固提升改造工程(东部片区)答疑补遗文件</t>
+          <t>国网重庆电力渝西片区2026年原集体企业和各级产业单位第十四次物资区域联合授权公开谈判采购采购公告</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -932,7 +920,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -951,34 +939,30 @@
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>永川区</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>农村供水管网巩固提升改造工程</t>
+          <t>采购项目名称为物资，具体采购内容包括第十四次物资区域联合授权公开谈判采购。</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>供水管网</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>永川区农村供水管网巩固提升改造工程(东部片区)答疑补遗文件 永川区农村供水管网巩固提升改造工程（东部片区） 补遗文件（01） 各潜在投标人： 现将“永川区农村供水管网巩固提升改造工程（东部片区）”招标文件补遗通知如下，本次发布的补遗文件中 的所有内容与招标文件具有同等法律效力，如与招标文件、答疑补遗文件（01）网不一致时，以本补遗文件为准。 请各潜在投标人自行下载本补遗文件，不管下载与否，都视为全部知晓其全部内容。 一、本招标项目招标文件第二章投标人须知前附表第1.4.1项第1条第（3）款中“具备建设行政主管部门颁发的有 效的安全生产许可证，企业主要负责人、拟派项目经理具备相应的由建设行政主管部门颁发的有效的安全生产 务 考核合格证书。”修改为： “（3）具备建设行政主管部门颁发的有效的安全生产许可证，企业主要负责人、拟派项目经理具备相应的由水 行政主管部门颁发的有效的安全生产考核合格证书”。 商 二、本招标项目招标文件第二章投标人须知前附表第1.4.1项中第3条“业绩要求”修改为： “投标人自2023年1月1日起至投标截止日止（以合同工程完工日期或工程竣工日期为准），完成过1个单项合同 输配水管网长度不少于100km的水利工程施工道业绩。 提供：供该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴 定书）的证明材料。若提供的上述业绩证明材料不能体现上述业绩指标的，应补充提供业主证明。 管 注：（1）当上述业绩证明材料中针对同一指标存在不一致时，以合同工程完工证书（或合同工程验收鉴定书或 工程竣工证书副本或竣工验收鉴定书）的证明材料为准。（2）投标人提供的业绩为联合体业绩的，其在该业绩 中的工作分工应与本项目承担的工作一致。” 三、本招标项目招标文国件第二章投标人须知前附表第1.4.1项中第5条中的“5.3项目经理业绩要求”修改为： “投标人拟派的项目经理自2023年1月1日起至投标截止日止（以合同工程完工日期或工程竣工日期为准），完成 过1个单项合同输配水管网长度不少于100km的水利工程施工业绩，并在该业绩中担任项目经理。 中 提供：供该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴 定书）的证明材料。若提供的上述业绩证明材料不能体现上述业绩指标的，应补充提供业主证明。 注：（1）当上述业绩证明材料中针对同一指标存在不一致时，以合同工程完工证书（或合同工程验收鉴定书或 工程竣工证书副本或竣工验收鉴定书）的证明材料为准。（2）投标人提供的业绩为联合体业绩的，其在该业绩 中的工作分工应与本项目承担的工作一致。” 四、本招标项目的投标文件递交的截止时间（投标截止时间）调整为2026年9月4日9时30分（北京时间），开标 时间及投标保证金递交截止时间相应顺延。 招标人：重庆市永川区惠永水务有限公司 招标代理机构：重庆永川政鑫综合能源有限公司 2026年8月20日 信息来源:https://www.chinapipe.net/project/d3076870.html cqdingjiu 2026.08.21 10:06:46</t>
+          <t>国网重庆电力渝西片区2026年原集体企业和各级产业单位第十四次物资区域联合授权公开谈判采购采购公告 采购项目编 采购项目状态 正在采购 CY2026S5W4E 号 国网重庆电力渝西片区2026年原集体企业 采购项目名称 和各级产业单位第十四次物资区域联合授 采购类型 物资 权公开谈判采购 采购文件获取截止时 开启应答文 2026-08-25 09:00:00 2026-09-01 09:00:00 间 件时间 网 供应商提出澄清问题 截止时间 国网重庆市电力公司永川供电 开启应答文件地点 ETP 采购人 务分公司 招标代理机 重庆市渝北区青枫北路20号凤 招标代理机构 重庆展泽工程咨询有限公司 构地址 凰D座9楼部分办公用 招标代理机构邮编 401120 商联系人 供应商服务大厅 联系电话 400-1047-177 传真 电子邮箱 JZD_WZ@163.com 信息来源:https://www.chinapipe.net/project/d3078339.html 道 cqdingjiu 2026.08.24 12:31:36 管 国 中</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>输配水管网：100km</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -986,14 +970,14 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>重庆, 农村供水管网, 巩固提升改造, 东部片区, 管材招标</t>
+          <t>重庆, 物资, 采购</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>长寿区海棠、石堰、龙河片区污水管网建设项目(二期)招标公告</t>
+          <t>国网重庆电力主城一片区2026年原集体企业和各级产业单位第十四次物资区域联合授权公开谈判采购采购公告</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1003,7 +987,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1022,49 +1006,45 @@
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>长寿区</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>新改建及修复DN300mm-DN1200mm排水管道20.187公里，其中新改建管道15.21公里，修复管道4.977公里，Ⅲ、Ⅳ级结构性及功能性缺陷修复453处。</t>
+          <t>采购项目名称为'国网重庆电力主城一片区2026年原集体企业和各级产业单位第十四次物资区域联合授权公开谈判采购'，采购类型为物资。</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>项目业主为重庆市长寿区住房和城乡建设服务中心，建设资金来自财政资金，项目出资比例为100%。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>DN300mm-DN1200mm排水管道</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>长寿区海棠、石堰、龙河片区污水管网建设项目(二期)招标公告 长寿区海棠、石堰、龙河片区污水管网建设项目（二期）招标公告 1.招标条件 本招标项目长寿区海棠、石堰、龙河片区污水管网建设项目已由重庆市长寿区发展和改革委员会以长改发投 〔2024〕169号文批准建设，项目业主为重庆市长寿区住房和城乡建设服务中心，建设资金来自财政资金，项目 出资比例为100%，招标人为重庆长寿乡村建设集团有限公司。项目已具备招标条件，现对该项目的施工进行公 开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：长寿区海棠镇、龙河镇、新市街道、云台镇。 2.2 项目概况与建设规模：新改建及修复DN300mm-DN1200mm排水管道20.187公里，其中新改建管道15.21公里， 务 修复管道4.977公里，Ⅲ、Ⅳ级结构性及功能性缺陷修复453处。 2.3 本次招标项目合同估算金额：4139.45万元。 2.4 招标范围：详见招标人提供的本工程的施工图图纸、图商说、设计变更以及工程量清单所明确的全部工程内容。 2.5 工期要求：270日历天。 缺陷责任期要求：24个月。 道 3.政府采购工程 3.投标人资格要求 管 3.1 本次招标要求投标人须具备以下条件： 3.1.1 本次招标要求投标人具备的资质条件：建设行政主管部门颁发的有效的市政公用工程施工总承包三级及以 上资质； 国 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 中 3.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需 在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网 导航栏“主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登 记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公 告发布至2026-08-25 15:00:00前。 4.3招标人应于2026-08-28 18:00:00前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交 易网（长寿区）（https://www.cqggzy.com/changshouweb/）发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-14 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn）和重庆市公共资源交易网（长寿区） （https://www.cqggzy.com/changshouweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源 交易监督网上发布。] 7.联系方式 招 标 人: 重庆长寿乡村建设集团有限公司 代理机构: 中新创达咨询有限公司 地 址: 重庆市长寿区桃源大道3号一号商务楼5-6楼 地 址: 邮 编: 邮 编: 项目负责人: 刘老师 项目负责人: 钟亮 网 电 话: 023-40233279 电 话: 19132912275 传 真: 传 真: 电子邮箱: 电子邮箱务: 开户银行: 开户银行: 账 号: 账 号: 商 监督部门: 重庆市长寿区发展和改革委员会 电 话: 023-40245080 2026年08月20日 长寿区海棠、石堰、龙河片区污水管网建设道项目（二期） 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公 中国农业银行股份有限公司重庆自由贸易 312601010400083780000033561 司 管试验区分行 重庆联合产权交易所集团股份有限公 中国建设银行股份有限公司重庆渝中支行 6232813760003317764 司 重庆联合产权交易所集国团股份有限公 重庆银行股份有限公司七星岗支行 15010202900420146632392 司 信息来源:https://www.chinapipe.net/project/d3076848.html cqdingjiu 20中26.08.21 10:06:46</t>
+          <t>国网重庆电力主城一片区2026年原集体企业和各级产业单位第十四次物资区域联合授权公开谈判采购采购公告 采购项目编 采购项目状态 正在采购 CY2026S1W4E 号 国网重庆电力主城一片区2026年原集体企 采购项目名称 业和各级产业单位第十四次物资区域联合 采购类型 物资 授权公开谈判采购 采购文件获取截止时 开启应答文 2026-08-25 09:00:00 2026-09-01 09:00:00 间 件时间 网 供应商提出澄清问题 截止时间 国网重庆市电力公司市区供电 开启应答文件地点 详见采购公告 采购人 务分公司 招标代理机 重庆市渝北区青枫北路20号凤 招标代理机构 重庆展泽工程咨询有限公司 构地址 凰D座9楼部分办公用 招标代理机构邮编 401120 商联系人 供应商服务大厅 联系电话 400-1047-177 传真 电子邮箱 JZD_WZ@163.com 信息来源:https://www.chinapipe.net/project/d3078338.html 道 cqdingjiu 2026.08.24 12:31:36 管 国 中</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>排水管道：20.187公里；管道：15.21公里；管道：4.977公里</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>重庆, 物资, 采购公告</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部刺丝滚笼、塑钢模板、泄水管询价采购公告</t>
+          <t>忠县忠州和白公街道特色农业节水灌溉保障工程勘察设计招标计划表</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1074,7 +1054,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1095,47 +1075,47 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>万州区</t>
+          <t>忠县</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>渝万高铁站前1标位于重庆市万州区和忠县境内,起止里程DK14+233.2~D1K47+550.4，正线长度33.01km，中标造价31.73亿元。管区内共有隧道8座/22.36km，斜井2座/1.76km;桥梁15座/8.97km，其中，预制及架设梁301孔，(40+64+40)m和(45+100+45)m连续梁各1联;区间路基22段/1.68km，土石方约67万方，负责DK0+000~DK57+136段小型构件预制。</t>
+          <t>本工程为9720亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站21座，整治山坪塘44口，建设主要建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>中标造价31.73亿元</t>
+          <t>合同预估金额为137.18万元</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>刺丝滚笼,塑钢模板,泄水管</t>
+          <t>节水灌溉设备、智能监控系统、气象监测设备、虫情监测设备、土壤墒情监测设备</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部刺丝滚笼、塑钢模板、泄水管询价采购公告 中铁十一局集团有限公司重庆至万州高铁站前 1标项目经理部 刺丝滚笼、塑钢模板、泄水管询价采购公告 询价编号： ZT1105-XJ-2026-590 尊敬的 各潜 在供应商 : 网 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与 中铁十一局集团有限公司重庆至万州高铁站 前 1标项目经理部 ZT1105-XJ-2026-590， 刺丝滚笼、塑钢模板、泄水管 的报价。 一、 项目概况 务 渝万高铁站前 1标位于重庆市万州区和忠县境内,起止里程DK14+233.2~ D1K47+550.4，正线长度 33.01km，中标造 价 31.73 亿元。管区内共有隧道8座/22.36km，斜井2座/1.76km;桥梁15座/8.97km，其中，预制及架设梁 301 孔，(40+64+40)m和(45+100+45)m连续梁各1联;区间路基22段/1.68km，土石方约67万方，负 责DK0+000~DK57+136段小型构件预制。合同工期54.7月商，开工日期为2022年11月01日，竣工日期为2027 年04 月30日。 二、 询价内容 道 本次 计划对刺丝滚笼、塑钢模板、泄水管 进行询价，询价内容如下： 询价物资一览表 管 计 序 物资 量 包件号 规格型号 数量 备注 号 名称 单 位 国 刺丝 1 GL-01 2.5mm 6m0.5m 米 6500 半径 ≥225mm，包括刀片刺绳、挂丝、连接卡、支架 滚笼 防护 中 栅栏 2 GL-01 用立 50X30X765X2.5mm 套 500 含抱箍、螺栓等配件 柱支 架 平 塑钢 3 MB-01 350X300mm 方 19.2 400*400,1个挡水沿，配固定手柄 模板 米 平 塑钢 4 MB-01 350X300mm 方 19.2 400*400,2个挡水沿，配固定手柄 模板 米 平 塑钢 5 MB-01 300X300mm 方 75.6 2个挡水沿，配固定手柄 模板 米 平 塑钢 6 MB-01 300X300mm 方 75.6 1个挡水沿，配固定手柄 模板 米 7 SSG-01 管篦 PVC250X200x10mm 个 220 材质硬聚氯乙烯 PVC，详见附图 PVC 8 SSG-01 泄水 135X38mm 块 220 材质硬聚氯乙烯 PVC，详见附图 管盖 U型 9 SSG-01 125mm 个 900 详见附图 管卡 UPV 材质硬聚氯乙烯 PVC，两端接头采用阴阳螺纹连接详见 10 SSG-01 C排 125X8mm螺纹 米 2870 附图 水管 UPV 11 SSG-01 C弯 DN125X8mm90° 个 240 材质硬聚氯乙烯 PVC，详见附图 管 UPV 网 125X125X110mm弹性密 12 SSG-01 C三 个 120 材质硬聚氯乙烯 PVC，详见附图 封圈异径斜三通 通 无压 埋地 务 排污 排水 用硬 13 SSG-01 DN125 个 150 材质硬聚氯乙烯 PVC，详见附图 聚氯 商 乙烯 管 T 型接 头 道 合 计 管 说明： 1. 表中数量为计划数量，实际 采购 过程中可能有所调整，最终结算按照实际 采购 数量结算。 2.收货地点：中铁十一局集团有限公司重庆至万州高铁站前1标项目经理部 三、 技术质量 及报价国 要求 1. 此次 询价物资 各项技术性能要 符合 甲方 的要求，质量满足甲方项目部正常使用的要求，保证 产品 的质量合 格。 具体要求或图纸见询价文件技术规格书。 。 中 2 .报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、 结算及付款方式 每个月 15 日为双方价款结算日期（即上月 16 日至当月 15 日内），结算前双方要在对帐确认单上签字认可，乙 方按双方确认的金额开具增值税专用发票，并自发票开具之日起 7日内传递给甲方。甲乙双方在增值税专用发票 传递过程中必须留取相应的交接签证手续。自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发 票认证完成之日起第6个月，支付至本次结算金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内， 累计支付总额不超结算总金额的75%，剩余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理 末次结算后第二年，支付金额应大于等于尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总 额的15%；办理末次结算后第四年，全部付清）。 五、 报价 人资格要求 1.营业范围要求：在中华人民共和国境内依法注册，具有询价物资生产或供应经验的生产商或代理商，并且具有 合法有效的营业执照。 2.生产能力要求： 生产商须具备 询价 物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定 。 代理商需出具制造厂出具签字盖章的授权函。 3.财务能力要求：报价人为增值税一般纳税人或小规模纳税人，有依法纳税的良好记录。 4.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8月至今） 国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；每种物资全指标技术参数性能满足 国家和行业最新标准的各项规定。 5.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年8月至今）企业或企业法定代表人有人民法院生效判决、裁定 认定的行贿犯罪记录的。④ 对纳入国家铁路局“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接受 通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合作 方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 网 6.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 务 ★7 .下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 六、 报价人需要提供的资料 1. 营业执照复印件、 法人身份证复印件、 开户许可证、商授权委托书 、 报价表 和报价人资格要求中所需的证明资 料， 所有资料需加盖公司鲜章。 2. 产品质量检测报告等质量证明文件。 道 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、 询价 报名截止 时间 管 有意参加本次询价采购的报价人 须在铁建云链平台 （ https:// www.crccep. cn） 完成供应商注册，并 于 202 6 年 8 月 20 日 9时 00 分 至 202 6 年 8 月 24 日 9时 00 分在网上 完成报名工作。 八、 询价 截止 时间 国 凡有意参加本次询价采购的报价人，请于 202 6 年 8 月 24 日 14 时 00分 前 提交报价。截止时间前未完成 报价 文 件传输的，视为放弃 报价 。 供应商报价必须严格按照《 报价表 》格式进行报价。 中 九、 联系方式 采购 组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村 71号 联系人：胡先生 联系电话： 13983336494 （提供平台服务支持） 采购人名称：中铁十一局集团有限公司重庆至万州高铁站前 1标项目经理部 地址： 重庆市万州区双河口街道檬兴路万州现代综合物流中心信息交易大厅（中铁十一局） 联系人： 唐大伟 联系电话： 18323391938（提供采购服务支持、保证金退还） 中铁十一局集团有限公司物资设备集中采购管理中心 第五分中心 2026 年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3076805.html cqdingjiu 2026.08.21 10:06:47 网 务 商 道 管 国 中</t>
+          <t>忠县忠州和白公街道特色农业节水灌溉保障工程勘察设计招标计划表 重庆市工程建设项目招标计划表 项目名称 忠县忠州和白公街道特色农业节水灌溉保障工程勘察设计 招标法人 或招标人 忠县水库运行管理中心 网 名称（盖 章） 项目批准 文件及文 忠发改审批〔2026〕794号 务 号 本工程为9720亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站21座，整治山坪塘44口，建设 主要建设 水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤 内容 墒情系统。 商 招标项目 招标方 招标文件计 拟交易 合同预估 序号 招标内容 备注 名称 式 划发布时间 场所 金额(万元) 本工程为9720道亩柑橘 等特色农业提供抗旱 忠县忠州 供水，新建节水灌溉 本计划表所 和白公街 提灌站21座，整治山 忠县公 列招标项目 招标项目 道特色农 坪塘44口，建设水肥 公开招 共资源 信息均为暂 管 1 业节水灌 2026-08 137.18 一体化系统，完善田 标 综合交 定，最终以 溉保障工 间引水渠堰、排水沟 易中心 实际招标时 程勘察设 及管网，分片区安装 的信息为准 计 智能监控、气象、虫 国 情、土壤墒情系统。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3078219.html 中 cqdingjiu 2026.08.24 12:31:36</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>抗旱供水；新建节水灌溉提灌站21座；整治山坪塘44口；建设水肥一体化系统；完善田间引水渠堰、排水沟及管网；安装智能监控、气象、虫情、土壤墒情系统</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>重庆, 万州, 高铁站前, 刺丝滚笼, 塑钢模板, 泄水管, 询价采购</t>
+          <t>重庆, 节水灌溉, 柑橘, 抗旱供水, 提灌站, 山坪塘, 水肥一体化, 智能监控, 气象, 虫情, 土壤墒情</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告</t>
+          <t>忠县新生街道特色农业节水灌溉保障工程勘察设计招标计划表</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1166,47 +1146,47 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>垫江县</t>
+          <t>忠县</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目，主要内容包括河堤护岸岸线整治2100m；产业路扩宽及油化改造775.3m；新建污水管网450m，化粪池2座；产业基地水肥一体化改造45亩等。</t>
+          <t>本工程为9720亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站21座，整治山坪塘44口，建设主要建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>项目总投资金额为642.89万元，本次招标项目合同估算金额约为5014864.52元。</t>
+          <t>合同预估金额为137.18万元</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>水利水电工程施工</t>
+          <t>节水灌溉设备、水肥一体化系统、智能监控系统、气象监测设备、虫情监测设备、土壤墒情监测设备</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目招标公告 1.招标条件 本招标项目 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目 已由 垫江县发展和 改革委员会 以 垫江发改委发〔2026〕20号 文批准建设，项目业主为 垫江县太平镇人民政府，建设资金来 自 大中型后扶资金及自筹资金 ，项目出资比例为 100% ，招标人为垫江县太平镇人民政府。项目已具备招 标条件，现对本项目施工进行公开招标，评标办法采用经评审的最低投标价法。网 务 2.项目概况与招标范围 商 2.1 建设地点：垫江县太平镇桂花村 道 2.2 项目概况与建设规模：主要为河堤护岸岸线整治2100m；产业路扩宽及油化改造775.3m；新建污水管网450m， 化粪池2座；产业基地水肥一体化改造45亩等。 管 2.3 本项目工程总投资金额：642.89万元 国 本次招标项目合同估算金额：约5014864.52元 中 2.4 招标范围：本工程施工图纸所含全部的施工内容，具体以招标人发布的工程量清单为准。 2.5 工期要求：工期为360日历天 ，缺陷责任期为24个月。 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：□是 否，因专门面向中小企业预留无法确保充分供应、充分竞争，根据 《政府采购促进中小企业发展管理办法》第六条第(三)“按本办法规定预留采购份额无法确保充分供应、充分竞 争，或者存在可能影响政府采购目标实现的情形”的规定，本项目不专门面向中小企业预留。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 网 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的水利水电工程施工总承包三级 务 及以上资质。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相商应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 道 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 管 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com国/dianjiangweb/)、重庆市公共资源交易监督网下载招标文件、工程量清单、电子图纸等资 料。参与投标的投标人需在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共 资源交易监督网完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交易监督网导航栏“主体信息”页面中“市场主体信息 登记”、“中CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流 程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交易监督 网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-24 17:00:00前。 5.3招标人应于2026-08-28 17:00:00前在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重 庆市公共资源交易监督网发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-28 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网(垫江县) (https://www.cqggzy.com/dianjiangweb/)、重庆市公共资源交 易监督网发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 垫江县太平镇人民政府 代理机构: 重庆皓辰建设工程咨询有限公司 重庆市渝北区金开大道1228号大雅金开国际1 地 址: 重庆市垫江县太平镇牡丹路191号 地 址: 栋9-2 邮 编: 邮 编: 项目负责人: 余老师 项目负责人: 雷雨得 电 话: 13996889839 电 话: 023-86018770 18580880860 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 垫江县发展和改革委员会 电 话: 023-74517161 网 2026年08月19日 垫江县2026年度大中型水库移民后期扶持项目—太平镇美丽移民村建设项目 务 户名 开户行 投标保证金账号 垫江县公共资源交易中心 中国农业银行重庆垫江支行 316301010400077950000005966 垫江县公共资源交易中心 中国银行重庆垫江支行 111616885778VA00139 商 垫江县公共资源交易中心 重庆农村商业银行垫江支行 2501010120010009065000128 垫江县公共资源交易中心 工商银行重庆垫江支行营业部 9558853100016843371 垫江县公共资源交易中心 重庆银行垫江支行 820101040000584-101195 道 附件：垫江县2026年度大中型水库移民后期扶持项目-.zip https://www.cqggzy.com/trade/014001/dac54522-3264-4eac-ae47-f434567ce374?categoryNum=014001001007 信息来源:https://www.chinapipe.net管/project/d3076788.html cqdingjiu 2026.08.21 10:06:47 国 中</t>
+          <t>忠县新生街道特色农业节水灌溉保障工程勘察设计招标计划表 重庆市工程建设项目招标计划表 项目名称 忠县新生街道特色农业节水灌溉保障工程勘察设计 招标法人 或招标人 忠县水库运行管理中心 网 名称（盖 章） 项目批准 文件及文 忠发改审批〔2026〕794号 务 号 本工程为9720亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站21座，整治山坪塘44口，建设 主要建设 水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤 内容 墒情系统。 商 招标项目 招标方 招标文件计 拟交易 合同预估 序号 招标内容 备注 名称 式 划发布时间 场所 金额(万元) 本工程为9720亩道柑橘等 特色农业提供抗旱供 忠县新生 水，新建节水灌溉提 本计划表所 街道特色 灌站21座，整治山坪 忠县公 列招标项目 招标项目 农业节水 塘44口，建设水肥一 公开招 共资源 信息均为暂 管 1 2026-08 137.18 灌溉保障 体化系统，完善田间 标 综合交 定，最终以 工程勘察 引水渠堰、排水沟及 易中心 实际招标时 设计 管网，分片区安装智 的信息为准 能监控、气象、虫情、 国 土壤墒情系统。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3078218.html 中 cqdingjiu 2026.08.24 12:31:37</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>污水管网：450m</t>
+          <t>抗旱供水；新建节水灌溉提灌站21座；整治山坪塘44口；建设水肥一体化系统；完善田间引水渠堰、排水沟及管网；分片区安装智能监控、气象、虫情、土壤墒情系统</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 水利, 移民, 后期扶持</t>
+          <t>重庆, 节水灌溉, 柑橘, 抗旱供水, 提灌站, 山坪塘, 水肥一体化, 智能监控</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>万州区新田等6个镇乡农村饮水质量提升项目招标计划表</t>
+          <t>忠县洋渡、任家镇等乡镇特色农业节水灌溉保障工程勘察设计招标计划表</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1216,7 +1196,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1237,32 +1217,32 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>万州区</t>
+          <t>忠县</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>新建水厂1座（新建2000m³茨竹水厂），输、配水管道改造与新建，管道总长约226.127km，管径DN20~DN250，管材为涂塑钢管。</t>
+          <t>本工程为1.7万亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站18座，整治山坪塘28口，建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>合同预估金额：5000万元</t>
+          <t>合同预估金额为138.71万元</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>涂塑钢管</t>
+          <t>节水灌溉设备、智能监控系统、气象监测设备、虫情监测设备、土壤墒情监测设备</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>万州区新田等6个镇乡农村饮水质量提升项目招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区新田等6个镇乡农村饮水质量提升项目 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 及文号 务 新建水厂1座（新建2000m3茨竹水厂），输、配水管道改造与新建，管道总长约226.127km，管 主要建设内容 径DN20~DN250，管材为涂塑钢管。 招标项目名 招标方 招标文件计划 拟交易场 合同预估金 序号 招标内容 备注 称 式 发布时间 所 额(万元) 商 万州区新田 万州区新田 重庆市万 招标项目 等6个镇乡农 等6个镇乡农 公开招 州区公共 1 村饮水质量提 2026-08 5000.00 村饮水质量 标 资源交易 升项目道施工总 提升项目 中心 承包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076721.html 管 cqdingjiu 2026.08.21 10:06:48 国 中</t>
+          <t>忠县洋渡、任家镇等乡镇特色农业节水灌溉保障工程勘察设计招标计划表 重庆市工程建设项目招标计划表 项目名称 忠县洋渡、任家镇等乡镇特色农业节水灌溉保障工程勘察设计 招标法人 或招标人 忠县水库运行管理中心 网 名称（盖 章） 项目批准 文件及文 忠发改审批[2026]328号 务 号 本工程为1.7万亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站18座，整治山坪塘28口，建 主要建设 设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土 内容 壤墒情系统。 商 招标项目名 招标 招标文件计 拟交易 合同预估 序号 招标内容 备注 称 方式 划发布时间 场所 金额(万元) 本工程为1.7道万亩柑橘 等特色农业提供抗旱 忠县洋渡、 供水，新建节水灌溉 本计划表所 任家镇等乡 提灌站18座，整治山 忠县公 列招标项目 招标项目 镇特色农业 坪塘28口，建设水肥 公开 共资源 信息均为暂 管 1 2026-08 138.71 节水灌溉保 一体化系统，完善田 招标 综合交 定，最终以 障工程勘察 间引水渠堰、排水沟 易中心 实际招标时 设计 及管网，分片区安装 的信息为准 智能监控、气象、虫 国 情、土壤墒情系统。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3078217.html 中 cqdingjiu 2026.08.24 12:31:37</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>管道：226.127km</t>
+          <t>排水钢管 Φ200*6m：3000米</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1270,14 +1250,14 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机</t>
+          <t>重庆, 节水灌溉, 柑橘, 抗旱供水, 提灌站, 山坪塘, 水肥一体化, 智能监控, 气象, 虫情, 土壤墒情</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>万州区大周等4个镇乡街道农村饮水质量提升项目招标计划表</t>
+          <t>荣昌区2026年古昌镇高标准农田建设项目招标公告</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1308,47 +1288,47 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>万州区</t>
+          <t>荣昌区</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>新建50m³蓄水池4口、取水池2座；新建50m³/d-100m³/d水厂2座；改造100m³/d-300m³/d水厂5座；铺设DN25-DN250涂塑钢管约86km；新建提水泵站8座；配套阀井、电磁流量计等有关设施。</t>
+          <t>新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007亩。主要内容包括水田整治、缓坡整治、梯台整治、恢复地类整治、耕地复耕整治、农机进出通道修建、提灌站修建、输水管道铺设、排水沟改建、田间道路改建等。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>合同预估金额：3000万元</t>
+          <t>项目总投资金额1592.15万元，本次招标项目合同估算金额1420.76万元，全部来自财政资金。</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>DN25-DN250涂塑钢管</t>
+          <t>高标准农田建设相关材料及设备，如PE输水管道、排水沟、田间道路等。</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>万州区大周等4个镇乡街道农村饮水质量提升项目招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区大周等4个镇乡街道农村饮水质量提升项目 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 及文号 务 新建50m3蓄水池4口、取水池2座；新建50m3/d-100m3/d水厂2座；改造100m3/d-300m3/d水厂5 主要建设内容 座；铺设DN25-DN250涂塑钢管约86km；新建提水泵站8座；配套阀井、电磁流量计等有关设 施。 招标项目名 招标方 招标文件计划 拟交易场 合同预估金 序号 招标内容 商 备注 称 式 发布时间 所 额(万元) 万州区大周 万州区大周 重庆市万 招标项目 等4个镇乡街 等4个镇乡街 公开招 州区公共 1 道农村饮水 道农村饮道水质 2026-08 3000.00 标 资源交易 质量提升项 量提升项目施 中心 目 工总承包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3076720.html cqdingjiu 2026.08.21 10:06:49 国 中</t>
+          <t>荣昌区2026年古昌镇高标准农田建设项目招标公告 荣昌区2026年古昌镇高标准农田建设项目招标公告 1.招标条件 1. 招标条件 本招标项目荣昌区2026年古昌镇高标准农田建设项目已由重庆市荣昌区农业农村委员会以荣农发〔2026〕64号批 准建设，项目业主为重庆市荣昌区农田建设中心，建设资金来自财政资金，项目出资比例为100%，招标人为重 庆市荣昌区农田建设中心。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用经评审的最 网 低投标价法。 2.项目概况与招标范围 2. 项目概况与招标范围 务 2.1 建设地点： 古昌镇百合堂村、玉带村 2.2 项目概况与建设规模：新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007 商 亩。 2.3 本项目工程总投资金额：1592.15万元 本次招标项目合同估算金额：1420.76万元 道 2.4 招标范围：水田整治2622.50亩，缓坡整治21.95亩，梯台整治186.23亩，恢复地类整治44.26亩，耕地复耕整 治283.09亩，农机进出通道8338m；新修提灌站1座，改建提灌站2座，新修Φ250PE输水管道2732m、Φ200PE输水 管道267m、Φ160PE输水管道20928m、Φ110PE输水管道7412m，改建沟带路(1.8×0.8×1.0m)799m，维 管 修2.0×1.5m排水沟1395m、0.8×1.0m排水沟784m；改建3.0m宽田间道6573m、4.0m宽田间道728m。包括所提供的 施工设计图所示范围内的所有内容，具体以招标人提供的图纸、工程量清单、答疑资料、澄清资料、其他补遗 资料等相关内容为准。若施工图与工程量清单不一致时，以工程量清单为准。 2.5 工期要求：工期为1国80日历天 ，缺陷责任期为24个月。 2.6 标段划分（如有）： / 2.7 其他： 中/ 3.政府采购工程 3. 政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式：本项目整体面向中小企业。 4.投标人资格要求 4. 投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包三级及以 上资质或市政公用工程施工总承包三级及以上资质或水利水电工程施工总承包三级及以上资质 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（荣昌区）下载招标文件、 工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网（荣昌区）完成市场主体信息登 记以及CA数字证书办理，办理方式请参见重庆市公共资源交易网（荣昌区）导航栏“主体信息”页面中“市场 主体信息登记”、“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法 完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网（荣昌区）本项目招标公告网页下方“我网要提问”栏提出疑问，提问时间 从本公告发布至2026-08-26 17:30:00前。 5.3招标人应于2026-08-28 18:00:00前在重庆市公共资源交易网（荣昌区）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-16 09:30，投标人应当在投标截止时间前，通过互 务 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 商 本次招标公告同时在重庆市公共资源交易网（荣昌区）、重庆市公共资源交易监督网发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆市荣昌区农田建设中心 代理机构: 重庆富毅项目管理有限公司 道 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 李老师 项目负责人: 陈航 管 电 话: 023-85265043 电 话: 16623666557 传 真: 传 真: 电子邮箱: 电子邮箱: 国 开户银行: 开户银行: 账 号: 账 号: 监督部门:中重庆市荣昌区发展和改革委员会 电 话: 023-61471361 2026年08月21日 信息来源:https://www.chinapipe.net/project/d3078214.html cqdingjiu 2026.08.24 12:31:37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>涂塑钢管：86km；提水泵站：8座</t>
+          <t>排水钢管 Φ200*6m：3000米</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>重庆, 农村饮水质量提升项目, 管材招标, 合同预估金额</t>
+          <t>高标准农田建设, PE输水管道, 排水沟, 田间道路</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>二航科工新燕尾山项目纤维编绕拉挤电缆保护套管采购询价通知公告</t>
+          <t>重庆中法供水2026年金属补偿器及柔性橡胶接头采购项目(第三次)比选公告</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1358,7 +1338,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1380,42 +1360,42 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本项目西起太阳岗立交(不含太阳岗立交)，往东穿越铜锣山，止于内环南泉立交(不含南泉立交)。项目全长约6.8km，其中二标段长约3.62公里，采用主干路标准，设计车速60km/h，标准路幅为双向6车道，主要工程包括长隧道1座(新燕尾山隧道，长2542m)，简易立交1座(花溪立交),互通式立交2座(南温泉立交、苦竹坝立交)。</t>
+          <t>重庆中法供水2026年金属补偿器及柔性橡胶接头采购项目(第三次)比选公告</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>采购项目资金为企业自筹。</t>
+          <t>项目资金来自企业自筹，出资比例为100%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>纤维编绕拉挤电缆保护套管(BWFRP100/2.0，79158米)</t>
+          <t>柔性橡胶接头,金属补偿器</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>二航科工新燕尾山项目纤维编绕拉挤电缆保护套管采购询价通知公告 中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程项目询比采购 公告 中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程项目已具备采 购条件，现公开邀请供应商参加询比采购活动。 网 1. 采购项目简介 1.1 采购项目名称：中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机 电工程项目。 务 1.2采购方案编号：FA00000674478。 1.3 采购人：中交二航局科工（武汉）有限公司西南片区新燕尾山隧道工程施工二标段项目道路照明机电工程 项目经理部。 商 1.4 采购代理机构：中交二航局科工（武汉）有限公司。 1.5 采购项目资金：企业自筹。 道 1.6 采购项目概况：新燕尾山隧道工程位于重庆市内环吉庆隧道北侧，四横线分流道鹿角隧道南侧，西接白居 寺大桥，东接内环快速路，并向东延伸接渝黔复线高速，其所在的道路系统呈东西布置，为主城区南部片区重 要干道。本项目西起太阳岗立交(不含太阳岗立交)，往东穿越铜锣山，止于内环南泉立交(不含南泉立交)。项目 管 全长约6.8km，其中二标段长约3.62公里，采用主干路标准，设计车速60km/h，标准路幅为双向6车道，主要工程 包括长隧道1座(新燕尾山隧道，长2542m)，简易立交1座(花溪立交),互通式立交2座(南温泉立交、苦竹坝立交)。 2.采购范围及相关要求 国 2.1 采购范围：纤维编绕拉挤电缆保护套管（BWFRP100/2.0，79158米）。 2.2 交货期：以甲方实际订单要求为准。 中 2.3 交货地点：重庆市巴南区新燕尾山项目甲方指定位置。 2.4 物资质量标准：满足国家法律法规、标准、规范、设计参数及技术规格书要求。 3.供应商资格要求 3.1 供应商应依法设立且满足如下要求： （1）资质要求：在中华人民共和国境内依法注册，具有独立法人资格、具有采购物资生产或供应经验的企业， 并且具有合法、有效的“三证合一”的营业执照,代理商需提供制造商授权委托书。 （2）财务要求：必须是经税务部门注册登记核准的一般纳税人，有依法纳税的良好记录，提供近三年的财务报 告。 （3）业绩要求：同类产品销售业绩不少于2个，并具备与本招标项目需求相适应的供货能力。 （4）信誉要求：本项目投标截止期前未被“信用中国”、“中国政府采购网”、中国交建物资采购管理信息系 统网站列入失信被执行人、违法案件当事人、违法失信行为记录名单。 （5）其他要求：提供运输方案及生产周期。 3.2 供应商不得存在下列情形之一： （1）处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； （2）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （3）已列入黑名单，且未解除限制期限； （4）其他： / 。 4.供应商报名 4.1有意参加询比采购活动的单位，请于2026年 8 月 20 日 11 时 00 分至2026 网 年 8 月 25 日 11 时 00 分（北京时间、下同），登录“中交招采网”（网 址：https://zjzcw.iccec.cn）进行报名并下载采购文件。 4.2 已在网并且已通过采购人层级供应商或已增加采购人为合作单位的供应商、上级供应商可直接参与询比采 务 购。在网平级单位供应商未增加采购人为合作单位需进行合作意向申请通过后参与询比采购。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择采购人，审核通过后方可参与询比 采购。 商 5. 供应商报价 5.1 报价结束（递交响应文件截止）时间：2026年 8 月 25 日 11 时 00 分。 道 5.2 供应商应在报价结束时间前，登录“中交招采网”进行线上报价并上传电子响应文件。逾期未完成上传的 电子响应文件，采购人将拒收。 5.3电子采购的供应商报价文件由线上电子报价表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 管 子报价表的数据为准。 6. 开标 6.1开标时间：与报价结国束时间相同。 6.2开标地点：本次采购在“中交招采网”平台线上开标，不举办现场开标，现场开标地点/。 7. 发布公告的媒介 中 本询比采购公告在中交招采网上发布。 8. 评审办法 本项目评审办法采用 经评审的最低价法 。 9. 合同主要条款 9.1 付款条件：无预付款，到货后办理结算，双方办理完结算手续、卖方提供符合合同要求的正式发票给买方 后60天，买方支付该批材料价值80%的货款，完工结算后支付至97%，剩余3%为质保金，质保期2年，两年后供 应方申请返还3%（无息）；银行转账、承兑、18个月供应链金融混合支付方式。 9.2履约保证金的递交： （1）□不要求递交 （2）要求递交 保证金金额：2万元 ； 保证金形式：银行转账、银行保函等电子保函；其他形式：无 。 10. 成交供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”（网址：https://zjzcw.iccec.cn）发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联 系4006765885中标服务费请按7咨询。 10.1收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： 网 （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； 务 （3）在1000万元（含）至3000万元之间的，每次收取1000元； （4）在3000万元（含）至1亿元之间的，每次收取3000元； （5）在1亿元（含）以上的，每次收取5000元。 商 10.2支付流程 （1）通知推送：中标结果发布后，系统自动道推送缴费通知（含应缴金额及支付链接）； （2）费用查询：供应商登录“中交招采网-服务管理”模块查看待支付费用； （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 管 （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网- 服务管理－发票下载”模块获取。 11.监督机构 国 监督机构名称：中交二航局科工（武汉）有限公司纪委监察部 举报电话：中027-82796466 举报邮箱：sneb_kggs@ccccltd.cn 12.其他 投标保证金采用银行转账形式的需转至中交二航局科工（武汉）有限公司账户（账 号：42001186108053006379-0006开户行：建行武汉长江支行，行号：105521000053），并备注二航科工燕尾山机 电照明项目纤维编绕管投标保证金。 13.联系方式 采购 人：中交二航局科工（武汉）有限公司 采购代理机构：中交二航局科工（武汉）有限公司 地 址：武汉市新洲区双柳街星谷大道158号地 址：武汉市新洲区双柳街星谷大道158号 邮政编码：430400 邮政编 码：430400 联系人：李鑫 联系人：毕明 月 电 话：18186145302 电 话：17853118573 电子邮件：18186145302@ccccltd.cn 电子邮件：bimingyue@ccccltd.cn 2026年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3076715.html cqdingjiu 2026.08.21 10:06:50 网 务 商 道 管 国 中</t>
+          <t>重庆中法供水2026年金属补偿器及柔性橡胶接头采购项目(第三次)比选公告 重庆中法供水2026年金属补偿器及柔性橡胶接头采购项目（第三次） 比选公告 1.比选条件 网 本比选项目重庆中法供水2026年金属补偿器及柔性橡胶接头采购项目（第三次），比选人为重庆中法供水有限公 司，比选项目资金来自企业自筹，出资比例为100%，项目已具备比选条件。现对本项目进行公开比选，诚邀有 兴趣的潜在投标人参与投标。 2.项目概况与比选范围 务 2.1 金属补偿器、柔性橡胶接头采购清单 商 序号 存货编码 材料名称 规格型号 单位 数量 最高单价限价（元） 1 10302603 柔性橡胶接头 DN40（PN10) 个 200 146 1 2 道 10302607 柔性橡胶接头 DN40（PN16) 个 10 146 22 3 10302601 柔性橡胶接头 DN50（PN10） 个 500 186 3 管 4 10302604 柔性橡胶接头 DN50（PN16） 个 10 186 4 5 10302602 柔性橡胶接头 DN80（PN10） 个 200 252 …… 国 6 10202125 柔性橡胶接头 DN80（PN16） 个 10 252 7 10202120 柔性橡胶接头 DN100（PN10） 个 10 300 8 1030中2605 柔性橡胶接头 DN100（PN16） 个 10 300 9 10202121 柔性橡胶接头 DN150（PN10） 个 10 500 10 10202123 柔性橡胶接头 DN150（PN16） 个 10 500 11 10202124 柔性橡胶接头 DN150（PN25) 个 10 660 12 10202122 柔性橡胶接头 DN200（PN10） 个 10 680 13 10302606 柔性橡胶接头 DN200（PN16） 个 10 720 14 10200481 柔性橡胶接头 DN300（PN16） 个 10 1400 15 10302155 金属补偿器 DN40 个 100 230 16 10302157 金属补偿器 DN40 (25KG) 个 10 240 17 10302156 金属补偿器 DN40（16kg） 个 10 230 18 10302140 金属补偿器 DN50 个 100 270 19 10302148 金属补偿器 DN50 （16kg） 个 10 270 20 10302151 金属补偿器 DN50(25KG) 个 10 300 21 10302141 金属补偿器 DN80 个 100 390 22 10302145 金属补偿器 DN80 (16KG) 个 10 390 23 10302146 金属补偿器 DN80 (25KG) 个 10 435 24 10302142 金属补偿器 DN100 个 10 455 25 10302147 金属补偿器 DN100 (16KG) 个 10 455 26 10302152 金属补偿器 DN100(25KG) 个 10 550 27 10302143 金属补偿器 DN150 个 10 630 28 10302149 金属补偿器 DN150 （16kg） 个 10 630 29 10302153 金属补偿器 DN150(25KG) 个 10 840 30 10302144 金属补偿器 DN200 个 10 900 网 31 10302150 金属补偿器 DN200 （16kg） 个 10 950 32 10302154 金属补偿器 DN200(25KG) 个 10 1250 2.2 供货数量、时间和批次：根据工程实际进度与比选人的要求进行务供货，以实际供货量为准，供货时间达到 商务条款的规定。 2.3 交货地点：比选人指定的施工现场。 商 2.4 供货期：两年。 3.投标人资格要求 道 3.1 本次比选允许投标人以投标货物的下列身份参加投标： ?制造商 管 ?代理商、经销商 3.1.1 投标人为制造商应符合以下要求： 投标人必须是依法设立国的，并在中国注册的，具有独立法人地位的企业。 【提供有效的营业执照】 3.1.2 投标人为代理商或经销商应符合以下要求： 中 若投标人为授权代理商或经销商，必须是依法设立的，并在中国注册的，具有独立法人地位的企业,同时应具备 投标产品的制造商对参加本项目投标的授权书。 【提供有效的营业执照、授权书】 注：① 一个制造商仅能委托一个代理商或经销商参加投标，否则均按否决投标处理。 ② 制造商及其授权的代理商或经销商不能同时参加本项目投标，否则均按否决投标处理。 3.2 投标人2025年的年度财务状况不亏损。若投标人为授权代理商或经销商，只能提供本单位的财务状况。 【提供由会计师事务所或审计机构出具的无保留意见的财务审计报告及会计报表，财务报表至少包括现金流量 表、资产负债表、利润表】 3.3 投标产品的制造商须通过质量ISO9001、环境ISO14001、职业健康体系ISO45001认证。 【提供有效的证书】 3.4 投标人须提供2023年1月1日至投标截止日止（以合同签订时间为准）,签订的30万元及以上的同类型产品购 销合同至少1个。 【提供采购合同、不低于前述金额50％的发票，合同与发票的项目名称须一致】 注：①若投标人开具的发票上未能体现具体项目，需附上税务出具的发票清单（清单上需显示采购项目为同类 型产品）。 ②若提供的合同为年度合同未体现具体金额，但实际供货金额达到30万元及以上，应提供与该合同对应的30万元 及以上的同类型产品发票作为佐证。 3.5 根据本次采购清单及技术规范的要求，投标人须承诺具备相关的技术手段和措施、保证产品设计使用寿 命10年以上。 3.6 投标产品的制造商须具备特种设备制造许可证（压力管道）。 网 【提供有效的证书】 3.7 投标人须承诺保证5年内不得停产同型号的投标产品。 务 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 3.8 投标产品须提供卫生疾控中心出具的卫生检测报告和质量监督机构出具的质量检验报告。 【提供有效的检验检测报告】 商 3.9 投标人承诺不得存在下列情形之一： 1）被人民法院列入失信被执行人名单且在被道执行期内； 2）被国家、重庆市（含市或任意区县）有关行政部门行政处罚，且在处罚期限内； 3）投标截止日前两年内（指2024年1月1日至投标截止日止），投标人或其法定代表人被人民法院判定犯行贿罪 管 的； 4）投标截止日前五年内（指2021年1月1日至投标截止日止），投标人与重庆中法供水有限公司有违约情况或终 止合同情况的。 国 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 3.10 投标截止日前五年内（指2021年1月1日至投标截止日止），投标人无在我司因产品及服务等对公司生产、 经营、安全造成不良影响的记录；若投标人出现过供水通报事项，因产品质量问题对生产、安全造成影响，存 中 在合同违约等问题，不予参加本次项目投标。 【按照第六章 三、资格审查部分“无不良记录承诺函”提供承诺函，若经验证承诺函不属实，将对中标人作 否决投标处理。】 3.11 投标样品要求： 3.11.1 投标人需提供以下规格型号数量的样品： 【金属补偿器 DN40壹件】，提供的样品应满足第五章技术要求规定。样品为投标人免费提供，不计入采购清 单内。 3.11.2 投标样品同投标文件一并递交。每件样品上分别标明样品的投标人、生产厂家、品牌、名称、规格、型号等 （格式自拟），投标样品必须密封装箱，且在密封包装外贴样品一览表（格式自拟），注明提供样品的投标人、 生产厂家、品牌、名称、规格、型号、数量等。 3.11.3 投标人的样品在开标当日递交至样品区（样品区地点：开标当日咨询比选代理机构），中标人的投标样 品不退还，其余投标人的样品在中标公示期满后5个工作日内退还，如不领取，投标样品按废品处理。 3.11.4 上述对投标样品的密封和标识要求是为便于评标，请投标人积极配合，未按上述要求对投标样品进行密封 和标识的，不作否决投标处理，但由此造成的其他后果由投标人自行承担。 3.12 若投标人违反重庆中法供水有限公司《供应商负面清单管理办法》规定且在处罚期内的，按否决投标处理 （评标委员会根据比选公告后附“供应商负面清单”进行评审）。 3.13 本次比选不接受联合体投标。 特别说明： （1） 本比选文件要求提供的所有检测报告须为近2年内的检测报告（2024年1月1日-投标截止日），此要求不 包括卫生许可批件及其检测报告。 （2） 上述所须提交的相关证明材料复印件均应加盖投标单位法人章并装入投标文件资格审查部分中。上述有 一条不满足则投标文件由评标委员会作否决投标处理。 网 （3） 比选人有权对投标人提供的以上资料进行核实，若发现存在弄虚作假，取消其投标、中标资格，投标人 承担因此造成的相关责任并赔偿相应损失。 务 4.比选文件的获取 4.1 投标人于2026年08月21 日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子 版，以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，采购人和采购代理机构都 商 视为投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的 一切后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 道 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价（须同时递交投标文件）。在投 标截止时间前未按时报名、报价并管上传电子投标文件、递交纸质投标文件，投标文件被视为无效。 4.4 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)上传电子投标文件，电子投标文件应加盖投标人 的单位印章。 国 4.5 投标人在递交投标文件时向招标代理机构支付500 元/份标书费，否则将拒绝接收投标文件。 5.投标文件的递交 中 5.1电子版投标文件递交时间：2026年08月27日10时00分（北京时间）前，投标人自行上传至重庆水务集团电子商 务平台(https://www.cqswjt.cn)； 5.2纸质版投标文件递交时间：2026年08月27日09时30分至10时00分（北京时间），地点：重庆水务集团招标采购 中心（重庆市两江新区嘉华路36号重庆水务大厦五楼。导航：重庆水务大厦东门）。 5.3投标截止时间：2026年08月27 日10时00分（北京时间）。 5.4逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 比 选 人：重庆中法供水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝北区悦来镇悦来水厂 地 址：重庆市两江新区嘉华路36号重庆水务大厦 联 系 人：陈老师 联 系 人： 崔畅 电 话：023-67585971 电 话： 13896264537 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3078192.html cqdingjiu 2026.08.24 12:31:37 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>DN40(PN10)个 200; DN40(PN16)个 10; DN50(PN10)个 500; DN50(PN16)个 10; DN80(PN10)个 200; DN80(PN16)个 10; DN100(PN10)个 10; DN100(PN16)个 10; DN150(PN10)个 10; DN150(PN16)个 10; DN150(PN25)个 10; DN200(PN10)个 10; DN200(PN16)个 10; DN300(PN16)个 10; DN40个 100; DN40(25KG)个 10; DN40(16kg)个 10; DN50个 100; DN50(16kg)个 10; DN50(25KG)个 10; DN80个 100; DN80(16KG)个 10; DN80(25KG)个 10; DN100个 10; DN100(16KG)个 10; DN100(25KG)个 10; DN150个 10; DN150(16kg)个 10; DN150(25KG)个 10; DN200个 10; DN200(16kg)个 10; DN200(25KG)个 10</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 光纤电缆保护套管</t>
+          <t>重庆, 金属补偿器, 柔性橡胶接头, 采购项目, 比选公告</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程变更公告</t>
+          <t>川渝高竹新区引调水工程项目招标计划表</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1425,7 +1405,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1444,34 +1424,30 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>巴南区</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程变更公告</t>
+          <t>新建两岔水库取水浮船1座，设计取水规模为2万m/d；新建两岔水库取水浮船-坛高水厂原输水管道21km。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>合同预估金额为508万元</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>天然气表后管道安装工程</t>
+          <t>取水浮船、输水管道</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程变更公告 重庆巴南天然气有限责任公司 重庆国际生物城配套公寓项目天然气表后管道安装工程 变更公 告 公告编号： RQBGGG202608200006 本公司于2026年08月19日发布的重庆国际生物城配套公寓项目天然气表后管道安装工程公告（编 号：RQCGXY202608170010），现做出如下变更： 网 1、对采购文件第一卷“采购需求“中墙体管道暗埋的具体内容进行明确。墙体管道暗埋应包含墙体开槽，输送 用不锈钢波纹管及钢制槽板的安装，墙体恢复，暗埋管道视频记录。 2、对由响应供应商提供的钢制槽板的规格进行明确。钢制槽板为U型开口槽，采用热镀锌Q235B钢板，钢板厚度 务 不得小于1.2mm，尺寸不得小于U40*30*1.2（宽40mm,高30mm,壁厚1.2mm热镀锌） 3、对由响应供应商提供的F型不锈钢三通，材质可以选用黄铜进行替代。 4、采购文件第二卷“技术规范及要求“中增加T/CECS633-2019 《燃气用户工程不锈钢波纹软管技术规程》。 以上内容在合同中也同步进行调整。 商 除上述变更外，原公告其余内容仍有效。 道 重庆巴南天然气有限责任公司 管 2026-08-20 信息来源:https://www.chinapipe.net/project/d3076704.html cqdingjiu 2026.08.21 10:国06:50 中</t>
+          <t>川渝高竹新区引调水工程项目招标计划表 重庆市工程建设项目招标计划表 项目名称 川渝高竹新区引调水工程项目 招标法人或招 标人名称（盖 重庆北碚农业发展有限公司 网 章） 项目批准文件 及文号 务 新建两岔水库取水浮船1座，设计取水规模为2万m/d；新建两岔水库取水浮船-坛高水厂原输 主要建设内容 水管道21km。 招标项目 招标方 招标文件计划 拟交易场 合同预估金额 序号 招标内容 备注 名称 式 发布时间 所 (万元) 商 新建两岔水库取水浮 川渝高竹 船1座，设计取水规 重庆市北 招标项目 新区引调 模为2万m/d；新 公开招 碚区公共 1 2026-08 508.00 水工程项 建两岔水库道取水浮 标 资源综合 目 船-坛高水厂原输水 交易中心 管道21km。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3078130.html cqdingjiu 2026.08.24 12:31:38 国 中</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>排水钢管 Φ200*6m：3000米</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1479,14 +1455,14 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>重庆, 天然气表后管道安装工程, 变更公告</t>
+          <t>重庆, 川渝高竹新区, 引调水工程, 取水浮船, 输水管道</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>合川区中南片区污水管网工程(一期)招标计划表</t>
+          <t>石阡县2026年第二批农村供水提质改造项目竞争性磋商公告</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1517,47 +1493,47 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>合川区</t>
+          <t>石阡县</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300-D800管道130米，新增检查井11座，新建D300排水管道38米；紫外光修复 D300-D800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米，螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米，不锈钢快速锁修复 D1000管道42米；完成 D300-D1000管道清障189米、清淤2627米。</t>
+          <t>农村供水提质改造项目</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>合同预估金额为1708.44万元</t>
+          <t>预算金额：1950000.00元，最高限价：1911000.00元</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>排水管道、检查井、紫外线修复设备、螺旋缠绕修复材料、树脂修复材料、不锈钢快速锁修复设备</t>
+          <t>供水提质改造相关设备和材料</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>合川区中南片区污水管网工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目 合川区中南片区污水管网工程（一期） 名称 招标 网 法人 或招 标人 重庆市合川区住房和城乡建设委员会 名称 （盖 务 章） 项目 批准 文件 合川发改投〔2025〕19 号 商 及文 号 主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300-D800管道130米，新增检查井11座，新 主要 建D300排水管道38米；紫外光修复 D300-D道800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米， 建设 螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米，不锈钢快速锁修复 D1000管道42 内容 米；完成 D300-D1000管道清障189米、清淤2627米。 拟 招 招标文 合同预 招标 管 交 序 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 所 国 重 庆 市 合川 合 招标 区中 主要建设内容包含多项管网修复及新建工程，具体为：原位开挖修复 D300- 川 项目 中 南片 D800管道130米，新增检查井11座，新建D300排水管道38米；紫外光修复 公 区 区污 D300-D800排水管道712米，紫外光内衬+钢套筒修复 D300-D800排水管道755米， 开 公 1 2026-09 1708.44 水管 螺旋缠绕修复 D1000-D1600管道73米，局部树脂修复 D300-D800排水管道125米， 招 共 网工程 不锈钢快速锁修复 D1000管道42米；完成 D300-D1000管道清障189米、清 标 资 （一 淤2627米。 源 期） 交 易 中 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076543.html cqdingjiu 2026.08.21 10:06:50</t>
+          <t>石阡县2026年第二批农村供水提质改造项目竞争性磋商公告 竞争性磋商公告 项目概况 石阡县2026年第二批农村供水提质改造项目 项目的潜在供应商应在铜仁市大力城项目管理有限责任公司（铜 仁市碧江区时代天街1号楼16层16-7室）获取磋商文件，并于2026 年9月 1 日 14 点30分（北京时间）前递 交响应文件。 网 一、项目基本情况 项目编号： TRDLC-2026-022 务 项目名称：石阡县2026年第二批农村供水提质改造项目 采购方式： 竞争性磋商 预算金额： 1950000.00元 商 最高限价： 1911000.00元 采购需求：详见磋商文件 道 合同履行期限： 3个月（90日历天） 本项目（否）接受联合体投标。 管 二、申请人的资格要求： （一）满足《中华人民共和国政府采购法》第二十二条规定； 国 （二）落实政府采购政策需满足的资格要求（根据项目实际情况）： 按财库〔2014〕68号、财库〔2017〕141 号、财库〔2019〕9号、财库〔2020〕46号、财库〔2022〕19号等文件执行。 （三）本项目的特定资格要求：1.本项目是专门面向中小企业采购，若工程的承建企业是中小企业，请供应商按照 中 《政府采购促进中小企业发展管理办法》(财库〔2020〕46号）出具规定的《中小企业声明函》；2.其他特殊资格 要求：本次招标要求投标人须具备水利水电工程施工总承包叁级及以上及以上资质，具备有效的安全生产许可 证；并在人员、设备、资金等方面具有相应的施工能力，其中，投标人拟派项目负责人(项目经理)须具备 水利 水电 专业 贰 级注册建造师，具备有效的安全生产考核合格证书 (B证)，在投标截止日有在其他在 建建设工程(含已经获得中标通知书未开工)担任项目负责人(包括工程总承包中的施工负责人)的，不得以拟派项 目负责人(项目经理) 的身份参加本次投标。 三、获取磋商文件 （一）时间： 2026年 8 月 21 日 17:00 至 2026 年 8 月 28 日 17:00 （北京时间，法定节假 日除外） （二）地点：铜仁市碧江区时代天街1号楼16层16-7室 （三）方式：现场获取，报名时需提交的资料：营业执照复印件，法定代表人身份证明及身份证复印件、授权 委托书原件（法定代表人报名的无需提供此项资料）、被授权人身份证原件及复印件（法定代表人报名的无需 提供此项资料）、上述资料均需加盖单位公章。 网上邮件报名获取：营业执照复印件，法定代表人身份证明及身份证复印件、授权委托书原件（法定代表人报 名的无需提供此项资料）、被授权人身份证原件及复印件（法定代表人报名的无需提供此项资料）、上述资料 均加盖单位公章后将扫描件发送到QQ邮箱1094532301@QQ.com后领取。注：发送后请及时联系18385937396。 注：被授权人需提供本单位2026年任意一个月缴纳社保证明。 （四）售价：人民币300元/套 四、提交响应文件截止时间、开标时间和地点 （一）时间： 2026 年 9 月 1 日 14 点 30 分（北京时间） （二）开标地点：石阡县水务局7楼会议室 五、公告期限 自本公告发布之日起3个工作日。 网 六、其他补充事宜 1.根据《关于印发中小企业划型标准规定的通知》的规定，本项目所属行业分类为 建筑业 。 务 2.采购信息发布网站：在贵州省招标投标公共服务平台上公布。 七、对本次采购提出询问，请按以下方式联系。 商 1.采购人信息： 名 称： 石阡县农村水利水电站 道 地 址： 石阡县泉都街道佛顶山大道水务局办公楼 联系方式： 0856-7931646 管 2.采购代理机构信息： 名 称： 铜仁市大力城项目管理有限责任公司 地 址： 铜仁市碧江区国时代天街1号楼16层16-7室 联系方式： 15286751783 3.项目联系方式： 中 项目联系人： 杨帅 电 话： 15286751783 信息来源:https://www.chinapipe.net/project/d3078119.html cqdingjiu 2026.08.24 12:31:38</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>D800管道：130米；D300排水管道：38米；D800排水管道：755米；D1600管道：73米；D800排水管道：125米；D800排水管道：712米；D1000管道：42米；检查井：11座；管道：189米</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>重庆, 污水管网工程, 管网修复, 新建工程, 排水管道, 检查井, 紫外线修复, 螺旋缠绕修复, 树脂修复, 不锈钢快速锁修复</t>
+          <t>重庆, 管材招标, 农村供水提质改造</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>重庆市自来水有限公司球墨铸铁管及管件2026-2027(2年)采购项目(第二次)答疑补遗文件</t>
+          <t>万州区后山至弹子农村连片供水保障提升工程招标计划表</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1567,7 +1543,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1586,30 +1562,34 @@
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>本次采购项目涉及球墨铸铁管及管件的供应，具体包括样品的规格和数量要求。</t>
+          <t>新建供水规模10000立方米/天的净水厂1座，厂外配水主干管网长度约40公里，村镇配水支线管网长度约100公里，配套一体化供水泵站共15座，新增原水管约1公里。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>合同预估金额6000万元</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>球墨铸铁管及管件</t>
+          <t>供水设备、管道</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>重庆市自来水有限公司球墨铸铁管及管件2026-2027(2年)采购项目(第二次)答疑补遗文件 重庆市自来水有限公司球墨铸铁管及管件2026-2027（2年）采购项目（第二次）答疑 提问1：样品20CM长含承口吗？如果含承口20CM那就太短，标识LOGO无法体现完整建议≥20CM 答1：球墨铸铁管样品含承口，样品长度≥20CM 网 务 招标人：重庆市自来水有限公司 招标代理机构：重庆水务集团公用工程咨询有限公司 商 2026年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d30道76446.html cqdingjiu 2026.08.21 10:06:50 管 国 中</t>
+          <t>万州区后山至弹子农村连片供水保障提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 万州区后山至弹子农村连片供水保障提升工程 招标法人或招 标人名称（盖 重庆长江水务有限公司 网 章） 项目批准文件 万州发改审投〔2026〕82 号 及文号 务 新建供水规模 10000 立方米/天的净水厂 1 座，厂外配水主干管网长度约 40 公里，村镇配水支线 主要建设内容 管网长度约 100 公里，配套一体化供水泵站共 15 座，新增原水管约 1 公里。 招标项目名 招标方 招标文件计划 合同预估金 序号 招标内容 拟交易场所 备注 称 式 发布时间 额(万元) 商 万州区后山至 万州区后山 招标项目 弹子农村连片 重庆市万州 至弹子农村 公开招 1 供水保障提升 2026-08 区公共资源 6000.00 连片供水保 标 工程施工道总承 交易中心 障提升工程 包 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3078105.html 管 cqdingjiu 2026.08.24 12:31:38 国 中</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>净水厂设备及配件；配水管网及配件；一体化供水泵站设备及配件；原水管</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1617,14 +1597,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>重庆, 球墨铸铁管, 管件, 采购项目</t>
+          <t>重庆, 供水, 管网, 管材, 招标</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>大足区中心城区和龙水镇市政公共排水设施运维(材料)更正一号公告</t>
+          <t>重庆涪陵电力实业股份有限公司2026年第4批物资公开谈判采购采购公告</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1634,7 +1614,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1655,12 +1635,12 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>大足区</t>
+          <t>渝北区</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>大足区中心城区和龙水镇市政公共排水设施的运维(材料)。</t>
+          <t>重庆涪陵电力实业股份有限公司2026年第4批物资公开谈判采购</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1670,12 +1650,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>管道</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>大足区中心城区和龙水镇市政公共排水设施运维(材料)更正一号公告 一、更正项 更正项 更正子项 更正前内容 更正后内容 网上投标 网上投标截止时间 2026-08-20 15:00:00 2026-08-25 15:00:00 递交投标响应文件 线下递交投标（响应）文件开始时间 2026-08-20 14:30:00 2026-08-25 14:30:00 递交投标响应文件 线下递交投标（响应）文件截止时间 2026-08-20 15:00:00 2026-08-25 15:00:00 网 开标 开标时间 2026-08-20 15:00:00 2026-08-25 15:00:00 招标采购（附件） 附件 务 二、补遗更正说明 清单限价重新做调整，开标时间已更正，详见更正文件内容 商 三、联系方式 采购执行方： 道 单位名称：重庆誉双项目管理有限公司 联系人：陈老师 联系电话：13996336872 采购需求方： 管 单位名称：重庆市大足区茂泰市政工程有限公司 联系人：谢老师 联系电话：18523539371 信息来源:https://www.chinapipe.net/project/d3076319.html 国 cqdingjiu 2026.08.21 10:06:50 中</t>
+          <t>重庆涪陵电力实业股份有限公司2026年第4批物资公开谈判采购采购公告 采购项目编 采购项目状态 正在采购 FLDL-JTWZ-2026D 号 重庆涪陵电力实业股份有限公司2026 采购项目名称 采购类型 物资 年第4批物资公开谈判采购 采购文件获取截止时 开启应答文 2026-08-25 09:00:00 2026-09-01 09:00:00 间 件时间 供应商提出澄清问题 网 截止时间 开启应答文件地点 详见附件 采购人 重庆涪陵电力实业股份有限公司 招标代理机 重庆市渝北区青枫北路20号凤凰D 招标代理机构 重庆展泽工程咨询有限公司 务 构地址 座9楼部分办公用 招标代理机构邮编 401120 联系人 供应商服务大厅 联系电话 400-1047-177 传真 商 电子邮箱 JZD_WZ@163.com 信息来源:https://www.chinapipe.net/project/d3078035.html cqdingjiu 2026.08.24 12:31:38 道 管 国 中</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1684,18 +1664,18 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>重庆, 管材招标</t>
+          <t>重庆, 2026年, 第4批物资公开谈判采购, 管道</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>璧山区2026年大路街道三台村智慧设施农业建设项目招标计划表</t>
+          <t>荣昌区2026年吴家镇高标准农田建设项目答疑补遗文件</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1726,47 +1706,47 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>璧山区</t>
+          <t>荣昌区</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>项目主要建设内容包括：1.新建茄果类智能种植温室11256平方米；2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、二氧化碳补施系统1套、智能环境控制系统1套、作业物流装备1套；3.项目后勤及仓储配套（含装修）5000平方米；4.土方回填及场地平整53000平方米；5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米；6.都市农文旅配套建设1000平方米。</t>
+          <t>新建管道 PE 管管件工程量问题；新建道路石方工程量问题；重庆市双业融资担保有限公司信用资质、履约能力问题；建筑工程概算费用问题；总价报价下浮率计算问题；招标文件下载问题；施工单位盖章问题；建筑工程或者市政工程土石方施工业绩问题；投标文件格式填写问题；合同工程完工证书证明材料问题；招标人提供的工程量清单单项最高限价问题；投标函附录中工期、分包、工程质量要求和缺陷责任期对应约定内容问题；我公司业绩为三个项目合并招标问题；边坡治理施工业绩问题；任一清单的综合单价低于警戒线问题；业绩要求的竣工时间问题；财务报告提供问题；我公司业绩合同金额问题；招标人确定中标人问题；低价说明证明材料问题；招标人是否委派业主专家参与评标问题；我公司业绩项目经理变更问题；财务报告提供问题；专业分包业绩问题；投标文件制作系统软件导出的电子投标文件格式问题；项目经理以前在其他公司执业的业绩问题；在职的已退休的注册人员问题；投标函附录中的合同条款号填写问题；评标办法中已标价工程量清单要求的承诺问题；评标专家不被围猎问题。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>合同预估金额为9182.25万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>温度调控系统、水肥一体化设备、人工补光系统、二氧化碳补施系统、智能环境控制系统、作业物流装备</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>璧山区2026年大路街道三台村智慧设施农业建设项目招标计划表 重庆市工程建设项目招标计划表 项目 璧山区2026年大路街道三台村智慧设施农业建设项目 名称 招标 法人 或招 网 标人 中农良品（重庆）生态农业有限公司 名称 （盖 章） 项目 批准 务 文件 及文 号 主要 1.新建茄果类智能种植温室11256平方米；2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、二氧化碳补施系统1套、智能环境控制系统1套、作业物流 建设 装备1套；3.项目后勤及仓储配套（含装修）5000平方米；4.土方回填及场地平整53000平方米；5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米；6. 内容 都市农文旅配套建设1000平方米。 商 招 拟 标 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 称 道 璧 山 区2026 重 年 庆 大 市 路 公 招标 街 管 共 项目 道 资 三 公 源 台 项目主要建设内容包括：1.新建茄果类智能种植温室11256平方米； 2.设备采购：购置温度调控系统1套、水肥一体化设备1套、人工补光系统1套、 开 交 1 村 二氧化碳补施系统1套、智能环境控制系统1套、作业物流装备1套； 3.项目后勤及仓储配套（含装修）5000平方米； 4.土方回填及场地平整53000平 2026-09 9182.25 招 易 智 方米； 5.新建道路1584米、水渠管网1387米、停车场6500平方米；配套绿化15000平方米； 6.都市农文旅配套建设1000平方米。 标 中 慧 心 设 国 璧 施 山 农 分 业 中 建 心 设 项 目 中 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3076777.html cqdingjiu 2026.08.21 10:06:51</t>
+          <t>荣昌区2026年吴家镇高标准农田建设项目答疑补遗文件 荣昌区2026年吴家镇高标准农田建设项目 答疑通知 各潜在投标人： 现将“荣昌区2026年吴家镇高标准农田建设项目”答疑通知发布如下： 问题1：招标清单内新建管道工程里面110管～250管设计清单量给的管件工程量太大，设计不合理，平均2米一个 管件，设计脑子有包吗？pe管根本用不了这么多管件，属于虚量。重新整理一下减少到现有的10分之一吧；新建 道路石方量也太大了。属于虚方，减少至原有工程量三分之一。这些虚方不删除网会导致虚方未施工情况导致工 程量变更或者滋生腐败。 回复： 1、关于新建管道 PE 管管件工程量问题：经核实，本项目工程量清单中约20米一个管件。本次招标清单工程量不 作修改，结算时按合同约定据实计量结算。 务 2、关于新建道路石方工程量问题：清单石方量为设计预算量。石方开挖受现场实际地质情况变化影响，本次招 标清单工程量不作调整，结算按现场实际完成合格工程量依据合同约定据实计量。 提示：投标单位报价时综合 考虑上述现场不确定因素，自主合理报价。 商 问题2：请问重庆市双业融资担保有限公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，目前 查出双业融资担保多条被执行案件，都是因为不能履行保函的见索即付，拒绝赔付。相关业主方在招标文件补 遗通知中直接将重庆双业融资担保有限公司列入担保公司回避名单，拒绝重庆双业融资担保有限公司所出具的 保函。由此可见重庆双业融资担保有限公司的信用资质、履约能力、根本无能力是存在很大问题的。请问以重 庆双业融资担保有限公司目前的被执行和不履道行投标担保责任的情况是否符合招标文件的要求? 回复： 根据招标文件规定,纸质投标保函的开具要求为纸质投标保函的开立人应当是具有相应资格的银行、保险机构、 融资担保公司，其信用资质、履约能力、担保能力、赔付流程、安全保密等应符合工程保函业务条件。纸质投 标保函应合法合规，符合招投标行政监督部门、行业主管部门和金融监管部门的相关规定，满足招标文件约定 管 要求。投标人应选择在渝依法设立总部或者设有分支机构的金融机构开具纸质投标保函。投标人对所提交的纸 质投标保函的真实性、合法性、有效性负责。 问题3：1、建筑工程概算费用名称：碎石垫层(厚15cm）、步道)C25砼(厚15、cm，)的单位均为M3，是否应为m2， 国 因碎石垫层47.5元/m3,C25砼(厚15cm，衔接道路)93.26元/m3材料成本都不够？ （2）总价报价下浮率=[（投标总报价最高限价-暂定金额、暂列金、安全生产费）-（投标总报价暂定金额、暂 列金、安全生产费）]/（投标总报价最高限价-暂定金额、暂列金、安全生产费）*100%；这个公司是否有误2、 2/ 回复： 中 1、碎石垫层 (厚 15cm）、步道 C25 砼 (厚 15cm) 计量单位不作修改。 2、按：总价报价下浮率 =[（投标总报价最高限价 - 暂列金额、暂估价、安全文明施工及环境保护费暂定金额）- （投标总报价 - 暂列金额、暂估价、安全文明施工及环境保护费暂定金额）]/（投标总报价最高限价 - 暂列金额、 暂估价、安全文明施工及环境保护费暂定金额）×100%。 问题4：招标文件下载不了。 回复：可以通过重庆市电子招投标系统投标文件制作软件-新建工程-浏览[50022620260802001010101].CQZF这个文 件包-读取CA锁填写投标单位-点确定-通过打印按钮-另存就可以了。 问题5：报告中施工单位盖章由我公司盖章，请问需要提供联合体协议书吗？ 回复：需要。 问题6：建筑工程或者市政工程土石方施工业绩满足吗？ 回复：按招标文件要求提供。 问题7：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可以 不填(空白)，对此有无要求？ 回复：填“/”。 问题8：合同工程完工证书（或合同工程验收鉴定书或工程竣工证书副本或竣工验收鉴定书）的证明材料，请问 竣工证明材料只能是上述几种吗？例如竣工报告、完工证明、单位工程验收鉴定书和竣工验收证书等证明材料 符合要求吗？ 回复：竣工报告、竣工验收证书可以；完工证明、单位工程验收鉴定书不可以。 问题9：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 回复：可以。 问题10：投标函附录中，工期、分包、工程质量要求和缺陷责任期对应的约定内容，可以统一填写“达到招标文 件要求”吗？ 回复：可以。 问题11：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收，请 问我公司业绩满足业绩要求吗？ 回复;不满足，按招标文件投标人须知前附表1.4.1投标人资质条件、能力和信誉3、业绩要求执行。 网 问题12：边坡治理施工业绩符合吗？ 回复：不符合。 问题13：任一清单的综合单价低于警戒线，就要提供说明吗？ 务 回复：不是，仅主要清单单项报价低于招标文件规定的对应的异常低价警戒线的须提供。 问题14：业绩要求的竣工时间是指竣工验收时间吗？ 回复：是的。 商 问题15：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 回复：按招标文件投标人须知前附表1.4.1投标人资质条件、能力和信誉中的财务要求执行。 问题16：我公司业绩合同金额1600万元及以上道，但是竣工报告业绩金额小于1600万元，请问是否满足业绩要求？ 回复：不满足本项目业绩要求。该业绩的合同协议书和合同工程完工证书（或合同工程验收鉴定书或工程竣工 证书副本或竣工验收鉴定书或竣工验收证书或竣工报告）中载明的金额为准。 问题17：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知书发 管 出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予提前注 销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 回复：是否加盖正本字样无强制要求。 国 问题18：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗？ 回复：真实签订、具备法律效力且可印证履约的正式文件，可以作为低价说明证明材料，说明证明材料是否符 合要求，由评标委员会进行评审。 中 问题19：请问招标人是否委派业主专家参与评标吗？ 回复：本项目不委派业主专家。 问题20：我公司业绩项目经理变更过，竣工验收报告中能够体现项目经理名字，请问还需要提供项目经理变更证 明材料吗？ 回复：需要。 问题21：财务报告可以不提供财务报表附注吗？ 回复：可以不提供。 问题22：土地场平施工业绩满足吗？ 回复：不满足。 问题23：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要 提供其他格式之外的其他承诺？ 回复：包含，不需要提供格式之外的其他承诺。 问题24：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗？ 回复：不需要。 问题25：我公司合同协议书和竣工报告中无法体现项目经理名字，合同专用条款中能体现项目经理名字，请问能 提供合同专用条款的关键页来证明是拟派项目经理的业绩吗？ 回复：不能。 问题26：有没有人行贿专家，有的话我们就不参加了。 回复：该质疑与本项目无关。如有人行贿专家等围标串标的违法行为相关线索，请潜在投标人向有关行政监督 部门举报。 问题27：财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加强审计报告查验工作的通知》中要求 会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第十四条规定审计业务出具的报告（以 下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标人提 供的财务报告需要赋码和提供深度查询截图吗？ 回复：招标文件中对是否提供财务报告申请赋码及查询截图未作要求，投标人按网招标文件第二章投标须知前附 表1.4.1投标人资质条件、能力和信誉中2.财务要求提供材料即可。 问题28：土石方施工业绩满足业绩要求吗？ 回复：不能 务 问题29：本项目是异地评标吗？ 回复：非异地 商 问题30：我公司业绩符合招标文件要求，在工程完成80%后因项目经理离职申请项目经理变更，请问招标人我公 司业绩可以作为变更后的项目经理业绩吗？ 回复：项目完成 80% 后变更项目经理的，需提供合法有效的项目经理变更相关证明材料，该业绩可以认定为变 更后项目经理的业绩；否则不予认可该项目经理业绩。 道 问题31：专业分包业绩满足业绩要求吗？ 回复：不满足。 问题32：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 管 不一致的以哪个为准？ 回复：除重庆市电子招投标系统中锁定不可以修改的格式外（如投标函等），均以加盖公章的PDF招标文件中的 投标文件格式为准。 国 问题33：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗？ 回复：不需要。 问题34：项中目经理以前在其他公司执业的业绩可以在本项目作为项目经理业绩使用吗？ 回复：项目经理在其他单位任职期间的项目经理业绩，若全套业绩资料能够证实在该项目担任项目经理，可予 以接受，由评标委员会综合评审。 问题35：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、注册证 及在本单位注册的证明文件替代？ 回复：不可以。招标文件明确要求提供投标单位缴纳养老保险证明，不设置退休人员替代材料，招标人不放宽 资格条件。 问题36：投标函附录中的合同条款号可以填写“/”吗？ 回复：投标函附录中的合同条款号填写内容不作强制性要求。 问题37：评标办法中已标价工程量清单要求的承诺需要在报价部分和资格审查资料中进行单独承诺吗？ 回复：投标人承诺已标价工程量清单满足第二章“投标人须知前附表”第3.2款第14条要求，如有差错则按第二章 “投标人须知前附表”第3.2款第13条要求原则进行处理（或结算），承诺书格式详见第八章投标文件格式。 问题38：现在除了没有警戒线和技术方案的低价项目评标专家不被围猎，哪个项目不围猎评标专家，请问招标人 如何保证公平？ 回复：该质疑与本项目无关。如有人围猎专家等围标串标的违法行为相关线索，请潜在投标人向有关行政监督 部门举报。 问题39：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 回复：除重庆市电子招投标系统中锁定不可以修改的格式外（如投标函等），均以加盖公章的PDF招标文件中的 投标文件格式为准。 注:本答疑补遗通知书与原招标文件有冲突的地方，以本答疑补遗通知书为准，本答疑补遗通知书作为招标文件 的组成部分。请各投标人自行下载，不管下载与否均视为投标人己全部知晓。 招 标 人：重庆市荣昌区农田建设中心 招标代理机构：重庆心恒工程招标代理有限公司 2026年08月21日 信息来源:https://www.chinapipe.net/project/d3078019.html 网 cqdingjiu 2026.08.24 12:31:38 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>水渠管网：1387米</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>重庆, 智慧设施农业, 招标计划, 项目内容, 资金情况, 产品种类</t>
+          <t>塑料管不计匹配分</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>长寿区江南街道污水处理厂更新改造工程项目公告</t>
+          <t>大渡口区2024年居民户内燃气安全设施整改项目(二期)、大渡口区2024年城市燃气管道等老化更新改造项目(二期)招标公告</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1776,7 +1756,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1797,47 +1777,47 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>长寿区</t>
+          <t>大渡口区</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>本项目包括但不限于新建混凝池-三沉池，还建格栅池，厌氧池新增搅拌机，好氧池联通孔短流整改、拆除填料及底部曝气盘，增设可提升曝气系统，原斜管沉淀池改造为二沉池（新增中心筒、改造成多斗排泥、提高液位，更换三角堰），拆除原有污泥池，新增临时污泥储罐务并还建污泥池，污泥堆场临时改建及恢复，实施技改期间的临时排放工程，进行基础的自控改造。</t>
+          <t>大渡口区2024年居民户内燃气安全设施整改项目（二期）更换居民气表约11700只、居民灶前自闭阀约112717只、燃气连接用不锈钢波纹软管约112717根。大渡口区2024年城市燃气管道等老化更新改造项目（二期）更新改造庭院埋地燃气管网约6913m，更新改造燃气立管及表后管道约9419户，更新切断阀约489套等，并配套实施管网开挖回填、路面恢复、绿化恢复等。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>企业自筹，出资比例为100%</t>
+          <t>本项目工程总投资金额：5800.7万元，大渡口区2024年居民户内燃气安全设施整改项目（二期）总投资3165.12万元，大渡口区2024年城市燃气管道等老化更新改造项目（二期）总投资2635.58万元。</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>污水处理设备</t>
+          <t>燃气安全设施、城市燃气管道等老化更新改造</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>长寿区江南街道污水处理厂更新改造工程项目公告 长寿区江南街道污水处理厂更新改造工程比选公告 1. 比选条件 本比选项目长寿区江南街道污水处理厂更新改造工程，比选人为重庆环保投资集团有限公司，资金来源为企业 自筹，出资比例为100%。现对该项目进行公开比选，诚邀有兴趣的潜在参选人参与比选。 2. 项目概况与比选范围 网 2.1项目概况：长寿区江南街道污水处理厂更新改造工程包括但不限于以下内容新建混凝池-三沉池；还建格栅池； 厌氧池新增搅拌机，好氧池联通孔短流整改、拆除填料及底部曝气盘，增设可提升曝气系统；原斜管沉淀池改 造为二沉池（新增中心筒、改造成多斗排泥、提高液位，更换三角堰）。拆除原有污泥池，新增临时污泥储罐 务 并还建污泥池；污泥堆场临时改建及恢复；实施技改期间的临时排放工程；进行基础的自控改造。 2.2 比选范围：长寿区江南街道污水处理厂更新改造工程施工图范围中的所有工作内容，包括但不限于土建工 程、设备及安装工程、工艺管道工程、电气工程、临排工程等内容，具体以比选人提供的图纸、技术规范、设 备需求清单、答疑资料、澄清资料、其他补遗资料等相关商内容为准。 2.3 建设地点：重庆市长寿区江南街道。 2.4 工期：110日历天（实际开工日期以监理工道程师签发的工程开工通知明确的开工日期为准），缺陷责任期24 个月。 3. 参选人资格要求 管 3.1 本次比选要求参选人具备以下条件： （1）独立法人资格； （2）建设行政主管部国门颁发的有效的市政公用工程施工总承包二级及以上资质； 3.2 参选人还应在资质、业绩、资金、人员等方面具有相应的服务能力，详见比选文件第二章参选人须知前附 表第1.4.1项内容。 中 3.3本次比选不接受联合体参选。 4. 比选文件的获取 4.1 参选人于2026年8月19日起可自行在重庆水务集团电子商务平台（https://www.cqswjt.cn）上下载比选文件电 子版，以及答疑、补遗等比选截止时间前公布的所有相关资料，不管参选人下载与否，比选人和代理机构都视 为参选人收到以上资料并全部知晓有关比选过程和事宜，如因参选人自身原因未能下载相关资料由此产生的一 切后果由参选人自行负责。各参选单位应随时关注网上（https://www.cqswjt.cn）发布的比选文件及相关修改内容。 4.2 参选人须在重庆水务集团电子商务平台（https://www.cqswjt.cn）进行供应商注册，填写相关信息，审批过后 成为平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标（仍须同时提交纸质版参选文件）。参选 人需提前在重庆水务集团电子商务平台（https://www.cqswjt.cn）上注册、报名，下载比选文件，上传参选文件电 子档并报价。在比选截止时间前未按时报名、报价并上传参选文件电子档、递交纸质版参选文件者，将被否决 参选。 5. 比选文件的递交 5.1 参选文件递交时间：2026年8月 27 日09时00分至09时30分，地点：重庆市两江新区嘉华路36号重庆水务 大厦5楼。 5.2 比选截止时间：2026年8月 27 日09时30分（北京时间）。 5.3 逾期送达的或者未送达指定地点的参选文件，比选人不予受理。 6. 发布比选公告的媒介 本次比选公告在重庆水务集团电子商务平台（https：//www.cqswjt.cn）上发布。 7. 联系方式 比选人：重庆环保投资集团有限公司 地 址：重庆市两江新区礼环南路102号 网 联系人：曹老师 电话：023-71618725 务 代理机构：重庆招标采购（集团）有限责任公司 地址：重庆市江北区五简路2号重庆咨询大厦A座2004室 商 联系人：高老师 电话：023-67706841 道 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 管 信息来源:https://www.chinapipe.net/project/d3076456.html cqdingjiu 2026.08.21 10:06:51 国 中</t>
+          <t>大渡口区2024年居民户内燃气安全设施整改项目(二期)、大渡口区2024年城市燃气管道等老化更新改造项目(二 期)招标公告 大渡口区2024年居民户内燃气安全设施整改项目（二期）、大渡口区2024年城市燃气管道等老化更新改造项目 （二期）招标公告 1.招标条件 本招标项目大渡口区2024年居民户内燃气安全设施整改项目（二期）、大渡口区2024年城市燃气管道等老化更新 改造项目（二期）已由重庆市大渡口区发展和改革委员会以渡发改审发[2026]15号、渡发改审发[2026]16号批准 建设，项目业主为重庆市大渡口区经济和信息化委员会，代建业主为重庆燃气集团股份有限公司大渡口分公司， 建设资金来自争取上级资金、区级财政配套及社会资金，项目出资比例为100%网，招标人为重庆燃气集团股份有 限公司大渡口分公司。项目已具备招标条件，现对该项目的工程总承包进行公开招标，评标办法采用综合评估 法。 2.项目概况与招标范围 务 2.1 建设地点：重庆市大渡口区 2.2 项目概况与建设规模： 商 1.大渡口区2024年居民户内燃气安全设施整改项目（二期）更换居民气表约11700只、居民灶前自闭阀约112717只、 燃气连接用不锈钢波纹软管约112717根。 2.大渡口区2024年城市燃气管道等老化更新改道造项目（二期）更新改造庭院埋地燃气管网约6913m，更新改造燃 气立管及表后管道约9419户，更新切断阀约489套等，并配套实施管网开挖回填、路面恢复、绿化恢复等。 2.3 本项目工程总投资金额：5800.7万元，大渡口区2024年居民户内燃气安全设施整改项目（二期）总投资3165.12 万元，大渡口区2024年城市燃气管道等老化更新改造项目（二期）总投资2635.58万元。 管 本次招标项目合同估算金额：5195.561015万元，其中大渡口区2024年居民户内燃气安全设施整改项目（二期）工 程设计费59.350905万元，工程费2849.79万元；大渡口区2024年城市燃气管道等老化更新改造项目（二期）工程设 计费47.44011万元，工程费2238.98万元。 国 2.4 招标范围：主要包括施工图设计、工程施工等内容，具体范围为： (1)设计部分：本项目范围内的施工图设计、施工及竣工验收阶段、质量保修阶段的设计配合服务，以及协助招 标人完成审中批手续办理等工作。按招标人要求按质按时提交设计成果，并取得国家相关职能部门的批准。 (2)施工部分：包括但不限于设计范围内所涉及的工作内容。 (3)其他部分：项目预算编制、总承包管理（对承包项目的质量、安全、工期、造价等全面管控和负责）。 2.5 工期要求：总工期540日历天，缺陷责任期24个月。其中： 设计周期：施工图设计90日历天； 施工工期：450日历天； 2.6 标段划分（如有）：/ 2.7 其他：/ 3.政府采购工程 3.1 是否属于政府采购工程：是 3.2 是否专门面向中小企业预留：是 本项目以联合体形式面向中小企业，以联合体形式参加本次投标的，联合体中中小企业承担的合同份额需达 到40%以上。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件： 同时具备建设行政主管部门颁发的有效的以下资质： 网 4.1.1.1 设计资质：投标人应同时具备以下(1)、(2)项资质 (1)投标人应具备以下A、B、C项资质之一： 务 A.工程设计综合甲级资质。 B.工程设计市政行业乙级及以上资质。 C.工程设计市政行业(城镇燃气工程)专业乙级及以上资质商。 (2)具备《中华人民共和国特种设备设计许可证》(压力管道)公用管道GB1级或《中华人民共和国特种设备生产许 可证》(压力管道设计)公用管道GB1级。 道 4.1.1.2 施工资质：投标人应同时具备以下(1)、(2)项资质 (1)投标人应具备以下A、B项资质之一： 管 A.具备建设行政主管部门颁发的有效的市政公用工程施工总承包二级及以上资质。 B.具备建设行政主管部门颁发的有效的石油化工工程施工总承包三级及以上资质。 (2)具备有效的《中华人国民共和国特种设备安装改造维修许可证》公用管道GB1级或《中华人民共和国特种设备安 装改造修理许可证》公用管道GB1级或《中华人民共和国特种设备生产许可证》公用管道安装GB1级。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的实施能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 中 4.2 本次招标接受联合体投标。联合体投标的，应满足下列要求：联合体单位成员不得超过2家（含联合体牵头 人），且联合体牵头人须由负责施工的联合体成员予以担任，具体详见投标人须知前附表1.4.2。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件、工程量清单 （如有）、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字 证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责 任自负。 5.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 布至2026-08-26 17:00:00前。 5.3招标人应于2026-08-28 23:59:59前在重庆市公共资源交易网发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-14 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网和重庆市公共资源交易网发布。[提示：依法必须招标项目的招 标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆燃气集团股份有限公司大渡口分公司 代理机构: 重庆市义渡工程管理有限公司 重庆市大渡口区春晖路街道翠华园小区11 重庆市大渡口区文体路126号锦天商务中 地 址: 地 址: 栋3层 心东楼535室 邮 编: 400084 邮 编: 400084 项目负责人: 任老师 项目负责人: 唐书霞网 电 话: 023-68551113 电 话: 023-85786930 传 真: 传 真: 电子邮箱: 电子邮箱:务 开户银行: 开户银行: 账 号: 账 号: 商 监督部门: 重庆市大渡口区发展和改革委员会 电 话: 023-68083238 2026年08月21日 信息来源:https://www.chinapipe.net/project/d30道77961.html cqdingjiu 2026.08.24 12:31:38 管 国 中</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>更换居民气表约11700只、居民灶前自闭阀约112717只、燃气连接用不锈钢波纹软管约112717根；更新改造庭院埋地燃气管网约6913m，更新改造燃气立管及表后管道约9419户，更新切断阀约489套等。</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 污水处理厂</t>
+          <t>重庆, 燃气安全设施, 城市燃气管道, 老化更新改造, 投资金额, 项目总投资</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>潼南区新胜镇、双江镇污水处理厂更新改造工程项目项目公告</t>
+          <t>荣昌区2026年安富街道高标准农田建设项目招标公告</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1847,7 +1827,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1868,47 +1848,47 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>潼南区</t>
+          <t>荣昌区</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>本项目包括两个子项目：一是潼南区新胜镇污水处理厂的更新改造，主要内容是新增一体化污水处理设备基础，更新现有污水处理系统设备，升级处理系统，新建风机房-配电室防尘防渗地坪；二是潼南区双江镇污水处理厂的更新改造，内容包括将原有斜管沉淀池改建为好氧池，新建竖流沉淀池，更新老旧及故障设备，新建储药加药区和一体化危废储存间，完善污水处理配套设施。</t>
+          <t>改造提升高标准农田326.59亩，其中高效节水灌溉面积130亩。主要内容包括梯台修筑、梯田修筑、稻虾地块修筑、恢复地类整治、输水管道安装、排水沟修建、机耕道改建等。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>本项目资金来源为企业自筹，出资比例为100%。</t>
+          <t>项目总投资金额181.43万元，本次招标项目合同估算金额166.35万元，全部由财政资金支持。</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>污水处理设备、一体化设备、沉淀池、好氧池、竖流沉淀池、储药加药区、一体化危废储存间、污水处理配套设施</t>
+          <t>建筑工程施工</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>潼南区新胜镇、双江镇污水处理厂更新改造工程项目项目公告 潼南区新胜镇、双江镇污水处理厂更新改造工程比选公告 1. 比选条件 本比选项目潼南区新胜镇、双江镇污水处理厂更新改造工程，比选人为重庆环保投资集团有限公司，资金来源 为企业自筹，出资比例为100%。现对该项目进行公开比选，诚邀有兴趣的潜在参选人参与比选。 2. 项目概况与比选范围 网 2.1项目概况：潼南区新胜镇污水处理厂更新改造工程，主要建设内容为新增200m?/d一体化污水处理设备基础； 更新现有污水处理系统设备，提高现有沉淀池二沉池、三沉池液位；升级处理系统（干化池改建为污泥池，新 增叠螺脱水机，改建污泥堆场及雨棚）；新建风机房－配电室防尘防渗地坪。潼南区双江镇污水处理厂更新改 务 造工程，主要建设内容为将原有斜管沉淀池改建为好氧池，新建3座竖流沉淀池，配套安装相关设备；更新污水 处理系统中老旧及故障设备；新建储药加药区与一体化危废储存间，完善污水处理配套设施。 2.2 比选范围：潼南区新胜镇、双江镇污水处理厂更新改造工程施工图范围中的工作内容（一体化设备采购及 相关安装工作除外），包括但不限于土建工程、附属工程商（包括但不限于绿化工程、工艺管线工程、电气及自 控工程、临排清淤工程等）、一体化污水处理设备基础、标准化建设、配套设备材料采购及安装工程等内容， 其中一体化设备采购及相关安装工作不在本次比选范围内；具体以比选人提供的图纸、技术规范、工程量清单、 答疑资料、澄清资料、其他补遗资料等相关内容为准。 道 2.3 建设地点：潼南区新胜镇、双江镇。 2.4 工期：120日历天（实际开工日期以监理工程师签发的工程开工通知明确的开工日期为准），缺陷责任期24 个月。 管 3. 参选人资格要求 3.1 本次比选要求参选人具备以下条件： 国 （1）独立法人资格； （2）建设行政主管部门颁发的有效的市政公用工程施工总承包二级及以上资质； 中 3.2 参选人还应在资质、业绩、资金、人员等方面具有相应的服务能力，详见比选文件第二章参选人须知前附 表第1.4.1项内容。 3.3本次比选不接受联合体参选。 4. 比选文件的获取 4.1 参选人于2026年8月19日起可自行在重庆水务集团电子商务平台（https://www.cqswjt.cn）上下载比选文件电 子版，以及答疑、补遗等比选截止时间前公布的所有相关资料，不管参选人下载与否，比选人和代理机构都视 为参选人收到以上资料并全部知晓有关比选过程和事宜，如因参选人自身原因未能下载相关资料由此产生的一 切后果由参选人自行负责。各参选单位应随时关注网上（https://www.cqswjt.cn）发布的比选文件及相关修改内容。 4.2 参选人须在重庆水务集团电子商务平台（https://www.cqswjt.cn）进行供应商注册，填写相关信息，审批过后 成为平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标（仍须同时提交纸质版参选文件）。参选 人需提前在重庆水务集团电子商务平台（https://www.cqswjt.cn）上注册、报名，下载比选文件，上传参选文件电 子档并报价。在比选截止时间前未按时报名、报价并上传参选文件电子档、递交纸质版参选文件者，将被否决 参选。 5. 比选文件的递交 5.1 参选文件递交时间：2026年8月27日09时00分至09时30分，地点：重庆市两江新区嘉华路36号重庆水务大厦5 楼。 5.2 比选截止时间：2026年8月27日09时30分（北京时间）。 5.3 逾期送达的或者未送达指定地点的参选文件，比选人不予受理。 6. 发布比选公告的媒介 本次比选公告在重庆水务集团电子商务平台（https：//www.cqswjt.cn）上发布。 7. 联系方式 网 比选人：重庆环保投资集团有限公司 地 址：重庆市两江新区礼环南路102号 务 联系人：陈老师 电话：023-42756696 商 代理机构：重庆招标采购（集团）有限责任公司 道 地址：重庆市江北区五简路2号重庆咨询大厦A座2004室 联系人：高老师 管 电话：023-67706841 重庆水务电子商务平台国咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3076454.html cqdingjiu 2026.08.21 10:06:51 中</t>
+          <t>荣昌区2026年安富街道高标准农田建设项目招标公告 荣昌区2026年安富街道高标准农田建设项目招标公告 1.招标条件 1. 招标条件 本招标项目荣昌区2026年安富街道高标准农田建设项目已由重庆市荣昌区农业农村委员会以荣农发〔2026〕64号 批准建设，项目业主为重庆市荣昌区农田建设中心，建设资金来自 财政资金，项目出资比例为100%，招标人 为重庆市荣昌区农田建设中心。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用经评审 网 的最低投标价法。 2.项目概况与招标范围 2. 项目概况与招标范围 务 2.1 建设地点：安富街道斑竹村 2.2 项目概况与建设规模：改造提升高标准农田326.59亩，商其中高效节水灌溉面积130亩。 2.3 本项目工程总投资金额：181.43万元 本次招标项目合同估算金额：166.35万元 道 2.4 招标范围：梯台修筑127.5亩，梯田修筑61.56亩，稻虾地块修筑128.83亩，恢复地类整治1.22亩；新建Φ160PE 输水管道1949米，C25混凝土排水沟（0.5m*0.6m）320米；改建3.0m宽C25混凝土机耕道905米。包括所提供的施 工设计图所示范围内的所有内容，具体以招标人提供的图纸、工程量清单、答疑资料、澄清资料、其他补遗资 管 料等相关内容为准。若施工图与工程量清单不一致时，以工程量清单为准。 2.5 工期要求：工期为180日历天 ，缺陷责任期为24个月。 2.6 标段划分（如有）：国 / 2.7 其他： / 3.政府采购工程 中 3. 政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式：本项目整体面向中小企业。 4.投标人资格要求 4. 投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包三级及以 上资质或市政公用工程施工总承包三级及以上资质或水利水电工程施工总承包三级及以上资质。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（荣昌区）下载招标文件、 工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网（荣昌区）完成市场主体信息登 记以及CA数字证书办理，办理方式请参见重庆市公共资源交易网（荣昌区）导航栏“主体信息”页面中“市场 主体信息登记”、“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法 完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网（荣昌区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-26 17:30:00前。 网 5.3招标人应于2026-08-28 18:00:00前在重庆市公共资源交易网（荣昌区）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-16 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 务 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网（荣昌区）、重庆市公共资源交易监督网发布。[提示：依法必须招 商 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆市荣昌区农田建设中心 代理机构: 重庆富毅项目管理有限公司 地 址: 地道 址: 邮 编: 邮 编: 项目负责人: 李老师 项目负责人: 陈航 电 话: 023-85265043 管电 话: 16623666557 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 国开户银行: 账 号: 账 号: 监督部门: 重庆市荣昌区发展和改革委员会 中 电 话: 023-61471361 2026年08月21日 信息来源:https://www.chinapipe.net/project/d3077954.html cqdingjiu 2026.08.24 12:31:39</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>梯台修筑127.5亩，梯田修筑61.56亩，稻虾地块修筑128.83亩，恢复地类整治1.22亩；新建Φ160PE输水管道1949米，C25混凝土排水沟（0.5m*0.6m）320米；改建3.0m宽C25混凝土机耕道905米。</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 污水处理厂更新改造</t>
+          <t>高标准农田, 改造提升, 建筑工程施工, 财政资金, 重庆, 荣昌区</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表</t>
+          <t>大渡口区2025年老化燃气管道及设施更新改造项目(一期)EPC招标公告</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1918,7 +1898,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1937,30 +1917,34 @@
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>大渡口区</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>给重庆医科大学附属第二医院医疗教学配套业务用房配置第二市政水源</t>
+          <t>大渡口区燃气管线及燃气相关设施设备改造提升，实现燃气管线智能化管理和保障燃气供给安全。</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>采购预算 409674.71元</t>
+          <t>项目总投资金额7255.57万元，本次招标项目合同估算金额6408.986万元。</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>市政水源</t>
+          <t>燃气管道及相关设施设备</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表 重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程单一来源采购方式公示表 采购需求单位(全称) 重庆医科大学附属第二医院总务科 项目名称 重庆医科大学附属第二医院医疗教学配套业务用房第二市政水源工程 项目内容 给重庆医科大学附属第二医院医疗教学配套业务用房配置第二市政水源 采购预算 409674.71元 网 拟采购供应商全称 东部自来水分公司 配套业务用房第二市政水源从重庆水资源产业股份有限公司东部自来水分公司管辖范围 单一来源采购理由 的管网具体接入，属于市政管网施工，具有特殊要求。 务 公示时间 2026年8月19日-2026年8月25日 联系人及联系电话 刘老师 023-63693215 注：1.以上陈述是否真实，欢迎社会各界监督，公示时间商至少5个工作日； 2.公示期内无异议的，采购管理处将进行该项目采购；有异议请将意见反映采购人。 信息来源:https://www.chinapipe.net/project/d30道76334.html cqdingjiu 2026.08.21 10:06:51 管 国 中</t>
+          <t>大渡口区2025年老化燃气管道及设施更新改造项目(一期)EPC招标公告 大渡口区2025年老化燃气管道及设施更新改造项目（一期）EPC招标公告 1.招标条件 本招标项目 大渡口区2025年老化燃气管道及设施更新改造项目（一期） 已由 重庆市大渡口区发展和改革委 员会 以 渡发改审发〔2026〕19号 批准建设，项目业主为 重庆市大渡口区经济和信息化委员会 ，代建业 主为 重庆燃气集团股份有限公司大渡口分公司 ，建设资金来自 争取上级资金、区级财政配套及业主自 筹 ，项目出资比例为 100% ，招标人为 重庆燃气集团股份有限公司大渡口分公司 。项目已具备招标条 件，现对该项目的工程总承包进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：重庆市大渡口区 2.2 项目概况与建设规模：大渡口区燃气管线及燃气相关设施设备改造提升，实现燃气管线智能化管理和保障 燃气供给安全。其中，燃气管线智能化管理包含智能燃气系统设备1018台(套)、保障燃气供给安全包含居民立管 务 更换6443户、户外切断阀1500个、智能家用报警器5000套、户外表箱更换11024个、调压箱更换1025台、标志 桩(砖)10000块。 2.3 本项目工程总投资金额：7255.57万元 商 本次招标项目合同估算金额：6408.986万元，其中工程设计费125.526万元、建筑安装工程费4179.22万元、专业设 备材料类费用2104.24万元。 2.4 招标范围：主要包括施工图设计、工程施道工、设备供货等内容，具体范围为： （1）设计部分：本项目范围内的施工图设计、施工及竣工验收阶段、质量保修阶段的设计配合服务，以及协助 招标人完成审批手续办理等工作。按招标人要求按质按时提交设计成果，并取得国家相关职能部门的批准。 管 （2）施工部分：包括但不限于设计范围内所涉及的工作内容。 （3）设备供货：完成本项目设计范围内的专业设备材料供货、调试及质保。 （4）其他部分：项目国软件智能化工作、预算编制、总承包管理（对承包项目的质量、安全、工期、造价等全面 管控和负责）。 2.5 工期要求：总工期18个月，缺陷责任期24个月。其中： 中 设计周期：施工图设计 90 日历天；其他服务18个月； 专业设备材料到货时间、施工工期：15个月。 2.6 标段划分（如有）： / 2.7 其他：质量保质期：专业设备材料和软件质量保证期5年，国家对于三包产品质保期有规定的从其规定。 3.政府采购工程 3.1 是否属于政府采购工程：是 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式： 本项目以联合体形式面向中小企业，以联合体形式参加本次投标的，联合体中中小企业承担的合同份额需达 到 40 %以上。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件： 同时具备建设行政主管部门颁发的有效的以下资质： 4.1.1.1 设计资质：投标人应同时具备以下(1)、(2)项资质 (1)投标人应具备以下A、B、C项资质之一: A.工程设计综合甲级资质。 B.工程设计市政行业乙级及以上资质。 C.工程设计市政行业(城镇燃气工程)专业乙级及以上资质。 网 (2)具备《中华人民共和国特种设备设计许可证》(压力管道)公用管道GB1级或《中华人民共和国特种设备生产许 可证》(压力管道设计)公用管道GB1级。 务 4.1.1.2 施工资质：投标人应同时具备以下(1)、(2)项资质 (1)投标人应具备以下A、B项资质之一 A.具备建设行政主管部门颁发的有效的市政公用工程施工商总承包二级及以上资质。 B.具备建设行政主管部门颁发的有效的石油化工工程施工总承包三级及以上资质。 (2)具备有效的《中华人民共和国特种设备安装道改造维修许可证》公用管道GB1级或《中华人民共和国特种设备安 装改造修理许可证》公用管道GB1级或《中华人民共和国特种设备生产许可证》公用管道安装GB1级。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的实施能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 管 4.2 本次招标接受联合体投标。联合体投标的，应满足下列要求： 联合体成员单位不得超过3家，具体详见投 标人须知前附表1.4.2。 .技术成果经济补偿 本次招标对未中标人投国标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件、工程量清单 （如有）、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字 中 证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字 证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责 任自负。 5.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 布至2026-08-26 17:00:00前。 5.3招标人应于2026-08-28 23:59:59前在重庆市公共资源交易网发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-15 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网发布。[提示：依法必须招标项目的招 标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆燃气集团股份有限公司大渡口分公司 代理机构: 重庆市义渡工程管理有限公司 重庆市大渡口区春晖路街道翠华园小区11 重庆市大渡口区文体路126号锦天商务中 地 址: 地 址: 栋3层 心东楼535室 邮 编: 邮 编: 项目负责人: 任先生 项目负责人: 严力 电 话: 023-68551113 电 话: 023-85786930 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市大渡口区发展和改革委员会 电 话: 023-68083238 2026年08月21日 网 信息来源:https://www.chinapipe.net/project/d3077935.html cqdingjiu 2026.08.24 12:31:39 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>智能燃气系统设备1018台(套)，居民立管务更换6443户，户外切断阀1500个，智能家用报警器5000套，户外表箱更换11024个，调压箱更换1025台，标志桩(砖)10000块。</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -1968,14 +1952,14 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>重庆, 燃气管道, 老化改造, 智能化管理, 燃气供给安全</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>中铁二院工程集团有限责任公司G319黔江区正阳至城西段改建工程管线探测工作线上询价采购公告</t>
+          <t>国网重庆电力主城一片区2026年原集体企业和各级产业单位新增第三次物资区域联合授权物资框架协议公开谈判采购资格预审公告</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1985,7 +1969,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2004,29 +1988,25 @@
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>黔江区</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>本项目服务内容为G319黔江区正阳至城西段改建工程管线探测工作。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>管线探测工作</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>中铁二院工程集团有限责任公司G319黔江区正阳至城西段改建工程管线探测工作线上询价采购公告 中铁二院工程集团有限责任公司G319黔江区正阳至城西 段改建工程管线探测工作线上询价采购 ZTEYCQ-XJ-2026-019 网 采购单位: 中铁二院工程集团有限责任公司 发布时间: 2026-08-19 16:10 报价截止时间: 务 2026-08-21 17:00 招标方联系人: 杨先生 招标方联系电话: 商 13883021521 招标方邮箱: 监督方联系人: 李先生 道 监督方联系电话: 15823237919 监督方邮箱: 保证金: 0元 管 结算与发票信息: 详情 交货信息: 详情 国 其他说明事项: 标的明细 流水号：询2026081900304 中 计量单 技术标准及要 序号 标的名称 数量 交货期 送货地址 位 求 G319黔江区正阳至城西段 合同签订后5天内完成 西南区-重庆市-市辖 1 1 项 详见询价文件 改建工程管线探测工作 本项目服务内容。 区-黔江区-项目地点 信息来源:https://www.chinapipe.net/project/d3076309.html cqdingjiu 2026.08.21 10:06:51</t>
+          <t>国网重庆电力主城一片区2026年原集体企业和各级产业单位新增第三次物资区域联合授权物资框架协议公开谈判 采购资格预审公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3077904.html cqdingjiu 2026.08.24 12:31:39 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2035,18 +2015,18 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类, 匹配程度, 匹配关键词</t>
+          <t>重庆, 管材, 招标</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告</t>
+          <t>2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀采购项目(包1、包2)(第二次)招标公告</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2056,7 +2036,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2075,49 +2055,45 @@
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>涪陵区</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>本项目主要涉及室外蒸汽管道φ219x6mm的安装，管道材质为20#，地上敷设，蒸汽管道运行压力1.08MPa，管道设计压力1.2MPa。蒸汽管道系统包括从锅炉房分汽缸到6#和8#车间分汽缸的所有蒸汽管道、管件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸等的采购、运输、安装、保温工作。还包括钢结构桁架工程的采购、运输、制作、安装、防腐工作，以及管道附件及控制系统的采购、运输、安装、接线等工作。此外，还需要进行调试与验收，确保蒸汽管道系统能够正常使用并备案。</t>
+          <t>为重庆分质供水有限公司提供不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀等设备材料。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>项目总投资额为580.643717万元，全部为企业自筹资金。</t>
+          <t>每个包合同暂估金额为110万。</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>蒸汽管道、管件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸、钢结构桁架、阀门、压力表、温度表、流量计、电动/气动执行机构、配套仪表电缆、桥架、保护管</t>
+          <t>不锈钢可调式减压阀,不锈钢静音式止回阀,不锈钢微量排气阀,不锈钢闸阀,不锈钢表前阀,不锈钢球阀,Y型过滤器</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告 乌江涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程招标公告 1.招标条件 本招标项目乌江涪陵榨菜绿色智能化生产基地(一期)已由重庆市涪陵区发展和改革委员会以重庆市企业投资项目 备案证2020-500102-13-03-000003 批准建设，项目业主为重庆市涪陵榨菜集团股份有限公司，建设资金来自企业 自筹，项目出资比例为100% ，招标人为重庆市涪陵榨菜集团股份有限公司。项目已具备招标条件，现对乌江 涪陵榨菜绿色智能化生产基地(一期)6#、8#车间蒸汽管道安装工程施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 2.1 建设地点： 重庆市涪陵区马鞍街道人和社区 。 网 2.2 项目概况与建设规模：建筑面积约369384.27㎡。本项目蒸汽管道主要为室外蒸汽管道φ219x6mm，管道材质： 20#地上敷设，由14#锅炉房分汽缸分别接至6#和8#智能化车间分汽缸，蒸汽管道运行压力1.08MPa，管道设计压 力1.2MPa。 务 2.3 本次招标项目合同估算金额：580.643717万元。 2.4 招标范围： 商 （1）蒸汽管道系统本体：从锅炉房分汽缸后（含分气缸阀门）至6#车间、8#车间分气缸处，所有蒸汽管道、管 件、法兰、螺栓垫片、管道支吊架、补偿器、疏水阀组、分气缸等的采购、运输、安装、保温（含保温层及保 护层）工作。 道 （2）钢结构桁架工程：负责本项目范围内所有钢结构架空桁架（管廊）的采购、运输、制作、安装、防腐工作。 （3）管道附件及控制系统：负责本工程范围内所有阀门、压力表、温度表、流量计、电动/气动执行机构以及配 套仪表电缆、桥架、保护管的采购、运输、安装、接线。负责与DCS/PLC系统接口的接线与联动调试。 管 （4）调试与验收：组织并确保整个蒸汽管道系统（含分气缸后段末端管道、桁架及其安全附件）通过项目所在 地特种设备安全监察管理部门实施的安装监督检验。负责报检、配合现场检验、整改、出具深化图纸并由设计 单位审核盖章、特种设备法定报检取证的全部费用，包括但不限于：施工前办理安装告知，设计院盖章审核， 施工中接受并通过安装国监督检验，最终负责取得《压力管道安装监督检验证书》与《特种设备使用登记证》， 确保蒸汽管道投入使用并备案，提交全套法定检验报告。 （5）土建工作部分 中 1）管架和桁架基础的施工，包括但不限于钢结构桁架的混凝土独立基础的土方开挖、浇筑、养护及回填恢复。 2）管道穿墙/板孔洞的开挖、封堵与修复。 3）室内外地面的开挖（包括但不限于疏水井、沟槽开挖、通行地沟、设备基础开挖）与恢复（包括但不限于土 方回填、渣土弃运、地面硬化）。 4）桁架及设备接地线的施工，包括但不限于接地极制作、接地干线敷设，并与厂区主接地网可靠连接，接地电 阻测试合格。 具体详见施工图、招标文件、工程量清单、答疑补遗等资料。 2.5 工期要求： 60 日历天 缺陷责任期要求： 24 个月 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：投标人应同时具备以下(1)、(2)项资质： （1）具备建设行政主管部门颁发的有效的建筑工程施工总承包二级及以上资质； （2）具备有效的《中华人民共和国特种设备生产许可证》（许可子项目：工业管道安装GC2级及以上）。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 网 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 务 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（涪陵区） （https://www.cqggzy.com/fulingweb/）下载招标文件、工程商量清单、电子图纸等资料。参与投标的投标人需在重 庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏 “主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网（涪陵区道）（https://www.cqggzy.com/fulingweb/）本项目招标公告网页下 方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-23 17:00:00前。 4.3招标人应于2026-08-24 18:00:00前在重庆市公共资源交易网（涪陵区）（https://www.cqggzy.com/fulingweb/）发 布澄清。 5.投标文件递交的内容 管 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-09 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 国 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（涪陵区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 中重庆市涪陵榨菜集团股份有限公司 代理机构: 中招国际招标有限公司 重庆两江新区黄山大道中段53号5-1（双 地 址: 重庆市涪陵区江北街道办事处二渡村一组 地 址: 鱼座A栋5楼） 邮 编: 408000 邮 编: 项目负责人: 徐老师 项目负责人: 寿云凤 电 话: 13212467016 电 话: 023-68881331-9032 传 真: 传 真: 电子邮箱: bsd2me@126.com 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市涪陵区发展和改革委员会 电 话: 023-72203687 2026年08月19日 乌江 涪陵 榨菜 绿色 智能 化生 产基地 (一 期)6#、 8#车 网 间蒸 汽管 道安 装工 务 程 中 中 国 国 重 银 重 商民 重 庆 行 庆 生 庆 涪 股 涪 银 涪 陵 份 陵 行 陵 重 投 公 有 道公 股 公 庆 标 共 限 共 份 共 银 开 保 户 资 公 资 有 资 行 户 证 110292140553VA00154 9902001860445897 430102029007791845-275 名 源 司 源 限 源 涪 行 金 交 重 交 公 交 陵 账 管 易 庆 易 司 易 支 号 有 涪 有 重 有 行 限 陵 限 庆 限 公 马 公 涪 公 国 司 鞍 司 陵 司 支 支 行 行 中 信息来源:https://www.chinapipe.net/project/d3076300.html cqdingjiu 2026.08.21 10:06:51</t>
+          <t>2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀采购 项目(包1、包2)(第二次)招标公告 2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀采购 项目（包1、包2）（第二次）招标公告 1.招标条件 网 本招标项目2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢 止回阀采购项目（包1、包2）（第二次）（项目名称），招标人为重庆分质供水有限公司，招标项目资金来自企 业自筹（资金来源），项目已具备招标条件。现对本项目进行公开招标，诚邀有兴趣的潜在投标人参与投标。 务 2.项目概况与招标范围 2.1项目地点：招标人指定地点。 2.2项目概况：为重庆分质供水有限公司提供不锈钢闸阀、商不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈 钢止回阀等设备材料。 不锈钢类阀门按统一下浮比例进行报价（具体规格见招标文件第五章“供货要求”）。 道 注：①投标人可以任意选择1个或2个分包进行投标，但是同一个投标人只能中标一个分包，当同一个投标人同时 在2个分包中被评审确定为第一中标候选人的，则按照包1、包2的顺序，确定其为第一中标候选人，在其他分包 中不再被确定为中标候选人，按评审结果排序依次递补中标候选人。 管 ②投标人根据参投分包分别制作投标文件、分别填写投标文件中的项目名称，如下： 包1项目分包名称：2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、 不锈钢止回阀采购项目（包1）（第二次）； 国 包2项目分包名称：2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、 不锈钢止回阀采购项目（包2）（第二次）。 每个包合同暂估金额为110万（注：超出合同服务期或合同期间结算金额达到合同暂估金额时，合同自动终止)。 中 供货区域分别为： 包1：北区（涉及区域两江新区、沙坪坝区、北碚区及其他区县，区域可根据甲方工程需求调整）及重庆分质供 水有限公司市外所有项目。 包2：.南区（涉及区域渝中区、南岸区、巴南区、九龙坡区、大渡口区及其他区县，区域可根据甲方工程需求调 整）及重庆分质供水有限公司市外所有项目。 2.3招标范围：为重庆分质供水有限公司提供不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈 钢止回阀等设备材料 2.4货物清单 序号 名称 规格型号 压力等级 单位 备注 1 不锈钢可调式减压阀 DN15 1.6MPa 件 带压力表 2 不锈钢可调式减压阀 DN20 1.6MPa 件 带压力表 3 不锈钢可调式减压阀 DN25 1.6MPa 件 带压力表；提供样品一个 4 不锈钢可调式减压阀 DN32 1.6MPa 件 带压力表 5 不锈钢可调式减压阀 DN40 1.6MPa 件 带压力表 6 不锈钢可调式减压阀 DN50 1.6MPa 件 带压力表 7 不锈钢可调式减压阀 DN65 1.6MPa 件 带压力表 8 不锈钢可调式减压阀 DN80 1.6MPa 件 带压力表 9 不锈钢可调式减压阀 DN100 1.6MPa 件 带压力表 10 不锈钢静音式止回阀 DN15 1.6MPa 件 带压力表；含不锈钢螺栓 11 不锈钢静音式止回阀 DN15 2.5MPa 件 带压力表；含不锈钢螺栓 网 12 不锈钢静音式止回阀 DN20 1.6MPa 件 带压力表；含不锈钢螺栓 13 不锈钢静音式止回阀 DN20 2.5MPa 件 带压力表；含不锈钢螺栓 14 不锈钢静音式止回阀 DN25 1.6MPa 件 带压力表；含不锈钢螺栓 务 15 不锈钢静音式止回阀 DN25 2.5MPa 件 带压力表；含不锈钢螺栓 16 不锈钢静音式止回阀 DN32 1.6MPa 件 带压力表；含不锈钢螺栓 17 不锈钢静音式止回阀 DN32 2.5MPa 件 带压力表；含不锈钢螺栓 商 18 不锈钢静音式止回阀 DN40 1.6MPa 件 带压力表；含不锈钢螺栓 19 不锈钢静音式止回阀 DN40 2.5MPa 件 带压力表；含不锈钢螺栓 20 不锈钢静音式止回阀 DN50 1.6MPa 件 带压力表；含不锈钢螺栓 道 21 不锈钢静音式止回阀 DN50 2.5MPa 件 带压力表；含不锈钢螺栓 22 不锈钢静音式止回阀 DN65 1.6MPa 件 带压力表；含不锈钢螺栓 23 不锈钢静音式止回阀 DN65 2.5MPa 件 带压力表；含不锈钢螺栓 管 24 不锈钢静音式止回阀 DN80 1.6MPa 件 带压力表；含不锈钢螺栓 25 不锈钢静音式止回阀 DN80 2.5MPa 件 带压力表；含不锈钢螺栓 26 不锈钢静音式止回阀 DN100 1.6MPa 件 带压力表；含不锈钢螺栓 国 27 不锈钢静音式止回阀 DN100 2.5MPa 件 带压力表；含不锈钢螺栓 28 不锈钢微量排气阀 DN15 1.6MPa 件 29 不锈钢微量排气阀 DN20 1.6MPa 件 中 30 不锈钢微量排气阀 DN25 1.6MPa 件 31 不锈钢微量排气阀 DN32 1.6MPa 件 32 不锈钢微量排气阀 DN40 1.6MPa 件 33 不锈钢微量排气阀 DN50 1.6MPa 件 34 不锈钢闸阀 DN15 1.6MPa 件 35 不锈钢闸阀 DN20 1.6MPa 件 36 不锈钢闸阀 DN25 1.6MPa 件 37 不锈钢闸阀 DN25 2.5MPa 件 38 不锈钢闸阀 DN32 1.6MPa 件 39 不锈钢闸阀 DN32 2.5MPa 件 40 不锈钢闸阀 DN40 1.6MPa 件 41 不锈钢闸阀 DN40 2.5MPa 件 42 不锈钢闸阀 DN50 1.6MPa 件 43 不锈钢闸阀 DN50 2.5MPa 件 44 不锈钢闸阀 DN65 1.6MPa 件 含不锈钢螺栓 45 不锈钢闸阀 DN65 2.5MPa 件 含不锈钢螺栓 46 不锈钢闸阀 DN80 1.6MPa 件 含不锈钢螺栓 47 不锈钢闸阀 DN80 2.5MPa 件 含不锈钢螺栓 48 不锈钢闸阀 DN100 1.6MPa 件 含不锈钢螺栓 49 不锈钢闸阀 DN100 2.5MPa 件 含不锈钢螺栓 50 不锈钢表前阀 DN15 1.6MPa 件 51 不锈钢表前阀 DN20 1.6MPa 件 52 不锈钢表前阀 DN25 1.6MPa 件 网 53 不锈钢表前阀 DN40 1.6MPa 件 54 不锈钢表前阀 DN50 1.6MPa 件 55 不锈钢表前阀 DN65 1.6MPa 件 务 56 不锈钢表前阀 DN80 1.6MPa 件 57 不锈钢表前阀 DN100 1.6MPa 件 58 不锈钢球阀 DN15 1.6MPa 件 商 59 不锈钢球阀 DN20 1.6MPa 件 60 不锈钢球阀 DN25 1.6MPa 件 61 不锈钢球阀 DN32 1.6MPa 件 道 62 不锈钢球阀 DN40 1.6MPa 件 63 不锈钢球阀 DN50 1.6MPa 件 64 不锈钢球阀 DN65 1.6MPa 件 管 65 Y型过滤器 DN15 1.6MPa 件 66 Y型过滤器 DN15 2.5MPa 件 67 Y型过滤器 DN20 1.6MPa 件 国 68 Y型过滤器 DN20 2.5MPa 件 69 Y型过滤器 DN25 1.6MPa 件 70 Y型过滤器 DN25 2.5MPa 件 中 71 Y型过滤器 DN32 1.6MPa 件 72 Y型过滤器 DN32 2.5MPa 件 73 Y型过滤器 DN40 1.6MPa 件 74 Y型过滤器 DN40 2.5MPa 件 75 Y型过滤器 DN50 1.6MPa 件 76 Y型过滤器 DN50 2.5MPa 件 77 Y型过滤器 DN65 1.6MPa 件 78 Y型过滤器 DN65 2.5MPa 件 2.5 交货地点：招标人指定地点。 2.6 交货期：按业主要求进行供货。合同生效之日起2年或达到合同暂估金额时，合同自行终止。 2.7其他： 2.7.1投标人须按照采购清单要求提供相应型号数量的样品，投标样品须密封装箱，且在密封包装外贴样品一览表 （格式自拟），注明提供样品的投标人名称、生产厂家、品牌、名称、型号、数量等； 2.7.2每件样品上必须分别标明样品的投标人、生产厂家、品牌、名称、型号等（格式自拟），开标时同投标文件 一起提交，由评标委员会核验（提交地点见开标当日交易中心大厅展牌）。本项目第一中标候选人的样品不退还 （第二、三名中标候选人样品在中标通知书发出后5个工作日内退还），其余投标人的样品在评标结束后半小时 内当场退还，如不领取，自行负责。 2.7.3上述要求除递交的样品型号数量应相符外，其余不作为废标的条款，但投标人应主动配合按此要求进行递交。 3.投标人资格要求 3.1 投标人必须是按照国家法律法规设立的，并在中国注册的，具有法人地位的企业；投标人为投标货物的制造 网 商、代理商或经销商。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表 第1.4.1项内容。 务 3.3本次招标不接受联合体投标。 4.招标文件的获取 商 4.1 本项目招标不需报名，凡有意参加投标者，请于2026年8月21日起在重庆市公共资源交易网 （www.cqggzy.com）下载本招标项目的招标文件等投标截止时间前公布的所有相关资料，不管投标人下载与否， 招标人和招标代理机构都视为投标人收到以上资料并全部知晓有关招标过程和事宜，由此产生的一切后果由投 标人自负。 道 4.2、招标文件每份售价1000元，售后不退。投标单位在递交投标文件时通过扫描二维码方式支付购买招标文件 的费用，否则招标人和招标代理机构拒绝接收其投标文件。 管 5.投标文件的递交 5.1、投标文件递交的截止时间（投标截止时间，下同）为2026年9月14日11时00分（北京时间）前，地点为重庆 市渝北区青枫北路6号渝兴广场B10栋2层重庆市公共资源交易中心开标厅（具体房间见开标当天大厅展牌）。 国 5.2、逾期送达的、未送达指定地点的或者不按照招标文件要求密封的投标文件，招标人将予以拒收。 6.发布公告的媒介 中 本次招标公告在重庆市公共资源交易网(www.cqggzy.com)上发布。 7.联系方式 招 标 人：重庆分质供水有限公司 地 址：重庆市两江新区水务大厦 联 系 人：张老师 电 话：17783738201 招标代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市两江新区嘉华路36号水务大厦 联 系 人：罗辑 电 话：18223151922（工作时间9:00-12:00；14：00-17:00其余时间请勿致电） 2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀采 购项目（包1）（第二次） 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公 中国民生银行股份有限公司重庆分 9902001764108013 司 行 重庆联合产权交易所集团股份有限公 重庆农村商业银行股份有限公司沙 0304010120010028835008268 司 坪坝支行 重庆联合产权交易所集团股份有限公 网 重庆三峡银行九龙坡支行 9696801051298012 司 重庆联合产权交易所集团股份有限公 中信银行重庆上清寺支行 3111230034020042416 司 务 重庆联合产权交易所集团股份有限公 中国农业银行股份有限公司重庆自 312601010400083780000005565 司 由贸易试验区分行 重庆联合产权交易所集团股份有限公 招商银行股份有限公司重庆分行 123904808710630019269 司 商 重庆联合产权交易所集团股份有限公 中国建设银行股份有限公司重庆渝 6232813760000632694 司 中支行 重庆联合产权交易所集团股份有限公 重庆道银行股份有限公司七星岗支行 15010202900420146618927 司 信息来源:https://www.chinapipe.net/project/d3077898.html cqdingjiu 2026.08.24 12:31:39 管 国 中</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>蒸汽管道：1.08M</t>
+          <t>DN15 1.6MPa 件 带压力表,DN20 1.6MPa 件 带压力表,DN25 1.6MPa 件 带压力表；提供样品一个,DN32 1.6MPa 件 带压力表,DN40 1.6MPa 件 带压力表,DN50 1.6MPa 件 带压力表,DN65 1.6MPa 件 带压力表,DN80 1.6MPa 件 带压力表,DN100 1.6MPa 件 带压力表,DN15 2.5MPa 件 带压力表；含不锈钢螺栓,DN20 2.5MPa 件 带压力表；含不锈钢螺栓,DN25 2.5MPa 件 带压力表；含不锈钢螺栓,DN32 2.5MPa 件 带压力表；含不锈钢螺栓,DN40 2.5MPa 件 带压力表；含不锈钢螺栓,DN50 2.5MPa 件 带压力表；含不锈钢螺栓,DN65 2.5MPa 件 带压力表；含不锈钢螺栓,DN80 2.5MPa 件 带压力表；含不锈钢螺栓,DN100 2.5MPa 件 带压力表；含不锈钢螺栓,DN15 1.6MPa 件,DN20 1.6MPa 件,DN25 1.6MPa 件,DN25 2.5MPa 件,DN32 1.6MPa 件,DN32 2.5MPa 件,DN40 1.6MPa 件,DN40 2.5MPa 件,DN50 1.6MPa 件,DN50 2.5MPa 件,DN65 1.6MPa 件 含不锈钢螺栓,DN65 2.5MPa 件 含不锈钢螺栓,DN80 1.6MPa 件 含不锈钢螺栓,DN80 2.5MPa 件 含不锈钢螺栓,DN100 1.6MPa 件 含不锈钢螺栓,DN100 2.5MPa 件 含不锈钢螺栓,DN15 1.6MPa 件,DN20 1.6MPa 件,DN25 1.6MPa 件,DN40 1.6MPa 件,DN50 1.6MPa 件,DN65 1.6MPa 件,DN80 1.6MPa 件,DN100 1.6MPa 件,DN15 1.6MPa 件,DN20 1.6MPa 件,DN25 1.6MPa 件,DN32 1.6MPa 件,DN40 1.6MPa 件,DN50 1.6MPa 件,DN65 1.6MPa 件,DN80 1.6MPa 件,DN100 1.6MPa 件</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>重庆, 蒸汽管道, 安装工程, 资金情况, 产品种类</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程询比采购公告</t>
+          <t>龙兴新城污水管网工程建设及整治修复项目(二期)招标计划表</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2127,7 +2103,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2146,29 +2122,25 @@
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>巴南区</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>完成重庆国际生物城配套公寓项目（民用1020户）天然气表后管道定制化服务。（含安装燃气输送用不锈钢波纹管RSB-IF-13—12240米（预估）、双外螺纹球阀DN15-1020个、燃气管道自闭阀DN15-1020个，其它配套管件及辅材，墙体管道暗埋等）</t>
+          <t>管网工程、土石方工程等。</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>合同预估金额为2500万元</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>天然气表后管道定制化服务</t>
+          <t>管网工程、土石方工程</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>重庆巴南天然气有限责任公司重庆国际生物城配套公寓项目天然气表后管道安装工程询比采购公告 采购公告 公告编号： RQXYGG202608190057 一、采购项目基本情况 采购人：重庆巴南天然气有限责任公司 网 采购项目编号：RQCGXY202608170010 采购项目名称：重庆国际生物城配套公寓项目天然气表后管道安装工程 务 采购内容和范围：完成重庆国际生物城配套公寓项目 （民用1020户）天然气表后管道定制化服务。（含安装燃 气输送用不锈钢波纹管RSB-IF-13—12240米（预估）、双外螺纹球阀DN15-1020个、燃气管道自闭阀DN15-1020个， 其它配套管件及辅材，墙体管道暗埋等） 二、供应商资格要求 商 1. 资质要求:资质要求： 1.响应供应商为中华人民共和国境内合法注册的独立法人或其他组织，具有独立承担民事责任能力，具有独立订 立合同的权利。 道 2.响应供应商应具备市政公用工程施工总承包三级及以上资质、具备有效的安全生产许可证。 3.响应供应商应为本项目配备项目负责人一名，持有市政公用工程或机电工程专业二级建造师及以上资质，且为 本单位在职人员并提供社保证明。 4.响应供应商应为本项目配备专职安全员一名，持有安全生产考核合格C证，且为本单位在职人员并提供社保证 管 明。 5.项目负责人及专职安全员社保证明期限须包含2026年5月至2026年7月。提供的社保证明，须体现上述人员的姓 名、身份证号（或社保号）、单位名称、本单位参保时间（或起始参保时间），并带有社保部门公章或社保部 门的有效电子印章。 2. 信用要求:6.信用要求国： （1）响应供应商（含联合体响应的成员单位）未被“国家企业信用信息公示系统” 网站（www.gsxt.gov.cn）列 入严重违法失信企业名单（如：提供网站查询界面截图）； （2）响应供应商（含联合体响应的成员单位）未被 “信用中国”网站（www.creditchina.gov.cn）列入严重失信 主体名单（中如：提供网站查询界面截图）。 三、采购文件的获取 采购文件在 华润守正采购交易平台 发布，不再另行线下提供纸质采购文件，凡有意参与者请自行登录守正平台 查看和下载采购文件。 四、响应文件的提交 响应文件提交 / 报价截止时间： 2026-08-25 08:00:00 （北京时间，若有变化另行通知）。 响应文件提交 / 报价方式：在响应文件提交 / 报价截止时间前，通过 华润守正采购交易平台 提交电子响应文件或 报价，逾期提交将被拒收。 五、采购人联系方式 联系人：何俊 电话：15178855716 邮箱：1460553040@qq.com 六、采购明细 行号 采购内容 需求数量 单位 补充说明 1 重庆国际生物城配套公寓项目天然气表后管道定制化服务 1 元/次 具体内容详见采购文件 七、答疑澄清、通知 答疑澄清、通知等文件一经在 华润守正采购交易平台 发布，视为已发放给相应供应商（发放时间即为发出时 间），请随时关注 华润守正采购交易平台 发布的相关信息，并及时查阅和处理。 八、服务费交纳 网 本项目向成交人收取服务费,供应商收到预成交通知书和服务费交款通知书10日内,向平台运营方(华润守正招标有 限公司)支付服务费,经确认无误后由采购人发送成交通知书。平台运营方在收到服务费后向成交人开具服务费发 票。 收费标准：项目总成交金额＜50万元的采购项目，免收服务费。项目总成交金额≥50万元的采购项目，按成交金 务 额的0.15%向成交人收取（金额四舍五入，精确到分）。单项目总收费封顶100000元。其他说明：（1）总价采购， 收费基数为成交金额；单价、费率采购，收费基数为预算金额。（2）单项目存在多个成交人情形的，按总成交 金额计算收费总额，各成交人按成交比例分摊；项目总成交金额50万以上，但单个成交人成交金额少于50万仍按 比例收取服务费。 商 退款说明：成交通知书发布后,平台提供相关服务已完成,成交人已交纳服务费不予退还。 多成交人服务费收取示例： 以某项目总成交金额100万为例,A、B、C多成交人情形,总服务费为0.15万, 供应商A成交金额为50万,A服务费为0.075万; 供应商B成交金额为30万,B服务费为0.045万; 道 供应商C成交金额为20万,C服务费为0.03万。 九、其它事项 管 1.本公告在 华润守正采购交易平台 ( https://www.szecp.com.cn/ )上公开发布。 2.本项目采购通过守正平台线上进行，供应商需注册 华润守正采购交易平台 ，通过平台进行响应文件的递交或 报价，具体操作步骤可查阅网站首页帮助中心的操作手册，也可以联系守正客服。 国 3.如对采购项目有异议，请登录 华润守正采购交易平台 ,通过异议菜单提出。 2026年08月19日 中 信息来源:https://www.chinapipe.net/project/d3076125.html cqdingjiu 2026.08.21 10:06:52</t>
+          <t>龙兴新城污水管网工程建设及整治修复项目(二期)招标计划表 重庆市工程建设项目招标计划表 项目名称 龙兴新城污水管网工程建设及整治修复项目（二期） 招标法人或招标 重庆两江新区龙兴新城建设投资有限公司 人名称（盖章） 网 项目批准文件及 文号 主要建设内容 主要建设内容管网工程、土石方工程等。 务 招标方 招标文件计划 拟交易场 合同预估金额 序号 招标项目名称 招标内容 备注 式 发布时间 所 (万元) 龙兴新城污水 招标项目 主要建设内容 重庆市公 管网工程建设 商公开招 1 管网工程、土 2026-09 共资源交 2500.00 及整治修复项目 标 石方工程等。 易中心 （二期） 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 道 信息来源:https://www.chinapipe.net/project/d3077891.html cqdingjiu 2026.08.24 12:31:40 管 国 中</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2181,14 +2153,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>重庆, 天然气表后管道安装工程, 管材招标</t>
+          <t>重庆, 污水管网工程, 二期, 管网工程, 土石方工程, 2500万元</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)非金属管道管件阀门采购招标公告</t>
+          <t>李市镇农村饮水管网改建工程竞争性磋商公告</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2198,7 +2170,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2217,25 +2189,29 @@
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>江津区</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>重庆市映天辉氯碱化工有限公司拟开展废盐综合利用联产20万吨/年离子膜烧碱项目(一期12万吨/年)建设。</t>
+          <t>李市镇农村饮水管网改建工程</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>项目资金来自业主自筹，项目出资比例为100%。本次招标项目货物采购估算金额约为330万元。</t>
+          <t>预算金额：1,653,882.29元</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>非金属管道管件阀门</t>
+          <t>水管</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)非金属管道管件阀门采购招标公告 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采购招标公告 1、招标条件 本招标项目废盐综合利用联产20万吨/年离子膜烧碱项目已由重庆市长寿区发展和改革委员会以 重庆市企业投 资项目备案证（2207-500115-04-05-168305）批准建设，项目业主为重庆市映天辉氯碱化工有限公司，建设资金来 自业主自筹，项目出资比例为100%，招标人为重庆市映天辉氯碱化工有限公司。项目已具备招标条件，现对本 项目的（一期12万吨/年）非金属管道管件阀门采购进行公开招标。 网 2、项目概况 2.1 建设地点：重庆长寿经济技术开发区化北路2号。 务 2.2、项目概况与建设规模： 重庆市映天辉氯碱化工有限公司（以下简称“映天辉”）位于重庆长寿经济技术开发区化北路2号，始建于2004 年5月，占地430亩，注册资本34800万元。现为国有控股企商业，是一家集氯碱生产经营、新材料研发经营于一体 的专业型、科技型综合企业，系国家级高新技术企业。 映天辉作为长寿经开区氯碱产业基础平台的龙头化工企业，现有一条氯碱生产线，生产规模为20万吨/年烧碱 （折100%NaOH计）。为建设并贯通氯碱化工道循环经济产业链，保障下游产业链装置氯气需求，实现氯碱产品的 升级和高端化发展，增加产品附加值，降低成本，提高竞争力，映天辉公司经过充分调研和反复论证后，拟开 展废盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）建设。装置在正常运行情况下，按照每年 8000 小时操作。具体要求及参数以第五章货物需求一览表及技术规格标准和要求为准。 管 2.3 本次招标项目货物采购估算金额： 约 330 万元。 2.4招标范围： 本次招标项目为：“废国盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采 购”包括不限于非金属管道管件阀门所含设计、制造、试验、出厂检验、防腐、运输（含保护、包装及运输、 货到现场车板交货）、保险（交货验收前）、指导安装、调试、备件及专用工具、税费、技术资料和图纸及质 保期内的各种备品、备件的供应及相关的技术服务、产品质量证明书及原材料检测报告等。（详见“第五章货 物需求一览中表及技术规格标准和要求”）。 2.5 交货地点：货物运送至买方指定地点； 2.6 交货期： 2.6.1合同签订后3个月内，所有货物运送招标人现场并具备安装条件。 2.6.2 中标方应于合同签订之日起7天内，向买方提交完整的技术资料，以供设计院开展相关设计工作。 3、投标人资格要求 3.1 投标人应符合以下要求： （1）投标人具备有效的营业执照。 注：不得将投标人营业执照记载的经营范围作为评审因素。 （2）投标人具备有效的《中华人民共和国特种设备生产许可证》压力管道管子-B级及以上资质、压力管道管 件B2级及以上资质； （3）投标人具备塑料管道管子、管件的型式试验证书。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3本次招标不接受代理商投标，不接受联合体投标。 4. 招标文件的获取 4.1 凡愿意参加的潜在投标人，从2026年 8 月19 日起至投标截止时间前，均可登录重庆市公共资源交易网 （www.cqggzy.com）直接下载获取招标文件、答疑等开标前的有关资料。在公告期间，各投标人应随时关注网上 发布的招标文件答疑、补遗、澄清等文件内容，不管投标人是否下载，均视为已知晓招标文件的全部内容和有 关事宜。本项目不需要报名，直接投标。 网 5.投标文件的递交 5.1 投标文件递交的截止时间为 2026年 9 月10 日上午09时30分，地点在重庆市公共资源交易中心开标厅（地 址：重庆市两江新区青枫北路6号渝兴广场B10栋2层），具体开标地点详见一、二楼大厅显示屏。 务 5.2逾期送达的或者未送达指定地点的，或者未按照招标文件要求密封的投标文件，招标人将拒收。 6、发布公告的媒介 商 本次招标公告在中国招标投标公共服务平台、重庆市公共资源交易网上发布。 7、联系方式 道 招 标 人：重庆市映天辉氯碱化工有限公司 地 址：重庆长寿经济技术开发区化北路二号 管 联 系 人：张先生 电 话：023-40717888 国 招标代理机构： 重庆招标采购（集团）有限责任公司 地 址：重庆市两江新区五里店五简路2号重庆咨询大厦A栋20楼2001室 中 项目负责人：彭文婷 电 话： 023-67703002 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）非金属管道管件阀门采购 户名 开户行 投标保证金账号 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000631258 支行 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051303372 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630010400 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000002549 贸易试验区分行 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835014652 坝支行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146619529 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764260665 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020038958 信息来源:https://www.chinapipe.net/project/d3076119.html cqdingjiu 2026.08.21 10:06:52 网 务 商 道 管 国 中</t>
+          <t>李市镇农村饮水管网改建工程竞争性磋商公告 本项目保证金支持电子投标保函形式，如需申请保函请点击右上角“申请投标保函” 项目概况： “李市镇农村饮水管网改建工程”项目的潜在供应商应在“网上获取”获取采购文件，并于 2026年9月1日 10:00 （北京时间）前递交响应文件。 一、项目基本情况 网 项目号：JJQ26B00032 项目名称：李市镇农村饮水管网改建工程 务 采购方式：竞争性磋商 预算金额：1,653,882.29元 商 最高限价：1,653,882.29元 采购需求： 包号：1 道 包内容 最高限价 数量 单位 简要技术要求 李市镇农村饮水管网改建工程 1,653,882.29元 1 项 详见竞争性磋商文件。 最高限价总计：1,653,882.29元 管 合同履行期限：详见竞争性磋商文件。 本项目是否接受联合体：否 国 二、申请人的资格要求 1、满足《中华人民共和国政府采购法》第二十二条规定。 中 2、落实政府采购政策需满足的资格要求： 本项目专门面向中小企业采购，承建企业应为中小微企业（提供中小企业声明函）或监狱企业（提供监狱企业 证明文件）或残疾人福利性单位（提供残疾人福利性单位声明函）。 注： ①“中小企业声明函”应由供应商出具，并加盖供应商公章，声明函格式详见本竞争性磋商文件第七篇“中小 企业声明函”； ②“监狱企业证明文件”应当由供应商（承建企业）提供其属于监狱企业的证明文件，该证明文件由省级以上 监狱管理局、戒毒管理局（含新疆生产建设兵团）出具； ③“残疾人福利性单位声明函”应由供应商（承建企业）提供其出具的“残疾人福利性单位声明函”，并加盖 该残疾人福利性单位公章。 3、本项目的特定资格要求： ①供应商具备建设行政主管部门颁发的有效的水利水电工程施工总承包叁级及以上资质。（响应文件中提供有 效的证书复印件并加盖供应商公章） ②供应商具备建设行政主管部门颁发的有效的安全生产许可证。（响应文件中提供有效的安全生产许可证复印 件并加盖供应商公章） 三、获取竞争性磋商文件的地点、方式、期限及售价 获取文件期限：2026年8月21日 至 2026年8月28日。 每天上午09:00:00至12:00:00，下午12:00:00至17:00:00。（北京时间，法定节假日除外 ） 文件购买费:0.00元/包 获取文件地点：网上获取 方式或事项： 网 （一）供应商应通过重庆市政府采购网（www.ccgp-chongqing.gov.cn）登记加入“重庆市政府采购供应商库”。 务 （二）磋商文件获取方式：凡有意参加磋商的供应商，请到“重庆市政府采购网”→“个人中心”→“在线开 评标”→“电子标书在线获取”处在线下载或获取本项目磋商文件以及图纸、澄清等磋商前公布的所有项目资料 （本次不提供纸质版磋商文件），无论供应商下载或获取与否，均视为已知晓所有磋商内容。磋商文件获取期 限：自公告发布之日起五个工作日。 商 （三）采购公告所附磋商文件仅供阅览使用，供应商只有登录“重庆市政府采购网”→“个人中心”→“在线 开评标”→“电子标书在线获取”处完成网上获取磋商文件才被视为合法获取了采购文件，否则其响应文件将 被拒绝。即：未通过“重庆市政府采购网”→“个人中心”→“在线开评标”→“电子标书在线获取”处下载、 获取磋商文件，将无法上传响应文件。 道 注意事项：本项目为重庆市江津区政府采购电子标项目，首次参与电子标的供应商须申请重庆市政府采购网账 号密码、办理CA证书并下载响应文件制作系统，制作电子响应文件进行互联网线上响应，具体操作流程请下载 采购公告附件进行查看。因未注册重庆市政府采购网账号、未办理CA证书、操作不当等原因造成无法递交响应 管 文件或递交响应文件失败的后果由供应商自行承担。 1.CA证书的办理流程：登录“重庆市政府采购网”→“个人中心”→“在线开评标”→“电子招投标中心” →“相关下载”栏目，下载附件《重庆市全流程电子招投标项目供应商办理正式CA签章流程手册》，并按照要 求操作。 国 2.响应文件制作：登录“重庆市政府采购网”→“个人中心”→“在线开评标”→“电子招投标中心”→“相关 下载”栏目，下载附件《【供应商必看】政府采购（CA版）供应商投标前软件安装手册》、《政府采购全程电 子化采购系统供应商操作手册（CA证书签章版）》和下载响应文件制作工具，并按下载的操作手册引导，完成 中 电子响应文件制作。 四、磋商响应文件递交 磋商响应文件递交开始时间： 2026年8月24日 09:00 磋商响应文件递交截止时间： 2026年9月1日 10:00 磋商响应文件递交地点：本项目采用网上递交方式，投标人于投标截止时间前使用平台提供的客户端投标工具 编制投标文件，然后登录“重庆市政府采购网”，进入“在线开评标”栏目，在“我的投标项目”→“在线投 标”板块提交。 五、评审信息 磋商开始时间： 2026年9月1日 10:00 磋商地点：本项目采用网上开标方式，投标人可在“重庆市政府采购网”→“个人中心”→“在线开评 标”→“开评标大厅”远程参与开标（开标必备设备：CA证书和可以无线上网的笔记本电脑（必须带有摄像头、 麦克风和声卡等功能）、无线网卡等），因投标人自身原因导致未能在规定时间内解密电子投标文件或参与开 标的，其后果由投标人自行承担 六、公告期限 自本公告发布之日起3个工作日 七、其他补充事宜 1.投标人如未在规定时间内（系统默认30分钟，可根据现场响应情况进行延长/变更）解密电子投标文件的情形约 定： （1）因政府采购全程电子化系统客观原因影响解密时间的，采购人/采购代理机构可根据现场实际情况延长解密 时间。投标人在仍不能解密的情况下，投标人可向采购人/采购代理机构申请，网启用上传不加密的电子备份文件 的方法作为补救措施；在规定的时间内，投标人既不解密，也未提供不加密的电子备份文件作为补救措施的， 视为投标人主动放弃对该项目的投标资格。 （2）因投标人主观原因未完成解密工作的，且未在规定时间内提供有效不加密的备份文件的，都视为投标人在 务 提交投标文件截止时间后撤销投标文件，响应无效且投标人不得再参与本项目后续采购活动。如果项目提供了 保证金的，保证金扣除不予退还。 2.本项目采用全流程电子招投标。各投标人需熟悉了解整个政府采购电子化开评标全过程。具体电子化采购规则 以及操作指南请下载项目公告附件《重庆市全流程电子招商投标项目投标人办理正式CA签章流程手册》和《政府 采购全程电子化采购系统供应商操作手册（CA证书签章版）》、《【供应商必看】政府采购（CA版）供应商投 标前软件安装手册》，并按其要求操作。 八、联系方式 道 1、采购人信息 采购人：重庆市江津区李市镇人民政府 管 采购经办人：黄老师 采购人电话：023-47712801 国 采购人地址：重庆市江津区李市镇回龙路57号 2、采购代理机构信息 中 代理机构：重庆爱采招标代理有限公司 代理机构经办人：李老师 代理机构电话：023-62551600 代理机构地址：重庆市巴南区李渡路59号（李家沱大融城B4栋）2-1、2-2 3、项目联系方式 项目联系人：黄老师 项目联系人电话：023-47712801 https://www.cqggzy.com/trade/014005/1666888712375808000?categoryNum=014005001 信息来源:https://www.chinapipe.net/project/d3077886.html cqdingjiu 2026.08.24 12:31:40</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2244,18 +2220,18 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 资金, 产品</t>
+          <t>重庆, 水管, 农村饮水管网改建工程</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)衬氟管道及管件采购招标公告</t>
+          <t>长安工业渝北工厂供水管网泄露检测及修复询比采购公告</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2284,45 +2260,49 @@
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>渝北区</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>重庆市映天辉氯碱化工有限公司拟开展废盐综合利用联产20万吨/年离子膜烧碱项目(一期12万吨/年)，包括衬氟管道及管件的采购。</t>
+          <t>长安工业渝北工厂供水管网泄露检测及修复询比采购</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>项目资金来自业主自筹，项目出资比例为100%。货物采购估算金额约为225万元。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>衬氟管道及管件</t>
+          <t>供水管网泄露检测及修复设备和服务</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>废盐综合利用联产20万吨／年离子膜烧碱项目(一期12万吨／年)衬氟管道及管件采购招标公告 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）衬氟管道及管件采购招标公告 1、招标条件 本招标项目废盐综合利用联产20万吨/年离子膜烧碱项目已由重庆市长寿区发展和改革委员会以 重庆市企业投 资项目备案证（2207-500115-04-05-168305）批准建设，项目业主为重庆市映天辉氯碱化工有限公司，建设资金来 自业主自筹，项目出资比例为100%，招标人为重庆市映天辉氯碱化工有限公司。项目已具备招标条件，现对本 项目的（一期12万吨/年）衬氟管道及管件采购进行公开招标。 网 2、项目概况 2.1 建设地点：重庆长寿经济技术开发区化北路2号。 务 2.2、项目概况与建设规模： 重庆市映天辉氯碱化工有限公司（以下简称“映天辉”）位于重庆长寿经济技术开发区化北路2号，始建于2004 年5月，占地430亩，注册资本34800万元。现为国有控股企商业，是一家集氯碱生产经营、新材料研发经营于一体 的专业型、科技型综合企业，系国家级高新技术企业。 映天辉作为长寿经开区氯碱产业基础平台的龙头化工企业，现有一条氯碱生产线，生产规模为20万吨/年烧碱 （折100%NaOH计）。为建设并贯通氯碱化工道循环经济产业链，保障下游产业链装置氯气需求，实现氯碱产品的 升级和高端化发展，增加产品附加值，降低成本，提高竞争力，映天辉公司经过充分调研和反复论证后，拟开 展废盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）建设。装置在正常运行情况下，按照每年 8000 小时操作。具体要求及参数以第五章货物需求一览表及技术规格标准和要求为准。 管 2.3 本次招标项目货物采购估算金额： 约225万元。 2.4招标范围： 本次招标项目为：“废国盐综合利用联产20万吨/年离子膜烧碱项目（一期12万吨/年）衬氟管道及管件采购一批” 包括但不限于制造、涂漆、包装、运输、配合验收工作、检验检测、产品质量证明书等。（详见“第五章货物 （材料）需求一览表及技术规格标准和要求”）。 2.5 交货地点：货物运送至买方指定地点； 中 2.6 交货期： 2.6.1合同签订后 3个月内，所有货物运送招标人现场并具备安装条件。 2.6.2 中标方应于合同签订之日起7天内，向招标方提交完整的技术资料，以供设计院开展设备相关设计工作。 3、投标人资格要求 3.1 投标人应符合以下要求： （1）投标人具备有效的营业执照。 注：不得将投标人营业执照记载的经营范围作为评审因素。 （2）具备有效的《中华人民共和国特种设备生产许可证》-压力管道元件制造-元件组合装置。 （3）具有防腐管道元件特种设备型式试验证书。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3本次招标不接受代理商投标，不接受联合体投标。 4、招标文件的获取 4.1 凡愿意参加的潜在投标人，从2026年8 月 19 日起至投标截止时间前，均可登录重庆市公共资源交易网 （www.cqggzy.com）直接下载获取招标文件、答疑等开标前的有关资料。在公告期间，各投标人应随时关注网上 发布的招标文件答疑、补遗、澄清等文件内容，不管投标人是否下载，均视为已知晓招标文件的全部内容和有 关事宜。本项目不需要报名，直接投标。 5、投标文件的递交 5.1 投标文件递交的截止时间为 2026年 9 月 10 日上午09时30分，地点在重庆市公共资源交易中心开标厅 （地址：重庆市两江新区青枫北路6号渝兴广场B10栋2层），具体开标地点详见网一、二楼大厅显示屏。 5.2逾期送达的或者未送达指定地点的，或者未按照招标文件要求密封的投标文件，招标人将拒收。 6、发布公告的媒介 务 本次招标公告在 中国招标投标公共服务平台、重庆市公共资源交易网上发布。 7、联系方式 商 招 标 人：重庆市映天辉氯碱化工有限公司 地 址：重庆长寿经济技术开发区化北路二号 道 联 系 人：张先生 电 话：023-40717888 管 招标代理机构： 重庆招标采购（集团）有限责任公司 地 址：重庆市两江新区国五里店五简路2号重庆咨询大厦A栋20楼2001室 项目负责人：彭文婷 电 话： 023-67703002 中 废盐综合利用联产20万吨／年离子膜烧碱项目（一期12万吨／年）衬氟管道及管件采购 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630011190 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835003139 坝支行 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000000834 贸易试验区分行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146638621 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051302432 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000620855 支行 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020013554 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764235261 信息来源:https://www.chinapipe.net/project/d3076111.html cqdingjiu 2026.08.21 10:06:52</t>
+          <t>长安工业渝北工厂供水管网泄露检测及修复询比采购公告 【长安工业渝北工厂供水管网泄露检测及修复询比采购】采购公告 采购单位 重庆长安智能工业技术服务有限公司 代理机构 标的物 长安工业渝北工厂供水管网泄露检测及修复询比采购 长安工业渝北工厂供水管网泄露检测及修复询比采购公告 网 务 重庆长安智服对长安工业渝北工厂供水管网泄露检测及修复询比采购。现邀具有此采购项供应能力的厂商前来 参与采购活动。请按照本采购文件的要求递交响应文件 1.项目概况与采购范围 商 1.1 采购项目名称：长安工业渝北工厂供水管网泄露检测及修复询比采购 1.2 采购人：长安智服 道 1.3 采购方式：询比采购 1.4采购范围：长安工业渝北工厂供水管网泄露检测及修复询比采购 管 1.5 工期：全面检测总工期：40个工作日。 1.6服务地点：重庆长安工业（集团）有限责任公司机加区 国 2.供应商资格要求 2.1资质要求：供应商须具备法人资格，提供《营业执照》复印件，加盖供应商单位公章。 中 2.2 业绩要求：/。 2.3本项目不接受“三无”供应商投标（“三无”供应商是指：无实缴注册资本、无参保人员、无生产经营场所 的供应商）。供应商须提供不属于“三无”供应商的证明材料： （1）提供有实缴注册资本的证明材料（若供应商属事业单位的不作要求），如：“天眼查”或“企查查”APP 显示实缴资本的页面截图；或国家有关法律法规规定的具有验资资格的机构出具的验资报告等；或其他第三方 机构提供的可以证明供应商有实缴注册资本的证明材料。 （2）提供为员工缴纳社会保险的证明材料，供应商为员工缴纳社会保险汇总表（至少提交近3个月社会保险汇总 表）。 （3）提供有生产经营场所的证明材料，如：不动产权证书复印件，或生产经营场所的租赁合同复印件。 上述材料需加盖供应商单位公章。 2.4人员要求： 委托代理人必须为供应商本单位人员。提供供应商本单位为该委托代理人缴纳养老保险的证明材料（近3个月）， 加盖供应商单位公章。 说明：（1）投标人提交的上述资格审查资料均为扫描件（原件或复印件的扫描件均可），扫描件须清晰可辨； （2）投标人在《投标函》中承诺其提供的上述相关证明材料真实有效，不存在弄虚作假情形。 3.采购文件的获取 3.1 获取时间：2026年8月21日至2026年8月23日17时00分止。 3.2 获取方式：在“南方数字供应链”电子采购平台下载采购文件。 操作：在浏览器中输入平台网址，打开门户页面→点击【供应商/竞买人登录】→在工作台页面点击【询比采购】 菜单→点击【可参与项目】→选择本项目→登记联系人信息→下载采购文件。 说明：参加采购活动的供应商，需在“南方数字供应链”电子采购平台完成注册、办理CA证书（可使用手机下载 “中招互连APP”办理CA证书）。供应商操作指南：打开门户页面→在顶部右网侧点击【帮助中心】→在下拉菜 单中点击【操作手册】→点击【非招标业务-供应商操作手册】。 4.投标文件递交和开标 务 4.1 投标文件递交截止时间：2026年8月 27日北京时间9:30分结束。 4.2递交方式：在“南方数字供应链”电子采购平台上传递交投标文件电子版。 供应商除了在平台递交电子投标文件外，还需递交纸质版商投标文件1份（采购人用于存档）。纸质版投标文件投 递渠道方式为邮寄递交或现场投递。邮寄递交地址：重庆江北区大石坝8村长安公司5号门岗 。联系人：陈敏 13896127511。 4.3 开标时间：2026年8月27日北京时间 9：30道分。开标地点：网上。 说明：本次采购项目为非涉密项目，所投递的响应文件不得涉及国家秘密、工作秘密及其他内部敏感信息。 4.4洽谈时间与地点:采购人电话通知。 管 5、发布采购信息的媒介 本项目采购信息在“南方数字供应链平台”（https://www.cse-ssc.com）-“非招标采购”业务板块上发布。 国 6、联系方式： 采购人：重庆长安智能工业技术服务有限公司 中 地址：重庆市江北区大石坝8村长安公司5号门岗 联系人：陈 敏 联系电话：13896127511 信息来源:https://www.chinapipe.net/project/d3077867.html cqdingjiu 2026.08.24 12:31:41</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>全面检测总工期：40个工作日。</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>重庆, 废盐综合利用, 离子膜烧碱, 衬氟管道, 管件采购</t>
+          <t>重庆, 供水管网泄露检测及修复, 询比采购</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>重庆市益康环保工程有限公司永川分公司蒸汽管道改造项目询价采购公告</t>
+          <t>重庆市九龙坡区城市老旧小区供水管网漏损治理及二次供水设施更新改造工程(二期)一标段答疑补遗文件</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2332,7 +2312,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2353,12 +2333,12 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>永川区</t>
+          <t>九龙坡区</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>蒸汽管道改造</t>
+          <t>重庆市九龙坡区城市老旧小区供水管网漏损治理及二次供水设施更新改造工程(二期)一标段</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2368,32 +2348,32 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>蒸汽管道</t>
+          <t>供水管网漏损治理及二次供水设施更新改造</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>重庆市益康环保工程有限公司永川分公司蒸汽管道改造项目询价采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3076108.html cqdingjiu 2026.08.21 10:06:52 网 务 商 道 管 国 中</t>
+          <t>重庆市九龙坡区城市老旧小区供水管网漏损治理及二次供水设施更新改造工程(二期)一标段答疑补遗文件 重庆市九龙坡区城市老旧小区供水管网漏损治理及二次供水设施更新改造工程（二期）一标段 答疑及补遗通知 各潜在投标人： 现将重庆市九龙坡区城市老旧小区供水管网漏损治理及二次供水设施更新改造工程（二期）一标段答疑及补遗 通知相关内容发布如下： 网 一、答疑部分 质疑1：请问这个项目有图纸和工程量清单吗？？ 务 回复：本项目图纸和工程量清单将随本答疑及补遗通知一并发出。 质疑2：本项目包含适用13%税率的设备货物、适用9%税率的泵房安装工程，招标文件第五章供货要求“六、其 他”的第6.6条明确说明可分开填报不同税率，但投标函仅商设置一个税率填写位置，仅支持填报单一税率，无法 分项填报，请问投标函中填报的税率是否不影响评标，填任意税率即可？ 回复：投标函中填报的税率不影响评标，若投标人分别填报设备及安装的增值税税率时，可填写在投标函部 分“7. （其他补充说明） ”中。 道 质疑3：本次招标对水泵、变频器、PLC有品牌要求，技术标为暗标。请问投标品牌响应在招标文件投标文件格 式要求中的哪里？ 管 回复：可在资格审查部分其他资料中响应。 质疑4：1、通用条款15.3明确约定""在工程项目竣工前，承包人已经提供履约担保的，发包人不得同时预留工程 质量保证金""。但专用条款15.3.2又选择""工程竣工结算时一次性扣留质量保证金""（3%工程款）。同时专用条 款7.3.1要求履约担保金国额为中标合同金额的10%。 请明确：本项目是否在提供10%履约担保的情况下，仍同时扣留3%质量保证金？若如此，是否与通用条款矛盾？ 招标条款规定："二供设备泵房标准化改造部分内容不允许投标人出现严重不平衡报价[严重不平衡报价指：总价 报价下浮率与清单子目综合单价报价浮动比超过±5%（即总价报价下浮率-严重不平衡报价清单子目综合单价报 中 价下浮率）&gt;±5%]"。 该条款存在以下问题： （1）"总价报价下浮率"的基准是什么？是最高限价还是估算金额？招标文件未明确。 （2）"清单子目综合单价报价浮动比"如何计算？是否指每个子目单独计算下浮率？ （3）如果某个子目投标人报价为零（如招标人提供的单项限价中金额为零的项目），该子目是否纳入不平衡报 价审查？ （4）计算公式"（总价报价下浮率-严重不平衡报价清单子目综合单价报价下浮率）&gt;±5%"中，两个"下浮率"的 定义是否一致？ 【请求事项】 请招标人明确： （1）"总价报价下浮率"和"清单子目综合单价报价浮动比"的具体计算公式和基准值； （2）为零金额项目的处理方式； （3）建议一，提供一个不平衡报价审查的计算示例，便于投标人自查。 （4）因本招标为最低价中标法，建议二，投标人采用统一下浮比例，不得采用不平衡报价，承诺统一下浮比例， 这样投标人报价简单、评标专家也更轻松，避免逐一审核，后期审计等也简单化，根据限价和投标人下浮比例 能快速完成各项工作。 回复：（1）"总价报价下浮率"和"清单子目综合单价报价浮动比"的具体计算公式详见招标文件第二章投标人须知 前附表3.2.5投标报价的其他要求中第4条，"总价报价下浮率"的基准是总价最高限价。 （2）详见招标文件招标文件第二章投标人须知前附表3.2.5投标报价的其他要求中第3条。 （3）由投标人自行设置不平衡报价审查的计算示例，便于自查。 网 （4）不采纳，按招标文件及答疑补遗文件执行。 务 质疑5：通用条款与专用条款关于付款比例存在矛盾； 通用合同条款第3.2款约定付款比例为：预付款10%、交货款60%、验收款25%、结清款5%。 而专用合同条款第3.2款约定的付款比例为：预付款20%、商进度款60%（分批次）、验收后付至80%、审计后付 至97%、质保金3%。 虽然专用合同条款通常优先于通用条款，但专用条款中多处仍引用了通用条款的表述（如"交货款"、"验收款"等 概念），且专用条款的3.2.2款（交货款）和3.2道.3款（验收款）中付款比例留空（"向卖方支付合同价格的___%"）， 未填写具体比例。 这可能导致合同履行过程中对付款金额产生争议。 管 请招标人明确： （1）专用条款中3.2.2款（交货款）和3.2.3款（验收款）的空白比例应如何填写？ （2）如专用条款已通国过3.2款的重新约定替代了通用条款的付款方式，建议删除或修改专用条款中引用通用条款 的空白条款，避免歧义。 回复：（1）专用条款中3.2.2款（交货款）空白比例为60%。（2）不一致的地方以专用合同条款为准。 中 质疑6：通用条款与专用条款关于付款比例存在矛盾； 通用合同条款第3.2款约定付款比例为：预付款10%、交货款60%、验收款25%、结清款5%。 而专用合同条款第3.2款约定的付款比例为：预付款20%、进度款60%（分批次）、验收后付至80%、审计后付 至97%、质保金3%。 虽然专用合同条款通常优先于通用条款，但专用条款中多处仍引用了通用条款的表述（如"交货款"、"验收款"等 概念），且专用条款的3.2.2款（交货款）和3.2.3款（验收款）中付款比例留空（"向卖方支付合同价格的___%"）， 未填写具体比例。 这可能导致合同履行过程中对付款金额产生争议。 请招标人明确： （1）专用条款中3.2.2款（交货款）和3.2.3款（验收款）的空白比例应如何填写？ （2）如专用条款已通过3.2款的重新约定替代了通用条款的付款方式，建议删除或修改专用条款中引用通用条款 的空白条款，避免歧义。 回复：详见质疑5回复内容。 质疑7：业绩要求规定："完成过1个合同金额达到400万元及以上（提供的业绩包含本次投标货物类别和其他货物 类别的，业绩中的本次投标货物类别部分的合同金额须达到该金额要求）二次供水设备（至少包括水泵及配套 电机、变频器）供货及安装业绩。"该条款存在以下歧义： （1）"本次投标货物类别"概念模糊。是指"二次供水设备"这一大类，还是指投标人本次投标所涵盖的具体设备 （如水泵、电机、变频器等）？ （2）如果业绩合同是一个大型总包项目，其中包含了二次供水设备，但合同并未明确拆分出"二次供水设备"部 分的金额，投标人如何证明该部分金额达到400万元？ 请问建设水厂的大于400万的合同业绩，其含有多种水泵、电机、变频器等设备网，是否满足本次要求？ 回复：（1）“本次投标货物类别”是指二次供水设备（至少包括水泵及配套电机、变频器）。（2）1.可提供采 购单位出具证明；2.按招标文件执行。 务 质疑8：本工程为常规食品智能化工厂，不存在独一无二施工技术难点，无需项目经理持有两项大额钢结构工业 项目业绩。招标文件设置双重业绩壁垒，市场达标主体稀缺，存在量身定制招标文件嫌疑。竞争不充分难以形 成良性竞价，极易造成国有资金损失，请调整评审条件，商否则我方提交监督举报。业绩要求规定："完成过1个合 同金额达到400万元及以上（提供的业绩包含本次投标货物类别和其他货物类别的，业绩中的本次投标货物类别 部分的合同金额须达到该金额要求）二次供水设备（至少包括水泵及配套电机、变频器）供货及安装业绩。" 该条款存在以下歧义： 道 （1）"本次投标货物类别"概念模糊。是指"二次供水设备"这一大类，还是指投标人本次投标所涵盖的具体设备 （如水泵、电机、变频器等）？ 管 （2）如果业绩合同是一个大型总包项目，其中包含了二次供水设备，但合同并未明确拆分出"二次供水设备"部 分的金额，投标人如何证明该部分金额达到400万元？ （3）"提供采购单位证明"作为补充证明材料，其格式、内容深度均无明确要求，可能导致评审标准难以统一执 行，存在主观判断空间国。 请招标人明确： （1）"本次投标货物类别"的具体定义；是仅仅楼宇二供设备？还是各类自来水加压泵站（还变频加压、无负压 中 设泵等？ （2）当业绩合同未单独列明二次供水设备金额时，可接受哪些类型的证明材料（如合同附页、结算单据、审计 报告的明细等）； （3）"采购单位证明"的格式要求和最低内容标准。 回复：（1）“本次投标货物类别”是指二次供水设备（至少包括水泵及配套电机、变频器）。（2）当业绩合同 未单独列明二次供水设备金额时，可采购单位出具证明材料。（3）"采购单位证明"的格式由采购单位自拟，内 容须响应符合招标文件的要求。（4）质疑8问题中“本工程为常规食品智能化工厂，不存在独一无二施工技术难 点，无需项目经理持有两项大额钢结构工业项目业绩。招标文件设置双重业绩壁垒，市场达标主体稀缺，存在 量身定制招标文件嫌疑。竞争不充分难以形成良性竞价，极易造成国有资金损失，请调整评审条件，否则我方 提交监督举报。”的描述与本项目无关，本项目未设置“项目经理持有两项大额钢结构工业项目业绩”等相关 要求。 质疑9：付款方式与交货验收节奏不匹配，对投标人现金流压力巨大; 专用合同条款第3.2款约定的付款节点为： （1）合同签订后10日内支付20%预付款； （2）每批次安装调试完成并经联动试车72小时验收合格后20个工作日内付至当次批次货款的60%； （3）总量100%完成后付至80%； （4）审计后付至97%； （5）质保期满30个工作日内支付剩余3%质保金。 存在以下问题： （1）"分批次"定义模糊：招标文件未明确如何划分批次。若招标人将37套设备分网为几十个小批次，每批次仅支 付60%，意味着投标人需要垫付大量资金用于生产和安装，直到所有批次完成才能收到80%的款项，资金占用周 期极长。 （2）审计周期不确定：付至80%后，需等待"审计单位审核"才能付至97%。审计流程耗时无明确时限，如果审计 务 拖延，投标人将长期被拖欠17%的巨额款项。 （3）预付款比例偏低：本项目涉及设备供货、泵房改造、安防系统、管网连接等多项工作内容，前期投入 大，20%的预付款难以覆盖原材料采购和前期施工成本。 商 请招标人明确： （1）"分批次"的具体划分标准和原则； 道 （2）审计完成的最长时限承诺； （3）考虑提高预付款比例至30%，或增设进度款节点，以减轻投标人合理的资金压力 管 回复：（1）"分批次"的具体划分标准和原则是按招标人下达的任务书执行。（2）按《重庆市九龙坡区政府投资 项目管理实施细则》执行。（3）按招标文件执行。 国 质疑10：付款方式与交货验收节奏不匹配，对投标人现金流压力巨大; 专用合同条款第3.2款约定的付款节点为： 中 （1）合同签订后10日内支付20%预付款； （2）每批次安装调试完成并经联动试车72小时验收合格后20个工作日内付至当次批次货款的60%； （3）总量100%完成后付至80%； （4）审计后付至97%； （5）质保期满30个工作日内支付剩余3%质保金。 存在以下问题： （1）"分批次"定义模糊：招标文件未明确如何划分批次。若招标人将37套设备分为几十个小批次，每批次仅支 付60%，意味着投标人需要垫付大量资金用于生产和安装，直到所有批次完成才能收到80%的款项，资金占用周 期极长。 （2）审计周期不确定：付至80%后，需等待"审计单位审核"才能付至97%。审计流程耗时无明确时限，如果审计 拖延，投标人将长期被拖欠17%的巨额款项。 （3）预付款比例偏低：本项目涉及设备供货、泵房改造、安防系统、管网连接等多项工作内容，前期投入 大，20%的预付款难以覆盖原材料采购和前期施工成本。 请招标人明确： （1）"分批次"的具体划分标准和原则； （2）审计完成的最长时限承诺； （3）考虑提高预付款比例至30%，或增设进度款节点，以减轻投标人合理的资金压力 回复：详见质疑9回复内容。 质疑11：技术部分（暗标）编制要求存在内在矛盾; 网 请招标人明确： （1）在技术暗标中引用设备品牌名称是否会被认定为"显示与投标人企业有关的信息"？ 务 （2）技术方案中引用设备制造商公开发布的技术资料（含制造商名称）是否允许？ （3）建议明确技术暗标的审查标准，避免因理解不一致导致误判。 商 回复：本项目技术部分为符合性评审，技术部分的编制要求按招标文件第二章投标人须知前附表3.7.5编制要求执 行。 质疑12：质保期服务与5年运维服务的责任边道界不清；招标文件同时要求投标人提供： （1）质量保证期服务（60个月）："包含但不限于质保期内因设备质量问题引起的所有质量问题、维修维护、保 养和易损耗件的提供等"。 管 （2）5年运维服务："包括但不限于保障二次供水设施的泵房内的供水设备、水箱、阀门、控制系统、消毒设备、 压力容器、仪表、降噪减振装置及供水管道等设施设备的安全正常运行，5年运维期间定期巡查、清洁、保养、 维修、水箱清洗、配件更换等全部费用。" 两者在时间上高度重合国（均为60个月），服务内容也大量重叠（维修、保养、配件更换、巡查、清洁等），但招 标文件未明确： （1）质保期服务与运维服务是否为同一套服务？如果是，为何分别表述？如果不是，两者的具体分工和责任边 界是什么？ 中 （2）"质保期内因设备质量问题"与"运维期间"的故障责任如何区分？例如，一台水泵在投运第3年出现故障，是 由于设备质量原因还是运维不当？判断标准是什么？ （3）投标人在报价时，应将上述费用归入"质保期服务"还是"运维服务"，还是分别报价？ 请招标人明确： （1）质保期服务与5年运维服务的关系（是否同一事项的不同表述）； （2）两者服务内容和责任边界的具体划分； （3）报价时是否需要分别列项，还是可以合并报价。 回复：5年运维纳入质保期服务中，相关费用纳入投标报价中。 质疑13：漏报漏项视为包含在总价中的条款过于苛刻；招标文件及合同相关条款规定："若因卖方在投标报价时 有漏报、漏项的情况发生，买方均视为卖方已充分理解招标文件要求，漏报、漏项部分已包含在其投标报价之 中。" 该条款将所有风险完全转嫁给投标人，存在以下问题： （1）招标文件篇幅长、内容多（含技术规范、设备参数表、图纸等），要求投标人零失误地识别所有隐含的、 或描述不清的工作内容是不现实的。 （2）部分工作内容在招标文件中描述模糊或缺失（如前述末梢压力监测点、泵房改造的具体范围等），投标人 难以准确报价，非故意漏项不应被认定为"已充分理解招标文件要求"。 （3）该条款与《民法典》关于显失公平的合同条款的规制精神相悖，可能导致合同履行过程中的大量争议。 本项目招标又是执行工程清单报价，故应不存在漏报情形，漏报应该属于招标人的责任； 回复：本项目按清单进行报价，非投标人原因产生的漏报漏项按合同相关规定执网行。 质疑14：漏报漏项视为包含在总价中的条款过于苛刻；招标文件及合同相关条款规定："若因卖方在投标报价时 务 有漏报、漏项的情况发生，买方均视为卖方已充分理解招标文件要求，漏报、漏项部分已包含在其投标报价之 中。" 该条款将所有风险完全转嫁给投标人，存在以下问题： 商 （1）招标文件篇幅长、内容多（含技术规范、设备参数表、图纸等），要求投标人零失误地识别所有隐含的、 或描述不清的工作内容是不现实的。 （2）部分工作内容在招标文件中描述模糊或道缺失（如前述末梢压力监测点、泵房改造的具体范围等），投标人 难以准确报价，非故意漏项不应被认定为"已充分理解招标文件要求"。 （3）该条款与《民法典》关于显失公平的合同条款的规制精神相悖，可能导致合同履行过程中的大量争议。 管 建议招标人修改该条款，改为： "若因招标文件描述不清或存在歧义导致投标人漏报、漏项的，双方应本着公平合理的原则协商解决；若因卖方 疏忽大意导致明显、重大的漏项，卖方应在不增加合同价款的前提下补足相关内容。" 国 回复：详见质疑13回复内容。 中 质疑15：近年来，宏观经济与行业周期波动较大，部分优质企业可能因战略性投入、研发开支加大、或应对不可 抗力的短期市场冲击等原因导致单个会计年度出现临时性、非经常性亏损，请问能否将 2025度财务状况不亏损 调整为“2025年的财务状况良好”？这样能够更宽容、客观地看待企业在复杂周期中的正常经营波动，避免将此 类具备实力和潜力的企业排除在外。 回复：本项目招标文件对投标人财务要求按照《重庆市工程建设项目货物采购招标文件示范文本2026年版》设置， 不予调整。 质疑16：1、请问闸阀、止回阀、排气阀其阀体和阀芯能否采用比招标要求更好的不锈阀体和阀芯。 2、招标要求对电磁水表采集器要求为锂电磁；在上传成功率中标采用GPRS上传。请问，本电磁水表安装在泵房 内，一般采用市政供电，数据接入就地控制系统的PLC柜，这两种要求是否矛盾？ 3、招标文件第106页列举了水泵品牌推荐表，之前没有南方和威派格在列，请问本次入围是否是经过性能测试发 现比国内其他品牌更节能或更稳定？是否通知过国内其他品牌水泵进行过公开公平公正的测评？还是他们提前 做了商务工作？能否让国内十大著名品牌水泵均参与一次公开、公平、公正的测评，并决定入围？ 4、请问水泵是否可以采用比招标文件技术要求更高的一级能效水泵？ 5、请问是否可以采用集水泵、电机、变频、控制于一体的一级能效水泵，其水泵电机、材质、能效均优于原招 标技术要求。变频控制系统采用厂家配套的变频控制系统。 6、请问标准化泵房的建设标准是什么？ 回复：（1）闸阀、止回阀、排气阀其阀体和阀芯可以采用不锈阀体和阀芯。 （2）项目按招标要求选用锂电磁采集器，采用GPRS作为数据主上传通道；泵房现有市政电源，PLC有线系统可 作为配套条件，在现场移动信号不良时，增设有线传输设备作为备用通信链路，不改变招标文件规定的主传输 方式。 （3）推荐品牌仅为列举参考，不属于限制性条款，不限制其他合格品牌参与投标。 （4）可以采用。 网 （5）本项目不接受水泵、电机、变频、控制一体化设备，水泵、电机、变频、控制柜应为分体独立成套设备， 设备操作面板应采用中文面板，尺寸不小于10英寸。 务 （6）详见设计图纸。 质疑17：1、请问闸阀、止回阀、排气阀其阀体和阀芯能商否采用比招标要求更好的不锈阀体和阀芯。 2、招标要求对电磁水表采集器要求为锂电磁；在上传成功率中标采用GPRS上传。请问，本电磁水表安装在泵房 内，一般采用市政供电，数据接入就地控制系统的PLC柜，这两种要求是否矛盾？ 道 2、招标文件第106页列举了水泵品牌推荐表，之前没有南方和威派格在列，请问本次入围是否是经过性能测试发 现比国内其他品牌更节能或更稳定？是否通知过国内其他品牌水泵进行过公开公平公正的测评？还是他们提前 做了商务工作？能否让国内十大著名品牌水泵均参与一次公开、公平、公正的测评，并决定入围？ 管 3、请问水泵是否可以采用比招标文件技术要求更高的一级能效水泵？ 4、请问是否可以采用集水泵、电机、变频、控制于一体的一级能效水泵，其水泵电机、材质、能效均优于原招 标技术要求。变频控制系统采用厂家配套的变频控制系统。 国 5、请问标准化泵房的建设标准是什么？ 回复：详见质疑16回复内容。 中 质疑18：（3）水泵、电机、变频器具有制造商授权书。 注：本招标项目同一标段中，一个制造商对同一品牌同一型号的货物，仅能委托一个代理商参加投标，否则各 相关投标均无效；同一品牌同一型号货物的制造商和代理商不得在本招标项目同一标段中投标，否则各相关投 标均无效。 请问是不是一个水泵品牌只能授权一个投标人，如果多个投标人用同一个品牌授权则无效？ 回复：对本条制造商授权有调整，详见补遗内容。 质疑19：请问正在执行的合同，货还未供完，能作为本次业绩投标吗？ 回复：此类情况不满足招标文件要求。 质疑20：第六章投标文件格式（三）分项报价表中包含多个不同类别的报价表格，请问本次招标报价是以后续发 布的工程量清单报价为准，还是以已发布的招标文件中的分项报价表格式为准？请予以明确。 回复：以本答疑补遗通知发布的工程量清单报价为准进行填报。第六章投标文件格式（三）分项报价表有调整， 详见补遗部分内容。 质疑21：请问招标文件第五章供货要求中要求提供的“...技术参数响应”、“设备质保期为 5 年，质保期内，供 货方应免费“包修””等相关资料，是否仅需在投标文件资格审查阶段作出承诺即可，相关资料在中标后再提 供？ 回复：仅需在投标文件资格审查阶段作出承诺即可。 网 质疑22：招标文件中第二章投标人须知前附表1.4.1投标人资质条件、能力和信誉中3.业绩要求要达到 400 万及以 上，......该业绩的合同文件和完成供货证明（合同文件须提供首页、 签章页以及体现上述业绩指标的关键页；完 务 成供货证明须提供 以下材料之一：使用单位验收报告、使用单位入库单、使用单位验收单、供货发票；） 请问完成供货证明须提供的证明材料中的供货发票，是该合同的全额发票吗？为证明合同真实性，建议提供完 整合同及其对应的全额发票复印件。 商 回复：此处“供货发票”是指满足同一合同发票金额400万元及以上的供货发票，可以为单张或者多张累计。 道 质疑23：招标文件3.投标人资格要求3.1.1 投标人为制造商应符合以下要求 （ 3 ）水泵、电机、变频器具有投标货 物制造商授权书 ； 问题：当制造商投标时，制造商不是水泵生产厂家时，为什么不要提供水泵、电机、变频器具有投标货物制造 管 商授权书 ？只要求代理商提供，是否对于我们代理商来说不公平 回复：对本条制造商授权有调整，详见补遗内容。 国 质疑24：招标文件3.投标人资格要求3.1.1 投标人为制造商应符合以下要求 （ 3 ）水泵、电机、变频器具有投标货 物制造商授权书 ； 中 问题：当制造商投标时，制造商不是水泵生产厂家时，参与投标是否也需要提供水泵、 电机、变频器具有投 标货物制造商授权书 ？ 回复：对本条制造商授权有调整，详见补遗内容。 质疑25：ABB变频器是否需要每天均配置中文面板？ 回复：每台ABB变频器需要配置中文面板。 质疑26：气压罐是否可以采用国产品牌？ 回复：可以，性能满足招标文件要求。 质疑27：管网型智能监控终端及系统是不是必须采用远通公司产品？设备制造商自己的是否可行？ 回复：管网型智能监控终端制造商可自行制造，数据接入和传输满足招标文件要求，并接入重庆市自来水公司 二供平台。 质疑28：招标文件要求质保期间定期免费巡查、清洁、维修、水箱清洗.请问有哪些项目有水箱？水箱是否完全 利旧？ 回复：详见图纸。 质疑29：投标文件内还需要提供二供设备的组成清单吗？若需要，请问放在哪里？会不会和工程量清单冲突？还 是不需要，只提供招标文件要求的工程量报价清单即可 回复：不需要组成清单，按本答疑补遗通知提供的工程量报价清单报价即可。网 质疑30：投标文件内还需要提供二供设备的组成清单吗？若需要，请问放在哪里？会不会和工程量清单冲突？ 务 回复：不需要组成清单，按本答疑补遗通知提供的工程量报价清单报价即可。 商 质疑31：请问***现在被人民法院列为被执行人且有1000多万股权冻结到2028年，因为不能履行保函的见索即付， 拒绝赔付。相关业主方在招标文件补遗通知中直接将***列入担保公司回避名单，拒绝***所出具的保函。由此可见 ***的信用资质、履约能力、根本无能力是存在很大问题的。请问以***目前的被执行和不履行投标担保责任的情 况是否符合招标文件的要求? 道 回复：按招标文件执行。 管 质疑32：二供设备运行数据及电磁水表数据必须接入重庆市自来水有限公司平台，请问重庆市自来水有限公司平 台是否免费开放，若收费，请问是否包含在本次限价内？ 回复：因重庆市自来水国有限公司平台涉密，有条件开放，开放费用纳入投标报价。 质疑33：招标文件要求质保期间定期免费巡查、清洁、维修、水箱清洗.请问这个时间规律，分别一个月做几次？ 会不会写入合同中？ 中 回复：质保期间每月一次定期巡查、设备日常维护、泵房环境清洁维护。二供水箱清洗每年二次，质保期内的 巡查维护清洁费用纳入合同报价。 质疑34：招标文件要求包含 2 年流量费用并列入报价中，请问工程量限价清单里面会包含吗？若没有包含怎么报？ 回复：项目按招标要求选用锂电磁采集器，采用GPRS作为数据主上传通道；泵房现有市政电源，PLC有线系统 可作为配套条件，在现场移动信号不良时，增设有线传输设备作为备用通信链路。 投标人须配套提供每月30M的4G流量卡或每月10M专线流量，上述两年流量服务周期内产生的相关费用，统一包 含在投标总报价中。 质疑35：招标要求“2.4 招标范围 ：包括二供设备泵房标准化改造排水沟的整治、墙面改造、地面铺装、 门禁等 以具体清单为准 ；二供设备泵房安防系统设备供货、安装、调试、试运行 ；二供设备供货、安装、调试、试运 行 ；施工期间的供水保障 ；以泵房外墙为界 ，泵房内外进出水管的连接、进水电磁水表的采购和安装。”因没 有图纸，其墙面和地面改造标准是什么？ 回复：以补遗图纸为准。 质疑36：招标要求"二供设备运行数据及电磁水表数据必须接入重庆市自来水有限公司平台 ，具体详见监控终端 及系统参数要求 "请问其平台接入是否免费开放IP协议？如果不是免费开放，投标人自行施工接入，其IP协议收 费标准请公示并纳入预算中！ 回复：因重庆市自来水有限公司平台涉密，有条件开放，IP协议接入平台工作内容包含PLC数据、视频安防数据 的采集、分析，接入智能监控终端；完成二次供水泵房采集数据上传至平台，实现数据展示及数据分析功能 （平台终身授权）。 质疑37：招标文件第五章供货要求对二供设备提出了相关的技术要求，本次技术文件为暗标，请问投标人是否需 要一一响应，如果需要，应该在投标格式文件哪个位置提供技术响应表？ 回复： 本项目技术部分仅需对招标文件第三章评标办法前附表2.2.1技术评审标准进行响应。 质疑38：本次招标范围内，众多项目在满足招标文件要求的流量、扬程的情况下网，其对应水泵选型功率比招标文 件要求的小，请问水泵功率在满足招标文件要求的流量、扬程的情况下小于招标文件要求功率？ 回复：水泵功率在满足招标文件要求的流量、扬程的情况下可以小于招标文件要求功率。 务 质疑39：招标文件第六章投标文件格式中的投标函部分列有（二）分项报价表格式，然而本项目同时发布的工程 量清单与之存在明显不匹配的情况。请问是否可删除分项报价表格式并添加工程量清单？ 回复：本项目招标文件第六章投标文件格式中的投标函部分（二）分项报价表中，投标人按本答疑及补遗发布 的清单格式进行填报。 商 质疑40： 招标文件 114 页要求提供分项报价表，其为根据二供设备参数分项报价，但是提供的工程量清单又是工 程类清单，请问报价是按工程类报价（须招标人提供广联达的限价电子招标文件），不用按照 114 页的分项报价 表报价？还是按照 114 页的分项报价表报价，道不管本次提供的工程量清单，那么请业主提供具体货物分项？还是 不用提供分项报价表？ 回复：本项目招标文件第六章投标文件格式中的投标函部分（二）分项报价表中，投标人按本答疑及补遗发布 的清单格式进行填报。 管 质疑41：请问本次最低价中标，会不会恶意废标，废标原因是否会公示？ 回复：若有废标情况，废标原因将按相关规定进行公示。 国 质疑42：请问本次招标项目图纸会提供吗？好久提供？ 回复：本次招标项目图纸将随本通知一并发出。 中 质疑43：请问本次招标有电磁水表吗？招标文件没有看到其清单？ 回复：本次招标包含电磁水表。 质疑44：本次招标业绩要求400万以上的二供设备合同，我司有类似业绩合同没完全验收，但均已完成供货安装， 有监理单位的设备验货单，提供监理单位的验货单是否满足招标文件业绩要求？ 回复：按招标文件要求执行。 质疑45：本次招标业绩要求400万以上的二供设备合同，但二供本身定义比较模糊宽泛，是必须小区二次供水业 绩合同才满足要求还包含小区二次供水在内的加压供水设备、自来水输配水加压站、片区无负压加压站、片区 变频供水加压站等（其均含有水泵、电机、变频器等供水核心部件）均满足要求？ 回复：供水业绩合同可以是小区二次加压供水设备，也可以是片区变频无负压加压站。 质疑46："水泵、电机、变频器具有投标货物制造商授权书；"这类条件设定算不算是隐性门槛。能否取消该条款， 如不取消如何保证招标的公平和公正，如何解释才能不算是门槛。 回复：对本条制造商授权有调整，详见补遗内容。 质疑47：“质量保证期： 60个月”是从什么时候计算，是竣工验收报告时间还是结算审计完成时间计算。 回复：从竣工验收报告时间开始计算。 质疑48：中标后，“二供设备运行数据及电磁水表数据必须接入重庆市自来水有限公司平台”是有施工方直接和 自来水公司对接联系还是在业主的主持协调下与自来水公司对接。 回复：施工方和自来水公司对接联系。 质疑49：“若出现投标人投标报价相同的，以投标人提供的业绩合同金额大小从高到低的优先”，该评判标准是 以单个业绩还是所提供所有业绩的总和" 回复：评判标准是以单个业绩中合同金额大小从高到低的优先。 质疑50：本项目委派业主专家吗？ 网 回复：不委派。 质疑51：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗？ 务 回复：低价说明证明材料由投标人自行提供。 质疑52：请问招标人是否委派业主专家参与评标吗？ 商 回复：不委派。 质疑53：有没有人行贿专家，有的话我们就不参加了。 道 回复：此问题与本项目无关。 质疑54：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 管 回复：按招标文件执行。 质疑55：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 回复：财务要求按招标国文件执行。 质疑56：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知书发 出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予提前注 销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 中 回复：可以加盖，但是否加盖不作为否决投标。 质疑57：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗？ 回复：不需要。 质疑58：财务报告可以不提供财务报表附注吗？ 回复：可以不提供，是否提供不作为否决投标。 质疑59：本项目是异地评标吗？ 回复：按相关要求执行。 质疑60：现在除了没有警戒线和技术方案的低价项目评标专家不被围猎，哪个项目不围猎评标专家，请问招标人 如何保证公平？ 回复：此问题与本项目无关。 质疑61：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 回复：以PDF为准，但重庆市电子招投标系统中锁定不可以修改的格式以重庆市电子招投标系统中的格式为准。 质疑62：财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加强审计报告查验工作的通知》中要求 会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第十四条规定审计业务出具的报告（以 下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标人提 供的财务报告需要赋码和提供深度查询截图吗？ 回复：财务要求按招标文件执行。 质疑63：招标文件第六章投标文件格式中（三）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要 提供其他格式之外的其他承诺？ 网 回复：不需要。 务 二、补遗通知 1、本项目增设“代建业主”，代建业主为：重庆市自来水有限公司。 商 2、本项目招标文件中第一章招标公告“1.招标条件”中“招标项目资金来自”及第二章投标人须知前附 表1.2.2“资金来源及比例”修改为：优先使用超长期特别国债，不足部分由重庆自来水有限公司解决。 3、将招标文件第一章招标公告“3.投标人资格道要求”和第二章投标人须知前附表“1.4.1 投标人资质条件、能力 和信誉”中“水泵、电机、变频器具有投标货物制造商授权书。注:本招标项目同一标段中，一个制造商对同一 品牌同一型号的货物,仅能委托一个代理商参加投标，否则各相关投标均无效;同一品牌同一型号货物的制造商和 代理商不得在本招标项目同一标段中投标，否则各相关投标均无效”全文修改为:“投标成套供水设备应具有成 套供水设备制造商的授权书;成套供水设备的制造商和其授权的代理商不得在本招标项目同一标段中投标，否则 管 各相关投标均无效”。 4、本项目招标文件第二章投标人须知前附表3.2.5投标报价的其他要求中： “4.不平衡报价：二供国设备泵房标准化改造部分内容不允许投标人出现严重不平衡报价[严重不平衡报价指:总价 报价下浮率与清单子目综合单价报价浮动比超过±5%(即总价报价下浮率-严重不平衡报价清单子目综合单价报 价下浮率)&gt;±5%]，若在评标时发现潜在投标人出现严重不平衡报价的情况，其投标文件由评标委员会作否决投 标处理。暂列金额（若有）、暂估价（若有）、安全文明施工费（若有）等暂定金额必须按照招标文件给定的 金额填报，中否则由评标委员会作否决投标处理。”修改为：“4.不平衡报价：本项目所有清单不允许投标人出现 严重不平衡报价[严重不平衡报价指:总价报价下浮率与清单子目综合单价报价浮动比超过±5%(即总价报价下浮 率-严重不平衡报价清单子目综合单价报价下浮率)&gt;±5%]，若在评标时发现潜在投标人出现严重不平衡报价的 情况，其投标文件由评标委员会作否决投标处理。暂列金额（若有）、暂估价（若有）、安全文明施工费（若 有）等暂定金额必须按照招标文件给定的金额填报，否则由评标委员会作否决投标处理。”。 5、本项目招标文件第六章投标文件格式中的投标函部分（二）分项报价表中，表格的格式修改为：投标人按本 答疑及补遗发布的清单格式进行填报。 6、本项目清单及图纸随本答疑补遗通知一并发出，由投标人自行下载。 7、本项目投标总报价最高限价为：10476100.87元（大写：壹仟零肆拾柒万陆仟壹佰元捌角柒分），各项固定单 价报价最高限价详见附件，投标人的投标报价不得超过其最高限价，否则由评标委员会作否决投标处理。本项 目异常低价警戒线为7333270.61元（大写：柒佰叁拾叁万叁仟贰佰柒拾元陆角壹分）。 8、本项目投标截止时间（开标时间）延期到2026年9月7日09时30分（北京时间），开标地点不变，投标保证金 缴纳时间相应顺延。 注：已发出的招标文件与本次答疑及补遗通知不一致的内容，以本通知为准。请各潜在投标人自行在网上下载 本通知相关内容，不管下载与否，都视为全部知晓其全部内容。 招标人：重庆市九龙坡区城市管理局 招标代理机构：中技国际招标有限公司 2026年8月21日 https://www.cqggzy.com/trade/014001/58795bf3-0369-4f2e-8909-e99f831facfb?categoryNum=014001002002 信息来源:https://www.chinapipe.net/project/d3077858.html cqdingjiu 2026.08.24 12:31:41 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>排水钢管 Φ200*6m：3000米</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>重庆, 蒸汽管道, 改造项目, 询价采购</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>南岸区融侨大道、江南大道片区2023年排水管网改造项目(三标段)招标计划表</t>
+          <t>两江天宫殿钢筋、型材、商砼、管材采购(第二次)招标公告</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2403,7 +2383,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2422,49 +2402,45 @@
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>南岸区</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>包括改造市政混接点194个，改造管网8582米，缺陷管网开挖修复1355米，非开挖修复8679米。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>总投资概算未明确具体金额，但合同预估金额为6600万元。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>排水管网改造</t>
+          <t>钢筋、型材、商砼、管材</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>南岸区融侨大道、江南大道片区2023年排水管网改造项目(三标段)招标计划表 重庆市工程建设项目招标计划表 项目名 南岸区融侨大道、江南大道片区 2023年排水管网改造项目（三标段） 称 网 招标法 人或招 重庆市南岸区城市建设发展（集团）有限公司 标人名称 （盖章） 务 项目批 准文件 南岸发改〔2024〕304《南岸区融侨大道、江南大道片区2023年排水管网改造项目总投资概算的批复》 及文号 主要建 包括改造市政混接点194个，改造管网8582米，商管径d300~d1500;缺陷管网开挖修复1355米，管 设内容 径d300~d600;非开挖修复8679米，管径d300~d1200。 招标文件 拟交 合同预估 招标内 招标 序号 招标项目名称 计划发布 易场 金额(万 备注 道容 方式 时间 所 元) 51处雨 污混错 重庆 招标项 接点位 管 市公 目 改 南岸区融侨大道、江南大道片区 2023年排 公开 共资 1 造，1082 2026-08 6600.00 水管网改造项目（三标段） 招标 源交 个管网 易中 三四级 国 心 缺陷修 复。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 中 信息来源:https://www.chinapipe.net/project/d3076097.html cqdingjiu 2026.08.21 10:06:52</t>
+          <t>两江天宫殿钢筋、型材、商砼、管材采购(第二次)招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3077792.html cqdingjiu 2026.08.24 12:31:42 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>管网：8582米；缺陷管网：1355米</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>重庆, 排水管网改造, 资金情况, 产品种类</t>
+          <t>重庆, 管材</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购公告</t>
+          <t>万州区旧城供水管网改造工程(三期)管材等材料采购(第二次)招标公告</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2495,47 +2471,47 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>永川区</t>
+          <t>万州区</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>项目位于永川区三教镇，项目占地面积41673.42㎡（62.51亩），总建筑面积6078.71㎡，新建净水厂1座，规模5万吨/天，新建厂外管网4.6km（DN200～DN1000），配套建设净水处理系统、排泥水处理系统、综合楼、生产建（构）筑物以及附属建筑物等。</t>
+          <t>该项目对百安坝等3个街道老旧市政供水管道及附属设施进行改造，配套智慧水务物联网感知设备建设，共计改造老旧市政供水管道84.2千米。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>项目合同额1.7亿元</t>
+          <t>项目资金来自超长期特别国债资金及业主自筹，项目出资比例为100%，本次招标项目货物采购估算金额为2500万元。</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>钢筋混凝土排水管</t>
+          <t>管材、管件、阀门类、伸缩器、电磁流量计、法兰及其他等材料</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购公告 永川三教水厂项目 已具备采购条件，现公开邀请供应商参加询比采购活动。 1.采购项目简介 1.1 采购项目名称：中交一公局重庆工程有限公司2026年8月钢筋混凝土排水管询比采购。 1.2 采购方案编号：FA00000663117。 网 1.3 采购人：中交一公局重庆工程有限公司。 1.4 采购代理机构：/。 务 1.5 采购项目资金：已落实 1.6 采购项目概况： 商 永川三教水厂项目：项目位于永川区三教镇，项目占地面积41673.42㎡（62.51亩），总建筑面积6078.71㎡，新建 净水厂1座，规模5万吨/天，新建厂外管网4.6km（DN200～DN1000），配套建设净水处理系统、排泥水处理系统、 综合楼、生产建（构）筑物以及附属建筑物等。项目合同额1.7亿元，工期450天。 道 项目地址：重庆市永川区。 2.采购范围及相关要求 管 2.1 采购范围：钢筋混凝土排水管。 2.2 交货期：2026年9月-2026年12月。 2.3 交货地点：重庆市永国川区项目指定地点。 2.4 物资质量标准：满足《混凝土和钢筋混凝土排水管》（GB/T 11836-2023）的相关要求。 3.供应商资格要求 中 3.1 供应商应依法设立且满足如下要求： （1）资质要求：本次询比采购要求供应商须是在中华人民共和国境内依法注册，具有合法有效的营业执照、税 务登记、组织机构代码等证件，具有独立法人资格、具有采购物资生产经营范围的生产商或代理商（销售商）。 （2）财务要求：供应商必须是经税务部门注册登记核准的纳税人，有依法纳税的良好记录。 （3）业绩要求：无。 （4）信誉要求：无不良履约记录、未列入工程所在地质量监督部门和中国交建、中交一公局集团企业黑名单。 因质量原因被交通部质监站通报，正在进行整改的生产厂家和产品不得参与投标。生产商或代理商（销售商） 具有良好的社会信誉，近3年内没有与骗取合同有关的犯罪或严重违法行为而引起的诉讼和仲裁；近3年不曾在合 同中严重违约或被逐；财产未被接管或冻结，企业未处于禁止或取消投标状态；在最高人民法院、信用中国 （www.creditchina.gov.cn）或各级信用信息共享平台查询拟入库单位无不良行为记录。 （5）其他要求：无。 3.2 供应商不得存在下列情形之一： （1）处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； （2）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （3）已列入黑名单，且未解除限制期限； （4）其他：无。 4.供应商报名 4.1 有意参加询比采购活动的单位，请于2026年8月19日15时00分至2026年8月26日17时00分（北京时间，下同，法 定公休日、节假日不休），登录“中交招采网”（网址：https://zjzcw.iccec.cn）进行报名并下载采购文件。 4.2 已在网并且已通过采购人层级供应商或已增加采购人为合作单位的供应商、上级供应商可直接参与询比采 网 购。在网平级单位供应商未增加采购人为合作单位需进行合作意向申请通过后参与询比采购。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择采购人，审核通过后方可参与询比 采购。 务 5.供应商报价 5.1 报价结束（递交响应文件截止）时间为2026年8月26日17时00分。 商 5.2 供应商应在报价结束时间前，登录“中交招采网”进行线上报价并上传电子响应文件。逾期未完成上传的电 子响应文件，采购人将拒收。 5.3电子采购的供应商响应文件由线上电子报价道表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 子报价表的数据为准。 6.开标 管 6.1 开标时间：与报价结束时间相同。 6.2 开标地点：本次采购在“中交招采网”平台线上开标，不举办现场开标。 国 7.发布公告的媒介 本询比采购公告在 “中交招采网” 上发布。 中 8.评审办法 本项目评审办法采用 经评审的最低价法 。 9.合同主要条款 9.1 付款条件：按月结算，上月11日至本月10日为一个结算对账期，乙方必须按照甲方要求开具合规的增值税专 用发票，无发票不予付款。结算完成后1个月内支付已结算金额的70%，剩余30%货款在结算完成后3个月内支付。 付款方式为银行转账，甲方有权采用票据支付或者供应链支付的方式支付货款，因此产生的费用包含在综合单 价中，乙方不得因此调价和索赔。如遇业主支付不及时，乙方应予理解。 9.2 履约保证金的递交： （1）R不要求递交 （2）要求递交，保证金金额：/，保证金形式：/，其他形式：/ 。 10.监督机构 监督机构名称： 中交一公局重庆工程有限公司审计部 11.成交供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联系400-676-5885，中标服务费请按7咨询。 11.1 收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： 网 （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； （3）在1000万元（含）至3000万元之间的，每次收取1000元； 务 （4）在3000万元（含）至1亿元之间的，每次收取3000元； （5）在1亿元（含）以上的，每次收取5000元。 商 11.2 支付流程 （1）通知推送：中标结果发布后，系统自动推送缴费通知（含应缴金额及支付链接）； 道 （2）费用查询：供应商登录“中交招采网—供应商协同—服务费”模块查看待支付费用； （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 管 （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网— 供应商协同—服务费—发票查询”模块获取。 12.其他 国 / 。 13.联系方式 中 采 购 人：中交一公局重庆工程有限公司 地 址：重庆市江北区创富路5号 邮 编：361021 联 系 人：汪仁宽 电 话：13527572392 电子邮件：1176245792@qq.com 项目联系人及电话： 序号 项目名称 联系人 联系电话 1 永川三教水厂项目 高博 17788661005 中交一公局重庆工程有限公司 2026年8月19日 物资信息 序号 设备物资名称 设备物资说明 税率 单位 网 1 钢筋混凝土排水管 2000mm Ⅲ级 承插口 13% 米 信息来源:https://www.chinapipe.net/project/d3076078.html 务 cqdingjiu 2026.08.21 10:06:52 商 道 管 国 中</t>
+          <t>万州区旧城供水管网改造工程(三期)管材等材料采购(第二次)招标公告 万州区旧城供水管网改造工程（三期）管材等材料采购 （第二次）招标公告 1.招标条件 本招标项目万州区旧城供水管网改造工程（三期）管材等材料采购已由 重庆市万州区发展和改革委员以 万 州发改审投【2025】16号 批准建设，项目业主为 重庆长江水务有限公司，招标项目资金来自 超长期特别国 债资金及业主自筹 ，项目出资比例为 100% ，招标人为 重庆长江水务有限公司 。项目因首次招标失败， 现对该项目的 管材等材料采购进行第二次公开招标，评标办法采用经评审的最低投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 万州区五桥片区 。 2.2 项目概况与建设规模：该项目对百安坝等3个街道老旧市政供水管道及附属设施进行改造，配套智慧水务物联 务 感知设备建设，共计改造老旧市政供水管道84.2千米。其中，改造DN150供水管线8.1千米、DN200供水管线29.3 千米、DN250供水管线23千米、DN300供水管线5.1千米、DN400管线11.9千米、DN500供水管线6.8千米，管道材 质为3PE防腐内热熔防腐钢管。 2.3 本次招标项目货物采购估算金额： 2500万元。 商 2.4 招标范围： 包括完成管材、管件、阀门类、伸缩器、电磁流量计、法兰及其他等材料的供货（设 计、制造，含备品、备件、专用工器具等）、道装配（含出厂前组装、测试和检验、现场整体组装等）、 装卸、运输（含包装、保险）、验收，以及质量保证期内的维修、维护、保养、人员培训和其它相关伴随服务 等工作内容。 管 2.5 交货地点： 业主指定的施工现场。 2.6 交货期： 60日历天，计划开始交货日期：2026年9月30日（具体以实际通知为准）。 3.政府采购工程 国 3.投标人资格要求 3.1 本次招标允许投标人以投标货物的下列身份参加投标： 中 制造商 代理商（包括经销商、制造商下属销售子公司） 3.1.1 投标人为制造商应符合以下要求： （1）具备独立法人资格； 3.1.2 投标人为代理商应符合以下要求： （1）具备独立法人资格； （2）具备3PE防腐内热熔防腐钢管具有制造商授权书； 注：本招标项目中，一个制造商对同一品牌同一型号的货物，仅能委托一个代理商参加投标，否则 各相关投标均无效；同一品牌同一型号货物的制造商和代理商不得在本招标项目中投标，否则各相关投标均无 效。 （3）投标货物制造商应符合上述3.1.1项的规定。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表第1.4.1 项内容。 3.3 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在本次招标公告同时在 重庆市公共资源交易监督网和 重庆市公共资源交易网（万州区）上发布。下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人 需在本次招标公告同时在 重庆市公共资源交易监督网和重庆市公共资源交易网（万州区）上发布。完成市场主 体信息登记以及CA数字证书办理，办理方式请参见本次招标公告同时在 重庆市公共资源交易监督网和重庆市公 共资源交易网（万州区）上发布。导航栏“主体信息”页面中“市场主体信息登网记”、“CA 数字证书办理”。 若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在本次招标公告同时在 重庆市公共资源交易监督网和重庆市公共资源交易网（万州区）上发布。本 项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发布至2026-08-25 17:00:00前。 4.3招标人应于2026-08-27 17:00:00前在本次招标公告同时在 重庆市公共资源交易监督网和重庆市公共资源交易网 务 （万州区）上发布。发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-11 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 商 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在本次招标公告同时在 重庆市公共资源交易监督网和重庆市公共资源交易网（万州区）上发 布。发布。[提示：依法必须招标项目的招标道公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 重庆长江水务有限公司 代理机构: 重庆大渝庆项目管理有限公司 重庆市万州区南滨大道1999号（财 重庆市渝北区重庆北站南广场汽车站西 地 址: 管地 址: 富广场）1幢B座第四层 投WORK北站大厦906室 邮 编: 404000 邮 编: 404000 项目负责人: 夏雨 项目负责人: 唐晓帆 国 电 话: 13896299659 电 话: 17723636501 传 真: 传 真: 电子邮箱: 电子邮箱: 598381793@qq.com 中 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市万州区发展和改革委员会 电 话: 023-58339255 2026年08月21日 信息来源:https://www.chinapipe.net/project/d3077724.html cqdingjiu 2026.08.24 12:31:42</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>厂外管网：4.6km；钢筋混凝土排水管：2000m</t>
+          <t>排水钢管 DN150: 8.1千米；DN200: 29.3千米；DN250: 23千米；DN300: 5.1千米；DN400: 11.9千米；DN500: 6.8千米，材质为3PE防腐内热熔防腐钢管</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 钢筋混泥土排水管, 永川三教水厂项目</t>
+          <t>重庆, 管材, 招标, 改造工程</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>中国铁路成都局集团有限公司重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标招标公告</t>
+          <t>2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀采购项目(包1、包2)(第二次)招标公告</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2545,7 +2521,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2564,49 +2540,45 @@
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>大渡口区</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标。</t>
+          <t>为重庆分质供水有限公司提供不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀等设备材料。</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>项目出资比例为100%，资金已落实。</t>
+          <t>每个包合同暂估金额为110万元。</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>施工劳务</t>
+          <t>不锈钢可调式减压阀,不锈钢静音式止回阀,不锈钢微量排气阀,不锈钢闸阀,不锈钢表前阀,不锈钢球阀,Y型过滤器</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>中国铁路成都局集团有限公司重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施 工劳务招标招标公告 重庆市大渡口区萤石及配套企业 35 千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标公告 招标编号：DXNZBCQ-GC-2026-13 1. 招标条件 本建设项目重庆市大渡口区萤石及配套企业 35 千伏专用变电站项目穿越渝贵等网铁路防护工程施工劳务招标已由 《中国铁路成都局集团有限公司关于重庆市大渡 口 区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防 护工程施工图设计的复函》（科信技审〔2025 〕115号）批准建设，建设单位为重庆建桥置业有限公司，建设资 金使用外委资金，项 目出资比例为100%，资金已落实。招标人为中国铁路成都局集团有限公司重庆工务段。本 项目已具备法定招标条件，现进行公开招标，特邀请有意向的投标人参加投标。 务 2. 项目概况与招标范围 2.1 项目概况 商 2.1.1建设地点：渝贵线K38+838、南疏Ⅰ线K10+808、川黔线K1+622、川黔线K3+781、兴珞上行线K38+619、兴珞 下行线K38+635、小西线K1+633、南疏Ⅱ线K11+257。 2.1.2建设规模：重庆市大渡 口区萤石及配套企道业35千伏专用变电站项目穿越渝贵等铁 路防护工程，本项目工分为5个交叉工点。工点一采用明挖直埋方式下穿渝贵铁路新白沙沱长江多线特大桥第14孔 （渝贵线K38+838）；工点二采用顶进套管方式下穿南疏 Ⅰ 线K10+808（ 已停用）、川黔线K3+781（ 已停用 ）； 工点三采用明挖直埋方式下穿兴珞线陈家湾双线特大桥（上行线K38+619、下行线K38+635）；工点四采用顶进 管 套管方式下穿。 2.2 招标范围：重庆市大渡口区萤石及配套企业35千伏专用变电站项目穿越渝贵等铁路防护工程施工劳务招标。 即涉铁部分第第三章桥涵，第六章通信、信号、信息及灾害监测，第十章大型临时设施和过渡工程，第十一章 其他费用中的安全生产国费以及非涉铁部分。 2.3标段划分：本项目施工招标划分为1个标段。 2.4计划工期：240日历天，计划开工日期：2026年10月8日，计划竣工日期：2027年6月4日。 中 2.5 其他说明：___/___。 3. 投标人资格要求 3.1本次招标要求投标人为在中华人民共和国境内合法注册的独立法人，具备有效的营业执照、施工企业资质和 安全生产许可证等，并在人员、设备、资金等方面具备相应的施工能力。资格要求如下： 3.1.1 标段编号：全标段 （1）资质要求：施工劳务企业资质。 （2）业绩要求：近3年内完成过铁路营业线类似项目业绩。 （3）项目负责人要求:具有工程师及以上职称，2 年及以上类似铁路营业线项目管理工作经验， 良好的职业道德， 且未在其他在建工程项目任职。 （4）本标段不接受联合体投标申请。 （投标人资格要求详见招标公告附件） 3.2 各投标人可就上述标段中的 1 个标段进行投标。 3.3投标人未在“信用中国”网站（www.creditchina.gov.cn）中被列入失信被执行人名单，投标人未在国家企业信 用信息公示系统（www.gsxt.gov.cn）中被列入严重违法失信企业名单，投标人未被列入铁路工程建设失信行 为“黑名单”，投标人及其法定代表人、拟委派的项目经理在近3年不曾有行贿犯罪记录； 其他信誉要求：未被取消或暂停投标资格、不存在辖内失信的情形、不存在最近一期国铁集团施工企业评价为D 级且在整改期内的情形。 4. 招标文件的获取 4.1凡有意参加投标者，请于2026年08月20日00时00分至2026年08月25日00时00，在重庆龙头寺旅游集散中心（重 庆市两江新区天宫殿街道昆仑大道56号附1号5楼办公室）持单位介绍信获取招标网文件。 4.2招标文件每套售价0元，售后不退。 4.3其他：凡有意参加投标者可通过网上登记获取招标文件，将获取招标文件材料扫描件（PDF格式）发送 务 至dxncq_bgs@163.com邮箱登记，由招标代理人通过电子邮件方式向有意参加投标者发送招标文件。 5. 投标文件的递交 5.1投标文件递交时间为2026年09 月10 日08时30分至2026年商09月10 日09时00分，递交比选申请文件的截止时间（比 选截止时间，下同）为2026年09月10日09时00分，地点为重庆龙头寺旅游集散中心（重庆市两江新区天宫殿街道 昆仑大道56号附1号5楼开标室）。 5.2逾期送达的或者未送达指定地点或者不按照道招标文件要求密封的投标文件，招标代理人不予受理。 6. 发布公告的媒介 本次招标公告在国铁采购平台（https://cg.95306.cn）发布。 管 7. 联系方式 招 标 人：中国铁路成都局集团有限公司 招标代理机构：成都大西南铁路监理 国 重庆工务段 有限公司 地 址：重庆市九龙坡区黄桷坪街道铁 地 址：成都市金牛区站西桥西街305 中 路3村161号 号府河路苑9栋14楼 邮 编： / 邮 编：610081 法定代表人： 法定代表人 或其委托代理人： 或其委托代理人： 联 系 人： 任女士 联 系 人：汤女士 电 话： 17393148353 电 话：023-61896910 传 真： / 传 真： / 电子邮箱： / 电子邮箱：dxncq_bgs@163.com 网 址： / 网 址： / 开户银行： / 开户银行： / 账 号： / 账 号： / 2026年08月19日 附件： 获取招标文件信息表 申请人名称： （加盖公章） 项目名称：（按公告名称填写） 获取招标文件起止时间：（按照公告时间填写） 项目编号：（按照公告填写） 单位名称 经办人 联系电话 电子邮箱 标段 资料提交时间 备注 网 注：须附经办人介绍信、身份证复印件、单位营业执照复印件。 信息来源:https://www.chinapipe.net/project/d3075989.html cqdingjiu 2026.08.21 10:06:53 务 商 道 管 国 中</t>
+          <t>2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀采购 项目(包1、包2)(第二次)招标公告 2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀采购 项目（包1、包2）（第二次）招标公告 1.招标条件 网 本招标项目2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢 止回阀采购项目（包1、包2）（第二次）（项目名称），招标人为重庆分质供水有限公司，招标项目资金来自企 业自筹（资金来源），项目已具备招标条件。现对本项目进行公开招标，诚邀有兴趣的潜在投标人参与投标。 务 2.项目概况与招标范围 2.1项目地点：招标人指定地点。 2.2项目概况：为重庆分质供水有限公司提供不锈钢闸阀、商不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈 钢止回阀等设备材料。 不锈钢类阀门按统一下浮比例进行报价（具体规格见招标文件第五章“供货要求”）。 道 注：①投标人可以任意选择1个或2个分包进行投标，但是同一个投标人只能中标一个分包，当同一个投标人同时 在2个分包中被评审确定为第一中标候选人的，则按照包1、包2的顺序，确定其为第一中标候选人，在其他分包 中不再被确定为中标候选人，按评审结果排序依次递补中标候选人。 管 ②投标人根据参投分包分别制作投标文件、分别填写投标文件中的项目名称，如下： 包1项目分包名称：2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、 不锈钢止回阀采购项目（包1）（第二次）； 国 包2项目分包名称：2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、 不锈钢止回阀采购项目（包2）（第二次）。 每个包合同暂估金额为110万（注：超出合同服务期或合同期间结算金额达到合同暂估金额时，合同自动终止)。 中 供货区域分别为： 包1：北区（涉及区域两江新区、沙坪坝区、北碚区及其他区县，区域可根据甲方工程需求调整）及重庆分质供 水有限公司市外所有项目。 包2：.南区（涉及区域渝中区、南岸区、巴南区、九龙坡区、大渡口区及其他区县，区域可根据甲方工程需求调 整）及重庆分质供水有限公司市外所有项目。 2.3招标范围：为重庆分质供水有限公司提供不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈 钢止回阀等设备材料 2.4货物清单 序号 名称 规格型号 压力等级 单位 备注 1 不锈钢可调式减压阀 DN15 1.6MPa 件 带压力表 2 不锈钢可调式减压阀 DN20 1.6MPa 件 带压力表 3 不锈钢可调式减压阀 DN25 1.6MPa 件 带压力表；提供样品一个 4 不锈钢可调式减压阀 DN32 1.6MPa 件 带压力表 5 不锈钢可调式减压阀 DN40 1.6MPa 件 带压力表 6 不锈钢可调式减压阀 DN50 1.6MPa 件 带压力表 7 不锈钢可调式减压阀 DN65 1.6MPa 件 带压力表 8 不锈钢可调式减压阀 DN80 1.6MPa 件 带压力表 9 不锈钢可调式减压阀 DN100 1.6MPa 件 带压力表 10 不锈钢静音式止回阀 DN15 1.6MPa 件 带压力表；含不锈钢螺栓 11 不锈钢静音式止回阀 DN15 2.5MPa 件 带压力表；含不锈钢螺栓 网 12 不锈钢静音式止回阀 DN20 1.6MPa 件 带压力表；含不锈钢螺栓 13 不锈钢静音式止回阀 DN20 2.5MPa 件 带压力表；含不锈钢螺栓 14 不锈钢静音式止回阀 DN25 1.6MPa 件 带压力表；含不锈钢螺栓 务 15 不锈钢静音式止回阀 DN25 2.5MPa 件 带压力表；含不锈钢螺栓 16 不锈钢静音式止回阀 DN32 1.6MPa 件 带压力表；含不锈钢螺栓 17 不锈钢静音式止回阀 DN32 2.5MPa 件 带压力表；含不锈钢螺栓 商 18 不锈钢静音式止回阀 DN40 1.6MPa 件 带压力表；含不锈钢螺栓 19 不锈钢静音式止回阀 DN40 2.5MPa 件 带压力表；含不锈钢螺栓 20 不锈钢静音式止回阀 DN50 1.6MPa 件 带压力表；含不锈钢螺栓 道 21 不锈钢静音式止回阀 DN50 2.5MPa 件 带压力表；含不锈钢螺栓 22 不锈钢静音式止回阀 DN65 1.6MPa 件 带压力表；含不锈钢螺栓 23 不锈钢静音式止回阀 DN65 2.5MPa 件 带压力表；含不锈钢螺栓 管 24 不锈钢静音式止回阀 DN80 1.6MPa 件 带压力表；含不锈钢螺栓 25 不锈钢静音式止回阀 DN80 2.5MPa 件 带压力表；含不锈钢螺栓 26 不锈钢静音式止回阀 DN100 1.6MPa 件 带压力表；含不锈钢螺栓 国 27 不锈钢静音式止回阀 DN100 2.5MPa 件 带压力表；含不锈钢螺栓 28 不锈钢微量排气阀 DN15 1.6MPa 件 29 不锈钢微量排气阀 DN20 1.6MPa 件 中 30 不锈钢微量排气阀 DN25 1.6MPa 件 31 不锈钢微量排气阀 DN32 1.6MPa 件 32 不锈钢微量排气阀 DN40 1.6MPa 件 33 不锈钢微量排气阀 DN50 1.6MPa 件 34 不锈钢闸阀 DN15 1.6MPa 件 35 不锈钢闸阀 DN20 1.6MPa 件 36 不锈钢闸阀 DN25 1.6MPa 件 37 不锈钢闸阀 DN25 2.5MPa 件 38 不锈钢闸阀 DN32 1.6MPa 件 39 不锈钢闸阀 DN32 2.5MPa 件 40 不锈钢闸阀 DN40 1.6MPa 件 41 不锈钢闸阀 DN40 2.5MPa 件 42 不锈钢闸阀 DN50 1.6MPa 件 43 不锈钢闸阀 DN50 2.5MPa 件 44 不锈钢闸阀 DN65 1.6MPa 件 含不锈钢螺栓 45 不锈钢闸阀 DN65 2.5MPa 件 含不锈钢螺栓 46 不锈钢闸阀 DN80 1.6MPa 件 含不锈钢螺栓 47 不锈钢闸阀 DN80 2.5MPa 件 含不锈钢螺栓 48 不锈钢闸阀 DN100 1.6MPa 件 含不锈钢螺栓 49 不锈钢闸阀 DN100 2.5MPa 件 含不锈钢螺栓 50 不锈钢表前阀 DN15 1.6MPa 件 51 不锈钢表前阀 DN20 1.6MPa 件 52 不锈钢表前阀 DN25 1.6MPa 件 网 53 不锈钢表前阀 DN40 1.6MPa 件 54 不锈钢表前阀 DN50 1.6MPa 件 55 不锈钢表前阀 DN65 1.6MPa 件 务 56 不锈钢表前阀 DN80 1.6MPa 件 57 不锈钢表前阀 DN100 1.6MPa 件 58 不锈钢球阀 DN15 1.6MPa 件 商 59 不锈钢球阀 DN20 1.6MPa 件 60 不锈钢球阀 DN25 1.6MPa 件 61 不锈钢球阀 DN32 1.6MPa 件 道 62 不锈钢球阀 DN40 1.6MPa 件 63 不锈钢球阀 DN50 1.6MPa 件 64 不锈钢球阀 DN65 1.6MPa 件 管 65 Y型过滤器 DN15 1.6MPa 件 66 Y型过滤器 DN15 2.5MPa 件 67 Y型过滤器 DN20 1.6MPa 件 国 68 Y型过滤器 DN20 2.5MPa 件 69 Y型过滤器 DN25 1.6MPa 件 70 Y型过滤器 DN25 2.5MPa 件 中 71 Y型过滤器 DN32 1.6MPa 件 72 Y型过滤器 DN32 2.5MPa 件 73 Y型过滤器 DN40 1.6MPa 件 74 Y型过滤器 DN40 2.5MPa 件 75 Y型过滤器 DN50 1.6MPa 件 76 Y型过滤器 DN50 2.5MPa 件 77 Y型过滤器 DN65 1.6MPa 件 78 Y型过滤器 DN65 2.5MPa 件 2.5 交货地点：招标人指定地点。 2.6 交货期：按业主要求进行供货。合同生效之日起2年或达到合同暂估金额时，合同自行终止。 2.7其他： 2.7.1投标人须按照采购清单要求提供相应型号数量的样品，投标样品须密封装箱，且在密封包装外贴样品一览表 （格式自拟），注明提供样品的投标人名称、生产厂家、品牌、名称、型号、数量等； 2.7.2每件样品上必须分别标明样品的投标人、生产厂家、品牌、名称、型号等（格式自拟），开标时同投标文件 一起提交，由评标委员会核验（提交地点见开标当日交易中心大厅展牌）。本项目第一中标候选人的样品不退还 （第二、三名中标候选人样品在中标通知书发出后5个工作日内退还），其余投标人的样品在评标结束后半小时 内当场退还，如不领取，自行负责。 2.7.3上述要求除递交的样品型号数量应相符外，其余不作为废标的条款，但投标人应主动配合按此要求进行递交。 3.投标人资格要求 3.1 投标人必须是按照国家法律法规设立的，并在中国注册的，具有法人地位的企业；投标人为投标货物的制造 商、代理商或经销商。 网 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表 第1.4.1项内容。 务 3.3本次招标不接受联合体投标。 4.招标文件的获取 4.1 本项目招标不需报名，凡有意参加投标者，请于2026年8月21日起在重庆市公共资源交易网（www.cqggzy.com） 下载本招标项目的招标文件等投标截止时间前公布的所有商相关资料，不管投标人下载与否，招标人和招标代理 机构都视为投标人收到以上资料并全部知晓有关招标过程和事宜，由此产生的一切后果由投标人自负。 4.2、招标文件每份售价1000元，售后不退。投标单位在递交投标文件时通过扫描二维码方式支付购买招标文件 的费用，否则招标人和招标代理机构拒绝接收道其投标文件。 5.投标文件的递交 5.1、投标文件递交的截止时间（投标截止时间，下同）为2026年9月14日11时00分（北京时间）前，地点为重庆 管 市渝北区青枫北路6号渝兴广场B10栋2层重庆市公共资源交易中心开标厅（具体房间见开标当天大厅展牌）。 5.2、逾期送达的、未送达指定地点的或者不按照招标文件要求密封的投标文件，招标人将予以拒收。 6.发布公告的媒介 国 本次招标公告在重庆市公共资源交易网(www.cqggzy.com)上发布。 7.联系方式 中 招 标 人：重庆分质供水有限公司 地 址：重庆市两江新区水务大厦 联 系 人：张老师 电 话：17783738201 招标代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市两江新区嘉华路36号水务大厦 联 系 人：罗辑 电 话：18223151922（工作时间9:00-12:00；14：00-17:00其余时间请勿致电） 2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀采 购项目（包1）（第二次） 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公 中国民生银行股份有限公司重庆分行 9902001764108013 司 重庆联合产权交易所集团股份有限公 重庆农村商业银行股份有限公司沙坪 0304010120010028835008268 司 坝支行 重庆联合产权交易所集团股份有限公 重庆三峡银行九龙坡支行 9696801051298012 司 重庆联合产权交易所集团股份有限公 中信银行重庆上清寺支行 3111230034020042416 司 网 重庆联合产权交易所集团股份有限公 中国农业银行股份有限公司重庆自由 312601010400083780000005565 司 贸易试验区分行 重庆联合产权交易所集团股份有限公 招商银行股份有限公司重庆分行 123904808710630019269 司 务 重庆联合产权交易所集团股份有限公 中国建设银行股份有限公司重庆渝中 6232813760000632694 司 支行 重庆联合产权交易所集团股份有限公 重庆银行股份有商限公司七星岗支行 15010202900420146618927 司 信息来源:https://www.chinapipe.net/project/d3077649.html 道 cqdingjiu 2026.08.24 12:31:42 管 国 中</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>DN15 1.6MPa 件 带压力表；含不锈钢螺栓</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>重庆, 不锈钢闸阀, 不锈钢表前阀, 不锈钢减压阀, 不锈钢排气阀, 不锈钢止回阀, 管材招标</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>长江流域云阳青龙段污水管网一体化建设项目招标计划表</t>
+          <t>重庆市秀山自治县2026年提升农村饮水质量专项行动项目-溶溪片区(一标段)答疑补遗文件</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2637,47 +2609,47 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>云阳县</t>
+          <t>秀山土家族苗族自治县</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>新建污水管网55.5千米，其中DN200管网12千米、DN300管网24千米、DN400管网19.5千米等。</t>
+          <t>重庆市秀山自治县2026年提升农村饮水质量专项行动项目-溶溪片区(一标段)答疑及补遗通知</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>合同预估金额：9100.00万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>污水管网</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>长江流域云阳青龙段污水管网一体化建设项目招标计划表 重庆市工程建设项目招标计划表 项目名称 长江流域云阳青龙段污水管网一体化建设项目 招标法人或 招标人名称 云阳县青江环境综合整治有限公司 网 （盖章） 项目批准文 云阳发改资环【2025】55号 件及文号 务 主要建设内 新建污水管网55.5千米，其中DN200管网12千米、DN300管网24千米、DN400管网19.5千米等。 容 招标方 招标文件计 拟交易场 合同预估金额 序号 招标项目名称 招标内容 备注 式 划发布时间 所 (万元) 商 长江流域云阳 新建污水管网55.5千米， 重庆市公 青龙段污水管 其中DN200管网12千 公开招 共资源交 1 网一体化建设 米、DN300管网24千 2026-08 9100.00 标 易中心云 项目EPC总承 米、DN40道0管网19.5千 招标项目 阳分中心 包 米等。 新建污水管网55.5千米， 长江流域云阳 重庆市公 其中DN200管网12千 青龙段污水管 公开招 共资源交 2 管米、DN300管网24千 2026-08 140.00 网一体化建设 标 易中心云 米、DN400管网19.5千 项目监理 阳分中心 米等监理。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 国 信息来源:https://www.chinapipe.net/project/d3075867.html cqdingjiu 2026.08.21 10:06:53 中</t>
+          <t>重庆市秀山自治县2026年提升农村饮水质量专项行动项目-溶溪片区(一标段)答疑补遗文件 重庆市秀山自治县2026年提升农村饮水质量专项行动项目-溶溪片区（一标段）答疑及补遗通知 各潜在投标人： 现将重庆市秀山自治县2026年提升农村饮水质量专项行动项目-溶溪片区（一标段）答疑及补遗通知发布如下： 答疑部分： 网 问题一、请问重庆双业融资担保有限公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，因为不 能履行保函的见索即付，拒绝赔付。相关业主方在招标文件补遗通知中直接将重庆双业融资担保有限公司列入 担保公司回避名单，拒绝重庆双业融资担保有限公司所出具的保函。由此可见重庆双业融资担保有限公司的信 用资质、履约能力、根本无能力是存在很大问题的。请问以重庆双业融资担保有限公司目前的被执行和不履行 务 投标担保责任的情况是否符合招标文件的要求？ 答：投标人对所提交的履约保函的真实性、合法性、有效性负责，具体要求详见招标文件。 问题二、我司已完供水工程，验收证明材料为"工程竣工商验收鉴定书或者完工验收鉴定书"是否可认定为满足招标 文件要求的业绩的工程竣工验收合格的证明材料 答：满足业绩证明材料要求，业绩的其他要求是否满足由评标委员会依据本项目的招标文件评审后确定。 道 问题三、供水工程是否可认定为满足招标文件要求的供水管网施工业绩 答：供水工程含供水管网满足业绩类别要求，业绩的其他要求是否满足由评标委员会依据本项目的招标文件评 审后确定。 管 问题四、本项目要求投标人具备单项合同额1000万元及以上供水管网施工业绩，请问我司已完房屋建筑工程里面 供水管网金额达到1000万元及以上且有业主出的业主证明，该项目是否可认定为符合招标文件规定的供水管网业 绩标准。 国 答：房屋建筑工程含供水管网且金额达到1000万元及以上，满足招标文件规定的业绩类别和金额的要求，业绩的 其他要求是否满足由评标委员会依据本项目的招标文件评审后确定。 问题五、年度供水管网安装及维护维修劳务合同下子项累计金额达标，提供年度合同+子合同+竣工验收材料+发 中 票是否满足？ 答：不满足招标文件业绩要求。 问题六、本项目委派业主专家吗？ 答：招标文件已明确。 问题七、1、财务报告可以不提供财务报表附注吗？ 答：财务报告可以不提供报表附注。 2、投标函附录中，工期、分包、工程质量、缺陷责任期等要求可以统一填写"达到招标文件要求"吗？ 答：投标函附录中，工期、分包、工程质量、缺陷责任期等要求可以统一填写为"达到招标文件要求”。 3、招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要提供 其他格式之外的其他承诺？ 答：招标文件第八章投标文件格式中(二)承诺部分包含招标文件要求的所有承诺。 4、是否有业代专家参与评标，不要模糊的回答什么依法组建评标委员会。请明确回复有或者没有。 答：招标文件已明确。 5、有人提了一个与项目投标无关的问题。 答：该问题与投标文件编制无关。 6、业绩竣工验收证明材料中有单位盖的项目部章是否认可呢？ 答：不满足业绩证明材料要求。 7、有人提了一个与项目投标无关的问题。 网 答：该问题与本次招标项目无关。 问题八、重庆市电子招投标系统投标文件-报价部分"己标价工程量清单"-"投标总价"页面招标人名称需要填写吗？ 务 答：招标文件未做要求，请投标人自行决定。 问题九、招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 商 答：若招标人提供的工程量清单单项最高限价金额为“0”，则该项清单综合单价报价可以为“0”。 问题十、投标函中的缺陷责任期可以填"达到招标文件的要求"吗？ 道 答：可以。 问题十一、有人提了一个与项目投标无关的问题 管 答：该问题与本次招标项目无关。 问题十二、投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填"/"或"无"还是可以不填 （空白），对此有无要求？ 国 答:填“/”或“无”均可。 问题十三、我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司 盖章，请问需要提供联合体协议书吗？ 中 答：若投标人提供的公司业绩为 epc 业绩，且合同协议书或工程竣工验收合格的证明材料或业主证明能证明该 投标人承担的工作为施工任务的，则不需要提供联合体协议书；若投标人提供的公司业绩为 epc 业绩，但合同协 议书或工程竣工验收合格的证明材料或业主证明不能证明该投标人承担的工作为施工任务的，则需要提供联合 体协议书 问题十四、任一清单的综合单价低于警戒线，就要提供说明吗？ 答：本项目只设置总价异常低价警戒线，不设置单项报价异常低价警戒线。 问题十五、投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写"达到招标文件要求"吗？ 答：投标函附录中，工期、分包、工程质量、缺陷责任期等要求可以统一填写为"达到招标文件要求”。 问题十六、可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗？ 答：不可以。 问题十七、水利灌溉包含供水管网施工业绩满足吗？ 答：水利灌溉工程含供水管网满足业绩类别要求，业绩的其他要求是否满足由评标委员会依据本项目的招标文 件评审后确定。 问题十八、招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 答：若招标人提供的工程量清单单项最高限价金额为“0”，则该项清单综合单价报价可以为“0”。 问题十九、有人提了一个与项目投标无关的问题。 答：该问题与本次招标项目无关。 问题二十、我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收， 请问我公司业绩满足业绩要求吗？ 网 答：不满足招标文件业绩要求。 问题二十一、招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通 知书发出后5日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予 务 提前注销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 答：不需要。 问题二十二、业绩要求的竣工时间是指竣工验收时间吗？商 答：业绩要求的竣工时间是指合同工程完工日期或工程竣工日期。 问题二十三、有人提了一个与项目投标无关的道问题。 答：该问题与本项目无关。 问题二十四、财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 管 答：可以，按招标文件第二章“投标人须知前附表”第1.4.1项第2条要求，投标人须提供会计师事务所或审计机 构出具的合法有效的带二维码的财务审计报告及财务报表，财务报表须至少包括现金流量表、资产负债表、利 润表。 国 问题二十五、现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养 老保险证明材料复印件递交吗？ 答：不需要。 中 问题二十六、自来水厂或者净水厂含管网施工业绩满足业绩要求吗？ 答：自来水厂含管网或者净水厂含管网满足业绩类别要求，业绩的其他要求是否满足由评标委员会依据本项目 的招标文件评审后确定。 问题二十七、有人提了一个与项目投标无关的问题。 答：该问题与本项目无关。 问题二十八、财务报告可以不提供财务报表附注吗？ 答：财务报告可以不提供报表附注。 问题二十九、重庆市电子招投标系统投标文件-报价部分"己标价工程量清单"-"投标总价"页面招标人名称需要填 写吗？ 答：招标文件未做要求，请投标人自行决定。 问题三十、招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还 需要提供其他格式之外的其他承诺？ 答：招标文件第八章投标文件格式中(二)承诺部分包含招标文件要求的所有承诺。 问题三十一、有人提了一个与项目投标无关的问题。 答：该问题与本项目无关。 问题三十二、乡、镇供水厂及供水管道业绩满足业绩要求吗？ 答：乡、镇供水厂及供水管道含供水管网满足业绩类别要求，业绩的其他要求是否满足由评标委员会依据本项 目的招标文件评审后确定。 问题三十三、财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加强审计报告查验工作的通知》 中要求会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第网十四条规定审计业务出具的报告 （以下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标 人提供的财务报告需要赋码和提供深度查询截图吗？ 答：不需要提供深度查询截图。投标人应提供合法有效的财务审计报告及财务报表，并对其真实性负责，招标 务 人有权对投标人提供的资料进行核实，若发现弄虚作假，按相关规定取消其中标资格，并按相关法律法规报招 标投标监督部门。 问题三十四、技术负责人在资格审查部分中提供了工程类高级及以上职称证后，在商务部分中再提供工程类高 级及以上职称证可以加分吗？ 商 答：可以。 问题三十五、专业分包业绩满足业绩要求吗？道 答：不满足招标文件业绩要求。 问题三十六、请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件 管 格式不一致的以哪个为准？ 答：若招标文件中第八章的投标文件格式与制作软件中格式有不一致的情况，则应以加盖电子印章的招标文件 （即PDF版）为准（除制作软件自动生成无法修改的外），其制作软件中的格式是为方便投标人编制投标文件使 用。 国 问题三十七、在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、 注册证及在本单位注册的证明文件替代？ 中 答：不可以。 问题三十八、市政工程包含给水管网施工业绩满足业绩要求吗？ 答：市政工程含供水管网满足业绩类别要求，业绩的其他要求是否满足由评标委员会依据本项目的招标文件评 审后确定。 问题三十九、本项目委派业主专家吗？ 答：招标文件已明确。 问题四十、1、本项目总价是否有异常低价警戒线？ 答：本项目设置总价异常低价警戒线。 2、本项目清单综合单价是否有异常低价警戒线？如有具体是警戒线金额或百分比是多少？ 答：本项目只设置总价异常低价警戒线，不设置单项报价异常低价警戒线。 3、招标清单中限价为0或空白的清单能不能报价？ 答：若招标人提供的工程量清单单项最高限价金额为“0”，则该项清单综合单价报价可以为“0”。 4、招标清单中限价为0或空白的清单能不能不报价？ 答：若招标人提供的工程量清单单项最高限价金额为“0”，则该项清单综合单价报价可以为“0”。 5、本项目评标委员会是否有招标人代表？ 答：招标文件已明确。 补遗部分： 招标文件投标人须知前附表10.7其他2.交易服务费修改为：“2.交易服务费：按照网渝发改收费〔2023〕115号文件 规定，重庆联合产权交易所集团股份有限公司将向中标人收取交易服务费，本项目交易服务费由中标人全额支 付。” 招标人：秀山秀兴发展集团有限公司 务 招标代理机构：重庆杨川建筑工程咨询有限公司 2026年8月21日 商 信息来源:https://www.chinapipe.net/project/d3077605.html cqdingjiu 2026.08.24 12:31:43 道 管 国 中</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>DN200管网：12千米；DN300管网：24千米；DN400管网：19.5千米；污水管网：55.5千米</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 污水管网, 资金情况, 产品种类</t>
+          <t>重庆, 提升农村饮水质量, 专项行动项目</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>中国电建水电四局华中公司重庆轨道交通17号线一期5标项目雨污水排水迁改工程施工劳务分包采购项目公开询比采购公告</t>
+          <t>酉阳县桃花源新城供水工程管网安装工程专业分包采购公告</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2706,45 +2678,49 @@
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>酉阳土家族苗族自治县</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>重庆轨道交通17号线一期5标段包含金凤北站（不含）～终点（3站5区间的土建）：高龙大道站、斑竹林站、石家院子站、金凤北站～高龙大道站区间、高龙大道站～斑竹林站区间、斑竹林站～石家院子站区间、石家院子站～终点区间、7/17号线联络线区间。采购范围为雨污水排水迁改工程。</t>
+          <t>酉阳县桃花源新城供水工程管网安装工程专业分包</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>建设资金来源已落实，但具体资金数额未明确。</t>
+          <t>暂无明确资金信息</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>雨污水排水迁改工程</t>
+          <t>管网安装工程</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>中国电建水电四局华中公司重庆轨道交通17号线一期5标项目雨污水排水迁改工程施工劳务分包采购项目公开询 比采购公告 询比采购公告 采购编号： PC-0104-26J6-FP0895 一、采购条件 受中国水利水电第四工程局有限公司重庆轨道交通17号线一期5标项目委托，中水电四局华中（武汉）工程有限 公司以公开询比方式采购重庆轨道交通17号线一期5标雨污水排水迁改工程项目网，建设资金来源已落实。目前项 目已具备采购条件，现进行公开询比采购。 二、项目概况、采购范围 务 1、项目概况：重庆轨道交通17号线一期5标段包含金凤北站（不含）～终点（3 站5 区间的土建）：高龙大道 站、斑竹林站、石家院子站、金凤北站～高龙大道站区间、高龙大道站～斑竹林站区间、斑竹林站～石家院子 站区间、石家院子站～终点区间、7/17号线联络线区间。 2、采购范围： 商 （1）雨污水排水迁改工程 （2）工程招标范围工作内容：17号线一期5标道中高龙大道站、斑竹林站及高斑竖井位于城市既有道路下方，设计 采用明挖法施工。为保证市政排水管网的正常使用，在明挖施工前需对既有管网进行临时迁改，车站结构施工 后进行恢复。施工PE钢带管长度2387米、B型排水管长度2799m、钢筋混凝土管127米，检查井239座劳务部分。 （3）施工内容详见工程量清单，以及为完成此项工程而做的一切工作。 管 3、计划工期:计划开工日期：2026年9月25日（具体时间以采购人通知为准），计划完工日期：2027年 12 月25 日； 合同工期总日历天数为457天。 4、质量要求：符合《国给水排水管道工程施工及验收规范》（GB 50268）、《混凝土结构工程施工质量验收规范》 （GB 50204）、《城镇道路工程施工与质量验收规范》（CJJ 1-2008）以及项目所在地最新的相关法规、标准和 图集。工程质量全面达到设计要求和标准，其中：验收合格率 100%，优良率达 90%以上，工程综合验收质量评 定达优良标准。 中 5、付款方式：采用银行转账/支票支付工程价款，月度结算完成具备付款条件后30天内工程进度款支付比例约定 为扣除各项保证金及费用后应付价款不低于65%；清算完成并签订《退场协议》后30天内工程进度款支付比例约 定为扣除各项保证金及费用后应付价款不低于80%；清算完成并签订《退场协议》后一年内工程进度款支付比例 约定为扣除响应人缺陷责任等相关费用后应付价款不低于90%；清算完成并签订《退场协议》，办理完成保证金 退还手续后两年内，工程进度款支付比例约定为扣除响应人缺陷责任等相关费用后应付价款的100%。 6、其他：无。 三、响应人资格要求 响应人必须满足以下全部资格要求： （1）资质要求：施工劳务不分等级 （2）主要人员要求:授权委托人（如有）及项目经理、专职安全员应提供社保和劳动合同。其中劳动合同至少提 供首、末两页，并且包含有关人员的详细信息;社保证明应提供响应截止时间前三个月的社保缴纳记录。 （3）安全三类人员要求:应提供企业主要负责人安全A证、项目经理B证、专职安全员C证。 （4）响应人具有良好的银行资信和商业信誉，没有处于被责令停业，财产被接管、冻结、破产状态。 （5）响应人应具有 雨污水排水迁改 工程的施工业绩，在近 5年内(2021年7月-2026年7月内签订)的施工合同不少 于 1 个，且签订单项合同金额均在 100 万元以上（应附成交通知书和（或）合同扫描件）。 （6）其它要求:无。 （7）本次采购不接受联合体响应。 四、采购文件的获取 凡满足本公告规定资格要求并有意参加的响应人，请于2026年8月22日10时00分前在中国电建采购招标数智化平台 （https://bid.powerchina.cn/bidweb/#/login，以下简称“数智化平台”）获取采购文件，采购文件免费提供。 五、响应文件的递交 1、响应文件递交的截止时间（响应截止时间，下同）为2026年8月26日10时30分网（北京时间），响应人应在截止 时间前通过数智化平台递交电子响应文件。 2、本次采购将通过数智化平台全程在线开展，电子响应文件的加密、提交等流程须响应人在线进行操作。响应 人须提前办理数字证书用于在线递交响应文件，办理方式详见数智化平台首页，并严格按照要求进行在线操作， 务 因操作流程失误造成的递交失败将由响应人自行承担后果。 3、开启由“数智化平台”在响应截止时间后自动对响应文件进行解密，响应人及时关注开启结果。 4、响应截止时间如有变动，采购人将及时通知已获取采商购文件的响应人。 六、发布公告的媒介 本次询比采购公告同时在中国电建阳光采购网道（https://bid-zb.powerchina.cn）上发布。 七、评审办法 采用综合评估法。 管 八、联系方式 采 购 人： 中水电四局华中（武汉）工程有限公司 国 地 址： 湖北省武汉市江岸区塔子湖东路健美街30号立城中心商务楼13、14层 邮 编： 430014 中 联 系 人： 王飞 电 话： 15827222587 电子邮箱： 107830343@qq.com 九、提出异议的渠道和方式 单位名称： 中水电四局华中（武汉）工程有限公司 电 话： 17708178186 电子邮箱： sjhzgsjw@163.com 十、纪检监督机构 响应人或者其他利害关系人认为本次采购活动存在违规违纪行为的，可以书面形式向中国水利水电第四工程局 有限公司中水电四局华中（武汉）工程有限公司纪委办公室（联系方式：17708178186）提出投诉。 2026年8月 19 日 报价网址:https://bid.powerchina.cn/notice/detail?id=2409510708 信息来源:https://www.chinapipe.net/project/d3075750.html cqdingjiu 2026.08.21 10:06:53 网 务 商 道 管 国 中</t>
+          <t>酉阳县桃花源新城供水工程管网安装工程专业分包采购公告 酉阳县桃花源新城供水工程管网安装工程专业分包 采购公告 一、采购概况 1.采购名称：【酉阳县桃花源新城供水工程管网安装工程专业分包】 网 2.工程概况： 工程名称：酉阳县桃花源新城供水工程 务 项目地址：重庆市酉阳县桃花源新城 建筑规模：【新建5万吨m3/d的水厂一座（含水厂进场道路工程、水厂总图工程、水厂常规处理工程、泥沙处理 工程、水厂电气自控安装工程、水厂厂前办公楼建筑工程商）；5万吨m3/d的取水泵站一座（含泵站的土建工程、 设备采购及安装工程、泵站外电源实施工程）；铺设原水输水管网总长度约16.7公里（含管网土建及安装工程、 管材及管件采购工程）；配套建设新城供水主管约77km（含管网土建及安装工程、管材及管件采购工程）】。 3.标段划分：【本工程仅一个标段】。 道 4.采购内容：【酉阳县桃花源新城供水工程管网安装工程】。 5.质量要求：【达到一次性验收合格标准，工程质量符合国家现行相关规范、规定标准】。 管 6.工期要求：【暂定开工日期：2026年9月20日，竣工日期2026年11月20日，总工期61日历天。实际开竣工日期以 发包人要求为准，分包人应无条件配合且不得对此安排提出异议或索赔】。 7.安全文明要求：【工国程质量符合强制性质量标准，符合国家和重庆市现行有关施工质量验收规范要求，并达到 合格标准，一次验收质量达到合格等级满足承包人质量和管理行为的要求,同时满足项目部技术质量交底要求， 通过验收。质量管理目标：创重庆市优质工程“巴渝杯”。具体施工标准满足《中建四局交通公司房屋建筑项 目安全标准化图集（2026版）》。 中 8.付款条件：【1、本工程无预付款；2、按月支付，按每月完成合格实物量的75%支付进度款；3、合同范围内所 有工程完工确认合格后调整支付比例至85%；4、结算完成后付至分公司终审值的97%，剩余3%质量保证金在本 项目工程验收合格满两年后扣除维修费用且完善甲方请款流程后一次性无息返还。】 9.拟选定成交单位数：【 1 】。 二、报价人资格 1.报价人报名前需通过“云筑网”（网址：https://jicai.yzw.cn/home）认证并进入中建系统合格分供方资源库，经 采购人资格审查合格后方可参与报价。 2.报价人需具备以下基本条件：【具备营业执照、市政公用工程施工总承包贰级及以上资质、安全生产许可证、 有类似项目工程业绩（报名时需上传以上相关附件资料）资信良好，有一定资金能力、人员结构完善、管理能 力强等】。 3.本次采购不接受联合体报价。 4.如报价单位提供虚假资料的，任何时候一经发现，取消其报价资格。 三、报价报名 1.报名时间：【截至2026年8月23日9时，以“云筑网”平台显示时间为准】，逾期不再接受报名。 2.报名方式：通过“云筑网”进行网上报名，不接受其他方式报名。 3.已在“云筑网”完成分供方注册的报价人，可直接在“云筑网”签收采购公告后报名。 未在“云筑网”注册的报价人，需先进行注册，提交以下资料【包括企业营业执照、资质证书、安全生产许可 证、银行开户许可证、主要业绩材料及证明、法定代表人身份证明及身份证等】，经采购人审查合格并完成分 供方认证后，方可报名。 4. 报价保证金：本次报价的报价保证金为【1000】元，报价人应于报价截止日24小时前缴纳。 5.首轮响应文件开启后无条淘汰报价最高的前10%且不少于1家单位（小数向上取整）。 四、发放采购文件 网 1.采购人通过“云筑网”对资格审查合格的报价人发放采购文件。 2.发放时间：见云筑网要求时间。 务 3.联系人：现场联系人：苏忠明 联系方式： 18608774750 ，分公司成本管控中心：【赵经理】，联系方式： 【15925129017】，联系地址：【昆明市官渡区新亚洲体育场星都总部基地48栋 】。 4.其他未尽事宜详见采购文件。 商 采购人：中国建筑第四工程局有限公司 道 日 期：2026年8月20日 管 信息来源:https://www.chinapipe.net/project/d3077567.html cqdingjiu 2026.08.24 12:31:43 国 中</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>型排水管：2799m；钢筋混凝土管：127米；检查井：239座</t>
+          <t>铺设原水输水管网总长度约16.7公里，配套建设新城供水主管约77km</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>重庆, 轨道交通, 雨污水排水迁改, 施工劳务分包</t>
+          <t>酉阳县桃花源新城供水工程, 管网安装工程专业分包, 重庆, 管网安装工程</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>万州区2026年超长期特别国债高标准农田建设项目拟进行预制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜的信息公告</t>
+          <t>重庆市益康环保工程有限公司永川分公司污水外排管道迁改项目询比采购公告</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2754,7 +2730,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>房建</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2775,27 +2751,27 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>万州区</t>
+          <t>永川区</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>本项目涉及预制钢筋砼管、成品混凝土仿木栏杆等材料的采购。</t>
+          <t>污水外排管道迁改</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>建设资金为国债资金，项目出资比例为100%。具体预算金额未在文本中明确列出。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>预制钢筋砼管,成品混凝土仿木栏杆</t>
+          <t>排水钢管</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>万州区2026年超长期特别国债高标准农田建设项目拟进行预制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜的 信息公告 1.采购条件 1.1本项目万州区2026年超长期特别国债高标准农田建设项目工程已由 重庆市万州路桥建设有限公司承建，项目 业主为重庆市万州区农业技术与机械推广中心，代建业主为重庆市万州区农业发展有限公司，建设资金为国债 资金，项目出资比例为 100% ，承包人为重庆市万州路桥建设有限公司。项目已具备施工条件，现对该项目的预 制钢筋砼管、成品混凝土仿木栏杆等材料采购事宜发布信息公告。 网 2.项目概况与采购范围 2.1建设地点：重庆市万州区走马镇、瀼渡镇、罗田镇、余家镇、高梁镇、分水镇、柱山乡等7个镇乡。 务 2.2本项目材料采购拟进行比选情况如下： 罗田镇谷山片区材料采购费暂定金额约： 17.5万元； 余家镇桥亭片区材料采购费暂定金额约： 17.99万元； 商 柱山乡山田片区材料采购费暂定金额约： 26.32 万元； 走马镇凉风片区材料采购费暂定金额约： 15.道66万元； 瀼渡镇高村片区材料采购费暂定金额约： 17.72 万元； 分水镇大冲片区材料采购费暂定金额约： 47.12 万元； 管 高梁镇茨坪片区材料采购费暂定金额约： 10.7万元； （以上片区片区金额为暂定金额，最终比选限价金额以比选文件为准）。 国 2.3计划采购周期： 以合同签订为准 日历天。 2.4采购范围：本项目各片区所包含的预制钢筋砼管、成品混凝土仿木栏杆等材料。 中 3.供应商资格要求 3.1本次材料采购要求供应商具备独立企业法人，具有本次所需材料生产能力的厂家或经销商等，其经营范围和 权限应满足本次所需材料的要求，并依法取得国家行政主管部门颁发的有效工商营业执照(建筑材料销售或水泥 制品制造、水泥制品销售等相关营业资格），所提供产品必须满足各项检测要求，达到国家现行标准规定的合 格标准。具有良好的商业信誉和充分的供应保障能力，具备相应售后服务能力。要求竞选人为一般纳税人，可 开具13%税率增值税专用发票，提供一般纳税人认定证明。 3.2本次供应商单位优先选择万州本地企业。 3.3本次 不接受 联合体竞选。 4. 报名要求 4.1报名时间：2026年8月 19日9:00起至 8月21日17:00止。 4.2报名地点：重庆市万州路桥建设有限公司经营部（重庆市万州区天城东路278号）。 4.3报名时，须提交有效的营业执照(有效工商营业执照((建筑材料销售或水泥制品制造、水泥制品销售等相关营 业资格）)，前述证书均为复印件并加盖单位公章。法定代表人参加报名的不需要授权委托书，只需要提供法定 代表人身份证明；非法定代表人参加报名的除提供法定代表人身份证明外还须提供授权委托书、委托代理人身 份证明。 4.4 本项目材料采购需提前报名。经资格预审合格后，通知资格预审合格的供应商，到承包人单位领取相关文件。 4.5本项目材料采购设七个片区进行比选，为保证比选公平、公正、有效，规定同一参选单位报名片区上限为2个， 且最终仅限中选一个片区。 5.联系方式 承包人：重庆市万州路桥建设有限公司 地 址：重庆市万州区天城东路278号 网 联系人： 张红娟 电 话：15923491915 务 邮 箱： 商 重庆市万州路桥建设有限公司 2026年8月19日 道 信息来源:https://www.chinapipe.net/project/d3075512.html cqdingjiu 2026.08.21 10:06:53 管 国 中</t>
+          <t>重庆市益康环保工程有限公司永川分公司污水外排管道迁改项目询比采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3077531.html cqdingjiu 2026.08.24 12:31:43 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2804,18 +2780,18 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>重庆, 预制钢筋砼管, 成品混凝土仿木栏杆, 国债资金, 高标准农田建设</t>
+          <t>重庆, 四川, 管材, 招标</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资(污水管道)招标采购流标公告</t>
+          <t>重庆市巴南区龙洲湾片区城市污水管网更新改造工程施工招标公告</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2846,47 +2822,47 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>酉阳土家族苗族自治县</t>
+          <t>巴南区</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资(污水管道)公开招标采购。</t>
+          <t>本项目改建及修复管网总长度约30.98公里，雨污水错混接改造以及管网缺失改造DN300-DN600排水管网约2.0公里；修复DN300-DN1000管道约28.98公里。</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>项目总投资金额：10063.6万元，本次招标项目合同估算金额：6033.535232万元</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>污水管道</t>
+          <t>排水管网</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资(污水 管道)招标采购流标公告 发布单位：中国铁建/中铁十一局/六公司 发布时间：2026-08-19 10:40:49 投标截至时间：2026-08-18 10:00:00 内容： 各投标人： 网 中铁十一局集团第六工程有限公司酉阳县钟多、桃花源片区污水管网新建改造工程(二期)项目经理部物资（污水 管道）公开招标采购（采购编号： CR1106-JC-2026-26-02）评标工作，已于北京时间2026年08月18日10:00整，在 铁建云链（https://www.crccep.com）线上平台公开开标。评审委员会根据招标文件载明的评审办法完成评审工作， 现将评审结果公示如下： 务 一、招标公告发布日期及媒体 招标公告发布日期：2026年07月27日至2026年08月01日 商 招标公告媒体：铁建云链（https://www.crccep.com） 二、拟中标信息 道 公开招标采购编号：CR1106-JC-2026-26-02 包件号：WSGD-01 序号 供应商名称 推荐排序 管 1 无 1 国 以上包件有效投标不足三家，本次招标做流标处理。 三、公示时间 中 自2026年08月19日始，至2026年08月22日止。在公示期间，所有竞标人和其他利害关系人如对公示的评审结果有 异议，可以向相关监督部门举报，逾期将不再受理。举报人必须由其法定代表人或者授权代表签字并盖章，其 他组织或者个人举报的，必须由其主要负责人或者本人签字，并附有效身份证明复印件。举报人如实反映情况 受法律保护。 公示期满，如无异议，即时生效。 监督竞诉受理部门： 中铁十一局集团第六工程有限公司招采中心 联系电话：18671041790 信息来源:https://www.chinapipe.net/project/d3075461.html cqdingjiu 2026.08.21 10:06:53</t>
+          <t>重庆市巴南区龙洲湾片区城市污水管网更新改造工程施工招标公告 重庆市巴南区龙洲湾片区城市污水管网更新改造工程施工招标公告 1.招标条件 本招标项目 重庆市巴南区龙洲湾片区城市污水管网更新改造工程 已由 重庆市巴南区发展和改革委员会 以 巴南发改审发〔2026〕103号 批准建设，项目业主为重庆市城镇排水事务中心，代建业主为重庆水务环境 控股集团管网有限公司，建设资金来自 争取上级补助资金及区级财政资金配套 ，项目出资比例为100%，招 标人为重庆水务环境控股集团管网有限公司。项目已具备招标条件，现对该项目的施工进行公开招标，评标办 法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：重庆市巴南区龙洲湾街道 2.2 项目概况与建设规模：本项目改建及修复管网总长度约30.98公里，雨污水错混接改造以及管网缺失改 造DN300-DN600排水管网约2.0公里；修复DN300-DN1000管道约28.98公里。危大工程主要涉及深基坑及有限空 务 间作业，其中深基坑对应部位与环节为：加井修复、裂管工作井部分；有限空间作业主要为非开挖修复工程。 2.3 本项目工程总投资金额：10063.6万元 商 本次招标项目合同估算金额：6033.535232万元 2.4 招标范围：招标人提供的工程量清单及编制说明、设计图纸、技术文件等包括的所有工作内容，包括但不 限于：施工图所示范围内的土石方工程，管网改扩建，管道缺陷修复，路面破除恢复、相关附属设施破除及恢 复、行道树的移栽等所有工作内容。具体详见道招标人提供的工程量清单。 2.5 工期要求：270日历天 缺陷责任期要求：24个月 管 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 国 3.1 是否属于政府采购工程：是 3.2 是否专门中面向中小企业预留：是 专门面向中小企业预留的实施方式：本项目以合同分包形式面向中小企业，分包给中小企业的合同份额需达 到40%以上。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件、工程量清单、 电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理， 办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。 若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 布至2026-08-26 17:00:00前。 5.3招标人应于2026-08-28 23:59:59前在重庆市公共资源交易网发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-20 10:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在“重庆市公共资源交易监督网”和“重庆市公共资源交易网”发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 网 招 标 人: 重庆水务环境控股集团管网有限公司 代理机构: 重庆市工程管理有限公司 地 址: 重庆市渝中区重庆总部城A区11栋 地 址: 重庆市两江新区五简路2号重咨大厦A座 邮 编: 邮 编: 务 项目负责人: 程鹏 项目负责人: 鲜颖 电 话: 023-63995075 电 话: 17323966277 传 真: 传 真商: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 道账 号: 监督部门: 重庆市巴南区发展和改革委员会 电 话: 023-66221670 管 2026年08月21日 重庆市巴南区龙洲湾片区城市污水管网更新改造工程施工 户名 开户行 投标保证金账号 国 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020004772 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000697127 支行 中 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051303175 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000013052 贸易试验区分行 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630016759 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146619084 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835012249 坝支行 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764158547 信息来源:https://www.chinapipe.net/project/d3077506.html cqdingjiu 2026.08.24 12:31:43</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>DN300-DN600排水管网约2.0公里；修复DN300-DN1000管道约28.98公里</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 酉阳县, 污水管网, 新建改造工程</t>
+          <t>重庆, 管材, 招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>协同创新区-四期房建三标段镀锌管件物资竞价采购公告</t>
+          <t>土桥、宗申、界石排水箱涵清污分流改造项目施工招标公告</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2896,7 +2872,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>房建</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2918,42 +2894,42 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>详见附件。</t>
+          <t>本项目改建及修复管网总长度约30.63公里，雨污水错混接改造以及管网缺失改造DN300-DN800排水管网约6.35公里；修复DN300-DN1200管道约24.28公里。</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>项目总投资金额：9551.19万元，本次招标项目合同估算金额：5383.510617万元</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>镀锌管件</t>
+          <t>排水管网</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>协同创新区-四期房建三标段镀锌管件物资竞价采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3075420.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
+          <t>土桥、宗申、界石排水箱涵清污分流改造项目施工招标公告 土桥、宗申、界石排水箱涵清污分流改造项目施工招标公告 1.招标条件 本招标项目 土桥、宗申、界石排水箱涵清污分流改造项目 已由 重庆市巴南区发展和改革委员会 以 巴南发 改审发〔2026〕102号 批准建设，项目业主为重庆市城镇排水事务中心，代建业主为重庆水务环境控股集团管网 有限公司，建设资金来自 争取上级补助资金及区级财政资金配套 ，项目出资比例为100%，招标人为重庆水务 环境控股集团管网有限公司。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估 法。 2.项目概况与招标范围 网 2.1 建设地点：重庆市巴南区花溪、李家沱街道及界石镇 务 2.2 项目概况与建设规模：本项目改建及修复管网总长度约30.63公里，雨污水错混接改造以及管网缺失改 造DN300-DN800排水管网约6.35公里；修复DN300-DN1200管道约24.28公里。项目存在危大工程，危大工程主要 涉及深基坑及有限空间作业，其中深基坑对应部位与环节为：加井修复、微顶管井施工，裂管工作井部分；有 限空间作业主要为箱涵内施工管网及非开挖修复工程。 商 2.3 本项目工程总投资金额：9551.19万元 道 本次招标项目合同估算金额：5383.510617万元 管 2.4 招标范围：招标人提供的工程量清单及编制说明、设计图纸、技术文件等包括的所有工作内容，包括但不限 于：施工图所示范围内的土石方工程，管网改扩建，管道缺陷修复，路面破除恢复、相关附属设施破除及恢复、 行道树的移栽等所有工国作内容。具体详见招标人提供的工程量清单。 2.5 工期要求中：270日历天 缺陷责任期要求：24个月 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 3.1 是否属于政府采购工程：是 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式：本项目以合同分包形式面向中小企业，分包给中小企业的合同份额需达 到40%以上。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质； 网 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 务 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿商。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人道在投标前可在重庆市公共资源交易网下载招标文件、工程量清单、 电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理， 办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。 若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 管 布至2026-08-26 17:00:00前。 5.3招标人应于2026-08-28 23:59:59前在重庆市公共资源交易网发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-20 10:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登国录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公中告同时在“重庆市公共资源交易监督网”和“重庆市公共资源交易网”发布。[提示：依法必须招标 项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆水务环境控股集团管网有限公司 代理机构: 重庆市工程管理有限公司 地 址: 重庆市渝中区重庆总部城A区11栋 地 址: 重庆市两江新区五简路2号重咨大厦A座 邮 编: 邮 编: 项目负责人: 程鹏 项目负责人: 鲜颖 电 话: 023-63995075 电 话: 17323966277 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市巴南区发展和改革委员会 电 话: 023-66221670 2026年08月21日 土桥、宗申、界石排水箱涵清污分流改造项目施工 户名 开户行 投标保证金账号 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000012057 贸易试验区分行 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020039234 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764235311 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146612313 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 网9696801051301643 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630014874 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835008473 坝支行 务 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000764299 支行 商 水施-02土桥、宗申、界石排水箱涵清污分流改造项目-管网修复子项附件详见链 接：https://www.cqggzy.com/trade/014001/b09ced5a-3672-45a5-94be-2dcdcab6972e?categoryNum=014001001002 水施-01土桥、宗申、界石排水箱涵清污分流道改造项目-管网改造子项附件详见链 接：https://www.cqggzy.com/trade/014001/b09ced5a-3672-45a5-94be-2dcdcab6972e?categoryNum=014001001002 信息来源:https://www.chinapipe.net/project/d3077435.html cqdingjiu 2026.08.24 12:31:44 管 国 中</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>排水管网修复</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 商机</t>
+          <t>重庆, 排水管网, 管网修复, 管网改造</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>长江一级支流溉澜溪流域(新华水库混流箱涵)污水收集效能提升工程(渝北区)施工答疑补遗文件</t>
+          <t>巫溪县花台片区川主、农坡等5个村迁建区特色农业抗旱供水保障工程勘察设计招标计划表</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2963,7 +2939,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2984,47 +2960,47 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>渝北区</t>
+          <t>巫溪县</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>长江一级支流溉澜溪流域(新华水库混流箱涵)污水收集效能提升工程(渝北区)施工答疑补遗文件</t>
+          <t>主要整治孝子溪大堰水渠约17.5km;新建孝子溪水库引水管道约17.5km,其中需新建引水隧洞内置管道约1.5km;新建柑橘基地管网约3.25km;改建6000m蓄水池1座；新建2000m蓄水池2座；新建1000m蓄水池1座；新建500m³蓄水池2座；新建柑橘基地滴灌系统1套。</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>合同预估金额为340万元（含水土保持施工图设计）。</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>勘察设计服务</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>长江一级支流溉澜溪流域(新华水库混流箱涵)污水收集效能提升工程(渝北区)施工答疑补遗文件 长江一级支流溉澜溪流域（新华水库混流箱涵）污水收集效能提升工程（渝北区）施工答疑文件 各潜在投标人： 现将“长江一级支流溉澜溪流域（新华水库混流箱涵）污水收集效能提升工程（渝北区）施工”公开招标项目 答疑文件发布。本答疑文件是在招标文件的基础上作出的澄清、说明或补正，与招标文件具有同等法律效力， 若相关内容与原招标文件不一致时，一律以本答疑文件内容为准。 网 一、答疑部分： 问题一：1、我公司于2026年进行了优势合并整合，现准备使用合并前公司项目业绩作为本次我司投标的投标人 业绩证明，并提供上级主管单位出具的相关吸收合并文件或两家公司签订的吸收合并协议，请问是否可视为满 务 足招标业绩要求？ 2、我单位为中型企业，其控股股东为大企业，但我单位不属于大企业的分支机构，也不存在与大企业的负责人 为同一人的情形。鉴于此种情况，我单位应提供《中小企业声明函（工程类）》还是《中小企业承担合同份额 承诺函》？ 商 回复：1. 满足，但还需满足招标文件对业绩的其他要求。最终由评标委员会根据投标人提供的证明材料并结合 招标文件要求进行评审； 道 2. 贵司其控股股东为大企业，故需提供中小企业承担合同份额承诺函。 问题二：本项目有无业主专家参与评标？ 管 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 问题三：请明确是否有业主专家 是否异地评标 回复：1. 该项目评标委国员会由招标人按法律法规及相关规定依法组建。 2.本项目是异地评标。 问题四：1、财务报告可以不提供财务报表附注吗? 中 2、投标函附录中，工期、分包、工程质量、缺陷责任期等要求可以统一填写"达到招标文件要求"吗? 3、招标文件第八章投标文件格式中(二)承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要提供其 他格式之外的其他承诺? 4、是否有业代专家参与评标，不要模糊的回答什么依法组建评标委员会。请明确回复有或者没有。 5、本项目是否异地评标？ 6、业绩竣工验收证明材料中有单位盖的项目部章是否认可呢？ 回复：1. 可以不提供财务报表附注。 2. 可以统一填写"达到招标文件要求"。 3. 投标人自行核实招标文件要求提供的承诺要求，如有需要，还需补充提供招标文件第八章投标文件格式中 （二）承诺部分之外的其他承诺。 4. 该项目评标委员会由招标人按法律法规及相关规定依法组建。 5. 本项目是异地评标。 6. 不认可。 问题五：请问**公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，因为不能履行保函的见索即 付，拒绝赔付。 相关业主方在招标文件补遗通知中直接将**公司列入担保公司回避名单，拒绝**公司所出具的保函。由此可 见**公司的信用资质、履约能力、根本无能力是存在很大问题的。请问以**公司目前的被执行和不履行投标担保 责任的情况是否符合招标文件的要求? 回复：纸质投标保函的开立人应当是具有相应资格的银行、保险机构、融资担保公司，其信用资质、履约能力、 担保能力、赔付流程、安全保密等应符合工程保函业务条件。纸质投标保函应合网法合规，符合招投标行政监督 部门、行业主管部门和金融监管部门的相关规定，满足招标文件约定要求。投标人应选择在渝依法设立总部或 者设有分支机构的金融机构开具纸质投标保函。投标人对所提交的纸质投标保函的真实性、合法性、有效性负 责。以纸质投标保函形式交纳投标保证金是否符合招标文件要求，由评标委员会评标时，根据招标文件要求进 行独立评审，并作出相应评审判断。 务 问题六：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 回复：经核实，招标文件（PDF签章版）中投标文件格式商与重庆市电子招投标系统投标文件制作软件中格式一致。 可能因重庆市电子招投标系统投标文件制作软件中的格式页边距与招标文件（PDF签章版）不一致的原因导致格 式显示不一致，该情形不影响投标人编制投标文件。若重庆市电子招投标系统投标文件制作软件导出的投标文 件格式与招标文件（PDF签章版）的投标文件格式不一致，以重庆市电子招投标系统投标文件制作软件导出的投 标文件格式为准。 道 问题七：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖 章，请问需要提供联合体协议书吗？ 管 回复：若投标人提供的公司业绩为epc业绩，且合同协议书或工程竣工验收合格的证明材料或业主证明能证明该 投标人承担的工作为施工任务的，则不需要提供联合体协议书；若投标人提供的公司业绩为epc业绩，但合同协 议书或工程竣工验收合格的证明材料或业主证明不能证明该投标人承担的工作为施工任务的，则需要提供联合 体协议书。 国 问题八：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可 以不填(空白)，对此有无要求？ 回复：投标中文件中下划线上、空格处、表格中无需要填写或无法填写内容的，填“/”或“无”均可。 问题九：公园施工业绩符合吗？ 回复：公园概念太宽泛，无法判定该施工业绩是否属市政工程，请投标人自行核实，并按招标文件要求提供施 工业绩证明材料，其是否满足要求应由评标委员会根据证明材料具体内容进行判定。 问题十：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需 要提供其他格式之外的其他承诺？ 回复：投标人自行核实招标文件要求提供的承诺要求，如有需要，还需补充提供招标文件第八章投标文件格式中 （二）承诺部分之外的其他承诺。 问题十一：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收， 请问我公司业绩满足业绩要求吗？ 回复：不满足。 问题十二：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗？ 回复：投标人投标总报价低于招标文件规定的对应的异常低价警戒线的，应提供报价合理性说明，并提供必要 的证明材料。证明材料由投标人自行提供，但提供的说明不得降低或者改变原设计方案、技术工艺、施工标准， 不得影响项目的质量、安全、工期、结算等正常履约。 问题十三：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 回复：按照招标文件要求“提供：会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表，财务 报表须至少包括现金流量表、资产负债表、利润表”。 问题十四：业绩要求的竣工时间是指竣工验收时间吗？ 回复：本项目业绩要求所指竣工时间，即为工程竣工验收合格证明载明的竣工验收时间。 问题十五：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知 书发出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面网通知相关金融机构本项目准 予提前注销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 回复：纸质投标保函原件上未加盖“正本”字样的，不因此否决投标，但投标人应确保提交的保函为唯一正本。 若因保函真伪问题导致的一切不利后果由投标人自行承担。 务 问题十六：燃气管道安装施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 商 问题十七：请问招标人是否委派业主专家参与评标吗？ 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 道 问题十八：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 回复：根据招标文件“投标人的工程量清单单项报价不得为零报价（招标人提供的工程量清单单项最高限价中 金额为零的除外）或者负数报价”，招标人提供的工程量清单单项最高限价中金额为零的，该项清单综合单价 管 报价可以为0。 问题十九：自来水厂或者净水厂施工业绩满足业绩要求吗？ 回复：满足，但还需满国足招标文件对业绩的其他要求。 问题二十：财务报告可以不提供财务报表附注吗？ 回复：可以不提供财务报表附注。 中 问题二十一：老旧小区室外环境改造施工业绩符合吗？ 回复：不满足。 问题二十二：有人提出一个无关问题。 回复：无关问题不予回复。 问题二十三：任一清单的综合单价低于警戒线，就要提供说明吗？ 回复：本招标项目单项报价未设置异常低价警戒线。 问题二十四：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题二十五：本项目是异地评标吗？ 回复：本项目是异地评标。 问题二十六：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、 注册证及在本单位注册的证明文件替代？ 回复：不满足。 问题二十七：污水处理厂提标改造施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题二十八：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 回复：可以填“达到招标文件的要求”。 问题二十九：财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加网强审计报告查验工作的通知》 中要求会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第十四条规定审计业务出具的报告 （以下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标 人提供的财务报告需要赋码和提供深度查询截图吗？ 务 回复：投标人提供的财务报告不需要赋码和提供深度查询截图。 问题三十：有人提出一个无关问题。 回复：无关问题不予回复。 商 问题三十一：我公司业绩合同金额3600万元及以上，但是竣工报告业绩金额小于3600万元，请问是否满足业绩要 求？ 道 回复：按招标文件执行。“当上述业绩证明材料中针对同一指标存在不一致时，以工程竣工验收合格的证明材 料为准”。 问题三十二：专业分包业绩满足业绩要求吗？ 管 回复：专业分包业绩可满足业绩要求，但还需满足招标文件对业绩的其他要求。 问题三十三：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养 老保险证明材料复印件国递交吗？ 回复：不需要。 问题三十四：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要 中 求”吗？ 回复：可以统一填写“达到招标文件要求”。 问题三十五：市政桥梁施工业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题三十六：有人提出一个无关问题。 回复：无关问题不予回复。 问题三十七：本项目委派业主专家吗？ 回复：该项目评标委员会由招标人按法律法规及相关规定依法组建。 特别提示：本通知与招标文件具有同等法律效力，若招标文件与本通知不一致时，一律以本通知为准。 招标人：重庆水务环境控股集团管网有限公司 招标代理机构：重庆市工程管理有限公司 2026年8月19日 信息来源:https://www.chinapipe.net/project/d3075975.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
+          <t>巫溪县花台片区川主、农坡等5个村迁建区特色农业抗旱供水保障工程勘察设计招标计划表 重庆市工程建设项目招标计划表 项目 巫溪县花台片区川主、农坡等5个村迁建区特色农业抗旱供水保障工程勘察设计 名称 招标 法人 或招 标人巫溪县宁之源建设开发（集团）有限公司 名称 网 （盖 章） 项目 批准 文件 及文 号 务 主要 整治孝子溪大堰水渠约17.5km;新建孝子溪水库引水管道约17.5km,其中需新建引水隧洞内置管道约1.5km;新建柑橘基地管网约3.25km;改建6000m蓄水池1座；新建2000m蓄水池2座；新建1000m蓄水池1座；新建500m3 建设 蓄水池2座；新建柑橘基地滴灌系统1套 内容 序号 招标项目名称 招标内容 招标方式 招标文件计划发布时间 拟交易场所 合同预估金额(万元) 备注 招标 巫溪县花台片区川主、农坡 初步设计阶段勘察设计、施工 重庆市公共资源 项目1 等5个村迁建区特色农业抗旱 图阶段勘察设计、水土保持方案 公开招标 2026-09 交易中心巫溪分 340.00 （含水土保持施工图设计）、 供水保障工程勘察设计 洪水影响评价、水资源论证 商中心 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3078207.html cqdingjiu 2026.08.24 12:31:44 道 管 国 中</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>孝子溪水库引水管道：17.5km；其中需新建引水隧洞内置管道：1.5km；柑橘基地管网：3.25km</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标</t>
+          <t>重庆, 管材招标, 勘察设计, 资金情况, 产品种类</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>中化重庆涪陵化工搬迁后污水处理厂建设项目招标计划表</t>
+          <t>涪陵区李渡新区水厂工程(一期)施工招标公告</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3034,7 +3010,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3060,42 +3036,42 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>新建一体化提升泵站及管道约5000m，投资约800万元。</t>
+          <t>涪陵区李渡新区水厂工程(一期)设计水量目标为10万m/d，二期水量目标为20万m/d，采用混凝、沉淀、过滤、消毒常规水处理工艺。一期工程项目主要建设内容包括取水及原水输送工程、净水厂工程、配水工程三部分。</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>投资约800万元</t>
+          <t>项目业主为重庆水务环境控股集团渝东自来水有限公司，建设资金来自争取三峡后续工作专项资金、银行贷款和业主自筹等，项目出资比例为100%。</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>施工</t>
+          <t>取水及原水输送工程、净水厂工程、配水工程、供配电专项工程等施工，设备采购与安装（不含智慧化自控设备采购及伴随服务部分）、系统调试与试运行、市政设施保护、拆除与恢复、电力和燃气管线迁改；厂区道路、绿化景观、围墙等配套设施；施工临时道路、施工临时用水与施工临时用电（含道路、用水、用电的手续办理）、施工围挡、配合完成不少于一项区级及以上的科技创新项目、“后五通”的接入等。</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>中化重庆涪陵化工搬迁后污水处理厂建设项目招标计划表 重庆市工程建设项目招标计划表 项目名称 中化重庆涪陵化工搬迁后污水处理厂建设项目 招标法人或 招标人名称 重庆市涪陵交通旅游建设投资集团有限公司 网 （盖章） 项目批准文 涪发改委发[2019] 505号 件及文号 务 主要建设内 新建一体化提升泵站及管道约5000m，投资约800万元。 容 招标 招标 招标文件计 拟交易 合同预估 序号 招标项目名称 备注 内容 方式 划发布时间 场所 金额(万元) 商 本招标计划与2026年5 月25日发布的招标项目 中化重庆涪陵 重庆市 名称为“中化重庆涪陵 招标项目 化工搬迁后污 涪陵区 公道开 化工搬迁后污水处理厂 1 水处理厂建设 施工 2026-09 公共资 800.00 招标 建设项目（场外连接管 项目（场外干 源交易 网）”的招标计划，除 管部分） 中心 招标项目名称调整外， 其余内容完全一致。 管 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075591.html cqdingjiu 2026.08.21 10:国06:54 中</t>
+          <t>涪陵区李渡新区水厂工程(一期)施工招标公告 涪陵区李渡新区水厂工程（一期）施工招标公告 1.招标条件 本招标项目涪陵区李渡新区水厂工程（一期）已由重庆市发展和改革委员会以渝发改振兴〔2025〕468号文批准 建设，项目业主为重庆水务环境控股集团渝东自来水有限公司，建设资金来自争取三峡后续工作专项资金、银 行贷款和业主自筹等，项目出资比例为100% ，招标人为重庆水务环境控股集团渝东自来水有限公司。项目已具 备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：涪陵区义和街道，马鞍街道。 务 2.2 项目概况与建设规模： 商 涪陵区李渡新区水厂工程（一期）设计水量目标为10万m/d，二期水量目标为20万m/d，采用混凝、沉淀、 过滤、消毒常规水处理工艺。 道 一期工程项目主要建设内容包括取水及原水输送工程、净水厂工程、配水工程三部分。 管 （一）取水及原水输水工程：新建总规模20万m/d取水工程，深井取水泵房一座（土建按20万m/d实施，设 备分期安装），DN1200--DN1400原水输水管道约4.08千米。 国 （二）净水厂工程：新建10万m/d净水厂一座； 中 （三）配水工程：新建5.5万m/d加压泵站一座、高位水池一座，配套建设配水管道约20千米。 2.3 本次招标项目合同估算金额：约36148万元。 2.4 招标范围： 包括但不限于：施工图设计范围内的取水及原水输送工程、净水厂工程、配水工程、供配电专项工程等施工， 设备采购与安装（不含智慧化自控设备采购及伴随服务部分）、系统调试与试运行、市政设施保护、拆除与恢 复、电力和燃气管线迁改；厂区道路、绿化景观、围墙等配套设施；施工临时道路、施工临时用水与施工临时 用电（含道路、用水、用电的手续办理）、施工围挡、配合完成不少于一项区级及以上的科技创新项目、“后 五通”的接入等。 2.5 工期要求：30个月 缺陷责任期要求：24个月 2.6 标段划分： 本次招标为一个标段 2.7 是否属于政府采购工程：否 网 3.政府采购工程 3.投标人资格要求 务 3.1 本次招标要求投标人须具备以下条件： 商 3.1.1 本次招标要求投标人具备的资质条件： 道 （1）投标人具备独立法人资格。 管 （2）具备建设行政主管部门颁发的有效的市政公用工程施工总承包一级及以上资质。 3.1.2 投标人还应在人员国、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 中 3.2 本次招标接受联合体投标。联合体投标的，应满足下列要求： （1）联合体成员单位不能超过 2家，且联合体成员均须具备独立法人资格。 （2）联合体各方应按招标文件提供的格式签订联合体共同投标协议，并在共同投标协议中明确约定各方拟承担 的工作范围和责任。 （3）联合体各成员应按共同投标协议分工内容提供对应建安工程的资质和业绩。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件、工程量清单、 电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理， 办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。 若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 布至2026-08-25 17:00:00前。 4.3招标人应于2026-08-31 17:30:00前在重庆市公共资源交易网发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-22 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期网未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/）、重庆市公共资源交易网 （https://www.cqggzy.com/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上 务 发布。] 7.联系方式 重庆水务环境控股集团渝东自来水有限 招 标 人: 代理机构: 重庆国际投资咨询集团有限公司 公司 商 重庆市两江新区五里店五简路2号重庆咨询 地 址: 重庆市涪陵区兴华中路71号 地 址: 大厦A幢 邮 编: 邮 编: 道 项目负责人: 蔺老师 项目负责人: 谭杨杰 电 话: 023-72220219 电 话: 023-67107374 传 真: 传 真: 管 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 国 监督部门: 重庆市发展和改革委员会 电 话: 023-67575878 中 2026年08月21日 涪陵区李渡新区水厂工程（一期）施工 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051303399 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835014387 坝支行 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000753318 支行 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630015509 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146638778 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000011634 贸易试验区分行 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764324610 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020026676 信息来源:https://www.chinapipe.net/project/d3077140.html cqdingjiu 2026.08.24 12:31:44</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>一体化提升泵站及管道：5000m</t>
+          <t>排水钢管 Φ200*6m：3000米</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机</t>
+          <t>重庆, 管材, 招标, 水厂工程</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>綦江区污水处理厂设施设备更新改造工程(二期)招标公告</t>
+          <t>中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购公告</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3105,7 +3081,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3126,47 +3102,47 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>綦江区</t>
+          <t>渝中区</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>对三江污水处理站、綦齿园污水处理厂、信家岩污水处理站的设施设备进行更新改造，包括配电柜、风机、污水提升泵、在线监测等设备的更新更换，以及对工艺落后的污水厂完成工艺技改；北渡污水厂、赶水污水处理厂、工业园区污水厂、食品园污水厂零星设施更新等。</t>
+          <t>新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>上级补助和业主自筹，项目出资比例为100%，本项目工程总投资金额约1327.40万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>污水处理设施设备</t>
+          <t>管材</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>綦江区污水处理厂设施设备更新改造工程(二期)招标公告 1.招标条件 本招标项目 綦江区污水处理厂设施设备更新改造工程（二期） 已由 重庆市綦江区发展和改革委员会 以 重庆市企业投资备案证（项目代码：2502-500110-04-01-844057） 批准建设，项目业主为 重庆南州城市管 理服务有限公司 ，建设资金来自 上级补助和业主自筹 ，项目出资比例为 100% ，招标人为 重庆南州 城市管理服务有限公司。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用经评审的最低 投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 綦江区 2.2 项目概况与建设规模：对三江污水处理站、綦齿园污水处理厂、信家岩污水处理站的设施设备进行更新改造， 务 包括配电柜、风机、污水提升泵、在线监测等设备更新更换，以及对工艺落后的污水厂完成工艺技改；北渡污 水厂、赶水污水处理厂、工业园区污水厂、食品园污水厂零星设施更新等。 2.3 本项目工程总投资金额： 约1327.40万元 商 2.4 招标范围： 本项目设计施工图和招标文件、答疑、补遗、工程量清单等资料所涉及的全部内容。 2.5 工期要求： 180日历天 道 缺陷责任期要求： 24个月 2.6 标段划分（如有）： / 管 2.7 其他： / 3.政府采购工程 国 3.1 是否属于政府采购工程：否 4.投标人资格要求 中 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包三级 及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（綦江区） （https://www.cqggzy.com/qijiangweb/）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重 庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏 “主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易网（綦江区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-22 18:00:00前。 5.3招标人应于2026-09-11 18:00:00前在重庆市公共资源交易网（綦江区）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-28 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（綦江区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆南州城市管理服务有限公司 代理机构: 永卓国际工程技术有限公司 地 址: 重庆市綦江区红星美凯龙生活广场3幢19-3 地 址: 两江新区网泰山大道东段98号2幢10-12号 邮 编: 邮 编: 项目负责人: 赵老师 项目负责人: 廖淼 电 话: 023-48690537 电 话: 务023-60391733 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 商开户银行: 账 号: 账 号: 监督部门: 道 电 话: 2026年08月18日 綦江区污水处理厂设施设备更新改造工程（二期） 管 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051287453 中国农业银行股份有限公司重庆自由贸 重庆联合产权交易所集国团股份有限公司 312601010400083780000031123 易试验区分行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146631326 信息来源:https://www.chinapipe.net/project/d3075589.html 中 cqdingjiu 2026.08.21 10:06:54</t>
+          <t>中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管 材询比采购公告 中铁十一局集团有限公司建安分公司招标采购中心就中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房 及配套综合交通枢纽工程CQZSG-2标段项目经理部管材组织询比采购，诚邀有意向的合格供应商参与报价。 一、项目概况及询比采购内容 1.1项目概况 网 （1）新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程位于重庆市中心渝中区中部，具体位置为菜园 坝立交桥以西，龙家湾隧道以东，菜袁路以北，王家坡以南。正在建设的地铁18号线贴临站房北侧，地铁26/27 号线从站区地下通过。项目共划分为4个施工标段，CQZSG-1标段：为国铁站房、地铁站台区域；站北路密不可 分的边坡及场坪工程，包含土石方工程和边坡支护工程，不含机电工程，由中铁建设承建。CQZSG-2标段：为 务 枢纽配套工程，地铁区间、西广场、成都局剩余还建，由中铁十一局承建。CQZSG-3标段：地铁区间、CTC、 站场、东广场，由中铁建工承建。CQZSG-4标段：人防车库、铁路自营车场、综合开发生产配套房屋等，由中 铁二局承建。 （2）标段概况：我方负责新建重庆至黔江铁路重庆站站商房及配套综合交通枢纽工程CQZSG-2标段全部施工内容 （简称B区），主要包含：（1）B区投影范围内盖板以下27号线、26号线明挖区间基坑支护、土石方、区间主体 结构及配套防水、综合接地工程（不含砌筑墙体、装饰装修和机电安装工程），以及承轨层以下市政排水 涵DK1+196（196m）和行包通道；（2）轨道交通26号线暗挖隧道预留工程，其中26左线487m，26号右线408m； （3）站北路E、F、H连接匝道工程，其中E匝道道247m、F匝道285.5m、H匝道174m；（4）B区盖板及以上还建房 屋，其中西侧盖板约3.56万㎡，还建房屋等总建筑面积约3.50万㎡。 1.2询比内容 详见拟采购货物一览表 管 二、供应商资格要求 2.1供应商必须是“中国铁建云链平台”注册并通过审核的供应商。 2.2本次询比采购不接受国被列入“《2026年中国铁建合作方警示名录》、《中铁十一局集团有限公司不良行为供 应商名录》、《JD采购网失信名单》（此项核查针对JMRH项目）”中的供应商,不接受近一年内在铁路建设工程 网公布有违法行为记录及物资供应不良记录、被中国铁路总公司限制投标或已清退出铁路市场的供货商（此项 核查针对铁路站房项目），不接受在铁建云链平台被标记的不良行为供应商。 中 2.3供应商在报价时，如是法定代表人签字的需提供法定代表人身份证复印件、如是法人授权代理人签字的需提 供授权委托书及被授权人身份证复印件。 2.4询比响应供应商需提供营业执照复印件。 2.5其它要求：提供样品、每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌 等质量证明文件，甲方凭此报告检验质量。 2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 三、拟采购物资及相关要求 3.1拟采购物资一览表 交 序 物资 型号 单 项目 货 交货日 数量 备注 号 名称 规格 位 名称 地 期 址 重 直 庆 径6:0mm 市 包含车 PVC 批次交 壁 渝 丝、黑 1 （袖 米 7100 货与零 厚4:-45.mm 中 色胶布、 阀管） 星交货 单节 新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 区 管筛、 （具体 长4m CQZSG-2 标段项目经理部 菜 管箍、 以项目 园 堵头等 通知为 坝 一切相 准） 直 网 重 关费用 2 PE管 米 7100 径2:5mm 庆 站 合计 14200 务 3.2技术规格书： 按询比文件第二章项目技术规格书执行 商 3.3结算和付款 3.3.1采购物资报价规则： 道 固定价格。 3.3.2付款方式 （1）货款支付方式：支付方式包管括但不限于银行转账、银行汇票、银行本票、支票、银行承兑汇票、商业承兑 汇票、财务公司票据、供应链票据、其他数字化信用凭证，票据贴息费用由 供货单位 承担。 （2）付款周期：本合同无预付款。甲方在收到乙方提交的合规增值税专用发票，并经税务机关认证通过后次月 支付乙方上月供应期所国供合格物资70%货款，全部货物供应完毕后三个月内付至95%，剩余货款暂时扣留作为质 量保证金，供货完毕后，由乙方提交结算确认单，经甲方审核通过后做最终结算，待所有物资验收合格后12个月 内无息付清。 （3）逾期付款约定：如甲方付款逾期，双方秉持“长期合作，友好往来”原则，在逾期付款行为发生后一年内 中 乙方不向甲方收取逾期付款利息。若一年甲方仍未支付款项，需向乙方支付逾期付款利息，逾期付款利息起算 时间为全部款项到期之日一年后至付清之日，逾期利息的利率为合同订立时中国人民银行授权全国银行间同业 拆借中心公布的一年期贷款市场报价利率(LPR)1倍。 3.4拟采购物资相关的要求 3.4.1本次询比为整体采购，询比响应供应商报价时须写明单价、到站价和运距，报价包含货物制造、运输、装卸、 售后服务等交付采购人使用前所有可能发生的费用，收到报价后不再增补任何费用。 3.4.2交货期：按照采购人规定的期限内分批次运抵交付。 3.4.3供货地点：甲方指定的甲方所属 中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通 枢纽工程CQZSG-2标段项目施工现场。 3.4.4询比响应供应商必须保证产品的质量及售后服务。询比响应供应商提供的货物制造标准及技术规范等，必须 符合最新相关国家标准、部颁标准相关标准和规范的要求，进场提供相关检验检测报告。 3.4.5采购方在确定成交供应商后有权对成交产品的结构、规格做适当调整，调整内容将以工作联系函形式提前发 至供应商。 3.4.6售后服务：本批采购货物若在验收阶段出现不符合规格或质量标准，供应商必须接受退货要求，并在采购人 规定期限内等量补运合格产品，若未按时交付影响采购人使用，供应商必须承担由此给采购单位造成的后续经 济损失。 3.4.7报价方不得虚报各项技术指标，所供货物若不能符合技术要求，成交供应商必须接受全额退还货款，并承担 由此给采购单位造成的经济损失。 3.4.8验收方法及标准 （1）验收依据：询比采购文件、厂家货物技术标准说明及国家有关的质量标准规定，均为验收依据。 （2）货物验收：货物运抵采购人指定交货处后由双方对照采购清单及技术要求进行验收。 （3）其它要求：每批次货物必须附符合规范要求的出厂质量检验报告、型式检验报告及合格证或吊牌等质量证 明文件，甲方凭此报告检验质量。 网 （4）2.6袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠像胶带，另配堵头。 四、报价文件递交 务 4.1此次报价供应商需制作电子报价文件，在递交截止时间前线上递交报价文件。 4.2报价文件递交截止时间：2026年08月24日15时00分。 商 4.3报价文件递交地点：中国铁建云链平台（www.crccep.cn），供应商须登录该平台，在报价文件递交截止时间 前完成所有报价文件资料的上传。 五、发布公告的媒介 道 本次询比公告发布媒体:中国招标投标公共服务平台(www.cebpubservice.com)、中国铁建云链平台（www.crccep.cn） 上同时发布。 管 六、联系方式 1.采购组织单位：中铁十一局集团有限公司建安分公司招标采购中心 地 址：湖北省武汉市国武昌区丁字桥路47号 联 系 人：张先生 联系电话：027-87258521 中 电子邮件：2454774350@qq.com 2.采购人：中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程 CQZSG-2 标段项 目经理部 地 址：重庆市渝中区菜袁路59号 联 系 人：金先生 联系电话：16607273445 电子邮件：2285445503@qq.com 2026年08月21日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3077066.html cqdingjiu 2026.08.24 12:31:44</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠橡胶带，另配堵头。</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>重庆, 綦江区, 污水处理厂, 设施设备更新改造, 管材招标</t>
+          <t>重庆, 管材, 询比采购</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>南岸区峡口、迎龙片区农村供水保障提升工程招标计划表</t>
+          <t>中铁十一局集团有限公司新建成渝中线铁路(四川段)站前施工CYZXZQ-1标项目经理部过轨管询价采购公告</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3176,7 +3152,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3191,38 +3167,42 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>南岸区</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>本工程主要内容包括新（改）建峡口、道迎龙片区4个乡镇DN20～DN300农村供水管网81km，新建3座一体化智慧加压泵站。对朱家岩水厂进行升级改造：更换陈旧、老化的工艺、电气设备及自控、仪表系统，对全厂进行智能化、标准化改造，增加高级工艺控制系统，建设智能化、标准化的农村供水区级管理平台。</t>
+          <t>本次计划对过轨管材料进行询价，询价内容包括DN125米、DN180米、DN125个、DN180个四种过轨管及其接头。</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>概算批复工程建安费2975.27万元。</t>
+          <t>本项目中标金额为26.38亿元，总体工期为1826日历天，计划开工日期为2022年11月30日，计划竣工日期为2027年11月29日。</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>农村供水管网、智慧加压泵站、水厂升级改造、智能控制系统、加药系统、金属防腐工程、入户管道、入户水表、监测计量基础设施。</t>
+          <t>过轨管</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>南岸区峡口、迎龙片区农村供水保障提升工程招标计划表 重庆市工程建设项目招标计划表 项目 南岸区峡口、迎龙片区农村供水保障提升工程 名称 招标 网 法人 或招 标人 重庆市江南城市建设发展（集团）有限公司 名称 务 （盖 章） 项目 批准 商 文件 南岸发改﹝2026﹞156号 及文 号 本工程主要内容包括新（改）建峡口、道迎龙片区4个乡镇DN20～DN300农村供水管网81km，新建3座一体 主要 化智慧加压泵站。对朱家岩水厂进行升级改造：更换陈旧、老化的工艺、电气设备及自控、仪表系统， 建设 对全厂进行智能化、标准化改造，增加高级工艺控制系统，建设智能化、标准化的农村供水区级管理平 内容 台。概算批复工程建安费2975.27万元。 管 拟 招 招标文 合同预 招标 交 序 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 国 所 南岸 重 区峡 庆 口、 中 市 迎龙 朱家岩水厂升级改造工程：对全厂老旧设备进行设备更新；对全 公 片区 公 厂进行智慧化改造，增加高级工艺控制系统；对厂区建筑和构筑 共 农村 开 1 物修缮；优化加药系统投加模式，增加精确加药系统；对全厂部 2026-08 资 1600.00 供水 招 分老旧管道进行更换；金属防腐工程，对金属设备和管道的防锈 源 保障 标 刷漆工作。 交 提升 招标 易 工程 项目 中 （一 心 标段） 南岸 重 区峡 庆 口、 市 迎龙 公 片区 管网工程：延伸、改造峡口镇、迎龙镇等4个乡镇 46 公里 公 共 农村 DN40~DN300 配水主支管，36公里 DN20入户管道，新建3座一体 开 2 2026-08 资 1300.00 供水 化智慧加压泵房，入户水表改造 1752 户，并配套建设监测计量 招 源 保障 基础设施。 标 交 提升 易 工程 中 （二 心 标段） 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075572.html cqdingjiu 2026.08.21 10:06:54 网 务 商 道 管 国 中</t>
+          <t>中铁十一局集团有限公司新建成渝中线铁路(四川段)站前施工CYZXZQ-1标项目经理部过轨管询价采购公告 中铁十一局集团有限公司新建成渝中线铁路（四川 段）站前施工CYZXZQ-1标项目经理部 过轨管询价采购公告 询价编号：ZT1105-XJ-2026-457-2 网 尊敬的各潜在供应商: 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与中铁十一局集团有限公司新建成渝中线铁路 （四川段）站前施工CYZXZQ-1标项目经理部ZT1105-XJ-2026-457-2，过轨管的报价。 务 一、项目概况 中铁十一局集团有限公司新建成渝中线铁路四川段CYZXZQ-1标位于四川省成都市金牛区、成华区、 龙泉驿区 以及安岳境内。主线起止里程 DK282+986～DK288+400,全商长5.414公里。中标金额26.38亿元。 主要工程内容：“一隧一路两厂”,其中隧道0.5座/4.854公里，路基0.56 公里/1.21万方，管片厂1处/10380m管片预 制，板厂1处/96.51公里III 型 板 预制。其中蜀安隧道为我标段的重难点工程，盾构段拟采用1台直径14m 的土压 平衡盾构开挖。本标段报价总价26.38亿元。道 总体工期：1826日历天，计划开工日期2022年11月30日，计划竣工日期2027年11月29日。 管 二、询价内容 本次计划对过轨管材料进行询价，询价内容如下： 国 询价物资一览表 序号 包件号 物资名称 规格型号 计量单位 数量 备注 中 1 过轨管 DN125 米 840 2 过轨管 DN180 米 840 GGG-01 3 过轨管接头 DN125 个 140 4 过轨管接头 DN180 个 140 合计 说明：1.表中数量为计划数量，实际采购过程中可能有所调整，最终结算按照实际采购数量结算。 收货地点：四川省成都市成华区成铁路局客机整备所 三、技术质量及报价要求 1.此次过轨管主要技术性能及规格应满足《地下通信管道用塑料管 第 2 部分：实壁管》 （YD/T 841.2-2016），《给水用聚乙烯(PE)管道系统第 2 部分：管材》（GB/T 13663.2-2018），《地下通信管道 用塑料管 第 1 部分：总则》（YD/T 841.1-2016），《电力电缆导管技术条件 第 3 部分：实壁类塑料电缆导管》 （DL/T 802.3-2023）的要求，质量满足甲方项目部正常使用的要求，保证产品的质量合格，详见技术规格书。 2.报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、结算及付款方式 自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发票认证完成之日起第6个月，支付至本次结算 金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内，累计支付总额不超结算总金额的75%，剩 余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理末次结算后第二年，支付金额应大于等于 尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总额的15%；办理末次结算后第四年，全部 付清）。 五、报价人资格要求 1.营业范围要求：在中华人民共和国境内依法注册，具有询价物资生产或供应网经验的生产商或代理商，并 且具有合法有效的营业执照。 2.生产能力要求：生产商须具备询价物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定。代 理商需出具制造厂出具签字盖章的授权函。 务 3.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8月至今） 国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；每种物资全指标技术参数性能满足 国家和行业最新标准的各项规定。 商 4.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年8月至今）企业或企业法定代表人有人民法院生效判决、裁定 认定的行贿犯罪记录的。④ 对纳入国家铁路局道“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接受 通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合作 方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 5.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 管 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 ★6.下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 国 六、报价人需要提供的资料 1.营业执照复印件、法人身份证复印件、开户许可证、授权委托书、报价表和报价人资格要求中所需的证明资料， 所有资料需中加盖公司鲜章。 2.生产厂家资质，产品质量检测报告等质量证明文件。 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、询价报名截止时间 有意参加本次询价采购的报价人须在铁建云链平台（https://www.crccep.cn）完成供应商注册，并于2026年8月22 日9时00分至2026年8月25日9时00分在网上完成报名工作。 八、询价截止时间 凡有意参加本次询价采购的报价人，请于 2026年8月25日14时00分 前提交报价。截止时间前未完成报价文件传 输的，视为放弃报价。 供应商报价必须严格按照《报价表》格式进行报价。 九、联系方式 采购组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村71号 采购人名称：中铁十一局集团有限公司新建成渝中线铁路（四川段）站前施工CYZXZQ-1标项目经理部 地址：四川省成都市成华区华盛路58号19栋 联系人：向渝 联系电话：15178784487（提供采购服务支持） 中铁十一局集团有限公司 物资设备集中采购管理中心第五分中心 网 2026年8月22日 务 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3078608.html cqdingjiu 2026.08.24 12:31:45 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>DN300农村供水管网：81km</t>
+          <t>DN125米：840米；DN180米：840米；DN125个：140个；DN180个：140个</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -3230,14 +3210,14 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>重庆, 农村供水保障提升工程, 管材招标, 资金情况, 产品种类</t>
+          <t>重庆, 四川, 管材, 招标, 商机</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>北碚区东阳天府片区农村供水提升工程招标计划表</t>
+          <t>太行项目不锈钢管件采购招标公告</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3262,38 +3242,42 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>北碚区</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>工程建设区域为东阳及天府片区，主要建设内容包含改造供水管网437千米，其中DN200供水主要建设内容管网35千米，DN100~DN150供水管网82千米，DN100以下供水管网320千米，并配套建设管网附属设施。</t>
+          <t>法兰及其垫片,沟槽管件,铸铁管件,阀门,检查口,铜制管件,管道用材,套管,补偿器及软接头,过滤器,塑料管件,复合管件,不锈钢管件,钢制管件,阻火器,水箱,其它管件及管道用器材,铝合金管件,玻璃钢管件</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>合同预估金额为8457万元</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>供水管网</t>
+          <t>不锈钢管件</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>北碚区东阳天府片区农村供水提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 北碚区东阳天府片区农村供水提升工程 招标法人或招 标人名称（盖 重庆北碚文旅产业发展有限公司 网 章） 项目批准文件 及文号 务 工程建设区域为东阳及天府片区，主要建设内容包含改造供水管网437千米，其中DN200供水 主要建设内容 管网35千米，DN100~DN150供水管网82千米，DN100以下供水管网320千米，并配套建设管网 附属设施。 招标项目名 招标内 招标方 招标文件计划 拟交易场 合同预估金 序号 商 备注 称 容 式 发布时间 所 额(万元) 北碚区东阳 招标项目 重庆市公 天府片区农 施工招 公开招 1 2026-08 共资源交 8457.00 村供水提升 标 道标 易中心 工程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075569.html 管 cqdingjiu 2026.08.21 10:06:55 国 中</t>
+          <t>太行项目不锈钢管件采购招标公告 四川省工业设备安装集团有限公司 压缩空气供应系统、供水系统、燃油供应系统及变配电系统（室外电缆工艺 用） 太行项目不锈钢管件采购 招标公告 四川省工业设备安装集团有限公司 现就 压缩空气供应系统、供水系统、燃油供应系统及变配电系统（室外 电缆工艺用） 的 法兰及其垫片,沟槽管件,铸铁管件,阀门,检查口,铜制管件,管道用材,套管,补偿器及软接头,过 滤器,塑料管件,复合管件,不锈钢管件,钢制管件,阻火器,水箱,其它管件及管道用器材,铝合金管件,玻璃钢管件 采 购事宜进行公开招标，欢迎有意向的供应商参加投标。 一、采购内容 网 法兰及其垫片,沟槽管件,铸铁管件,阀门,检查口,铜制管件,管道用材,套管,补偿器及软接头,过滤器,塑料管件,复合管 件,不锈钢管件,钢制管件,阻火器,水箱,其它管件及管道用器材,铝合金管件,玻璃钢管件 ，预计总用量约为： 见 附件 。 不锈钢管件 务 二、项目概况 项目名称： 压缩空气供应系统、供水系统、燃油供应系统及变配电系统（室外电缆工艺用） 项目地址： 四川成都市东部新区简州新城指定地点 商 建筑规模： 0㎡ 其他详见招标文件。 三、招标方式 本次采购招标采用公开招标的方式进行，并在道善建云采（四川华西集团有限公司及下属分子公司）发布招标公 告，网址为：https://scm.zghxsjy.com/。 四、投标人资格要求 在善建云采（四川华西集团有限公司及下属分子公司）（https://scm.zghxsjy.com/）已注册的合格分供商均可参与 管 投标。 五、招投标时间节点 （一）招标文件发售截止时间： 2026-08-28 09:00:00 ； 国 （二）投标保证金缴纳的截止时间为： 2026-08-28 09:30:00 ； （三）本次招标的投标截止时间为： 2026-08-28 10:10:00 ； （四）本次招标的开标时间为： 2026-08-28 10:10:00 ； （五）电子标书费售价：人民币 40 元/套，售后不退。 中 六、缴费注意事项 为保证招投标的公平公正，善建云采（四川华西集团有限公司及下属分子公司）已与银行实现系统对接，从缴 费账号生成、缴费确认、标书下载和投标功能开放，全部实现自动化、线上化，请投标人务必按照下述要求缴 纳标书费和投标保证金，避免影响投标。 电子标书费缴纳： 1、投标人一旦决定投标，请在善建云采（四川华西集团有限公司及下属分子公司）上点击“交标书费”，银行 系统会随机自动为该次缴费生成一次性的唯一银行账号。 2、请投标人务必把标书费转入上述银行账户。投标人缴费后，银行系统会同步自动将缴费信息推送至善建云采 （四川华西集团有限公司及下属分子公司）和投标人，善建云采（四川华西集团有限公司及下属分子公司）系 统亦同步开放权限，投标人即可在善建云采（四川华西集团有限公司及下属分子公司）浏览和下载标书。 3、投标人务必严格按照上述要求进行投标操作。若投标人缴费到错误账号，善建云采（四川华西集团有限公司 及下属分子公司）无法开放投标功能，由此无法购买标书、无法投标、退回款项延迟等产生的一切损失，均由 投标人自行承担。 投标保证金缴纳： 1、投标人在善建云采（四川华西集团有限公司及下属分子公司）上点击“交投标保证金”后，由银行系统自动 为该次缴费生成唯一银行账号。 2、请投标人务必把投标保证金转入上述银行账户。投标人缴费后，银行系统会同步自动将缴费信息推送至善建 云采（四川华西集团有限公司及下属分子公司）和投标人，善建云采（四川华西集团有限公司及下属分子公司） 系统亦同步开放权限，投标人即可在善建云采（四川华西集团有限公司及下属分子公司）上传投标文件和填报 投标数据。 3、投标人务必严格按照上述要求进行投标操作。若投标人缴费到错误账号，善建云采（四川华西集团有限公司 及下属分子公司）无法开放投标功能，由此无法投标、退回款项延迟等产生的一切损失，均由投标人自行承担。 投标人缴纳投标保证金必须由投标人对公账户转账，不接受个人账户转款、现金缴存、他人代缴。若出现投标 人使用个人账户转款、现金缴存、他人代缴、未按系统自动生成的对应账号转款、超额转款等，平台将无法自 动退款。在中标公示结束后3个工作日内未收到保证金退款，投标人应在10个工作日后向四川华西数产科技集团 有限公司提供完整的书面缴费依据，四川华西数产科技集团有限公司将在收到投标人提供的完整缴费依据后， 在7个工作日内核实并退款。若出现上述情况投标人可编辑含有“招标项目名称”、“招标单位”的短信发送至： 19950205781（本号码只接受短信联系方式），也可到访四川华西数产科技集团有限公司进行沟通。 系统每次生成的账号，均为一次性账号和唯一性账号，标书费账号与投标保证金账号不同，项目与项目间账号 不同。 七、投标文件的递交 招标人仅接受投标人通过善建云采（四川华西集团有限公司及下属分子公司）提交的投标文件，不接受通过其 他方式提交的书面投标文件。线上投标内容具有法律效力且具有唯一性，请投标网人慎重对待。 八、其他描述 九、其他资格要求 务 十、其他事项 若对招标公告有其他不明事项，请致电： 业务咨询联系人： 安虹静 ，联系电话： 15883776766 ； 商 技术支持联系人： 集采技术部 ，联系电话： 02883382846 ； 十一、声明 本招标公告仅为信息发布，不构成任何法律意义上的要约或承诺。 现予公告。 道 四川省工业设备安装集团有限公司 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3078483.html 管 cqdingjiu 2026.08.24 12:31:45 国 中</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>DN150供水管网：82千米；DN100以下供水管网：320千米；主要建设内容包含改造供水管网：437千米；管网：35千米</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -3301,14 +3285,14 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 农村供水提升工程, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>不锈钢管件, 四川, 成都, 招标公告</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>北碚区澄江片区农村供水提升工程招标计划表</t>
+          <t>【屏山县龙华、龙溪、大乘污水管网疏通及修复项目劳务分包工程】询比公告</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3333,53 +3317,57 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>宜宾市</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>北碚区</t>
+          <t>屏山县</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>改造取水泵站一座，改造DN600供水管网2.9km，DN50~DN300供水管网88.863km，DN25供水管网68.5km及其附属设施。</t>
+          <t>屏山县龙华、龙溪、大乘污水管网疏通及修复项目劳务分包工程</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>合同预估金额：8741.00万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>供水管网及相关附属设施</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>北碚区澄江片区农村供水提升工程招标计划表 重庆市工程建设项目招标计划表 项目名称 北碚区澄江片区农村供水提升工程 招标法人或招标 重庆北碚文旅产业发展有限公司 人名称（盖章） 网 项目批准文件及 文号 改造取水泵站一座，改造DN600供水管网2.9km，DN50~DN300供水管网88.863km，DN25供 主要建设内容 务 水管网68.5km及其附属设施。 招标项目名 招标文件计划 合同预估金 序号 招标内容 招标方式 拟交易场所 备注 称 发布时间 额(万元) 招标项目 北碚区澄江 商重庆市公共 1 片区农村供 施工招标 公开招标 2026-08 资源交易中 8741.00 水提升工程 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 道 信息来源:https://www.chinapipe.net/project/d3075568.html cqdingjiu 2026.08.21 10:06:55 管 国 中</t>
+          <t>【屏山县龙华、龙溪、大乘污水管网疏通及修复项目劳务分包工程】询比公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3078449.html cqdingjiu 2026.08.24 12:31:45 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>DN600供水管网：2.9km；DN300供水管网：88.863km；水管网：68.5km</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机</t>
+          <t>重庆, 四川, 近三天, 管材招标商机</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>涪陵区江东街道农村供水保障能力提升工程(二期)招标计划表</t>
+          <t>成都市中兴供水有限公司2026-2028年度管网施工劳务比选磋商公告</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3389,7 +3377,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3404,38 +3392,42 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>武侯区</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>主要改造及延伸配水管188.2千米，新建加压泵站4座，新建计量监测设施建设以及配套电气工程。</t>
+          <t>本项目比选人为成都市中兴供水有限公司，主要从事市政基础设施、城市供水管网的投资、建设与运营。根据公司业务范围及建设需求，现面向社会进行给水管网施工单位的公开比选，邀请有能力的优秀比选申请人参加我公司的项目比选，并选出二至三家优秀企业共同承担2026年及2028年度成都市中兴供水有限公司供水区域内给水管网的施工任务。</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>预算金额为3137.22万元</t>
+          <t>中选的单位，按照工程预估1000万元作为暂定金额签订合同。</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>管道、加压泵站、计量监测设施、电气设备</t>
+          <t>给水管网施工劳务</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>涪陵区江东街道农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区江东街道农村供水保障能力提升工程（二期） 名称 招标 法人 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 项目 网 批准 文件 涪陵发改〔2026〕471号 及文 号 主要 改造及延伸配水管 188.2千米，新建加压泵站4座，新建计量监测设施 建设 以及配套电气工程。 务 内容 招 标 合 文 同 招 件 预 招标 标 招标方 计 拟交易 备 序号 招标项目名商称 估 项目 内 式 划 场所 注 金额 容 发 (万 布 元) 时 间 重 道 庆 市 涪 陵 公 区 改造及延伸配水管 188.2千米，新建加压泵站4座，新建计量监测设施 开 公 1 涪陵区江东街道农村供水保障能力提升工程（二期） 2026-09 3137.22 管以及配套电气工程。 招 共 标 资 源 交 易 中 心 国 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075558.html cqdingjiu 2026.08.21 10:06:55 中</t>
+          <t>成都市中兴供水有限公司2026-2028年度管网施工劳务比选磋商公告 （一）概况 1、本项目比选人为成都市中兴供水有限公司，主要从事市政基础设施、城市供水管网的投资、建设与运营。根 据公司业务范围及建设需求，现面向社会进行给水管网施工单位的公开比选，邀请有能力的优秀比选申请人参 加我公司的项目比选，并选出二至三家优秀企业共同承担2026年及2028年度成都市中兴供水有限公司供水区域内 给水管网的施工任务。 2、本项目比选为企业自主谈判，组织形式为自行谈判。 网 3、中选的单位，按照工程预估1000万元作为暂定金额签订合同。 （二）比选范围 务 1、工作内容涉及:1）管道施工；2）各类管井砌筑、管道保护等；3）PE管、铸铁管、钢管、衬塑复合管等 给水管道安装（包含建筑体内的管道安装）；4）旧管拆除及新接管道的连接；5）特殊施工项目，如顶管（若实 际项目中涉及）、少量构筑物修建及改造等。 商 2、服务期：2年，以任务发放的开始和结束时间为准。 3、服务地点：成都市武侯区金花辖区约12.9平方公里。 道 4、比选申请人根据自身资质、能力、条件等，可选择不同的模式进行报价，详见比选文件 （三）比选申请人资格要求 管 1、具有独立企业法人资格，持有合法有效的营业执照，注册资金50万元以上，财务状况良好，具有税务部门认 可的增值税纳税人认定表（书），可开具国家认可的增值税专用发票。 2、具有：①国家建设行政主管部门颁发的市政工程总承包叁级及以上资质或房屋建筑工程施工总承包叁级及以 上资质；②有效的施工国作业劳务资质、有效的安全生产许可证（①②可任具其一） 3、业绩要求：申请人应于2024年至2025年期间承接并完成施工至少两个以上的类似工程的劳务分包作业（类似 工程是指：市政给水（或供水或输水）管道工程施工业绩或市政给水（或供水或输水）管道工程，申请人须提 供合同及相关的履行证明），并在人员、设备、资金等方面具有相应的施工能力。 中 4、信誉要求：未处于四川省行政区域内有关行政处罚期间，且未处于投标禁入期内；近3年或成立至今（成立不 足3年的）在经营活动中没有重大违法违规记录。在“信用中国”网站（www.creditchina.gov.cn）中未列入失信被 执行人和重大税收违法案件当事人名单 5、主要人员配备要求： ①项目负责人、技术负责人要求：项目负责人或技术负责人具有工程类中级工程师及以上职称。(项目负责人或 技术负责人相关证书在合同签订时需交由比选人，待合同履行完毕退还) ②本项目管理人员中须至少配备施工员、安全员、资料员、材料员、造价员各1名。 ③主要人员（项目负责人、技术负责人、施工员、安全员、资料员、材料员、造价员）应是比选申请人本单位 人员。 6、不接受联合体参选。 （四）比选文件获取 1、比选申请人报名时需提供：法定代表人持加盖机构鲜章的本人身份证复印件，或授权代理人持法定代表人签 发并加盖机构鲜章的授权委托书原件、加盖机构鲜章的本人身份证复印件；企业营业执照副本复印件；资质证 书副本复印件；安全生产许可证副本复印件；纳税人资格证复印件；开户许可证复印件；管道施工合同及相关 的履行证明。 注：以上所有复印件均须加盖比选申请人鲜章，且须携带原件，现场查验。 2、比选人在接受报名后即对比选申请人资格条件进行审查，条件合格者即可领取商务谈判文件。 3、获取时间：2026年8月24日起（工作日上午9：30至12：00，下午14：00 至17：30）。 4、获取地点：成都市武侯区草金路中段999号附9号成都市中兴供水有限公司二楼成控部 （五）参选文件递交 1、参选文件应按以下规定文件格式及附件要求的内容填写并装订。 网 2、递交参选文件时，应同时提供以下资料查验，否则比选人有权拒收：①营业执照副本原件②安全生产许可证 副本原件③项目经理注册证原件④税务部门认可的纳税人认定表（书）⑤项目负责人或技术负责人具备的相关 资质证书。 务 3、投标文件的递交的截止时间（以比选人通知为准），地点为成都市武侯区草金路中段999号附9号成都市中兴 供水有限公司二楼成控部。 4、逾期送达或未送到指定地点的投标文件，比选人不予商受理。 （六）联系人及联系电话 联系人：杜老师 道 联系电话：028-8200 6199转823 17828175202 公司网站：http://www.zxwatersupply.com/ 管 信息来源:https://www.chinapipe.net/project/d3078430.html cqdingjiu 2026.08.24 12:31:45 国 中</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>加压泵站：4座</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -3443,14 +3435,14 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>成都, 供水, 管网施工, 劳务比选</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>涪陵区龙桥街道农村供水保障能力提升工程招标计划表</t>
+          <t>PPR管及管件采购/78020049-PS202608200813采购变更公告(第1号)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3460,7 +3452,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3475,53 +3467,49 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>涪陵区</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>改造荣桂水厂老化、破损、生锈的输水管道7.36公里。马武水厂增设废水回收及污泥浓缩系统1套。荣桂水厂增设废水回收及污泥浓缩系统1套。新建配水管道总长0.74公里；改造配水管道总长139.42公里。新建1座微型集成泵房及改造1座泵站(原牌坊泵站)。新增管网监测设施40套。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>预估合同金额为3236.36万元人民币</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>输水管道、废水回收及污泥浓缩系统、配水管道、微型集成泵房、泵站、管网监测设施</t>
+          <t>PPR管及管件</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>涪陵区龙桥街道农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 涪陵区龙桥街道农村供水保障能力 项目名称 提升工程 招标法人 或招标人 重庆水务环境控股集团渝东自来水 名称（盖 有限公司 章） 网 项目批准 文件及文 涪陵发改〔2026〕466号 号 改造荣桂水厂老化、破损、生锈的 务 输水管道7.36公里。马武水厂增设 废水回收及污泥浓缩系统1套。荣 桂水厂增设废水回收及污泥浓缩系 主要建设 统1套。新建配水管道总长0.74公里； 商 内容 改造配水管道总长139.42公里。新 建1座微型集成泵房及改造1座泵 站(原牌坊泵站)。新增管网监测设 施40套。 道 招标 合同 招 文件 预估 标 招标方 拟交易 备 招标项目 序号 招标项目名称 计划 金 内 式 场所 注 管 发布 额(万 容 时间 元) 改造荣桂水厂老化、 破损、生锈的输水管 国 道7.36公里。马武水厂 增设废水回收及污泥 重庆 浓缩系统1套。荣桂水 市涪 厂增设废水回收及污 公 陵区 中 涪陵区龙桥街道农村供水保障能力 泥浓缩系统1套。新建 开 1 2026-09 公共 3236.36 提升工程 配水管道总长0.74公里； 招 资源 改造配水管道总 标 交易 长139.42公里。新建1 中心 座微型集成泵房及改 造1座泵站(原牌坊泵 站)。新增管网监测设 施40套。 本计划表所列招标项目信息均为暂 备注 定，最终以实际招标时的信 信息来源:https://www.chinapipe.net/project/d3075556.html cqdingjiu 2026.08.21 10:06:55</t>
+          <t>PPR管及管件采购/78020049-PS202608200813采购变更公告(第1号) 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 信息来源:https://www.chinapipe.net/project/d3078524.html cqdingjiu 2026.08.24 12:31:45 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>输水管道：7.36公里；配水管道：0.74公里；配水管道：139.42公里</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>涪陵区龙桥街道, 农村供水保障能力提升工程, 输水管道, 废水回收及污泥浓缩系统, 配水管道, 微型集成泵房, 泵站, 管网监测设施</t>
+          <t>塑料管不计匹配分</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>涪陵区百胜镇农村供水保障能力提升工程招标计划表</t>
+          <t>北部基地平原公司关于FRPP管Φ160及配套弯头项目采购公告</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3531,7 +3519,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3546,53 +3534,49 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>涪陵区</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>整治De315原水管长1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1套及配套电气工程。</t>
+          <t>北部基地平原公司关于FRPP管Φ160及配套弯头项目采购公告</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>合同金额1489.90万元</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>管材、水泵、加压泵站、废水处理系统、电气工程</t>
+          <t>FRPP管Φ160PN1.0*13.3-黑色, FRPP弯头(90°)Φ160PN1.0*13.3-R=1.5D-黑色</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>涪陵区百胜镇农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区百胜镇农村供水保障能力提升工程 名称 招标 法人 或招 标人重庆水务环境控股集团渝东自来水有限公司 名称 网 （盖 章） 项目 批准 文件涪陵发改〔2026〕465号 及文 号 务 主要 建设整治 De315原水管长 1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1套及配套电气工程。 内容 招 拟 标 招招标文 合同预 交 序项 标件计划 估金 备 招标内容 易 号目 方发布时 额(万 注 场 名 商 式间 所 元) 称 涪 陵 区 重 百 庆 胜 市 招标 镇 涪 项目 农 道 陵 村 公 区 供整治 De315原水管长 1.66公里及附属设施，更换取水泵站水泵1套，新建及整治输配水管网总长111.47公里及附属设施，管径De25~De200，新建加压泵站2座，百胜水厂新建废水处理系统1开 公 1 2026-09 1489.90 水套及配套电气工程。 招 共 保 标 资 障 源 能 交 力 易 提 中 管 升 心 工 程 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075553.html 国 cqdingjiu 2026.08.21 10:06:55 中</t>
+          <t>北部基地平原公司关于FRPP管Φ160及配套弯头项目采购公告 根据成都云图控股股份有限公司采购管理制度，本着“公开、公平、公正、诚信”的原则，诚邀具备投标资格 供应商参加投标。 1 项目概况 1.1 项目名称：北部基地平原公司关于FRPP管Φ160及配套弯头项目 1.2 项目编号：ZB-2608-1047 1.3 交货地点和时间：按实际订单地址及交期要求； 1.4 物资名称及数量： 网 标的编码 标的名称 规格型号 计量单位 数量 TMP91386 FRPP管Φ160PN1.0*13.3-黑色 4米/根 米 80 务 TMP91392 FRPP弯头(90°)Φ160PN1.0*13.3-R=1.5D-黑色 个 8 2 投标人资格要求 2.1 具有独立法人资格； 商 2.2 具有本项目相应履约能力； 2.3 未被纳入成都云图控股股份有限公司供应商“黑名单”。 3 投标方式 道 登录云图控股采购平台（https://srm.wintrueholding.com/），根据注册要求填报公司信息并上传资质文件，获得准 入审核后报名申请参加本项目。本项目所有的招标公告、变更澄清、中标公告均在本网进行公示。具体查阅本 网站首页下载专区的“供应商系统操作手册”。 4 时间安排 管 投标截止时限：2026-08-25 13:00，投标人应于该时限前完成平台注册、报名、标书费缴纳、投标保证金缴纳、平 台报价和标书上传等工作。 5 标书费与保证金 国 5.1 标书费：0人民币/份，售后不退还； 5.2 投标保证金：0人民币/份； 5.3 标书费和投标保证金请分开支付，收款账号详见项目缴费单，转账时需备注平台提供的缴费附言。 5.4 投标保证金退还：未中标单位在中标公告发布后7个工作日内无息退还；中标单位在签订合同后转为履约保证 中 金，按合同约定履约后7个工作日内退还。 5.5 投标人存在下列行为之一的，投标保证金将不予退还： 5.5.1 违反《供应商廉洁诚信承诺书》的； 5.5.2 在投标活动中有弄虚作假、围标串标的； 5.5.3 中标人放弃中标项目的； 5.5.4 中标公告发出后7个工作日内，中标人无正当理由不与招标人签订合同的、提出附加条件、更改合同实质性 内容的； 5.5.5 中标人拒不足额缴纳招标公告文件所要求履约保证金的； 5.5.6 法律法规规定不予退还的其他情形。 6 招标业务联系方式：白焱公 手机：15315813736 邮箱： 。 7 其他咨询与投诉热线400-066-7019，接通后请按语音提示拨号： 拨号1 设备备件类业务和企业微信相关问题咨询。 拨号2 SRM平台注册、缴费、系统操作、大宗原料业务咨询。 拨号3 标书费发票开具。 拨号4 投诉与举报，或将相关投诉举报资料发至邮箱likaijuan@wintrueholding.com，我们将妥善处理。 成都云图控股股份有限公司供应中心 2026-08-22 11:46 网 附件： 务 点击查看内容 信息来源:https://www.chinapipe.net/project/d3078468.html 商 cqdingjiu 2026.08.24 12:31:47 道 管 国 中</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>取水泵站水泵：1套；及整治输配水管网：111.47公里；加压泵站：2座</t>
+          <t>FRPP管Φ160PN1.0*13.3-黑色: 80米, FRPP弯头(90°)Φ160PN1.0*13.3-R=1.5D-黑色: 8个</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>涪陵区百胜镇, 农村供水保障能力提升工程, 管材招标, 重庆</t>
+          <t>FRPP管, 弯头, 四川</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>涪陵区清溪镇农村供水保障能力提升工程招标计划</t>
+          <t>中铁六局四川南广铁路站前三标工程隧道管材物资采购公告</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3602,7 +3586,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3617,53 +3601,57 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>岳池县</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>对清溪水厂原取水口进行改造。改造清溪厂输水管道长6.38公里。清溪水厂新建3000m³/d集成水厂1套，增设废水回收及污泥浓缩系统1套。新建配水管道总长2.46公里。改造配水管道总长145.04公里。四合村泵站增加1套备用加压泵。新增管网监测设施35套。</t>
+          <t>中铁六局四川南广铁路站前三标工程隧道管材物资采购</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>合同预估金额：2888.89万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>集成水厂、输水管道、配水管道、加压泵、管网监测设施</t>
+          <t>三通接头,接头,防结晶封器,内燃机车导水管套,PVC管,HDPE管,弯头,盲管</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>涪陵区清溪镇农村供水保障能力提升工程招标计划 重庆市工程建设项目招标计划表 项目名称 涪陵区清溪镇农村供水保障能力提升工程 招标法人 或招标人 重庆水务环境控股集团渝东自来水有限公司 网 名称（盖 章） 项目批准 文件及文 涪陵发改〔2026〕467号 务 号 对清溪水厂原取水口进行改造。改造清溪水厂输水管道长6.38公里。清溪水厂新建3000m3/d集成水 主要建设 厂1套，增设废水回收及污泥浓缩系统1套。新建配水管道总长2.46公里。改造配水管道总长145.04 内容 公里。四合村泵站增加1套备用加压泵。新商增管网监测设施35套。 招标项目 招标方 招标文件计 拟交易场 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 所 (万元) 对清溪水厂原道取水口进行 改造。改造清溪水厂输水 管道长6.38公里。清溪水厂 涪陵区清 新建3000m3/d集成水厂1套， 重庆市涪 招标项目 溪镇农村 增设废水回收及污泥浓缩 公开招 陵区公共 管 1 供水保障 2026-09 2888.89 系统1套。新建配水管道总 标 资源交易 能力提升 长2.46公里。改造配水管道 中心 工程 总长145.04公里。四合村泵 站增加1套备用加压泵。新 国 增管网监测设施35套。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075552.html 中 cqdingjiu 2026.08.21 10:06:55</t>
+          <t>中铁六局四川南广铁路站前三标工程隧道管材物资采购公告 XSJZ-NG-2026-3119 采购单位:新建雄商高速铁路雄安新区至商丘段站前XSZQ-5标段（二工区） 发布时间:2026-08-22 10:08 报价截止时间:2026-08-26 09:30 招标方联系人:王晓磊 网 招标方联系电话:15075136153 招标方邮箱:15075136153@163.com 务 监督方联系人:李波 监督方联系电话:13832379603 商 监督方邮箱:13832379603@163.com 保证金:2500.0元 道 结算与发票信息: 结算方式：中信支付或承兑 支付条件：半年分期付款 发票种类：增值税专票 管 发票抬头：中铁六局集团有限公司石家庄铁路建设分公司 税号：91130104673209036N 其他要求：付款条件：双方签订纸质版采购合同后按交付数量按期结算，结算完成后，甲方在收到乙方开具的 正式的增值税专用发票后180天内，向乙方支付不超过当月结算金额的80%，合同履行完毕双方确认无误并签订 封账协议后，最高向乙国方支付开累结算金额的90%，剩余10%作为质保金，质保期12个月，在最后一批货物质保 期满后90日内无息支付，如发生纠纷，则延后至纠纷最终解决后60天内付清。质量保证金的支付并不免除乙方对 交付货物质量的保证责任。乙方同意给予6个月的付款宽限期，在此宽期间内不视为甲方违约且不计息。 交货信息: 交货方式:汽中车运输 收货人:王晓磊 收货人联系方式:15075136153 其他说明事项: 流水号：询2026082200036 计 交 标的 量 标的编号 规格型号 数量 技术标准及要求 货 送货地址 名称 单 期 位 西南区-四川省-广安市-岳池 三通 县-中铁六局集团有限公司四 0950192127691 Φ100mm 150.0 个 Q/CR562.4-2018 接头 川南广铁路NGZQSG-03标段 项目经理部 西南区-四川省-广安市-岳池 县-中铁六局集团有限公司四 4900095010026 接头 100 1500.0 个 Q/CR562.4-2018 川南广铁路NGZQSG-03标段 项目经理部 西南区-四川省-广安市-岳池 防结 县-中铁六局集团有限公司四 0908200376935 晶密 DN100 1526.0 个 Q/CR562.4-2018 川南广铁路NGZQSG-03标段 封器 项目经理部 内燃 西南区-四川省-广安市-岳池 机车 DF8B 县-中铁六局集团有限公司四 2712999297927 10.0 个 GB/T 5836.1-2018 导水 36×20×13mm 川南广铁路NGZQSG-03标段 管套 项目经理部 西南区-四川省-广安市-岳池 PVC 县-中铁六局集团有限公司四 1602621010057 32 5051.0 米 GB/T 5836.1-2018 管 川南广铁路NGZQSG-03标段 项目经理部 西南区-四川省-广安市-岳池 网 PVC 县-中铁六局集团有限公司四 1602621010005 100 100.0 米 GB/T 5836.1-2018 管 川南广铁路NGZQSG-03标段 项目经理部 务西南区-四川省-广安市-岳池 PVC 县-中铁六局集团有限公司四 1602621010007 110 3525.0 米 GB/T 5836.1-2018 管 川南广铁路NGZQSG-03标段 项目经理部 商 西南区-四川省-广安市-岳池 PVC 县-中铁六局集团有限公司四 1609827153587 DN110 250.0 个 GB/T 5836.1-2018 弯头 川南广铁路NGZQSG-03标段 项目经理部 道 高密度聚乙烯，双壁波 西南区-四川省-广安市-岳池 电力 纹管(壁厚10mm),内 县-中铁六局集团有限公司四 1602012241079 过轨 HDPE 110mm 1563.0 米 径100mm，环刚度不小 川南广铁路NGZQSG-03标段 管 于16KN/㎡ 项目经理部 管 高密度聚乙烯，双壁波 西南区-四川省-广安市-岳池 电力 纹管(壁厚10mm),内 县-中铁六局集团有限公司四 1602012241079 过轨 HDPE 110mm 2986.0 米 径100mm，环刚度不小 川南广铁路NGZQSG-03标段 管 于16KN/㎡ 项目经理部 国 西南区-四川省-广安市-岳池 县-中铁六局集团有限公司四 0903244206213 盲管 DN100 6210.0 米 Q/CR562.4-2018 川南广铁路NGZQSG-03标段 中 项目经理部 西南区-四川省-广安市-岳池 县-中铁六局集团有限公司四 0903244206208 盲管 DN80 200.0 米 Q/CR562.4-2018 川南广铁路NGZQSG-03标段 项目经理部 西南区-四川省-广安市-岳池 县-中铁六局集团有限公司四 0903244032393 盲管 50mm×2m 7172.0 米 Q/CR562.4-2018 川南广铁路NGZQSG-03标段 项目经理部 报价网址:http://www.crecgec.com 信息来源:https://www.chinapipe.net/project/d3078392.html cqdingjiu 2026.08.24 12:31:47</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>清溪水厂输水管道：6.38公里；配水管道：2.46公里；四合村泵站：1套；新商增管网：35套；管道：6.38公里；增管网：35套</t>
+          <t>Φ100mm三通接头：150个；100mm接头：1500个；DN100防结晶封器：1526个；DF8B内燃机车导水管套：10个；PVC管：5051米；PVC管：100米；PVC管：3525米；DN110弯头：250个；HDPE过轨管：1563米；HDPE过轨管：2986米；DN100盲管：6210米；DN80盲管：200米；50mm×2m盲管：7172米</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>塑料管不计匹配分</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>涪陵区珍溪镇农村供水保障能力提升工程(一期)招标计划表</t>
+          <t>81-西南-大邑西岭文体-水泥制品-询比采购公告</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3673,7 +3661,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3688,53 +3676,49 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>涪陵区</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>改造11000m³/d(旺水垭6000m³/d和二水厂5000m³/d)原水处理系统及辅助设施，主要包括加氯系统、加药系统、清水池、絮凝池、重力无阀滤池、污水处理回收池、二水厂泵房设备等及其他辅助设施。更换旺水垭水厂至张家塘配水管13.5km，张家塘至滴水配水管长3.3km，全长16.8km；滴水至洪湖配水管长0.3km；更换八一水库至旺水垭水厂引水管1.7km，更换珍溪二水厂至珍溪大桥配水管5km，新建应急泵站至百汇大桥配水管9km；百汇至观将泵站4.5km；共计37.3km。</t>
+          <t>水泥制品</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>合同预估金额3427.27万元</t>
+          <t>项目预算金额为290万元</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>管材</t>
+          <t>II级钢筋混凝土管、II级钢筋混凝土管、II级钢筋混凝土管、II级钢筋混凝土管、II级钢筋混凝土管、II级中钢筋混凝土管、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土井筒、预制偏心井盖、预制偏心井盖、预制偏心井盖、预制偏心井盖、单算偏沟式雨水口、双算偏沟式雨水口、钢筋混凝土矩形检查井、钢筋混凝土矩形检查井、钢筋混凝土矩形检查井、钢筋混凝土矩形检查井</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>涪陵区珍溪镇农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目名 涪陵区珍溪镇农村供水保障能力提升工程（一期） 称 招标法 网 人或招 重庆水务环境控股集团渝东自来水有限公司 标人名称 （盖章） 项目批 务 准文件 涪陵发改〔2026〕476号 及文号 (一)改造11000m3/d(旺水垭6000m3/d和二水厂5000m3/d)原水处理系统及辅助设施，主要有加氯系统、 加药系统、清水池、絮凝池、重力无阀滤池、商污水处理回收池、二水厂泵房设备等及其他辅助设施。 主要建 (二)更换旺水垭水厂至张家塘配水管13.5km，张家塘至滴水配水管长3.3km，全长16.8km；滴水至洪 设内容 湖配水管长0.3km；更换八一水库至旺水垭水厂引水管1.7km，更换珍溪二水厂至珍溪大桥配水管5km， 新建应急泵站至百汇大桥配水管9km：百汇至观将泵站4.5km；共计37.3km。 道 招标项目 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 场所 (万元) (一)改造11000m3/d(旺水 垭6000m3/d和二水厂5000m3/d) 管 原水处理系统及辅助设施，主 要有加氯系统、加药系统、清 水池、絮凝池、重力无阀滤池、 污水处理回收池、二水厂泵房 涪陵国区珍 设备等及其他辅助设施。(二) 重庆市 招标项 溪镇农村 更换旺水垭水厂至张家塘配水 涪陵区 目 供水保障 公开招 1 管13.5km，张家塘至滴水配水 2026-09 公共资 3427.27 能力提升 标 管长3.3km，全长16.8km；滴水 源交易 中工程（一 至洪湖配水管长0.3km；更换八 中心 期） 一水库至旺水垭水厂引水 管1.7km，更换珍溪二水厂至珍 溪大桥配水管5km，新建应急 泵站至百汇大桥配水管9km： 百汇至观将泵站4.5km；共 计37.3km。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075551.html cqdingjiu 2026.08.21 10:06:56</t>
+          <t>81-西南-大邑西岭文体-水泥制品-询比采购公告 物资采购 【招标公告】81-西南-大邑西岭文体-水泥制品-询比采购 招标编号：cscec2026082000002023946 项目：大邑县西岭文体智能装备功能区基础设施建设工程(二标段) 发布时间：2026-08-21 10:43:38 报名截止：2026-08-26 21:59:00 区域：四川省成都市 招标品类：水泥制品 招标（资格预审）公告 网 中建八局第一建设有限公司 物资采购 务 采 购 商 公 告 道 物资名称： 水泥制品 采购编号： cscec2026082000002023946 采购时间： 2026/8/20 管 第一章采购公告 根据中建八局第一建设有限公司（以下简称公司）管理方针，为满足施工生产需要，现就本采购公告所述工程 项目所需物资进行采购，欢迎符合条件的响应人参加，有关事宜公告如下： 国 一、采购基本信息 采 1 购 人 中建八局第一建设有中限公司 采 2 购 内水泥制品 容 采 3 购 范大邑县西岭文体智能装备功能区基础设施建设工程(二标段)水泥制品 围 概 4 算 金290万元 额 采 5 购 方询比采购 □竞价采购 □谈判采购 □直接采购 式 采 6 购 品 无 □ 品 有 牌 品 要 牌 求 要 ； 求：/ 牌 采 7 购 数见：附件1采购清单 量 质 8 量 标22S521《预制装配式混凝土检查井》、 GB/T-11836-2023《混凝土和钢筋混凝土排水管》，16S518《雨水口》若采购进行时标准规范更新，则以更新后的标准执行 准 付 9 款 方 按 个 月 月 后 □ 3 每 0个 两 工 个 作 月 日 □ 内 季 支 度 付 支 至 付 85 货 % 款 ， ： 满 甲 18 方 个 在 月 每 后 支 30 付 个 周 工 期 作 满 日 后 内 的 支 次 付 月 至 3 9 0 5 日 %, 前 满 支 24 付 个 本 月 周 后 期 30个 结 工 算 作 货 日 款 内 的 支 65% 付 。 至 双 10 方 0% 办 ， 理 以 完 上 成 为 物 2年 资 分 总 4 结 次 算 支 后 付 ， ） 甲 等 方 额 自 付 物 至 资 结 总 算 结 值 算 （ 办 且 理 不 之 超 日 本 起 合 2 同 年 含 平 税 均 金 分 额 4 ） 次 的 （ / 以 %。 每半年为期限支付一次，结算办理完毕满6个月后30个工作日内支付至结算值的75%，满12 式 计 11价 方固定单价□浮动单价 式 增 值 12计 税一般计税 □简易计税 方 式 采 13购 限无 □有，随采购文件发布 价 评 审 14基□无 有，根据预设规则系统自动结算 准 价 响 应 15保□无 有，金额： 10000元 证 金 保 证 金 16缴云筑网 □指定账户（二选一） 纳 方 式 产 17地 要国产 □进口 求 二、响应人资格要求 （一）基本资格要求 网 1．具备法律主体资格，具有独立承担民事责任能力、独立订立及履行合同能力的在中华人民共和国境内注册的 法人或其他组织。 务 2．具备：一般纳税人资格 小规模纳税人。 3．具备国家有关部门、行业或公司要求必须取得的质量、计量、安全、环保认证及其他经营许可；近两年在信 用中国无经营异常或严重违法失信记录；与本级或上下级单位没有不良合作记录。 商 4．响应人注册成立1 年以上，响应人的企业注册资本不得低于 100 万元。 5．响应人须具有3年内混凝土或水泥制品的分供业绩。 道 6．具有良好的商业信誉和健全财务会计制度，能提供会计年度报告。 7．法律、行政法规和本采购公告规定的其他条件。 管 8．采购产品必须是符合国家标准的产品。 9．未与我司存在恶意诉讼、恶意讨薪等法律纠纷。 国 10．响应人未处于被责令停业、响应资格被取消或财产被接管、冻结和破产。 11．未与其他报名单位在云筑网显示信息相关联，报名单位ip不可重复，母子单位不可同时报名，mac地址也不 可重复； 中 12．响应人须为独立法人单位或是经法人单位授权的下属单位。凡是以“**分公司”等非独立法人单位名义报名 或者参与公司采购的供应商必须出具由其上级法人单位加盖公章的授权委托书（格式见附件），否则不得通过 资格审核； 13．响应人在云筑网报名后需积极配合我方完成考察，对于考察未通过或不配合考察的分供商，不予通过资审； 14．能贯彻执行采购文件/框架协议规定的该产品的质量验收标准，接受质量投诉处罚等主要规定； 15．同时符合上述条件，且所提供的资质文件和材料必须真实在有效期内，响应主体一致的响应人，经综合审查 合格后，方可参与响应报价。 （二）相关资格要求 1．资质要求：具有经营规模年收入/ 万元以上，响应企业注册资本不低于 100 万元，工商注册时间不低于 1 年。 2．业绩要求：响应人须具有3年内（ 混凝土或水泥制品）的分供业绩 。 3．其他要求：/ 。 （三）其他要求 启信宝显示响应人为三级关联以内的，不得参加同一采购任务的报价。 三、响应报名 （一）报名方式 通过云筑网进行报名（网址https://www.yzw.cn/）。 （二）报名时间 以云筑网公示报名截止时间为准，逾期不再接受延期报名。 （三）资料范围 网 供应商资格预审表、营业执照、企业法人证明书或法人授权委托书、税务登记证、纳税人身份证明、近三年的 业绩和发票、响应保证金纳税承诺函等等，以上资料扫描件在云筑网报名时以附件形式上传。（必传，否则不 予通过资审。格式详见：第二章 响应文件格式） 务 （四）报名截止时间 自发布公告起不少于48小时。 商 （五）费用承担 响应人在为本次采购所进行的现场考察、事实调查和响应资料编制等一切活动中引起的费用开支和法律事务， 由响应人自行承担，采购人概不承担任何费用道和法律责任。 （六）采购清单 序号 材料名称 规格型号 单位 数量 管 1 II级钢筋混凝土管 DN300*50mm，含胶圈 m 1100.00 2 II级钢筋混凝土管 DN500*55mm，含胶圈 m 1500.00 3 II级钢筋混凝土国管 DN600*60mm，含胶圈 m 1000.00 4 II级钢筋混凝土管 DN800*80mm，含胶圈 m 1100.00 5 II级钢筋混凝土管 DN1000*100mm，含胶圈 m 350.00 6 II级中钢筋混凝土管 DN1200*120mm，含胶圈 m 200.00 7 钢筋混凝土检查井上井室 C30,D800*140mm，含爬梯 m 100.00 8 钢筋混凝土检查井上井室 C30,D1000*140mm，含爬梯 m 100.00 9 钢筋混凝土检查井上井室 C30,D1200*140mm，含爬梯 m 100.00 10 钢筋混凝土检查井上井室 C30,D1500*150mm，含爬梯 m 100.00 11 钢筋混凝土检查井上井室 C30,D1800*180mm，含爬梯 m 100.00 12 钢筋混凝土检查井下井室 C30,D800*140mm，含爬梯，含140mm厚底座 m 100.00 13 钢筋混凝土检查井下井室 C30,D1000*140mm，含爬梯，含140mm厚底座 m 100.00 14 钢筋混凝土检查井下井室 C30,D1200*140mm，含爬梯，含140mm厚底座 m 100.00 15 钢筋混凝土检查井下井室 C30,D1500*150mm，含爬梯，含150mm厚底座 m 100.00 16 钢筋混凝土检查井下井室 C30,D1800*180mm，含爬梯，含180mm厚底座 m 100.00 17 钢筋混凝土井筒 C30,D800*120mm，含爬梯 m 400.00 18 预制偏心井盖 φ1280变800，厚度140mm，含吊钩 个 100.00 19 预制偏心井盖 φ1480变800，厚度140mm，含吊钩 个 100.00 20 预制偏心井盖 φ1800变800，厚度160mm，含吊钩 个 100.00 21 预制偏心井盖 φ2160变800，厚度200mm，含吊钩 个 100.00 22 单算偏沟式雨水口 700*400*800mm*70mm厚度 个 180.00 23 双算偏沟式雨水口 1560*400*800mm*70mm厚度 个 100.00 24 钢筋混凝土矩形检查井 1700*1100*160mm m 10.00 25 钢筋混凝土矩形检查井 1700*1700*160mm m 4.00 26 钢筋混凝土矩形检查井 2100*1800*220mm m 6.00 27 钢筋混凝土矩形检查井 2400*2000*220mm m 4.00 四、响应保证金/响应保证金保险 网 （一）响应保证金/响应保证金保险 1．本次采购的响应保证金为10000 元，允许使用保险或保函等非现金交易担保方式，所有响应单位均要在平台 务 缴纳响应保证金，支付成功后点击页面【去响应】按钮，响应人方可正常参与。 2．云筑网方式：响应人应在采购文件签收后、开启响应文件2天前通过云筑网交付响应保证金或购买响应保证金 保险（报名阶段不需要缴纳响应保证金/保险），购买响应保证金保险视同缴纳响应保证金。 商 3．指定账户方式：响应人应在采购文件签收后、开启响应文件2天前通过“指定账户”交付响应保证金（报名阶 段不需缴纳响应保证金）。指定账户信息及保证金缴纳联系人信息详见采购文件。 4．公司上年度分供商评选名单中三星及以上道供应商、二级及以上分包商免除响应保证金缴纳。 （二）保证金退还 1．未成交退还：未成交响应人的响应保证金在公布成交结果后30个工作日内无息退还，成交人的响应保证金 不 管 转为履约保证金。履约保证金在合同履行完毕并办理完毕总结算书后/ 日内无息退还（履约保证金在签订项目执 行合同时另行约定）。 2．响应保证金有效时间：采购有效期内。 国 3．响应保证金风险指示： （1）响应人未按照采购文件足额缴纳响应保证金，响应无效； 中 （2）响应人未将响应保证金缴纳至采购文件中注明的指定账户，响应无效； （3）响应人已缴纳响应保证金，但未在本次响应保证金缴纳的截止时间前到达响应保证金指定账户，响应无效； （4）响应人缴纳响应保证金的汇款或转账信息中的单位名称与报名单位不完全一致，报名无效； （5）因响应人资料手续不全或不及时申请的原因，导致响应保证金滞后退还或无法退还的情况，责任和后果由 报价单位自行承担。 4．有下列情形之一的，响应保证金将不予退还： (1) 提供虚假的材料谋取成交的； (2) 经采购人审定，有围采串采行为的； (3) 成交人在收到成交通知书后，未在规定期限内与采购人签署合同或未按采购文件规定提交履约担保或未按照 采购文件要求条款签订合同的。 (4) 违反廉政承诺内容或发生其它违规行为的。 (5) 其他。 5．本次采购执行过程受评审小组成员集体监控，由评审组长负责采购执行问题反馈及处理，采购执行过程主要 不良情形及处理标准如下： （1）不良情形一：响应过程中若经评审小组评定为徇私舞弊、串通围采、恶意报价扰乱采购秩序的； 处理标准：不予成交，且在云筑网平台添加不良行为记录、没收保证金，并视情节对不良行为分供单位于云筑 网平台限制合作6-12个月或纳入不合格供应商名录，限制合作范围：公司下属所有项目。 （2）不良情形二：成交单位在响应中恶意低价，扰乱响应环境或低价成交后现场履约不良，实际所供物资与要 求质量不符，影响项目正常物资使用需求的； 处理标准：视情况对不良行为分供单位于云筑网平台限制合作12-24个月或纳入网不合格供应商名录，限制合作范 围：公司下属所有项目。 （3）不良情形三：成交单位无故拒供、擅自变更或者终止履约合同，不履行合同义务或供应能力出现重大问题 的； 务 处理标准：视情况对不良行为分供单位于云筑网平台限制合作12-24个月或纳入不合格供应商名录，限制合作范 围：公司下属所有项目。 （4）不良情形四：资审通过分供单位报价阶段，本次报商价与半年内参加我单位同品类同规格同要求的历史报价 无故存在不合理偏差，经采购工作小组共同决议为不良行为情形的； 处理标准：在云筑网平台添加不良行为记录，并视情况对不良行为分供单位于云筑网平台限制合作6-12个月或纳 入不合格供应商名录，限制合作范围:公司下属道所有项目。 五、报名文件要求 报名文件内容及顺序 管 （1）供应商资格预审表；（必填项） （2）营业执照扫描件；（必填项，正副本均可） 国 （3）一般/小规模纳税人税务登记证明；（必填项，若三证合一上传营业执照内即可；网上税务系统资格查询截 图亦可） （4）响应人提供最新的纳税信用评价信息表（必须为2025年度，若不能提供，需提供说明）、税收完税证明 中 （填发时间近3个月内）、无欠税证明（填发时间近3个月内）； （5）法定代表人身份证明（法人签字并加盖公章）；或法定代表人授权委托书（法人及委托人签字并加盖公章） 及被授权委托人在本单位缴纳的6个月的社保证明；法定代表人身份证明或法定代表人授权委托书身份证及签字 两处均需要盖章，仅盖一处章不予通过资审（必填项）。 （6）企业在“信用中国”网站信用报告自查（要求信用信息报告生成日期不早于采购公告发布时间，并保持其 完整性，盖公司公章）；（必填项） （7）近三年的混凝土或水泥制品 业绩证明合同、对应的发票；（必填项） （8）《绿色建材评价- 混凝土或水泥制品》T/CECS 10025-2019认证证书；（选填项） （9）采购人认为其他所需上传的资料，按以下第/（可多选）条进行约定。 ①《实施工业产品生产许可证管理的产品目录》内的物资工业产品生产许可证； ②本次采购品类的检测报告、代理商需提供厂家授权书、分供合同、发票、履约评价、业主表扬信； ③资源管理部门管理底线要求资料：/（详细描述其他资源使用部门发布的以上未体现的所需管理底线要求资 料）； ④样品提交：根据本项采购要求，评审小组决定报名单位不需要送样；（对于需要寄送样品未寄送的不予通过 资审） 样品数量清单 序号 采购物名称 材料规格、材质、性能、品牌等要求 样品要求 备注 1 / 2 提交地点及收件人：/，联系人及电话 /。 网 样品提交截止时间：/ 年/ 月/ 日 /时前（云筑网报名结束后48小时内）。 （一）报名文件要求 务 1.具体格式详见《第二章 响应文件格式》，以上资料均要求每页加盖公章后扫描成一个PDF文件，不接受单张图 片附件多次上传，不接受其他格式资料，扫描件不清晰视为无效资料；报名时将该PDF文件资料作为报名附件上 传至云筑网；提供虚假报名资料的单位，一经发现，取消其报名资格；报名文件应加盖企业公章，复印件应清 晰、完整； 商 2.若未按响应文件格式要求上传资料、资料不全、资料未签字盖章（空白页、无需填报的页面及目录不做要求）、 资料模糊不清晰均视为无效报名，不予通过资格预审。 道 六、资格审核说明及采购文件发放 （一）资格审核不通过的情形 1．信用中国存在不良行为、黑名管单记录及失信联合惩戒记录（本项采购期间）；与中建八局各子公司存在不良 合作记录 2．被识别有涉嫌围采串采行为的； 国 3．未响应采购公告的实质性要求和条件的； 4．主要内容、格式与采购公告规定不符的或关键内容不全、字迹模糊、无法辨认的； 中 5．响应人提供虚假资料、隐瞒误导采购单位的； 6．响应人或其成员不正当地影响资审工作的； 7．响应人以他人名义递交响应文件、串通递交响应文件、报名文件雷同、以行贿手段或者以弄虚作假等方式递 交响应文件的； 8．云筑网平台报名和响应报价为IP地址相同、显示关联交易方的； 9．启信宝等外部平台查询的信息，经审议后，视为关联交易方的； 10．响应人存在因低价成交后中途恶意调价或恶意停工的； 11．发生相关诉讼且未积极配合解决的、发生上访且造成恶劣影响的，围堵项目部或公司的； 12．响应人资质证书、证件过期，且未上传延期文件的； 13．不满足采购公告相关要求的； 14．响应人不得存在的其他情形：/。 （二）采购文件发放时间 1．发放形式：采购文件以电子版形式发布，不发布书面采购文件； 2．发放对象：经资格审查入围的响应人，收到云筑网短信通知后可登录云筑网（网址http://www.yzw.cn)下载采 购文件。 七、无效采购及其他条款 （一）资审对响应人数量要求 1.资格预审合格条件的响应人数量需满足以下要求：拟成交分供商数量(N)≤3时，有效分供商数量不少于2N+2； 拟成交分供商数量(N)&gt;3时，有效分供商数量不少于N+4。 2.因响应人资审通过不递交响应文件造成影响的，将对响应人暂停响应资格或标网记为不良行为。 （二）延长报名时间或重新组织采购 满足资格预审合格条件的响应人数量不满足要求时，可适当延长报名时间或重新组织采购。 务 （三）特别说明 1.参与采购活动的各方应对采购文件和响应文件中的商业和技术等秘密保密，否则应承担相应的法律责任。 商 2.填写附件2“供应商资格预审表”时，请务必填写上响应人正确邮箱、联系人、联系电话。 （四）采购人联系方式 道 1.各响应单位若对： （1）云筑网供应商账号的注册、维护、密码管理、信息变更； 管 （2）云筑网响应流程与操作方法； （3）成交后的合同订立与订单履约操作等存在疑问的，请详细阅读了解附件2《云筑集采供应商操作手册》，必 要时可通过云筑网在线客服或服务热线：4006-818-555沟通解决。 国 2.各响应单位若对本次采购内容、资格审核要求等存在疑问需要咨询的，请联系： 经办人：熊浩吉联系方式：18223201367 中 资审负责人：刘日光 联系方式：15889573755 3.若对资审结果有异议，需要申诉的，请联系： 申诉邮箱：zjbjcaigou@163.com或zj81caigou@163.com 中建八局第一建设有限公司 2026年8月20日 第二章响应文件格式 封面 中建八局第一建设有限公司 水泥制品物资采购 资 质 文 件 响应单位名称（签章）： 响应单位法人（签字）： 网 响应授权代表（签字）： 联 系 电 话 ： 往来函件邮箱： 务 公司网址（如有）： 报名文件提交日期： 装订顺序 资料名称 备商注 1 响应报名文件封面 必填项 2 报名文件目录 - 3 供应商资格预审表 道必填项 4 营业执照扫描件 必填项 5 一般/小规模纳税人税务登记证明 必填项 6 响应人纳税信用评价信管息表 必填项 7 税收完税证明 必填项 8 无欠税证明 必填项 9 法定代表人国身份证明 必填项 10 法定代表人授权委托书与6个月的社保证明 或填项 11 “信用中国”网站信用报告自查 必填项 12 中响应保证金承诺函 必填项 13 资质证明文件 必填项 14 响应品类对应的近3年业绩合同及发票 必填项 15 绿色建材评价证明 选填项 一、 供应商资格预审表（必填项） 企业名称 响应产品 水泥制品 响应品牌 生产地址 有限责任公司 2023年销售额 (万元) □股份有限公司 □中外合资企业 企业类型 2024年销售额 (万元) □全民所有制企业 □集体所有制企业 2025年销售额 (万元) □独资企业 营业执照号 法定代表人 营业执照 员工人数 注册资本 成立日期 营业期限 企业情况 仓库个数 仓库面积 姓 名 身份证号 被授权人 联系电话 电子邮箱 近三年期产品应用情况（不仅限于我司项目） 已完工程名称 发包工程联系人 联系电话 所供应物资名称 合同额（万元） 合同签订时间 网 二、 营业执照扫描件（必填项） 三、 一般/小规模纳税人税务登记证明（必填项） 务 四、 响应人纳税信用评价信息表（必填项） 2025年 商 五、 税收完税证明（必填项） 填发时间近3个月内 道 六、无欠税证明（必填项） 填发时间近3个月内 管 七、法定代表人身份证明（必填项） 响应人名称： 国 单位性质：有限责任公司 地址： 成立时间：中 年 月 日 经营期限： （姓名）系（公司）的法定代表人，职务：电话：。 特此证明。 附：法定代表人身份证复印件(正反面) 响应人：（盖单位章） 法定代表人：（签字） 年 月 日 八、法定代表人授权委托书（或填项） 响应负责人为法人时不填 中建八局第一建设有限公司： 本授权书声明：位于（公司地址） 的（公司名称） 的（法定代表人姓名）代表本公司授权（被授权人姓名）为 本公司的唯一合法代理人，代表本公司参加81-西南-大邑西岭文体-水泥制品-询比采购采购活动，并在整个采购 采购活动中，以本公司名义全权处理确认采购相关信息，采购工程报价、议价，交纳相关费用，签订合同，除 另有授权委托书外，执行和完成合同周期内的服务等一切与之有关的事务，并保证所提供的资质证明材料真实、 合法、完整、有效。 本授权书于2026年月日签字生效，授权期限自签字生效之日起，至合同履行完成之日止。授权期限内无特殊情况 不变更合法代理人（被授权人）。 法定代表人：(签字) 被授权人：(签字) 授权单位名称：（盖章） 联系电话： 网 附：被授权人身份证复印件(正反面) 九、被授权人在本单位近6个月的社保证明（或填项） 务 响应负责人为法人时不填 十、信用中国报告（必填项） 信用中国企业信用信息报告需满足以下两点要求：1、要商求报告生成日期不早于采购公告发布时间；2、“信用中 国”信用信息报告上传需保持其完整性，否则视为无效报告，不予通过资格预审。 信用中国网址：（https://www.creditchina.gov.cn） 道 十一、响应保证金缴纳承诺函（必填项） 管 中建八局第一建设有限公司 ： 我司自愿缴纳响应保证金1.0 万元，并进一步承诺如下： 我司若在响应或履约过国程中违反有关法律法规及响应文件、合同规定，或有下列情形之一的，贵司可将我司响 应保证金作为罚金进行扣除，同时依照相关响应文件条款进行处罚。 1．我司无正当理由拒签合同； 中 2．我司违法行为导致成交结果被确认无效的； 3. 我司在响应有效期内撤销或修改其响应文件； 4. 我司成交签订合同后未按合同要求进行履约的； 5. 我司行为影响采购工作进行的； 6. 我司出现其他违法、违约情况以及采购小组评定为恶意行为的。 响应单位（盖章）： 法定代表人（签字）： 日期： 年 月 日 十二、业绩合同及发票（必填项） 序号 签约单位 施工地点 施工内容 合同金额 签订时间 备注 合同关键页 对应发票 十三、绿色建材评价认证资料（选填项） 网 请查看报价网 址：https://xy.yzw.cn/sj/bid-detail?tenderId=&amp;source=3&amp;tenderCode=cscec2026082000002023946&amp;tenantId=cscec 务 信息来源:https://www.chinapipe.net/project/d3078565.html cqdingjiu 2026.08.24 12:31:48 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>应急泵站：9km；百汇至观将泵站：4.5km；泵站：9km</t>
+          <t>DN300*50mm，含胶圈：1100.00m；DN500*55mm，含胶圈：1500.00m；DN600*60mm，含胶圈：1000.00m；DN800*80mm，含胶圈：1100.00m；DN1000*100mm，含胶圈：350.00m；DN1200*120mm，含胶圈：200.00m；C30,D800*140mm，含爬梯：100.00m；C30,D1000*140mm，含爬梯：100.00m；C30,D1200*140mm，含爬梯：100.00m；C30,D1500*150mm，含爬梯：100.00m；C30,D1800*180mm，含爬梯：100.00m；C30,D800*140mm，含爬梯，含140mm厚底座：100.00m；C30,D1000*140mm，含爬梯，含140mm厚底座：100.00m；C30,D1200*140mm，含爬梯，含140mm厚底座：100.00m；C30,D1500*150mm，含爬梯，含150mm厚底座：100.00m；C30,D1800*180mm，含爬梯，含180mm厚底座：100.00m；C30,D800*120mm，含爬梯：400.00m；φ1280变800，厚度140mm，含吊钩：100.00个；φ1480变800，厚度140mm，含吊钩：100.00个；φ1800变800，厚度160mm，含吊钩：100.00个；φ2160变800，厚度200mm，含吊钩：100.00个；700*400*800mm*70mm厚度：180.00个；1560*400*800mm*70mm厚度：100.00个；1700*1100*160mm：10.00m；1700*1700*160mm：4.00m；2100*1800*220mm：6.00m；2400*2000*220mm：4.00m</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 供水, 改造</t>
+          <t>水泥制品, 采购公告</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>涪陵区武陵山镇农村供水保障能力提升工程招标计划表</t>
+          <t>中铁十五局集团四公司、地下公司、新能源公司八月份三次物资采购招标公告</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3744,7 +3728,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3759,53 +3743,49 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>涪陵区</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>新建及整治输配水管网总长124.26千米，新建加压泵站5座，新建高位水箱4座（总容积354立方米），武陵山水厂新建废水处理系统1套及配套电气工程等。</t>
+          <t>中铁十五局集团四公司、地下公司、新能源公司八月份三次物资采购招标公告</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>合同预估金额1861.77万元</t>
+          <t>招标项目资金已落实</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>输配水管网、加压泵站、高位水箱、废水处理系统、电气工程</t>
+          <t>空调,房屋改造材料,商品混凝土,道砟,绿化材料,运营监测系统,聚丙烯粗纤维,门窗,施工设备配件,混凝土</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>涪陵区武陵山镇农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区武陵山镇农村供水保障能力提升工程 名称 招标 网 法人 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 务 （盖 章） 项目 批准 商 文件 涪陵发改〔2026〕468号 及文 号 主要 道 新建及整治输配水管网总长 124.26千米，新建加压泵站 5座，新建高位水箱4座（总容积 354立方米），武 建设 陵山水厂新建废水处理系统1套及配套电气工程等。 内容 招 管 拟 标 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 国 称 涪 陵 区 中 重 武 庆 陵 市 山 招标 涪 镇 项目 陵 农 公 区 村 新建及整治输配水管网总长 124.26千米，新建加压泵站 5座，新建高 开 公 1 供 位水箱4座（总容积 354立方米），武陵山水厂新建废水处理系统1套 2026-09 1861.77 招 共 水 及配套电气工程等。 标 资 保 源 障 交 能 易 力 中 提 心 升 工 程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075549.html cqdingjiu 2026.08.21 10:06:56</t>
+          <t>中铁十五局集团四公司、地下公司、新能源公司八月份三次物资采购招标公告 中铁十五局集团四公司、地下公司、新能源公司八月份三次物资采购招标公告 招标编号：CR15G-2026-WZJC-0820 1.招标条件 1.1本招标项目 中铁十五局集团第四工程有限公司豫东南高新区全民健身、产城融合及职教园区EPC总承包项 目经理部，招标人为中铁十五局集团第四工程有限公司豫东南高新区全民健身、网产城融合及职教园区EPC总承包 项目经理部，招标项目资金已落实，该项目已具备招标条件，现对 空调 采购进行公开招标。 1.2 本招标项目 中铁十五局集团广元市昭化城区老旧小区改造建设项目(四期)一标段(第五立面整治)项目经理部， 招标人为 中铁十五局集团广元市昭化城区老旧小区改造建设项目(四期)一标段(第五立面整治)项目经理部 ， 务 招标项目资金已落实，该项目已具备招标条件，现对 房屋改造材料 采购进行公开招标。 1.3 本招标项目 中铁十五局集团有限公司G3京台高速公路蚌埠互通至路口枢纽段改扩建土建工程JTBL-06标段项 目经理部 ，招标人为 中铁十五局集团有限公司G3京台高速公路蚌埠互通至路口枢纽段改扩建土建工程JTBL-06 标段项目经理部 ，招标项目资金已落实，该项目已具备招商标条件，现对 商品混凝土 采购进行公开招标。 1.4 本招标项目中铁十五局集团有限公司克拉玛依融进实业发展有限公司铁路专用线EPC项目经理部 ，招标人 为 中铁十五局集团有限公司克拉玛依融进实业发展有限公司铁路专用线EPC项目经理部 ，招标项目资金已落 实，该项目已具备招标条件，现对道砟、商品道混凝土采购进行公开招标。 1.5 本招标项目 中铁十五局集团有限公司平漯周高铁站前五标项目经理部 ，招标人为 中铁十五局集团有限 公司平漯周高铁站前五标项目经理部 ，招标项目资金已落实，该项目已具备招标条件，现对 绿化材料 采购进 行公开招标。 管 1.6 本招标项目 中铁十五局集团有限公司河南信阳300MW先进压缩空气储能项目经理部 ，招标人为 中铁十 五局集团有限公司河南信阳300MW先进压缩空气储能项目经理部 ，招标项目资金已落实，该项目已具备招标条 件，现对 运营监测系统、聚丙烯粗纤维、门窗 采购进行公开招标。 国 1.7 本招标项目 中铁十五局集团城市轨道交通工程有限公司广州东至花都天贵城际项目二工区 ，招标人为 中铁十五局集团城市轨道交通工程有限公司广州东至花都天贵城际项目二工区 ，招标项目资金已落实，该项目 已具备招标条件，现对 施工设备配件 采购进行公开招标。 中 1.8 本招标项目 中铁十五局集团上海新能源发展有限公司白花山风电场二期工程项目经理部 ，招标人为 中 铁十五局集团上海新能源发展有限公司白花山风电场二期工程项目经理部 ，招标项目资金已落实，该项目已具 备招标条件，现对 混凝土 采购进行公开招标。 2.项目概况与招标内容 2.1项目概况 2.1.1 项目位于河南省信阳市潢川县，信阳师范学院理工学院二期用地面积约644.1亩，建设规模为265630平方米， 满足12000人的办学需要。建设内容包含图文信息中心、学生服务及活动中心、会议中心、教学楼、实验楼、学 院楼、看台、学生宿舍、餐厅、师生活动中心、单身教师公寓、人防工程及附属用房、南门车行景观桥等。 2.1.2 广元市昭化城区老旧小区改造建设项目(四期)一标段(第五立面整治) 项目位于四川省广元市,本工程总建筑 面积25554平方米。项目总体分为3个片区进行改造，分别是：红土垭片区（47栋）、老城片区（53栋）、新城片区 （51栋）；本项目为既有建筑屋面提升改造项目，主要内容为拆除原建筑屋面彩钢棚(含彩钢瓦、钢屋架、钢柱、 私建构筑物及其他)，改造原建筑屋面增设轻钢屋架坡屋面，搭设成品树脂瓦屋面，降低原建筑顶棚高度，同时 包含屋面防水、屋面排水、防雷接地等工程。 2.1.3 G3京台高速公路蚌埠互通至路口枢纽段改扩建工程项目起点位于蚌埠市高新区仁和村，止于合肥市肥东县 牌坊回族满族乡吴杰衖村，与GY京台高速蚌埠互通至大刘郢枢纽段顺接，沿线经过3市、6区县、13乡镇，全 长107.02公里；蚌埠市境内2.946公里，滁州市境内70.952公里，合肥市境内33.122公里。 其中由中铁十五局集团有 限公司承建的京台高速JTBL-06标段，位于安徽省合肥市肥东县白龙镇境内，起讫桩号K991+010~K1008+100，线 路全长17.09公里，主要承担标段内所有土建、交通导改、路面、绿化的施工。 主要工程内容包括： 路基工程： 挖方65.51万方、填方108.8万方。 路面工程：水稳28.59万方，沥青19.64万方。 桥、涵工程：桥梁共计14座（上跨 桥5座、主线桥7座、路口枢纽匝道桥2座）；分离立交涵洞130座（拆除新建盖板涵8座、两侧接长盖板涵16座、 两侧接长圆管涵106座）；桩基186根，总计桩长4341m；混凝土11.58万方；钢筋4082t。 其他工程：服务区一个 （草庙服务区）、改路、改沟及附属工程。 2.1.4 项目位于新疆维吾尔自治区克拉玛依市乌尔禾区，克塔线达尔布特站东侧。项目场地位于天山北麓准噶尔 盆地北缘山前冲、洪积砾质平原，地形平缓开阔，项目场地平均海拔为328~335M，地势自北向南缓倾，自然坡 度5~15°。主要为戈壁砾漠地貌，植被稀疏，地表覆盖有大厚度第四系全新统洪积物。 本项目施工线路自达尔 布特站两端咽喉接轨(起点K31+921.887、终点K33+640.817)，在站房对侧距离车站最外侧股道50M处，新建克拉 玛依融进实业发展有限公司铁路专用线1条，线路与车站贯通式布置，长度1.59KM，专用线有效长1041M， 设780x26M堆场1座，在达尔布特站百口泉端设牵出线1条，有效长850M，在牵出网线上设轨道衡1座。并在塔城端 咽喉设机待线1条，有效长55M。线路铺轨总长度3.572公里。电力专业进行电缆路径测量、电缆沟开挖及回填、 电缆敷设设备基坑开挖、基础制作、电杆组立，金具安装，导线架设、设备安装;通信专业进行光电缆路径测量、 光电缆沟开挖、光电缆敷设、设备安装;信号专业进行光电缆路径测量、光电缆沟开挖、光电缆敷设、新增室内 外设备安装。 务 2.1.5 新建平顶山至漯河至周口高速铁路位于河南省中南部，自西向东衔接平顶山市、漯河市和周口市。线路西 起郑万高铁平顶山西站，向东经平顶山南、舞阳县北，在漯河市与京广高铁漯河西站并站，经周口市商水县北 后，折向南沿郑阜高铁东侧走行至姚庄线路所，正线预留向商丘方向延伸条件，联络线引入既有周口东站郑阜 商 高铁场。本标段为PLZZQ-5标段，正线全长28.228公里，里程DK091+559.4～DK120+023.77，主要工程包括：站场 路基工程2.3公里；双线桥梁2座共25.932公里；单孔涵洞197.82横延米；无砟道床55.628公里，材料场1处、填料集 中加工站1处、混凝土集中拌和站2处、混凝土构配件预制场2处、制(存)梁场1处、钢梁拼装场1处，漯河西站场 相关工程。建设工期2023年3月31日至2026年9月10日，总工期为1259日历天。 道 2.1.6 河南信阳300MW压缩空气储能EPC总承包项目，要建设内容：地下储气库（地下储气库包含储气硐室及运 输通道，运输通道长度477米，按双车道设置；储气硐室长度1260米，采用直径15m硐径进行布置，）；地上建筑 工程（主要有储能车间、释能车间、工艺冷水泵房、工艺热水泵房、综合水泵房、综合楼等厂房及附属建筑）。 合同工期18个月。 管 2.1.7 中铁十五局集团城市轨道交通工程有限公司广州东至花都天贵城际项目二工区施工范围：京白1#盾构井、 京白2#盾构井、京溪路站～京白1#盾构井盾构区间、京白1#盾构井～京白2#盾构井盾构区间、京白2#盾构井～白 云东平站盾构区间。京白1#盾构井为地下一层双柱三跨矩形框架结构，设计总长度为70.0m，宽度31.4m,基坑深 度45.5~46.1m，京白2#国盾构井兼区间跟随所为地下一层双柱三跨矩形框架结构，设计总长度为100.0m，标准段 宽26.8m，盾构扩大端宽度为33m，埋深41m。三个盾构区间，隧道总长8453m，盾构采用6台TBM&amp;土压平衡双模 盾构法施工。隧道管片外径8500mm、内径7700mm、厚400mm、标准环宽1.6m、错缝拼接，混凝土强度等 级C50P12。区间隧道主要穿越：强风化花岗岩、中风化花岗岩，微风化花岗岩。 中 2.1.8 贵港白花山风电场二期工程项目场址位于场址位于贵港市港北区庆丰镇、奇石乡一带山脊。风电场中心位 置坐标约为E109°42.720’，N23°19.589’。场址海拔约300m~600m，距贵港市的直线距离约为28km，距南宁市 约170km。规划装机容量为90MW，本阶段拟安装7 台7.15MW(1 台限发0.25MW)和6 台6.7MW 风力发电机组，初 拟轮毂高度为120m，拟新建4 回35kV 集电线路，配套新建一座220kV 升压站，以一回220kV 线路送出至大圩光伏 升压站220kV 间隔，送出线路长度约25km。项目主要由进场及场内道路、风电机组、变电箱、1 座220kV 升压站 （不含配套储能装置，拟租赁储能）、35kV 集电线路、220kV 联络线路（本标段不包含联络线路施工）等组成。 2.2招标内容及包件划分 2.2.1 招标内容及包件划分：详见招标公告附件1《招标物资包件清单》，本次招标一包一投。 2.2.2 招标方式：采用国内公开招标方式。 3.招标依据 3.1本次招标的依据为： （1）《中华人民共和国招标投标法》； （2）《中华人民共和国招标投标法实施条例》（国务院第613号令）； （3）《工程建设项目货物招标投标办法》（国家发展改革委等七部委令第27号）； （4）《评标委员会和评标方法暂行规定》（国家发展改革委等七部委令第12号）； （5）《中国铁建股份有限公司物资采购管理规定（试行）》（中国铁建供应链〔2025〕106号）； （6）其他相关法律、法规、规章。 4.投标人资格审查及要求 4.1 本次招标资格审查采用资格后审的方式。 4.2 本次招标要求投标人须具备以下条件： 网 4.2.1空调（KT）： （1）营业范围要求：在中华人民共和国境内依法注册，具有独立法人资格、具有招标物资生产或供应经验的生 务 产商或代理商，并且提供投标人合法有效的营业执照扫描件； （2）财务能力要求：投标人须提供2024、2025年财务报表（资产负债表、现金流量表和利润表），新成立的公司 （2026年1月1日以后成立的）仅需提供成立后的财务报表；须开具13%的增值税专业发票；投标人具备投标包件 履约的资金保障能力； 商 （3）质量保证能力要求：投标物资质量符合或高于国家现行标准；须提供具有CMA或CNAS认证检测机构出具 的2024年至今招标物资任意种类/原材料质量合格的检验报告至少1份； 道 （4）供货业绩要求：须提供投标人2024年至今同类招标物资任意种类在同类工程项目或国内重点工程建设项目 供货业绩证明至少1份（须提供合同扫描件，时间以合同签订日期为准）； （5）履约信用要求：投标人近三年（2023年至今）无因自身履约问题而引起的法律诉讼、没有与骗取合同有关 管 的犯罪或严重违法行为，招标期内没有被处以责令停业、暂停投标、财产被接管、冻结、破产状态等，不在项 目行业主管部门限制投标的处罚期内、投标人在招标阶段内未被人民法院列为失信被执行人、不在最新版《中 国铁建合作方警示名录》、《中国铁建行贿人黑名单》、《中铁十五局集团有限公司高风险合作方警示名录》、 《中铁十五局集团有限公司物资不合格供应商名册》范围内；投标人须提供投标人及其法定代表人自递交投标 文件之日起前三年内中国国裁判文书网（ http://wenshu.court.gov.cn）诉讼及仲裁的查询结果截图；投标人须提供在 国家企业信用信息公示系统中未被列入严重违法失信企业名单的查询结果截图、“信用中国”网站 （www.creditchina.gov.cn）或“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）中未被列入失信被执行人 查询结果截图； 中 （6）其他要求： ①生产商不得与其所授权的代理商共同参与同一包件的招标，生产商或代理商具备提供延伸服务的能力，具备 跨地域的供应、集散能力。 ②本次招标不接受联合体参与。 ③法定代表人或单位负责人为同一个人的两个及以上供应商或母公司、全资子公司存在控股、管理关系的，不 得参与同一个包件招标。 房屋改造材料（FWGZCL）： （1）营业范围要求：在中华人民共和国境内依法注册，具有招标物资生产或供应经验的生产商或代理商，并且 提供投标人合法有效的营业执照扫描件； （2）财务能力要求：投标人须提供2025年财务报表（资产负债表、现金流量表和利润表），新成立的公司 （2026年1月1日以后成立的）仅需提供成立后的财务报表；须开具13%的增值税专业发票； （3）质量保证能力要求：投标物资质量符合或高于国家现行标准；须提供具有CMA或CNAS认证检测机构出具 的2024年至今招标物资任意种类/原材料质量合格的检验报告至少1份； （4）供货业绩要求：须提供投标人2024年至今同类招标物资任意种类在同类工程项目或国内重点工程建设项目 供货业绩证明至少1份（须提供合同扫描件，时间以合同签订日期为准）； （5）履约信用要求：投标人近三年（2023年至今）无因自身履约问题而引起的法律诉讼、没有与骗取合同有关 的犯罪或严重违法行为，招标期内没有被处以责令停业、暂停投标、财产被接管、冻结、破产状态等，不在项 目行业主管部门限制投标的处罚期内、投标人在招标阶段内未被人民法院列为失信被执行人、不在最新版《中 国铁建合作方警示名录》、《中国铁建行贿人黑名单》、《中铁十五局集团有限公司高风险合作方警示名录》、 《中铁十五局集团有限公司物资不合格供应商名册》范围内；投标人须提供投标人及其法定代表人自递交投标 文件之日起前三年内中国裁判文书网（ http://wenshu.court.gov.cn）诉讼及仲裁的查询结果截图；投标人须提供在 国家企业信用信息公示系统中未被列入严重违法失信企业名单的查询结果截图、“信用中国”网站 （www.creditchina.gov.cn）或“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）中未被列入失信被执行人 查询结果截图； （6）其他要求： 网 ①生产商不得与其所授权的代理商共同参与同一包件的招标，生产商或代理商具备提供延伸服务的能力，具备 跨地域的供应、集散能力。 务 ②本次招标不接受联合体参与。 ③法定代表人或单位负责人为同一个人的两个及以上供应商或母公司、全资子公司存在控股、管理关系的，不 得参与同一个包件招标。 商 商品混凝土（SPHNT-1）、商品混凝土（SPHNT-2）： （1）营业范围要求：在中华人民共和国境内依法注册，具有招标物资生产或供应经验的生产商或代理商，并且 提供投标人合法有效的营业执照扫描件； 道 （2）财务能力要求：投标人须提供2025年财务报表（资产负债表、现金流量表和利润表），新成立的公司 （2026年1月1日以后成立的）仅需提供成立后的财务报表； 管 （3）质量保证能力要求：投标物资质量符合或高于国家现行标准；须提供具有CMA或CNAS认证检测机构出具 的2024年至今招标物资任意种类/原材料质量合格的检验报告至少1份； （4）供货业绩要求：须提供投标人2023年至今同类招标物资任意种类在同类工程项目或国内重点工程建设项目 供货业绩证明至少1份国（须提供合同扫描件，时间以合同签订日期为准）； （5）履约信用要求：投标人近三年（2023年至今）无因自身履约问题而引起的法律诉讼、没有与骗取合同有关 的犯罪或严重违法行为，招标期内没有被处以责令停业、暂停投标、财产被接管、冻结、破产状态等，不在项 目行业主管中部门限制投标的处罚期内、投标人在招标阶段内未被人民法院列为失信被执行人、不在最新版《中 国铁建合作方警示名录》、《中国铁建行贿人黑名单》、《中铁十五局集团有限公司高风险合作方警示名录》、 《中铁十五局集团有限公司物资不合格供应商名册》范围内；投标人须提供投标人及其法定代表人自递交投标 文件之日起前三年内中国裁判文书网（ http://wenshu.court.gov.cn）诉讼及仲裁的查询结果截图；投标人须提供在 国家企业信用信息公示系统中未被列入严重违法失信企业名单的查询结果截图、“信用中国”网站 （www.creditchina.gov.cn）或“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）中未被列入失信被执行人 查询结果截图； （6）其他要求： ①生产商不得与其所授权的代理商共同参与同一包件的招标，生产商或代理商具备提供延伸服务的能力，具备 跨地域的供应、集散能力。 ②本次招标不接受联合体参与。 ③法定代表人或单位负责人为同一个人的两个及以上供应商或母公司、全资子公司存在控股、管理关系的，不 得参与同一个包件招标。 ④商品混凝土（SPHNT-1）、商品混凝土（SPHNT-2）包件,同一投标人可同时参与投标，但最多只能中标1个包 件。 道砟（DZ）、商品混凝土（SPHNT-3）： （1）营业范围要求：在中华人民共和国境内依法注册，具有招标物资生产或供应经验的生产商或代理商，并且 提供投标人合法有效的营业执照扫描件； （2）财务能力要求：投标人有依法纳税的良好记录；投标人须提供2025年财务报表（资产负债表、现金流量表 和利润表），新成立的公司（2026年1月1日以后成立的）仅需提供成立后的财务报表； （3）质量保证能力要求：投标物资质量符合或高于国家现行标准；须提供具有CMA或CNAS认证检测机构出具 的2023年至今招标物资任意种类/原材料质量合格的检验报告至少1份； （4）供货业绩要求：须提供投标人2023年至今同类招标物资任意种类在同类工程项目或国内重点工程建设项目 供货业绩证明至少1份（须提供合同扫描件，时间以合同签订日期为准； 网 （5）履约信用要求：投标人近三年（2023年至今）无因自身履约问题而引起的法律诉讼、没有与骗取合同有关 的犯罪或严重违法行为，招标期内没有被处以责令停业、暂停投标、财产被接管、冻结、破产状态等，不在项 目行业主管部门限制投标的处罚期内、投标人在招标阶段内未被人民法院列为失信被执行人、不在最新版《中 国铁建合作方警示名录》、《中国铁建行贿人黑名单》、《中铁十五局集团有限公司高风险合作方警示名录》、 务 《中铁十五局集团有限公司物资不合格供应商名册》范围内。投标人须提供投标人及其法定代表人自递交投标 文件之日起前三年内中国裁判文书网（ http://wenshu.court.gov.cn）诉讼及仲裁的查询结果截图。投标人须提供在 国家企业信用信息公示系统中未被列入严重违法失信企业名单的查询结果截图、“信用中国”网站 （www.creditchina.gov.cn）或“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）中未被列入失信被执行人 商 查询结果截图。 （6）其他要求： ①生产商不得与其所授权的代理商共同参与同道一包件的招标，生产商或代理商具备提供延伸服务的能力，具备 跨地域的供应、集散能力。 ②本次招标不接受联合体参与。 管 ③法定代表人或单位负责人为同一个人的两个及以上供应商或母公司、全资子公司存在控股、管理关系的，不 得参与同一个包件招标。 绿化材料（LHCL）： 国 （1）营业范围要求：在中华人民共和国境内依法注册，具有招标物资生产或供应经验的生产商或代理商，并且 提供投标人合法有效的营业执照扫描件； （2）财务中能力要求：投标人须提供2025年财务报表（资产负债表、现金流量表和利润表），新成立的公司 （2026年1月1日以后成立的）仅需提供成立后的财务报表； （3）质量保证能力要求：投标物资质量符合或高于国家现行标准； （4）供货业绩要求：须提供投标人2023年至今同类招标物资任意种类在同类工程项目或国内重点工程建设项目 供货业绩证明至少1份（须提供合同扫描件，时间以合同签订日期为准）； （5）履约信用要求：投标人近三年（2023年至今）无因自身履约问题而引起的法律诉讼、没有与骗取合同有关 的犯罪或严重违法行为，招标期内没有被处以责令停业、暂停投标、财产被接管、冻结、破产状态等，不在项 目行业主管部门限制投标的处罚期内、投标人在招标阶段内未被人民法院列为失信被执行人、不在最新版《中 国铁建合作方警示名录》、《中国铁建行贿人黑名单》、《中铁十五局集团有限公司高风险合作方警示名录》、 《中铁十五局集团有限公司物资不合格供应商名册》范围内；投标人须提供投标人及其法定代表人自递交投标 文件之日起前三年内中国裁判文书网（ http://wenshu.court.gov.cn）诉讼及仲裁的查询结果截图；投标人须提供在 国家企业信用信息公示系统中未被列入严重违法失信企业名单的查询结果截图、“信用中国”网站 （www.creditchina.gov.cn）或“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）中未被列入失信被执行人 查询结果截图； （6）其他要求： ①生产商不得与其所授权的代理商共同参与同一包件的招标，生产商或代理商具备提供延伸服务的能力，具备 跨地域的供应、集散能力。 ②本次招标不接受联合体参与。 ③法定代表人或单位负责人为同一个人的两个及以上供应商或母公司、全资子公司存在控股、管理关系的，不 得参与同一个包件招标。 运营监测系统（JCXT）、聚丙烯粗纤维（CXW）、门窗（MC）： （1）营业范围要求：在中华人民共和国境内依法注册，具有招标物资生产或供应经验的生产商或代理商，并且 提供投标人合法有效的营业执照扫描件； （2）财务能力要求：投标人须提供2025年财务报表（资产负债表、现金流量表和利润表），新成立的公司 （2026年1月1日以后成立的）仅需提供成立后的财务报表；投标人具备投标包件履约的资金保障能力； 网 （3）质量保证能力要求：投标物资质量符合或高于国家现行标准；须提供具有CMA或CNAS认证检测机构出具 的2024年至今招标物资任意种类/原材料质量合格的检验报告至少1份； （4）供货业绩要求：须提供投标人2023年至今同类招标物资任意种类在同类工程项目或国内重点工程建设项目 务 供货业绩证明至少1份（须提供合同扫描件，时间以合同签订日期为准）； （5）履约信用要求：投标人近三年（2023年至今）无因自身履约问题而引起的法律诉讼、没有与骗取合同有关 的犯罪或严重违法行为，招标期内没有被处以责令停业、暂停投标、财产被接管、冻结、破产状态等，不在项 目行业主管部门限制投标的处罚期内、投标人在招标阶段商内未被人民法院列为失信被执行人、不在最新版《中 国铁建合作方警示名录》、《中国铁建行贿人黑名单》、《中铁十五局集团有限公司高风险合作方警示名录》、 《中铁十五局集团有限公司物资不合格供应商名册》范围内；投标人须提供投标人及其法定代表人自递交投标 文件之日起前三年内中国裁判文书网（ http://wenshu.court.gov.cn）诉讼及仲裁的查询结果截图；投标人须提供在 国家企业信用信息公示系统中未被列入严重违道法失信企业名单的查询结果截图、“信用中国”网站 （www.creditchina.gov.cn）或“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）中未被列入失信被执行人 查询结果截图； （6）其他要求： 管 ①生产商不得与其所授权的代理商共同参与同一包件的招标，生产商或代理商具备提供延伸服务的能力，具备 跨地域的供应、集散能力。 ②本次招标不接受联合国体参与。 ③法定代表人或单位负责人为同一个人的两个及以上供应商或母公司、全资子公司存在控股、管理关系的，不 得参与同一个包件招标。 中 施工设备配件（SGSBPJ）： （1）营业范围要求：在中华人民共和国境内依法注册，具有招标物资生产或供应经验的生产商或代理商，并且 提供投标人合法有效的营业执照扫描件； （2）财务能力要求：投标人有依法纳税的良好记录；投标人须提供2025年财务报表（资产负债表、现金流量表 和利润表），新成立的公司（2026年1月1日以后成立的）仅需提供成立后的财务报表； （3）质量保证能力要求：投标物资质量符合或高于国家现行标准；须提供具有CMA或CNAS认证检测机构出具 的2024年至今招标物资任意种类/原材料质量合格的检验报告至少1份； （4）供货业绩要求：须提供投标人2024年至今同类招标物资任意种类在同类工程项目或国内重点工程建设项目 供货业绩证明至少1份（须提供合同扫描件，时间以合同签订日期为准）； （5）履约信用要求：投标人近三年（2023年至今）无因自身履约问题而引起的法律诉讼、没有与骗取合同有关 的犯罪或严重违法行为，招标期内没有被处以责令停业、暂停投标、财产被接管、冻结、破产状态等，不在项 目行业主管部门限制投标的处罚期内、投标人在招标阶段内未被人民法院列为失信被执行人、不在最新版《中 国铁建合作方警示名录》、《中国铁建行贿人黑名单》、《中铁十五局集团有限公司高风险合作方警示名录》、 《中铁十五局集团有限公司物资不合格供应商名册》范围内；投标人须提供投标人及其法定代表人自递交投标 文件之日起前三年内中国裁判文书网（ http://wenshu.court.gov.cn）诉讼及仲裁的查询结果截图；投标人须提供在 国家企业信用信息公示系统中未被列入严重违法失信企业名单的查询结果截图、“信用中国”网站 （www.creditchina.gov.cn）或“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）中未被列入失信被执行人 查询结果截图； （6）其他要求： ①生产商不得与其所授权的代理商共同参与同一包件的招标，生产商或代理商具备提供延伸服务的能力，具备 跨地域的供应、集散能力。 ②本次招标不接受联合体参与。 ③法定代表人或单位负责人为同一个人的两个及以上供应商或母公司、全资子公司存在控股、管理关系的，不 得参与同一个包件招标。 混凝土（HNT）： 网 （1）营业范围要求：在中华人民共和国境内依法注册，具有招标物资生产或供应经验的生产商或代理商，并且 提供投标人合法有效的营业执照扫描件； 务 （2）财务能力要求：投标人有依法纳税的良好记录；投标人须提供2025年财务报表（资产负债表、现金流量表 和利润表），新成立的公司（2026年1月1日以后成立的）仅需提供成立后的财务报表； （3）质量保证能力要求：投标物资质量符合或高于国家现行标准；须提供具有CMA或CNAS认证检测机构出具 的2024年至今招标物资任意种类/原材料质量合格的检验报商告至少1份； （4）供货业绩要求：须提供投标人2024年至今同类招标物资任意种类在同类工程项目或国内重点工程建设项目 供货业绩证明至少1份（须提供合同扫描件，时间以合同签订日期为准）； 道 （5）履约信用要求：投标人近三年（2023年至今）无因自身履约问题而引起的法律诉讼、没有与骗取合同有关 的犯罪或严重违法行为，招标期内没有被处以责令停业、暂停投标、财产被接管、冻结、破产状态等，不在项 目行业主管部门限制投标的处罚期内、投标人在招标阶段内未被人民法院列为失信被执行人、不在最新版《中 国铁建合作方警示名录》、《中国铁建行贿人黑名单》、《中铁十五局集团有限公司高风险合作方警示名录》、 管 《中铁十五局集团有限公司物资不合格供应商名册》范围内；投标人须提供投标人及其法定代表人自递交投标 文件之日起前三年内中国裁判文书网（ http://wenshu.court.gov.cn）诉讼及仲裁的查询结果截图；投标人须提供在 国家企业信用信息公示系统中未被列入严重违法失信企业名单的查询结果截图、“信用中国”网站 （www.creditchina.gov.cn）或“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）中未被列入失信被执行人 查询结果截图； 国 （6）其他要求： ①生产商不中得与其所授权的代理商共同参与同一包件的招标，生产商或代理商具备提供延伸服务的能力，具备 跨地域的供应、集散能力。 ②本次招标不接受联合体参与。 ③法定代表人或单位负责人为同一个人的两个及以上供应商或母公司、全资子公司存在控股、管理关系的，不 得参与同一个包件招标。 5.招标文件的获取 5.1凡有意参加投标者，请登陆中国铁建云链平台（www.crccep.cn）注册会员，查询拟参与投标包件进行网上报 名、支付标书费、下载电子招标文件，不接受线下打款支付标书费。 5.2招标文件售卖截止时间为：2026年8月28日17时00分（北京时间）。潜在投标人须在招标文件售卖截止时间前 完成中国铁建云链平台（www.crccep.cn）注册报名，并申请办理CA锁用于电子投标文件的签章、加密及解密 （CA办理所需资料及程序详见中国铁建云链平台首页-小鹿课堂-帮助中心-铁建云链平台数字证书办理流程）。 5.3本次招标一包一投，包件划分情况见招标公告附件1《招标物资包件清单》。 5.4招标文件每包件售价见招标公告附件1《招标物资包件清单》，售后不退。 5.5获取购买招标文件发票的方式：详见招标公告附件2。 6.投标文件的递交 网 6.1此次招标投标人需制作电子投标文件，并使用CA锁对投标文件进行加密，在递交截止时间前线上递交投标文 件，电子投标文件命名为“投标人名称-包件号”。 6.2投标文件递交截止时间：2026年9月15日09时00分（北京时间）。 务 6.3投标文件递交地点：中国铁建云链平台（www.crccep.cn），投标人须登陆该平台，在投标文件递交截止时间 前完成所有投标文件的上传。投标文件递交截止时间前未完成投标文件传输的，视为放弃投标资格。 6.4如招标人有需求，被评为中标候选人的投标人应无偿提商供纸质版投标文件，纸质版投标文件内容须与电子版 文件内容完全一致。 7.开标 道 7.1电子投标文件的解密 （1）电子投标文件解密时间：2026年9月15日09时00分至2026年9月15日10时00分（北京时间）。 管 （2）各投标人必须在规定的投标文件解密时间内登录中国铁建云链平台（www.crccep.cn）完成投标文件解密， 如因投标人自身原因导致所递交的投标文件无法在规定的时间内解密的，视为无效投标文件，后果及责任由投 标人自行负责。 8.发布公告的媒介 国 8.1本次招标公告在以下平台同时发布： （1） 中国招标投标公共服务平台(www.cebpubservice.com) 中 （2）中国铁建云链平台（www.crccep.cn） 8.2 本次招标安排如有变化，招标人将通过以上平台发布通知。 9.现场踏勘 本次招标不统一组织投标人踏勘工地路况，请各潜在投标人自行踏勘。 10.招标人信息及相关方联系方式 10.1招标人及联系方式： 1、招标人：中铁十五局集团第四工程有限公司豫东南高新区全民健身、产城融合及职教园区EPC总承包项目经 理部 联系人：韩工 电话：17361600714 2、招标人：中铁十五局集团广元市昭化城区老旧小区改造建设项目(四期)一标段(第五立面整治) 项目经理部 联系人：王工 电话：13508239573 3、招标人：中铁十五局集团有限公司G3京台高速公路蚌埠互通至路口枢纽段改扩建土建工程JTBL-06标段项目经 理部 联系人：李孝哲 电话：15290024948 4、招标人：中铁十五局集团有限公司克拉玛依融进实业发展有限公司铁路专用线EPC项目经理部 联系人：李振洋 电话：15649009369 5、招标人：中铁十五局集团有限公司平漯周高铁站前五标项目经理部 联系人：刘佳鑫 电话：15690863825 网 6、招标人：中铁十五局集团有限公司河南信阳300MW先进压缩空气储能项目经理部 联系人：李工 电话：15838025226 务 7、招标人：中铁十五局集团城市轨道交通工程有限公司广州东至花都天贵城际项目二工区 联系人：李莹波 电话：15639127367 商 8、招标人：中铁十五局集团上海新能源发展有限公司白花山风电场二期工程项目经理部 联系人：贾晓川 电话：15938849374 道 10.2招标组织机构及联系方式 招标组织机构：中铁十五局集团有限公司物资设备管理中心 管 地址：上海市静安区共和新路666号 招标文件答疑联系人：林工 电话：15515315800 邮箱：3246999219@qq.com 投标保证金退还联系人国：李会计 电话：13700791836 铁建云链平台技术支持：400-6296-888 中 2026年8月21日 附件1 招标物资包件清单 招标物资包件清单 招标 投标 物资名 计量 文件 保证金 序号 招标人名称 包件号 规格型号 数量 称 单位 售价 （万 （元） 元） 中铁十五局集 团第四工程有 限公司豫东南 高新区全民健 1 KT 空调 详见附件清单1 批 1 1000 3 身、产城融合 及职教园 区EPC总承包 项目经理部 钢板吊 YPT JS K 2 ㎡ 1911.7 顶板 FM-3000×1000×12mm-1mm 网 合成树 3 ASA-G-Z-A-960×400×3mm 个 1021.54 脂瓦 合成树 务 4 ASA-G-Z-A-1050×500×3mm ㎡ 18952.33 脂瓦 钢结构 5 防火涂 GT-N S F-Fp2.00 吨 53.69 料 商 油漆及 6 清洗用 2号 普通型 Kg 315870 溶剂油 道 7 氟碳漆 冰灰GY09二涂层 Kg 3699.63 金属雕 8 2000×380×16mm ㎡ 4317.82 中铁十五局集 花板 团广元市昭化 管 9 天沟 304 2×2000mm 吨 42.11 城区老旧小区 10 改造建设项 FWGZCL PVC管 DN110 m 3644.79 500 2 目(四期)一标段 金属面 11 (第五立面整 国岩棉夹 JYB3200×1150×5 ㎡ 741.4 治)项目经理部 芯板 普通聚 合物改 中 12 性水泥 LWIP CM Kg 12459.57 基防水 涂膜 SBS改性 沥青耐 13 根穿刺 SBS PYCu M M 3m ㎡ 9802.39 防水卷 材 14 地漏 PVC DN110 水封式 其他 个 321.18 15 PVC管 DN32 m 5605.48 防雷测 16 125×125×60mm 台 376.73 试盒 17 C15 m 60 18 C20 m 1140 19 中铁十五局集 商品混 C25 m 670 SPHNT-1 300 1 20 团有限公司G3 凝土 C30 m 750 京台高速公路 21 蚌埠互通至路 C35 m 580 22 口枢纽段改扩 C40 m 80 建土建工 23 C20 m 300 程JTBL-06标段 网 24 项目经理部 商品混 C25 m 780 SPHNT-2 500 2 25 凝土 C30 m 7650 26 C35 m 60 务 27 道砟 0.075mm-45mm m 2000 DZ 500 2 28 道砟 16-63mm m 10000 商品混 29 C15 m 150 商 凝土 商品混 30 C20 m 150 中铁十五局集 凝土 团有限公司克 商品混 道 31 拉玛依融进实 C25 m 400 凝土 业发展有限公 司铁路专用 商品混 32 SPHNT-3 C30 m 2500 1000 3 线EPC项目经 凝土 管 理部 商品混 33 C35 m 1500 凝土 商品混 34 C40 m 12000 国凝土 商品混 35 C45 m 500 凝土 中铁十五局集 36 中草籽 / Kg 6364.52 团有限公司平 漯周高铁站前 LHCL 500 2 五标项目经理 37 灌木 / 株 105804.6 部 中铁十五局集 运营监 38 JCXT 详见附件清单2 套 1 500 3 团有限公司河 测系统 南信阳300MW 聚丙烯 直径0.95±0.05mm，长度45-65mm， 39 先进压缩空气 CXW 吨 180 500 2 粗纤维 -0.92g/cm 储能项目经理 40 部 MC 门窗 详见附件清单3 批 1 500 2 中铁十五局集 团城市轨道交 通工程有限公 施工设 41 SGSBPJ 详见附件清单4 批 1 500 1 司广州东至花 备配件 都天贵城际项 目二工区 42 中铁十五局集 混凝土 C45 立方米 12606 团上海新能源 43 混凝土 C20 立方米 1800 发展有限公司 HNT 1000 3 白花山风电场 44 混凝土 C25 立方米 1025 二期工程项目 45 经理部 混凝土 C30 立方米 1850 注：1.以上所有包件物资材料数量、规格、型号在实施阶段可能有一定调整，最终数量、规格、型号应以买方下 达的发货订单为准。 网 2.供货时间为根据指导性施工组织设计确定的时间，实际供货时间可能有一定调整，实际供货时间以买方发货订 单的时间为准。 务 附件2发票开具说明 商 增值税电子发票开具说明 尊敬的各位投标人，如需开具增值税电子发票，请在本次开标结束后，五个工作日内将电子版开票信息（可编 辑Word版）”发送至中铁十五局集团有限公司物资设备管理中心—财务部，QQ邮箱：5438281@qq.com 联系人： 道 李会计，联系电话：13698883541 （一）发票开具要求： 管 1、开票信息严格按以下格式提供，严禁空格、增行等！！！ 2、电子版开票信息申请，请以“**单位发票开具资料”命名主题发送5438281@qq.com 邮箱；此信息将作为投标 人发票开具依据。 国 3、未按上述要求提供发票开具资料的，我方视同自愿放弃取得发票，将不再开具发票；发票开出后，非因工作 人员输入失误，一律不退不换。 4、开具增值税电子专用发票、电子普通发票请在邮箱中查询，不再邮寄。 中 （二）开具增值税发票提供信息： 汇款金额： 标书费： 服务费： 采购编号： 投标包件： 发票种类： （增值税电子专用发票或增值税电子普通发票）必选！！！ 公司名称： 收件人姓 名： 纳税人识别号： 纳税人资格： （一般纳税人或小规模纳税人） 地址： 电话： 收票邮箱： 开户行： 账号： 投标保证金交付说明：凡第一次参与中铁十五局投标的供应商在交付投标保证金同时必须将企业营业执照和开 户许可证（需注明开户行联行号）扫描件以“**单位营业执照等资料”命名主题发送至中铁十五局集团有限公司 物资设备管理中心—财务部，QQ邮箱：5438281@qq.com，否则无法对供应商进行维护，以免影响各单位正常投 标。 报名网址：https://www.crccep.cn/findNotices?noticeId=635086822493495296&amp;columnId=BiddingAnnouncement 信息来源:https://www.chinapipe.net/project/d3078356.html cqdingjiu 2026.08.24 12:31:49 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>及整治输配水管网：124.26千米；加压泵站：5座</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>涪陵区武陵山镇, 农村供水保障能力提升工程, 重庆, 输配水管网, 加压泵站, 高位水箱, 废水处理系统, 电气工程</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>涪陵区江东街道农村供水保障能力提升工程(一期)招标计划表</t>
+          <t>不锈钢材料招标公告</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3815,7 +3795,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3830,53 +3810,49 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>涪陵区</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>建设配水管网总长34.80km，新建加压泵站2座、改造已成泵站2座、新建加氯加药间1座、新建高位水箱7座、新建计量监测设施以及配套电气工程。</t>
+          <t>不锈钢材料</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>合同预估金额3503.77万元</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>配水管网、加压泵站、加氯加药间、高位水箱、计量监测设施、电气工程</t>
+          <t>不锈钢材料</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>涪陵区江东街道农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目名 涪陵区江东街道农村供水保障能力提升工程（一期） 称 招标法 网 人或招 重庆水务环境控股集团渝东自来水有限公司 标人名称 （盖章） 项目批 务 准文件 涪陵发改〔2026〕470 号 及文号 主要建 建设配水管网总长 34.80km，新建加压泵站 2 座、改造已成泵站 2 座、新建加氯加药间 1 座、新建高位 设内容 水箱 7 座、新建计量监测设施以及配套电气工程商。 招 招标文件 拟交 合同预估 序 招标项 标 备 招标内容 计划发布 易场 金额(万 号 目名称 方 注 道 时间 所 元) 式 涪陵区 重庆 招标项 江东街 市涪 目 建设配水管网总长 34.80km，新建加压泵站 2 座、 公 道农村 陵区 管 改造已成泵站 2 座、新建加氯加药间 1 座、新建高 开 1 供水保 2026-09 公共 3503.77 位水箱 7 座、新建计量监测设施以及配套电气工 招 障能力 资源 程。 标 提升工程 交易 （一期） 中心 国 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075548.html cqdingjiu 20中26.08.21 10:06:56</t>
+          <t>不锈钢材料招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3078292.html cqdingjiu 2026.08.24 12:31:50 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>配水管网：34.80km；加压泵站：2座；已成泵站：2座</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>重庆, 农村供水保障能力提升工程, 配水管网, 加压泵站, 加氯加药间, 高位水箱, 计量监测设施, 电气工程</t>
+          <t>不锈钢, 材料, 招标</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>中国电建水电五局二公司重庆轨道交通17号线一期7标内外涂环氧消防复合钢管管件采购项目公开竞价采购(二次挂网)变更公告(一)</t>
+          <t>西南油气田分公司致密气项目部金浅26井地面集输工程招标公告</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3886,7 +3862,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3901,49 +3877,49 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>详见附件。</t>
+          <t>金浅26井地面集输工程包括井口模块、除砂器橇、三相分离器橇、密闭装油橇、凝析油罐模块、气田水罐模块、放空分液罐模块、放空模块、出站模块等配套工程。</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>项目估算金额：450万元（含税）</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>内外涂环氧消防复合钢管管件</t>
+          <t>地面集输工程所需设备和材料</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>中国电建水电五局二公司重庆轨道交通17号线一期7标内外涂环氧消防复合钢管管件采购项目公开竞价采购(二次 挂网)变更公告(一) 详见附件。 信息来源:https://www.chinapipe.net/project/d3075376.html cqdingjiu 2026.08.21 10:06:56 网 务 商 道 管 国 中</t>
+          <t>西南油气田分公司致密气项目部金浅26井地面集输工程招标公告 第一章 招标公告 西南油气田分公司致密气项目部金浅26井地面集输工程 招标公告 招标编号：ZY26-XN301-GC0253-01 网 1．招标条件 本招标项目西南油气田分公司致密气项目部金浅26井地面集输工程己由西南油气田分公司致密油气勘探开发项目 部批准建设，项目业主为西南油气田分公司致密油气勘探开发项目部，建设资金来自自筹，项目出资比例 务 为100%，招标人为西南油气田分公司致密油气勘探开发项目部。项目己具备招标条件，现对该项目进行公开招 标。 2．项目概况与招标范围 商 2.1建设地点 四川省绵阳市。 道 2.2建设规模及主要建设内容 为保障2026年分公司及项目部产量目标的完成，根据已批复的《关于金浅26井地面集输工程初步设计的批复》 （致密油气〔2026〕99号），结合致密油气勘探开发项目部产能及配套建设工程工作安排需要，拟启动施工单位 管 招标工作。招标人为中国石油天然气股份有限公司西南油气田分公司致密油气勘探开发项目部。项目估算金额： 450万元（含税）。 2.3计划工期 国 合同签订之日起至工程竣工验收止，需书面承诺按甲方要求时间完成。 2.4标段划分及各标段具体内容 中 本次招标共1个标段，具体要求： 标段一：金浅26井地面集输工程：新建金浅26井1座分为井口模块、除砂器橇、三相分离器橇、密闭装油橇、凝 析油罐模块、气田水罐模块、放空分液罐模块、放空模块、出站模块共计九部分等配套工程。该项目估算金额 450万元（含税）。 工程量为初步预估工程量，实际工程量以单位工程施工图0版（工程开工前予以下发）为准。站内设备/阀门、管 材、管配件等为甲供，钢结构、土建及自控等常规用料为乙供；线路直管、热弯、热收缩套（带）为甲供，其 他为乙供，最终以甲乙双方实际签订甲乙供料界面划分清单为准。 2.5招标范围 对金浅26井地面集输工程施工部分进行公开招标。其中具体包含但不限于 （1）站场部分：包括包含工艺安装、总图、结构、建筑、给排水及消防、油漆涂装及保温、热工、绝缘接头焊 接、一次仪表安装、电气（不含投建运实施的外供电）、仪器仪表校检、安全阀检定、入场前的标准化布局 （总图布置及门禁系统）、降噪等施工；不含通信、系统组态、数字化交付、无损检测、防爆电气检测和土建 专业检测。 （2）负责甲供材料的领取、存放、转运、使用、回收、退库、记录等；负责乙供材料（场站：钢结构、给排水 材料、总图土建材料、部分螺栓、垫片等 （3）负责施工过程中环境保护，包括废料、废液、建渣等垃圾回收和处理工作以及设备、设施的保护工作； （4）负责焊接工艺评定（含返修）、焊接工艺规程编制及引用工作； （5）负责配合进行单机试运和联合调试，并按照发包人通知负责投产保运工作； （6）负责特种设备（压力容器）安装告知工作，配合接受地方部门监督检验； （7）按设计要求、标准规范及政府相关管理部门要求应进行特殊要求的检验试验及复检项目； （8）负责本工程工程作业过程中涉及到的地方行政单位、企事业单位及当地居民关系协调； （9）负责道路、河流、沟渠、国防光缆等穿越手续办理及穿越费用的缴纳关工网作。 2.6本次招标设最高投标限价 详见《金浅26井试采地面集输工程（主体工程）招标合同价款说明》，详见第五章报价要求，不满足的其投标将 务 被否决。 报价方式为在此最高投标限价标准的基础上，报整体下浮比例（不含安全文明施工费、规费、税金等不可竞争 费用）。下浮百分比须大于或等于7%，最多保留两位小数。（举例说明： 报价方式为在此最高投标限价标准 的基础上，报整体下浮比例（不含安全文明施工费、规费商、税金等不可竞争费用）。下浮百分比须大于或等 于7%，最多保留两位小数。如：8%、8.0%、9.10%，10.12%均符合要求；若下浮费率为负数或者超过两位小数， 如：-1%，2.432%则不符合要求，投标将被否决。（投标人报价需充分考虑两年内市场变化因素，服务期限内单 价价格不作调整）。 道 2.7质量要求 合格。达到设计要求，无质量、安全事故事件发生，符合国家和行业有关施工及验收规范，以及国家和行业有 关管理规定进行施工和验收。 管 2.8 投标人存在待认定失信行为的处理要求：若投标人在中国石油物资有限公司西南分公司组织实施的其他招标 项目中发生失信行为且当前处于待认定处理期间，应当在投标文件中履行告知义务。对于正式认定处理的失信 行为导致暂停投标资格情形的，招标人有权取消其中标人资格。 国 *3. 投标人资格要求 *1.投标人具备合格有效的加载统一社会信用代码的营业执照。 中 *2.本项目： 不接受联合体投标。 允许，允许分包内容：主体工程（工艺焊接、电仪等）以外的部分，部分非主体、非关键性工作。报建设单 位审批同意后可按程序进行分包。 要求：投标人须承诺：投标人须承诺：投标人拟在中标后将中标项目的部分非主体、非关键性工作进行专业工 程分包或劳务分包的，应取得招标人的同意，将分包单位资质、分包合同和HSE合同等报招标人备案，且分包商 须具有满足分包项目性质要求的资质，分包施工负责人（分包项目经理）具有满足分包项目性质要求的注册建 造师执业资格。接受分包的单位不得再次分包。 对于不具备分包条件或者不符合分包规定的，招标人有权在签订合同或者中标人提出分包要求时予以拒绝。发 现中标人转包或违法分包时，可要求其改正；对于拒不改正的，可报请业主有关部门查处，并终止合同。具体 按照招标人及上级单位发布的相关制度要求执行。 *投标人须承诺：如分包商分包项目为中国石油天然气集团有限公司管理专业，分包商须在中国石油工程建设管 理平台承包商资源库内选择，通过的资质类别和等级与分包项目资质要求一致，状态正常。 不允许代理商投标。 *3.资质要求： *3.1有要求，资质要求： 金浅26井地面集输工程中金浅26井站建设规模7万立方米/天，设计压力8.5 兆帕，属于小型石油化工工程，投标 人须具有石油化工工程施工总承三级及以上资质，具有承压类特种设备安装、修理、改造许可项目工业管道安装 （GC1）许可子项目的中华人民共和国特种设备生产许可证（原中华人民共和国特种设备安装改造维修许可证 （压力管道）：GC类GC1级资质）。过渡期应符合《市场监管总局办公厅关于特种设备行政许可有关事项的通 知》（市监特设发〔2022〕17号）。 注：提供证书资料的影印件，同时在全国建筑市场监管公共服务平台（网址：http://jzsc.mohurd.gov.cn）进行查 询，并将带有“企业资质证书号”的查询结果页面进行截图，载入投标文件中。 网 *3.2投标人须具备有效的许可范围为建筑施工的安全生产许可证（许可证应在有效期内且许可范围与本项目主体 工程相关）。 注：提供证书资料的影印件，同时在企业所在省市相关政府网站（或政府相关信息系统）进行查询，并将查询 务 结果页面截图，载入投标文件中。 *3.3投标人须通过中石油统一组织的公开招标资格评审，通过结果在中国石油工程建设管理平台承包商资源库查 询，通过的资质类别和等级与本项目资质要求一致，状态正常（投标人因换领证书发生等级变更的，应及时维 护承包商资源库等级状态，若换领后证书等级高于承包商商资源库显示等级的，以承包商资源库显示的为准）。 *4人员资格和要求： 有人员要求，人员要求： 道 *4.1项目经理：须具有二级注册建造师资格（机电工程专业）并在注册有效期内且具备有效的安全生产考核合格 证书（B证）。且在施工期间不得担任其他在建项目的项目经理（需提供书面承诺）。 管 注：提供证书和相关佐证资料的影印件，同时在全国建筑市场监管公共服务平台（网 址：http://jzsc.mohurd.gov.cn）进行查询，并将载有“执业注册信息”的查询结果页面进行截图，载入投标文件 中。 若提供的一级建造师注国册证书，须符合《住房和城乡建设部办公厅关于全面实行一级建造师电子注册证书的通知 （建办市〔2021〕40号）的要求，否则会因为注册证书无效而被否决投标。（一级建造师打印电子证书后，应在 个人签名处手写本人签名，未手写签名或签名图像笔迹不一致的，该电子证书无效，下载时间需为提交文件截 至之日前180日内） 中 *4.2 技术负责人：具有5年及以上类似本工程工作经验（提供曾经参与工程的业主证明文件，第一个项目至最新 一个项目时间间隔不低于五年），大学本科及以上学历；且在施工期间不得担任其他在建项目的技术负责人 （需提供书面承诺）。 注：提供学历证书的影印件。 *项目经理与技术负责人不允许兼任。 *4.3安全管理人员：具有不少于1名专职安全员，且应具有在有效期范围内专职安全生产管理人员证书C3且在施 工期间不得担任其他在建项目的安全管理人员（需提供书面承诺）。 注：提供证书资料的影印件。 5.机具设备要求： 无要求。 *6.业绩要求: 近年（2024年1月1日至投标截止时间）（已完成 □已完成或新承接或正在实施）不少于1个类似项目。类 似项目:天然气集输工程工艺安装或天然气处理装置工艺安装施工，业绩证明材料：业绩需提供合同复印件及能 够证明项目完工投运的资料。【合同复印件、完工交接或竣工验收）证明无法体现业绩所需要求的，应提供设 计文件或业主证明进行补充佐证】注：业绩时间以完成投运时间为准 。 *7.财务要求： 7.1要求，投标人为资不抵债的，投标将被否决。 需提供经审计的财务证明资料：投标人需提供2024年度或2025年度经会计师事务所或审计机构审计的财务会计 报表财务报表，包括资产负债表、现金流量表、利润表；若为事业单位投标，提供相关财务证明资料。若投标 人成立时间晚于2026年1月1日，提供成立以来的财务状况表。 网 *8.信誉要求 1、投标人没有处于被责令停业,财产被接管、冻结、破产等状态； 务 2、投标人2024年至投标文件递交截止之日无直接影响本项目履约能力的违法、违规不良记录；不良记录包括但 不限于以下情形：因涉嫌犯罪被办案机关立案追查、审查起诉、被法院判决有罪；在和招标人历史合同履约中 存在因商业欺诈、产品质量问题等实质性侵害招标人权益的行为；被国家、招标人及其上级部门明文规定暂停 或取消交易资格； 商 3、2024年1月1日至投标截止时间投标人、法定代表人或者负责人、拟委任的项目经理无行贿犯罪。 4、投标人没有法律、行政法规规定的其他限制参与招投标活动的情形。 道 5、投标人在开标当日不得在存在以下情形： （1）投标人被“国家企业信用信息公示系统”网站（www.gsxt.gov.cn）列入严重违法失信企业名单。 管 （2）投标人被人民法院在“信用中国”网站（www.creditchina.gov.cn）列入严重失信主体名单。法定代表人或者 负责人被人民法院中国执行信息公开网（https://zxgk.court.gov.cn/shixin/）列为失信被执行人。 （3）开标当日被中国石油招标投标网暂停或取消投标资格。 国 （4）投标人、拟委任的项目经理被“全国建筑市场监管公共服务平台”网站 （http://jzsc.mohurd.gov.cn/asite/jsbpp/index）列入黑名单，或虽然被“全国建筑市场监管公共服务平台”网站 （http://jzsc.mohurd.gov.cn/asite/jsbpp/index）列入黑名单但移除黑名单日期在投标截止时间之后的。 中 据《中国石油天然气集团有限公司“三商”黑名单管理办法》，投标人被纳入“三商”黑名单的惩戒相关 内容见下表。投标人应在投标文件中承诺响应该要求（格式见招标文件第六章投标文件格式）。 黑名单 惩戒适 惩戒主体 惩戒范围 惩戒阶段 信息查询 等级 用 正在参与投标、谈判 或其他竞争性方式采 以中国石油 实行“一处受罚， 1、纳入黑名单的“三商”。 集团公 购的，应认定其不具 招标投标网 全集团 处处受限”，不 2、纳入黑名单的“三商”的法定代表人 司级 有相关资格。 公示信息为 区分类型 （或负责人）、实际控制人在惩戒期内 已经完成定商活动的， 准。 在其他法人企业或组织担任法定代表人 不予发放中标或成交 内 （或负责人）、实际控制人的，该其他 通知书。 网：http/:/bdie.nergyaheadc.npc/#/ 法人企业或组织。 已经发出中标或成交 外 企业级 原则上本单位 通知书的，不再继续 网：hptt/s/:wwwc.npcbdidnigc.om/ 签订合同。 以上1-4条款、6条款投标人在投标文件中提供书面承诺，5条款约定要求以开标当日在相应网站的查询结果为准。 招标专业机构协助评标委员会将通过“信用中国”、“国家企业信用信息公示系统”、“全国建筑市场监管公 共服务平台”和资质、资格强制要求的政府发证机关官方网站方式核查投标人信誉及所提供的证书、资料的真 实性、有效性；核查投标人有无直接影响本项目履约能力的异常、有无违法违规记录等情形。 *9.其他要求： 投标人须提供书面承诺满足《金浅26井试采地面集输工程（主体工程）招标合同价款说明》合同结算条款 相关内容。 投标单位必须提交《廉洁自律承诺书》详见附件《廉洁自律承诺书模板》，招标结束后，中标 单位提交的《廉洁自律承诺书》将作为合同附件。 以上“*”号条款，如不满足，其投标将被否决 4．招标文件的获取 4.1凡有意参加投标的潜在投标人，请于2026-08-21至2026-08-26 23:59:59（北京时间，下同）内完成以下步骤后登 录中国石油电子招标投标交易平台下载电子招标文件。 网 ① 投标登记 登录中国石油电子招标投标交易平台，搜索本项目，在拟投标标包处点击“报名”，网 址：http://ebidmanage.cnpcbidding.com/bidder/ebid/base/login.html。 务 （如未在中国石油电子招标投标交易平台上注册过的潜在投标人需要先注册并通过平台审核。具体操作请参考 中国石油招标投标网操作指南中“投标人用户手册”相关章节。） ② 支付标书费 商 登陆中国石油招标中心招标文件购买平台，在可购买的订单列表下支付标书费，网 址：http://www2.cnpcbidding.com/#/wel/index。 道 （登陆账号和中国石油电子招标投标交易平台一致，密码需要重新设置。投标人首次登录需通过手机验证码登 录，登录后设置登录密码，提交成功后可以同时使用户名密码或手机验证码登录。详见附件《中国石油招标中 心投标商用户操作手册》，咨询电话:4008800114。） 管 4.2招标文件按项目售价为200元人民币／标包（标段），请有意参加投标的潜在投标人确认自身资格条件是否满 足要求，售后不退，应自负其责。 4.3本次招标文件采取线上发售的方式。潜在投标人在4.1规定的时间内完成4.1规定的2项工作（投标登记和支付标 书费）后，潜在投标人国可在中国石油电子招标投标交易平台下载招标文件。 4.4潜在投标人在中国石油招标中心招标文件购买平台上付款成功后，在“我的订单”中会生成一条购买记录， 点击订单详情，自行下载招标文件电子发票，不再开具纸质发票。 中 4.5此次采购招标项目为全流程网上操作，需要使用U-key完成投标工作。 ① 所有首次参与中国石油招标项目投标人必须办理U-key。具体办理通知公告及操作手册下载方法如下：登录中 国石油招标投标网首页：https://www.cnpcbidding.com“通知公告栏目”的“操作指南”中“电子招投标平 台Ukey办理通知公告及操作手册”，即可下载“Ukey办理通知公告及操作手册.zip”。 ② 已办理U-key的投标人应复核U-key证书是否处于有效期内，如证书失效，需按上述程序购买新的U-key。 5．投标文件的递交 5.1本次招标采取网上递交电子投标文件的投标方式 投标文件递交的截止时间（投标截止时间及开标时间，下同）为2026-09-11 08:30:00，投标人应在截止时间前通过 中国石油电子招标投标交易平台递交电子投标文件。 注：请投标人注意：为确保投标有效，对于使用“投标客户端”编制的投标文件，在按照操作要求进行信息关 联、签章、加密和上传后，确保上传的文件的附件状态都是验签完成。点击验签确认，当前状态是“已确认”， 并且下方出现“撤标”按键，才视为成功提交投标文件。其它状态都是投标不成功，请投标人密切关注！如在 投标截止时间前未能成功上传投标文件，投标将被拒绝。（为避免投标人在投标文件递交截止时间前未能成功 上传投标文件，建议投标人提前2日递交投标文件）具体操作流程参见“操作指南-投标人操作手册”。 5.2逾期上传的投标文件，中国石油电子招标投标交易平台将予以拒收。 5.3 潜在投标人应在投标截止时间前须按标段提交投标保证金，每标段 5 万元。 6．发布公告的媒介 本次招标公告在中国招标投标公共服务平台（http://www.cebpubservice.com）、中国石油招标投标 网(http://www.cnpcbidding.com)上发布。（适用于依法必须招标项目） 注：本项目中标候选人公示的内容将包含单位资质证书、项目经理等相关信息，以接受社会监督。若有造假， 将按照法律法规及本招标文件相关规定处理，请投标人认真核实投标资料，确保真实无误。（详见投标文件格 式中公示信息表，投标人需填写） 网 7．联系方式 招 标 人：西南油气田分公司致密油气勘探开发项目部 招标机构：中国石油物资有限公司西南分公司 地 务地 址：四川省成都市青羊区小关庙 址： / 街6号 邮 邮 编： 610017 编： / 商联 系 人： 邹女士/张先 联 系 人： 王老师 生 电 电 话： 18728590001 话： 028-68250085/028-68250035 传 传 真： / 真： / 道 电子邮 电子邮件： / 件： / 网 网 址： / 管 址： / 开户银行： / 开户银行： / 账 账 号： / 国 号： / 财务咨询： 许女 士 电 话： 028-68233741 中 网站注册、U-Key办理、招标管理平台（购买招标文件及投标保证金递交）及电子交易平台操作指导： 咨询电话：4008800114 交易平台运营机构：中油物采信息技术有限公司 能源一号网站邮箱：energyahead@cnpc.com.cn 请务必在操作前认真阅读操作手册，如有疑问再在工作时间咨询。 中国石油物资有限公司西南分公司 (中国石油天然气集团有限公司招标中心西南分中心) 2026年8月21日 附件：投标商操作手册V1.1.pdf 附件：投标保证保险理赔服务书-中意财险.doc 附件：投标保证金保险功能操作手册-投标人.docx 信息来源:https://www.chinapipe.net/project/d3078290.html 网 cqdingjiu 2026.08.24 12:31:50 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>用于地面集输工程的建设</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>管材, 地面集输工程, 四川</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026年石柱分公司黄水镇黄连大道通信管道建设招标公告</t>
+          <t>喜德县冕山镇及两河口镇污水管道改造建设项目施工的招标文件预公示</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3953,7 +3929,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3968,33 +3944,37 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>凉山彝族自治州</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>石柱土家族自治县</t>
+          <t>喜德县</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>本次修复选择开挖换管：开挖约80米，2孔110波纹管、2孔蜂窝管，新建两通信手控井。</t>
+          <t>喜德县冕山镇及两河口镇污水管道改造建设项目的具体内容见附件信息。</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>项目资金已落实。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>通信管道</t>
+          <t>污水管道</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026年石柱分公司黄水镇黄连大道通信管道建设招标公告 ZB_ZHAOBIAOGONGGAO_START 本询比项目为 2026年石柱分公司黄水镇黄连大道通信管道建设 （标段 编号： CQBBFA202604170051 ），采购人为 中国电信股份有限公司石柱分公司 ，采购代理机构为 。项目 资金已落实。 具备采购条件，现进行公开询比，特邀请有意向的且具有提供标的物能力的潜在供应商（以下简 称供应商）参加询比响应。 1.项目概况与采购内容 1.1项目概况： 2026年石柱分公司黄水黄连大道通信管道修复项目主要针对黄水网黄连大道受损通信管道进行修 复80米 本次集中询比合同有效期为： 2026.9-2026.12 1.2采购内容 及标包划分情况： 务 1.2.1 本次询比的规模、货物名称、数量及主要技术参数、交货期及交货地点具体如下：黄水镇黄连大道80米通 信管道修复。 序号 标包名称 产品名称 规格型号 数量 交货地点 交货期 商 2026年石柱分公司黄水 黄水镇黄连 1 镇黄连大道通信管道建 管道建设 新建2孔110波纹管、 新建2孔蜂窝管 80 2026.12.20 大道 设 道 本项目 不划分标包 。 ${ } ${ 本项目允许供应商同时成交的最多标包数为 0 个。 } 本项目将按照最新的《中国电信供应商不良行为管 理规则》执行供应商不良行为处理结果，请重点关注处理结果适用的供应商主体、被处理产品、处理范围、禁 限期、处理措施等关键内容，请务必登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）查阅《中国 管 电信供应商不良行为管理规则》。 本项目根据《中国电信供应商不良行为管理规则》选择适用备选处理措施 （但涉及生产安全责任事故的处理结果不适用备选措施）。 1.2.2成交供应商数量： 1 个，每个成交供应商对应的份额如下 ： [请在此处自行编辑与采购方案相同的成交原则] 国 ${ 1.2.2成交供应商数量如下： [ 请在此处自行编辑与采购方案相同的有效供应商及成交供应商数量原则相关表格 ] 每个成交供应商对应的份额如下: [请在此处自行编辑与采购方案相同的份额分配原则] } 1.3本项目 设置最高 响应限价 。 设置最高响应限价，最高响应限价为不含税31000元人民币/计算方法，供应商响应报价高于最高 响应限价的，其响应将被否决 供应商响应报价高于最高响应限价的，其响应 将被否决。 ${ } 2.供应商中资格要求 2.1供应商基本资格要求 2.1.1 供应商 应为 中华人民共和国境内 法律上和财务上独立的法人或依法登记注册的其他组织，合法运作并 独立于采购人和采购代理机构。 供应商应具有良好的银行资信和商业信誉。法人下属不具备法人资格的分支机 构参与响应的，应提供所属法人针对本项目或覆盖本项目的经营事项的有效授权。 2.1.2 供应商 的法定代表人或负责人为同一人或者存在控股、管理关系的不同 供应商 ，不得参加同一标包响应或 者未划分标包的同一询比项目响应。 ${ 2.1.3 } ${ 2.1.3 } 2.1.4 本次询比 不接受 联合体响应。 ${如 供应商 为联合体，应满足下列要求： （1） 联合体各方必须按询比文件提供的格式签订联合体协议书，明确联合体牵头人和各方的权利义务； （2）由同一 专业的单位组成的联合体，按照资质等级较低的单位确定资质等级； （3）联合体各方不得再以自己名义单独或 加入其他联合体在同一标包或者未划分标包的同一询比项目中响应。 ${ （4） 。} } 2.1.5 本次询比 不接受代理商响应。 ${ （1）产品制造商注册地在中华人民共和国境外（与中华人民共和国有正常贸易与往来的国家或地区）及香港、 澳门、台湾地区且必须使用代理商响应和签订销售合同的；（2）产品制造商为注册地在中华人民共和国境内的 外资企业（包括香港、澳门、台湾地区资本）或者由外国投资者（包括香港、澳门、台湾地区）享有绝对控制权 （最大或最多表决权）的企业且必须使用代理商响应和签订销售合同的。代理商响应的，应满足下列要求 ： } ${ （1） ${ （2） 供应商与产品制造商 的代理合作关系迄今为止应已持续 0 年（含）以上。 } ${ （3） } } ${ 2.1.6 与供应商有产品代工制造关系的制造商不得参加同一标包响应或者未划分标包的同一询比项目响 应。 } 2.1.7 供应商须提供2022年1月1日至本项目发布公告之日的同类项目（通信管道施工类）证明材料， 合同累计金额不低于3万元（含税） 2.2供应商不得存在下列情形之一 （1） 为采购人不具有独立法人资格的附属机构（单位）； （2） 被依法暂停或取消 投标/ 响应资格的； （3） 被责令停产停业、暂扣或者吊销许可证、暂扣或者吊销执照； （4） 进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （5） 在最近三年内（自 2022年04月01日 起）被相关行业主管部门或司法机关认定有骗取 中标/成交 、严重 违约、重大工程质量或者安全问题的； 网 （6） 在最近五年内（自 2022年06月01日 起）被判处单位行贿罪，且行贿行为与采购活动相关的（以“中国 裁判文书网”的生效判决为准）； （7） 在最近五年内（自 2022年06月01日 起）被判处合同诈骗罪的（以“中国裁判文书网”的生效判决为 务 准）； （8） 被最高人民法院在“信用中国”网站（www.creditchina.gov.cn）或各级信用信息共享平台中列入失信被执 行人名单，已执行完毕或不再执行的除外； 商 （9） 为本询比项目提供过设计、编制技术规范和其他文件的咨询服务 ； （10） 为本工程项目的相关监理人，或者与本工程项目的相关监理人存在隶属关系或者其他利害关系； 道 （11） 为本询比项目的代建人 ； （12） 为本询比项目的采购代理机构 ； 管 （13） 与本询比项目的监理人或代建人或采购代理机构同为一个法定代表人 ； （14） 与本询比项目的监理人或代建人或采购代理机构存在控股或参股关系 ； （15） 被工商行政管理国机关在国家企业信用信息公示系统中列入严重违法失信企业名单的； （16） 中国电信在职员工违规担任供应商法定代表人并参与采购活动的； （17） 中国电信集团有限公司/中国电信股份有限公司中层及以上管理人员违反有关领导人员配偶、子女及其配 中 偶经商办企业行为管理规定，其配偶、子女及其配偶经商办企业参与采购活动的； （18） 中国电信领导人员离职或退休后三年内违反《国有企业领导人员廉洁从业若干规定》等相关规定任职、 投资入股的私营企业、外资企业和中介机构，参与其原任职单位采购活动的； ${ （19） } （19） 其他按照中国电信供应商不良行为处理结果及《中国电信供应商不良行为管理规则》的结 果执行规则，应对供应商及其响应产品在本项目中执行禁止采购处理措施的； （20） 法律法规、询比文件限定的其他情形。 ${ 供应商 是代理商的，本条所指的 供应商 也包括其所代理的制造商。 } ${ 联合体响应的，联合体成员均不得 存在上述任一情形。 } 2.3产品资格要求 2.3.1 产品 应是来自中华人民共和国 ${或是与中华人民共和国有正常贸易与往来的国家或地区} 的 成熟稳定的 产品 。 ${ 2.3.2 产品 。 } ${ 2.3.3 产品 。 } ${ 2.3.4 。 } ${ 2.3.5 。 } 2.3.6 产品应符合中国电信相关技术要求， 并满足以下关键技术指标： （1） 序号 技术指标 具体要求 1 开挖深度 埋深≥0.8m（道路≥1.2m） 2 施工规格 本次修复选择开挖换管：开挖约80米，2孔110波纹管、2孔蜂窝管，新建两通信手控井 ${ 2.3.7 产品 业绩要求： 。 } ${ 2.3.8 。 } ${ 2.4 产品制造商资格要求 2.4.1 制造商应提供合法有效的登记 （或注册）证明文件，应具有良好的银行资信和商业信誉。 } ${ 2.4.2 } ${ 2.4.2 } ${ 2.4.3 } ${ 2.4.4 } ${ 2.4.5 } ${ 2.5现场考察 } ${ 2.6评价检测 } 2.7 法律法规规定的其他要求。 3.资格审查方法 本项目将进行资格后审，资格审查标准和内容见询比文件第三章“评审办法”，凡未通过资格后审的供应商， 其响应将被否决 。 网 4.询比文件的获取 4.1询比文件获取时间: 2026年08月25日 00时00分00秒 至 2026年09月01日 00时00分00秒 （北京时间，下同）。 4.2询比文件获取方式：登录“中国电信阳光采购网（https://caigou.c务hinatelecom.com.cn）”后，通过“招投标-采 购文件领取”模块或通过“电子采购入口”跳转中国电信电子采购系统，进入本项目进行询比文件登记申领， 未在系统注册的供应商须先进行注册，注册方法详见本公告“ 7 供应商注册”。 4.3询比文件费用： 本项目不收取文件费用。 ${每套售价商 0 元人民币，售后不退。支付要求： } 5.响应文件的递交 5.1响应文件递交截止时间（即响应截止时间）为： 2026年09月02日 00时00分00秒 道 5.2 电子响应文件的提交方式：登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投 标-我的项目”模块或通过“电子采购入口”跳转中国电信电子采购系统，选择本项目进行响应文件提交，供应 商应在响应文件提交截止时间之前通过电子采购系统完成加密电子响应文件的上传。供应商未在电子采购系统 进行询比文件申领登记或电子响应管文件未按照要求加密的，将无法通过电子采购系统提交电子响应文件 。 5.3 本项目将于响应文件提交截止同一时间通过中国电信电子采购系统开启响应文件， 采购人/采购代理机构 邀 请响应供应商的法定代表人或者其委托代理人准时参加 。 国 ${ 6.样品的递交 6.1样品递交的时间、地点：于 递交至 。 } 7. 供应商注册 7.1 中国电信阳光采购网注册 未注册过的潜在供应商，须通过中国电信阳光采购网（https://caigou.chinatelecom.com.cn）首页“立即注册”模 中 块完成注册后，方可申领本项目询比文件。 7.2 CA证书办理 参加询比响应的潜在供应商须提前办理CA证书，并确保CA证书在使用时有效。CA证书办理流程详见中国电信 阳光采购网首页“操作指引-CA办理”。 7.3 技术支撑联系方式 服务热线：4000111884 服务邮箱：zb_support@chinatelecom.cn（电子采购系统技术支撑） ctsc@chinatelecom.cn（CA证书办理技术支撑） 8. 发布公告的媒介 本询比公告在 中国电信阳光采购网（https://caigou.chinatelecom.com.cn） 、中国招标投标公共服务平台 （http://www.cebpubservice.com/） 上发布，其他媒介转载无效。 9. 联系及异议接收方式 9.1 联系方式 采 购 人: 中国电信股份有限公司石柱分公司 采购代理机构: 地 址： 重庆市石柱县城南路6号 地 址： 无 邮 编： 邮 编： 无 联 系 人： 马卫平 联 系 人： 无 电 话： 17365204567 电 话： 无 电子邮件： 17365204567@189.cn 电子邮件： 无 网 址： www.chinatelecom.com.cn或“/” 网 址： 无 网 开户银行： 无 账 号： 无 9.2 异议接收方式 务 登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投标-采购异议-提出异议”模块提出。 采购代理机构： 商 2026年08月25日 信息来源:https://www.chinapipe.net/project/d30道75344.html cqdingjiu 2026.08.21 10:06:56 管 国 中</t>
+          <t>喜德县冕山镇及两河口镇污水管道改造建设项目施工的招标文件预公示 内容详见附件信息 信息来源:https://www.chinapipe.net/project/d3078281.html cqdingjiu 2026.08.24 12:31:50 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4007,14 +3987,14 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>四川, 污水管道</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>重庆站站房CQZSG-4标项目蓝色PVC袖阀管(外径60mm)询价采购公告</t>
+          <t>甘眉工业园区污水管网建设项目施工招标文件(公告板)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4024,7 +4004,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4039,14 +4019,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>重庆站站房CQZSG-4标项目蓝色PVC袖阀管(外径60mm)询价采购公告</t>
+          <t>甘眉工业园区污水管网建设项目的具体内容见附件信息。</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4056,12 +4036,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>蓝色PVC袖阀管，外径60mm，壁厚4.5-5mm PVC管</t>
+          <t>管网</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>重庆站站房CQZSG-4标项目蓝色PVC袖阀管(外径60mm)询价采购公告 ZTEJWZ-JZ-2026-询027（一） 采购单位:重庆站站房CQZSG-4标段项目经理部 发布时间:2026-08-18 19:06 报价截止时间:2026-08-21 10:00 招标方联系人:刘健 网 招标方联系电话:13540650091 招标方邮箱: 务 监督方联系人:纪委 监督方联系电话:028-87653066 商 监督方邮箱: 保证金:0.0元 道 结算与发票信息: 结算方式：上月21日至本月的20日为一个结算周期，当月20日为本月的结算截止日期。结算时根据甲方检验合格 及双方共同签认的凭证计算当月实际收货数量。 管 支付条件：结算完成后，甲方在收到乙方开具的正式的增值税专用发票后第1个月支付该批物资结算金额的70%， 第12个月支付20%，剩余10%在第18-24月内按月均衡支付。 发票种类：增值税专用国发票 发票抬头：中铁二局集团有限公司 税号：9151中0100MA61RKR7X3 其他要求： 交货信息: 交货方式:点数验收 收货人:刘健 收货人联系方式:13540650091 其他说明事项: 流水号：询2026081800458 交 标的 规格 计量 标的编号 数量 技术标准及要求 货 送货地址 名称 型号 单位 期 蓝色PVC袖阀管，外 西南区-重庆市-市辖区-渝中区-重 袖阀 径60mm，壁 庆市菜园坝立交以西，龙家湾隧道 0950999183764 - 23188.0 米 管 厚4.5-5mm PVC管，承压 以东，菜袁路以北，王家坡以南的 不小于5MPa,节长4m 地块内，原重庆站。 报价网址:http://www.crecgec.com 信息来源:https://www.chinapipe.net/project/d3075317.html cqdingjiu 2026.08.21 10:06:56 网 务 商 道 管 国 中</t>
+          <t>甘眉工业园区污水管网建设项目施工招标文件(公告板) 内容详见附件信息 信息来源:https://www.chinapipe.net/project/d3078278.html cqdingjiu 2026.08.24 12:31:50 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4074,14 +4054,14 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>塑料管不计匹配分</t>
+          <t>重庆, 四川, 管材, 招标</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>涪陵区蔺市街道农村供水保障能力提升工程(一期)招标计划表</t>
+          <t>水电五局成眉机电安装项目铸铁井盖物资采购需求</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4091,7 +4071,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4106,53 +4086,49 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>涪陵区</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>新建、更换配水管网396.72km（dn20-dn160PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收及污泥浓缩处理系统。</t>
+          <t>详见附件。</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>合同金额：3611.91万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>dn20-dn160PE管、DN40-DN250抗菌耐磨涂塑钢管</t>
+          <t>铸铁井盖</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>涪陵区蔺市街道农村供水保障能力提升工程(一期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区蔺市街道农村供水保障能力提升工程（一期） 名称 招标 法人 或招 标人重庆水务环境控股集团渝东自来水有限公司 名称 网 （盖 章） 项目 批准 文件涪陵发改〔2026〕474号 及文 号 主要 务 建设新建、更换配水管网 396.72km（dn20-dnl60PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收及污泥浓缩处理系统。 内容 拟 招招标文 合同预 招标 交 序 标件计划 估金 备 项目招标内容 易 号 方发布时 额(万 注 名称 场 式间 元) 所 商 重 庆 涪陵 市 区蔺 招标 市街 涪 项目 道农 陵 公 区 村供 新建、更换配水管网 396.72km（dn20-dnl60PE管、DN40-DN250抗菌耐磨涂塑钢管）及配套附属设施;新建测控井108座；调蓄水箱1座;泵房设备更换2台；蔺市水厂、龙泉水厂配套废水回收 开 公 1 水保 2026-09 3611.91 及污泥浓缩处理系统。 招 共 障能 道 标 资 力提 源 升工程 交 （一 易 期） 中 心 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075278.html 管 cqdingjiu 2026.08.21 10:06:57 国 中</t>
+          <t>水电五局成眉机电安装项目铸铁井盖物资采购需求 详见附件。 信息来源:https://www.chinapipe.net/project/d3078222.html cqdingjiu 2026.08.24 12:31:50 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>配水管网：396.72km</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机</t>
+          <t>重庆, 四川, 管材招标</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>涪陵区李渡街道农村供水保障能力提升工程招标计划表</t>
+          <t>四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4162,7 +4138,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4177,53 +4153,57 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>武胜县</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>改造李渡街道15个村（社区）配水主支管道，更换配水主管网193.71千米（DN250-DN40抗菌耐磨涂塑钢管、dn40-dn25PE管）及配套附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治3座，新建测控井78座。</t>
+          <t>四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告 四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告 四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005已具备采购条件，现公开邀请供应商参加询比采购活动。</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>项目批准文件：涪陵发改[2026]469号</t>
+          <t>项目资金已落实。</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>DN250-DN40抗菌耐磨涂塑钢管、dn40-dn25PE管</t>
+          <t>聚乙烯热收缩套,聚乙烯胶粘带,防腐膏,聚丙烯胶粘带,聚乙烯补伤片</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>涪陵区李渡街道农村供水保障能力提升工程招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区李渡街道农村供水保障能力提升工程 名称 招标 法人 网 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 务 项目 批准 文件 涪陵发改〔2026〕469号 及文 号 商 主要 改造李渡街道 15个村（社区）配水主支管道，更换配水主管网 193.71 千米（DN250-DN40 抗菌耐磨涂塑钢管、dn40-dn25PE管）及配套 建设 附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治 3座，新建测控井78座。 内容 招 拟 标 道 招 招标文 合同预 交 序 项 标 件计划 估金 备 招标内容 易 号 目 方 发布时 额(万 注 场 名 式 间 元) 所 称 管 涪 陵 区 重 李 庆 渡 市 街 国 招标 涪 道 项目 陵 农 公 区 村 改造李渡街道 15个村（社区）配水主支管道，更换配水主管网 193.71 千米（DN250-DN40 抗菌耐磨涂 开 公 1 供 塑钢管、dn40-dn25PE管）及配套附属设施，泵站改造1座，新建集成泵站4座，蓄水池整治 3座，新建 2026-09 2372.74 招 共 水中测控井78座。 标 资 保 源 障 交 能 易 力 中 提 心 升 工 程 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075277.html cqdingjiu 2026.08.21 10:06:57</t>
+          <t>四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告 四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告 四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005已具备采购条件，现公 开邀请供应商参加询比采购活动。 1.采购项目简介 1.1采购项目名称：四川油建国家石油天然气大流量计量站成都分站高压检定能网力建设工程防腐材料JLZ-005。 1.2采购人：四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程。 1.3采购执行人：四川石油天然气建设工程有限责任公司采购中心（招标中心）。 务 1.4采购项目资金落实情况：已落实。 1.5采购项目概况：四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005。 商 1.6成交供应商数量及成交份额： 1家，成交份额： 道 第一名：；第二名：；第三名：…… 管 2.采购范围及相关要求（B） 2.1采购范围：${招标/采购范围}。 国 含税 单价 序 行项目 数 监造 物料编码 物资名称 规格型号 产品标准（技术要求） 单位 限 号 号 量 要求 价/ 中 元 辐射交联 不监 1 00010 A19040301000691 聚乙烯热 60.3×450 GB/T23257-2017 套 12 18 造 收缩套 辐射交联 不监 2 00020 A19040301000699 聚乙烯热 114×450 GB/T23257-2017 套 6 30 造 收缩套 辐射交联 不监 3 00030 A19040301000700 聚乙烯热 219.1×450 GB/T23257-2017 套 10 55 造 收缩套 辐射交联 不监 4 00040 A19040301000697 聚乙烯热 323.9×450 GB/T23257-2017 套 10 57 造 收缩套 辐射交联 不监 5 00050 A19040301000694 聚乙烯热 406.4×450 GB/T23257-2017 套 10 90 造 收缩套 辐射交联 不监 6 00060 A19040301000693 聚乙烯热 610×520 GB/T23257-2017 套 16 145 造 收缩套 厚胶型聚 宽50mm厚 不监 7 00070 A19040103000195 乙烯胶粘 度≥1.2mm，配套 SY/T0414-2017 米 800 2.2 造 带 底漆6L 粘贴体防 公 不监 8 00080 A19040405000001 SY/T7036-2016 41.5 53 腐膏 斤 造 粘贴体防 宽100mm厚 不监 9 00090 A19040404000001 SY/T7036-2016 米 400 11 腐带 度≥1.8mm 造 聚丙烯胶 不监 10 00100 A19040103000028 宽75mm×1.4mm SY/T7036-2016 米 800 4.5 粘带 网 造 聚乙烯补 不监 11 00110 A19040401000014 250×1.8mm GB/T23257-2017 kg 100 18 伤片 造 务 2.2交货期：下订单后（15 ）天到货。。 2.3交货地点：四川省广安市武胜县胜利镇柿花场村收货人：佘小兵18981930563。 2.4物资质量标准或主要技术性能指标：详见2.1采购范围商的产品标准（技术要求）。 2.5采购物资名称、规格型号、执行标准、单价限价以本表和分项报价单为准，行项目号、物料编码与系统物资 明细相对应。 道 3.供应商资格要求 3.1供应商应依法设立且具备承担本采购项目的资质条件、能力和信誉： 管 供应商资格要求1：供应商在中华人民共和国境内依法注册，具备合格有效的营业执照、税务登记证、组织机 构 代码 (执行“三证合一”改革的投标人，无需单独提供组织机构代码证和税务登记证，只需提供加载统一代码的 营业执照即可)； 供应商资格要求2：本国次采购不接受联合体。只接受制造商 供应商资格要求3：供应商在云梦泽系统中供应商状态必须正常（非临时供应商），同时具有相应产品的准入产 品品类编码状态正常，本次采购准入产品品类编码 为：A19040301，A19040103，A19040405，A19040404，A19040401。 中 备注：“有效的”是指云梦泽系统资源库中供应商状态及产品（以品类编码为准）状态均为“正常”，状态以 评审当日云梦泽系统供应商状态及产品状态为准。潜在投标人应自行确认云梦泽资源库中状态是否符合采购文 件要求。 供应商资格要求4：供应商未被“国家企业信用信息公示系统”网站（www.gsxt.gov.cn）列入严重违法失信 企 业 名 单 ， 授 权 代 表 人 、 法 定 代 表 人 或 者 负 责 人 未 在 中 国 执 行 信 息 公 开 网 （http://zxgk.court.gov.cn/） 中被列入失信被执行人名单。（提供网站查询截图） 供应商资格要求5：供应商被中国石油天然气集团（股份）有限公司、中国石油工程建设有限公司、四川油建公 司列为“三商”黑名单，“三商”预警清单，取消准入资格、禁止准入、暂停交易资格、 年度评价不合格的 （复查合格除外），采购无效。 供应商资格要求6：在《中国石油天然气集团有限公司采购产品质量监督抽查情况通报》中响应产品被处罚的响 应无效（复查合格的除外）。 供应商资格要求7：根据《中国石油天然气集团有限公司投标人失信行为管理办法》的规定，供应商开标当日未 被中国石油招标投标网暂停或取消投标资格。供应商失信分以开标当日中国石油招标投标网查询的失信行为信 息为准。 供应商资格要求8：供应商须提供书面承诺没有被处于被责令停业,暂扣或者吊销认可证、暂扣或者吊销执照，财 产被接管、冻结、破产、资不抵债等状态； 供应商资格要求9：供应商须提供书面承诺，说明2023年1月1日至投标截止日没有发生因未履行合同、延期交货、 产品质量问题原因导致的合同终止或被起诉产生法律纠纷。 4.采购文件的获取 4.1本项目在云梦泽智慧平台发布，凡有意参加投标的潜在供应商，请于北京时间公告发布时间至2026-08-25 14:00:00严格按照下列步骤完成采购文件购买： 登录云梦泽智慧平台(https://www.ymzec.com/bid/web-outportal/)参与并购买电子采购文件。（具体操作详见：云 梦泽智慧平台&gt;通知公告&gt;操作说明中的“投标人用户手册”的相关章节，平台的操作问题咨询电话：956100 转6）。 网 4.2采购文件每套售价为0.00元人民币，请有意参加投标的潜在供应商确认自身资格条件是否满足要求，售后不退， 应自负其责。 务 4.3采购文件下载：潜在供应商在4.1规定的时间内完成参与并购买电子采购文件操作后，即可在“我的项目”中 下载采购文件。 4.4本次招标项目为全流程网上操作。 商 5.响应文件的递交 5.1 响应文件递交的截止时间（投标截止时间及开标时间，下同）：2026-08-28 10:00（北京时间），投标人应在 截止时间前通过云梦泽智慧平台（https://www道.ymzec.com/bid/web-outportal/）递交电子响应文件，具体操作步骤 见下： ① 在递交电子响应文件前，请确保完成响应文件的制作生成（具体可参考操作手册中制作投标文件的相关章 节）。 管 ② 登录云梦泽智慧平台，进入到投标业务系统的【投标人端】。通过点击顶部导航栏的 “招标投标” 按钮，进入 【招标投标系统首页】，再点击 “进入系统” 按钮，进入【投标端业务系统】 ③ 找到递交入口，在投国标人端的相关项目管理 - 投标 - 进入项目 - 网上投标路径下，找到响应文件递交的操作界 面。点击 “递交” 按钮，上传已制作好的响应文件，并确认签名。 特别注意：为避免受网速及网站技术支持时间的影响，建议于投标截止时间24小时之前完成网上电子响应文件的 递交。 中 5.2响应文件递交截止时间未成功递交的电子响应文件将不被系统接受，视为主动撤回响应文件。 5.3开标地点（网上开标）：云梦泽智慧平台(https://www.ymzec.com/bid/web-outportal/)（所有供应商可登录云梦 泽智慧平台在线参加开标仪式）。 5.4如需递交投标保证金，潜在供应商应在投标截止时间前递交投标保证金（CNY）：。投标保证金有效期与投 标有效期一致，投标保证金采用电汇形式递交，具体递交步骤见下： ①企业钱包充值：潜在投标人应先使用基本存款账户绑定企业钱包，且使用该基本存款账户向企业钱包充值， 使用其他账户进行充值，资金将自动原路退回。 企业钱包充值账户信息： 账户名称：中国石油电子招投标保证金 开户行名称：昆仑银行股份有限公司大庆分行 行号：313265010019 银行账号：26902197555010000027 ②投标保证金递交：选择意向参与的招标项目，并在“递交保证金”环节中选择“钱包支付”方式完成递交。 递交前，请务必检查企业钱包可用余额是否充足。如余额不足，请按①及时充值。 潜在投标人对采购文件有疑问请咨询招标机构联系人；对平台操作有疑问请咨询技术支持团队：956100转6，请 在工作时间咨询。 招标公告/采购公告中未尽事宜或与采购文件不符之处，以采购文件为准。 6.响应文件开启时间和地点 响应文件开启在响应文件递交截止时间的同一时间进行，地点为云梦泽平台在线开启，邀请所有供应商的法定 代表人或其委托代理人登录云梦泽平台招标投标专区参加在线开启会议，供应商网未参加开启会议的，视为默认 开启结果。采取视频会议远程开启的，以采购人通知为准。 7.发布公告的媒介 务 本采购公告在云梦泽招标投标专区上发布。 8.联系方式 采购人（或采购执行人）：四川油建国家石油天然气大流商量计量站成都分站高压检定能力建设工程 地址：成都双流区黄甲镇西航港大道中四段2929号工程建设公司四川油建公司生产科研基地采购中心（招标中心） 联 系人：陈羽璨 道 电话：13658018051 电子邮件：chenyc827_sc@cnpc.com.cn 管 2026年8月21日 信息来源:https://www.c国hinapipe.net/project/d3078197.html cqdingjiu 2026.08.24 12:31:51 中</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>配水主管网：193.71千米；泵站：1座；集成泵站：4座</t>
+          <t>[object Object],[object Object],[object Object],[object Object],[object Object],[object Object],[object Object],[object Object],[object Object],[object Object],[object Object]</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 改造, 配水主支管道, 更换配水主管网, 抗菌耐磨涂塑钢管, 泵站改造, 集成泵站, 蓄水池整治, 测控井</t>
+          <t>重庆, 四川, 管材, 招标, 商机</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>涪陵区珍溪镇农村供水保障能力提升工程(二期)招标计划表</t>
+          <t>南江县城污水处理厂水污染治理设施提标改造项目详细勘察服务磋商公告</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4248,53 +4228,57 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>巴中市</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>南江县</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>本项目对珍溪镇23个村(社区)安装配水管网660km及配套附属设施，其中：1.De160~De40的PE管主要建设有232km；2.连接各村社的De32~De20的PE管有381km；3.219~32的衬塑钢管47km。(二)购置安装泵站14座(一用一备共计28台水泵)，其中新建泵商站10座、更换泵站4座及配套电力设施;新建不锈钢水箱2座等。(三)购置安装(0~25kg)减压阀61个;排污阀(25kg）3个。</t>
+          <t>详细勘察服务</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>合同预估金额为2182.77万元</t>
+          <t>预算资金：¥389940.00元</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>PE管、衬塑钢管、水泵、不锈钢水箱、减压阀、排污阀</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>涪陵区珍溪镇农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目名称 涪陵区珍溪镇农村供水保障能力提升工程（二期） 招标法人 或招标人 重庆水务环境控股集团渝东自来水有限公司 网 名称（盖 章） 项目批准 文件及文 涪陵发改〔2026〕477号 务 号 (一)本项目对珍溪镇23个村(社区)安装配水管网660km及配套附属设施，其中：1.De160~De40的PE管 主要建设 有232km；2.连接各村社的De32~De20的PE管有381km；3.219~32的衬塑钢管47km。(二)购置安装泵 内容 站14座(一用一备共计28台水泵)，其中新建泵商站10座、更换泵站4座及配套电力设施;新建不锈钢水 箱2座等。(三)购置安装(0~25kg)减压阀61个;排污阀(25kg）3个。 招标项目名 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 称 式 划发布时间 场所 (万元) 道 (一)本项目对珍溪镇23个 村(社区)安装配水管网660km 及配套附属设施，其 中：1.De160~De40的PE管 管 有232km；2.连接各村社 涪陵区珍溪 重庆市 的De32~De20的PE管有381km； 招标项目 镇农村供水 涪陵区 3.219~32的衬塑钢 公开招 1 保障能力提 2026-09 公共资 2182.77 管47km。(二)购置安装泵 标 升工国程（二 源交易 站14座(一用一备共计28台水 期） 中心 泵)，其中新建泵站10座、更 换泵站4座及配套电力设施; 新建不锈钢水箱2座等。(三) 中 购置安装(0~25kg)减压阀61 个;排污阀(25kg）3个。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075275.html cqdingjiu 2026.08.21 10:06:57</t>
+          <t>南江县城污水处理厂水污染治理设施提标改造项目详细勘察服务磋商公告 四川文欣工程项目管理有限公司（采购代理机构）受南江县雾源污水处理有限公司（采购人）的委托，拟对南 江县城污水处理厂水污染治理设施提标改造项目详细勘察服务采用竞争性磋商方式进行采购，特邀请符合本次 采购要求的供应商参加本项目的磋商。 一、采购项目基本情况 1.项目编号：SWUEECG202642431 网 2.项目名称：南江县城污水处理厂水污染治理设施提标改造项目详细勘察服务 3.采购人：南江县雾源污水处理有限公司。 务 4.采购代理机构：四川文欣工程项目管理有限公司。 二、资金情况 预算资金：¥389940.00元（大写：叁拾捌万玖仟玖佰肆拾商元整） 三、采购项目简介： 详细要求详见磋商文件第五章。 道 四、供应商邀请方式 通过在西南联合产权交易所阳光采购平台（https://swueecg.com/#/index）发布公告的方式，邀请符合相应资格条 管 件的供应商参与采购活动。 五、供应商参加本次采购活动应具备下列条件 1.具有独立承担民事责国任的能力； 2.具有良好的商业信誉和健全的财务会计制度； 3.具有履行合同所必需的设备和专业技术能力； 中 4.具有依法缴纳税收和社会保障资金的良好记录； 5.参加本次采购活动前三年内，在经营活动中没有重大违法记录； 6.法律、行政法规规定的其他条件； 7.落实采购政策需满足的资格要求： 本项目属于专门面向中小企业采购的项目,供应商应为中小微企业（监狱企业、残疾人福利性单位视同小微企 业）。 8.采购项目的特殊要求： ①本项目专门面向中小企业采购,供应商应为中小微企业（监狱企业、残疾人福利性单位视同小微企业）； ②供应商须具有建设行政主管部门颁发的工程勘察（岩土工程（勘察））乙级及以上资质； 六、禁止参加本次采购活动的供应商 1.根据《关于在政府采购活动中查询及使用信用记录有关问题的通知》（财库〔2016〕125号）的要求，四川文欣 工程项目管理有限公司将通过“信用中国”网站（www.creditchina.gov.cn）、“中国政府采购网”网站 （www.ccgp.gov.cn）等渠道查询供应商在采购公告发布之日前的信用记录并保存信用记录结果网页截图，拒绝列 入失信被执行人名单、重大税收违法案件当事人名单、政府采购严重违法失信行为记录名单中的供应商报名参 加本项目的采购活动（以联合体形式参加本项目采购活动，联合体成员存在不良信用记录的，视同联合体存在 不良信用记录）。 2.为采购项目提供整体设计、规范编制或者项目管理、监理、检测等服务的供应商，不得参加本采购项目。供应 商为采购人、采购代理机构在确定采购需求、编制磋商文件过程中提供咨询论证，其提供的咨询论证意见成为 磋商文件中规定的供应商资格条件、技术服务商务要求、评审因素和标准、采购合同等实质性内容条款的，视 同为采购项目提供规范编制。 七、磋商文件获取方式、时间、地点： 网 磋商文件自2026年08月21日9:00至2026年08月27日18：00（北京时间，法定节假日除外）在西南联合产权交易所电 子招采平台网站https://www.swueecg.com，按照网上操作流程（资料下载-供应商操作手册）获取。 本项目磋商文件费用¥ 200.00元/份，供应商须通过本单位对公银行账户转账方式交纳磋商文件费用（不接收个 务 人转账），磋商文件售后不退，参加采购活动的资格不能转让。转账前请核实阳光采购平台转账页面的“项目 信息”，认真阅读“注意事项”并按照“支付信息”进行转账，以磋商文件费用到达指定账户为准，在文件获 取截止时间内未到账的不能获取磋商文件，视为报名不成功。 八、递交响应文件截止时间：2026年09月01日9:30（北京商时间）。 九、递交响应文件地点：响应文件必须在递交响应文件截止时间前送达磋商地点（磋商地点：南江县红塔大 道167号红塔锦城3楼）。逾期送达、密封和标注错误的响应文件，四川文欣工程项目管理有限公司恕不接收。本 次采购不接收邮寄的响应文件，但因邮寄导致道投标截止时间以后送达的响应文件，响应文件不予接收。 十、磋商地点：南江县红塔大道167号红塔锦城3楼。 十一、联系方式 管 采 购 人：南江县雾源污水处理有限公司 通讯地址：四川省巴中市南江县集州街道文光社区中院社 国 邮 编：635600 联 系 人：吴先生 中 联系电话：0827-8177739 采购代理机构：四川文欣工程项目管理有限公司 通讯地址：四川省巴中市巴州区体育馆对面龙北街122号三楼 邮 编：635600 联 系 人：秦女士 联系电话：0827-5267676 信息来源:https://www.chinapipe.net/project/d3078163.html cqdingjiu 2026.08.24 12:31:51</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>配水管网：660km；的衬塑钢管：47km；泵站：4座；泵站：10座；换泵站：4座</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>涪陵区, 珍溪镇, 农村供水, 提升工程, 衬塑钢管, 水泵, 不锈钢水箱, 减压阀, 排污阀</t>
+          <t>管材招标, 重庆, 四川, 近三天</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>涪陵区蔺市街道农村供水保障能力提升工程(二期)招标计划表</t>
+          <t>绵阳市中心医院蒸汽管道改造(第二次)采购公告</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4304,7 +4288,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>房建</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4319,38 +4303,42 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>绵阳市</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>绵阳市</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长105.307km（dn20-dn40PE管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建1座改造3座；新建测控井52座。</t>
+          <t>蒸汽管道改造</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>合同预估金额：2652.89万元</t>
+          <t>最高限价：26.7万元</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>净水设备、PE管、抗菌耐磨涂塑钢管</t>
+          <t>蒸汽管道</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>涪陵区蔺市街道农村供水保障能力提升工程(二期)招标计划表 重庆市工程建设项目招标计划表 项目 涪陵区蔺市街道农村供水保障能力提升工程（二期） 名称 招标 法人 网 或招 标人 重庆水务环境控股集团渝东自来水有限公司 名称 （盖 章） 务 项目 批准 文件 涪陵发改〔2026〕475号 及文 号 商 主要 八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长 105.307km（dn20-dn40PE 建设 管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建 1座改造3座；新建测控井 52座。 内容 拟 招 招标文 合同预 招标 交 序 道 标 件计划 估金 备 项目 招标内容 易 号 方 发布时 额(万 注 名称 场 式 间 元) 所 重 庆 涪陵 管 市 区蔺 涪 招标 市街 陵 项目 道农 公 区 村供 八方碑水厂扩容购置3000m/d净水设备1套；堡子水厂购置3000m/d净水设备1套；新建、更换管网总长 开 公 1 水保 105.307km（dn20-dn40PE 管、DN32-DN300抗菌耐磨涂塑钢管）及配套附属设施；泵站新建 1座改造3座； 2026-09 2652.89 国 招 共 障能 新建测控井 52座。 标 资 力提 源 升工程 交 （二 易 期） 中 中 心 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3075274.html cqdingjiu 2026.08.21 10:06:57</t>
+          <t>绵阳市中心医院蒸汽管道改造(第二次)采购公告 因工作需要，绵阳市中心医院拟对蒸汽管道改造进行竞争性谈判采购，现面向社会公示，诚邀符合条件要求的 供应商参加。 一、项目编号：MYCH竞谈（2026）013号 二、项目名称：蒸汽管道改造 三、最高限价：26.7万元 网 四、采购内容：蒸汽管道改造 五、参加投标的供应商应具备的条件： 务 1. 具有独立承担民事责任的能力。 2. 具有良好的商业信誉和健全的财务会计制度。 商 3. 具有履行合同所必须的设备和专业技术能力。 4. 有依法缴纳税收和社会保障资金的良好记录。 道 5. 供应商参加本次政府采购活动前三年内，在经营活动中没有重大违法记录。 6. 本项目参加政府采购活动的投标人、法定代表人(非法人负责人、自然人本人)在前3年内不得具有行贿犯罪记 录。 管 7. 法律、行政法规规定的其他条件。 8. 特种设备生产许可证--工业管道GC2。 国 9. 安全生产许可证。 六、提交报名文件方式： 中 1、供应商按照附件要求提交响应文件即视为报名成功。（要求详见附件） 2、供应商提交响应文件资料（盖鲜章）要求按顺序扫描成一个PDF文件发送到2242490135@qq.com邮箱，邮件 名为：蒸汽管道改造+公司名称。邮件正文内容为：公司名称、业务员姓名、业务员联系电话，不按照要求发送 邮件将被拒绝报名。 3、提交响应文件截止时间：2026年8月25日17：00 七、开标时间和地点： 1、开标时间和地点电话另行通知。 八、联系人及电话： 项目咨询：唐老师 0816-2229106 报名咨询：刘老师 18081208357 监督电话： 0816-2237353 竞争性谈判文件-蒸汽管道改造.docx 绵阳市中心医院采购科 2026年8月20日 信息来源:https://www.chinapipe.net/project/d3078145.html 网 cqdingjiu 2026.08.24 12:31:51 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>管网：105.307km；泵站：1座</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -4358,14 +4346,14 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>蒸汽管道改造, 四川</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目项目公告</t>
+          <t>中国电子系统工程第三建设有限公司,中微半导体设备(四川)有限公司工业用房及配套设施项目,UPVC管道,谈判采购项目公告</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4375,7 +4363,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4390,29 +4378,37 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>本项目涉及管道为鱼洞污水处理厂专件厂线管网，管道编号为WD4-WD8+1，该管道为自流管道，位于鱼轻桥至河嘴倒虹井段，主要用于收集输送鱼洞大江商至华熙片区的生活污水。该段管道管径为DN600，管道为混凝土管，主要采用架空明敷的方式沿河敷设。该管道自建成投运以来已有20余年，管道及污水井老化严重现象十分明显，容易出现破损从而造成污水溢流，造成环保风险。为规避环保风险且保障该段管道以及鱼洞污水厂的正常收水及运行，需对该段管道进行改造。</t>
+          <t>中微半导体设备成都研发及生产基地暨西南总部项目洁净室及一般机电包项目【UPVC】将开启线上采购。</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>项目资金来自企业自筹</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>DN600混凝土管，检查井</t>
+          <t>UPVC管道</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目项目公告 重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目（项目名称）比选公告 1.比选条件 本比选项目重庆市排水有限公司鱼洞污水处理厂2026年专件厂线管网改造项目（项目名称），比选人为重庆市排 网 水有限公司，比选项目资金来自企业自筹（资金来源），项目已具备比选条件。中标后合同与重庆市豪洋水务 建设管理有限公司签订。现对本项目进行公开比选，诚邀有兴趣的潜在投标人参与投标。 2.项目概况与比选范围 务 2.1 建设地点：重庆市巴南区 2.2 项目概况：本项目涉及管道为鱼洞污水处理厂专件厂线管网，管道编号为WD4-WD8+1,该管道为自流管道， 位于鱼轻桥至河嘴倒虹井段，主要用于收集输送鱼洞大江商至华熙片区的生活污水。该段管道管径为DN600，管道 为混凝土管，主要采用架空明敷的方式沿河敷设。该管道自建成投运以来已有20余年，管道及污水井老化严重现 象十分明显，容易出现破损从而造成污水溢流，造成环保风险。为规避环保风险且保障该段管道以及鱼洞污水 厂的正常收水及运行，需对该段管道进行改造。 道 2.3 比选范围：拆除现状管道为DN600混凝土管，同时需拆除并新建9座检查井。 2.4 工期要求：30日历天，以甲方通知进场时间为准。 管 2.5缺陷责任期要求：24个月 3.投标人资格要求 国 3.1 本次比选要求投标人须具备以下条件： 3.1.1 本次比选要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰级 及以上资质。 中 3.1.2 投标人还应在人员、设备、资金等方面具有相应的施工能力，详见比选文件第二章投标人须知前附表第1.4.1 项内容。 3.2 本次比选接受不联合体投标。 4.比选文件的获取 4.1 投标人于2026年8月 18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子 版，以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都 视为投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的 一切后果由投标人自行负责。各投标单位应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行供应商注册，填写相关信息，审批过后成为 平台供应商。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价、递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，将被否决投标。 4.4 比选文件每份售价800元，售后不退。投标单位在递交纸质投标文件时扫描支付，否则比选人拒绝接收其投标 文件。 5.投标文件的递交 5.1 电子投标文件递交时间：2026年8月24日14时30分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年8月24日14时00分至14时30分（北京时间），地点：重庆水务招标采购中心 （重庆市两江新区嘉华路36号重庆水务大厦5楼）。 5.3 投标截止时间：2026年 8月24日14时30分（北京时间）。 网 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 务 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 商 比 选 人：重庆市排水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝中区长江滨江路126号 地 址：重庆市两江新区嘉华路36号重庆水务大厦 道 联 系 人： 黄老师 联 系 人： 黄晓华 电 话： 023-67767416 电 话： 18523396416 管 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3075272.html 国 cqdingjiu 2026.08.21 10:06:57 中</t>
+          <t>中国电子系统工程第三建设有限公司，中微半导体设备(四川)有限公司工业用房及配套设施项目，UPVC管道， 谈判采购项目公告 中国电子系统工程第三建设有限公司,中微半导体设备(四川)有限公司工业用房及配套设施项目，UPVC管道，谈 判采购项目公告 中微半导体设备成都研发及生产基地暨西南总部项目洁净室及一般机电包项目-【UPVC】-谈判采购公告 中国电子系统工程第三建设有限公司-中微半导体设备成都研发及生产基地暨西南总部项目洁净室及一般机电包 项目【UPVC】将开启线上采购，请在公告要求时间内参与报名，如有问题，请联系采购工程师。 网 报价须知: 1、项目名称：中微半导体设备成都研发及生产基地暨西南总部项目洁净室及一般机电包项目 务 2、项目地址：成都市德富大道以东，康强三路以南，康强二路以北，安泰七路以西 3、报价需包含：13.00%增值税及运费 4、报名截止时间：2026-08-21 19:00:00 商 5、报名通过后可参与报价，报价资料需提供可编辑版及PDF盖章版各1份 （1）报价单（2）选型技术附件及技术偏离表道（2）相关资质授权文件 6、报价公司名称需与合同签订单位名称一致 7、采购工程师：郭帅，联系方式:19975802654,邮箱:guoshuai@cetjd.com 管 8、报价截至时间：2026-08-23 20:00:00 国 信息来源:https://www.chinapipe.net/project/d3078054.html 中 cqdingjiu 2026.08.24 12:31:52</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4421,18 +4417,18 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>重庆, 排水公司, 污水处理厂, 管网改造, DN600混凝土管, 检查井</t>
+          <t>塑料管不计匹配分</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>重庆市潼南城区老旧供水管网改造工程招标计划</t>
+          <t>水电五局卡拉水电站地厂项目经理部镀锌钢管等物资采购需求</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4442,7 +4438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4457,53 +4453,49 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>潼南区</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>改建潼南城区输水主管网约39.63km及配套相应阀门阀件等，对城区供水管网上商老旧阀门阀件、设施设备进行更换，合理增设部分计量及压力监控、水质监控等。</t>
+          <t>水电五局卡拉水电站地厂项目经理部镀锌钢管等物资采购需求</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>合同预估金额：918.00万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>城区配套阀门阀件改造工程</t>
+          <t>镀锌钢管等物资</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>重庆市潼南城区老旧供水管网改造工程招标计划 重庆市工程建设项目招标计划表 项目名称 重庆市潼南城区老旧供水管网改造工程 招标法人或招 标人名称（盖 重庆市潼南自来水有限公司 网 章） 项目批准文件 及文号 务 主要建设内容 改建潼南城区输水主管网约39.63km及配套相应阀门阀件等 招标方 招标文件计 拟交易场 合同预估 序号 招标项目名称 招标内容 备注 式 划发布时间 所 金额(万元) 对城区供水管网上商 重庆市潼南城 老旧阀门阀件、设 区老旧供水管 重庆市潼 招标项目 施设备进行更换， 网改造工程 公开招 南区公共 1 保障供水管网稳定 2026-09 918.00 （城区配套阀 标 资源交易 运行合道理增设部分 门阀件改造工 中心 计量及压力监控、 程） 水质监控等。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 管 信息来源:https://www.chinapipe.net/project/d3075266.html cqdingjiu 2026.08.21 10:06:58 国 中</t>
+          <t>水电五局卡拉水电站地厂项目经理部镀锌钢管等物资采购需求 详见附件。 信息来源:https://www.chinapipe.net/project/d3078004.html cqdingjiu 2026.08.24 12:31:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>输水主管网：39.63km</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>重庆, 四川, 近三天, 管材招标商机</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>关于为【重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购】公开选取【工程设计】机构的公告</t>
+          <t>绵阳市游仙区(城区)老旧燃气管道等更新改造工程项目(一期)施工(重发公告第0次)第1次答疑文件</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4513,7 +4505,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4528,33 +4520,37 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>绵阳市</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>开州区</t>
+          <t>游仙区</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>该项目涉及硬化生产便道、建设防旱池和蓄水池、建造育苗大棚和小棚、安装水源处理和水肥一体化设施、新建设备管理房以及完善蔬菜基地配套设施等内容。</t>
+          <t>绵阳市游仙区(城区)老旧燃气管道等更新改造工程项目(一期)施工</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>工程总投资335万元。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>工程设计服务</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>关于为【重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购】公开选取【工程设计】 机构的公告 我单位在重庆市网上中介超市公开选取工程设计中介服务机构，现将相关事项公告如下： 该项目为直接选取项目，由采购人从报名的中介服务机构中直接选定一家中介服务机构进行项目服务。 项目 重庆市开州区2026年河堰镇清泉社区高山蔬菜基地配套设施项目设计服务采购 名称 网 采购 重庆市开州区河堰镇人民政府 人 投资 审批 否 务 项目 是否 破产 商 业务 否 服务 项目 采购 道 所需 中介 其他 服务 事项 管 所需 服务 工程设计 类型 项目实施地点为国河堰镇清泉社区，项目建设内容为：硬化2米宽生产便道5.5千米，100方防旱池1口，50方 服务 蓄水池1口，标准自动化育苗大棚1个，蔬菜小棚20个，水源处理设施1套，水肥一体化配套设施1套，新 内容 建50平方米设备管理房，完善蔬菜基地配套设施等。工程总投资335万元。选取此项目设计单位（含预算 编制服务）。 中 中介 机构 资质（资格）要求 要求 资质 （资 1、报名单位提供有效的营业执照，资质证书（资质丙级或丙级以上），具备从事项目设计服务工作； 2、 格） 具有独立承担民事责任的能力； 3、具有良好的商业信誉和健全的财务会计制度； 4、具有履行合同所必 要求 需的专业技术能力； 5、有依法缴纳税收和社会保障资金的良好记录。 说明 其他 要求 无 说明 服务 时限 无要求，按照合同双方自行约定 说明 服务 3.1%费率 金额 金额 按文件要求执行 说明 选取 直接选取 方式 需规 避机 构 规避 原因 选取 2026-08-20 16:00:00 （选取时间到达后不接受报名，建议中介机构至少在选取开始半小时前完成报名。） 时间 采购 人业 网 务咨 重庆市开州区河堰镇人民政府（18716685679） 询电 话 采购 务 需求 26清泉社区项目设计服务采购说明.pdf 书下 载 商 2026-08-18 信息来源:https://www.chinapipe.net/project/d3075198.html 道 cqdingjiu 2026.08.21 10:06:58 管 国 中</t>
+          <t>绵阳市游仙区(城区)老旧燃气管道等更新改造工程项目(一期)施工(重发公告第0次)第1次答疑文件 “绵阳市游仙区（城区）老旧燃气管道等更新改造工程项目(一期）施工”补遗01号 致各潜在投标人： 1.现对本项目招标工程量清单和招标控制价文件调整后重新上传，请各投标人以重新上传的招标工程量清 单和招标控制价为准。 2.本项目开标时间、投标文件递交截止时间及保证金缴纳截止时间更正为2026网年09月08日09时10分。 3.招标文件其他内容不变，请各投标人请自行下载查阅。由此带来的不便，敬请谅解！ 务 招标人：绵阳市游仙区市政工程建设维护中心 商 招标代理机构：四川鑫宇工程项目管理有限公司 2026年08月21日 道 信息来源:https://www.chinapipe.net/project/d3077993.html cqdingjiu 2026.08.24 12:31:52 管 国 中</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4563,18 +4559,18 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>绵阳市游仙区, 老旧燃气管道, 更新改造, 项目, 施工</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目招标公告</t>
+          <t>会禄高速公路机电项目玻璃钢管、玻璃钢管箱采购公开招标公告</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4584,7 +4580,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>房建</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4599,33 +4595,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>开州区</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1.建设果园水肥一体化系统1套，对示范柑桔果园建设水肥一体智能化系统;2.果园运输线4000米(含轨道主机、叉车、周转箱、三轮车等配套设施设备);3.建设排灌站一处;4.建设1.8米宽生产便道2000米，务周转场300平方米;5.配备载重无人机1台、小型挖机1台、电子控制屏1个;6.建设智慧平台与监测系统软硬件系统等。</t>
+          <t>详见附件。</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>项目总投资金额：500万元，本次招标项目合同估算金额：446.278921万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>柑橘基地改造提升项目</t>
+          <t>玻璃钢管、玻璃钢管箱</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目招标公告 1.招标条件 本招标项目重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目已由重庆市开州区发展和改革委员会以开州 发改审〔2026〕357号批准建设，项目业主为重庆市开州区长沙镇人民政府，建设资金来自开州区2026年中央和 市级提前批财政衔接推进乡村振兴补助资金，项目出资比例为 100% ，招标人为重庆市开州区长沙镇人民 政府。项目已具备招标条件，现对该项目的施工进行公开招标，评标办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：开州区长沙镇桔香村 2.2 项目概况与建设规模：1.建设果园水肥一体化系统1套，对示范柑桔果园建设水肥一体智能化系统;2.果园运输 线4000米(含轨道主机、叉车、周转箱、三轮车等配套设施设备);3.建设排灌站一处;4.建设1.8米宽生产便道2000米， 务 周转场300平方米;5.配备载重无人机1台、小型挖机1台、电子控制屏1个;6.建设智慧平台与监测系统软硬件系统等。 2.3 本项目工程总投资金额： 500万元 本次招标项目合同估算金额： 446.278921万元 商 2.4 招标范围：招标人发布的由重庆中煜华资工程技术有限公司设计的《重庆市开州区2026年长沙镇桔香村柑橘 基地改造提升项目》施工图及图纸说明、招标文件(含补遗)及工程量清单、答疑资料、澄清资料范围内所涉及的 工作内容，具体以招标人发布的工程量清单及道施工图为准。 2.5 工期要求： 150日历天 缺陷责任期要求： 12个月 管 2.6 标段划分（如有）： / 2.7 其他： / 国 3.政府采购工程 3.1 是否属于政府采购工程：是 中 3.2 是否专门面向中小企业预留：否，按照《政府采购促进中小企业发展管理办法》第六条第(三)“按照本办法 规定预留采购份额 无法确保充分供应、充分竞争，或者存在可能影响政府采购目标实现的情形”的规定，故本 项目不专门面向中小企业预留。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包叁级及以 上资质或市政公用工程施工总承包叁级及以上资质或水利水电工程施工总承包叁级及以上资质； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在 重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）下载招 标文件、工程量清单、电子图纸等资料。参与投标的投标人需在 重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）完成市 场主体信息登记以及CA数字证书办理，办理方式请参见 重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、 重庆市公共资源交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）导航栏“主体信息”页面中“市场主 体信息登记”、“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完 成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区） （https://www.cqggzy.com/kaizhouweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告 发布至2026-08-21 17:00:00前。 5.3招标人应于2026-08-25 23:59:59前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源 交易网（开州区）（https://www.cqggzy.com/kaizhouweb/）发布澄清。 6.投标文件递交的内容 网 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-21 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 务 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn ）、重庆市公共资源交易网（开州区） （https://www.cqggzy.com/kaizhouweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交 易监督网上发布。] 商 8.联系方式 招 标 人: 重庆市开州区长沙镇人民政府 代理机构: 重庆毅仁建设项目管理有限公司 重庆市开州区文峰街道天鹅湖社区富厚街158号附10 地 址: 重庆市开州区长沙镇山花街1号 地 址: 道号 邮 编: 邮 编: 项目负责人: 丁敬余 项目负责人: 谭毅 电 话: 15826368887 管电 话: 13452653126 传 真: 传 真: 电子邮箱: 1415705480@qq.com 电子邮箱: 开户银行: 国 开户银行: 账 号: 账 号: 监督部门:中重庆市开州区公共资源交易管理局 电 话: 023-52218977 2026年08月17日 重庆市开州区2026年长沙镇桔香村柑橘基地改造提升项目 户名 开户行 投标保证金账号 重庆市开州区公共资源交易中心 重庆农村商业银行股份有限公司开州支行 3401010120010012772000200 中国农业银行股份有限公司重庆开州支行营 重庆市开州区公共资源交易中心 314401010400104500000006031 业部 中国工商银行股份有限公司重庆开州支行营 重庆市开州区公共资源交易中心 9558853100005824176 业部 重庆市开州区公共资源交易中心 重庆银行股份有限公司开州支行 680101040007547-100984 重庆市开州区公共资源交易中心 中国银行股份有限公司重庆开州支行 108865555576VA00149 信息来源:https://www.chinapipe.net/project/d3075199.html cqdingjiu 2026.08.21 10:06:58</t>
+          <t>会禄高速公路机电项目玻璃钢管、玻璃钢管箱采购公开招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3077959.html cqdingjiu 2026.08.24 12:31:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4634,18 +4626,18 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>重庆, 柑橘基地改造, 水肥一体化系统, 运输线, 排灌站, 生产便道, 无人机, 小型挖机, 智慧平台</t>
+          <t>重庆, 四川, 管材, 招标</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>万盛城区老旧供水管网更新改造工程答疑及补遗(一)</t>
+          <t>城投·三清华庭建设项目燃气管道安装工程(第四次)竞争性磋商公告</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4655,7 +4647,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4670,18 +4662,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>万盛区</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>万盛城区老旧供水管网更新改造工程答疑及补遗。</t>
+          <t>燃气管道安装工程</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4691,12 +4679,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>供水管网</t>
+          <t>燃气管道</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>万盛城区老旧供水管网更新改造工程答疑及补遗(一) 万盛城区老旧供水管网更新改造工程 答疑及补遗（一） 各潜在投标人： 现将万盛城区老旧供水管网更新改造工程答疑及补遗（一）相关条款通知如下： 网 一、答疑 问题1：请问招标人是否委派业主专家参与评标吗？ 务 答：是，本项目评标委员会共7人，其中在重庆市综合评标专家库随机抽取5人，招标人代表2人。? 问题2：本项目是否采用异地评标方式？ 答：是 。 商 问题3：本项目是否有业主代表，如有，请明确业主代表数量。 答：是，本项目评标委员会共7人，其中在重道庆市综合评标专家库随机抽取5人，招标人代表2人 。 问题4：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 答：可以。 管 问题5：污水处理厂提标改造及附属管道施工业绩满足吗？ 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 国 问题6：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可以 不填(空白)，对此有无要求？ 答：无要求。? 中 问题7：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖章， 请问需要提供联合体协议书吗？ 。 答： 根据招标文件第二章“投标人须知前附表”1.4.1 第3条业绩要求中：“注：（2）投标人提供的业绩为联 合体业绩的，其在该业绩中的工作分工应与本项目承担的工作一致。”要求，故需要提供联合体协议书。 问题8：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要求”吗？ 答：填写“达到招标文件的要求”或按照招标文件相关条款填写具体内容均可 。 问题9：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 答：投标人的工程量清单单项报价不得为零报价(招标人提供的工程量清单单项最高限价中金额为零的除外)或者 负数报价，否则由评标委员会作否决投标处理。 问题10：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知书发 出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予提前注 销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 答：需要。但不将加盖正本作为评审因素。 问题11：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收，请 问我公司业绩满足业绩要求吗？ 答：不满足。? 问题12：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 答：可以 。 问题13：业绩要求的竣工时间是指竣工验收时间吗？ 答：是的。 网 问题14：重庆市电子招投标系统投标文件-报价部分“己标价工程量清单”-“投标总价”页面招标人名称需要填 写吗？ 务 答：由投标人自行决定是否填写，是否填写不作为评审因素。 问题15：请问招标人是否委派业主专家参与评标吗？ 答：是，本项目评标委员会共7人，其中在重庆市综合评商标专家库随机抽取5人，招标人代表2人。 问题16：自来水厂或者净水厂含管道施工业绩满足业绩要求吗？ 答：投标人提供的业绩合同规模和工程类别需道满足招标文件要求。? 问题17：有没有人行贿专家，有的话我们就不参加了。 答：本项目评标委员会由招标人按法律法规及相关规定依法组建。 管 问题18：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要 提供其他格式之外的其他承诺？ 答：请各潜在投标人仔国细阅读招标文件，并按招标文件要求提供相应承诺。 问题19：财务报告可以不提供财务报表附注吗？ 答：可以。 中 问题20：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 问题21：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、注册证 及在本单位注册的证明文件替代？ 答：退休证等材料不能替代养老保险证明，按招标文件执行。? 问题22：本项目是异地评标吗？ 答：是。 问题23：现在除了没有警戒线和技术方案的低价项目评标专家不被围猎，哪个项目不围猎评标专家，请问招标人 如何保证公平？ 答：本项目招标文件严格按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本（2026年版）》编制， 且本项目评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 问题24：没有低价警戒线怎么保证中高价呢？ 答：本项目未设置低价警戒线，通过综合评估法对各潜在投标人进行评审。分值由技术、商务、报价组成，综 合实力优良的投标人合理中高价可依靠综合得分优势参与竞争，同时招标文件履约追责条款约束投标人理性报 价，保障合理报价竞争环境。 问题25：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗？ 答：现场递交纸质保函原件的人员不作要求 。 问题26：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 网 答：电子投标系统中锁定不可修改的格式（如封面、投标函）直接填空即可，其他投标文件格式以加盖公章的 招标文件PDF文件为准。? 问题27：专业分包业绩满足业绩要求吗？ 务 答：不满足。 问题28： 市政道路包含给水管网施工业绩满足业绩要求吗？ 商 答：投标人提供的业绩合同规模和工程类别需满足招标文件要求。 问题29：技术负责人在资格审查部分中提供了工程类高级及以上职称证后，在商务部分中再提供工程类高级及以 上职称证可以加分吗？ 道 答：可以。 问题30：万盛的项目挂綦江来投这样都还控制不了还全是你们万盛公司中的？是有啥猫腻是吧？参考之前的项目 管 全是万盛的公司中的！业主、专家全是你们自己人吧？ 答：本项目招标文件严格按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本（2026年版）》编制， 且本项目评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 国 二、补遗 1、本次重新发布本项目的工程量清单，在《重庆市公共资源交易网》(綦江区) （https://www.cqggzy.com/qijiangweb/）网上发布，请投标人自行下载。 中 招 标 人：重庆市万盛经济技术开发区城市管理局 招标代理机构：重庆力圣建设工程咨询有限公司 2026年8月18日 信息来源:https://www.chinapipe.net/project/d3074975.html cqdingjiu 2026.08.21 10:06:58</t>
+          <t>城投·三清华庭建设项目燃气管道安装工程(第四次)竞争性磋商公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3077958.html cqdingjiu 2026.08.24 12:31:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4705,18 +4693,18 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>重庆, 供水管网, 更新改造</t>
+          <t>重庆, 四川, 管材招标</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告</t>
+          <t>璞玉源水务2026成都市蒲江县管道直饮水入户项目设计施工总承包招标公告</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4726,7 +4714,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4741,53 +4729,57 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>巴南区</t>
+          <t>蒲江县</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>为解决片区内涝问题，在李家沱街道、花溪街道改建d400-d800雨水管网9665m，管材采用高密度聚乙烯(HDPE)缠绕结构壁管B型管；改建d1000-d1400雨水管网664m，管材采用高密度聚乙烯(HDPE)缠绕结构壁管B型管、III级钢筋混凝土管；改建d1500-d2000雨水管网426m，管材采用III级钢筋混凝土管；改建d2100-d2600雨水管网1000m，管材采用III级钢筋混凝土管；修复雨水管网5345m，增加智能感知设备6套。</t>
+          <t>管道直饮水入户项目的建设内容包括设计及施工总承包。</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>本次招标项目工程费估算金额：11061.83万元，勘察设计合同估算金额：334.544万元。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>雨水管网、高密度聚乙烯(HDPE)缠绕结构壁管B型管、III级钢筋混凝土管、智能感知设备</t>
+          <t>管道直饮水入户设备</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告 重庆市巴南区土桥片区内涝积水整治工程勘察设计招标公告 1.招标条件 本招标项目 重庆市巴南区土桥片区内涝积水整治工程已由重庆市巴南区发展和改革委员会以巴南发改审 发[2025]33号文批准建设，项目业主为重庆市巴南区住房和城乡建设委员会，代建业主为重庆市巴南公路建设有 限公司，建设资金来自区级财政资金统筹，项目出资比例为 100%，招标人为重庆市巴南公路建设有限公司。 项目已具备招标条件，现对该工程的勘察设计进行公开招标，评标办法采用综合评估法。 网 2.项目概况与招标范围 2.1 建设地点：重庆市巴南区花溪街道、李家沱街道 务 2.2 项目概况与建设规模：为解决片区内涝问题，在李家沱街道、花溪街道改建 d400-d800 雨水管网 9665m，管材 采用高密度聚乙烯(HDPE)缠绕结构壁管 B型管；改建 d1商000-d1400雨水管网 664m，管材采用高密度聚乙 烯(HDPE)缠绕结构壁管 B 型管、III 级钢筋混凝土管；改建 d1500-d2000 雨水管网 426m，管材采用III 级钢筋混凝 土管;改建 d2100-d2600 雨水管网 1000m，管材采用 III 级钢筋混凝土管；修复雨水管网 5345m，增加智能感知设 备6 套。 道 2.3 本项目工程总投资金额：13477.10万元 管 本次招标项目工程费估算金额：11061.83万元 国 本次招标项目勘察设计合同估算金额：334.544万元 中 2.4 招标范围：主要包括勘察、施工图设计（包含高边坡、深基坑）和相应阶段的勘察工作，以及提供施工现场 全过程技术服务，并配合业主办理相关手续等，具体范围为： （1）勘察部分：完成本项目范围内的勘察工作，包括但不限于排水管网排查、1:500地形图测量、地质钻勘、管 线内窥、物探、综合管线测量，市政管网错混接点测量及调查等工作，解决区域地下空间臭气问题，勘察成果 需达到重庆市城市建成区排水管网排查技术导则的要求，并配合业主完成对应的成果审查等事宜。 （2）设计部分：包括不限于完成本项目的施工图设计、施工期间交通组织设计、桥梁（涉轨）安全论证方案及 施工期间至竣工验收阶段，质量保修阶段的设计配合服务，配合办理施工图审查相关手续及竣工验收阶段、质 量保修阶段的设计服务等工作以及协助招标人完成各项审批手续办理等工作。 2.5 勘察设计服务期限：30日历天 2.6 标段划分（如有）：/ 2.7 其他：/ 3.政府采购工程 3.投标人资格要求 3.1 本次招标要求投标人须具备以下条件： 网 3.1.1 本次招标要求投标人具备的资质条件： 务 投标人应同时具有建设行政主管部门颁发的下列勘察和设计两类资质： 商 I、投标人应具备下列勘察资质之一： 道 ①工程勘察综合甲级资质。 管 ②工程勘察专业类（岩土工程）专业甲级资质和工程勘察专业类（工程测量）甲级资质； 国 II、投标人应具备下列设计资质之一： 中 ①工程设计综合甲级资质； ②工程设计市政行业甲级资质； ③工程设计市政行业(燃气工程、轨道交通工程除外)甲级资质； ④工程设计市政行业(排水工程)甲级资质。 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的勘察设计能力，详见招标文件第二章投标人须知 前附表第1.4.1项内容。 3.2 本次招标接受联合体投标。联合体投标的，应满足下列要求：联合体组成单位数量不超过2家，由负责设计 任务的单位作为联合体牵头人。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件及其附件、澄 清、修改、补充通知、最高限价通知等资料。参与投标的投标人需在重庆市公共网资源交易网完成市场主体信息 登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息 登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程 电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 务 布至2026-08-23 12:00:00前。 4.3招标人应于2026-08-26 17:00:00前在重庆市公共资源交易网发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-24 09:30，投标人应当在投标截止时间前，通过互 商 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督道网、重庆市公共资源交易网、重庆市公共资源交易网（巴南区） 发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 重庆市巴南公路建设有限公司 代理机构: 重庆云远项目管理有限公司 管 地 址: 重庆市巴南区龙洲大道265号 地 址: 重庆市九龙坡区渝隆大厦28楼 邮 编: 邮 编: 项目负责人: 牟老师 项目负责人: 李强 国 电 话: 023-66238079 电 话: 023-68434996 传 真: 传 真: 电子邮箱: 电子邮箱: 中 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市巴南区发展和改革委员会 电 话: 023-66221670 2026年08月18日 重庆市巴南区土桥片区内涝积水整治工程勘察设计 户名 开户行 投标保证金账号 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000001675 贸易试验区分行 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051304894 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020041267 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764210157 中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000682897 支行 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835000509 坝支行 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146639123 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630018252 信息来源:https://www.chinapipe.net/project/d3074953.html cqdingjiu 2026.08.21 10:06:58 网 务 商 道 管 国 中</t>
+          <t>璞玉源水务2026成都市蒲江县管道直饮水入户项目设计施工总承包招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3077945.html cqdingjiu 2026.08.24 12:31:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>d800 雨水管网：9665m；d1400雨水管网：664m；d2000 雨水管网：426m；d2600 雨水管网：1000m；雨水管网：5345m</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 雨水管网, 高密度聚乙烯, 钢筋混凝土管</t>
+          <t>管道直饮水入户项目, 成都市蒲江县, 设计施工总承包</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>重庆管道公司2026年涪陵压气站管道、设备防腐项目-非招标公告</t>
+          <t>采气二厂集输管道智能检测项目(2026~2028年)(重招)招标公告</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4797,7 +4789,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>房建</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4812,33 +4804,29 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>涪陵区</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>涪陵作业区涪陵压气站空压机、阀门等设备、消防泵房消防管道、循环水管道油漆出现锈蚀情况，为保证设施安全运行，对站场设备、消防管道及附属钢结构进行打磨除锈、油漆防腐。</t>
+          <t>集输管道智能检测</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>管道、设备防腐</t>
+          <t>智能检测设备</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>重庆管道公司2026年涪陵压气站管道、设备防腐项目-非招标公告 公告发布时间: 2026年08月18日09时02分19秒 一、概述 1.2.1项目概况：涪陵作业区涪陵压气站空压机、阀门等设备、消防泵房消防管道、循环水管道油漆出现锈蚀情况， 为保证设施安全运行，对站场设备、消防管道及附属钢结构进行打磨除锈、油漆防腐。 二、采购项目与标段 交货期限: 开工之日起90日内完工 网 质保期限(月): 标段 序号 标段名称 标段描述 编号 重庆管道公司2026年涪陵 涪陵作业区涪陵压气站空压务机、阀门等设备、消防泵房消防管道、循 1 1 压气站管道、设备防腐项 环水管道油漆出现锈蚀情况，为保证设施安全运行，对站场设备、消 目 防管道及附属钢结构进行打磨除锈、油漆防腐。 三、供应商资格要求 商 *1、响应人资质要求（1）响应人必须是依照中华人民共和国法律在国内注册，具备合格有效的营业执照的法人、 其他组织；与采购人存在利害关系可能影响询比采购公正性的法人、其他组织或者个人，不得参加响应。单位 负责人为同一人或者存在控股、管理关系的不同单位，不得参加同一标段响应或者未划分标段的同一询比项目 响应。（2）响应人须具备防水防腐保温工程专业承包二级及以上资质。*2、信誉要求响应人在响应文件提交截 止当日不存在以下情况：（1）响应人被“国道家企业信用信息公示系统”网站（www.gsxt.gov.cn）列入严重违法 失信企业名单（响应文件提交截止时间前已移出的除外）。（2）响应人被“信用中国”网站 （www.creditchina.gov.cn）列入严重失信主体名单（响应文件提交截止时间前已移出的除外）。（3）响应人或其 法定代表人、负责人、拟委任的项目经理被“中国执行信息公开网”（http://zxgk.court.gov.cn/shixin/）列入失信 被执行人名单（响应文件提交截止时间前已移出的除外），响应文件中需提供有效身份证号供查询。（4）响应 管 人、拟委任的项目经理被“全国建筑市场监管公共服务平台”网站（https://jzsc.mohurd.gov.cn/home）列入黑名单 （响应文件提交截止时间前已移出的除外）。上述（1）-（4）条以评审当日评审小组从官网查询信息为准。（5） 被国家管网集团或西南管道公司暂停、取消投标资格或业务承揽资格。（6）法律、行政法规规定的其他不允许 参与投标的情况。 国 四、询比文件的获取 4.1 有意向参加项目者，于2026年08月20日09时05分22秒前，登录数字供应链平台进行项目报名。 中 4.2 报名成功后于2026年08月18日09时01分42秒至2026年08月24日09时05分22秒，登录数字供应链平台进行项目下 载询比文件。 五、响应文件的递交 5.1 请于2026年08月24日11时00分00秒前，登录数字供应链平台递交项目响应文件。 5.2 逾期将无法进行递交响应文件，采购人将不予受理。 5.3 供应商在递交响应文件前，应按照有关规定提供人民币0万元项目保证金。 六、响应文件的开启 6.1 响应文件的开启时间2026年08月24日11时06分00秒 6.1 响应文件的开启地点供应链系统上 七、采购人信息 地址： 邮编： 联系人：舒建华 联系电话：18581824001 电子邮件：shujh@pipechina.com.cn 传真： 开户银行： 账户名： 账号： 信息来源:https://www.chinapipe.net/project/d3074904.html cqdingjiu 2026.08.21 10:06:59 网 务 商 道 管 国 中</t>
+          <t>采气二厂集输管道智能检测项目(2026~2028年)(重招)招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3077939.html cqdingjiu 2026.08.24 12:31:52 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4851,14 +4839,14 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>智能检测, 管道</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>重庆燃气集团股份有限公司输配分公司大渡口调压站至二郎调压站次高压燃气管线工程(大渡口段)公告</t>
+          <t>西充县旧城区排水防涝设施建设和虹溪河及洗笔路片区污水管网更新改造项目招标公告</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4868,7 +4856,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4883,53 +4871,57 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>南充市</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>大渡口区</t>
+          <t>西充县</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>安装部分包括材料验收、运输及履带式挖掘机及人工布管、管道管件安装、新旧管道的碰口、安装DN400直埋球阀1座、管道和商焊口的除锈及防腐、管道下沟后15KV电火花检测、管道的清管、强度及严密性试验、警示带敷设和线路标志桩（砖）安装、监检手续等。土建部分包括清表、扫线、平整场地、沟槽、基坑、阀井砌筑、回填土方、余方弃置、人工开挖人行道（花台）、公路及路面恢复、其他线缆穿跨越工道程施工、交通组织、水工保护等。</t>
+          <t>该项目涉及三个子项目：(一) 南充市西充县旧国城区排水防涝设施建设改造项目，包括更新改造不同规格的HDPE双壁波纹雨水管和混凝土雨水管，以及配套检查井和雨水口的改造；(二) 南充市西充县虹溪河片区污水管网更新改造项目，包括改造和新建不同规格的污水主管网和支管网，以及配套安装物联感知设备；(三) 南充市西充县洗笔路片区污水管网更新改造项目，包括改造和新建不同规格的污水管网，以及配套安装物联感知设备。</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>项目总投资额为37744.54万元。</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>燃气管线工程</t>
+          <t>HDPE双壁波纹雨水管、混凝土雨水管、HDPE双壁波纹污水管、钢筋砼承插排水管、物联感知设备等。</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>重庆燃气集团股份有限公司输配分公司大渡口调压站至二郎调压站次高压燃气管线工程(大渡口段)公告 采购 公告 公告编号： RQXYGG202608130064 一、采购项目基本情况 网 采购人：重庆燃气集团股份有限公司输配分公司 采购项目编号：RQCGXY202608130040 务 采购项目名称：大渡口调压站至二郎调压站次高压燃气管线工程（大渡口段） 采购内容或范围：安装部分： ①材料验收（甲供材料：阀门、管材、弯头、标志桩等）、运输及履带式挖掘机及人工布管； ②管道管件安装， 新旧管道的碰口；③安装DN400直埋球阀1座； ④管道和商焊口的除锈及防腐； ⑤管道下沟后15KV电火花检测； ⑥管道的清管，强度及严密性试验；⑦警示带敷设和线路标志桩（砖）安装； ⑧监检手续等。 土建部分： ①清表； ②扫线、平整场地； ③沟槽、基坑、阀井砌筑； ④回填土方； ⑤余方弃置； ⑥人工开挖人行道（花 台），公路及路面恢复； ⑦其他线缆穿跨越工道程施工，交通组织； ⑧水工保护等。 （具体内容详见施工图纸和 工程量清单） 公告发布时间 ：2026-08-18 14:39:10 管 二、采购人联系方式 联系人：王瑶 电话：023-67502265 国 邮箱：wangyao232@crcgas.com 三、采购明细 中 行号 采购内容 需求数量 单位 补充说明 拟邀请单位 大渡口调压站至二郎调压站次高压燃气管线 重庆燃气安装工程有限责任公 1 1 项目 无 工程(大渡口段) 司 四、服务费交纳 本项目不收取服务费。 五、 其他 事项 1.本公告在华润守正 采购交易 平 台（ https://www.szecp.com.cn/ ）上公开 发布。 2. 本项目采购通过守正平台线上进行，供应商需注册华润守正 采购交易 平台，通过平台进行响应文件的递交或 报价，具体操作步骤可查阅网站首页帮助中心的操作手册，也可以联系守正客服。 3 .答疑澄清、通知等文件一经在华润守正 采购交易 平台发布，视为已发放给相应供应商（发放时间即为发出时 间），请随时关注华润守正 采购交易 平台发布的相关信息，并及时查阅和处理。 4 .若有参与意向 ， 请于 2026-08-22 00:00:00前联系采购人 （联系方式见公示内容）反馈。 5 .若有异议 ， 请于 2026-08-22 00:00:00前提出异议 。 信息来源:https://www.chinapipe.net/project/d3074793.html cqdingjiu 2026.08.21 10:06:59 网 务 商 道 管 国 中</t>
+          <t>西充县旧城区排水防涝设施建设和虹溪河及洗笔路片区污水管网更新改造项目招标公告 西充县旧城区排水防涝设施建设和虹溪河及洗笔路片区污水管网更新改造项目 (项目名称)设计施工总承 包 / 标段 招标公告 1. 招标条件 网 1.1本招标项目 西充县旧城区排水防涝设施建设和虹溪河及洗笔路片区污水管网更新改造项目 (项目名称)已 由 西充县发展和改革局 (项目审批、核准或备案机关名称)以 西发改[2025]253号、西发改[2025]209号、西发改 [2025]215号 （批文名称及编号）批准建设，项目业主为 西充县公用事业服务中心 ， 建设资金来自 上级 务 资金和地方配套资金 （资金来源），项目出资比例为 100% ，招标人为 四川德恒建设发展集团有限公 司 。项目已具备招标条件，现对该项目的设计施工总承包进行公开招标。 1.2本招标项目由 西充县发展和改革局 （核准机关名称）核准（招标事项核准文号为 西发改[2025]253号、 西发改[2025]209号、西发改[2025]215号 ）的招标组织形式商为 委托招标 。 招标人选择的招标代理机构是 四川华景工程项目管理有限公司。 2. 项目概况与招标范围 道 管 2.1 建设地点：西充县晋城镇、南台街道、常林 镇。 2.2建设规模： （一）南充市西充县旧国城区排水防涝设施建设改造项目：更新改造DN600～DN800HDPE双壁波纹雨水管5765m， 更新改造DN1000～DN1200混凝土雨水管889m，配套检查井273座、改造雨水口485个;更新改 造DN400～DN800HDPE双壁波纹污水管3512m，配套检查井150座;修复改造DN200～DN2000的HDPE和混凝土管 网33000m。整治内涝点3处，更新改造DN600～DN800HDPE双壁波纹雨水管660m、DN1000～DN1600混凝土雨水 管2704m及中检查井、雨水口等配套设施。配套智能排水感知设备1套，主要包括监控设备、液位仪、气体检测智 慧井盖及配套附属设施等。 （二）南充市西充县虹溪河片区污水管网更新改造项目：改造污水主管网dn600-1800约30.93公里、污水检查 井386个，污水支管网dn200-600约38.92公里、污水检查井486个;新建污水主管网dn600-1800约3.44公里、污水检查 井85个，污水支管网dn200-600约9.73公里、污水检查井243个;污水管网材质为钢筋砼承插排水管;配套安装物联感 知设备。 （三）南充市西充县洗笔路片区污水管网更新改造项目：改造dn500-dn800污水管网55.57公里，配套改造污水检 查井633个;新建dn400-dn800污水收集管网15.97公里，配套建设检查井399个;新安装检查井盖损毁、水位、有毒气 体等报警设备约1792个，配套安装物联感知设备。 2.3计划工期：720日历天（其中设计工期90日历天，施工工期630日历 天）。 2.4招标范围：本标段范围内的施工图设计、工程施工、竣工验收及整体移交、质量缺陷责任期内缺陷修复等相 关工作。 2.5 质量目标：设计：符合国家现行设计规范标准和要求；施工：符合国家现行有关工程施工验收规范合格标准。 2.6 标段划分：设计、施工总承包为一个标段。 2.7概算投资额：37744.54万元。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质要求： （1）具备独立法人资格；（2）设计资质：具备行政主管部门颁发的工程设计市政行业（排 水工程）甲级及以上资质；施工资质：具备建设行政主管部门颁发的市政公用工网程施工总承包贰级及以上资 质 ，施工单位须具备有效的安全生产许可证。 3.1.2业绩要求：（本项为多选） 务 设计业绩要求：近年（ 2023年01月01日 至投标截止时间，不少于3年） 已完成或新承接或正在设计 不少于 1 （1 至3个）个类似项目。类似项目是指: 项目总投资不低于15000万元的市政工程类设计业绩（若 为联合体，由联合体设计单位提供） 。 施工业绩要求：近年（ 2023年01月01日 至投标截止时间商，不少于3年） 已完成或新承接或正在施工 不少于 1 （1 至3个）个类似项目。类似项目是指: 单项合同金额不低于15000万元的市政工程类施工业绩 （若为联合体，由联合体施工单位提供；牵头单位或成员单位均可提供） 。 □ 无业绩要求。 道 3.1.3项目经理的资格要求： 具有一级注册建造师（注册专业：市政公用工程） □ 由设计负责人兼 任 由施工负责人兼任， / （业绩要求），须为本单位人员（若为联合体投标，须为联合体牵头人人 员）。 管 3.1.4设计负责人的资格要求： 具有注册公用设备工程师（给水排水）证书（若为联合体，须为联合体设计单 位人员） ，须为投标人本单位人员。 3.1.5施工负责人（建造国师，下同）的资格要求： 具有市政公用工程专业一级注册 (注册专业)（级别）建造 师，具有省级及以上住房城乡建设主管部门颁发的安全生产考核合格证（B证），须为投标人本单位人员。 3.2本次招标接受联合体投标。联合体投标的，联合体牵头人应为 □ 设计单位 施工单位，同时满足下列 要求： 联合体成员家数不超过3家；联合体各方不得再以自己名义单独或参加其他联合体在同一标段中投标； 中 投标人组成联合体投标的，应签订联合体协议书，明确各成员权利义务、承包范围、职责分工等；牵头人全权 代表联合体参加投标和签署文件。 □ 3.3 本次招标范围中施工部分的工作仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大 企业、与大企业的负责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，本项目联合体协议书 中职责分工为承揽施工工作的所有单位均应属于中小企业）。具体标准以《工业和信息化部、国家统计局、国 家发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业〔2011〕300号）中 的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、存在特殊要求外，我市依法必须 招标的国家投资工程，施工部分招标控制价在8000万元以下3000万元以上的，原则上勾选此项。） □ 3.4 本次招标范围中施工部分的工作仅面向小微企业发包（其中属于大、中企业的分支机构、存在控股股东 为大、中企业、与大、中企业的负责人为同一人的情形的企业均不属于小微企业。若为联合体投标的，本项目 联合体协议书中职责分工为承揽施工工作的所有单位均应属于小微企业）。具体标准以《工业和信息化部、国 家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业 〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供小微企业声明函。（除技术复杂、存在特殊要求 外，我市依法必须招标的国家投资工程，施工部分招标控制价在3000万元及以下的，原则上勾选此项。） 4. 招标文件的获取 4.1 凡有意参加投标者，请于 2026年08月22日 00时00分 开始，登录全国公共资源交易平台（四川省）（网 址：http://ggzyjy.sc.gov.cn）-&gt;交易平台入口-&gt;南充市-&gt;南充交易系统-建设网、或登录《四川建设网》 （http://www.sccin.com）-&gt;电子招标-&gt;南充市公共资源交易平台登录入口，投标人凭单位CA数字证书（包括但 不限于CFCA、四川CA、重庆CA、天威诚信等）登录，免费获取招标文件（联系电话：028-85569858）。 4.2 除上述方式外，招标人不提供其他任何报名和招标文件获取的方式。 5. 投标文件的递交 5.1 投标文件递交的截止时间（投标截止时间，下同）为 2026年09月15日 09时10分 ，投标人应在投标截止时间 前，登录全国公共资源交易平台（四川省）（网址：http://ggzyjy.sc.gov.cn）-&gt;交易平台入口-&gt;南充市-&gt;南充交易 系统-建设网、或登录《四川建设网》（http://www.sccin.com）-&gt;电子招标-&gt;南充市公共资源交易平台登录入口， 凭单位CA数字证书登录，在线递交经投标人数字证书签名制作的数据加密电子投标文件。开标地点为：南充市 公共资源交易服务中心（南充市涪江路19号五楼）本项目开标室。 5.2 逾期送达的或者未送达指定地点的投标文件，招标人不予受理。 网 6. 发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省）》和 四川建设网 (公告发布的其它媒介名称）上发布。 务 7. 行政监督部门 单位名称： 西充县住房和城乡建设局 商 联系电话： 0817-4222761 8. 联系方式 道 □ 招标代理机构： / 招标代理机构： 四川华景工程项目管理有 招 标 人： 四川德恒建设发展集团有限公司 限公司 地 址： 四川省南充市西充县南台街道城南新区“数字西充.城市超 地 址： 成都市蛟龙港双流园区海滨广 脑”四楼406室 管 场11号楼1603室 邮 编： 637299 邮 编： 610000 联 系 人： 王老师 联 系 人： 凌先生 电 话： 0817-8050003 项目负责人： 王仕科 传 真： 0817-8050003 电 话： 028-60613388 电子邮件： / 国 传 真： 028-60613388 网 址： / 电子邮件： / 开户银行： / 网 址： / 账 号： / 开户银行： / 账 号： / 中 2026年08月21日 注： （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不 得作为资质要求。 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工 程相应指标，类似项目业绩的定义应明确，用语准确无歧义。 （4）招标人限定的联合体成员数量不得少于设定的资质个数。 信息来源:https://www.chinapipe.net/project/d3077901.html cqdingjiu 2026.08.24 12:31:53</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>排水管道、污水管网、物联感知设备的更新改造和安装。</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>塑料管不计匹配分</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>石柱公司2026-2027年度用户供水管道安装及管网抢(维)修工程(第二次)项目公告</t>
+          <t>中国五冶西充县太平水厂、鹤鸣庵水厂及配套管网建设项目劳务分包采购公告</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4939,7 +4931,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4954,33 +4946,37 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>南充市</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>石柱土家族自治县</t>
+          <t>西充县</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-2027年度用户供水管道安装及管网抢（维）修服务</t>
+          <t>西充县太平水厂、鹤鸣庵水厂及配套管网建设项目劳务分包</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>项目资金来自企业自筹，合同估算金额约280万元</t>
+          <t>采购控制价：2761.638256万元（含税）</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>供水管道安装及管网抢（维）修服务</t>
+          <t>劳务分包</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>石柱公司2026-2027年度用户供水管道安装及管网抢(维)修工程(第二次)项目公告 石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程（第二次）（比选公告 1.比选条件 本比选项目石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程（第二次）（项目名称），比选人 为重庆石柱水利水电实业开发有限公司，比选项目资金来自企业自筹（资金来源），项目已具备比选条件。现 对本项目进行公开比选，诚邀有兴趣的潜在投标人参与投标。 网 2.项目概况与比选范围 2.1 建设地点：比选人指定地点 务 2.2 项目概况与建设规模：2026-2027年度用户供水管道安装及管网抢（维）修服务 2.3 本次比选项目合同估算金额：约280万元 商 2.4 比选范围：完成石柱公司2026-2027年度用户供水管道安装及管网抢（维）修工程包括公司供水范围内用户 各类管道及管件安装、水表安装及更换、阀门安装等、并完成配套土建工程、零星签证等工程量清单所列项目、 管网抢维修和公司所属生产单元零星项目，具体内容详见第五章 工程量清单。 道 2.5 工期要求：1年 缺陷责任期要求：24个月 管 3.投标人资格要求 3.1 本次比选要求投标人须具备以下条件： 国 3.1.1 本次比选要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰级 及以上资质； 3.1.2 投标人还应在人员、设备、资金等方面具有相应的施工能力，详见比选文件第二章投标人须知前附表第1.4.1 中 项内容。 3.2 本次比选不接受联合体投标。 4.比选文件的获取 4.1 投标人于2026年08月18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子版， 以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都视为 投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的一切 后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价，递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，被视为无效。 4.4比选文件每份售价1000 元，售后不退。投标人在递交纸质投标文件时支付，否则比选人拒绝接收其投标文 件。 5.投标文件的递交 5.1电子投标文件递交时间：2026年08月24日10时00分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年08月24日09时30分至10时00分，地点：水务集团招标采购中心（重庆市两江新 区嘉华路36号重庆水务大厦五楼）。 5.3 投标截止时间：2026年08月24日10时00分（北京时间）。 网 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 6.发布公告的媒介 务 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 7.联系方式 商 比 选 人：重庆石柱水利水电实业开发有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市石柱土家族自治县都督大道11号 地 址：重庆市两江新区嘉华路36号重庆水务大厦1018 联 系 人：王老师 联 系 人：颜老师 道 电 话：13658292968 电 话：023-67901915 重庆水务电子商务平台咨询电话：管023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3074720.html cqdingjiu 2026.08.21 10:06:59 国 中</t>
+          <t>中国五冶西充县太平水厂、鹤鸣庵水厂及配套管网建设项目劳务分包采购公告 一、采购人基本信息： 1、采购人名称：中国五冶集团有限公司 2、地址：四川省成都市锦江区五冶路9号 3、联系人：刘工 网 4、电话：028-80803115 二、采购项目概况 务 1、采购名称：西充县太平水厂、鹤鸣庵水厂及配套管网建设项目 劳务分包 2、项目地点：南充市西充县太平镇 商 3、采购范围：西充县太平水厂、鹤鸣庵水厂及配套管网建设项目劳务分包。 4、采购控制价：2761.638256万元（含税） 道 三、投标单位条件 1、资质要求：本次采购要求投标人在中华人民共和国境内注册，具有独立法人资格，具备合法有效的营业执照， 管 具备住建部门颁发的处于有效期内的施工劳务企业资质（不分类别和等级），且具有有效的安全生产许可证； 2、财务要求：提供上一年度经审计的财务报表（带二维码）。 3、业绩要求：能够反国映近年类似工程业绩的合同或竣工验收有效证明。 4、信誉要求：①投标单位没有处于被责令停业、投标资格被取消、财产被接管、冻结或破产状态等；②近三年 内没有发生骗取中标及发生重大质量、安全或诚信等严重违约、失信或违法问题；③投标单位应为“中国五矿 集团有限公司供应链管理平台（http：//ec.minmetals.com.cn/）”已准入供方；不在中国五矿集团供应商“黑名 中 单”中，服务关系未被五冶集团停用或被评为D级，在五冶内无不良记录。④近三年无直接起诉或仲裁采购人的 案件，且无连带采购人被诉并承担责任的诉讼或仲裁。 5、经营状态：无异常； 6、其他要求：须组建完整健全的项目团队，相应岗位须具备匹配岗位的证书，且团队人员必须是投标单位在册 员工。（包括项目经理、技术负责人、安全员、质量员、材料员、劳资员等）； 7、本次招标不接受联合体投标。 四、资格预审文件的获取 凡有意参加本次采购内容的投标单位，请于本公告发布之日起通过中国五矿集团有限公司供应链管理平台（网 址：https://ec.minmetals.com.cn/）按《资格预审申请表》（详见附件）提交申请。 五、资格预审文件提交截止时间 资格预审文件提交截止时间为2026年8月28日19：00(北京时间)，逾期提交的将被系统拒绝。 时间： 2026 年8月 21 日 信息来源:https://www.chinapipe.net/project/d3077864.html cqdingjiu 2026.08.24 12:31:53 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4989,18 +4985,18 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>重庆, 供水管道安装, 管网抢修, 企业自筹, 280万元</t>
+          <t>四川, 劳务分包, 管材</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>万盛城区老旧供水管网更新改造工程(甲供材料)答疑(一)</t>
+          <t>马边彝族自治县自来水有限责任公司年度材料采购(AGR及PVC—U材料)-更正公告</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5010,7 +5006,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5025,49 +5021,57 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>乐山市</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>马边彝族自治县</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>万盛城区老旧供水管网更新改造工程涉及3PE防腐钢管的采购，其管道部分壁厚需符合国标标准并达到设计要求。</t>
+          <t>马边彝族自治县自来水有限责任公司年度材料采购更正公告（第1次）</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>项目详情中未提及具体资金情况。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>3PE防腐钢管</t>
+          <t>智能水表-有线光电传输智能水表,智能水表-NB-IOT物联网带阀水表,智能水表-智能远传水表-远传水表(超声波水表)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>万盛城区老旧供水管网更新改造工程(甲供材料)答疑(一) 万盛城区老旧供水管网更新改造工程（甲供材料） 答疑（一） 各潜在投标人： 现将万盛城区老旧供水管网更新改造工程（甲供材料）答疑（一）相关条款通知如下： 网 一、答疑 问题1：请问招标人是否委派业主专家参与评标吗？ 务 答：是，本项目评标委员会共7人，其中在重庆市综合评标专家库随机抽取5人，招标人代表2人。 问题2：万盛的项目挂綦江来投这样都还控制不了还全是你们万盛公司中的？是有啥猫腻是吧？参考之前的项目 全是万盛的公司中的！业主、专家全是你们自己人吧？ 商 答：本项目招标文件严格按照《重庆市工程建设项目货物采购招标文件示范文本（2026年版）》编制，且本项目 评标委员会由招标人按法律法规及相关规定依法组建，欢迎各潜在投标人积极参与投标。 问题3：3PE管道部分壁厚是多少呢？ 道 答：本项目采购的3PE防腐钢管的管道部分壁厚须符合国标标准并达到设计要求。 招 标 人：重庆市万盛经济技术开发区城市管理局 管 招标代理机构：重庆力圣建设工程咨询有限公司 2026年8月18日 国 信息来源:https://www.chinapipe.net/project/d3074712.html cqdingjiu 2026.08.21 10:06:59 中</t>
+          <t>马边彝族自治县自来水有限责任公司年度材料采购(AGR及PVC—U材料)-更正公告 马边彝族自治县自来水有限责任公司年度材料采购更正公告（第1次） 一、项目基本情况： 原公告的采购项目编号：CGPT-XM-JZXCS-HW-202608-0041 网 原公告的采购项目名称：马边彝族自治县自来水有限责任公司年度材料采购 首次公告日期：2026年8月17日 务 二、更正信息： 更正事项：招标文件内容更正 商 更正原因：调整文件内容 更正内容： 道 1、原内容： 第五章 采购项目技术、服务、采购合同内容条款及其他商务要求 管 二、采购清单及单价最高限价说明（实质性要求） “2、智能水表-有线光电传输智能水表（铁壳带阀）、3、智能水表-NB-IOT物联网带阀水表（铁壳带阀）” 国 现更正为：“2、智能水表-有线光电传输智能水表、3、智能水表-NB-IOT物联网带阀水表” 2、原内容： 中 第五章 采购项目技术、服务、采购合同内容条款及其他商务要求 三、技术要求（实质性要求） “1、智能水表-智能远传水表（铁壳带阀）-远传水表(超声波水表)；⑩材质：不锈钢及标准以上材质，应保证耐 用性。” “2、智能水表-有线光电传输智能水表（铁壳带阀）；⑩材质：不锈钢及标准以上材质，应保证耐用性。” “3、智能水表-NB-IOT物联网带阀水表（铁壳带阀）技术要求” 现更正为：“1、智能水表-智能远传水表-远传水表(超声波水表)；⑩材质：不锈钢及标准以上材质，应保证耐用 性。” “2、智能水表-有线光电传输智能水表；⑩材质：不锈钢及标准以上材质，应保证耐用性。” “3、智能水表-NB-IOT物联网带阀水表技术要求；新增“材质：满足规格标准及以上材质，应保证耐用 性。” 3、原采购文件中关于报价均按“单价最高限价同比例下浮 %”执行。 更正日期：2026年08月21日 三、其他补充事宜：其他内容以更正后的招标文件为准。 四、凡对本次公告内容提出询问，请按以下方式联系。 1、采购人 名称：马边彝族自治县自来水有限责任公司 网 地址：马边彝族自治县民建镇东光大道435号 联系方式：彭老师 0833-4521369 务 2、采购代理机构 商 名称：四川达群工程管理有限公司 地址：四川省乐山市市中区嘉定中路570号25楼8号 道 联系方式：曹老师 0833-2137555 管 信息来源:https://www.chinapipe.net/project/d3077838.html cqdingjiu 2026.08.24 12:31:53 国 中</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>智能水表-有线光电传输智能水表；智能水表-NB-IOT物联网带阀水表；智能水表-智能远传水表-远传水表(超声波水表)</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 3PE防腐钢管, 资金情况, 产品种类</t>
+          <t>塑料管不计匹配分</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>重庆中法供水2026年普通防腐钢管及管件采购项目(第三次)项目公告</t>
+          <t>邛崃经芦山至荥经高速公路项目邛崃段占压邛崃市天然气有限公司输气管道迁改工程设计比选公告</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5077,7 +5081,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5092,29 +5096,37 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>邛崃市</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>本项目涉及普通防腐钢管及管件的采购，包括各种规格的钢高频焊管和钢螺旋焊管，以及相应的管件如钢套筒、钢制标准接头等。</t>
+          <t>邛崃经芦山至荥经高速公路项目邛崃段占压邛崃市天然气有限公司输气管道迁改工程设计。</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>项目资金来自企业自筹，出资比例为100%。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>钢高频焊管,钢螺旋焊管,钢套筒,钢制标准接头,钢制渐缩,钢制三通,钢制双盘短管,钢制弯头</t>
+          <t>设计服务</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>重庆中法供水2026年普通防腐钢管及管件采购项目(第三次)项目公告 重庆中法供水2026年普通防腐钢管及管件采购项目（第三次）比选公告 1.比选条件 本比选项目重庆中法供水2026年普通防腐钢管及管件采购项目（第三次），比选人为重庆中法供水有限公司，比 选项目资金来自企业自筹，出资比例为100%，项目已具备比选条件。现对本项目进行公开比选，诚邀有兴趣的 潜在投标人参与投标。 网 2.项目概况与比选范围 2.1 普通防腐钢管及管件采购清单： 务 序号 存货编码 材料名称 规格型号 单位 数量 最高单价限价（元） 1 10400177 钢高频焊管 D89*4 5 米 61.92 2 10400181 钢高频焊管 D108*5 300 米 88.89 商 3 10400182 钢高频焊管 D159*5 5 米 132.18 4 10400206 钢高频焊管 D159*6 5 米 152.13 5 10400290 钢螺旋焊管 DN219*6 5 米 196.68 道 6 10400291 钢螺旋焊管 DN219*8 5 米 244.80 7 10400292 钢螺旋焊管 DN325*8 5 米 361.28 8 10400293 钢螺旋焊管 DN377*8 5 米 423.12 管 9 10400294 钢螺旋焊管 DN426*8 5 米 475.89 10 10400295 钢螺旋焊管 DN426*10 5 米 574.29 11 10400297 钢螺旋焊管 DN529*8 5 米 595.76 国 12 10400298 钢螺旋焊管 DN529*10 5 米 718.91 13 10400299 钢螺旋焊管 DN630*10 5 米 861.50 14 10400300 钢螺旋焊管 DN720*10 5 米 987.95 中 15 10400301 钢螺旋焊管 DN820*10 5 米 1133.08 16 10400302 钢螺旋焊管 DN920*10 5 米 1279.51 17 10400304 钢螺旋焊管 DN1020*10 5 米 1424.64 18 10400305 钢螺旋焊管 DN1020*12 5 米 1652.24 19 10400306 钢螺旋焊管 DN1220*10 5 米 1709.70 20 10400307 钢螺旋焊管 DN1220*12 5 米 1982.83 21 10400308 钢螺旋焊管 DN1420*12 5 米 2375.96 22 10400309 钢螺旋焊管 DN1420*14 5 米 2697.83 23 10400332 钢螺旋焊管 DN1120*10 5 米 1574.96 24 10400342 钢螺旋焊管 DN1020*14 5 米 1879.02 25 10400322 钢螺旋焊管（特加强） DN820*10 5 米 1133.08 26 10200490 钢套筒 D159*500cm 5 个 159.00 27 10200491 钢套筒 D219*500cm 5 个 240.00 28 10200492 钢套筒 D273*500cm 5 个 300.00 29 10200493 钢套筒 D325*500cm 5 个 361.00 30 10200494 钢套筒 D377*500cm 5 个 436.00 31 10200495 钢套筒 D426*500cm 5 个 482.00 32 10200589 钢套筒 D159*1000cm 5 个 226.00 33 10200590 钢套筒 D219*1000cm 5 个 1627.00 34 10200591 钢套筒 D273*1000cm 5 个 2501.00 35 10200592 钢套筒 D325*1000cm 5 个 488.00 36 10200593 钢套筒 D377*1000cm 5 个 591.00 网 37 10200598 钢套筒 D426*1000cm 5 个 833.00 38 10200155 钢制标准接头 D108 5 个 91.00 39 10200156 钢制标准接头 D159 5 个 160.06 务 40 10200157 钢制标准接头 D219 5 个 319.41 41 10200158 钢制标准接头 D273 5 个 396.63 42 10200159 钢制标准接头 D325 5 个 475.96 商 43 10200160 钢制标准接头 D426 5 个 619.87 44 10200161 钢制标准接头 D529 5 个 779.22 45 10200162 钢制标准接头 D630 5 个 1068.44 道 46 10200163 钢制标准接头 D720 5 个 1214.46 47 10200164 钢制标准接头 D820 5 个 1428.34 48 10200165 钢制标准接头 D920 5 个 1600.14 管 49 10200169 钢制标准接头 D1220 5 个 2297.57 50 10200170 钢制标准接头 D1420 5 个 3027.02 51 10200171 钢制标准接头 D1020 5 个 2194.19 国 52 10300309 钢制大小头 DN65*DN50 5 个 14.74 53 10200667 钢制渐缩 D108＞57 3 个 21.06 54 10200668 钢制渐缩 D108＞89 3 个 26.00 中 55 10200695 钢制渐缩 D159＞108 3 个 40.72 56 10200671 钢制渐缩 D219＞159 3 个 68.09 57 10200672 钢制渐缩 D219＞108 3 个 80.03 58 10201605 钢制渐缩 219*125 3 个 75.82 59 10200694 钢制渐缩 D273＞108 3 个 129.87 60 10200673 钢制渐缩 D273＞159 3 个 94.07 61 10200674 钢制渐缩 D273＞219 3 个 84.94 62 10200675 钢制渐缩 D325＞108 3 个 184.63 63 10200676 钢制渐缩 D325＞159 3 个 143.91 64 10200680 钢制渐缩 D325＞219 3 个 131.98 65 10200677 钢制渐缩 D325＞273 3 个 124.25 66 10200684 钢制渐缩 D426＞325 3 个 285.01 67 10200685 钢制渐缩 D529＞325 3 个 617.76 68 10200679 钢制渐缩 D529＞426 3 个 547.56 69 10200659 钢制渐缩 D630＞325 3 个 756.00 70 10200687 钢制渐缩 D630＞426 3 个 728.00 71 10201539 钢制渐缩 D630＞529 3 个 722.00 72 10200690 钢制渐缩 D720＞630 3 个 848.00 73 10200691 钢制渐缩 D720＞529 3 个 842.00 74 10200682 钢制渐缩 D820＞720 3 个 913.00 75 10200692 钢制渐缩 D920＞720 3 个 1053.00 76 10201519 钢制渐缩 D920*820 3 个 1064.00 77 10200652 钢制渐缩 D1020＞820 3 个 1305.00 网 78 10200693 钢制渐缩 D1020＞920 3 个 1322.00 79 10201738 钢制渐缩 1220*820 3 个 1806.00 80 10201507 钢制渐缩 1220＞1020 3 个 1834.00 务 81 10201624 钢制三盘三通 D108⊥108 3 个 224.64 82 10200371 钢制三盘三通 DN200⊥100 3 个 435.24 83 10200373 钢制三盘三通 DN200⊥200 3 个 599.51 商 84 10201531 钢制三通 108*108 3 个 58.97 85 10200285 钢制三通 219*108 3 个 187.43 86 10201341 钢制双盘短管 89*400mm 3 个 139.00 道 87 10201342 钢制双盘短管 89*800mm 3 个 178.31 88 10201340 钢制双盘短管 108*300mm 3 个 158.65 89 10201299 钢制双盘短管 DN108*500mm 3 个 185.33 管 90 10201300 钢制双盘短管 DN108*1000mm 3 个 258.34 91 10201301 钢制双盘短管 DN108*1500mm 3 个 329.94 92 10201332 钢制双盘短管 159*300mm 3 个 251.32 国 93 10201339 钢制双盘短管 159*750mm 3 个 348.19 94 10201303 钢制双盘短管 DN159*1000mm 3 个 402.95 95 10201304 钢制双盘短管 DN159*1500mm 3 个 508.25 中 96 10201305 钢制双盘短管 DN219*500mm 3 个 463.32 97 10201306 钢制双盘短管 DN219*1000mm 3 个 672.52 98 10201307 钢制双盘短管 DN219*1500mm 3 个 876.00 99 10201312 钢制双盘短管 DN219*750mm 3 个 581.26 100 10201338 钢制双盘短管 273*1250mm 3 个 1010.88 101 10201458 钢制双盘渐缩 108*57 3 个 109.51 102 10201469 钢制双盘渐缩 108*89 3 个 117.94 103 10201514 钢制双盘渐缩 159*108 3 个 185.33 104 10201748 钢制双盘渐缩 200*80 3 个 294.84 105 10201462 钢制双盘渐缩 219*108 3 个 256.93 106 10201513 钢制双盘渐缩 219*159 3 个 280.80 107 10201465 钢制双盘渐缩 D273＞108 3 个 339.77 108 10201467 钢制双盘渐缩 D273＞219 3 个 388.91 109 10201770 钢制双盘渐缩 D273＞159 3 个 365.04 110 10201461 钢制双盘渐缩 325*219 3 个 477.36 111 10301108 钢制弯头 89*90° 3 个 28.78 112 10200702 钢制弯头 D108×90° 100 个 43.52 113 10200701 钢制弯头 D159×90° 3 个 84.24 114 10200705 钢制弯头 D219*90° 3 个 231.66 115 10200706 钢制弯头 D273*90° 3 个 300.46 116 10200709 钢制弯头 D325*90° 3 个 418.39 117 10200711 钢制弯头 D426*90° 3 个 744.12 118 10200712 钢制弯头 D529*90° 3 个 1352.05 网 119 10200764 钢制弯头 D570*90° 3 个 1474.20 120 10200714 钢制弯头 D630*90° 3 个 1535.98 121 10200715 钢制弯头 D720*90° 3 个 1742.36 务 122 10200717 钢制弯头 DN720*90°*12mm 3 个 1989.47 123 10200720 钢制弯头 D920*90° 3 个 2935.30 124 10200722 钢制弯头 D820*90° 3 个 2325.23 商 125 10200762 钢制弯头 D1020*90° 3 个 4829.55 126 10200723 钢制弯头 D1220*90° 3 个 6039.80 127 10200724 钢制弯头 D1420*90° 3 个 8297.00 道 注：管材按照米数进行报价，管件按照件数进行报价。 2.2 供货数量、时间和批次：根据工程实际进度与比选人的要求进行供货，以实际供货量为准，供货时间达到商 务条款的规定。 管 2.3 交货地点：比选人指定的施工现场。 2.4 供货期：两年。 国 3.投标人资格要求 3.1 本次比选允许投标人以投标货物的下列身份参加投标： 中 ?制造商 3.1.1 投标人为制造商应符合以下要求： 投标人必须是依法设立的，并在中国注册的，具有独立法人地位的企业。 【提供有效的营业执照】 3.2 投标人2025年的年度财务状况不亏损。 【提供由会计师事务所或审计机构出具的无保留意见的财务审计报告及会计报表，财务报表至少包括现金流量 表、资产负债表、利润表】 3.3 投标产品的制造商须通过质量ISO9001、环境ISO14001、职业健康体系ISO45001认证。 【提供有效的证书】 3.4 投标人须提供2023年1月1日至投标截止日止（以合同签订时间为准）,签订的30万元及以上的钢管及管件产品 购销合同至少1个。 【提供采购合同、不低于前述金额50％的发票，合同与发票的项目名称须一致】 注：①若投标人开具的发票上未能体现具体项目，需附上税务出具的发票清单（清单上需显示采购项目为钢管 及管件产品）。 ②若提供的合同为年度合同未体现具体金额，但实际供货金额达到30万元及以上，应提供与该合同对应的30万元 及以上的钢管及管件产品发票作为佐证。 3.5 投标人须为所投投标产品制造商，此次所提供的普通防腐钢管及管件必须是自己工厂所制造的产品，不得外 购他人产品。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函及工商部门出具的本产品商标或品牌证明文件】 3.6 投标产品过水部分涉及的涂料须提供行政主管部门出具的有效的“卫生许可网批件”及卫生疾控中心出具的卫 生检测报告。 【提供行政主管部门出具的有效的“卫生许可批件”及卫生疾控中心出具的卫生检测报告】 务 3.5 根据本次采购清单及技术规范的要求，投标人须承诺具备相关的技术手段和措施、保证产品设计使用寿命 20 年以上。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 商 3.6 投标人须承诺保证5年内不得停产同型号的投标产品。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 道 3.7 办事机构和库房【比选人有权对中标人的办事机构及库房进行实地核查，若发现与提供资料不符，将视为提 供虚假资料，按相关规定取消其中标资格，其投标保证金不予退还。】 投标人承诺：收到中标通知书后30日内提供租赁合同或产权证明，并提供重庆库房卫星定位图片。 管 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 【卫星定位图片：手机打开地图，搜索该地址、进行标注，然后截图或者电脑打开地图（地图软件不限），搜 索该地址、选择卫星模国式、进行标注、然后截图均可。】 3.8 符合第五章“技术要求”普通防腐钢管及管件技术要求。 【根据技术要求提供技术响应表，并根据技术条款要求提供对应的检测报告等。】 中 3.9 售后服务承诺【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】： 1）货物交付及付款方式要求，满足第四部分合同协议书第3条及第10条；供货单位应确保产品的及时供应，承诺 因产品供应不及时造成的一切损失均由供货单位负责赔偿。 2）有完整的售后服务方案、培训计划并在合同签订后为比选人免费提供培训服务。 3）售后服务承诺书，满足第四部分合同协议书第11条；承诺质保期后提供2年及以上定期免费巡查、保养计划。 4）承诺接到分派的工单1小时内联系用户约定维修时间，在24小时内处理完毕工单，且让用户满意。若工单超时、 未在规定时间内告知比选人维修时间或工单处理未让用户满意造成返单的，按比选人制度进行处罚。 3.10 投标人承诺不得存在下列情形之一： 1）被人民法院列入失信被执行人名单且在被执行期内； 2）被国家、重庆市（含市或任意区县）有关行政部门行政处罚，且在处罚期限内； 3）投标截止日前两年内（指2024年1月1日至投标截止日止），投标人或其法定代表人被人民法院判定犯行贿罪 的； 4）投标截止日前五年内（指2021年1月1日至投标截止日止），投标人与重庆中法供水有限公司有违约情况或终 止合同情况的。 【按照第六章 三、资格审查部分“承诺函格式”提供承诺函】 3.11 投标截止日前五年内（指2021年1月1日至投标截止日止），投标人无在我司因产品及服务等对公司生产、经 营、安全造成不良影响的记录；若投标人出现过供水通报事项，因产品质量问题对生产、安全造成影响，存在 合同违约等问题，不予参加本次项目投标。 【按照第六章 三、资格审查部分“无不良记录承诺函”提供承诺函，若经验证承诺函不属实，将对中标人作否 决投标处理。】 网 3.12 投标样品要求： 3.12.1 投标人需提供以下规格型号数量的样品： 务 【①钢螺旋焊管 DN219*8 壹件 ②钢制弯头 D108*90°壹件】，提供的样品应满足第五章技术要求规定。样品为 投标人免费提供，管材样品不低于20CM，不计入采购清单内。 3.12.2 投标样品同投标文件一并递交。每件样品上分别标明样品的投标人、生产厂家、品牌、名称、规格、型号等 （格式自拟），投标样品必须密封装箱，且在密封包装外商贴样品一览表（格式自拟），注明提供样品的投标人、 生产厂家、品牌、名称、规格、型号、数量等。 3.12.3 投标人的样品在开标当日递交至样品区（样品区地点：开标当日咨询比选代理机构），中标人的投标样品 不退还，其余投标人的样品在中标公示期满后道5个工作日内退还，如不领取，投标样品按废品处理。 3.12.4 上述对投标样品的密封和标识要求是为便于评标，请投标人积极配合，未按上述要求对投标样品进行密封 和标识的，不作否决投标处理，但由此造成的其他后果由投标人自行承担。 管 3.13 若投标人违反重庆中法供水有限公司《供应商负面清单管理办法》规定且在处罚期内的，按否决投标处理 （评标委员会根据比选公告后附“供应商负面清单”进行评审）。 3.14 本次比选不接受联合体投标。 国 特别说明： （1） 本比选文件要求提供的所有检测报告须为近2年内的检测报告（2024年1月1日-投标截止日），此要求不包 括卫生许可批件及其检测报告。 中 （2） 上述所须提交的相关证明材料复印件均应加盖投标单位法人章并装入投标文件资格审查部分中。上述有一 条不满足则投标文件由评标委员会作否决投标处理。 （3） 比选人有权对投标人提供的以上资料进行核实，若发现存在弄虚作假，取消其投标、中标资格，投标人承 担因此造成的相关责任并赔偿相应损失。 4.比选文件的获取 4.1 投标人于2026年8月18日起可自行在重庆水务集团电子商务平台(https://www.cqswjt.cn)上下载比选文件电子版， 以及答疑、补遗等投标截止时间前公布的所有相关资料，不管投标人下载与否，比选人和比选代理机构都视为 投标人收到以上资料并全部知晓有关比选过程和事宜，如因投标人自身原因未能下载相关资料由此产生的一切 后果由投标人自行负责。各投标人应随时关注网上(https://www.cqswjt.cn)发布的比选文件及相关修改内容。 4.2 投标人须在重庆水务集团电子商务平台(https://www.cqswjt.cn)进行投标人注册，填写相关信息，审批过后成为 平台投标人。 4.3 此项目将在重庆水务集团电子商务平台系统上进行电子开、评标。投标人需提前在重庆水务集团电子商务平台 (https://www.cqswjt.cn)上注册、报名，下载比选文件，上传电子投标文件并报价，递交纸质投标文件。在投标截 止时间前未按时报名、报价并上传电子投标文件、递交纸质投标文件者，被视为无效。 4.4比选文件每份售价 500 元，售后不退。投标人在递交纸质投标文件时扫描支付，否则比选人拒绝接收其投标文 件。 5.投标文件的递交 5.1电子投标文件递交时间：2026年8月26日14时30分（北京时间）前，投标人自行上传至重庆水务集团电子商务 平台(https://www.cqswjt.cn)； 5.2 纸质投标文件递交时间：2026年8月26日14时00分至14时30分，地点：水务集团招标采购中心（重庆市两江新 区嘉华路36号重庆水务大厦五楼。导航：重庆水务大厦东门）。 5.3 投标截止时间：2026年8月26日14时30分（北京时间）。 5.4 逾期送达的或者未送达指定地点的投标文件，比选人不予受理。 网 6.发布公告的媒介 本次比选公告在重庆水务集团电子商务平台(https://www.cqswjt.cn)上发布。 务 7.联系方式 比 选 人：重庆中法供水有限公司 比选代理机构：重庆水务集团公用工程咨询有限公司 地 址：重庆市渝北区悦来镇悦来水厂 地 址：重庆市两商江新区嘉华路36号重庆水务大厦10楼1018 联 系 人：陈老师 联 系 人：周洲 电 话：023-67585971 电 话：18602396399 道 重庆水务电子商务平台咨询电话：023-67453670（工作时间：9：00-12：30；14：00-17：00） 信息来源:https://www.chinapipe.net/project/d3074673.html 管 cqdingjiu 2026.08.21 10:06:59 国 中</t>
+          <t>邛崃经芦山至荥经高速公路项目邛崃段占压邛崃市天然气有限公司输气管道迁改工程设计比选公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3077596.html cqdingjiu 2026.08.24 12:31:53 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5127,14 +5139,14 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>四川, 设计比选公告</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>南岸区茶园片区乡镇老旧供水管网更新改造工程更正公告</t>
+          <t>自贡水务投资集团有限公司供水管道及设施防腐招采公告</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5159,53 +5171,57 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>自贡市</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>南岸区</t>
+          <t>自贡市</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>本项目比选范围修改为：在项目动工前完成水土保持方案审批程序，项目建设过程开展水土保持监管测工作。</t>
+          <t>钢管及设施防腐</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>最高限价80万元</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>供水管网</t>
+          <t>钢管及设施防腐</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>南岸区茶园片区乡镇老旧供水管网更新改造工程更正公告 南岸区茶园片区乡镇老旧供水管网更新改造工程更正公 告 发布日期： 2026年8月18日 网 首次公示日期： 2026年8月14日 更正日期： 2026年8月18日 采购人名称： 重庆市江南城市建设发展（集团）有限公司务 采购人地址： 重庆市南岸区米兰路51号电子信息标准化厂房2号楼 联系人： 赵老师 商 电话： 023-62820331 采购代理机构名称： 重庆多杰数字科技咨询服务有限公司 采购代理机构地址： 重庆市重庆市经开区重庆市经开区长生桥镇江峡路8号13-1幢1楼 道 经办人名称： 李佩奇、戴沛轩、李倩 联系电话： 023-67648437 本项目比选范围修改为：在项目动工前完成水土保持方案审批程序，项目建设过程开展 更正事项： 水土保持监管测工作。 https://www.gec123.com/notices/detail/1665701682723590144 信息来源:https://www.c国hinapipe.net/project/d3074669.html cqdingjiu 2026.08.21 10:07:01 中</t>
+          <t>自贡水务投资集团有限公司供水管道及设施防腐招采公告 自贡水务投资集团有限公司现对供水管道及设施防腐招采项目进行公开招采，现以公 告方式邀请符合本次招采要求的承包商参加招采，内容如下： 一、公告网址：自贡水务投资集团有限公司（http://www.zgwater.com） 二、项目名称：自贡水务投资集团有限公司供水管道及设施防腐招采项目 网 三、承包金额：最高限价80万元。 四、合同有效期限：贰年。 务 五、承包内容：钢管及设施防腐（见下表） 序号 项目名称 规格型号 单位 数量 商 三水厂部分 1 西部水厂管廊管道及加压站部分管道防腐 / ㎡ 500 2 钢制设施、 / ㎡ 6100 设备防腐 3 高新区景苑小区管道防腐 / ㎡ 55 道 4 长葫引水管道DN1200钢管防腐 DN1200 ㎡ 1380 5 一桥硬合厂宿舍侧DN400钢管防腐 DN400 ㎡ 16.5 6 一桥硬合厂宿舍侧DN300钢管防腐 DN300 ㎡ 14.15 管 合计 8065.65 六、中选承包商确定方式：采用最低价法，按总价最低原则确定1家为中选承包商。 国 七、承包商参加本次招采活动应具备的条件： 1、承包商营业执照经营范围须包含承包内容； 中 2、具有独立承担民事责任能力； 3、具有良好的商业信誉和健全的财务会计制度； 4、具有履行施工合同所必须的资金实力、施工专业团队和能力； 5、有依法缴纳税收和社会保障资金的良好记录； 6、参加国内招标等活动前三年内，在经营活动中没有重大违法记录； 7、本项目不接受联合体参加，单位负责人为同一人或存在控股、管理或存在其他利益关系的不同单位，不得同 时参加本次招采。 八、禁止参加本次招采活动的承包商 根据相关规定，拒绝列入失信被执行人名单、重大税收违法案件当事人名单、严重违法失信行为记录名单中的 承包商报名参加本次招采活动。 九、报名方式、时间、地点： 1、报名方式：现场报名、网上报名 1）现场报名：承包商将单位营业执照复印件、防水防腐保温工程专业承包贰级及以上资质证书、《授权委托 书》、经办人身份证复印件、《承包商报名登记表》（均加盖单位公章）交到四川省自贡市自流井区华商北 路199号华商.国际城30栋（自贡水务投资集团有限公司907室）。 2）网上报名：承包商将单位营业执照复印件、防水防腐保温工程专业承包贰级及以上资质证书、《授权委托 书》、经办人身份证复印件、《承包商报名登记表》扫描件（均加盖单位公章）发送至308896569@qq.com。 2、报名截止时间为：2026年8月28日。 3、招采承包文件免费获取，报名后招采资格不能转让。 备注：由承包商自行选择报名方式，招采人依据报名提交的资料收取响应文件。 网 十、递交响应文件截止时间：2026年9月9日上午12:00（北京时间）。 十一、递交响应文件地点：四川省自贡市自流井区华商北路199号华商.国际城30栋11-01号（自贡水务投资集团有 限公司907室，联系人：王文祥）。响应件必须在递交响应文件截止时间前送达招采地点。逾期送达、密封和标 务 注错误的响应文件，招采单位恕不接收。本次招采接收邮寄的响应文件。 十二、项目评审时间：由招采方自行确定时间组织评审。 十三、招采结果：招采结果会在响应文件递交截止时间后商的15个工作日之内在本网站公布。 十四、联系方式 1、招采人：自贡水务投资集团有限公司 道 2、地 址：四川省自贡市自流井区华商北路199号华商.国际城30栋11-01号（自贡水务投资集团有限公司907室） 3、联系人及电话：王文祥 0813-2203668 管 信息来源:https://www.chinapipe.net/project/d3077586.html cqdingjiu 2026.08.24 12:31:53 国 中</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>西部水厂管廊管道及加压站部分管道防腐 500㎡，钢制设施、设备防腐 6100㎡，高新区景苑小区管道防腐 55㎡，长葫引水管道DN1200钢管防腐 1380㎡，一桥硬合厂宿舍侧DN400钢管防腐 16.5㎡，一桥硬合厂宿舍侧DN300钢管防腐 14.15㎡</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 商机</t>
+          <t>重庆, 四川, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部排水钢管询价采购公告</t>
+          <t>四川省眉山市东坡区管道直饮水项目设计-施工总承包招标公告</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5215,7 +5231,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5230,49 +5246,57 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>眉山市</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>东坡区</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>中铁十一局集团宜涪高铁3标项目，位于重庆市石柱土家族自治县。合同金额28.01亿元，合同工期73个月，主要工程包括新方斗山隧道、石板坡隧道、城北隧道、刘家坪隧道、刘家店子1号大桥工程、刘家店子2号大桥、城北大桥、冉家湾大桥，采用移动模架和支商架法现浇施工，正线铺无砟道床43.808Km。</t>
+          <t>管道直饮水项目的具体内容未在提供的信息中明确列出。</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>合同金额28.01亿元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>排水钢管Φ200*6m</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部排水钢管询价采购公告 中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 排水钢管询价采购公告 询价编号：ZT1105-XJ-2026-561-1 尊敬的各潜在供应商: 网 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与中铁十一局集团有限公司宜涪高铁重庆段站 前3标项目经理ZT1105-XJ-2026-561-1，排水钢管材料的报价。 一、项目概况 务 中铁十一局集团宜涪高铁3标项目，位于重庆市石柱土家族自治（县）。合同金额28.01亿元，合同工期73个月， 开工日期：2024年12月，竣工日期：2030年12月。主要工程：新方斗山隧道(10660m)、石板坡隧道(4148m)、城北 隧道(3228m)、刘家坪隧道(2077m);刘家店子1号大桥工程(224.096m)、刘家店子2号大桥(232.099m)、城北大 桥(330.241m)、冉家湾大桥(355.245m),采用移动模架和支商架法现浇施工，其中24米移动模架施工6孔；32米支架法 施工5孔，移动模架施工28孔;正线铺无砟道床43.808Km。 二、询价内容 道 本次计划对排水钢管、GG-01材料进行询价，询价内容如下： 询价物资一览表 管 序号 包件号 物资名称 规格型号 计量单位 数量 备注 1 GG-01 排水钢管 Φ200*6m 米 3000 Q235B，壁厚6mm 合计 3000 国 说明：1.表中数量为计划数量，实际采购过程中可能有所调整，最终结算按照实际采购数量结算。 2.收货地点：中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 中 三、技术质量及报价要求 1. 此次排水钢管、GG-01各项技术性能：Q235B 碳素结构钢无缝钢管，符合 GB/T8163 标准。质量需满足甲方项 目部正常使用的要求，保证产品的质量合格，满足试验室检测所有要求，详见技术规格书。 2.报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、结算及付款方式 自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发票认证完成之日起第6个月，支付至本次结算 金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内，累计支付总额不超结算总金额的75%，剩 余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理末次结算后第二年，支付金额应大于等于 尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总额的15%；办理末次结算后第四年，全部 付清）。 五、报价人资格要求 1.营业范围要求：在中华人民共和国境内依法注册、符合项目经营范围，具有询价物资生产或供应经验 的生产商或代理商，并且具有合法有效的营业执照。 2.生产能力要求：生产商须具备询价物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定。代 理商需出具制造厂出具签字盖章的授权函。 3.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8 月至今）国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；需满足排水钢管的相关所 有要求。 4.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年12月至今）企业或企业法定代表人有人民法院生效判决、裁 定认定的行贿犯罪记录的。④ 对纳入国家铁路局“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接 受通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合 作方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 网 5.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 务 ★6.下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 六、报价人需要提供的资料 1.营业执照复印件、法人身份证复印件、开户许可证、授商权委托书、报价表和报价人资格要求中所需的证明资料， 所有资料需加盖公司鲜章。 2.生产厂家资质，产品质量检测报告等质量证明文件。 道 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、询价报名截止时间 管 有意参加本次询价采购的报价人须在铁建云链平台（https://www.crccep.cn）完成供应商注册，并于2026年8月18 日9时00分至2026年8月21日9时00分在网上完成报名工作。 八、询价截止时间 国 凡有意参加本次询价采购的报价人，请于 2026年8月21日14时00分 前提交报价。截止时间前未完成报价文件传 输的，视为放弃报价。 供应商报价必须严格按照《报价表》格式进行报价。 中 九、联系方式 采购组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村71号 采购人名称：中铁十一局集团有限公司宜涪高铁重庆段站前3标项目经理部 地址：重庆市石柱土家族自治县金彰工业园区C区中铁十一局项目部 联系人：罗先生 联系电话：18580400001（提供采购服务支持） 中铁十一局集团有限公司 物资设备集中采购管理中心第五分中心 2026年8月18日 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3074654.html cqdingjiu 2026.08.21 10:07:01 网 务 商 道 管 国 中</t>
+          <t>四川省眉山市东坡区管道直饮水项目设计-施工总承包招标公告 请复制此链接，粘贴到浏览器地址栏打 开：https://ctbpsp.com/#/bulletinDetail?uuid=2b2344f6-47c0-4eb0-b41a-c9909027f3b8 信息来源:https://www.chinapipe.net/project/d3077575.html cqdingjiu 2026.08.24 12:31:53 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>重庆, 排水钢管, 询价采购</t>
+          <t>分析, 重庆, 四川, 近三天, 管材, 招标, 商机</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>中铁建设集团(重庆)建设有限公司重庆协同创新区供冷供热能源站及配套系统工程冷却塔、分集水器、水板式热交换机组采购竞价补遗公告二</t>
+          <t>射洪市2026年高标准农田建设项目(复兴及潼射片区)-施工-1招标公告</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5282,7 +5306,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5297,29 +5321,37 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>遂宁市</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>射洪市</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>重庆协同创新区供冷供热能源站及配套系统工程冷却塔、分集水器、水板式热交换机组采购。</t>
+          <t>本项目包括新建及改建高标准农田，涉及田块整治工程、灌溉排水工程、田间道路工程、土壤改良、农田输配电工程、农田防护与生态保护工程。</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>项目资金来自中央投资、省级配套资金、县级配套资金，出资比例为100%。</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>冷却塔、分集水器、水板式热交换机组</t>
+          <t>高标准农田建设相关材料与设备</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>中铁建设集团(重庆)建设有限公司重庆协同创新区供冷供热能源站及配套系统工程冷却塔、分集水器、水板式热 交换机组采购竞价补遗公告二 各 投标单位 ： 根据参加报名的潜在投标单位数量不满足招标方充分竞价要求的情况，此次重庆协同创新区供冷供热能源站及 配套系统工程冷却塔、分集水器、水板式热交换机组采购竞价资格预审报名截止日期将延期至 8月19日（周三） 上午9:00。 特此说明。 网 中铁建设集团（重庆）建设有限公司 2026年8月17日 务 信息来源:https://www.chinapipe.net/project/d3074650.html cqdingjiu 2026.08.21 10:07:01 商 道 管 国 中</t>
+          <t>射洪市2026年高标准农田建设项目(复兴及潼射片区)-施工-1招标公告 1. 招标条件 1.1本招标项目射洪市2026年高标准农田建设项目（复兴及潼射片区）（项目名称）已由射洪市发展和改革局 （项目审批、核准或备案机关名称）以射洪市发展和改革局关于射洪市2026年高标准农田建设项目可行性研究报 告的批复（射发改发〔2025〕421号）（批文名称及编号）批准建设，项目业主为射洪市茂乾实业有限责任公司， 建设资金来自中央投资、省级配套资金、县级配套资金（资金来源），出资比例为100%，招标人为射洪市茂乾 实业有限责任公司。项目已具备招标条件，现对该项目的 / 施工进行公开招标。 网 1.2本招标项目为遂宁市行政区域内的国家投资工程建设项目，射洪市发展和改革局（核准机关名称）核准（招 标事项核准文号为射发改发〔2025〕421号）的招标组织形式为 委托招标。招标人选择的招标代理机构是四川 丰和工程管理有限公司。 务 2. 项目概况与招标范围 2.1 项目概况 2.1建设地点：复兴片区：金凤社区、大龙村、雷堂村、玉商贞村、观花村、金罐村、新桥村、红桂桥村、灵华村、 博古村、喻家沟村、九圣村；潼射片区：板桥沟村。 2.2规模：新建及改建高标准农田（含田块整冶工程、灌溉排水工程、田间道路工程、土壤改良、农田输配电工 程、农田防护与生态保护工程）。 道 2.3工期：270日历天。 2.4标段划分：复兴及潼射片区施工标段。_（简要说明本次招标项目的建设地点、规模、建设内容、计划工期、 管 标段划分等）。 2.2 招标范围 本项目工程量清单及图国纸范围所示的全部内容_（简要说明本次招标标段名称、招标范围与内容、合同计划工期 等）。 3. 投标人资格要求 中 3.1本次招标要求投标人须具备行政主管部门颁发的水利水电工程施工总承包贰级及以上资质，并在人员、设备、 资金等方面具有相应的施工能力。 3.2本次招标 不接受联合体投标。 3.3各投标人均可就上述合同标段中的1个(具体数量)合同标段投标。招标人不允许投标人拟派的同一批项目主要 人员（项目经理、技术负责人）在1个及以上标段任职。 4. 招标文件的获取 4.1 凡有意参加投标者，请于2026年08月22日00时00分至2026年09月13日17时00分开始登陆：全国公共资源交易 平台（四川省· 遂宁市）（网址：https://www.snsggzyjy.cn ）—“登录”—“遂宁市建设工程网上交易后台管理 系统”，通过数字证书免费下载招标资料（招标文件、技术资料等）（报名结束时间为2026年9月13日17时00 分）。 4.2 除上述方式外，招标人不提供其他任何报名和招标文件获取的方式。 5. 投标文件的递交 5.1投标文件递交的截止时间（投标截止时间，下同）为2026年09月14日09时30分，投标人应在投标截止时间前在 线递交经投标人数字证书加密的数据电文形式投标文件。 6. 发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）上发布。其他发布公告的媒介全国公共资源交易平台（四川 省·遂宁市）（招标人自行选择，也可不填）。 7. 本项目招标投标行政监督部门 行政监督部门：射洪市农业农村局电 话：0825-6681313 传 真：/ 电子邮件：/ 地 址：射洪市广寒路 网 8. 招标人承诺 本招标文件已经招标人（含招标代理机构）审查，不存在违反国家法律、法规、政策的情形。因招标文件设置 违反国家法律、法规、政策造成的相应后果，由招标人（含招标代理机构）负责。 务 9. 联系方式 招 标 人：射洪市茂乾实业有限责任公司招标代理机构：四川丰和工程管理有限公司 商 地 址：射洪市紫云文化公园B-6栋地 址：中国（四川）自由贸易试验区成都高新区益州大道中段722 号3栋1单元21楼2104号 邮 编：629200邮 编：610041 道 联 系 人：谭老师联 系 人：王女士 电 话：0825-6915636电 话：028-85251050 管 传 真：/ 传 真：/ 电子邮件：/电子邮件：/ 国 网 址：/网 址：/ 开户银行：/开户银行：中国银行雅安雨城区支行 中 账 号：/账 号 ：130737176102 信息来源:https://www.chinapipe.net/project/d3077563.html cqdingjiu 2026.08.24 12:31:54</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5332,14 +5364,14 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>重庆协同创新区, 供冷供热能源站, 冷却塔, 分集水器, 水板式热交换机组, 采购竞价</t>
+          <t>高标准农田, 新建及改建, 水利工程, 四川, 遂宁</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>城口县东安及河鱼片区污水管网建设项目(一期)招标计划表</t>
+          <t>盐边县城北片区和清源片区老旧街区改造项目施工一标段招标公告</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5364,53 +5396,57 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>攀枝花市</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>城口县</t>
+          <t>盐边县</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>在城口县东安镇新建一座污水处理站，铺设不同直径的污水管道共计29.3公里，包括dn110、dn160、dn200、DN300、DN400等规格的污水管道，以及DN200压力管道7.4公里，建设配套泵站2座和化粪池56座、隔油池32座。</t>
+          <t>对盐边县城北、清源片区老旧街区进行商提升改造，包括改造中环北路、西环北路、清河西路、盐中巷外立面排危改造约12.28万平方米，街区路面整治约12000平方米，街区雨污排水管网改造约10千米，改造适老化、适儿化服务用房约5000平方米，社区综合服务生活市场改造8500平方米，街区屋面防水改造约9900平方米，改造3500平方米街区边角地配套停车场及充电桩等基础设施，增设路灯280盏，公共活动健身区15处，街角口袋公园4处，改造清河西路、盐中巷街区安道全防护栏5公里，街区架空线入地4千米，弱电管网整治5千米，并同步完善消防、安防、垃圾收储、便民生活设施等配套公共服务设施。</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>合同预估金额为3400万元人民币。</t>
+          <t>项目总投资额：14500万元。</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>污水管网、泵站、化粪池、隔油池</t>
+          <t>市政公用工程施工总承包</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>城口县东安及河鱼片区污水管网建设项目(一期)招标计划表 重庆市工程建设项目招标计划表 项 名 目 称城口县东安及河鱼片区污水管网建设项目（一期） 招标 法人 或招 标人城口县生态环境局 名称 （盖 网 章） 项目 批准 文件 及文 号 主 建 内 要 设 容 在 污 城 水 口 处 县 理 东 站 安 1座 镇 ， 等 改 片 建 区 后 新 设 建 计 污 规 水 模 管 20 网 0m 29 3 . / 0 d 0 。 km，其中新建dn110污水管5.80km，dn160污水管2.75km，dn200污水管0.57km，DN300污水干管4.36km，D 务 N400污水干管8.12km，DN200压力管7.4km,以及建设配套泵站2座,化粪池56座，隔油池32座。改扩建 序号 招标项目名称 招标内容 招标方式 招标文件计划发布时间 拟交易场所 合同预估金额(万元) 备注 招 项 标 目1 城 建 口 设 县 项 东 目 安 （ 及 一 河 期 鱼 ） 片区污水管网 工程施工 公开招标 2026-09 城 易 口 中 县 心 公共资源交 3400.00 本 暂 为 计 定 准 划 ， 。 表 最 所 终 列 以 招 实 标 际 项 招 目 标 信 时 息 的 均 信 为 息 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3074602.html 商 cqdingjiu 2026.08.21 10:07:01 道 管 国 中</t>
+          <t>盐边县城北片区和清源片区老旧街区改造项目施工一标段招标公告 1. 招标条件 1.1本招标项目盐边县城北片区和清源片区老旧街区改造项目(项目名称)已由盐边县发展和改革局(项目 审批、核准或备案机关名称)以关于盐边县城北片区和清源片区老旧街区改造项目可行性研究报告的批复、盐边 发改〔2025〕301号（批文名称及编号）批准建设，项目业主为盐边发展（集团）有限责任公司，建设资金来自 争取上级资金及业主自筹（资金来源），项目出资比例为 100% ，招标人为盐边发展（集团）有限责任公司。 项目已具备招标条件，现对该项目的施工进行公开招标。 网 1.2本招标项目由盐边县发展和改革局 （核准机关名称）核准（招标事项核准文号为盐边发改〔2025〕301号） 的招标组织形式为委托招标（□自行招标委托招标）。招标人选择的招标代理机构是四川骏浩达工程项目管 理有限公司。 务 2. 项目概况与招标范围 2.1 建设地点：盐边县城北片区和清源片区。 2.2 项目规模：拟对盐边县城北、清源片区老旧街区进行商提升改造，包括改造中环北路、西环北路、清河西路、 盐中巷外立面排危改造约12.28万平方米，街区路面整治约12000平方米，街区雨污排水管网改造约10千米，改造 适老化、适儿化服务用房约5000平方米，社区综合服务生活市场改造8500平方米，街区屋面防水改造约9900平方 米，改造3500平方米街区边角地配套停车场及充电桩等基础设施，增设路灯280盏，公共活动健身区15处，街角 口袋公园4处，改造清河西路、盐中巷街区安道全防护栏5公里，街区架空线入地4千米，弱电管网整治5千米，并同 步完善消防、安防、垃圾收储、便民生活设施等配套公共服务设施。 本项目一标段建设内容：对盐边县城北片区中环北路周边房屋外立面排危改造，进行污水管网、雨水管网、局 部给水管网、绿化改造，飞线整治、社区综合服务生活市场改造，并同步完善消防、安防、垃圾收储、便民生 管 活设施等配套公共服务设施。 2.3 项目总投资额：14500万元。 2.4 计划工期：180日历国天。 2.5 招标范围：包括但不限于施工图纸（含变更）和相应工程量清单中的全部工程内容及竣工验收合格及整体 移交、工程保修期内的缺陷修复和保修工作等内容。 中 2.6 标段划分：施工1个标段。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质条件：具有独立法人资格；具有建设行政主管部门颁发的市政公用工程施工总承包二级及以上资质；具 有有效的安全生产许可证。 3.1.2业绩要求： 近年（ 2021 年 1 月 1 日至投标截止时间，不少于3年）（□已完成已完成或新承接或正在施工） 不少于 1 （1至3个）个类似项目。类似项目是指:单项合同金额不低于2000万元的市政工程类项目施工业绩。 □无业绩要求。 3.1.3项目经理的资格要求： 项目经理（项目负责人）资格：市政公用工程 (注册专业)二级及以上（级别）建造师，具有省级及以上住房 城乡建设主管部门颁发的安全生产考核合格证（B证）， / （业绩要求），须为本单位人员（若为联合 体投标，须为联合体牵头人人员）。 □园林绿化工程项目经理（项目负责人）资格： / （职称级别）专业技术职称， / （业绩要 求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受不接受联合体投标。联合体投标的，应满足下列要求： / 。 3.3各投标人均可就上述 1 (具体数量)标段投标。 3.4本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东网为大企业、与大企业的负责 人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体 标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通 知》（工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术 复杂、存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在3000万元以下的施工项目(标段)应勾 务 选此项。） 4. 招标文件的获取 4.1凡有意参加投标者，请于 2026 年 8 月 22 日开始登陆商：□全国公共资源交易平台（四川省） （网址：http://ggzyjy.sc.gov.cn）—“登录”——“交易主体”—“建设工程”，通过数字证书免费下载招标资料 （招标文件、技术资料等）。全国公共资源交易平台（四川省· 攀枝花 市（州））（网 址： http://ggzy.panzhihua.gov.cn/ ）—“登录”—“ 建设工程 ”，通过数字证书免费下载招标资料（招标 文件、技术资料等）。 道 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 管 投标文件递交的截止时间（投标截止时间，下同）为 2026 年 9 月 14 日 9 时 30分，投标人应在投 标截止时间前在线递交经投标人数字证书加密的数据电文形式投标文件。 6. 发布公告的媒介 国 本次招标公告在《全国公共资源交易平台（四川省）》和全国公共资源交易平台（四川省.攀枝花 市） (公告发布的其它媒介名称）上发布。 中 7. 行政监督部门 单位名称：盐边县住房和城乡建设局 联系电话：0812-8653726 8. 联系方式 招 标 人：盐边发展（集团）有限责任公司 地 址：四川省盐边县新九镇盐边钒钛产业开发区钛兴南路1号 邮 编：617100 联 系 人：任老师 电 话：0812-8655576 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / □ 招标代理机构： / 招标代理机构：四川骏浩达工程项目管理有限公司 网 地 址：四川省攀枝花市盐边县桐子林镇中环南路146号 邮 编：617100 务 联 系 人：袁溢龙 项目负责人：袁溢龙 商 电 话：0812-8655535 传 真： / 道 电子邮件： / 网 址： / 管 开户银行： / 账 号： / 国 中 2026 年 8 月 21 日 注： （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不得 作为资质要求。 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工程 相应指标，类似项目业绩的定义应明确，用语准确无歧义。 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受投 标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 信息来源:https://www.chinapipe.net/project/d3077560.html cqdingjiu 2026.08.24 12:31:54 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>dn110污水管：5.80km；dn160污水管：2.75km；dn200污水管：0.57km；DN200压力管：7.4km；泵站：2座</t>
+          <t>雨污排水管网：10千米；弱电管网：5千米</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>重庆, 四川, 管材, 招标</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>阀门产业园(管网改造)项目招标公告</t>
+          <t>川东北现代农业融合发展示范园项目设计施工总承包招标公告</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5435,29 +5471,37 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>南充市</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>南充市</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>场平面积800亩；新建厂房10000平方米，并完善相关基础配套设施等；新建道路长4000米，包括道路、综合管网等基础配套设施等。</t>
+          <t>本项目总占地面积为149道225.64平方米，总建筑面积151550.12平方米，其中新建标准化厂房143913平方米、综合管理用房7637.12平方米，配套建设配套厂区道路、停车场、绿化工程、污水管网、给水管网、强弱电工程等配套工程。</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>本项目工程总投资金额：55000万元 本次招标项目合同估算金额：184.669075万元</t>
+          <t>项目总投资36633万元</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>土石方开挖回填、砼支墩、污水管道安装、检查井砌筑、河堤修复等</t>
+          <t>设计施工总承包</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>阀门产业园(管网改造)项目招标公告 阀门产业园（管网改造）项目招标公告 1.招标条件 本招标项目 阀门产业园（管网改造）项目已由垫江县发展和改革委员会以垫江发改委发【2022】459 号（批文 名称及编号）批准建设，项目业主为 垫江县丹香建设有限公司，建设资金来自 自筹资金 （资金来源）， 项目出资比例为 100% ，招标人为 垫江县丹香建设有限公司。项目已具备招标条件，现对该项目的施工进 行公开招标，评标办法采用经评审的最低投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 重庆市垫江县高新区县城组团 2.2 项目概况与建设规模： 场平面积800亩；新建厂房10000平方米，并完善相关基础配套设施等；新建道路 务 长4000米，包括道路、综合管网等基础配套设施等。 2.3 本项目工程总投资金额：55000万元 本次招标项目合同估算金额：184.669075万元 商 2.4 招标范围： 包括土石方开挖回填、砼支墩、污水管道安装、检查井砌筑、河堤修复等。具体详见施工图和 工程量清单。 道 2.5 工期要求：建设工期180日历天 缺陷责任期要求：24个月 管 2.6 标段划分（如有）： / 2.7 其他： / 3.政府采购工程 国 3.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 中 4.1.1 本次招标要求投标人具备的资质条件： 具备建设行政主管部门颁发的有效的市政公用工程施工总承包叁 级及以上资质 ； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标 不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （垫江县）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（垫江县）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资 源交易监督网、重庆市公共资源交易网（垫江县）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 4.2投标人可在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）本项目招标公告网页下方“我要 提问”栏提出疑问，提问时间从本公告发布至2026-08-24 09:00:00前。 4.3招标人应于2026-08-24 23:59:59前在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-18 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（垫江县）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 招 标 人: 垫江县丹香建设有限公司 代理机构: 重庆博钰大数据科技有限公司 地 址: 地 址: 重庆市垫江县桂溪街道南内街88号 网 邮 编: 邮 编: 项目负责人: 熊老师 项目负责人: 郭威 电 话: 023-74630098 电 话: 023-74692498 务 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 商 账 号: 账 号: 监督部门: 垫江县发展和改革委员会 电 话: 023-74517161 道 2026年08月18日 信息来源:https://www.chinapipe.net/project/d3074578.html cqdingjiu 2026.08.21 10:07:02 管 国 中</t>
+          <t>川东北现代农业融合发展示范园项目设计施工总承包招标公告 1. 招标条件 1.1本招标项目川东北现代农业融合发展示范园项目(项目名称)已由西充县发展和改革局(项目审批、核准或备 案机关名称)以川投资备【2605-511325-04-01-291937】FGQB-0492 号（批文名称及编号）批准建设，项目业主为 西充县德恒建设开发有限责任公司， 建设资金来自企业自筹、银行贷款以及东西部协作资金（资金来源），项 目出资比例为100%，招标人为西充县德恒建设开发有限责任公司。项目已具备招标条件，现对该项目的设计施 工总承包进行公开招标。 网 1.2本招标项目由西充县发展和改革局（核准机关名称）核准（招标事项核准文号为川投资备 【2605-511325-04-01-291937】FGQB-0492 号）的招标组织形式为委托招标。 招标人选择的招标代理机构是四川云 霓工程管理咨询有限公司。 务 2. 项目概况与招标范围 2.1 项目名称：川东北现代农业融合发展示范园项目。 商 2.2建设地点：南充市临江新区西充片区。 2.3建设内容及规模：本项目总占地面积为149道225.64平方米，总建筑面积151550.12平方米，其中新建标准化厂 房143913平方米、综合管理用房7637.12平方米，配套建设配套厂区道路、停车场、绿化工程、污水管网、给水管 网、强弱电工程等配套工程。 2.4计划工期：720日历天。 管 2.5招标范围：本项目设计内容包括但不限于:施工图设计及设计经济测算(含总体投资、清单预算编制等)工作以 及后续配合服务。本项目施工内容包括但不限于:本工程的全部施工设计图纸所表达的范围，项目整体交付以及 竣工验收合格后工程缺陷责任期内的缺陷修复和工程保修等相关工作。 国 2.6标段划分：设计施工总承包1个标段。 2.7标段投资额：项目总投资36633万元。 中 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质要求：设计资质要求：具备独立法人资格，具备建设行政主管部门颁发的建筑行业（建筑工程）设计 专业乙级及以上资质；施工资质要求：具备独立法人资格，具备建设行政主管部门颁发的建筑工程施工总承包 二级及以上资质，施工单位须具备有效的安全生产许可证。 3.1.2业绩要求：（本项为多选） □ 设计业绩要求：近年（ 年 月 日 至投标截止时间，不少于3年） 不少 于 （1 至3个）个类似项目。类似项目是指: 。 □ 施工业绩要求：近年（ 年 月 日 至投标截止时间，不少于3年） 不少 于 （1 至3个）个类似项目。类似项目是指: 。 无业绩要求。 3.1.3项目经理的资格要求：具有建筑工程专业二级及以上注册建造师证书□ 由设计负责人兼任由施工负 责人兼任，/（业绩要求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.1.4设计负责人的资格要求：具有二级及以上注册建筑师证书，须为投标人本单位人员。 3.1.5施工负责人（建造师，下同）的资格要求：具有建筑工程专业二级及以上注册建造师证书(注册专业)（级 别）建造师，具有省级及以上住房城乡建设主管部门颁发的安全生产考核合格证（B证），须为投标人本单位人 员。 3.2本次招标接受联合体投标。联合体投标的，联合体牵头人应为 □ 设计单位施工单位，同时满足下列要求： ①联合体成员须具有独立法人资格或有效的营业执照，②组成联合体的成员不得超过3家；③联合体各方应签订 联合体协议书，明确联合体牵头人和各方权利义务，并由联合体各方向招标人承担连带责任；④组成联合体投 标应符合相关法律法规对联合体投标的有关规定，联合体各方不得再以自己名义单独或参加其他联合体在同一 工程项目中投标；⑤联合体牵头人负责本项目递交投标文件、缴纳投标保证金等网相关事宜。 □ 3.3 本次招标范围中施工部分的工作仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大 企业、与大企业的负责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，本项目联合体协议书 中职责分工为承揽施工工作的所有单位均应属于中小企业）。具体标准以《工业和信息化部、国家统计局、国 务 家发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业〔2011〕300号）中 的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、存在特殊要求外，我市依法必须 招标的国家投资工程，施工部分招标控制价在8000万元以下3000万元以上的，原则上勾选此项。） 商 □ 3.4 本次招标范围中施工部分的工作仅面向小微企业发包（其中属于大、中企业的分支机构、存在控股股东 为大、中企业、与大、中企业的负责人为同一人的情形的企业均不属于小微企业。若为联合体投标的，本项目 联合体协议书中职责分工为承揽施工工作的所有单位均应属于小微企业）。具体标准以《工业和信息化部、国 家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业 〔2011〕300号）中的“建筑业”划型标准为准道，投标人应提供小微企业声明函。（除技术复杂、存在特殊要求 外，我市依法必须招标的国家投资工程，施工部分招标控制价在3000万元及以下的，原则上勾选此项。） 4. 招标文件的获取 管 4.1 凡有意参加投标者，请于 2026年08月22日 00时00分 开始，登录全国公共资源交易平台（四川省）（网 址：http://ggzyjy.sc.gov.cn）-&gt;交易平台入口-&gt;南充市-&gt;南充交易系统-建设网、或登录《四川建设网》 （http://www.sccin.com）-&gt;电子招标-&gt;南充市公共资源交易平台登录入口，投标人凭单位CA数字证书（包括但 不限于CFCA、四川CA、重庆CA、天威诚信等）登录，免费获取招标文件（联系电话：028-85569858）。 国 4.2 除上述方式外，招标人不提供其他任何报名和招标文件获取的方式。 5. 投标文件的递交 中 5.1 投标文件递交的截止时间（投标截止时间，下同）为 2026年09月11日 09时10分 ，投标人应在投标截止时间 前，登录全国公共资源交易平台（四川省）（网址：http://ggzyjy.sc.gov.cn）-&gt;交易平台入口-&gt;南充市-&gt;南充交易 系统-建设网、或登录《四川建设网》（http://www.sccin.com）-&gt;电子招标-&gt;南充市公共资源交易平台登录入口， 凭单位CA数字证书登录，在线递交经投标人数字证书签名制作的数据加密电子投标文件。开标地点为：南充市 公共资源交易服务中心（南充市涪江路19号五楼）本项目开标室。 5.2 逾期送达的或者未送达指定地点的投标文件，招标人不予受理。 6. 发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省）》和四川建设网(公告发布的其它媒介名称）上发布。 7. 行政监督部门 单位名称：西充县住房和城乡建设局 联系电话：0817-4222761 8. 联系方式 □ 招标代理机构： / 招标代理机构：四川云霓工程管理咨询有 招 标 人：西充县德恒建设开发有限责任公司 限公司 地 址：四川省南充市西充县南台街道城南新区数字西充城市超 地 址：成都市武侯区西部智谷D区4 脑三楼303室 栋1单元502号 邮 编：637200 邮 编：610000 联 系 人：张先生 联 系 人：周女士 电 话：0817-8050003 项目负责人：潘云霄 传 真：/ 电 话：028-87776867 电子邮件：/ 传 真：/ 网 址：/ 电子邮件：网/ 开户银行：/ 网 址：/ 账 号：/ 开户银行：/ 账 号：/ 务 商 注： （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家道对投标人资质的强制性规定。不是国家规定必须具备的资质，不 得作为资质要求。 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工 程相应指标，类似项目业绩的定义应明确，用语准确无歧义。 管 （4）招标人限定的联合体成员数量不得少于设定的资质个数。 信息来源:https://www.chinapipe.net/project/d3077557.html 国 cqdingjiu 2026.08.24 12:31:54 中</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5470,7 +5514,2099 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>重庆, 管网改造, 投资金额, 产品种类</t>
+          <t>现代农业融合发展示范园项目, 设计施工总承包, 四川, 南充市, 西充片区, 36633万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>广元市朝天区污水管网提升改造项目(六标段)施工招标公告</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>朝天区</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>中子镇转斗（含何家坝）、校场坝生活污商水处理站覆盖范围内的排水管网更新改造以及检查井等附属设施建设。</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>项目估算总投资10498.09万元，资金来源为争取上级资金及地方政府配套资金。</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>排水管网更新改造及附属设施建设</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>广元市朝天区污水管网提升改造项目(六标段)施工招标公告 1. 招标条件 1.1本招标项目广元市朝天区污水管网提升改造项目(项目名称)已由 广元市朝天区发展和改革局(项目审批、核 准或备案机关名称)以 广朝发改项目[2024]108号 （批文名称及编号）批准建设，项目业主为 广元市朝天区 城市建设开发有限责任公司 ，建设资金来自争取上级资金及地方政府配套资金（资金来源），项目出资比例 为 100% ，招标人为广元市朝天区城市建设开发有限责任公司 。项目已具备招标条件，现对该项目的施 工进行公开招标。 网 1.2本招标项目由 广元市朝天区发展和改革局 （核准机关名称）核准（招标事项核准文号为 广朝发改项 目[2024]108号 ）的招标组织形式为 委托招标（□自行招标 委托招标）。招标人选择的招标代理机构 是 中科标禾工程项目管理有限公司 。 务 2. 项目概况与招标范围 2.1 建设地点：朝天区中子镇（转斗、校场坝） 。 2.2 建设规模： 中子镇转斗（含何家坝）、校场坝生活污商水处理站覆盖范围内的排水管网更新改造以及检查 井等附属设施建设 。 2.3 计划投资及资金来源：项目估算总投资 10498.09万元。资金来源为争取上级资金及地方政府配套资金 。 道 2.4 计划工期： 240日历天 。 2.5 招标范围：本项目施工图纸及清单范围内所包含的全部工作内容的施工。 管 2.6 标段划分：施工1个标段。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 国 3. 投标人资格要求 3.1 本次招标要求投标人须具备： 中 3.1.1 资质条件：具备独立企业法人资格，具备建设行政主管部门颁发的 市政公用工程施工总承包三级及以上资质（须具备有效的安全生产许可证）。 3.1.2 业绩要求： □近年（ 年 月 日至投标截止时间，不少于 3 年）（多项选择： □已完成□已完成或 新承接或正在施工）不少于 （ 1 至 3 个）个类似项目。类似项目是 指: 。 无业绩要求。 3.1.3 项目经理的资格要求： 项目经理（项目负责人）资格： 市政公用工程(注册专业)二级及以上(级别)建造师，具有省级及以上住房城 乡建设主管部门颁发的安全生产考核合格证（B 证），/ （业绩要求） ，须为本单位人员（若为联合体投 标，须为联合体牵头人人员）。 □园林绿化工程项目经理（项目负责人）资格： （职称级别）专业技术职称， （业绩要求） ，须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。3.3 各投标人均可就上 述 1个 (具体数量)标段投标 。 3.4 本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企业、与大企业的负 责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具 体标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的 通知》（工信部联企业〔2011〕300 号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除 技术复杂、存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在 3000万元以下的施工项目 (标 段) 应勾选此项。） 4. 招标文件的获取 网 4.1 凡有意参加投标者，请于 2026年08月22日开始登录：全国公共资源交易平台（四川省 · 广元市）（网 址： http://www.gyggzyjy.cn/）—“电子交易平台”，通过数字证书免费下载招标资料（招标文件、技术资料 等）。 务 4.2 招标人不提供招标文件获取的其他方式。 商 5.投标文件的递交 道 投标文件递交的截止时间（投标截止时间，下同）为 2026 年09月11日 09时00 分，投标人应在投 标截止时间前在线递交经投标人数字证书加密的数据电文形式投标文件。 6. 发布公告的媒介 管 本次招标公告在《全国公共资源交易平台（四川省）》和全国公共资源交易平台（四川省广元市）上发布。 7.行政监督部门 国 单位名称： 广元市朝天区住房和城乡建设局 联系电话：0839-8622102 中 8. 联系方式 招 标 人：广元市朝天区城市建设开发有限责任公司 地 址：广元市朝天区朝天镇潜溪路一段 邮 编：628012 联 系 人： 刘先生（异议联系人） 电 话： 18398751706 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / 招标代理机构：中科标禾工程项目管理有限公司 地 址： 成都市锦江区锦东路668号国嘉新视界14楼 邮 编： 610065 联 系 人： 吴老师 项目负责人： 王旭波 电 话： 028-86618391 传 真： / 网 电子邮件： / 网 址： / 务 开户银行： / 账 号： / 商 信息来源:https://www.chinapipe.net/project/d3077552.html 道 cqdingjiu 2026.08.24 12:31:54 管 国 中</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>80</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>污水管网, 提升改造, 排水管网, 更新改造, 检查井, 市政公用工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目(一期)施工招标公告</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>苍溪县</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>新改建管道:DN300污水管道162m、DN500 污水管道1884m、DN600 污水管道112m、DN300 雨水管道466.50m、DN600 雨水管道609m、 DN800 雨水管商道 390m、 DN1000 雨水管道1029m。并对涉及破损路面及配套设施等进行恢复。</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>项目业主为苍溪县城市管网事务中心，建设资金来自争取上级财政资金和地方自筹（资金来源），项目出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>DN300、DN500、DN600、DN800、DN1000 污水管道和雨水管道</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目(一期)施工招标公告 1. 招标条件 1.1本招标项目苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目（一期）(项目名称)已由苍溪 县发展和改革局(项目审批、核准或备案机关名称)以苍发改投资[2025]135号（批文名称及编号）批准建设，项目 业主为苍溪县城市管网事务中心，建设资金来自争取上级财政资金和地方自筹（资金来源），项目出资比例 为100%，招标人为苍溪县城市管网事务中心。项目已具备招标条件，现对该项目的施工进行公开招标。 1.2本招标项目由苍溪县发展和改革局（核准机关名称）核准（招标事项核准文网号为苍发改投资[2025]135号）的 招标组织形式为委托招标（□自行招标 委托招标）。招标人选择的招标代理机构是四川伟瑞项目管理有限公 司。 2. 项目概况与招标范围 务 2.1建设地点：陵江镇、百利镇。 2.2建设内容及规模：新改建管道:DN300污水管道162m、DN500 污水管道1884m、DN600 污水管道112m、DN300 雨水管道466.50m、DN600 雨水管道609m、 DN800 雨水管商道 390m、 DN1000 雨水管道1029m。并对涉及破损路面 及配套设施等进行恢复。 2.3工期：300日历天。 道 2.4招标范围： 工程量清单及图纸所示全部内容。 2.5标段划分： 一个标段。 管 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人国须具备 3.1.1资质条件：具备独立法人资格，具备国家行政主管部门颁发的市政公用工程施工总承包三级及以上资质（须 具备有效的安全生产许可证）。 中 3.1.2业绩要求： □近年（ 年 月 日至投标截止时间，不少于3年）（多项选择：□已完成 □已完成或新承接或正在 施工）不少于 （1 至3个）个类似项目。类似项目是指: 。 无业绩要求。 3.1.3项目经理的资格要求： 项目经理（项目负责人）资格：市政公用工程(注册专业)贰级及以上（级别）建造师，具有省级及以上住房城 乡建设主管部门颁发的安全生产考核合格证（B证）， （业绩要求） ，须为本单位人员（若为联合 体投标，须为联合体牵头人人员）。 □园林绿化工程项目经理（项目负责人）资格： （职称级别）专业技术职称， （业绩 要求） ，须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： 。 3.3各投标人均可就上述 1个 (具体数量)标段投标 。 □ 3.4本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企业、与大企业的负责 人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体 标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通 知》（工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术 复杂、存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在3000万元以下的施工项目(标段) 应勾 选此项。） 4. 招标文件的获取 4.1 凡有意参加投标者，请于2026年8月22日0时0分开始登录：全国公共资源交易平台（四川省·广元市） （网址：http://www.gyggzyjy.cn/）—“电子交易平台”，通过数字证书免费下载招标资料（招标文件、技术资料 等）。 4.2 招标人不提供招标文件获取的其他方式。 网 5. 投标文件的递交 投标文件递交的截止时间（投标截止时间，下同）为2026年9月18日09时30分，投标人应在投标截止时间前在线 务 递交经投标人数字证书加密的数据电文形式投标文件。 6. 发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省）》商和《全国公共资源交易平台（四川省.广元 市）》(公告发布的其它媒介名称）上发布。 7. 行政监督部门 道 行政监督部门:苍溪县住房和城乡建设局 联系电话0839-5222082 管 8. 联系方式 招 标 人：苍溪县城市国管网事务中心 地 址：苍溪县陵江镇嘉陵路西段72号 邮 编：/ 中 联 系 人：马先生（异议受理） 电 话：0839-2320019 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / 招标代理机构：四川伟瑞项目管理有限公司 地 址：四川省成都市金牛区金府路593号7栋12层9号 邮 编：610036 联 系 人：谢先生 电 话：028-62812735 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / 网 信息来源:https://www.chinapipe.net/project/d3077551.html 务 cqdingjiu 2026.08.24 12:31:54 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>排水和雨水排放</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>80</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>苍溪县, 污水管网改造, 延伸覆盖, DN300, DN500, DN600, DN800, DN1000, 雨水管道, 污水管道</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>广元市朝天区污水管网提升改造项目(五标段)施工招标公告</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>朝天区</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>本项目管网部分为新建排水主管网长度约2.08km（雨水管网约0.88km，污水管网约1.2km），管径DN300～DN800；现状管道清淤疏通长度约为1.23km；配套建设检查井等附属构筑物以及路面恢复提升；道路部分为埋地排水管道施工路面破除与恢复，同时对设计范围内其他道路进行路面黑化提升，项目共涉及7条道路的路面改造，其中车行道改造面积约9188平方米，人行道改造约3295平方米。</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>项目估算总投资10498.09万元，资金来源为争取上级资金及地方政府配套资金。</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>排水主管网、雨水管网、污水管网、检查井、路面恢复提升材料</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>广元市朝天区污水管网提升改造项目(五标段)施工招标公告 1. 招标条件 1.1本招标项目广元市朝天区污水管网提升改造项目(项目名称)已由 广元市朝天区发展和改革局(项目审批、核 准或备案机关名称)以 广朝发改项目[2024]108号 （批文名称及编号）批准建设，项目业主为 广元市朝天区 城市建设开发有限责任公司 ，建设资金来自争取上级资金及地方政府配套资金（资金来源），项目出资比例 为 100% ，招标人为广元市朝天区城市建设开发有限责任公司 。项目已具备招标条件，现对该项目的施 工进行公开招标。 网 1.2本招标项目由 广元市朝天区发展和改革局 （核准机关名称）核准（招标事项核准文号为 广朝发改项 目[2024]108号 ）的招标组织形式为 委托招标（□自行招标 委托招标）。招标人选择的招标代理机构 是 中科标禾工程项目管理有限公司 。 务 2. 项目概况与招标范围 2.1 建设地点：朝天区水磨沟镇 。 2.2 建设规模：本项目管网部分为新建排水主管网长度约商为2.08km （雨水管网约0.88km，污水管网约1.2km），管 径DN300～DN800；现状管道清淤疏通长度约为1.23km；配套建设检查井等附属构筑物以及路面恢复提升；道路 部分为埋地排水管道施工路面破除与恢复，同时对设计范围内其他道路进行路面黑化提升，项目共涉及7条道路 的路面改造，其中车行道改造面积约9188平方米，人行道改造约3295平方米。 道 2.3 计划投资及资金来源：项目估算总投资 10498.09万元。资金来源为争取上级资金及地方政府配套资金 。 2.4 计划工期： 240日历天 。 管 2.5 招标范围：本项目施工图纸及清单范围内所包含的全部工作内容的施工。 2.6 标段划分：施工1个标段。 （说明本次招标项目的国建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 中 3.1 本次招标要求投标人须具备： 3.1.1 资质条件：具备独立企业法人资格，具备建设行政主管部门颁发的 市政公用工程施工总承包三级及以上资质（须具备有效的安全生产许可证）。3.1.2 业绩要求： □近年（ 年 月 日至投标截止时间，不少于 3 年）（多项选择： □已完成□已完成或 新承接或正在施工）不少于 （ 1 至 3 个）个类似项目。类似项目是 指: 。 无业绩要求。 3.1.3 项目经理的资格要求： 项目经理（项目负责人）资格： 市政公用工程(注册专业)二级及以上(级别)建造师，具有省级及以上住房城 乡建设主管部门颁发的安全生产考核合格证（B 证），/ （业绩要求） ，须为本单位人员（若为联合体投 标，须为联合体牵头人人员）。 □园林绿化工程项目经理（项目负责人）资格： （职称级别）专业技术职称， （业绩要求） ，须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。3.3 各投标人均可就上 述 1个 (具体数量)标段投标 。 3.4 本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企业、与大企业的负 责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具 体标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的 通知》（工信部联企业〔2011〕300 号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除 技术复杂、存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在 3000万元以下的施工项目 (标 段) 应勾选此项。） 4. 招标文件的获取 网 4.1 凡有意参加投标者，请于 2026年08月22日开始登录：全国公共资源交易平台（四川省 · 广元市）（网 址： http://www.gyggzyjy.cn/）—“电子交易平台”，通过数字证书免费下载招标资料（招标文件、技术资料 等）。 务 4.2 招标人不提供招标文件获取的其他方式。 1. 投标文件的递交 商 投标文件递交的截止时间（投标截止时间，下同）为 2026年09月11日 09时00 分，投标人应在投标 截止时间前在线递交经投标人数字证书加密的数据电文形式投标文件。 6. 发布公告的媒介 道 本次招标公告在《全国公共资源交易平台（四川省）》和全国公共资源交易平台（四川省广元市）上发 布。 管 7.行政监督部门 单位名称： 广元市朝天区住房和城乡建设局 联系电话：0839国-8622102 8. 联系方式 中 招 标 人：广元市朝天区城市建设开发有限责任公司 地 址：广元市朝天区朝天镇潜溪路一段 邮 编：628012 联 系 人： 刘先生（异议联系人） 电 话： 18398751706 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / 招标代理机构：中科标禾工程项目管理有限公司 地 址： 成都市锦江区锦东路668号国嘉新视界14楼 邮 编： 610065 联 系 人： 吴老师 项目负责人： 王旭波 电 话： 028-86618391 传 真： / 电子邮件： / 网 网 址： / 开户银行： / 务 账 号： / 信息来源:https://www.chinapipe.net/project/d3077550.html 商 cqdingjiu 2026.08.24 12:31:54 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>排水主管网 Φ300~Φ800mm 约2.08km；雨水管网 Φ300~Φ800mm 约0.88km；污水管网 Φ300~Φ800mm 约1.2km；现状管道清淤疏通长度约1.23km；配套建设检查井等附属构筑物；路面恢复提升材料，车行道改造面积约9188平方米，人行道改造约3295平方米。</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>80</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>排水管网, 提升改造, 市政工程, 污水处理, 路面修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>四川省犍为第一中学扩建项目施工招标计划</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>房建</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>乐山市</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>犍为县</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>新建教学综合楼14500㎡、学生宿舍8500㎡、食堂3000㎡，以及附属用房、排水管网等配套基础设施。</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>估算总投资100000000.00元</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>房屋建筑</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>四川省犍为第一中学扩建项目施工招标计划 犍为县发展和改革局关于《四川省犍 为第一中学扩建项目可行性研究报告 项目批准文件及文号 招标项目名称 四川省犍为第一中学扩建项目施工 （代项目建议书）》的批复(犍发改项 （如有） 目审〔2025〕248号)(犍发改项目审 〔2025〕248号) 招标人 四川省犍为第一中学 联系人及联系方式 杨先生:0833-4266336 估算总投资 100000000.00 项目分类 房屋建网筑工程 （元） 项目占地约42.7亩。新建教学综合楼14500㎡、学生宿舍8500㎡、食堂3000㎡，以及附属用房、排 招标项目概况 水管网等配套基础设施。 务 序号 招标内容 投标人主要资格条件要求 预计招标时间 拟招标内容 1 施工 / 2026-09-21 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 商 信息来源:https://www.chinapipe.net/project/d3077548.html cqdingjiu 2026.08.24 12:31:55 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>80</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>扩建项目, 施工招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>大英县润民供水有限公司2026年PE供水管材管件采购(第二次)竞争性磋商公告</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>遂宁市</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>大英县</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>采购PE供水管材管件</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>PE供水管材管件</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>大英县润民供水有限公司2026年PE供水管材管件采购(第二次)竞争性磋商公告 详见附件 信息来源:https://www.chinapipe.net/project/d3077526.html cqdingjiu 2026.08.24 12:31:55 网 务 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>PE供水管材管件, 四川</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>XD-24039-GS-UPVC管材、管件、阀门采购询比采购公告</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>郫都区</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>项目名称：2024年度成都&amp;绵阳区域洁净工程维修改造项目D标段；项目地点：四川省成都市郫都区；品牌范围：环琪、协羽。</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>UPVC管材、管件、阀门</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>XD-24039-GS-UPVC管材、管件、阀门采购询比采购公告 项目基本情况 项目名称： XD-24039-GS-UPVC管材、管件、阀门采购 项目编号： 000529-26XB1723 项目类型： 物资 采购方式： 询比采购 所属行业分类： 建筑业--建筑安装业 项目实施地点： 四川省成都市 招标人： 北京世源希达工程技术有限公司 代理机构： 网 项目概况： 1.项目名称：2024年度成都&amp;绵阳区域洁净工程维修改造项目D标段； 2.项目地点：四川省成都市郫 都区； 3.品牌范围：环琪、协羽； 4.品牌需报审通过方可使用。 其他： 标段/包信息 务 标段/包名称： XD-24039-GS-UPVC管材、管件、阀门采购 标段/包编号： 000529-26XB1723/01 文件获取开始时间： 2026-08-21 15:30 文件获取截止时间： 2026-08-24 15:30 商 文件发售金额(元)： 0 文件获取地点： 国投集团电子采购平台 截标/开标时间： 2026-08-25 15:30 开标形式： 线上开标 交货期（天）： 10 道 开标地点： 国投集团电子采购平台 交货期说明： 交货期：合同签订后10日历天交货，交货地点：四川省成都市郫都区 采购范围： 详见采购文件。 供应商基本要求： 1.具有法人资格和独立承担民事责任的能力。 2.具有履行合同所必需的设备和专业技术能力。 管 3.有依法缴纳税收和社会保障资金的良好记录。 4.没有处于责令关闭、注销或吊销执照状态；没有进入破产清算 程序或解散等其他丧失履约能力情形。 供应商资质要求： 无 供应商业绩要求： 近三年相关业绩1~3个。 国 供应商其他要求： 1.响应文件需提供报价函、报价表（盖章扫描件、excel文件）、报价方案（如有），视具体 要求提供相关技术图纸、资料等。 2.具有良好的商业信誉和良好的资金、财务状况。 3.平台使用费：中标供应商 需按国投系统要求支付相应平台使用费(0-5万:0元；5-20万:800元；20万以上:1200元)，具体可参照系统门户网站- 通知公告或帮助中心-常见问题。 供应商拟投中入项目负责人最低要求： 是否接受联合体投标： 否 备注： 招标人联系方式 招标人： 北京世源希达工程技术有限公司 联系人： 张文青 联系电话： 15600806706 联系地址： 北京市海淀区万寿路27号 代理机构联系方式 代理机构： 联系人： 座机： 手机号码： 电子邮箱： 联系地址： 相关说明 发布媒介： 本次采购公告在国投集团电子采购平台（https://www.sdicc.com.cn） 上发布，对于因其他网站转载 并发布的非完整版或修改版公告，而导致损失的情形，采购人及采购代理机构不予承担责任。 注册说明： 供应商登录电子采购平台门户网站，点击右上角【用户注册】注册用户账号，填写企业基本信息 提交审核，审核情况将在24小时内（不含法定节假日）进行反馈。基本信息审核通过的供应商，方可下载采购文 件，请合理安排注册时间。 平台使用费： 供应商若中标，须在取得成交通知书前缴纳平台使用费（收费标准及方式详见门户网站－通知 公告或帮助中心－常见问题）。 文件下载： 供应商登录电子采购平台门户网站，点击右上角【用户登录】-【供应商系统】，在【公告信息-采 购公告】或【我的邀请】中选择项目，点击【进入项目】进入工作台，在【采购文件】环节，点击【下载采购 文件】自行下载采购文件电子版，采购方不再提供纸质采购文件。 CA办理： 目前非招标项目可不办理ＣＡ。 帮助信息： 如需帮助请登录电子采购平台网站首页【帮助中心】-【操作指南】。 其他信息： 本次采购活动所有信息发布和联络以注册及参与项目时填写的信息为准，供应商应对填写的所有 信息的真实性和准确性负责，并自行承担信息有误导致的一切后果。 信息来源:https://www.chinapipe.net/project/d3077513.html cqdingjiu 2026.08.24 12:31:55 网 务 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>管材, 管件, 阀门</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>四川卓勤新材料科技有限公司基膜涂覆一体化项目(二期三标段)预应力高强混凝土管桩采购任务</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>工业</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>邛崃市</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>预应力高强混凝土管桩</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>自筹资金</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>预应力高强混凝土管桩</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>四川卓勤新材料科技有限公司基膜涂覆一体化项目(二期三标段)预应力高强混凝土管桩采购任务 一、项目基本情况： 1. 采购项目名称： 四川卓勤新材料科技有限公司基膜涂覆一体化项目（二期三标段） 2. 采购人 ： 中国机械工业建设集团有限公司 四川分公司 3. 采购内容 ： 预应力高强混凝土管桩 （详见响应文件材料清单） 网 4. 采购方式 ： 公开竞争性谈判 。 5. 资金来源 ： 自筹 资金 务 6.项目地点： 四川省成都市邛崃市天府新区半导体材料产业功能区崃岭大道 888号 。 7.货物质量标准或主要技术性能指标：质量达到国家及行业现行相关法律法规规定的生产、制造、验收规范合格 标准，且符合后续合同设计图纸要求。 商 二、分供商资格要求 1.本项目的特定资格要求： 道 （ 1）具有独立承担民事责任能力的法人、其他组织，并出具合法有效的营业执照或事业单位法人证书等国家 规定的相关证明；； （ 2 ）供应商应授权合法的人员参加谈判全过程，法定代表人直接参加的须提交其身份证原件及法定代表人 管 证明书，法定代表人授权代表参加谈判的，须出具法定代表人授权书及被授权人身份证原件； （ 3 ）财务状况报告：提供经审计的财务报告（至少包含资产负债表和利润表，成立时间至提交响应文件截 止时间不足一年的可提供成立后任意时段的资产负债表）或报价前六个月内其基本账户银行出具的资信证明 （附开户许可证或基本国账户信息）； （ 4 ）不得为 “信用中国”网站（www.creditchina.gov.cn）中列入“失信被执行人”和“重大税收违法案 件”当事人名单的供应商，不得为中国政府采购（www.ccgp.gov.cn）政府采购“严重违法失信行为记录名单”中 被财政部门禁止参加政府采购活动的供应商； 中 （ 5 ）无重大违法记录声明：供应商须出具参加采购活动前三年内，在经营活动中没有重大违法记录声明； 注： I.不同性质的法人或其他组织可按照国家法律规定提供合法资质；特殊行业 供应商 的分支机构 参与 谈判的 ，还须出具其主管单位或总公司为其参与本项目 报价 及履约行为承担民事责任的承诺书；特殊行 业 供应商 的分支机构 参与谈判 的，财务状况、税收缴纳、社会保障资金缴纳等由主管单位或总公司代缴 （代管）的，提供其主管单位或总公司相应证明材料及情况说明。 Ⅱ. 供应商 负责人为同一人或者存在直接控股、管理关系的不同供应商，不得同时参加本项目采购活动，否 则按 无效 处理。 Ⅲ.根据《关于在政府采购活动中查询及使用信用记录有关问题的通知》（财库〔2016〕125号）的规定，对列入 失信被执行人、重大税收违法案件当事人 名单、政府采购严重违法失信行为记录名单的供应商，拒绝参与本 项目采购活动； （ 6 ）本次采购不接受联合体。 三、采购文件的获取方式 时间： 2026 年 8 月 22 日 12:00 至 2026 年 8 月 25 日 12:00 地点 ：中机建设电子采购平台， http://eps.sinoconst.com.cn/ 方式：网上获取 四、响应文件的递交 截止时间： 2026年8 月 27 日 17 时 00 分 00 秒 ， 供应商 应在截止时间前将编制完成的 响应 文件进行盖章扫描后，上传至 “ 中机建设电子采购平台 ”的提交 响应 报价文件模块，逾期未 完成上传的，系统将拒绝接收 响应 文件并自动对其关闭。 五、谈判时间和地点 网 递交响应文件的分供商应委派代表准时参加谈判活动，谈判开始时间 2026年8 月 28 日 10 时 00 分 00 秒 。谈判方式是通过腾讯视频会议系统。 务 六、发布谈判公告的媒介 本次采购公告在中机建设电子采购平台（ eps.sinoconst.com.cn）发布 七、对本次采购提出询问，请按以下方式联系。 商 采购人信息：中国机械工业建设集团有限公司 四川分公司 地 址：四川省成都市天府新区华府大道 1段蓝道润置地2 707 联 系 人： 丁保平 电话： 13213128433 八、监督 管 本项目的 谈判采购 活动及其相关当事人应当接受有管辖权的 公司合规 监督部门依法实施的监督（公司 纪检部门）。 监督 人 ：邹 忠 国 联系电话： 13778280342 邮 箱： legal@sinoconst.com.cn 中 信息来源:https://www.chinapipe.net/project/d3077502.html cqdingjiu 2026.08.24 12:31:55</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>90</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>四川, 预应力高强混凝土管桩, 公开竞争性谈判, 自筹资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>宜宾市清源水务集团有限公司成品防腐无缝钢管采购项目招标/采购异常</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>其他/未识别</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>本项目因递交响应文件供应商不足2家而流标。</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>防腐无缝钢管</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>宜宾市清源水务集团有限公司成品防腐无缝钢管采购项目招标/采购异常 招标项目编号: JZXTP202608130003 所属行业分类: -- 网 代理机构: 务 -- 项目情况: 商 -- 招标/采购异常类型: 道 流标 管 招标/采购异常原因: 递交响应文件供应商不足2家，本项目流标。 国 是否转换采购方式: 否 中 招标/采购异常公告内容: 递交响应文件供应商不足2家，本项目流标。 附件: 公示PDF: 无 其他附件: 无 信息来源:https://www.chinapipe.net/project/d3077498.html cqdingjiu 2026.08.24 12:31:55</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>四川, 管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>宜宾高新区高场片区老旧小区改造项目等两个工程管网探测及测绘(第二次)询价邀请函公告</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>房建</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>宜宾市</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>宜宾市</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>本项目包括宜宾高新区高场片区老旧小区改造项目和宜宾高新区高场片区城中村配套基础设施项目的管网探测及测绘工作。</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>宜宾高新区高场片区老旧小区改造项目建安费用约8349.39万元，宜宾高新区高场片区城中村配套基础设施项目建安费用约12000万元。</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>管网探测设备及服务，建筑单体测绘设备及服务，原始地形地貌测绘设备及服务</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>宜宾高新区高场片区老旧小区改造项目等两个工程管网探测及测绘(第二次)询价邀请函公告 询价邀请函 各报价单位： 根据公司安排，将宜宾高新区高场片区老旧小区改造项目等两个工程管网探测及测绘（第二次）进行市场询价， 现诚邀贵公司就根据项目情况参与报价。 一、 项目名称 网 宜宾高新区高场片区老旧小区改造项目等两个工程管网探测及测绘（第二次） 二、项目概况 务 （一）项目地点：宜宾市高新区 （二）项目规模： 商 1.宜宾高新区高场片区老旧小区改造项目（子工程一）：本项目涉及高场片区11个老旧小区，房屋58栋，1956户 居民。改造小区燃气管道17160m，给排水管道18935m，电力和通信线路13320m，改造停车位685个；新增充电 桩137个，小区消防设施58套，户内燃气安全设施1956套，分类垃圾回收站点10个；改造闲置社区用房为日间照 料中心4430m、便民中心5420m，改造小区内道道路10192m及配套基础设施；建安费用约8349.39万元。 2.宜宾高新区高场片区城中村配套基础设施项目（一标段）（子工程二）：本项目实施范围约460亩，涉及户 数690户，共计2277人。具体建设内容包括新建公共配套用房总建筑面积21000m，其中养老托幼等服务设 施15000m、其他公服用房6000m；新建公共停车位1600个及配置400个充电桩；新改建城中村配套道路 管 约4.5km及其他基础设施建设。本标段建设内容包含对高场镇碧水街、通江街、河边街、中学街等进行道路整治、 电力通讯线路下地、人行道改造、街面外立面整治、街道绿化及亮化提升等；新建公共配套用房、公共停车位、 口袋公园等配套公共基础设施；建安费用约12000万元。 （三）工作内容： 国 1.管线探测：收集已有管线资料，现场踏勘；对井盖等明设管线实地调查，采用物探设备探明各类地下隐蔽管线 的规格参数、位置、埋深及走向；实测管线点坐标高程；整理核查数据，编制管线图纸、数据库及技术报告， 并开展相关质量检查验收工作。 中 2.建筑单体测绘：实测建筑平面轮廓、层高、标高、外立面、附属设施及角点坐标，核查建筑现状；绘制平 立剖面图纸，核算建筑面积、编制测绘图纸、计算书及正式测绘报告等相关内容。 3.原始地形地貌测绘：实测场地内建筑物、道路、水系、植被等地物要素及地面高程点，绘制带等高线原始地形 图纸，行程测绘成果。 三、报价人资格要求 （一）具有中国境内注册的独立法人资格。 （二）资质要求：具备国家建设行政主管部门颁发的测绘相关资质。 四、其他说明 （一）本次询价仅为市场调查行为，不作为定标依据。 （二）本次工期为30日历天。 五、递交资料内容 详见附件询价表，营业执照及资质证书。 六、其他要求 （一）报价文件递交截止日期为2026年8月24日17:00 （二）报价方式：网上递交。报价文件采用PDF文件并加盖鲜章，通过宜宾企业阳光采购服务平台线上递交。 （联系人：谢先生 ，电话：0831-8755160） 宜宾市高新投资集团有限公司 网 2026年8月21日 信息来源:https://www.chinapipe.net/project/d3077494.html 务 cqdingjiu 2026.08.24 12:31:55 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>宜宾高新区高场片区老旧小区改造项目：改造小区燃气管道17160m，给排水管道18935m，电力和通信线路13320m，改造停车位685个；新增充电桩137个，小区消防设施58套，户内燃气安全设施1956套，分类垃圾回收站点10个；改造闲置社区用房为日间照料中心4430m、便民中心5420m，改造小区内道路10192m及配套基础设施。宜宾高新区高场片区城中村配套基础设施项目：新建公共配套用房总建筑面积21000m，其中养老托幼等服务设施15000m、其他公服用房6000m；新建公共停车位1600个及配置400个充电桩；新改建城中村配套道路约4.5km及其他基础设施建设。</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>80</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>宜宾, 高新区, 老旧小区改造, 管网探测, 测绘</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>中煤广元煤炭储备项目设备安装工程钢管及型钢采购询价通知</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>能源</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>钢管及型钢采购</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>热浸锌镀锌无缝钢管,热浸锌镀锌钢管,热浸锌扁铁,热浸锌角钢,热浸锌槽钢,水煤气管热浸锌,无缝钢管</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>中煤广元煤炭储备项目设备安装工程钢管及型钢采购询价通知 中煤广元煤炭储备项目设备安装工程钢管及型钢采购 询价通知 中煤第九十二工程有限公司根据采购管理办法，现对“中煤广元煤炭储备项目设备安装工程”所需钢管及型钢 组织公开采购，现邀请符合资质要求的供应商报名参与。 一、采购范围 网 序号 物资名称 规格型号 单位 数量 备注 务 1 热浸锌镀锌无缝钢管 D219X6 米 3600 20# 2 热浸锌镀锌无缝钢管 D159X6 米 200 20# 3 热浸锌镀锌无缝钢管 D133X4 米 100 20#商 4 热浸锌镀锌无缝钢管 D108X4 米 200 20# 5 热浸锌镀锌无缝钢管 D89X4 米 60 20# 6 热浸锌镀锌无缝钢管 D76X3.5 米 道42 20# 7 热浸锌镀锌无缝钢管 D57X3.5 米 120 20# 8 热浸锌镀锌无缝钢管 D45X3 米 18 20# 9 热浸锌镀锌无缝钢管 D38X管3 米 90 20# 10 热浸锌镀锌无缝钢管 D32X3 米 400 20# 11 热浸锌镀锌钢管 DN100 米 900 Q235B 12 热浸锌镀锌钢管国DN65 米 300 Q235B 13 热浸锌镀锌钢管 DN50 米 1000 Q235B 14 热浸锌扁铁 80*8 m 1438 Q235B 15 热浸中锌扁铁 40*6 m 6675 Q235B 16 热浸锌角钢 50*50*5 m 2672 Q235B 17 热浸锌角钢 75*5 m 170 Q235B 18 热浸锌槽钢 10# m 790 Q235B 19 水煤气管热浸锌 DN25 m 1133 Q235B 20 水煤气管热浸锌 DN40 m 87 Q235B 21 水煤气管热浸锌 DN50 m 1083 Q235B 22 水煤气管热浸锌 DN100 m 130 Q235B 23 无缝钢管 D159*6 m 100 20# 1．项目名称：中煤广元煤炭储备项目设备安装工程 2．询价书编码：XJ20260805003 3．采购方式：公开询比 二、供应商资格要求 （一）具备纳税人资格的法人企业； （二）具备生产或经营资质，完成标的物供货能力的生产商或经销商； （三）企业经营、资信状况良好，无不良经营业绩，没有处于被责令停业、财产被接管、冻结、破产状态； （四）未列入中煤集团范围内供应商停用名单； （五）不属于被国家相关部门认定有严重失信行为且处于失信处置期内的供应商； （六）本次采购不接受联合体参与，法定代表人为同一人或者存在控股、管理关系的不同单位，不得同时参加 报价。 网 三、供应商报名、报价及采购文件获取 （一）供应商登录中煤供应链平台（http://ego.chinacoal.com），已注册用户的供应商直接登录通过系统网上报名 报价；未注册的供应商登录系统后先按要求填报企业相关资料，进行网上注册，待我公司进行准入评审后，按 务 照注册申请的账户登录系统网上报名报价。 （二）报名成功的供应商登陆中煤供应链平台下载采购文件。 （三）根据报价揭示情况进行资格后审 商 四、报价揭示时间、地点 （一）报价文件递交截止时间： 2026年8月25道日下午15: 00时(北京时间)。迟到的采购文件将被拒绝。 （二）报价揭示时间：2026年8月25日下午15: 00时(北京时间)。 （三）报价揭示地点：线上报价揭示 管 五、联系方式 采购单位：中煤第九十二工程有限公司 国 地址：河北邯郸市丛台路56号 采购联系人：王鑫：0310-7206473 中 现场联系人：张海鹏：13451436662 2026年8月21日 信息来源:https://www.chinapipe.net/project/d3077488.html cqdingjiu 2026.08.24 12:31:56</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>D219X6 米 3600; D159X6 米 200; D133X4 米 100; D108X4 米 200; D89X4 米 60; D76X3.5 米 120; D57X3.5 米 120; D45X3 米 18; D38X管3 米 90; D32X3 米 400; DN100 米 900; DN65 米 300; DN50 米 1000; 80*8 m 1438; 40*6 m 6675; 50*50*5 m 2672; 75*5 m 170; 10# m 790; DN25 m 1133; DN40 m 87; DN50 m 1083; DN100 m 130; D159*6 m 100</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>70</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 近三天, 管材招标, 商机</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>成都市绕城高速天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购/标段招标文件答疑文件001号</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>能源</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>成都市绕城高速天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购/标段</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>招标控制价为 6077139.16元</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>无缝钢管,直缝埋弧焊钢管,调压计量撬,球阀,电动球阀,手动球阀,电液联动球阀,绝缘接头,阻火器,流量调节阀,涡轮流量计,调压器,超压切断阀,电加热器,压力表,差压计,双金属温度计,压力变送器,差压变送器,温度变送器,可燃气体探测器,可燃气体控制器,信号管电伴热带,管汇,无损检测,表面处理,运输,整撬监检,气密性试验,组装及调试</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>成都市绕城高速天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购/标段招标文件答疑文件001号 致：各投标人 现就“成都市绕城高速天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购/标段”招标文件进行 答疑，按招标文件规定，本答疑文件是招标文件的组成部分。 提问1：按招标要求本项目的管汇采用埋地型式，分项报价表两根汇管，与技术规格书、数据表中汇管规格要求 不一致： 技术规格书所附的流程图，是否只有如下红框中一根汇管？ 请确认该项目所需管汇的数量，位置、规 格、设计标准等，管汇上是否需要设置排污？埋地汇管现场安装、组装、防腐等网工作是否由现场施工方统一负 责，我司仅负责提供相关的物料； 回复1：1）站内无汇管，站内采用埋地管汇，管汇数量为2根。 务 2）管汇数量为2根，采用管段+管件焊接形式的管汇，第一根位于MOV101和MOV102前，第二根位于一级调压 后，规格详见技术规格书，标准执行GB/T9948-2025。管汇无排污。 3）埋地管汇物料、安装、组装、防腐工作在招标范围内，由供应商负责。 商 提问2：技术规格书要求：“调压计量撬外设置外罩厢房，由华天司统一设计。”请确认华天司是否需要收取相 关设计费用、设计深度深度等，且该费用由我司负责？请提供华天司联系方式，及项目整体布置图、接管方位 等要求，以便我司明确外罩厢房的费用； 道 回复2：1）外罩厢房由华天司统一设计，不收取设计费。 2）外罩厢房暂按以下要求报价： 管 a、橇体配有全天候防雨隔音防护罩。 b、罩体外部为彩钢板，内部装有特殊材料可起到隔音、降噪、防火、保温作用。罩体降噪部分采用吸音、消音 的不燃或难燃材料制做。 国 c、防雨隔音外罩应满足调压橇在抗震、抗风、抗雨、散热、安全性和维修操作等各方面的要求。噪声水平满足 任意方向在距保证橇体边缘外1米处昼间噪音等效声级≤60dB（A）的范围要求，夜间噪声等效声级≤50dB（A） 的范围要求。 中 d、罩体内上梁及支柱需承受橇内单体最重设备的吊装要求，便于检修时吊运设备或零部件。 e、罩体每边的罩壁应能外开，以便于设备检修。 f、罩体应设置罩体应合理设置爆炸泄压口，设置自然通风百叶窗，满足罩内通风换气的要求。 g、罩体内应安装不少于2个防爆照明灯，满足检修照明需要。 h、罩内安装4台可燃气体探测器，探测器符合现行国家标准GB 50493-2009《石油化工可燃气体和有毒气体检测 报警设计规范》的有关规定。当罩内可燃气体浓度过高时，探测器将自动报警，并上传至控制室。 i、罩体外壁的油漆应适于安装地区的气候条件，颜色由买方指定。 提问3：招标分项报价表中，要求：33）流量调节阀 L946X-PN16 DN250，技术规格书中要求为DN300，数据表要 求： 厂家是否可以根据工艺参数要求自行选型，确定阀门规格？ 请确认该流量调节阀结构是否为V型球阀结构， V型球阀一般是等百分比调节，请确认是否可以？ L946X是否为调节阀的型号，是否有品牌要求？ 回复3：1）流量调节阀前后接管标准为DN300，在性能满足技术规格书要求的前提下，可自行选择阀门规格，需 提供计算书。 2）达到技术规格书要求即可。 3）无品牌要求。 提问4：招标分项报价表中阀门等设备规格数量与流程图不一致，是否以流程图为准？ 回复4：以流程图为准。 提问5：该项目球阀、电动头、电液联动执行机构、流量计等设备是否有品牌要求？ 回复5：无品牌要求。 提问6：招标分项报价表、技术规格书、数据表、流程图等，对调压器及切断阀口径进行了规定，请问厂家是否 可以结合技术规格书中的技术要求，自行调整调压器及切断阀口径？ 网 回复6：按技术规格书执行。 提问7：技术规格书中，整站设计温度：-19℃～50℃，部分设备数据单中“温度极限： -20/75℃”、“过滤分离 器设计温度：-19℃/70℃”，考虑到本站的环境温度及介质温度，采用设计温度：-19℃～50℃完全满足本站的要 务 求，请问可否将整站的设计温度统一为-19℃～50℃？ 回复7：设计温度统一为：-19℃/50℃。 提问8：技术规格书中，要求球阀阀体、球体采用锻钢A3商50 LF2，为低温材质， A105、WCB材质完全满足-19℃ 设计温度，请问是否可以采用锻钢A105（PN16以上）和铸钢WCB(PN16)球阀？ 回复8：橇外埋地电液联动球阀（ESD101、ESD401、ESD301）采用锻钢A350 LF2，其他球阀阀体、球体可采用锻 钢A105或锻钢A350 LF2。 道 提问9：请问电加热器的功率是否按60KW报价，还是需要厂家根据电加热器数据表中的进出口温度要求进行核 算调整？导热油是否在本次供货范围内？ 管 回复9：1、按技术规格书执行。2、在本次供货范围内。 提问10：技术规格书要求换热器设保温，结合本项目的环境温度，及天然气加热的温度，电加热器可以不设置保 温，请问可否取消此要求？ 国 回复10：按技术规格书执行。 提问11：过滤分离器数据表要求：差压变送器量程：0~0.6MPa，弹簧管差压计量程：0~0.6MPa，Y-150，精度1.5 级。通常，差压计量程0~0.1MPa，表盘80，差压变送器量程0~0.2MPa，请问可否按此配置？（注：因为过滤器 中 滤芯实际差压达到0.07MPa时就需要清洗滤芯） 回复11：按技术规格书执行。 提问12：技术规格书中涉及到4.站控系统要求，5.SIS系统基本要求，请确认该项目电气的交接界面为撬内接线箱 及配电箱，站控系统及SIS系统不在本次招标范围内； 回复12：1）交接界面为撬内接线箱及配电箱。 2）站控系统及SIS系统不在本次招标范围内。 提问13：投标报价明细表中序号9）～12）电动球阀的型号为Q967，此型号代表为焊接连接，而根据工艺流程图、 数据表应为法兰连接，请问序号9）～12）电动球阀是否为Q947、法兰连接球阀？ 回复13：以流程图为准。 提问14：投标报价明细表中序号18）、19），DN350 PN16和DN300 PN16球阀各2台，而工艺流程图中没有DN350 PN16球阀，只有DN300 PN16球阀4台，请问是否以工艺流程图为准？ 回复14：以流程图为准。 提问15：投标报价明细表中序号33）流量调节阀为DN250，而工艺流程图、数据表为DN300，请问是否以工艺流 程图为准？ 回复15：以流程图为准。 提问16：清单中温度变送器、温度计的数量与工艺流程图不一致。请问是否以工艺流程图为准？ 回复16：以流程图为准。 提问17：报价明细表中有2根汇管，而工艺流程图中只有1根，根据工艺结构，进口端、过滤分离器前端可不采用 埋地汇管，采用地面管道设计即可，请问是否取消清单中的1根汇管？ 回复17：站内无汇管，采用管段+管件焊接形式的管汇，管汇为2根。进口端、过滤分离器前端埋地管汇不能取 消，采用埋地方式，不能在地面上。 网 提问18：报价明细表中汇管规格为DN1100、DN1000，而技术规格书需求表为DN600、DN500。请问是否以技术 规格书的规格为准？ 务 回复18：以技术规格书为准。 提问19：报价明细表中可燃气体探测器数量为4只，而技术规格书中需求表中为8个，请问撬内可燃气体探测器数 量是否以实际数量为准？ 商 回复19：招标数量为4个。 提问20：除投标报价明细表中序号4调压计量撬外，请问撬外设备，如电液联动球阀、绝缘接头、阻火器、无缝 钢管、管件等是否只报材料价格，不含现场焊道接安装费用，其现场安装由招标方另行委托第三方来完成，投标 人提供技术支持？ 回复20：是。 管 提问21：技术规格书、数据表中要求DN100及以上球阀采用固定球、涡轮涡杆操作，但投标报价明细表中DN100 球阀为Q41，浮动球，手柄操作。请问DN100球阀是采用固定球、涡轮涡杆操作，还浮动球，手柄操作？ 回复21：DN100球阀采用固定球、涡轮涡杆操作。 国 提问22：数据表中要求加热器采用立式导热油电加热结构，为减小占地面积，方便维护，请问换热器可否采用卧 式直接电加热器结构，其操作、维护、效率更高？ 回复22：按技术规格书执行。 中 提问23：技术规格书要求调压器带阀位信号远传，但工艺流程图没有要求，请问调压器是否带阀位信号远传功能？ 回复23：不含阀位远传。 提问24：技术规格书提到电液联动球阀具有压降速度感测功能，即破管保护功能，请问本项目的进/出站共3台电 液联动球阀是否都要具有压降速度感测功能？ 回复24：是。 提问25：数据表中要求差压表的表盘直径为150，常规差压表表盘直径为80，150需要特殊定制。请问差压表的表 盘直径可否采用80？ 回复25：按技术规格书执行。 提问26：数据表中要求球阀阀体（含电动球阀、手动球阀、电液联动球阀）采用A350 LF2低温锻钢，根据本项目 实际使用环境及设计温度，采用常温A105锻钢即可满足。请问球阀阀体可否采用A105锻钢？ 回复26：橇外埋地电液联动球阀（ESD101、ESD401、ESD301）采用锻钢A350 LF2，其他球阀阀体、球体可采用 锻钢A105或锻钢A350 LF2。 提问27：数据表中要求电动球阀型式及结构为：分段式、阀体全焊接，两者相互矛盾，请问电动球阀阀体是否以 分段式结构为准？ 回复27：地上阀门采用分段式，地下阀门采用阀体全焊接。 提问28：数据单中要求一级调压器、超压切断阀采用低温锻钢阀体，请问一级调压器、超压切断阀可否采用低温 铸钢阀体？ 回复28：按技术规格书执行。 提问29：招标文件中规格定了调压器、超压切断阀口径，其口径偏大，请问调压器、超压切断阀口径可否调整？ 回复29：按招标文件执行。 网 提问30：技术规格书中有站控系统和SIS系统描述，但分项报价表不含站控系统和SIS系统，请问站控系统和SIS系 统是否在报价范围？若在报价范围，能否提供具体清单？ 回复30：交接界面为撬内接线箱及配电箱；站控系统及SIS系统不在本次招标范围内。 务 招标人：成都燃气集团股份有限公司 商 招标代理机构：四川成化工程项目管理有限公司 道 2026年8月21日 管 成都市绕城高速天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购/标段招标文件补遗文件001号 致：各投标人 现就“成都市绕城高速国天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购/标段”招标文件进行 补遗，按招标文件规定，本补遗文件是招标文件的组成部分。 一、原投标文件递交的截止时间（投标截止时间，下同）为2026年8月31日10时30分，现变更为：投标文件递交 的截止时间（投标截止时间，下同）为2026年9月7日10时30分，投标保证金递交截止时间相应顺延。 中 二、原招标文件招标控制价为 6078460.33元 ，其中暂列金为 / 。 现变更为：招标控制价为 6077139.16元 ，其中暂列金为 / 。 三、原招标文件第六章 投标文件格式□八、投标报价 分项报价表。 现变更为： □八、投标报价 分项报价表 单位：人民币元 设备仅填写含税投标单价 工程名称：成都市绕城高速天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购 单价 序号 材料(工程设备)名称、规格、型号 单位 数量 单价最高限价 小计 备注 报价 撬外 1 3PE无缝钢管_20#_D325*8，GB/T9948-2025 m 114.374 418.70 材料 2 3PE直缝埋弧焊钢管_L360M_D508*12，GB/T9711-2023 m 105.21 1243.23 3 3PE直缝埋弧焊钢管_L415M_D508*12，GB/T9711-2023 m 105.21 1159.06 4 调压计量撬（调压、计量、过滤、加热） 套 1 5054221.67 包括但不限于以下内容 1） 隔音罩 套 1 2） 爬梯及操作平台 个 10 3） 支座、支架 套 1 网 4） 橇间连接管线及管件、法兰等 套 1 5） 电缆线 套 1 6） 防爆接线箱 套 1 务 7） 防爆配电箱 套 1 8） 卧式过滤分离器 PN40 台 2 9） 电动球阀 Q947F-PN40 DN300 台 2 商 10） 电动球阀 Q947F-PN16 DN350 台 2 11） 电动球阀 Q947F-PN16 DN300 台 2 12） 电动球阀 Q947F-PN16 DN200 台 2 道 13） 法兰式手动球阀 Q347F-PN40 DN200 台 1 14） 法兰式手动球阀 Q347F-PN40 DN150 台 1 15） 法兰式手动球阀 Q41F-PN40 DN80 台 2 管 16） 法兰式手动球阀 Q41F-PN40 DN50 台 4 17） 法兰式手动球阀 Q41F-PN40 DN50 台 3 18） 法兰式手动球阀 Q347F-PN16 DN300 台 4 国 此项 19） 法兰式手动球阀 Q347F-PN16 DN300 台 2 不报 价 20） 法兰中式手动球阀 Q347F-PN16 DN200 台 1 21） 法兰式手动球阀 Q347F-PN16 DN150 台 4 22） 法兰式手动球阀 Q347F-PN16 DN100 台 2 23） 法兰式手动球阀 Q41F-PN16 DN20 台 4 24） 法兰式手动球阀 Q41F-PN16 DN50 台 2 25） 法兰式节流截止放空阀 J41Y-PN40 DN150 台 1 26） 法兰式节流截止放空阀 J41Y-PN40 DN80 台 2 27） 法兰式节流截止放空阀 J41Y-PN16 DN200 台 1 28） 法兰式节流截止放空阀 J41Y-PN16 DN150 台 3 29） 法兰式节流截止放空阀 J41Y-PN16 DN20 台 4 30） 法兰式阀套式排污阀 PW41Y-PN40 DN50 台 4 31） 法兰式先导式安全阀AF46F-PN16 DN100XDN150 台 2 32） 法兰式先导式安全阀AF46F-PN16 DN150XDN200 台 1 33） 流量调节阀 PN16 DN300 台 2 34） 涡轮流量计PN16 DN300 台 2 35） 涡轮流量计PN16 DN200 台 2 36） 工作调压器 PN40 DN200 台 2 37） 工作调压器PN16 DN150 台 2 38） 监控调压器 PN40 DN200 台 2 39） 监控调压器PN16 DN150 台 2 40） 超压切断阀 PN40 DN200 台 2 41） 超压切断阀PN16 DN150 台 2 42） 电加热器 60KW 台 2 网 43） 压力表YTS-100H 只 9 44） 差压计0～160Kpa 只 2 45） 双金属温度计WSS481W 只 5 务 46） 压力变送器0～6.0MPa 只 1 47） 压力变送器0～2.5MPa 只 3 48） 压力变送器0～0.6MPa 只 1 商 49） 差压变送器0～0.16MPa 只 2 50） 温度变送器-40～+80℃ 只 9 另预 道 留4个 探测 51） 可燃气体探测器 只 4 器的 安装 管 条件 按8个 探测 52） 可燃气体控制器 套 1 器考 国 虑 53） 信号管电伴热带 套 1 54） 管汇PN40 DN600 根 1 中 55） 管汇PN16 DN500 根 1 56） 无损检测 套 1 57） 表面处理 套 1 58） 运输 套 1 59） 整撬监检 套 1 60） 气密性试验 套 1 61） 组装及调试 套 1 此项 5 法兰手动球阀 Q41F-PN40_DN50 个 1 1122.22 不报 价 6 钢制等径三通_Q355B_DN250_7mm 个 1 455.56 7 钢制无缝弯_20#_DN300_8mm_3.0D_90° 个 6 520.00 8 钢制无缝弯头_L360M_DN500_12mm_3.0D_90° 个 5 2600.00 9 钢制无缝弯头_L415M_DN500_12mm_3.0D_90° 个 5 2860.00 10 钢制无缝弯头_Q355B_DN100_5mm_1.5D_90° 个 3 59.26 11 钢制无缝弯头_Q355B_DN200_7mm_1.5D_90° 个 5 195.56 此项 12 钢制异径接头_Q355B_DN250/150_7mm 个 1 200.00 不报 价 13 高压化肥无缝钢管_20#_D325*8 m 0.88 441.92 14 高压化肥无缝钢管_Q355B_D108*5 m 16.193 97.44 15 高压化肥无缝钢管_Q355B_D219*7 m 45.11 270.20 16 高压化肥无缝钢管_Q355B_D273*7 m 44.87 348.66 17 绝缘接头 JY-300-PN16 个 1 4160.00 网 18 绝缘接头 JY-500-PN16 个 1 12103.00 19 绝缘接头 JY-500-PN40 个 1 13689.00 20 冷缠带_一体带_50mm_含底漆 m2 务200.003 19.56 21 全焊接电液联动球阀_PN16_DN300 个 1 140000.00 22 全焊接电液联动球阀_PN16_DN500 个 1 230000.00 23 全焊接电液联动球阀_PN40_DN500 商个 1 240000.00 24 热收缩带_带底漆_加强级(1.5/1.0)_D108*500mm 个 3 37.04 25 热收缩带_带底漆_加强级(1.5/1.0)_D219*500mm 个 8 50.00 26 热收缩带_带底漆_加强级(1.5/1.0)_D27道3*500mm 个 8 55.56 27 热收缩带_带底漆_加强级(1.5/1.0)_D325*500mm 个 21 60.32 28 热收缩带_带底漆_加强级(1.5/1.0)_D530*500mm 个 40 84.17 29 热煨弯管_L360M_DN500_1管2mm_3.0D_50° 个 1 3766.67 30 热煨弯管_L415M_DN500_12mm_3.0D_50° 个 1 3766.67 31 中压对焊法兰 PN40_DN50 片 2 38.89 32 阻火器_PN16_D国N250 个 1 3388.89 合计 中 注：1.撬内设备、阀门及管线部分，由投标人按技术规格书要求设置标识牌及管线功能信息标注，标识牌为圆形、 直径80毫米，制作及材质要求为双色板雕刻+PVC+磁铁3-5粒按照直线分布。 2.工程安装调试合格后，由投标人按技术规格书要求，对撬内和撬外所有管线整体刷一道氟碳面漆，做法详见技 术规格书2.2.4。 3.上述两项工作不单独列项报价，其全部费用已包含在设备清单的综合报价中，由投标人在设备清单费用内自行 组价。 4.报价为送货至施工地点的到货价，包括设备材料费、运费、检验费、保险费、吊装费、撬装设备安装调试费、 税费等。 注：投标人的投标报价须满足招标文件相应要求。 三、招标文件以最新上传的招标文件版本为准。 四、招标文件涉及到的上述相关内容均做相应修改，其余内容不变。 招标人：成都燃气集团股份有限公司 招标代理机构：四川成化工程项目管理有限公司 2026年8月21日 信息来源:https://www.chinapipe.net/project/d3077478.html cqdingjiu 2026.08.24 12:31:56 网 务 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>排水钢管 Φ200*6m：3000米</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>重庆市, 四川省, 管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>四川省华蓥市重点采煤沉陷区华蓥市高兴镇城镇危旧房改造项目(三期)施工一标段招标公告</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>华蓥市</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>改造城镇危旧房约4.5万平方米，户数共220户，3栋共9个单元。配套小区内道路、供水、供电、供气主管网、消防、路灯等基础设施。新建道四通路与兴政路连接道路64米，铺设安置房一期商业街人行道5766平方米，配套完善排水、路灯、绿化等附属设施。</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>项目业主为华蓥市交通投资开发有限责任公司，建设资金来自上级补助和业主自筹（资金来源），项目出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>市政公用工程施工</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>四川省华蓥市重点采煤沉陷区华蓥市高兴镇城镇危旧房改造项目(三期)施工一标段招标公告 1. 招标条件 1.1本招标项目四川省华蓥市重点采煤沉陷区华蓥市高兴镇城镇危旧房改造项目（三期）(项目名称)已由 华蓥市发展和改革局(项目审批、核准或备案机关名称)以华蓥市发展和改革局关于四川省华蓥市重点采煤沉陷区 华蓥市高兴镇城镇危旧房改造项目（三期）可行性研究报告的批复、华发改投〔2023〕191号（批文名称及编号） 批准建设，项目业主为华蓥市交通投资开发有限责任公司，建设资金来自上级补助和业主自筹（资金来源）， 项目出资比例为100%，招标人为华蓥市交通投资开发有限责任公司。项目已具备招标条件，现对该项目的施工 进行公开招标。 网 1.2本招标项目由华蓥市发展和改革局（核准机关名称）核准（招标事项核准文号为华发改投〔2023〕191号）的 招标组织形式为委托招标（□自行招标 委托招标）。招标人选择的招标代理机构是华蓥市国晟工程项目管理 咨询有限公司。 务 2. 项目概况与招标范围 2.1建设地点：华蓥市高兴镇。 商 2.2建设内容及规模：改造城镇危旧房约4.5万平方米，户数共220户，3栋共9个单元。配套小区内道路、供水、供 电、供气主管网、消防、路灯等基础设施。 本次实施该项目一标段：其实施内容为：新建道四通路与兴政路连接道路64米，铺设安置房一期商业街人行道5766 平方米，配套完善排水、路灯、绿化等附属设施。 2.3计划工期：90日历天。 管 2.4招标范围：本项目施工一标段施工图纸及工程量清单范围内的所有工作。 2.5标段划分：施工一标段。 （说明本次招标项目的国建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 中 3.1.1资质条件：具有国家建设行政主管部门颁发的市政公用工程施工总承包三级及以上资质。 3.1.2业绩要求： □近年（至投标截止时间，不少于3年）（多项选择：□已完成 □已完成或新承接或正在施工）不少于（1至3个） 个类似项目。类似项目是指:。 无业绩要求。 3.1.3项目经理的资格要求： 项目经理（项目负责人）资格：市政公用工程(注册专业)二级及以上（级别）建造师，具有省级及以上住房城 乡建设主管部门颁发的安全生产考核合格证（B证），/（业绩要求），须为本单位人员（若为联合体投标，须为 联合体牵头人人员）。 □园林绿化工程项目经理（项目负责人）资格：（职称级别）专业技术职称，（业绩要求），须为本单位人员 （若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受不接受联合体投标。联合体投标的，应满足下列要求： /。 3.3各投标人均可就上述1(具体数量)标段投标。 3.4本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企业、与大企业的负责人 为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体标 准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》 （工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、 存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在3000万元以下的施工项目(标段) 应勾选此项。 ） 4. 招标文件的获取 网 4.1 凡有意参加投标者，请于2026-08-22 开始登录：全国公共资源交易平台（四川省·广安市）（网 址：https://gasggzy.cn）—“电子交易平台登录”—“投标登录”，通过数字证书免费下载招标资料（招标文件、 技术资料等）。 务 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 5.1投标文件递交的截止时间（投标截止时间，下同）为2商026-09-11 09:30，投标人应在投标截止时间前在线递交经 投标人数字证书加密的数据电文形式投标文件。 5.2 本项目开标实行（□见面开标使用不见面开标系统）开标方式，关于“不见面开标系统”的流程和注意事 项，请各交易主体在广安市公共资源交易网上道下载查看不见面开标系统操作指南。 6. 发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省）》和全国公共资源交易服务平台（四川省·四川 管 省）、全国公共资源交易平台（四川省· 广安市）(公告发布的其它媒介名称）上发布。 7.行政监督部门 单位名称：华蓥市发展国和改革局、华蓥市住房和城乡建设局 联系电话：0826-4895386、0826-4830288 8. 联系方式 中 招标人： 华蓥市交通投资开发有限责任公司 地 址： 四川省广安市华蓥市高兴火车站站前片区火车站北侧A幢1层商业4 邮 编： 638600 联系人： 王老师 电 话： 15196525437 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / 招标代理机构： 华蓥市国晟工程项目管理咨询有限公司 地 址： 四川省广安市华蓥市汪杜路397号附38号 邮 编： 638600 联系人： 唐老师 项目负责人： 唐玉琴 电 话： 13541983385 传 真： / 电子邮件： / 网 址： / 开户银行： / 网 账 号： / 日期：2026-08-21 务 注： （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家对投标人资商质的强制性规定。不是国家规定必须具备的资质，不得 作为资质要求。 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工程 相应指标，类似项目业绩的定义应明确，用语准确无歧义。 道 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受投 标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 管 信息来源:https://www.chinapipe.net/project/d3077474.html cqdingjiu 2026.08.24 12:31:57 国 中</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>80</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>四川, 华蓥市, 城镇危旧房改造, 市政公用工程, 施工一标段</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026年绵阳市安州区高标准农田建设项目施工招标公告</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>房建</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>绵阳市</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>安州区</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>本项目包括河清镇高标准改造提升高标准农田3万亩，秀水镇改造提升高标准农田0.6万亩，花荄镇改造提升高标准农田0.3万亩。</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>项目资金来自中央财政资金、地方财政配套资金，出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>高标准农田改造提升</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026年绵阳市安州区高标准农田建设项目施工招标公告 1. 招标条件 1.1本招标项目2026年绵阳市安州区高标准农田建设项目（项目名称）已由绵阳市农业农村局（项目审批、核准 或备案机关名称）以绵农发【2026】16号（批文名称及编号）批准建设，项目业主为绵阳市安州区土壤肥料站， 建设资金来自中央财政资金、地方财政配套资金（资金来源），出资比例为100%，招标人为绵阳市安州区土壤 肥料站。项目已具备招标条件，现对该项目的2026年绵阳市安州区高标准农田建设项目施工进行公开招标。 网 1.2本招标项目为绵阳市行政区域内的国家投资工程建设项目，绵阳市农业农村局（核准机关名称）核准（招标 事项核准文号为绵农发【2026】16号）的招标组织形式为□自行招标委托招标。招标人选择的招标代理机构是四 川中汇信成工程管理咨询有限公司。 2. 项目概况与招标范围 务 2.1 项目概况 建设地点：河清镇安罗村、白溪村、宝华村、广红村、桂商丰村、皇龙村、金华村、七一村、同盛村、同心村、 月溪村；秀水镇大泉村、农联村、蟠龙村、桥楼村和双泉村；花荄镇龙游村、狮回村。 建设内容及规模：①河清镇高标准改造提升高标准农田3万亩。②秀水镇改造提升高标准农田0.6万亩。③花荄镇 改造提升高标准农田0.3万亩。 道 标段划分：施工一个标段。 计划工期：360 日历天。 管 2.2 招标范围 本项目施工图纸及工程量清单所示的全部内容及发包人根据需要交由承包人实施的三通一平等建设内容（应具 备资质，须为可不执行国招标或政府采购程序的建设内容,应纳入工程变更审批）。 3. 投标人资格要求 中 3.1本次招标要求投标人须具备具备国家行政主管部门颁发的水利水电工程施工总承包二级或以上资质，近3年 （□已完工的□已完工的或正在施工的已完工的或正在施工的或新承接的）1个类似项目（类似项目指：单项合 同金额5000万元以上的水利或农业工程施工总承包（或工程总承包）），并在人员、设备、资金等方面具有相应 的施工能力。 3.2本次招标□接受不接受联合体投标。 联合体投标的，应满足下列要求：/。 3.3各投标人均可就上述合同标段中的1个(具体数量)合同标段投标。招标人□允许不允许投标人拟派的同一批项 目主要人员（项目经理、技术负责人）在1个及以上标段任职。 □3.4本次招标仅面向中小企业发包（其中属于大型企业的分支机构、存在控股股东为大型企业、与大型企业的 负责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。 具体标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定 的通知》（工信部联企业〔2011〕300 号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除 技术复杂、存在特殊要求外，我市依法必须招标的国家投资工程，投标最高限价在5000万元以下的施工项目（标 段）应勾选此项。） 4. 招标文件的获取 4.1凡有意参加投标者： 请于2026-08-21起登陆全国公共资源交易平台（四川省·绵阳市）（网址：http://ggzy.my.gov.cn），通过数字证 书免费下载招标资料（招标文件、技术资料等）。 4.2 除上述方式外，招标人不提供其他任何报名和招标文件获取的方式。 5. 投标文件的递交 5.1 投标文件递交的截止时间（投标截止时间，下同）为2026-09-10 09:20，投标人应在截止时间前通过全国公 共资源交易平台（四川省·绵阳市）（电子招标投标交易平台）在线递交经投标人数字证书签名制作的数据加 密电子投标文件。 网 5.2逾期送达的投标文件，电子招标投标交易系统将予以拒收。 6. 发布公告的媒介 务 本次招标公告在全国公共资源交易平台（四川省）上发布。其他发布公告的媒介：全国公共资源交易平台（四 川省·绵阳市）（招标人自行选择，也可不填）。 商 7. 本项目招标投标行政监督部门 行政监督部门：绵阳市农业农村局电 话：0816-2268914 道 传 真：/电子邮件：/ 地 址：/ 8. 招标人承诺 管 本招标文件已经招标人（含招标代理机构）审查，不存在违反国家法律、法规、政策的情形。因招标文件设置 违反国家法律、法规、政策造成的相应后果，由招标人（含招标代理机构）负责。 国 9. 联系方式 招标人： 绵阳市安州区土壤肥料站 招标代理机构： 四川中汇信成工程管理咨询有限公司 中 四川省成都市武侯区二环路南三段5号人南大 地 址： 绵阳市安州区花荄镇白鹤路3号 地 址： 厦B座9楼10号 邮 编： 622651 邮 编： 610000 联系人： 董先生 联系人： 秦先生 电 话： 0816-6155882 电 话： 028-87549149 信息来源:https://www.chinapipe.net/project/d3077437.html cqdingjiu 2026.08.24 12:31:57</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>80</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>高标准农田, 改造提升, 施工招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>金堂县2026年大豆单产提升工程施工招标公告</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>水利</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>金堂县</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>新建滴灌(喷灌)灌区16处，面积2070亩，配套机井5处、提灌站10处，利用现有供水泵站延伸管道灌溉700亩；新建提灌站5座；新建200m3圆形蓄水池10口，整治原有蓄水池4口；整治原有渠道10公里；购置智能灌溉机器人（车）2台。</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>政府资网金</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>水利设施</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>金堂县2026年大豆单产提升工程施工招标公告 1. 招标条件 1.1本招标项目 金堂县2026年大豆单产提升工程 (项目名称)已由 成都市农业农村局 (项目审批、核 准或备案机关名称)以 成都市农业农村局关于金堂县2026年大豆单产提升工程初步设计方案的批 复、[2026]2-33，成都市农业农村局关于金堂县2026年大豆单产提升工程初步设计方案变更的批复、[2026]8-18 （批文名称及编号）批准建设，项目业主为 金堂县农业农村局 ，建设资金来自 政府资 网 金 （资金来源），项目出资比例为 100% ，招标人为 成都金农兴投资管理有限公司。项目已具 备招标条件，现对该项目的施工进行公开招标。 1.2本招标项目由 成都市农业农村局 （核准机关名称）核准（招标事项核准文号 为 [2026]2-33、[2026]8-18 ）的招标组织形式为 委托招标 （□自行招务标 委托招标）。招标人选择 的招标代理机构是 四川朋顺工程项目管理有限公司 。 2. 项目概况与招标范围 商 2.1建设地点：官仓街道、栖贤街道。 2.2建设规模及内容：新建滴灌(喷灌)灌区16处，面积2070亩，配套机井5处、提灌站10处，利用现有供水泵站延 伸管道灌溉700亩；新建提灌站5座；新建200m3圆形蓄水池10口，整治原有蓄水池4口；整治原有渠道10公里；购 道 置智能灌溉机器人（车）2台。 2.3计划工期：180日历天。 2.4招标范围：本项目施工图及工程管量清单所示全部工程内容。 2.5质量标准：达到国家、行业现行验收合格标准。 2.6标段划分：本项目施工一个标段。 国 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 中 3.1本次招标要求投标人须具备 3.1.1资质要求： 具有国家行政主管部门颁发的水利水电工程施工总承包贰级及以上（含有效期内的叁级）资 质的单位 。 3.1.2业绩要求：（本项为多选） 近年（2023 年 01 月 01 日至投标截止时间，不少于3年）（多项选择：□已完成 已完成或新承接 或正在施工）不少于 1 （1 至3个）个类似项目。类似项目是指: 单项合同金额不低于500万 元水利工程相关施工业绩 。 □无业绩要求。 3.1.3项目负责人的资格要求：具有 水利水电工程专业二级及以上注册建造师 证 书， / （业绩要求） ，须为投标人本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 3.3本次招标仅面向中小企业发包（其中属于大型企业的分支机构、存在控股股东为大型企业、与大型企业的 负责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。 具体标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定 的通知》（工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除 技术复杂、存在特殊要求外，我省依法必须招标的国家投资工程，投标最高限价在3000万元以下的施工项目（标 段）应勾选此项。） 3.4各投标人均可就上述 1 (具体数量)标段投标，可中标的标段数量为 1 个。 4. 招标文件的获取 4.1凡有意参加投标者，请于 2026 年 08 月 22日起，使用CA数字证书在成都市公共资源电子交易云平 台(www.cdggzy.com）（以下简称“电子交易云平台”）免费下载招标资料（招标文件及相关资料），获得“拟 投标项目回执”。 网 4.2 招标人不提供邮购招标文件服务。 5. 投标文件的递交 务 ●（不见面开标）5.1 投标文件递交的截止时间（投标截止时间，下同）为2026年09月11日09时30分，招标人或其 委托代理机构，以及已在投标截止时间前按规定上传投标文件的投标人，均应在开标当日投标截止时间前登录 不见面开标系统（网址：www.cdggzy.com），录入相关人员姓名、电话等基本信息。投标人未按时登录不见面开 标系统，错过开标解密时间的，由投标人自行承担不利后商果。 ●（不见面开标）5.2 投标人应在解密开始后30分钟内在线完成投标文件解密。投标文件未能在规定时间内成功 解密的，视为投标人未在规定时间内提交投标文件，由投标人自行承担责任。不见面开标项目不接受投标人现 场递交光盘等形式的投标文件，不接受投标人道现场解密投标文件。 6. 发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）、成都市公共资源交易服务中心（网址：http://ggzyjy.sc.gov.cn、 管 www.cdggzy.com）上发布。 7. 行政监督 单位名称： 金堂县农业国农村局 联系电话： 028-84982519 8.联系方式 中 招 标 人： 成都金农兴投资管理有限公司 地 址：四川省成都市金堂县竹篙镇竹富路466号1栋2楼（食用菌产业园区） 邮 编： 610400 联 系 人： 邓老师 电 话： 028-84905666 招标代理机构： 四川朋顺工程项目管理有限公司 地 址： 成都市青羊区顺城大街269号富力中心A座2103 邮 编： 610000 联 系 人： 朱老师 电 话： 028-86925238 2026 年 08 月 21日 注： （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不得 作为资质要求。 网 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工程 相应指标，类似项目业绩的定义应明确，用语准确无歧义。 务 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受投 标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 信息来源:https://www.chinapipe.net/project/d3077434.html 商 cqdingjiu 2026.08.24 12:31:58 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>滴灌(喷灌)灌区设备、机井、提灌站、蓄水池、渠道整治设备、智能灌溉机器人（车）</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>80</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>金堂县, 大豆单产提升工程, 水利设施, 滴灌, 喷灌, 机井, 提灌站, 蓄水池, 渠道整治, 智能灌溉机器人</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>金堂县2026年玉米单产提升工程施工招标公告</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>房建</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>金堂县</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>新建输配水管道147.5km，新建首部枢纽21座，田间自动化控制闸阀1474套，中等流量喷枪1349道套、快速取水阀188套，300m3蓄水池2座，移动式喷灌设备10套。</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>政府资金，网项目出资比例为100%</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>输配水管道，首部枢纽，自动化控制闸阀，中等流量喷枪，快速取水阀，蓄水池，移动式喷灌设备</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>金堂县2026年玉米单产提升工程施工招标公告 1. 招标条件 1.1本招标项目 金堂县2026年玉米单产提升工程 (项目名称)已由 成都市农业农村局 (项目审批、核 准或备案机关名称)以 成都市农业农村局关于金堂县2026年玉米单产提升工程初步设计方案的批复、[2026] 2-32， 成都市农业农村局关于金堂县2026年玉米单产提升工程初步设计方案变更的批复、[2026] 8-17 （批文名称及编 号）批准建设，项目业主为 金堂县农业农村局 ，建设资金来自 政府资金 （资金来源）， 网 项目出资比例为 100% ，招标人为 成都金农兴投资管理有限公司 。项目已具备招标条件，现对该 项目的施工进行公开招标。 1.2本招标项目由 成都市农业农村局 （核准机关名称）核准（招标事项核准文号为 ）的招标组织形式 为 委托招标 （□自行招标 委托招标）。招标人选择的招标代理机构务是 四川方裕工程项目管理有限 公司 。 2. 项目概况与招标范围 商 2.1建设地点：金堂县。 2.2建设规模及内容：新建输配水管道147.5km，新建首部枢纽21座（其中包括自动反冲洗砂石过滤器、自动反冲 洗叠片式过滤器，增压水泵，施肥设施及相应的电气设施等），田间自动化控制闸阀1474套，中等流量喷枪1349 道 套、快速取水阀188套，300m3蓄水池2座，移动式喷灌设备10套。 2.3计划工期：180日历天。 2.4招标范围：本项目施工图及工程管量清单所示全部工程内容。 2.5质量标准：达到国家、行业现行验收合格标准。 2.6标段划分：本项目施工一个标段。 国 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 中 3.1本次招标要求投标人须具备 3.1.1资质要求： 具有国家行政主管部门颁发的水利水电工程施工总承包贰级及以上（含有效期内的叁级）资 质的单位 。 3.1.2业绩要求：（本项为多选） 近年（2023 年 01 月 01 日至投标截止时间，不少于3年）（多项选择：□已完成 已完成或新承接 或正在施工）不少于 1 （1 至3个）个类似项目。类似项目是指: 单项合同金额不低于500万 元水利工程相关施工业绩 。 □无业绩要求。 3.1.3项目负责人的资格要求：具有 水利水电工程专业二级及以上注册建造师 证 书， / （业绩要求） ，须为投标人本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： / 。 3.3本次招标仅面向中小企业发包（其中属于大型企业的分支机构、存在控股股东为大型企业、与大型企业的 负责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。 具体标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定 的通知》（工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除 技术复杂、存在特殊要求外，我省依法必须招标的国家投资工程，投标最高限价在3000万元以下的施工项目（标 段）应勾选此项。） 3.4各投标人均可就上述 1 (具体数量)标段投标，可中标的标段数量为 1 个。 4. 招标文件的获取 4.1凡有意参加投标者，请于2026 年 08 月 22日起，使用CA数字证书在成都市公共资源电子交易云平 台(www.cdggzy.com）（以下简称“电子交易云平台”）免费下载招标资料（招标文件及相关资料），获得“拟 投标项目回执”。 网 4.2 招标人不提供邮购招标文件服务。 5. 投标文件的递交 务 ●（不见面开标）5.1 投标文件递交的截止时间（投标截止时间，下同）为2026年09月14日09时30分，招标人或其 委托代理机构，以及已在投标截止时间前按规定上传投标文件的投标人，均应在开标当日投标截止时间前登录 不见面开标系统（网址：www.cdggzy.com），录入相关人员姓名、电话等基本信息。投标人未按时登录不见面开 标系统，错过开标解密时间的，由投标人自行承担不利后商果。 ●（不见面开标）5.2 投标人应在解密开始后30分钟内在线完成投标文件解密。投标文件未能在规定时间内成功 解密的，视为投标人未在规定时间内提交投标文件，由投标人自行承担责任。不见面开标项目不接受投标人现 场递交光盘等形式的投标文件，不接受投标人道现场解密投标文件。 6. 发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）、成都市公共资源交易服务中心（网址：http://ggzyjy.sc.gov.cn、 管 www.cdggzy.com）上发布。 7. 行政监督 单位名称： 金堂县农业国农村局 联系电话： 028-84982519 8.联系方式 中 招 标 人： 成都金农兴投资管理有限公司 地 址：四川省成都市金堂县竹篙镇竹富路466号1栋2楼（食用菌产业园区） 邮 编： 610400 联 系 人： 邓老师 电 话： 028-84905666 招标代理机构： 四川方裕工程项目管理有限公司 地 址： 成都市郫都区福粮路锦巷兰台十一栋2106 邮 编： 610000 联 系 人： 刘老师 电 话： 028-63947572 2026 年 08 月 21日 注： （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不得 作为资质要求。 网 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工程 相应指标，类似项目业绩的定义应明确，用语准确无歧义。 务 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受投 标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 商 信息来源:https://www.chinapipe.net/project/d3077433.html cqdingjiu 2026.08.24 12:31:58 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>排水钢管 Φ200*6m：3000米</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>80</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>金堂县, 2026年玉米单产提升工程, 输配水管道, 自动化控制闸阀, 蓄水池, 移动式喷灌设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>攀枝花市钒钛高新区金江片区排水防涝能力提升工程施工招标公告</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>攀枝花市</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>攀枝花市</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>项目改造金江片区排水防涝管网及设施，主要包含以下内容:（1）改造B*H=600*800排水边沟2238m;（2）改造B*H=1500*2000排洪沟1306道m，B*H=2000*1500排洪沟120m,B*H=2500*3000排洪沟450m，B*H=3500*4000排洪沟2800m，B*H=5000*4000 排洪沟2845mB*H=6000*4000排洪沟545m;（3）排洪沟清淤18484m;排洪涵清淤2500m;（4）改造两座雨水调蓄池，规模为8000t/d和1000t/d;（5）同步布设智能物联感知设备。</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>总投资6920万元</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>排水边沟、排洪沟、雨水调蓄池、智能物联感知设备</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>攀枝花市钒钛高新区金江片区排水防涝能力提升工程施工招标公告 1. 招标条件 1.1本招标项目攀枝花市钒钛高新区金江片区排水防涝能力提升工程(项目名称)已由攀枝花钒钛高新技术 产业开发区科技创新和经济发展局(项目审批、核准或备案机关名称)以关于批复攀枝花市钒钛高新区金江片区排 水防涝能力提升工程可行性研究报告的函、攀钒钛科经函[2025]56号（批文名称及编号）批准建设，项目业主为 攀枝花钒钛高新技术产业开发区投资和政务服务中心，建设资金来自上级补助资金及地方配套资金（资金来 源），项目出资比例为100%，招标人为攀枝花钒钛高新技术产业开发区投资和政务服务中心。项目已具备招标 条件，现对该项目的施工进行公开招标。 网 1.2本招标项目由攀枝花钒钛高新技术产业开发区科技创新和经济发展局（核准机关名称）核准（招标事项核准 文号为攀钒钛科经函[2025]56号）的招标组织形式为委托招标（□自行招标 委托招标）。招标人选择的招标代 理机构是四川省中城泰达工程咨询集团有限公司。 务 2. 项目概况与招标范围 2.1项目名称：攀枝花市钒钛高新区金江片区排水防涝能力提升工程。 商 2.2建设地点：攀枝花市钒钛高新区金江片金江片区。 2.3建设内容及投资：项目改造金江片区排水防涝管网及设施，主要包含以下内容:（1）改造B*H=600*800排水边 沟2238m;（2）改造B*H=1500*2000排洪沟1306道m，B*H=2000*1500排洪沟120m,B*H=2500*3000排洪 沟450m，B*H=3500*4000排洪沟2800m，B*H=5000*4000 排洪沟2845mB*H=6000*4000排洪沟545m;（3）排洪沟清 淤18484m;排洪涵清淤2500m;（4）改造两座雨水调蓄池，规模为8000t/d和1000t/d;（5）同步布设智能物联感知设 备；总投资6920万元。 管 2.4招标范围：本项目施工图设计范围内的全部内容，施工直至竣工验收合格及整体移交、工程保修期内的缺陷 修复和保修工作等全部工作，具体范围详见招标工程量清单。 2.5标段划分：1个标段。 国 2.6计划工期：540日历天。 2.7质量要求：达到国家现行施工质量验收规范的合格标准 。 中 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质条件： （1）具有独立法人资格；（2）具有建设行政主管部门颁发的市政公用工程施工总承包二级及 以上资质 。 3.1.2业绩要求： 近年（ 2023 年 1 月 1 日至投标截止时间，不少于3年）（□已完成 已完成或新承接或正在施工）不少于 1 （1至3个）个类似项目。类似项目是指: 市政公用工程施工业绩(业绩需提供省级及以上公共资源交易网中标公示 查询截图，在建或新承接还需提供中标通知书及施工合同，已完成的还需提供中标通知书、施工合同及竣工验 收报告 。 □无业绩要求。 3.1.3项目经理的资格要求： 项目经理（项目负责人）资格： 市政公用工程 (注册专业)二级及以上（级别）建造师，具有省级及以上住房 城乡建设主管部门颁发的安全生产考核合格证（B证），/（业绩要求），须为本单位人员（若为联合体投标，须 为联合体牵头人人员）。 □园林绿化工程项目经理（项目负责人）资格： （职称级别）专业技术职称， （业绩 要求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： 。 3.3各投标人均可就上述 1 (具体数量)标段投标。 □ 3.4本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股网东为大企业、与大企业的负责人 为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体标 准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》 （工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、 存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在3000万元以下的施工项目(标段)应勾选此项。 务 ） 4. 招标文件的获取 4.1 凡有意参加投标者，请于 2026 年 08 月 22 日开始登陆商：□全国公共资源交易平台（四川省）（网 址：http://ggzyjy.sc.gov.cn）—“登录”——“交易主体”—“建设工程”，通过数字证书免费下载招标资料（招 标文件、技术资料等）。全国公共资源交易平台（四川省· 攀枝花 市（州））（网址： http://www. pzhggzy.cn ）—“登录”—“ 攀枝花市工程建设交易系统 ”，通过数字证书免费下载招标资料（招标文件、技术资料等）。 道 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 管 投标文件递交的截止时间（投标截止时间，下同）为2026年09月14日9时30分，投标人应在投标截止时间前在线 递交经投标人数字证书加密的数据电文形式投标文件。 6. 发布公告的媒介 国 本次招标公告在《全国公共资源交易平台（四川省）》和全国公共资源交易平台（四川省·攀枝花 市）(公告发布的其它媒介名称）上发布。 7.行政监督部门 中 单位名称： 攀枝花钒钛高新技术产业开发区自然资源和建设交通局 联系电话： / 8. 联系方式 招 标 人：攀枝花钒钛高新技术产业开发区投资和政务服务中心 地 址：攀枝花市仁和区科创路8号 邮 编：617000 联 系 人：彭老师 电 话：0812-3982759 传 真：/ 电子邮件：/ 网 址：/ 开户银行：/ 账 号：/ 招标代理机构：四川省中城泰达工程咨询集团有限公司 地 址：成都市金牛区金科中路32号迪舒美领4栋12号 网 邮 编：610000 联 系 人：饶先生 务 项目负责人：饶寨东 电 话：028-87776626 商 信息来源:https://www.chinapipe.net/project/d3077430.html cqdingjiu 2026.08.24 12:31:58 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>排水边沟 B*H=600*800 2238m; 排洪沟 B*H=1500*2000 1306道m, B*H=2000*1500 120m, B*H=2500*3000 450m, B*H=3500*4000 2800m, B*H=5000*4000 2845m, B*H=6000*4000 545m; 排洪沟清淤 18484m; 排洪涵清淤 2500m; 雨水调蓄池 8000t/d 和 1000t/d</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>80</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>排水防涝, 排水边沟, 排洪沟, 雨水调蓄池</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>中二十四局集团上海电务电化有限公司天眉乐高速公路项目JD3标、JA3标隔离栅、防落物网、防眩板、电缆、光缆及硅芯管询价补遗公告</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>乐山市</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>乐山市</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>本次询价采购JD-03包件硅芯管的底色、色谱如下：商序号规格底色添加色标颜色1Φ40/33黑色黑色道2Φ40/33黑色白色1x43Φ40/33黑色黄色1x44Φ40/33黑色蓝色管1x45Φ40/33黑色绿色1x46Φ40/33黑色红色1x47Φ40/33黑色国紫色1x48Φ40/33黑色白色2x39Φ40/33黑色黄色2x310Φ40/33黑色蓝色2x311Φ40/33黑色绿色2x312Φ40/33黑色红色2x313Φ40/33黑色紫色2x314Φ40/33黑色白色3x215Φ40/33黑色黄色3x216Φ40/33黑色蓝色3x217Φ40/33黑色绿色3x218Φ40/33黑色红色3x2</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>硅芯管</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>中二十四局集团上海电务电化有限公司天眉乐高速公路项目JD3标、JA3标隔离栅、防落物网、防眩板、电缆、 光缆及硅芯管询价补遗公告 各潜在报价单位： 为保障本次询价采购工作公平、公正、公开开展，确保各报价单位准确、完整理解本次询价项目相关要求，针 对本次 【 中铁二十四局集团上海电务电化有限公司天眉乐高速公路项目 JD3标、JA3标隔离栅、防落物网、防眩 板、电缆、光缆及硅芯管询价 】 （询价编号： CR24(2026)-DWDH-XJ-TML-JDJA-01）询价文件，经采购单位核 查确认，现对文件相关内容作如下 补遗 、补充及更正，本 补遗 与原询价文件具有同等法律效力。 网 一、 补遗如下 1.原文件内容：【 第二章 供应商报价 ， 报价函附件 3付款方的承诺 】 ； 务 更正后内容：【第二章 供应商报价，报价函附件 3付款 方式 的承诺】 ， 报价单位 应说明响应询价文件中的付款 方式。 2. 本次询价采购 JD-03包件硅芯管的底色、色谱如下： 商 序号 规格 底色 添加色标 颜 色 1 Φ40/33 黑色 黑色 道 2 Φ40/33 黑色 白色 1×4 3 Φ40/33 黑色 黄色 1×4 4 Φ40/33 黑色 兰色 管1×4 5 Φ40/33 黑色 绿色 1×4 6 Φ40/33 黑色 红色 1×4 7 Φ40/33 黑色 国紫色 1×4 8 Φ40/33 黑色 白色 2×3 9 Φ40/33 黑色 黄色 2×3 中 10 Φ40/33 黑色 兰色 2×3 11 Φ40/33 黑色 绿色 2×3 12 Φ40/33 黑色 红色 2×3 13 Φ40/33 黑色 紫色 2×3 14 Φ40/33 黑色 白色 3×2 15 Φ40/33 黑色 黄色 3×2 16 Φ40/33 黑色 兰色 3×2 17 Φ40/33 黑色 绿色 3×2 18 Φ40/33 黑色 红色 3×2 3.本次询价采购采用经评审的最低投标价报价法：质量、服务满足询价文件全部实质性条款，经资格及符合性审 查合格后，按有效报价由低至高排序，推荐合理最低价为成交供应商。 二、补充说明事项 1.本 补遗 为本次询价文件的组成部分，与原询价文件内容不一致之处，以本 补遗 为准；本 补遗 未提及的内容， 仍按原询价文件规定执行。 2.各报价单位须充分研读本 补遗 全部内容，严格按照 补遗 后的完整文件要求编制、提交报价文件，未结合本 补 遗 制作的报价文件，视为无效报价。 3 .各潜在报价单位收到本 补遗 后，无需单独回复确认，自行落实文件解读及报价编制工作即可。 三、联系方式 1.采购 组织 单位 ： 中铁二十四局集团有限公司设备物资集采中心电务分中心 联 系 人： 陈先生 联系 电话： 021-51226136 2.采购人 ： 中铁二十四局集团上海电务电化有限公司天眉乐高速公路项目 JD3标网、JA3标项目经理部 地 址： 四川省乐山市市中区佛光路 525号 技术 联系人： 左先生 务 联系 电话： 19136188150 中铁二十四局集团有限公司设备物资集采中心电务分中心 商 2026 年 8 月 20 日 信息来源:https://www.chinapipe.net/project/d3077384.html 道 cqdingjiu 2026.08.24 12:31:58 管 国 中</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Φ40/33黑色白色1x4；Φ40/33黑色黄色1x4；Φ40/33黑色蓝色1x4；Φ40/33黑色绿色1x4；Φ40/33黑色红色1x4；Φ40/33黑色国紫色1x4；Φ40/33黑色白色2x3；Φ40/33黑色黄色2x3；Φ40/33黑色蓝色2x3；Φ40/33黑色绿色2x3；Φ40/33黑色红色2x3；Φ40/33黑色紫色2x3；Φ40/33黑色白色3x2；Φ40/33黑色黄色3x2；Φ40/33黑色蓝色3x2；Φ40/33黑色绿色3x2；Φ40/33黑色红色3x2</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>80</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 近三天, 管材, 招标商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>贡井区2026年大豆单产提升工程招标计划</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>自贡市</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>贡井区</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>实施建设大豆种植智能滴灌系统2处，共计300亩智能滴灌示范区网，新建蓄水池23座；开展大豆单产提升技术推广。</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>估算总投资14455000.00元</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>智能滴灌系统、蓄水池</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>贡井区2026年大豆单产提升工程招标计划 项目批准文件及文号 贡发改批[2026]18号(贡发 招标项目名称 贡井区2026年大豆单产提升工程 （如有） 改批[2026]18号) 招标人 自贡市贡井区农业农村局 联系人及联系方式 陈老师:0813-3307310 估算总投资 14455000.00 项目分类 市政基础设施工程 （元） 新建、改造6处农村机电提灌站及农村机电提灌站相关设施建设，提升改善大豆灌面约30000亩; 招标项目概况 实施建设大豆种植智能滴灌系统2处，共计300亩智能滴灌示范区网，新建蓄水池23座;开展大豆单 产提升技术推广。 序号 招标内容 投标人主要资格条件要求 预计招标时间 拟招标内容 1 施工 详见招标文件 2026-09-21 00:00:00 务 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3077426.html 商 cqdingjiu 2026.08.24 12:31:58 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>新建蓄水池23座；实施建设大豆种植智能滴灌系统2处，共计300亩智能滴灌示范区网。</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>80</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>贡井区, 2026年, 大豆单产提升工程, 智能滴灌系统, 蓄水池, 投资金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>隆昌市住房和城乡建设局隆昌市城市核心区南部片区燃气配套管网改造项目焊缝探伤检测采购废标公告</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>能源</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>内江市</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>隆昌市</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>隆昌市城市核心区南部片区燃气配套管网改造项目焊缝探伤检测采购</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>焊缝探伤检测服务</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>隆昌市住房和城乡建设局隆昌市城市核心区南部片区燃气配套管网改造项目焊缝探伤检测采购废标公告 一、项目基本情况 采购项目编号：N5110832026000184 采购项目名称：隆昌市城市核心区南部片区燃气配套管网改造项目焊缝探伤检测采购 二、项目终止的原因 网 终止合同包：合同包1 终止原因： 务 合同包一的废标原因为：符合专业条件的供应商或者对招标文件作实质响应的供应商不足三家的；。 三、项目后续执行情况 商 合同包1:重新开展采购活动 道 四、其他补充事宜 投诉受理单位：本项目同级财政部门，即内江市隆昌市财政局 管 联系电话：0832-3911628 联系人：钟老师 国 地址：隆昌市滨江路3段64号 五、凡对本次公告内容提出询问，请按以下方式联系。 中 1.采购人信息 名称：隆昌市住房和城乡建设局 地址：四川省隆昌市金鹅街道康复东路62号 联系方式：18581037348 2.采购代理机构信息 名称：四川梦意招标代理有限公司 地址：四川省内江市隆昌市金鹅镇环城北路二段81号 联系方式：18283278039 3.项目联系方式 项目联系人：袁女士 电话：18283278039 四川梦意招标代理有限公司 2026年08月21日 信息来源:https://www.chinapipe.net/project/d3077360.html cqdingjiu 2026.08.24 12:31:59 网 务 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>70</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>隆昌市, 燃气配套管网改造, 焊缝探伤检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>崇州市三江街道舒桥社区农饮水接水工程(红线外)询比公告</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>其他/未识别</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>崇州市</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>崇州市三江街道舒桥社区农饮水接水工程(红线外)询比公告</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>崇州市三江街道舒桥社区农饮水接水工程(红线外)询比公告 采购方式 公开询比 招标编号 AA202607031JCCD 招标业主 四川京创建设工程有限公司成都分公司 所属地区 四川省 发布时间 2026-08-21 截止时间 2026-08-27 正文详见图片 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 报价网址：http://ecp.capitalwater.cn/ 国 信息来源:https://www.chinapipe.net/project/d3077281.html 中 cqdingjiu 2026.08.24 12:31:59</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>四川, 管材招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>华蓥市全域乡村振兴建设项目(一期)21号公路和美乡村建设项目二标段招标公告</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>华蓥市</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>对全市5万亩高标准农田进行提档升级，建设粮油园区3万亩，全域开展农村人居环境整治，打造乡村旅游聚居村落80个，配套建设乡村振兴道路、停车场和标识导视系统等旅游服务设施等。</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>项目业主为华蓥市农业农村局，建设资金来自财政资金及地方专项债券资金，项目出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>市政公用工程施工</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>华蓥市全域乡村振兴建设项目(一期)21号公路和美乡村建设项目二标段招标公告 1. 招标条件 1.1本招标项目华蓥市全域乡村振兴建设项目(一期)(项目名称)已由华蓥市发展和改革局(项目审批、核 准或备案机关名称)以《华蓥市发展和改革局关于华蓥市全域乡村振兴建设项目(一期)可行性研究报告的批复》 （华发改投〔2022〕37号）（批文名称及编号）批准建设，项目业主为华蓥市农业农村局，建设资金来自财政资 金及地方专项债券资金（资金来源），项目出资比例为100%，招标人为华蓥市农业农村局。项目已具备招标条 件，现对该项目的施工进行公开招标。 网 1.2本招标项目由华蓥市发展和改革局（核准机关名称）核准（招标事项核准文号为华发改投〔2022〕37号）的招 标组织形式为委托招标（□自行招标 委托招标）。招标人选择的招标代理机构是华蓥市国晟工程项目管理咨 询有限公司。 务 2. 项目概况与招标范围 2.1标段划分：21号公路和美乡村建设项目二标段。 2.2建设地点：华蓥市古桥街道、阳和镇、红岩乡。 商 2.3建设内容及规模：对全市5万亩高标准农田进行提档升级，建设粮油园区3 万亩，全域开展农村人居环境整治， 打造乡村旅游聚居村落80个，配套建设乡村振兴道路、停车场和标识导视系统等旅游服务设施等。 道 本次实施该项目21号公路和美乡村建设项目二标段，其实施内容为：21号公路沿线人居环境整治、新建厕所（含 给排水安装工程）、新建一体化净水厂三座，配套建设供水管网，在公路沿线设置标识导视及其他配套附属设 施工程等。 管 2.4计划工期：90日历天。 2.5招标范围：本项目21号公路和美乡村建设项目二标段施工图纸及工程量清单范围内的所有工作。 （说明本次招标项目的国建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 中 3.1.1资质条件：具备国家建设行政主管部门颁发的市政公用工程施工总承包三级及以上资质。 3.1.2业绩要求： □近年（ 年 月 日至投标截止时间，不少于3年）（□已完成 □已完成或新承接或正在施工）不少 于 （1 至3个）个类似项目。类似项目是指: 。 无业绩要求。 3.1.3项目经理的资格要求： 项目经理（项目负责人）资格：市政公用工程(注册专业)二级及以上（级别）建造师，具有省级及以上住房城 乡建设主管部门颁发的安全生产考核合格证（B证）， / （业绩要求） ，须为本单位人员（若为联合体投 标，须为联合体牵头人人员）。 □园林绿化工程项目经理（项目负责人）资格： （职称级别）专业技术职称， （业绩 要求） ，须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： /。 3.3各投标人均可就上述 1 (具体数量)标段投标 。 3.4本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企业、与大企业的负责 人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体 标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通 知》（工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术 复杂、存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在3000万元以下的施工项目(标段) 应勾 选此项。） 4. 招标文件的获取 4.1 凡有意参加投标者，请于2026年08月22日开始登陆：全国公共资源交易平台（四川省·广安市（州）） （网址：https://zhjy.gazhcs.com/）—“登录”—“投标登录”，通过数字证书免网费下载招标资料（招标文件、技 术资料等）。 4.2 招标人不提供招标文件获取的其他方式。 务 5. 投标文件的递交 5.1投标文件递交的截止时间（投标截止时间，下同）为2026年09月11日09时30分，投标人应在投标截止时间前在 线递交经投标人数字证书加密的数据电文形式投标文件。 商 5.2本项目开标实行（□见面开标；使用不见面开标系统）开标方式，关于“不见面开标系统”的流程和注意 事项，请各交易主体在广安市公共资源交易网上下载查看不见面开标系统操作指南。 6. 发布公告的媒介 道 本次招标公告在《全国公共资源交易平台（四川省）》和全国公共资源交易平台（四川省· 广安市）(公 告发布的其它媒介名称）上发布。 管 7.行政监督部门 单位名称：华蓥市发展和改革局 联系电话：0826-48215国39 8.联系方式 招 标 人：华蓥市农业农村局 中 地 址：四川省广安市华蓥市华翠路9号 邮 编：638600 联 系 人：赵先生 电 话：18160128811 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / □ 招标代理机构： / 招标代理机构：华蓥市国晟工程项目管理咨询有限公司 地 址：四川省广安市华蓥市汪杜路397号附38号 邮 编：638600 联 系 人：谭先生 项目负责人：唐玉琴 网 电 话：0826-4666655 传 真： / 务 电子邮件： / 网 址： / 商 开户银行： / 账 号： / 道 2026年08月21日 管 注： （1）若划分标段，则国填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不得 作为资质要求。 中 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工程 相应指标，类似项目业绩的定义应明确，用语准确无歧义。 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受投 标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 信息来源:https://www.chinapipe.net/project/d3077250.html cqdingjiu 2026.08.24 12:32:02</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>70</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>乡村振兴, 公路, 农村人居环境整治, 乡村旅游</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>中铁七局三公司供应链分公司金属波纹管框架询价公告</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>其他/未识别</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>温江区</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>预应力混凝土用金属波纹管</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>金属波纹管</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>中铁七局三公司供应链分公司金属波纹管框架询价公告 GYLKJ2026-050 采购单位:中铁七局集团第三工程有限公司 发布时间:2026-08-21 08:56 报价截止时间:2026-08-25 18:00 招标方联系人:杨浩 网 招标方联系电话:18829048334 招标方邮箱: 务 监督方联系人:物资部 监督方联系电话:86367038 商 监督方邮箱: 保证金:0.0元 道 结算与发票信息: 结算方式： 管 支付条件： 发票种类： 发票抬头： 国 税号： 其他要求：中 交货信息: 交货方式: 收货人: 收货人联系方式: 其他说明事项: 流水号：询2026082100043 交 计量 技术标准及 标的编号 标的名称 规格型号 数量 货 送货地址 单位 要求 期 预应力混凝土用 西南区-四川省-成都市-温江区-中 0409001000042 JBG-100Z 13365.0 米 Φ80 金属波纹管 铁七局成温邛高速项目工地 预应力混凝土用 西南区-四川省-成都市-温江区-中 0409001000042 JBG-100Z 36027.0 米 Φ90 金属波纹管 铁七局成温邛高速项目工地 预应力混凝土用 西南区-四川省-成都市-温江区-中 0409001000042 JBG-100Z 920.0 米 Φ100 金属波纹管 铁七局成温邛高速项目工地 报价网址:http://www.crecgec.com 信息来源:https://www.chinapipe.net/project/d3077249.html cqdingjiu 2026.08.24 12:32:02 网 务 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>13365.0米 Φ80；36027.0米 Φ90；920.0米 Φ100</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>85</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>金属波纹管, 成都</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>布拖县2026年农村生活污水治理项目施工招标公告</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>凉山彝族自治州</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>布拖县</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>新建2m³三道格化粪池584座、3m³三格化粪池1022座、20m³三格化粪池2座、30m³三格化粪池2座，配套建设入户管、支管、干管、检查井、过滤池等。</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>项目资金来自除布拖县2026年中央和省级财政常态化帮扶资金外的其他渠道，不足部分由业主多渠道筹集。</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>化粪池、管线</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>布拖县2026年农村生活污水治理项目施工招标公告 1. 招标条件 1.1 本招标项目 布拖县2026年农村生活污水治理项目 (项目名称)已由 布拖县发展和改革局 (项目审 批、核准或备案机关名称)以 布发改经信函〔2026〕24号 （批文名称及编号）批准建设 ，项目业主为 凉 山彝族自治州布拖生态环境局 ，建设资金来自 除布拖县2026年中央和省级财政常态化帮扶资金外，不足部 分由业主多渠道筹集。 （资金来源），项目出资比例为 100% ，招标人为 凉山彝族自治州布拖生态环境 局 。项目已具备招标条件，现对该项目的施工进行公开招标。 网 1.2 本招标项目由 布拖县发展和改革局 （核准机关名称）核准（招标事项核准文号为 布发改经信函 〔2026〕24号 ）的招标组织形式为 委托招标 。 招标人选择的招标代理机构是四川兴泉工程项目管理有限 公司。 务 2. 项目概况与招标范围 2.1 建设地点：布拖县俄里坪镇延务村，乐安镇若普村，商 龙潭 镇沿江村、 合井村、 四菲戈洛村 。 2.2 建设规模：主要建设标准内容为新建2m3三道格化粪池 584座、 3m3三格化粪池 1022座、 20m3三格化粪池 2座、 30m3三格化 粪池 2座。配套建设入户管、 支管、 干管、 检查井、 过滤 管 池等。 项目所有新建化粪池、 管线统一采用地理式设计方式 建设。 国 中 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1 本次招标要求投标人须具备 3.1.1资质条件：具备独立法人资格，具有行政主管部门颁发的市政公用工程施 工总承包三级及以上资质。 3.1.2业绩要求： 近年（ 2023年01月01日 至投标截止时间，不少于3年）已完成 不少于1（1 至3个）个类似项目。类似项目 是指:市政公用工程类施工业绩1000万元及以上。 □ 无业绩要求。 3.1.3项目经理的资格要求 项目经理（项目负责人）资格：市政公用工程二级及以上(注册专业)（级别）建造师，具有省级及以上住房 城乡建设主管部门颁发的安全生产考核合格证（B证），/（业绩要求） ，须为本单位人员（若为联合体投标， 须为联合体牵头人人员）。 □ 园林绿化工程项目经理（项目负责人）资格： （职称级别）专业技术职 称， （业绩要求） ，须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2 本次招标不接受 联合体投标。 3.3 各投标人均可就上述1(具体数量)标段投标 。 3.4 本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企业、与大企业的负责 人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体 标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通 知》（工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术 复杂、存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在3000万元以下的施工项目(标段) 应勾 选此项。） 网 4. 招标文件的获取 4.1 凡有意参加投标者，请于 2026年08月20日 登录四川建设网（http://www.sccin.com/）进入“电子招标”栏目， 通过“凉山州公共资源交易平台登录入口”凭单位CFCA数字证书登录，登录并下载招标资料（招标文件、技术 务 资料等）（联系电话：028-85569858）。 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 商 投标文件递交的截止时间（投标截止时间，下同）为 2026年09月18日 09时00分 ，投标人应在投标截止时间前 在线递交经投标人数字证书加密的数据电文形式投标文件。 道 6. 发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省）》和四川建设网(公告发布的其它媒介名称）上发布。 管 7. 行政监督部门 单位名称：布拖县住房和城乡建设局 联系电话：/ 国 8. 联系方式 招 标 人：凉山彝族自治州布拖生态环境局 中 地 址：四川省布拖县平圳路15号 邮 编：615400 联 系 人：刘老师 电 话：0834-8533776 传 真：/ 电子邮件：/ 网 址：/ 开户银行：/ 账 号：/ □ 招标代理机构： / 招标代理机构：四川兴泉工程项目管理有限公司 地 址：四川省成都市天府新区华阳街道中兴上街199号 邮 编：610000 联 系 人：张旭宇 项目负责人：陈程 网 电 话：18308205888 传 真：/ 务 电子邮件：/ 网 址：/ 商 开户银行：/ 账 号：/ 道 2026年08月19日 管 注： （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人国的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不得 作为资质要求。 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工程 相应指标，类似项目业绩的定义应明确，用语准确无歧义。 中 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受投 标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 信息来源:https://www.chinapipe.net/project/d3077246.html cqdingjiu 2026.08.24 12:32:02</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2m³三道格化粪池584座、3m³三格化粪池1022座、20m³三格化粪池2座、30m³三格化粪池2座，配套建设入户管、支管、干管、检查井、过滤池等。</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>80</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>农村生活污水治理, 化粪池, 管线</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>凉山州·西昌市特殊教育学校学前教育教学楼改扩建项目招标计划</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>凉山彝族自治州</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>西昌市</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>本项目总规划用地面积为6665.90平方米，总建筑面积约10823.11平方米（其中已建建筑面积4519.92平方米，本次项目建筑面积6303.19平方米），项目总体包含新建1座地下车库及1栋学前教育教学楼和1栋大门，其中地上建筑面积4601.97平方米（学前教育教学楼和大门）；地下建筑面积1701.22平方米（包括地下车库、人防地下室、设备用房等）；改造教学楼及宿舍面积约4519.92平方米（含建筑外墙改造及消防管网改造）；绿化面积约2473.01平方米；道路及广场用地约1814.05平方米；400米室外消防给水管网、200米生活给水管网、400米室外污水管网、400米室外雨水管网、220米室外强电管网、220米室外弱电管网、1个混凝土格栅池等。</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>估算总投资35177600.00元</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>网房屋建筑工程</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>凉山州·西昌市特殊教育学校学前教育教学楼改扩建项目招标计划 西昌市发展和改革局关于凉山 州·西昌市特殊教育学校学前教 招标项目 凉山州·西昌市特殊教育学校学前教育教 项目批准文件及文号 育教学楼改扩建项目可行性研究 名称 学楼改扩建项目 （如有） 报告（代项目建议书）批复(西 发改审批〔2026〕49号) 招标人 西昌市特殊教育学校 联系人及联系方式 赵先生:0834-3223595 估算总投资 35177600.00 项目分类 网房屋建筑工程 （元） 本项目总规划用地面积为6665.90平方米，总建筑面积约10823.11平方米（其中已建建筑面积4519.92平 方米，本次项目建筑面积6303.19平方米），项目总体包含新建1座地下车库及1栋学前教育教学楼和1 栋大门，其中地上建筑面积4601.97平方米（学前教育教学楼和大门）；地下建筑面积1701.22平方米 务 招标项目 （包括地下车库、人防地下室、设备用房等）；改造教学楼及宿舍面积约4519.92平方米（含建筑外 概况 墙改造及消防管网改造）；绿化面积约2473.01平方米；道路及广场地用地约1814.05平方米；400米室 外消防给水管网、200米生活给水管网、400米室外污水管网、400米室外雨水管网、220米室外强电管 网、220米室外弱电管网、1个混凝土格栅池等。 商 拟招标内 序号 招标内容 投标人主要资格条件要求 预计招标时间 容 1 施工 详见招标文件 2026-09-21 00:00:00 备注：提前发布的招标计划内容仅供各方主体道提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3077244.html cqdingjiu 2026.08.24 12:32:02 管 国 中</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>外消防给水管网：200米；生活给水管网：400米；室外污水管网：400米；室外雨水管网：220米；米室外弱电管网：1个</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>80</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>凉山州, 西昌市, 特殊教育学校, 学前教育教学楼, 改扩建项目, 施工, 管材招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>东河(苍溪段)流域水污染治理工程招标计划</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>苍溪县</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>新建污水收集主支管网34.48km、污水入户管64.87km；对现有1座300m³/d污水处理站进行改扩建，将污水处理能力提升至500m³/d；新建污水资源化利用设施3套、视频监控系统9套、水质监测网络1套、水环境风险预警网络1套、监控平台1套；新建150m³/d污水处理站2座、200m³/d污水处理站1座、700m³/d污水处理站1座、化粪池1座、污水提升泵站11座、标志牌9块。</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>估算总投资69670300元</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>市政基础设施工程</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>东河(苍溪段)流域水污染治理工程招标计划 招标项目 东河（苍溪段）流域水污染治理工 项目批准文件及文 苍发改投资〔2026〕 号 名称 程 号 招标人 广元市苍溪生态环境局 联系人及联系方式 王老师;08395587000 估算总投资 69670300 项目分类 市政基础设施工程 （元） 新建污水收集主支管网34.48km、污水入户管64.87km；对现有1座300m3/d污水处理站进行改扩建， 招标项目 将污水处理能力提升至500m3/d；新建污水资源化利用设施3套、视网频监控系统9套、水质监测网络1 概况 套、水环境风险预警网络1套、监控平台1套；新建150m3/d污水处理站2座、200m3/d污水处理站1座、 700m3/d污水处理站1座、化粪池1座、污水提升泵站11座、标志牌9块。 序号 招标内容 预计招标时间 拟交易场所 拟招标内 务 完成本项目施工及 容 1 2026-08 苍溪县 监理等 商 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 道 信息来源:https://www.chinapipe.net/project/d3077243.html cqdingjiu 2026.08.24 12:32:03 管 国 中</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>排水钢管 Φ200*6m：3000米；排水入户管；污水处理站；资源化利用设施；视频监控系统；水质监测网络；水环境风险预警网络；监控平台；污水处理站；化粪池；污水提升泵站；标志牌</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>80</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>东河(苍溪段)流域水污染治理工程, 四川, 市政基础设施工程, 污水处理站, 资源化利用设施, 视频监控系统, 水质监测网络, 水环境风险预警网络, 监控平台</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>苍溪县构溪河流域水生态保护修复工程项目招标计划</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>苍溪县</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>新建生态缓冲带23597.6m2；新建底质改良及微地形改造面积约112287m2、新建挺水植物面 招标项目概积22457.4m2、沉水植物面积56143.5m2、浮叶植物面积11228.7m2、网鱼蚌螺修复区面积44914.8m2； 新建生态沟渠1858m，新建污水收集主支管1.6km、入户管1.2km。</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>估算总投资 27726700 元</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>市政基础设施工程</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>苍溪县构溪河流域水生态保护修复工程项目招标计划 招标项目名 苍溪县构溪河流域水生态保护修复 项目批准文件及文 苍发改投资〔2026〕 64号 称 工程 号 招标人 广元市苍溪生态环境局 联系人及联系方式 王老师;08395587000 估算总投资 27726700 项目分类 市政基础设施工程 （元） 新建生态缓冲带23597.6m2；新建底质改良及微地形改造面积约112287m2、新建挺水植物面 招标项目概 积22457.4m2、沉水植物面积56143.5m2、浮叶植物面积11228.7m2、网鱼蚌螺修复区面积44914.8m2； 况 新建生态沟渠1858m，新建污水收集主支管1.6km、入户管1.2km。 序号 招标内容 预计招标时间 拟交易场所 完成本项目施工及 1 2026-08 务市辖区 拟招标内容 监理等 本项目施工及监理 2 2026-08 市辖区 等 商 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 道 信息来源:https://www.chinapipe.net/project/d3077240.html cqdingjiu 2026.08.24 12:32:03 管 国 中</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>排水钢管 Φ200*6m：3000米</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>80</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>苍溪县, 构溪河流域, 水生态保护修复, 市政基础设施工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>开江县2026年大豆单产提升工程项目招标计划</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>其他/未识别</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>达州市</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>开江县</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>建设大豆单产提升工程示范区3万亩，其中核心区-水肥一体化滴网灌工程1750亩、辐射区-水源工程28250亩。</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>估算总投资14500000元</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>大豆单产提升工程</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>开江县2026年大豆单产提升工程项目招标计划 招标项目名 项目批准文件及 开江县2026年大豆单产提升工程项目 达市农[2026]25号 称 文号（如有） 联系人及联系方 招标人 开江县农业农村局 唐老师；17748170115 式 估算总投资 14500000 项目分类 农业综合 （元） 建设大豆单产提升工程示范区3万亩，其中核心区-水肥一体化滴网灌工程1750亩、辐射区-水源工 招标项目概 程28250亩。项目规划建设大豆3万亩单产提升工程。涵盖“基础设施+智慧农业+技术集成”三大 况 板块。具体招标内容以招标文件为主。 序号 招标内容 投标人主要资格条件要求 预计招标时间 拟招标内容 务 1 施工、设备等 以最终发布的招标文件为准 2026-09-21 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3077175.html 商 cqdingjiu 2026.08.24 12:32:03 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>80</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>开江县, 2026年, 大豆单产提升工程, 招标计划, 四川, 管材</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>中国铁路成都局集团有限公司成铁总承包公司隆昌市石盘滩大型灌区提升改造项目管道下穿成渝铁路、成渝高铁项目钢筋混凝土管采购流标公告</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>内江市</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>隆昌市</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>钢筋混凝土管采购</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>钢筋混凝土管</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>中国铁路成都局集团有限公司成铁总承包公司隆昌市石盘滩大型灌区提升改造项目管道下穿成渝铁路、成渝高 铁项目钢筋混凝土管采购流标公告 一、项目名称：隆昌市石盘滩大型灌区提升改造项目管道下穿成渝铁路、成渝高铁工程钢筋混凝土管采购（编 号：WZ 2026-057） 二、公告发布日期：2026年8月18日 三、报名截止时间：2026年8月20日 网 四、拟开标时间：2026年8月27日9：30 五、流标原因：报名采购申请人数少于3家，采购流标。 务 六、联系人：刘老师，联系电话：18349359223。 特此公告！ 商 道 采购人名称：成都铁路工程总承包有限责任公司 日期：2026年8月21日 管 信息来源:https://www.chinapipe.net/project/d3077107.html cqdingjiu 2026.08.24 12:32:03 国 中</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>80</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 管材招标, 商机</t>
         </is>
       </c>
     </row>

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078437.html</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -619,7 +619,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>管材4802米；预制构件247个</t>
+          <t>https://www.chinapipe.net/project/d3078389.html</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -690,7 +690,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078606.html</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078567.html</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -828,7 +828,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米；DN110PE输水管道0.7公里；DN89x4.5毫米涂塑无缝钢管5.564公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378公里；DN100涂塑钢管15.883公里；DN80 涂塑钢管11.624公里；DN65 涂塑钢管13.336公里；DN50涂塑钢管37.861公里；DN40涂塑钢管93.378</t>
+          <t>https://www.chinapipe.net/project/d3078450.html</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -895,7 +895,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>排水材料</t>
+          <t>https://www.chinapipe.net/project/d3078467.html</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078339.html</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078338.html</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>抗旱供水；新建节水灌溉提灌站21座；整治山坪塘44口；建设水肥一体化系统；完善田间引水渠堰、排水沟及管网；安装智能监控、气象、虫情、土壤墒情系统</t>
+          <t>https://www.chinapipe.net/project/d3078219.html</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>抗旱供水；新建节水灌溉提灌站21座；整治山坪塘44口；建设水肥一体化系统；完善田间引水渠堰、排水沟及管网；分片区安装智能监控、气象、虫情、土壤墒情系统</t>
+          <t>https://www.chinapipe.net/project/d3078218.html</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米</t>
+          <t>https://www.chinapipe.net/project/d3078217.html</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米</t>
+          <t>https://www.chinapipe.net/project/d3078214.html</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>DN40(PN10)个 200; DN40(PN16)个 10; DN50(PN10)个 500; DN50(PN16)个 10; DN80(PN10)个 200; DN80(PN16)个 10; DN100(PN10)个 10; DN100(PN16)个 10; DN150(PN10)个 10; DN150(PN16)个 10; DN150(PN25)个 10; DN200(PN10)个 10; DN200(PN16)个 10; DN300(PN16)个 10; DN40个 100; DN40(25KG)个 10; DN40(16kg)个 10; DN50个 100; DN50(16kg)个 10; DN50(25KG)个 10; DN80个 100; DN80(16KG)个 10; DN80(25KG)个 10; DN100个 10; DN100(16KG)个 10; DN100(25KG)个 10; DN150个 10; DN150(16kg)个 10; DN150(25KG)个 10; DN200个 10; DN200(16kg)个 10; DN200(25KG)个 10</t>
+          <t>https://www.chinapipe.net/project/d3078192.html</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米</t>
+          <t>https://www.chinapipe.net/project/d3078130.html</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078119.html</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>净水厂设备及配件；配水管网及配件；一体化供水泵站设备及配件；原水管</t>
+          <t>https://www.chinapipe.net/project/d3078105.html</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078035.html</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078019.html</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>更换居民气表约11700只、居民灶前自闭阀约112717只、燃气连接用不锈钢波纹软管约112717根；更新改造庭院埋地燃气管网约6913m，更新改造燃气立管及表后管道约9419户，更新切断阀约489套等。</t>
+          <t>https://www.chinapipe.net/project/d3077961.html</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>梯台修筑127.5亩，梯田修筑61.56亩，稻虾地块修筑128.83亩，恢复地类整治1.22亩；新建Φ160PE输水管道1949米，C25混凝土排水沟（0.5m*0.6m）320米；改建3.0m宽C25混凝土机耕道905米。</t>
+          <t>https://www.chinapipe.net/project/d3077954.html</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>智能燃气系统设备1018台(套)，居民立管务更换6443户，户外切断阀1500个，智能家用报警器5000套，户外表箱更换11024个，调压箱更换1025台，标志桩(砖)10000块。</t>
+          <t>https://www.chinapipe.net/project/d3077935.html</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077904.html</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>DN15 1.6MPa 件 带压力表,DN20 1.6MPa 件 带压力表,DN25 1.6MPa 件 带压力表；提供样品一个,DN32 1.6MPa 件 带压力表,DN40 1.6MPa 件 带压力表,DN50 1.6MPa 件 带压力表,DN65 1.6MPa 件 带压力表,DN80 1.6MPa 件 带压力表,DN100 1.6MPa 件 带压力表,DN15 2.5MPa 件 带压力表；含不锈钢螺栓,DN20 2.5MPa 件 带压力表；含不锈钢螺栓,DN25 2.5MPa 件 带压力表；含不锈钢螺栓,DN32 2.5MPa 件 带压力表；含不锈钢螺栓,DN40 2.5MPa 件 带压力表；含不锈钢螺栓,DN50 2.5MPa 件 带压力表；含不锈钢螺栓,DN65 2.5MPa 件 带压力表；含不锈钢螺栓,DN80 2.5MPa 件 带压力表；含不锈钢螺栓,DN100 2.5MPa 件 带压力表；含不锈钢螺栓,DN15 1.6MPa 件,DN20 1.6MPa 件,DN25 1.6MPa 件,DN25 2.5MPa 件,DN32 1.6MPa 件,DN32 2.5MPa 件,DN40 1.6MPa 件,DN40 2.5MPa 件,DN50 1.6MPa 件,DN50 2.5MPa 件,DN65 1.6MPa 件 含不锈钢螺栓,DN65 2.5MPa 件 含不锈钢螺栓,DN80 1.6MPa 件 含不锈钢螺栓,DN80 2.5MPa 件 含不锈钢螺栓,DN100 1.6MPa 件 含不锈钢螺栓,DN100 2.5MPa 件 含不锈钢螺栓,DN15 1.6MPa 件,DN20 1.6MPa 件,DN25 1.6MPa 件,DN40 1.6MPa 件,DN50 1.6MPa 件,DN65 1.6MPa 件,DN80 1.6MPa 件,DN100 1.6MPa 件,DN15 1.6MPa 件,DN20 1.6MPa 件,DN25 1.6MPa 件,DN32 1.6MPa 件,DN40 1.6MPa 件,DN50 1.6MPa 件,DN65 1.6MPa 件,DN80 1.6MPa 件,DN100 1.6MPa 件</t>
+          <t>https://www.chinapipe.net/project/d3077898.html</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077891.html</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077886.html</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>全面检测总工期：40个工作日。</t>
+          <t>https://www.chinapipe.net/project/d3077867.html</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米</t>
+          <t>https://www.chinapipe.net/project/d3077858.html</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077792.html</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>排水钢管 DN150: 8.1千米；DN200: 29.3千米；DN250: 23千米；DN300: 5.1千米；DN400: 11.9千米；DN500: 6.8千米，材质为3PE防腐内热熔防腐钢管</t>
+          <t>https://www.chinapipe.net/project/d3077724.html</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>DN15 1.6MPa 件 带压力表；含不锈钢螺栓</t>
+          <t>https://www.chinapipe.net/project/d3077649.html</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077605.html</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>铺设原水输水管网总长度约16.7公里，配套建设新城供水主管约77km</t>
+          <t>https://www.chinapipe.net/project/d3077567.html</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077531.html</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>DN300-DN600排水管网约2.0公里；修复DN300-DN1000管道约28.98公里</t>
+          <t>https://www.chinapipe.net/project/d3077506.html</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>排水管网修复</t>
+          <t>https://www.chinapipe.net/project/d3077435.html</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>孝子溪水库引水管道：17.5km；其中需新建引水隧洞内置管道：1.5km；柑橘基地管网：3.25km</t>
+          <t>https://www.chinapipe.net/project/d3078207.html</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米</t>
+          <t>https://www.chinapipe.net/project/d3077140.html</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>袖阀管承压不小于5MPa，单节接头处带连接丝扣(配相应连接头)，间距50cm打孔缠橡胶带，另配堵头。</t>
+          <t>https://www.chinapipe.net/project/d3077066.html</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>DN125米：840米；DN180米：840米；DN125个：140个；DN180个：140个</t>
+          <t>https://www.chinapipe.net/project/d3078608.html</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078483.html</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078449.html</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078430.html</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078524.html</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>FRPP管Φ160PN1.0*13.3-黑色: 80米, FRPP弯头(90°)Φ160PN1.0*13.3-R=1.5D-黑色: 8个</t>
+          <t>https://www.chinapipe.net/project/d3078468.html</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Φ100mm三通接头：150个；100mm接头：1500个；DN100防结晶封器：1526个；DF8B内燃机车导水管套：10个；PVC管：5051米；PVC管：100米；PVC管：3525米；DN110弯头：250个；HDPE过轨管：1563米；HDPE过轨管：2986米；DN100盲管：6210米；DN80盲管：200米；50mm×2m盲管：7172米</t>
+          <t>https://www.chinapipe.net/project/d3078392.html</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>DN300*50mm，含胶圈：1100.00m；DN500*55mm，含胶圈：1500.00m；DN600*60mm，含胶圈：1000.00m；DN800*80mm，含胶圈：1100.00m；DN1000*100mm，含胶圈：350.00m；DN1200*120mm，含胶圈：200.00m；C30,D800*140mm，含爬梯：100.00m；C30,D1000*140mm，含爬梯：100.00m；C30,D1200*140mm，含爬梯：100.00m；C30,D1500*150mm，含爬梯：100.00m；C30,D1800*180mm，含爬梯：100.00m；C30,D800*140mm，含爬梯，含140mm厚底座：100.00m；C30,D1000*140mm，含爬梯，含140mm厚底座：100.00m；C30,D1200*140mm，含爬梯，含140mm厚底座：100.00m；C30,D1500*150mm，含爬梯，含150mm厚底座：100.00m；C30,D1800*180mm，含爬梯，含180mm厚底座：100.00m；C30,D800*120mm，含爬梯：400.00m；φ1280变800，厚度140mm，含吊钩：100.00个；φ1480变800，厚度140mm，含吊钩：100.00个；φ1800变800，厚度160mm，含吊钩：100.00个；φ2160变800，厚度200mm，含吊钩：100.00个；700*400*800mm*70mm厚度：180.00个；1560*400*800mm*70mm厚度：100.00个；1700*1100*160mm：10.00m；1700*1700*160mm：4.00m；2100*1800*220mm：6.00m；2400*2000*220mm：4.00m</t>
+          <t>https://www.chinapipe.net/project/d3078565.html</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078356.html</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078292.html</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>用于地面集输工程的建设</t>
+          <t>https://www.chinapipe.net/project/d3078290.html</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078281.html</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078278.html</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078222.html</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>[object Object],[object Object],[object Object],[object Object],[object Object],[object Object],[object Object],[object Object],[object Object],[object Object],[object Object]</t>
+          <t>https://www.chinapipe.net/project/d3078197.html</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078163.html</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078145.html</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078054.html</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3078004.html</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077993.html</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077959.html</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077958.html</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077945.html</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077939.html</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>排水管道、污水管网、物联感知设备的更新改造和安装。</t>
+          <t>https://www.chinapipe.net/project/d3077901.html</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077864.html</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>智能水表-有线光电传输智能水表；智能水表-NB-IOT物联网带阀水表；智能水表-智能远传水表-远传水表(超声波水表)</t>
+          <t>https://www.chinapipe.net/project/d3077838.html</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077596.html</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>西部水厂管廊管道及加压站部分管道防腐 500㎡，钢制设施、设备防腐 6100㎡，高新区景苑小区管道防腐 55㎡，长葫引水管道DN1200钢管防腐 1380㎡，一桥硬合厂宿舍侧DN400钢管防腐 16.5㎡，一桥硬合厂宿舍侧DN300钢管防腐 14.15㎡</t>
+          <t>https://www.chinapipe.net/project/d3077586.html</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077575.html</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077563.html</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>雨污排水管网：10千米；弱电管网：5千米</t>
+          <t>https://www.chinapipe.net/project/d3077560.html</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077557.html</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077552.html</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>排水和雨水排放</t>
+          <t>https://www.chinapipe.net/project/d3077551.html</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>排水主管网 Φ300~Φ800mm 约2.08km；雨水管网 Φ300~Φ800mm 约0.88km；污水管网 Φ300~Φ800mm 约1.2km；现状管道清淤疏通长度约1.23km；配套建设检查井等附属构筑物；路面恢复提升材料，车行道改造面积约9188平方米，人行道改造约3295平方米。</t>
+          <t>https://www.chinapipe.net/project/d3077550.html</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077548.html</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077526.html</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077513.html</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077502.html</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077498.html</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>宜宾高新区高场片区老旧小区改造项目：改造小区燃气管道17160m，给排水管道18935m，电力和通信线路13320m，改造停车位685个；新增充电桩137个，小区消防设施58套，户内燃气安全设施1956套，分类垃圾回收站点10个；改造闲置社区用房为日间照料中心4430m、便民中心5420m，改造小区内道路10192m及配套基础设施。宜宾高新区高场片区城中村配套基础设施项目：新建公共配套用房总建筑面积21000m，其中养老托幼等服务设施15000m、其他公服用房6000m；新建公共停车位1600个及配置400个充电桩；新改建城中村配套道路约4.5km及其他基础设施建设。</t>
+          <t>https://www.chinapipe.net/project/d3077494.html</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>D219X6 米 3600; D159X6 米 200; D133X4 米 100; D108X4 米 200; D89X4 米 60; D76X3.5 米 120; D57X3.5 米 120; D45X3 米 18; D38X管3 米 90; D32X3 米 400; DN100 米 900; DN65 米 300; DN50 米 1000; 80*8 m 1438; 40*6 m 6675; 50*50*5 m 2672; 75*5 m 170; 10# m 790; DN25 m 1133; DN40 m 87; DN50 m 1083; DN100 m 130; D159*6 m 100</t>
+          <t>https://www.chinapipe.net/project/d3077488.html</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米</t>
+          <t>https://www.chinapipe.net/project/d3077478.html</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077474.html</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077437.html</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>滴灌(喷灌)灌区设备、机井、提灌站、蓄水池、渠道整治设备、智能灌溉机器人（车）</t>
+          <t>https://www.chinapipe.net/project/d3077434.html</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米</t>
+          <t>https://www.chinapipe.net/project/d3077433.html</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>排水边沟 B*H=600*800 2238m; 排洪沟 B*H=1500*2000 1306道m, B*H=2000*1500 120m, B*H=2500*3000 450m, B*H=3500*4000 2800m, B*H=5000*4000 2845m, B*H=6000*4000 545m; 排洪沟清淤 18484m; 排洪涵清淤 2500m; 雨水调蓄池 8000t/d 和 1000t/d</t>
+          <t>https://www.chinapipe.net/project/d3077430.html</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Φ40/33黑色白色1x4；Φ40/33黑色黄色1x4；Φ40/33黑色蓝色1x4；Φ40/33黑色绿色1x4；Φ40/33黑色红色1x4；Φ40/33黑色国紫色1x4；Φ40/33黑色白色2x3；Φ40/33黑色黄色2x3；Φ40/33黑色蓝色2x3；Φ40/33黑色绿色2x3；Φ40/33黑色红色2x3；Φ40/33黑色紫色2x3；Φ40/33黑色白色3x2；Φ40/33黑色黄色3x2；Φ40/33黑色蓝色3x2；Φ40/33黑色绿色3x2；Φ40/33黑色红色3x2</t>
+          <t>https://www.chinapipe.net/project/d3077384.html</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>新建蓄水池23座；实施建设大豆种植智能滴灌系统2处，共计300亩智能滴灌示范区网。</t>
+          <t>https://www.chinapipe.net/project/d3077426.html</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077360.html</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077281.html</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077250.html</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>13365.0米 Φ80；36027.0米 Φ90；920.0米 Φ100</t>
+          <t>https://www.chinapipe.net/project/d3077249.html</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2m³三道格化粪池584座、3m³三格化粪池1022座、20m³三格化粪池2座、30m³三格化粪池2座，配套建设入户管、支管、干管、检查井、过滤池等。</t>
+          <t>https://www.chinapipe.net/project/d3077246.html</t>
         </is>
       </c>
       <c r="N95" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>外消防给水管网：200米；生活给水管网：400米；室外污水管网：400米；室外雨水管网：220米；米室外弱电管网：1个</t>
+          <t>https://www.chinapipe.net/project/d3077244.html</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米；排水入户管；污水处理站；资源化利用设施；视频监控系统；水质监测网络；水环境风险预警网络；监控平台；污水处理站；化粪池；污水提升泵站；标志牌</t>
+          <t>https://www.chinapipe.net/project/d3077243.html</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>排水钢管 Φ200*6m：3000米</t>
+          <t>https://www.chinapipe.net/project/d3077240.html</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077175.html</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>https://www.chinapipe.net/project/d3077107.html</t>
         </is>
       </c>
       <c r="N100" t="n">

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -552,7 +552,8 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078437.html</t>
+          <t>包括雨水检查井、钢筋砼承插式雨水管道铺设、中粗砂回填等内容
+https://www.chinapipe.net/project/d3078437.html</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -619,7 +620,8 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078389.html</t>
+          <t>中建五局第三建设有限公司鑫旭达西南地区生产基地项目室外管材及预制构件采购
+https://www.chinapipe.net/project/d3078389.html</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -690,7 +692,8 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078606.html</t>
+          <t>项目服务内容自动农业气象监测系统、土壤墒情监测系统、智能虫情测报系统、杀虫控制系统、水肥一体化、宣传片拍摄等。
+https://www.chinapipe.net/project/d3078606.html</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -757,7 +760,8 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078567.html</t>
+          <t>西部（重庆）科学城德感片区污水管网修复完善工程项目所需（白沙部分新增）市政工程专业分包工程，包括非开挖紫外光修复、安装前道内部勘测、清淤、封堵气囊、导排水，钢内衬成环回顶，铺设防划垫膜，主物料的拉入、连接充气设备、安装排水软管、物料的充气/紫外光固化、冷却物料、切除管口扎头多余务、抽出内膜、CCTV检测验收、拆除堵通水修复，管道铺设、管件、检查井、完成建筑垃圾清理，路面恢复等主要工序和辅助工序。
+https://www.chinapipe.net/project/d3078567.html</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -828,7 +832,8 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078450.html</t>
+          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项目设备材料招标公告
+https://www.chinapipe.net/project/d3078450.html</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -895,7 +900,8 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078467.html</t>
+          <t>本项目涉及采购钢带增强聚乙烯螺旋波纹管和钢带波纹管密封胶圈，用于重庆高速巨能建设集团有限公司城开高速城开隧道泄水洞施工项目。
+https://www.chinapipe.net/project/d3078467.html</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -962,7 +968,8 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078339.html</t>
+          <t>采购项目名称为物资，具体采购内容包括第十四次物资区域联合授权公开谈判采购。
+https://www.chinapipe.net/project/d3078339.html</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1029,7 +1036,8 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078338.html</t>
+          <t>采购项目名称为'国网重庆电力主城一片区2026年原集体企业和各级产业单位第十四次物资区域联合授权公开谈判采购'，采购类型为物资。
+https://www.chinapipe.net/project/d3078338.html</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1100,7 +1108,8 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078219.html</t>
+          <t>本工程为9720亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站21座，整治山坪塘44口，建设主要建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。
+https://www.chinapipe.net/project/d3078219.html</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1171,7 +1180,8 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078218.html</t>
+          <t>本工程为9720亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站21座，整治山坪塘44口，建设主要建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。
+https://www.chinapipe.net/project/d3078218.html</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1242,7 +1252,8 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078217.html</t>
+          <t>本工程为1.7万亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站18座，整治山坪塘28口，建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。
+https://www.chinapipe.net/project/d3078217.html</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1313,7 +1324,8 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078214.html</t>
+          <t>新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007亩。主要内容包括水田整治、缓坡整治、梯台整治、恢复地类整治、耕地复耕整治、农机进出通道修建、提灌站修建、输水管道铺设、排水沟改建、田间道路改建等。
+https://www.chinapipe.net/project/d3078214.html</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1380,7 +1392,8 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078192.html</t>
+          <t>重庆中法供水2026年金属补偿器及柔性橡胶接头采购项目(第三次)比选公告
+https://www.chinapipe.net/project/d3078192.html</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1447,7 +1460,8 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078130.html</t>
+          <t>新建两岔水库取水浮船1座，设计取水规模为2万m/d；新建两岔水库取水浮船-坛高水厂原输水管道21km。
+https://www.chinapipe.net/project/d3078130.html</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1518,7 +1532,8 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078119.html</t>
+          <t>农村供水提质改造项目
+https://www.chinapipe.net/project/d3078119.html</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1589,7 +1604,8 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078105.html</t>
+          <t>新建供水规模10000立方米/天的净水厂1座，厂外配水主干管网长度约40公里，村镇配水支线管网长度约100公里，配套一体化供水泵站共15座，新增原水管约1公里。
+https://www.chinapipe.net/project/d3078105.html</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1660,7 +1676,8 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078035.html</t>
+          <t>重庆涪陵电力实业股份有限公司2026年第4批物资公开谈判采购
+https://www.chinapipe.net/project/d3078035.html</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1731,7 +1748,8 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078019.html</t>
+          <t>新建管道 PE 管管件工程量问题；新建道路石方工程量问题；重庆市双业融资担保有限公司信用资质、履约能力问题；建筑工程概算费用问题；总价报价下浮率计算问题；招标文件下载问题；施工单位盖章问题；建筑工程或者市政工程土石方施工业绩问题；投标文件格式填写问题；合同工程完工证书证明材料问题；招标人提供的工程量清单单项最高限价问题；投标函附录中工期、分包、工程质量要求和缺陷责任期对应约定内容问题；我公司业绩为三个项目合并招标问题；边坡治理施工业绩问题；任一清单的综合单价低于警戒线问题；业绩要求的竣工时间问题；财务报告提供问题；我公司业绩合同金额问题；招标人确定中标人问题；低价说明证明材料问题；招标人是否委派业主专家参与评标问题；我公司业绩项目经理变更问题；财务报告提供问题；专业分包业绩问题；投标文件制作系统软件导出的电子投标文件格式问题；项目经理以前在其他公司执业的业绩问题；在职的已退休的注册人员问题；投标函附录中的合同条款号填写问题；评标办法中已标价工程量清单要求的承诺问题；评标专家不被围猎问题。
+https://www.chinapipe.net/project/d3078019.html</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1802,7 +1820,8 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077961.html</t>
+          <t>大渡口区2024年居民户内燃气安全设施整改项目（二期）更换居民气表约11700只、居民灶前自闭阀约112717只、燃气连接用不锈钢波纹软管约112717根。大渡口区2024年城市燃气管道等老化更新改造项目（二期）更新改造庭院埋地燃气管网约6913m，更新改造燃气立管及表后管道约9419户，更新切断阀约489套等，并配套实施管网开挖回填、路面恢复、绿化恢复等。
+https://www.chinapipe.net/project/d3077961.html</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -1873,7 +1892,8 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077954.html</t>
+          <t>改造提升高标准农田326.59亩，其中高效节水灌溉面积130亩。主要内容包括梯台修筑、梯田修筑、稻虾地块修筑、恢复地类整治、输水管道安装、排水沟修建、机耕道改建等。
+https://www.chinapipe.net/project/d3077954.html</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -1944,7 +1964,8 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077935.html</t>
+          <t>大渡口区燃气管线及燃气相关设施设备改造提升，实现燃气管线智能化管理和保障燃气供给安全。
+https://www.chinapipe.net/project/d3077935.html</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -2011,7 +2032,8 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077904.html</t>
+          <t>项目详细内容无法识别
+https://www.chinapipe.net/project/d3077904.html</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -2078,7 +2100,8 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077898.html</t>
+          <t>为重庆分质供水有限公司提供不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀等设备材料。
+https://www.chinapipe.net/project/d3077898.html</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -2145,7 +2168,8 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077891.html</t>
+          <t>管网工程、土石方工程等。
+https://www.chinapipe.net/project/d3077891.html</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -2216,7 +2240,8 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077886.html</t>
+          <t>李市镇农村饮水管网改建工程
+https://www.chinapipe.net/project/d3077886.html</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -2287,7 +2312,8 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077867.html</t>
+          <t>长安工业渝北工厂供水管网泄露检测及修复询比采购
+https://www.chinapipe.net/project/d3077867.html</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -2358,7 +2384,8 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077858.html</t>
+          <t>重庆市九龙坡区城市老旧小区供水管网漏损治理及二次供水设施更新改造工程(二期)一标段
+https://www.chinapipe.net/project/d3077858.html</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -2425,7 +2452,8 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077792.html</t>
+          <t>项目详细内容无法识别
+https://www.chinapipe.net/project/d3077792.html</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -2496,7 +2524,8 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077724.html</t>
+          <t>该项目对百安坝等3个街道老旧市政供水管道及附属设施进行改造，配套智慧水务物联网感知设备建设，共计改造老旧市政供水管道84.2千米。
+https://www.chinapipe.net/project/d3077724.html</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -2563,7 +2592,8 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077649.html</t>
+          <t>为重庆分质供水有限公司提供不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀等设备材料。
+https://www.chinapipe.net/project/d3077649.html</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -2634,7 +2664,8 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077605.html</t>
+          <t>重庆市秀山自治县2026年提升农村饮水质量专项行动项目-溶溪片区(一标段)答疑及补遗通知
+https://www.chinapipe.net/project/d3077605.html</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -2705,7 +2736,8 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077567.html</t>
+          <t>酉阳县桃花源新城供水工程管网安装工程专业分包
+https://www.chinapipe.net/project/d3077567.html</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -2776,7 +2808,8 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077531.html</t>
+          <t>污水外排管道迁改
+https://www.chinapipe.net/project/d3077531.html</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -2847,7 +2880,8 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077506.html</t>
+          <t>本项目改建及修复管网总长度约30.98公里，雨污水错混接改造以及管网缺失改造DN300-DN600排水管网约2.0公里；修复DN300-DN1000管道约28.98公里。
+https://www.chinapipe.net/project/d3077506.html</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -2914,7 +2948,8 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077435.html</t>
+          <t>本项目改建及修复管网总长度约30.63公里，雨污水错混接改造以及管网缺失改造DN300-DN800排水管网约6.35公里；修复DN300-DN1200管道约24.28公里。
+https://www.chinapipe.net/project/d3077435.html</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -2985,7 +3020,8 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078207.html</t>
+          <t>主要整治孝子溪大堰水渠约17.5km;新建孝子溪水库引水管道约17.5km,其中需新建引水隧洞内置管道约1.5km;新建柑橘基地管网约3.25km;改建6000m蓄水池1座；新建2000m蓄水池2座；新建1000m蓄水池1座；新建500m³蓄水池2座；新建柑橘基地滴灌系统1套。
+https://www.chinapipe.net/project/d3078207.html</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -3056,7 +3092,8 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077140.html</t>
+          <t>涪陵区李渡新区水厂工程(一期)设计水量目标为10万m/d，二期水量目标为20万m/d，采用混凝、沉淀、过滤、消毒常规水处理工艺。一期工程项目主要建设内容包括取水及原水输送工程、净水厂工程、配水工程三部分。
+https://www.chinapipe.net/project/d3077140.html</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -3127,7 +3164,8 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077066.html</t>
+          <t>新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购
+https://www.chinapipe.net/project/d3077066.html</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -3202,7 +3240,8 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078608.html</t>
+          <t>本次计划对过轨管材料进行询价，询价内容包括DN125米、DN180米、DN125个、DN180个四种过轨管及其接头。
+https://www.chinapipe.net/project/d3078608.html</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -3277,7 +3316,8 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078483.html</t>
+          <t>法兰及其垫片,沟槽管件,铸铁管件,阀门,检查口,铜制管件,管道用材,套管,补偿器及软接头,过滤器,塑料管件,复合管件,不锈钢管件,钢制管件,阻火器,水箱,其它管件及管道用器材,铝合金管件,玻璃钢管件
+https://www.chinapipe.net/project/d3078483.html</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -3352,7 +3392,8 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078449.html</t>
+          <t>屏山县龙华、龙溪、大乘污水管网疏通及修复项目劳务分包工程
+https://www.chinapipe.net/project/d3078449.html</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -3427,7 +3468,8 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078430.html</t>
+          <t>本项目比选人为成都市中兴供水有限公司，主要从事市政基础设施、城市供水管网的投资、建设与运营。根据公司业务范围及建设需求，现面向社会进行给水管网施工单位的公开比选，邀请有能力的优秀比选申请人参加我公司的项目比选，并选出二至三家优秀企业共同承担2026年及2028年度成都市中兴供水有限公司供水区域内给水管网的施工任务。
+https://www.chinapipe.net/project/d3078430.html</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -3494,7 +3536,8 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078524.html</t>
+          <t>项目详细内容无法识别
+https://www.chinapipe.net/project/d3078524.html</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -3561,7 +3604,8 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078468.html</t>
+          <t>北部基地平原公司关于FRPP管Φ160及配套弯头项目采购公告
+https://www.chinapipe.net/project/d3078468.html</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -3636,7 +3680,8 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078392.html</t>
+          <t>中铁六局四川南广铁路站前三标工程隧道管材物资采购
+https://www.chinapipe.net/project/d3078392.html</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -3703,7 +3748,8 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078565.html</t>
+          <t>水泥制品
+https://www.chinapipe.net/project/d3078565.html</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -3770,7 +3816,8 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078356.html</t>
+          <t>中铁十五局集团四公司、地下公司、新能源公司八月份三次物资采购招标公告
+https://www.chinapipe.net/project/d3078356.html</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -3837,7 +3884,8 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078292.html</t>
+          <t>不锈钢材料
+https://www.chinapipe.net/project/d3078292.html</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -3904,7 +3952,8 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078290.html</t>
+          <t>金浅26井地面集输工程包括井口模块、除砂器橇、三相分离器橇、密闭装油橇、凝析油罐模块、气田水罐模块、放空分液罐模块、放空模块、出站模块等配套工程。
+https://www.chinapipe.net/project/d3078290.html</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -3979,7 +4028,8 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078281.html</t>
+          <t>喜德县冕山镇及两河口镇污水管道改造建设项目的具体内容见附件信息。
+https://www.chinapipe.net/project/d3078281.html</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -4046,7 +4096,8 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078278.html</t>
+          <t>甘眉工业园区污水管网建设项目的具体内容见附件信息。
+https://www.chinapipe.net/project/d3078278.html</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -4113,7 +4164,8 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078222.html</t>
+          <t>详见附件。
+https://www.chinapipe.net/project/d3078222.html</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -4188,7 +4240,8 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078197.html</t>
+          <t>四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告 四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告 四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005已具备采购条件，现公开邀请供应商参加询比采购活动。
+https://www.chinapipe.net/project/d3078197.html</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -4263,7 +4316,8 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078163.html</t>
+          <t>详细勘察服务
+https://www.chinapipe.net/project/d3078163.html</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -4338,7 +4392,8 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078145.html</t>
+          <t>蒸汽管道改造
+https://www.chinapipe.net/project/d3078145.html</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -4413,7 +4468,8 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078054.html</t>
+          <t>中微半导体设备成都研发及生产基地暨西南总部项目洁净室及一般机电包项目【UPVC】将开启线上采购。
+https://www.chinapipe.net/project/d3078054.html</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -4480,7 +4536,8 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3078004.html</t>
+          <t>水电五局卡拉水电站地厂项目经理部镀锌钢管等物资采购需求
+https://www.chinapipe.net/project/d3078004.html</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -4555,7 +4612,8 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077993.html</t>
+          <t>绵阳市游仙区(城区)老旧燃气管道等更新改造工程项目(一期)施工
+https://www.chinapipe.net/project/d3077993.html</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -4622,7 +4680,8 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077959.html</t>
+          <t>详见附件。
+https://www.chinapipe.net/project/d3077959.html</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -4689,7 +4748,8 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077958.html</t>
+          <t>燃气管道安装工程
+https://www.chinapipe.net/project/d3077958.html</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -4764,7 +4824,8 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077945.html</t>
+          <t>管道直饮水入户项目的建设内容包括设计及施工总承包。
+https://www.chinapipe.net/project/d3077945.html</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -4831,7 +4892,8 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077939.html</t>
+          <t>集输管道智能检测
+https://www.chinapipe.net/project/d3077939.html</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -4906,7 +4968,8 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077901.html</t>
+          <t>该项目涉及三个子项目：(一) 南充市西充县旧国城区排水防涝设施建设改造项目，包括更新改造不同规格的HDPE双壁波纹雨水管和混凝土雨水管，以及配套检查井和雨水口的改造；(二) 南充市西充县虹溪河片区污水管网更新改造项目，包括改造和新建不同规格的污水主管网和支管网，以及配套安装物联感知设备；(三) 南充市西充县洗笔路片区污水管网更新改造项目，包括改造和新建不同规格的污水管网，以及配套安装物联感知设备。
+https://www.chinapipe.net/project/d3077901.html</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -4981,7 +5044,8 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077864.html</t>
+          <t>西充县太平水厂、鹤鸣庵水厂及配套管网建设项目劳务分包
+https://www.chinapipe.net/project/d3077864.html</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -5056,7 +5120,8 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077838.html</t>
+          <t>马边彝族自治县自来水有限责任公司年度材料采购更正公告（第1次）
+https://www.chinapipe.net/project/d3077838.html</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -5131,7 +5196,8 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077596.html</t>
+          <t>邛崃经芦山至荥经高速公路项目邛崃段占压邛崃市天然气有限公司输气管道迁改工程设计。
+https://www.chinapipe.net/project/d3077596.html</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -5206,7 +5272,8 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077586.html</t>
+          <t>钢管及设施防腐
+https://www.chinapipe.net/project/d3077586.html</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -5281,7 +5348,8 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077575.html</t>
+          <t>管道直饮水项目的具体内容未在提供的信息中明确列出。
+https://www.chinapipe.net/project/d3077575.html</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -5356,7 +5424,8 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077563.html</t>
+          <t>本项目包括新建及改建高标准农田，涉及田块整治工程、灌溉排水工程、田间道路工程、土壤改良、农田输配电工程、农田防护与生态保护工程。
+https://www.chinapipe.net/project/d3077563.html</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -5431,7 +5500,8 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077560.html</t>
+          <t>对盐边县城北、清源片区老旧街区进行商提升改造，包括改造中环北路、西环北路、清河西路、盐中巷外立面排危改造约12.28万平方米，街区路面整治约12000平方米，街区雨污排水管网改造约10千米，改造适老化、适儿化服务用房约5000平方米，社区综合服务生活市场改造8500平方米，街区屋面防水改造约9900平方米，改造3500平方米街区边角地配套停车场及充电桩等基础设施，增设路灯280盏，公共活动健身区15处，街角口袋公园4处，改造清河西路、盐中巷街区安道全防护栏5公里，街区架空线入地4千米，弱电管网整治5千米，并同步完善消防、安防、垃圾收储、便民生活设施等配套公共服务设施。
+https://www.chinapipe.net/project/d3077560.html</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -5506,7 +5576,8 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077557.html</t>
+          <t>本项目总占地面积为149道225.64平方米，总建筑面积151550.12平方米，其中新建标准化厂房143913平方米、综合管理用房7637.12平方米，配套建设配套厂区道路、停车场、绿化工程、污水管网、给水管网、强弱电工程等配套工程。
+https://www.chinapipe.net/project/d3077557.html</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -5581,7 +5652,8 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077552.html</t>
+          <t>中子镇转斗（含何家坝）、校场坝生活污商水处理站覆盖范围内的排水管网更新改造以及检查井等附属设施建设。
+https://www.chinapipe.net/project/d3077552.html</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -5656,7 +5728,8 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077551.html</t>
+          <t>新改建管道:DN300污水管道162m、DN500 污水管道1884m、DN600 污水管道112m、DN300 雨水管道466.50m、DN600 雨水管道609m、 DN800 雨水管商道 390m、 DN1000 雨水管道1029m。并对涉及破损路面及配套设施等进行恢复。
+https://www.chinapipe.net/project/d3077551.html</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -5731,7 +5804,8 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077550.html</t>
+          <t>本项目管网部分为新建排水主管网长度约2.08km（雨水管网约0.88km，污水管网约1.2km），管径DN300～DN800；现状管道清淤疏通长度约为1.23km；配套建设检查井等附属构筑物以及路面恢复提升；道路部分为埋地排水管道施工路面破除与恢复，同时对设计范围内其他道路进行路面黑化提升，项目共涉及7条道路的路面改造，其中车行道改造面积约9188平方米，人行道改造约3295平方米。
+https://www.chinapipe.net/project/d3077550.html</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -5806,7 +5880,8 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077548.html</t>
+          <t>新建教学综合楼14500㎡、学生宿舍8500㎡、食堂3000㎡，以及附属用房、排水管网等配套基础设施。
+https://www.chinapipe.net/project/d3077548.html</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -5881,7 +5956,8 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077526.html</t>
+          <t>采购PE供水管材管件
+https://www.chinapipe.net/project/d3077526.html</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -5956,7 +6032,8 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077513.html</t>
+          <t>项目名称：2024年度成都&amp;绵阳区域洁净工程维修改造项目D标段；项目地点：四川省成都市郫都区；品牌范围：环琪、协羽。
+https://www.chinapipe.net/project/d3077513.html</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -6031,7 +6108,8 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077502.html</t>
+          <t>预应力高强混凝土管桩
+https://www.chinapipe.net/project/d3077502.html</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -6098,7 +6176,8 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077498.html</t>
+          <t>本项目因递交响应文件供应商不足2家而流标。
+https://www.chinapipe.net/project/d3077498.html</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -6173,7 +6252,8 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077494.html</t>
+          <t>本项目包括宜宾高新区高场片区老旧小区改造项目和宜宾高新区高场片区城中村配套基础设施项目的管网探测及测绘工作。
+https://www.chinapipe.net/project/d3077494.html</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -6248,7 +6328,8 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077488.html</t>
+          <t>钢管及型钢采购
+https://www.chinapipe.net/project/d3077488.html</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -6323,7 +6404,8 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077478.html</t>
+          <t>成都市绕城高速天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购/标段
+https://www.chinapipe.net/project/d3077478.html</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -6398,7 +6480,8 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077474.html</t>
+          <t>改造城镇危旧房约4.5万平方米，户数共220户，3栋共9个单元。配套小区内道路、供水、供电、供气主管网、消防、路灯等基础设施。新建道四通路与兴政路连接道路64米，铺设安置房一期商业街人行道5766平方米，配套完善排水、路灯、绿化等附属设施。
+https://www.chinapipe.net/project/d3077474.html</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -6473,7 +6556,8 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077437.html</t>
+          <t>本项目包括河清镇高标准改造提升高标准农田3万亩，秀水镇改造提升高标准农田0.6万亩，花荄镇改造提升高标准农田0.3万亩。
+https://www.chinapipe.net/project/d3077437.html</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -6548,7 +6632,8 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077434.html</t>
+          <t>新建滴灌(喷灌)灌区16处，面积2070亩，配套机井5处、提灌站10处，利用现有供水泵站延伸管道灌溉700亩；新建提灌站5座；新建200m3圆形蓄水池10口，整治原有蓄水池4口；整治原有渠道10公里；购置智能灌溉机器人（车）2台。
+https://www.chinapipe.net/project/d3077434.html</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -6623,7 +6708,8 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077433.html</t>
+          <t>新建输配水管道147.5km，新建首部枢纽21座，田间自动化控制闸阀1474套，中等流量喷枪1349道套、快速取水阀188套，300m3蓄水池2座，移动式喷灌设备10套。
+https://www.chinapipe.net/project/d3077433.html</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -6698,7 +6784,8 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077430.html</t>
+          <t>项目改造金江片区排水防涝管网及设施，主要包含以下内容:（1）改造B*H=600*800排水边沟2238m;（2）改造B*H=1500*2000排洪沟1306道m，B*H=2000*1500排洪沟120m,B*H=2500*3000排洪沟450m，B*H=3500*4000排洪沟2800m，B*H=5000*4000 排洪沟2845mB*H=6000*4000排洪沟545m;（3）排洪沟清淤18484m;排洪涵清淤2500m;（4）改造两座雨水调蓄池，规模为8000t/d和1000t/d;（5）同步布设智能物联感知设备。
+https://www.chinapipe.net/project/d3077430.html</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -6773,7 +6860,8 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077384.html</t>
+          <t>本次询价采购JD-03包件硅芯管的底色、色谱如下：商序号规格底色添加色标颜色1Φ40/33黑色黑色道2Φ40/33黑色白色1x43Φ40/33黑色黄色1x44Φ40/33黑色蓝色管1x45Φ40/33黑色绿色1x46Φ40/33黑色红色1x47Φ40/33黑色国紫色1x48Φ40/33黑色白色2x39Φ40/33黑色黄色2x310Φ40/33黑色蓝色2x311Φ40/33黑色绿色2x312Φ40/33黑色红色2x313Φ40/33黑色紫色2x314Φ40/33黑色白色3x215Φ40/33黑色黄色3x216Φ40/33黑色蓝色3x217Φ40/33黑色绿色3x218Φ40/33黑色红色3x2
+https://www.chinapipe.net/project/d3077384.html</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -6848,7 +6936,8 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077426.html</t>
+          <t>实施建设大豆种植智能滴灌系统2处，共计300亩智能滴灌示范区网，新建蓄水池23座；开展大豆单产提升技术推广。
+https://www.chinapipe.net/project/d3077426.html</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -6923,7 +7012,8 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077360.html</t>
+          <t>隆昌市城市核心区南部片区燃气配套管网改造项目焊缝探伤检测采购
+https://www.chinapipe.net/project/d3077360.html</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -6998,7 +7088,8 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077281.html</t>
+          <t>崇州市三江街道舒桥社区农饮水接水工程(红线外)询比公告
+https://www.chinapipe.net/project/d3077281.html</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -7073,7 +7164,8 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077250.html</t>
+          <t>对全市5万亩高标准农田进行提档升级，建设粮油园区3万亩，全域开展农村人居环境整治，打造乡村旅游聚居村落80个，配套建设乡村振兴道路、停车场和标识导视系统等旅游服务设施等。
+https://www.chinapipe.net/project/d3077250.html</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -7148,7 +7240,8 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077249.html</t>
+          <t>预应力混凝土用金属波纹管
+https://www.chinapipe.net/project/d3077249.html</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -7223,7 +7316,8 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077246.html</t>
+          <t>新建2m³三道格化粪池584座、3m³三格化粪池1022座、20m³三格化粪池2座、30m³三格化粪池2座，配套建设入户管、支管、干管、检查井、过滤池等。
+https://www.chinapipe.net/project/d3077246.html</t>
         </is>
       </c>
       <c r="N95" t="n">
@@ -7298,7 +7392,8 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077244.html</t>
+          <t>本项目总规划用地面积为6665.90平方米，总建筑面积约10823.11平方米（其中已建建筑面积4519.92平方米，本次项目建筑面积6303.19平方米），项目总体包含新建1座地下车库及1栋学前教育教学楼和1栋大门，其中地上建筑面积4601.97平方米（学前教育教学楼和大门）；地下建筑面积1701.22平方米（包括地下车库、人防地下室、设备用房等）；改造教学楼及宿舍面积约4519.92平方米（含建筑外墙改造及消防管网改造）；绿化面积约2473.01平方米；道路及广场用地约1814.05平方米；400米室外消防给水管网、200米生活给水管网、400米室外污水管网、400米室外雨水管网、220米室外强电管网、220米室外弱电管网、1个混凝土格栅池等。
+https://www.chinapipe.net/project/d3077244.html</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -7373,7 +7468,8 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077243.html</t>
+          <t>新建污水收集主支管网34.48km、污水入户管64.87km；对现有1座300m³/d污水处理站进行改扩建，将污水处理能力提升至500m³/d；新建污水资源化利用设施3套、视频监控系统9套、水质监测网络1套、水环境风险预警网络1套、监控平台1套；新建150m³/d污水处理站2座、200m³/d污水处理站1座、700m³/d污水处理站1座、化粪池1座、污水提升泵站11座、标志牌9块。
+https://www.chinapipe.net/project/d3077243.html</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -7448,7 +7544,8 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077240.html</t>
+          <t>新建生态缓冲带23597.6m2；新建底质改良及微地形改造面积约112287m2、新建挺水植物面 招标项目概积22457.4m2、沉水植物面积56143.5m2、浮叶植物面积11228.7m2、网鱼蚌螺修复区面积44914.8m2； 新建生态沟渠1858m，新建污水收集主支管1.6km、入户管1.2km。
+https://www.chinapipe.net/project/d3077240.html</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -7523,7 +7620,8 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077175.html</t>
+          <t>建设大豆单产提升工程示范区3万亩，其中核心区-水肥一体化滴网灌工程1750亩、辐射区-水源工程28250亩。
+https://www.chinapipe.net/project/d3077175.html</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -7598,7 +7696,8 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://www.chinapipe.net/project/d3077107.html</t>
+          <t>钢筋混凝土管采购
+https://www.chinapipe.net/project/d3077107.html</t>
         </is>
       </c>
       <c r="N100" t="n">

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材, 招标, 商机</t>
+          <t>四川, 管材, 招标, 商机</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>重庆, 管材, 预制构件, 采购</t>
+          <t>管材, 预制构件, 采购</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>重庆, 市政工程, 污水管网修复</t>
+          <t>市政工程, 污水管网修复</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 排水材料</t>
+          <t>管材, 招标, 排水材料</t>
         </is>
       </c>
     </row>
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>重庆, 物资, 采购</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -1041,11 +1041,11 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>重庆, 物资, 采购公告</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -1113,11 +1113,11 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>重庆, 节水灌溉, 柑橘, 抗旱供水, 提灌站, 山坪塘, 水肥一体化, 智能监控, 气象, 虫情, 土壤墒情</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -1185,11 +1185,11 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>重庆, 节水灌溉, 柑橘, 抗旱供水, 提灌站, 山坪塘, 水肥一体化, 智能监控</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -1257,11 +1257,11 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>重庆, 节水灌溉, 柑橘, 抗旱供水, 提灌站, 山坪塘, 水肥一体化, 智能监控, 气象, 虫情, 土壤墒情</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>重庆, 金属补偿器, 柔性橡胶接头, 采购项目, 比选公告</t>
+          <t>金属补偿器, 柔性橡胶接头, 采购项目, 比选公告</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>重庆, 川渝高竹新区, 引调水工程, 取水浮船, 输水管道</t>
+          <t>川渝高竹新区, 引调水工程, 取水浮船, 输水管道</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 农村供水提质改造</t>
+          <t>管材招标, 农村供水提质改造</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>重庆, 供水, 管网, 管材, 招标</t>
+          <t>供水, 管网, 管材, 招标</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>重庆, 2026年, 第4批物资公开谈判采购, 管道</t>
+          <t>2026年, 第4批物资公开谈判采购, 管道</t>
         </is>
       </c>
     </row>
@@ -1755,11 +1755,7 @@
       <c r="N19" t="n">
         <v>0</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>塑料管不计匹配分</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1829,7 +1825,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>重庆, 燃气安全设施, 城市燃气管道, 老化更新改造, 投资金额, 项目总投资</t>
+          <t>燃气安全设施, 城市燃气管道, 老化更新改造, 投资金额, 项目总投资</t>
         </is>
       </c>
     </row>
@@ -1897,11 +1893,11 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>高标准农田, 改造提升, 建筑工程施工, 财政资金, 重庆, 荣昌区</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1969,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>重庆, 燃气管道, 老化改造, 智能化管理, 燃气供给安全</t>
+          <t>燃气管道, 老化改造, 智能化管理, 燃气供给安全</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2037,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标</t>
+          <t>管材, 招标</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2173,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>重庆, 污水管网工程, 二期, 管网工程, 土石方工程, 2500万元</t>
+          <t>污水管网工程, 二期, 管网工程, 土石方工程, 2500万元</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2245,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>重庆, 水管, 农村饮水管网改建工程</t>
+          <t>水管, 农村饮水管网改建工程</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2317,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>重庆, 供水管网泄露检测及修复, 询比采购</t>
+          <t>供水管网泄露检测及修复, 询比采购</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2457,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>重庆, 管材</t>
+          <t>管材</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2529,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 改造工程</t>
+          <t>管材, 招标, 改造工程</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2597,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>重庆, 不锈钢闸阀, 不锈钢表前阀, 不锈钢减压阀, 不锈钢排气阀, 不锈钢止回阀, 管材招标</t>
+          <t>不锈钢闸阀, 不锈钢表前阀, 不锈钢减压阀, 不锈钢排气阀, 不锈钢止回阀, 管材招标</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2669,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>重庆, 提升农村饮水质量, 专项行动项目</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2741,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>酉阳县桃花源新城供水工程, 管网安装工程专业分包, 重庆, 管网安装工程</t>
+          <t>酉阳县桃花源新城供水工程, 管网安装工程专业分包, 管网安装工程</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2813,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材, 招标</t>
+          <t>四川, 管材, 招标</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2885,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>管材, 招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2953,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>重庆, 排水管网, 管网修复, 管网改造</t>
+          <t>排水管网, 管网修复, 管网改造</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3025,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>重庆, 管材招标, 勘察设计, 资金情况, 产品种类</t>
+          <t>管材招标, 勘察设计, 资金情况, 产品种类</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3097,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 水厂工程</t>
+          <t>管材, 招标, 水厂工程</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3169,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>重庆, 管材, 询比采购</t>
+          <t>管材, 询比采购</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3245,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材, 招标, 商机</t>
+          <t>重庆, 管材, 招标, 商机</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3321,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>不锈钢管件, 四川, 成都, 招标公告</t>
+          <t>不锈钢管件, 招标公告</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3397,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>重庆, 四川, 近三天, 管材招标商机</t>
+          <t>重庆, 近三天, 管材招标商机</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3473,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>成都, 供水, 管网施工, 劳务比选</t>
+          <t>供水, 管网施工, 劳务比选</t>
         </is>
       </c>
     </row>
@@ -3543,11 +3539,7 @@
       <c r="N44" t="n">
         <v>0</v>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>塑料管不计匹配分</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3613,7 +3605,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>FRPP管, 弯头, 四川</t>
+          <t>FRPP管, 弯头</t>
         </is>
       </c>
     </row>
@@ -3687,11 +3679,7 @@
       <c r="N46" t="n">
         <v>0</v>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>塑料管不计匹配分</t>
-        </is>
-      </c>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3753,11 +3741,11 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>水泥制品, 采购公告</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3881,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>不锈钢, 材料, 招标</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3949,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>管材, 地面集输工程, 四川</t>
+          <t>管材, 地面集输工程</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4025,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>四川, 污水管道</t>
+          <t>污水管道</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4093,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材, 招标</t>
+          <t>重庆, 管材, 招标</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4161,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材招标</t>
+          <t>重庆, 管材招标</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4237,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材, 招标, 商机</t>
+          <t>重庆, 管材, 招标, 商机</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4313,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>管材招标, 重庆, 四川, 近三天</t>
+          <t>管材招标, 重庆, 近三天</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4389,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>蒸汽管道改造, 四川</t>
+          <t>蒸汽管道改造</t>
         </is>
       </c>
     </row>
@@ -4475,11 +4463,7 @@
       <c r="N57" t="n">
         <v>0</v>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>塑料管不计匹配分</t>
-        </is>
-      </c>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4545,7 +4529,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>重庆, 四川, 近三天, 管材招标商机</t>
+          <t>重庆, 近三天, 管材招标商机</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4673,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材, 招标</t>
+          <t>重庆, 管材, 招标</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4741,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材招标</t>
+          <t>重庆, 管材招标</t>
         </is>
       </c>
     </row>
@@ -4975,11 +4959,7 @@
       <c r="N64" t="n">
         <v>0</v>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>塑料管不计匹配分</t>
-        </is>
-      </c>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5053,7 +5033,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>四川, 劳务分包, 管材</t>
+          <t>劳务分包, 管材</t>
         </is>
       </c>
     </row>
@@ -5127,11 +5107,7 @@
       <c r="N66" t="n">
         <v>0</v>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>塑料管不计匹配分</t>
-        </is>
-      </c>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5205,7 +5181,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>四川, 设计比选公告</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5257,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>重庆, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5333,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>分析, 重庆, 四川, 近三天, 管材, 招标, 商机</t>
+          <t>分析, 重庆, 近三天, 管材, 招标, 商机</t>
         </is>
       </c>
     </row>
@@ -5429,11 +5405,11 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>高标准农田, 新建及改建, 水利工程, 四川, 遂宁</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5485,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材, 招标</t>
+          <t>重庆, 管材, 招标</t>
         </is>
       </c>
     </row>
@@ -5581,11 +5557,11 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>现代农业融合发展示范园项目, 设计施工总承包, 四川, 南充市, 西充片区, 36633万元</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5713,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>苍溪县, 污水管网改造, 延伸覆盖, DN300, DN500, DN600, DN800, DN1000, 雨水管道, 污水管道</t>
+          <t>污水管网改造, 延伸覆盖, DN300, DN500, DN600, DN800, DN1000, 雨水管道, 污水管道</t>
         </is>
       </c>
     </row>
@@ -5885,11 +5861,11 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>扩建项目, 施工招标</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5941,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>PE供水管材管件, 四川</t>
+          <t>PE供水管材管件</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6093,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>四川, 预应力高强混凝土管桩, 公开竞争性谈判, 自筹资金</t>
+          <t>预应力高强混凝土管桩, 公开竞争性谈判, 自筹资金</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6161,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>四川, 管材, 招标</t>
+          <t>管材, 招标</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6237,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>宜宾, 高新区, 老旧小区改造, 管网探测, 测绘</t>
+          <t>高新区, 老旧小区改造, 管网探测, 测绘</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6313,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>重庆, 四川, 近三天, 管材招标, 商机</t>
+          <t>重庆, 近三天, 管材招标, 商机</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6389,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>重庆市, 四川省, 管材, 招标</t>
+          <t>重庆市, 管材, 招标</t>
         </is>
       </c>
     </row>
@@ -6485,11 +6461,11 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>四川, 华蓥市, 城镇危旧房改造, 市政公用工程, 施工一标段</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -6561,11 +6537,11 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>高标准农田, 改造提升, 施工招标</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -6637,11 +6613,11 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>金堂县, 大豆单产提升工程, 水利设施, 滴灌, 喷灌, 机井, 提灌站, 蓄水池, 渠道整治, 智能灌溉机器人</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6693,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>金堂县, 2026年玉米单产提升工程, 输配水管道, 自动化控制闸阀, 蓄水池, 移动式喷灌设备</t>
+          <t>2026年玉米单产提升工程, 输配水管道, 自动化控制闸阀, 蓄水池, 移动式喷灌设备</t>
         </is>
       </c>
     </row>
@@ -6789,11 +6765,11 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>排水防涝, 排水边沟, 排洪沟, 雨水调蓄池</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6845,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>重庆, 四川, 近三天, 管材, 招标商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+          <t>重庆, 近三天, 管材, 招标商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
         </is>
       </c>
     </row>
@@ -6941,11 +6917,11 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>贡井区, 2026年, 大豆单产提升工程, 智能滴灌系统, 蓄水池, 投资金额</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -7021,7 +6997,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>隆昌市, 燃气配套管网改造, 焊缝探伤检测</t>
+          <t>燃气配套管网改造, 焊缝探伤检测</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7073,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>四川, 管材招标</t>
+          <t>管材招标</t>
         </is>
       </c>
     </row>
@@ -7169,11 +7145,11 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>乡村振兴, 公路, 农村人居环境整治, 乡村旅游</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -7245,11 +7221,11 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>金属波纹管, 成都</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7377,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>凉山州, 西昌市, 特殊教育学校, 学前教育教学楼, 改扩建项目, 施工, 管材招标</t>
+          <t>凉山州, 特殊教育学校, 学前教育教学楼, 改扩建项目, 施工, 管材招标</t>
         </is>
       </c>
     </row>
@@ -7473,11 +7449,11 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>东河(苍溪段)流域水污染治理工程, 四川, 市政基础设施工程, 污水处理站, 资源化利用设施, 视频监控系统, 水质监测网络, 水环境风险预警网络, 监控平台</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -7549,11 +7525,11 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>苍溪县, 构溪河流域, 水生态保护修复, 市政基础设施工程</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7605,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>开江县, 2026年, 大豆单产提升工程, 招标计划, 四川, 管材</t>
+          <t>2026年, 大豆单产提升工程, 招标计划, 管材</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7681,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>重庆, 四川, 管材招标, 商机</t>
+          <t>重庆, 管材招标, 商机</t>
         </is>
       </c>
     </row>

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -7221,11 +7221,11 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>金属波纹管</t>
         </is>
       </c>
     </row>

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>重庆市潼南区提升农村饮水质量工程(潼南区农村供水保障工程)第二批勘察设计招标公告</t>
+          <t>重庆市涪陵区金炬物流有限公司白涛哨楼村1250kVA专变工程零星物资采购询价公告</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -527,192 +527,192 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>重庆市涪陵区金炬物流有限公司白涛哨楼村1250kVA专变工程的零星物资采购。</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>重庆市涪陵区金炬物流有限公司白涛哨楼村1250kVA专变工程零星物资采购询价公告 详见附件 信息来源:https://www.chinapipe.net/project/d3079433.html cqdingjiu 2026.08.25 10:30:20 网 务 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>重庆市涪陵区金炬物流有限公司白涛哨楼村1250kVA专变工程的零星物资采购。
+https://www.chinapipe.net/project/d3079433.html</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>重庆市潼南区提升农村饮水质量工程(潼南区农村供水保障工程)第二批勘察设计招标公告</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>区</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>项目包括连接3座水厂至各镇街的主管道、需改造的镇街水厂、管网和其他村社管网等。</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>项目总投资金额为79803.85万元，本次招标项目工程费估算金额为36890.82万元，本次招标项目勘察设计合同估算金额约为1678.53万元。</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>项目总投资金额为79803.85万元，本次招标项目工程费估算金额为36890.82万元，勘察设计合同估算金额约为1678.53万元。</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>勘察设计服务</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>重庆市潼南区提升农村饮水质量工程(潼南区农村供水保障工程)第二批勘察设计招标公告 1.招标条件 本招标项目重庆市潼南区提升农村饮水质量工程（潼南区农村供水保障工程）已由重庆市潼南区发展和改革委 员会以潼发改审〔2025〕59号文批准建设，项目业主为重庆市潼南区水务（集团）有限公司，建设资金来自地方 政府专项债和业主自筹，项目出资比例为100%，招标人为重庆市潼南区水务（集团）有限公司。项目已具备招 标条件，现对该工程第二批的勘察设计进行公开招标，评标办法采用综合评估法□经评审的最低投标价法。 2.项目概况与招标范围 网 2.1 建设地点：重庆市潼南区23个镇街 2.2 项目概况与建设规模：项目包括连接3座水厂至各镇街的主管道、需改造的镇街水厂、管网和其他村社管网等。 务 2.3 本项目工程总投资金额：79803.85万元 本次招标项目工程费估算金额：36890.82万元 本次招标项目勘察设计合同估算金额：约1678.53万元 商 2.4 招标范围：按现行勘察设计规范及招标人要求，完成本项目建设内容范围内的工程勘察（含初勘、详勘、施 工勘察及测绘、管网普查）、初步设计（含初步设计概算编制）、施工图设计（含施工图预算编制）的全部勘 察设计工作，以及施工全过程至项目竣工验收道过程中的后期服务工作。各阶段设计成果必须通过行业主管部门 的审查，审查后的成果提交招标人，并配合招标人办理各项相关行政审批手续。 2.5 勘察设计服务期限：勘察设计合同签订至提交勘察设计资料、管网普查资料、项目竣工验收合格止。合同签 订后90天内提交所有成果资料且获得相关批复文件。 管 2.6 标段划分（如有）： / 2.7 其他： / 国 3.投标人资格要求 3.1 本次招标要求投标人须具备以下条件： 中 3.1.1 本次招标要求投标人具备的资质条件： 投标人应同时具备建设行政主管部门颁发的下列勘察和设计两类资质： （1）投标人应具备下列勘察资质之一： ①工程勘察综合甲级资质。 ②工程勘察专业类岩土工程甲级资质； ③工程勘察专业类岩土工程（勘察）甲级资质。 （2）投标人应具备下列设计资质之一： ①工程设计综合甲级资质。 ②工程设计水利行业甲级资质； ③工程设计水利行业（引调水）专业甲级资质。 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的勘察设计能力，详见招标文件第二章投标人须知 前附表第1.4.1项内容。 3.2 本次招标接受 □不接受联合体投标。联合体投标的，应满足下列要求：①组成联合体的成员数量不得 超过2家；②联合体各方应按照招标文件提供的格式签订联合体协议书，明确联合体牵头人和各方权利义务；③ 联合体各方均应当具备承担招标项目的相应能力；联合体牵头人为承担本项目设计任务的单位；④联合体各方 不得再以自己名义单独或参加其他联合体在本项目中投标。 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（潼南区）下载招标文件及 其附件、澄清、修改、补充通知、最高限价通知等资料。参与投标的投标人需在重庆市公共资源交易网完成市 场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市 场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法 完成全流程电子招投标的，责任自负。 网 4.2投标人可在重庆市公共资源交易网（潼南区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-28 17:00:00前。 4.3招标人应于2026-09-04 18:00:00前在重庆市公共资源交易网（潼南区）发布澄清。 5.投标文件递交的内容 务 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-25 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 商 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网（潼南区）、重庆市公共资源交易监督网发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 道 招 标 人: 重庆市潼南区水务（集团）有限公司 代理机构: 重庆精聚达项目管理有限公司 重庆市潼南区桂林街道办事处福田路666号 重庆市两江新区黄山大道中段70号两江 地 址: 地 址: (自主承诺) 星界2栋20楼 邮 编: 管 邮 编: 项目负责人: 陈仁柯 项目负责人: 董娜 电 话: 15086967566 电 话: 023-67396293 传 真: 国 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 中 账 号: 监督部门: 重庆市潼南区发展和改革委员会 电 话: 023-44582386 2026年08月24日 重庆市潼南区提升农村饮水质量工程（潼南区农村供水保障工程）第二批勘察设计 户名 开户行 投标保证金账号 重庆市潼南区公共资源交易中心 重庆农村商业银行潼南支行 1701010120010009567000001 重庆市潼南区公共资源交易中心 中国农业银行潼南兴潼支行 311912010400014410000006234 重庆市潼南区公共资源交易中心 中国银行重庆潼南支行 114481524626VA00192 重庆市潼南区公共资源交易中心 重庆银行股份有限公司潼南支行 750102029007977301-602 信息来源:https://www.chinapipe.net/project/d3079247.html cqdingjiu 2026.08.25 09:25:41</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>重庆市潼南区提升农村饮水质量工程(潼南区农村供水保障工程)第二批勘察设计招标公告 1.招标条件 本招标项目重庆市潼南区提升农村饮水质量工程（潼南区农村供水保障工程）已由重庆市潼南区发展和改革委 员会以潼发改审〔2025〕59号文批准建设，项目业主为重庆市潼南区水务（集团）有限公司，建设资金来自地方 政府专项债和业主自筹，项目出资比例为100%，招标人为重庆市潼南区水务（集团）有限公司。项目已具备招 标条件，现对该工程第二批的勘察设计进行公开招标，评标办法采用综合评估法□经评审的最低投标价法。 2.项目概况与招标范围 网 2.1 建设地点：重庆市潼南区23个镇街 2.2 项目概况与建设规模：项目包括连接3座水厂至各镇街的主管道、需改造的镇街水厂、管网和其他村社管网等。 务 2.3 本项目工程总投资金额：79803.85万元 本次招标项目工程费估算金额：36890.82万元 本次招标项目勘察设计合同估算金额：约1678.53万元 商 2.4 招标范围：按现行勘察设计规范及招标人要求，完成本项目建设内容范围内的工程勘察（含初勘、详勘、施 工勘察及测绘、管网普查）、初步设计（含初步设计概算编制）、施工图设计（含施工图预算编制）的全部勘 察设计工作，以及施工全过程至项目竣工验收道过程中的后期服务工作。各阶段设计成果必须通过行业主管部门 的审查，审查后的成果提交招标人，并配合招标人办理各项相关行政审批手续。 2.5 勘察设计服务期限：勘察设计合同签订至提交勘察设计资料、管网普查资料、项目竣工验收合格止。合同签 订后90天内提交所有成果资料且获得相关批复文件。 管 2.6 标段划分（如有）： / 2.7 其他： / 国 3.投标人资格要求 3.1 本次招标要求投标人须具备以下条件： 中 3.1.1 本次招标要求投标人具备的资质条件： 投标人应同时具备建设行政主管部门颁发的下列勘察和设计两类资质： （1）投标人应具备下列勘察资质之一： ①工程勘察综合甲级资质。 ②工程勘察专业类岩土工程甲级资质； ③工程勘察专业类岩土工程（勘察）甲级资质。 （2）投标人应具备下列设计资质之一： ①工程设计综合甲级资质。 ②工程设计水利行业甲级资质； ③工程设计水利行业（引调水）专业甲级资质。 3.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的勘察设计能力，详见招标文件第二章投标人须知 前附表第1.4.1项内容。 3.2 本次招标接受 □不接受联合体投标。联合体投标的，应满足下列要求：①组成联合体的成员数量不得 超过2家；②联合体各方应按照招标文件提供的格式签订联合体协议书，明确联合体牵头人和各方权利义务；③ 联合体各方均应当具备承担招标项目的相应能力；联合体牵头人为承担本项目设计任务的单位；④联合体各方 不得再以自己名义单独或参加其他联合体在本项目中投标。 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网（潼南区）下载招标文件及 其附件、澄清、修改、补充通知、最高限价通知等资料。参与投标的投标人需在重庆市公共资源交易网完成市 场主体信息登记以及 CA 数字证书办理，办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市 场主体信息登记”“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和 CA 数字证书办理导致无法 完成全流程电子招投标的，责任自负。 网 4.2投标人可在重庆市公共资源交易网（潼南区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-28 17:00:00前。 4.3招标人应于2026-09-04 18:00:00前在重庆市公共资源交易网（潼南区）发布澄清。 5.投标文件递交的内容 务 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-25 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 商 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网（潼南区）、重庆市公共资源交易监督网发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 7.联系方式 道 招 标 人: 重庆市潼南区水务（集团）有限公司 代理机构: 重庆精聚达项目管理有限公司 重庆市潼南区桂林街道办事处福田路666号 重庆市两江新区黄山大道中段70号两江 地 址: 地 址: (自主承诺) 星界2栋20楼 邮 编: 管 邮 编: 项目负责人: 陈仁柯 项目负责人: 董娜 电 话: 15086967566 电 话: 023-67396293 传 真: 国 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 中 账 号: 监督部门: 重庆市潼南区发展和改革委员会 电 话: 023-44582386 2026年08月24日 重庆市潼南区提升农村饮水质量工程（潼南区农村供水保障工程）第二批勘察设计 户名 开户行 投标保证金账号 重庆市潼南区公共资源交易中心 重庆农村商业银行潼南支行 1701010120010009567000001 重庆市潼南区公共资源交易中心 中国农业银行潼南兴潼支行 311912010400014410000006234 重庆市潼南区公共资源交易中心 中国银行重庆潼南支行 114481524626VA00192 重庆市潼南区公共资源交易中心 重庆银行股份有限公司潼南支行 750102029007977301-602 信息来源:https://www.chinapipe.net/project/d3079247.html cqdingjiu 2026.08.25 10:30:20</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>项目包括连接3座水厂至各镇街的主管道、需改造的镇街水厂、管网和其他村社管网等。
 https://www.chinapipe.net/project/d3079247.html</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>80</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>管材, 招标, 勘察设计</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>荣昌区2026年安富街道高标准农田建设项目招标公告</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>水利</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>荣昌区</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>改造提升高标准农田326.59亩，其中高效节水灌溉面积130亩。主要包括梯台修筑、梯田修筑、稻虾地块修筑、恢复地类整治、输水管道安装、排水沟修建、机耕道改建等内容。</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>项目总投资金额181.43万元，本次招标项目合同估算金额166.35万元，全部由财政资金支持，项目出资比例为100%。</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>高标准农田改造工程</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>荣昌区2026年安富街道高标准农田建设项目招标公告 1.招标条件 1. 招标条件 本招标项目 荣昌区2026年安富街道高标准农田建设项目已由重庆市荣昌区农业农村委员会以荣农发〔2026〕64 号批准建设，项目业主为重庆市荣昌区农田建设中心，建设资金来自 财政资金，项目出资比例为100%，招标人为重庆市荣昌区农田建设中心。项目已具备招标条件，现对本项目施 工进行公开招标，评标办法采用经评审的最低投标价法。 网 2.项目概况与招标范围 2. 项目概况与招标范围 务 2.1 建设地点： 安富街道斑竹村 2.2 项目概况与建设规模：改造提升高标准农田326.59亩，其中高效节水灌溉面积130亩。 商 2.3 本项目工程总投资金额：181.43万元 本次招标项目合同估算金额：166.35万元 道 2.4 招标范围：梯台修筑127.5亩，梯田修筑61.56亩，稻虾地块修筑128.83亩，恢复地类整治1.22亩；新建Φ160PE 输水管道1949米，C25混凝土排水沟（0.5m*0.6m）320米；改建3.0m宽C25混凝土机耕道905米。包括所提供的施 工设计图所示范围内的所有内容，具体以招标人提供的图纸、工程量清单、答疑资料、澄清资料、其他补遗资 料等相关内容为准。若施工图与工程量清单不一致时，以工程量清单为准。 管 2.5 工期要求：工期为 180日历天 ，缺陷责任期为 24个月。 2.6 标段划分（如有）： / 国 2.7 其他： / 3.政府采购工程 中 3. 政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式：本项目整体面向中小企业。 4.投标人资格要求 4. 投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包三级及以 上资质或市政公用工程施工总承包三级及以上资质或水利水电工程施工总承包三级及以上资质。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标不接受联合体投标。 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （荣昌区）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（荣昌区）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资 源交易监督网、重庆市公共资源交易网（荣昌区）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 5.2投标人可在重庆市公共资源交易网（荣昌区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-28 17:30:00前。 5.3招标人应于2026-08-31 18:00:00前在重庆市公共资源交易网（荣昌区）发布澄清。 6.投标文件递交的内容 网 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-16 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 务 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（荣昌区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 商 招 标 人: 重庆市荣昌区农田建设中心 代理机构: 重庆富毅项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 道 项目负责人: 李老师 项目负责人: 陈航 电 话: 023-85265043 电 话: 16623666557 传 真: 传 真: 管 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 国 监督部门: 重庆市荣昌区发展和改革委员会 电 话: 023-61471361 中 2026年08月24日 荣昌区2026年安富街道高标准农田建设项目 户名 开户行 投标保证金账号 重庆市荣昌区公共资源交易中心 中国建设银行荣昌支行 50001173600050206823-000176 重庆市荣昌区公共资源交易中心 中国农业银行昌州支行 311717010400018810000005753 重庆市荣昌区公共资源交易中心 重庆农村商业银行股份有限公司荣昌支行 1901040120010005391001010 重庆市荣昌区公共资源交易中心 中国工商银行荣昌支行 9558853100013298421 信息来源:https://www.chinapipe.net/project/d3079245.html cqdingjiu 2026.08.25 09:25:40</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>项目总投资金额181.43万元，本次招标项目合同估算金额166.35万元，全部由财政资金支持。</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>高标准农田改造材料及设施，包括PE输水管道、混凝土排水沟、混凝土机耕道等。</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>荣昌区2026年安富街道高标准农田建设项目招标公告 1.招标条件 1. 招标条件 本招标项目 荣昌区2026年安富街道高标准农田建设项目已由重庆市荣昌区农业农村委员会以荣农发〔2026〕64 号批准建设，项目业主为重庆市荣昌区农田建设中心，建设资金来自 财政资金，项目出资比例为100%，招标人为重庆市荣昌区农田建设中心。项目已具备招标条件，现对本项目施 工进行公开招标，评标办法采用经评审的最低投标价法。 网 2.项目概况与招标范围 2. 项目概况与招标范围 务 2.1 建设地点： 安富街道斑竹村 2.2 项目概况与建设规模：改造提升高标准农田326.59亩，其中高效节水灌溉面积130亩。 商 2.3 本项目工程总投资金额：181.43万元 本次招标项目合同估算金额：166.35万元 道 2.4 招标范围：梯台修筑127.5亩，梯田修筑61.56亩，稻虾地块修筑128.83亩，恢复地类整治1.22亩；新建Φ160PE 输水管道1949米，C25混凝土排水沟（0.5m*0.6m）320米；改建3.0m宽C25混凝土机耕道905米。包括所提供的施 工设计图所示范围内的所有内容，具体以招标人提供的图纸、工程量清单、答疑资料、澄清资料、其他补遗资 料等相关内容为准。若施工图与工程量清单不一致时，以工程量清单为准。 管 2.5 工期要求：工期为 180日历天 ，缺陷责任期为 24个月。 2.6 标段划分（如有）： / 国 2.7 其他： / 3.政府采购工程 中 3. 政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式：本项目整体面向中小企业。 4.投标人资格要求 4. 投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包三级及以 上资质或市政公用工程施工总承包三级及以上资质或水利水电工程施工总承包三级及以上资质。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标不接受联合体投标。 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （荣昌区）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（荣昌区）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资 源交易监督网、重庆市公共资源交易网（荣昌区）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 5.2投标人可在重庆市公共资源交易网（荣昌区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-28 17:30:00前。 5.3招标人应于2026-08-31 18:00:00前在重庆市公共资源交易网（荣昌区）发布澄清。 6.投标文件递交的内容 网 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-16 10:00，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 务 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（荣昌区）发布。[提示：依法必须招 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 商 招 标 人: 重庆市荣昌区农田建设中心 代理机构: 重庆富毅项目管理有限公司 地 址: 地 址: 邮 编: 邮 编: 道 项目负责人: 李老师 项目负责人: 陈航 电 话: 023-85265043 电 话: 16623666557 传 真: 传 真: 管 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 国 监督部门: 重庆市荣昌区发展和改革委员会 电 话: 023-61471361 中 2026年08月24日 荣昌区2026年安富街道高标准农田建设项目 户名 开户行 投标保证金账号 重庆市荣昌区公共资源交易中心 中国建设银行荣昌支行 50001173600050206823-000176 重庆市荣昌区公共资源交易中心 中国农业银行昌州支行 311717010400018810000005753 重庆市荣昌区公共资源交易中心 重庆农村商业银行股份有限公司荣昌支行 1901040120010005391001010 重庆市荣昌区公共资源交易中心 中国工商银行荣昌支行 9558853100013298421 信息来源:https://www.chinapipe.net/project/d3079245.html cqdingjiu 2026.08.25 10:30:20</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>改造提升高标准农田326.59亩，其中高效节水灌溉面积130亩。主要包括梯台修筑、梯田修筑、稻虾地块修筑、恢复地类整治、输水管道安装、排水沟修建、机耕道改建等内容。
 https://www.chinapipe.net/project/d3079245.html</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>未识别到明确匹配关键词</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>荣昌区2026年古昌镇高标准农田建设项目招标公告</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>水利</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>荣昌区</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007亩。</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>项目总投资金额1592.15万元，本次招标项目合同估算金额1420.76万元。</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>水田整治、缓坡整治、梯台整治、恢复地类整治、耕地复耕整治、农机进出通道、提灌站、输水管道、排水沟、田间道等。</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>荣昌区2026年古昌镇高标准农田建设项目招标公告 1.招标条件 1. 招标条件 本招标项目 荣昌区2026年古昌镇高标准农田建设项目已由重庆市荣昌区农业农村委员会以荣农发〔2026〕64号 批准建设，项目业主为重庆市荣昌区农田建设中心，建设资金来自 财 政资金，项目出资比例为100%，招标人为重庆市荣昌区农田建设中心。项目已具备招标条件，现对本项目施工 进行公开招标，评标办法采用经评审的最低投标价法。 网 2.项目概况与招标范围 2. 项目概况与招标范围 务 2.1 建设地点：古昌镇百合堂村、玉带村 2.2 项目概况与建设规模：新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007 亩。 商 2.3 本项目工程总投资金额：1592.15万元 本次招标项目合同估算金额：1420.76万元 道 2.4 招标范围：水田整治2622.50亩，缓坡整治21.95亩，梯台整治186.23亩，恢复地类整治44.26亩，耕地复耕整 治283.09亩，农机进出通道8338m；新修提灌站1座，改建提灌站2座，新修Φ250PE输水管道2732m、Φ200PE输水 管道267m、Φ160PE输水管道20928m、Φ110PE输水管道7412m，改建沟带路(1.8×0.8×1.0m)799m，维 管 修2.0×1.5m排水沟1395m、0.8×1.0m排水沟784m；改建3.0m宽田间道6573m、4.0m宽田间道728m。包括所提供的 施工设计图所示范围内的所有内容，具体以招标人提供的图纸、工程量清单、答疑资料、澄清资料、其他补遗 资料等相关内容为准。若施工图与工程量清单不一致时，以工程量清单为准。 2.5 工期要求：工期为 国180日历天 ，缺陷责任期为 24个月。 2.6 标段划分（如有）： / 2.7 其他： 中 / 3.政府采购工程 3. 政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式：本项目整体面向中小企业。 4.投标人资格要求 4. 投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包三级及以 上资质或市政公用工程施工总承包三级及以上资质或水利水电工程施工总承包三级及以上资质。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标不接受联合体投标。 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （荣昌区）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（荣昌区）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资 源交易监督网、重庆市公共资源交易网（荣昌区）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 5.2投标人可在重庆市公共资源交易网（荣昌区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-28 17:30:00前。 网 5.3招标人应于2026-08-31 18:00:00前在重庆市公共资源交易网（荣昌区）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-16 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 务 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（荣昌区）发布。[提示：依法必须招 商 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆市荣昌区农田建设中心 代理机构: 重庆富毅项目管理有限公司 地 址: 地 址: 道 邮 编: 邮 编: 项目负责人: 李老师 项目负责人: 陈航 电 话: 023-85265043 管电 话: 16623666557 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 国开户银行: 账 号: 账 号: 监督部门:中重庆市荣昌区发展和改革委员会 电 话: 023-61471361 2026年08月24日 荣昌区2026年古昌镇高标准农田建设项目 户名 开户行 投标保证金账号 重庆市荣昌区公共资源交易中心 中国工商银行荣昌支行 9558853100013298439 重庆市荣昌区公共资源交易中心 中国农业银行昌州支行 311717010400018810000005713 重庆市荣昌区公共资源交易中心 重庆农村商业银行股份有限公司荣昌支行 1901040120010005391001011 重庆市荣昌区公共资源交易中心 中国建设银行荣昌支行 50001173600050206823-000132 信息来源:https://www.chinapipe.net/project/d3079244.html cqdingjiu 2026.08.25 09:25:41</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007亩。
-https://www.chinapipe.net/project/d3079244.html</t>
-        </is>
-      </c>
       <c r="N4" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>高标准农田, 管材, 招标</t>
+          <t>高标准农田, 改造, PE输水管道, 混凝土排水沟, 机耕道</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>永川区2026年高标准农田建设项目三标段(松溉镇)、永川区2026年高标准农田建设项目四标段(临江镇)、永川区2026年高标准农田建设项目五标段(何埂镇)、永川区2026年高标准农田建设项目六标段(南大街街道)招标公告</t>
+          <t>荣昌区2026年古昌镇高标准农田建设项目招标公告</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -743,48 +743,48 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>永川区</t>
+          <t>荣昌区</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>永川区2026年高标准农田建设项目包括四个标段，分别位于松溉镇、临江镇、何埂镇和南大街街道。每个标段的主要内容包括田块整治工程、灌溉与排水工程、田间道路工程、农田输配电工程、其他工程、农田地力提升工程及设备购置工程。</t>
+          <t>新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007亩。水田整治2622.50亩，缓坡整治21.95亩，梯台整治186.23亩，恢复地类整治44.26亩，耕地复耕整治283.09亩，农机进出通道8338m；新修提灌站1座，改建提灌站2座，新修Φ250PE输水管道2732m、Φ200PE输水管道267m、Φ160PE输水管道20928m、Φ110PE输水管道7412m，改建沟带路(1.8×0.8×1.0m)799m，维修2.0×1.5m排水沟1395m、0.8×1.0m排水沟784m；改建3.0m宽田间道6573m、4.0m宽田间道728m。</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>建设资金来自上级资金，项目出资比例为100%。项目合同估算金额分别为：永川区2026年高标准农田建设项目三标段（松溉镇）1972.99万元；永川区2026年高标准农田建设项目四标段（临江镇）837.36万元；永川区2026年高标准农田建设项目五标段（何埂镇）2085.37万元；永川区2026年高标准农田建设项目六标段（南大街街道）3228.18万元。</t>
+          <t>项目总投资金额：1592.15万元，本次招标项目合同估算金额：1420.76万元</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>高标准农田建设相关材料和服务，如田块整治材料、灌溉设施、排水系统、田间道路建设材料、电力设施等。</t>
+          <t>高标准农田建设</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>永川区2026年高标准农田建设项目三标段(松溉镇)、永川区2026年高标准农田建设项目四标段(临江镇)、永川 区2026年高标准农田建设项目五标段(何埂镇)、永川区2026年高标准农田建设项目六标段(南大街街道)招标公告 1.招标条件 本招标项目永川区2026年高标准农田建设项目已由重庆市永川区发展和改革委员会以永发改审批﹝2026﹞37号文 批准建设，建设资金来自上级资金，项目出资比例为100%，项目法人为重庆市永川区农业综合开发项目服务中 心，招标人为重庆市永川区农业综合开发项目服务中心。项目已具备招标条件，现对该永川区2026年高标准农田 建设项目三标段（松溉镇）、永川区2026年高标准农田建设项目四标段（临江镇）、永川区2026年高标准农田建 设项目五标段（何埂镇）、永川区2026年高标准农田建设项目六标段（南大街街道）的施工进行公开招标，评标 办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：三标段：松溉镇；四标段：临江镇；五标段：何埂镇；六标段：南大街街道。 2.2 项目概况与建设规模：永川区2026年高标准农田建设项目三标段（松溉镇）主要建设内容：项目位于松溉镇 务 茅园村、旗山村、打鱼河村、鱼岭村、新街子村。项目建设规模为8916亩，其中主要建设内容包含田块整治工程、 灌溉与排水工程、田间道路工程、农田输配电工程、其他工程、农田地力提升工程及设备购置工程。 永川区2026年高标准农田建设项目四标段（临江镇）主要建设内容：（1）田块整治部分：梯田整治1088.58亩， 商 梯台整治48.27亩，恢复地类整治17.71亩，农机通道5671m。（2）灌溉与排水工程：新修泵站2座，新修200m3蓄 水池1座，新修囤水田8口，维修山坪塘5座以及输水管道安装及涵洞工程等。（3）田间道路工程：新修3.0m混凝 土机耕道旱地段3618m，新修3.0m混凝土机耕道水田段529m；维修3.0m混凝土机耕道517m，维修3.0m混凝土机耕道 (扩宽)348m，维修4.5m混凝土机耕道226m等。（4）其他工程：标识标牌安装。（5）农田地力提升工程：地力 培肥1154.6亩。 道 永川区2026年高标准农田建设项目五标段（何埂镇）主要建设内容：项目位于何埂镇丰乐、狮子、长丰、花园、 一碗水、联盟、新泉、玉宝、转角店村等9个村。项目建设规模为102191.10亩，其中主要建设内容包含田块整治 工程、灌溉与排水工程、田间道路工程、农田输配电工程、其他工程、农田地力提升工程及设备购置工程。 管 永川区2026年高标准农田建设项目六标段（南大街街道）主要建设内容：（1）田块整治部分：梯田整治1848.77 亩，梯台整治1196亩，恢复地类整治367.05亩，农机通道8589m。（2）灌溉与排水工程：新修泵站5座，新 修200m3蓄水池14座，新修囤水田7口，维修山坪塘30座以及输水管道安装及涵洞工程等。（3）田间道路工程： 改建3.0m宽田间道1455国6m，改建3.5m宽田间道1890m；新建3.0m宽田间道3852m，新建田间道交叉口89处；新建 田间道错车道22处；新建田间道弯道加宽26处；新建田间道回车道19处；改建2.0m宽生产路251m；（4）其他工 程：标识标牌安装。（5）农田地力提升工程：地力培肥3411.82亩。 2.3 本次招标中项目合同估算金额：永川区2026年高标准农田建设项目三标段（松溉镇）1972.99万元；永川区2026 年高标准农田建设项目四标段（临江镇）837.36万元；永川区2026年高标准农田建设项目五标段（何埂 镇）2085.37万元；永川区2026年高标准农田建设项目六标段（南大街街道）3228.18万元。 2.4 招标范围：永川区2026年高标准农田建设项目三标段（松溉镇）、永川区2026年高标准农田建设项目四标段 （临江镇）、永川区2026年高标准农田建设项目五标段（何埂镇）、永川区2026年高标准农田建设项目六标段 （南大街街道）施工图纸范围内包含的全部内容，以及本项目招标期内招标人发布的澄清（答疑）、修改（补 遗）通知文件、技术交底等，具体以招标人公布的施工图和工程量清单为准。 2.5 工期要求：工期为360日历天，缺陷责任期为12个月。 2.6 标段划分： 序号 招标标段名称 1 永川区2026年高标准农田建设项目三标段（松溉镇） 2 永川区2026年高标准农田建设项目四标段（临江镇） 3 永川区2026年高标准农田建设项目五标段（何埂镇） 4 永川区2026年高标准农田建设项目六标段（南大街街道） 2.7 其他：各投标人只能就本次招标四个标段的其中一个标段进行投标，若同时对两个及以上标段进行投标，则 由评标委员会作否决投标处理。 3.政府采购工程 3.1 是否属于政府采购工程：是。 3.2 是否专门面向中小企业预留：是。 专门面向中小企业预留的实施方式：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 网 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包三级及以 上资质或市政公用工程施工总承包三级及以上资质或水利水电工程施工总承包三级及以上资质。 务 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标不接受联合体投标。 商 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn/）和重庆市公共资源交易网（永川区）（http://www.cqggzy.com/yongchuanweb/）下载 招标文件、工程量清单、电子图纸等资料。参道与投标的投标人需在重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn/）和重庆市公共资源交易网（永川区）（http://www.cqggzy.com/yongchuanweb/）完成 市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/） 和重庆市公共资源交易网（永川区）（http://www.cqggzy.com/yongchuanweb/）导航栏“主体信息”页面中“市场 主体信息登记”、“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法 管 完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/）和重庆市公共资源交易网（永川区） （http://www.cqggzy.com/yongchuanweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告 发布至2026-08-27 23:59:59前。 5.3招标人应于2026-09-国02 23:59:59前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/）和重庆市公共资源 交易网（永川区）（http://www.cqggzy.com/yongchuanweb/）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-18 09:30，投标人应当在投标截止时间前，通过互 联网使用C中A数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/）和重庆市公共资源交易网（永川区） （http://www.cqggzy.com/yongchuanweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源 交易监督网上发布。] 8.联系方式 招 标 人: 重庆市永川区农业综合开发项目服务中心 代理机构: 重庆永川政鑫综合能源有限公司 地 址: 重庆市永川区人民北路6号 地 址: 重庆市永川区昌州大道东段179号 邮 编: 邮 编: 项目负责人: 肖老师 项目负责人: 苏萍 电 话: 023-49899533 电 话: 023-49621986 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市永川区发展和改革委员会 电 话: 023-49821625 2026年08月24日 信息来源:https://www.chinapipe.net/project/d3079239.html cqdingjiu 2026.08.25 09:25:40 网 务 商 道 管 国 中</t>
+          <t>荣昌区2026年古昌镇高标准农田建设项目招标公告 1.招标条件 1. 招标条件 本招标项目 荣昌区2026年古昌镇高标准农田建设项目已由重庆市荣昌区农业农村委员会以荣农发〔2026〕64号 批准建设，项目业主为重庆市荣昌区农田建设中心，建设资金来自 财 政资金，项目出资比例为100%，招标人为重庆市荣昌区农田建设中心。项目已具备招标条件，现对本项目施工 进行公开招标，评标办法采用经评审的最低投标价法。 网 2.项目概况与招标范围 2. 项目概况与招标范围 务 2.1 建设地点：古昌镇百合堂村、玉带村 2.2 项目概况与建设规模：新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007 亩。 商 2.3 本项目工程总投资金额：1592.15万元 本次招标项目合同估算金额：1420.76万元 道 2.4 招标范围：水田整治2622.50亩，缓坡整治21.95亩，梯台整治186.23亩，恢复地类整治44.26亩，耕地复耕整 治283.09亩，农机进出通道8338m；新修提灌站1座，改建提灌站2座，新修Φ250PE输水管道2732m、Φ200PE输水 管道267m、Φ160PE输水管道20928m、Φ110PE输水管道7412m，改建沟带路(1.8×0.8×1.0m)799m，维 管 修2.0×1.5m排水沟1395m、0.8×1.0m排水沟784m；改建3.0m宽田间道6573m、4.0m宽田间道728m。包括所提供的 施工设计图所示范围内的所有内容，具体以招标人提供的图纸、工程量清单、答疑资料、澄清资料、其他补遗 资料等相关内容为准。若施工图与工程量清单不一致时，以工程量清单为准。 2.5 工期要求：工期为 国180日历天 ，缺陷责任期为 24个月。 2.6 标段划分（如有）： / 2.7 其他： 中 / 3.政府采购工程 3. 政府采购工程 3.1 是否属于政府采购工程：是 □否 3.2 是否专门面向中小企业预留：是 专门面向中小企业预留的实施方式：本项目整体面向中小企业。 4.投标人资格要求 4. 投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包三级及以 上资质或市政公用工程施工总承包三级及以上资质或水利水电工程施工总承包三级及以上资质。 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标不接受联合体投标。 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网、重庆市公共资源交易网 （荣昌区）下载招标文件、工程量清单、电子图纸等资料。参与投标的投标人需在重庆市公共资源交易监督网、 重庆市公共资源交易网（荣昌区）完成市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资 源交易监督网、重庆市公共资源交易网（荣昌区）导航栏“主体信息”页面中“市场主体信息登记”、“CA 数 字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的， 责任自负。 5.2投标人可在重庆市公共资源交易网（荣昌区）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间 从本公告发布至2026-08-28 17:30:00前。 网 5.3招标人应于2026-08-31 18:00:00前在重庆市公共资源交易网（荣昌区）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-16 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 务 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网、重庆市公共资源交易网（荣昌区）发布。[提示：依法必须招 商 标项目的招标公告，必须在重庆市公共资源交易监督网上发布。] 8.联系方式 招 标 人: 重庆市荣昌区农田建设中心 代理机构: 重庆富毅项目管理有限公司 地 址: 地 址: 道 邮 编: 邮 编: 项目负责人: 李老师 项目负责人: 陈航 电 话: 023-85265043 管电 话: 16623666557 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 国开户银行: 账 号: 账 号: 监督部门:中重庆市荣昌区发展和改革委员会 电 话: 023-61471361 2026年08月24日 荣昌区2026年古昌镇高标准农田建设项目 户名 开户行 投标保证金账号 重庆市荣昌区公共资源交易中心 中国工商银行荣昌支行 9558853100013298439 重庆市荣昌区公共资源交易中心 中国农业银行昌州支行 311717010400018810000005713 重庆市荣昌区公共资源交易中心 重庆农村商业银行股份有限公司荣昌支行 1901040120010005391001011 重庆市荣昌区公共资源交易中心 中国建设银行荣昌支行 50001173600050206823-000132 信息来源:https://www.chinapipe.net/project/d3079244.html cqdingjiu 2026.08.25 10:30:20</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>永川区2026年高标准农田建设项目包括四个标段，分别位于松溉镇、临江镇、何埂镇和南大街街道。每个标段的主要内容包括田块整治工程、灌溉与排水工程、田间道路工程、农田输配电工程、其他工程、农田地力提升工程及设备购置工程。
-https://www.chinapipe.net/project/d3079239.html</t>
+          <t>新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007亩。水田整治2622.50亩，缓坡整治21.95亩，梯台整治186.23亩，恢复地类整治44.26亩，耕地复耕整治283.09亩，农机进出通道8338m；新修提灌站1座，改建提灌站2座，新修Φ250PE输水管道2732m、Φ200PE输水管道267m、Φ160PE输水管道20928m、Φ110PE输水管道7412m，改建沟带路(1.8×0.8×1.0m)799m，维修2.0×1.5m排水沟1395m、0.8×1.0m排水沟784m；改建3.0m宽田间道6573m、4.0m宽田间道728m。
+https://www.chinapipe.net/project/d3079244.html</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>高标准农田建设, 新建, 改造, 灌溉, 水田整治, 缓坡整治, 梯台整治, 恢复地类整治, 耕地复耕整治, 农机进出通道, 提灌站, 输水管道, 排水沟, 田间道</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>城南污水厂服务片区污水管网更新改造工程施工(二标段)招标控制价</t>
+          <t>永川区2026年高标准农田建设项目三标段(松溉镇)、永川区2026年高标准农田建设项目四标段(临江镇)、永川区2026年高标准农田建设项目五标段(何埂镇)、永川区2026年高标准农田建设项目六标段(南大街街道)招标公告</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -813,31 +813,35 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>永川区</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>城南污水厂服务片区污水管网更新改造工程</t>
+          <t>[object Object]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>建设资金来自上级资金，项目出资比例为100%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>高标准农田建设</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>城南污水厂服务片区污水管网更新改造工程施工(二标段)招标控制价 详见附件。 信息来源:https://www.chinapipe.net/project/d3079202.html cqdingjiu 2026.08.25 09:25:42 网 务 商 道 管 国 中</t>
+          <t>永川区2026年高标准农田建设项目三标段(松溉镇)、永川区2026年高标准农田建设项目四标段(临江镇)、永川 区2026年高标准农田建设项目五标段(何埂镇)、永川区2026年高标准农田建设项目六标段(南大街街道)招标公告 1.招标条件 本招标项目永川区2026年高标准农田建设项目已由重庆市永川区发展和改革委员会以永发改审批﹝2026﹞37号文 批准建设，建设资金来自上级资金，项目出资比例为100%，项目法人为重庆市永川区农业综合开发项目服务中 心，招标人为重庆市永川区农业综合开发项目服务中心。项目已具备招标条件，现对该永川区2026年高标准农田 建设项目三标段（松溉镇）、永川区2026年高标准农田建设项目四标段（临江镇）、永川区2026年高标准农田建 设项目五标段（何埂镇）、永川区2026年高标准农田建设项目六标段（南大街街道）的施工进行公开招标，评标 办法采用综合评估法。 2.项目概况与招标范围 网 2.1 建设地点：三标段：松溉镇；四标段：临江镇；五标段：何埂镇；六标段：南大街街道。 2.2 项目概况与建设规模：永川区2026年高标准农田建设项目三标段（松溉镇）主要建设内容：项目位于松溉镇 务 茅园村、旗山村、打鱼河村、鱼岭村、新街子村。项目建设规模为8916亩，其中主要建设内容包含田块整治工程、 灌溉与排水工程、田间道路工程、农田输配电工程、其他工程、农田地力提升工程及设备购置工程。 永川区2026年高标准农田建设项目四标段（临江镇）主要建设内容：（1）田块整治部分：梯田整治1088.58亩， 商 梯台整治48.27亩，恢复地类整治17.71亩，农机通道5671m。（2）灌溉与排水工程：新修泵站2座，新修200m3蓄 水池1座，新修囤水田8口，维修山坪塘5座以及输水管道安装及涵洞工程等。（3）田间道路工程：新修3.0m混凝 土机耕道旱地段3618m，新修3.0m混凝土机耕道水田段529m；维修3.0m混凝土机耕道517m，维修3.0m混凝土机耕道 (扩宽)348m，维修4.5m混凝土机耕道226m等。（4）其他工程：标识标牌安装。（5）农田地力提升工程：地力 培肥1154.6亩。 道 永川区2026年高标准农田建设项目五标段（何埂镇）主要建设内容：项目位于何埂镇丰乐、狮子、长丰、花园、 一碗水、联盟、新泉、玉宝、转角店村等9个村。项目建设规模为102191.10亩，其中主要建设内容包含田块整治 工程、灌溉与排水工程、田间道路工程、农田输配电工程、其他工程、农田地力提升工程及设备购置工程。 管 永川区2026年高标准农田建设项目六标段（南大街街道）主要建设内容：（1）田块整治部分：梯田整治1848.77 亩，梯台整治1196亩，恢复地类整治367.05亩，农机通道8589m。（2）灌溉与排水工程：新修泵站5座，新 修200m3蓄水池14座，新修囤水田7口，维修山坪塘30座以及输水管道安装及涵洞工程等。（3）田间道路工程： 改建3.0m宽田间道1455国6m，改建3.5m宽田间道1890m；新建3.0m宽田间道3852m，新建田间道交叉口89处；新建 田间道错车道22处；新建田间道弯道加宽26处；新建田间道回车道19处；改建2.0m宽生产路251m；（4）其他工 程：标识标牌安装。（5）农田地力提升工程：地力培肥3411.82亩。 2.3 本次招标中项目合同估算金额：永川区2026年高标准农田建设项目三标段（松溉镇）1972.99万元；永川区2026 年高标准农田建设项目四标段（临江镇）837.36万元；永川区2026年高标准农田建设项目五标段（何埂 镇）2085.37万元；永川区2026年高标准农田建设项目六标段（南大街街道）3228.18万元。 2.4 招标范围：永川区2026年高标准农田建设项目三标段（松溉镇）、永川区2026年高标准农田建设项目四标段 （临江镇）、永川区2026年高标准农田建设项目五标段（何埂镇）、永川区2026年高标准农田建设项目六标段 （南大街街道）施工图纸范围内包含的全部内容，以及本项目招标期内招标人发布的澄清（答疑）、修改（补 遗）通知文件、技术交底等，具体以招标人公布的施工图和工程量清单为准。 2.5 工期要求：工期为360日历天，缺陷责任期为12个月。 2.6 标段划分： 序号 招标标段名称 1 永川区2026年高标准农田建设项目三标段（松溉镇） 2 永川区2026年高标准农田建设项目四标段（临江镇） 3 永川区2026年高标准农田建设项目五标段（何埂镇） 4 永川区2026年高标准农田建设项目六标段（南大街街道） 2.7 其他：各投标人只能就本次招标四个标段的其中一个标段进行投标，若同时对两个及以上标段进行投标，则 由评标委员会作否决投标处理。 3.政府采购工程 3.1 是否属于政府采购工程：是。 3.2 是否专门面向中小企业预留：是。 专门面向中小企业预留的实施方式：本项目整体面向中小企业。 4.投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 网 4.1.1 本次招标要求投标人具备的资质条件：具备建设行政主管部门颁发的有效的建筑工程施工总承包三级及以 上资质或市政公用工程施工总承包三级及以上资质或水利水电工程施工总承包三级及以上资质。 务 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1条内容。 4.2 本次招标不接受联合体投标。 商 5.招标文件的获取 5.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn/）和重庆市公共资源交易网（永川区）（http://www.cqggzy.com/yongchuanweb/）下载 招标文件、工程量清单、电子图纸等资料。参道与投标的投标人需在重庆市公共资源交易监督网 （http://ggzyjyjgj.cq.gov.cn/）和重庆市公共资源交易网（永川区）（http://www.cqggzy.com/yongchuanweb/）完成 市场主体信息登记以及CA数字证书办理，办理方式请参见重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/） 和重庆市公共资源交易网（永川区）（http://www.cqggzy.com/yongchuanweb/）导航栏“主体信息”页面中“市场 主体信息登记”、“CA 数字证书办理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法 管 完成全流程电子招投标的，责任自负。 5.2投标人可在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/）和重庆市公共资源交易网（永川区） （http://www.cqggzy.com/yongchuanweb/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告 发布至2026-08-27 23:59:59前。 5.3招标人应于2026-09-国02 23:59:59前在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/）和重庆市公共资源 交易网（永川区）（http://www.cqggzy.com/yongchuanweb/）发布澄清。 6.投标文件递交的内容 6.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-18 09:30，投标人应当在投标截止时间前，通过互 联网使用C中A数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 6.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 7.发布公告的媒介 本次招标公告同时在重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/）和重庆市公共资源交易网（永川区） （http://www.cqggzy.com/yongchuanweb/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源 交易监督网上发布。] 8.联系方式 招 标 人: 重庆市永川区农业综合开发项目服务中心 代理机构: 重庆永川政鑫综合能源有限公司 地 址: 重庆市永川区人民北路6号 地 址: 重庆市永川区昌州大道东段179号 邮 编: 邮 编: 项目负责人: 肖老师 项目负责人: 苏萍 电 话: 023-49899533 电 话: 023-49621986 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市永川区发展和改革委员会 电 话: 023-49821625 2026年08月24日 信息来源:https://www.chinapipe.net/project/d3079239.html cqdingjiu 2026.08.25 10:30:21 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>城南污水厂服务片区污水管网更新改造工程
-https://www.chinapipe.net/project/d3079202.html</t>
+          <t>[object Object]
+https://www.chinapipe.net/project/d3079239.html</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -845,14 +849,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>管材招标</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>中国电建水电九局CQ某项目其他施工材料采购项目公开竞价采购公告</t>
+          <t>城南污水厂服务片区污水管网更新改造工程施工(二标段)招标控制价</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -862,7 +866,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -884,467 +888,463 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
+          <t>城南污水厂服务片区污水管网更新改造工程</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>城南污水厂服务片区污水管网更新改造工程施工(二标段)招标控制价 详见附件。 信息来源:https://www.chinapipe.net/project/d3079202.html cqdingjiu 2026.08.25 10:30:21 网 务 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>城南污水厂服务片区污水管网更新改造工程
+https://www.chinapipe.net/project/d3079202.html</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>中国电建水电九局CQ某项目其他施工材料采购项目公开竞价采购公告</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>水利</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>项目位于重庆市，主要采购砂浆、水泥、水泥（或混凝土）空心砖、砂石料、PVC管材、种植土、草皮等其他施工材料。</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>项目资金来源于中国水利水电第九工程局有限公司的工程款资金。</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>项目资金来源于中国水利水电第九工程局有限公司的工程款。</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>砂浆、水泥、水泥（或混凝土）空心砖、砂石料、PVC管材、种植土、草皮等。</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>中国电建水电九局CQ某项目其他施工材料采购项目公开竞价采购公告 询比采购公告 项目编号：PC-0109-26J5-FG0266 一、采购条件 受中国水利水电第九工程局有限公司（以下简称“采购人”）委托，中国水利水电第九工程局有限公司采购与 招标中心（以下简称“采购机构”）以公开询比方式采购其他施工材料，计划使网用项目工程款资金用于本次询 比采购后所签订合同的支付。报价方式为一次报价，现将有关报价事项告知如下： 二、项目概况、采购范围 务 1、项目概况：项目位于重庆市，交通便利。 2、采购范围：工程用其他材料。 3、采购内容及数量：主要为砂浆、水泥、水泥（或混凝商土）空心砖、砂石料、PVC管材、种植土、草皮等其他 施工材料1批。详见询比采购文件报价表。 4、报价要求： 道 采用固定综合单价形式，在本合同执行期内不做任何调价。单价包含出厂价格、包装费、保险费、运输费、装 卸车费（含货到工地现场卸车费）、过江过路过桥费、合理利润、税金税费、代理费、货物交付前所需进行检 测检验费、售后服务以及市场价格涨幅风险费等各类费用；包括其它运至需方指定交货地点货物交付之前发生 的一切费用，以及与其他土建及相关专业的配合协调关系费用。 管 在供货周期内，出现市场价格波动、实际数量增减、供应时间调整等情况下本固定综合单价在合同执行期间 均不予调整。 项目实施过程中，因施国工图、设计变更或其它因素产生清单外新增项目的，由双方共同向不少于3家供应商询价， 以询价最低价为成交价格，双方签订补充协议后实施。 5、交货时间： 中 交货时间：采购合同签订后，按采购人或采购人发出的排产函要求供货。 6、交货地点： 交货地点：项目部指定位置，具体交货地点以采购方书面通知为准。 7.技术、质量要求 （1）要求为全新国产产品，卖方所供产品质量必须满足国家和行业标准、设计和买方使用要求，产品所用材料 必须符合国家标准。如遇国家或行业标准更新，以最新标准为准； （2）卖方应根据买方使用计划组织供货，所有供货质量确保达到上述要求。材料进场后，抽检不合格而产生的 一切费用及由此给采购人造成的损失由成交人承担。买方保留在例行送检之外随时抽检及送检产品的权利，检 验机构为具有相应检测项目资质的第三方检测机构。若检验不合格，卖方承担由此发生的全部费用。 （3）项目涉及到的图纸及规范要求的，卖方必须仔细阅读并充分掌握。图纸详细内容，须对接项目人员（李工， 联系电话：13595171151）至现场查阅，供货所有材料质量需满足图纸及规范要求。 （4）供应材料规格型号除满足合同约定外，还须满足买方与建设单位封样定样要求。 8、付款方式： （1）实行先货后款，按月结算，以每个自然月为一个供货对账结算周期，第一个月供货结束后，第二个月22日 前双方对账办理结算签认，双方对账结算后，卖方提供报价时确定税率全额增值税专用发票，买方在收到全额 发票后办理入账，买方办理入账后次月15日前（即第三个月15日前）支付第一个月供货结算货款的80%，以此类 推。供货结束后双方办理最终结算；工程竣工验收合格之日起2个月内，买方累计支付至总结算金额的90%；第 三方审计机构完成最终审计并出具审计报告之日起30日内，买方累计支付至总结算金额的97%；其余3%为质保金， 质保金在双方办理最终结算满24个月后30个工作日内无息支付。 （2）在材料到货验收合格双方对账结算后，成交人提供齐全的付款资料办理入账（包括但不限于：结算单、当 期结算金额100%发票、交货验收合格证明、产品质量证明、产品技术资料、进场验收单等）。 （3）成交人同意采购人通过转账支票、银行电汇、供应融资、商业承兑汇票、资产等方式支付货款，采用承兑 汇票支付时，贴现费用及供应融资方式产生的费用由成交人承担。 网 （4）如遇特殊情况（如节假日、银行系统升级、自然灾害、政府行政调节等等）不能及时付款，双方应以诚实 信用原则，卖方应给予供货，保持买方工地不断货停工，买方应在相关机构恢复正常工作的第一时间支付相应 货款；若卖方未履行向买方开具增值税专用发票等合同约定的义务或其它紧急情况买方延迟支付款项，买方不 务 承担延迟支付责任，卖方不得以此为由向采购人提出任何经济赔偿（索赔）或调价。 （5）在合同有效期内卖方不能完全或不履行合同义务，买方有权要求卖方继续履行并承担给买方造成的损失， 损失部分买方可从任何一笔应付款或预付款保函或质保金或履约保证金中扣除。 商 三、供应商资格要求 1.响应人必须是在中国境内注册的企业法人，能独立承担民事责任、具有独立法人资格的企业，并提供有效的营 业执照。不得为外资（含港澳台）独资或入股道企业。 2.响应人能开具增值税专用发票（一票制）。当各响应人税率不一致时，采用税前价格进行评审，单价在合同执 行期间保持不变，不予调价。 管 1. 响应人在2023年1月1日至今签订的合同，应具有与本次采购任一项相同或类似销售业绩不少于2份。 （合同扫描件至少包含:合同买卖双方盖章页、合同签订时间和业绩要求中的关键信息页）。 4.响应人提供近三个年度（2023年-2025年）会计师事务所或审计机构审计的财务审计报告（包括资产负债表、现 金流量表、利润表）或国企业财务报表（包括资产负债表、现金流量表、利润表）。 5.本次询价采购不接受联合体参与。 6.响应人不中存在《中华人民共和国招标投标法》、《中华人民共和国招标投标法实施条例》等禁止投标的情形。 7.供应商须为中国电力建设股份有限公司或其子企业在采购平台上的注册供应商，且供应商在采购平台的注册或 认证时间不少于2年，公司成立时间不少于3年。其中，满足上述条件但非中国水利水电第九工程局有限公司认证 供应商的（中国电力建设股份有限公司认证供应商除外），应在项目开标前完成采购平台中‘中国水利水电第 九工程局有限公司认证供应商’的身份认证。 四、保证金 1、形式：保证金或银行保函形式 2、金额：人民币壹万元整 五、采购文件的获取 1.领取时间： 2026年8月24日至2026年8月28日17:00 （上午9:00-11:30，下午13:30-17:00）。 2. 领取地点：贵州省贵阳市观山湖区诚信南路501号22楼采购与招标中心。 3. 所需材料： · 单位营业执照副本复印件（加盖公章）。 · 法定代表人授权委托书（见附件）及被授权人身份证原件及复印件。 · 领取材料前法人/委托人应先联系采购方确认相关事项。 1. 注意事项：1）采购文件仅限现场领取，未在规定时间内按要求提供完整材料者，将无法领取采购文件。2） 本采购项目为线下采购，所有相关文件，包括但不限于质疑、澄清等都应通过线下方式递交。 六、响应文件的递交 1. 响应文件递交的截止时间（投标截止时间，下同）为2026年9月1日14时00分（北京时间），响应文件递交地点 为贵阳市观山湖区诚信南路501号国际企业大厦22楼2206开标室。 2. 逾期送达的或者未送达指定地点的响应文件，采购人不予受理。 网 3. 响应截止时间及递交地点如有变动，采购人将及时以书面形式通知所有已获取询比采购文件的响应供应商。 4. 响应人递交响应文件包含纸质响应文件正本1份、副本3份。 务 5.响应文件递交时，响应供应商委托代理人需携带身份证原件和委托书，在响应文件开启前供采购人查验。 七、成交结果公示 商 定标完成后，在工程项目部公示栏内公示。 八、联系方式 道 采购机构：中国水利水电第九工程局有限公司采购与招标中心 地 址：贵州省贵阳市观山湖区诚信南路501号水电国际企业大厦 管 邮 编：550081 联 系 人：吴 工 国 电 话：0851-87980539 九、提出异议的渠道和方式 中 电 话：0851-87980539 电子邮箱：sdjjczzxwz@9j.powerchina.cn 十、纪检监督机构 中国水利水电第九工程局有限公司纪委办公室 监督电话：0851-87980543 2026年8月24日 报价网址:https://bid.powerchina.cn/notice/detail?id=2409514530 信息来源:https://www.chinapipe.net/project/d3079159.html cqdingjiu 2026.08.25 09:25:42</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>中国电建水电九局CQ某项目其他施工材料采购项目公开竞价采购公告 询比采购公告 项目编号：PC-0109-26J5-FG0266 一、采购条件 受中国水利水电第九工程局有限公司（以下简称“采购人”）委托，中国水利水电第九工程局有限公司采购与 招标中心（以下简称“采购机构”）以公开询比方式采购其他施工材料，计划使网用项目工程款资金用于本次询 比采购后所签订合同的支付。报价方式为一次报价，现将有关报价事项告知如下： 二、项目概况、采购范围 务 1、项目概况：项目位于重庆市，交通便利。 2、采购范围：工程用其他材料。 3、采购内容及数量：主要为砂浆、水泥、水泥（或混凝商土）空心砖、砂石料、PVC管材、种植土、草皮等其他 施工材料1批。详见询比采购文件报价表。 4、报价要求： 道 采用固定综合单价形式，在本合同执行期内不做任何调价。单价包含出厂价格、包装费、保险费、运输费、装 卸车费（含货到工地现场卸车费）、过江过路过桥费、合理利润、税金税费、代理费、货物交付前所需进行检 测检验费、售后服务以及市场价格涨幅风险费等各类费用；包括其它运至需方指定交货地点货物交付之前发生 的一切费用，以及与其他土建及相关专业的配合协调关系费用。 管 在供货周期内，出现市场价格波动、实际数量增减、供应时间调整等情况下本固定综合单价在合同执行期间 均不予调整。 项目实施过程中，因施国工图、设计变更或其它因素产生清单外新增项目的，由双方共同向不少于3家供应商询价， 以询价最低价为成交价格，双方签订补充协议后实施。 5、交货时间： 中 交货时间：采购合同签订后，按采购人或采购人发出的排产函要求供货。 6、交货地点： 交货地点：项目部指定位置，具体交货地点以采购方书面通知为准。 7.技术、质量要求 （1）要求为全新国产产品，卖方所供产品质量必须满足国家和行业标准、设计和买方使用要求，产品所用材料 必须符合国家标准。如遇国家或行业标准更新，以最新标准为准； （2）卖方应根据买方使用计划组织供货，所有供货质量确保达到上述要求。材料进场后，抽检不合格而产生的 一切费用及由此给采购人造成的损失由成交人承担。买方保留在例行送检之外随时抽检及送检产品的权利，检 验机构为具有相应检测项目资质的第三方检测机构。若检验不合格，卖方承担由此发生的全部费用。 （3）项目涉及到的图纸及规范要求的，卖方必须仔细阅读并充分掌握。图纸详细内容，须对接项目人员（李工， 联系电话：13595171151）至现场查阅，供货所有材料质量需满足图纸及规范要求。 （4）供应材料规格型号除满足合同约定外，还须满足买方与建设单位封样定样要求。 8、付款方式： （1）实行先货后款，按月结算，以每个自然月为一个供货对账结算周期，第一个月供货结束后，第二个月22日 前双方对账办理结算签认，双方对账结算后，卖方提供报价时确定税率全额增值税专用发票，买方在收到全额 发票后办理入账，买方办理入账后次月15日前（即第三个月15日前）支付第一个月供货结算货款的80%，以此类 推。供货结束后双方办理最终结算；工程竣工验收合格之日起2个月内，买方累计支付至总结算金额的90%；第 三方审计机构完成最终审计并出具审计报告之日起30日内，买方累计支付至总结算金额的97%；其余3%为质保金， 质保金在双方办理最终结算满24个月后30个工作日内无息支付。 （2）在材料到货验收合格双方对账结算后，成交人提供齐全的付款资料办理入账（包括但不限于：结算单、当 期结算金额100%发票、交货验收合格证明、产品质量证明、产品技术资料、进场验收单等）。 （3）成交人同意采购人通过转账支票、银行电汇、供应融资、商业承兑汇票、资产等方式支付货款，采用承兑 汇票支付时，贴现费用及供应融资方式产生的费用由成交人承担。 网 （4）如遇特殊情况（如节假日、银行系统升级、自然灾害、政府行政调节等等）不能及时付款，双方应以诚实 信用原则，卖方应给予供货，保持买方工地不断货停工，买方应在相关机构恢复正常工作的第一时间支付相应 货款；若卖方未履行向买方开具增值税专用发票等合同约定的义务或其它紧急情况买方延迟支付款项，买方不 务 承担延迟支付责任，卖方不得以此为由向采购人提出任何经济赔偿（索赔）或调价。 （5）在合同有效期内卖方不能完全或不履行合同义务，买方有权要求卖方继续履行并承担给买方造成的损失， 损失部分买方可从任何一笔应付款或预付款保函或质保金或履约保证金中扣除。 商 三、供应商资格要求 1.响应人必须是在中国境内注册的企业法人，能独立承担民事责任、具有独立法人资格的企业，并提供有效的营 业执照。不得为外资（含港澳台）独资或入股道企业。 2.响应人能开具增值税专用发票（一票制）。当各响应人税率不一致时，采用税前价格进行评审，单价在合同执 行期间保持不变，不予调价。 管 1. 响应人在2023年1月1日至今签订的合同，应具有与本次采购任一项相同或类似销售业绩不少于2份。 （合同扫描件至少包含:合同买卖双方盖章页、合同签订时间和业绩要求中的关键信息页）。 4.响应人提供近三个年度（2023年-2025年）会计师事务所或审计机构审计的财务审计报告（包括资产负债表、现 金流量表、利润表）或国企业财务报表（包括资产负债表、现金流量表、利润表）。 5.本次询价采购不接受联合体参与。 6.响应人不中存在《中华人民共和国招标投标法》、《中华人民共和国招标投标法实施条例》等禁止投标的情形。 7.供应商须为中国电力建设股份有限公司或其子企业在采购平台上的注册供应商，且供应商在采购平台的注册或 认证时间不少于2年，公司成立时间不少于3年。其中，满足上述条件但非中国水利水电第九工程局有限公司认证 供应商的（中国电力建设股份有限公司认证供应商除外），应在项目开标前完成采购平台中‘中国水利水电第 九工程局有限公司认证供应商’的身份认证。 四、保证金 1、形式：保证金或银行保函形式 2、金额：人民币壹万元整 五、采购文件的获取 1.领取时间： 2026年8月24日至2026年8月28日17:00 （上午9:00-11:30，下午13:30-17:00）。 2. 领取地点：贵州省贵阳市观山湖区诚信南路501号22楼采购与招标中心。 3. 所需材料： · 单位营业执照副本复印件（加盖公章）。 · 法定代表人授权委托书（见附件）及被授权人身份证原件及复印件。 · 领取材料前法人/委托人应先联系采购方确认相关事项。 1. 注意事项：1）采购文件仅限现场领取，未在规定时间内按要求提供完整材料者，将无法领取采购文件。2） 本采购项目为线下采购，所有相关文件，包括但不限于质疑、澄清等都应通过线下方式递交。 六、响应文件的递交 1. 响应文件递交的截止时间（投标截止时间，下同）为2026年9月1日14时00分（北京时间），响应文件递交地点 为贵阳市观山湖区诚信南路501号国际企业大厦22楼2206开标室。 2. 逾期送达的或者未送达指定地点的响应文件，采购人不予受理。 网 3. 响应截止时间及递交地点如有变动，采购人将及时以书面形式通知所有已获取询比采购文件的响应供应商。 4. 响应人递交响应文件包含纸质响应文件正本1份、副本3份。 务 5.响应文件递交时，响应供应商委托代理人需携带身份证原件和委托书，在响应文件开启前供采购人查验。 七、成交结果公示 商 定标完成后，在工程项目部公示栏内公示。 八、联系方式 道 采购机构：中国水利水电第九工程局有限公司采购与招标中心 地 址：贵州省贵阳市观山湖区诚信南路501号水电国际企业大厦 管 邮 编：550081 联 系 人：吴 工 国 电 话：0851-87980539 九、提出异议的渠道和方式 中 电 话：0851-87980539 电子邮箱：sdjjczzxwz@9j.powerchina.cn 十、纪检监督机构 中国水利水电第九工程局有限公司纪委办公室 监督电话：0851-87980543 2026年8月24日 报价网址:https://bid.powerchina.cn/notice/detail?id=2409514530 信息来源:https://www.chinapipe.net/project/d3079159.html cqdingjiu 2026.08.25 10:30:21</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>项目位于重庆市，主要采购砂浆、水泥、水泥（或混凝土）空心砖、砂石料、PVC管材、种植土、草皮等其他施工材料。
 https://www.chinapipe.net/project/d3079159.html</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="N8" t="n">
         <v>0</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>西部(重庆)科学城西三镇老旧小区改造项目—东鹏周边配套(新乾路)污水管网维修工程招标公告</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>市政</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>九龙坡区</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>本项目实施东鹏周边配套（新乾路）污水管网维修，包括但不限于：排污清淤、DN800管道维修、DN400管道维修、检查井改造等。</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>项目业主为重庆铝产业开发投资集团有限公司，建设资金来自专项债券，项目出资比例为100%，招标人为重庆铝产业开发投资集团有限公司。</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>市政公用工程施工</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>西部(重庆)科学城西三镇老旧小区改造项目—东鹏周边配套(新乾路)污水管网维修工程招标公告 1.招标条件 本招标项目 西部（重庆）科学城西三镇老旧小区改造项目—东鹏周边配套（新乾路）污水管网维修工程 ， 项目业主为 重庆铝产业开发投资集团有限公司 ，建设资金来自 专项债券 ，项目出资比例为 100% ，招 标人为 重庆铝产业开发投资集团有限公司 。项目已具备招标条件，现对该项目的施工进行公开比价，评 标办法采用经评审的最低投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 重庆市九龙坡区西彭镇。 2.2 项目概况与建设规模： 本项目实施东鹏周边配套（新乾路）污水管网维修，包括但不限于：排污清 淤、DN800管道维修、DN400管道维修、检查井改造等。 务 2.3 本次招标项目合同估算金额：350万元 2.4 招标范围： 招标人提供的工程量清单、设计图纸（如有）、技术文件（如有）等包括的所有工作内容，包 括但不限于:施工方案所示范围内的土石方工程，排污清商淤，管网改扩建，管道缺陷修复，管网CCTV检测，检查 井改造，路面破除恢复、相关附属设施破除及恢复等所有工作内容。具体详见招标人提供的工程量清单。 2.5 工期要求： 20 日历天 道 缺陷责任期要求： 24个月 2.6 标段划分（如有）： / 管 2.7 其他：/ 3.政府采购工程 3.投标人资格要求 国 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件： 具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰 级及以上资质 ； 中 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见比价文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件、工程量清单、 电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及CA数字证书办理， 办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”、“CA 数字证书办 理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 布至2026-08-25 17:00:00前。 4.3招标人应于2026-08-26 23:59:59前在重庆市公共资源交易网发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-08-28 14:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资 源交易监督网上发布。] 7.联系方式 招 标 人: 重庆铝产业开发投资集团有限公司 代理机构: 鼎信项目管理咨询有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 陈老师 项目负责人: 刘白冰 电 话: 65801996 电 话: 18523355792 网 传 真: 传 真: 02367038453 电子邮箱: 电子邮箱: 开户银行: 开户银行: 务 账 号: 账 号: 监督部门: 商 电 话: 2026年08月24日 西部（重庆）科学城西三镇老旧小区改造项道目—东鹏周边配套（新乾路）污水管网维修工程 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051300100 管 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835010772 坝支行 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764061147 国中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000630078 支行 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000001308 贸易试验区分行 中 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630010305 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020022446 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146638771 信息来源:https://www.chinapipe.net/project/d3079143.html cqdingjiu 2026.08.25 09:25:42</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>西部(重庆)科学城西三镇老旧小区改造项目—东鹏周边配套(新乾路)污水管网维修工程招标公告 1.招标条件 本招标项目 西部（重庆）科学城西三镇老旧小区改造项目—东鹏周边配套（新乾路）污水管网维修工程 ， 项目业主为 重庆铝产业开发投资集团有限公司 ，建设资金来自 专项债券 ，项目出资比例为 100% ，招 标人为 重庆铝产业开发投资集团有限公司 。项目已具备招标条件，现对该项目的施工进行公开比价，评 标办法采用经评审的最低投标价法。 2.项目概况与招标范围 网 2.1 建设地点： 重庆市九龙坡区西彭镇。 2.2 项目概况与建设规模： 本项目实施东鹏周边配套（新乾路）污水管网维修，包括但不限于：排污清 淤、DN800管道维修、DN400管道维修、检查井改造等。 务 2.3 本次招标项目合同估算金额：350万元 2.4 招标范围： 招标人提供的工程量清单、设计图纸（如有）、技术文件（如有）等包括的所有工作内容，包 括但不限于:施工方案所示范围内的土石方工程，排污清商淤，管网改扩建，管道缺陷修复，管网CCTV检测，检查 井改造，路面破除恢复、相关附属设施破除及恢复等所有工作内容。具体详见招标人提供的工程量清单。 2.5 工期要求： 20 日历天 道 缺陷责任期要求： 24个月 2.6 标段划分（如有）： / 管 2.7 其他：/ 3.政府采购工程 3.投标人资格要求 国 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件： 具备建设行政主管部门颁发的有效的市政公用工程施工总承包贰 级及以上资质 ； 中 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见比价文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件、工程量清单、 电子图纸等资料。参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及CA数字证书办理， 办理方式请参见重庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”、“CA 数字证书办 理”。若投标人未及时完成市场主体信息登记和CA数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发 布至2026-08-25 17:00:00前。 4.3招标人应于2026-08-26 23:59:59前在重庆市公共资源交易网发布澄清。 5.投标文件递交的内容 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-08-28 14:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资 源交易监督网上发布。] 7.联系方式 招 标 人: 重庆铝产业开发投资集团有限公司 代理机构: 鼎信项目管理咨询有限公司 地 址: 地 址: 邮 编: 邮 编: 项目负责人: 陈老师 项目负责人: 刘白冰 电 话: 65801996 电 话: 18523355792 网 传 真: 传 真: 02367038453 电子邮箱: 电子邮箱: 开户银行: 开户银行: 务 账 号: 账 号: 监督部门: 商 电 话: 2026年08月24日 西部（重庆）科学城西三镇老旧小区改造项道目—东鹏周边配套（新乾路）污水管网维修工程 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公司 重庆三峡银行九龙坡支行 9696801051300100 管 重庆农村商业银行股份有限公司沙坪 重庆联合产权交易所集团股份有限公司 0304010120010028835010772 坝支行 重庆联合产权交易所集团股份有限公司 中国民生银行股份有限公司重庆分行 9902001764061147 国中国建设银行股份有限公司重庆渝中 重庆联合产权交易所集团股份有限公司 6232813760000630078 支行 中国农业银行股份有限公司重庆自由 重庆联合产权交易所集团股份有限公司 312601010400083780000001308 贸易试验区分行 中 重庆联合产权交易所集团股份有限公司 招商银行股份有限公司重庆分行 123904808710630010305 重庆联合产权交易所集团股份有限公司 中信银行重庆上清寺支行 3111230034020022446 重庆联合产权交易所集团股份有限公司 重庆银行股份有限公司七星岗支行 15010202900420146638771 信息来源:https://www.chinapipe.net/project/d3079143.html cqdingjiu 2026.08.25 10:30:21</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>本项目实施东鹏周边配套（新乾路）污水管网维修，包括但不限于：排污清淤、DN800管道维修、DN400管道维修、检查井改造等。
 https://www.chinapipe.net/project/d3079143.html</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="N9" t="n">
         <v>85</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>污水管网维修, 市政公用工程, 专项债券</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>西部(重庆)科学城, 西三镇老旧小区改造, 污水管网维修, 市政公用工程, 重庆铝产业开发投资集团有限公司, 专项债券</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>港桥园区万春路施工范围内供水管道迁改工程、永川区万笋连接道施工范围内供水管道迁改工程材料采购公告</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>市政</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>永川区</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>港桥园区万春路施工范围内供水管道迁改工程、永川区万笋连接道施工范围内供水管道迁改工程材料采购</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>单位自筹资金</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>供水管道</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>港桥园区万春路施工范围内供水管道迁改工程、永川区万笋连接道施工范围内供水管道迁改工程材料采购公告 一、竞争性谈判内容 项目编号：26ZXGA028 项目名称：港桥园区万春路施工范围内供水管道迁改工程、永川区万笋连接道施工范围内供水管道迁改工程材 料采购 采购方式：公开招标 网 最高限价：2364296.39元 采购需求： 务 一、竞争性谈判内容 采购标的对应的中小 最高限价 保证金 成交供应商数量 包号及名称 企业划分标准所属行 （元） （元） （名） 业 商 港桥园区万春路施工范围内供水管道迁改工程、永 川区万笋连接道施工范围内供水管道迁改工程材料 2364296.39 47000.00 1 工业 采购 二、资金来源 道 单位自筹资金。 三、供应商资格条件 管 （一）满足《中华人民共和国政府采购法》第二十二条规定；无 （二）本项目的特定资格要求：无。 国 四、投标、开标有关说明 （一）凡有意参加投标的投标人，请在重庆市公共资源交易网（永川区）上下载本项目招标文件以及图纸、澄 清等开标前中公布的所有项目资料，无论投标人领取或下载与否，均视为已知晓所有招标内容。 （二）招标文件公告期限：自采购公告发布之日（2026年8月24日）起五个工作日。 （三）招标文件提供期限 1.招标文件提供期限：2026年8月24日-2026年8月31日。 （四）投标地点：重庆市永川区公共资源事务中心（重庆市永川区昌州大道东段179号2楼） （五）递交投标文件的时间及地点： 递交开始时间：2026年9月15日北京时间9:00。 递交截止时间：2026年9月15日北京时间9:30。 （六）开标时间：2026年9月15日北京时间9:30 （七）开标地点：同投标地点 五、投标保证金和采购件费文 （一）投标保证金递交 1.投标人应足额交纳投标保证金（保证金金额详见本篇，一、招标项目内容），并汇至所投包对应的账户，投标 保证金的到账截止时间同投标截止时间。 投标保证金账户： (1) 银行名称： 民生银行 银行账号： 9902001805899539 网 银行账户名称： 重庆联合产权交易所集团股份有限公司 银行支行： 中国民生银行股份有限公司重庆分行营业部 务 (2) 银行名称： 重庆农村商业银行 银行账号： 0205010120010028826010739 商 银行账户名称： 重庆联合产权交易所集团股份有限公司 银行支行： 重庆农村商业银行股份有限公司江道北支行 (3) 银行名称： 中国农业银行 管 银行账号： 6228400477035264867 银行账户名称： 重庆联合产权交易所集团股份有限公司 国 银行支行： 中国农业银行股份有限公司重庆自由贸易试验区分行 2.各投标人在银行转账（电汇）时，须充分考虑银行转账（电汇）的时间差风险，如同城转账、异地转账或汇款、 跨行转账或电汇的时间要求。 中 （二）保证金退还方式 1.未中标人的投标保证金开标后五个工作日内退付给投标人； 2.中标人的投标保证金自开标结束后，划转给各采购单位作为项目履约保证金（如果有）。 重庆公共资源交易中心永川分中心咨询电话：023-49820075 （三）采购文件费递交 1.采购文件费缴纳方式：供应商通过网银、转账、电汇等方式在规定的时间内，按规定金额将采购文件费从供应 商银行账户转至下面指定的账户，否则，报名无效。供应商须充分考虑银行转账（电汇）的时间差风险，如同 城转账、异地转账或汇款、跨行转账或电汇的时间要求。 2.采购文件费用：人民币500.00元/份（售后不退）。 3.采购文件费账户： 户名:重庆永川政鑫综合能源有限公司益川分公司 账号:11286000000023711 开户银行:华夏银行重庆分行永川支行（转账时备注项目名称分包或者项目编号） 4.供应商提交采购文件费截止时间(即到账时间) 与递交投标文件截止时间相同。 六、采购项目需落实的采购政策 （一）按照《财政部 生态环境部关于印发环境标志产品政府采购品目清单的通知》（财库〔2019〕18号）和 《财政部 发展改革委关于印发节能产品政府采购品目清单的通知》（财库〔2019〕19号）的规定，落实国家节 能环保政策。 （二）按照财政部、工业和信息化部关于印发《政府采购促进中小企业发展管理网办法》的通知（财库〔2020〕46 号）的规定，落实促进中小企业发展政策。 （三）按照《财政部、司法部关于政府采购支持监狱企业发展有关问题的通知》（财库〔2014〕68号）的规定， 落实支持监狱企业发展政策。 务 （四）按照《三部门联合发布关于促进残疾人就业政府采购政策的通知》（财库〔2017〕 141号）的规定，落实 支持残疾人福利性单位发展政策。 七、投标有关规定 商 （一）单位负责人为同一人或者存在直接控股、管理关系的不同投标人，不得参加同一合同项（包）下的采购 活动。 道 （二）为采购项目提供整体设计、规范编制或者项目管理、监理、检测等服务的投标人，不得再参加该采购项 目的其他采购活动。 （三）本项目若有澄清文件一律在重庆市公共资源交易网（永川区）（https://www.cqggzy.com/yongchuanweb/） 管 上发布，请各投标人注意下载；无论投标人下载与否，均视同投标人已知晓本项目澄清文件的内容。 （四）超过投标截止时间递交的投标文件，恕不接收。 （五）投标费用：无论国投标结果如何，投标人参与本项目投标的所有费用均应由投标人自行承担。 （六）本项目不接受联合体参与投标。 （七）本项目不接受合同分包。 中 （八）按照《财政部关于在政府采购活动中查询及使用信用记录有关问题的通知》财库〔2016〕125号，投标人 列入失信被执行人、重大税收违法案件当事人名单、采购严重违法失信行为记录名单及其他不符合《中华人民 共和国政府采购法》第二十二条规定条件的投标人，将拒绝其参与采购活动。 八、联系方式 （一）采购人：重庆市永川区惠永水务有限公司 联系人：李老师 电 话：13618262877 地 址：重庆市永川区永泰路401号昌州古韵19栋 （二）采购代理机构：重庆永川政鑫综合能源有限公司 联系人：陈仕培 电 话：023-49621986 地 址：重庆市永川区昌州大道东段179号 信息来源:https://www.chinapipe.net/project/d3079142.html cqdingjiu 2026.08.25 09:25:42 网 务 商 道 管 国 中</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>港桥园区万春路施工范围内供水管道迁改工程、永川区万笋连接道施工范围内供水管道迁改工程材料采购公告 一、竞争性谈判内容 项目编号：26ZXGA028 项目名称：港桥园区万春路施工范围内供水管道迁改工程、永川区万笋连接道施工范围内供水管道迁改工程材 料采购 采购方式：公开招标 网 最高限价：2364296.39元 采购需求： 务 一、竞争性谈判内容 采购标的对应的中小 最高限价 保证金 成交供应商数量 包号及名称 企业划分标准所属行 （元） （元） （名） 业 商 港桥园区万春路施工范围内供水管道迁改工程、永 川区万笋连接道施工范围内供水管道迁改工程材料 2364296.39 47000.00 1 工业 采购 二、资金来源 道 单位自筹资金。 三、供应商资格条件 管 （一）满足《中华人民共和国政府采购法》第二十二条规定；无 （二）本项目的特定资格要求：无。 国 四、投标、开标有关说明 （一）凡有意参加投标的投标人，请在重庆市公共资源交易网（永川区）上下载本项目招标文件以及图纸、澄 清等开标前中公布的所有项目资料，无论投标人领取或下载与否，均视为已知晓所有招标内容。 （二）招标文件公告期限：自采购公告发布之日（2026年8月24日）起五个工作日。 （三）招标文件提供期限 1.招标文件提供期限：2026年8月24日-2026年8月31日。 （四）投标地点：重庆市永川区公共资源事务中心（重庆市永川区昌州大道东段179号2楼） （五）递交投标文件的时间及地点： 递交开始时间：2026年9月15日北京时间9:00。 递交截止时间：2026年9月15日北京时间9:30。 （六）开标时间：2026年9月15日北京时间9:30 （七）开标地点：同投标地点 五、投标保证金和采购件费文 （一）投标保证金递交 1.投标人应足额交纳投标保证金（保证金金额详见本篇，一、招标项目内容），并汇至所投包对应的账户，投标 保证金的到账截止时间同投标截止时间。 投标保证金账户： (1) 银行名称： 民生银行 银行账号： 9902001805899539 网 银行账户名称： 重庆联合产权交易所集团股份有限公司 银行支行： 中国民生银行股份有限公司重庆分行营业部 务 (2) 银行名称： 重庆农村商业银行 银行账号： 0205010120010028826010739 商 银行账户名称： 重庆联合产权交易所集团股份有限公司 银行支行： 重庆农村商业银行股份有限公司江道北支行 (3) 银行名称： 中国农业银行 管 银行账号： 6228400477035264867 银行账户名称： 重庆联合产权交易所集团股份有限公司 国 银行支行： 中国农业银行股份有限公司重庆自由贸易试验区分行 2.各投标人在银行转账（电汇）时，须充分考虑银行转账（电汇）的时间差风险，如同城转账、异地转账或汇款、 跨行转账或电汇的时间要求。 中 （二）保证金退还方式 1.未中标人的投标保证金开标后五个工作日内退付给投标人； 2.中标人的投标保证金自开标结束后，划转给各采购单位作为项目履约保证金（如果有）。 重庆公共资源交易中心永川分中心咨询电话：023-49820075 （三）采购文件费递交 1.采购文件费缴纳方式：供应商通过网银、转账、电汇等方式在规定的时间内，按规定金额将采购文件费从供应 商银行账户转至下面指定的账户，否则，报名无效。供应商须充分考虑银行转账（电汇）的时间差风险，如同 城转账、异地转账或汇款、跨行转账或电汇的时间要求。 2.采购文件费用：人民币500.00元/份（售后不退）。 3.采购文件费账户： 户名:重庆永川政鑫综合能源有限公司益川分公司 账号:11286000000023711 开户银行:华夏银行重庆分行永川支行（转账时备注项目名称分包或者项目编号） 4.供应商提交采购文件费截止时间(即到账时间) 与递交投标文件截止时间相同。 六、采购项目需落实的采购政策 （一）按照《财政部 生态环境部关于印发环境标志产品政府采购品目清单的通知》（财库〔2019〕18号）和 《财政部 发展改革委关于印发节能产品政府采购品目清单的通知》（财库〔2019〕19号）的规定，落实国家节 能环保政策。 （二）按照财政部、工业和信息化部关于印发《政府采购促进中小企业发展管理网办法》的通知（财库〔2020〕46 号）的规定，落实促进中小企业发展政策。 （三）按照《财政部、司法部关于政府采购支持监狱企业发展有关问题的通知》（财库〔2014〕68号）的规定， 落实支持监狱企业发展政策。 务 （四）按照《三部门联合发布关于促进残疾人就业政府采购政策的通知》（财库〔2017〕 141号）的规定，落实 支持残疾人福利性单位发展政策。 七、投标有关规定 商 （一）单位负责人为同一人或者存在直接控股、管理关系的不同投标人，不得参加同一合同项（包）下的采购 活动。 道 （二）为采购项目提供整体设计、规范编制或者项目管理、监理、检测等服务的投标人，不得再参加该采购项 目的其他采购活动。 （三）本项目若有澄清文件一律在重庆市公共资源交易网（永川区）（https://www.cqggzy.com/yongchuanweb/） 管 上发布，请各投标人注意下载；无论投标人下载与否，均视同投标人已知晓本项目澄清文件的内容。 （四）超过投标截止时间递交的投标文件，恕不接收。 （五）投标费用：无论国投标结果如何，投标人参与本项目投标的所有费用均应由投标人自行承担。 （六）本项目不接受联合体参与投标。 （七）本项目不接受合同分包。 中 （八）按照《财政部关于在政府采购活动中查询及使用信用记录有关问题的通知》财库〔2016〕125号，投标人 列入失信被执行人、重大税收违法案件当事人名单、采购严重违法失信行为记录名单及其他不符合《中华人民 共和国政府采购法》第二十二条规定条件的投标人，将拒绝其参与采购活动。 八、联系方式 （一）采购人：重庆市永川区惠永水务有限公司 联系人：李老师 电 话：13618262877 地 址：重庆市永川区永泰路401号昌州古韵19栋 （二）采购代理机构：重庆永川政鑫综合能源有限公司 联系人：陈仕培 电 话：023-49621986 地 址：重庆市永川区昌州大道东段179号 信息来源:https://www.chinapipe.net/project/d3079142.html cqdingjiu 2026.08.25 10:30:22 网 务 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>港桥园区万春路施工范围内供水管道迁改工程、永川区万笋连接道施工范围内供水管道迁改工程材料采购
 https://www.chinapipe.net/project/d3079142.html</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="N10" t="n">
         <v>80</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>供水管道, 材料采购</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)答疑补遗文件</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>市政</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)答疑补遗文件</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>原文未提及</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>排水管网</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)答疑补遗文件 龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)答疑补遗文件 2026-08-24 项目编号：50011120260806002010101 龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)招标人答疑文件 一、质疑内容及答疑回复： 网 现将“龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)”招标的投标人质疑内容答疑如下： 质疑1：报价合理性说明是否可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料还 务 需要提供其他的证明材料吗 答疑1：报价合理性说明的证明材料由投标人自行考虑提供，其提供的材料是否满足招标文件要求由评标委员会 评定。 商 质疑2：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗财政部 国务院国资委 金融监管总 局2023年9月14日发布的《关于加强审计报告查验工作的通知》中要求会计师事务所应当按照规定将其承办《中 华人民共和国注册会计师法》第十四条规定审计业务出具的报告（以下简称审计报告）上传注册会计师行业统 一监管平台（以下简称统一监管平台）并申请道赋码。本项目投标人提供的财务报告需要赋码和提供深度查询截 图吗 答疑2：需提供会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表、附注，财务报表须至少包 括现金流量表、资产负债表、利润表。投标人提供的财务报告不需要赋码和深度查询截图。 管 质疑3：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖章， 请问需要提供联合体协议书吗 答疑3：需要。 国 质疑4：投标函中的缺陷责任期可以填“达到招标文件的要求”吗 答疑4：可以。 中 质疑5：任一清单的综合单价低于警戒线，就要提供说明吗 答疑5：招标文件列举部分任一清单单项的综合单价低于警戒线，就需要提供说明。 质疑6：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收，请 问我公司业绩满足业绩要求吗 答疑6：是否满足招标文件要求由评标委员会评定。 质疑7：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要求”吗 答疑7：可以。 质疑8：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗 答疑8：详见答疑1. 质疑9：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗 答疑9：可以。 质疑10：业绩要求的竣工时间是指竣工验收时间吗 答疑10：是的。 质疑11：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知书发 出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予提前注 销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗 答疑11：满足招标文件要求即可。 质疑12：请问招标人是否委派业主专家参与评标吗 答疑12：本项目评标委员会由招标人依法组建。 网 质疑13 ：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗 答疑13：需提供会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表、附注，财务报表须至少包 务 括现金流量表、资产负债表、利润表。 质疑14：燃气管道安装施工业绩满足吗 答疑14：业绩是否满足招标文件要求由评标委员会评定。商 质疑15：有没有人行贿专家，有的话我们就不参加了。 答疑15：本项目遵循公开、公平、公正的原则道进行招标，如发现相关线索，请潜在投标人依法向有关部门反 映。 质疑16：重庆市电子招投标系统投标文件-报价部分“己标价工程量清单”-“投标总价”页面招标人名称需要填 写吗 管 答疑16：填与不填均可，此项不作为评审要求。 质疑17：自来水厂或者净水厂施工业绩满足业绩要求吗 国 答疑17：业绩是否满足招标文件要求由评标委员会评定。 质疑18：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要 提供其他格式之外的其他承诺 中 答疑18：已包含招标文件中要求的全部承诺，是否额外提供承诺由投标人自行决定。 质疑19：本项目是异地评标吗 答疑19：是的。 质疑20：老旧小区室外环境改造施工业绩符合吗 答疑20：业绩是否满足招标文件要求由评标委员会评定。 质疑21：财务报告可以不提供财务报表附注吗 答疑21：需提供会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表、附注，财务报表须至少包 括现金流量表、资产负债表、利润表。 质疑22：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗 答疑22：不需要。 质疑23：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准 答疑23：若不一致，以盖公章的招标文件PDF文件为准。 质疑24：乡、镇供水厂及供水管道业绩满足业绩要求吗 答疑24：业绩是否满足招标文件要求由评标委员会评定。 质疑25：现在除了没有警戒线和技术方案的低价项目评标专家不被围猎，哪个项目不围猎评标专家，请问招标人 如何保证公平 答疑25：本项目遵循公开、公平、公正的原则进行招标，如发现相关线索，请潜在投标人依法向有关部门反映。 网 质疑26：财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加强审计报告查验工作的通知》中要求 会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第十四条规定审计业务出具的报告（以 下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标人提 供的财务报告需要赋码和提供深度查询截图吗 务 答疑26：详见答疑2。 质疑27：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、注册证 及在本单位注册的证明文件替代 商 答疑27：需按招标文件要求提供养老保险证明材料，退休人员不满足招标文件要求。 质疑28：专业分包业绩满足业绩要求吗 道 答疑28：业绩是否满足招标文件要求由评标委员会评定。 质疑29：污水处理厂提标改造施工业绩满足吗 管 答疑29：业绩是否满足招标文件要求由评标委员会评定。 质疑30：投标人投标总报价或者部分单项报价低于招标文件规定的对应的异常低价警戒线的，投标人未提供报价 合理性说明或者提供的国说明不能证明其报价合理性的，由评标委员会作否决投标处理。部分单项报价是指单项 工程的合价低于警戒线提供合理说明还是清单综合单价低于警戒线提供合理说明呢 答疑30：招标文件中已列举部分单项，部分单项报价是指单项工程的单价低于警戒线提供合理说明。 中 质疑31：专业分包业绩是否符合招标文件业绩要求 答疑31：业绩是否满足招标文件要求由评标委员会评定。 质疑32 ：市政管网项目业绩是否符合招标文件业绩要求 答疑32:业绩是否满足招标文件要求由评标委员会评定。 质疑33:完成过1个市政基础施工业绩，请问有业绩金额要求吗 答疑33：没有业绩金额要求。 质疑34 ：本工程要求市政公用工程施工总承包二级及以上资质，技术负责人要求中工，但是项目经理却要求一 级建造师，建议项目经理为二级 答疑34：按招标文件要求执行。 质疑35 ：低于警戒线，是否需要提供根据当地原材料的价格及人工、机械做出相应的分析表和提供之前做过相 关项目的低价项目原材料合同及发票、结清证明、台账、转账明细 答疑35：详见答疑1。 质疑36 ：低价标就是低价标，谁低谁做。不仅设总价超警戒线要写说明，还要设子项超警戒线说明，真是既要 当婊子，又要立牌坊。 答疑36：本招标文件按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本》（2026年版）和《重庆 市建设工程项目评标方法规定》渝发改规范〔2025〕9号编制。 质疑37 ：总报价超低价警戒线要写合理性说明，对分部分项超低价警戒线也要写说明。投标企业是以总报价来 平衡项目是否赢亏，不是以某个子项来平衡，招标人还有必要设置某个子项超低价警戒线也要写说明吗建议只 保留总报价超低价警戒线需写说明。 答疑37：按招标文件要求执行。 网 质疑38：请问XX融资担保有限公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，目前查出XX 融资担保多条被执行案件，都是因为不能履行保函的见索即付，拒绝赔付。相关业主方在招标文件补遗通知中 直接将XX融资担保有限公司列入担保公司回避名单，拒绝XX融资担保有限公司所出具的保函。由此可见XX融资 担保有限公司的信用资质、履约能力、根本无能力是存在很大问题的。请问以XX融资担保有限公司目前的被执 务 行和不履行投标担保责任的情况是否符合招标文件的要求? 答疑38：纸质投标保函的开立人应当是具有相应资格的银行、保险机构、融资担保公司，其信用资质、履约能力、 担保能力、赔付流程、安全保密等应符合工程保函业务条件。纸质投标保函应合法合规，符合招投标行政监督 部门、行业主管部门和金融监管部门的相关规定，满足招商标文件约定要求。投标人应选择在渝依法设立总部或 者设有分支机构的金融机构开具纸质投标保函。投标人对所提交的纸质投标保函的真实性、合法性、有效性负 责。本招标项目投标保函的具体要求详见招标文件第二章投标人须知前附表第3.4款投标保证金，履约保函的具 体要求详见招标文件第二章投标人须知前附表第7.6.1项履约担保。 道 质疑39：请问XX融资担保有限公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，目前查出XX 融资担保多条被执行案件，都是因为不能履行保函的见索即付，拒绝赔付。相关业主方在招标文件补遗通知中 直接将XX融资担保有限公司列入担保公司回避名单，拒绝XX融资担保有限公司所出具的保函。由此可见XX融资 担保有限公司的信用资质、履约能力、根本无能力是存在很大问题的。请问以XX融资担保有限公司目前的被执 管 行和不履行投标担保责任的情况是否符合招标文件的要求? 答疑39：详见答疑38。 国 注：本次答疑内容与招标文件不一致的地方，以本次答疑文件为准。 中 招标人：重庆大足实业发展集团有限公司 招标代理机构：中阜鼎聚工程项目管理（重庆）有限公司 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3079084.html cqdingjiu 2026.08.25 09:25:43</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)答疑补遗文件
-https://www.chinapipe.net/project/d3079084.html</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>排水管网, 能力提升工程</t>
+          <t>供水管道, 材料采购, 公开招标</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)答疑补遗文件</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>龙岗片区(濿溪河以北)一分区排水管网能力提升工程(一标段)答疑补遗文件</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>排水管网</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)答疑补遗文件 龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)答疑补遗文件 2026-08-24 项目编号：50011120260806002010101 龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)招标人答疑文件 一、质疑内容及答疑回复： 网 现将“龙岗片区(濑溪河以北)一分区排水管网能力提升工程(一标段)”招标的投标人质疑内容答疑如下： 质疑1：报价合理性说明是否可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料还 务 需要提供其他的证明材料吗 答疑1：报价合理性说明的证明材料由投标人自行考虑提供，其提供的材料是否满足招标文件要求由评标委员会 评定。 商 质疑2：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗财政部 国务院国资委 金融监管总 局2023年9月14日发布的《关于加强审计报告查验工作的通知》中要求会计师事务所应当按照规定将其承办《中 华人民共和国注册会计师法》第十四条规定审计业务出具的报告（以下简称审计报告）上传注册会计师行业统 一监管平台（以下简称统一监管平台）并申请道赋码。本项目投标人提供的财务报告需要赋码和提供深度查询截 图吗 答疑2：需提供会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表、附注，财务报表须至少包 括现金流量表、资产负债表、利润表。投标人提供的财务报告不需要赋码和深度查询截图。 管 质疑3：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公司盖章， 请问需要提供联合体协议书吗 答疑3：需要。 国 质疑4：投标函中的缺陷责任期可以填“达到招标文件的要求”吗 答疑4：可以。 中 质疑5：任一清单的综合单价低于警戒线，就要提供说明吗 答疑5：招标文件列举部分任一清单单项的综合单价低于警戒线，就需要提供说明。 质疑6：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收，请 问我公司业绩满足业绩要求吗 答疑6：是否满足招标文件要求由评标委员会评定。 质疑7：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要求”吗 答疑7：可以。 质疑8：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗 答疑8：详见答疑1. 质疑9：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗 答疑9：可以。 质疑10：业绩要求的竣工时间是指竣工验收时间吗 答疑10：是的。 质疑11：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知书发 出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予提前注 销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗 答疑11：满足招标文件要求即可。 质疑12：请问招标人是否委派业主专家参与评标吗 答疑12：本项目评标委员会由招标人依法组建。 网 质疑13 ：财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗 答疑13：需提供会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表、附注，财务报表须至少包 务 括现金流量表、资产负债表、利润表。 质疑14：燃气管道安装施工业绩满足吗 答疑14：业绩是否满足招标文件要求由评标委员会评定。商 质疑15：有没有人行贿专家，有的话我们就不参加了。 答疑15：本项目遵循公开、公平、公正的原则道进行招标，如发现相关线索，请潜在投标人依法向有关部门反 映。 质疑16：重庆市电子招投标系统投标文件-报价部分“己标价工程量清单”-“投标总价”页面招标人名称需要填 写吗 管 答疑16：填与不填均可，此项不作为评审要求。 质疑17：自来水厂或者净水厂施工业绩满足业绩要求吗 国 答疑17：业绩是否满足招标文件要求由评标委员会评定。 质疑18：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要 提供其他格式之外的其他承诺 中 答疑18：已包含招标文件中要求的全部承诺，是否额外提供承诺由投标人自行决定。 质疑19：本项目是异地评标吗 答疑19：是的。 质疑20：老旧小区室外环境改造施工业绩符合吗 答疑20：业绩是否满足招标文件要求由评标委员会评定。 质疑21：财务报告可以不提供财务报表附注吗 答疑21：需提供会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表、附注，财务报表须至少包 括现金流量表、资产负债表、利润表。 质疑22：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗 答疑22：不需要。 质疑23：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准 答疑23：若不一致，以盖公章的招标文件PDF文件为准。 质疑24：乡、镇供水厂及供水管道业绩满足业绩要求吗 答疑24：业绩是否满足招标文件要求由评标委员会评定。 质疑25：现在除了没有警戒线和技术方案的低价项目评标专家不被围猎，哪个项目不围猎评标专家，请问招标人 如何保证公平 答疑25：本项目遵循公开、公平、公正的原则进行招标，如发现相关线索，请潜在投标人依法向有关部门反映。 网 质疑26：财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加强审计报告查验工作的通知》中要求 会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第十四条规定审计业务出具的报告（以 下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标人提 供的财务报告需要赋码和提供深度查询截图吗 务 答疑26：详见答疑2。 质疑27：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、注册证 及在本单位注册的证明文件替代 商 答疑27：需按招标文件要求提供养老保险证明材料，退休人员不满足招标文件要求。 质疑28：专业分包业绩满足业绩要求吗 道 答疑28：业绩是否满足招标文件要求由评标委员会评定。 质疑29：污水处理厂提标改造施工业绩满足吗 管 答疑29：业绩是否满足招标文件要求由评标委员会评定。 质疑30：投标人投标总报价或者部分单项报价低于招标文件规定的对应的异常低价警戒线的，投标人未提供报价 合理性说明或者提供的国说明不能证明其报价合理性的，由评标委员会作否决投标处理。部分单项报价是指单项 工程的合价低于警戒线提供合理说明还是清单综合单价低于警戒线提供合理说明呢 答疑30：招标文件中已列举部分单项，部分单项报价是指单项工程的单价低于警戒线提供合理说明。 中 质疑31：专业分包业绩是否符合招标文件业绩要求 答疑31：业绩是否满足招标文件要求由评标委员会评定。 质疑32 ：市政管网项目业绩是否符合招标文件业绩要求 答疑32:业绩是否满足招标文件要求由评标委员会评定。 质疑33:完成过1个市政基础施工业绩，请问有业绩金额要求吗 答疑33：没有业绩金额要求。 质疑34 ：本工程要求市政公用工程施工总承包二级及以上资质，技术负责人要求中工，但是项目经理却要求一 级建造师，建议项目经理为二级 答疑34：按招标文件要求执行。 质疑35 ：低于警戒线，是否需要提供根据当地原材料的价格及人工、机械做出相应的分析表和提供之前做过相 关项目的低价项目原材料合同及发票、结清证明、台账、转账明细 答疑35：详见答疑1。 质疑36 ：低价标就是低价标，谁低谁做。不仅设总价超警戒线要写说明，还要设子项超警戒线说明，真是既要 当婊子，又要立牌坊。 答疑36：本招标文件按照《重庆市房屋建筑和市政基础设施工程施工招标文件示范文本》（2026年版）和《重庆 市建设工程项目评标方法规定》渝发改规范〔2025〕9号编制。 质疑37 ：总报价超低价警戒线要写合理性说明，对分部分项超低价警戒线也要写说明。投标企业是以总报价来 平衡项目是否赢亏，不是以某个子项来平衡，招标人还有必要设置某个子项超低价警戒线也要写说明吗建议只 保留总报价超低价警戒线需写说明。 答疑37：按招标文件要求执行。 网 质疑38：请问XX融资担保有限公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，目前查出XX 融资担保多条被执行案件，都是因为不能履行保函的见索即付，拒绝赔付。相关业主方在招标文件补遗通知中 直接将XX融资担保有限公司列入担保公司回避名单，拒绝XX融资担保有限公司所出具的保函。由此可见XX融资 担保有限公司的信用资质、履约能力、根本无能力是存在很大问题的。请问以XX融资担保有限公司目前的被执 务 行和不履行投标担保责任的情况是否符合招标文件的要求? 答疑38：纸质投标保函的开立人应当是具有相应资格的银行、保险机构、融资担保公司，其信用资质、履约能力、 担保能力、赔付流程、安全保密等应符合工程保函业务条件。纸质投标保函应合法合规，符合招投标行政监督 部门、行业主管部门和金融监管部门的相关规定，满足招商标文件约定要求。投标人应选择在渝依法设立总部或 者设有分支机构的金融机构开具纸质投标保函。投标人对所提交的纸质投标保函的真实性、合法性、有效性负 责。本招标项目投标保函的具体要求详见招标文件第二章投标人须知前附表第3.4款投标保证金，履约保函的具 体要求详见招标文件第二章投标人须知前附表第7.6.1项履约担保。 道 质疑39：请问XX融资担保有限公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，目前查出XX 融资担保多条被执行案件，都是因为不能履行保函的见索即付，拒绝赔付。相关业主方在招标文件补遗通知中 直接将XX融资担保有限公司列入担保公司回避名单，拒绝XX融资担保有限公司所出具的保函。由此可见XX融资 担保有限公司的信用资质、履约能力、根本无能力是存在很大问题的。请问以XX融资担保有限公司目前的被执 管 行和不履行投标担保责任的情况是否符合招标文件的要求? 答疑39：详见答疑38。 国 注：本次答疑内容与招标文件不一致的地方，以本次答疑文件为准。 中 招标人：重庆大足实业发展集团有限公司 招标代理机构：中阜鼎聚工程项目管理（重庆）有限公司 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3079084.html cqdingjiu 2026.08.25 10:30:22</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>龙岗片区(濿溪河以北)一分区排水管网能力提升工程(一标段)答疑补遗文件
+https://www.chinapipe.net/project/d3079084.html</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>排水管网, 能力提升工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>开州至梁平高速公路KWLTJC标项目预应力波纹管采购公告</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>交通</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>梁平区</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>开州区</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>本项目位于开州至梁平高速公路KWLTJC标段中K56+320~K96+292.165段，该段落主要经过万州区余家镇，梁平区复平镇、合兴街道、星桥镇、安商胜镇、仁贤街道、金带街道，桥隧比29.7%，在仁贤街道设置枢纽互通与G5515张南高速交通转换，最后向南至金带街道设置金带枢纽互通与G42沪蓉高速交通转换，终点桩号K96+292.165，路线全长39.97km。</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>本项目预应力波纹管采购限价（含税）为人民币：1618996.63元（大写：壹佰陆拾壹万捌仟玖佰玖拾陆元陆角叁分）。</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>预应力波纹管</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>开州至梁平高速公路KWLTJC标项目预应力波纹管采购公告 供应商应当在投标截止时间前，通过注册供应商账号在重庆高速集团物资采购平台 （http://113.250.85.222:8099/merchants/login）上进行报价并将投标文件扫描上传至该平台。 第一章 优选公告 根据《重庆巨能建设（集团）有限公司采购管理办法》、《重庆巨能建设（集团）有限公司物资采购管理办法》 等有关规定，对重庆巨能建设集团路桥工程有限公司开州至梁平高速公路KWLTJC标项目预应力波纹管采购进行 优选，现将本次采购有关事项通知如下： 网 一、优选项目概况 （一）优选项目名称： 开州至梁平高速公路KWLTJC标项目预应力波纹管采购 ； 务 （二）项目地点：重庆市梁平区； （三）优选项目概况：本项目位于开州至梁平高速公路KWLTJC标段中K56+320~K96+292.165段，该段落主要经 过万州区余家镇，梁平区复平镇、合兴街道、星桥镇、安商胜镇、仁贤街道、金带街道，桥隧比29.7%，在仁贤街 道设置枢纽互通与G5515张南高速交通转换，最后向南至金带街道设置金带枢纽互通与G42沪蓉高速交通转换， 终点桩号K96+292.165，路线全长39.97km。其中万州境5.98km（K56+320~K62+300）、梁平境33.99km（K62+300- K96+292.156），公路等级四车道高速公路，设计时速100km/h； 道 （四）包件划分： 本次优选设置1个包件 ； （五）中选人数： 1名 ； 管 （六）优选内容（或范围）： 详见预应力波纹管采购限价及报价表 ； 二、竞选人资格要求 1、竞选人必须是在中国华人民共和国境内依法注册、具有一般纳税人资格、具有优选标的物生产经营范围或建筑 材料的生产商、代理商或销售商；税率为13%。 2、具有良好的财务状况。竞选人须具备一定的垫资能力和垫资期限，如竞选人中标，须对支付材料款过程中办 理手续所需的时间给予充分理解，在资金紧张阶段对支付时间给予充分理解。 中 3、本次优选不接受联合体参选，单位负责人为同一人或者存在控股、管理关系的不同单位，不得同时参加竞选， 否则，相关竞选均被否决； 4、竞选人必须为巨能集团集采平台内的合格供应商（状态为：可投标），否则视为未参与竞选（高速集团内部 单位除外）。 5、须在三年内与巨能集团无诉讼纠纷的公司； 6、须在国家企业信用信息公示系统中未被列入严重违法失信企业名单； 三、采购方式：公开优选。 四、采购限价 本项目预应力波纹管采购限价（含税）为人民币：1618996.63元（大写：壹佰陆拾壹万捌仟玖佰玖拾陆元陆角叁 分），具体详见附件《预应力波纹管采购限价表》。本次优选项目采用含税价填报，税率为 13 %的增值税专用 发票。 五、竞选保证金 （一）缴纳金额及方式：人民币：/元（大写：/），在优选文件规定的递交优选文件截止时间前，竞选人通过企 业账户采用现金转账的方式直接划付至采购人指定账户，采购人不接受自然人转账。竞选保证金缴纳凭证须作 为竞选文件的组成部分，未缴纳者将取消竞选资格。竞选人自行考虑汇入时间风险，如同城汇入、异地汇入、 跨行汇入的时间要求。 账户名称：重庆巨能建设集团路桥工程有限公司 开户银行：厦门银行股份有限公司重庆渝北支行 账 号：80508400000406 行 号：313653070076 网 备注：“路桥开州至梁平高速公路KWLTJC标项目预应力波纹管采购竞选保证金” 六、优选文件的获取 务 （一）在优选文件发布之日至竞选截止日期2026年08月28 日10时00分内，供应商登录重庆高速集团物资采购平台 （http://113.250.85.222:8099/merchants/login）获取优选文件。自优选文件发布之日起，视为竞选人知晓本工程优 选的所有过程和全部事宜。 七、竞选文件的提交 商 （一）电子版竞选文件递交：竞选人在竞选截止时间内将签章完善的竞选文件扫描件（PDF格式），上传至重庆 高速集团物资采购平台（http://113.250.85.222:8099/merchants/login），逾期未上传平台自动拒收，竞选人必须保 证平台提交电子版资料与纸质版一致。 道 为方便工作人员统计报价，竞选人同时上传《竞选报价书》电子版（Excel或Word格式）至平台，此条件不作为 废选条件。 管 （二）纸质版竞选文件递交：一正一副，竞选人须在竞选截止时间内将签章完善的竞选文件提交采购人指定地 点，逾期拒收，作无效竞选处理，递交地址：重庆市九龙坡区高龙大道延长段377号7栋（1-3楼）巨能路桥公司。 竞选文件须装入密封袋内，封口处粘贴封条，并在封条的封口处加盖竞选人单位公章（鲜章），“竞选文件” 封袋上写明如下内容： 国 优选项目名称：开州至梁平高速公路KWLTJC标预应力波纹管采购项目。 竞选人名称： 中 在2026年08月28 日10时00分前不得开启（加盖竞选人单位公章鲜章） 八、踏勘 采购人不组织优选预备会，不组织现场考察，建议竞选人自行进行现场踏勘，竞选人可以选择多种运输方式和 多种运输线路，竞选人的综合费用不因运输方式和运输线路的变化而调整，竞选人报价时应将此因素考虑在内。 九、监督部门 重庆巨能建设集团路桥工程有限公司工程部； 监督电话：工程部023-68850703； 十、评选时间、地点 （一）优选单位：重庆巨能建设集团路桥工程有限公司； （二）地点：重庆市九龙坡区高龙大道延长段377号7栋（1-3楼）巨能路桥公司215会议室； （三）联系人及电话：廖薇 15923576859； 信息来源:https://www.chinapipe.net/project/d3078856.html cqdingjiu 2026.08.25 09:25:43 网 务 商 道 管 国 中</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>开州至梁平高速公路KWLTJC标项目预应力波纹管采购公告 供应商应当在投标截止时间前，通过注册供应商账号在重庆高速集团物资采购平台 （http://113.250.85.222:8099/merchants/login）上进行报价并将投标文件扫描上传至该平台。 第一章 优选公告 根据《重庆巨能建设（集团）有限公司采购管理办法》、《重庆巨能建设（集团）有限公司物资采购管理办法》 等有关规定，对重庆巨能建设集团路桥工程有限公司开州至梁平高速公路KWLTJC标项目预应力波纹管采购进行 优选，现将本次采购有关事项通知如下： 网 一、优选项目概况 （一）优选项目名称： 开州至梁平高速公路KWLTJC标项目预应力波纹管采购 ； 务 （二）项目地点：重庆市梁平区； （三）优选项目概况：本项目位于开州至梁平高速公路KWLTJC标段中K56+320~K96+292.165段，该段落主要经 过万州区余家镇，梁平区复平镇、合兴街道、星桥镇、安商胜镇、仁贤街道、金带街道，桥隧比29.7%，在仁贤街 道设置枢纽互通与G5515张南高速交通转换，最后向南至金带街道设置金带枢纽互通与G42沪蓉高速交通转换， 终点桩号K96+292.165，路线全长39.97km。其中万州境5.98km（K56+320~K62+300）、梁平境33.99km（K62+300- K96+292.156），公路等级四车道高速公路，设计时速100km/h； 道 （四）包件划分： 本次优选设置1个包件 ； （五）中选人数： 1名 ； 管 （六）优选内容（或范围）： 详见预应力波纹管采购限价及报价表 ； 二、竞选人资格要求 1、竞选人必须是在中国华人民共和国境内依法注册、具有一般纳税人资格、具有优选标的物生产经营范围或建筑 材料的生产商、代理商或销售商；税率为13%。 2、具有良好的财务状况。竞选人须具备一定的垫资能力和垫资期限，如竞选人中标，须对支付材料款过程中办 理手续所需的时间给予充分理解，在资金紧张阶段对支付时间给予充分理解。 中 3、本次优选不接受联合体参选，单位负责人为同一人或者存在控股、管理关系的不同单位，不得同时参加竞选， 否则，相关竞选均被否决； 4、竞选人必须为巨能集团集采平台内的合格供应商（状态为：可投标），否则视为未参与竞选（高速集团内部 单位除外）。 5、须在三年内与巨能集团无诉讼纠纷的公司； 6、须在国家企业信用信息公示系统中未被列入严重违法失信企业名单； 三、采购方式：公开优选。 四、采购限价 本项目预应力波纹管采购限价（含税）为人民币：1618996.63元（大写：壹佰陆拾壹万捌仟玖佰玖拾陆元陆角叁 分），具体详见附件《预应力波纹管采购限价表》。本次优选项目采用含税价填报，税率为 13 %的增值税专用 发票。 五、竞选保证金 （一）缴纳金额及方式：人民币：/元（大写：/），在优选文件规定的递交优选文件截止时间前，竞选人通过企 业账户采用现金转账的方式直接划付至采购人指定账户，采购人不接受自然人转账。竞选保证金缴纳凭证须作 为竞选文件的组成部分，未缴纳者将取消竞选资格。竞选人自行考虑汇入时间风险，如同城汇入、异地汇入、 跨行汇入的时间要求。 账户名称：重庆巨能建设集团路桥工程有限公司 开户银行：厦门银行股份有限公司重庆渝北支行 账 号：80508400000406 行 号：313653070076 网 备注：“路桥开州至梁平高速公路KWLTJC标项目预应力波纹管采购竞选保证金” 六、优选文件的获取 务 （一）在优选文件发布之日至竞选截止日期2026年08月28 日10时00分内，供应商登录重庆高速集团物资采购平台 （http://113.250.85.222:8099/merchants/login）获取优选文件。自优选文件发布之日起，视为竞选人知晓本工程优 选的所有过程和全部事宜。 七、竞选文件的提交 商 （一）电子版竞选文件递交：竞选人在竞选截止时间内将签章完善的竞选文件扫描件（PDF格式），上传至重庆 高速集团物资采购平台（http://113.250.85.222:8099/merchants/login），逾期未上传平台自动拒收，竞选人必须保 证平台提交电子版资料与纸质版一致。 道 为方便工作人员统计报价，竞选人同时上传《竞选报价书》电子版（Excel或Word格式）至平台，此条件不作为 废选条件。 管 （二）纸质版竞选文件递交：一正一副，竞选人须在竞选截止时间内将签章完善的竞选文件提交采购人指定地 点，逾期拒收，作无效竞选处理，递交地址：重庆市九龙坡区高龙大道延长段377号7栋（1-3楼）巨能路桥公司。 竞选文件须装入密封袋内，封口处粘贴封条，并在封条的封口处加盖竞选人单位公章（鲜章），“竞选文件” 封袋上写明如下内容： 国 优选项目名称：开州至梁平高速公路KWLTJC标预应力波纹管采购项目。 竞选人名称： 中 在2026年08月28 日10时00分前不得开启（加盖竞选人单位公章鲜章） 八、踏勘 采购人不组织优选预备会，不组织现场考察，建议竞选人自行进行现场踏勘，竞选人可以选择多种运输方式和 多种运输线路，竞选人的综合费用不因运输方式和运输线路的变化而调整，竞选人报价时应将此因素考虑在内。 九、监督部门 重庆巨能建设集团路桥工程有限公司工程部； 监督电话：工程部023-68850703； 十、评选时间、地点 （一）优选单位：重庆巨能建设集团路桥工程有限公司； （二）地点：重庆市九龙坡区高龙大道延长段377号7栋（1-3楼）巨能路桥公司215会议室； （三）联系人及电话：廖薇 15923576859； 信息来源:https://www.chinapipe.net/project/d3078856.html cqdingjiu 2026.08.25 10:30:22 网 务 商 道 管 国 中</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>本项目位于开州至梁平高速公路KWLTJC标段中K56+320~K96+292.165段，该段落主要经过万州区余家镇，梁平区复平镇、合兴街道、星桥镇、安商胜镇、仁贤街道、金带街道，桥隧比29.7%，在仁贤街道设置枢纽互通与G5515张南高速交通转换，最后向南至金带街道设置金带枢纽互通与G42沪蓉高速交通转换，终点桩号K96+292.165，路线全长39.97km。
 https://www.chinapipe.net/project/d3078856.html</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="N12" t="n">
         <v>90</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>四川, 管材招标, 预应力波纹管</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>开州至梁平高速公路, 预应力波纹管采购</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>南岸区2025年市政消防安全隐患整治工程详细管网物探采购公告</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>市政</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>南岸区</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>采用规范要求手段对本次检测区域内详细管网物探。</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>预算金额：240,000.00元</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>管网物探</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>南岸区2025年市政消防安全隐患整治工程详细管网物探采购公告 一、采购方式：公开招标 二、预算金额：240,000.00元 三、项目详情概况 网 包号：1 包内容 最高限价 数量 单位 服务要求 采用规范要求手段对本次检测区域内详细管网物探。 240,000.00元 1 项 详见比选文件。 务 最高限价金额总计：240,000.00元 四、供应商资格要求 1.资质条件、营业执照 商 （1）比选申请人应同时具备以下资质： ①具有建设行政主管部门颁发的工程勘察综合甲级资质。 道 ②具有自然资源主管部门颁发的有效的甲级测绘资质证书（专业类别需包含工程测量）。 竞标人须在竞标文件资格审查部分提供有效的资质证书复印件。 管 （2）具备有效的营业执照。 竞标人须在竞标文件资格审查部分提供有效的营业执照复印件。 国 2.竞标截止日竞标资格情况 竞标人自行承诺（格式见第六章竞标文件格式）不得存在下列情形之一： 中 （1）被人民法院列入失信被执行人名单且在被执行期内； （2）被列入《重庆市工程建设领域招标投标信用管理暂行办法》规定的重点关注名单且记分达到12分且在记分 有效期内； （3）被列入《重庆市工程建设领域招标投标信用管理暂行办法》规定的重庆市工程建设领域招标投标失信惩戒 对象名单（以下称黑名单）且在记分有效期内； （4）被国家、重庆市（含市或任意区县）有关行政部门处以暂停投标资格行政处罚，且在处罚期限内； （5）被重庆市市级有关行业主管部门暂停在渝承揽新业务且在暂停期内。 竞标人须在竞标文件资格审查部分提供承诺。 3.业绩要求 竞标人自2021年1月1日起至投标截止日止（以合同签订时间为准），承接过1个地下管线测量业绩。 竞标人须在投标文件资格审查部分提供类似业绩的合同协议书证明材料。 4.项目负责人的资格要求 4.1拟派项目负责人须是供应商单位人员，具备测量或测绘专业的高级及以上职称并具备注册测绘师资格。 提供：有效的身份证、注册证、职称证及供应商为其缴纳的养老保险证明材料或劳动用工合同。 4.2竞标人须承诺拟派项目负责人履职和未被禁止参与投标。 4.2.1履职承诺要求：承诺拟派项目负责人中标后在本项目履职，签订合同时拟派的项目负责人必须与竞标文件中 的项目负责人一致，并满足办理相关手续的要求。不能按承诺履职的，按合同相关条款处罚并上报行政主管部 门，给招标人造成损失的，竞标人依法承担违约赔偿责任。拟派项目负责人中标后不得随意更换。 4.2.2未被禁止参与投标承诺要求：承诺拟派项目负责人未被重庆市市级有关行业主管部门暂停在渝承揽新业务。 若被暂停在渝承揽新业务但仍参加投标，将被否决投标；已取得中标候选人资格或中标资格的，招标人有权取 消其中标候选人资格或中标资格；给招标人造成损失的，投标人依法承担赔偿责网任或违约责任。 4.2.3未提供上述承诺或承诺内容不符合要求的，由评标委员会作否决投标处理。以上承诺同时作为合同的附件。 投标人须在投标文件资格审查部分提供拟派项目负责人履职和未被禁止参与投标的承诺（承诺格式见第六章投 务 标文件格式）。 6.其他要求 （1）其他主要管理人员： 商 比选申请人自行承诺中选后在签订合同之前，按照比选文件要求配备满足服务要求的服务人员，出具任命文件。 任命文件应当明确项目班子人员的职责、岗位设置、人员配备，并书面通知建设单位。相关人员应持有注册职 业资格证或岗位证书，并提供本单位为其缴纳道的养老保险证明材料或劳动用工合同。 五、获取采购文件的地点、方式、期限及售价 管 获取文件期限:2026年8月24日 至 2026年8月26日 文件购买费:500.00元 国 获取文件地点：行采家（https://www.gec123.com/） 方式或事项： 中 1.竞标人在竞标前可在行采家（https://www.gec123.com/）进行注册。 2.潜在竞标人请在“行采家”网上下载本项目竞争性比选文件以及补遗等开标前公布的所有项目资料，无论竞标 人下载与否，均视为已知晓所有比选内容。 3.凡有意参加比选的竞标人，请于2026年8月24日起-2026年8月26日（9:00-17:00）内完成报名，未在规定时间内完 成报名不得参与竞标。报名方式为： 3.1比选文件售价：500元/份（售后不退），在递交竞标文件时支付比选文件费用，售后不退。 3.2潜在竞标人将《比选文件发售登记表》（加盖竞标人公章）扫描后发送至317562187@qq.com邮箱进行报名。 注：比选申请人须满足以下要求，其竞标文件才被接受： （1）按时报名； （2）按时签到并递交竞标文件。 六、投标信息 投标文件递交开始时间： 2026年8月28日 09:00 投标文件递交结束时间： 2026年8月28日 09:30 投标文件递交地点：南岸区公共资源交易平台（汇南公司）（地址：重庆市南岸区茶园新区广福大道12号行政中 心B区2号楼4楼）。 七、开标信息 网 开标时间： 2026年8月28日 09:30 开标地点：南岸区公共资源交易平台（汇南公司）（地址：重庆市南岸区茶园新区广福大道12号行政中心B区2号 楼4楼）。 务 八、联系方式 1、采购人：重庆市江南城市建设发展（集团）有限公司 商 采购经办人：马老师 采购人电话：023-62820331 道 采购人地址：重庆市南岸区茶园花街二期A栋(长生桥地铁站东) 代理机构：重庆国正工程咨询有限公司 管 代理机构经办人：谢老师 代理机构电话：15696212365 代理机构地址：重庆市国重庆市渝北区渝北区金山路5号加州一号22-1 信息来源:https://www.chinapipe.net/project/d3078801.html cqdingjiu 2026.08.25 09:25:43 中</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>南岸区2025年市政消防安全隐患整治工程详细管网物探采购公告 一、采购方式：公开招标 二、预算金额：240,000.00元 三、项目详情概况 网 包号：1 包内容 最高限价 数量 单位 服务要求 采用规范要求手段对本次检测区域内详细管网物探。 240,000.00元 1 项 详见比选文件。 务 最高限价金额总计：240,000.00元 四、供应商资格要求 1.资质条件、营业执照 商 （1）比选申请人应同时具备以下资质： ①具有建设行政主管部门颁发的工程勘察综合甲级资质。 道 ②具有自然资源主管部门颁发的有效的甲级测绘资质证书（专业类别需包含工程测量）。 竞标人须在竞标文件资格审查部分提供有效的资质证书复印件。 管 （2）具备有效的营业执照。 竞标人须在竞标文件资格审查部分提供有效的营业执照复印件。 国 2.竞标截止日竞标资格情况 竞标人自行承诺（格式见第六章竞标文件格式）不得存在下列情形之一： 中 （1）被人民法院列入失信被执行人名单且在被执行期内； （2）被列入《重庆市工程建设领域招标投标信用管理暂行办法》规定的重点关注名单且记分达到12分且在记分 有效期内； （3）被列入《重庆市工程建设领域招标投标信用管理暂行办法》规定的重庆市工程建设领域招标投标失信惩戒 对象名单（以下称黑名单）且在记分有效期内； （4）被国家、重庆市（含市或任意区县）有关行政部门处以暂停投标资格行政处罚，且在处罚期限内； （5）被重庆市市级有关行业主管部门暂停在渝承揽新业务且在暂停期内。 竞标人须在竞标文件资格审查部分提供承诺。 3.业绩要求 竞标人自2021年1月1日起至投标截止日止（以合同签订时间为准），承接过1个地下管线测量业绩。 竞标人须在投标文件资格审查部分提供类似业绩的合同协议书证明材料。 4.项目负责人的资格要求 4.1拟派项目负责人须是供应商单位人员，具备测量或测绘专业的高级及以上职称并具备注册测绘师资格。 提供：有效的身份证、注册证、职称证及供应商为其缴纳的养老保险证明材料或劳动用工合同。 4.2竞标人须承诺拟派项目负责人履职和未被禁止参与投标。 4.2.1履职承诺要求：承诺拟派项目负责人中标后在本项目履职，签订合同时拟派的项目负责人必须与竞标文件中 的项目负责人一致，并满足办理相关手续的要求。不能按承诺履职的，按合同相关条款处罚并上报行政主管部 门，给招标人造成损失的，竞标人依法承担违约赔偿责任。拟派项目负责人中标后不得随意更换。 4.2.2未被禁止参与投标承诺要求：承诺拟派项目负责人未被重庆市市级有关行业主管部门暂停在渝承揽新业务。 若被暂停在渝承揽新业务但仍参加投标，将被否决投标；已取得中标候选人资格或中标资格的，招标人有权取 消其中标候选人资格或中标资格；给招标人造成损失的，投标人依法承担赔偿责网任或违约责任。 4.2.3未提供上述承诺或承诺内容不符合要求的，由评标委员会作否决投标处理。以上承诺同时作为合同的附件。 投标人须在投标文件资格审查部分提供拟派项目负责人履职和未被禁止参与投标的承诺（承诺格式见第六章投 务 标文件格式）。 6.其他要求 （1）其他主要管理人员： 商 比选申请人自行承诺中选后在签订合同之前，按照比选文件要求配备满足服务要求的服务人员，出具任命文件。 任命文件应当明确项目班子人员的职责、岗位设置、人员配备，并书面通知建设单位。相关人员应持有注册职 业资格证或岗位证书，并提供本单位为其缴纳道的养老保险证明材料或劳动用工合同。 五、获取采购文件的地点、方式、期限及售价 管 获取文件期限:2026年8月24日 至 2026年8月26日 文件购买费:500.00元 国 获取文件地点：行采家（https://www.gec123.com/） 方式或事项： 中 1.竞标人在竞标前可在行采家（https://www.gec123.com/）进行注册。 2.潜在竞标人请在“行采家”网上下载本项目竞争性比选文件以及补遗等开标前公布的所有项目资料，无论竞标 人下载与否，均视为已知晓所有比选内容。 3.凡有意参加比选的竞标人，请于2026年8月24日起-2026年8月26日（9:00-17:00）内完成报名，未在规定时间内完 成报名不得参与竞标。报名方式为： 3.1比选文件售价：500元/份（售后不退），在递交竞标文件时支付比选文件费用，售后不退。 3.2潜在竞标人将《比选文件发售登记表》（加盖竞标人公章）扫描后发送至317562187@qq.com邮箱进行报名。 注：比选申请人须满足以下要求，其竞标文件才被接受： （1）按时报名； （2）按时签到并递交竞标文件。 六、投标信息 投标文件递交开始时间： 2026年8月28日 09:00 投标文件递交结束时间： 2026年8月28日 09:30 投标文件递交地点：南岸区公共资源交易平台（汇南公司）（地址：重庆市南岸区茶园新区广福大道12号行政中 心B区2号楼4楼）。 七、开标信息 网 开标时间： 2026年8月28日 09:30 开标地点：南岸区公共资源交易平台（汇南公司）（地址：重庆市南岸区茶园新区广福大道12号行政中心B区2号 楼4楼）。 务 八、联系方式 1、采购人：重庆市江南城市建设发展（集团）有限公司 商 采购经办人：马老师 采购人电话：023-62820331 道 采购人地址：重庆市南岸区茶园花街二期A栋(长生桥地铁站东) 代理机构：重庆国正工程咨询有限公司 管 代理机构经办人：谢老师 代理机构电话：15696212365 代理机构地址：重庆市国重庆市渝北区渝北区金山路5号加州一号22-1 信息来源:https://www.chinapipe.net/project/d3078801.html cqdingjiu 2026.08.25 10:30:22 中</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>采用规范要求手段对本次检测区域内详细管网物探。
 https://www.chinapipe.net/project/d3078801.html</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="N13" t="n">
         <v>90</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>管网物探, 240,000.00元</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>豪洋水务江津供水2026-2027年度球墨铸铁管及管件采购项目流标公告</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>市政</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>江津区</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>豪洋水务江津供水2026-2027年度球墨铸铁管及管件采购项目于2026年 8月24日10时00分开始在重庆 水务集团电子商务平台进行公开比选。</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>原文未提及</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>球墨铸铁管及管件</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>豪洋水务江津供水2026-2027年度球墨铸铁管及管件采购项目流标公告 豪洋水务江津供水2026-2027年度球墨铸铁管及管件采购项目（项目名称）于2026年 8月24日10时00分开始在重庆 水务集团电子商务平台进行公开比选，本项目现已流标，流标原因：投标截止时间投标人不足三家流标。 特此公告。 网 代理机构：重庆水务集团公用工程咨询有限公司 务 2026年 8月24日 信息来源:https://www.chinapipe.net/project/d3078761.html 商 cqdingjiu 2026.08.25 09:25:43 道 管 国 中</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>豪洋水务江津供水2026-2027年度球墨铸铁管及管件采购项目于2026年 8月24日10时00分开始在重庆 水务集团电子商务平台进行公开比选。
-https://www.chinapipe.net/project/d3078761.html</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>80</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>球墨铸铁管, 管件, 采购项目</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>渡舟—龙桥天然气长输管道投产前耐压试验项目招标公告</t>
+          <t>豪洋水务江津供水2026-2027年度球墨铸铁管及管件采购项目流标公告</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1375,33 +1375,33 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>涪陵区、长寿区</t>
+          <t>江津区</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>本项目是对渡舟至龙桥天然气长输管道进行投产前的耐压试验，包括对管道本体、焊缝、管件及迁改衔接管段的检测，以确保其安全性和可靠性。</t>
+          <t>豪洋水务江津供水2026-2027年度球墨铸铁管及管件采购项目</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>项目资金来自企业自筹，项目出资比例为100%，合同估算金额约为94万元。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>耐压试验服务</t>
+          <t>球墨铸铁管及管件</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>渡舟—龙桥天然气长输管道投产前耐压试验项目招标公告 1. 招标条件 本招标项目 渡舟一龙桥天然气长输管道投产前耐压试验 已由 重庆国隆能源发展有限公司 以 国隆 能源公司2026年第11次总经理办公会会议纪要 批准实施，项目业主为 重庆国隆能源发展有限公司 ，资金 来自 企业自筹，项目出资比例为 100% ，招标人为 重庆国隆能源发展有限公司 。项目已具 备招标条件，现对该项目的试验服务进行招标。 网 2. 项目概况与招标范围 2.1 项目地点： 重庆市涪陵区、长寿区 务 2.2 项目概况与建设规模： 渡舟-龙桥天然气长输管道横跨重庆市长寿区、涪陵区，线路总长36.665km，起于中 石油重庆气矿垫江采输气作业区渡舟中心站，止于涪陵化工配气站。管道主体采用D355.6x10L245NB直缝埋弧焊 钢管，长江穿越段采用无缝钢管；全线采用3PE外防腐层及强制电流阴极保护系统，管道原设计压力4.OMPa，设 计输气量3×108m/a。 商 本管线沿线途经旱地、水田、陡坡、林地、城市绿化带及密集居民区，配套建设有但渡、花桥、长江共3座阀室。 管线于2007年12月开工建设，2009年7月竣工，2009年9月正式投运；2019年12月因下游生产装置停产全线停运。 停运期间有专业运维单位负责，管道均进行了氮气置换保护，管道阴保系统正常运行。 道 2.3 本次招标项目合同估算金额： 约94万元 2.4 招标范围： 根据相关规范，拟采用水作试压介质，分六段对管道进行耐压试验，以便检验长期停运后 管道本体、焊缝、管件及迁改衔接管段的结构强度与密封可靠性，消除管道变形、锈蚀、接口密封不严等潜在 管 安全隐患。试验合格后确认管道恢复输气生产的最大工作压力。（具体以实施方案内容为准）。 2.5 工期要求： 30 日历天 3. 政府采购工程国 3.1 是否属于政府采购工程：否 中 4. 投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件： 同时具备下列资质：（1）建设行政主管部门颁发的石油化工工程 施工总承包贰级及以上资质。（2）有效的《特种设备安装改造维修许可证》许可项目压力管道安装许可子项目 长输管道安装GA2及以上； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 5. 招标文件的获取 5.1 本招标项目采用纸质招投标，投标人在投标前可在重庆市公共资源交易网（涪陵区）下载招标文件、工程 量清单、电子图纸等资料。 5.2 在递交投标文件时完成投标报名，资料费500元，售后不退，未在规定时间内报名的单位投标文件将会被拒 收。 6. 投标文件的递交 6.1 本项目投标截止时间为 2026 年 9 月 1 日 9 时 30 分，投标人应当在投标截止时间前， 按规定到场递交投标文件。 6.2 投标文件的递交时间为 2026 年 9 月 1 日 9 时 00 分-2026年9月 1 日 9 时 30 分。 7. 发布公告的媒介 网 本次招标公告同时在 重庆市公共资源交易网（涪陵区）上发布。 8. 联系方式 务 招 标 人： 重庆国隆能源发展有限公司 招标代理机构： 重庆矩佳工程管理有限公司 地 址：重庆市涪陵区金科铂金国际 地 址：重庆市涪陵区太极大道15号3号楼负一楼 商 联系人： 姚老师 联系人： 刘老 师 电 话： 023-72101141 电 话： 023-72372283 道 2026 年 8 月 24 日 管 信息来源:https://www.chinapipe.net/project/d3078638.html cqdingjiu 2026.08.25 09:25:43 国 中</t>
+          <t>豪洋水务江津供水2026-2027年度球墨铸铁管及管件采购项目流标公告 豪洋水务江津供水2026-2027年度球墨铸铁管及管件采购项目（项目名称）于2026年 8月24日10时00分开始在重庆 水务集团电子商务平台进行公开比选，本项目现已流标，流标原因：投标截止时间投标人不足三家流标。 特此公告。 网 代理机构：重庆水务集团公用工程咨询有限公司 务 2026年 8月24日 信息来源:https://www.chinapipe.net/project/d3078761.html 商 cqdingjiu 2026.08.25 10:30:23 道 管 国 中</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>本项目是对渡舟至龙桥天然气长输管道进行投产前的耐压试验，包括对管道本体、焊缝、管件及迁改衔接管段的检测，以确保其安全性和可靠性。
-https://www.chinapipe.net/project/d3078638.html</t>
+          <t>豪洋水务江津供水2026-2027年度球墨铸铁管及管件采购项目
+https://www.chinapipe.net/project/d3078761.html</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1409,14 +1409,14 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>天然气长输管道, 耐压试验, 企业自筹, 94万元</t>
+          <t>豪洋水务, 江津供水, 2026-2027年度, 球墨铸铁管, 管件采购项目</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>中建四局(四川)建设有限公司总部重庆交通大学双福校区三期建设项目(图情中心组团)工程总承包(EPC)项目雨水管网工程采购公告</t>
+          <t>渡舟—龙桥天然气长输管道投产前耐压试验项目招标公告</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1447,188 +1447,188 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
+          <t>涪陵区、长寿区</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>渡舟-龙桥天然气长输管道横跨重庆市长寿区、涪陵区，线路总长36.665km，起于中石油重庆气矿垫江采输气作业区渡舟中心站，止于涪陵化工配气站。管道主体采用D355.6x10L245NB直缝埋弧焊钢管，长江穿越段采用无缝钢管；全线采用3PE外防腐层及强制电流阴极保护系统，管道原设计压力4.0MPa，设计输气量3×10^8m³/a。</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>约94万元</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>耐压试验服务</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>渡舟—龙桥天然气长输管道投产前耐压试验项目招标公告 1. 招标条件 本招标项目 渡舟一龙桥天然气长输管道投产前耐压试验 已由 重庆国隆能源发展有限公司 以 国隆 能源公司2026年第11次总经理办公会会议纪要 批准实施，项目业主为 重庆国隆能源发展有限公司 ，资金 来自 企业自筹，项目出资比例为 100% ，招标人为 重庆国隆能源发展有限公司 。项目已具 备招标条件，现对该项目的试验服务进行招标。 网 2. 项目概况与招标范围 2.1 项目地点： 重庆市涪陵区、长寿区 务 2.2 项目概况与建设规模： 渡舟-龙桥天然气长输管道横跨重庆市长寿区、涪陵区，线路总长36.665km，起于中 石油重庆气矿垫江采输气作业区渡舟中心站，止于涪陵化工配气站。管道主体采用D355.6x10L245NB直缝埋弧焊 钢管，长江穿越段采用无缝钢管；全线采用3PE外防腐层及强制电流阴极保护系统，管道原设计压力4.OMPa，设 计输气量3×108m/a。 商 本管线沿线途经旱地、水田、陡坡、林地、城市绿化带及密集居民区，配套建设有但渡、花桥、长江共3座阀室。 管线于2007年12月开工建设，2009年7月竣工，2009年9月正式投运；2019年12月因下游生产装置停产全线停运。 停运期间有专业运维单位负责，管道均进行了氮气置换保护，管道阴保系统正常运行。 道 2.3 本次招标项目合同估算金额： 约94万元 2.4 招标范围： 根据相关规范，拟采用水作试压介质，分六段对管道进行耐压试验，以便检验长期停运后 管道本体、焊缝、管件及迁改衔接管段的结构强度与密封可靠性，消除管道变形、锈蚀、接口密封不严等潜在 管 安全隐患。试验合格后确认管道恢复输气生产的最大工作压力。（具体以实施方案内容为准）。 2.5 工期要求： 30 日历天 3. 政府采购工程国 3.1 是否属于政府采购工程：否 中 4. 投标人资格要求 4.1 本次招标要求投标人须具备以下条件： 4.1.1 本次招标要求投标人具备的资质条件： 同时具备下列资质：（1）建设行政主管部门颁发的石油化工工程 施工总承包贰级及以上资质。（2）有效的《特种设备安装改造维修许可证》许可项目压力管道安装许可子项目 长输管道安装GA2及以上； 4.1.2 投标人还应在人员、业绩、设备、资金等方面具有相应的施工能力，详见招标文件第二章投标人须知前附 表第1.4.1项内容。 4.2 本次招标不接受联合体投标。 5. 招标文件的获取 5.1 本招标项目采用纸质招投标，投标人在投标前可在重庆市公共资源交易网（涪陵区）下载招标文件、工程 量清单、电子图纸等资料。 5.2 在递交投标文件时完成投标报名，资料费500元，售后不退，未在规定时间内报名的单位投标文件将会被拒 收。 6. 投标文件的递交 6.1 本项目投标截止时间为 2026 年 9 月 1 日 9 时 30 分，投标人应当在投标截止时间前， 按规定到场递交投标文件。 6.2 投标文件的递交时间为 2026 年 9 月 1 日 9 时 00 分-2026年9月 1 日 9 时 30 分。 7. 发布公告的媒介 网 本次招标公告同时在 重庆市公共资源交易网（涪陵区）上发布。 8. 联系方式 务 招 标 人： 重庆国隆能源发展有限公司 招标代理机构： 重庆矩佳工程管理有限公司 地 址：重庆市涪陵区金科铂金国际 地 址：重庆市涪陵区太极大道15号3号楼负一楼 商 联系人： 姚老师 联系人： 刘老 师 电 话： 023-72101141 电 话： 023-72372283 道 2026 年 8 月 24 日 管 信息来源:https://www.chinapipe.net/project/d3078638.html cqdingjiu 2026.08.25 10:30:23 国 中</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>渡舟-龙桥天然气长输管道横跨重庆市长寿区、涪陵区，线路总长36.665km，起于中石油重庆气矿垫江采输气作业区渡舟中心站，止于涪陵化工配气站。管道主体采用D355.6x10L245NB直缝埋弧焊钢管，长江穿越段采用无缝钢管；全线采用3PE外防腐层及强制电流阴极保护系统，管道原设计压力4.0MPa，设计输气量3×10^8m³/a。
+https://www.chinapipe.net/project/d3078638.html</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>80</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>天然气长输管道, 耐压试验</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>中建四局(四川)建设有限公司总部重庆交通大学双福校区三期建设项目(图情中心组团)工程总承包(EPC)项目雨水管网工程采购公告</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>市政</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>江津区</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>包括雨水检查井、钢筋砼承插式雨水管道铺设、中粗砂回填等内容</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>项目详细内容无法识别</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>雨水管网工程</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>中建四局(四川)建设有限公司总部重庆交通大学双福校区三期建设项目(图情中心组团)工程总承包(EPC)项目雨 水管网工程采购公告 一、采购概况 1.采购名称：【重庆交通大学双福校区三期建设项目（图情中心组团）工程总承包（EPC）项目雨水管网工程】。 2.工程概况：【1.项目概况：本项目规划用地82876.94㎡，总建筑面积约108691.83㎡，其中9#行政楼建筑层 数6F/-2F，建筑高度为31.5m，10#图书馆建筑层数8F/-2F，建筑高度为57.1m，11#研究生楼建筑层数6F/-1F，建筑 高度为31.5m，12#地下车库建筑层数-2F，建筑高度为-8.7m。2.结构类型：所有楼栋主要结构形式为框架结构3.工 网 程地点: 重庆市江津区福星大道1号】。 3.标段划分：【本工程仅一个标段】。 4.采购内容：【重庆交通大学双福校区三期建设项目（图情中心组团务）工程总承包（EPC）项目雨水管网工程， 包括雨水检查井、钢筋砼承插式雨水管道铺设、中粗砂回填等内容，详见工程量清单】。 5.质量要求：【（1）质量标准：（1）工程施工的质量要求：工程质量应符合强制性质量标准，符合国家和重庆 市现行有关施工质量验收规范要求，并达到合格标准。商 （2）质量创优目标：/ 】。 6.工期要求：【暂定开工日期：2026年9月15日，竣工日期：2027年10月30日，总工期410日历天】。 道 7.文明要求：【（1）安全控制目标：杜绝发生重伤及以上生产安全责任事故，安全轻伤事故率小于1‰；不发生 社会影响较大的其他事故或险肇事件。 （2）安全生产、文明施工达到《管建筑施工安全检查标准（JGJ59-2011）》合格要求。 （3）杜绝机械设备事故、火灾事故和公共安全事故、防止职业病发生；贯彻落实《职业病防治法》、《职业健 康监护技术规范》等国家法律法规要求，关爱员工健康，不发生职业健康损誉事件。 国 （4）创优目标：市级建筑施工安全文明工地】。 8.付款条件：【 中 （1）月进度付款，按照甲方累计确认的已完合格工程量工程价款的【75】%，挂账后于60天内支付应付进度款； （2）乙方完成承包范围内全部工作内容并经甲方经验收合格，挂账后于60天内付款至已完成合格工程量工程价 款的【80】%。 （3）乙方完成承包范围内的全部工作内容并经验收合格及有关部门备案，且双方完成最终结算后，于60天内支 付至合格工程结算总价的【97】%，剩余【3】%作为工程质量保修金。养护期2年，扣除已发生的维护费用后， 甲方无息退还剩余保修金。 （4）本工程采用【银行转账、供应链（一年期以内）、票据（一年期以内）、以物抵债】方式向乙方支付货款。 如涉及贴息费用，贴息费由【甲】方承担。如由甲方承担贴息费，乙方须提供银行出具的贴息相关证明材料， 贴息费甲乙双方通过结算方式办理，乙方根据结算金额开具发票，贴息所产生的增值税税金由【乙方】承担， 甲方按合同中约定的工程进度款支付条件进行支付，贴息费不再产生逾期利息。】。 9.拟选定成交单位数：【1家】。 二、响应人资格 1.响应人报名前需通过“云筑网”（网址：https://jicai.yzw.cn/home）认证并进入中建系统合格分供商资源库，经 采购人资格审查合格后方可参与报价。 2.响应人须具备以下基本条件： （1）具有公司制独立法人主体资格，经营范围有效，时间有效（提供营业执照、法人身份证复印件、授权委托 书、被委托人身份证复印件等证明资料，在本公司本级资源库内分供商可不提供）； （2）办公场所、组织架构：具有固定的办公场所，公司组织架构合理，人员配置充足（提供企业简介、固定办 公地点影像资料、公司组织架构证明等证明资料，在本公司本级资源库内分供商可不提供）； （3）纳税人资格：提供纳税人证明或税务事项通知等证明资料（在本公司本级资源库内分供商可不提供）； （4）诚信经营：经核查政府平台近两年内无、质量事故通报，云筑网无不良记录，不得存在挂靠，必须为法人 直营单位（提供政府平台（中国裁判文书网、中国执行信息公开网、国家企业信用信息公示系统）查询记录截 图、法人直营承诺书等资料证明，在本公司本级资源库内分供商可不提供）； 网 （5）合法经营：遵守国家法律、依法经营、合约期间无违法犯罪记录、无因管理不善、履约不力导致的案件； （6）历史业绩：根据采购物提供对应业绩资料（提供相关合同关键页等资料证明，在本公司本级资源库内分供 商可不提供） 务 （7）资质：本工程无专业承包资质要求】。 3.响应资格审核不通过的情形： 商 1)在云筑网被本上级单位列为“不良行为分供商”或“禁用分供商”； 2)涉嫌围采串采的，如:法人身份证号重复、法人手机号重复、联系人重复、联系人手机号重复、IP地址重 复、MAC地址重复、邮箱地址重复、工商关联道的不同单位; 3)在严重失信或被执行企业名单； 4)分供商(法人)处于被限制高消费状态、司法拍卖影响企业正常运行、破产清算影响企业正常运营； 管 5)“换马甲”的中建股份、中建四局原禁用单位； 6）响应人未上传采购公告要求之资料，或上传资料不符合要求； 国 4.本次采购【不接受】联合体响应。 5.如响应单位提供虚假资料的，任何时候一经发现，取消其响应资格。 中 三、报名响应 1.响应时间：【以“云筑网”平台显示时间为准】，逾期不再接受响应。 2.响应方式：通过“云筑网”进行网上报名，不接受其他方式响应。 3.已在“云筑网”完成分供商注册的响应人，可直接在“云筑网”签收采购公告后响应。 4.响应担保：本次响应担保为【/】元，响应人应于报价截止日24小时前缴纳。 四、资格审查资料清单及格式 响应人报名时需按资格审查要求上传至云筑网，具体要求：按照顺序签字盖章扫描成一个PDF文件以附件形式上 传云筑网，统一命名为：响应报名文件-****单位，不得上传多个附件或压缩文件，不按要求上传资料的资格审 查不通过。 （一）资格审查资料清单（本级库内单位可不提供）： 1)《分供商准入资格预审表》（见附件1）； 2)法定代表人身份证明(见附件2)； 3)法定代表人授权书(见附件3)； 4)被委托人身份证明(见附件4)； 5)企业证明资料(见附件5)； 6)纳税证明或税务事项通知(见附件6)； 7)诚信经营证明(见附件7)； 8)现场拟派人员证书扫描件(见附件8)； 9)近3年施工类似业绩资料（见附件9）； 网 10)响应单位可提供的其他证明企业情况的资料。 五、发放采购文件 务 1.采购人通过“云筑网”对资格审查合格的响应人发放采购文件。 2.发放时间：【以“云筑网”平台显示时间为准 】。 商 3.联系人：【王青松】，联系方式：【18323827265】，联系地址：【四川省成都市双流区金为创新中心19楼】。 4.其他未尽事宜详见采购文件。 道 六、投诉通道 响应人如遇账款、合同、结算、廉洁、安全、环保、禁用等相关问题，可通过云筑网分供商投诉平台 （https://ts.yzw.cn/complaint）提交投诉材料，平台将按规定予以受理和处理。 管 采购人： 中国建筑第四工程局有限公司 国 信息来源:https://www.chinapipe.net/project/d3078437.html cqdingjiu 2026.08.25 09:25:43 中</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>中建四局(四川)建设有限公司总部重庆交通大学双福校区三期建设项目(图情中心组团)工程总承包(EPC)项目雨 水管网工程采购公告 一、采购概况 1.采购名称：【重庆交通大学双福校区三期建设项目（图情中心组团）工程总承包（EPC）项目雨水管网工程】。 2.工程概况：【1.项目概况：本项目规划用地82876.94㎡，总建筑面积约108691.83㎡，其中9#行政楼建筑层 数6F/-2F，建筑高度为31.5m，10#图书馆建筑层数8F/-2F，建筑高度为57.1m，11#研究生楼建筑层数6F/-1F，建筑 高度为31.5m，12#地下车库建筑层数-2F，建筑高度为-8.7m。2.结构类型：所有楼栋主要结构形式为框架结构3.工 网 程地点: 重庆市江津区福星大道1号】。 3.标段划分：【本工程仅一个标段】。 4.采购内容：【重庆交通大学双福校区三期建设项目（图情中心组团务）工程总承包（EPC）项目雨水管网工程， 包括雨水检查井、钢筋砼承插式雨水管道铺设、中粗砂回填等内容，详见工程量清单】。 5.质量要求：【（1）质量标准：（1）工程施工的质量要求：工程质量应符合强制性质量标准，符合国家和重庆 市现行有关施工质量验收规范要求，并达到合格标准。商 （2）质量创优目标：/ 】。 6.工期要求：【暂定开工日期：2026年9月15日，竣工日期：2027年10月30日，总工期410日历天】。 道 7.文明要求：【（1）安全控制目标：杜绝发生重伤及以上生产安全责任事故，安全轻伤事故率小于1‰；不发生 社会影响较大的其他事故或险肇事件。 （2）安全生产、文明施工达到《管建筑施工安全检查标准（JGJ59-2011）》合格要求。 （3）杜绝机械设备事故、火灾事故和公共安全事故、防止职业病发生；贯彻落实《职业病防治法》、《职业健 康监护技术规范》等国家法律法规要求，关爱员工健康，不发生职业健康损誉事件。 国 （4）创优目标：市级建筑施工安全文明工地】。 8.付款条件：【 中 （1）月进度付款，按照甲方累计确认的已完合格工程量工程价款的【75】%，挂账后于60天内支付应付进度款； （2）乙方完成承包范围内全部工作内容并经甲方经验收合格，挂账后于60天内付款至已完成合格工程量工程价 款的【80】%。 （3）乙方完成承包范围内的全部工作内容并经验收合格及有关部门备案，且双方完成最终结算后，于60天内支 付至合格工程结算总价的【97】%，剩余【3】%作为工程质量保修金。养护期2年，扣除已发生的维护费用后， 甲方无息退还剩余保修金。 （4）本工程采用【银行转账、供应链（一年期以内）、票据（一年期以内）、以物抵债】方式向乙方支付货款。 如涉及贴息费用，贴息费由【甲】方承担。如由甲方承担贴息费，乙方须提供银行出具的贴息相关证明材料， 贴息费甲乙双方通过结算方式办理，乙方根据结算金额开具发票，贴息所产生的增值税税金由【乙方】承担， 甲方按合同中约定的工程进度款支付条件进行支付，贴息费不再产生逾期利息。】。 9.拟选定成交单位数：【1家】。 二、响应人资格 1.响应人报名前需通过“云筑网”（网址：https://jicai.yzw.cn/home）认证并进入中建系统合格分供商资源库，经 采购人资格审查合格后方可参与报价。 2.响应人须具备以下基本条件： （1）具有公司制独立法人主体资格，经营范围有效，时间有效（提供营业执照、法人身份证复印件、授权委托 书、被委托人身份证复印件等证明资料，在本公司本级资源库内分供商可不提供）； （2）办公场所、组织架构：具有固定的办公场所，公司组织架构合理，人员配置充足（提供企业简介、固定办 公地点影像资料、公司组织架构证明等证明资料，在本公司本级资源库内分供商可不提供）； （3）纳税人资格：提供纳税人证明或税务事项通知等证明资料（在本公司本级资源库内分供商可不提供）； （4）诚信经营：经核查政府平台近两年内无、质量事故通报，云筑网无不良记录，不得存在挂靠，必须为法人 直营单位（提供政府平台（中国裁判文书网、中国执行信息公开网、国家企业信用信息公示系统）查询记录截 图、法人直营承诺书等资料证明，在本公司本级资源库内分供商可不提供）； 网 （5）合法经营：遵守国家法律、依法经营、合约期间无违法犯罪记录、无因管理不善、履约不力导致的案件； （6）历史业绩：根据采购物提供对应业绩资料（提供相关合同关键页等资料证明，在本公司本级资源库内分供 商可不提供） 务 （7）资质：本工程无专业承包资质要求】。 3.响应资格审核不通过的情形： 商 1)在云筑网被本上级单位列为“不良行为分供商”或“禁用分供商”； 2)涉嫌围采串采的，如:法人身份证号重复、法人手机号重复、联系人重复、联系人手机号重复、IP地址重 复、MAC地址重复、邮箱地址重复、工商关联道的不同单位; 3)在严重失信或被执行企业名单； 4)分供商(法人)处于被限制高消费状态、司法拍卖影响企业正常运行、破产清算影响企业正常运营； 管 5)“换马甲”的中建股份、中建四局原禁用单位； 6）响应人未上传采购公告要求之资料，或上传资料不符合要求； 国 4.本次采购【不接受】联合体响应。 5.如响应单位提供虚假资料的，任何时候一经发现，取消其响应资格。 中 三、报名响应 1.响应时间：【以“云筑网”平台显示时间为准】，逾期不再接受响应。 2.响应方式：通过“云筑网”进行网上报名，不接受其他方式响应。 3.已在“云筑网”完成分供商注册的响应人，可直接在“云筑网”签收采购公告后响应。 4.响应担保：本次响应担保为【/】元，响应人应于报价截止日24小时前缴纳。 四、资格审查资料清单及格式 响应人报名时需按资格审查要求上传至云筑网，具体要求：按照顺序签字盖章扫描成一个PDF文件以附件形式上 传云筑网，统一命名为：响应报名文件-****单位，不得上传多个附件或压缩文件，不按要求上传资料的资格审 查不通过。 （一）资格审查资料清单（本级库内单位可不提供）： 1)《分供商准入资格预审表》（见附件1）； 2)法定代表人身份证明(见附件2)； 3)法定代表人授权书(见附件3)； 4)被委托人身份证明(见附件4)； 5)企业证明资料(见附件5)； 6)纳税证明或税务事项通知(见附件6)； 7)诚信经营证明(见附件7)； 8)现场拟派人员证书扫描件(见附件8)； 9)近3年施工类似业绩资料（见附件9）； 网 10)响应单位可提供的其他证明企业情况的资料。 五、发放采购文件 务 1.采购人通过“云筑网”对资格审查合格的响应人发放采购文件。 2.发放时间：【以“云筑网”平台显示时间为准 】。 商 3.联系人：【王青松】，联系方式：【18323827265】，联系地址：【四川省成都市双流区金为创新中心19楼】。 4.其他未尽事宜详见采购文件。 道 六、投诉通道 响应人如遇账款、合同、结算、廉洁、安全、环保、禁用等相关问题，可通过云筑网分供商投诉平台 （https://ts.yzw.cn/complaint）提交投诉材料，平台将按规定予以受理和处理。 管 采购人： 中国建筑第四工程局有限公司 国 信息来源:https://www.chinapipe.net/project/d3078437.html cqdingjiu 2026.08.25 10:30:23 中</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>包括雨水检查井、钢筋砼承插式雨水管道铺设、中粗砂回填等内容
 https://www.chinapipe.net/project/d3078437.html</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>70</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>四川, 管材, 招标, 商机</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="N16" t="n">
+        <v>90</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>雨水管网工程, 排水钢管</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>五局三西南(重庆)鑫旭达项目室外管材及预制构件采购公告</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>房建</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>重庆市</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>中建五局第三建设有限公司鑫旭达西南地区生产基地项目室外管材及预制构件采购</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>本次采购估价：28万元</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>室外管材及预制构件</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>五局三西南(重庆)鑫旭达项目室外管材及预制构件采购公告 中建五局第三建设有限公司重庆城市公司 五局三西南（重庆）鑫旭达项目室外管材及预制构件采购 五局三西南（重庆）鑫旭达西南地区生 产基地项目室外管材及预制构件采购公告 网 采购编号:cscecXXX 务 商 道 采购人：中建五局第三建设有限公司 采购日期： 2026 年 08 月 管 鑫旭达西南地区生产基地项目室外管材及预制构件采购公告 国 中建五局第三建设有限公司鑫旭达西南地区生产基地项目室外管材及检查井采购，现面向社会公开采购，诚邀 符合资格条件、能提供优质服务的国内专业公司参加采购合作事宜。 一、基本情况 中 1、采购组织单位：鑫旭达西南地区生产基地项目 2、本次采购内容：室外管材及预制构件 3、工程地点：重庆市涪陵高新区聚业大道北侧 4、合同履约期限：2026年08月-2027年12月 5、本次采购预估数量：管材4802米；预制构件247个 6、本次采购估价：28万元 7、本次采购报价方式：价税分离单价报价 8、计划进场日期：2026年08月28日 9、响应担保：0.28万元（采购完成后若无违规、不诚信操作可立即退还） 10、质量要求：必须符合相应国家标准，若行业标准或地方标准高于国家标准的，执行行业标准或地方标准。材 料尺寸、外管、环刚度、强度以及用料等均国家符合质量验收标准。 11、品牌要求：管材：顾地、中财、利财、联塑、伟星等同等级品牌。 二、付款方式： 1、支付方式：本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保理、商业承兑汇票、国内信用证、 应收账款电子凭证及其他】常规支付方式的付款方式。 2、过程付款方式：甲方在次月的30日支付上月月度结算货款的【70】%，双方办理完毕最终结算后【60】个日 历天内付至总结算货款（且不超含税合同价款）的【97】%，预留质保金【3】%在保修期满且乙方已履行完所 有的保修责任后付清。甲乙双方协商一致同意本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保 理、商业承兑汇票、国内信用证、应收账款电子凭证及其他】常规支付方式的付款方式，付款过程中产生的贴 息费用及手续费由【乙方】承担，每次付款前乙方应提供结算值【100%】的发票，否则甲方可拒绝付款。 网 三、报名条件： 1、报名参与单位必须是独立的法人单位，具备一般纳税人资格供方优先。报名参与单位在近2年内不曾在任何合 同中违约或因报名参与单位的原因而使任何合同被解除、未发生因自身原因造成的诉讼情况。报名参与单位应 务 具备较强的资源组织能力、供货能力、抗风险能力、售后服务能力和资金实力。响应方应随时接受采购方对响 应方设备性能、合格证、保险资料等进行检查。 2、未被列入失信被执行人、重大税收违法案件当事人名单、政府采购严重违法失信行为记录名单； 商 3、未处于被责令停业、响应资格被取消或者财产被接管、冻结和破产状态； 4、不在中建局及公司、分公司不合格名录/黑名单内； 道 5、单位负责人为同一人或者存在直接控股、管理关系的不同响应人，不得同时参加本工程响应； 6、符合《中华人民共和国采购法》、《政府采购法》等法律法规的要求； 管 7、响应单位报名阶段提供与采购标的物规格型号相符的以下证书，可认定为本次采购的绿色建材分供商：绿色 建材产品一星、二星、三星认证证书；中建绿色建材企业认证证书；绿色产品认证证书；中国环境保护标志证 书；中国节能标志证书；中国森林认证证书；入选工信部和省级绿色工厂，享受绿色建材分供商优惠条件。绿 色建材分供商需将认证证书以电子版或扫描件的形式与报名文件一同上传至云筑网。 国 四、响应报名 1、网络报名地点：响应人登录（http://www.yzw.cn），进入平台，填报企业相关资料，进行网络注册认证，通知 我司进行资审通过后，进行网上报名。 中 2、报名所需提交的资料包括： （1）营业执照，建筑业企业资质证书、安全生产标准化证书复印件(正副本均可)、法定代表人授权书证明原件。 （2）参与单位近两年的工作业绩（主要为所招地区业绩）。 （3）参与单位资信等级证书，质量、环境、职业健康安全管理体系认证书原件。 （4）参与单位可提供的其他证明企业情况的资料。 3、采购文件的获取：经资格审查入围的响应人，将对其发放电子版采购文件，登录中建采购网络交易采购平台 （http://www.yzw.cn），网上获取采购文件电子版，并依据文件要求于平台上响应截止日前进行网上响应。 4、严禁报名IP地址重复，IP地址重复者资审均不通过。 五、对本次采购提出询问，请按以下方式联系： 联系人：杨飞 联系电话：16623122372 中建五局第三建设有限公司 2026年08月20日 附件一： 法定代表人授权书 网 致：中建五局第三建设有限公司 务 本授权书声明：位于 （填公司地址） 的 （填公司名称） 的 （填法人 姓名）代表本公司授权 （填被授权人姓名）为本公司的唯一合法代理人，代表本公司参加中建五局第三建设 有限公司 XX项目XX采购采购活动，并在整个采购活动中，以本公司名义全权处理包括递交企业和产品响应资 质材料，确认响应相关信息，响应产品报价、议价，交纳商相关费用，签订采购合同，执行和完成采购周期内的 售后服务等一切与之有关的事务，并保证所提供的资质证明材料真实、合法、完整、有效。 道 本授权书于： 年 月 日签字生效，特此声明。 授权期限为： 年 月 日起至合同终止。授权期限内无特殊情况不变更合法代理人（被授权 人）。 管 法定代表人(签字) 被授权人(签字) 国 授权单位名称（盖章） 联系电话 中 授权人身份证正面 授权人身份证背面 被授权人身份证正面 被授权人身份证背面 点击查看内容 信息来源:https://www.chinapipe.net/project/d3078389.html cqdingjiu 2026.08.25 09:25:44</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>五局三西南(重庆)鑫旭达项目室外管材及预制构件采购公告 中建五局第三建设有限公司重庆城市公司 五局三西南（重庆）鑫旭达项目室外管材及预制构件采购 五局三西南（重庆）鑫旭达西南地区生 产基地项目室外管材及预制构件采购公告 网 采购编号:cscecXXX 务 商 道 采购人：中建五局第三建设有限公司 采购日期： 2026 年 08 月 管 鑫旭达西南地区生产基地项目室外管材及预制构件采购公告 国 中建五局第三建设有限公司鑫旭达西南地区生产基地项目室外管材及检查井采购，现面向社会公开采购，诚邀 符合资格条件、能提供优质服务的国内专业公司参加采购合作事宜。 一、基本情况 中 1、采购组织单位：鑫旭达西南地区生产基地项目 2、本次采购内容：室外管材及预制构件 3、工程地点：重庆市涪陵高新区聚业大道北侧 4、合同履约期限：2026年08月-2027年12月 5、本次采购预估数量：管材4802米；预制构件247个 6、本次采购估价：28万元 7、本次采购报价方式：价税分离单价报价 8、计划进场日期：2026年08月28日 9、响应担保：0.28万元（采购完成后若无违规、不诚信操作可立即退还） 10、质量要求：必须符合相应国家标准，若行业标准或地方标准高于国家标准的，执行行业标准或地方标准。材 料尺寸、外管、环刚度、强度以及用料等均国家符合质量验收标准。 11、品牌要求：管材：顾地、中财、利财、联塑、伟星等同等级品牌。 二、付款方式： 1、支付方式：本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保理、商业承兑汇票、国内信用证、 应收账款电子凭证及其他】常规支付方式的付款方式。 2、过程付款方式：甲方在次月的30日支付上月月度结算货款的【70】%，双方办理完毕最终结算后【60】个日 历天内付至总结算货款（且不超含税合同价款）的【97】%，预留质保金【3】%在保修期满且乙方已履行完所 有的保修责任后付清。甲乙双方协商一致同意本合同采用【银行转账支票、网银转账、银行承兑汇票、银行保 理、商业承兑汇票、国内信用证、应收账款电子凭证及其他】常规支付方式的付款方式，付款过程中产生的贴 息费用及手续费由【乙方】承担，每次付款前乙方应提供结算值【100%】的发票，否则甲方可拒绝付款。 网 三、报名条件： 1、报名参与单位必须是独立的法人单位，具备一般纳税人资格供方优先。报名参与单位在近2年内不曾在任何合 同中违约或因报名参与单位的原因而使任何合同被解除、未发生因自身原因造成的诉讼情况。报名参与单位应 务 具备较强的资源组织能力、供货能力、抗风险能力、售后服务能力和资金实力。响应方应随时接受采购方对响 应方设备性能、合格证、保险资料等进行检查。 2、未被列入失信被执行人、重大税收违法案件当事人名单、政府采购严重违法失信行为记录名单； 商 3、未处于被责令停业、响应资格被取消或者财产被接管、冻结和破产状态； 4、不在中建局及公司、分公司不合格名录/黑名单内； 道 5、单位负责人为同一人或者存在直接控股、管理关系的不同响应人，不得同时参加本工程响应； 6、符合《中华人民共和国采购法》、《政府采购法》等法律法规的要求； 管 7、响应单位报名阶段提供与采购标的物规格型号相符的以下证书，可认定为本次采购的绿色建材分供商：绿色 建材产品一星、二星、三星认证证书；中建绿色建材企业认证证书；绿色产品认证证书；中国环境保护标志证 书；中国节能标志证书；中国森林认证证书；入选工信部和省级绿色工厂，享受绿色建材分供商优惠条件。绿 色建材分供商需将认证证书以电子版或扫描件的形式与报名文件一同上传至云筑网。 国 四、响应报名 1、网络报名地点：响应人登录（http://www.yzw.cn），进入平台，填报企业相关资料，进行网络注册认证，通知 我司进行资审通过后，进行网上报名。 中 2、报名所需提交的资料包括： （1）营业执照，建筑业企业资质证书、安全生产标准化证书复印件(正副本均可)、法定代表人授权书证明原件。 （2）参与单位近两年的工作业绩（主要为所招地区业绩）。 （3）参与单位资信等级证书，质量、环境、职业健康安全管理体系认证书原件。 （4）参与单位可提供的其他证明企业情况的资料。 3、采购文件的获取：经资格审查入围的响应人，将对其发放电子版采购文件，登录中建采购网络交易采购平台 （http://www.yzw.cn），网上获取采购文件电子版，并依据文件要求于平台上响应截止日前进行网上响应。 4、严禁报名IP地址重复，IP地址重复者资审均不通过。 五、对本次采购提出询问，请按以下方式联系： 联系人：杨飞 联系电话：16623122372 中建五局第三建设有限公司 2026年08月20日 附件一： 法定代表人授权书 网 致：中建五局第三建设有限公司 务 本授权书声明：位于 （填公司地址） 的 （填公司名称） 的 （填法人 姓名）代表本公司授权 （填被授权人姓名）为本公司的唯一合法代理人，代表本公司参加中建五局第三建设 有限公司 XX项目XX采购采购活动，并在整个采购活动中，以本公司名义全权处理包括递交企业和产品响应资 质材料，确认响应相关信息，响应产品报价、议价，交纳商相关费用，签订采购合同，执行和完成采购周期内的 售后服务等一切与之有关的事务，并保证所提供的资质证明材料真实、合法、完整、有效。 道 本授权书于： 年 月 日签字生效，特此声明。 授权期限为： 年 月 日起至合同终止。授权期限内无特殊情况不变更合法代理人（被授权 人）。 管 法定代表人(签字) 被授权人(签字) 国 授权单位名称（盖章） 联系电话 中 授权人身份证正面 授权人身份证背面 被授权人身份证正面 被授权人身份证背面 点击查看内容 信息来源:https://www.chinapipe.net/project/d3078389.html cqdingjiu 2026.08.25 10:30:23</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>中建五局第三建设有限公司鑫旭达西南地区生产基地项目室外管材及预制构件采购
 https://www.chinapipe.net/project/d3078389.html</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="N17" t="n">
         <v>80</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>管材, 预制构件, 采购</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>秀山县2026年龙池镇、雅江镇基地信息化建设项目-第二次询比公告</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>房建</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>秀山土家族苗族自治县</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>项目服务内容自动农业气象监测系统、土壤墒情监测系统、智能虫情测报系统、杀虫控制系统、水肥一体化、宣传片拍摄等。</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>采购金额：566037.74元（不含税）。</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>信息化建设类</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>秀山县2026年龙池镇、雅江镇基地信息化建设项目-第二次询比公告 询比公告-秀山县2026年龙池镇、雅江镇基地信息化建设项目-第二次 2026-08-22 ZB_ZHAOBIAOGONGGAO_START 本询比项目为秀山县2026年龙池镇、雅江镇基地信息化建设项目-第二次 （标段编号：CQBBFA2026080700101），采购人为中国电信股份有限公司秀山分公司，采购代理机构为鼎信项目 管理咨询有限公司。项目资金已落实。具备采购条件，现进行公开询比，特邀请有意向的且具有提供标的物能 力的潜在供应商（以下简称供应商）参加询比响应。 网 1.项目概况与采购内容 1.1项目概况：（1）项目地点：重庆市秀山县。 务 （2）采购金额：566037.74元（不含税）。 （3）工作范围：项目服务内容自动农业气象监测系统、土壤墒情监测系统、智能虫情测报系统、杀虫控制系统、 水肥一体化、宣传片拍摄等，具体以技术规范书为准。 商 （4）项目进度要求：整个工期90天。 1.2采购内容及标包划分情况： 1.2.1 道 序号 标包名称 产品名称 规格型号 数量 交货地点 交货期 管 秀山县2026年龙池镇、雅江镇基地信息化建 1 集成服务 - - 重庆市秀山县 整个工期90天 设项目 本项目不划分标包。国 本项目将按照最新的《中国电信供应商不良行为管理规则》执行供应商不良行为处理结果，请重点关注 处理结果适用的供应商主体、被处理产品、处理范围、禁限期、处理措施等关键内容，请务必登录中国电信阳 光采购网（https://caigou.chinatelecom.com.cn）查阅《中国电信供应商不良行为管理规则》。本项目根据《中国 电信供应商中不良行为管理规则》选择适用备选处理措施（但涉及生产安全责任事故的处理结果不适用备选措 施）。 1.2.2成交供应商数量：1个，每个成交供应商对应的份额如下： [第一成交供应商：份额100%] 1.3本项目设置最高响应限价。最高响应限价为566037.74元人民币（不含税），供应商响应报价高于最高 响应限价的，其响应将被否决。 序号 采购内容 最高限价 备注 1 信息化建设类 566037.74 不含税价格 2.供应商资格要求 2.1供应商基本资格要求 2.1.1 供应商应为中华人民共和国境内法律上和财务上独立的法人或依法登记注册的其他组织，合法运作 并独立于采购人和采购代理机构。提供有效的行政管理部门登记的主体资格证件（包括但不限于营业执照、事 业单位法人证书、社会团体法人登记证书等）。法人下属不具备法人资格的分支机构参与响应的，应提供所属 法人针对本项目或覆盖本项目的经营事项的有效授权。 2.1.2 供应商的法定代表人或负责人为同一人或者存在控股、管理关系的不同供应商，不得参加同一标包 响应或者未划分标包的同一询比项目响应。 2.1.3 本次询比不接受联合体响应。} 2.1.4 本次询比不接受代理商响应。 } 2.1.5 供应商须承诺为本项目开具增值税专用发票。 2.1.6资质要求：供应商须具备建设行政主管部门颁发的电子与智能化工程专业承包贰级及以上资质，提供清晰、 完整、有效的行政主管部门颁发的资质证书扫描件。已按照《住房和城乡建设部关于印发建设工程企业资质管 理制度改革方案的通知》（建市〔2020〕94号）规定取得新资质证书的（在2020年11月30日之后），应提供相应 等级的最新资质证书扫描件。 2.1.7安全生产条件：供应商须具有建设行政主管部门颁发的安全生产许可证，企业主要负责人具有相应建设行政 主管部门颁发的安全生产考核合格证A证（企业名称为响应单位名称），提供相应证书扫描件，评委有权对相应 证书进行核验，如存在不实不予认可。 网 2.1.8业绩要求：供应商须提供2024年1月1日至本项目发布公告之日的类似项目（信息化建设类）业绩证明材料至 少一个，且单个合同金额不低于30.00万元（含税）。 注：业绩证明材料包括: 务 1）合同关键页扫描件，合同关键页包括体现合同标的、合同金额（如有）、合同签订时间、合同盖章页，否则 不予认可；合同中能体现合同金额的，以合同金额与合同签订时间为准；如不能体现合同金额，以合同对应订 单的累计金额与订单时间为准。 商 2）该合同对应的其中一张发票扫描件，发票主体名称须与合同双方或其下属分公司名称一致，发票开具时间在 本项目公告发布之日前。评审委员会有权在国家税务总局全国增值税发票查验平台 （https://inv-veri.chinatax.gov.cn/）进行发票查验，如查验结果与提供发票信息不一致则该发票不予认可。 道 如需检查以上相关资料原件，则须在要求时间内提供。 2.1.9项目团队人员要求：供应商须为本项目配备项目经理1人、施工员1人、安全员1人。 管 a）项目经理须具备相应建设行政主管部门颁发的安全生产考核合格证B证（扫描件），项目经理须具备在响应 单位注册的二级及以上注册建造师执业资格（专业为机电工程），提供项目经理有效期内身份证扫描件，相关 建造师资质证书的证明材料（如电子证照或相关官方网站查询截图等）。 b）供应商为本项目配国备的施工员、质量员须附上岗证书、有效期内身份证；安全员须附相应建设行政主管部门 颁发的“安全生产考核合格证C证”、有效期内身份证（扫描件）。 注： 中 ①人员不得兼任，如人员兼任，不予认可。项目经理、安全员须提供社保局出具由响应单位缴纳的2026年4月1日 之后任意一个月的社保证明，其它人员如为第三方公司代缴社保，则还须提供第三方公司与供应商的代缴协议 或类似证明。 ②评委有权通过原件核查或登陆全国建筑市场监管公共服务平台 （https://jzsc.mohurd.gov.cn/home）、全国或当地住房和城乡建设委员会官方网站等网络查验等方式进一步核实 响应文件中的相关信息。若供应商存在任何形式的弄虚作假行为，一经查实，则将否决其响应。 ③以上资料原件备查，如评审时需要核查，接到正式通知后，须在规定时间内提供，否则不予认可。 2.1.10购买保险要求：供应商须符合《安全生产责任保险实施办法》相关要求，购买包含安全生产责任险在内的 人身意外类相关保险（保障范围须覆盖本项目全部实施人员，累计保险赔付额度不低于200万元/人）。供应商须 提供相应的保单证明，或承诺在合同签订前完成购买并达到相应保额。 2.2供应商不得存在下列情形之一 （1） 为采购人不具有独立法人资格的附属机构（单位）； （2） 被依法暂停或取消投标/响应资格的； （3） 被责令停产停业、暂扣或者吊销许可证、暂扣或者吊销执照； （4） 进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （5） 在最近三年内（自2023年09月01日起）被相关行业主管部门或司法机关认定有骗取中标/成交、严重 违约、重大工程质量或者安全问题的； （6） 在最近五年内（自2021年09月01日起）被判处单位行贿罪，且行贿行为与采购活动相关的（以“中 国裁判文书网”的生效判决为准）； （7） 在最近五年内（自2021年09月01日起）被判处合同诈骗罪的（以“中国裁判文书网”的生效判决为 准）； （8） 被最高人民法院在“信用中国”网站（www.creditchina.gov.cn）或各级信用信息共享平台中列入失 信被执行人名单，已执行完毕或不再执行的除外； 网 （9） 为本询比项目提供过设计、编制技术规范和其他文件的咨询服务； （10） 为本工程项目的相关监理人，或者与本工程项目的相关监理人存在隶属关系或者其他利害关系； 务 （11） 为本询比项目的代建人； （12） 为本询比项目的采购代理机构； 商 （13） 与本询比项目的监理人或代建人或采购代理机构同为一个法定代表人； （14） 与本询比项目的监理人或代建人或采购代理机构存在控股或参股关系； 道 （15） 被工商行政管理机关在国家企业信用信息公示系统中列入严重违法失信企业名单的； （16）中国电信在职员工违规担任供应商法定代表人并参与采购活动的； 管 （17）中国电信集团有限公司/中国电信股份有限公司中层及以上管理人员违反有关领导人员配偶、子女 及其配偶经商办企业行为管理规定，其配偶、子女及其配偶经商办企业参与采购活动的； （18）中国电信领导人员离职或退休后三年内违反《国有企业领导人员廉洁从业若干规定》等相关规定 任职、投资入股的私营国企业、外资企业和中介机构，参与其原任职单位采购活动的； （19）其他按照中国电信供应商不良行为处理结果及《中国电信供应商不良行为管理规则》的结果执行 规则，应对供应商及其响应产品在本项目中执行禁止采购处理措施的； （20）法律法规、询比文件限定的其他情形。 中 2.3产品资格要求 2.3.1 产品应是来自中华人民共和国的成熟稳定的产品。 2.4法律法规规定的其他要求。 3.资格审查方法 本项目将进行资格后审，资格审查标准和内容见询比文件第三章“评审办法”，凡未通过资格后审的供应商， 其响应将被否决。 4.询比文件的获取 4.1询比文件获取时间:2026年08月24日 17时00分00秒至2026年08月27日 17时00分00秒（北京时间，下同）。 4.2询比文件获取方式：登录“中国电信阳光采购网（https://caigou.chinatelecom.com.cn）”后，通过“招 投标-采购文件领取”模块或通过“电子采购入口”跳转中国电信电子采购系统，进入本项目进行询比文件登记 申领，未在系统注册的供应商须先进行注册，注册方法详见本公告“7供应商注册”。 4.3询比文件费用：本项目不收取文件费用。 5.响应文件的递交 5.1响应文件递交截止时间（即响应截止时间）为：2026年09月01日 15时00分00秒 5.2电子响应文件的提交方式：登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通 过“招投标-我的项目”模块或通过“电子采购入口”跳转中国电信电子采购系统，选择本项目进行响应文件提 交，供应商应在响应文件提交截止时间之前通过电子采购系统完成加密电子响应文件的上传。供应商未在电子 采购系统进行询比文件申领登记或电子响应文件未按照要求加密的，将无法通过电子采购系统提交电子响应文 件。 5.3本项目将于响应文件提交截止同一时间通过中国电信电子采购系统开启响应文件，采购人/采购代理机 构邀请响应供应商的法定代表人或者其委托代理人准时参加。 网 7.供应商注册 7.1中国电信阳光采购网注册 未注册过的潜在供应商，须通过中国电信阳光采购网（https://caigou.chinatelecom.com.cn）首页“立即注 务 册”模块完成注册后，方可申领本项目询比文件。 7.2 CA证书办理 参加询比响应的潜在供应商须提前办理CA证书，并确保商CA证书在使用时有效。CA证书办理流程详见中 国电信阳光采购网首页“操作指引-CA办理”。 7.3技术支撑联系方式 道 服务热线：4000111884 服务邮箱：zb_support@chinatelecom.cn（电子采购系统技术支撑） 管 ctsc@chinatelecom.cn（CA证书办理技术支撑） 8.发布公告的媒介 本询比公告在 中国电国信阳光采购网（https://caigou.chinatelecom.com.cn）、中国招标投标公共服务平台 （http://www.cebpubservice.com/）上发布，其他媒介转载无效。 9.联系及异议接收方式 中 9.1联系方式 采 购 人: 中国电信股份有限公司秀山分公司 采购代理机构: 鼎信项目管理咨询有限公司 地 址： 地 址： 邮 编： 邮 编： 408000 联 系 人： 谭老师 联 系 人： 姚老师 电 话： 19123814835 电 话： 18183123500 电子邮件： 电子邮件： yufei.cq@chinaccs.cn 网 址： 网 址： 开户银行： 中国工商银行袁家岗支行 账 号： 9558833100007360570 9.2异议接收方式 登录中国电信阳光采购网（https://caigou.chinatelecom.com.cn）后，通过“招投标-采购异议-提出异议” 模块提出。 采购代理机构：鼎信项目管理咨询有限公司 2026年08月22日 信息来源:https://www.chinapipe.net/project/d3078606.html cqdingjiu 2026.08.25 09:25:44 网 务 商 道 管 国 中</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>项目服务内容自动农业气象监测系统、土壤墒情监测系统、智能虫情测报系统、杀虫控制系统、水肥一体化、宣传片拍摄等。
-https://www.chinapipe.net/project/d3078606.html</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>管材, 预制构件</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>中建桥梁有限公司西部(重庆)科学城德感片区污水管网修复完善工程项目(白沙部分新增)市政工程采购公告</t>
+          <t>中铁十一局集团第二工程有限公司通江县2025年超长期国债高标准农田建设项目经理部水泥涵管询价采购公告</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1653,50 +1653,58 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>巴中市</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>通江县</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>西部（重庆）科学城德感片区污水管网修复完善工程项目所需（白沙部分新增）市政工程专业分包工程，包括非开挖紫外光修复、安装前道内部勘测、清淤、封堵气囊、导排水，钢内衬成环回顶，铺设防划垫膜，主物料的拉入、连接充气设备、安装排水软管、物料的充气/紫外光固化、冷却物料、切除管口扎头多余务、抽出内膜、CCTV检测验收、拆除堵通水修复，管道铺设、管件、检查井、完成建筑垃圾清理，路面恢复等主要工序和辅助工序。</t>
+          <t>该项目涉及11个乡镇（街道）32个村的农田基础设施建设，包括新建和改造提升部分，主要采购水泥涵管。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>项目资金来自2025年超长期国债，具体金额未明确。</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>市政工程专业分包工程</t>
+          <t>水泥涵管</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>中建桥梁有限公司西部(重庆)科学城德感片区污水管网修复完善工程项目(白沙部分新增)市政工程采购公告 为满足中建桥梁有限公司对中建桥梁有限公司西部（重庆）科学城德感片区污水管网修复完善工程项目生产需 求，现就西部（重庆）科学城德感片区污水管网修复完善工程项目所需（白沙部分新增）市政工程专业分包工 程进行采购，诚邀符合资格要求、能提供优质服务的供应商参与报名。 一、工程概况 1、采购主体：中建桥梁有限公司 网 2、工程地址：重庆市江津区 3、采购内容：非开挖紫外光修复、安装前道内部勘测、清淤、封堵气囊、导排水，钢内衬成环回顶，铺设防划 垫膜，主物料的拉入、连接充气设备、安装排水软管、物料的充气/紫外光固化、冷却物料、切除管口扎头多余 务 废料，抽出内膜、CCTV检测验收、拆除堵通水修复，管道铺设、管件、检查井、完成建筑垃圾清理，路面恢复 等一切所需要的主要工序和上述未明示但实际完成承包项目内容所需的辅助工序所包括的全部工作内容。 二、报名单位资格要求 商 1、具有中华人民共和国企业独立法人资格，持有工商行政管理部门核发并通过最近年检的法人营业执照。代理 人须得到报名单位的授权。 2、资质要求：具备有效的资质证书、安全生道产许可证及相关认证证书，须具备市政公用工程施工总承包资质叁 级及以上资质或具有相关资质成建制单位；具备法律主体资格，具有独立订立及履行合同的能力，可开具增值 税专用发票。 3、业绩要求：在国内有关部门和行业的监督检查中没有不良记录；与中建桥梁有限公司及下属各单位没有不良 管 合作记录； 4、人员、设备、资金、服务、信誉等方面具有相应的能力。 5、成交分供商同意使国用云筑网（http://www.yzw.cn）筑易签电子签章功能完成采购合同签订；鼓励无纸化办公， 推荐分供商使用云筑网电子公章功能完成采购报名和报价工作。 6、存在以下情形的，原则上不得参与本次采购： 中 （1）严重违法失信企业； （2）失信被执行企业； （3）经营异常企业； （4）采购主体本上级单位禁用分供商的“换马甲”企业。 三、报名 1、报名方式 已在云筑网（http://www.yzw.cn）上注册的供应商，并经中建股份本下级任意单位认证“专业分包类”的分供商， 登录后即可报名。 2、报名时间。 公告发布时间： 2026 年8 月20 日（北京时间）。 报名截止时间为： 2026 年 8 月 24日 09 时 00 分（北京时间），具体以云筑网公示时间为准。 3、采购文件的获取 经资格审查入围的报名单位，登录云筑网下载采购文件，并依据采购文件要求于采购文件响应截止日前在云筑 网上递交响应文件。 4、报名及采购文件响应阶段 IP 地址相同的分供商直接淘汰。报名阶段存在信息重叠、工商关联（同一高管或 董监高，或股权关联（四层及以下））的分供商最多允许一家通过资格审查；报价阶段存在信息重叠、工商关联 （同一高管或董监高，或股权关联（四层及以下））的分供商直接淘汰。 5、报名附件格式参照公告附件要求，内容包括： （1）《分包商资质审查表》； 网 （2） 三证合一的营业执照； （3） 资质证书 务 （4） 安全生产许可证 （5） 法定代表人身份证明，授权委托书，授权委托人身份证复印件（正反面）； （6） 其他证明企业情况的资料（如企业荣誉及相关证书商，业绩等，办公场所、生产车间、仓储照片等）； 上述资料（1）至（5）项为必须项，第（6）项为选择项，报名单位可根据公司实际情况选择填写第6（项），所 有报名资料按照以上顺序盖章后扫描成一个 PDF 版电子文件，报名时将 PDF 版电子文件上传至云筑网。 道 四、保证金 报名成功并通过资审的分供商，在签收采购文件前缴纳1万元的采购响应保证金，报名单位可通过云筑网线上缴 纳保证金或购买保证保险（二选一），保证金在采购成交结果公示后30个工作日内退还，保险不予退还。 管 保证金缴纳操作如有问题，请报名单位联系云筑网客服，联系电话：4006-818-555。 若发生下列情况之一，采购人不予退还响应人所缴纳的保证金： 国 （1）响应人在响应截止日至采购人发布成交通知之日期间撤销其响应文件的； （2）提供虚假的材料谋取成交的； 中 （3）成交分供商收到成交通知后在规定的期限内未按采购文件要求签订采购合同的； （4）违反廉政承诺内容的； （5）采购期间发生其它违法、违规行为的。 五、联系方式 联系人：张继涛 电话：13919184919 联系人：游镇华 电话：13212385162 信息来源:https://www.chinapipe.net/project/d3078567.html cqdingjiu 2026.08.25 09:25:44</t>
+          <t>中铁十一局集团第二工程有限公司通江县2025年超长期国债高标准农田建设项目经理部水泥涵管询价采购公告 中铁十一局集团第二工程有限公司通江县 2025年超长期国债高标准农田建设项目经理部水泥涵管询价采购公告 询价编号： ZT1102-XJ-2026-522-2 中铁十一局集团第二工程有限公司通江县 2025年超长期国债高标准农田建设项目因施工需要，拟采购一批工程 物资（清单如下表）， 本次询价只接受在中国铁建采购平台 —铁建云链（https://www.crccep.com/）注册通过审 核的供应商 在线报价， 请有意向并符合要求的供应商按以下要求于 202 6 年 8 月 2 8 日 上 午 1 0 点 00分之前 将报 价文件签字盖章扫描件（所有报价文件资料须扫描成一份 PDF文件 ）上传至铁建网云链平台并进行报价维护操作。 一、 物资需求表 计 务 序 物资 量 需求 备 规格型号 技术标准 需求量 到货地点 号 名称 单 日期 注 位 商 202 6 混凝 四川省巴中市通江县高标准农田建设项目 各 年 8 1 土涵 DN300 GB/T 11836-2023 米 12.00 村 施工现场 月 30 管 日 道 混凝 2 土涵 DN400 GB/T 11836-2023 米 765.00 管 混凝 管 3 土涵 DN600 GB/T 11836-2023 米 85.00 管 混凝 4 土涵 DN800 国GB/T 11836-2023 米 33.00 管 混凝 5 土涵 DN1000 GB/T 11836-2023 米 12.00 中 管 混凝 6 土涵 DN1200 GB/T 11836-2023 米 12.00 管 合 919 .00 计 二、 项目简介： 通江县 2025年超长期国债高标准农田建设项目共计涉及11个乡镇（街道）32个村（社区）,其中新建部分涉及高 明新区周子坪村，广纳镇东山村、顺石岭村、 石墩村，铁佛镇大佛寺村、印合寨村、金山村、文峰村，民胜镇 贾家粱村、火铺山村、白盘梁村、弯柏树村，火炬镇犀凤村、苟家坝村，沙溪镇复兴场村、桑丝坪村，洪口镇 苟家湾村，松溪乡祭田坝村等8个镇18个村。改造提升部分涉及诺江镇七水村，广纳镇新桥村、檬子垭村、广纳 街道居委会，铁佛镇补巴石村，民胜镇鹦鸽嘴村，麻石镇云昙村、印顶寨村、马三垭村，火炬镇老君观村、园 铧山村、玉马村，三溪镇永乐村、桅杆坪村等7个镇14个村。幅员面积222.56平方千米。 三、有关要求： 1.投标单位资格条件： 1.1营业范围：在中华人民共和国境内依法经国家工商、税务机关登记注册，符合询价物资经营范围，具有独立 企业法人资格的生产厂家；投标人如是代理商，须代理符合资格要求的生产厂家参加投标，提供生产厂出具的 针对本包件授权函原件或投标物资生产厂销售代理证明，生产厂家不得与其所授权的代理商共同参与报价。 1.2财务能力：投标人具有依法纳税的良好记录。 1.3质量保证能力：出具满足询价公告技术要求的近2年投标物资质量检验报告。 1.4供货业绩：具有近两年与本次询价物资相同类型的物资供货业绩相关证明材料（附中标通知书）。 2.报价资料要求： 授权委托书（代理人）、报价函、营业执照、投标物质量检测报告（如有）、生产许可证（如 有）、质量管理体系认证（如有）、投标单位资质证书（如有）、相关业绩（如有）及我方需要的其他资料。 网 3.采用固定价结算，物资报价为货物的到站总价， 包含但不限于材料费、加工费、试验费、包装费、搬运、储存、 装车费、 卸车费（采用随车吊装卸）、 运杂费、 服务费 、 售后服务费等 。 报价注意事项： 以下各村卸货点以各村村委会定位（ +10km）为最终卸货点，测算价格时需充分考虑运距， 务 并结合项目现场实际情况，报价为到地头现场施工区域的价格， 乡村机耕道路较差较窄，无法大车运输，只能 使用 5-6米长车辆运输（单桥随车吊）， 含卸车费，卸车地点较为分散，共计 32个村对应 54个卸车地点（幅员 面积222.56平方千米），各村对应数量如下： 商 卸货点 涵管型号 (承插式） 数量（ m) 民胜镇白盘梁村 DN300混凝土涵管 3 DN400混凝土涵管 48 道 DN600混凝土涵管 19 DN1200混凝土涵管 12 铁佛镇补巴石村 DN400混凝土涵管 75 管 铁佛镇大佛寺村 DN300混凝土涵管 9 DN800混凝土涵管 6 DN400混凝土涵管 10 国 广纳镇东山村 DN400混凝土涵管 27 火炬镇渡水溪村 DN800混凝土涵管 6 DN400混凝土涵管 41 中 沙溪镇复兴场村 DN400混凝土涵管 18 DN600混凝土涵管 11 洪口镇苟家湾村 DN400混凝土涵管 65 广纳镇石庙村 DN400混凝土涵管 9 松溪乡祭天坝村 DN400混凝土涵管 42 DN800混凝土涵管 6 民胜镇贾家梁村 DN400混凝土涵管 6 铁佛镇金山村 DN400混凝土涵管 10 DN600混凝土涵管 9 火炬镇老君观村 DN400混凝土涵管 8 DN600混凝土涵管 4 广纳镇檬子垭村 DN400混凝土涵管 28 诺江镇七水村 DN400混凝土涵管 12 DN1000混凝土涵管 4 广纳镇石墩村 DN400混凝土涵管 43 广纳镇顺石岭村 DN400混凝土涵管 3 DN600混凝土涵管 4 DN800混凝土涵管 3 民胜镇弯柏树村 DN400混凝土涵管 15 三溪镇桅杆坪村 DN800混凝土涵管 12 铁佛镇文峰村 DN400混凝土涵管 32 火炬镇犀凤村 DN400混凝土涵管 59 广纳镇新桥村 DN1000混凝土涵管 8 网 DN400混凝土涵管 4 麻石镇印顶寨村 DN400混凝土涵管 12 铁佛镇印合寨 DN400混凝土涵管 18 务 民胜镇鹦哥嘴村 DN400混凝土涵管 60 DN600混凝土涵管 12 三溪镇永乐村 DN400混凝土涵管 12 商 火炬镇玉马村 DN600混凝土涵管 6 火炬镇圆铧山村 DN400混凝土涵管 17 麻石镇云昙村 DN400混凝土涵管 40 道 DN600混凝土涵管 20 诺江镇周子坪村 DN400混凝土涵管 51 919 管 以上信息请仔细阅读，可联系项目人员了解详情。 4.表中数量为暂定数量，结算数量以实际验收的数量为准。 国 5.货物验收方式： 5.1货物到工地后，甲方应及时组织验收，乙方应提供随货同行的装车单、出厂合格证及检测报告。 中 5.2 按米验收、检尺复核：货物到达甲方工地，甲方组织人员对水泥涵管的厚度、尺寸等检尺测量，按米验收， 检测结果不符合我方标准的，将一律退回，由此发生的费用由责任方承担。 6.货款结算支付方式： 6.1货款支付方式： 银行转账（ 10 0%） 6.2付款周期： （ 1）乙方账户必须是合同中约定的在主管国税机关备案的账户，甲方在收到乙方提交的合规增值税专用发票， 并经税务机关认证通过后 12 个月内支付乙方供应期所供合格物资 7 0 % 货款， 18 个月内支付乙方供应期所供合 格物资 95 % 货款，剩余货款暂时扣留作为质量保证金，质量保证金在该批物资验收合格 6 个月后无息返还，但 质量保证金的支付并不免除乙方对交付物资质量的保证责任。 （ 2）货款支付过程中，如我方付款不到位或延迟，自最后一笔货款支付之日起1年内不追究我方的违约责任； 如超过1年未支付，逾期利息自未支付货款的第13个月开始起算，利率为合同订立时中国人民银行授权全国银行 间同业拆借中心公布的一年期贷款市场报价利率(LPR)，逾期利息不超过欠款总额的3%。 7. 投标 保证金要求： 无 8.报价有效期：9 0 天。 9.技术指标：满足国家,建设部,及巴中市的有关工程法律,法规,规范标准和监理公司的质量管理体系文件（不限于 下列规范标准）。 ①《混凝土和钢筋混凝土排水管》 (GB/T 11836-2023) 10.评标方式：采用最低价中标，即通过评审且经评审的报价最低的报价人为第一中标候选人的评标方法（ 以不 含税价格进行评审 ），但明显低于成本价的或超过项目可以接受价格的除外。 11.其他要求：如果必须提供的报价资料不齐全，将进行报价作废处理。 四、联系人及联系方式： 网 采 购 人：中铁十一局集团第二工程有限公司通江县 2025年超长期国债高标准农田建设项目经理部 地 址：四川省巴中市通江县壁州大道中段 85号 务 联 系 人：尚渊增（采购单位联系人） 联系电话： 17870126174 商 联 系 人：李先生 (组织单位联系人) 联系电话： 18834 171936 道 20 2 6 年 8 月 23 日 管 报 价 函 询价编号： ZT1102-XJ-2026-522-2 中铁十一局集团第二工国程有限公司通江县 2025年超长期国债高标准农田建设项目经理部 ： 我方已经仔细阅读 ZT1102-XJ-2026-522-2 （询价编号）询价函 ，愿意参加 ZT1102-XJ-2026-522-2 （询价编号） 的 报价 ，若中标我方将以此作为物资及服务必须严格遵循的合同条件的组成部分, 我方报价如下 ： 中 产 含 价税 品 规格型 单 税 税 备 序号 质量标准 数量 合计 名 号 位 单 率 注 （元） 称 价 混 凝 GB/T 1 土 DN300 米 12.00 11836-2023 涵 管 混 凝 GB/T 2 土 DN400 米 765.00 11836-2023 涵 管 混 凝 GB/T 3 土 DN600 米 85.00 11836-2023 涵 管 混 凝 GB/T 4 土 DN800 米 33.00 11836-2023 涵 管 混 凝 GB/T 5 土 DN1000 米 12.00 11836-2023 涵 管 混 凝 GB/T 6 土 DN1200 米 12.00 11836-2023 涵 管 9 合计 19 - - - 网 .00 我单位郑重承诺：已认真研读本次询价邀请函所列物资全部技术指标及相关要求，承诺所投物资 完全符合本项目技术标准及技术指标要求 。 若我单位提供物资不符合项目技术指标要求，或收到中标 /签约通知后无故推诿、拒签合同、放 弃中选资格的，自愿接受项目单位将我单位 纳入不良行为供应商名录 等一切处理措施，承担由 务 此产生的全部责任及损失。 报价注意事项： 各村卸货点以各村村委会定位（ +10km）为最终卸货点，测算价格时需充分考虑运距，并 结合项目现场实际情况，报价为到地头现场施工区域的价格，乡村机耕道路较差较窄，无法大车运输，只能使 用5-6米长车辆运输（单桥随车吊），含卸车费，卸车地商点较为分散，共计32个村对应54个卸车地点 。 我方同意 报价函 在规定的 报价 截止日期起 9 0天内有效，对我方具有约束力，并可随时接受中标。我方慎重保 证， 报价 文件的所有内容及提供给 采购 人的所有证明文件和资料是真实的、准确的，一旦发现上述资料和信息 的失实和错误，贵方将有权宣布本单位 报价 作废。 道 在正式合同准备签订或执行之前，本 报价 函、 采购 人的书面通知 等 将构成约束我们双方的合同。我方理解 采 购 人不一定接受最低价或收到的任何 报价 文件。 管 我方联系方式：联系人 : 联系电话： 邮箱： 报价人： 公司 /厂（章） 20 年 月 日 国 信息来源:https://www.chinapipe.net/project/d3079346.html 中 cqdingjiu 2026.08.25 10:30:23</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>西部（重庆）科学城德感片区污水管网修复完善工程项目所需（白沙部分新增）市政工程专业分包工程，包括非开挖紫外光修复、安装前道内部勘测、清淤、封堵气囊、导排水，钢内衬成环回顶，铺设防划垫膜，主物料的拉入、连接充气设备、安装排水软管、物料的充气/紫外光固化、冷却物料、切除管口扎头多余务、抽出内膜、CCTV检测验收、拆除堵通水修复，管道铺设、管件、检查井、完成建筑垃圾清理，路面恢复等主要工序和辅助工序。
-https://www.chinapipe.net/project/d3078567.html</t>
+          <t>该项目涉及11个乡镇（街道）32个村的农田基础设施建设，包括新建和改造提升部分，主要采购水泥涵管。
+https://www.chinapipe.net/project/d3079346.html</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>市政工程, 污水管网修复</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项目设备材料招标公告</t>
+          <t>达州绕城项目电力管道材料询价公告</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1706,7 +1714,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1721,47 +1729,43 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>武隆区</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项目设备材料招标公告</t>
+          <t>达州绕城项目电力管道材料的公开市场询价。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>项目资金来自重庆市武隆区提升农村饮水质量专项行动（2025-2027）项目资金，项目出资比例为100%。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>涉及饮用水卫生安全产品的卫生许可批件</t>
+          <t>电力管道材料</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项 目设备材料招标公告 1.招标条件 本招标项目武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水 厂工程已由重庆市武隆区发展和改革委员会以武隆水利发〔2025〕295号、武隆水利发〔2025〕 296号、武隆水 利发〔2025〕311号、武隆水利发〔2025〕313号批准建设，项目业主为重庆市庆祥水资源开发有限公司，招标项 目资金来自重庆市武隆区提升农村饮水质量专项行动（2025-2027）项目资金，项目出资比例为100%，招标人为 重庆武隆城市发展(集团)有限公司。项目已具备招标条件，现对该4个项目设备材料采购进行公开招标，评标办 法采用经评审的最低投标价法。 网 2.项目概况与招标范围 务 2.1 建设地点：武隆区黄莺乡、芙蓉街道、火炉镇、土地乡 商 2.2 项目概况与建设规模 道 （1）武隆区黄莺乡龙洞水厂工程：该工程由取水工程、输水工程、厂区工程和配水工程组成。取水工程新建30 立方米取水井1座 ;输水工程新增DN110PE输水管道0.7公里,DN89x4.5 毫米涂塑无缝钢管 管 5.564 公里，配套减压池1座及配套相应阀门井 ;厂区工程新增日处理规模500立方米一体化净水设备1套，更换消 毒加药设备1套，改造现有厂区管理房厂 :配水工程新建配水管道85.72公里及配套附属设施，新建减压池11 座，100立方米调蓄水池(补氯)1座（本工程的设备材料部分）。 国 （2）武隆区芙蓉街道白杨村集中供水工程：设计供水规模为1256立方米/天，安装管网共计 172.082公里，其 中DN100涂塑钢管15.883公里，DN80 涂塑钢管11.624公里，DN65 涂塑钢管13.336公里，DN50涂塑钢管37.861公里， 中 DN40涂塑钢管93.378公里 ;新建30立方米加氯池及配套加氯设备用房1座 ;新建泵站1座(扬程280米，3.84方/小 时，功率18.5千瓦) ;新建减压池25座 ;管网配套各类阀井共计376座，其中闸阀井245座，泄水阀井65座，排气 阀井 66 座（本工程的设备材料部分）。 （3）武隆区火炉镇万峰水厂工程：改造及延伸供水管道总长71.133 公里，其中：改造供水管道59.085公里，延 伸供水管道 12.048 公里，新建减压池 10 个，新建表井 312 座等（本工程的设备材料部分）。 （4）武隆区土地乡桂花水厂工程：工程供水规模为 500 吨/天。主要建设内容：一是水源引水工程。新增取 水水源点 2 处，安装引水管道总长 12.502 公里；二是供水管道工程41.216 公里；三是厂区围墙改造工程等 （本工程的设备材料部分）。 2.3 本次招标项目货物采购估算金额：1701.27万元。 2.4 招标范围：包含所列货物制造、包装、运输、保险至现场、设备及设备的安装调试(管网不含安装)、检验、 检测、退换货、质保期内售后服务、税费等完成本项目所产生的所有费用。 2.5 交货地点：重庆市武隆区（招标人指定地点）。 2.6 交货期：60日历天，计划开始交货日期：合同签订后10天内开始交货。 3.政府采购工程 网 3.投标人资格要求 3.1 本次招标允许投标人以投标货物的下列身份参加投标： 务 制造商 商 代理商（包括经销商、制造商下属销售子公司） 道 3.1.1 投标人为制造商应符合以下要求： 管 （1）具备独立法人资格； 国 （2）具备有效的《涉及饮用水卫生安全产品卫生许可批件》。 中 3.1.2 投标人为代理商应符合以下要求： （1）具备独立法人资格； （2）投标货物制造商应具备有效的《涉及饮用水卫生安全产品卫生许可批件》。； （3） 涂塑无缝钢管具有制造商授权书。 注：本招标项目同一标段中，一个制造商对同一品牌同一型号的货物，仅能委托一个代理商参加投标，否则各 相关投标均无效； 同一品牌同一型号货物的制造商和代理商不得在本招标项目同一标段中投标，否则各相关 投标均无效。 3.2 投标人还应在业绩、资金、人员等方面具有相应的供货能力，详见招标文件第二章投标人须知前附表 第1.4.1项内容。 3.3 本次招标不接受联合体投标。 .技术成果经济补偿 本次招标对未中标人投标文件中的技术成果给予经济补偿。 给予经济补偿的，网招标人将按如下标准支付经济补 偿费： 4.招标文件的获取 4.1本招标项目采用全流程电子招投标，投标人在投标前可在重庆市公共资源交易网下载招标文件及相关资料。 务 参与投标的投标人需在重庆市公共资源交易网完成市场主体信息登记以及 CA 数字证书办理，办理方式请参见重 庆市公共资源交易网导航栏“主体信息”页面中“市场主体信息登记”“CA 数字证书办理”。若投标人未及时 完成市场主体信息登记和 CA 数字证书办理导致无法完成全流程电子招投标的，责任自负。 4.2投标人可在重庆市公共资源交易网（武隆区）（https://www.cqggzy.com/wulongweb）和重庆市公共资源交易监 商 督网（http://ggzyjyjgj.cq.gov.cn/）本项目招标公告网页下方“我要提问”栏提出疑问，提问时间从本公告发布 至2026-08-26 12:00:00前。 4.3招标人应于2026-08-26 12:00:00前在重庆市公共资源交易网（武隆区）（https://www.cqggzy.com/wulongweb）和 重庆市公共资源交易监督网（http://ggzyjyjgj.cq.gov.cn/）发布澄清。 5.投标文件递交的内容 道 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-11 09:30，投标人应当在投标截止时间前，通过互 联网使用CA数字证书登录重庆市电子招投标系统，将加密的电子投标文件上传。 5.2未按要求加密的电子投标文件，将无法上传至重庆市电子招投标系统，逾期未完成投标文件上传的，视为撤 回投标文件。 管 6.发布公告的媒介 本次招标公告同时在重庆市公共资源交易网（武隆区）（https://www.cqggzy.com/wulongweb）和重庆市公共资源 交易监督网（http://ggzyjyjgj.cq.gov.cn/）发布。[提示：依法必须招标项目的招标公告，必须在重庆市公共资源交 易监督网上发布。] 7.联系方式 国 招 标 人: 重庆武隆城市发展（集团）有限公司 代理机构: 中大宇辰项目管理有限公司 地 址: 重庆市武隆区望江苑1栋 地 址: 渝北区新牌坊二路136号路华苑小区 邮 编: 中 邮 编: 项目负责人: 张老师 项目负责人: 欧朝华 电 话: 023-77721580 电 话: 18996416879 传 真: 传 真: 电子邮箱: 电子邮箱: 开户银行: 开户银行: 账 号: 账 号: 监督部门: 重庆市武隆区发展和改革委员会 电 话: 023-77765552 2026年08月22日 武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个 项目设备材料 户名 开户行 投标保证金账号 重庆联合产权交易所集团股份有限公 中国建设银行股份有限公司重庆渝中支 6232813760003413621 司 行 重庆联合产权交易所集团股份有限公 中国农业银行股份有限公司重庆自由贸 312601010400083780000031794 司 易试验区分行 重庆联合产权交易所集团股份有限公 重庆银行股份有限公司七星岗支行 15010202900420146631981 司 信息来源:https://www.chinapipe.net/project/d3078450.html cqdingjiu 2026.08.25 09:25:44 网 务 商 道 管 国 中</t>
+          <t>达州绕城项目电力管道材料询价公告 各供应商： 我司需调查现阶段材料市场价格情况，现对达州绕城项目电力管道材料进行公开市场询价，有意向参与本次询 价的供应商，请于2026年8月26日12:00之前填写报价清单，并将盖章版扫描件发送至QQ邮 箱：1259370225@qq.com进行报价。 请相关供应商积极配合，谢谢！ 网 咨询电话：028-61107713 技术设计部 务 信息来源:https://www.chinapipe.net/project/d3079316.html cqdingjiu 2026.08.25 10:30:24 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项目设备材料招标公告
-https://www.chinapipe.net/project/d3078450.html</t>
+          <t>达州绕城项目电力管道材料的公开市场询价。
+https://www.chinapipe.net/project/d3079316.html</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>达州绕城项目, 电力管道材料, 询价公告</t>
         </is>
       </c>
     </row>
@@ -1818,12 +1822,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>管材</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>宝兴县农村供水水质提升项目/标段施工招标补遗书01号 宝兴县农村供水水质提升项目（项目名称）/标段施工招标补遗书01号 致：各潜在投标人 宝兴县农村供水水质提升项目（项目名称）/标段施工招标作如下补遗，内容如下： 网 1、宝兴县农村供水水质提升项目（项目名称）/标段施工招标招标工程量清单数据文件及招标文件已重新上传， 请投标人自行下载。由此给各潜在投标人带来的不便，敬请谅解。 务 招标人：宝兴县水利综合服务中心（盖单位章） 招标代理机构：攀钢集团工科工程咨询有限公司（盖单位章） 商 日期：2026年08月24日 信息来源:https://www.chinapipe.net/project/d3079265.html 道 cqdingjiu 2026.08.25 09:25:45 管 国 中</t>
+          <t>宝兴县农村供水水质提升项目/标段施工招标补遗书01号 宝兴县农村供水水质提升项目（项目名称）/标段施工招标补遗书01号 致：各潜在投标人 宝兴县农村供水水质提升项目（项目名称）/标段施工招标作如下补遗，内容如下： 网 1、宝兴县农村供水水质提升项目（项目名称）/标段施工招标招标工程量清单数据文件及招标文件已重新上传， 请投标人自行下载。由此给各潜在投标人带来的不便，敬请谅解。 务 招标人：宝兴县水利综合服务中心（盖单位章） 招标代理机构：攀钢集团工科工程咨询有限公司（盖单位章） 商 日期：2026年08月24日 信息来源:https://www.chinapipe.net/project/d3079265.html 道 cqdingjiu 2026.08.25 10:30:24 管 国 中</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1833,11 +1837,11 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>分析, 重庆, 近三天, 管材, 招标商机</t>
+          <t>农村供水水质提升项目, 管材, 招标</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1903,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>大英县红旗工业园区污水处理厂改造与配套设施改建项目(三标段)设计补遗01号 大英县红旗工业园区污水处理厂改造与配套设施改建项目 （三标段）设计补遗01号 致各潜在投标人： 网 1、现将原招标公告中5. 招标文件的获取5.1凡有意参加投标者，请于2026年8月20日00时00分至2026年8月8日17 时00分开始登陆：全国公共资源交易平台（四川省·遂宁市）（网址：https://www.snsggzyjy.cn）—“登 录”—“ 遂宁市建设工程网上交易后台管理系统”，通过数字证书免费下载招标资料（招标文件、技术资料 等）（报名结束时间为2026年8月8日17时00分）。 务 变更为： 招标文件的获取5.1凡有意参加投标者，请于2026年8月20日00时00分至2026年9月8日17时00分开始登陆：全国公共 资源交易平台（四川省·遂宁市）（网址：https://www.s商nsggzyjy.cn）—“登录”—“ 遂宁市建设工程网上交易 后台管理系统”，通过数字证书免费下载招标资料（招标文件、技术资料等）（报名结束时间为2026年9月8日17 时00分）。 2、 现将原评标办法（综合评估法）评标办法道前附表2.2.4（1）资信业绩评分标准 企业资质 满足招标公告资 质要求得7分。 变更为： 管 原评标办法（综合评估法）评标办法前附表2.2.4（1）资信业绩评分标准 企业业绩 企业业绩： 2023年01月01日 以来具有1个已完成或新承接或正在设计的类似业绩得5分，每增加1个加2分，本项满分7分。（注：类似业绩提 供合同扫描件，时间以合同签订时间为准） 3、原评标办法（综合国评估法）评标办法前附表2.2.4（2）设计方案设计大纲评分标准的内容变更以重新上传的招 标文件为准。 中 4、本项目补遗招标文件重新上传，请潜在投标人以附件内容为准，请各潜在投标人仔细查阅下载相关资料，投 标人因任何原因未上网查询、下载补遗文件及其附件资料造成的一切后果自行负责，本项目开标时间不变。 招标人： 四川大英经济开发区管理委员会 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3079263.html cqdingjiu 2026.08.25 09:25:45</t>
+          <t>大英县红旗工业园区污水处理厂改造与配套设施改建项目(三标段)设计补遗01号 大英县红旗工业园区污水处理厂改造与配套设施改建项目 （三标段）设计补遗01号 致各潜在投标人： 网 1、现将原招标公告中5. 招标文件的获取5.1凡有意参加投标者，请于2026年8月20日00时00分至2026年8月8日17 时00分开始登陆：全国公共资源交易平台（四川省·遂宁市）（网址：https://www.snsggzyjy.cn）—“登 录”—“ 遂宁市建设工程网上交易后台管理系统”，通过数字证书免费下载招标资料（招标文件、技术资料 等）（报名结束时间为2026年8月8日17时00分）。 务 变更为： 招标文件的获取5.1凡有意参加投标者，请于2026年8月20日00时00分至2026年9月8日17时00分开始登陆：全国公共 资源交易平台（四川省·遂宁市）（网址：https://www.s商nsggzyjy.cn）—“登录”—“ 遂宁市建设工程网上交易 后台管理系统”，通过数字证书免费下载招标资料（招标文件、技术资料等）（报名结束时间为2026年9月8日17 时00分）。 2、 现将原评标办法（综合评估法）评标办法道前附表2.2.4（1）资信业绩评分标准 企业资质 满足招标公告资 质要求得7分。 变更为： 管 原评标办法（综合评估法）评标办法前附表2.2.4（1）资信业绩评分标准 企业业绩 企业业绩： 2023年01月01日 以来具有1个已完成或新承接或正在设计的类似业绩得5分，每增加1个加2分，本项满分7分。（注：类似业绩提 供合同扫描件，时间以合同签订时间为准） 3、原评标办法（综合国评估法）评标办法前附表2.2.4（2）设计方案设计大纲评分标准的内容变更以重新上传的招 标文件为准。 中 4、本项目补遗招标文件重新上传，请潜在投标人以附件内容为准，请各潜在投标人仔细查阅下载相关资料，投 标人因任何原因未上网查询、下载补遗文件及其附件资料造成的一切后果自行负责，本项目开标时间不变。 招标人： 四川大英经济开发区管理委员会 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3079263.html cqdingjiu 2026.08.25 10:30:24</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1913,7 +1917,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>分析, 重庆, 近三天, 管材, 招标商机</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1979,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>仁美镇基础设施建设项目(二期)EPC设计施工总承包标段招标公告 仁美镇基础设施建设项目(二期)EPC (项目名称)设计施工总承包标段标段招标公告 1. 招标条件 1.1本招标项目仁美镇基础设施建设项目(二期)EPC(项目名称)已由丹棱县发展和改革局(项目审批、核准或备案机 关名称)以丹棱发改[2026]116号（批文名称及编号）批准建设，项目业主为丹棱县仁美镇人民政府，建设资金来 自上级资金、县级配套资金（资金来源），项目出资比例为100%，招标人为丹网棱县仁美镇人民政府。项目已具 备招标条件，现对该项目的设计施工总承包进行公开招标。 1.2本招标项目由丹棱县发展和改革局（核准机关名称）核准（招标事项核准文号为丹棱发改[2026]116号）的招 标组织形式为□自行招标 委托招标。招标人选择的招标代理机构是 四川久河工程技术有限公司。 务 2. 项目概况与招标范围 2.1建设地点：丹棱县仁美镇。 商 2.2项目概况：改建道路约1.5km，改造雨水管网1.5km，污水管网3km，配套综合整治提升工程;周边房屋整治提 升工程；新建1个占地约8亩的停车场(新增停车位约100个)，改扩建市政道路约0.5km，增设充电桩设施，配套涵 管、照明等基础设施;新建新区黑化道路约0.4km,新建雨水管网0.5km，污水管网约0.5km，人行横道约0.8km，配 套弱电、照明等基础设施。 道 2.3招标范围：设计范围：含本项目施工图设计、配合施工图审查、按招标人要求提供各阶段符合要求的设计成 果并通过审查、新增及变更设计、参加交（竣）工验收、资料归档并移交、施工期间现场服务及后续服务工作、 施工图预算编制工作等内容。施工范围：包含但不限于施工图纸 (含变更)和相应工程量清单所表达的范围及竣工 管 验收合格的整体移交、工程保修期内的缺陷修复和保修工作、后续配合工作等内容。 2.4计划工期：365日历天（其中：设计60日历天，施工305日历天）。 2.5资金来源：上级资金国、县级配套资金。 2.6标段划分：1个标段，具体划分为：设计施工总承包1个标段。 2.7 本次招标实行资格后审。 中 2.8 本次招标采用电子招标。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质要求：须具有独立企业法人资格，施工单位须具备国家建设行政主管部门颁发的市政公用工程施工总承 包三级及以上资质，设计单位须具备国家建设行政主管部门颁发的工程设计市政行业（给水工程、排水工程、 道路工程）专业设计乙级及以上资质（投标人或联合体成员单位企业注册地不在四川省行政区域内的省外企业 须提供在有效期内的四川省住房和城乡建设厅官网已公开的入川信息网页截图），并在人员、设备、资金等方 面具有相应的施工、设计能力，施工单位须具备有效的安全生产许可证。 3.1.2业绩要求：（本项为多选） □设计业绩要求：近年（至投标截止时间，不少于3年） 已完成不少于（1 至3个）个类似项目。类似项目是指: 。 □施工业绩要求：近年（至投标截止时间，不少于3年）已完成不少于（1至3个）个类似项目。类似项目是指: 。 无业绩要求。 3.1.3项目经理的资格要求： 具有市政公用工程专业二级及以上注册建造师和省级及以上住房城乡建设主管部门 颁发的安全生产考核合格证（B 证）□由设计负责人兼任由施工负责人兼任，须为本单位人员（若为联合体投 标，须为联合体牵头人人员）。 3.1.4设计负责人的资格要求：具有注册土木工程师（道路工程），须为投标人本网单位人员（联合体投标的，应为 联合体中设计单位人员）。 3.1.5施工负责人（建造师，下同）的资格要求：具备市政公用工程二级及以上注册建造师，具有省级及以上住房 城乡建设主管部门颁发的安全生产考核合格证（B证），须为投标人本单位人员（联合体投标的，应为联合体中 务 施工单位人员）。 3.2本次招标接受联合体投标。联合体投标的，联合体牵头人应为□设计单位施工单位，同时满足下列要求： （1）联合体资质应符合法律法规的规定，并按照联合体协议约定的职责分工予以认定，且各成员单位只能承担 自身资质范围内的相应工作；（2）本次组成联合体总数商不得超过2家，其中施工单位不超过1家，设计单位不超 过1家，由施工单位作为联合体牵头人；（3）联合体投标，应由联合体牵头人获取招标文件和提交投标保证金， 在制作数据电文形式投标文件时，投标人名称应填写联合体牵头人名称。如未按要求进行投标，导致投标文件 无法读取，由投标人自行负责。（4）联合体各方不得再以自己名义单独或参加其他联合体在同一工程项目中投 标。 道 3.3本次招标范围中施工部分的工作仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企 业、与大企业的负责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，本项目联合体协议书中 职责分工为承揽施工工作的所有单位均应属于中小企业）。具体标准以《工业和信息化部、国家统计局、国家 管 发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业〔2011〕300号）中的“建 筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、存在特殊要求外，我省依法必须招标的 国家投资工程，施工部分招标控制价在3000万元以下的，应勾选此项。）。 4. 招标文件的获国取 4.1凡有意参加投标者，请于2026-08-25 00:00至2026-08-31 23:59 (北京时间，下同），在全国公共资源交易平台 （四川省·眉山市）（https://www.msggzy.org.cn）,凭注册认证的数字证书免费获取招标文件等资料。未在眉山市 中 公共资源电子交易平台网完成网上注册的企业，按流程完成注册并领取企业身份认证数字证书后，方可按以上 要求购买招标文件，此为获取招标文件唯一途径。 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-14 09:30，电子投标文件递交的网址为全国公共资 源交易平台（四川省·眉山市）（https://www.mssggzy.org.cn），开标地点丹棱县政务服务和公共资源交易服务 中心（丹棱县外西街6号） 5.2逾期送达的或者未送达到指定地点的投标文件，招标人不予受理。 6. 发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）(http://ggzyjy.sc.gov.cn)、全国公共资源交易平台（四川省·眉 山市）（https://www.mssggzy.org.cn）上发布。 7. 联系方式 招 标 人：丹棱县仁美镇人民政府 地 址：丹棱县仁美镇母店街100号 邮 编：620200 联系人：黄老师 电 话：028-37280022 传 真：/ 电子邮件：/ 网 址：/ 网 开户银行：/ 账 号：/ 务 □ 招标代理机构：/ 招标代理机构： 四川久河工程技术有限公司 商 地 址：成都市金牛区蜀西路52号4栋15楼1505-2 邮 编：610036 道 联系人：李老师 电 话：028-60176405 管 传 真：/ 电子邮件：/ 网 址：/ 国 开户银行：/ 账 号：/ 中 项目负责人：李芳 地 址：成都市金牛区蜀西路52号4栋15楼1505-2 邮 编：610036 联 系 人：李老师 电 话：028-60176405 传 真：/ 电子邮件：/ 网 址：/ 行政监督部门 单位名称：丹棱县住房和城乡建设局 联系电话：028-37202172 信息来源:https://www.chinapipe.net/project/d3079259.html cqdingjiu 2026.08.25 09:25:45 网 务 商 道 管 国 中</t>
+          <t>仁美镇基础设施建设项目(二期)EPC设计施工总承包标段招标公告 仁美镇基础设施建设项目(二期)EPC (项目名称)设计施工总承包标段标段招标公告 1. 招标条件 1.1本招标项目仁美镇基础设施建设项目(二期)EPC(项目名称)已由丹棱县发展和改革局(项目审批、核准或备案机 关名称)以丹棱发改[2026]116号（批文名称及编号）批准建设，项目业主为丹棱县仁美镇人民政府，建设资金来 自上级资金、县级配套资金（资金来源），项目出资比例为100%，招标人为丹网棱县仁美镇人民政府。项目已具 备招标条件，现对该项目的设计施工总承包进行公开招标。 1.2本招标项目由丹棱县发展和改革局（核准机关名称）核准（招标事项核准文号为丹棱发改[2026]116号）的招 标组织形式为□自行招标 委托招标。招标人选择的招标代理机构是 四川久河工程技术有限公司。 务 2. 项目概况与招标范围 2.1建设地点：丹棱县仁美镇。 商 2.2项目概况：改建道路约1.5km，改造雨水管网1.5km，污水管网3km，配套综合整治提升工程;周边房屋整治提 升工程；新建1个占地约8亩的停车场(新增停车位约100个)，改扩建市政道路约0.5km，增设充电桩设施，配套涵 管、照明等基础设施;新建新区黑化道路约0.4km,新建雨水管网0.5km，污水管网约0.5km，人行横道约0.8km，配 套弱电、照明等基础设施。 道 2.3招标范围：设计范围：含本项目施工图设计、配合施工图审查、按招标人要求提供各阶段符合要求的设计成 果并通过审查、新增及变更设计、参加交（竣）工验收、资料归档并移交、施工期间现场服务及后续服务工作、 施工图预算编制工作等内容。施工范围：包含但不限于施工图纸 (含变更)和相应工程量清单所表达的范围及竣工 管 验收合格的整体移交、工程保修期内的缺陷修复和保修工作、后续配合工作等内容。 2.4计划工期：365日历天（其中：设计60日历天，施工305日历天）。 2.5资金来源：上级资金国、县级配套资金。 2.6标段划分：1个标段，具体划分为：设计施工总承包1个标段。 2.7 本次招标实行资格后审。 中 2.8 本次招标采用电子招标。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质要求：须具有独立企业法人资格，施工单位须具备国家建设行政主管部门颁发的市政公用工程施工总承 包三级及以上资质，设计单位须具备国家建设行政主管部门颁发的工程设计市政行业（给水工程、排水工程、 道路工程）专业设计乙级及以上资质（投标人或联合体成员单位企业注册地不在四川省行政区域内的省外企业 须提供在有效期内的四川省住房和城乡建设厅官网已公开的入川信息网页截图），并在人员、设备、资金等方 面具有相应的施工、设计能力，施工单位须具备有效的安全生产许可证。 3.1.2业绩要求：（本项为多选） □设计业绩要求：近年（至投标截止时间，不少于3年） 已完成不少于（1 至3个）个类似项目。类似项目是指: 。 □施工业绩要求：近年（至投标截止时间，不少于3年）已完成不少于（1至3个）个类似项目。类似项目是指: 。 无业绩要求。 3.1.3项目经理的资格要求： 具有市政公用工程专业二级及以上注册建造师和省级及以上住房城乡建设主管部门 颁发的安全生产考核合格证（B 证）□由设计负责人兼任由施工负责人兼任，须为本单位人员（若为联合体投 标，须为联合体牵头人人员）。 3.1.4设计负责人的资格要求：具有注册土木工程师（道路工程），须为投标人本网单位人员（联合体投标的，应为 联合体中设计单位人员）。 3.1.5施工负责人（建造师，下同）的资格要求：具备市政公用工程二级及以上注册建造师，具有省级及以上住房 城乡建设主管部门颁发的安全生产考核合格证（B证），须为投标人本单位人员（联合体投标的，应为联合体中 务 施工单位人员）。 3.2本次招标接受联合体投标。联合体投标的，联合体牵头人应为□设计单位施工单位，同时满足下列要求： （1）联合体资质应符合法律法规的规定，并按照联合体协议约定的职责分工予以认定，且各成员单位只能承担 自身资质范围内的相应工作；（2）本次组成联合体总数商不得超过2家，其中施工单位不超过1家，设计单位不超 过1家，由施工单位作为联合体牵头人；（3）联合体投标，应由联合体牵头人获取招标文件和提交投标保证金， 在制作数据电文形式投标文件时，投标人名称应填写联合体牵头人名称。如未按要求进行投标，导致投标文件 无法读取，由投标人自行负责。（4）联合体各方不得再以自己名义单独或参加其他联合体在同一工程项目中投 标。 道 3.3本次招标范围中施工部分的工作仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企 业、与大企业的负责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，本项目联合体协议书中 职责分工为承揽施工工作的所有单位均应属于中小企业）。具体标准以《工业和信息化部、国家统计局、国家 管 发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业〔2011〕300号）中的“建 筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、存在特殊要求外，我省依法必须招标的 国家投资工程，施工部分招标控制价在3000万元以下的，应勾选此项。）。 4. 招标文件的获国取 4.1凡有意参加投标者，请于2026-08-25 00:00至2026-08-31 23:59 (北京时间，下同），在全国公共资源交易平台 （四川省·眉山市）（https://www.msggzy.org.cn）,凭注册认证的数字证书免费获取招标文件等资料。未在眉山市 中 公共资源电子交易平台网完成网上注册的企业，按流程完成注册并领取企业身份认证数字证书后，方可按以上 要求购买招标文件，此为获取招标文件唯一途径。 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-14 09:30，电子投标文件递交的网址为全国公共资 源交易平台（四川省·眉山市）（https://www.mssggzy.org.cn），开标地点丹棱县政务服务和公共资源交易服务 中心（丹棱县外西街6号） 5.2逾期送达的或者未送达到指定地点的投标文件，招标人不予受理。 6. 发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）(http://ggzyjy.sc.gov.cn)、全国公共资源交易平台（四川省·眉 山市）（https://www.mssggzy.org.cn）上发布。 7. 联系方式 招 标 人：丹棱县仁美镇人民政府 地 址：丹棱县仁美镇母店街100号 邮 编：620200 联系人：黄老师 电 话：028-37280022 传 真：/ 电子邮件：/ 网 址：/ 网 开户银行：/ 账 号：/ 务 □ 招标代理机构：/ 招标代理机构： 四川久河工程技术有限公司 商 地 址：成都市金牛区蜀西路52号4栋15楼1505-2 邮 编：610036 道 联系人：李老师 电 话：028-60176405 管 传 真：/ 电子邮件：/ 网 址：/ 国 开户银行：/ 账 号：/ 中 项目负责人：李芳 地 址：成都市金牛区蜀西路52号4栋15楼1505-2 邮 编：610036 联 系 人：李老师 电 话：028-60176405 传 真：/ 电子邮件：/ 网 址：/ 行政监督部门 单位名称：丹棱县住房和城乡建设局 联系电话：028-37202172 信息来源:https://www.chinapipe.net/project/d3079259.html cqdingjiu 2026.08.25 10:30:25 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2046,12 +2050,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>供水管线、雨水管线、污水管线、供电线路、燃气管线、通信管线、路边停车位、充电桩、广告牌等附属基础设施</t>
+          <t>供水管线、雨水管线、污水管线、供电线路、燃气管线、通信管线、停车位、充电桩、广告牌等附属基础设施</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>仁寿县普宁大道地下管线及附属设施建设项目EPC设计施工总承包标段招标公告 仁寿县普宁大道地下管线及附属设施建设项目EPC (项目名称)设计施工总承包标段标段招标公告 1. 招标条件 1.1本招标项目仁寿县普宁大道地下管线及附属设施建设项目EPC(项目名称)已由仁寿县发展和改革局(项目审批、 核准或备案机关名称)以仁发改〔2025〕91号（批文名称及编号）批准建设，项目业主为仁寿县鑫城建设开发有 限责任公司，建设资金来自地方政府专项债券资金和县本级财政资金（资金来源），项目出资比例为100%，招 标人为仁寿县鑫城建设开发有限责任公司。项目已具备招标条件，现对该项目的网设计施工总承包进行公开招标。 1.2本招标项目由仁寿县发展和改革局（核准机关名称）核准（招标事项核准文号为仁发改〔2025〕91号）的招标 组织形式为□自行招标 委托招标。招标人选择的招标代理机构是 仁寿汇鑫招标采购代理有限公司。 务 2. 项目概况与招标范围 2.1建设地点：仁寿县普宁街道。 2.2建设规模：更新和升级DN250供水管线3.04千米、更新商和升级DN400-DN1000雨水管线3.04千米、更新和升 级DN300-DN800污水管线3.04千米、更新和升级供电线路1.52千米、更新和升级燃气管线3.04千米、更新和升级12 孔通信管线3.04千米，配套更新改造路边停车位、充电桩、广告牌等附属基础设施。 2.3总投资：项目总投资12000万元。本次招标道最高限价9999.34万元，其中（其中工程费最高限价为9847.34万元， 设计费最高限价为152万元） 2.4招标范围：（1）工程设计：包括但不限于复核并修正前期勘察、测绘、设计成果文件，根据项目情况提出合 理化建议，施工图设计、专项方案和专项设计、施工图预算、新增及变更设计、效果图设计制作、竣工图设计 管 制作，施工期间现场服务等及后续服务，符合评审的工程量清单及招标控制价清单编制要求，参加交（竣）工 验收、资料归档并移交、后续设计配合工作等红线范围内的所有设计内容。 （2）工程施工：包括但不限于设计范围内的所有工作内容，按设计、施工总承包模式进行设计范围内的工程施 工。 国 2.5计划工期：780日历天（其中设计60日历天，施工720日历天）。 2.6工程质量要求：设计：符合国家、地方和行业现行设计规范、规程、规定、标准并通过审查，并满足施工需 中 求。施工：符合国家、地方和行业现行施工质量验收标准，满足设计要求，工程质量合格。 2.7资金来源：地方政府专项债券资金和县本级财政资金。 2.8标段划分： 1个标段，具体划分为：/ 。 2.9 本次招标实行资格后审。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质要求：1.须具备独立企业法人资格，具备国家建设行政主管部门颁发的工程设计市政行业乙级及以上资 质。2.须具备独立企业法人资格，具备国家建设行政主管部门颁发的市政公用工程施工总承包一级及以上资质， 施工单位须具备有效的安全生产许可证。 3.1.2业绩要求：（本项为多选） □设计业绩要求：近年（至投标截止时间，不少于3年） 已完成不少于（1 至3个）个类似项目。类似项目是指: 。 □施工业绩要求：近年（至投标截止时间，不少于3年）已完成不少于（1至3个）个类似项目。类似项目是指: 。 无业绩要求。 3.1.3项目经理的资格要求： 由施工负责人兼任□由设计负责人兼任由施工负责人兼任，须为本单位人员（若 为联合体投标，须为联合体牵头人人员）。 网 3.1.4设计负责人的资格要求：具备注册土木工程师（道路工程）证书，须为投标人本单位人员（联合体投标的， 应为联合体中设计单位人员）。 3.1.5施工负责人（建造师，下同）的资格要求：具备市政公用工程一级注册建造师，具有省级及以上住房城乡建 务 设主管部门颁发的安全生产考核合格证（B证），须为投标人本单位人员（联合体投标的，应为联合体中施工单 位人员）。 3.2本次招标接受联合体投标。联合体投标的，联合体牵头人应为□设计单位施工单位，同时满足下列要求： 1. 联合体各方均具备独立企业法人资格； 商 2.联合体牵头单位应具备国家建设行政主管部门颁发的市政公用工程施工总承包一级及以上资质； 3.联合体总数不得超过2家，其中施工单位不超道过1家，设计单位不超过1家； 4.联合体各方应签订联合体协议书，明确联合体牵头人和各方权利义务； 5.联合体各方不得以自己名义在本招标项目中单独或参加其他联合体对本项目投标； 管 6.本项目投标报名、投标保证金缴纳、递交投标文件等相关事项均由牵头人负责，牵头人进行的该行为对联合体 各成员具有约束力。 □3.3本次招标范围中施国工部分的工作仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企 业、与大企业的负责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，本项目联合体协议书中 职责分工为承揽施工工作的所有单位均应属于中小企业）。具体标准以《工业和信息化部、国家统计局、国家 发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业〔2011〕300号）中的“建 筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、存在特殊要求外，我省依法必须招标的 中 国家投资工程，施工部分招标控制价在3000万元以下的，应勾选此项。）。 4. 招标文件的获取 4.1凡有意参加投标者，请于2026-08-25 09:00至2026-08-31 17:00 (北京时间，下同），在全国公共资源交易平台 （四川省·眉山市）（https://www.msggzy.org.cn）,凭注册认证的数字证书免费获取招标文件等资料。未在眉山市 公共资源电子交易平台网完成网上注册的企业，按流程完成注册并领取企业身份认证数字证书后，方可按以上 要求购买招标文件，此为获取招标文件唯一途径。 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-14 09:30，电子投标文件递交的网址为全国公共资 源交易平台（四川省·眉山市）（https://www.mssggzy.org.cn），开标地点眉山市政务服务和公共资源交易服务 中心（眉山市东坡区眉州大道东二段5号综合楼一楼）。 5.2逾期送达的或者未送达到指定地点的投标文件，招标人不予受理。 6. 发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）(http://ggzyjy.sc.gov.cn)、全国公共资源交易平台（四川省·眉 山市）（https://www.mssggzy.org.cn）上发布。 7. 联系方式 招 标 人：仁寿县鑫城建设开发有限责任公司 地 址：仁寿城投大厦A栋6楼 邮 编：620500 联系人：万老师 网 电 话：028-36655323 传 真： 务 电子邮件： 网 址： 商 开户银行： 账 号： 道 □ 招标代理机构：/ □ 招标代理机构：仁寿汇鑫招标采购代理有限公司 管 地 址：仁寿城投大厦 B 栋 4 楼 邮 编：620500 联系人：曾老师 国 电 话：028-35030616 传 真： 中 电子邮件： 网 址： 开户银行： 账 号： 项目负责人： 地 址： 邮 编： 联 系 人： 电 话： 传 真： 电子邮件： 网 址： 行政监督部门 单位名称：仁寿县住房和城乡建设局 联系电话：028-36202205 信息来源:https://www.chinapipe.net/project/d3079257.html 网 cqdingjiu 2026.08.25 09:25:45 务 商 道 管 国 中</t>
+          <t>仁寿县普宁大道地下管线及附属设施建设项目EPC设计施工总承包标段招标公告 仁寿县普宁大道地下管线及附属设施建设项目EPC (项目名称)设计施工总承包标段标段招标公告 1. 招标条件 1.1本招标项目仁寿县普宁大道地下管线及附属设施建设项目EPC(项目名称)已由仁寿县发展和改革局(项目审批、 核准或备案机关名称)以仁发改〔2025〕91号（批文名称及编号）批准建设，项目业主为仁寿县鑫城建设开发有 限责任公司，建设资金来自地方政府专项债券资金和县本级财政资金（资金来源），项目出资比例为100%，招 标人为仁寿县鑫城建设开发有限责任公司。项目已具备招标条件，现对该项目的网设计施工总承包进行公开招标。 1.2本招标项目由仁寿县发展和改革局（核准机关名称）核准（招标事项核准文号为仁发改〔2025〕91号）的招标 组织形式为□自行招标 委托招标。招标人选择的招标代理机构是 仁寿汇鑫招标采购代理有限公司。 务 2. 项目概况与招标范围 2.1建设地点：仁寿县普宁街道。 2.2建设规模：更新和升级DN250供水管线3.04千米、更新商和升级DN400-DN1000雨水管线3.04千米、更新和升 级DN300-DN800污水管线3.04千米、更新和升级供电线路1.52千米、更新和升级燃气管线3.04千米、更新和升级12 孔通信管线3.04千米，配套更新改造路边停车位、充电桩、广告牌等附属基础设施。 2.3总投资：项目总投资12000万元。本次招标道最高限价9999.34万元，其中（其中工程费最高限价为9847.34万元， 设计费最高限价为152万元） 2.4招标范围：（1）工程设计：包括但不限于复核并修正前期勘察、测绘、设计成果文件，根据项目情况提出合 理化建议，施工图设计、专项方案和专项设计、施工图预算、新增及变更设计、效果图设计制作、竣工图设计 管 制作，施工期间现场服务等及后续服务，符合评审的工程量清单及招标控制价清单编制要求，参加交（竣）工 验收、资料归档并移交、后续设计配合工作等红线范围内的所有设计内容。 （2）工程施工：包括但不限于设计范围内的所有工作内容，按设计、施工总承包模式进行设计范围内的工程施 工。 国 2.5计划工期：780日历天（其中设计60日历天，施工720日历天）。 2.6工程质量要求：设计：符合国家、地方和行业现行设计规范、规程、规定、标准并通过审查，并满足施工需 中 求。施工：符合国家、地方和行业现行施工质量验收标准，满足设计要求，工程质量合格。 2.7资金来源：地方政府专项债券资金和县本级财政资金。 2.8标段划分： 1个标段，具体划分为：/ 。 2.9 本次招标实行资格后审。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质要求：1.须具备独立企业法人资格，具备国家建设行政主管部门颁发的工程设计市政行业乙级及以上资 质。2.须具备独立企业法人资格，具备国家建设行政主管部门颁发的市政公用工程施工总承包一级及以上资质， 施工单位须具备有效的安全生产许可证。 3.1.2业绩要求：（本项为多选） □设计业绩要求：近年（至投标截止时间，不少于3年） 已完成不少于（1 至3个）个类似项目。类似项目是指: 。 □施工业绩要求：近年（至投标截止时间，不少于3年）已完成不少于（1至3个）个类似项目。类似项目是指: 。 无业绩要求。 3.1.3项目经理的资格要求： 由施工负责人兼任□由设计负责人兼任由施工负责人兼任，须为本单位人员（若 为联合体投标，须为联合体牵头人人员）。 网 3.1.4设计负责人的资格要求：具备注册土木工程师（道路工程）证书，须为投标人本单位人员（联合体投标的， 应为联合体中设计单位人员）。 3.1.5施工负责人（建造师，下同）的资格要求：具备市政公用工程一级注册建造师，具有省级及以上住房城乡建 务 设主管部门颁发的安全生产考核合格证（B证），须为投标人本单位人员（联合体投标的，应为联合体中施工单 位人员）。 3.2本次招标接受联合体投标。联合体投标的，联合体牵头人应为□设计单位施工单位，同时满足下列要求： 1. 联合体各方均具备独立企业法人资格； 商 2.联合体牵头单位应具备国家建设行政主管部门颁发的市政公用工程施工总承包一级及以上资质； 3.联合体总数不得超过2家，其中施工单位不超道过1家，设计单位不超过1家； 4.联合体各方应签订联合体协议书，明确联合体牵头人和各方权利义务； 5.联合体各方不得以自己名义在本招标项目中单独或参加其他联合体对本项目投标； 管 6.本项目投标报名、投标保证金缴纳、递交投标文件等相关事项均由牵头人负责，牵头人进行的该行为对联合体 各成员具有约束力。 □3.3本次招标范围中施国工部分的工作仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企 业、与大企业的负责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，本项目联合体协议书中 职责分工为承揽施工工作的所有单位均应属于中小企业）。具体标准以《工业和信息化部、国家统计局、国家 发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业〔2011〕300号）中的“建 筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、存在特殊要求外，我省依法必须招标的 中 国家投资工程，施工部分招标控制价在3000万元以下的，应勾选此项。）。 4. 招标文件的获取 4.1凡有意参加投标者，请于2026-08-25 09:00至2026-08-31 17:00 (北京时间，下同），在全国公共资源交易平台 （四川省·眉山市）（https://www.msggzy.org.cn）,凭注册认证的数字证书免费获取招标文件等资料。未在眉山市 公共资源电子交易平台网完成网上注册的企业，按流程完成注册并领取企业身份认证数字证书后，方可按以上 要求购买招标文件，此为获取招标文件唯一途径。 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 5.1投标文件递交的截止时间（投标截止时间，下同）为2026-09-14 09:30，电子投标文件递交的网址为全国公共资 源交易平台（四川省·眉山市）（https://www.mssggzy.org.cn），开标地点眉山市政务服务和公共资源交易服务 中心（眉山市东坡区眉州大道东二段5号综合楼一楼）。 5.2逾期送达的或者未送达到指定地点的投标文件，招标人不予受理。 6. 发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）(http://ggzyjy.sc.gov.cn)、全国公共资源交易平台（四川省·眉 山市）（https://www.mssggzy.org.cn）上发布。 7. 联系方式 招 标 人：仁寿县鑫城建设开发有限责任公司 地 址：仁寿城投大厦A栋6楼 邮 编：620500 联系人：万老师 网 电 话：028-36655323 传 真： 务 电子邮件： 网 址： 商 开户银行： 账 号： 道 □ 招标代理机构：/ □ 招标代理机构：仁寿汇鑫招标采购代理有限公司 管 地 址：仁寿城投大厦 B 栋 4 楼 邮 编：620500 联系人：曾老师 国 电 话：028-35030616 传 真： 中 电子邮件： 网 址： 开户银行： 账 号： 项目负责人： 地 址： 邮 编： 联 系 人： 电 话： 传 真： 电子邮件： 网 址： 行政监督部门 单位名称：仁寿县住房和城乡建设局 联系电话：028-36202205 信息来源:https://www.chinapipe.net/project/d3079257.html 网 cqdingjiu 2026.08.25 10:30:25 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2065,7 +2069,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机</t>
+          <t>管材招标, 地下管线, 附属设施, EPC设计施工总承包</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2086,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2112,27 +2116,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>该项目包括农业种植园的设计和施工，涉及土地平整、灌溉系统安装、排水管道铺设等工程。</t>
+          <t>该项目包括农业种植园的设计和施工，涉及土地平整、灌溉系统安装、道路建设以及相关配套设施的完善。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>项目资金来源为企业自筹，投资比例为100%，具体金额未明确。</t>
+          <t>项目资金来源为企业自筹，占比100%，具体金额未明确。</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>主要产品类别包括排水管道、灌溉设备、土壤改良材料等。</t>
+          <t>主要产品类别包括管道、阀门、补偿器等。</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>筠连县农业种植园项目设计施工总承包标段招标公告 1.招标条件： 1 1..12本本招招标标项项目目筠由连 筠县连农县业发种展植和园改项革目局 (（项核目准名机称关)已名由称 筠）连核县准发（展招和标改事革项局核 (准项文目号审为批 川、投核资准备或【备2案50机7-关51名152称7-)0以4- 0川1-投21资83备54【】2F5G0Q7-B5-101654217 -号04 ）-01的-2招18标35组4】织F形GQ式B为-06委41托 号招 （标批 （文 自名行称招及标编 号 委）托批招准标建）设。，招项标目人业选主择为的 四招川标筠代禾理农机业构科是技鸿有鲲限咨公询司集 团，有建限设公资司金 来。自 银行贷款及企业自筹 （资金来源），项目出资比例为 100% ，招标人为 四川筠禾农业科技有限公司 。项目已具备招标条件，现对该项目的设计施工总承包进行公开招标。 2.项目概况与招标范围： 22222施2（ ..... . 12345 6工 说 建建服概招 标工 明 设设务算标 段作 本 地内工总范 划内 次 点容期投围 分容 招 ：及：资： ：包 标 筠规7：设 本 2 括 项 0 连模 2计 项 日1 ： 目 9 县： 工 目 历0 本 的 0 沐本 作 共 万天 项 建 爱项 内 划 元。 目 设 镇目 容 分 。 施 地 。拟 包 为工 点 建 括 1个图 、 设 ： 标及 规 农 完 段工 模 业 成 。程 及 种 本量 投 植 标清 资 园 段单 额 4 内 0 所 、 1 全 5 包 计 5 部 .8 括 划 工 7亩 的 工 程 ， 全 期 建 其 部 、 设 中 内 招 内 ： 容 标 容 旱 、 范 的 地 重 围 施 种 要 、 工 植 设 标 图 3 备 段 设 01 和 划 计 30 重 分 . 及 61 要 及 施 亩 材 标 工 、 料 段 图 水 采 投 预 田 购 资 算 种 、 额 编 植 安 等 制 10 装 ） 工 02 及 。 5 作 .2 发， 6亩 包包 。 人含 本 临但 项 时不 目 交限 主 办于 要 的本 建 与项 设 本目 内 项所 容 目涉 有 相及 田 关的 型 的边 调 施坡 整 工、 、 任基 土 务坑 地 （等 整 包专 理 括项 、 满设 坡 足计 改 工， 梯 程达 、 竣到 土 工相 地 验应 肥 收报 力 需批 提 求深 升 ，度 、 同并 水 时通 肥 完过 一 成审 体 设批 化 计工 、 施作 配 工， 套 总需 灌 承配 溉 包合 用 范招 蓄 围标 水 内人 池 工送 及 程财 沟 施评 渠 工评 和 及审 提 重工 灌 要作 站 材， 修 料且 筑 、对 、 设财 配 备政 套 采评 生 购审 产 安中 道 装心 路 内提 建 容出 设 所的 、 涉疑 农 及问 田 的需 输 一在 配 切1个 电 检工 工 测作 程 检日 建 验内 设 工以 等 作纸 。 ，质并文承件担进承行包回方复应，承施担工的过相程关设费计用服）务、、竣工工程验质收量、缺保陷修责及任工期程内施的工设相计关后管续理跟工踪作服，务并等对。承包工程的质量、安全、工期等全面负责。 3.投标人资格要求： 段 此 333 3333 设施无 3 ... ....中 项 111 1112 .3 本.. ...本 12 345 计工业 本投 。 资业 项设施 次 次 业业绩 次标 ） 质绩 目计工 招 招 绩绩要 招 。 要要 经负负 标 标 要要求 标 求求 理责责 要 接 求求。 范 ：： 的人人 求 受 ：： 围 （ 资的（ （投 联 近近 中 本 格资建 1标 合 年年 ） 施 项 要格造 人 体 （（ 具 工 为 求要师 须 投 有 部 22 多 ：求， 00 具 标 独 22 分 选 ：下 33 备 。 水 立 的 年年 ） 同注 联 利 法 工 ） 11 册 合 水 人 月月 作 的土 体 电 资 仅 11 资木 投 工 日日 格 面 格工 标 程 至至 的 向 要程 的 专 投投 企 中 求师 ， 业 标标 业 小 ：（ 联 二 截截 。 民 水水合 级 止止 （ 营 利利体 及 时时 2 企 ） 水水牵 以 间间 业 设 电电头 上 ，， 发 计 工工人 建 不不 包 单 程程应 造 少少 ， 位 ）专为 师 于于 （ ： 业 ， 33 设 其 由 年年 具 二须 计 中 设 ）） 备 级为 单 属 计 （（ 国 及投 位 于 负 家 以 标 已已 大 责 施 行 上人 完完 企 人 工 政 建本 成成 业 兼 单 主 造单 的 任 已已 位 管 师位 分 完完 ， 部 ， 由人 支 成成 同 门 具 施员 机 或或 时 颁 有 工。 构 新新 满 发 省 负 、 承承 足 的 级 责 存 接接 下 工 及 人 在 或或 列 程 以 兼 控 正正 要 设 上 任 股 在在 求 计 住 ， 股 设施 ： 农 房 （ 东 计工 林 城（ 业 为 ）） 行 乡1 绩 大 ） 不不 业 建 要 企 联 少少 （ 设 求 业 合 于于 农 主 ） 、 体 11 业 管 ， 与 （（ 成 工 部 须 大 11 员 程 门 至至 为 企 总 ） 颁 33 本 业 数 个个 乙 发 单 的 不 ）） 级 的 位 负 得 个个 及 安 人 责 超 类类 以 全 员 人 过 似似 上 生 （ 为 3 项项 资 产家 若 同 目目 质 考（ 为 一 。。 。 核含 联 人 类类 （ 合联 合 的 似似 3 格合 ） 体 情 项项 证体 施 投 形 目目 （牵 工 标 的 是是 B头 单 ， 企 证 指指 单 位 须 业 ） :: 位 改改 ： 为 均 ，） 造造 具 联 不 须， 或或 备 合 属 为联 新新 国 体 于 投合 建建 家 牵 中 标体 面面 行 头 小 人牵 积积 政 人 企 本头 不不 主 人 业 单人 低低 管 员 。 位必 于于 部 ） 若 人须 11 门 。 为 员 5500 是 颁 00 联 。 00 具 发 亩亩 合 备 的 的的 体 国 水 农农 投 家 利 业业 标 行 水 类类 的 政 电 设施 ， 主 工 计工 本 管 程 业业 项 部 施 绩绩 目 门 工 （（ 联 颁 总 含含 合 发 承 设设 体 的 包 计计 协 水 二 的施 议 利 级 设工 书 水 及 计总 中 电 以 施承 职 工 上 工包 责 程 资 总、 分 施 质 承施 工 工 包工 为 ， 总 业总 承 施 承 绩承 揽 工 包 或包 施 单 二 勘） 工 位 级 察 工 须 。 及 设 作 具 以 计 的 备 上 业 所 有 资 绩 有 效 质 或 单 的 的 设 位 安 单 计 均 全 位 业 应 生 。 绩 属 产 （ ） 于 许 2 中 ） 可 。 小 联 证 企 合 。 业 体 且 资 为 质 民 应 营 符 企 合 业 法 ） 律 。 法 具 规 体 的 标 规 准 定 以 ， 《 并 工 按 业 照 和 联 信 合 息 体 化 协 部 议 、 约 国 定 家 的 统 职 计 责 局 分 、 工 国 予 家 以 发 认 展 定 和 （ 改 3） 革 联 委 合 员 体 会 投 、 标 财 ， 政 应 部 由 关 联 于 合 印 体 发 牵 中 头 小 人 企 获 业 取 划 招 型 标 标 文 准 件 规 和 定 提 的 交 通 投 知 标 》 保 （ 证 工 金 信 ， 部 在 联 制 企 作 业 数 〔 据 20 电 11 文 〕 形 30 式 0号 投 ） 标 中 文 的 件 “ 时 建 ， 筑 投 业 标 ” 人 划 名 型 称 标 应 准 填 为 写 准 联 ， 合 投 体 标 牵 人 头 应 人 提 名 供 称 中 。 小 如 民 未 营 按 企 要 业 求 声 进 明 行 函 投 。 标 （ ， 除 导 技 致 术 投 复 标 杂 文 、 件 存 无 在 法 特 读 殊 取 要 ， 求 由 外 投 ， 标 我 人 省 自 依 行 法 负 必 责 须 。 招 （ 标 4） 的 联 国 合 家 体 投 各 资 方 工 不 程 得 ， 再 施 以 工 自 部 己 分 名 招 义 标 单 控 独 制 或 价 参 在 加 30 其 00 他 万 联 元 合 以 体 下 在 的 同 ， 一 应 标 勾选 4.招标文件的获取： 44..12 凡招有标意人参不加提投供标邮者购，招请标于文 件20服26务-08。-25 00:00 至 2026-09-01 00:00 （电子招标文件的获取，不受获取截止时间限制，任何时间段均可获取），登录宜宾市公共资源交易信息网（http://ggzy.yibin.gov.cn/），凭数字证书和密码获取招标文件及其它招标资料（含招标电子技术标文件，格式为*.ZBJ、招标电子商务标文件，格式为*.ZBS、图纸）。另，可通过本项目招标公告附件，免费获取招标文件。 5.投标文件的递交： 55投5 .. . 12 3标 投电 逾人 标子 期应 文投 递在 件标 交投 递文 的标 交件 或截 的递 者止 截交 未时 止方 按间 时式 指前 间： 定在 （ 方线 投 式递 标 递交 截 交经 止 或投 时 未标 间 送人 ， 达数 下 指字 同 定证 ） 地书 为 点加 的 2 密 0 投 26 的标 -0 数 9 文 - 据 1 件 4 电 0 ， 9 文 : 招 00 形 。 标式人投不标予文受件理。。 6.发布公告的媒介： 本次招标公告在《全国公共资源交易平台（四川省）》和 宜宾市公共资源交易信息、 (公告发布的其它媒介名称）上发布。 信息来源:https://www.chinapipe.net/project/d3079253.html 网 cqdingjiu 2026.08.25 09:25:45 务 商 道 管 国 中</t>
+          <t>筠连县农业种植园项目设计施工总承包标段招标公告 1.招标条件： 1 1..12本本招招标标项项目目筠由连 筠县连农县业发种展植和园改项革目局 (（项核目准名机称关)已名由称 筠）连核县准发（展招和标改事革项局核 (准项文目号审为批 川、投核资准备或【备2案50机7-关51名152称7-)0以4- 0川1-投21资83备54【】2F5G0Q7-B5-101654217 -号04 ）-01的-2招18标35组4】织F形GQ式B为-06委41托 号招 （标批 （文 自名行称招及标编 号 委）托批招准标建）设。，招项标目人业选主择为的 四招川标筠代禾理农机业构科是技鸿有鲲限咨公询司集 团，有建限设公资司金 来。自 银行贷款及企业自筹 （资金来源），项目出资比例为 100% ，招标人为 四川筠禾农业科技有限公司 。项目已具备招标条件，现对该项目的设计施工总承包进行公开招标。 2.项目概况与招标范围： 22222施2（ ..... . 12345 6工 说 建建服概招 标工 明 设设务算标 段作 本 地内工总范 划内 次 点容期投围 分容 招 ：及：资： ：包 标 筠规7：设 本 2 括 项 0 连模 2计 项 日1 ： 目 9 县： 工 目 历0 本 的 0 沐本 作 共 万天 项 建 爱项 内 划 元。 目 设 镇目 容 分 。 施 地 。拟 包 为工 点 建 括 1个图 、 设 ： 标及 规 农 完 段工 模 业 成 。程 及 种 本量 投 植 标清 资 园 段单 额 4 内 0 所 、 1 全 5 包 计 5 部 .8 括 划 工 7亩 的 工 程 ， 全 期 建 其 部 、 设 中 内 招 内 ： 容 标 容 旱 、 范 的 地 重 围 施 种 要 、 工 植 设 标 图 3 备 段 设 01 和 划 计 30 重 分 . 及 61 要 及 施 亩 材 标 工 、 料 段 图 水 采 投 预 田 购 资 算 种 、 额 编 植 安 等 制 10 装 ） 工 02 及 。 5 作 .2 发， 6亩 包包 。 人含 本 临但 项 时不 目 交限 主 办于 要 的本 建 与项 设 本目 内 项所 容 目涉 有 相及 田 关的 型 的边 调 施坡 整 工、 、 任基 土 务坑 地 （等 整 包专 理 括项 、 满设 坡 足计 改 工， 梯 程达 、 竣到 土 工相 地 验应 肥 收报 力 需批 提 求深 升 ，度 、 同并 水 时通 肥 完过 一 成审 体 设批 化 计工 、 施作 配 工， 套 总需 灌 承配 溉 包合 用 范招 蓄 围标 水 内人 池 工送 及 程财 沟 施评 渠 工评 和 及审 提 重工 灌 要作 站 材， 修 料且 筑 、对 、 设财 配 备政 套 采评 生 购审 产 安中 道 装心 路 内提 建 容出 设 所的 、 涉疑 农 及问 田 的需 输 一在 配 切1个 电 检工 工 测作 程 检日 建 验内 设 工以 等 作纸 。 ，质并文承件担进承行包回方复应，承施担工的过相程关设费计用服）务、、竣工工程验质收量、缺保陷修责及任工期程内施的工设相计关后管续理跟工踪作服，务并等对。承包工程的质量、安全、工期等全面负责。 3.投标人资格要求： 段 此 333 3333 设施无 3 ... ....中 项 111 1112 .3 本.. ...本 12 345 计工业 本投 。 资业 项设施 次 次 业业绩 次标 ） 质绩 目计工 招 招 绩绩要 招 。 要要 经负负 标 标 要要求 标 求求 理责责 要 接 求求。 范 ：： 的人人 求 受 ：： 围 （ 资的（ （投 联 近近 中 本 格资建 1标 合 年年 ） 施 项 要格造 人 体 （（ 具 工 为 求要师 须 投 有 部 22 多 ：求， 00 具 标 独 22 分 选 ：下 33 备 。 水 立 的 年年 ） 同注 联 利 法 工 ） 11 册 合 水 人 月月 作 的土 体 电 资 仅 11 资木 投 工 日日 格 面 格工 标 程 至至 的 向 要程 的 专 投投 企 中 求师 ， 业 标标 业 小 ：（ 联 二 截截 。 民 水水合 级 止止 （ 营 利利体 及 时时 2 企 ） 水水牵 以 间间 业 设 电电头 上 ，， 发 计 工工人 建 不不 包 单 程程应 造 少少 ， 位 ）专为 师 于于 （ ： 业 ， 33 设 其 由 年年 具 二须 计 中 设 ）） 备 级为 单 属 计 （（ 国 及投 位 于 负 家 以 标 已已 大 责 施 行 上人 完完 企 人 工 政 建本 成成 业 兼 单 主 造单 的 任 已已 位 管 师位 分 完完 ， 部 ， 由人 支 成成 同 门 具 施员 机 或或 时 颁 有 工。 构 新新 满 发 省 负 、 承承 足 的 级 责 存 接接 下 工 及 人 在 或或 列 程 以 兼 控 正正 要 设 上 任 股 在在 求 计 住 ， 股 设施 ： 农 房 （ 东 计工 林 城（ 业 为 ）） 行 乡1 绩 大 ） 不不 业 建 要 企 联 少少 （ 设 求 业 合 于于 农 主 ） 、 体 11 业 管 ， 与 （（ 成 工 部 须 大 11 员 程 门 至至 为 企 总 ） 颁 33 本 业 数 个个 乙 发 单 的 不 ）） 级 的 位 负 得 个个 及 安 人 责 超 类类 以 全 员 人 过 似似 上 生 （ 为 3 项项 资 产家 若 同 目目 质 考（ 为 一 。。 。 核含 联 人 类类 （ 合联 合 的 似似 3 格合 ） 体 情 项项 证体 施 投 形 目目 （牵 工 标 的 是是 B头 单 ， 企 证 指指 单 位 须 业 ） :: 位 改改 ： 为 均 ，） 造造 具 联 不 须， 或或 备 合 属 为联 新新 国 体 于 投合 建建 家 牵 中 标体 面面 行 头 小 人牵 积积 政 人 企 本头 不不 主 人 业 单人 低低 管 员 。 位必 于于 部 ） 若 人须 11 门 。 为 员 5500 是 颁 00 联 。 00 具 发 亩亩 合 备 的 的的 体 国 水 农农 投 家 利 业业 标 行 水 类类 的 政 电 设施 ， 主 工 计工 本 管 程 业业 项 部 施 绩绩 目 门 工 （（ 联 颁 总 含含 合 发 承 设设 体 的 包 计计 协 水 二 的施 议 利 级 设工 书 水 及 计总 中 电 以 施承 职 工 上 工包 责 程 资 总、 分 施 质 承施 工 工 包工 为 ， 总 业总 承 施 承 绩承 揽 工 包 或包 施 单 二 勘） 工 位 级 察 工 须 。 及 设 作 具 以 计 的 备 上 业 所 有 资 绩 有 效 质 或 单 的 的 设 位 安 单 计 均 全 位 业 应 生 。 绩 属 产 （ ） 于 许 2 中 ） 可 。 小 联 证 企 合 。 业 体 且 资 为 质 民 应 营 符 企 合 业 法 ） 律 。 法 具 规 体 的 标 规 准 定 以 ， 《 并 工 按 业 照 和 联 信 合 息 体 化 协 部 议 、 约 国 定 家 的 统 职 计 责 局 分 、 工 国 予 家 以 发 认 展 定 和 （ 改 3） 革 联 委 合 员 体 会 投 、 标 财 ， 政 应 部 由 关 联 于 合 印 体 发 牵 中 头 小 人 企 获 业 取 划 招 型 标 标 文 准 件 规 和 定 提 的 交 通 投 知 标 》 保 （ 证 工 金 信 ， 部 在 联 制 企 作 业 数 〔 据 20 电 11 文 〕 形 30 式 0号 投 ） 标 中 文 的 件 “ 时 建 ， 筑 投 业 标 ” 人 划 名 型 称 标 应 准 填 为 写 准 联 ， 合 投 体 标 牵 人 头 应 人 提 名 供 称 中 。 小 如 民 未 营 按 企 要 业 求 声 进 明 行 函 投 。 标 （ ， 除 导 技 致 术 投 复 标 杂 文 、 件 存 无 在 法 特 读 殊 取 要 ， 求 由 外 投 ， 标 我 人 省 自 依 行 法 负 必 责 须 。 招 （ 标 4） 的 联 国 合 家 体 投 各 资 方 工 不 程 得 ， 再 施 以 工 自 部 己 分 名 招 义 标 单 控 独 制 或 价 参 在 加 30 其 00 他 万 联 元 合 以 体 下 在 的 同 ， 一 应 标 勾选 4.招标文件的获取： 44..12 凡招有标意人参不加提投供标邮者购，招请标于文 件20服26务-08。-25 00:00 至 2026-09-01 00:00 （电子招标文件的获取，不受获取截止时间限制，任何时间段均可获取），登录宜宾市公共资源交易信息网（http://ggzy.yibin.gov.cn/），凭数字证书和密码获取招标文件及其它招标资料（含招标电子技术标文件，格式为*.ZBJ、招标电子商务标文件，格式为*.ZBS、图纸）。另，可通过本项目招标公告附件，免费获取招标文件。 5.投标文件的递交： 55投5 .. . 12 3标 投电 逾人 标子 期应 文投 递在 件标 交投 递文 的标 交件 或截 的递 者止 截交 未时 止方 按间 时式 指前 间： 定在 （ 方线 投 式递 标 递交 截 交经 止 或投 时 未标 间 送人 ， 达数 下 指字 同 定证 ） 地书 为 点加 的 2 密 0 投 26 的标 -0 数 9 文 - 据 1 件 4 电 0 ， 9 文 : 招 00 形 。 标式人投不标予文受件理。。 6.发布公告的媒介： 本次招标公告在《全国公共资源交易平台（四川省）》和 宜宾市公共资源交易信息、 (公告发布的其它媒介名称）上发布。 信息来源:https://www.chinapipe.net/project/d3079253.html 网 cqdingjiu 2026.08.25 10:30:25 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>该项目包括农业种植园的设计和施工，涉及土地平整、灌溉系统安装、排水管道铺设等工程。
+          <t>该项目包括农业种植园的设计和施工，涉及土地平整、灌溉系统安装、道路建设以及相关配套设施的完善。
 https://www.chinapipe.net/project/d3079253.html</t>
         </is>
       </c>
@@ -2141,7 +2145,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>农业种植园, 设计施工总承包, 排水管道, 灌溉系统</t>
+          <t>农业种植园, 设计施工总承包, 管道, 阀门, 补偿器</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2207,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>彭州市龙安村片区城中村改造项目施工/标段招标公告 彭州市龙安村片区城中村改造项目施工/标段 招标公告 1．招标条件 网 1.1本招标项目彭州市龙安村片区城中村改造项目施工/标段已由彭州市发展和改革局以彭发改可研〔2025〕6号批 准建设，项目业主为彭州市昕宸兴建设发展有限公司，建设资金来自国家投资-政府投资，项目出资比例为100%， 招标人为彭州市昕宸兴建设发展有限公司。项目已具备招标条件，现进行公开招标。 务 1.2本招标项目由彭州市发展和改革局核准（招标事项核准文号为彭发改可研〔2025〕6号）的招标组织形式为委 托招标。招标人选择的招标代理机构是四川明清工程咨询有限公司。 本标段行政监督部门为彭州市住房和城乡建设局，采用“评定分离”方式进行评标定标。 商 2．项目概况与招标范围 道 2.1 项目地点：彭州市天彭街道。 2.2 建设规模及内容：彭州市龙安村片区城中村改造项目主要改造范围为彭州市天彭街道，具体范围为东至三环 路，南至黄龙东路，西至滨河北路，北至景瑞路。本次征拆范围约2102.3亩，包括集体土地约 2054.97亩，国有土 管 地约47.33亩；总改造户数约1241 户，涉及拆迁安置人员3712人，拟拆迁建筑面积7.46万平方米。项目新建配套道 路长约3000米，建设内容包括道路工程、市政管线工程(给水工程、雨水工程、污水工程、燃气工程、电力工程、 通讯工程)、交安工程、照明及多杆合一工程、绿化景观等。 2.3 招标范围：本项目施国工图纸及工程量清单所示范围内的全部工程内容直至竣工验收合格及整体移交、质量缺 陷责任期内的缺陷修复、保修等相关工作。 2.4 计划工期：450日历天。 中 2.5标段划分：本次招标为 1 个标段。 3．投标人资格要求 3.1 本次招标要求投标人： 3.1.1须具有国家建设行政主管部门颁发的市政公用工程施工总承包一级及以上资质的单位； 3.1.2信誉要求：不存在投标人须知第1.4.3项规定的限制投标的情形； 3.1.3所有投标人（无资质企业除外）应具有针对本标段的《成都市建设领域市场主体基础信息网络登记表》（如 投标人为联合体，则联合体所有成员均应具有）、《成都市建设领域从业人员基础信息网络登记表》（如投标 人为联合体，则联合体所有成员均应具有）。 3.1.4 拟派项目经理（项目负责人）具有市政公用工程专业一级或以上注册建造师证书，须具备有效的安全生产 考核合格B证，/（业绩要求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.1.5财务要求：无财务要求； 3.1.6类似工程业绩要求： 近年（2023年01月01日至投标截止时间，不少于3年）已完成的项目共不少于1个类似工程业绩。 类似工程业绩是指:单个合同金额14000万元及以上的市政公用工程施工业绩(若为联合体投标的，联合体任意一方 提供业绩均可) 3.2本次招标接受联合体投标。 联合体投标的，应满足下列要求：须具有国家建设行政主管部门颁发的市政公用工程施工总承包一级及以上资 质的单位作为联合体牵头人。联合体成员（含联合体牵头人）家数须不超过2家。 联合体需符合有关联合体投标的规定和要求，并提交了联合体协议，明确联合体网牵头人和各方权利义务。 3.3 各投标人均可就上述1个标段投标，可中标的标段数量为1个。 务 4．招标文件的获取 4.1凡有意参加投标者，请于2026年08月25日起，在成都市公共资源电子交易云平台(www.cdggzy.com）（以下简称 “电子交易云平台”）免费下载招标资料（招标文件及相商关资料），获得“拟投标项目回执”。 4.2招标人不提供 邮购招标文件服务。 5．投标文件的递交 道 5.1 投标文件递交的截止时间（投标截止时间，下同）为2026年09月16日09时30分，招标人或其委托代理机构，以 及已在投标截止时间前按规定上传投标文件的投标人，均应在开标当日投标截止时间前登录不见面开标系统 （网址：www.cdggzy.com），录入相关人员姓名、电话等基本信息。投标人未按时登录不见面开标系统，错过开 管 标解密时间的，由投标人自行承担不利后果。 5.2 投标人应在解密开始后30分钟内在线完成投标文件解密。投标文件未能在规定时间内成功解密的，视为投标 人未在规定时间内提交投标文件，由投标人自行承担责任。不见面开标项目不接受投标人现场递交光盘等形式 的投标文件，不接受投国标人现场解密投标文件。 6．发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）（网址：http://ggzyjy.sc.gov.cn/）上发布。 中 7．行政监督部门 单位名称：彭州市住房和城乡建设局 联系电话：028-83701718 8. 联系方式 招标人：彭州市昕宸兴建设发展有限公司 地 址：彭州市天彭街道龙塔北路30号 邮 编：/ 联系人：张女士 电 话：028-88504118 传 真：/ 电子邮件：/ 网 址：/ 开户银行：/ 账 号：/ 招标代理机构：四川明清工程咨询有限公司 网 地 址：成都市二环路南三段5号人南大厦B座2楼 邮 编：/ 务 联系人：侯先生 项目负责人：滕欣燕 商 电 话：028-85581109 传 真：/ 道 电子邮件：/ 网 址：/ 管 开户银行：/ 账 号：/ 国 信息来源:https://www.chinapipe.net/project/d3079250.html 中 cqdingjiu 2026.08.25 09:25:46</t>
+          <t>彭州市龙安村片区城中村改造项目施工/标段招标公告 彭州市龙安村片区城中村改造项目施工/标段 招标公告 1．招标条件 网 1.1本招标项目彭州市龙安村片区城中村改造项目施工/标段已由彭州市发展和改革局以彭发改可研〔2025〕6号批 准建设，项目业主为彭州市昕宸兴建设发展有限公司，建设资金来自国家投资-政府投资，项目出资比例为100%， 招标人为彭州市昕宸兴建设发展有限公司。项目已具备招标条件，现进行公开招标。 务 1.2本招标项目由彭州市发展和改革局核准（招标事项核准文号为彭发改可研〔2025〕6号）的招标组织形式为委 托招标。招标人选择的招标代理机构是四川明清工程咨询有限公司。 本标段行政监督部门为彭州市住房和城乡建设局，采用“评定分离”方式进行评标定标。 商 2．项目概况与招标范围 道 2.1 项目地点：彭州市天彭街道。 2.2 建设规模及内容：彭州市龙安村片区城中村改造项目主要改造范围为彭州市天彭街道，具体范围为东至三环 路，南至黄龙东路，西至滨河北路，北至景瑞路。本次征拆范围约2102.3亩，包括集体土地约 2054.97亩，国有土 管 地约47.33亩；总改造户数约1241 户，涉及拆迁安置人员3712人，拟拆迁建筑面积7.46万平方米。项目新建配套道 路长约3000米，建设内容包括道路工程、市政管线工程(给水工程、雨水工程、污水工程、燃气工程、电力工程、 通讯工程)、交安工程、照明及多杆合一工程、绿化景观等。 2.3 招标范围：本项目施国工图纸及工程量清单所示范围内的全部工程内容直至竣工验收合格及整体移交、质量缺 陷责任期内的缺陷修复、保修等相关工作。 2.4 计划工期：450日历天。 中 2.5标段划分：本次招标为 1 个标段。 3．投标人资格要求 3.1 本次招标要求投标人： 3.1.1须具有国家建设行政主管部门颁发的市政公用工程施工总承包一级及以上资质的单位； 3.1.2信誉要求：不存在投标人须知第1.4.3项规定的限制投标的情形； 3.1.3所有投标人（无资质企业除外）应具有针对本标段的《成都市建设领域市场主体基础信息网络登记表》（如 投标人为联合体，则联合体所有成员均应具有）、《成都市建设领域从业人员基础信息网络登记表》（如投标 人为联合体，则联合体所有成员均应具有）。 3.1.4 拟派项目经理（项目负责人）具有市政公用工程专业一级或以上注册建造师证书，须具备有效的安全生产 考核合格B证，/（业绩要求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.1.5财务要求：无财务要求； 3.1.6类似工程业绩要求： 近年（2023年01月01日至投标截止时间，不少于3年）已完成的项目共不少于1个类似工程业绩。 类似工程业绩是指:单个合同金额14000万元及以上的市政公用工程施工业绩(若为联合体投标的，联合体任意一方 提供业绩均可) 3.2本次招标接受联合体投标。 联合体投标的，应满足下列要求：须具有国家建设行政主管部门颁发的市政公用工程施工总承包一级及以上资 质的单位作为联合体牵头人。联合体成员（含联合体牵头人）家数须不超过2家。 联合体需符合有关联合体投标的规定和要求，并提交了联合体协议，明确联合体网牵头人和各方权利义务。 3.3 各投标人均可就上述1个标段投标，可中标的标段数量为1个。 务 4．招标文件的获取 4.1凡有意参加投标者，请于2026年08月25日起，在成都市公共资源电子交易云平台(www.cdggzy.com）（以下简称 “电子交易云平台”）免费下载招标资料（招标文件及相商关资料），获得“拟投标项目回执”。 4.2招标人不提供 邮购招标文件服务。 5．投标文件的递交 道 5.1 投标文件递交的截止时间（投标截止时间，下同）为2026年09月16日09时30分，招标人或其委托代理机构，以 及已在投标截止时间前按规定上传投标文件的投标人，均应在开标当日投标截止时间前登录不见面开标系统 （网址：www.cdggzy.com），录入相关人员姓名、电话等基本信息。投标人未按时登录不见面开标系统，错过开 管 标解密时间的，由投标人自行承担不利后果。 5.2 投标人应在解密开始后30分钟内在线完成投标文件解密。投标文件未能在规定时间内成功解密的，视为投标 人未在规定时间内提交投标文件，由投标人自行承担责任。不见面开标项目不接受投标人现场递交光盘等形式 的投标文件，不接受投国标人现场解密投标文件。 6．发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）（网址：http://ggzyjy.sc.gov.cn/）上发布。 中 7．行政监督部门 单位名称：彭州市住房和城乡建设局 联系电话：028-83701718 8. 联系方式 招标人：彭州市昕宸兴建设发展有限公司 地 址：彭州市天彭街道龙塔北路30号 邮 编：/ 联系人：张女士 电 话：028-88504118 传 真：/ 电子邮件：/ 网 址：/ 开户银行：/ 账 号：/ 招标代理机构：四川明清工程咨询有限公司 网 地 址：成都市二环路南三段5号人南大厦B座2楼 邮 编：/ 务 联系人：侯先生 项目负责人：滕欣燕 商 电 话：028-85581109 传 真：/ 道 电子邮件：/ 网 址：/ 管 开户银行：/ 账 号：/ 国 信息来源:https://www.chinapipe.net/project/d3079250.html 中 cqdingjiu 2026.08.25 10:30:25</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2217,7 +2221,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>市政公用工程施工, 道路工程, 市政管线工程, 拆迁改造</t>
+          <t>市政公用工程, 城中村改造, 道路工程, 市政管线工程</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2268,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>安装引水管网31.68km，管材采用PE100管(1.6MPa)，管径dn225~dn50；输配水管网59.4km，管材采用PPR管，管径dn25；安装智能化水表1663块。</t>
+          <t>安装引水管网31.68km，管材采用PE100管(1.6MPa)，管径dn225~dn50；安装输配水管网59.4km，管材采用PPR管，管径dn25；安装智能化水表1663块。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2279,12 +2283,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>喜德县2026年饮水水质提升工程(维修养护)项目招标计划公告 喜德县2026年饮水水质提升工程（维修养护）项目招标计划公告 喜德县发展改革和经济信息化局关 于喜德县2026年饮水水质提升工程 招标项目 喜德县2026年饮水水质提升工程（维 项目批准文件及文号 （维修养护）项目可行性研究报告 名称 修养护）项目 （如有） （代项目建议书）的批复(喜发改 经信函【2026】133号) 招标人 喜德县水利局 联系人及联系方式 阿网苦:13795644938 估算总投资 790.16 项目分类 水利工程 （元） (1)引水建筑物:安装引水管网31.68km，管材采用PE100管(1.6MPa)，管径dn225~dn50;其 务 招标项目 中dn225PE100管(1.6MPa)3.95km,dn125PE100管(1.6MPa)6.45km,dn90PE100 概况 管(1.6MPa)2.53km,dn75PE100管(1.6MPa)6.4km，dn50PE100管(1.6MPa)12.35km;(2)输配水建筑物:安装 输配水管网59.4km，管材采用PPR管，管径dn25。(3)智慧水务:安装智能化水表1663块。 序号 招标内容 商投标人主要资格条件要求 预计招标时间 拟招标内 喜德县2026年饮水水质提升工程（维 以发布的招标公告、招标文件为 容 1 2026-09-30 00:00:00 修养护）项目施工 准 备注：提前发布的招标计划内容仅供各方主体道提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3079246.html cqdingjiu 2026.08.25 09:25:46 管 国 中</t>
+          <t>喜德县2026年饮水水质提升工程(维修养护)项目招标计划公告 喜德县2026年饮水水质提升工程（维修养护）项目招标计划公告 喜德县发展改革和经济信息化局关 于喜德县2026年饮水水质提升工程 招标项目 喜德县2026年饮水水质提升工程（维 项目批准文件及文号 （维修养护）项目可行性研究报告 名称 修养护）项目 （如有） （代项目建议书）的批复(喜发改 经信函【2026】133号) 招标人 喜德县水利局 联系人及联系方式 阿网苦:13795644938 估算总投资 790.16 项目分类 水利工程 （元） (1)引水建筑物:安装引水管网31.68km，管材采用PE100管(1.6MPa)，管径dn225~dn50;其 务 招标项目 中dn225PE100管(1.6MPa)3.95km,dn125PE100管(1.6MPa)6.45km,dn90PE100 概况 管(1.6MPa)2.53km,dn75PE100管(1.6MPa)6.4km，dn50PE100管(1.6MPa)12.35km;(2)输配水建筑物:安装 输配水管网59.4km，管材采用PPR管，管径dn25。(3)智慧水务:安装智能化水表1663块。 序号 招标内容 商投标人主要资格条件要求 预计招标时间 拟招标内 喜德县2026年饮水水质提升工程（维 以发布的招标公告、招标文件为 容 1 2026-09-30 00:00:00 修养护）项目施工 准 备注：提前发布的招标计划内容仅供各方主体道提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3079246.html cqdingjiu 2026.08.25 10:30:25 管 国 中</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>安装引水管网31.68km，管材采用PE100管(1.6MPa)，管径dn225~dn50；输配水管网59.4km，管材采用PPR管，管径dn25；安装智能化水表1663块。
+          <t>安装引水管网31.68km，管材采用PE100管(1.6MPa)，管径dn225~dn50；安装输配水管网59.4km，管材采用PPR管，管径dn25；安装智能化水表1663块。
 https://www.chinapipe.net/project/d3079246.html</t>
         </is>
       </c>
@@ -2341,7 +2345,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>估算总投资9000000.000000元</t>
+          <t>估算总投资900万元人民币</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2351,7 +2355,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>西充县2026年宜居宜业和美乡村建设项目招标计划公告 西充县2026年宜居宜业和美乡村建设项目招标计划公告 拟招标项目名称 西充县2026年宜居宜业和美乡村建设项目 项目批准文件 / 项目批准文号 / 冯先 招标人（建设单位） 西充县农业农村局 联系人及联系方式 生:18281776606 网 招标代理机构 / 联系人及联系方式 / 估算总投资（元） 9000000.000000 项目分类 农业综合 新建及整治灌溉渠系、实施土地平整、，修建机耕道路、新建及改造蓄水池等水源工程， 招标项目概况 务 新建标准化钢架大棚铺设微喷灌管道，配套建设水肥一体化系统等。 拟招标内容 投标人主要资格 序号 招标内容 预商计招标时间 条件要求 1 监理 2026-09-24 00:00:00 2 施工 2026-09-24 00:00:00 道 3 货物和设备采购 2026-09-24 00:00:00 4 设计 2026-09-24 00:00:00 注:提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招标人 最终发布的招标公告和招标文件为管准。 信息来源:https://www.chinapipe.net/project/d3079243.html cqdingjiu 2026.08.25 09:25:46 国 中</t>
+          <t>西充县2026年宜居宜业和美乡村建设项目招标计划公告 西充县2026年宜居宜业和美乡村建设项目招标计划公告 拟招标项目名称 西充县2026年宜居宜业和美乡村建设项目 项目批准文件 / 项目批准文号 / 冯先 招标人（建设单位） 西充县农业农村局 联系人及联系方式 生:18281776606 网 招标代理机构 / 联系人及联系方式 / 估算总投资（元） 9000000.000000 项目分类 农业综合 新建及整治灌溉渠系、实施土地平整、，修建机耕道路、新建及改造蓄水池等水源工程， 招标项目概况 务 新建标准化钢架大棚铺设微喷灌管道，配套建设水肥一体化系统等。 拟招标内容 投标人主要资格 序号 招标内容 预商计招标时间 条件要求 1 监理 2026-09-24 00:00:00 2 施工 2026-09-24 00:00:00 道 3 货物和设备采购 2026-09-24 00:00:00 4 设计 2026-09-24 00:00:00 注:提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招标人 最终发布的招标公告和招标文件为管准。 信息来源:https://www.chinapipe.net/project/d3079243.html cqdingjiu 2026.08.25 10:30:26 国 中</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2365,7 +2369,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>重庆, 管材招标</t>
+          <t>2026年, 宜居宜业和美乡村建设项目, 农业综合, 灌溉渠系, 土地平整, 机耕道路, 蓄水池, 标准化钢架大棚, 微喷灌管道, 水肥一体化系统</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2431,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>乐山市金口河区污水处理厂扩容及配套污水管网更新改造项目设计招标公告 1. 招标条件 1.1本招标项目 乐山市金口河区污水处理厂扩容及配套污水管网更新改造项目 (项目名称)已由 乐山市金口 河区发展和改革局 (项目审批、核准或备案机关名称)以 金发改投资〔2026〕73号 （批文名称及编号）批准 建设，项目业主为 乐山市金口河区住房和城乡建设局 ， 建设资金来自 拟申请地方政府专项债券资金及地 方财政配套资金 （资金来源），项目出资比例为 100% ，招标人为 乐山市金口河区住房和城乡建设局 。 项目已具备招标条件，现对该项目的设计进行公开招标。 网 1.2本招标项目由 乐山市金口河区发展和改革局 （核准机关名称）核准（招标事项核准文号为 金发改投资 〔2026〕73号 ）的招标组织形式为 委托招标 。 招标人选择的招标代理机构是 四川华景工程项目管理 有限公司。 务 2. 项目概况与招标范围 1、建设地点：乐山市金口河区。 商 2、规模及投资额：对金口河区生活污水处理设备及配套管网进行扩容改造。新建 2000 立方米调节池、改造污水 提升泵站、生化处理池，并完善双路供电系统；更新改造进出水在线监测设备，增设各工艺段实时监测系统， 升级污水自控系统、搭建智慧水务平台，同步道实施 4 座单座库容 1000 立方米二沉池提质改造，改扩建化验室约 2000 平方米、配套新增化验设备，同时改造 15 公里厂内外污水压力管网，将原管径 DN300扩容至 DN600-1200， 将原有处理规模由 5000 吨/日提升至 6000 吨/日。项目总投资约：7000 万元。 3、设计服务期限：500日历天。 管 4、招标范围：本项目用地范围内的方案设计、初步设计、施工图设计、工程设计概预算及后续服务（包括但不 限于预算评审配合、相关审查备案、技术交底、施工期间设计驻场、设计变更、参与主体及竣工验收、竣工结 算配合等相关设计服务）。 国 5、标段划分：设计 1 个标段。 （说明本次招标项目的建设地点、规模及投资额、设计服务期限、招标范围、标段划分及标段投资额等）。 中 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质要求： 具备行政主管部门颁发的工程设计市政行业（排水工程）乙级及以上资质和工程设计建筑行业 (建筑工程)乙级及以上资质 。 3.1.2业绩要求： 近年（ 2023年01月01日 至投标截止时间，不少于3年） 已完成或新承接或正在设计 不少于 1 （1 至3个）个类似项目。类似项目是指: 项目总投资不低于 4000 万元的市政工程类设计业绩 。 3.1.3项目负责人的资格要求：具有 注册公用设备工程师（给水排水） 证书 / （业绩要求） ，须为本单 位人员（若为联合体投标，须为联合体牵头单位人员）。 3.2本次招标 接受 联合体投标。 联合体投标的，应满足下列要求： 3.2.1 联合体成员(含牵头单位)不得 超过 2 家；3.2.2 联合体各方签订联合体协议书，明确联合体牵头人（由具有工程设计市政行业（排水工程）乙级 及以上资质的设计单位作为牵头人）和各方的权利和义务；3.2.3 由同一专业的单位组成的联合体，按照资质等 级较低的单位确定资质等级；3.2.4 联合体各方不得再以自己名义单独或参加其他联合体在同一标段中投标；3.2.5 由联合体牵头人负责本项目投标报名，投标文件编制、签署、授权、承诺、盖章、递交等。 4. 技术成果经济补偿 本次招标对未中标人投标文件中的技术成果 不给予 经济补偿。 5. 招标文件的获取 5.1 凡有意参加投标者，请于 2026年08月25日 至 2026年08月29日 登陆乐山市公共资源交易服务平台官网 （http://www.lsggzy.com.cn/），在首页点击“用户登录”入口。通过数字证书免费下载招标资料（招标文件、技 术资料等）。 5.2 招标人不提供招标文件获取的其他方式。 6. 投标文件的递交 网 投标文件递交的截止时间（投标截止时间，下同）为 2026年09月16日 09时00分 投标人应在截止时间前通过乐 山市公共资源交易服务平台官网（http://www.lsggzy.com.cn/），在首页点击“用户登录”入口，凭单位CFCA数 字证书登录在线递交经投标人数字证书签名制作的数据加密电子投标文件。 务 7. 发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省）》和 《全国公共资源交易平台（四川省·乐山 市）》 (公告发布的其它媒介名称）上发布。 商 8. 行政监督部门 单位名称： 乐山市金口河区发展和改革局 道 联系电话： 0833-2714918 9. 联系方式 管 招 标 人： 乐山市金口河区住房和城乡建设局 地 址： 乐山市金口河区春和路 123 号 国 邮 编： 614700 联 系 人： 姜老师 中 电 话： 0833-5022619 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / 招标代理机构： 四川华景工程项目管理有限公司 地 址： 成都蛟龙港双流园区海滨广场11号楼1603室 邮 编： 610037 联 系 人： 田老师 项目负责人： 田秀陆 电 话： 028-60613388 传 真： / 电子邮件： / 网 址： / 开户银行： / 网 账 号： / 务 2026年08月24日 注： 商 （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不 得作为资质要求。 道 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工 程相应指标，类似项目业绩的定义应明确，用语准确无歧义。 类似业绩类型参照住建部总承包资质和专业资 质的分类标准设定，不得设定特定行业的业绩。 管 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受 投标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 信息来源:https://www.c国hinapipe.net/project/d3079240.html cqdingjiu 2026.08.25 09:25:46 中</t>
+          <t>乐山市金口河区污水处理厂扩容及配套污水管网更新改造项目设计招标公告 1. 招标条件 1.1本招标项目 乐山市金口河区污水处理厂扩容及配套污水管网更新改造项目 (项目名称)已由 乐山市金口 河区发展和改革局 (项目审批、核准或备案机关名称)以 金发改投资〔2026〕73号 （批文名称及编号）批准 建设，项目业主为 乐山市金口河区住房和城乡建设局 ， 建设资金来自 拟申请地方政府专项债券资金及地 方财政配套资金 （资金来源），项目出资比例为 100% ，招标人为 乐山市金口河区住房和城乡建设局 。 项目已具备招标条件，现对该项目的设计进行公开招标。 网 1.2本招标项目由 乐山市金口河区发展和改革局 （核准机关名称）核准（招标事项核准文号为 金发改投资 〔2026〕73号 ）的招标组织形式为 委托招标 。 招标人选择的招标代理机构是 四川华景工程项目管理 有限公司。 务 2. 项目概况与招标范围 1、建设地点：乐山市金口河区。 商 2、规模及投资额：对金口河区生活污水处理设备及配套管网进行扩容改造。新建 2000 立方米调节池、改造污水 提升泵站、生化处理池，并完善双路供电系统；更新改造进出水在线监测设备，增设各工艺段实时监测系统， 升级污水自控系统、搭建智慧水务平台，同步道实施 4 座单座库容 1000 立方米二沉池提质改造，改扩建化验室约 2000 平方米、配套新增化验设备，同时改造 15 公里厂内外污水压力管网，将原管径 DN300扩容至 DN600-1200， 将原有处理规模由 5000 吨/日提升至 6000 吨/日。项目总投资约：7000 万元。 3、设计服务期限：500日历天。 管 4、招标范围：本项目用地范围内的方案设计、初步设计、施工图设计、工程设计概预算及后续服务（包括但不 限于预算评审配合、相关审查备案、技术交底、施工期间设计驻场、设计变更、参与主体及竣工验收、竣工结 算配合等相关设计服务）。 国 5、标段划分：设计 1 个标段。 （说明本次招标项目的建设地点、规模及投资额、设计服务期限、招标范围、标段划分及标段投资额等）。 中 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质要求： 具备行政主管部门颁发的工程设计市政行业（排水工程）乙级及以上资质和工程设计建筑行业 (建筑工程)乙级及以上资质 。 3.1.2业绩要求： 近年（ 2023年01月01日 至投标截止时间，不少于3年） 已完成或新承接或正在设计 不少于 1 （1 至3个）个类似项目。类似项目是指: 项目总投资不低于 4000 万元的市政工程类设计业绩 。 3.1.3项目负责人的资格要求：具有 注册公用设备工程师（给水排水） 证书 / （业绩要求） ，须为本单 位人员（若为联合体投标，须为联合体牵头单位人员）。 3.2本次招标 接受 联合体投标。 联合体投标的，应满足下列要求： 3.2.1 联合体成员(含牵头单位)不得 超过 2 家；3.2.2 联合体各方签订联合体协议书，明确联合体牵头人（由具有工程设计市政行业（排水工程）乙级 及以上资质的设计单位作为牵头人）和各方的权利和义务；3.2.3 由同一专业的单位组成的联合体，按照资质等 级较低的单位确定资质等级；3.2.4 联合体各方不得再以自己名义单独或参加其他联合体在同一标段中投标；3.2.5 由联合体牵头人负责本项目投标报名，投标文件编制、签署、授权、承诺、盖章、递交等。 4. 技术成果经济补偿 本次招标对未中标人投标文件中的技术成果 不给予 经济补偿。 5. 招标文件的获取 5.1 凡有意参加投标者，请于 2026年08月25日 至 2026年08月29日 登陆乐山市公共资源交易服务平台官网 （http://www.lsggzy.com.cn/），在首页点击“用户登录”入口。通过数字证书免费下载招标资料（招标文件、技 术资料等）。 5.2 招标人不提供招标文件获取的其他方式。 6. 投标文件的递交 网 投标文件递交的截止时间（投标截止时间，下同）为 2026年09月16日 09时00分 投标人应在截止时间前通过乐 山市公共资源交易服务平台官网（http://www.lsggzy.com.cn/），在首页点击“用户登录”入口，凭单位CFCA数 字证书登录在线递交经投标人数字证书签名制作的数据加密电子投标文件。 务 7. 发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省）》和 《全国公共资源交易平台（四川省·乐山 市）》 (公告发布的其它媒介名称）上发布。 商 8. 行政监督部门 单位名称： 乐山市金口河区发展和改革局 道 联系电话： 0833-2714918 9. 联系方式 管 招 标 人： 乐山市金口河区住房和城乡建设局 地 址： 乐山市金口河区春和路 123 号 国 邮 编： 614700 联 系 人： 姜老师 中 电 话： 0833-5022619 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / 招标代理机构： 四川华景工程项目管理有限公司 地 址： 成都蛟龙港双流园区海滨广场11号楼1603室 邮 编： 610037 联 系 人： 田老师 项目负责人： 田秀陆 电 话： 028-60613388 传 真： / 电子邮件： / 网 址： / 开户银行： / 网 账 号： / 务 2026年08月24日 注： 商 （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不 得作为资质要求。 道 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工 程相应指标，类似项目业绩的定义应明确，用语准确无歧义。 类似业绩类型参照住建部总承包资质和专业资 质的分类标准设定，不得设定特定行业的业绩。 管 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受 投标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 信息来源:https://www.c国hinapipe.net/project/d3079240.html cqdingjiu 2026.08.25 10:30:26 中</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2437,11 +2441,11 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>污水处理厂扩容, 配套污水管网更新改造, 设计方案, 市政工程, 排水工程</t>
+          <t>污水处理厂扩容, 污水管网更新改造, 市政工程, 设计招标</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2462,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>房建</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2476,39 +2480,31 @@
           <t>四川省</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>德阳市</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>德阳市</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>德阳智能制造产教融合项目</t>
+          <t>与招标内容 道 2.1项目概况 德阳智能制造产教融合项目本项目位于四川省德阳市旌阳区长江西路沿线与天府大道北延线（二环路）交汇处 西北角地块。 建设内容及规模：本工程平时为地下停车场，战时为二等人员掩蔽所，人防工程应建总建筑面 管 积14720.18㎡，（十层及十层以上）+190208*0.025（九层及九层以下埋深小于3m）+655（九层及九层以下埋深大 于3m）人防实际工程总建筑面积14910.15㎡，项目总建筑面积324848㎡，项目合同工期：随土建工程进度。 2.2招标内容 ：详见招标公告附件《招标物资包件清单》，本次招标一包一投。 国 2.3招标内容及包件划分 2.3.1招标内容及包件划分：详见招标公告附件1《招标物资包件清单》，本次招标一包一投。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>未明确提及具体金额</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>消防设施,管道,阀门,管件,电线电缆,照明设备,开关插座,灯具,门窗,卫生洁具,地板材料,墙面材料,装饰材料,五金配件,其他建材</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>中铁十八局集团第五工程有限公司德阳天府旌城(科教片区)B类项目总承包-德阳智能制造产教融合项目总平材料、 装饰装修材料，铝单板材料、铝型材材料公开招标招标公告 招标公告 中铁十八局集团第五工程有限公司德阳天府旌城（科教片区）B类项目总承包-德阳智能制造产教融合项目总平材 料、装饰装修材料，铝单板材料、铝型材材料公开招标 招标编号：CRCC-1805ZB-DYTFXC-2026-08 网 1.招标条件 1.1本项目为中铁十八局集团第五工程有限公司德阳天府旌城（科教片区）B类项目总承包德阳智能制造产教融合 项目施工，项目建设单位为德阳发展城市建设开发有限公司，建设资金已落实。 务 本次招标的招标人为中铁十八局集团第五工程有限公司德阳天府旌城（科教片区）B类项目总承包-德阳智能制造 产教融合项目(以下简称：德阳智能制造产教融合项目）。 根据国家相关文件规定，建设单位、股份公司、集团公司商有关物资管理规定，现对以上项目具备招标条件的施 工物资总平材料、装饰装修、铝单板、铝型材 材料进行公开招标。 2.项目概况与招标内容 道 2.1项目概况 德阳智能制造产教融合项目本项目位于四川省德阳市旌阳区长江西路沿线与天府大道北延线（二环路）交汇处 西北角地块。建设内容及规模：本工程平时为地下停车场，战时为二等人员掩蔽所，人防工程应建总建筑面 管 积14720.18㎡，（十层及十层以上）+190208*0.025（九层及九层以下埋深小于3m）+655（九层及九层以下埋深大 于3m）人防实际工程总建筑面积14910.15㎡，项目总建筑面积324848㎡，项目合同工期：随土建工程进度。 2.2招标内容 ：详见招标公告附件《招标物资包件清单》，本次招标一包一投。 国 2.3招标内容及包件划分 2.3.1招标内容及包件划分：详见招标公告附件1《招标物资包件清单》，本次招标一包一投。 中 2.3.2招标方式：采用国内公开招标方式。 3.招标依据 3.1本次招标的依据为： （1）《中华人民共和国招标投标法》； （2）《中华人民共和国招标投标法实施条例》（国务院第613号令）； （3）《工程建设项目货物招标投标办法》（国家发展改革委等七部委令第27号）； （4）《评标委员会和评标方法暂行规定》（国家发展改革委等七部委令第12号）； （5）《中国铁建股份有限公司物资采购管理规定（试行）》（中国铁建供应链〔2025〕106号）； （6）其他相关法律、法规、规章。 4.投标人资格审查及要求 4.1本次招标资格审查采用资格后审的方式。 4.2本次招标包件号（ZP-01、ZZ-01、LP-01、LC-01、） 要求投标人须具备以下条件： （1）营业范围： 在中华人民共和国境内依法注册，具有独立法人资格、具有招标物资生产或供应经验的生产厂 家 或代理商 ，并且具有合法有效的营业执照； （2）财务能力： 投标人必须是经税务部门注册登记核准的一般纳税人或小规模纳税人，有依法纳税的良好记录， 具有良好的资金财务状况，投标人须提供2024、2025年经会计师事务所审计的财务审计报告及相关报表（财务审 计报告及相关报表需提供扫描件），期间注册的新公司仅需提供成立后的报表（至少需提供最近一年报表） （3） 质量保证能力： 检测机构出具满足国家现行验收标准要求的投标物资质量检验报告。 网 （4） 履约信用：2具有良好的社会信誉，投标人具有良好的社会信誉，不接受存在以下任何一种情况的公司投 标。 ①在“国家企业信用信息公示系统”（https://www.gsxt.gov.cn/index.html）被列入严重违法失信名单和经营异常 务 名单。 ②在“中国执行信息公开网”(http://zxgk.court.gov.cn）被列入失信被执行人。③在纳税信用登记信息系统 （https://12366.chinatax.gov.cn/）被列入纳税信用等级为C、D级的企业。 商 ④在信用中国(https://www.creditchina.gov.cn/?navPage=0）被列入严重失信和经营异常被执行人。 ⑤不接受在最新一期《中国铁建选择合作方风险警示名录》中的供应商以及被采购人列入风险警示合作名录的 供应商。 道 其他要求： 不接受联合体投标。 5.招标文件的获取 管 5.1凡有意参加投标者，请登陆中国铁建云链平台（www.crccep.cn）注册会员，查询拟参与投标包件进行 网上报 名、支付标书费、下载电子招标文件 。 5.2凡有意参加投标者，国请登陆中国铁建云链平台（www.crccep.com）注册会员，查询拟参与投标包件进行网上报 名、下载电子招标文件。招标文件售卖截止时间为：2026年8月24日- 2026年8月2 9日23时59分 。潜在投标人须在 招标文件售卖截止时间前完成中国铁建云链平台（www.crccep.com）注册报名，并申请办理CA锁，用于电子投 标文件的签章、加密及解密（CA办理所需资料及程序详见中国铁建云链平台首页-小鹿课堂-帮助中心-铁建云链 平台数字证书办理流程）， 并在相应时间内 将所需购买包件的招标文件售价足额现金转入到招标组织机构指定 中 银行账户（开户名称：中铁十八局集团有限公司物资集中采购中心；开户银行：交通银行北京西区支行；账号： 99011231018000668621此账号仅用于支付标书款 ， 保证金账号请参照第二章投标人须知前附表中相关内容 ） 在 汇款单上注明投标单位名称（ 产教融合 ）+德阳标书款 及所投 包件号 。 投标人在铁建云链平台报名时 请上传 标书款银行汇款凭证 ，招标组织机构核实标书款后，方可下载标书。 5.3本次招标一包一投，包件划分情况见招标公告附件1《招标物资包件清单》。 5.4招标文件每包件售价见招标公告附件1《招标物资包件清单》 ， 售后不退 。 5.5获取购买招标文件发票的方式：投标人在中国铁建云链平台（www.crccep.cn）自行申请。 6.投标文件的递交 6.1此次招标投标人需制作电子投标文件，并使用CA锁对投标文件进行加密，在递交截止时间前 线上递交投标文 件 ， 电子投标文件命名为 “投标人名称-包件号” 。 6.2投标文件递交截止时间：2026年9月21日10时00分 。 6.3投标文件递交地点：中国铁建云链平台（www.crccep.cn），投标人须登陆该平台，在投标文件递交截止时间 前完成所有投标文件的上传。 投标文件递交截止时间前未完成投标文件传输的，视为放弃投标资格。 6.4如招标人有需求，被评为中标候选人的投标人应无偿提供纸质版投标文件，纸质版投标文件内容须与电子版 文件内容完全一致。 7.开标 7.1电子投标文件的解密 （1）电子投标文件解密时间：2026年9月21日10时00分至11时00分 。 （2）各投标人必须在规定的投标文件解密时间内登录中国铁建云链平台（www.crccep.cn）完成投标文件解密， 如因投标人自身原因导致所递交的投标文件无法在规定的时间内解密的，视为无效投标文件，后果及责任由投 标人自行负责。 8.发布公告的媒介 网 8.1本次招标公告在以下平台同时发布： （1） 中国招标投标公共服务平台(www.cebpubservice.com) 务 （2）中国铁建云链平台（www.crccep.cn） 8.2本次招标安排如有变化，招标人将通过以上平台发布通知。 商 9.现场踏勘 本次招标不统一组织投标人踏勘工地路况，请各潜在投标人自行踏勘。 道 10.招标人信息及相关方联系方式 10.1招标人及联系方式： 管 （1）招标人： 中铁十八局集团第五工程有限公司德阳天府旌城（科教片区）B类项目总承包-德阳智能制造产教 融合项目 联系人： 徐广占13821179612 国 10.2招标组织单位及联系方式 招标组织单位： 中铁十八局集团有限公司物资集中采购中心 中 地址：天津市津南区大沽南路中铁十八局东区集采中心 招标文件答疑联系人： 苍宇 电话：13672001117 邮箱：wbtaozi1983@126.com 铁建云链平台技术支持：400-6296-888 2026年8月2 4日 附件1：（包件号：ZP-01） 物 招标 投标 招标人 资 计量 包件数 文件 保证金 序号 包件号 规格型号 名称 名 单位 量 售价 （万 称 （元） 元） 中铁十 八局集 团第五 工程有 限公司 防 德阳天 火 府旌城 电 1 （科教 ZP-01 FGQJ-P100×100mm-F1 米 7.63 500 1 5 缆 片区）B 桥 类项目 网 架 总承包- 德阳智 能制造 产教融 务 合项目 防火电 2 FGQJ-P150×100mm-F1 米 110.00 缆桥架 商 防火电 3 FGQJ-P200×100mm-F1 米 198.39 缆桥架 防火电 4 FGQJ-P300×100mm-F1 米 64.84 缆桥架 道 防火电 5 FGQJ-P300×150mm-F1 米 12.24 缆桥架 防火电 6 FGQJ-P300×200mm-F2 米 5.00 管 缆桥架 钢制槽 7 式电缆 100×100mm 米 264.09 桥架 国 钢制槽 8 式电缆 200×100mm 米 91.68 桥架 钢制中槽 9 式电缆 200×150mm 米 80.19 桥架 钢制槽 10 式电缆 400×200mm 米 22.38 桥架 钢制槽 11 式电缆 300×150mm 米 131.96 桥架 铝合金 12 电缆桥 LQJ-C-A-100×100mm-P 米 57.05 架 铝合金 13 电缆桥 LQJ-C-A-200×100mm-P 米 31.11 架 铝合金 14 电缆桥 LQJ-C-A-300×100mm-P 米 50.19 架 热镀锌 15 金属线 100×100mm 米 480.28 槽 JD 16 G DN25 米 263.64 管 热镀锌 17 金属线 200×100mm 米 59.68 槽 网 18 JDG管 DN20 米 22523.05 19 JDG管 DN32 米 350.62 电气配 20 SC钢镀锌DN50 米 44.64 务 管 LED感应 21 220V 12W 套 44.00 灯 商 LED吸顶 22 220V 1×8W 套 16.00 灯 LED吸顶 23 220V 1×8W 套 10.00 灯 道 LED单管 24 220V 16W 套 12.00 灯 LED单管 25 220V 16W 套 93.00 管 灯 LED单管 26 220V 16W 套 22.00 灯 LED双管 国 27 220V 2×16W 套 28.00 灯 LED单管 28 220V 16W 套 2.00 灯 中 29 LED壁灯 220V 2×13W 套 28.00 30 LED筒灯 220V 5W 个 3.00 LED吸顶 31 220V 9W 个 1.00 灯 32 LED筒灯 220V 9W 个 45.00 LE D 33 220V 7W 个 40.00 筒 灯 34 LED筒灯 220V 5W 个 61.00 35 LED筒灯 220V 7W 个 35.00 36 LED筒灯 220V 9W 个 2.00 37 LED筒灯 220V 9W 个 15.00 38 LED筒灯 220V 12W 个 8.00 LED天棚 39 220V 30W 套 168.00 信号灯 40 LED筒灯 220V 15W 个 144.00 41 LED筒灯 220V 20W 个 64.00 42 LED筒灯 220V 15W 个 23.00 43 照明灯 220V 300W 个 48.00 44 照明灯 220V 150W 个 168.00 45 灯盘 1200×200mm 28W 套 76.00 46 灯盘 1200×100mm 18W 套 74.00 47 灯盘 600×600mm 32W 套 10.00 网 普通开 48 单联单控感应250V 10A 个 15.00 关 普通开 49 双联单控暗装250V 10A 个 70.00 关 务 普 通 50 单联单控暗装250V 10A 个 57.00 开 关商 暗装式 51 单相二、三极五孔250V 10A 个 910.00 插座 普通开 道 52 三联单控250V 10A 个 62.00 关 暗装式 53 单相二、三孔250V 15A 个 910.00 插座 管 空调开 54 MB1-63/3P D16 套 30.00 关箱 暗装式 55 三孔暗装250V 20A 个 11.00 插座 国 暗装式 56 单相二、三极250V 10A 个 77.00 插座 暗装式 57 中防水双联二三极250V 10A 个 41.00 插座 暗装式 58 五孔220V 10A 个 2.00 插座 等电位 59 300×200×120mm 个 9.00 端子箱 无线远 60 DN65 个 1.00 传水表 等电位 61 联结端 MEB 300×200×120mm 套 10.00 子箱 无线远 62 DN80 个 1.00 传水表 无线远 63 DN50 个 14.00 传水表 64 闸阀 Z手动41W-16P DN65 个 4.00 65 截止阀 J手动11W-16T DN15 个 8.00 66 闸阀 Z手动41H-16Q DN50 个 2.00 截 67 止 J手动11W-16T DN20 个 19.00 阀 68 截止阀 J手动11W-16T DN25 个 13.00 69 截止阀 J手动11W-16T DN50 个 9.00 70 止回阀 H手动14W-16T DN15 个 18.00 71 止回阀 H手动14W-16P DN20 个 2.00 72 减压阀 DN65 1.6MPa 个 1.00 网 73 减压阀 DN50 1.6MPa 个 11.00 74 减压阀 DN80 1.6MPa 个 1.00 铸铁自 务 75 动排气 DN25 1.6MPa 个 13.00 阀 衬塑钢 76 Q235B DN15×3mm 米 70.00 管 商 衬塑钢 77 Q235B DN20×2.2mm 米 36.00 管 衬塑钢 道 78 Q235B DN50×3mm 米 165.00 管 衬塑钢 79 Q235B DN65×3.5mm 米 175.00 管 管 PPR给水 80 DN15 1.5mm 米 367.81 管 衬塑钢 81 Q235B DN80×4mm 米 65.00 管 国 PPR给水 82 DN20 1.5mm 米 60.40 管 PPR给水 83 中DN32 1.5mm 米 23.35 管 PP R给 84 DN25 1.5mm 米 244.63 水 管 PPR给水 85 DN40 3.2mm 米 57.08 管 PPR给水 86 DN50 3mm 米 70.03 管 PPR给水 87 DN65 3mm 米 9.57 管 PPR给水 88 DN15 2mm 米 83.49 管 PPR给水 89 DN20 2mm 米 6.88 管 橡塑隔 平 90 声保温 500×40×20mm 方 5.00 材料 米 储水式 91 电热水 50L 2.2kW 台 15.00 器 92 铸铁管 DN75 米 10.00 93 铸铁管 DN50 米 41.79 94 铸铁管 DN100 米 276.85 95 UPVC管 DN75×3mm 米 51.14 96 铸铁管 DN150 米 51.32 网 97 UPVC管 DN50×2.5mm 米 200.46 98 UPVC管 DN150×3.5mm 米 36.53 99 UPVC管 DN100×3.2mm 米 516.29 务 100 地漏 不锈钢DN100其他直通式 个 2.00 地 101 不锈钢DN50内插式其他 个 68.00 漏 商 102 地漏 塑料DN50直通式其他 个 60.00 103 地漏 塑料DN100水封式直通式 个 1.00 铸铁漏 104 DN200 道个 12.00 斗 铸铁清 105 DN150 个 3.00 扫口 87型雨水 管 106 B-GB-200mm-A-Ⅰ 个 3.00 斗 87型雨水 107 B-GB-100mm-A-Ⅰ 个 20.00 斗 国 108 防火阀 FHF W-Y-200×320mm 个 1.00 109 防火阀 FHF W-Y-200×200mm 个 8.00 110 防火阀 FHF S-K-320×250mm 个 4.00 中 111 防火阀 FHF S-K-320×200mm 个 4.00 112 防火阀 FHF S-K-400×320mm 个 1.00 113 防火阀 FHF S-K-400×200mm 个 1.00 114 防火阀 FHF S-K-500×250mm 个 2.00 115 防火阀 FHF W-K-630×250mm 个 1.00 116 防火阀 FHF S-K-500×320mm 个 5.00 117 防火阀 FHF W-K-600×500mm 个 1.00 铝合金 118 单层百 200×200mm 个 1.00 叶风口 单层百 叶风口 119 150×150mm 个 26.00 带调节 阀 单层百 叶风口 120 200×150mm 个 4.00 带调节 阀 单层百 叶风口 121 200×200mm 个 82.00 带调节 阀 热镀锌 平 122 钢板风 0.5mm 方 637.38 管 米 热镀锌 平 123 钢板风 1mm 方 100.00 网 管 米 热镀锌 平 124 钢板风 0.6mm 方 341.77 管 米 务 热镀锌 平 125 钢板风 0.75mm 方 600.00 管 米 商 绝热用 平 126 玻璃棉 11kg/m1100×3000×40mm A1 方 48.87 毡 米 板式平 道 127 DN100 PN16 个 10.00 焊法兰 板式平 128 DN150 PN16 个 10.00 焊法兰 管 板式平 129 DN200 PN16 个 10.00 焊法兰 130 闸阀 Z手动41W-16P DN200 个 1.00 131 闸阀 Z手动国41W-16P DN300 个 2.00 干粉灭 132 ABC-磷酸二氢铵 具 52.00 火剂 中 金 属 133 接 86型60mm 个 99.00 线 盒 平 塑胶跑 134 13mm 方 10872.15 道 米 135 篮球架 地埋式篮球架娱乐型 套 12.00 HDPE双 136 壁波纹 DN200 SN8 米 572.57 管 HDPE双 137 壁波纹 DN400 SN8 米 413.70 管 HDPE双 138 壁波纹 DN800 SN8 米 509.55 管 HDPE双 139 壁波纹 DN300 SN8 米 803.85 管 140 PE管 DN100 3.2mm 米 581.94 141 PE管 DN32 2.3mm 米 83.68 142 PE管 DN20 2mm 米 169.93 143 PE管 DN25 2mm 米 357.17 144 PE管 DN40 2.4mm 米 1334.78 网 145 PE管 DN50 2.4mm 米 180.35 146 PE管 DN63 2.5mm 米 616.83 147 PE管 DN80 3mm 米 302.52 务 PVC排水 148 DN100×3×4000mm 米 27.68 管 衬塑钢 149 Q235B DN50×3mm 米商69.04 管 衬 塑 150 Q235B DN65×3.5mm 米 63.64 钢 道 管 衬塑钢 151 Q235B DN80×4mm 米 38.02 管 管 100 0m m- Ⅱ 152 钢筋混国凝土排水管 米 271.59 级- 承 插 式 中 钢筋混 153 凝土排 300mm-Ⅱ级-承插管 米 132.31 水管 钢筋混 154 凝土排 400mm-Ⅱ级-承插口 米 46.056 水管 钢筋混 155 凝土排 600mm-Ⅱ级-承插口 米 32.73 水管 钢丝网 骨架塑料 156 SRTP-L-PE-160×4.5mm-1.6MPa 米 104.73 (聚乙烯) 复合管 钢丝网 骨架塑料 157 SRTP-L-PE-200×6mm-1MPa 米 1451.56 (聚乙烯) 复合管 钢丝网 骨架塑料 158 SRTP-L-PE-110×4mm-1.6MPa 米 411.04 (聚乙烯) 复合管 159 UPVC管 DN32×2mm 米 6394.192 160 雨水口 预制混凝土偏沟式单篦400×700mm 个 79.00 预制混 161 凝土沟 500×600×100mm C40 米 1300.00 盖板 网 预制混 凝土检 162 800mm 130mm 800mm 米 78.00 查井井 筒 务 预制混 163 凝土检 Φ1000×1400mm 座 74.00 查井 商 预制混 164 凝土检 Ф1200×1411mm 座 26.00 查井 预制混 道 165 凝土检 Ф1500×1473mm 座 12.00 查井 球墨铸 166 重型Φ700 管套 78.78 铁井盖 球墨铸 167 铁雨水 一篦500×600×45mm 块 21.114 篦子 国 钢筋混 168 凝土化 G13-100SQF 套 2.00 粪池 中 169 旗杆 不锈钢89mm 11m 根 1.00 球场围 170 立柱式3×4m 组 270.00 网 LED庭院 171 50W 套 19.00 灯 LED投光 172 400W 220V 套 24.00 灯 公路LED 173 照明灯 60-130-IB 套 44.00 具 174 高杆灯 30m 500W 座 4.00 LED鸟窝 175 12W 个 1.00 射树灯 室外消 176 SS普通100/65mm-1.6MPa 套 4.00 火栓 177 喷头 120mm 个 414.00 178 喷头 80mm 个 24.00 179 喷头 4mm 个 80.00 180 喷头 60mm 个 121.00 球墨铸 181 铁管(定 DN200 米 280.00 制) 球墨铸 182 铁管(定 DN300 米 450.00 制) 灭 火 网 183 4kg 2个 个 26.00 器 箱 纳米 184 硅PU密 20kg/桶 桶 4680.50 务 封底漆 平 人工草 185 0.8×0.8m 方 7327.37 皮 商 米 合成材 平 料运动 186 多功能运动场地渗水型浇筑型 方 7055.99 场地面 道 米 层 187 UPVC管 DN20×2mm 米 102.94 188 UPVC管 DN25×2mm 米 560.45 管 189 UPVC管 DN32×2mm 米 211.12 190 UPVC管 DN100×2.4mm 米 27.67 LED线条 191 220V 国12W 1000mm 套 10.80 灯 LED线条 192 220V 36W 1500mm 套 164.80 灯 LED中线条 193 220V 30W 1200mm 套 904.90 灯 感应小 194 135×60×85mm 套 56.00 便器 195 UPVC管 DN100×5mm 米 2004.73 196 UPVC管 DN50×4mm 米 278.71 197 UPVC管 DN125×3mm 米 932.46 198 UPVC管 DN150×7mm 米 719.97 千 199 紫铜管 拉制T2(Y) 15.88×1mm 655.17 克 紫 200 铜 拉制T2(Y) 9.5×0.8mm 千克 581.01 管 千 201 紫铜管 拉制T2(Y) 19.05×1mm 320.23 克 千 202 紫铜管 拉制T2(Y) 12.7×0.75mm 172.73 克 千 203 紫铜管 拉制T2(Y) 38.1×1.5mm 139.15 克 千 204 紫铜管 拉制T2(Y) 22.2×1mm 120.17 克 千 205 紫铜管 拉制T2(Y) 28.6×1.2mm 187.22 克 千 206 紫铜管 拉制T2(Y) 31.8×1.3mm 20.58 克 网 排烟防 207 PFHF WS-K-400×400mm 个 1.00 火阀 排烟防 208 PFHF WSDj-K-1000×400mm 个 1.00 火阀 务 排烟防 209 PFHF WSDc-K-630×500mm 个 3.00 火阀 排烟防 210 PFHF WS-K-800×400mm 个商1.00 火阀 防火卷 211 帘控制 FJK-S D-XMZ001 个 1.00 器 道 球墨铸 212 2000×1250×50mm 个 72.00 铁盖板 小型生 管 活污水 213 CT-P-10m/h-D 套 1.00 处理成 套设备 钢制三 碳钢100×100×100mm焊接等径正三 214 国 个 4.00 通 通 空调分 215 FQZHN-01D 套 155.00 支器 高密中度 聚乙烯 外护管 216 聚氨酯 DN32 3.5mm 米 880.00 泡沫塑 料预制 保温管 镀 锌 衬 217 DN150 米 1055.90 塑 钢 管 镀锌衬 218 DN150 米 178.03 塑钢管 镀锌衬 219 DN100 米 229.42 塑钢管 镀锌衬 220 DN65 米 37.08 塑钢管 镀锌衬 221 DN125 米 374.48 塑钢管 镀锌衬 222 DN150 米 417.68 塑钢管 镀锌衬 223 DN100 米 2021.35 塑钢管 镀锌衬 224 DN32 米 416.15 塑钢管 网 镀锌衬 225 DN80 米 301.41 塑钢管 镀锌衬 226 DN50 米 6.50 塑钢管 务 镀 锌 衬 227 DN200 米 59.82 塑商 钢 管 镀锌衬 228 DN200 米 1 塑钢管 道 镀锌衬 229 DN50 米 1100.28 塑钢管 管 备注：本次招标范围内灯具、开关等各类石材、装饰材料，所有样品均须提交业主单位审核选定；各投标单位 须全力配合、严格满足招标方及业主提出的各项材料规格、品质、外观、技术参数要求。 附件2：（包件号：ZZ-01） 国 计 招标 投标 序 物资 量 文件 保证金 招标人名称 包件号 规格型号 包件数量 号 名称 单 售价 （万 中 位 （元） 元） 中铁十八局 集团第五工 程有限公司 德阳天府旌城 平 铝扣 1 （科教片区） ZZ-01 600×600×0.8mm 方 1.59 500 3 0 板 B类项目总 米 承包-德阳 智能制造产 教融合项目 平方 2 钢丝网 0.9mm 10×10mm 62.30 米 纤维增强石 3 2700×800×12mm 块 3514.75 膏板 平方 4 装饰石膏板 P 2400×1200×12mm 944.19 米 纤维增强硅 平方 5 酸钙冲孔天 595×595×12mm 1333.71 米 花板 中密度纤维 6 1830×1220×12mm 张 663.00 板 洗手台 平方 7 人造石 86.00 面(定制) 米 平方 8 矿棉板吊顶 600×600×12mm 651.00 米 平方 9 抗倍特板 2440×1220×18mm 356.00 米 网 建筑幕墙用 平方 10 YP 2mm 3003 51.92 氟碳铝单板 米 平方 11 PVC地胶 2mm 759.30 米 务 平方 12 PVC地胶 4.5mm 7031.75 米 13 楼梯栏杆 Q235 3mm 1200mm 米 350.00 商 建筑幕墙用 平方 14 YP 3mm 3003 3280.00 氟碳铝单板 米 15 楼梯栏杆 钢制2mm 900mm 米 65.00 道 玻璃 16 1200mm 米 160.00 栏板 建筑幕墙用 平方 17 YP 3mm 3003 479.82 氟碳铝单板 米 管 建筑幕墙用 平方 18 YP 3mm 3003 887.26 氟碳铝单板 米 建筑装饰用 平方 19 N-国PET-FPT 2.5mm-3003 102.00 铝单板 米 建筑装饰用 平方 20 N-PET-FPT 2mm-3003 114.87 铝单板 米 建筑中幕墙用 平方 21 YP 3mm 3003 1172.20 氟碳铝单板 米 铝合金压型 平方 22 3004 H44 33000×400×1mm 16.50 板 米 绝热用玻璃 平方 23 11kg/m1200×3000×40mm A1 1333.70 棉毡 米 平方 24 玻璃棉卷毡 50mm &lt;0.045W/m.K≥16kg/m 1250.00 米 建筑幕墙陶 平方 25 20mm 1721.00 板 米 钢化夹胶双 平方 26 6×0.76mm 12.54 层防火玻璃 米 外墙保温结 平方 27 2780×600×120mm 4910.00 构一体化板 米 平方 28 铝扣板 1200×600×1.2mm 564.57 米 平方 29 夹胶玻璃 8mm 1.52mm 8mm 83.60 米 平方 30 夹胶玻璃 6+2.28PVB+6Low-E+12A+8mm 14.76 米 平方 31 纸面石膏板 SHC 2440×1200×9.5mm 518.80 米 高密度纤维 32 HDF-GP REG 1220×2440×9mm 张 2077.00 板 难燃 平 型挤 33 1200×600×80mm 方 74767.00 塑聚 网 米 苯板 预制树脂混 34 350×350mm 米 70.217 凝土排水沟 务 平方 35 不锈钢盖板 Q235 800×1000×50mm 119.50 米 36 斜天沟 600×350×3mm 吨 1.41 商 钢质防火卷 平方 37 GFJ-4555-C2-Ⅰ 12.50 帘 米 建筑外墙用 38 WNZ P 吨 98.08 腻子 道 建筑室内用 39 内墙 千克 24630.70 腻子 外墙柔性腻 40 SⅠ 吨 14.77 管 子 无障碍卫生 41 不锈钢710×250mm 套 48.00 间扶手 国 立方 42 岩棉 80mm 110kg/m 76.00 米 43 电动开窗器 1450×550mm 套 411.00 钢结构防火 44 中GT-N S P-Fp1.00 千克 5300.00 涂料 建筑防火岩 立方 45 60kg/m-100×50×120mm 95.00 棉板 米 内墙防霉涂 46 25kg/桶 千克 72.00 料 防雨百叶风 47 方形630×320mm 个 30.00 口 48 仿瓷涂料 固态散装 千克 3793.00 内墙 49 无机 25kg 桶 80.00 涂料 内墙 50 无机 25kg 桶 175.00 涂料 环氧 千 51 富锌 H06-21 2.5kg/桶 2122.00 克 底漆 环氧 公 52 云铁 环保型 6421.00 斤 漆 氟碳 千 53 灰色6063三涂层 115.00 漆 克 防火 卷帘 54 FJK-S D-XMZ001 个 13.00 控制 器 网 抗碱 千 55 WQ-DQ-2 1550.00 底漆 克 矿物 棉装 务 56 600×1200×15mm 块 1212.00 饰吸 声板 铝合 商 金建 6005 T5 5000mm银灰 57 筑喷 吨 20.30 色LF4-55 漆型 材 道 耐候 58 12瓶 支 17063.00 胶 聚乙 平 59 管烯泡 1000×2000×30mm 方 810.60 沫板 米 建筑 用轻 60 国 50×0.6 米 4867.00 钢龙 骨 建筑 用轻 61 中 DV 75×50×0.6mm 米 1399.00 钢龙 骨 建筑 用轻 62 DV 75×40×0.6mm 米 818.00 钢龙 骨 铝合 平 TMRG 63 金T型 方 3215.00 600×600×1.2×1.2mm 龙骨 米 防静 平 电活 64 HDW600-40QD 方 8.40 动地 米 板 栏杆 扶手 65 角 75×75×6mm 米 73.92 钢(定 制) 内墙 千 66 防霉 25kg/桶 170.00 克 涂料 合成 树脂 67 乳液 面漆合格品 吨 13.30 外墙 涂料 弹性 网千 68 建筑 外墙面涂Ⅰ型 2791.00 克 涂料 乳胶 千 69 漆面 22kg白色务 1468.00 克 漆 内墙 千 70 无机 20kg 4571.00 克 涂料商 干混 自流 71 DSL M10 吨 311.60 平砂 道 浆 矿物 棉装 72 600×1200×15mm 块 2885.00 饰吸 管 声板 钢制 73 置物 1 0.3×0.9×0.3m 个 82.00 国 架 槽型 铝合 千 74 85×85×4mm 408.00 金型 克 中 材 单层 75 防雨 1000×630mm 个 24.00 百叶 防雨 76 百叶 方形1250×1200mm 个 10.00 风口 中密 77 度纤 2440×1220×10mm 张 59.00 维板 无机 78 保温 400kg/m 吨 373.60 砂浆 岩面 玻纤 加强 聚酯 平 胎SBS 79 4mm 方 10167.00 双面 米 改性 沥青 防水 卷材 网 聚合 物水 80 泥防 JSⅡ 吨 43.50 水涂 务 料 非固 化橡 商 胶沥 千 81 20kg 15171.20 青防 克 水涂 料 道 聚氨 酯防 千 82 20kg 11757.83 水涂 克 料 管 聚合 物水 83 泥抹 M15 吨 28.80 灰砂 国 浆 平 钢盖 84 Q235 900×900×1.2mm 方 232.00 板 中 米 大理 平 85 石门 20mm 方 61.50 槛石 米 平 石英 86 600×300×18mm 方 496.50 砖 米 花岗 平 87 石地 G F600×300×30mm CA 方 2570.00 砖 米 人造 平 大理 88 2000×700×12mm 方 21.00 石面 米 板 泡沫 立 89 混凝 FC A04-C1-W5-S 方 206.20 土 米 泡沫 立 90 混凝 FC A10-C4-W40-S 方 226.00 土 米 脱硫 石膏 91 轻质130m 吨 355.78 抹灰 砂浆 平 枫木 92 4000×100×22mm 方 2163.50 地板 米 平 枫木 93 4000×100×18mm 方 2168.30 地板 网 米 踢脚 94 不锈钢2000×60×1.2mm 米 1056.00 线 务平 玻璃 95 DZ-GG-FB-BL-3.5 方 12.00 幕墙 米 平 玻璃商 96 DZ-RG-FB-BL-3.5 方 75.00 幕墙 米 平 玻璃 97 SM-MK-NT-BL-3.5 方 1408.00 道 幕墙 米 平 玻璃 98 GJ-YK-KF-BL-1.5 方 65.00 幕墙 管 米 平 玻璃 99 QB-LD-FB-BL-3.5 方 252.24 幕墙 米 国 平 玻璃 100 DZ-BK-WT-BL-3.5 方 15.60 幕墙 米 中 平 玻璃 101 DZ-BK-WT-BL-3.5 方 213.62 幕墙 米 平 玻璃 102 GJ-BY-FB-BL-1.5 方 440.281 幕墙 米 平 玻璃 103 DY-LJ-KF-BL-1 方 37.705 幕墙 米 挡水 104 1×0.9×0.8m 个 0.45 板 建筑 用轻 105 QT 120×80×8mm 米 84.77 钢龙 骨 挡水 106 1×0.85×0.75m 个 21.20 板 挡水 107 1×0.85×0.75m 个 356.62 板 纸面 平 108 石膏 SHC 2440×1200×18mm 方 530.04 板 米 FTC 立 109 保温 A级防火 方 164.00 材料 米 耐碱 玻璃 平 110 纤维 140g/m 方 820.95 网 网格 米 布 耐碱 玻璃 务平 111 纤维 130g/m 方 20110 网格 米 布 合 商 268570.613 计 备注：本次招标范围内地板、大理石等各类石材、装饰材料，所有样品均须提交业主单位审核选定；各投标单 位须全力配合、严格满足招标方及业主提出的道各项材料规格、品质、外观、技术参数要求。 附件3：（包件号：LP-01） 管 招标文件售价 投标保证金 序号 招标人名称 包件号 物资名称 规格型号 计量单位 包件数量 （元） （万元） 德阳智能制造产教 1 LP-01 铝单板 3mm 平方米 70000 500 5 0 融合项目 国 附件3.1 备注：本次招标铝单板供货以实际到场产品型号为准，产品具体详见附件3.1，施工期间存在图纸变更、型号参 数调整的可中能，最终供货型号以甲方确认的最新图纸为准。 附件4：（包件号：L C -01） 计量单 招标文件售价 投标保证金 序号 招标人名称 包件号 物资名称 规格型号 包件数量 位 （元） （万元） 德阳智能制造产教 1 L C -01 铝型材 FeAl52Si5 吨 200 500 1 0 融合项目 合计 200 备注：本次招标铝型材可能因施工期间存在图纸变更、型号参数调整的可能，最终供货型号以甲方确认的最新 图纸为准。供货以实际到场产品型号为准，产品具体详见招标文件附件1.2铝型材清单附件 点击查看内容 信息来源:https://www.chinapipe.net/project/d3079200.html cqdingjiu 2026.08.25 09:25:46</t>
+          <t>中铁十八局集团第五工程有限公司德阳天府旌城(科教片区)B类项目总承包-德阳智能制造产教融合项目总平材料、 装饰装修材料，铝单板材料、铝型材材料公开招标招标公告 招标公告 中铁十八局集团第五工程有限公司德阳天府旌城（科教片区）B类项目总承包-德阳智能制造产教融合项目总平材 料、装饰装修材料，铝单板材料、铝型材材料公开招标 招标编号：CRCC-1805ZB-DYTFXC-2026-08 网 1.招标条件 1.1本项目为中铁十八局集团第五工程有限公司德阳天府旌城（科教片区）B类项目总承包德阳智能制造产教融合 项目施工，项目建设单位为德阳发展城市建设开发有限公司，建设资金已落实。 务 本次招标的招标人为中铁十八局集团第五工程有限公司德阳天府旌城（科教片区）B类项目总承包-德阳智能制造 产教融合项目(以下简称：德阳智能制造产教融合项目）。 根据国家相关文件规定，建设单位、股份公司、集团公司商有关物资管理规定，现对以上项目具备招标条件的施 工物资总平材料、装饰装修、铝单板、铝型材 材料进行公开招标。 2.项目概况与招标内容 道 2.1项目概况 德阳智能制造产教融合项目本项目位于四川省德阳市旌阳区长江西路沿线与天府大道北延线（二环路）交汇处 西北角地块。建设内容及规模：本工程平时为地下停车场，战时为二等人员掩蔽所，人防工程应建总建筑面 管 积14720.18㎡，（十层及十层以上）+190208*0.025（九层及九层以下埋深小于3m）+655（九层及九层以下埋深大 于3m）人防实际工程总建筑面积14910.15㎡，项目总建筑面积324848㎡，项目合同工期：随土建工程进度。 2.2招标内容 ：详见招标公告附件《招标物资包件清单》，本次招标一包一投。 国 2.3招标内容及包件划分 2.3.1招标内容及包件划分：详见招标公告附件1《招标物资包件清单》，本次招标一包一投。 中 2.3.2招标方式：采用国内公开招标方式。 3.招标依据 3.1本次招标的依据为： （1）《中华人民共和国招标投标法》； （2）《中华人民共和国招标投标法实施条例》（国务院第613号令）； （3）《工程建设项目货物招标投标办法》（国家发展改革委等七部委令第27号）； （4）《评标委员会和评标方法暂行规定》（国家发展改革委等七部委令第12号）； （5）《中国铁建股份有限公司物资采购管理规定（试行）》（中国铁建供应链〔2025〕106号）； （6）其他相关法律、法规、规章。 4.投标人资格审查及要求 4.1本次招标资格审查采用资格后审的方式。 4.2本次招标包件号（ZP-01、ZZ-01、LP-01、LC-01、） 要求投标人须具备以下条件： （1）营业范围： 在中华人民共和国境内依法注册，具有独立法人资格、具有招标物资生产或供应经验的生产厂 家 或代理商 ，并且具有合法有效的营业执照； （2）财务能力： 投标人必须是经税务部门注册登记核准的一般纳税人或小规模纳税人，有依法纳税的良好记录， 具有良好的资金财务状况，投标人须提供2024、2025年经会计师事务所审计的财务审计报告及相关报表（财务审 计报告及相关报表需提供扫描件），期间注册的新公司仅需提供成立后的报表（至少需提供最近一年报表） （3） 质量保证能力： 检测机构出具满足国家现行验收标准要求的投标物资质量检验报告。 网 （4） 履约信用：2具有良好的社会信誉，投标人具有良好的社会信誉，不接受存在以下任何一种情况的公司投 标。 ①在“国家企业信用信息公示系统”（https://www.gsxt.gov.cn/index.html）被列入严重违法失信名单和经营异常 务 名单。 ②在“中国执行信息公开网”(http://zxgk.court.gov.cn）被列入失信被执行人。③在纳税信用登记信息系统 （https://12366.chinatax.gov.cn/）被列入纳税信用等级为C、D级的企业。 商 ④在信用中国(https://www.creditchina.gov.cn/?navPage=0）被列入严重失信和经营异常被执行人。 ⑤不接受在最新一期《中国铁建选择合作方风险警示名录》中的供应商以及被采购人列入风险警示合作名录的 供应商。 道 其他要求： 不接受联合体投标。 5.招标文件的获取 管 5.1凡有意参加投标者，请登陆中国铁建云链平台（www.crccep.cn）注册会员，查询拟参与投标包件进行 网上报 名、支付标书费、下载电子招标文件 。 5.2凡有意参加投标者，国请登陆中国铁建云链平台（www.crccep.com）注册会员，查询拟参与投标包件进行网上报 名、下载电子招标文件。招标文件售卖截止时间为：2026年8月24日- 2026年8月2 9日23时59分 。潜在投标人须在 招标文件售卖截止时间前完成中国铁建云链平台（www.crccep.com）注册报名，并申请办理CA锁，用于电子投 标文件的签章、加密及解密（CA办理所需资料及程序详见中国铁建云链平台首页-小鹿课堂-帮助中心-铁建云链 平台数字证书办理流程）， 并在相应时间内 将所需购买包件的招标文件售价足额现金转入到招标组织机构指定 中 银行账户（开户名称：中铁十八局集团有限公司物资集中采购中心；开户银行：交通银行北京西区支行；账号： 99011231018000668621此账号仅用于支付标书款 ， 保证金账号请参照第二章投标人须知前附表中相关内容 ） 在 汇款单上注明投标单位名称（ 产教融合 ）+德阳标书款 及所投 包件号 。 投标人在铁建云链平台报名时 请上传 标书款银行汇款凭证 ，招标组织机构核实标书款后，方可下载标书。 5.3本次招标一包一投，包件划分情况见招标公告附件1《招标物资包件清单》。 5.4招标文件每包件售价见招标公告附件1《招标物资包件清单》 ， 售后不退 。 5.5获取购买招标文件发票的方式：投标人在中国铁建云链平台（www.crccep.cn）自行申请。 6.投标文件的递交 6.1此次招标投标人需制作电子投标文件，并使用CA锁对投标文件进行加密，在递交截止时间前 线上递交投标文 件 ， 电子投标文件命名为 “投标人名称-包件号” 。 6.2投标文件递交截止时间：2026年9月21日10时00分 。 6.3投标文件递交地点：中国铁建云链平台（www.crccep.cn），投标人须登陆该平台，在投标文件递交截止时间 前完成所有投标文件的上传。 投标文件递交截止时间前未完成投标文件传输的，视为放弃投标资格。 6.4如招标人有需求，被评为中标候选人的投标人应无偿提供纸质版投标文件，纸质版投标文件内容须与电子版 文件内容完全一致。 7.开标 7.1电子投标文件的解密 （1）电子投标文件解密时间：2026年9月21日10时00分至11时00分 。 （2）各投标人必须在规定的投标文件解密时间内登录中国铁建云链平台（www.crccep.cn）完成投标文件解密， 如因投标人自身原因导致所递交的投标文件无法在规定的时间内解密的，视为无效投标文件，后果及责任由投 标人自行负责。 8.发布公告的媒介 网 8.1本次招标公告在以下平台同时发布： （1） 中国招标投标公共服务平台(www.cebpubservice.com) 务 （2）中国铁建云链平台（www.crccep.cn） 8.2本次招标安排如有变化，招标人将通过以上平台发布通知。 商 9.现场踏勘 本次招标不统一组织投标人踏勘工地路况，请各潜在投标人自行踏勘。 道 10.招标人信息及相关方联系方式 10.1招标人及联系方式： 管 （1）招标人： 中铁十八局集团第五工程有限公司德阳天府旌城（科教片区）B类项目总承包-德阳智能制造产教 融合项目 联系人： 徐广占13821179612 国 10.2招标组织单位及联系方式 招标组织单位： 中铁十八局集团有限公司物资集中采购中心 中 地址：天津市津南区大沽南路中铁十八局东区集采中心 招标文件答疑联系人： 苍宇 电话：13672001117 邮箱：wbtaozi1983@126.com 铁建云链平台技术支持：400-6296-888 2026年8月2 4日 附件1：（包件号：ZP-01） 物 招标 投标 招标人 资 计量 包件数 文件 保证金 序号 包件号 规格型号 名称 名 单位 量 售价 （万 称 （元） 元） 中铁十 八局集 团第五 工程有 限公司 防 德阳天 火 府旌城 电 1 （科教 ZP-01 FGQJ-P100×100mm-F1 米 7.63 500 1 5 缆 片区）B 桥 类项目 网 架 总承包- 德阳智 能制造 产教融 务 合项目 防火电 2 FGQJ-P150×100mm-F1 米 110.00 缆桥架 商 防火电 3 FGQJ-P200×100mm-F1 米 198.39 缆桥架 防火电 4 FGQJ-P300×100mm-F1 米 64.84 缆桥架 道 防火电 5 FGQJ-P300×150mm-F1 米 12.24 缆桥架 防火电 6 FGQJ-P300×200mm-F2 米 5.00 管 缆桥架 钢制槽 7 式电缆 100×100mm 米 264.09 桥架 国 钢制槽 8 式电缆 200×100mm 米 91.68 桥架 钢制中槽 9 式电缆 200×150mm 米 80.19 桥架 钢制槽 10 式电缆 400×200mm 米 22.38 桥架 钢制槽 11 式电缆 300×150mm 米 131.96 桥架 铝合金 12 电缆桥 LQJ-C-A-100×100mm-P 米 57.05 架 铝合金 13 电缆桥 LQJ-C-A-200×100mm-P 米 31.11 架 铝合金 14 电缆桥 LQJ-C-A-300×100mm-P 米 50.19 架 热镀锌 15 金属线 100×100mm 米 480.28 槽 JD 16 G DN25 米 263.64 管 热镀锌 17 金属线 200×100mm 米 59.68 槽 网 18 JDG管 DN20 米 22523.05 19 JDG管 DN32 米 350.62 电气配 20 SC钢镀锌DN50 米 44.64 务 管 LED感应 21 220V 12W 套 44.00 灯 商 LED吸顶 22 220V 1×8W 套 16.00 灯 LED吸顶 23 220V 1×8W 套 10.00 灯 道 LED单管 24 220V 16W 套 12.00 灯 LED单管 25 220V 16W 套 93.00 管 灯 LED单管 26 220V 16W 套 22.00 灯 LED双管 国 27 220V 2×16W 套 28.00 灯 LED单管 28 220V 16W 套 2.00 灯 中 29 LED壁灯 220V 2×13W 套 28.00 30 LED筒灯 220V 5W 个 3.00 LED吸顶 31 220V 9W 个 1.00 灯 32 LED筒灯 220V 9W 个 45.00 LE D 33 220V 7W 个 40.00 筒 灯 34 LED筒灯 220V 5W 个 61.00 35 LED筒灯 220V 7W 个 35.00 36 LED筒灯 220V 9W 个 2.00 37 LED筒灯 220V 9W 个 15.00 38 LED筒灯 220V 12W 个 8.00 LED天棚 39 220V 30W 套 168.00 信号灯 40 LED筒灯 220V 15W 个 144.00 41 LED筒灯 220V 20W 个 64.00 42 LED筒灯 220V 15W 个 23.00 43 照明灯 220V 300W 个 48.00 44 照明灯 220V 150W 个 168.00 45 灯盘 1200×200mm 28W 套 76.00 46 灯盘 1200×100mm 18W 套 74.00 47 灯盘 600×600mm 32W 套 10.00 网 普通开 48 单联单控感应250V 10A 个 15.00 关 普通开 49 双联单控暗装250V 10A 个 70.00 关 务 普 通 50 单联单控暗装250V 10A 个 57.00 开 关商 暗装式 51 单相二、三极五孔250V 10A 个 910.00 插座 普通开 道 52 三联单控250V 10A 个 62.00 关 暗装式 53 单相二、三孔250V 15A 个 910.00 插座 管 空调开 54 MB1-63/3P D16 套 30.00 关箱 暗装式 55 三孔暗装250V 20A 个 11.00 插座 国 暗装式 56 单相二、三极250V 10A 个 77.00 插座 暗装式 57 中防水双联二三极250V 10A 个 41.00 插座 暗装式 58 五孔220V 10A 个 2.00 插座 等电位 59 300×200×120mm 个 9.00 端子箱 无线远 60 DN65 个 1.00 传水表 等电位 61 联结端 MEB 300×200×120mm 套 10.00 子箱 无线远 62 DN80 个 1.00 传水表 无线远 63 DN50 个 14.00 传水表 64 闸阀 Z手动41W-16P DN65 个 4.00 65 截止阀 J手动11W-16T DN15 个 8.00 66 闸阀 Z手动41H-16Q DN50 个 2.00 截 67 止 J手动11W-16T DN20 个 19.00 阀 68 截止阀 J手动11W-16T DN25 个 13.00 69 截止阀 J手动11W-16T DN50 个 9.00 70 止回阀 H手动14W-16T DN15 个 18.00 71 止回阀 H手动14W-16P DN20 个 2.00 72 减压阀 DN65 1.6MPa 个 1.00 网 73 减压阀 DN50 1.6MPa 个 11.00 74 减压阀 DN80 1.6MPa 个 1.00 铸铁自 务 75 动排气 DN25 1.6MPa 个 13.00 阀 衬塑钢 76 Q235B DN15×3mm 米 70.00 管 商 衬塑钢 77 Q235B DN20×2.2mm 米 36.00 管 衬塑钢 道 78 Q235B DN50×3mm 米 165.00 管 衬塑钢 79 Q235B DN65×3.5mm 米 175.00 管 管 PPR给水 80 DN15 1.5mm 米 367.81 管 衬塑钢 81 Q235B DN80×4mm 米 65.00 管 国 PPR给水 82 DN20 1.5mm 米 60.40 管 PPR给水 83 中DN32 1.5mm 米 23.35 管 PP R给 84 DN25 1.5mm 米 244.63 水 管 PPR给水 85 DN40 3.2mm 米 57.08 管 PPR给水 86 DN50 3mm 米 70.03 管 PPR给水 87 DN65 3mm 米 9.57 管 PPR给水 88 DN15 2mm 米 83.49 管 PPR给水 89 DN20 2mm 米 6.88 管 橡塑隔 平 90 声保温 500×40×20mm 方 5.00 材料 米 储水式 91 电热水 50L 2.2kW 台 15.00 器 92 铸铁管 DN75 米 10.00 93 铸铁管 DN50 米 41.79 94 铸铁管 DN100 米 276.85 95 UPVC管 DN75×3mm 米 51.14 96 铸铁管 DN150 米 51.32 网 97 UPVC管 DN50×2.5mm 米 200.46 98 UPVC管 DN150×3.5mm 米 36.53 99 UPVC管 DN100×3.2mm 米 516.29 务 100 地漏 不锈钢DN100其他直通式 个 2.00 地 101 不锈钢DN50内插式其他 个 68.00 漏 商 102 地漏 塑料DN50直通式其他 个 60.00 103 地漏 塑料DN100水封式直通式 个 1.00 铸铁漏 104 DN200 道个 12.00 斗 铸铁清 105 DN150 个 3.00 扫口 87型雨水 管 106 B-GB-200mm-A-Ⅰ 个 3.00 斗 87型雨水 107 B-GB-100mm-A-Ⅰ 个 20.00 斗 国 108 防火阀 FHF W-Y-200×320mm 个 1.00 109 防火阀 FHF W-Y-200×200mm 个 8.00 110 防火阀 FHF S-K-320×250mm 个 4.00 中 111 防火阀 FHF S-K-320×200mm 个 4.00 112 防火阀 FHF S-K-400×320mm 个 1.00 113 防火阀 FHF S-K-400×200mm 个 1.00 114 防火阀 FHF S-K-500×250mm 个 2.00 115 防火阀 FHF W-K-630×250mm 个 1.00 116 防火阀 FHF S-K-500×320mm 个 5.00 117 防火阀 FHF W-K-600×500mm 个 1.00 铝合金 118 单层百 200×200mm 个 1.00 叶风口 单层百 叶风口 119 150×150mm 个 26.00 带调节 阀 单层百 叶风口 120 200×150mm 个 4.00 带调节 阀 单层百 叶风口 121 200×200mm 个 82.00 带调节 阀 热镀锌 平 122 钢板风 0.5mm 方 637.38 管 米 热镀锌 平 123 钢板风 1mm 方 100.00 网 管 米 热镀锌 平 124 钢板风 0.6mm 方 341.77 管 米 务 热镀锌 平 125 钢板风 0.75mm 方 600.00 管 米 商 绝热用 平 126 玻璃棉 11kg/m1100×3000×40mm A1 方 48.87 毡 米 板式平 道 127 DN100 PN16 个 10.00 焊法兰 板式平 128 DN150 PN16 个 10.00 焊法兰 管 板式平 129 DN200 PN16 个 10.00 焊法兰 130 闸阀 Z手动41W-16P DN200 个 1.00 131 闸阀 Z手动国41W-16P DN300 个 2.00 干粉灭 132 ABC-磷酸二氢铵 具 52.00 火剂 中 金 属 133 接 86型60mm 个 99.00 线 盒 平 塑胶跑 134 13mm 方 10872.15 道 米 135 篮球架 地埋式篮球架娱乐型 套 12.00 HDPE双 136 壁波纹 DN200 SN8 米 572.57 管 HDPE双 137 壁波纹 DN400 SN8 米 413.70 管 HDPE双 138 壁波纹 DN800 SN8 米 509.55 管 HDPE双 139 壁波纹 DN300 SN8 米 803.85 管 140 PE管 DN100 3.2mm 米 581.94 141 PE管 DN32 2.3mm 米 83.68 142 PE管 DN20 2mm 米 169.93 143 PE管 DN25 2mm 米 357.17 144 PE管 DN40 2.4mm 米 1334.78 网 145 PE管 DN50 2.4mm 米 180.35 146 PE管 DN63 2.5mm 米 616.83 147 PE管 DN80 3mm 米 302.52 务 PVC排水 148 DN100×3×4000mm 米 27.68 管 衬塑钢 149 Q235B DN50×3mm 米商69.04 管 衬 塑 150 Q235B DN65×3.5mm 米 63.64 钢 道 管 衬塑钢 151 Q235B DN80×4mm 米 38.02 管 管 100 0m m- Ⅱ 152 钢筋混国凝土排水管 米 271.59 级- 承 插 式 中 钢筋混 153 凝土排 300mm-Ⅱ级-承插管 米 132.31 水管 钢筋混 154 凝土排 400mm-Ⅱ级-承插口 米 46.056 水管 钢筋混 155 凝土排 600mm-Ⅱ级-承插口 米 32.73 水管 钢丝网 骨架塑料 156 SRTP-L-PE-160×4.5mm-1.6MPa 米 104.73 (聚乙烯) 复合管 钢丝网 骨架塑料 157 SRTP-L-PE-200×6mm-1MPa 米 1451.56 (聚乙烯) 复合管 钢丝网 骨架塑料 158 SRTP-L-PE-110×4mm-1.6MPa 米 411.04 (聚乙烯) 复合管 159 UPVC管 DN32×2mm 米 6394.192 160 雨水口 预制混凝土偏沟式单篦400×700mm 个 79.00 预制混 161 凝土沟 500×600×100mm C40 米 1300.00 盖板 网 预制混 凝土检 162 800mm 130mm 800mm 米 78.00 查井井 筒 务 预制混 163 凝土检 Φ1000×1400mm 座 74.00 查井 商 预制混 164 凝土检 Ф1200×1411mm 座 26.00 查井 预制混 道 165 凝土检 Ф1500×1473mm 座 12.00 查井 球墨铸 166 重型Φ700 管套 78.78 铁井盖 球墨铸 167 铁雨水 一篦500×600×45mm 块 21.114 篦子 国 钢筋混 168 凝土化 G13-100SQF 套 2.00 粪池 中 169 旗杆 不锈钢89mm 11m 根 1.00 球场围 170 立柱式3×4m 组 270.00 网 LED庭院 171 50W 套 19.00 灯 LED投光 172 400W 220V 套 24.00 灯 公路LED 173 照明灯 60-130-IB 套 44.00 具 174 高杆灯 30m 500W 座 4.00 LED鸟窝 175 12W 个 1.00 射树灯 室外消 176 SS普通100/65mm-1.6MPa 套 4.00 火栓 177 喷头 120mm 个 414.00 178 喷头 80mm 个 24.00 179 喷头 4mm 个 80.00 180 喷头 60mm 个 121.00 球墨铸 181 铁管(定 DN200 米 280.00 制) 球墨铸 182 铁管(定 DN300 米 450.00 制) 灭 火 网 183 4kg 2个 个 26.00 器 箱 纳米 184 硅PU密 20kg/桶 桶 4680.50 务 封底漆 平 人工草 185 0.8×0.8m 方 7327.37 皮 商 米 合成材 平 料运动 186 多功能运动场地渗水型浇筑型 方 7055.99 场地面 道 米 层 187 UPVC管 DN20×2mm 米 102.94 188 UPVC管 DN25×2mm 米 560.45 管 189 UPVC管 DN32×2mm 米 211.12 190 UPVC管 DN100×2.4mm 米 27.67 LED线条 191 220V 国12W 1000mm 套 10.80 灯 LED线条 192 220V 36W 1500mm 套 164.80 灯 LED中线条 193 220V 30W 1200mm 套 904.90 灯 感应小 194 135×60×85mm 套 56.00 便器 195 UPVC管 DN100×5mm 米 2004.73 196 UPVC管 DN50×4mm 米 278.71 197 UPVC管 DN125×3mm 米 932.46 198 UPVC管 DN150×7mm 米 719.97 千 199 紫铜管 拉制T2(Y) 15.88×1mm 655.17 克 紫 200 铜 拉制T2(Y) 9.5×0.8mm 千克 581.01 管 千 201 紫铜管 拉制T2(Y) 19.05×1mm 320.23 克 千 202 紫铜管 拉制T2(Y) 12.7×0.75mm 172.73 克 千 203 紫铜管 拉制T2(Y) 38.1×1.5mm 139.15 克 千 204 紫铜管 拉制T2(Y) 22.2×1mm 120.17 克 千 205 紫铜管 拉制T2(Y) 28.6×1.2mm 187.22 克 千 206 紫铜管 拉制T2(Y) 31.8×1.3mm 20.58 克 网 排烟防 207 PFHF WS-K-400×400mm 个 1.00 火阀 排烟防 208 PFHF WSDj-K-1000×400mm 个 1.00 火阀 务 排烟防 209 PFHF WSDc-K-630×500mm 个 3.00 火阀 排烟防 210 PFHF WS-K-800×400mm 个商1.00 火阀 防火卷 211 帘控制 FJK-S D-XMZ001 个 1.00 器 道 球墨铸 212 2000×1250×50mm 个 72.00 铁盖板 小型生 管 活污水 213 CT-P-10m/h-D 套 1.00 处理成 套设备 钢制三 碳钢100×100×100mm焊接等径正三 214 国 个 4.00 通 通 空调分 215 FQZHN-01D 套 155.00 支器 高密中度 聚乙烯 外护管 216 聚氨酯 DN32 3.5mm 米 880.00 泡沫塑 料预制 保温管 镀 锌 衬 217 DN150 米 1055.90 塑 钢 管 镀锌衬 218 DN150 米 178.03 塑钢管 镀锌衬 219 DN100 米 229.42 塑钢管 镀锌衬 220 DN65 米 37.08 塑钢管 镀锌衬 221 DN125 米 374.48 塑钢管 镀锌衬 222 DN150 米 417.68 塑钢管 镀锌衬 223 DN100 米 2021.35 塑钢管 镀锌衬 224 DN32 米 416.15 塑钢管 网 镀锌衬 225 DN80 米 301.41 塑钢管 镀锌衬 226 DN50 米 6.50 塑钢管 务 镀 锌 衬 227 DN200 米 59.82 塑商 钢 管 镀锌衬 228 DN200 米 1 塑钢管 道 镀锌衬 229 DN50 米 1100.28 塑钢管 管 备注：本次招标范围内灯具、开关等各类石材、装饰材料，所有样品均须提交业主单位审核选定；各投标单位 须全力配合、严格满足招标方及业主提出的各项材料规格、品质、外观、技术参数要求。 附件2：（包件号：ZZ-01） 国 计 招标 投标 序 物资 量 文件 保证金 招标人名称 包件号 规格型号 包件数量 号 名称 单 售价 （万 中 位 （元） 元） 中铁十八局 集团第五工 程有限公司 德阳天府旌城 平 铝扣 1 （科教片区） ZZ-01 600×600×0.8mm 方 1.59 500 3 0 板 B类项目总 米 承包-德阳 智能制造产 教融合项目 平方 2 钢丝网 0.9mm 10×10mm 62.30 米 纤维增强石 3 2700×800×12mm 块 3514.75 膏板 平方 4 装饰石膏板 P 2400×1200×12mm 944.19 米 纤维增强硅 平方 5 酸钙冲孔天 595×595×12mm 1333.71 米 花板 中密度纤维 6 1830×1220×12mm 张 663.00 板 洗手台 平方 7 人造石 86.00 面(定制) 米 平方 8 矿棉板吊顶 600×600×12mm 651.00 米 平方 9 抗倍特板 2440×1220×18mm 356.00 米 网 建筑幕墙用 平方 10 YP 2mm 3003 51.92 氟碳铝单板 米 平方 11 PVC地胶 2mm 759.30 米 务 平方 12 PVC地胶 4.5mm 7031.75 米 13 楼梯栏杆 Q235 3mm 1200mm 米 350.00 商 建筑幕墙用 平方 14 YP 3mm 3003 3280.00 氟碳铝单板 米 15 楼梯栏杆 钢制2mm 900mm 米 65.00 道 玻璃 16 1200mm 米 160.00 栏板 建筑幕墙用 平方 17 YP 3mm 3003 479.82 氟碳铝单板 米 管 建筑幕墙用 平方 18 YP 3mm 3003 887.26 氟碳铝单板 米 建筑装饰用 平方 19 N-国PET-FPT 2.5mm-3003 102.00 铝单板 米 建筑装饰用 平方 20 N-PET-FPT 2mm-3003 114.87 铝单板 米 建筑中幕墙用 平方 21 YP 3mm 3003 1172.20 氟碳铝单板 米 铝合金压型 平方 22 3004 H44 33000×400×1mm 16.50 板 米 绝热用玻璃 平方 23 11kg/m1200×3000×40mm A1 1333.70 棉毡 米 平方 24 玻璃棉卷毡 50mm &lt;0.045W/m.K≥16kg/m 1250.00 米 建筑幕墙陶 平方 25 20mm 1721.00 板 米 钢化夹胶双 平方 26 6×0.76mm 12.54 层防火玻璃 米 外墙保温结 平方 27 2780×600×120mm 4910.00 构一体化板 米 平方 28 铝扣板 1200×600×1.2mm 564.57 米 平方 29 夹胶玻璃 8mm 1.52mm 8mm 83.60 米 平方 30 夹胶玻璃 6+2.28PVB+6Low-E+12A+8mm 14.76 米 平方 31 纸面石膏板 SHC 2440×1200×9.5mm 518.80 米 高密度纤维 32 HDF-GP REG 1220×2440×9mm 张 2077.00 板 难燃 平 型挤 33 1200×600×80mm 方 74767.00 塑聚 网 米 苯板 预制树脂混 34 350×350mm 米 70.217 凝土排水沟 务 平方 35 不锈钢盖板 Q235 800×1000×50mm 119.50 米 36 斜天沟 600×350×3mm 吨 1.41 商 钢质防火卷 平方 37 GFJ-4555-C2-Ⅰ 12.50 帘 米 建筑外墙用 38 WNZ P 吨 98.08 腻子 道 建筑室内用 39 内墙 千克 24630.70 腻子 外墙柔性腻 40 SⅠ 吨 14.77 管 子 无障碍卫生 41 不锈钢710×250mm 套 48.00 间扶手 国 立方 42 岩棉 80mm 110kg/m 76.00 米 43 电动开窗器 1450×550mm 套 411.00 钢结构防火 44 中GT-N S P-Fp1.00 千克 5300.00 涂料 建筑防火岩 立方 45 60kg/m-100×50×120mm 95.00 棉板 米 内墙防霉涂 46 25kg/桶 千克 72.00 料 防雨百叶风 47 方形630×320mm 个 30.00 口 48 仿瓷涂料 固态散装 千克 3793.00 内墙 49 无机 25kg 桶 80.00 涂料 内墙 50 无机 25kg 桶 175.00 涂料 环氧 千 51 富锌 H06-21 2.5kg/桶 2122.00 克 底漆 环氧 公 52 云铁 环保型 6421.00 斤 漆 氟碳 千 53 灰色6063三涂层 115.00 漆 克 防火 卷帘 54 FJK-S D-XMZ001 个 13.00 控制 器 网 抗碱 千 55 WQ-DQ-2 1550.00 底漆 克 矿物 棉装 务 56 600×1200×15mm 块 1212.00 饰吸 声板 铝合 商 金建 6005 T5 5000mm银灰 57 筑喷 吨 20.30 色LF4-55 漆型 材 道 耐候 58 12瓶 支 17063.00 胶 聚乙 平 59 管烯泡 1000×2000×30mm 方 810.60 沫板 米 建筑 用轻 60 国 50×0.6 米 4867.00 钢龙 骨 建筑 用轻 61 中 DV 75×50×0.6mm 米 1399.00 钢龙 骨 建筑 用轻 62 DV 75×40×0.6mm 米 818.00 钢龙 骨 铝合 平 TMRG 63 金T型 方 3215.00 600×600×1.2×1.2mm 龙骨 米 防静 平 电活 64 HDW600-40QD 方 8.40 动地 米 板 栏杆 扶手 65 角 75×75×6mm 米 73.92 钢(定 制) 内墙 千 66 防霉 25kg/桶 170.00 克 涂料 合成 树脂 67 乳液 面漆合格品 吨 13.30 外墙 涂料 弹性 网千 68 建筑 外墙面涂Ⅰ型 2791.00 克 涂料 乳胶 千 69 漆面 22kg白色务 1468.00 克 漆 内墙 千 70 无机 20kg 4571.00 克 涂料商 干混 自流 71 DSL M10 吨 311.60 平砂 道 浆 矿物 棉装 72 600×1200×15mm 块 2885.00 饰吸 管 声板 钢制 73 置物 1 0.3×0.9×0.3m 个 82.00 国 架 槽型 铝合 千 74 85×85×4mm 408.00 金型 克 中 材 单层 75 防雨 1000×630mm 个 24.00 百叶 防雨 76 百叶 方形1250×1200mm 个 10.00 风口 中密 77 度纤 2440×1220×10mm 张 59.00 维板 无机 78 保温 400kg/m 吨 373.60 砂浆 岩面 玻纤 加强 聚酯 平 胎SBS 79 4mm 方 10167.00 双面 米 改性 沥青 防水 卷材 网 聚合 物水 80 泥防 JSⅡ 吨 43.50 水涂 务 料 非固 化橡 商 胶沥 千 81 20kg 15171.20 青防 克 水涂 料 道 聚氨 酯防 千 82 20kg 11757.83 水涂 克 料 管 聚合 物水 83 泥抹 M15 吨 28.80 灰砂 国 浆 平 钢盖 84 Q235 900×900×1.2mm 方 232.00 板 中 米 大理 平 85 石门 20mm 方 61.50 槛石 米 平 石英 86 600×300×18mm 方 496.50 砖 米 花岗 平 87 石地 G F600×300×30mm CA 方 2570.00 砖 米 人造 平 大理 88 2000×700×12mm 方 21.00 石面 米 板 泡沫 立 89 混凝 FC A04-C1-W5-S 方 206.20 土 米 泡沫 立 90 混凝 FC A10-C4-W40-S 方 226.00 土 米 脱硫 石膏 91 轻质130m 吨 355.78 抹灰 砂浆 平 枫木 92 4000×100×22mm 方 2163.50 地板 米 平 枫木 93 4000×100×18mm 方 2168.30 地板 网 米 踢脚 94 不锈钢2000×60×1.2mm 米 1056.00 线 务平 玻璃 95 DZ-GG-FB-BL-3.5 方 12.00 幕墙 米 平 玻璃商 96 DZ-RG-FB-BL-3.5 方 75.00 幕墙 米 平 玻璃 97 SM-MK-NT-BL-3.5 方 1408.00 道 幕墙 米 平 玻璃 98 GJ-YK-KF-BL-1.5 方 65.00 幕墙 管 米 平 玻璃 99 QB-LD-FB-BL-3.5 方 252.24 幕墙 米 国 平 玻璃 100 DZ-BK-WT-BL-3.5 方 15.60 幕墙 米 中 平 玻璃 101 DZ-BK-WT-BL-3.5 方 213.62 幕墙 米 平 玻璃 102 GJ-BY-FB-BL-1.5 方 440.281 幕墙 米 平 玻璃 103 DY-LJ-KF-BL-1 方 37.705 幕墙 米 挡水 104 1×0.9×0.8m 个 0.45 板 建筑 用轻 105 QT 120×80×8mm 米 84.77 钢龙 骨 挡水 106 1×0.85×0.75m 个 21.20 板 挡水 107 1×0.85×0.75m 个 356.62 板 纸面 平 108 石膏 SHC 2440×1200×18mm 方 530.04 板 米 FTC 立 109 保温 A级防火 方 164.00 材料 米 耐碱 玻璃 平 110 纤维 140g/m 方 820.95 网 网格 米 布 耐碱 玻璃 务平 111 纤维 130g/m 方 20110 网格 米 布 合 商 268570.613 计 备注：本次招标范围内地板、大理石等各类石材、装饰材料，所有样品均须提交业主单位审核选定；各投标单 位须全力配合、严格满足招标方及业主提出的道各项材料规格、品质、外观、技术参数要求。 附件3：（包件号：LP-01） 管 招标文件售价 投标保证金 序号 招标人名称 包件号 物资名称 规格型号 计量单位 包件数量 （元） （万元） 德阳智能制造产教 1 LP-01 铝单板 3mm 平方米 70000 500 5 0 融合项目 国 附件3.1 备注：本次招标铝单板供货以实际到场产品型号为准，产品具体详见附件3.1，施工期间存在图纸变更、型号参 数调整的可中能，最终供货型号以甲方确认的最新图纸为准。 附件4：（包件号：L C -01） 计量单 招标文件售价 投标保证金 序号 招标人名称 包件号 物资名称 规格型号 包件数量 位 （元） （万元） 德阳智能制造产教 1 L C -01 铝型材 FeAl52Si5 吨 200 500 1 0 融合项目 合计 200 备注：本次招标铝型材可能因施工期间存在图纸变更、型号参数调整的可能，最终供货型号以甲方确认的最新 图纸为准。供货以实际到场产品型号为准，产品具体详见招标文件附件1.2铝型材清单附件 点击查看内容 信息来源:https://www.chinapipe.net/project/d3079200.html cqdingjiu 2026.08.25 10:30:26</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>德阳智能制造产教融合项目
+          <t>与招标内容 道 2.1项目概况 德阳智能制造产教融合项目本项目位于四川省德阳市旌阳区长江西路沿线与天府大道北延线（二环路）交汇处 西北角地块。 建设内容及规模：本工程平时为地下停车场，战时为二等人员掩蔽所，人防工程应建总建筑面 管 积14720.18㎡，（十层及十层以上）+190208*0.025（九层及九层以下埋深小于3m）+655（九层及九层以下埋深大 于3m）人防实际工程总建筑面积14910.15㎡，项目总建筑面积324848㎡，项目合同工期：随土建工程进度。 2.2招标内容 ：详见招标公告附件《招标物资包件清单》，本次招标一包一投。 国 2.3招标内容及包件划分 2.3.1招标内容及包件划分：详见招标公告附件1《招标物资包件清单》，本次招标一包一投。
 https://www.chinapipe.net/project/d3079200.html</t>
         </is>
       </c>
@@ -2517,7 +2513,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>管材, 管道</t>
+          <t>AI解析失败</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2560,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高寺镇污水处理厂标段土建及安装工程)(第三次)劳务分包竞争性磋商公告</t>
+          <t>乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高寺镇污水处理厂标段土建及安装工程)(第三次)劳务分包竞争性磋商公告 乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高寺镇污水处理厂标段土建及安装工程)(第三 次)劳务分包的潜在供应商应在四川佳旗建设工程有限公司获取磋商文件，并于2026年8月28日15点30分（北京 时间）前提交响应文件。</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2579,21 +2575,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高寺镇污水处理厂标段土建及安装工程)(第三 次)劳务分包竞争性磋商公告 乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高寺镇污水处理厂标段土建及安装工程)(第三 次）劳务分包的潜在供应商应在四川佳旗建设工程有限公司获取磋商文件，并于2026年8月28日15点30分（北京 时间）前提交响应文件。 一、项目基本情况 1.项目名称：乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高网寺镇污水处理厂标段土建及安 装工程)(第三次)劳务分包 2.采购方式：竞争性磋商 务 3.采购预算（暂估价）：105万元。 4.建设规模：高寺镇污水处理厂标段预估工程量： 土建方面：新建一座辅助用房、一座调节池、一座高效沉商淀池；改造原滤池为污泥池；拆除原入场大门改建及 入场道路。涉及施工工程量有：池体挖方约1200m，回填约240方；辅助用房基础挖方约150m，回填约110方； 入场道路约25米；滤池填料清理约30方；主体结构合计混凝土浇筑量约380m；钢筋用量约50t； 安装方面：高寺镇场外管网新增及改造共计约道4000米。 5.建设地点：乐至县高寺镇 6.计划工期：90日历天。 管 7.标段划分：无。 8.分包内容：本次磋商范围内所有施工内容的劳务、机械及辅材。 国 9.本项目是否接受联合体参与：不接受联合体投标。 二、申请人的资格要求 中 1.满足以下规定： （1）具有独立承担民事责任的能力； （2）具有良好的商业信誉和健全的财务会计制度； （3）具有履行合同所必需的设备和专业技术能力； （4）有依法缴纳税收和社会保障资金的良好记录； （5）参加采购活动前三年内，在经营活动中没有重大违法记录。 2.本项目的特定资格要求： （1）具有有效的施工劳务资质； （2）具有有效的安全生产许可证； 3.禁止参加磋商的情形： （1）列入失信被执行人名单； （2）列入重大税收违法案件当事人名单； （3）列入政府采购严重违法失信名单； （4）列入政府采购严重违法失信行为记录名单。 （5）乐至县国有投资集团有限责任公司劳务供应商库中的不合格供应商。 三、获取磋商文件 时间：2026年8月25日至2026年8月27日，每天上午9:00至12:00，下午14:30至17:00（北京时间，法定节假日除外） 地点：四川佳旗建设工程有限公司205办公室 网 方式：获取磋商文件时，经办人员通过现场提交以下资料：单位介绍信（介绍信上写明联系电话、QQ邮箱；报 名成功后磋商文件通过QQ邮箱发送，或现场自带U盘拷贝）、经办人身份证复印件、企业法人身份证复印件、 营业执照副本复印件、资质证书副本复印件、安全生产许可证副本复印件、投标单位提供委托人的三个月及以 务 上社保证明（法人本人报名除外）。 备注：1.以上资料需要加盖鲜章且不支持邮寄。 2.请投标单位认真准备报名资料；如有错误、不齐等情况商不予报名。 磋商文件每套售价：400.00元（售后不退） 四、响应文件提交 道 截止时间：2026年8月28日15点30分（北京时间） 地点：乐至县国有投资集团有限责任公司2楼会议室(若发生变动，将提前通过电话予以通知） 管 五、开启 时间：2026年8月28日15点30分（北京时间） 国 地点：乐至县国有投资集团有限责任公司2楼会议室(若发生变动，将提前通过电话予以通知） 六、公告期限 中 自本公告发布之日起3个工作日。 七、其他补充事宜 本公告在乐至县国有投资集团有限责任公司官网（http：//www.lzgytzjt.com）发布。 八、联系方式 发包人：四川佳旗建设工程有限公司 地址：四川省资阳市乐至县文庙沟165号 联系人：向老师 联系电话：13629016114 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3079181.html cqdingjiu 2026.08.25 09:25:51</t>
+          <t>乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高寺镇污水处理厂标段土建及安装工程)(第三 次)劳务分包竞争性磋商公告 乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高寺镇污水处理厂标段土建及安装工程)(第三 次）劳务分包的潜在供应商应在四川佳旗建设工程有限公司获取磋商文件，并于2026年8月28日15点30分（北京 时间）前提交响应文件。 一、项目基本情况 1.项目名称：乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高网寺镇污水处理厂标段土建及安 装工程)(第三次)劳务分包 2.采购方式：竞争性磋商 务 3.采购预算（暂估价）：105万元。 4.建设规模：高寺镇污水处理厂标段预估工程量： 土建方面：新建一座辅助用房、一座调节池、一座高效沉商淀池；改造原滤池为污泥池；拆除原入场大门改建及 入场道路。涉及施工工程量有：池体挖方约1200m，回填约240方；辅助用房基础挖方约150m，回填约110方； 入场道路约25米；滤池填料清理约30方；主体结构合计混凝土浇筑量约380m；钢筋用量约50t； 安装方面：高寺镇场外管网新增及改造共计约道4000米。 5.建设地点：乐至县高寺镇 6.计划工期：90日历天。 管 7.标段划分：无。 8.分包内容：本次磋商范围内所有施工内容的劳务、机械及辅材。 国 9.本项目是否接受联合体参与：不接受联合体投标。 二、申请人的资格要求 中 1.满足以下规定： （1）具有独立承担民事责任的能力； （2）具有良好的商业信誉和健全的财务会计制度； （3）具有履行合同所必需的设备和专业技术能力； （4）有依法缴纳税收和社会保障资金的良好记录； （5）参加采购活动前三年内，在经营活动中没有重大违法记录。 2.本项目的特定资格要求： （1）具有有效的施工劳务资质； （2）具有有效的安全生产许可证； 3.禁止参加磋商的情形： （1）列入失信被执行人名单； （2）列入重大税收违法案件当事人名单； （3）列入政府采购严重违法失信名单； （4）列入政府采购严重违法失信行为记录名单。 （5）乐至县国有投资集团有限责任公司劳务供应商库中的不合格供应商。 三、获取磋商文件 时间：2026年8月25日至2026年8月27日，每天上午9:00至12:00，下午14:30至17:00（北京时间，法定节假日除外） 地点：四川佳旗建设工程有限公司205办公室 网 方式：获取磋商文件时，经办人员通过现场提交以下资料：单位介绍信（介绍信上写明联系电话、QQ邮箱；报 名成功后磋商文件通过QQ邮箱发送，或现场自带U盘拷贝）、经办人身份证复印件、企业法人身份证复印件、 营业执照副本复印件、资质证书副本复印件、安全生产许可证副本复印件、投标单位提供委托人的三个月及以 务 上社保证明（法人本人报名除外）。 备注：1.以上资料需要加盖鲜章且不支持邮寄。 2.请投标单位认真准备报名资料；如有错误、不齐等情况商不予报名。 磋商文件每套售价：400.00元（售后不退） 四、响应文件提交 道 截止时间：2026年8月28日15点30分（北京时间） 地点：乐至县国有投资集团有限责任公司2楼会议室(若发生变动，将提前通过电话予以通知） 管 五、开启 时间：2026年8月28日15点30分（北京时间） 国 地点：乐至县国有投资集团有限责任公司2楼会议室(若发生变动，将提前通过电话予以通知） 六、公告期限 中 自本公告发布之日起3个工作日。 七、其他补充事宜 本公告在乐至县国有投资集团有限责任公司官网（http：//www.lzgytzjt.com）发布。 八、联系方式 发包人：四川佳旗建设工程有限公司 地址：四川省资阳市乐至县文庙沟165号 联系人：向老师 联系电话：13629016114 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3079181.html cqdingjiu 2026.08.25 10:30:30</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高寺镇污水处理厂标段土建及安装工程)(第三次)劳务分包竞争性磋商公告
+          <t>乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高寺镇污水处理厂标段土建及安装工程)(第三次)劳务分包竞争性磋商公告 乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(高寺镇污水处理厂标段土建及安装工程)(第三 次)劳务分包的潜在供应商应在四川佳旗建设工程有限公司获取磋商文件，并于2026年8月28日15点30分（北京 时间）前提交响应文件。
 https://www.chinapipe.net/project/d3079181.html</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2646,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>施工劳务</t>
+          <t>施工劳务、机械及辅材</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(中天镇污水处理厂标段土建及安装工程)劳务分 包竞争性磋商公告 乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目（中天镇污水处理厂标段土建及安装工程）劳 务分包的潜在供应商应在四川佳旗建设工程有限公司获取磋商文件，并于2026年8月28日15点00分（北京时间） 前提交响应文件。 一、项目基本情况 1.项目名称：乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目（网中天镇污水处理厂标段土建及安 装工程）劳务分包 2.采购方式：竞争性磋商 务 3.采购预算（暂估价）：90万元。 4.建设规模：中天镇污水处理厂标段预估工程量： 中天场站地基处理换填约900m；旧设施拆除挖除约1500m商，回填约1100m；池体挖方约1100m，填方 约300m；主体结构合计混凝土浇筑量约750m，钢筋用量约50t；中天镇管网新增及改造共计约1400米。 5.建设地点：乐至县中天镇 道 6.计划工期：90日历天。 7.标段划分：无。 管 8.分包内容：本次磋商范围内所有施工内容的劳务、机械及辅材。 9.本项目是否接受联合体参与：不接受联合体投标。 二、申请人的资格要求国 1.满足以下规定： （1）具有独立承担民事责任的能力； 中 （2）具有良好的商业信誉和健全的财务会计制度； （3）具有履行合同所必需的设备和专业技术能力； （4）有依法缴纳税收和社会保障资金的良好记录； （5）参加采购活动前三年内，在经营活动中没有重大违法记录。 2.本项目的特定资格要求： （1）具有有效的施工劳务资质； （2）具有有效的安全生产许可证； 3.禁止参加磋商的情形： （1）列入失信被执行人名单； （2）列入重大税收违法案件当事人名单； （3）列入政府采购严重违法失信名单； （4）列入政府采购严重违法失信行为记录名单。 （5）乐至县国有投资集团有限责任公司劳务供应商库中的不合格供应商。 三、获取磋商文件 时间：2026年8月25日至2026年8月27日，每天上午9:00至12:00，下午14:30至17:00（北京时间，法定节假日除外） 地点：四川佳旗建设工程有限公司205办公室 方式：获取磋商文件时，经办人员通过现场提交以下资料：单位介绍信（介绍信网上写明联系电话、QQ邮箱；报 名成功后磋商文件通过QQ邮箱发送，或现场自带U盘拷贝）、经办人身份证复印件、企业法人身份证复印件、 营业执照副本复印件、资质证书副本复印件、安全生产许可证副本复印件、投标单位提供委托人的三个月及以 上社保证明（法人本人报名除外）。 务 备注：1.以上资料需要加盖鲜章且不支持邮寄。 2.请投标单位认真准备报名资料；如有错误、不齐等情况不予报名。 磋商文件每套售价：400.00元（售后不退） 商 四、响应文件提交 截止时间：2026年8月28日15点00分（北京时间道） 地点：乐至县国有投资集团有限责任公司2楼会议室(若发生变动，将提前通过电话予以通知） 五、开启 管 时间：2026年8月28日15点00分（北京时间） 地点：乐至县国有投资集团有限责任公司2楼会议室(若发生变动，将提前通过电话予以通知） 国 六、公告期限 自本公告发布之日起3个工作日。 中 七、其他补充事宜 本公告在乐至县国有投资集团有限责任公司官网（http：//www.lzgytzjt.com）发布。 八、联系方式 发包人：四川佳旗建设工程有限公司 地址：四川省资阳市乐至县文庙沟165号 联系人：向老师 联系电话：13629016114 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3079180.html cqdingjiu 2026.08.25 09:25:51</t>
+          <t>乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目(中天镇污水处理厂标段土建及安装工程)劳务分 包竞争性磋商公告 乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目（中天镇污水处理厂标段土建及安装工程）劳 务分包的潜在供应商应在四川佳旗建设工程有限公司获取磋商文件，并于2026年8月28日15点00分（北京时间） 前提交响应文件。 一、项目基本情况 1.项目名称：乐至县建制镇污水处理厂生活污水设施及配套管网升级改造项目（网中天镇污水处理厂标段土建及安 装工程）劳务分包 2.采购方式：竞争性磋商 务 3.采购预算（暂估价）：90万元。 4.建设规模：中天镇污水处理厂标段预估工程量： 中天场站地基处理换填约900m；旧设施拆除挖除约1500m商，回填约1100m；池体挖方约1100m，填方 约300m；主体结构合计混凝土浇筑量约750m，钢筋用量约50t；中天镇管网新增及改造共计约1400米。 5.建设地点：乐至县中天镇 道 6.计划工期：90日历天。 7.标段划分：无。 管 8.分包内容：本次磋商范围内所有施工内容的劳务、机械及辅材。 9.本项目是否接受联合体参与：不接受联合体投标。 二、申请人的资格要求国 1.满足以下规定： （1）具有独立承担民事责任的能力； 中 （2）具有良好的商业信誉和健全的财务会计制度； （3）具有履行合同所必需的设备和专业技术能力； （4）有依法缴纳税收和社会保障资金的良好记录； （5）参加采购活动前三年内，在经营活动中没有重大违法记录。 2.本项目的特定资格要求： （1）具有有效的施工劳务资质； （2）具有有效的安全生产许可证； 3.禁止参加磋商的情形： （1）列入失信被执行人名单； （2）列入重大税收违法案件当事人名单； （3）列入政府采购严重违法失信名单； （4）列入政府采购严重违法失信行为记录名单。 （5）乐至县国有投资集团有限责任公司劳务供应商库中的不合格供应商。 三、获取磋商文件 时间：2026年8月25日至2026年8月27日，每天上午9:00至12:00，下午14:30至17:00（北京时间，法定节假日除外） 地点：四川佳旗建设工程有限公司205办公室 方式：获取磋商文件时，经办人员通过现场提交以下资料：单位介绍信（介绍信网上写明联系电话、QQ邮箱；报 名成功后磋商文件通过QQ邮箱发送，或现场自带U盘拷贝）、经办人身份证复印件、企业法人身份证复印件、 营业执照副本复印件、资质证书副本复印件、安全生产许可证副本复印件、投标单位提供委托人的三个月及以 上社保证明（法人本人报名除外）。 务 备注：1.以上资料需要加盖鲜章且不支持邮寄。 2.请投标单位认真准备报名资料；如有错误、不齐等情况不予报名。 磋商文件每套售价：400.00元（售后不退） 商 四、响应文件提交 截止时间：2026年8月28日15点00分（北京时间道） 地点：乐至县国有投资集团有限责任公司2楼会议室(若发生变动，将提前通过电话予以通知） 五、开启 管 时间：2026年8月28日15点00分（北京时间） 地点：乐至县国有投资集团有限责任公司2楼会议室(若发生变动，将提前通过电话予以通知） 国 六、公告期限 自本公告发布之日起3个工作日。 中 七、其他补充事宜 本公告在乐至县国有投资集团有限责任公司官网（http：//www.lzgytzjt.com）发布。 八、联系方式 发包人：四川佳旗建设工程有限公司 地址：四川省资阳市乐至县文庙沟165号 联系人：向老师 联系电话：13629016114 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3079180.html cqdingjiu 2026.08.25 10:30:30</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2669,7 +2665,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>污水处理厂, 生活污水设施, 配套管网升级改造, 施工劳务</t>
+          <t>管材招标, 污水处理厂, 管网改造</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2712,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>成都市金牛区通锦路、通锦西一巷市政道路及排水管网建设工程施工/标段。</t>
+          <t>成都市金牛区通锦路和通锦西一巷的市政道路及排水管网建设工程。</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2726,17 +2722,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>排水管网</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>通锦路、通锦西一巷市政道路及排水管网建设工程施工/标段招标文件提前公示 招标人（建设单 行业分 标段类 联系人及联 拟建项目名称 标段名称 招标文件 位） 类 型 系方式 通锦路、通锦西一 通锦路、通锦西一 通锦路、通锦西一 成都市金牛国投 巷市政道路及排水 施工招 巷市政道路及排水 冉先 巷市政道路及排水 市政 建设有限公司 管网建设工程施工/ 标 管网建设工 生028-87576215 管网建设工程 标段 程824.pdf 其他：招标文件以实际招标公告发布时的招标文件为准。 网 信息来源:https://www.chinapipe.net/project/d3079176.html cqdingjiu 2026.08.25 09:25:51 务 商 道 管 国 中</t>
+          <t>通锦路、通锦西一巷市政道路及排水管网建设工程施工/标段招标文件提前公示 招标人（建设单 行业分 标段类 联系人及联 拟建项目名称 标段名称 招标文件 位） 类 型 系方式 通锦路、通锦西一 通锦路、通锦西一 通锦路、通锦西一 成都市金牛国投 巷市政道路及排水 施工招 巷市政道路及排水 冉先 巷市政道路及排水 市政 建设有限公司 管网建设工程施工/ 标 管网建设工 生028-87576215 管网建设工程 标段 程824.pdf 其他：招标文件以实际招标公告发布时的招标文件为准。 网 信息来源:https://www.chinapipe.net/project/d3079176.html cqdingjiu 2026.08.25 10:30:31 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>成都市金牛区通锦路、通锦西一巷市政道路及排水管网建设工程施工/标段。
+          <t>成都市金牛区通锦路和通锦西一巷的市政道路及排水管网建设工程。
 https://www.chinapipe.net/project/d3079176.html</t>
         </is>
       </c>
@@ -2792,27 +2788,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>项目详情见附件。</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>梓潼县农村供水高质量发展三年提升项目其他材料采购项目-招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3079101.html cqdingjiu 2026.08.25 09:25:51 网 务 商 道 管 国 中</t>
+          <t>梓潼县农村供水高质量发展三年提升项目其他材料采购项目-招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3079101.html cqdingjiu 2026.08.25 10:30:31 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别
+          <t>项目详情见附件。
 https://www.chinapipe.net/project/d3079101.html</t>
         </is>
       </c>
@@ -2821,7 +2817,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>分析, 重庆, 近三天, 管材, 招标商机</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2879,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>梓潼县农村供水高质量发展三年提升项目PE管采购项目-招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3079099.html cqdingjiu 2026.08.25 09:25:51 网 务 商 道 管 国 中</t>
+          <t>梓潼县农村供水高质量发展三年提升项目PE管采购项目-招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3079099.html cqdingjiu 2026.08.25 10:30:31 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2945,7 +2941,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2955,7 +2951,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>梓潼县农村供水高质量发展三年提升项目钢管采购项目-招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3079097.html cqdingjiu 2026.08.25 09:25:51 网 务 商 道 管 国 中</t>
+          <t>梓潼县农村供水高质量发展三年提升项目钢管采购项目-招标公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3079097.html cqdingjiu 2026.08.25 10:30:31 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2969,7 +2965,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>钢管</t>
+          <t>农村供水, 高质量发展, 三年提升项目, 钢管采购</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3027,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>绵阳市游仙区(城区)老旧燃气管道等更新改造工程项目(一期)施工补遗02号 绵阳市游仙区（城区）老旧燃气管道等更新改造工程项目(一期）施工 补遗02号 致：各潜在投标人 网 1.本项目招标控制价文件重新上传。请以上传后的招标控制价文件为准。 2.本项目开标时间、投标文件递交截止时间及保证金缴纳截止时间更正为2026年09月10日09时10分。 务 3.招标文件其他内容不变，请各投标人自行下载查询。由此带来的不便，敬请谅解！ 商 招标人：绵阳市游仙区市政工程建设维护中心 招标代理机构：四川鑫宇工程项目管理有限公司 道 2026年8月24日 管 信息来源:https://www.chinapipe.net/project/d3078977.html cqdingjiu 2026.08.25 09:25:52 国 中</t>
+          <t>绵阳市游仙区(城区)老旧燃气管道等更新改造工程项目(一期)施工补遗02号 绵阳市游仙区（城区）老旧燃气管道等更新改造工程项目(一期）施工 补遗02号 致：各潜在投标人 网 1.本项目招标控制价文件重新上传。请以上传后的招标控制价文件为准。 2.本项目开标时间、投标文件递交截止时间及保证金缴纳截止时间更正为2026年09月10日09时10分。 务 3.招标文件其他内容不变，请各投标人自行下载查询。由此带来的不便，敬请谅解！ 商 招标人：绵阳市游仙区市政工程建设维护中心 招标代理机构：四川鑫宇工程项目管理有限公司 道 2026年8月24日 管 信息来源:https://www.chinapipe.net/project/d3078977.html cqdingjiu 2026.08.25 10:30:31 国 中</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3107,7 +3103,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>巴中市巴州区平梁至光辉片区小型引调水工程勘察设计补遗01号 巴中市巴州区平梁至光辉片区小型引调水工程勘察设计 补遗01号 致各潜在投标人： 关于巴中市巴州区平梁至光辉片区小型引调水工程勘察设计招标文件，需要更正: 网 一、将“投标保证金的金额： 1000.00元（小写）, 壹万元整元（大写）。”内容更正为“投标保证金的金额： 10000.00元（小写）, 壹万元整（大写）。” 二、招标文件第三章评标办法中2.2.4其他人员：“1、具有工程类中级职称得2分；高级及以上职称得3分；具有 务 注册土木工程师（水利水电工程）水工结构资格证加1分。本项最高得4分。”内容更正为：“1、水工专业负责 人：具有工程类中级职称得2分；高级及以上职称得3分；具有注册土木工程师（水利水电工程）水工结构资格证 加1分。本项最高得4分。” 三、开标时间更改为：2026年9月16日09：00。 商 四、其他内容不变。 道 招标人: 巴中源通水务集团有限公司（盖单位章） 编制单位: 四川和达建设工程有限公司 （盖单位章） 管 2026年08月24日 国 信息来源:https://www.chinapipe.net/project/d3078976.html 中 cqdingjiu 2026.08.25 09:25:52</t>
+          <t>巴中市巴州区平梁至光辉片区小型引调水工程勘察设计补遗01号 巴中市巴州区平梁至光辉片区小型引调水工程勘察设计 补遗01号 致各潜在投标人： 关于巴中市巴州区平梁至光辉片区小型引调水工程勘察设计招标文件，需要更正: 网 一、将“投标保证金的金额： 1000.00元（小写）, 壹万元整元（大写）。”内容更正为“投标保证金的金额： 10000.00元（小写）, 壹万元整（大写）。” 二、招标文件第三章评标办法中2.2.4其他人员：“1、具有工程类中级职称得2分；高级及以上职称得3分；具有 务 注册土木工程师（水利水电工程）水工结构资格证加1分。本项最高得4分。”内容更正为：“1、水工专业负责 人：具有工程类中级职称得2分；高级及以上职称得3分；具有注册土木工程师（水利水电工程）水工结构资格证 加1分。本项最高得4分。” 三、开标时间更改为：2026年9月16日09：00。 商 四、其他内容不变。 道 招标人: 巴中源通水务集团有限公司（盖单位章） 编制单位: 四川和达建设工程有限公司 （盖单位章） 管 2026年08月24日 国 信息来源:https://www.chinapipe.net/project/d3078976.html 中 cqdingjiu 2026.08.25 10:30:31</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3173,17 +3169,17 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>招标控制价：99765900元，其中建安工程费用93205100元，设计费1447000元，预备费5113800元。</t>
+          <t>招标控制价为99765900元，其中建安工程费用93205100元，设计费1447000元，预备费5113800元。</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>生活污水厂网河湖一体化治理设备</t>
+          <t>排水管网及污水处理设施</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>关于凯江流域(罗江区段)7个城镇生活污水厂网河湖一体化综合治理招标文件的澄清/补遗 凯江流域(罗江区段)7 个城镇生活污水厂网河湖一体化综合治理（项目名称）设计施工总承包/标段补遗文件01号 致各潜在投标人： 一、原招标文件第二章投标人须知3.2.4最高投标限价或其计算方法—招标控制价修改为：招标控制价：99765900 元 网 二、原招标文件第二章投标人须知3.2.5投标报价的其他要求—其他：修改为：一、招标控制价99765900元。其中： 1、建安工程费用93205100元；2、设计费为1447000元；3、与建设项目相关的其他费用0元；4、预备费5113800元。 务 三、清单已重新上传，请自行下载。 其余内容不变。 商 信息来源:https://www.chinapipe.net/project/d3078975.html cqdingjiu 2026.08.25 09:25:52 道 管 国 中</t>
+          <t>关于凯江流域(罗江区段)7个城镇生活污水厂网河湖一体化综合治理招标文件的澄清/补遗 凯江流域(罗江区段)7 个城镇生活污水厂网河湖一体化综合治理（项目名称）设计施工总承包/标段补遗文件01号 致各潜在投标人： 一、原招标文件第二章投标人须知3.2.4最高投标限价或其计算方法—招标控制价修改为：招标控制价：99765900 元 网 二、原招标文件第二章投标人须知3.2.5投标报价的其他要求—其他：修改为：一、招标控制价99765900元。其中： 1、建安工程费用93205100元；2、设计费为1447000元；3、与建设项目相关的其他费用0元；4、预备费5113800元。 务 三、清单已重新上传，请自行下载。 其余内容不变。 商 信息来源:https://www.chinapipe.net/project/d3078975.html cqdingjiu 2026.08.25 10:30:32 道 管 国 中</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3232,16 +3228,8 @@
           <t>四川省</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>巴中市</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>巴中市</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>勘察设计/标段流标公告</t>
@@ -3259,7 +3247,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>关于巴中曾口化工园天然气保障及管道建设项目勘察设计/标段流标公告 关于巴中曾口化工园天然气保障及管道建设项目 (项目名称)勘察设计/标段流标公告 致各投标人： 网 巴中曾口化工园天然气保障及管道建设项目（项目名称）勘察设计/标段招标项目，于2026年08月24日09时00分在 巴中市公共资源交易服务中心开标。因截止本项目投标文件递交的截止时间(投标截止时间)2026年08月24日09 时00分递交投标文件不足三家，故本项目流标。 务 招标人：巴中科发商业管理有限公司 商 2026年08月24日 道 信息来源:https://www.chinapipe.net/project/d3078973.html cqdingjiu 2026.08.25 09:25:52 管 国 中</t>
+          <t>关于巴中曾口化工园天然气保障及管道建设项目勘察设计/标段流标公告 关于巴中曾口化工园天然气保障及管道建设项目 (项目名称)勘察设计/标段流标公告 致各投标人： 网 巴中曾口化工园天然气保障及管道建设项目（项目名称）勘察设计/标段招标项目，于2026年08月24日09时00分在 巴中市公共资源交易服务中心开标。因截止本项目投标文件递交的截止时间(投标截止时间)2026年08月24日09 时00分递交投标文件不足三家，故本项目流标。 务 招标人：巴中科发商业管理有限公司 商 2026年08月24日 道 信息来源:https://www.chinapipe.net/project/d3078973.html cqdingjiu 2026.08.25 10:30:32 管 国 中</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3273,7 +3261,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>管材招标</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -3308,8 +3296,16 @@
           <t>四川省</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>眉山市</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>眉山市</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>本项目为天府大道眉山段道路工程水环境污染防治工程，涉及混凝土和排水管的公开招标。</t>
@@ -3327,7 +3323,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>天府大道眉山段道路工程水环境污染防治工程混凝土、排水管公开招标公告(第二次) 详见附件 信息来源:https://www.chinapipe.net/project/d3078974.html cqdingjiu 2026.08.25 09:25:52 网 务 商 道 管 国 中</t>
+          <t>天府大道眉山段道路工程水环境污染防治工程混凝土、排水管公开招标公告(第二次) 详见附件 信息来源:https://www.chinapipe.net/project/d3078974.html cqdingjiu 2026.08.25 10:30:32 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3388,27 +3384,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>本项目主要对道江北片区长寿路、弄弄坪中路、大花地东路16号、新民路、烂院子综合楼等5个老旧小区，改造燃气管道2.67千米，改造排水防涝管网及沟渠20.97千米；改造小区相关道路1.215千米；改造人行道2.92千米；改造给水管网2.45千米，改造供电电缆8.5千米，改造居民活动场地3400平方米，改造停车场3420平方米以及安全隐患治理等配套基础设施。</t>
+          <t>本项目主要对江北片区长寿路、弄弄坪中路、大花地东路16号、新民路、烂院子综合楼等5个老旧小区进行改造，包括燃气管道、排水防涝管网及沟渠、小区道路、人行道、给水管网、供电电缆、居民活动场地、停车场以及安全隐患治理等配套基础设施的改造。</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>项目总投资为6270.05万元；本标段工程费为22507291.86元</t>
+          <t>项目总投资为6270.05万元，本标段工程费为22507291.86元。</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>燃气管道、排水防涝管网、小区相关道路、人行道、给水管网、供电电缆、居民活动场地、停车场、安全隐患治理等配套基础设施</t>
+          <t>市政公用设施改造</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>攀枝花市东区江北片区长寿路小区等5个老旧小区改造配套基础设施建设项目(项目名称)施工二标段招标公告 攀枝花市东区江北片区长寿路小区等5个老旧小区改造配套基础设施建设项目 (项目名称)施工 二标段招标公 告 1. 招标条件 1.1本招标项目 攀枝花市东区江北片区长寿路小区等5个老旧小区改造配套基础设施建设项目 (项目 名称)已由 攀枝花市东区发展和改革局 (项目审批、核准或备案机关名称)以 攀枝花市东区发展和改革局关 于攀枝花市东区江北片区长寿路小区等5个老旧小区改造配套基础设施建设项目网可行性研究报告的批复、攀东发 改审批〔2023〕55号 （批文名称及编号）批准建设，项目业主为 攀枝花市东区人民政府瓜子坪街道办事处 ， 建设资金来自 争取中央预算内资金及地方配套资金 （资金来源），项目出资比例为 100% ，招标人为 攀枝花市东区人民政府瓜子坪街道办事处 。项目已具备招标条件，现对该项目的施工进行公开招标。 务 1.2本招标项目由 攀枝花市东区发展和改革局 （核准机关名称）核准（招标事项核准文号为 攀东发改审批 〔2023〕55号 ）的招标组织形式为 委托招标 （□自行招标 委托招标）。招标人选择的招标代理机构 是 四川志泽建设项目管理有限公司 。 2. 项目概况与招标范围 商 2.1建设地点:攀枝花市东区江北片区。 2.2建设规模及主要建设内容：项目建设主要对道江北片区长寿路、弄弄坪中路、大花地东路 16 号、新民路、烂院 子综合楼等 5 个老旧小区，改造燃气管道 2.67 千米，改造排水防涝管网及沟渠 20.97千米；改造小区相关道路 1.215 千米；改造人行道 2.92 千米；改造给水管网 2.45 千米，改造供电电缆 8.5 千米，改造居民活动场地 3400 平 方米，改造停车场 3420 平方米以及安全隐患治理等配套基础设施。涉及区域居民 2508 户，7524 人。具体以施工图 （含工程设计变更；引用的标准规范、技术规程和标准设计图集等）和工程量清单涵盖的内容为准。 管 2.3项目总投资为：6270.05万元；本标段工程费为22507291.86元； 2.4招标范围：施工图（含工程设计变更；引用的标准规范、技术规程和标准设计图集等）和工程量清单涵盖的 全部内容。 国 2.5计划工期：90日历天。 2.6标段划分中：施工1个标段 。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质条件：具有独立的企业法人，具有建设行政主管部门颁发的市政公用工程施工总承包贰级及以上资质 。 3.1.2业绩要求： □近年（ 年 月 日至投标截止时间，不少于3年）（□已完成 □已完成或新承接或正在施工）不少 于 （1至3个）个类似项目。类似项目是指: 。 无业绩要求。 3.1.3项目经理的资格要求： 项目经理（项目负责人）资格： 市政公用工程 (注册专业)贰级及以上（级别）建造师，具有省级及以上住 房城乡建设主管部门颁发的安全生产考核合格证（B证）， （业绩要求），须为本单位人员（若为联 合体投标，须为联合体牵头人人员）。 □园林绿化工程项目经理（项目负责人）资格： （职称级别）专业技术职称， （业绩 要求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： 。 3.3各投标人均可就上述 1 (具体数量)标段投标。 3.4本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企业、与大企业的负责 人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体 标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通 知》（工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术 复杂、存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在300网0万元以下的施工项目(标段)应勾 选此项。） 4. 招标文件的获取 务 4.1 凡有意参加投标者，请于 2026 年 08 月 25 日开始登陆：□全国公共资源交易平台（四川省） （网址：http://ggzyjy.sc.gov.cn）—“登录”——“交易主体”—“建设工程”，通过数字证书免费下载招标资料 （招标文件、技术资料等）。全国公共资源交易平台（四川省· 攀枝 市（州））（网 址：http://ggzy.panzhihua.gov.cn/ ）—“登录”—“ 攀枝花市工程建设交易系统 ”，通过数字证书免费下载 招标资料（招标文件、技术资料等）。 商 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 道 投标文件递交的截止时间（投标截止时间，下同）为 2026 年 09 月 14 日 09 时30 分，投标人应 在投标截止时间前在线递交经投标人数字证书加密的数据电文形式投标文件。 管 6. 发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省）》和 全国公共资源交易平台（四川省攀枝花 市）》 (公告发布的其它媒介名称）上发布。 国 7. 行政监督部门 单位名称： 攀枝花市东区住房和城乡建设局 中 联系电话：0812-2232257 8. 联系方式 招 标 人： 攀枝花市东区人民政府瓜子坪街道办事处 地 址：攀枝花市东区隆庆路134号 邮 编： 617000 联 系 人： 胡先生 电 话： 15182716067 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / □ 招标代理机构： / 招标代理机构：四川志泽建设项目管理有限公司 地 址：成都市成华区双林路44号 邮 编：610041 联 系 人： 徐文秀 项目负责人： 徐文秀 网 电 话：028-84383659 传 真： 028-84383659 务 电子邮件： / 网 址： / 商 开户银行： / 账 号： / 道 2026 年 08 月 24 日 信息来源:https://www.chinapipe.net/project/d3078970.html 管 cqdingjiu 2026.08.25 09:25:52 国 中</t>
+          <t>攀枝花市东区江北片区长寿路小区等5个老旧小区改造配套基础设施建设项目(项目名称)施工二标段招标公告 攀枝花市东区江北片区长寿路小区等5个老旧小区改造配套基础设施建设项目 (项目名称)施工 二标段招标公 告 1. 招标条件 1.1本招标项目 攀枝花市东区江北片区长寿路小区等5个老旧小区改造配套基础设施建设项目 (项目 名称)已由 攀枝花市东区发展和改革局 (项目审批、核准或备案机关名称)以 攀枝花市东区发展和改革局关 于攀枝花市东区江北片区长寿路小区等5个老旧小区改造配套基础设施建设项目网可行性研究报告的批复、攀东发 改审批〔2023〕55号 （批文名称及编号）批准建设，项目业主为 攀枝花市东区人民政府瓜子坪街道办事处 ， 建设资金来自 争取中央预算内资金及地方配套资金 （资金来源），项目出资比例为 100% ，招标人为 攀枝花市东区人民政府瓜子坪街道办事处 。项目已具备招标条件，现对该项目的施工进行公开招标。 务 1.2本招标项目由 攀枝花市东区发展和改革局 （核准机关名称）核准（招标事项核准文号为 攀东发改审批 〔2023〕55号 ）的招标组织形式为 委托招标 （□自行招标 委托招标）。招标人选择的招标代理机构 是 四川志泽建设项目管理有限公司 。 2. 项目概况与招标范围 商 2.1建设地点:攀枝花市东区江北片区。 2.2建设规模及主要建设内容：项目建设主要对道江北片区长寿路、弄弄坪中路、大花地东路 16 号、新民路、烂院 子综合楼等 5 个老旧小区，改造燃气管道 2.67 千米，改造排水防涝管网及沟渠 20.97千米；改造小区相关道路 1.215 千米；改造人行道 2.92 千米；改造给水管网 2.45 千米，改造供电电缆 8.5 千米，改造居民活动场地 3400 平 方米，改造停车场 3420 平方米以及安全隐患治理等配套基础设施。涉及区域居民 2508 户，7524 人。具体以施工图 （含工程设计变更；引用的标准规范、技术规程和标准设计图集等）和工程量清单涵盖的内容为准。 管 2.3项目总投资为：6270.05万元；本标段工程费为22507291.86元； 2.4招标范围：施工图（含工程设计变更；引用的标准规范、技术规程和标准设计图集等）和工程量清单涵盖的 全部内容。 国 2.5计划工期：90日历天。 2.6标段划分中：施工1个标段 。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 3.1.1资质条件：具有独立的企业法人，具有建设行政主管部门颁发的市政公用工程施工总承包贰级及以上资质 。 3.1.2业绩要求： □近年（ 年 月 日至投标截止时间，不少于3年）（□已完成 □已完成或新承接或正在施工）不少 于 （1至3个）个类似项目。类似项目是指: 。 无业绩要求。 3.1.3项目经理的资格要求： 项目经理（项目负责人）资格： 市政公用工程 (注册专业)贰级及以上（级别）建造师，具有省级及以上住 房城乡建设主管部门颁发的安全生产考核合格证（B证）， （业绩要求），须为本单位人员（若为联 合体投标，须为联合体牵头人人员）。 □园林绿化工程项目经理（项目负责人）资格： （职称级别）专业技术职称， （业绩 要求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受 不接受联合体投标。联合体投标的，应满足下列要求： 。 3.3各投标人均可就上述 1 (具体数量)标段投标。 3.4本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企业、与大企业的负责 人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体 标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通 知》（工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术 复杂、存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在300网0万元以下的施工项目(标段)应勾 选此项。） 4. 招标文件的获取 务 4.1 凡有意参加投标者，请于 2026 年 08 月 25 日开始登陆：□全国公共资源交易平台（四川省） （网址：http://ggzyjy.sc.gov.cn）—“登录”——“交易主体”—“建设工程”，通过数字证书免费下载招标资料 （招标文件、技术资料等）。全国公共资源交易平台（四川省· 攀枝 市（州））（网 址：http://ggzy.panzhihua.gov.cn/ ）—“登录”—“ 攀枝花市工程建设交易系统 ”，通过数字证书免费下载 招标资料（招标文件、技术资料等）。 商 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 道 投标文件递交的截止时间（投标截止时间，下同）为 2026 年 09 月 14 日 09 时30 分，投标人应 在投标截止时间前在线递交经投标人数字证书加密的数据电文形式投标文件。 管 6. 发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省）》和 全国公共资源交易平台（四川省攀枝花 市）》 (公告发布的其它媒介名称）上发布。 国 7. 行政监督部门 单位名称： 攀枝花市东区住房和城乡建设局 中 联系电话：0812-2232257 8. 联系方式 招 标 人： 攀枝花市东区人民政府瓜子坪街道办事处 地 址：攀枝花市东区隆庆路134号 邮 编： 617000 联 系 人： 胡先生 电 话： 15182716067 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / □ 招标代理机构： / 招标代理机构：四川志泽建设项目管理有限公司 地 址：成都市成华区双林路44号 邮 编：610041 联 系 人： 徐文秀 项目负责人： 徐文秀 网 电 话：028-84383659 传 真： 028-84383659 务 电子邮件： / 网 址： / 商 开户银行： / 账 号： / 道 2026 年 08 月 24 日 信息来源:https://www.chinapipe.net/project/d3078970.html 管 cqdingjiu 2026.08.25 10:30:32 国 中</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>本项目主要对道江北片区长寿路、弄弄坪中路、大花地东路16号、新民路、烂院子综合楼等5个老旧小区，改造燃气管道2.67千米，改造排水防涝管网及沟渠20.97千米；改造小区相关道路1.215千米；改造人行道2.92千米；改造给水管网2.45千米，改造供电电缆8.5千米，改造居民活动场地3400平方米，改造停车场3420平方米以及安全隐患治理等配套基础设施。
+          <t>本项目主要对江北片区长寿路、弄弄坪中路、大花地东路16号、新民路、烂院子综合楼等5个老旧小区进行改造，包括燃气管道、排水防涝管网及沟渠、小区道路、人行道、给水管网、供电电缆、居民活动场地、停车场以及安全隐患治理等配套基础设施的改造。
 https://www.chinapipe.net/project/d3078970.html</t>
         </is>
       </c>
@@ -3417,7 +3413,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>攀枝花市东区江北片区, 老旧小区改造, 基础设施建设项目, 燃气管道, 排水防涝管网, 道路改造, 人行道改造, 给水管网改造, 供电电缆改造, 居民活动场地改造, 停车场改造, 安全隐患治理</t>
+          <t>攀枝花市东区江北片区, 老旧小区改造, 市政公用设施, 燃气管道, 排水防涝管网, 小区道路, 人行道, 给水管网, 供电电缆, 居民活动场地, 停车场</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3455,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>东部新区</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3479,7 +3475,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>东部新区污水处理厂站及配套管网建设项目施工/标段招标公告 东部新区污水处理厂站及配套管网建设项目施工/标段 招标公告 1．招标条件 网 1.1本招标项目东部新区污水处理厂站及配套管网建设项目施工/标段已由成都东部新区战略研究局以川投资备 【2405-510186-04-01-839189】第FGQB-0123号批准建设，项目业主为成都东部环境发展有限公司，建设资金来自 国家投资-非政府投资，项目出资比例为100%，招标人为成都东部环境发展有限公司。项目已具备招标条件，现 进行公开招标。 务 1.2本招标项目由成都东部新区战略研究局核准（招标事项核准文号为川投资备【2405-510186-04-01-839189】 第FGQB-0123号）的招标组织形式为委托招标。招标人选择的招标代理机构是中锦军贤工程咨询集团有限公司。 本标段行政监督部门为成都东部新区管理委员会农业农村商局，采用“评定分离”方式进行评标定标。 2．项目概况与招标范围 道 2.1 建设地点：成都东部新区； 2.2 建设规模：新建约7.956km厂外污水管道，新建污水提升泵站2座，污水处理站1座，改建污水处理厂站17座， 管 新增设置潜污泵6台； 2.3 计划工期：450日历天； 2.4 招标范围：本项目招国标文件、设计施工图纸及工程量清单范围内的全部内容，施工直至竣工验收合格及整体 移交、工程保修期内的缺陷修复和保修工作等全部工作； 2.5 标段划分：一个标段； 中 2.6 质量标准：工程质量符合国家相关工程建设规范合格标准。 3．投标人资格要求 3.1 本次招标要求投标人： 3.1.1须具有建设行政主管部门颁发的市政公用工程施工总承包三级及以上资质； 3.1.2信誉要求：不存在投标人须知第1.4.3项规定的限制投标的情形； 3.1.3所有投标人（无资质企业除外）应具有针对本标段的《成都市建设领域市场主体基础信息网络登记表》、 《成都市建设领域从业人员基础信息网络登记表》。 3.1.4拟派项目经理（项目负责人）具有市政公用工程专业一级或以上注册建造师证书，须具备有效的安全生产考 核合格B证，/（业绩要求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.1.5财务要求： 近3年（限定在3年以内）无亏损； 3.1.6类似工程业绩要求： 近年（2023年01月01日至投标截止时间，不少于3年）已完成或正在施工或新承接的项目共不少于1个类似工程业 绩。 类似工程业绩是指:单个合同金额不低于5000万元的市政公用工程施工业绩。 3.2本次招标不接受联合体投标。 3.3 各投标人均可就上述1个标段投标，可中标的标段数量为1个。 网 4．招标文件的获取 4.1凡有意参加投标者，请于2026年08月25日起，在成都市公共资源电子交易云平台(www.cdggzy.com）（以下简称 “电子交易云平台”）免费下载招标资料（招标文件及相关资料），获得“拟投标项目回执”。 务 4.2招标人不提供 邮购招标文件服务。 5．投标文件的递交 商 5.1 投标文件递交的截止时间（投标截止时间，下同）为2026年09月15日09时30分，招标人或其委托代理机构，以 及已在投标截止时间前按规定上传投标文件的投标人，均应在开标当日投标截止时间前登录不见面开标系统 （网址：www.cdggzy.com），录入相关人员姓名、电话等基本信息。投标人未按时登录不见面开标系统，错过开 标解密时间的，由投标人自行承担不利后果。道 5.2 投标人应在解密开始后30分钟内在线完成投标文件解密。投标文件未能在规定时间内成功解密的，视为投标 人未在规定时间内提交投标文件，由投标人自行承担责任。不见面开标项目不接受投标人现场递交光盘等形式 的投标文件，不接受投标人现场解密投标文件。 管 6．发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）、成都市公共资源交易服务中心（网址：http://ggzyjy.sc.gov.cn、 www.cdggzy.com）上发国布。 7．行政监督部门 中 单位名称：成都东部新区管理委员会农业农村局 联系电话：028-86360020 8. 联系方式 招标人：成都东部环境发展有限公司 地 址：成都东部新区玉成街道龙王庙社区一组179号 邮 编：641420 联系人：欧阳先生 电 话：028-27332920 传 真：/ 电子邮件：/ 网 址：/ 开户银行：/ 账 号：/ 招标代理机构：中锦军贤工程咨询集团有限公司 地 址：成都市双流区东升街道龙桥路6 号 132 栋 7 楼 邮 编：610200 网 联系人：李先生 项目负责人：唐贤萍 务 电 话：028-83119888 传 真：/ 商 电子邮件：/ 网 址：/ 道 开户银行：/ 账 号：/ 管 信息来源:https://www.chinapipe.net/project/d3078961.html cqdingjiu 2026.08.25 09:国25:53 中</t>
+          <t>东部新区污水处理厂站及配套管网建设项目施工/标段招标公告 东部新区污水处理厂站及配套管网建设项目施工/标段 招标公告 1．招标条件 网 1.1本招标项目东部新区污水处理厂站及配套管网建设项目施工/标段已由成都东部新区战略研究局以川投资备 【2405-510186-04-01-839189】第FGQB-0123号批准建设，项目业主为成都东部环境发展有限公司，建设资金来自 国家投资-非政府投资，项目出资比例为100%，招标人为成都东部环境发展有限公司。项目已具备招标条件，现 进行公开招标。 务 1.2本招标项目由成都东部新区战略研究局核准（招标事项核准文号为川投资备【2405-510186-04-01-839189】 第FGQB-0123号）的招标组织形式为委托招标。招标人选择的招标代理机构是中锦军贤工程咨询集团有限公司。 本标段行政监督部门为成都东部新区管理委员会农业农村商局，采用“评定分离”方式进行评标定标。 2．项目概况与招标范围 道 2.1 建设地点：成都东部新区； 2.2 建设规模：新建约7.956km厂外污水管道，新建污水提升泵站2座，污水处理站1座，改建污水处理厂站17座， 管 新增设置潜污泵6台； 2.3 计划工期：450日历天； 2.4 招标范围：本项目招国标文件、设计施工图纸及工程量清单范围内的全部内容，施工直至竣工验收合格及整体 移交、工程保修期内的缺陷修复和保修工作等全部工作； 2.5 标段划分：一个标段； 中 2.6 质量标准：工程质量符合国家相关工程建设规范合格标准。 3．投标人资格要求 3.1 本次招标要求投标人： 3.1.1须具有建设行政主管部门颁发的市政公用工程施工总承包三级及以上资质； 3.1.2信誉要求：不存在投标人须知第1.4.3项规定的限制投标的情形； 3.1.3所有投标人（无资质企业除外）应具有针对本标段的《成都市建设领域市场主体基础信息网络登记表》、 《成都市建设领域从业人员基础信息网络登记表》。 3.1.4拟派项目经理（项目负责人）具有市政公用工程专业一级或以上注册建造师证书，须具备有效的安全生产考 核合格B证，/（业绩要求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.1.5财务要求： 近3年（限定在3年以内）无亏损； 3.1.6类似工程业绩要求： 近年（2023年01月01日至投标截止时间，不少于3年）已完成或正在施工或新承接的项目共不少于1个类似工程业 绩。 类似工程业绩是指:单个合同金额不低于5000万元的市政公用工程施工业绩。 3.2本次招标不接受联合体投标。 3.3 各投标人均可就上述1个标段投标，可中标的标段数量为1个。 网 4．招标文件的获取 4.1凡有意参加投标者，请于2026年08月25日起，在成都市公共资源电子交易云平台(www.cdggzy.com）（以下简称 “电子交易云平台”）免费下载招标资料（招标文件及相关资料），获得“拟投标项目回执”。 务 4.2招标人不提供 邮购招标文件服务。 5．投标文件的递交 商 5.1 投标文件递交的截止时间（投标截止时间，下同）为2026年09月15日09时30分，招标人或其委托代理机构，以 及已在投标截止时间前按规定上传投标文件的投标人，均应在开标当日投标截止时间前登录不见面开标系统 （网址：www.cdggzy.com），录入相关人员姓名、电话等基本信息。投标人未按时登录不见面开标系统，错过开 标解密时间的，由投标人自行承担不利后果。道 5.2 投标人应在解密开始后30分钟内在线完成投标文件解密。投标文件未能在规定时间内成功解密的，视为投标 人未在规定时间内提交投标文件，由投标人自行承担责任。不见面开标项目不接受投标人现场递交光盘等形式 的投标文件，不接受投标人现场解密投标文件。 管 6．发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）、成都市公共资源交易服务中心（网址：http://ggzyjy.sc.gov.cn、 www.cdggzy.com）上发国布。 7．行政监督部门 中 单位名称：成都东部新区管理委员会农业农村局 联系电话：028-86360020 8. 联系方式 招标人：成都东部环境发展有限公司 地 址：成都东部新区玉成街道龙王庙社区一组179号 邮 编：641420 联系人：欧阳先生 电 话：028-27332920 传 真：/ 电子邮件：/ 网 址：/ 开户银行：/ 账 号：/ 招标代理机构：中锦军贤工程咨询集团有限公司 地 址：成都市双流区东升街道龙桥路6 号 132 栋 7 楼 邮 编：610200 网 联系人：李先生 项目负责人：唐贤萍 务 电 话：028-83119888 传 真：/ 商 电子邮件：/ 网 址：/ 道 开户银行：/ 账 号：/ 管 信息来源:https://www.chinapipe.net/project/d3078961.html cqdingjiu 2026.08.25 10:国30:32 中</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3493,7 +3489,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>成都东部新区, 污水处理厂站, 配套管网建设项目, 市政公用工程施工</t>
+          <t>污水处理厂站, 配套管网, 市政公用工程</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3536,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>本工程主要建筑物包括自然能泵房、桃坪中心村提水管道、务科村输水管道、蓄水池等。共建设取水口集水池1座，自然能泵房1座，蓄水池2座，减压池1座，消毒设备2套，新建管道共计21.004km。</t>
+          <t>工程主要建筑物由自然能泵房、桃坪中心村提水管道、务科村输水管道、和蓄水池等组成。本项目共建设取水口集水池1座，自然能泵房1座，蓄水池2座，减压池1座，消毒设备2套，新建管道共计21.004km，其中动力管道长3.839km;桃坪中心村提水管长11.033km。</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3555,12 +3551,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026年天地坝镇桃坪中心村火山组、岩头组青花椒水系工程招标计划公告 2026年天地坝镇桃坪中心村火山组、岩头组青花椒水系工程招标计划公告 招标项目名称 2026年天地坝镇桃坪中心村火山组、岩头组青花椒水系工程 项目批准文件及文号（如有） 金 批 阳 复 县 (金 水 水 利 发 局 〔 关 20 于 26 2 〕 02 6 6 1 年 号 天 ) 地坝镇桃坪中心村火山组、岩头组青花椒水系工程初步设计报告(代项目建议书、代可行性研究报告)的 招标人 金阳县水利局 联系人及联系方式 张老师:08348733445 估 （ 算 元 总 ） 投资 9750200.00 项目分类 水利工程 招标项目概况 2 村 02 输 6年 水 天 管 地 道 坝 6. 镇 132 桃 km 坪 . 中心村火山组、岩头组青花椒水系工程，工程主要建筑物由自然能泵房、桃坪中心村提水管道、务科村输水管道、和蓄水池等组成。本项目共建设取水口集水池1座，自然能泵房1座，蓄水池2座，减压池1座，消毒设备2套，新建管道共计21.004km，其中动力管道长3.839km;桃坪中心村提水管长11.033km;务科 拟招标内容 序 1 号招 施 标 工 内 招 容 标 投 详 标 见 人 招 主 标 要 文 资 件 格条件要求预 202 计 6- 招 09 标 -24 时 0 间 0:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078959.html 网 cqdingjiu 2026.08.25 09:25:53 务 商 道 管 国 中</t>
+          <t>2026年天地坝镇桃坪中心村火山组、岩头组青花椒水系工程招标计划公告 2026年天地坝镇桃坪中心村火山组、岩头组青花椒水系工程招标计划公告 招标项目名称 2026年天地坝镇桃坪中心村火山组、岩头组青花椒水系工程 项目批准文件及文号（如有） 金 批 阳 复 县 (金 水 水 利 发 局 〔 关 20 于 26 2 〕 02 6 6 1 年 号 天 ) 地坝镇桃坪中心村火山组、岩头组青花椒水系工程初步设计报告(代项目建议书、代可行性研究报告)的 招标人 金阳县水利局 联系人及联系方式 张老师:08348733445 估 （ 算 元 总 ） 投资 9750200.00 项目分类 水利工程 招标项目概况 2 村 02 输 6年 水 天 管 地 道 坝 6. 镇 132 桃 km 坪 . 中心村火山组、岩头组青花椒水系工程，工程主要建筑物由自然能泵房、桃坪中心村提水管道、务科村输水管道、和蓄水池等组成。本项目共建设取水口集水池1座，自然能泵房1座，蓄水池2座，减压池1座，消毒设备2套，新建管道共计21.004km，其中动力管道长3.839km;桃坪中心村提水管长11.033km;务科 拟招标内容 序 1 号招 施 标 工 内 招 容 标 投 详 标 见 人 招 主 标 要 文 资 件 格条件要求预 202 计 6- 招 09 标 -24 时 0 间 0:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078959.html 网 cqdingjiu 2026.08.25 10:30:33 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>本工程主要建筑物包括自然能泵房、桃坪中心村提水管道、务科村输水管道、蓄水池等。共建设取水口集水池1座，自然能泵房1座，蓄水池2座，减压池1座，消毒设备2套，新建管道共计21.004km。
+          <t>工程主要建筑物由自然能泵房、桃坪中心村提水管道、务科村输水管道、和蓄水池等组成。本项目共建设取水口集水池1座，自然能泵房1座，蓄水池2座，减压池1座，消毒设备2套，新建管道共计21.004km，其中动力管道长3.839km;桃坪中心村提水管长11.033km。
 https://www.chinapipe.net/project/d3078959.html</t>
         </is>
       </c>
@@ -3569,7 +3565,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>水利工程, 管道, 投资金额</t>
+          <t>2026年天地坝镇桃坪中心村火山组、岩头组青花椒水系工程, 水利工程, 管道, 投资</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3627,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>金阳县易地搬迁集中安置点基础设施补短板建设项目招标计划公告 金阳县易地搬迁集中安置点基础设施补短板建设项目招标计划公告 金阳县发展改革和经济信息化局关 于金阳县易地搬迁集中安置点基础 招标项目名 金阳县易地搬迁集中安置点基础设施补 项目批准文件及文号 设施补短板建设项目可行性研究报告 称 短板建设项目 （如有） (代项目建议书)的批复(金发改经信 【2026】131号) 招标人 金阳县农业农村局 联系人及联系方式 阿网力里火:18280672416 估算总投资 6096000.00 项目分类 市政基础设施工程 （元） 招标项目概 新建硬化通组路面9610.68m，排水沟529.80m，钢筋砼圆管涵14m，挡土墙31m;敷设双壁波纹 务 况 管4033.38m，配套建设检查井317座，安装太阳能路灯85套等。 投标人主要 序号 招标内容 资格条件要 预计招标时间 商 求 拟招标内容 新建硬化通组路面9610.68m，排水沟529.80m，钢筋砼圆管 1 涵14m，挡土墙31m;敷设双壁波纹管4033.38m，配套建设 * 2026-09-22 00:00:00 检查井317座，安装太阳能路灯85套等。 道 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078958.html 管 cqdingjiu 2026.08.25 09:25:53 国 中</t>
+          <t>金阳县易地搬迁集中安置点基础设施补短板建设项目招标计划公告 金阳县易地搬迁集中安置点基础设施补短板建设项目招标计划公告 金阳县发展改革和经济信息化局关 于金阳县易地搬迁集中安置点基础 招标项目名 金阳县易地搬迁集中安置点基础设施补 项目批准文件及文号 设施补短板建设项目可行性研究报告 称 短板建设项目 （如有） (代项目建议书)的批复(金发改经信 【2026】131号) 招标人 金阳县农业农村局 联系人及联系方式 阿网力里火:18280672416 估算总投资 6096000.00 项目分类 市政基础设施工程 （元） 招标项目概 新建硬化通组路面9610.68m，排水沟529.80m，钢筋砼圆管涵14m，挡土墙31m;敷设双壁波纹 务 况 管4033.38m，配套建设检查井317座，安装太阳能路灯85套等。 投标人主要 序号 招标内容 资格条件要 预计招标时间 商 求 拟招标内容 新建硬化通组路面9610.68m，排水沟529.80m，钢筋砼圆管 1 涵14m，挡土墙31m;敷设双壁波纹管4033.38m，配套建设 * 2026-09-22 00:00:00 检查井317座，安装太阳能路灯85套等。 道 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078958.html 管 cqdingjiu 2026.08.25 10:30:33 国 中</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3641,11 +3637,11 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>重庆, 近三天, 管材招标商机</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3703,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>金阳县2026年热水河乡克业村等10个村基础设施补短建设项目招标计划公告 金阳县2026年热水河乡克业村等10个村基础设施补短建设项目招标计划公告 金阳县发展改革和经济信息化局 关于金阳县2026年热水河克业村 招标项目 金阳县2026年热水河乡克业村等10个村基 项目批准文件及文号 等10个村基础设施补短板建设项 名称 础设施补短建设项目 （如有） 目可行性研究报告(代项目建议书) 的批复(金发改经信【2026】118 号) 网 招标人 金阳县农业农村局 联系人及联系方式 阿力里火:18280672416 估算总投资 7397700.00 项目分类 市政基础设施工程 （元） 务 通组路原有路基上硬化1627m，原有入户路基上硬化工程1597.0m，粮食晾晒坝子硬化4237.0m2，太 招标项目 阳能路灯590套，HDPE双壁波纹管dn300~dn400污水管230m，农具存放室34.72m2，农具存放室改造 概况 及配套排水沟、挡墙等。 商 投标人主 序 招标内容 要资格条 预计招标时间 号 件要求 拟招标内 通组路原有路基上硬化1627m，原有入户路基上硬化工 容 道 程1597.0m，粮食晾晒坝子硬化4237.0m2，太阳能路灯590 1 * 2026-09-22 00:00:00 套，HDPE双壁波纹管dn300~dn400污水管230m，农具存放 室34.72m2，农具存放室改造及配套排水沟、挡墙等。 备注：提前发布的招标计划内容仅管供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078957.html cqdingjiu 2026.08.25 09:25:53 国 中</t>
+          <t>金阳县2026年热水河乡克业村等10个村基础设施补短建设项目招标计划公告 金阳县2026年热水河乡克业村等10个村基础设施补短建设项目招标计划公告 金阳县发展改革和经济信息化局 关于金阳县2026年热水河克业村 招标项目 金阳县2026年热水河乡克业村等10个村基 项目批准文件及文号 等10个村基础设施补短板建设项 名称 础设施补短建设项目 （如有） 目可行性研究报告(代项目建议书) 的批复(金发改经信【2026】118 号) 网 招标人 金阳县农业农村局 联系人及联系方式 阿力里火:18280672416 估算总投资 7397700.00 项目分类 市政基础设施工程 （元） 务 通组路原有路基上硬化1627m，原有入户路基上硬化工程1597.0m，粮食晾晒坝子硬化4237.0m2，太 招标项目 阳能路灯590套，HDPE双壁波纹管dn300~dn400污水管230m，农具存放室34.72m2，农具存放室改造 概况 及配套排水沟、挡墙等。 商 投标人主 序 招标内容 要资格条 预计招标时间 号 件要求 拟招标内 通组路原有路基上硬化1627m，原有入户路基上硬化工 容 道 程1597.0m，粮食晾晒坝子硬化4237.0m2，太阳能路灯590 1 * 2026-09-22 00:00:00 套，HDPE双壁波纹管dn300~dn400污水管230m，农具存放 室34.72m2，农具存放室改造及配套排水沟、挡墙等。 备注：提前发布的招标计划内容仅管供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078957.html cqdingjiu 2026.08.25 10:30:33 国 中</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3779,7 +3775,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>金阳县2025年洛觉镇马店村高山免养殖项目招标计划公告 金阳县2025年洛觉镇马店村高山免养殖项目招标计划公告 金阳县发展改革和经济信息化局 关于金阳县2025年洛觉镇马店村 招标项目 金阳县2025年洛觉镇马店村高山免养殖 项目批准文件及文号 高山免养殖项目可行性研究报 名称 项目 （如有） 告(代项目建议书)的批复(金发改 经信【2025】100号) 招标人 金阳县农业农村局 联系人及联系方式 何网吉海:18989254045 估算总投资 8670425.39 项目分类 房屋建筑工程 （元） 招标项目 项目流转农业设施用地29.67亩。新建养殖大棚5472,00m、隔离室及兽医室116,55m、消毒棚76.00m， 务 概况 改造养殖大棚2956.50m，并完善堆粪场、消毒池、挡墙、给排水管网、变配电等室外公用工程等。 投标人主 序号 招标内容 要资格条 预计招标时间 商 件要求 拟招标内 项目流转农业设施用地29.67亩。新建养殖大棚5472,00m、隔 容 离室及兽医室116,55m、消毒棚76.00m，改造养殖大 1 * 2026-09-22 00:00:00 棚2956.50m，并完善堆粪场、消毒池、挡墙、给排水管网、 道 变配电等室外公用工程等。 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078956.html 管 cqdingjiu 2026.08.25 09:25:53 国 中</t>
+          <t>金阳县2025年洛觉镇马店村高山免养殖项目招标计划公告 金阳县2025年洛觉镇马店村高山免养殖项目招标计划公告 金阳县发展改革和经济信息化局 关于金阳县2025年洛觉镇马店村 招标项目 金阳县2025年洛觉镇马店村高山免养殖 项目批准文件及文号 高山免养殖项目可行性研究报 名称 项目 （如有） 告(代项目建议书)的批复(金发改 经信【2025】100号) 招标人 金阳县农业农村局 联系人及联系方式 何网吉海:18989254045 估算总投资 8670425.39 项目分类 房屋建筑工程 （元） 招标项目 项目流转农业设施用地29.67亩。新建养殖大棚5472,00m、隔离室及兽医室116,55m、消毒棚76.00m， 务 概况 改造养殖大棚2956.50m，并完善堆粪场、消毒池、挡墙、给排水管网、变配电等室外公用工程等。 投标人主 序号 招标内容 要资格条 预计招标时间 商 件要求 拟招标内 项目流转农业设施用地29.67亩。新建养殖大棚5472,00m、隔 容 离室及兽医室116,55m、消毒棚76.00m，改造养殖大 1 * 2026-09-22 00:00:00 棚2956.50m，并完善堆粪场、消毒池、挡墙、给排水管网、 道 变配电等室外公用工程等。 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078956.html 管 cqdingjiu 2026.08.25 10:30:33 国 中</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3855,7 +3851,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>广元市滨河北路二段改建项目招标计划公告 广元市滨河北路二段改建项目招标计划公告 招标项目名称 广元市滨河北路二段改建项目 项目批准文件及文号 招标人 广元市城市发展集团有限公司 联系人及联系方式 高女士;3362291 估算总投资（元） 52920000 项目分类 网市政基础设施工程 道路改造长度约1.591km，双向四车道，项目包含道路、排水、交安、照明工程以及万达大 招标项目概况 桥下穿拓宽，配套海绵绿化、综合管线改造等相关附属设施。 序号 招标内容 预计招标时间 拟交易场所 务 拟招标内容 1 勘察设计 2026-09 市辖区 商 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d30道78953.html cqdingjiu 2026.08.25 09:25:54 管 国 中</t>
+          <t>广元市滨河北路二段改建项目招标计划公告 广元市滨河北路二段改建项目招标计划公告 招标项目名称 广元市滨河北路二段改建项目 项目批准文件及文号 招标人 广元市城市发展集团有限公司 联系人及联系方式 高女士;3362291 估算总投资（元） 52920000 项目分类 网市政基础设施工程 道路改造长度约1.591km，双向四车道，项目包含道路、排水、交安、照明工程以及万达大 招标项目概况 桥下穿拓宽，配套海绵绿化、综合管线改造等相关附属设施。 序号 招标内容 预计招标时间 拟交易场所 务 拟招标内容 1 勘察设计 2026-09 市辖区 商 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d30道78953.html cqdingjiu 2026.08.25 10:30:33 管 国 中</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3865,11 +3861,11 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>滨河北路二段改建项目, 道路改造, 排水钢管</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3922,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>PE管、PVC管、玉米种子、肥料、农药、灌溉设备</t>
+          <t>水利工程</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>巴中市巴州区2026年玉米单产提升工程项目招标计划公告 巴中市巴州区2026年玉米单产提升工程项目招标计划公告 巴中市农业农村局关于巴中市 招标项目 项目批准文件及文号 巴州区2026年玉米单产提升工 巴中市巴州区2026年玉米单产提升工程项目 名称 （如有） 程项目初步设计和概算的批 复(巴农函〔2026〕14号) 招标人 巴中市巴州区农技推广服务中心 联系人及联系方式 刘先生:0827-5223861 网 估算总投资 26000000.00 项目分类 水利工程 （元） 建设玉米单产提升工程5万亩。安装室外地表水固定集成灌溉首部、室外地表水卧网式移动灌溉首 部、井用移动集成灌溉首部共146套。输配水管网：160PE管3000米、110PE管9500米。推广玉米全 招标项目 务 生育期精准调控5万亩。包括：玉米种子(含机械投入、人工投入)5万袋以及适用于5万亩所需的玉 概况 米水溶肥、叶面追肥、杀菌剂、杀虫剂、封闭除草剂、杂草防治等。安装智慧农业平台1套。铺设3 寸PVC刀刮布水带主管25万米。 拟招标内 序号 招标内容 投标人主要资格条件要求商预计招标时间 容 1 施工 以招标文件为准 2026-09-24 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 道 信息来源:https://www.chinapipe.net/project/d3078949.html cqdingjiu 2026.08.25 09:25:54 管 国 中</t>
+          <t>巴中市巴州区2026年玉米单产提升工程项目招标计划公告 巴中市巴州区2026年玉米单产提升工程项目招标计划公告 巴中市农业农村局关于巴中市 招标项目 项目批准文件及文号 巴州区2026年玉米单产提升工 巴中市巴州区2026年玉米单产提升工程项目 名称 （如有） 程项目初步设计和概算的批 复(巴农函〔2026〕14号) 招标人 巴中市巴州区农技推广服务中心 联系人及联系方式 刘先生:0827-5223861 网 估算总投资 26000000.00 项目分类 水利工程 （元） 建设玉米单产提升工程5万亩。安装室外地表水固定集成灌溉首部、室外地表水卧网式移动灌溉首 部、井用移动集成灌溉首部共146套。输配水管网：160PE管3000米、110PE管9500米。推广玉米全 招标项目 务 生育期精准调控5万亩。包括：玉米种子(含机械投入、人工投入)5万袋以及适用于5万亩所需的玉 概况 米水溶肥、叶面追肥、杀菌剂、杀虫剂、封闭除草剂、杂草防治等。安装智慧农业平台1套。铺设3 寸PVC刀刮布水带主管25万米。 拟招标内 序号 招标内容 投标人主要资格条件要求商预计招标时间 容 1 施工 以招标文件为准 2026-09-24 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 道 信息来源:https://www.chinapipe.net/project/d3078949.html cqdingjiu 2026.08.25 10:30:33 管 国 中</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4003,7 +3999,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>犍为县西街片区老旧街区改造更新项目(一期)设计施工总承包招标计划公告 犍为县西街片区老旧街区改造更新项目（一期）设计施工总承包招标计划公告 关于《犍为县西街片区老旧 招标项目 犍为县西街片区老旧街区改造更新项目（一 项目批准文件及文号 街区改造更新项目建议书》 名称 期）设计施工总承包 （如有） 的批复(犍发改项目 审[2026]92号) 招标人 犍为郡城建设发展集团有限公司 联系人及联系方式 粟老师:0833-4259930 网 估算总投资 82000000.00 项目分类 市政基础设施工程 （元） 对犍为县西街片区沿街道路进行改造提升，改造内容包括西街片区内生态空间及公共厕所等建筑改 造、环卫设施更新等;治理道路6.2公里，改造供水管网5.6公里、排水管网6.3公里、污水管网6.6公里， 招标项目 务 治理街区飞线8.5公里，改造路边停车位480个、配套充电桩102个，改造便民集市约4800平方 概况 米(含340个摊位)，街道两侧增设智慧灯杆325根，实施消防、无障碍、管网监测设备和检修设施等 配套基础设施改造。 拟招标内 序号 招标内容 投标人主要资格条商件要求 预计招标时间 容 1 设计施工总承包 按招标文件要求执行 2026-09-25 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 道 信息来源:https://www.chinapipe.net/project/d3078947.html cqdingjiu 2026.08.25 09:25:54 管 国 中</t>
+          <t>犍为县西街片区老旧街区改造更新项目(一期)设计施工总承包招标计划公告 犍为县西街片区老旧街区改造更新项目（一期）设计施工总承包招标计划公告 关于《犍为县西街片区老旧 招标项目 犍为县西街片区老旧街区改造更新项目（一 项目批准文件及文号 街区改造更新项目建议书》 名称 期）设计施工总承包 （如有） 的批复(犍发改项目 审[2026]92号) 招标人 犍为郡城建设发展集团有限公司 联系人及联系方式 粟老师:0833-4259930 网 估算总投资 82000000.00 项目分类 市政基础设施工程 （元） 对犍为县西街片区沿街道路进行改造提升，改造内容包括西街片区内生态空间及公共厕所等建筑改 造、环卫设施更新等;治理道路6.2公里，改造供水管网5.6公里、排水管网6.3公里、污水管网6.6公里， 招标项目 务 治理街区飞线8.5公里，改造路边停车位480个、配套充电桩102个，改造便民集市约4800平方 概况 米(含340个摊位)，街道两侧增设智慧灯杆325根，实施消防、无障碍、管网监测设备和检修设施等 配套基础设施改造。 拟招标内 序号 招标内容 投标人主要资格条商件要求 预计招标时间 容 1 设计施工总承包 按招标文件要求执行 2026-09-25 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 道 信息来源:https://www.chinapipe.net/project/d3078947.html cqdingjiu 2026.08.25 10:30:34 管 国 中</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4017,7 +4013,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>西街片区, 老旧街区改造, 道路改造, 管网改造</t>
+          <t>老旧街区改造, 道路改造, 管网改造</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4075,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>道孚县八美镇排水管网提升改造项目招标计划公告 道孚县八美镇排水管网提升改造项目招标计划公告 道孚县发展和改革局关于道孚县 项目批准文件及文号 八美镇排水管网提升改造项目可 招标项目名称 道孚县八美镇排水管网提升改造项目 （如有） 行性研究报告的批复(道发改投 【2024】291号) 招标人 道孚县住房和城乡建设局 联系人及联系方式 高老师:0836-7122067 网 估算总投资 53940000.00 项目分类 市政基础设施工程 （元） 提升改造排水管网20公里，其中新建排水管网10公里，修复排水管网10公里；新建内容包括管道 招标项目概况 及附属设施、道路恢复等。 务 序号 招标内容 投标人主要资格条件要求 预计招标时间 拟招标内容 1 施工 以发布的招标公告和招标文件为准 2026-09-25 00:00:00 2 监理 以发布的招标公告和招商标文件为准 2026-09-25 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078946.html 道 cqdingjiu 2026.08.25 09:25:54 管 国 中</t>
+          <t>道孚县八美镇排水管网提升改造项目招标计划公告 道孚县八美镇排水管网提升改造项目招标计划公告 道孚县发展和改革局关于道孚县 项目批准文件及文号 八美镇排水管网提升改造项目可 招标项目名称 道孚县八美镇排水管网提升改造项目 （如有） 行性研究报告的批复(道发改投 【2024】291号) 招标人 道孚县住房和城乡建设局 联系人及联系方式 高老师:0836-7122067 网 估算总投资 53940000.00 项目分类 市政基础设施工程 （元） 提升改造排水管网20公里，其中新建排水管网10公里，修复排水管网10公里；新建内容包括管道 招标项目概况 及附属设施、道路恢复等。 务 序号 招标内容 投标人主要资格条件要求 预计招标时间 拟招标内容 1 施工 以发布的招标公告和招标文件为准 2026-09-25 00:00:00 2 监理 以发布的招标公告和招商标文件为准 2026-09-25 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078946.html 道 cqdingjiu 2026.08.25 10:30:34 管 国 中</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4093,7 +4089,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>排水管网, 提升改造, 资金情况, 产品种类</t>
+          <t>排水管网, 提升改造, 投资额, 项目内容</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4141,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>估算总投资750万元</t>
+          <t>估算总投资7500000.00元</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4155,7 +4151,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>平昌县“川陕苏区红色平昌·巴山肉牛建圈强链”乡村振兴项目(元山镇)招标计划公告 平昌县“川陕苏区红色平昌·巴山肉牛建圈强链”乡村振兴项目(元山镇)招标计划公告 招项名 标目称平昌县“川陕苏区红色平昌·巴山肉牛建圈强链”乡村振兴项目(元山镇) 项目批准文件及文号（如有） 平昌县发展和改革局关于平昌县“川陕苏区红色平昌·巴山肉牛建圈强链"乡村振兴项目(元山镇)可行性研究报告的批复(平发改审[2026]134号) 招人标平昌县元山镇人民政府 联系人及联系方式 何先生:0827-6757786 估总（投元 算资）7500000.00 项目分类 农业综合 招项概 标目况 1管.高道辣40素00辣米椒、育32苗PE基支地管建道设30:0位0米于;寿3.牧南草山基村地，建总设占:位地于约通12亩木，村建，设种育植苗优大质棚牧共草计4007亩700，平含方土米地，清其表中、连翻体耕玻、璃起育垄苗等大工棚序34;改00建平泥方结米石，道钢路架2结.5构00薄公膜里育，苗路大面棚宽433.50米0平，方配米套;配必套要铺的设排5水0P设E灌施 。溉管网2023米及自动喷淋等设施设备;2.高梁标准化种植示范基地基础设施配套建设:位于插旗山村，服务2000亩高粱标准化种植示范基地，硬化入园道路2公里(路面宽3.5米、厚0.2米，C30混凝土路面);改建泥结石生产道路4公里(路面宽3米);加宽改造现有硬化道路100米(将原3米宽路面拓宽至3.5米);改扩建蓄水池10口(含坝体夯筑、清淤治漏及护坡工程);铺设灌溉管网7000米，其中75PE主 拟标容 招内序 1 号招 施 标 工 内容投求 详 标 见 人 招 主 标 要 文 资 件 格条件要预 202 计 6- 招 09 标 -25 时 0 间 0:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078943.html 网 cqdingjiu 2026.08.25 09:25:54 务 商 道 管 国 中</t>
+          <t>平昌县“川陕苏区红色平昌·巴山肉牛建圈强链”乡村振兴项目(元山镇)招标计划公告 平昌县“川陕苏区红色平昌·巴山肉牛建圈强链”乡村振兴项目(元山镇)招标计划公告 招项名 标目称平昌县“川陕苏区红色平昌·巴山肉牛建圈强链”乡村振兴项目(元山镇) 项目批准文件及文号（如有） 平昌县发展和改革局关于平昌县“川陕苏区红色平昌·巴山肉牛建圈强链"乡村振兴项目(元山镇)可行性研究报告的批复(平发改审[2026]134号) 招人标平昌县元山镇人民政府 联系人及联系方式 何先生:0827-6757786 估总（投元 算资）7500000.00 项目分类 农业综合 招项概 标目况 1管.高道辣40素00辣米椒、育32苗PE基支地管建道设30:0位0米于;寿3.牧南草山基村地，建总设占:位地于约通12亩木，村建，设种育植苗优大质棚牧共草计4007亩700，平含方土米地，清其表中、连翻体耕玻、璃起育垄苗等大工棚序34;改00建平泥方结米石，道钢路架2结.5构00薄公膜里育，苗路大面棚宽433.50米0平，方配米套;配必套要铺的设排5水0P设E灌施 。溉管网2023米及自动喷淋等设施设备;2.高梁标准化种植示范基地基础设施配套建设:位于插旗山村，服务2000亩高粱标准化种植示范基地，硬化入园道路2公里(路面宽3.5米、厚0.2米，C30混凝土路面);改建泥结石生产道路4公里(路面宽3米);加宽改造现有硬化道路100米(将原3米宽路面拓宽至3.5米);改扩建蓄水池10口(含坝体夯筑、清淤治漏及护坡工程);铺设灌溉管网7000米，其中75PE主 拟标容 招内序 1 号招 施 标 工 内容投求 详 标 见 人 招 主 标 要 文 资 件 格条件要预 202 计 6- 招 09 标 -25 时 0 间 0:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078943.html 网 cqdingjiu 2026.08.25 10:30:34 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4169,7 +4165,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>乡村振兴项目, 元山镇, 高粱标准化种植示范基地, 灌溉管网, 水泥路面, 泥结石道路, 蓄水池</t>
+          <t>管材招标, 灌溉管网, 水泥路面, 泥结石道路, 蓄水池, 高粱标准化种植示范基地</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4227,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>炉霍县洛秋乡人居环境综合整治提升建设项目招标计划公告 炉霍县洛秋乡人居环境综合整治提升建设项目招标计划公告 炉霍县发展和改革 局关于炉霍县洛秋 招标 项目批准文件及文号（如 乡人居环境综合整 项目 炉霍县洛秋乡人居环境综合整治提升建设项目 有） 治提升建设项目可 名称 行性研究报告的批复 (炉发改[2026]149号) 网 招标 降措老 炉霍县国有资产经营管理有限责任公司 联系人及联系方式 人 师:08362201588 估算 总投资 40000000.00 项务目分类 市政基础设施工程 （元） 新建一体化污水处理站1座，设计总规模250m/d,配套污水管网约4.275km; 净水处理站1座，设计总规 招标 模250m/d,配套供水DN150管道0.5km; 新建垃圾集中收集站33.28m,配套垃圾分类收集桶20套、垃圾转运车1 项目 辆；新建公共厕所2栋；道路整治0.4km; 建设公共停商车位100个、停车位配套充电桩30套；安装太阳能路灯146 概况 盏；其他配套建设附属基础设施。 拟招 序号 招标内容 投标人主要资格条件要求 预计招标时间 标内 容 1 施工 详见招标公告 道2026-09-24 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078941.html 管 cqdingjiu 2026.08.25 09:25:54 国 中</t>
+          <t>炉霍县洛秋乡人居环境综合整治提升建设项目招标计划公告 炉霍县洛秋乡人居环境综合整治提升建设项目招标计划公告 炉霍县发展和改革 局关于炉霍县洛秋 招标 项目批准文件及文号（如 乡人居环境综合整 项目 炉霍县洛秋乡人居环境综合整治提升建设项目 有） 治提升建设项目可 名称 行性研究报告的批复 (炉发改[2026]149号) 网 招标 降措老 炉霍县国有资产经营管理有限责任公司 联系人及联系方式 人 师:08362201588 估算 总投资 40000000.00 项务目分类 市政基础设施工程 （元） 新建一体化污水处理站1座，设计总规模250m/d,配套污水管网约4.275km; 净水处理站1座，设计总规 招标 模250m/d,配套供水DN150管道0.5km; 新建垃圾集中收集站33.28m,配套垃圾分类收集桶20套、垃圾转运车1 项目 辆；新建公共厕所2栋；道路整治0.4km; 建设公共停商车位100个、停车位配套充电桩30套；安装太阳能路灯146 概况 盏；其他配套建设附属基础设施。 拟招 序号 招标内容 投标人主要资格条件要求 预计招标时间 标内 容 1 施工 详见招标公告 道2026-09-24 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078941.html 管 cqdingjiu 2026.08.25 10:30:34 国 中</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4307,7 +4303,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>崇州明湖科创园双电源改造工程招标计划 崇州明湖科创园双电源改造工程招标计划 招标项目名称 崇州明湖科创园双电源改造工程 项目批准文件及文号（如有） 招标人 成都新蜀康建设投资有限公司 联系人及联系方式 杨女士028-81580680 估算总投资 能源（含电力、热力、煤炭、 12570000 项目分类 （元） 石化） 招标项目概况 新建10kv电缆2100米;排管800米;配套建设配电房改造、 配电柜等设施设备工程。 序号 拟招标内容 投标人主要资格条件 网预计招标时间 拟招标内容 1 施工招标 以发布的招标文件为准 2026年08月 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 务 信息来源:https://www.chinapipe.net/project/d3078938.html cqdingjiu 2026.08.25 09:25:54 商 道 管 国 中</t>
+          <t>崇州明湖科创园双电源改造工程招标计划 崇州明湖科创园双电源改造工程招标计划 招标项目名称 崇州明湖科创园双电源改造工程 项目批准文件及文号（如有） 招标人 成都新蜀康建设投资有限公司 联系人及联系方式 杨女士028-81580680 估算总投资 能源（含电力、热力、煤炭、 12570000 项目分类 （元） 石化） 招标项目概况 新建10kv电缆2100米;排管800米;配套建设配电房改造、 配电柜等设施设备工程。 序号 拟招标内容 投标人主要资格条件 网预计招标时间 拟招标内容 1 施工招标 以发布的招标文件为准 2026年08月 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 务 信息来源:https://www.chinapipe.net/project/d3078938.html cqdingjiu 2026.08.25 10:30:34 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4368,7 +4364,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>暂停米易县旧城区燃气管道及设施安全提升项目一标段设计施工总承包标段招投标活动。</t>
+          <t>米易县旧城区燃气管道及设施安全提升项目一标段设计施工总承包标段的评标结果因收到异议而暂停。</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4378,26 +4374,26 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>燃气管道及设施</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>关于暂停米易县旧城区燃气管道及设施安全提升项目一标段设计施工总承包标段招投标活动的通知 致各投标人及相关单位： 米易县旧城区燃气管道及设施安全提升项目一标段设计施工总承包标段，于2026年8月17日在攀枝花市公共资源 交易服务中心进行开、评标。本项目评标结果公示于2026年8月18日在《全国公共资源交易平台（四川省·攀枝 花市）》、《全国公共资源交易平台（四川省）》上发布，公示期为2026年8月18日至2026年8月21日。公示期间 收到有关单位对评标结果提出的异议，根据《中华人民共和国招标投标法实施条例》第五十四条规定，现暂停 本项目招投标活动，待异议处理完后另行通知。 网 务 招标人：米易县综合行政执法局 日期：2026年8月24日 商 信息来源:https://www.chinapipe.net/project/d3078880.html cqdingjiu 2026.08.25 09:25:55 道 管 国 中</t>
+          <t>关于暂停米易县旧城区燃气管道及设施安全提升项目一标段设计施工总承包标段招投标活动的通知 致各投标人及相关单位： 米易县旧城区燃气管道及设施安全提升项目一标段设计施工总承包标段，于2026年8月17日在攀枝花市公共资源 交易服务中心进行开、评标。本项目评标结果公示于2026年8月18日在《全国公共资源交易平台（四川省·攀枝 花市）》、《全国公共资源交易平台（四川省）》上发布，公示期为2026年8月18日至2026年8月21日。公示期间 收到有关单位对评标结果提出的异议，根据《中华人民共和国招标投标法实施条例》第五十四条规定，现暂停 本项目招投标活动，待异议处理完后另行通知。 网 务 招标人：米易县综合行政执法局 日期：2026年8月24日 商 信息来源:https://www.chinapipe.net/project/d3078880.html cqdingjiu 2026.08.25 10:30:34 道 管 国 中</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>暂停米易县旧城区燃气管道及设施安全提升项目一标段设计施工总承包标段招投标活动。
+          <t>米易县旧城区燃气管道及设施安全提升项目一标段设计施工总承包标段的评标结果因收到异议而暂停。
 https://www.chinapipe.net/project/d3078880.html</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>燃气管道, 设施安全提升</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4455,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>喜德县城区排水管道补短板项目施工标段的招标文件预公示 详见附件。 信息来源:https://www.chinapipe.net/project/d3078860.html cqdingjiu 2026.08.25 09:25:55 网 务 商 道 管 国 中</t>
+          <t>喜德县城区排水管道补短板项目施工标段的招标文件预公示 详见附件。 信息来源:https://www.chinapipe.net/project/d3078860.html cqdingjiu 2026.08.25 10:30:34 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4469,11 +4465,11 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>重庆, 近三天, 管材招标商机</t>
+          <t>排水管道, 补短板项目</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4531,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>武胜县嘉陵江沿线道路工程建设项目-滨江路北段(沿口古镇至李家湾段村道改建工程)设计施工总承包项目顶管 施工工程专业分包招标公告 中国华西企业股份有限公司安装工程公司 武胜县嘉陵江沿线道路工程建设项目-滨江路北段(沿口古镇至李家湾段 村道改建工程) 武胜县嘉陵江沿线道路工程建设项目-滨江路北段(沿口古镇至李家湾段村道改建工程)设计施工总 承包项目顶管施工工程专业分包 招标公告 中国华西企业股份有限公司安装工程公司现就武胜县嘉陵江沿线道路工程建设项目-滨江路北段 (沿口古镇至李家湾段村道改建工程)的给排水工程采购事宜进行公开招标，欢迎有意向的供应商参加投标。 一、采购内容 网 给排水工程，预计总用量约为： 295。 1、付款方式：按节点支付，第一次付款节点为：乙方顶管机械进场并安装完成验收合格后， 支付至暂定合同总额的20%。第二次付款节点为：顶管工程施工完成后，支付至乙方已完成合格工程量产值 的70%，项目竣工验收合格后，甲乙双方办理专业分包结算，结算办理完成30日内，付至结算价款的 97% ，留 务 3% 作为质量保修金。 二、项目概况 项目名称： 武胜县嘉陵江沿线道路工程建设项目-滨江路北段(沿口古镇至李家湾段村道改建 商 工程) 项目地址： 四川省广安市武胜县滨江路 建筑规模： 0㎡ 其他详见招标文件。 道 三、招标方式 本次采购招标采用公开招标的方式进行，并在善建云采（四川华西集团有限公司及下属分子 公司）发布招标公告，网址为：https://scm.zghxsjy.com/。 管 四、投标人资格要求 在善建云采（四川华西集团有限公司及下属分子公司）（https://scm.zghxsjy.com/）已注册的合 格分供商均可参与投标。 国 五、招投标时间节点 （一）招标文件发售截止时间： 2026-08-28 10:00:00； （二）投标保证金缴纳的截止时间为： 2026-08-28 10:00:00 ； （三）本次招标的投标截止时间为： 2026-08-28 10:00:00 ； （四）中本次招标的开标时间为： 2026-08-28 10:00:00 ； （五）电子标书费售价：人民币40.0 元/套，售后不退。 六、缴费注意事项 为保证招投标的公平公正，善建云采（四川华西集团有限公司及下属分子公司）已与银行实 现系统对接，从缴费账号生成、缴费确认、标书下载和投标功能开放，全部实现自动化、线上化，请投标人务 必按照下述要求缴纳标书费和投标保证金，避免影响投标。 电子标书费缴纳： 1、投标人一旦决定投标，请在善建云采（四川华西集团有限公司及下属分子公司）上点 击“交标书费”，银行系统会随机自动为该次缴费生成一次性的唯一银行账号。 2、请投标人务必把标书费转入上述银行账户。投标人缴费后，银行系统会同步自动将缴费信 息推送至善建云采（四川华西集团有限公司及下属分子公司）和投标人，善建云采（四川华西集团有限公司及 下属分子公司）系统亦同步开放权限，投标人即可在善建云采（四川华西集团有限公司及下属分子公司）浏览 和下载标书。 3、投标人务必严格按照上述要求进行投标操作。若投标人缴费到错误账号，善建云采（四川 华西集团有限公司及下属分子公司）法开放投标功能，由此法购买标书、法投标、退回款项延迟等产生的一切 损失，均由投标人自行承担。 投标保证金缴纳： 1、投标人在善建云采（四川华西集团有限公司及下属分子公司）上点击“交投标保证金”后， 由银行系统自动为该次缴费生成唯一银行账号。 2、请投标人务必把投标保证金转入上述银行账户。投标人缴费后，银行系统会同步自动将缴 费信息推送至善建云采（四川华西集团有限公司及下属分子公司）和投标人，善建云采（四川华西集团有限公 司及下属分子公司）系统亦同步开放权限，投标人即可在善建云采（四川华西集团有限公司及下属分子公司） 上传投标文件和填报投标数据。 3、投标人务必严格按照上述要求进行投标操作。若投标人缴费到错误账号，善建云采（四川 华西集团有限公司及下属分子公司）法开放投标功能，由此法投标、退回款项延迟等产生的一切损失，均由投 标人自行承担。 投标人缴纳投标保证金必须由投标人对公账户转账，不接受个人账户转款、现金缴存、他人 代缴。若出现投标人使用个人账户转款、现金缴存、他人代缴、未按系统自动生成的对应账号转款、超额转款 等，平台将法自动退款。在中标公示结束后3个工作日内未收到保证金退款，投标人应在10个工作日后向四川华 西数产科技集团有限公司提供完整的书面缴费依据，四川华西数产科技集团有限公司将在收到投标人提供的完 整缴费依据后，在7个工作日内核实并退款。若出现上述情况投标人可编辑含有“招标项目名称”、“招标单 位”的短信发送至：19950205781（本号码只接受短信联系方式），也可到访四川华西数产科技集团有限公司进 行沟通。 系统每次生成的账号，均为一次性账号和唯一性账号，标书费账号与投标保网证金账号不同， 项目与项目间账号不同。 七、投标文件的递交 招标人仅接受投标人通过善建云采（四川华西集团有限公司及下属分子公司）提交的投标文 务 件，不接受通过其他方式提交的书面投标文件。线上投标内容具有法律效力且具有唯一性，请投标人慎重对待。 八、其他描述 商 九、其他资格要求 十、其他事项 若对招标公告有其他不明事项，请致电： 业务咨询联系人： 钟经理 ，联系道电话： 15228995887； 技术支持联系人： 集采技术中心 ，联系电话： 02883387146； 管 十一、声明 本招标公告仅为信息发布，不构成任何法律意义上的要约或承诺。 现予公告。 中国华西企业股份有限公司安装工程公司 国 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3078834.html cqdingjiu 2026.08.25 09:25:55 中</t>
+          <t>武胜县嘉陵江沿线道路工程建设项目-滨江路北段(沿口古镇至李家湾段村道改建工程)设计施工总承包项目顶管 施工工程专业分包招标公告 中国华西企业股份有限公司安装工程公司 武胜县嘉陵江沿线道路工程建设项目-滨江路北段(沿口古镇至李家湾段 村道改建工程) 武胜县嘉陵江沿线道路工程建设项目-滨江路北段(沿口古镇至李家湾段村道改建工程)设计施工总 承包项目顶管施工工程专业分包 招标公告 中国华西企业股份有限公司安装工程公司现就武胜县嘉陵江沿线道路工程建设项目-滨江路北段 (沿口古镇至李家湾段村道改建工程)的给排水工程采购事宜进行公开招标，欢迎有意向的供应商参加投标。 一、采购内容 网 给排水工程，预计总用量约为： 295。 1、付款方式：按节点支付，第一次付款节点为：乙方顶管机械进场并安装完成验收合格后， 支付至暂定合同总额的20%。第二次付款节点为：顶管工程施工完成后，支付至乙方已完成合格工程量产值 的70%，项目竣工验收合格后，甲乙双方办理专业分包结算，结算办理完成30日内，付至结算价款的 97% ，留 务 3% 作为质量保修金。 二、项目概况 项目名称： 武胜县嘉陵江沿线道路工程建设项目-滨江路北段(沿口古镇至李家湾段村道改建 商 工程) 项目地址： 四川省广安市武胜县滨江路 建筑规模： 0㎡ 其他详见招标文件。 道 三、招标方式 本次采购招标采用公开招标的方式进行，并在善建云采（四川华西集团有限公司及下属分子 公司）发布招标公告，网址为：https://scm.zghxsjy.com/。 管 四、投标人资格要求 在善建云采（四川华西集团有限公司及下属分子公司）（https://scm.zghxsjy.com/）已注册的合 格分供商均可参与投标。 国 五、招投标时间节点 （一）招标文件发售截止时间： 2026-08-28 10:00:00； （二）投标保证金缴纳的截止时间为： 2026-08-28 10:00:00 ； （三）本次招标的投标截止时间为： 2026-08-28 10:00:00 ； （四）中本次招标的开标时间为： 2026-08-28 10:00:00 ； （五）电子标书费售价：人民币40.0 元/套，售后不退。 六、缴费注意事项 为保证招投标的公平公正，善建云采（四川华西集团有限公司及下属分子公司）已与银行实 现系统对接，从缴费账号生成、缴费确认、标书下载和投标功能开放，全部实现自动化、线上化，请投标人务 必按照下述要求缴纳标书费和投标保证金，避免影响投标。 电子标书费缴纳： 1、投标人一旦决定投标，请在善建云采（四川华西集团有限公司及下属分子公司）上点 击“交标书费”，银行系统会随机自动为该次缴费生成一次性的唯一银行账号。 2、请投标人务必把标书费转入上述银行账户。投标人缴费后，银行系统会同步自动将缴费信 息推送至善建云采（四川华西集团有限公司及下属分子公司）和投标人，善建云采（四川华西集团有限公司及 下属分子公司）系统亦同步开放权限，投标人即可在善建云采（四川华西集团有限公司及下属分子公司）浏览 和下载标书。 3、投标人务必严格按照上述要求进行投标操作。若投标人缴费到错误账号，善建云采（四川 华西集团有限公司及下属分子公司）法开放投标功能，由此法购买标书、法投标、退回款项延迟等产生的一切 损失，均由投标人自行承担。 投标保证金缴纳： 1、投标人在善建云采（四川华西集团有限公司及下属分子公司）上点击“交投标保证金”后， 由银行系统自动为该次缴费生成唯一银行账号。 2、请投标人务必把投标保证金转入上述银行账户。投标人缴费后，银行系统会同步自动将缴 费信息推送至善建云采（四川华西集团有限公司及下属分子公司）和投标人，善建云采（四川华西集团有限公 司及下属分子公司）系统亦同步开放权限，投标人即可在善建云采（四川华西集团有限公司及下属分子公司） 上传投标文件和填报投标数据。 3、投标人务必严格按照上述要求进行投标操作。若投标人缴费到错误账号，善建云采（四川 华西集团有限公司及下属分子公司）法开放投标功能，由此法投标、退回款项延迟等产生的一切损失，均由投 标人自行承担。 投标人缴纳投标保证金必须由投标人对公账户转账，不接受个人账户转款、现金缴存、他人 代缴。若出现投标人使用个人账户转款、现金缴存、他人代缴、未按系统自动生成的对应账号转款、超额转款 等，平台将法自动退款。在中标公示结束后3个工作日内未收到保证金退款，投标人应在10个工作日后向四川华 西数产科技集团有限公司提供完整的书面缴费依据，四川华西数产科技集团有限公司将在收到投标人提供的完 整缴费依据后，在7个工作日内核实并退款。若出现上述情况投标人可编辑含有“招标项目名称”、“招标单 位”的短信发送至：19950205781（本号码只接受短信联系方式），也可到访四川华西数产科技集团有限公司进 行沟通。 系统每次生成的账号，均为一次性账号和唯一性账号，标书费账号与投标保网证金账号不同， 项目与项目间账号不同。 七、投标文件的递交 招标人仅接受投标人通过善建云采（四川华西集团有限公司及下属分子公司）提交的投标文 务 件，不接受通过其他方式提交的书面投标文件。线上投标内容具有法律效力且具有唯一性，请投标人慎重对待。 八、其他描述 商 九、其他资格要求 十、其他事项 若对招标公告有其他不明事项，请致电： 业务咨询联系人： 钟经理 ，联系道电话： 15228995887； 技术支持联系人： 集采技术中心 ，联系电话： 02883387146； 管 十一、声明 本招标公告仅为信息发布，不构成任何法律意义上的要约或承诺。 现予公告。 中国华西企业股份有限公司安装工程公司 国 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3078834.html cqdingjiu 2026.08.25 10:30:35 中</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4549,7 +4545,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机</t>
+          <t>管材招标, 给排水工程</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4597,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>项目概算书评审</t>
+          <t>概算23000元</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4611,7 +4607,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>隆昌市城市主城核心区雨水管网及附属设施建设项目竞价公告 隆昌市发展和改革局（单位）隆昌市城市主城核心区雨水管网 及附属设施建设项目（中介服务项目）将在中 介服务网上交易平台进行公开竞价，现将有关内容公告如下： 一、项目概况及要求： 项目所 隆昌市 在地 项目基 详情见附件内容 本情况 网 项目需 【概算】隆昌市城市主城核心区雨水管网及附属设施建设项目.pdf 求材料 主城概算.pdf 竞价内 项目概算书评审 务 容范围 中介服 务完成 4天 期限要 商 求 竞价价 最低限价暂无，最高限价23000元 格区间 道 二、报名时间 2026年08月21日 18:00:00 ~ 2026年08月25日 18:00:00 三、报名条件 管 经认证注册入网，取得网上竞价资格的中介机构，可参与此中介服务项目的竞价。 资质类 型及等 工程咨询、工程设计资质 级要求 国 经营范 具有符合项目所属专业领域资质的投资咨询、工程管理、工程造价等。项目概算编制单位请主动回避 围要求 因不符合上述条件参加项目报名的，由参加者自行承担相应的法律责任。 中 咨询、 现场勘 自公告之日起至2026年08月25日 18:00:00止（节假日除外）接受咨询，有需要现场勘察的请与项目委托 察的时 人联系统一安排现场勘察。 间与方 式 备注 暂无 四、选取方式 公开竞价 五、联系方式 项目委 隆昌市发展和改革局 托单位 项目单 位联系 罗杰 人 联系电 13619005858 话 联系地 隆昌市 址 六、公告发布日期 2026年08月24日 11:14:04 免责申明：本网站是中介交易信息发布平台，所发布信息的真实性、合法性、有效性、完整性由信息发布者负 责 网 注册附件下载地址：http://zjfw-gc.sczwfw.gov.cn/zjcsmhwz/epointzjcs/pages/transInfo/tender 信息来源:https://www.chinapipe.net/project/d3078829.html cqdingjiu 2026.08.25 09:25:55 务 商 道 管 国 中</t>
+          <t>隆昌市城市主城核心区雨水管网及附属设施建设项目竞价公告 隆昌市发展和改革局（单位）隆昌市城市主城核心区雨水管网 及附属设施建设项目（中介服务项目）将在中 介服务网上交易平台进行公开竞价，现将有关内容公告如下： 一、项目概况及要求： 项目所 隆昌市 在地 项目基 详情见附件内容 本情况 网 项目需 【概算】隆昌市城市主城核心区雨水管网及附属设施建设项目.pdf 求材料 主城概算.pdf 竞价内 项目概算书评审 务 容范围 中介服 务完成 4天 期限要 商 求 竞价价 最低限价暂无，最高限价23000元 格区间 道 二、报名时间 2026年08月21日 18:00:00 ~ 2026年08月25日 18:00:00 三、报名条件 管 经认证注册入网，取得网上竞价资格的中介机构，可参与此中介服务项目的竞价。 资质类 型及等 工程咨询、工程设计资质 级要求 国 经营范 具有符合项目所属专业领域资质的投资咨询、工程管理、工程造价等。项目概算编制单位请主动回避 围要求 因不符合上述条件参加项目报名的，由参加者自行承担相应的法律责任。 中 咨询、 现场勘 自公告之日起至2026年08月25日 18:00:00止（节假日除外）接受咨询，有需要现场勘察的请与项目委托 察的时 人联系统一安排现场勘察。 间与方 式 备注 暂无 四、选取方式 公开竞价 五、联系方式 项目委 隆昌市发展和改革局 托单位 项目单 位联系 罗杰 人 联系电 13619005858 话 联系地 隆昌市 址 六、公告发布日期 2026年08月24日 11:14:04 免责申明：本网站是中介交易信息发布平台，所发布信息的真实性、合法性、有效性、完整性由信息发布者负 责 网 注册附件下载地址：http://zjfw-gc.sczwfw.gov.cn/zjcsmhwz/epointzjcs/pages/transInfo/tender 信息来源:https://www.chinapipe.net/project/d3078829.html cqdingjiu 2026.08.25 10:30:35 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4625,7 +4621,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>雨水管网, 附属设施, 项目概算</t>
+          <t>雨水管网, 附属设施, 概算, 23000元</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4683,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>道孚县八美镇排水管网提升改造项目招标计划 道孚县发展和改革局关于道孚县 项目批准文件及文号 八美镇排水管网提升改造项目可 招标项目名称 道孚县八美镇排水管网提升改造项目 （如有） 行性研究报告的批复(道发改投 【2024】291号) 招标人 道孚县住房和城乡建设局 联系人及联系方式 高老师:0836-7122067 估算总投资 53940000.00 项目分类 市政基础设施工程 （元） 网 提升改造排水管网20公里，其中新建排水管网10公里，修复排水管网10公里；新建内容包括管道 招标项目概况 及附属设施、道路恢复等。 序号 招标内容 投标人主要资格条件要求 预计招标时间 务 拟招标内容 1 施工 以发布的招标公告和招标文件为准 2026-09-25 00:00:00 2 监理 以发布的招标公告和招标文件为准 2026-09-25 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 商 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078797.html 道 cqdingjiu 2026.08.25 09:25:55 管 国 中</t>
+          <t>道孚县八美镇排水管网提升改造项目招标计划 道孚县发展和改革局关于道孚县 项目批准文件及文号 八美镇排水管网提升改造项目可 招标项目名称 道孚县八美镇排水管网提升改造项目 （如有） 行性研究报告的批复(道发改投 【2024】291号) 招标人 道孚县住房和城乡建设局 联系人及联系方式 高老师:0836-7122067 估算总投资 53940000.00 项目分类 市政基础设施工程 （元） 网 提升改造排水管网20公里，其中新建排水管网10公里，修复排水管网10公里；新建内容包括管道 招标项目概况 及附属设施、道路恢复等。 序号 招标内容 投标人主要资格条件要求 预计招标时间 务 拟招标内容 1 施工 以发布的招标公告和招标文件为准 2026-09-25 00:00:00 2 监理 以发布的招标公告和招标文件为准 2026-09-25 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 商 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3078797.html 道 cqdingjiu 2026.08.25 10:30:35 管 国 中</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4701,7 +4697,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>排水管网, 提升改造, 投资额</t>
+          <t>排水管网, 提升改造, 投资额, 项目内容</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4736,12 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>山东省路桥集团有限公司三公司钢管及管件谈判采购SDLQ2026HW103016采购公告正文详见图片。</t>
+          <t>山东省路桥集团有限公司三公司钢管及管件谈判采购</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4755,12 +4751,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>山东省路桥集团有限公司三公司钢管及管件谈判采购公告 山东省路桥集团有限公司三公司钢管及管件谈判采购SDLQ2026HW103016采购公告 正文详见图片 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 正文详见图片 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 信息来源:https://www.chinapipe.net/project/d3078800.html cqdingjiu 2026.08.25 09:25:55 网 务 商 道 管 国 中</t>
+          <t>山东省路桥集团有限公司三公司钢管及管件谈判采购公告 山东省路桥集团有限公司三公司钢管及管件谈判采购SDLQ2026HW103016采购公告 正文详见图片 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 正文详见图片 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 信息来源:https://www.chinapipe.net/project/d3078800.html cqdingjiu 2026.08.25 10:30:35 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>山东省路桥集团有限公司三公司钢管及管件谈判采购SDLQ2026HW103016采购公告正文详见图片。
+          <t>山东省路桥集团有限公司三公司钢管及管件谈判采购
 https://www.chinapipe.net/project/d3078800.html</t>
         </is>
       </c>
@@ -4769,7 +4765,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>钢管, 管件, 谈判采购</t>
+          <t>钢管, 管件</t>
         </is>
       </c>
     </row>
@@ -4804,16 +4800,8 @@
           <t>四川省</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>自贡市</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>自贡市</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>逸景台室外给水管道工程(庭院管道)二次供水设备采购</t>
@@ -4831,7 +4819,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>逸景台室外给水管道工程(庭院管道)二次供水设备采购竞争性谈判采购公告 四川致荣项目管理有限公司受自贡水投建设安装工程有限责任公司的委托，拟对逸景台室外给水管道工程（庭 院管道）二次供水设备采购进行国内竞争性谈判采购，兹邀请符合本次采购要求的供应商参加谈判，具体事项 如下： 一、项目编号：5103012026083010。 二、项目名称：逸景台室外给水管道工程（庭院管道）二次供水设备采购。 网 三、采购预算：350,000.00元。 四、采购项目内容： 务 序号 项目内容 单位 数量 备注 详细的项目 1 逸景台室外给水管道工程（庭院管道）二次供水设备采购 项 1 要求见第五章 商 五、供应商参加本采购活动应具备下列条件： （一）一般资格性要求 1.具有独立承担民事责任的能力。 道 2.具有良好的商业信誉和健全的财务会计制度。 3.具有履行合同所必需的设备和专业技术能力。 管 4.有依法缴纳税收和社会保障资金的良好记录。 5.参加本次采购活动前三年内，在经营活动中没有重大违法记录。 国 6.法律、行政法规规定的其他条件。 7.本项目不接受联合体参加谈判。 （二）其他中要求 1.本项目有供货时限要求，具体时限详见谈判文件。 2.本项目有税票要求，报名供应商必须具有开具增值税专票13%的条件。 3.本项目有质保要求，质保期5年，质保金质押时间5年。 4.供应商自2025年1月1日起至少有2个类似本项目的合同供货业绩（类似业绩：合同业绩采购清单中须包含变频水 泵或高区罐式无负压供水设备）。 六、供应商邀请方式：本次竞争性谈判邀请在四川招投标网（www.scbid.com）上以公告形式发布。 七、禁止参加本次采购活动的供应商（实质性要求）： 根据相关规定，拒绝列入失信被执行人名单、重大税收违法案件当事人名单、严重违法失信行为记录名单中的 供应商报名参加本次采购活动。 八、竞争性谈判文件获取时间、地点及费用： 竞争性谈判文件自2026年8月24日至2026年8月26日，每天上午09:00至下午17:00（北京时间，法定节假日除外）在 四川致荣项目管理有限公司现场或远程提供。 本项目竞争性谈判文件有偿获取：售价人民币300.00元/份。费用以现金或转账到以下账户： 收款单位：四川致荣项目管理有限公司 开户银行：中国工商银行股份有限公司自贡分行南湖支行 账号：2303 3043 0910 0001 566 （竞争性谈判文件提供后费用不退，谈判资格不能转让）。 邮购联系方式：请将报名资料电子版传至sc-zr@qq.com，联系电话：0813-6220222。 供应商在购买竞争性谈判文件时，经办人员现场或电子邮件提交下列有效资料：网 供应商为法人或者其他组织的，须提供单位介绍信（可参考附件格式）、经办人身份证明(加盖单位公章)、报名 登记表（详见附件）。 务 九、响应文件的递交： 1.递交响应文件截止时间：2026年8月27日14时30分（北京时间）。 2.响应文件必须在递交响应截止时间前送达评审地点。逾商期送达、密封和标注错误的响应文件不予接收。本次谈 判不接受邮寄的响应文件。 十、评审： 道 1.评审时间：与响应文件递交截止时间相同。 2.评审形式：线下纸质版文件评审。 管 3.评审地点：四川致荣项目管理有限公司开标大厅。（地址：自贡市高新工业园区新源路19号办公综合楼） 十一、联系方式： 采 购 人：自贡水投建国设安装工程有限责任公司 通讯地址：四川省自贡市自流井区丹阳街538号 联 系 人：尹先生 中 联系电话：0813-5896075 采购代理机构：四川致荣项目管理有限公司 通讯地址：自贡市高新工业园区新源路19号办公综合楼 邮 编：643000 联 系 人：周女士 联系电话：0813-6220222 邮箱地址：sc-zr@qq.com 信息来源:https://www.chinapipe.net/project/d3078675.html cqdingjiu 2026.08.25 09:26:00</t>
+          <t>逸景台室外给水管道工程(庭院管道)二次供水设备采购竞争性谈判采购公告 四川致荣项目管理有限公司受自贡水投建设安装工程有限责任公司的委托，拟对逸景台室外给水管道工程（庭 院管道）二次供水设备采购进行国内竞争性谈判采购，兹邀请符合本次采购要求的供应商参加谈判，具体事项 如下： 一、项目编号：5103012026083010。 二、项目名称：逸景台室外给水管道工程（庭院管道）二次供水设备采购。 网 三、采购预算：350,000.00元。 四、采购项目内容： 务 序号 项目内容 单位 数量 备注 详细的项目 1 逸景台室外给水管道工程（庭院管道）二次供水设备采购 项 1 要求见第五章 商 五、供应商参加本采购活动应具备下列条件： （一）一般资格性要求 1.具有独立承担民事责任的能力。 道 2.具有良好的商业信誉和健全的财务会计制度。 3.具有履行合同所必需的设备和专业技术能力。 管 4.有依法缴纳税收和社会保障资金的良好记录。 5.参加本次采购活动前三年内，在经营活动中没有重大违法记录。 国 6.法律、行政法规规定的其他条件。 7.本项目不接受联合体参加谈判。 （二）其他中要求 1.本项目有供货时限要求，具体时限详见谈判文件。 2.本项目有税票要求，报名供应商必须具有开具增值税专票13%的条件。 3.本项目有质保要求，质保期5年，质保金质押时间5年。 4.供应商自2025年1月1日起至少有2个类似本项目的合同供货业绩（类似业绩：合同业绩采购清单中须包含变频水 泵或高区罐式无负压供水设备）。 六、供应商邀请方式：本次竞争性谈判邀请在四川招投标网（www.scbid.com）上以公告形式发布。 七、禁止参加本次采购活动的供应商（实质性要求）： 根据相关规定，拒绝列入失信被执行人名单、重大税收违法案件当事人名单、严重违法失信行为记录名单中的 供应商报名参加本次采购活动。 八、竞争性谈判文件获取时间、地点及费用： 竞争性谈判文件自2026年8月24日至2026年8月26日，每天上午09:00至下午17:00（北京时间，法定节假日除外）在 四川致荣项目管理有限公司现场或远程提供。 本项目竞争性谈判文件有偿获取：售价人民币300.00元/份。费用以现金或转账到以下账户： 收款单位：四川致荣项目管理有限公司 开户银行：中国工商银行股份有限公司自贡分行南湖支行 账号：2303 3043 0910 0001 566 （竞争性谈判文件提供后费用不退，谈判资格不能转让）。 邮购联系方式：请将报名资料电子版传至sc-zr@qq.com，联系电话：0813-6220222。 供应商在购买竞争性谈判文件时，经办人员现场或电子邮件提交下列有效资料：网 供应商为法人或者其他组织的，须提供单位介绍信（可参考附件格式）、经办人身份证明(加盖单位公章)、报名 登记表（详见附件）。 务 九、响应文件的递交： 1.递交响应文件截止时间：2026年8月27日14时30分（北京时间）。 2.响应文件必须在递交响应截止时间前送达评审地点。逾商期送达、密封和标注错误的响应文件不予接收。本次谈 判不接受邮寄的响应文件。 十、评审： 道 1.评审时间：与响应文件递交截止时间相同。 2.评审形式：线下纸质版文件评审。 管 3.评审地点：四川致荣项目管理有限公司开标大厅。（地址：自贡市高新工业园区新源路19号办公综合楼） 十一、联系方式： 采 购 人：自贡水投建国设安装工程有限责任公司 通讯地址：四川省自贡市自流井区丹阳街538号 联 系 人：尹先生 中 联系电话：0813-5896075 采购代理机构：四川致荣项目管理有限公司 通讯地址：自贡市高新工业园区新源路19号办公综合楼 邮 编：643000 联 系 人：周女士 联系电话：0813-6220222 邮箱地址：sc-zr@qq.com 信息来源:https://www.chinapipe.net/project/d3078675.html cqdingjiu 2026.08.25 10:30:39</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4907,7 +4895,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>泸州市城市照明管理服务中心2026年照明设施维护材料采购竞争性谈判公告 项目概况 2026年照明设施维护材料采购的潜在供应商应在四川省政府采购一体化平台项目电子化交易系统（以下简称“项 目电子化交易系统”）获取采购文件，并于 2026年09月01日09时30分 （北京时间）前提交响应文件。本项目 通过项目电子化交易系统实行电子化采购。 一、项目基本情况 网 项目编号：N5105012026000317 项目名称：2026年照明设施维护材料采购 务 采购方式：竞争性谈判 预算金额：3,300,000.00元 采购需求：详见采购需求附件 商 合同履行期限： 采购包1：第一次供货：采购人和成交供应商道签订合同后30日内，成交供应商向采购人交付50%数量的货物。 第 二次供货：2026年11月30日前（以采购人通知时间为准）成交供应商向采购人交付剩余货物。 本项目是否接受联合体参与： 管 采购包1：不接受联合体投标 二、申请人的资格要求： 1.满足《中华人民共和国国政府采购法》第二十二条规定： （1）具有独立承担民事责任的能力； （2）具有良好的商业信誉和健全的财务会计制度； （3）具有履行合同所必需的设备和专业技术能力； 中 （4）有依法缴纳税收和社会保障资金的良好记录； （5）参加政府采购活动前三年内，在经营活动中没有重大违法记录。 2.落实政府采购政策需满足的资格要求： 采购包1：无 3.本项目的特定资格要求： 采购包1：无 三、获取采购文件 时间：2026年08月25日至2026年08月27日，每天上午00:00:00至12:00:00，下午12:00:00至23:59:59（北京时间） 途径：项目电子化交易系统-投标（响应）管理-未获取采购文件中选择本项目获取招标文件 方式：在线获取 售价：0元 四、响应文件提交 截止时间：2026年09月01日09时30分00秒（北京时间） 地点：通过项目电子化交易系统-投标（响应）管理在线提交响应文件 五、开启 时间：2026年09月01日09时30分00秒（北京时间） 地点：通过项目电子化交易系统-开标/开启大厅参与开启 六、公告期限 网 自本公告发布之日起3个工作日。 七、其他补充事宜 务 1.采购包1预算金额及最高限价详见附件。 2.监督管理部门：泸州市财政局采购科,电话：0830-2282871。 商 3.供应商信用融资：根据《四川省财政厅关于推进四川省政府采购供应商信用融资工作的通知》（川财 采[2018]123号）文件要求，为助力解决政府采购中标/成交供应商资金不足、融资难、融资贵的困难，促进供应 商依法诚信参加政府采购活动，有融资需求的供应商可根据四川政府采购网（https://www.ccgp-sichuan.gov.cn/） 公示的银行及其“政采贷”产品，自行选择符道合自身情况的“政采贷”银行及其产品，凭中标（成交）通知书 向银行提出贷款意向申请，并按照相关规定要求和贷款流程申请信用融资贷款。 八、凡对本次采购提出询问，请按以下方式联系。 管 1.采购人信息 名称：泸州市城市照明管理服务中心 地址：四川省泸州市江国阳区江阳南路210号 联系方式：0830-3195746 2.采购代理机构信息 中 名称：四川勤德建设工程造价咨询有限责任公司 地址：四川省泸州市江阳区佳乐世纪城金融中心9号楼702号 联系方式：0830-6668813 3.项目联系方式 项目联系人：郭女士 电话：0830-6668813 四川勤德建设工程造价咨询有限责任公司 2026年08月24日 相关附件： 采购需求.pdf 附件下载：采购需求.pdf 信息来源:https://www.chinapipe.net/project/d3078669.html cqdingjiu 2026.08.25 09:26:00 网 务 商 道 管 国 中</t>
+          <t>泸州市城市照明管理服务中心2026年照明设施维护材料采购竞争性谈判公告 项目概况 2026年照明设施维护材料采购的潜在供应商应在四川省政府采购一体化平台项目电子化交易系统（以下简称“项 目电子化交易系统”）获取采购文件，并于 2026年09月01日09时30分 （北京时间）前提交响应文件。本项目 通过项目电子化交易系统实行电子化采购。 一、项目基本情况 网 项目编号：N5105012026000317 项目名称：2026年照明设施维护材料采购 务 采购方式：竞争性谈判 预算金额：3,300,000.00元 采购需求：详见采购需求附件 商 合同履行期限： 采购包1：第一次供货：采购人和成交供应商道签订合同后30日内，成交供应商向采购人交付50%数量的货物。 第 二次供货：2026年11月30日前（以采购人通知时间为准）成交供应商向采购人交付剩余货物。 本项目是否接受联合体参与： 管 采购包1：不接受联合体投标 二、申请人的资格要求： 1.满足《中华人民共和国国政府采购法》第二十二条规定： （1）具有独立承担民事责任的能力； （2）具有良好的商业信誉和健全的财务会计制度； （3）具有履行合同所必需的设备和专业技术能力； 中 （4）有依法缴纳税收和社会保障资金的良好记录； （5）参加政府采购活动前三年内，在经营活动中没有重大违法记录。 2.落实政府采购政策需满足的资格要求： 采购包1：无 3.本项目的特定资格要求： 采购包1：无 三、获取采购文件 时间：2026年08月25日至2026年08月27日，每天上午00:00:00至12:00:00，下午12:00:00至23:59:59（北京时间） 途径：项目电子化交易系统-投标（响应）管理-未获取采购文件中选择本项目获取招标文件 方式：在线获取 售价：0元 四、响应文件提交 截止时间：2026年09月01日09时30分00秒（北京时间） 地点：通过项目电子化交易系统-投标（响应）管理在线提交响应文件 五、开启 时间：2026年09月01日09时30分00秒（北京时间） 地点：通过项目电子化交易系统-开标/开启大厅参与开启 六、公告期限 网 自本公告发布之日起3个工作日。 七、其他补充事宜 务 1.采购包1预算金额及最高限价详见附件。 2.监督管理部门：泸州市财政局采购科,电话：0830-2282871。 商 3.供应商信用融资：根据《四川省财政厅关于推进四川省政府采购供应商信用融资工作的通知》（川财 采[2018]123号）文件要求，为助力解决政府采购中标/成交供应商资金不足、融资难、融资贵的困难，促进供应 商依法诚信参加政府采购活动，有融资需求的供应商可根据四川政府采购网（https://www.ccgp-sichuan.gov.cn/） 公示的银行及其“政采贷”产品，自行选择符道合自身情况的“政采贷”银行及其产品，凭中标（成交）通知书 向银行提出贷款意向申请，并按照相关规定要求和贷款流程申请信用融资贷款。 八、凡对本次采购提出询问，请按以下方式联系。 管 1.采购人信息 名称：泸州市城市照明管理服务中心 地址：四川省泸州市江国阳区江阳南路210号 联系方式：0830-3195746 2.采购代理机构信息 中 名称：四川勤德建设工程造价咨询有限责任公司 地址：四川省泸州市江阳区佳乐世纪城金融中心9号楼702号 联系方式：0830-6668813 3.项目联系方式 项目联系人：郭女士 电话：0830-6668813 四川勤德建设工程造价咨询有限责任公司 2026年08月24日 相关附件： 采购需求.pdf 附件下载：采购需求.pdf 信息来源:https://www.chinapipe.net/project/d3078669.html cqdingjiu 2026.08.25 10:30:39 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4983,7 +4971,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>中二十四局集团上海电务电化有限公司天眉乐高速公路项目JD3标、JA3标隔离栅、防落物网、防眩板、电缆、 光缆及硅芯管询价补遗公告2 各潜在报价单位： 为保障本次询价采购工作公平、公正、公开开展，确保各报价单位准确、完整理解本次询价项目相关要求，针 对本次【中铁二十四局集团上海电务电化有限公司天眉乐高速公路项目JD3标、JA3标隔离栅、防落物网、防眩 板、电缆、光缆及硅芯管询价】（采购编号：CR24(2026)-DWDH-XJ-TML-JDJA-01）询价文件，经采购单位核查 确认，现对文件相关内容作如下补遗、补充及更正，本补遗与原询价文件具有同等法律效力。 网 一、补遗如下 1. 文件内容：【第一章 采购公告，3.1拟采购物资一览表，包件JD-02光缆第5项规格型号为GCYFTY-24B1】， 光缆具体规格型号以询价文件“第一章 采购公告3.1拟采购物资一览表中的规格型号”为准，系统上物资清单有 务 备注的，以备注为准。 2. 本次询价采购JD-02包件，若潜在报价单位经营范围内无音频线、音频配线架至楼内电话分线箱配线电缆 及SYKV-75-3电缆生产制造许可事项，仅可开展经销、贸易业务，无自产能力，可以进行外购，但质量等必须符 合本询价文件要求，供货时需按规范要求提供合格证、出商厂检测报告等质保资料。 二、补充说明事项 1. 本补遗为本次询价文件的组成部分，与原询道价文件内容不一致之处，以本补遗为准；本补遗未提及的内容， 仍按原询价文件规定执行。 2. 各报价单位须充分研读本补遗全部内容，严格按照补遗后的完整文件要求编制、提交报价文件，未结合本补 遗制作的报价文件，视为无效报价。 管 3. 各潜在报价单位收到本补遗后，无需单独回复确认，自行落实文件解读及报价编制工作即可。 三、联系方式 国 1.采购组织单位：中铁二十四局集团有限公司设备物资集采中心电务分中心 联 系 人：陈先生 中 联系电话：021-51226136 2.采购人：中铁二十四局集团上海电务电化有限公司天眉乐高速公路项目JD3标、JA3标项目经理 部 地 址：四川省乐山市市中区佛光路525号 技术联系人：左先生 联系电话：19136188150 中铁二十四局集团有限公司设备物资集采中心电务分中心 2026年8月22日 发布时间：2026-08-24 投标截至时间：2026-08-25 09:00:00发布单位：中铁二十四局集团有限公司设备物资集采中 心电务分中心 信息来源:https://www.chinapipe.net/project/d3078649.html cqdingjiu 2026.08.25 09:26:01 网 务 商 道 管 国 中</t>
+          <t>中二十四局集团上海电务电化有限公司天眉乐高速公路项目JD3标、JA3标隔离栅、防落物网、防眩板、电缆、 光缆及硅芯管询价补遗公告2 各潜在报价单位： 为保障本次询价采购工作公平、公正、公开开展，确保各报价单位准确、完整理解本次询价项目相关要求，针 对本次【中铁二十四局集团上海电务电化有限公司天眉乐高速公路项目JD3标、JA3标隔离栅、防落物网、防眩 板、电缆、光缆及硅芯管询价】（采购编号：CR24(2026)-DWDH-XJ-TML-JDJA-01）询价文件，经采购单位核查 确认，现对文件相关内容作如下补遗、补充及更正，本补遗与原询价文件具有同等法律效力。 网 一、补遗如下 1. 文件内容：【第一章 采购公告，3.1拟采购物资一览表，包件JD-02光缆第5项规格型号为GCYFTY-24B1】， 光缆具体规格型号以询价文件“第一章 采购公告3.1拟采购物资一览表中的规格型号”为准，系统上物资清单有 务 备注的，以备注为准。 2. 本次询价采购JD-02包件，若潜在报价单位经营范围内无音频线、音频配线架至楼内电话分线箱配线电缆 及SYKV-75-3电缆生产制造许可事项，仅可开展经销、贸易业务，无自产能力，可以进行外购，但质量等必须符 合本询价文件要求，供货时需按规范要求提供合格证、出商厂检测报告等质保资料。 二、补充说明事项 1. 本补遗为本次询价文件的组成部分，与原询道价文件内容不一致之处，以本补遗为准；本补遗未提及的内容， 仍按原询价文件规定执行。 2. 各报价单位须充分研读本补遗全部内容，严格按照补遗后的完整文件要求编制、提交报价文件，未结合本补 遗制作的报价文件，视为无效报价。 管 3. 各潜在报价单位收到本补遗后，无需单独回复确认，自行落实文件解读及报价编制工作即可。 三、联系方式 国 1.采购组织单位：中铁二十四局集团有限公司设备物资集采中心电务分中心 联 系 人：陈先生 中 联系电话：021-51226136 2.采购人：中铁二十四局集团上海电务电化有限公司天眉乐高速公路项目JD3标、JA3标项目经理 部 地 址：四川省乐山市市中区佛光路525号 技术联系人：左先生 联系电话：19136188150 中铁二十四局集团有限公司设备物资集采中心电务分中心 2026年8月22日 发布时间：2026-08-24 投标截至时间：2026-08-25 09:00:00发布单位：中铁二十四局集团有限公司设备物资集采中 心电务分中心 信息来源:https://www.chinapipe.net/project/d3078649.html cqdingjiu 2026.08.25 10:30:40 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4993,11 +4981,11 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5032,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>本次计划对过轨管材料进行询价，询价内容包括DN125米、DN180米、DN125个、DN180个四种过轨管及其接头。</t>
+          <t>中铁十一局集团有限公司新建成渝中线铁路四川段CYZXZQ-1标位于四川省成都市金牛区、成华区、龙泉驿区以及安岳境内。主线起止里程DK282+986～DK288+400，全长5.414公里。主要工程内容：“一隧一路两厂”，其中隧道0.5座/4.854公里，路基0.56公里/1.21万方，管片厂1处/10380m管片预制，板厂1处/96.51公里III型板预制。其中蜀安隧道为我标段的重难点工程，盾构段拟采用1台直径14m的土压平衡盾构开挖。</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>本项目中标金额为26.38亿元，总体工期为1826日历天，计划开工日期为2022年11月30日，计划竣工日期为2027年11月29日。</t>
+          <t>中标金额26.38亿元。</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5059,21 +5047,21 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>中铁十一局集团有限公司新建成渝中线铁路(四川段)站前施工CYZXZQ-1标项目经理部过轨管询价采购公告 中铁十一局集团有限公司新建成渝中线铁路（四川 段）站前施工CYZXZQ-1标项目经理部 过轨管询价采购公告 询价编号：ZT1105-XJ-2026-457-2 网 尊敬的各潜在供应商: 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与中铁十一局集团有限公司新建成渝中线铁路 （四川段）站前施工CYZXZQ-1标项目经理部ZT1105-XJ-2026-457-2，过轨管的报价。 务 一、项目概况 中铁十一局集团有限公司新建成渝中线铁路四川段CYZXZQ-1标位于四川省成都市金牛区、成华区、 龙泉驿区 以及安岳境内。主线起止里程 DK282+986～DK288+400,全商长5.414公里。中标金额26.38亿元。 主要工程内容：“一隧一路两厂”,其中隧道0.5座/4.854公里，路基0.56 公里/1.21万方，管片厂1处/10380m管片预 制，板厂1处/96.51公里III 型 板 预制。其中蜀安隧道为我标段的重难点工程，盾构段拟采用1台直径14m 的土压 平衡盾构开挖。本标段报价总价26.38亿元。道 总体工期：1826日历天，计划开工日期2022年11月30日，计划竣工日期2027年11月29日。 管 二、询价内容 本次计划对过轨管材料进行询价，询价内容如下： 国 询价物资一览表 序号 包件号 物资名称 规格型号 计量单位 数量 备注 中 1 过轨管 DN125 米 840 2 过轨管 DN180 米 840 GGG-01 3 过轨管接头 DN125 个 140 4 过轨管接头 DN180 个 140 合计 说明：1.表中数量为计划数量，实际采购过程中可能有所调整，最终结算按照实际采购数量结算。 收货地点：四川省成都市成华区成铁路局客机整备所 三、技术质量及报价要求 1.此次过轨管主要技术性能及规格应满足《地下通信管道用塑料管 第 2 部分：实壁管》 （YD/T 841.2-2016），《给水用聚乙烯(PE)管道系统第 2 部分：管材》（GB/T 13663.2-2018），《地下通信管道 用塑料管 第 1 部分：总则》（YD/T 841.1-2016），《电力电缆导管技术条件 第 3 部分：实壁类塑料电缆导管》 （DL/T 802.3-2023）的要求，质量满足甲方项目部正常使用的要求，保证产品的质量合格，详见技术规格书。 2.报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、结算及付款方式 自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发票认证完成之日起第6个月，支付至本次结算 金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内，累计支付总额不超结算总金额的75%，剩 余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理末次结算后第二年，支付金额应大于等于 尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总额的15%；办理末次结算后第四年，全部 付清）。 五、报价人资格要求 1.营业范围要求：在中华人民共和国境内依法注册，具有询价物资生产或供应网经验的生产商或代理商，并 且具有合法有效的营业执照。 2.生产能力要求：生产商须具备询价物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定。代 理商需出具制造厂出具签字盖章的授权函。 务 3.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8月至今） 国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；每种物资全指标技术参数性能满足 国家和行业最新标准的各项规定。 商 4.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年8月至今）企业或企业法定代表人有人民法院生效判决、裁定 认定的行贿犯罪记录的。④ 对纳入国家铁路局道“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接受 通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合作 方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 5.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 管 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 ★6.下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 国 六、报价人需要提供的资料 1.营业执照复印件、法人身份证复印件、开户许可证、授权委托书、报价表和报价人资格要求中所需的证明资料， 所有资料需中加盖公司鲜章。 2.生产厂家资质，产品质量检测报告等质量证明文件。 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、询价报名截止时间 有意参加本次询价采购的报价人须在铁建云链平台（https://www.crccep.cn）完成供应商注册，并于2026年8月22 日9时00分至2026年8月25日9时00分在网上完成报名工作。 八、询价截止时间 凡有意参加本次询价采购的报价人，请于 2026年8月25日14时00分 前提交报价。截止时间前未完成报价文件传 输的，视为放弃报价。 供应商报价必须严格按照《报价表》格式进行报价。 九、联系方式 采购组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村71号 采购人名称：中铁十一局集团有限公司新建成渝中线铁路（四川段）站前施工CYZXZQ-1标项目经理部 地址：四川省成都市成华区华盛路58号19栋 联系人：向渝 联系电话：15178784487（提供采购服务支持） 中铁十一局集团有限公司 物资设备集中采购管理中心第五分中心 网 2026年8月22日 务 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3078608.html cqdingjiu 2026.08.25 09:26:01 商 道 管 国 中</t>
+          <t>中铁十一局集团有限公司新建成渝中线铁路(四川段)站前施工CYZXZQ-1标项目经理部过轨管询价采购公告 中铁十一局集团有限公司新建成渝中线铁路（四川 段）站前施工CYZXZQ-1标项目经理部 过轨管询价采购公告 询价编号：ZT1105-XJ-2026-457-2 网 尊敬的各潜在供应商: 本着公平、公正、公开、诚实信用的原则，诚挚的邀请贵公司参与中铁十一局集团有限公司新建成渝中线铁路 （四川段）站前施工CYZXZQ-1标项目经理部ZT1105-XJ-2026-457-2，过轨管的报价。 务 一、项目概况 中铁十一局集团有限公司新建成渝中线铁路四川段CYZXZQ-1标位于四川省成都市金牛区、成华区、 龙泉驿区 以及安岳境内。主线起止里程 DK282+986～DK288+400,全商长5.414公里。中标金额26.38亿元。 主要工程内容：“一隧一路两厂”,其中隧道0.5座/4.854公里，路基0.56 公里/1.21万方，管片厂1处/10380m管片预 制，板厂1处/96.51公里III 型 板 预制。其中蜀安隧道为我标段的重难点工程，盾构段拟采用1台直径14m 的土压 平衡盾构开挖。本标段报价总价26.38亿元。道 总体工期：1826日历天，计划开工日期2022年11月30日，计划竣工日期2027年11月29日。 管 二、询价内容 本次计划对过轨管材料进行询价，询价内容如下： 国 询价物资一览表 序号 包件号 物资名称 规格型号 计量单位 数量 备注 中 1 过轨管 DN125 米 840 2 过轨管 DN180 米 840 GGG-01 3 过轨管接头 DN125 个 140 4 过轨管接头 DN180 个 140 合计 说明：1.表中数量为计划数量，实际采购过程中可能有所调整，最终结算按照实际采购数量结算。 收货地点：四川省成都市成华区成铁路局客机整备所 三、技术质量及报价要求 1.此次过轨管主要技术性能及规格应满足《地下通信管道用塑料管 第 2 部分：实壁管》 （YD/T 841.2-2016），《给水用聚乙烯(PE)管道系统第 2 部分：管材》（GB/T 13663.2-2018），《地下通信管道 用塑料管 第 1 部分：总则》（YD/T 841.1-2016），《电力电缆导管技术条件 第 3 部分：实壁类塑料电缆导管》 （DL/T 802.3-2023）的要求，质量满足甲方项目部正常使用的要求，保证产品的质量合格，详见技术规格书。 2.报价按要求综合报价，包含但不限于材料费、搬运、储存、装车、运杂、售后服务费、利润、税费等除到场所 需的一切费用。在报价税率不同时，以不含税总价作为评审依据。 四、结算及付款方式 自发票认证完成之日起第3个月，支付至本次结算金额的30%；自发票认证完成之日起第6个月，支付至本次结算 金额的累计70%（即在本阶段支付40%）；在办理末次结算后1年内，累计支付总额不超结算总金额的75%，剩 余25%的尾款在3年内付清，且甲方每年付款比例不低于15%（如：办理末次结算后第二年，支付金额应大于等于 尾款总额的15%；办理末次结算后第三年，支付金额应大于等于尾款总额的15%；办理末次结算后第四年，全部 付清）。 五、报价人资格要求 1.营业范围要求：在中华人民共和国境内依法注册，具有询价物资生产或供应网经验的生产商或代理商，并 且具有合法有效的营业执照。 2.生产能力要求：生产商须具备询价物资生产能力，生产工艺、装备必须符合国家产业发展政策的相关规定。代 理商需出具制造厂出具签字盖章的授权函。 务 3.质量保证能力要求：产品质量符合最新国家或行业质量标准并满足设计要求，具有近两年（2024年8月至今） 国家认可的第三方检测机构出具的报价物资达到国家标准的合格检测报告；每种物资全指标技术参数性能满足 国家和行业最新标准的各项规定。 商 4.履约信用要求：1.报价单位财产未被接管或冻结；2.报价单位不得存在的其他情形：①因存在不良行为被中国 国家铁路集团有限公司限制参与物资采购活动的；②报价物资被中国国家铁路集团有限公司禁止或暂停在铁路 上使用的；③自报价文件递交之日起前3年（2023年8月至今）企业或企业法定代表人有人民法院生效判决、裁定 认定的行贿犯罪记录的。④ 对纳入国家铁路局道“黑名单”管理的单位，在公布期限内，不接受其报价；3.不接受 通过“信用中国”网站查询相关主体为失信被执行人的报价单位；4.本次询价不接受在最新一期《中国铁建合作 方警示名录》范围内，以及被采购人或其上级单位列入限制交易供应商名单的报价单位。 5.经评审通过的报价相同的报价人，由报价文件内企业注册资本金较多的报价人排序在前;若企业注册资本金也相 管 同，则由铁建云链平台询价报名响应时间在前的报价人排序在前。若报名时间也相同，则由评审小组商议并出 具一致意见以确定排序。 ★6.下列情形拒绝报价：铁建云链网站查询供应商关联关系，且经评审委员会评定认为属于相互串通报价的行为。 国 六、报价人需要提供的资料 1.营业执照复印件、法人身份证复印件、开户许可证、授权委托书、报价表和报价人资格要求中所需的证明资料， 所有资料需中加盖公司鲜章。 2.生产厂家资质，产品质量检测报告等质量证明文件。 ★以上资料报价单位必须对应提供，资料缺失将导致报价被拒绝。 七、询价报名截止时间 有意参加本次询价采购的报价人须在铁建云链平台（https://www.crccep.cn）完成供应商注册，并于2026年8月22 日9时00分至2026年8月25日9时00分在网上完成报名工作。 八、询价截止时间 凡有意参加本次询价采购的报价人，请于 2026年8月25日14时00分 前提交报价。截止时间前未完成报价文件传 输的，视为放弃报价。 供应商报价必须严格按照《报价表》格式进行报价。 九、联系方式 采购组织单位：中铁十一局集团有限公司物资设备集中采购管理中心第五分中心 地址：重庆市沙坪坝区新桥新村71号 采购人名称：中铁十一局集团有限公司新建成渝中线铁路（四川段）站前施工CYZXZQ-1标项目经理部 地址：四川省成都市成华区华盛路58号19栋 联系人：向渝 联系电话：15178784487（提供采购服务支持） 中铁十一局集团有限公司 物资设备集中采购管理中心第五分中心 网 2026年8月22日 务 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3078608.html cqdingjiu 2026.08.25 10:30:40 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>本次计划对过轨管材料进行询价，询价内容包括DN125米、DN180米、DN125个、DN180个四种过轨管及其接头。
+          <t>中铁十一局集团有限公司新建成渝中线铁路四川段CYZXZQ-1标位于四川省成都市金牛区、成华区、龙泉驿区以及安岳境内。主线起止里程DK282+986～DK288+400，全长5.414公里。主要工程内容：“一隧一路两厂”，其中隧道0.5座/4.854公里，路基0.56公里/1.21万方，管片厂1处/10380m管片预制，板厂1处/96.51公里III型板预制。其中蜀安隧道为我标段的重难点工程，盾构段拟采用1台直径14m的土压平衡盾构开挖。
 https://www.chinapipe.net/project/d3078608.html</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>重庆, 管材, 招标, 商机</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5123,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>太行项目不锈钢管件采购招标公告 四川省工业设备安装集团有限公司 压缩空气供应系统、供水系统、燃油供应系统及变配电系统（室外电缆工艺 用） 太行项目不锈钢管件采购 招标公告 四川省工业设备安装集团有限公司 现就 压缩空气供应系统、供水系统、燃油供应系统及变配电系统（室外 电缆工艺用） 的 法兰及其垫片,沟槽管件,铸铁管件,阀门,检查口,铜制管件,管道用材,套管,补偿器及软接头,过 滤器,塑料管件,复合管件,不锈钢管件,钢制管件,阻火器,水箱,其它管件及管道用器材,铝合金管件,玻璃钢管件 采 购事宜进行公开招标，欢迎有意向的供应商参加投标。 一、采购内容 网 法兰及其垫片,沟槽管件,铸铁管件,阀门,检查口,铜制管件,管道用材,套管,补偿器及软接头,过滤器,塑料管件,复合管 件,不锈钢管件,钢制管件,阻火器,水箱,其它管件及管道用器材,铝合金管件,玻璃钢管件 ，预计总用量约为： 见 附件 。 不锈钢管件 务 二、项目概况 项目名称： 压缩空气供应系统、供水系统、燃油供应系统及变配电系统（室外电缆工艺用） 项目地址： 四川成都市东部新区简州新城指定地点 商 建筑规模： 0㎡ 其他详见招标文件。 三、招标方式 本次采购招标采用公开招标的方式进行，并在道善建云采（四川华西集团有限公司及下属分子公司）发布招标公 告，网址为：https://scm.zghxsjy.com/。 四、投标人资格要求 在善建云采（四川华西集团有限公司及下属分子公司）（https://scm.zghxsjy.com/）已注册的合格分供商均可参与 管 投标。 五、招投标时间节点 （一）招标文件发售截止时间： 2026-08-28 09:00:00 ； 国 （二）投标保证金缴纳的截止时间为： 2026-08-28 09:30:00 ； （三）本次招标的投标截止时间为： 2026-08-28 10:10:00 ； （四）本次招标的开标时间为： 2026-08-28 10:10:00 ； （五）电子标书费售价：人民币 40 元/套，售后不退。 中 六、缴费注意事项 为保证招投标的公平公正，善建云采（四川华西集团有限公司及下属分子公司）已与银行实现系统对接，从缴 费账号生成、缴费确认、标书下载和投标功能开放，全部实现自动化、线上化，请投标人务必按照下述要求缴 纳标书费和投标保证金，避免影响投标。 电子标书费缴纳： 1、投标人一旦决定投标，请在善建云采（四川华西集团有限公司及下属分子公司）上点击“交标书费”，银行 系统会随机自动为该次缴费生成一次性的唯一银行账号。 2、请投标人务必把标书费转入上述银行账户。投标人缴费后，银行系统会同步自动将缴费信息推送至善建云采 （四川华西集团有限公司及下属分子公司）和投标人，善建云采（四川华西集团有限公司及下属分子公司）系 统亦同步开放权限，投标人即可在善建云采（四川华西集团有限公司及下属分子公司）浏览和下载标书。 3、投标人务必严格按照上述要求进行投标操作。若投标人缴费到错误账号，善建云采（四川华西集团有限公司 及下属分子公司）无法开放投标功能，由此无法购买标书、无法投标、退回款项延迟等产生的一切损失，均由 投标人自行承担。 投标保证金缴纳： 1、投标人在善建云采（四川华西集团有限公司及下属分子公司）上点击“交投标保证金”后，由银行系统自动 为该次缴费生成唯一银行账号。 2、请投标人务必把投标保证金转入上述银行账户。投标人缴费后，银行系统会同步自动将缴费信息推送至善建 云采（四川华西集团有限公司及下属分子公司）和投标人，善建云采（四川华西集团有限公司及下属分子公司） 系统亦同步开放权限，投标人即可在善建云采（四川华西集团有限公司及下属分子公司）上传投标文件和填报 投标数据。 3、投标人务必严格按照上述要求进行投标操作。若投标人缴费到错误账号，善建云采（四川华西集团有限公司 及下属分子公司）无法开放投标功能，由此无法投标、退回款项延迟等产生的一切损失，均由投标人自行承担。 投标人缴纳投标保证金必须由投标人对公账户转账，不接受个人账户转款、现金缴存、他人代缴。若出现投标 人使用个人账户转款、现金缴存、他人代缴、未按系统自动生成的对应账号转款、超额转款等，平台将无法自 动退款。在中标公示结束后3个工作日内未收到保证金退款，投标人应在10个工作日后向四川华西数产科技集团 有限公司提供完整的书面缴费依据，四川华西数产科技集团有限公司将在收到投标人提供的完整缴费依据后， 在7个工作日内核实并退款。若出现上述情况投标人可编辑含有“招标项目名称”、“招标单位”的短信发送至： 19950205781（本号码只接受短信联系方式），也可到访四川华西数产科技集团有限公司进行沟通。 系统每次生成的账号，均为一次性账号和唯一性账号，标书费账号与投标保证金账号不同，项目与项目间账号 不同。 七、投标文件的递交 招标人仅接受投标人通过善建云采（四川华西集团有限公司及下属分子公司）提交的投标文件，不接受通过其 他方式提交的书面投标文件。线上投标内容具有法律效力且具有唯一性，请投标网人慎重对待。 八、其他描述 九、其他资格要求 务 十、其他事项 若对招标公告有其他不明事项，请致电： 业务咨询联系人： 安虹静 ，联系电话： 15883776766 ； 商 技术支持联系人： 集采技术部 ，联系电话： 02883382846 ； 十一、声明 本招标公告仅为信息发布，不构成任何法律意义上的要约或承诺。 现予公告。 道 四川省工业设备安装集团有限公司 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3078483.html 管 cqdingjiu 2026.08.25 09:26:01 国 中</t>
+          <t>太行项目不锈钢管件采购招标公告 四川省工业设备安装集团有限公司 压缩空气供应系统、供水系统、燃油供应系统及变配电系统（室外电缆工艺 用） 太行项目不锈钢管件采购 招标公告 四川省工业设备安装集团有限公司 现就 压缩空气供应系统、供水系统、燃油供应系统及变配电系统（室外 电缆工艺用） 的 法兰及其垫片,沟槽管件,铸铁管件,阀门,检查口,铜制管件,管道用材,套管,补偿器及软接头,过 滤器,塑料管件,复合管件,不锈钢管件,钢制管件,阻火器,水箱,其它管件及管道用器材,铝合金管件,玻璃钢管件 采 购事宜进行公开招标，欢迎有意向的供应商参加投标。 一、采购内容 网 法兰及其垫片,沟槽管件,铸铁管件,阀门,检查口,铜制管件,管道用材,套管,补偿器及软接头,过滤器,塑料管件,复合管 件,不锈钢管件,钢制管件,阻火器,水箱,其它管件及管道用器材,铝合金管件,玻璃钢管件 ，预计总用量约为： 见 附件 。 不锈钢管件 务 二、项目概况 项目名称： 压缩空气供应系统、供水系统、燃油供应系统及变配电系统（室外电缆工艺用） 项目地址： 四川成都市东部新区简州新城指定地点 商 建筑规模： 0㎡ 其他详见招标文件。 三、招标方式 本次采购招标采用公开招标的方式进行，并在道善建云采（四川华西集团有限公司及下属分子公司）发布招标公 告，网址为：https://scm.zghxsjy.com/。 四、投标人资格要求 在善建云采（四川华西集团有限公司及下属分子公司）（https://scm.zghxsjy.com/）已注册的合格分供商均可参与 管 投标。 五、招投标时间节点 （一）招标文件发售截止时间： 2026-08-28 09:00:00 ； 国 （二）投标保证金缴纳的截止时间为： 2026-08-28 09:30:00 ； （三）本次招标的投标截止时间为： 2026-08-28 10:10:00 ； （四）本次招标的开标时间为： 2026-08-28 10:10:00 ； （五）电子标书费售价：人民币 40 元/套，售后不退。 中 六、缴费注意事项 为保证招投标的公平公正，善建云采（四川华西集团有限公司及下属分子公司）已与银行实现系统对接，从缴 费账号生成、缴费确认、标书下载和投标功能开放，全部实现自动化、线上化，请投标人务必按照下述要求缴 纳标书费和投标保证金，避免影响投标。 电子标书费缴纳： 1、投标人一旦决定投标，请在善建云采（四川华西集团有限公司及下属分子公司）上点击“交标书费”，银行 系统会随机自动为该次缴费生成一次性的唯一银行账号。 2、请投标人务必把标书费转入上述银行账户。投标人缴费后，银行系统会同步自动将缴费信息推送至善建云采 （四川华西集团有限公司及下属分子公司）和投标人，善建云采（四川华西集团有限公司及下属分子公司）系 统亦同步开放权限，投标人即可在善建云采（四川华西集团有限公司及下属分子公司）浏览和下载标书。 3、投标人务必严格按照上述要求进行投标操作。若投标人缴费到错误账号，善建云采（四川华西集团有限公司 及下属分子公司）无法开放投标功能，由此无法购买标书、无法投标、退回款项延迟等产生的一切损失，均由 投标人自行承担。 投标保证金缴纳： 1、投标人在善建云采（四川华西集团有限公司及下属分子公司）上点击“交投标保证金”后，由银行系统自动 为该次缴费生成唯一银行账号。 2、请投标人务必把投标保证金转入上述银行账户。投标人缴费后，银行系统会同步自动将缴费信息推送至善建 云采（四川华西集团有限公司及下属分子公司）和投标人，善建云采（四川华西集团有限公司及下属分子公司） 系统亦同步开放权限，投标人即可在善建云采（四川华西集团有限公司及下属分子公司）上传投标文件和填报 投标数据。 3、投标人务必严格按照上述要求进行投标操作。若投标人缴费到错误账号，善建云采（四川华西集团有限公司 及下属分子公司）无法开放投标功能，由此无法投标、退回款项延迟等产生的一切损失，均由投标人自行承担。 投标人缴纳投标保证金必须由投标人对公账户转账，不接受个人账户转款、现金缴存、他人代缴。若出现投标 人使用个人账户转款、现金缴存、他人代缴、未按系统自动生成的对应账号转款、超额转款等，平台将无法自 动退款。在中标公示结束后3个工作日内未收到保证金退款，投标人应在10个工作日后向四川华西数产科技集团 有限公司提供完整的书面缴费依据，四川华西数产科技集团有限公司将在收到投标人提供的完整缴费依据后， 在7个工作日内核实并退款。若出现上述情况投标人可编辑含有“招标项目名称”、“招标单位”的短信发送至： 19950205781（本号码只接受短信联系方式），也可到访四川华西数产科技集团有限公司进行沟通。 系统每次生成的账号，均为一次性账号和唯一性账号，标书费账号与投标保证金账号不同，项目与项目间账号 不同。 七、投标文件的递交 招标人仅接受投标人通过善建云采（四川华西集团有限公司及下属分子公司）提交的投标文件，不接受通过其 他方式提交的书面投标文件。线上投标内容具有法律效力且具有唯一性，请投标网人慎重对待。 八、其他描述 九、其他资格要求 务 十、其他事项 若对招标公告有其他不明事项，请致电： 业务咨询联系人： 安虹静 ，联系电话： 15883776766 ； 商 技术支持联系人： 集采技术部 ，联系电话： 02883382846 ； 十一、声明 本招标公告仅为信息发布，不构成任何法律意义上的要约或承诺。 现予公告。 道 四川省工业设备安装集团有限公司 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3078483.html 管 cqdingjiu 2026.08.25 10:30:40 国 中</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5211,7 +5199,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>【屏山县龙华、龙溪、大乘污水管网疏通及修复项目劳务分包工程】询比公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3078449.html cqdingjiu 2026.08.25 09:26:01 网 务 商 道 管 国 中</t>
+          <t>【屏山县龙华、龙溪、大乘污水管网疏通及修复项目劳务分包工程】询比公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3078449.html cqdingjiu 2026.08.25 10:30:40 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5225,7 +5213,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>重庆, 近三天, 管材招标商机</t>
+          <t>污水管网, 疏通及修复</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5275,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>成都市中兴供水有限公司2026-2028年度管网施工劳务比选磋商公告 （一）概况 1、本项目比选人为成都市中兴供水有限公司，主要从事市政基础设施、城市供水管网的投资、建设与运营。根 据公司业务范围及建设需求，现面向社会进行给水管网施工单位的公开比选，邀请有能力的优秀比选申请人参 加我公司的项目比选，并选出二至三家优秀企业共同承担2026年及2028年度成都市中兴供水有限公司供水区域内 给水管网的施工任务。 2、本项目比选为企业自主谈判，组织形式为自行谈判。 网 3、中选的单位，按照工程预估1000万元作为暂定金额签订合同。 （二）比选范围 务 1、工作内容涉及:1）管道施工；2）各类管井砌筑、管道保护等；3）PE管、铸铁管、钢管、衬塑复合管等 给水管道安装（包含建筑体内的管道安装）；4）旧管拆除及新接管道的连接；5）特殊施工项目，如顶管（若实 际项目中涉及）、少量构筑物修建及改造等。 商 2、服务期：2年，以任务发放的开始和结束时间为准。 3、服务地点：成都市武侯区金花辖区约12.9平方公里。 道 4、比选申请人根据自身资质、能力、条件等，可选择不同的模式进行报价，详见比选文件 （三）比选申请人资格要求 管 1、具有独立企业法人资格，持有合法有效的营业执照，注册资金50万元以上，财务状况良好，具有税务部门认 可的增值税纳税人认定表（书），可开具国家认可的增值税专用发票。 2、具有：①国家建设行政主管部门颁发的市政工程总承包叁级及以上资质或房屋建筑工程施工总承包叁级及以 上资质；②有效的施工国作业劳务资质、有效的安全生产许可证（①②可任具其一） 3、业绩要求：申请人应于2024年至2025年期间承接并完成施工至少两个以上的类似工程的劳务分包作业（类似 工程是指：市政给水（或供水或输水）管道工程施工业绩或市政给水（或供水或输水）管道工程，申请人须提 供合同及相关的履行证明），并在人员、设备、资金等方面具有相应的施工能力。 中 4、信誉要求：未处于四川省行政区域内有关行政处罚期间，且未处于投标禁入期内；近3年或成立至今（成立不 足3年的）在经营活动中没有重大违法违规记录。在“信用中国”网站（www.creditchina.gov.cn）中未列入失信被 执行人和重大税收违法案件当事人名单 5、主要人员配备要求： ①项目负责人、技术负责人要求：项目负责人或技术负责人具有工程类中级工程师及以上职称。(项目负责人或 技术负责人相关证书在合同签订时需交由比选人，待合同履行完毕退还) ②本项目管理人员中须至少配备施工员、安全员、资料员、材料员、造价员各1名。 ③主要人员（项目负责人、技术负责人、施工员、安全员、资料员、材料员、造价员）应是比选申请人本单位 人员。 6、不接受联合体参选。 （四）比选文件获取 1、比选申请人报名时需提供：法定代表人持加盖机构鲜章的本人身份证复印件，或授权代理人持法定代表人签 发并加盖机构鲜章的授权委托书原件、加盖机构鲜章的本人身份证复印件；企业营业执照副本复印件；资质证 书副本复印件；安全生产许可证副本复印件；纳税人资格证复印件；开户许可证复印件；管道施工合同及相关 的履行证明。 注：以上所有复印件均须加盖比选申请人鲜章，且须携带原件，现场查验。 2、比选人在接受报名后即对比选申请人资格条件进行审查，条件合格者即可领取商务谈判文件。 3、获取时间：2026年8月24日起（工作日上午9：30至12：00，下午14：00 至17：30）。 4、获取地点：成都市武侯区草金路中段999号附9号成都市中兴供水有限公司二楼成控部 （五）参选文件递交 1、参选文件应按以下规定文件格式及附件要求的内容填写并装订。 网 2、递交参选文件时，应同时提供以下资料查验，否则比选人有权拒收：①营业执照副本原件②安全生产许可证 副本原件③项目经理注册证原件④税务部门认可的纳税人认定表（书）⑤项目负责人或技术负责人具备的相关 资质证书。 务 3、投标文件的递交的截止时间（以比选人通知为准），地点为成都市武侯区草金路中段999号附9号成都市中兴 供水有限公司二楼成控部。 4、逾期送达或未送到指定地点的投标文件，比选人不予商受理。 （六）联系人及联系电话 联系人：杜老师 道 联系电话：028-8200 6199转823 17828175202 公司网站：http://www.zxwatersupply.com/ 管 信息来源:https://www.chinapipe.net/project/d3078430.html cqdingjiu 2026.08.25 09:26:01 国 中</t>
+          <t>成都市中兴供水有限公司2026-2028年度管网施工劳务比选磋商公告 （一）概况 1、本项目比选人为成都市中兴供水有限公司，主要从事市政基础设施、城市供水管网的投资、建设与运营。根 据公司业务范围及建设需求，现面向社会进行给水管网施工单位的公开比选，邀请有能力的优秀比选申请人参 加我公司的项目比选，并选出二至三家优秀企业共同承担2026年及2028年度成都市中兴供水有限公司供水区域内 给水管网的施工任务。 2、本项目比选为企业自主谈判，组织形式为自行谈判。 网 3、中选的单位，按照工程预估1000万元作为暂定金额签订合同。 （二）比选范围 务 1、工作内容涉及:1）管道施工；2）各类管井砌筑、管道保护等；3）PE管、铸铁管、钢管、衬塑复合管等 给水管道安装（包含建筑体内的管道安装）；4）旧管拆除及新接管道的连接；5）特殊施工项目，如顶管（若实 际项目中涉及）、少量构筑物修建及改造等。 商 2、服务期：2年，以任务发放的开始和结束时间为准。 3、服务地点：成都市武侯区金花辖区约12.9平方公里。 道 4、比选申请人根据自身资质、能力、条件等，可选择不同的模式进行报价，详见比选文件 （三）比选申请人资格要求 管 1、具有独立企业法人资格，持有合法有效的营业执照，注册资金50万元以上，财务状况良好，具有税务部门认 可的增值税纳税人认定表（书），可开具国家认可的增值税专用发票。 2、具有：①国家建设行政主管部门颁发的市政工程总承包叁级及以上资质或房屋建筑工程施工总承包叁级及以 上资质；②有效的施工国作业劳务资质、有效的安全生产许可证（①②可任具其一） 3、业绩要求：申请人应于2024年至2025年期间承接并完成施工至少两个以上的类似工程的劳务分包作业（类似 工程是指：市政给水（或供水或输水）管道工程施工业绩或市政给水（或供水或输水）管道工程，申请人须提 供合同及相关的履行证明），并在人员、设备、资金等方面具有相应的施工能力。 中 4、信誉要求：未处于四川省行政区域内有关行政处罚期间，且未处于投标禁入期内；近3年或成立至今（成立不 足3年的）在经营活动中没有重大违法违规记录。在“信用中国”网站（www.creditchina.gov.cn）中未列入失信被 执行人和重大税收违法案件当事人名单 5、主要人员配备要求： ①项目负责人、技术负责人要求：项目负责人或技术负责人具有工程类中级工程师及以上职称。(项目负责人或 技术负责人相关证书在合同签订时需交由比选人，待合同履行完毕退还) ②本项目管理人员中须至少配备施工员、安全员、资料员、材料员、造价员各1名。 ③主要人员（项目负责人、技术负责人、施工员、安全员、资料员、材料员、造价员）应是比选申请人本单位 人员。 6、不接受联合体参选。 （四）比选文件获取 1、比选申请人报名时需提供：法定代表人持加盖机构鲜章的本人身份证复印件，或授权代理人持法定代表人签 发并加盖机构鲜章的授权委托书原件、加盖机构鲜章的本人身份证复印件；企业营业执照副本复印件；资质证 书副本复印件；安全生产许可证副本复印件；纳税人资格证复印件；开户许可证复印件；管道施工合同及相关 的履行证明。 注：以上所有复印件均须加盖比选申请人鲜章，且须携带原件，现场查验。 2、比选人在接受报名后即对比选申请人资格条件进行审查，条件合格者即可领取商务谈判文件。 3、获取时间：2026年8月24日起（工作日上午9：30至12：00，下午14：00 至17：30）。 4、获取地点：成都市武侯区草金路中段999号附9号成都市中兴供水有限公司二楼成控部 （五）参选文件递交 1、参选文件应按以下规定文件格式及附件要求的内容填写并装订。 网 2、递交参选文件时，应同时提供以下资料查验，否则比选人有权拒收：①营业执照副本原件②安全生产许可证 副本原件③项目经理注册证原件④税务部门认可的纳税人认定表（书）⑤项目负责人或技术负责人具备的相关 资质证书。 务 3、投标文件的递交的截止时间（以比选人通知为准），地点为成都市武侯区草金路中段999号附9号成都市中兴 供水有限公司二楼成控部。 4、逾期送达或未送到指定地点的投标文件，比选人不予商受理。 （六）联系人及联系电话 联系人：杜老师 道 联系电话：028-8200 6199转823 17828175202 公司网站：http://www.zxwatersupply.com/ 管 信息来源:https://www.chinapipe.net/project/d3078430.html cqdingjiu 2026.08.25 10:30:41 国 中</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5301,14 +5289,14 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>供水, 管网施工, 劳务比选</t>
+          <t>管网施工, 劳务比选, 供水管网</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司(宜宾分公司)碳钢无缝管-伸缩节询比采购公告</t>
+          <t>秀山县2026年龙池镇、雅江镇基地信息化建设项目-第二次询比公告</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5318,7 +5306,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>信息化建设类</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5333,58 +5321,50 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>宜宾市</t>
-        </is>
-      </c>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>珙县</t>
+          <t>秀山土家族苗族自治县</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司（宜宾分公司）碳钢无缝管-伸缩节询比采购公告</t>
+          <t>项目服务内容自动农业气象监测系统、土壤墒情监测系统、智能虫情测报系统、杀虫控制系统、水肥一体化、宣传片拍摄等。</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>采购金额：566037.74元（不含税）。</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>充气泵,伸缩节,液位仪油面镜,油壶,无缝钢管,弯头,角钢</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>四川华电珙县发电有限公司(宜宾分公司)碳钢无缝管-伸缩节询比采购公告 四川华电珙县发电有限公司（宜宾分公司）碳钢无缝管-伸缩节询比采购公告_采购信息_中国华电集团电子商务 平台 四川华电珙县发电有限公司（宜宾分公司）碳钢无缝管-伸缩节询比采购公告 一、采购单编号：GX-202608-007012 二、采购单名称：碳钢无缝管-伸缩节 三、采购代理机构：四川华电珙县发电有限公司（宜宾分公司） 四、采购方式：公开询比采购 五、采购类型：货物 六、报价方式：整单报价 七、报价截止时间：2026-08-28 14:44 八、交货时间： 2026-09-15 九、备注：技术咨询：李红刚 15908295461 请下载采购文件，确定物资名称、型号、数量及要求，并点击报价清单里的《查看》，再次确认物资名称、型号、数量及要求是否与采购文件一致。如存在采购文件与报价清单《查看》里的内容不一致，请致电技术。金额交易超过5万，请联系商务签署合同，到货后，可开具发票，货到验收，合格付款。送货时提供产品相关资料（合格证、检测报告等）要盖公司鲜章的原件。请附送货清单，保包含物资名称、数量及物资编码，如无 送货清单，拒收。商务咨询杨程18783187637 十、采购清单 序号 采购人 物资名称 税率 规格型号 单位数量用途 1 四川华电珙县发电有限公司（宜宾分公司）充气泵 13%充气泵\KKS222 部 1 2 四川华电珙县发电有限公司（宜宾分公司）伸缩节 13%伸缩节\DN200*250\06Cr19Ni10 只 5 3 四川华电珙县发电有限公司（宜宾分公司）液位仪油面镜13%液位仪油面镜\M27*1.5 个 10 4 四川华电珙县发电有限公司（宜宾分公司）油壶 13%油壶 把 1 5 四川华电珙县发电有限公司（宜宾分公司）无缝钢管 13%无缝钢管\φ16*3\1Cr18Ni9Ti 公斤300 6 四川华电珙县发电有限公司（宜宾分公司）弯头 13%弯头\φ219*8\Q235\90°\1.6MPa只 10 7 四川华电珙县发电有限公司（宜宾分公司）无缝钢管 13%无缝钢管\φ219*8\Q235 公斤750 十 8 一、 四 资 川 格 华 条 电 件 珙 内 县 容 发 ： 电有限公司（宜宾分公司）角钢 13%角钢\80*80*8\Q235 公斤580 网 十二、采购文件的获取 获取方式： 第一步：注册。请未注册的潜在供应商访问华电集团电子商务平台（https://www.chdtp.com），完成平台注册。服务咨询电话（08:00-20:00）：400-622-8787；平台信息审核时间为国家法定工作日的9:00-12:00；13:30-17:30。 第二步：网上报名。登录华电集团电子商务平台（https://www.chdtp.com）业务系统，点击菜单”非招采购系统“-“采购报价管理-询比采购-可参与项目”，点击“参与项目”报名，须正确填写联系人、电话等信息。 第三步：移动数字证书申请。安装移动数字证书APP(华电E盾企业版)后，请按照“移动数字证书操作指南”申请办理数字证书，在加密上传报价文件等环节须进行扫码签名，否则无法完成相关操作。（APP下载路径：安卓系统的手机终端APP需要进入“服务中心”－－资料下载－－点击“华电E盾企业版APP（安卓版)”；IOS系统的手机终端APP需要在苹果应用商店中搜索“华电E盾企业版”下载安装。移动数字证书操作指南下载路径：平台首页“服务专区”或进 入“服务中心”－－操作指南版块。)。 第四步：供应商客户端下载。登录业务系统，进入右上角工作台-右下角下载专区，下载供应商客户端和操作手册等相关文件。 十三、 报价响应文件的递交 递交方式：电子版响应文件通过供应商客户端递交至华电集团电子商务平台（https://www.chdtp.com）。 十四、异议提出渠道和方式： 供应商或者其他利害关系人对本招标项目的公告内容有异议的，请在公告期间提出。本项目仅接受通过华电集团电子商务平台投诉异议系统提出的异议，并通过平台告知处理动态。方式如下： 华电集团电子商务平台首页右下角→按照提示完成登录或身份验证→选择类型（非招标投诉）→选择关联采购单→选择阶段→上传支撑文件→维护提出人信息。 单位名称 姓名 联系电话 中国华电集团有限公司四川分公司夏博文02862356715 十五、监督部门： 务 供应商或者其他利害关系人认为采购活动不符合法律法规的，可以自知道或者应当知道之日起10日内进行投诉。本项目接受仅通过华电集团电子商务平台投诉异议系统提出的投诉，并通过平台告知处理动态。方式如下： 华电集团电子商务平台首页右下角→按照提示完成登录或身份验证→选择类型（非招标投诉）→选择关联采购单→选择阶段→上传支撑文件→维护提出人信息。 单位名称 姓名 联系电话 中国华电集团有限公司四川分公司夏博文02862356715 十六、采购单位联系方式 采购机构：四川华电珙县发电有限公司（宜宾分公司） 联 系 人：杨程 联系电话：18783187637 平台注册、使用等事宜，请拨打华电电子商务平台统一客户服务电话400-622-8787进行详询。 发 布 日期：2026-08-23 请到中国华电集团采购平台报价，网站：http://www.chdt商p.com/ 供应商服务：010-62228787转666 采购方服务：010-62228787转668 报名网址：https://www.chdtp.com/ 道 信息来源:https://www.chinapipe.net/project/d3078754.html cqdingjiu 2026.08.25 09:26:02 管 国 中</t>
-        </is>
-      </c>
+          <t>信息化建设类</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司（宜宾分公司）碳钢无缝管-伸缩节询比采购公告
-https://www.chinapipe.net/project/d3078754.html</t>
+          <t>项目服务内容自动农业气象监测系统、土壤墒情监测系统、智能虫情测报系统、杀虫控制系统、水肥一体化、宣传片拍摄等。
+https://www.chinapipe.net/project/d3078606.html</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>重庆, 近三天, 管材招标, 商机</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司(宜宾分公司)碳钢无缝管-伸缩节询比采购公告</t>
+          <t>中建桥梁有限公司西部(重庆)科学城德感片区污水管网修复完善工程项目(白沙部分新增)市政工程采购公告</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5394,7 +5374,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>市政工程专业分包工程</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5409,22 +5389,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>宜宾市</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>珙县</t>
-        </is>
-      </c>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司(宜宾分公司)碳钢无缝管-伸缩节询比采购公告</t>
+          <t>西部（重庆）科学城德感片区污水管网修复完善工程项目所需（白沙部分新增）市政工程专业分包工程，包括非开挖紫外光修复、安装前道内部勘测、清淤、封堵气囊、导排水，钢内衬成环回顶，铺设防划垫膜，主物料的拉入、连接充气设备、安装排水软管、物料的充气/紫外光固化、冷却物料、切除管口扎头多余务、抽出内膜、CCTV检测验收、拆除堵通水修复，管道铺设、管件、检查井、完成建筑垃圾清理，路面恢复等主要工序和辅助工序。</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5434,33 +5406,29 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>充气泵,伸缩节,液位仪油面镜,油壶,无缝钢管,弯头,角钢</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>四川华电珙县发电有限公司(宜宾分公司)碳钢无缝管-伸缩节询比采购公告 一、采购单编号：GX-202608-007012 二、采购单名称：碳钢无缝管-伸缩节 三、采购代理机构：四川华电珙县发电有限公司（宜宾分公司） 四、采购方式：公开询比采购 网 五、采购类型：货物 六、报价方式：整单报价 务 七、报价截止时间：2026-08-28 14:44 八、交货时间：2026-09-15 九、备注：技术咨询：李红刚 15908295461 请下载采购文商件，确定物资名称、型号、数量及要求，并点击报价清 单里的《查看》，再次确认物资名称、型号、数量及要求是否与采购文件一致。如存在采购文件与报价清单 《查看》里的内容不一致，请致电技术。金额交易超过5万，请联系商务签署合同，到货后，可开具发票，货到 验收，合格付款。送货时提供产品相关资料（合格证、检测报告等）要盖公司鲜章的原件。请附送货清单，保 包含物资名称、数量及物资编码，如无送货清道单，拒收。商务咨询杨程18783187637 十、采购清单 用 序号 采购人管物资名称 税率 规格型号 单位 数量 途 1 四川华电珙县发电有限公司（宜宾分公司） 充气泵 13% 充气泵\KKS222 部 1 伸缩 2 四川华电珙县发国电有限公司（宜宾分公司） 伸缩节 13% 只 5 节\DN200*250\06Cr19Ni10 液位仪油 3 四川华电珙县发电有限公司（宜宾分公司） 13% 液位仪油面镜\M27*1.5 个 10 面镜 4 四川中华电珙县发电有限公司（宜宾分公司） 油壶 13% 油壶 把 1 无缝钢 5 四川华电珙县发电有限公司（宜宾分公司） 无缝钢管 13% 公斤 300 管\φ16*3\1Cr18Ni9Ti 弯 6 四川华电珙县发电有限公司（宜宾分公司） 弯头 13% 只 10 头\φ219*8\Q235\90°\1.6MPa 7 四川华电珙县发电有限公司（宜宾分公司） 无缝钢管 13% 无缝钢管\φ219*8\Q235 公斤 750 8 四川华电珙县发电有限公司（宜宾分公司） 角钢 13% 角钢\80*80*8\Q235 公斤 580 十一、资格条件内容： 十二、采购文件的获取 获取方式： 第一步：注册。请未注册的潜在供应商访问华电集团电子商务平台（https://www.chdtp.com），完成平台注册。 服务咨询电话（08:00-20:00）：400-622-8787；平台信息审核时间为国家法定工作日的9:00-12:00；13:30-17:30。 第二步：网上报名。登录华电集团电子商务平台（https://www.chdtp.com）业务系统，点击菜单”非招采购系 统“-“采购报价管理-询比采购-可参与项目”，点击“参与项目”报名，须正确填写联系人、电话等信息。 第三步：移动数字证书申请。安装移动数字证书APP(华电E盾企业版)后，请按照“移动数字证书操作指南”申 请办理数字证书，在加密上传报价文件等环节须进行扫码签名，否则无法完成相关操作。（APP下载路径：安卓 系统的手机终端APP需要进入“服务中心”－－资料下载－－点击“华电E盾企业版APP（安卓版)”；IOS系统 的手机终端APP需要在苹果应用商店中搜索“华电E盾企业版”下载安装。移动数字证书操作指南下载路径：平 台首页“服务专区”或进入“服务中心”－－操作指南版块。)。 第四步：供应商客户端下载。登录业务系统，进入右上角工作台-右下角下载专区，下载供应商客户端和操作手 册等相关文件。 十三、 报价响应文件的递交 递交方式：电子版响应文件通过供应商客户端递交至华电集团电子商务平台（https://www.chdtp.com）。 网 十四、异议提出渠道和方式： 供应商或者其他利害关系人对本招标项目的公告内容有异议的，请在公告期间提出。本项目仅接受通过华电集 团电子商务平台投诉异议系统提出的异议，并通过平台告知处理动态。方式如下： 务 华电集团电子商务平台首页右下角→按照提示完成登录或身份验证→选择类型（非招标投诉）→选择关联采购 单→选择阶段→上传支撑文件→维护提出人信息。 商 单位名称 姓名 联系电话 中国华电集团有限公司四川分公司 夏博文 02862356715 十五、监督部门： 道 供应商或者其他利害关系人认为采购活动不符合法律法规的，可以自知道或者应当知道之日起10日内进行投诉。 本项目接受仅通过华电集团电子商务平台投诉异议系统提出的投诉，并通过平台告知处理动态。方式如下： 管 华电集团电子商务平台首页右下角→按照提示完成登录或身份验证→选择类型（非招标投诉）→选择关联采购 单→选择阶段→上传支撑文件→维护提出人信息。 单位名称 姓名 联系电话 国 中国华电集团有限公司四川分公司 夏博文 02862356715 十六、采购单位联系方式 中 采购机构：四川华电珙县发电有限公司（宜宾分公司） 联 系 人：杨程 联系电话：18783187637 平台注册、使用等事宜，请拨打华电电子商务平台统一客户服务电话400-622-8787进行详询。 发布日期：2026-08-23 信息来源:https://www.chinapipe.net/project/d3078751.html cqdingjiu 2026.08.25 09:26:02</t>
-        </is>
-      </c>
+          <t>市政工程专业分包工程</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司(宜宾分公司)碳钢无缝管-伸缩节询比采购公告
-https://www.chinapipe.net/project/d3078751.html</t>
+          <t>西部（重庆）科学城德感片区污水管网修复完善工程项目所需（白沙部分新增）市政工程专业分包工程，包括非开挖紫外光修复、安装前道内部勘测、清淤、封堵气囊、导排水，钢内衬成环回顶，铺设防划垫膜，主物料的拉入、连接充气设备、安装排水软管、物料的充气/紫外光固化、冷却物料、切除管口扎头多余务、抽出内膜、CCTV检测验收、拆除堵通水修复，管道铺设、管件、检查井、完成建筑垃圾清理，路面恢复等主要工序和辅助工序。
+https://www.chinapipe.net/project/d3078567.html</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>管材, 招标</t>
+          <t>市政工程, 污水管网修复</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>西南海吉星智慧产业园加工区项目及西南海吉星智慧产业园交易区项目工程镀锌钢管采购与供应工程集中采购公告</t>
+          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项目设备材料招标公告</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5470,7 +5438,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>房建</t>
+          <t>涉及饮用水卫生安全产品的卫生许可批件</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5485,58 +5453,50 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>成都市</t>
-        </is>
-      </c>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>新津区</t>
+          <t>武隆区</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>西南海吉星智慧产业园加工区及交易区项目工程镀锌钢管采购与供应</t>
+          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项目设备材料招标公告</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>采购保证金1万元（大写：壹万元），中建科工西部大区2025年度A级及以上分供方可免缴。</t>
+          <t>项目资金来自重庆市武隆区提升农村饮水质量专项行动（2025-2027）项目资金，项目出资比例为100%。</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>金属管材</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>西南海吉星智慧产业园加工区项目及西南海吉星智慧产业园交易区项目工程镀锌钢管采购与供应工程集中采购 公告 物资采购 【招标公告】西南海吉星智慧产业园加工区项目及西南海吉星智慧产业园交易区项目工程镀锌钢管采购与供应 工程集中采购 招标编号：cscec202608210000485884 项目：西南海吉星智慧产业园加工区项目工程 发布时间：2026-08-23 16:28:34 报名截止：2026-08-26 10:01:00 区域：四川省成都市新津区 网 招标品类：金属管材采购 招标（资格预审）公告 西南海吉星智慧产业园加工区项目及西南海吉星智慧产业园交易区项目工程镀锌钢管采购与供应工程集中采购 务 公告 根据中国建筑股份有限公司集中采购管理方针及中建科工采购管理规定，特组织西南海吉星智慧产业园加工区 项目及西南海吉星智慧产业园交易区项目工程镀锌钢管采购与供应工程集中采购，现通过“云筑网”（网 商 址www.yzw.cn）谈判采购。 一、基本情况 1.采购单位：中建科工集团有限公司（以下简道称中建科工）； 2.采购内容：西南海吉星智慧产业园加工区及交易区项目工程镀锌钢管采购与供应； 3.项目地点：成都市新津区普兴街道养正社区西创大道（工业园区）； 管 4.采购方法：谈判采购、资格预审的方式； 5.采购合同签订方式：本次采购分为二个标段，一标段：西南海吉星智慧产业园加工区项目工程镀锌钢管采购与 供应工程；二标段：南国海吉星智慧产业园交易区项目工程镀锌钢管采购与供应工程 二、分供商的资格条件 本次采购报中名的分供商单位需具备以下条件，方有响应资格： 1.分供商必须是独立的法人单位，具备一般纳税人资格。 2.分供商必须具备按国家要求施工本工程应具备的资质，且为 /（包含或以上）等级资质，在工程所在地已注册 或取得准入许可。 3.分供商在近三年内不曾在任何合同中违约或因分供商的原因而使任何合同被解除。 4.分供商应具备完成采购工程范围内施工任务的管理、技术、装备、劳动力等能力和资金实力。 5.现场代表、项目负责人、项目技术负责人必须具备同类工程施工的经验、业绩和执业资格。 6.具有工程项目特殊需求的应急能力。 三、采购报名 1.报名时间：具体以云筑网通知报名截止时间为准，逾期不再接受分供商单位的报名。 2.报名方式：采取网络报名方式，通过“云筑网”（网址www.yzw.cn）上进行报名，不接受其他方式报名，需上 传资格预审文件（详见附件）。 3.平台输入用户名和密码，成功登录后签收采购公告并点击报名；未在“云筑网”注册的分供商，需先通过平台 网页进行注册，注册信息通过审核合格后，再行报名。 四、资格审查 1.资格审查渠道 本次采购的分供商均由采购平台公开报名产生。通过平台直接报名的供应商，按照采购公告指定要求完成资格 预审。 2.资格审查资料清单 （1）企业基本情况表（格式参照附件）。 网 （2）法定代表人身份证明（格式参照附件）。 （3）法定代表人授权委托书（格式参照附件）。 务 （4）分供商单位营业执照、资质证书等（正副本均可）。 （5）企业简介、业绩证明（附合同关键页）。 （6）分供商单位资信等级证书，质量、环境、职业健康商安全管理体系认证证书。 （7）分供商单位可提供的其他证明企业情况的资料。 上述1-5项资料必须提供，6-7项若有可提供，道提供虚假资审资料的分供商单位，任何时候一经发现，取消其相应 资格。 以上所有审查资料，均需在报名时盖章上传至平台。 管 3.资格审查时间及地点 （1）资格审查时间：具体以云筑网时间为准（节假日除外）。 （2）资格审查方式：国以云筑网上资审材料为准。 （3）若需实地考察的，另行约定时间开展。 五、采购文件的发放时间及方式 中 1.发放时间：具体以云筑网时间为准。 2.发放形式：采购文件发布电子版，不发布书面采购文件。 3.发放平台或地点：采购方通过“云筑网”（网址www.yzw.cn）进行发放。 4.发放对象：采购资格审查合格的分供商，分供商通过网络平台直接下载采购文件。 5.报名单位所有报名和响应的ip地址、mac地址、法人信息、联系人信息、其他信息不得重复，否则将视为存在 围标嫌疑并全部淘汰。 备注：其他信息重复包含股东、分支机构、法人、董监高信息重复。 六、采购保证金及费用 本次采购的采购保证金1万元（大写：壹万元），中建科工西部大区2025年度A级及以上分供方可免缴。分供商 应在报名截止前通过“云筑网”交付，具体交付方式请自行阅读“云筑网”平台保证金操作手册（文件会随采 购文件发出）。本次响应必须通过“云筑网”交付。 采购保证金返还时间：采购保证金在确定成交人后30个工作日内以转账方式退还。 七、采购投诉渠道 邮箱名称:中建科工采购投诉 邮箱地址:zjkgzbcgts@cscec.com 请查看报价网 址：https://xy.yzw.cn/sj/bid-detail?tenderId=&amp;source=3&amp;tenderCode=cscec202608210000485884&amp;tenantId=cscec 信息来源:https://www.chinapipe.net/project/d3078749.html cqdingjiu 2026.08.25 09:26:02 网 务 商 道 管 国 中</t>
-        </is>
-      </c>
+          <t>涉及饮用水卫生安全产品的卫生许可批件</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>西南海吉星智慧产业园加工区及交易区项目工程镀锌钢管采购与供应
-https://www.chinapipe.net/project/d3078749.html</t>
+          <t>武隆区黄莺乡龙洞水厂工程、芙蓉街道白杨村集中供水工程、火炉镇万峰水厂工程、土地乡桂花水厂工程4个项目设备材料招标公告
+https://www.chinapipe.net/project/d3078450.html</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>西南海吉星智慧产业园, 镀锌钢管, 采购</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>邻水县2025年成渝现代高效特色农业带合作园区建设项目产业基地及配套设施建设工程施工标段施工招标公告</t>
+          <t>重庆高速巨能建设集团有限公司城开高速城开隧道泄水洞施工项目第一批物资(排水材料)进行优选采购公告</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5546,7 +5506,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>[object Object],[object Object]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5561,58 +5521,46 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>广安市</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>邻水县</t>
-        </is>
-      </c>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>新（改）建果园900亩，对果园进行调型、土壤培肥等；在果园内新建100m³混凝土蓄水池7个、整治灌溉山坪塘1个，安装灌溉管网6km（其中φ110mm管网4500m，φ160mm管网1500m）；修建0.6m×0.6m条石排水渠1.1km、1.8m宽生产便道5.5km；建设面积约200㎡柑橘产业社会化服务中心1个、500m³冷藏库1个及专家工作站1个。</t>
+          <t>本项目涉及采购钢带增强聚乙烯螺旋波纹管和钢带波纹管密封胶圈，用于重庆高速巨能建设集团有限公司城开高速城开隧道泄水洞施工项目。</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>项目业主为邻水县御临镇人民政府，建设资金来自2025年省级财政农业高质量发展资金及2026年大中型水库移民后期扶持资金（资金来源），出资比例为100%。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>灌溉管网、混凝土蓄水池、排水渠、柑橘产业社会化服务中心、冷藏库、专家工作站</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>邻水县2025年成渝现代高效特色农业带合作园区建设项目产业基地及配套设施建设工程施工标段施工招标公告 邻水县2025年成渝现代高效特色农业带合作园区建设项目产业基地及配套设施建设工程（项目名称) 施工 标 段施工招标公告 1. 招标条件 1.1本招标项目 邻水县2025年成渝现代高效特色农业带合作园区建设项目产业基地及配套设施建设工程 （项目 名称）已由 邻水县发展和改革局 （项目审批、核准或备案机关名称）以 邻水县发展和改革局关于邻水 县2025年成渝现代高效特色农业带合作园区建设项目产业基地及配套设施建设工网程可行性研究报告的批复、邻发改 〔2026〕490号（批文名称及编号）批准建设，项目业主为 邻水县御临镇人民政府，建设资金来自 2025年省级 财政农业高质量发展资金及2026年大中型水库移民后期扶持资金（资金来源），出资比例为 100% ，招标人 为 邻水县御临镇人民政府。项目已具备招标条件，现对该项目的 施工 施工进行公开招标。 务 1.2 本招标项目为四川省行政区域内的国家投资工程建设项目， 邻水县发展和改革局 （核准机关名称）核准 （招标事项核准文号为 邻发改〔2026〕490号 ）的招标组织形式为 □自行招标 委托招标。招标人选择 的招标代理机构是四川中联和创工程项目管理咨询有限公司 。 2. 项目概况与招标范围 商 2.1 项目概况 2.1.1标段划分：1 个标段。 道 2.1.2建设地点：邻水县御临镇滑滩村。 2.1.3建设内容及规模：新（改）建果园900亩，对果园进行调型、土壤培肥等；在果园内新建100m3混凝土蓄水 管 池7个、整治灌溉山坪塘1个，安装灌溉管网6km（其中φ110mm管网4500m，φ160mm管网1500m）；修建 0.6m×0.6m条石排水渠1.1km、1.8m 宽生产便道 5.5km；建设面积约200㎡柑橘产业社会化服务中心1个、500m3冷 藏库1个及专家工作站1个。（具体以施工图纸及财评清单为准）。 2.1.4计划工期：75日历国天。 （简要说明本次招标项目的建设地点、规模、建设内容、计划工期、标段划分等）。 2.2 招标范围 中 2.2.1质量标准：符合国家现行施工质量验收规范合格标准。 2.2.2计划工期：75日历天 。 2.2.3招标范围：本次招标工程量清单和施工图纸所示的全部内容的施工。（简要说明本次招标标段名称、招标范 围与内容、合同计划工期等）。 3. 投标人资格要求 3.1本次招标要求投标人须具备 独立企业法人资格，行政主管部门颁发的水利水电工程施工总承包三级及以上 和行政主管部门颁发的建筑装修装饰工程专业承包二级及以上 资质，近 3 年（已完工的□已完工的或正在 施工的 □已完工的或正在施工的或新承接的） 2 个类似项目（类似项目指：单个合同金额不低于500万元 及以上规模的水利工程类业绩(依法必须招标的项目:需附县级及以上公共资源交易服务平台截图、中标通知书、 合同协议书、项目法人或行政主管部门出具的完(竣)工验收(或预验收)鉴定书(或证书)或质量监督机构出具的 完(竣)工质量监督报告扫描件(或复印件);非依法必须招标的项目，可只附合同协议书、项目法人或行政主管部门 出具的完(竣)工验收(或预验收)鉴定书或质量监督机构出具的完(竣)工质量监督报告扫描件(或复印件)。业绩时 间以项目法人或行政主管部门出具的完(竣)工验收(或预验收)鉴定书(或证书)或质量监督机构出具的完(竣)工质 量监督报告时间为准。），并在人员、设备、资金等方面具有相应的施工能力。 3.2 本次招标接受□不接受联合体投标。 联合体投标的，应满足下列要求：（1）联合体成员为独立企业法人资格，牵头人须是具有水利水电工程施工总 承包三级及以上资质的施工单位；（2）组成联合体的成员不得超过 2 家（含牵头人）；(3)联合体各方应签订 《联合体协议书》，明确联合体牵头人和各方权利义务；(4)组成联合体投标应符合相关法律法规对联合体投标 的有关规定，联合体各方不得再以自己名义单独或参加其他联合体在同一工程项目中投标；(5)联合体牵头人负 责本项目投标报名、投标保证金缴纳、递交投标文件等相关事宜。 3.3各投标人均可就上述合同标段中的 1 个(具体数量)合同标段投标。招标人□允许不允许投标人拟派的同 一批项目主要人员（项目经理、技术负责人）在 1 个及以上标段任职。 3.4本次招标仅面向中小企业发包（其中属于大型企业的分支机构、存在控股股东为大型企业、与大型企业的 负责人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。 具体标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关网于印发中小企业划型标准规定 的通知》（工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除 技术复杂、存在特殊要求外，我省依法必须招标的国家投资工程，投标最高限价在3000万元以下的施工项目（标 段）应勾选此项。） 务 4. 招标文件的获取 4.1 凡有意参加投标者： 请于2026 年 8 月 23 日起登陆全国公共资源交易平台（四商川省·广安市）（网 址：https://gasggzy.cn/）—“电子交易平台登录入口”—“投标登录入口”，通过数字证书免费下载招标资料 （招标文件、技术资料等）。 □请于 年 月 日至 年 月 日，每日上午 时道至 时（北京时间，下同），下 午 时至 时，在 （详细地址）持有效证件（单位介绍信及购买人员身份证明）购买招标文件。招标文件每 套售价 元，售后不退。 4.2 除上述方式外，招标人不提供其他任何报名和招标文件获取的方式。 管 5. 投标文件的递交 5.1(A) 投标文件递交的截止时间（投标截止时间，下同）为 2026 年 9 月 14 日 09时 30 分，投标人应 在截止时间前通过全国国公共资源交易平台（四川省·广安市）（电子招标投标交易平台）在线递交经投标人数 字证书签名制作的数据加密电子投标文件，非加密电子投标文件光盘或U盘为备份投标文件，应按招标文件要求 密封并在投标截止时间前递交。 5.1(B)投标中文件递交的截止时间（投标截止时间，下同）为 年 月 日 时 分，地点 为 。 5.2(A)逾期送达的投标文件，电子招标投标交易系统将予以拒收。 5.2(B)逾期送达的、未送达指定地点的或者不按照招标文件要求密封的投标文件，招标人将予以拒收。 5.3开标方式:本项目开标实行(□见面开标;使用不见面开标系统)开标方式，关于“不见面开标系统”的流程和 注意事项，请各交易主体在广安市公共资源交易网上下载查看不见面开标系统操作指南。 6. 发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）上发布。其他发布公告的媒介 全国公共资源交易平台（四 川省·广安市） （招标人自行选择，也可不填）。 7. 本项目招标投标行政监督部门 行政监督部门： 邻水县农业农村局 电 话： 0826-3222801 传 真： / 电子邮件： / 地 址： 四川省广安市邻水县建新路110号 8. 招标人承诺 本招标文件已经招标人（含招标代理机构）审查，不存在违反国家法律、法规、政策的情形。因招标文件设置 违反国家法律、法规、政策造成的相应后果，由招标人（含招标代理机构）负责。 9. 联系方式 招 标 人： 邻水县御临镇人民政府 招标代理机构：四川中联和创工程项 目管理咨询有限公司 地 址： 广安市邻水县31县道附近 地 址： 四川省广安市广安区星 河街25号 邮 编： 638511 邮 编： 638000 网 联 系 人： 曹先生 联 系 人： 蓝川森 电 话： 15182047529 电 话：0826-2993596/15622881767 务 传 真： / 传 真： / 电子邮件： / 电子邮件：/ 网 址： / 网 址： / 商 开户银行： / 开户银行：/ 账 号： / 账 号 ： / 道 2026 年 8 月 21 日 管 信息来源:https://www.chinapipe.net/project/d3078967.html cqdingjiu 2026.08.25 09:26:03 国 中</t>
-        </is>
-      </c>
+          <t>[object Object],[object Object]</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>新（改）建果园900亩，对果园进行调型、土壤培肥等；在果园内新建100m³混凝土蓄水池7个、整治灌溉山坪塘1个，安装灌溉管网6km（其中φ110mm管网4500m，φ160mm管网1500m）；修建0.6m×0.6m条石排水渠1.1km、1.8m宽生产便道5.5km；建设面积约200㎡柑橘产业社会化服务中心1个、500m³冷藏库1个及专家工作站1个。
-https://www.chinapipe.net/project/d3078967.html</t>
+          <t>本项目涉及采购钢带增强聚乙烯螺旋波纹管和钢带波纹管密封胶圈，用于重庆高速巨能建设集团有限公司城开高速城开隧道泄水洞施工项目。
+https://www.chinapipe.net/project/d3078467.html</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>管材招标, 灌溉管网, 混凝土蓄水池, 排水渠, 柑橘产业社会化服务中心, 冷藏库, 专家工作站</t>
+          <t>管材, 招标, 排水材料</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>中铁十七局集团建筑公司阆中市排水防涝EPC建设项目防腐螺旋管公开询价公告</t>
+          <t>国网重庆电力渝西片区2026年原集体企业和各级产业单位第十四次物资区域联合授权公开谈判采购采购公告</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5622,7 +5570,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5637,43 +5585,31 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>南充市</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>阆中市</t>
-        </is>
-      </c>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>新改建迎宾大道东段、梧桐路支路、长安东路、御河路、博阳街东段等排水管网总长度8.2公里；新建排水防涝通道总长度2.9公里。主要包含排水工程、箱涵工程等。阆中市江南片区排水防涝建设项目：新改建张宪街、奎星大道、长盛大道、阆升路横街等排水管网总长度13公里；新建排水防涝通道及沟渠总长度3.8公里。主要包含排水工程、涵洞工程等。阆中市江南及工业园区片区道路及基础设施建设项目：改建迎宾大道东段、张宪街、奎星大道现状道路路面及基础配套设施，新建梧桐路支路、长安东路、御河路、博阳街东段、长盛大道、阆升路横街道路路面及基础配套设施。道路建设总长度7.9公里。主要包含道路工程、电气工程、交安工程、绿化工等。</t>
+          <t>采购项目名称为物资，具体采购内容包括第十四次物资区域联合授权公开谈判采购。</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>本次询价采购不含税限价金额41万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>防腐螺旋管</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>中铁十七局集团建筑公司阆中市排水防涝EPC建设项目防腐螺旋管公开询价公告 中铁十七局集团建筑公司阆中市排水防涝EPC建设项目防腐螺旋管公开询价 采购编号：ZT17-JZGS-2026-XJ30 中铁十七局集团建筑工程有限公司阆中市排水防涝EPC建设项目现需要采购防腐螺旋管一批，现进行公开询价采 购，本次询价采用一轮报价形式，诚邀有意向的合格供应商参与报价。 一、项目概况及询价采购内容 网 1.1项目概况 新改建迎宾大道东段、梧桐路支路、长安东路、御河路、博阳街东段等排水管网总长度 8.2 公里；新建排水防涝 务 通道总长度 2.9 公里。主要包含排水工程、箱涵工程等。阆中市江南片区排水防涝建设项目：新改建张宪街、奎 星大道、长盛大道、阆升路横街等排水管网总长度 13 公里；新建排水防涝通道及沟渠总长度 3.8公里。主要包含 排水工程、涵洞工程等。阆中市江南及工业园区片区道路及基础设施建设项目：改建迎宾大道东段、张宪街、 奎星大道现状道路路面及基础配套设施，新建梧桐路支路、长安东路、御河路、博阳街东段、长盛大道、阆升 路横街道路路面及基础配套设施。道路建设总长度 7.9 公商里。主要包含道路工程、电气工程、交安工程、绿化工 程等。合同工期365天。 1.2询价内容 详见拟采购货物一览表 道 二、供应商资格要求 2.1供货人必须经国家工商、税务机关登记注册、并符合投标项目经营范围、能独立承担民事责任、具有独立企 业法人资格。 管 2.2供应商必须是“中国铁建云链平台”注册并通过审核的供应商。 2.3报价人近两年没有与骗取合同有关的犯罪或严重违法行为，报价期内没有被处以责令停业、暂停投标、 财产被接管、冻结、破国产状态等，不在询价项目行业主管部门限制投标的处罚期内、报价人在报价阶段内未被 人民法院列为失信被执行人、不在最新一期《中国铁建选择合作方风险警示名录》以及被采购人列为风险警示 合作名录的供应商范围内。 2.4供应商在报价时，如是法定代表人签字的需提供法定代表人身份证复印件、如是法人授权代理人签字的需提 中 供授权委托书及被授权人身份证复印件。 2.5具有一定规模和良好的资金财务状况，具有一定的垫资能力。 2.6质量保证能力：产品质量符合国家及行业现行标准要求，符合施工现场技术要求，材料需经现场技术确定符 合要求，有按国家规定的标准检测和检验合格的专业生产设备。需出具合格证、质保书、第三方检测报告。要 求材质符合要求，保障通过验收。 2.7若采购单位需要，根据中标候选人顺序，要求提供报价产品的样品，附带对应的检测报告，中标候选人须承 诺具体供应产品与样品一致，由采购单位相关人员进行签样封存。如中标候选人无法满足或样品不合格，则取 消其中标资格。 2.8其它要求：本次询价投标人需缴纳投标保证金500元，投标保证金缴纳账户为：户名：中铁十七局集团建筑 工程有限公司阆中排水防涝EPC建设项目部，开户行：交通银行北京西区支行，账号：99011231017002158857。 请在备注栏注明：ZT17-JZGS-2026-XJ30-项目名称-XX包件报价保证金；汇款单位名称与投标单位名称必须一致， 否则视为无效汇款；不接受个人汇款。确定成交人后，保证金原账户退还，如发现恶意报价或中标后拒绝签订 合同，保证金不予退还，情节严重者，纳入不良行为供应商名录。 三、拟采购物资及相关要求 3.1拟采购物资一览表 物资名 项目 序号 型号规格 单位 数量 交货地址 交货日期 称 名称 中铁十七局集团建 四川省南充市阆中市江南及 以甲方采购计划为 防腐螺 DN219*6mm； 筑工程有限公司阆 工业园区片区中铁十七局集 1 米 2400 准。（需分批次进 旋管 三油两布 中市排水防涝EPC 团建筑工程有限公司阆中市 场） 建设项目 排水防涝EPC建设项目 合计 2400 3.2结算和付款 网 3.2.1采购物资报价规则：（本次询价采购不含税限价金额41万元，投标人不含税报价不得超过此限价。） 固定价格。 务 3.2.2付款方式 （1）货款支付方式： 银行转账（100 %） 商 □铁建银信（ %），兑付期限为： 个月 □银行承兑汇票（ %），兑付期限为： 个月 道 □商业承兑汇票（ %），兑付期限为： 个月 □其他 （ %） 票据贴息费用由 承担。 管 （2）付款周期：货到工地验收合格后，办理对账结算手续。每月 21 日至次月 20 日为一个结算期，对账结算后， 乙方向甲方开具等值的增值税专用发票，甲方收到发票后一个月内内支付当期对账结算货款的95%，剩余 5%留 作质保金，待质量保证国期满未发生质量问题时无息退还，但不解除质量责任。质保期两年。 3.3拟采购物资相关的要求 3.3.1本次询价为整体采购，询价响应供应商报价时须写明单价、到站价和运距，报价包含货物制造、运输、装卸、 中 售后服务等交付采购人使用前所有可能发生的费用，收到报价后不再增补任何费用。 3.4.2交货期：按照采购人规定的期限内全部运抵交付，本次询价物资需分批次进场，具体以采购人采购计划为准。 3.4.3供货地点：四川省南充市阆中市江南及工业园区片区中铁十七局集团建筑工程有限公司阆中市排水防涝EPC 建设项目。 3.4.4询价响应供应商必须提供产品的质量保证说明及售后服务承诺。询价响应供应商提供的货物制造标准及技术 规范等，必须符合最新相关国家标准、部颁标准相关标准和规范的要求，并且提供相关检验检测报告。 3.4.5采购方在确定成交供应商后有权对成交产品的结构、规格做适当调整，调整内容将以工作联系函形式提前发 至供应商。 3.4.6售后服务：本批采购货物若在验收阶段出现不符合规格或质量标准，供应商必须接受退货要求，并在采购人 规定期限内等量补运合格产品，若未按时交付影响采购人使用，供应商必须承担由此给采购单位造成的后续经 济损失。 3.4.7报价方不得虚报各项技术指标，所供货物若不能符合技术要求，成交供应商必须接受全额退还货款，并承担 由此给采购单位造成的经济损失。 3.4.8验收方法及标准 （1）验收依据：询价采购文件、厂家货物技术标准说明及国家有关的质量标准规定，均为验收依据。 （2）货物验收：货物运抵采购人指定交货处后由双方对照采购清单及技术要求进行验收。 3.4.9投标人投标前须提供样品，须经设计及监理单位确认合格。 四、报价文件递交 4.1此次报价供应商需制作电子报价文件，在递交截止时间前线上递交报价文件。 4.2报价文件递交截止时间：2026年8月25日10时00分。 4.3报价文件递交地点：中国铁建云链平台（www.crccep.cn），供应商须登录该平网台，在报价文件递交截止时间 前完成所有报价文件资料的上传。投标文件递交截止时间前未完成投标文件传输的，视为放弃投标资格。 五、发布公告的媒介 务 本次询价公告发布媒体:中国招标投标公共服务平台(www.cebpubservice.com)、中国铁建云链平台（www.crccep.cn） 上同时发布。 六、联系方式 商 采购组织单位：中铁十七局集团建筑工程有限公司 地址：山西省太原市小店区平阳路34号 道 联系人：王先生 联系电话：13820266508 采购人：中铁十七局集团建筑工程有限公司 管 2026年08月21日 国 报价网址：https://www.crccep.com 信息来源:https://www.chinapipe.net/project/d3078881.html 中 cqdingjiu 2026.08.25 09:26:03</t>
-        </is>
-      </c>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>新改建迎宾大道东段、梧桐路支路、长安东路、御河路、博阳街东段等排水管网总长度8.2公里；新建排水防涝通道总长度2.9公里。主要包含排水工程、箱涵工程等。阆中市江南片区排水防涝建设项目：新改建张宪街、奎星大道、长盛大道、阆升路横街等排水管网总长度13公里；新建排水防涝通道及沟渠总长度3.8公里。主要包含排水工程、涵洞工程等。阆中市江南及工业园区片区道路及基础设施建设项目：改建迎宾大道东段、张宪街、奎星大道现状道路路面及基础配套设施，新建梧桐路支路、长安东路、御河路、博阳街东段、长盛大道、阆升路横街道路路面及基础配套设施。道路建设总长度7.9公里。主要包含道路工程、电气工程、交安工程、绿化工等。
-https://www.chinapipe.net/project/d3078881.html</t>
+          <t>采购项目名称为物资，具体采购内容包括第十四次物资区域联合授权公开谈判采购。
+https://www.chinapipe.net/project/d3078339.html</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -5688,7 +5624,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司(宜宾分公司)膨胀节采购询比采购公告</t>
+          <t>国网重庆电力主城一片区2026年原集体企业和各级产业单位第十四次物资区域联合授权公开谈判采购采购公告</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5698,7 +5634,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5713,58 +5649,46 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>宜宾市</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>珙县</t>
-        </is>
-      </c>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>采购伸缩节，规格型号为DN610*1000\06Cr19Ni10，数量为16只；伸缩节\8600*6800*400\非金属材料，数量为6只。</t>
+          <t>采购项目名称为'国网重庆电力主城一片区2026年原集体企业和各级产业单位第十四次物资区域联合授权公开谈判采购'，采购类型为物资。</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>伸缩节</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>四川华电珙县发电有限公司(宜宾分公司)膨胀节采购询比采购公告 一、采购单编号：GX-202608-006980 二、采购单名称：膨胀节采购 三、采购代理机构：四川华电珙县发电有限公司（宜宾分公司） 四、采购方式：公开询比采购 网 五、采购类型：货物 六、报价方式：整单报价 务 七、报价截止时间：2026-08-26 16:01 八、交货时间：2026-09-17 九、备注：技术咨询：刘洋15298178097 请下载采购文件商，确定物资名称、型号、数量及要求，并点击报价清单 里的《查看》，再次确认物资名称、型号、数量及要求是否与采购文件一致。如存在采购文件与报价清单《查 看》里的内容不一致，请致电技术。金额交易超过5万，请联系商务签署合同，到货后，可开具发票，货到验收， 合格付款。送货时提供产品相关资料（合格证、检测报告等）要盖公司鲜章的原件。请附送货清单，保包含物 资名称、数量及物资编码，如无送货清单，拒道收。商务咨询杨程18783187637 十、采购清单 序号 采购人 物资名称 税率 规格型号 单位 数量 用途 管 四川华电珙县发电有限公司（宜宾分 伸缩 1 伸缩节 13% 只 16 公司） 节\DN610*1000\06Cr19Ni10 四川华电珙县发电有限公司（宜宾分 伸缩节\8600*6800*400\非金属复 2 国 伸缩节 13% 只 6 公司） 合材料 十一、资格条件内容： 中 十二、采购文件的获取 获取方式： 第一步：注册。请未注册的潜在供应商访问华电集团电子商务平台（https://www.chdtp.com），完成平台注册。 服务咨询电话（08:00-20:00）：400-622-8787；平台信息审核时间为国家法定工作日的9:00-12:00；13:30-17:30。 第二步：网上报名。登录华电集团电子商务平台（https://www.chdtp.com）业务系统，点击菜单”非招采购系 统“-“采购报价管理-询比采购-可参与项目”，点击“参与项目”报名，须正确填写联系人、电话等信息。 第三步：移动数字证书申请。安装移动数字证书APP(华电E盾企业版)后，请按照“移动数字证书操作指南”申 请办理数字证书，在加密上传报价文件等环节须进行扫码签名，否则无法完成相关操作。（APP下载路径：安卓 系统的手机终端APP需要进入“服务中心”－－资料下载－－点击“华电E盾企业版APP（安卓版)”；IOS系统 的手机终端APP需要在苹果应用商店中搜索“华电E盾企业版”下载安装。移动数字证书操作指南下载路径：平 台首页“服务专区”或进入“服务中心”－－操作指南版块。)。 第四步：供应商客户端下载。登录业务系统，进入右上角工作台-右下角下载专区，下载供应商客户端和操作手 册等相关文件。 十三、 报价响应文件的递交 递交方式：电子版响应文件通过供应商客户端递交至华电集团电子商务平台（https://www.chdtp.com）。 十四、异议提出渠道和方式： 供应商或者其他利害关系人对本招标项目的公告内容有异议的，请在公告期间提出。本项目仅接受通过华电集 团电子商务平台投诉异议系统提出的异议，并通过平台告知处理动态。方式如下： 华电集团电子商务平台首页右下角→按照提示完成登录或身份验证→选择类型（非招标投诉）→选择关联采购 单→选择阶段→上传支撑文件→维护提出人信息。 单位名称 姓名 联系电话 中国华电集团有限公司四川分公司 夏博文 02862356715 十五、监督部门： 网 供应商或者其他利害关系人认为采购活动不符合法律法规的，可以自知道或者应当知道之日起10日内进行投诉。 本项目接受仅通过华电集团电子商务平台投诉异议系统提出的投诉，并通过平台告知处理动态。方式如下： 务 华电集团电子商务平台首页右下角→按照提示完成登录或身份验证→选择类型（非招标投诉）→选择关联采购 单→选择阶段→上传支撑文件→维护提出人信息。 单位名称 姓名 联系电话 商 中国华电集团有限公司四川分公司 夏博文 02862356715 十六、采购单位联系方式 道 采购机构：四川华电珙县发电有限公司（宜宾分公司） 联 系 人：杨程 管 联系电话：18783187637 平台注册、使用等事宜，请拨打华电电子商务平台统一客户服务电话400-622-8787进行详询。 发布日期：2026-08-22国 信息来源:https://www.chinapipe.net/project/d3078753.html cqdingjiu 2026.08.25 09:26:03 中</t>
-        </is>
-      </c>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>采购伸缩节，规格型号为DN610*1000\06Cr19Ni10，数量为16只；伸缩节\8600*6800*400\非金属材料，数量为6只。
-https://www.chinapipe.net/project/d3078753.html</t>
+          <t>采购项目名称为'国网重庆电力主城一片区2026年原集体企业和各级产业单位第十四次物资区域联合授权公开谈判采购'，采购类型为物资。
+https://www.chinapipe.net/project/d3078338.html</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>管材, 招标</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>中电四-化工总部-眉山万华项目-工艺管道-标段3项目公告</t>
+          <t>忠县忠州和白公街道特色农业节水灌溉保障工程勘察设计招标计划表</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5774,7 +5698,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>节水灌溉设备、智能监控系统、气象监测设备、虫情监测设备、土壤墒情监测设备</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5789,58 +5713,50 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>眉山市</t>
-        </is>
-      </c>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>忠县</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>四川眉山高新技术产业园万华四川园区内的工艺管道项目。</t>
+          <t>本工程为9720亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站21座，整治山坪塘44口，建设主要建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>合同预估金额为137.18万元</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>工艺管道</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>中电四-化工总部-眉山万华项目-工艺管道-标段3项目公告 中电四-化工总部-眉山万华项目-工艺管道-标段3将开启线上报名，请在公告要求时间内参与报名，如有问题，请 联系采购工程师。 报价须知: 1. 立项名称：中电四-化工总部-眉山万华项目-工艺管道-标段3 2. 项目地址：四川眉山高新技术产业园万华四川园区内 网 3. 报价需包含：3%增值税 4. 报名资格要求： 务 a. 参与报名及报价的分包单位需具有化工行业管道施工经验，工艺管道焊接人员需持双证； b. 参与报名及报价的分包单位需要具备施工劳务不分等级资质及安全生产许可证； 商 c. 具有独立承担民事责任的能力； d. 具有良好的商业信誉和健全的财务会计制度； 道 e. 满足施工所需的人员及施工器械需求，可满足项目进度要求； f. 参与该标段前3年内，在经营活动中没有重大违法记录； 管 g. 不允许联合体参与投标； 5. 报名资料要求如下：（1）营业执照 （2）拟承接工程所需资质证书 （3）业绩合同扫描件 6. 报价资料需提供可编国辑版及PDF盖章版各1份： （1）报价单 （2）采购文件确认及偏离表 （3）提疑文件 （如有） （4）技术标、深化图纸等（如有） 7. 报价公司名称需与合同签订单位名称一致 中 8. 采购工程师：朱少强，联系方式：19901426632，邮箱：zhushaoqiang@ceccsc.com 技术工程师：张建保，联系方式：15832977507，邮箱：hbjianbao.zhang@cefoc.cn 项目经理 ：刘 婵，联系方式：18632851257，邮箱：chan.liu@cefoc.cn 9. 报名开始时间2026年08月22日 09:00，报名截止时间：2026年08月26日 00:00 10. 报价截止时间：2026年08月27日 17:30（暂定） 信息来源:https://www.chinapipe.net/project/d3078722.html cqdingjiu 2026.08.25 09:26:03</t>
-        </is>
-      </c>
+          <t>节水灌溉设备、智能监控系统、气象监测设备、虫情监测设备、土壤墒情监测设备</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>四川眉山高新技术产业园万华四川园区内的工艺管道项目。
-https://www.chinapipe.net/project/d3078722.html</t>
+          <t>本工程为9720亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站21座，整治山坪塘44口，建设主要建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。
+https://www.chinapipe.net/project/d3078219.html</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>工艺管道</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>中电四-化工总部-眉山万华项目-工艺管道-标段1项目公告</t>
+          <t>忠县新生街道特色农业节水灌溉保障工程勘察设计招标计划表</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5850,7 +5766,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>节水灌溉设备、水肥一体化系统、智能监控系统、气象监测设备、虫情监测设备、土壤墒情监测设备</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5865,58 +5781,50 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>眉山市</t>
-        </is>
-      </c>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>忠县</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>四川眉山高新技术产业园万华四川园区内的工艺管道项目。</t>
+          <t>本工程为9720亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站21座，整治山坪塘44口，建设主要建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>合同预估金额为137.18万元</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>工艺管道</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>中电四-化工总部-眉山万华项目-工艺管道-标段1项目公告 中电四-化工总部-眉山万华项目-工艺管道-标段1将开启线上报名，请在公告要求时间内参与报名，如有问题，请 联系采购工程师。 报价须知: 1. 立项名称：中电四-化工总部-眉山万华项目-工艺管道-标段1 2. 项目地址：四川眉山高新技术产业园万华四川园区内 网 3. 报价需包含：3%增值税 4. 报名资格要求： 务 a. 参与报名及报价的分包单位需具有化工行业管道施工经验，工艺管道焊接人员需持双证； b. 参与报名及报价的分包单位需要具备施工劳务不分等级资质及安全生产许可证； 商 c. 具有独立承担民事责任的能力； d. 具有良好的商业信誉和健全的财务会计制度； 道 e. 满足施工所需的人员及施工器械需求，可满足项目进度要求； f. 参与该标段前3年内，在经营活动中没有重大违法记录； 管 g. 不允许联合体参与投标； 5. 报名资料要求如下：（1）营业执照 （2）拟承接工程所需资质证书 （3）业绩合同扫描件 6. 报价资料需提供可编国辑版及PDF盖章版各1份： （1）报价单 （2）采购文件确认及偏离表 （3）提疑文件 （如有） （4）技术标、深化图纸等（如有） 7. 报价公司名称需与合同签订单位名称一致 中 8. 采购工程师：朱少强，联系方式：19901426632，邮箱：zhushaoqiang@ceccsc.com 技术工程师：张建保，联系方式：15832977507，邮箱：hbjianbao.zhang@cefoc.cn 项目经理 ：刘 婵，联系方式：18632851257，邮箱：chan.liu@cefoc.cn 9. 报名开始时间2026年08月22日 09:00，报名截止时间：2026年08月26日 00:00 10. 报价截止时间：2026年08月27日 17:30（暂定） 信息来源:https://www.chinapipe.net/project/d3078721.html cqdingjiu 2026.08.25 09:26:04</t>
-        </is>
-      </c>
+          <t>节水灌溉设备、水肥一体化系统、智能监控系统、气象监测设备、虫情监测设备、土壤墒情监测设备</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>四川眉山高新技术产业园万华四川园区内的工艺管道项目。
-https://www.chinapipe.net/project/d3078721.html</t>
+          <t>本工程为9720亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站21座，整治山坪塘44口，建设主要建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。
+https://www.chinapipe.net/project/d3078218.html</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>工艺管道, 招标</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>中电四-化工总部-眉山万华项目-工艺管道-标段2项目公告</t>
+          <t>忠县洋渡、任家镇等乡镇特色农业节水灌溉保障工程勘察设计招标计划表</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5926,7 +5834,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>节水灌溉设备、智能监控系统、气象监测设备、虫情监测设备、土壤墒情监测设备</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5941,58 +5849,50 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>眉山市</t>
-        </is>
-      </c>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>忠县</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>四川眉山高新技术产业园万华四川园区内的工艺管道项目。</t>
+          <t>本工程为1.7万亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站18座，整治山坪塘28口，建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>合同预估金额为138.71万元</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>工艺管道</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>中电四-化工总部-眉山万华项目-工艺管道-标段2项目公告 中电四-化工总部-眉山万华项目-工艺管道-标段2将开启线上报名，请在公告要求时间内参与报名，如有问题，请 联系采购工程师。 报价须知: 1. 立项名称：中电四-化工总部-眉山万华项目-工艺管道-标段2 2. 项目地址：四川眉山高新技术产业园万华四川园区内 网 3. 报价需包含：3%增值税 4. 报名资格要求： 务 a. 参与报名及报价的分包单位需具有化工行业管道施工经验，工艺管道焊接人员需持双证； b. 参与报名及报价的分包单位需要具备施工劳务不分等级资质及安全生产许可证； 商 c. 具有独立承担民事责任的能力； d. 具有良好的商业信誉和健全的财务会计制度； 道 e. 满足施工所需的人员及施工器械需求，可满足项目进度要求； f. 参与该标段前3年内，在经营活动中没有重大违法记录； 管 g. 不允许联合体参与投标； 5. 报名资料要求如下：（1）营业执照 （2）拟承接工程所需资质证书 （3）业绩合同扫描件 6. 报价资料需提供可编国辑版及PDF盖章版各1份： （1）报价单 （2）采购文件确认及偏离表 （3）提疑文件 （如有） （4）技术标、深化图纸等（如有） 7. 报价公司名称需与合同签订单位名称一致 中 8. 采购工程师：朱少强，联系方式：19901426632，邮箱：zhushaoqiang@ceccsc.com 技术工程师：张建保，联系方式：15832977507，邮箱：hbjianbao.zhang@cefoc.cn 项目经理 ：刘 婵，联系方式：18632851257，邮箱：chan.liu@cefoc.cn 9. 报名开始时间2026年08月22日 15:00，报名截止时间：2026年08月26日 00:00 10. 报价截止时间：2026年08月27日 17:30（暂定） 信息来源:https://www.chinapipe.net/project/d3078716.html cqdingjiu 2026.08.25 09:26:04</t>
-        </is>
-      </c>
+          <t>节水灌溉设备、智能监控系统、气象监测设备、虫情监测设备、土壤墒情监测设备</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>四川眉山高新技术产业园万华四川园区内的工艺管道项目。
-https://www.chinapipe.net/project/d3078716.html</t>
+          <t>本工程为1.7万亩柑橘等特色农业提供抗旱供水，新建节水灌溉提灌站18座，整治山坪塘28口，建设水肥一体化系统，完善田间引水渠堰、排水沟及管网，分片区安装智能监控、气象、虫情、土壤墒情系统。
+https://www.chinapipe.net/project/d3078217.html</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>工艺管道, 化工行业</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>四川鑫源矿业有限责任公司80万吨/年选矿厂管道设备竞价采购项目项目公告</t>
+          <t>荣昌区2026年古昌镇高标准农田建设项目招标公告</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6002,7 +5902,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>高标准农田建设相关材料及设备，如PE输水管道、排水沟、田间道路等。</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6017,58 +5917,50 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>四川省</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>甘孜藏族自治州</t>
-        </is>
-      </c>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>白玉县</t>
+          <t>荣昌区</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>本项目采用竞价采购方式采购，现邀请你单位参加四川鑫源矿业有限责任公司80万吨/年选矿厂管道设备竞价采购项目报价。</t>
+          <t>新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007亩。主要内容包括水田整治、缓坡整治、梯台整治、恢复地类整治、耕地复耕整治、农机进出通道修建、提灌站修建、输水管道铺设、排水沟改建、田间道路改建等。</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>采购资金来自四川鑫源矿业有限责任公司企业自筹，出资比例为100%。</t>
+          <t>项目总投资金额1592.15万元，本次招标项目合同估算金额1420.76万元，全部来自财政资金。</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>衬胶管,双金属管,陶瓷复合耐磨管</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>四川鑫源矿业有限责任公司80万吨/年选矿厂管道设备竞价采购项目项目公告 四川鑫源矿业有限责任公司80万吨/年选矿厂管道设备 竞价采购项目公告 致投标单位： 四川鑫源矿业有限责任公司80万吨/年选矿厂管道设备竞价采购项目已经由四川鑫源矿业有限责任公司批准实施， 采购资金来自四川鑫源矿业有限责任公司企业自筹，出资比例为100%，实施单位网为四川鑫源矿业有限责任公司。 本项目采用竞价采购方式采购，现邀请你单位参加四川鑫源矿业有限责任公司80万吨/年选矿厂管道设备竞价采 购项目报价。 1.项目名称：四川鑫源矿业有限责任公司80万吨/年选矿厂管道设备竞价采购项目。 务 2.项目编号及采购明细：CG0037WZ20260803 序号 设备名称 型号规格 数量 单位 备注 商 1 衬胶管 DN65 米 100 钢衬橡胶,6mm 2 衬胶管 DN150 米 200 钢衬橡胶,6mm 3 衬胶管 DN200 米 200 钢衬橡胶,6mm 道 4 衬胶管 DN300 米 1000 钢衬橡胶,6mm 5 衬胶管 DN350 米 1000 钢衬橡胶,6mm 6 衬胶管 DN450 米 1000 钢衬橡胶,6mm 管 7 双金属管 φ300 米 200 内衬非晶耐磨合金,16mm耐磨合金,9mm钢管 8 双金属管 φ194 米 200 内衬非晶耐磨合金,16mm耐磨合金,9mm钢管 9 双金属管 φ133 米 200 内衬非晶耐磨合金,16mm耐磨合金,9mm钢管 国 10 陶瓷复合耐磨管 φ194 米 190 自蔓延陶瓷,8mm陶瓷,6mm钢管 11 陶瓷复合耐磨管 φ133 米 220 自蔓延陶瓷,8mm陶瓷,6mm钢管 12 陶瓷复合耐磨管 φ114 米 480 自蔓延陶瓷,8mm陶瓷,6mm钢管 中 3.项目概况及范围： 注：采购报价为含税价，报价中包括设备款、运费、现场安装技术指导费、包装费、运输保险费等各种保险、 税金以及招标文件明示或暗示的风险、责任和义务等一切可能发生的费用（包括燃油费及材料涨价因素等）。 若国家税率调整，则按照不含税金额进行税点调整。 （1）资金来源：企业自筹。 （2）项目地点：四川省甘孜州白玉县四川鑫源矿业有限责任公司 （3）运输方式：汽车运输。因地方原因，成都至鑫源公司路段运输只能由康巴雪域物流承运，康巴雪域物流承 运部分费用由乙方承担，具体费用由乙方与康巴物流沟通。康巴雪域物流联系人：杨经理，电话：13881962962。 （4）质量：供货单位供应符合相关国家标准或我单位要求的产品规格，提供产品检验合格证。 （5）付款方式：无预付款；自合同签订之日起60天内到货，经甲方货到验收合格后，乙方开具合同全额13%增 值税专用发票（一票制，发票中物资的规格型号必须与合同中的规格型号完全一致，价格中包含货物价款、运 费等一切费用），设备自到厂验收合格三个月后支付90%合同款，剩余10%作为质保金，1年质保期满后无息支付， 质保期以甲方发票挂账日期开始计时；乙方不得提前要款。具体内容以最终签订合同为准。 4.供应商要求 （1）资格条件：在中华人民共和国境内注册的独立法人，具有有效的营业执照、开户许可证，具有较强的供货 能力、经济实力和良好的企业信誉及售后服务能力的生产厂家或授权代理商； （2）投标单位营业执照范围必须涉及相关设备制造或销售资质； （3）企业信誉要求：投标人未被纳入最高人民法院失信被执行人名单或信用中国失信惩戒对象名单，须提供中 华人民共和国最高人民法院官方网址(http://www.court.gov.cn/)“全国法院失信被执行人名单信息公布与查询” （http://zxgk.court.gov.cn/）栏目查询结果或“信用中国失信惩戒对象查询” （https：//www.creditchina.gov.cn/xinyongfuwu/shixinheimingdan/）查询结果； （4）本项目不接受联合体投标，不允许转包或分包。 网 5.保证金及提交方式：本项目无需保证金。 6.响应性文件：电子报价文件上传至《西部矿业阳光电商平台》。 务 7.报名及报价递交响应性文件要求： （1）报价响应文件递交的截止时间为：2026年8月24日08时00分至2026年8月27日8时00分。 商 （2）递交方式：由报价人在报价截止时间前将电子报价文件上传至《西部矿业阳光电商平台》。电子报价文件 未按时上传至西部矿业阳光电商平台的，招标人不予受理。（备注：建议报价人至少提前半小时将报价文件上 传，以避免由于系统操作不熟练等原因导致无法按时上传。） 道 （3）提交响应性文件时一并提供以下资料： 投标人（法人或委托代理人）身份证复印件； 管 法人授权委托书、委托代理人身份证复印件； 企业营业执照（三证合一）、相关资质证书等； 投标人针对本采购项目国的供货/技术方案。 注：以上各项如未提供或提供不全，均作为废标处理。 8、开标时间：电子报价文件递交截止时间：2026年8月27日08时00分。 中 9、联系人：司进龙 电 话：18919541560 信息来源:https://www.chinapipe.net/project/d3078687.html cqdingjiu 2026.08.25 09:26:04</t>
-        </is>
-      </c>
+          <t>高标准农田建设相关材料及设备，如PE输水管道、排水沟、田间道路等。</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>本项目采用竞价采购方式采购，现邀请你单位参加四川鑫源矿业有限责任公司80万吨/年选矿厂管道设备竞价采购项目报价。
-https://www.chinapipe.net/project/d3078687.html</t>
+          <t>新建高标准农田797.11亩，改造提升高标准农田5710.6亩，其中高效节水灌溉面积3007亩。主要内容包括水田整治、缓坡整治、梯台整治、恢复地类整治、耕地复耕整治、农机进出通道修建、提灌站修建、输水管道铺设、排水沟改建、田间道路改建等。
+https://www.chinapipe.net/project/d3078214.html</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>管材, 招标, 竞价采购</t>
+          <t>高标准农田建设, PE输水管道, 排水沟, 田间道路</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PPR管及管件采购/78020049-PS202608200813采购变更公告(第1号)</t>
+          <t>重庆中法供水2026年金属补偿器及柔性橡胶接头采购项目(第三次)比选公告</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6078,7 +5970,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>柔性橡胶接头,金属补偿器</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6093,46 +5985,46 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>重庆中法供水2026年金属补偿器及柔性橡胶接头采购项目(第三次)比选公告</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>项目资金来自企业自筹，出资比例为100%</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>PPR管及管件</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>PPR管及管件采购/78020049-PS202608200813采购变更公告(第1号) 网 务 商 道 管 国 中 网 务 商 道 管 国 中 网 务 商 道 管 国 中 信息来源:https://www.chinapipe.net/project/d3078524.html cqdingjiu 2026.08.25 09:26:04 网 务 商 道 管 国 中</t>
-        </is>
-      </c>
+          <t>柔性橡胶接头,金属补偿器</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别
-https://www.chinapipe.net/project/d3078524.html</t>
+          <t>重庆中法供水2026年金属补偿器及柔性橡胶接头采购项目(第三次)比选公告
+https://www.chinapipe.net/project/d3078192.html</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>金属补偿器, 柔性橡胶接头, 采购项目, 比选公告</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>北部基地平原公司关于FRPP管Φ160及配套弯头项目采购公告</t>
+          <t>川渝高竹新区引调水工程项目招标计划表</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6142,7 +6034,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>取水浮船、输水管道</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6157,117 +6049,5625 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
+          <t>新建两岔水库取水浮船1座，设计取水规模为2万m/d；新建两岔水库取水浮船-坛高水厂原输水管道21km。</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>合同预估金额为508万元</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>取水浮船、输水管道</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>新建两岔水库取水浮船1座，设计取水规模为2万m/d；新建两岔水库取水浮船-坛高水厂原输水管道21km。
+https://www.chinapipe.net/project/d3078130.html</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>80</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>川渝高竹新区, 引调水工程, 取水浮船, 输水管道</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>石阡县2026年第二批农村供水提质改造项目竞争性磋商公告</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>供水提质改造相关设备和材料</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>石阡县</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>农村供水提质改造项目</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>预算金额：1950000.00元，最高限价：1911000.00元</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>供水提质改造相关设备和材料</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>农村供水提质改造项目
+https://www.chinapipe.net/project/d3078119.html</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>80</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>管材招标, 农村供水提质改造</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>万州区后山至弹子农村连片供水保障提升工程招标计划表</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>供水设备、管道</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>新建供水规模10000立方米/天的净水厂1座，厂外配水主干管网长度约40公里，村镇配水支线管网长度约100公里，配套一体化供水泵站共15座，新增原水管约1公里。</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>合同预估金额6000万元</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>供水设备、管道</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>新建供水规模10000立方米/天的净水厂1座，厂外配水主干管网长度约40公里，村镇配水支线管网长度约100公里，配套一体化供水泵站共15座，新增原水管约1公里。
+https://www.chinapipe.net/project/d3078105.html</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>80</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>供水, 管网, 管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>重庆涪陵电力实业股份有限公司2026年第4批物资公开谈判采购采购公告</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>管道</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>渝北区</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>重庆涪陵电力实业股份有限公司2026年第4批物资公开谈判采购</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>管道</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>重庆涪陵电力实业股份有限公司2026年第4批物资公开谈判采购
+https://www.chinapipe.net/project/d3078035.html</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>70</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026年, 第4批物资公开谈判采购, 管道</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>荣昌区2026年吴家镇高标准农田建设项目答疑补遗文件</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>荣昌区</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>新建管道 PE 管管件工程量问题；新建道路石方工程量问题；重庆市双业融资担保有限公司信用资质、履约能力问题；建筑工程概算费用问题；总价报价下浮率计算问题；招标文件下载问题；施工单位盖章问题；建筑工程或者市政工程土石方施工业绩问题；投标文件格式填写问题；合同工程完工证书证明材料问题；招标人提供的工程量清单单项最高限价问题；投标函附录中工期、分包、工程质量要求和缺陷责任期对应约定内容问题；我公司业绩为三个项目合并招标问题；边坡治理施工业绩问题；任一清单的综合单价低于警戒线问题；业绩要求的竣工时间问题；财务报告提供问题；我公司业绩合同金额问题；招标人确定中标人问题；低价说明证明材料问题；招标人是否委派业主专家参与评标问题；我公司业绩项目经理变更问题；财务报告提供问题；专业分包业绩问题；投标文件制作系统软件导出的电子投标文件格式问题；项目经理以前在其他公司执业的业绩问题；在职的已退休的注册人员问题；投标函附录中的合同条款号填写问题；评标办法中已标价工程量清单要求的承诺问题；评标专家不被围猎问题。</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>新建管道 PE 管管件工程量问题；新建道路石方工程量问题；重庆市双业融资担保有限公司信用资质、履约能力问题；建筑工程概算费用问题；总价报价下浮率计算问题；招标文件下载问题；施工单位盖章问题；建筑工程或者市政工程土石方施工业绩问题；投标文件格式填写问题；合同工程完工证书证明材料问题；招标人提供的工程量清单单项最高限价问题；投标函附录中工期、分包、工程质量要求和缺陷责任期对应约定内容问题；我公司业绩为三个项目合并招标问题；边坡治理施工业绩问题；任一清单的综合单价低于警戒线问题；业绩要求的竣工时间问题；财务报告提供问题；我公司业绩合同金额问题；招标人确定中标人问题；低价说明证明材料问题；招标人是否委派业主专家参与评标问题；我公司业绩项目经理变更问题；财务报告提供问题；专业分包业绩问题；投标文件制作系统软件导出的电子投标文件格式问题；项目经理以前在其他公司执业的业绩问题；在职的已退休的注册人员问题；投标函附录中的合同条款号填写问题；评标办法中已标价工程量清单要求的承诺问题；评标专家不被围猎问题。
+https://www.chinapipe.net/project/d3078019.html</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>大渡口区2024年居民户内燃气安全设施整改项目(二期)、大渡口区2024年城市燃气管道等老化更新改造项目(二期)招标公告</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>燃气安全设施、城市燃气管道等老化更新改造</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>大渡口区</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>大渡口区2024年居民户内燃气安全设施整改项目（二期）更换居民气表约11700只、居民灶前自闭阀约112717只、燃气连接用不锈钢波纹软管约112717根。大渡口区2024年城市燃气管道等老化更新改造项目（二期）更新改造庭院埋地燃气管网约6913m，更新改造燃气立管及表后管道约9419户，更新切断阀约489套等，并配套实施管网开挖回填、路面恢复、绿化恢复等。</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>本项目工程总投资金额：5800.7万元，大渡口区2024年居民户内燃气安全设施整改项目（二期）总投资3165.12万元，大渡口区2024年城市燃气管道等老化更新改造项目（二期）总投资2635.58万元。</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>燃气安全设施、城市燃气管道等老化更新改造</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>大渡口区2024年居民户内燃气安全设施整改项目（二期）更换居民气表约11700只、居民灶前自闭阀约112717只、燃气连接用不锈钢波纹软管约112717根。大渡口区2024年城市燃气管道等老化更新改造项目（二期）更新改造庭院埋地燃气管网约6913m，更新改造燃气立管及表后管道约9419户，更新切断阀约489套等，并配套实施管网开挖回填、路面恢复、绿化恢复等。
+https://www.chinapipe.net/project/d3077961.html</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>70</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>燃气安全设施, 城市燃气管道, 老化更新改造, 投资金额, 项目总投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>荣昌区2026年安富街道高标准农田建设项目招标公告</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>建筑工程施工</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>荣昌区</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>改造提升高标准农田326.59亩，其中高效节水灌溉面积130亩。主要内容包括梯台修筑、梯田修筑、稻虾地块修筑、恢复地类整治、输水管道安装、排水沟修建、机耕道改建等。</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>项目总投资金额181.43万元，本次招标项目合同估算金额166.35万元，全部由财政资金支持。</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>建筑工程施工</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>改造提升高标准农田326.59亩，其中高效节水灌溉面积130亩。主要内容包括梯台修筑、梯田修筑、稻虾地块修筑、恢复地类整治、输水管道安装、排水沟修建、机耕道改建等。
+https://www.chinapipe.net/project/d3077954.html</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>大渡口区2025年老化燃气管道及设施更新改造项目(一期)EPC招标公告</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>燃气管道及相关设施设备</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>大渡口区</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>大渡口区燃气管线及燃气相关设施设备改造提升，实现燃气管线智能化管理和保障燃气供给安全。</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>项目总投资金额7255.57万元，本次招标项目合同估算金额6408.986万元。</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>燃气管道及相关设施设备</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>大渡口区燃气管线及燃气相关设施设备改造提升，实现燃气管线智能化管理和保障燃气供给安全。
+https://www.chinapipe.net/project/d3077935.html</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>80</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>燃气管道, 老化改造, 智能化管理, 燃气供给安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>国网重庆电力主城一片区2026年原集体企业和各级产业单位新增第三次物资区域联合授权物资框架协议公开谈判采购资格预审公告</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别
+https://www.chinapipe.net/project/d3077904.html</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀采购项目(包1、包2)(第二次)招标公告</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>不锈钢可调式减压阀,不锈钢静音式止回阀,不锈钢微量排气阀,不锈钢闸阀,不锈钢表前阀,不锈钢球阀,Y型过滤器</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>为重庆分质供水有限公司提供不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀等设备材料。</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>每个包合同暂估金额为110万。</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>不锈钢可调式减压阀,不锈钢静音式止回阀,不锈钢微量排气阀,不锈钢闸阀,不锈钢表前阀,不锈钢球阀,Y型过滤器</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>为重庆分质供水有限公司提供不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀等设备材料。
+https://www.chinapipe.net/project/d3077898.html</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>龙兴新城污水管网工程建设及整治修复项目(二期)招标计划表</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>管网工程、土石方工程</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>管网工程、土石方工程等。</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>合同预估金额为2500万元</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>管网工程、土石方工程</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>管网工程、土石方工程等。
+https://www.chinapipe.net/project/d3077891.html</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>80</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>污水管网工程, 二期, 管网工程, 土石方工程, 2500万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>李市镇农村饮水管网改建工程竞争性磋商公告</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>水管</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>江津区</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>李市镇农村饮水管网改建工程</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>预算金额：1,653,882.29元</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>水管</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>李市镇农村饮水管网改建工程
+https://www.chinapipe.net/project/d3077886.html</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>90</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>水管, 农村饮水管网改建工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>长安工业渝北工厂供水管网泄露检测及修复询比采购公告</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>供水管网泄露检测及修复设备和服务</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>渝北区</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>长安工业渝北工厂供水管网泄露检测及修复询比采购</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>供水管网泄露检测及修复设备和服务</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>长安工业渝北工厂供水管网泄露检测及修复询比采购
+https://www.chinapipe.net/project/d3077867.html</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>80</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>供水管网泄露检测及修复, 询比采购</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>重庆市九龙坡区城市老旧小区供水管网漏损治理及二次供水设施更新改造工程(二期)一标段答疑补遗文件</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>供水管网漏损治理及二次供水设施更新改造</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>九龙坡区</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>重庆市九龙坡区城市老旧小区供水管网漏损治理及二次供水设施更新改造工程(二期)一标段</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>供水管网漏损治理及二次供水设施更新改造</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>重庆市九龙坡区城市老旧小区供水管网漏损治理及二次供水设施更新改造工程(二期)一标段
+https://www.chinapipe.net/project/d3077858.html</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>两江天宫殿钢筋、型材、商砼、管材采购(第二次)招标公告</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>钢筋、型材、商砼、管材</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>钢筋、型材、商砼、管材</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别
+https://www.chinapipe.net/project/d3077792.html</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>管材</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>万州区旧城供水管网改造工程(三期)管材等材料采购(第二次)招标公告</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>管材、管件、阀门类、伸缩器、电磁流量计、法兰及其他等材料</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>万州区</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>该项目对百安坝等3个街道老旧市政供水管道及附属设施进行改造，配套智慧水务物联网感知设备建设，共计改造老旧市政供水管道84.2千米。</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>项目资金来自超长期特别国债资金及业主自筹，项目出资比例为100%，本次招标项目货物采购估算金额为2500万元。</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>管材、管件、阀门类、伸缩器、电磁流量计、法兰及其他等材料</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>该项目对百安坝等3个街道老旧市政供水管道及附属设施进行改造，配套智慧水务物联网感知设备建设，共计改造老旧市政供水管道84.2千米。
+https://www.chinapipe.net/project/d3077724.html</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>80</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>管材, 招标, 改造工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026年度重庆分质供水有限公司不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀采购项目(包1、包2)(第二次)招标公告</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>不锈钢可调式减压阀,不锈钢静音式止回阀,不锈钢微量排气阀,不锈钢闸阀,不锈钢表前阀,不锈钢球阀,Y型过滤器</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>为重庆分质供水有限公司提供不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀等设备材料。</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>每个包合同暂估金额为110万元。</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>不锈钢可调式减压阀,不锈钢静音式止回阀,不锈钢微量排气阀,不锈钢闸阀,不锈钢表前阀,不锈钢球阀,Y型过滤器</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>为重庆分质供水有限公司提供不锈钢闸阀、不锈钢表前阀、不锈钢减压阀、不锈钢排气阀、不锈钢止回阀等设备材料。
+https://www.chinapipe.net/project/d3077649.html</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>85</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>不锈钢闸阀, 不锈钢表前阀, 不锈钢减压阀, 不锈钢排气阀, 不锈钢止回阀, 管材招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>重庆市秀山自治县2026年提升农村饮水质量专项行动项目-溶溪片区(一标段)答疑补遗文件</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>秀山土家族苗族自治县</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>重庆市秀山自治县2026年提升农村饮水质量专项行动项目-溶溪片区(一标段)答疑及补遗通知</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>重庆市秀山自治县2026年提升农村饮水质量专项行动项目-溶溪片区(一标段)答疑及补遗通知
+https://www.chinapipe.net/project/d3077605.html</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>酉阳县桃花源新城供水工程管网安装工程专业分包采购公告</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>管网安装工程</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>酉阳土家族苗族自治县</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>酉阳县桃花源新城供水工程管网安装工程专业分包</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>暂无明确资金信息</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>管网安装工程</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>酉阳县桃花源新城供水工程管网安装工程专业分包
+https://www.chinapipe.net/project/d3077567.html</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>80</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>酉阳县桃花源新城供水工程, 管网安装工程专业分包, 管网安装工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>重庆市益康环保工程有限公司永川分公司污水外排管道迁改项目询比采购公告</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>排水钢管</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>永川区</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>污水外排管道迁改</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>排水钢管</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>污水外排管道迁改
+https://www.chinapipe.net/project/d3077531.html</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>四川, 管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>重庆市巴南区龙洲湾片区城市污水管网更新改造工程施工招标公告</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>排水管网</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>巴南区</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>本项目改建及修复管网总长度约30.98公里，雨污水错混接改造以及管网缺失改造DN300-DN600排水管网约2.0公里；修复DN300-DN1000管道约28.98公里。</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>项目总投资金额：10063.6万元，本次招标项目合同估算金额：6033.535232万元</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>排水管网</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>本项目改建及修复管网总长度约30.98公里，雨污水错混接改造以及管网缺失改造DN300-DN600排水管网约2.0公里；修复DN300-DN1000管道约28.98公里。
+https://www.chinapipe.net/project/d3077506.html</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>95</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>管材, 招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>土桥、宗申、界石排水箱涵清污分流改造项目施工招标公告</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>排水管网</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>本项目改建及修复管网总长度约30.63公里，雨污水错混接改造以及管网缺失改造DN300-DN800排水管网约6.35公里；修复DN300-DN1200管道约24.28公里。</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>项目总投资金额：9551.19万元，本次招标项目合同估算金额：5383.510617万元</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>排水管网</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>本项目改建及修复管网总长度约30.63公里，雨污水错混接改造以及管网缺失改造DN300-DN800排水管网约6.35公里；修复DN300-DN1200管道约24.28公里。
+https://www.chinapipe.net/project/d3077435.html</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>85</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>排水管网, 管网修复, 管网改造</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>巫溪县花台片区川主、农坡等5个村迁建区特色农业抗旱供水保障工程勘察设计招标计划表</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>勘察设计服务</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>巫溪县</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>主要整治孝子溪大堰水渠约17.5km;新建孝子溪水库引水管道约17.5km,其中需新建引水隧洞内置管道约1.5km;新建柑橘基地管网约3.25km;改建6000m蓄水池1座；新建2000m蓄水池2座；新建1000m蓄水池1座；新建500m³蓄水池2座；新建柑橘基地滴灌系统1套。</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>合同预估金额为340万元（含水土保持施工图设计）。</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>勘察设计服务</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>主要整治孝子溪大堰水渠约17.5km;新建孝子溪水库引水管道约17.5km,其中需新建引水隧洞内置管道约1.5km;新建柑橘基地管网约3.25km;改建6000m蓄水池1座；新建2000m蓄水池2座；新建1000m蓄水池1座；新建500m³蓄水池2座；新建柑橘基地滴灌系统1套。
+https://www.chinapipe.net/project/d3078207.html</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>80</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>管材招标, 勘察设计, 资金情况, 产品种类</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>涪陵区李渡新区水厂工程(一期)施工招标公告</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>取水及原水输送工程、净水厂工程、配水工程、供配电专项工程等施工，设备采购与安装（不含智慧化自控设备采购及伴随服务部分）、系统调试与试运行、市政设施保护、拆除与恢复、电力和燃气管线迁改；厂区道路、绿化景观、围墙等配套设施；施工临时道路、施工临时用水与施工临时用电（含道路、用水、用电的手续办理）、施工围挡、配合完成不少于一项区级及以上的科技创新项目、“后五通”的接入等。</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>涪陵区</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>涪陵区李渡新区水厂工程(一期)设计水量目标为10万m/d，二期水量目标为20万m/d，采用混凝、沉淀、过滤、消毒常规水处理工艺。一期工程项目主要建设内容包括取水及原水输送工程、净水厂工程、配水工程三部分。</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>项目业主为重庆水务环境控股集团渝东自来水有限公司，建设资金来自争取三峡后续工作专项资金、银行贷款和业主自筹等，项目出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>取水及原水输送工程、净水厂工程、配水工程、供配电专项工程等施工，设备采购与安装（不含智慧化自控设备采购及伴随服务部分）、系统调试与试运行、市政设施保护、拆除与恢复、电力和燃气管线迁改；厂区道路、绿化景观、围墙等配套设施；施工临时道路、施工临时用水与施工临时用电（含道路、用水、用电的手续办理）、施工围挡、配合完成不少于一项区级及以上的科技创新项目、“后五通”的接入等。</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>涪陵区李渡新区水厂工程(一期)设计水量目标为10万m/d，二期水量目标为20万m/d，采用混凝、沉淀、过滤、消毒常规水处理工艺。一期工程项目主要建设内容包括取水及原水输送工程、净水厂工程、配水工程三部分。
+https://www.chinapipe.net/project/d3077140.html</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>85</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>管材, 招标, 水厂工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>中铁十一局集团有限公司新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购公告</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>管材</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>重庆市</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>渝中区</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>管材</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>新建重庆至黔江铁路重庆站站房及配套综合交通枢纽工程CQZSG-2标段项目经理部管材询比采购
+https://www.chinapipe.net/project/d3077066.html</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>80</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>管材, 询比采购</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PPR管及管件采购/78020049-PS202608200813采购变更公告(第1号)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PPR管及管件</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>PPR管及管件</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别
+https://www.chinapipe.net/project/d3078524.html</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>北部基地平原公司关于FRPP管Φ160及配套弯头项目采购公告</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>FRPP管Φ160PN1.0*13.3-黑色, FRPP弯头(90°)Φ160PN1.0*13.3-R=1.5D-黑色</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>北部基地平原公司关于FRPP管Φ160及配套弯头项目采购公告</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
         <is>
           <t>项目详细内容无法识别</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>FRPP管Φ160PN1.0*13.3-黑色, FRPP弯头(90°)Φ160PN1.0*13.3-R=1.5D-黑色</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>北部基地平原公司关于FRPP管Φ160及配套弯头项目采购公告 根据成都云图控股股份有限公司采购管理制度，本着“公开、公平、公正、诚信”的原则，诚邀具备投标资格 供应商参加投标。 1 项目概况 1.1 项目名称：北部基地平原公司关于FRPP管Φ160及配套弯头项目 1.2 项目编号：ZB-2608-1047 1.3 交货地点和时间：按实际订单地址及交期要求； 1.4 物资名称及数量： 网 标的编码 标的名称 规格型号 计量单位 数量 TMP91386 FRPP管Φ160PN1.0*13.3-黑色 4米/根 米 80 务 TMP91392 FRPP弯头(90°)Φ160PN1.0*13.3-R=1.5D-黑色 个 8 2 投标人资格要求 2.1 具有独立法人资格； 商 2.2 具有本项目相应履约能力； 2.3 未被纳入成都云图控股股份有限公司供应商“黑名单”。 3 投标方式 道 登录云图控股采购平台（https://srm.wintrueholding.com/），根据注册要求填报公司信息并上传资质文件，获得准 入审核后报名申请参加本项目。本项目所有的招标公告、变更澄清、中标公告均在本网进行公示。具体查阅本 网站首页下载专区的“供应商系统操作手册”。 4 时间安排 管 投标截止时限：2026-08-25 13:00，投标人应于该时限前完成平台注册、报名、标书费缴纳、投标保证金缴纳、平 台报价和标书上传等工作。 5 标书费与保证金 国 5.1 标书费：0人民币/份，售后不退还； 5.2 投标保证金：0人民币/份； 5.3 标书费和投标保证金请分开支付，收款账号详见项目缴费单，转账时需备注平台提供的缴费附言。 5.4 投标保证金退还：未中标单位在中标公告发布后7个工作日内无息退还；中标单位在签订合同后转为履约保证 中 金，按合同约定履约后7个工作日内退还。 5.5 投标人存在下列行为之一的，投标保证金将不予退还： 5.5.1 违反《供应商廉洁诚信承诺书》的； 5.5.2 在投标活动中有弄虚作假、围标串标的； 5.5.3 中标人放弃中标项目的； 5.5.4 中标公告发出后7个工作日内，中标人无正当理由不与招标人签订合同的、提出附加条件、更改合同实质性 内容的； 5.5.5 中标人拒不足额缴纳招标公告文件所要求履约保证金的； 5.5.6 法律法规规定不予退还的其他情形。 6 招标业务联系方式：白焱公 手机：15315813736 邮箱： 。 7 其他咨询与投诉热线400-066-7019，接通后请按语音提示拨号： 拨号1 设备备件类业务和企业微信相关问题咨询。 拨号2 SRM平台注册、缴费、系统操作、大宗原料业务咨询。 拨号3 标书费发票开具。 拨号4 投诉与举报，或将相关投诉举报资料发至邮箱likaijuan@wintrueholding.com，我们将妥善处理。 成都云图控股股份有限公司供应中心 2026-08-22 11:46 网 附件： 务 点击查看内容 信息来源:https://www.chinapipe.net/project/d3078468.html 商 cqdingjiu 2026.08.25 09:26:06 道 管 国 中</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
         <is>
           <t>北部基地平原公司关于FRPP管Φ160及配套弯头项目采购公告
 https://www.chinapipe.net/project/d3078468.html</t>
         </is>
       </c>
-      <c r="N78" t="n">
+      <c r="N104" t="n">
         <v>85</v>
       </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>FRPP管, 弯头</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>FRPP管, 弯头, 四川</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>中铁六局四川南广铁路站前三标工程隧道管材物资采购公告</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>管材网线索</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>交通</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>三通接头,接头,防结晶封器,内燃机车导水管套,PVC管,HDPE管,弯头,盲管</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>四川省</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>广安市</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>岳池县</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
         <is>
           <t>中铁六局四川南广铁路站前三标工程隧道管材物资采购</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>原文未提及</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>三通接头,接头,防结晶封器,内燃机车导水管套,PVC管,HDPE管,弯头,盲管</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>中铁六局四川南广铁路站前三标工程隧道管材物资采购公告 XSJZ-NG-2026-3119 采购单位:新建雄商高速铁路雄安新区至商丘段站前XSZQ-5标段（二工区） 发布时间:2026-08-22 10:08 报价截止时间:2026-08-26 09:30 招标方联系人:王晓磊 网 招标方联系电话:15075136153 招标方邮箱:15075136153@163.com 务 监督方联系人:李波 监督方联系电话:13832379603 商 监督方邮箱:13832379603@163.com 保证金:2500.0元 道 结算与发票信息: 结算方式：中信支付或承兑 支付条件：半年分期付款 发票种类：增值税专票 管 发票抬头：中铁六局集团有限公司石家庄铁路建设分公司 税号：91130104673209036N 其他要求：付款条件：双方签订纸质版采购合同后按交付数量按期结算，结算完成后，甲方在收到乙方开具的 正式的增值税专用发票后180天内，向乙方支付不超过当月结算金额的80%，合同履行完毕双方确认无误并签订 封账协议后，最高向乙国方支付开累结算金额的90%，剩余10%作为质保金，质保期12个月，在最后一批货物质保 期满后90日内无息支付，如发生纠纷，则延后至纠纷最终解决后60天内付清。质量保证金的支付并不免除乙方对 交付货物质量的保证责任。乙方同意给予6个月的付款宽限期，在此宽期间内不视为甲方违约且不计息。 交货信息: 交货方式:汽中车运输 收货人:王晓磊 收货人联系方式:15075136153 其他说明事项: 流水号：询2026082200036 计 交 标的 量 标的编号 规格型号 数量 技术标准及要求 货 送货地址 名称 单 期 位 西南区-四川省-广安市-岳池 三通 县-中铁六局集团有限公司四 0950192127691 Φ100mm 150.0 个 Q/CR562.4-2018 接头 川南广铁路NGZQSG-03标段 项目经理部 西南区-四川省-广安市-岳池 县-中铁六局集团有限公司四 4900095010026 接头 100 1500.0 个 Q/CR562.4-2018 川南广铁路NGZQSG-03标段 项目经理部 西南区-四川省-广安市-岳池 防结 县-中铁六局集团有限公司四 0908200376935 晶密 DN100 1526.0 个 Q/CR562.4-2018 川南广铁路NGZQSG-03标段 封器 项目经理部 内燃 西南区-四川省-广安市-岳池 机车 DF8B 县-中铁六局集团有限公司四 2712999297927 10.0 个 GB/T 5836.1-2018 导水 36×20×13mm 川南广铁路NGZQSG-03标段 管套 项目经理部 西南区-四川省-广安市-岳池 PVC 县-中铁六局集团有限公司四 1602621010057 32 5051.0 米 GB/T 5836.1-2018 管 川南广铁路NGZQSG-03标段 项目经理部 西南区-四川省-广安市-岳池 网 PVC 县-中铁六局集团有限公司四 1602621010005 100 100.0 米 GB/T 5836.1-2018 管 川南广铁路NGZQSG-03标段 项目经理部 务西南区-四川省-广安市-岳池 PVC 县-中铁六局集团有限公司四 1602621010007 110 3525.0 米 GB/T 5836.1-2018 管 川南广铁路NGZQSG-03标段 项目经理部 商 西南区-四川省-广安市-岳池 PVC 县-中铁六局集团有限公司四 1609827153587 DN110 250.0 个 GB/T 5836.1-2018 弯头 川南广铁路NGZQSG-03标段 项目经理部 道 高密度聚乙烯，双壁波 西南区-四川省-广安市-岳池 电力 纹管(壁厚10mm),内 县-中铁六局集团有限公司四 1602012241079 过轨 HDPE 110mm 1563.0 米 径100mm，环刚度不小 川南广铁路NGZQSG-03标段 管 于16KN/㎡ 项目经理部 管 高密度聚乙烯，双壁波 西南区-四川省-广安市-岳池 电力 纹管(壁厚10mm),内 县-中铁六局集团有限公司四 1602012241079 过轨 HDPE 110mm 2986.0 米 径100mm，环刚度不小 川南广铁路NGZQSG-03标段 管 于16KN/㎡ 项目经理部 国 西南区-四川省-广安市-岳池 县-中铁六局集团有限公司四 0903244206213 盲管 DN100 6210.0 米 Q/CR562.4-2018 川南广铁路NGZQSG-03标段 中 项目经理部 西南区-四川省-广安市-岳池 县-中铁六局集团有限公司四 0903244206208 盲管 DN80 200.0 米 Q/CR562.4-2018 川南广铁路NGZQSG-03标段 项目经理部 西南区-四川省-广安市-岳池 县-中铁六局集团有限公司四 0903244032393 盲管 50mm×2m 7172.0 米 Q/CR562.4-2018 川南广铁路NGZQSG-03标段 项目经理部 报价网址:http://www.crecgec.com 信息来源:https://www.chinapipe.net/project/d3078392.html cqdingjiu 2026.08.25 09:26:06</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
         <is>
           <t>中铁六局四川南广铁路站前三标工程隧道管材物资采购
 https://www.chinapipe.net/project/d3078392.html</t>
         </is>
       </c>
-      <c r="N79" t="n">
+      <c r="N105" t="n">
         <v>0</v>
       </c>
-      <c r="O79" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>81-西南-大邑西岭文体-水泥制品-询比采购公告</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>II级钢筋混凝土管、II级钢筋混凝土管、II级钢筋混凝土管、II级钢筋混凝土管、II级钢筋混凝土管、II级中钢筋混凝土管、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土井筒、预制偏心井盖、预制偏心井盖、预制偏心井盖、预制偏心井盖、单算偏沟式雨水口、双算偏沟式雨水口、钢筋混凝土矩形检查井、钢筋混凝土矩形检查井、钢筋混凝土矩形检查井、钢筋混凝土矩形检查井</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>水泥制品</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>项目预算金额为290万元</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>II级钢筋混凝土管、II级钢筋混凝土管、II级钢筋混凝土管、II级钢筋混凝土管、II级钢筋混凝土管、II级中钢筋混凝土管、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井上井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土检查井下井室、钢筋混凝土井筒、预制偏心井盖、预制偏心井盖、预制偏心井盖、预制偏心井盖、单算偏沟式雨水口、双算偏沟式雨水口、钢筋混凝土矩形检查井、钢筋混凝土矩形检查井、钢筋混凝土矩形检查井、钢筋混凝土矩形检查井</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>水泥制品
+https://www.chinapipe.net/project/d3078565.html</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>中铁十五局集团四公司、地下公司、新能源公司八月份三次物资采购招标公告</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>空调,房屋改造材料,商品混凝土,道砟,绿化材料,运营监测系统,聚丙烯粗纤维,门窗,施工设备配件,混凝土</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>中铁十五局集团四公司、地下公司、新能源公司八月份三次物资采购招标公告</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>招标项目资金已落实</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>空调,房屋改造材料,商品混凝土,道砟,绿化材料,运营监测系统,聚丙烯粗纤维,门窗,施工设备配件,混凝土</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>中铁十五局集团四公司、地下公司、新能源公司八月份三次物资采购招标公告
+https://www.chinapipe.net/project/d3078356.html</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>不锈钢材料招标公告</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>不锈钢材料</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>不锈钢材料</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>不锈钢材料</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>不锈钢材料
+https://www.chinapipe.net/project/d3078292.html</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>西南油气田分公司致密气项目部金浅26井地面集输工程招标公告</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>地面集输工程所需设备和材料</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>金浅26井地面集输工程包括井口模块、除砂器橇、三相分离器橇、密闭装油橇、凝析油罐模块、气田水罐模块、放空分液罐模块、放空模块、出站模块等配套工程。</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>项目估算金额：450万元（含税）</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>地面集输工程所需设备和材料</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>金浅26井地面集输工程包括井口模块、除砂器橇、三相分离器橇、密闭装油橇、凝析油罐模块、气田水罐模块、放空分液罐模块、放空模块、出站模块等配套工程。
+https://www.chinapipe.net/project/d3078290.html</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>90</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>管材, 地面集输工程, 四川</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>喜德县冕山镇及两河口镇污水管道改造建设项目施工的招标文件预公示</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>污水管道</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>凉山彝族自治州</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>凉山彝族自治州</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>喜德县冕山镇及两河口镇污水管道改造建设项目的具体内容见附件信息。</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>污水管道</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>喜德县冕山镇及两河口镇污水管道改造建设项目的具体内容见附件信息。
+https://www.chinapipe.net/project/d3078281.html</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>四川, 污水管道</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>甘眉工业园区污水管网建设项目施工招标文件(公告板)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>管网</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>甘眉工业园区污水管网建设项目的具体内容见附件信息。</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>管网</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>甘眉工业园区污水管网建设项目的具体内容见附件信息。
+https://www.chinapipe.net/project/d3078278.html</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>水电五局成眉机电安装项目铸铁井盖物资采购需求</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>铸铁井盖</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>详见附件。</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>铸铁井盖</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>详见附件。
+https://www.chinapipe.net/project/d3078222.html</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 管材招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>聚乙烯热收缩套,聚乙烯胶粘带,防腐膏,聚丙烯胶粘带,聚乙烯补伤片</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告 四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告 四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005已具备采购条件，现公开邀请供应商参加询比采购活动。</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>项目资金已落实。</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>聚乙烯热收缩套,聚乙烯胶粘带,防腐膏,聚丙烯胶粘带,聚乙烯补伤片</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告 四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005询比采购公告 四川油建国家石油天然气大流量计量站成都分站高压检定能力建设工程防腐材料JLZ-005已具备采购条件，现公开邀请供应商参加询比采购活动。
+https://www.chinapipe.net/project/d3078197.html</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>85</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 管材, 招标, 商机</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>南江县城污水处理厂水污染治理设施提标改造项目详细勘察服务磋商公告</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>巴中市</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>巴中市</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>详细勘察服务</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>预算资金：¥389940.00元</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>详细勘察服务
+https://www.chinapipe.net/project/d3078163.html</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>80</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>管材招标, 重庆, 四川, 近三天</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>绵阳市中心医院蒸汽管道改造(第二次)采购公告</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>蒸汽管道</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>绵阳市</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>绵阳市</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>蒸汽管道改造</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>最高限价：26.7万元</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>蒸汽管道</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>蒸汽管道改造
+https://www.chinapipe.net/project/d3078145.html</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>80</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>蒸汽管道改造, 四川</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>中国电子系统工程第三建设有限公司,中微半导体设备(四川)有限公司工业用房及配套设施项目,UPVC管道,谈判采购项目公告</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>UPVC管道</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>中微半导体设备成都研发及生产基地暨西南总部项目洁净室及一般机电包项目【UPVC】将开启线上采购。</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>UPVC管道</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>中微半导体设备成都研发及生产基地暨西南总部项目洁净室及一般机电包项目【UPVC】将开启线上采购。
+https://www.chinapipe.net/project/d3078054.html</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>水电五局卡拉水电站地厂项目经理部镀锌钢管等物资采购需求</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>镀锌钢管等物资</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>水电五局卡拉水电站地厂项目经理部镀锌钢管等物资采购需求</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>镀锌钢管等物资</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>水电五局卡拉水电站地厂项目经理部镀锌钢管等物资采购需求
+https://www.chinapipe.net/project/d3078004.html</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 近三天, 管材招标商机</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>绵阳市游仙区(城区)老旧燃气管道等更新改造工程项目(一期)施工(重发公告第0次)第1次答疑文件</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>绵阳市</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>绵阳市</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>绵阳市游仙区(城区)老旧燃气管道等更新改造工程项目(一期)施工</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>绵阳市游仙区(城区)老旧燃气管道等更新改造工程项目(一期)施工
+https://www.chinapipe.net/project/d3077993.html</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>绵阳市游仙区, 老旧燃气管道, 更新改造, 项目, 施工</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>会禄高速公路机电项目玻璃钢管、玻璃钢管箱采购公开招标公告</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>玻璃钢管、玻璃钢管箱</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>详见附件。</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>玻璃钢管、玻璃钢管箱</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>详见附件。
+https://www.chinapipe.net/project/d3077959.html</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>城投·三清华庭建设项目燃气管道安装工程(第四次)竞争性磋商公告</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>燃气管道</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>燃气管道安装工程</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>燃气管道</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>燃气管道安装工程
+https://www.chinapipe.net/project/d3077958.html</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 管材招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>璞玉源水务2026成都市蒲江县管道直饮水入户项目设计施工总承包招标公告</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>管道直饮水入户设备</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>管道直饮水入户项目的建设内容包括设计及施工总承包。</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>管道直饮水入户设备</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>管道直饮水入户项目的建设内容包括设计及施工总承包。
+https://www.chinapipe.net/project/d3077945.html</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>80</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>管道直饮水入户项目, 成都市蒲江县, 设计施工总承包</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>采气二厂集输管道智能检测项目(2026~2028年)(重招)招标公告</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>智能检测设备</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>集输管道智能检测</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>智能检测设备</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>集输管道智能检测
+https://www.chinapipe.net/project/d3077939.html</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>智能检测, 管道</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>西充县旧城区排水防涝设施建设和虹溪河及洗笔路片区污水管网更新改造项目招标公告</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>HDPE双壁波纹雨水管、混凝土雨水管、HDPE双壁波纹污水管、钢筋砼承插排水管、物联感知设备等。</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>南充市</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>南充市</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>该项目涉及三个子项目：(一) 南充市西充县旧国城区排水防涝设施建设改造项目，包括更新改造不同规格的HDPE双壁波纹雨水管和混凝土雨水管，以及配套检查井和雨水口的改造；(二) 南充市西充县虹溪河片区污水管网更新改造项目，包括改造和新建不同规格的污水主管网和支管网，以及配套安装物联感知设备；(三) 南充市西充县洗笔路片区污水管网更新改造项目，包括改造和新建不同规格的污水管网，以及配套安装物联感知设备。</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>项目总投资额为37744.54万元。</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>HDPE双壁波纹雨水管、混凝土雨水管、HDPE双壁波纹污水管、钢筋砼承插排水管、物联感知设备等。</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>该项目涉及三个子项目：(一) 南充市西充县旧国城区排水防涝设施建设改造项目，包括更新改造不同规格的HDPE双壁波纹雨水管和混凝土雨水管，以及配套检查井和雨水口的改造；(二) 南充市西充县虹溪河片区污水管网更新改造项目，包括改造和新建不同规格的污水主管网和支管网，以及配套安装物联感知设备；(三) 南充市西充县洗笔路片区污水管网更新改造项目，包括改造和新建不同规格的污水管网，以及配套安装物联感知设备。
+https://www.chinapipe.net/project/d3077901.html</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>中国五冶西充县太平水厂、鹤鸣庵水厂及配套管网建设项目劳务分包采购公告</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>劳务分包</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>南充市</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>南充市</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>西充县太平水厂、鹤鸣庵水厂及配套管网建设项目劳务分包</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>采购控制价：2761.638256万元（含税）</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>劳务分包</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>西充县太平水厂、鹤鸣庵水厂及配套管网建设项目劳务分包
+https://www.chinapipe.net/project/d3077864.html</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>70</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>四川, 劳务分包, 管材</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>马边彝族自治县自来水有限责任公司年度材料采购(AGR及PVC—U材料)-更正公告</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>智能水表-有线光电传输智能水表,智能水表-NB-IOT物联网带阀水表,智能水表-智能远传水表-远传水表(超声波水表)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>乐山市</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>乐山市</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>马边彝族自治县自来水有限责任公司年度材料采购更正公告（第1次）</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>智能水表-有线光电传输智能水表,智能水表-NB-IOT物联网带阀水表,智能水表-智能远传水表-远传水表(超声波水表)</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>马边彝族自治县自来水有限责任公司年度材料采购更正公告（第1次）
+https://www.chinapipe.net/project/d3077838.html</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>邛崃经芦山至荥经高速公路项目邛崃段占压邛崃市天然气有限公司输气管道迁改工程设计比选公告</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>设计服务</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>邛崃经芦山至荥经高速公路项目邛崃段占压邛崃市天然气有限公司输气管道迁改工程设计。</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>设计服务</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>邛崃经芦山至荥经高速公路项目邛崃段占压邛崃市天然气有限公司输气管道迁改工程设计。
+https://www.chinapipe.net/project/d3077596.html</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>自贡水务投资集团有限公司供水管道及设施防腐招采公告</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>钢管及设施防腐</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>自贡市</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>自贡市</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>钢管及设施防腐</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>最高限价80万元</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>钢管及设施防腐</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>钢管及设施防腐
+https://www.chinapipe.net/project/d3077586.html</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>70</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 管材招标, 商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>四川省眉山市东坡区管道直饮水项目设计-施工总承包招标公告</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>眉山市</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>眉山市</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>管道直饮水项目的具体内容未在提供的信息中明确列出。</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>管道直饮水项目的具体内容未在提供的信息中明确列出。
+https://www.chinapipe.net/project/d3077575.html</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>分析, 重庆, 四川, 近三天, 管材, 招标, 商机</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>射洪市2026年高标准农田建设项目(复兴及潼射片区)-施工-1招标公告</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>高标准农田建设相关材料与设备</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>遂宁市</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>遂宁市</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>本项目包括新建及改建高标准农田，涉及田块整治工程、灌溉排水工程、田间道路工程、土壤改良、农田输配电工程、农田防护与生态保护工程。</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>项目资金来自中央投资、省级配套资金、县级配套资金，出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>高标准农田建设相关材料与设备</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>本项目包括新建及改建高标准农田，涉及田块整治工程、灌溉排水工程、田间道路工程、土壤改良、农田输配电工程、农田防护与生态保护工程。
+https://www.chinapipe.net/project/d3077563.html</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>盐边县城北片区和清源片区老旧街区改造项目施工一标段招标公告</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>市政公用工程施工总承包</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>攀枝花市</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>攀枝花市</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>对盐边县城北、清源片区老旧街区进行商提升改造，包括改造中环北路、西环北路、清河西路、盐中巷外立面排危改造约12.28万平方米，街区路面整治约12000平方米，街区雨污排水管网改造约10千米，改造适老化、适儿化服务用房约5000平方米，社区综合服务生活市场改造8500平方米，街区屋面防水改造约9900平方米，改造3500平方米街区边角地配套停车场及充电桩等基础设施，增设路灯280盏，公共活动健身区15处，街角口袋公园4处，改造清河西路、盐中巷街区安道全防护栏5公里，街区架空线入地4千米，弱电管网整治5千米，并同步完善消防、安防、垃圾收储、便民生活设施等配套公共服务设施。</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>项目总投资额：14500万元。</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>市政公用工程施工总承包</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>对盐边县城北、清源片区老旧街区进行商提升改造，包括改造中环北路、西环北路、清河西路、盐中巷外立面排危改造约12.28万平方米，街区路面整治约12000平方米，街区雨污排水管网改造约10千米，改造适老化、适儿化服务用房约5000平方米，社区综合服务生活市场改造8500平方米，街区屋面防水改造约9900平方米，改造3500平方米街区边角地配套停车场及充电桩等基础设施，增设路灯280盏，公共活动健身区15处，街角口袋公园4处，改造清河西路、盐中巷街区安道全防护栏5公里，街区架空线入地4千米，弱电管网整治5千米，并同步完善消防、安防、垃圾收储、便民生活设施等配套公共服务设施。
+https://www.chinapipe.net/project/d3077560.html</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>80</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>川东北现代农业融合发展示范园项目设计施工总承包招标公告</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>设计施工总承包</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>南充市</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>南充市</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>本项目总占地面积为149道225.64平方米，总建筑面积151550.12平方米，其中新建标准化厂房143913平方米、综合管理用房7637.12平方米，配套建设配套厂区道路、停车场、绿化工程、污水管网、给水管网、强弱电工程等配套工程。</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>项目总投资36633万元</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>设计施工总承包</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>本项目总占地面积为149道225.64平方米，总建筑面积151550.12平方米，其中新建标准化厂房143913平方米、综合管理用房7637.12平方米，配套建设配套厂区道路、停车场、绿化工程、污水管网、给水管网、强弱电工程等配套工程。
+https://www.chinapipe.net/project/d3077557.html</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>广元市朝天区污水管网提升改造项目(六标段)施工招标公告</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>排水管网更新改造及附属设施建设</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>中子镇转斗（含何家坝）、校场坝生活污商水处理站覆盖范围内的排水管网更新改造以及检查井等附属设施建设。</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>项目估算总投资10498.09万元，资金来源为争取上级资金及地方政府配套资金。</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>排水管网更新改造及附属设施建设</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>中子镇转斗（含何家坝）、校场坝生活污商水处理站覆盖范围内的排水管网更新改造以及检查井等附属设施建设。
+https://www.chinapipe.net/project/d3077552.html</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>80</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>污水管网, 提升改造, 排水管网, 更新改造, 检查井, 市政公用工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目(一期)施工招标公告</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DN300、DN500、DN600、DN800、DN1000 污水管道和雨水管道</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>新改建管道:DN300污水管道162m、DN500 污水管道1884m、DN600 污水管道112m、DN300 雨水管道466.50m、DN600 雨水管道609m、 DN800 雨水管商道 390m、 DN1000 雨水管道1029m。并对涉及破损路面及配套设施等进行恢复。</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>项目业主为苍溪县城市管网事务中心，建设资金来自争取上级财政资金和地方自筹（资金来源），项目出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>DN300、DN500、DN600、DN800、DN1000 污水管道和雨水管道</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>新改建管道:DN300污水管道162m、DN500 污水管道1884m、DN600 污水管道112m、DN300 雨水管道466.50m、DN600 雨水管道609m、 DN800 雨水管商道 390m、 DN1000 雨水管道1029m。并对涉及破损路面及配套设施等进行恢复。
+https://www.chinapipe.net/project/d3077551.html</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>80</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>污水管网改造, 延伸覆盖, DN300, DN500, DN600, DN800, DN1000, 雨水管道, 污水管道</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>广元市朝天区污水管网提升改造项目(五标段)施工招标公告</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>排水主管网、雨水管网、污水管网、检查井、路面恢复提升材料</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>本项目管网部分为新建排水主管网长度约2.08km（雨水管网约0.88km，污水管网约1.2km），管径DN300～DN800；现状管道清淤疏通长度约为1.23km；配套建设检查井等附属构筑物以及路面恢复提升；道路部分为埋地排水管道施工路面破除与恢复，同时对设计范围内其他道路进行路面黑化提升，项目共涉及7条道路的路面改造，其中车行道改造面积约9188平方米，人行道改造约3295平方米。</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>项目估算总投资10498.09万元，资金来源为争取上级资金及地方政府配套资金。</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>排水主管网、雨水管网、污水管网、检查井、路面恢复提升材料</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>本项目管网部分为新建排水主管网长度约2.08km（雨水管网约0.88km，污水管网约1.2km），管径DN300～DN800；现状管道清淤疏通长度约为1.23km；配套建设检查井等附属构筑物以及路面恢复提升；道路部分为埋地排水管道施工路面破除与恢复，同时对设计范围内其他道路进行路面黑化提升，项目共涉及7条道路的路面改造，其中车行道改造面积约9188平方米，人行道改造约3295平方米。
+https://www.chinapipe.net/project/d3077550.html</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>80</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>排水管网, 提升改造, 市政工程, 污水处理, 路面修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>四川省犍为第一中学扩建项目施工招标计划</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>房屋建筑</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>乐山市</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>乐山市</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>新建教学综合楼14500㎡、学生宿舍8500㎡、食堂3000㎡，以及附属用房、排水管网等配套基础设施。</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>估算总投资100000000.00元</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>房屋建筑</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>新建教学综合楼14500㎡、学生宿舍8500㎡、食堂3000㎡，以及附属用房、排水管网等配套基础设施。
+https://www.chinapipe.net/project/d3077548.html</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>大英县润民供水有限公司2026年PE供水管材管件采购(第二次)竞争性磋商公告</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PE供水管材管件</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>遂宁市</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>遂宁市</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>采购PE供水管材管件</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>PE供水管材管件</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>采购PE供水管材管件
+https://www.chinapipe.net/project/d3077526.html</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>PE供水管材管件, 四川</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>XD-24039-GS-UPVC管材、管件、阀门采购询比采购公告</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>UPVC管材、管件、阀门</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>项目名称：2024年度成都&amp;绵阳区域洁净工程维修改造项目D标段；项目地点：四川省成都市郫都区；品牌范围：环琪、协羽。</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>UPVC管材、管件、阀门</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>项目名称：2024年度成都&amp;绵阳区域洁净工程维修改造项目D标段；项目地点：四川省成都市郫都区；品牌范围：环琪、协羽。
+https://www.chinapipe.net/project/d3077513.html</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>管材, 管件, 阀门</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>四川卓勤新材料科技有限公司基膜涂覆一体化项目(二期三标段)预应力高强混凝土管桩采购任务</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>预应力高强混凝土管桩</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>预应力高强混凝土管桩</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>自筹资金</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>预应力高强混凝土管桩</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>预应力高强混凝土管桩
+https://www.chinapipe.net/project/d3077502.html</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>90</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>四川, 预应力高强混凝土管桩, 公开竞争性谈判, 自筹资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>宜宾市清源水务集团有限公司成品防腐无缝钢管采购项目招标/采购异常</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>防腐无缝钢管</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>本项目因递交响应文件供应商不足2家而流标。</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>防腐无缝钢管</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>本项目因递交响应文件供应商不足2家而流标。
+https://www.chinapipe.net/project/d3077498.html</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>四川, 管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>宜宾高新区高场片区老旧小区改造项目等两个工程管网探测及测绘(第二次)询价邀请函公告</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>管网探测设备及服务，建筑单体测绘设备及服务，原始地形地貌测绘设备及服务</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>宜宾市</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>宜宾市</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>本项目包括宜宾高新区高场片区老旧小区改造项目和宜宾高新区高场片区城中村配套基础设施项目的管网探测及测绘工作。</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>宜宾高新区高场片区老旧小区改造项目建安费用约8349.39万元，宜宾高新区高场片区城中村配套基础设施项目建安费用约12000万元。</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>管网探测设备及服务，建筑单体测绘设备及服务，原始地形地貌测绘设备及服务</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>本项目包括宜宾高新区高场片区老旧小区改造项目和宜宾高新区高场片区城中村配套基础设施项目的管网探测及测绘工作。
+https://www.chinapipe.net/project/d3077494.html</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>80</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>高新区, 老旧小区改造, 管网探测, 测绘</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>中煤广元煤炭储备项目设备安装工程钢管及型钢采购询价通知</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>热浸锌镀锌无缝钢管,热浸锌镀锌钢管,热浸锌扁铁,热浸锌角钢,热浸锌槽钢,水煤气管热浸锌,无缝钢管</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>钢管及型钢采购</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>热浸锌镀锌无缝钢管,热浸锌镀锌钢管,热浸锌扁铁,热浸锌角钢,热浸锌槽钢,水煤气管热浸锌,无缝钢管</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>钢管及型钢采购
+https://www.chinapipe.net/project/d3077488.html</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>70</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 近三天, 管材招标, 商机</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>成都市绕城高速天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购/标段招标文件答疑文件001号</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>无缝钢管,直缝埋弧焊钢管,调压计量撬,球阀,电动球阀,手动球阀,电液联动球阀,绝缘接头,阻火器,流量调节阀,涡轮流量计,调压器,超压切断阀,电加热器,压力表,差压计,双金属温度计,压力变送器,差压变送器,温度变送器,可燃气体探测器,可燃气体控制器,信号管电伴热带,管汇,无损检测,表面处理,运输,整撬监检,气密性试验,组装及调试</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>成都市绕城高速天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购/标段</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>招标控制价为 6077139.16元</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>无缝钢管,直缝埋弧焊钢管,调压计量撬,球阀,电动球阀,手动球阀,电液联动球阀,绝缘接头,阻火器,流量调节阀,涡轮流量计,调压器,超压切断阀,电加热器,压力表,差压计,双金属温度计,压力变送器,差压变送器,温度变送器,可燃气体探测器,可燃气体控制器,信号管电伴热带,管汇,无损检测,表面处理,运输,整撬监检,气密性试验,组装及调试</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>成都市绕城高速天然气高压输储气管道建设项目锦江调压站项目工艺设备材料采购/标段
+https://www.chinapipe.net/project/d3077478.html</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>重庆市, 管材, 招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>四川省华蓥市重点采煤沉陷区华蓥市高兴镇城镇危旧房改造项目(三期)施工一标段招标公告</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>市政公用工程施工</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>改造城镇危旧房约4.5万平方米，户数共220户，3栋共9个单元。配套小区内道路、供水、供电、供气主管网、消防、路灯等基础设施。新建道四通路与兴政路连接道路64米，铺设安置房一期商业街人行道5766平方米，配套完善排水、路灯、绿化等附属设施。</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>项目业主为华蓥市交通投资开发有限责任公司，建设资金来自上级补助和业主自筹（资金来源），项目出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>市政公用工程施工</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>改造城镇危旧房约4.5万平方米，户数共220户，3栋共9个单元。配套小区内道路、供水、供电、供气主管网、消防、路灯等基础设施。新建道四通路与兴政路连接道路64米，铺设安置房一期商业街人行道5766平方米，配套完善排水、路灯、绿化等附属设施。
+https://www.chinapipe.net/project/d3077474.html</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026年绵阳市安州区高标准农田建设项目施工招标公告</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>高标准农田改造提升</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>绵阳市</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>绵阳市</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>本项目包括河清镇高标准改造提升高标准农田3万亩，秀水镇改造提升高标准农田0.6万亩，花荄镇改造提升高标准农田0.3万亩。</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>项目资金来自中央财政资金、地方财政配套资金，出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>高标准农田改造提升</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>本项目包括河清镇高标准改造提升高标准农田3万亩，秀水镇改造提升高标准农田0.6万亩，花荄镇改造提升高标准农田0.3万亩。
+https://www.chinapipe.net/project/d3077437.html</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>金堂县2026年大豆单产提升工程施工招标公告</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>水利设施</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>新建滴灌(喷灌)灌区16处，面积2070亩，配套机井5处、提灌站10处，利用现有供水泵站延伸管道灌溉700亩；新建提灌站5座；新建200m3圆形蓄水池10口，整治原有蓄水池4口；整治原有渠道10公里；购置智能灌溉机器人（车）2台。</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>政府资网金</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>水利设施</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>新建滴灌(喷灌)灌区16处，面积2070亩，配套机井5处、提灌站10处，利用现有供水泵站延伸管道灌溉700亩；新建提灌站5座；新建200m3圆形蓄水池10口，整治原有蓄水池4口；整治原有渠道10公里；购置智能灌溉机器人（车）2台。
+https://www.chinapipe.net/project/d3077434.html</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>金堂县2026年玉米单产提升工程施工招标公告</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>输配水管道，首部枢纽，自动化控制闸阀，中等流量喷枪，快速取水阀，蓄水池，移动式喷灌设备</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>新建输配水管道147.5km，新建首部枢纽21座，田间自动化控制闸阀1474套，中等流量喷枪1349道套、快速取水阀188套，300m3蓄水池2座，移动式喷灌设备10套。</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>政府资金，网项目出资比例为100%</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>输配水管道，首部枢纽，自动化控制闸阀，中等流量喷枪，快速取水阀，蓄水池，移动式喷灌设备</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>新建输配水管道147.5km，新建首部枢纽21座，田间自动化控制闸阀1474套，中等流量喷枪1349道套、快速取水阀188套，300m3蓄水池2座，移动式喷灌设备10套。
+https://www.chinapipe.net/project/d3077433.html</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>80</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>2026年玉米单产提升工程, 输配水管道, 自动化控制闸阀, 蓄水池, 移动式喷灌设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>攀枝花市钒钛高新区金江片区排水防涝能力提升工程施工招标公告</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>排水边沟、排洪沟、雨水调蓄池、智能物联感知设备</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>攀枝花市</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>攀枝花市</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>项目改造金江片区排水防涝管网及设施，主要包含以下内容:（1）改造B*H=600*800排水边沟2238m;（2）改造B*H=1500*2000排洪沟1306道m，B*H=2000*1500排洪沟120m,B*H=2500*3000排洪沟450m，B*H=3500*4000排洪沟2800m，B*H=5000*4000 排洪沟2845mB*H=6000*4000排洪沟545m;（3）排洪沟清淤18484m;排洪涵清淤2500m;（4）改造两座雨水调蓄池，规模为8000t/d和1000t/d;（5）同步布设智能物联感知设备。</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>总投资6920万元</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>排水边沟、排洪沟、雨水调蓄池、智能物联感知设备</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>项目改造金江片区排水防涝管网及设施，主要包含以下内容:（1）改造B*H=600*800排水边沟2238m;（2）改造B*H=1500*2000排洪沟1306道m，B*H=2000*1500排洪沟120m,B*H=2500*3000排洪沟450m，B*H=3500*4000排洪沟2800m，B*H=5000*4000 排洪沟2845mB*H=6000*4000排洪沟545m;（3）排洪沟清淤18484m;排洪涵清淤2500m;（4）改造两座雨水调蓄池，规模为8000t/d和1000t/d;（5）同步布设智能物联感知设备。
+https://www.chinapipe.net/project/d3077430.html</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>中二十四局集团上海电务电化有限公司天眉乐高速公路项目JD3标、JA3标隔离栅、防落物网、防眩板、电缆、光缆及硅芯管询价补遗公告</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>硅芯管</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>乐山市</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>乐山市</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>本次询价采购JD-03包件硅芯管的底色、色谱如下：商序号规格底色添加色标颜色1Φ40/33黑色黑色道2Φ40/33黑色白色1x43Φ40/33黑色黄色1x44Φ40/33黑色蓝色管1x45Φ40/33黑色绿色1x46Φ40/33黑色红色1x47Φ40/33黑色国紫色1x48Φ40/33黑色白色2x39Φ40/33黑色黄色2x310Φ40/33黑色蓝色2x311Φ40/33黑色绿色2x312Φ40/33黑色红色2x313Φ40/33黑色紫色2x314Φ40/33黑色白色3x215Φ40/33黑色黄色3x216Φ40/33黑色蓝色3x217Φ40/33黑色绿色3x218Φ40/33黑色红色3x2</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>项目详细内容无法识别</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>硅芯管</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>本次询价采购JD-03包件硅芯管的底色、色谱如下：商序号规格底色添加色标颜色1Φ40/33黑色黑色道2Φ40/33黑色白色1x43Φ40/33黑色黄色1x44Φ40/33黑色蓝色管1x45Φ40/33黑色绿色1x46Φ40/33黑色红色1x47Φ40/33黑色国紫色1x48Φ40/33黑色白色2x39Φ40/33黑色黄色2x310Φ40/33黑色蓝色2x311Φ40/33黑色绿色2x312Φ40/33黑色红色2x313Φ40/33黑色紫色2x314Φ40/33黑色白色3x215Φ40/33黑色黄色3x216Φ40/33黑色蓝色3x217Φ40/33黑色绿色3x218Φ40/33黑色红色3x2
+https://www.chinapipe.net/project/d3077384.html</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>80</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 近三天, 管材, 招标商机, 项目地区, 项目内容, 资金情况, 产品种类</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>贡井区2026年大豆单产提升工程招标计划</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>智能滴灌系统、蓄水池</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>自贡市</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>自贡市</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>实施建设大豆种植智能滴灌系统2处，共计300亩智能滴灌示范区网，新建蓄水池23座；开展大豆单产提升技术推广。</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>估算总投资14455000.00元</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>智能滴灌系统、蓄水池</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>实施建设大豆种植智能滴灌系统2处，共计300亩智能滴灌示范区网，新建蓄水池23座；开展大豆单产提升技术推广。
+https://www.chinapipe.net/project/d3077426.html</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>隆昌市住房和城乡建设局隆昌市城市核心区南部片区燃气配套管网改造项目焊缝探伤检测采购废标公告</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>焊缝探伤检测服务</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>内江市</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>内江市</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>隆昌市城市核心区南部片区燃气配套管网改造项目焊缝探伤检测采购</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>焊缝探伤检测服务</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>隆昌市城市核心区南部片区燃气配套管网改造项目焊缝探伤检测采购
+https://www.chinapipe.net/project/d3077360.html</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>70</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>燃气配套管网改造, 焊缝探伤检测</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>崇州市三江街道舒桥社区农饮水接水工程(红线外)询比公告</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>崇州市三江街道舒桥社区农饮水接水工程(红线外)询比公告</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>崇州市三江街道舒桥社区农饮水接水工程(红线外)询比公告
+https://www.chinapipe.net/project/d3077281.html</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>四川, 管材招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>华蓥市全域乡村振兴建设项目(一期)21号公路和美乡村建设项目二标段招标公告</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>市政公用工程施工</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>广安市</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>对全市5万亩高标准农田进行提档升级，建设粮油园区3万亩，全域开展农村人居环境整治，打造乡村旅游聚居村落80个，配套建设乡村振兴道路、停车场和标识导视系统等旅游服务设施等。</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>项目业主为华蓥市农业农村局，建设资金来自财政资金及地方专项债券资金，项目出资比例为100%。</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>市政公用工程施工</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>对全市5万亩高标准农田进行提档升级，建设粮油园区3万亩，全域开展农村人居环境整治，打造乡村旅游聚居村落80个，配套建设乡村振兴道路、停车场和标识导视系统等旅游服务设施等。
+https://www.chinapipe.net/project/d3077250.html</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>中铁七局三公司供应链分公司金属波纹管框架询价公告</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>金属波纹管</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>成都市</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>预应力混凝土用金属波纹管</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>金属波纹管</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>预应力混凝土用金属波纹管
+https://www.chinapipe.net/project/d3077249.html</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>布拖县2026年农村生活污水治理项目施工招标公告</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>化粪池、管线</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>凉山彝族自治州</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>凉山彝族自治州</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>新建2m³三道格化粪池584座、3m³三格化粪池1022座、20m³三格化粪池2座、30m³三格化粪池2座，配套建设入户管、支管、干管、检查井、过滤池等。</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>项目资金来自除布拖县2026年中央和省级财政常态化帮扶资金外的其他渠道，不足部分由业主多渠道筹集。</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>化粪池、管线</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>新建2m³三道格化粪池584座、3m³三格化粪池1022座、20m³三格化粪池2座、30m³三格化粪池2座，配套建设入户管、支管、干管、检查井、过滤池等。
+https://www.chinapipe.net/project/d3077246.html</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>80</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>农村生活污水治理, 化粪池, 管线</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>凉山州·西昌市特殊教育学校学前教育教学楼改扩建项目招标计划</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>网房屋建筑工程</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>凉山彝族自治州</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>凉山彝族自治州</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>本项目总规划用地面积为6665.90平方米，总建筑面积约10823.11平方米（其中已建建筑面积4519.92平方米，本次项目建筑面积6303.19平方米），项目总体包含新建1座地下车库及1栋学前教育教学楼和1栋大门，其中地上建筑面积4601.97平方米（学前教育教学楼和大门）；地下建筑面积1701.22平方米（包括地下车库、人防地下室、设备用房等）；改造教学楼及宿舍面积约4519.92平方米（含建筑外墙改造及消防管网改造）；绿化面积约2473.01平方米；道路及广场用地约1814.05平方米；400米室外消防给水管网、200米生活给水管网、400米室外污水管网、400米室外雨水管网、220米室外强电管网、220米室外弱电管网、1个混凝土格栅池等。</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>估算总投资35177600.00元</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>网房屋建筑工程</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>本项目总规划用地面积为6665.90平方米，总建筑面积约10823.11平方米（其中已建建筑面积4519.92平方米，本次项目建筑面积6303.19平方米），项目总体包含新建1座地下车库及1栋学前教育教学楼和1栋大门，其中地上建筑面积4601.97平方米（学前教育教学楼和大门）；地下建筑面积1701.22平方米（包括地下车库、人防地下室、设备用房等）；改造教学楼及宿舍面积约4519.92平方米（含建筑外墙改造及消防管网改造）；绿化面积约2473.01平方米；道路及广场用地约1814.05平方米；400米室外消防给水管网、200米生活给水管网、400米室外污水管网、400米室外雨水管网、220米室外强电管网、220米室外弱电管网、1个混凝土格栅池等。
+https://www.chinapipe.net/project/d3077244.html</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>80</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>凉山州, 特殊教育学校, 学前教育教学楼, 改扩建项目, 施工, 管材招标</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>东河(苍溪段)流域水污染治理工程招标计划</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>市政基础设施工程</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>新建污水收集主支管网34.48km、污水入户管64.87km；对现有1座300m³/d污水处理站进行改扩建，将污水处理能力提升至500m³/d；新建污水资源化利用设施3套、视频监控系统9套、水质监测网络1套、水环境风险预警网络1套、监控平台1套；新建150m³/d污水处理站2座、200m³/d污水处理站1座、700m³/d污水处理站1座、化粪池1座、污水提升泵站11座、标志牌9块。</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>估算总投资69670300元</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>市政基础设施工程</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>新建污水收集主支管网34.48km、污水入户管64.87km；对现有1座300m³/d污水处理站进行改扩建，将污水处理能力提升至500m³/d；新建污水资源化利用设施3套、视频监控系统9套、水质监测网络1套、水环境风险预警网络1套、监控平台1套；新建150m³/d污水处理站2座、200m³/d污水处理站1座、700m³/d污水处理站1座、化粪池1座、污水提升泵站11座、标志牌9块。
+https://www.chinapipe.net/project/d3077243.html</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>苍溪县构溪河流域水生态保护修复工程项目招标计划</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>市政基础设施工程</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>广元市</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>新建生态缓冲带23597.6m2；新建底质改良及微地形改造面积约112287m2、新建挺水植物面 招标项目概积22457.4m2、沉水植物面积56143.5m2、浮叶植物面积11228.7m2、网鱼蚌螺修复区面积44914.8m2； 新建生态沟渠1858m，新建污水收集主支管1.6km、入户管1.2km。</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>估算总投资 27726700 元</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>市政基础设施工程</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>新建生态缓冲带23597.6m2；新建底质改良及微地形改造面积约112287m2、新建挺水植物面 招标项目概积22457.4m2、沉水植物面积56143.5m2、浮叶植物面积11228.7m2、网鱼蚌螺修复区面积44914.8m2； 新建生态沟渠1858m，新建污水收集主支管1.6km、入户管1.2km。
+https://www.chinapipe.net/project/d3077240.html</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>开江县2026年大豆单产提升工程项目招标计划</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>大豆单产提升工程</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>达州市</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>达州市</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>建设大豆单产提升工程示范区3万亩，其中核心区-水肥一体化滴网灌工程1750亩、辐射区-水源工程28250亩。</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>估算总投资14500000元</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>大豆单产提升工程</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>建设大豆单产提升工程示范区3万亩，其中核心区-水肥一体化滴网灌工程1750亩、辐射区-水源工程28250亩。
+https://www.chinapipe.net/project/d3077175.html</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>80</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>2026年, 大豆单产提升工程, 招标计划, 四川, 管材</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>中国铁路成都局集团有限公司成铁总承包公司隆昌市石盘滩大型灌区提升改造项目管道下穿成渝铁路、成渝高铁项目钢筋混凝土管采购流标公告</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>管材网线索</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>钢筋混凝土管</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>内江市</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>内江市</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>钢筋混凝土管采购</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>原文未提及</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>钢筋混凝土管</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>钢筋混凝土管采购
+https://www.chinapipe.net/project/d3077107.html</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>80</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>重庆, 四川, 管材招标, 商机</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/site/matches.xlsx
+++ b/site/matches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>城口县东部片区污水管网建设项目招标计划</t>
+          <t>肖家河污水厂两江新区范围配套污水管网整治工程施工答疑补遗文件</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,50 +525,47 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>城口县</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>项目新建污水收集管网20.6km，管道修复11.2km，修复结构性缺陷136处，错混漏接点整治52处；主要建设内容包括排污口改造40处，配套建设检查井420个；沿河岸线修复及生态净化植物约10000㎡，以及其他污水处理设施等。</t>
+          <t>肖家河污水厂两江新区范围配套污水管网整治工程</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>合同预估金额为6500万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>污水管网、管道、检查井、生态净化植物</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>城口县东部片区污水管网建设项目招标计划 项目名称 城口县东部片区污水管网建设项目 招标法人或 招标人名称 城口县城乡环境管理服务中心 （盖章） 项目批准文 件及文号 项目新建污水收集管网20.6km，管道修复11.2km，修复结构性缺网陷136处，错混漏接点整治52处； 主要建设内 排污口改造40处，配套建设检查井420个；沿河岸线修复及生态净化植物约10000㎡，以及其他污 容 水处理设施等 招标项目 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 名称 式 务划发布时间 场所 (万元) 项目新建污水收集管 网20.6km，管道修 复11.2km，修复结构性缺 城口县东 商 城口县 招标项目 陷136处，错混漏接点整 部片区污 公开招 公共资 1 治52处；排污口改造40处， 2026-09 6500.00 水管网建 标 源交易 配套建设检查井420个； 设项目 中心 沿河岸线修复及生态净化 道 植物约10000㎡，以及其他 污水处理设施等 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net管/project/d3079712.html cqdingjiu 2026.08.25 14:22:26 国 中</t>
+          <t>肖家河污水厂两江新区范围配套污水管网整治工程施工答疑补遗文件 各潜在投标人： 现将肖家河污水厂两江新区范围配套污水管网整治工程施工招标答疑发布如下： 一、答疑部分 问题一：1、我公司于2026年进行了优势合并整合，现准备使用合并前公司项目业绩作为本次我司投标的投标人 业绩证明，并提供上级主管单位出具的相关吸收合并文件或两家公司签订的吸收网合并协议，请问是否可视为满 足招标业绩要求？ 2、我单位为中型企业，其控股股东为大企业，但我单位不属于大企业的分支机构，也不存在与大企业的负责人 为同一人的情形。鉴于此种情况，我单位应提供《中小企业声明函（工程类）》还是《中小企业承担合同份额 务 承诺函》？ 回复：1、满足，但还需满足招标文件对业绩的其他要求。最终由评标委员会根据投标人提供的证明材料并结合 招标文件要求进行评审。 商 2、贵司其控股股东为大企业，故需提供中小企业承担合同份额承诺函。 道 问题二：本项目有无业主专家参与评标？ 回复：本项目评标委员会由招标人按法律法规及相关规定依法组建。 管 问题三：1、财务报告可以不提供财务报表附注吗? 2、投标函附录中，工国期、分包、工程质量、缺陷责任期等要求可以统一填写"达到招标文件要求"吗? 3、招标文件第八章投标文件格式中(二)承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要提供其 他格式之外的其他承诺? 中 4、是否有业代专家参与评标，不要模糊的回答什么依法组建评标委员会。请明确回复有或者没有。 5、本项目是否异地评标？ 6、业绩竣工验收证明材料中有单位盖的项目部章是否认可呢？ 回复：1、可以不提供财务报表附注。 2、可以统一填写"达到招标文件要求"。 3、本项目招标文件中要求的承诺已在投标文件格式“资格审查部分”的“(二)承诺”中集中编制，投标人若有 其他承诺，请自行考虑。 4、本项目评标委员会由招标人按法律法规及相关规定依法组建。 5、本项目采用异地评标。 6、业绩竣工验收证明材料盖项目部章不予认可。 问题四：请问xxxx现在被人民法院列为被执行人且有1000多万股权冻结到2028年，因为不能履行保函的见索即付， 拒绝赔付。 相关业主方在招标文件补遗通知中直接将xxxx列入担保公司回避名单，拒绝xxxx所出具的保函。由此可见xxxx的 信用资质、履约能力、根本无能力是存在很大问题的。请问以xxxx目前的被执行和不履行投标担保责任的情况是 否符合招标文件的要求? 回复：纸质投标保函的开立人应当是具有相应资格的银行、保险机构、融资担保公司，其信用资质、履约能力、 担保能力、赔付流程、安全保密等应符合工程保函业务条件。纸质投标保函应合法合规，符合招投标行政监督 部门、行业主管部门和金融监管部门的相关规定，满足招标文件约定要求。投标人应选择在渝依法设立总部或 者设有分支机构的金融机构开具纸质投标保函。投标人对所提交的纸质投标保函的真实性、合法性、有效性负 责。以纸质投标保函形式交纳投标保证金是否符合招标文件要求，由评标委员会评标时，根据招标文件要求进 行独立评审，并作出相应评审判断。 网 问题五：我公司业绩合同金额3800万元及以上，但是竣工报告业绩金额小于3800万元，请问是否满足业绩要求？ 务 回复：招标文件已明确当业绩证明材料中针对同一指标存在不一致时，以工程竣工验收合格的证明材料为准。 故竣工报告业绩金额小于3800万元不满足业绩要求。 商 问题六：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需 要提供其他格式之外的其他承诺？ 道 回复：本项目招标文件中要求的承诺已在投标文件格式“资格审查部分”的“(二)承诺”中集中编制，投标人若 有其他承诺，请自行考虑。 管 问题七：专业分包业绩满足业绩要求吗？ 回复：满足，但还需满国足招标文件对业绩的其他要求。 中 问题八：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 回复：若招标文件中第八章的投标文件格式与新点制作软件中格式有不一致的情况，则应以加盖电子印章的招 标文件（即PDF版）为准（除新点制作软件自动生成无法修改的外），其新点制作软件中的格式是为方便投标人 编制投标文件使用。 问题九：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可 以不填(空白)，对此有无要求？ 回复：均可未作要求，由投标人自行考虑。 问题十：乡、镇供水厂及供水管道业绩满足业绩要求吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。 问题十一：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知 书发出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予 提前注销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 回复：纸质投标保函原件上未加盖“正本”字样的，不因此否决投标，但投标人应确保提交的保函为唯一正本。 若因保函真伪问题导致的一切不利后果由投标人自行承担。 问题十二：1.老旧小区室外环境改造业绩满足吗？ 网 回复：不满足。 2.自来水厂或者净水厂施工业绩满足业绩要求吗？ 务 回复：满足，但还需满足招标文件对业绩的其他要求。 3.污水处理厂提标改造施工业绩满足吗？ 回复：满足，但还需满足招标文件对业绩的其他要求。商 4.市政桥梁施工业绩符合吗？ 道 回复：满足，但还需满足招标文件对业绩的其他要求。 管 5. 公园施工业绩满足吗？ 回复：公园概念过于宽泛，无法判定该施工业绩是否属于市政工程，请投标人自行核实，并按招标文件要求提 供业绩证明材料，其是国否满足要求应由评标委员会根据证明材料具体内容进行判定。 问题十三：任一清单的综合单价低于警戒线，就要提供说明吗？ 中 回复：本项目未对工程量清单综合单价作出异常低价警戒线要求。 问题十四：财政部 国务院国资委 金融监管总局2023年9月14日发布的《关于加强审计报告查验工作的通知》 中要求会计师事务所应当按照规定将其承办《中华人民共和国注册会计师法》第十四条规定审计业务出具的报告 （以下简称审计报告）上传注册会计师行业统一监管平台（以下简称统一监管平台）并申请赋码。本项目投标 人提供的财务报告需要赋码和提供深度查询截图吗？ 回复：投标人提供的财务报告不需要赋码和提供深度查询截图。 问题十五：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 回复：根据招标文件“投标人的工程量清单单项报价不得为零报价（招标人提供的工程量清单单项最高限价中 金额为零的除外）或者负数报价”，招标人提供的工程量清单单项最高限价中金额为零的，该项清单综合单价 报价可以为0。 问题十六：有人提出一个无关问题。 回复：无关问题不予回复。 问题十七：业绩要求的竣工时间是指竣工验收时间吗？ 回复：本项目业绩要求所指竣工时间，即为工程竣工验收合格证明载明的竣工验收时间。 问题十八：本项目是异地评标吗？ 网 回复：本项目是异地评标。 务 问题十九：我公司业绩为三个项目合并招标，三个项目合起来满足业绩要求，但分别签了三个合同和分别验收， 请问我公司业绩满足业绩要求吗？ 回复：不满足。 商 问题二十： 道 1.财务报告可以只提供审计报告、现金流量表、资产负债表、利润表吗？ 回复：按照招标文件要求“提供：会计师事务所或审计机构出具的合法有效的财务审计报告及财务报表，财务 管 报表须至少包括现金流量表、资产负债表、利润表”。 2.投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 回复：可以填“达到招国标文件的要求”。 3.现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险证明材 料复印件递交吗？ 中 回复：递交纸质保函原件无需提供投标单位授权委托书及本人身份证明。 4.有人提出一个无关问题 回复：无关问题不予回复。 问题二十一：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、 注册证及在本单位注册的证明文件替代？ 回复：退休人员不符合本项目对投标人相关人员的要求，必须按招标文件要求提供相关人员的养老保险证明。 问题二十二：我公司业绩为epc业绩，我公司与设计单位组成联合体承接，竣工验收报告中施工单位盖章由我公 司盖章，请问需要提供联合体协议书吗？ 回复：若投标人提供的公司业绩为epc业绩，且合同协议书或工程竣工验收合格的证明材料或业主证明能证明该 投标人承担的工作为施工任务的，则不需要提供联合体协议书；若投标人提供的公司业绩为epc业绩，但合同协 议书或工程竣工验收合格的证明材料或业主证明不能证明该投标人承担的工作为施工任务的，则需要提供联合 体协议书。 问题二十三：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗？ 回复：投标人投标总报价低于招标文件规定的对应的异常低价警戒线的，应提供报价合理性说明，并提供必要 的证明材料。证明材料由投标人自行提供，但提供的说明不得降低或者改变原设计方案、技术工艺、施工标准， 不得影响项目的质量、安全、工期、结算等正常履约。 问题二十四：有人提出一个无关问题。 回复：无关问题不予回复。 网 务 招标人：重庆水务环境控股集团管网有限公司 商 招标代理机构：重庆市投资咨询有限公司 2026年8月26日 道 信息来源:https://www.chinapipe.net/project/d3081038.html 管 cqdingjiu 2026.08.26 17:19:19 国 中</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>项目新建污水收集管网20.6km，管道修复11.2km，修复结构性缺陷136处，错混漏接点整治52处；主要建设内容包括排污口改造40处，配套建设检查井420个；沿河岸线修复及生态净化植物约10000㎡，以及其他污水处理设施等。
-https://www.chinapipe.net/project/d3079712.html</t>
+          <t>肖家河污水厂两江新区范围配套污水管网整治工程
+合计金额（元）：原文未提及
+https://www.chinapipe.net/project/d3081038.html</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>污水管网, 新建, 修复, 生态净化</t>
+          <t>肖家河污水厂, 两江新区, 配套污水管网整治工程</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>城口县高观及修齐片区污水管网建设项目招标计划</t>
+          <t>重庆市潼南区提升农村饮水质量工程(潼南区农村供水保障工程)第二批勘察设计答疑补遗文件</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -599,48 +596,49 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>城口县</t>
+          <t>潼南区</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>在城口县高观及修齐片区新建污水管网25.5公里，改造污水管网6.7公里。主要建设内容：新建DN300污水管网9.5公里，新建DN400污水管网8.2公里，新建DN500污水管网7.8公里；改造DN300污水管网3.8公里，改造DN400污水管网2.9公里，以及建设务检查井、沉砂池等配套设施。</t>
+          <t>本项目涉及农村供水保障工程的勘察设计工作。</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>合同预估金额2800万元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>DN300、DN400、DN500污水管网</t>
+          <t>勘察设计服务</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>城口县高观及修齐片区污水管网建设项目招标计划 项目名称 城口县高观及修齐片区污水管网建设项目 招标法人 或招标人 城口县城乡环境管理服务中心 名称（盖 章） 项目批准 文件及文 网 号 在城口县高观及修齐片区新建污水管网25.5公里，改造污水管网6.7公里。主要建设内容：新 主要建设 建DN300污水管网9.5公里，新建DN400污水管网8.2公里，新建DN500污水管网7.8公里；改造DN300 内容 污水管网3.8公里，改造DN400污水管网2.9公里，以及建设务检查井、沉砂池等配套设施。项目实施后， 消除管网空白区5.5平方公里，完善城镇污水收集管网，提高生活污水集中收集率20%。 招标项目 招标方 招标文件计 拟交易 合同预估金额 序号 招标内容 备注 名称 式 划发布时间 场所 (万元) 商 在城口县高观及修齐片区新建 污水管网25.5公里，改造污水 管网6.7公里。主要建设内容： 新建DN300污水管网9.5公里， 道 城口县高 新建DN400污水管网8.2公里， 城口县 招标项目 观及修齐 新建DN500污水管网7.8公里； 公开招 公共资 1 片区污水 改造DN300污水管网3.8公里， 2026-09 2800.00 标 源交易 管网建设 改造DN400污水管网2.9公里， 中心 项目 以及管建设检查井、沉砂池等配 套设施。项目实施后，消除管 网空白区5.5平方公里，完善城 镇污水收集管网，提高生活污 国水集中收集率20%。 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3079710.html 中 cqdingjiu 2026.08.25 14:22:25</t>
+          <t>重庆市潼南区提升农村饮水质量工程(潼南区农村供水保障工程)第二批勘察设计答疑补遗文件 各潜在投标人： 现就对重庆市公共资源交易网发布的《重庆市潼南区提升农村饮水质量工程（潼南区农村供水保障工程）第二 批勘察设计》招标文件作如下补遗： 1、本项目开标时间、投标截止时间及保证金递交截止时间修改为：2026年10月15日9时30 分。 招标人：重庆市潼南区水务（集团）有限公司 网 招标代理机构：重庆精聚达项目管理有限公司 2026年8月26日 务 信息来源:https://www.chinapipe.net/project/d3081033.html cqdingjiu 2026.08.26 17:19:20 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>在城口县高观及修齐片区新建污水管网25.5公里，改造污水管网6.7公里。主要建设内容：新建DN300污水管网9.5公里，新建DN400污水管网8.2公里，新建DN500污水管网7.8公里；改造DN300污水管网3.8公里，改造DN400污水管网2.9公里，以及建设务检查井、沉砂池等配套设施。
-https://www.chinapipe.net/project/d3079710.html</t>
+          <t>本项目涉及农村供水保障工程的勘察设计工作。
+合计金额（元）：原文未提及
+https://www.chinapipe.net/project/d3081033.html</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>高观及修齐片区, 污水管网, 新建, 改造, DN300, DN400, DN500</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026年度井盖、水篦子、波纹管材料供应商采购项目采购公告</t>
+          <t>德感食品示范园配套燃气管道工程随机抽取公告</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -650,7 +648,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -669,46 +667,47 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>江津区</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>采购内容包括球墨铸铁井盖、球墨铸铁水篦子、HDPE双壁波纹管等，合同期限为自签订之日起一年或累计采购金额达到预算采购总价，达到任一条件即合同终止。</t>
+          <t>本项目为江津德感食品示范园安装燃气管道和相关设备，包括燃气管道系统、调务压系统。</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>资金来源为公司自筹，预算总金额为48万元。</t>
+          <t>业主自筹，项目出资比例为100%。</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>球墨铸铁井盖、球墨铸铁水篦子、HDPE双壁波纹管</t>
+          <t>燃气管道及相关设备</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026年度井盖、水篦子、波纹管材料供应商采购项目采购公告 一、采购条件 本采购项目2026年度井盖、水篦子、波纹管材料供应商采购项目已由公司内部决策程序批准实施，采购人为重庆 远达城市运营服务有限公司。项目已具备采购条件，现采用询价方式邀请合格的供应商参加报价。 二、项目概况与采购内容 （一）项目名称：2026年度井盖、水篦子、波纹管材料供应商采购项目 网 （二）采购内容： 1.采购内容：球墨铸铁井盖、球墨铸铁水篦子、HDPE双壁波纹管等，具体规格型号及限价详见第三章《采购需 务 求》及限价清单； 2.合同期限：自签订之日起一年或累计采购金额达到预算采购总价，达到任一条件即合同终止； 3.资金来源：公司自筹，预算总金额为48万元； 商 4.交货地点：重庆市江津区区域内采购人指定地点。 （三）成交供应商数量：本项目最多确定2名成道交供应商。成交折扣以折扣报价最低的成交供应商成交折扣为准， 其他成交供应商必须无条件接受折扣报价最低成交供应商的成交折扣，若其他成交供应商不能承诺接受折扣报 价最低成交供应商成交折扣的，采购人有权启用第三名及排名以后的成交候选供应商。每名成交供应商最高结 算金额不超过24万元。 管 （四）采购方式：询价采购。 （五）交货期：根据采购人实际需求分批供货，每批次材料自采购人下达供货通知之日起7日内交付至指定地点。 （六）质保期：货物验国收合格之日起12个月。 三、供应商资格要求 （一）具有独立承担民事责任的能力，提供有效的营业执照（副本）、税务登记证（副本）、组织机构代码证 中 （或三证合一的营业执照）。 （二）具有良好的商业信誉和健全的财务会计制度。 （三）具有履行合同所必需的设备和专业技术能力。 （四）有依法缴纳税收和社会保障资金的良好记录。 （五）参加采购活动前三年内，在经营活动中没有重大违法记录。 （六）本项目不接受联合体报价。 （七）法律、行政法规规定的其他条件。 四、采购文件的获取 （一）获取时间：2026年8月25日至8月28日（法定节假日除外），每日上午9:00-11:30，下午14:00-17:00（北京时 间）。 （二）获取地点：重庆远达城市运营服务有限公司市场运营部（地址：重庆市江津区几江滨江中路41幢2楼）。 （三）获取方式：供应商法定代表人或其授权代理人携带单位介绍信原件、身份证复印件及营业执照副本复印件 （加盖公章）现场购买。采购文件售价为人民币200元/份，售后不退。 五、响应文件的提交 （一）提交截止时间：2026年8月31日14时30分（北京时间）。 （二）提交地点：重庆远达城市运营服务有限公司会议室。 （三）逾期送达或未送达指定地点的响应文件，采购人不予受理。 六、询价时间及地点 同响应文件提交截止时间及地点。 网 七、发布公告的媒介 本次采购公告在华信（集团）公司门户网站上发布。 务 八、联系方式 采购人：重庆远达城市运营服务有限公司 商 地 址：重庆市江津区几江滨江中路41幢2楼 联系人：文老师 道 电 话：13452051546 管 2026年8月25日 信息来源:https://www.c国hinapipe.net/project/d3079686.html cqdingjiu 2026.08.25 14:22:26 中</t>
+          <t>德感食品示范园配套燃气管道工程随机抽取公告 一、随机抽取条件 本招标项目为德感食品示范园配套燃气管道工程，业主为重庆津工工贸集团有限公司，建设资金：业主自筹， 项目出资比例为100%。项目已具备招标条件，现对该项目进行随机抽取。 二、项目概况与招标范围 （一）项目概况及发包范围： 网 本项目为江津德感食品示范园安装燃气管道和相关设备，本工程碰口点位于德感工业园区长江三路已建中压A级 燃气管道dn160(阀井后)，碰口点设计压力为0.4MPa，运行压力为0.2~0.3MPa(表压)。气源就近从园区中压燃气管 网接出，新建管道输送至用户调压系统，经调压后新建管道输送至用气点外控制总阀。包括燃气管道系统、调 务 压系统。具体工作内容详见设计图纸和工程量清单。 （二）工期：45日历天。 三、资格要求 商 （一）投标人须同时具备建设行政主管部门核发的市政公用工程施工总承包叁级及以上资质和国家市场监督管 理部门核发有效的《中华人民共和国特种设备生产许可证》，许可项目含公用管道（GB1）安装（含修理、改造） 或有效期内的旧版《特种设备安装改造维修许道可证》（GB1），并在人员、设备、资金、履约能力等方面具有相 应的施工能力； （二）须具备有效的营业执照、组织机构代码证、税务登记证，三证合一的中标人提供载有统一社会信用代码 的营业执照即可。 管 （三）项目经理：投标人拟派的项目经理必须已在投标人本单位注册并应具有相应的执业资格。 注：投标人须提供拟派项目经理建造师注册证、安全生产考核合格证、身份证、投标人为其缴纳的养老 保险证明材料。 国 四、合同价：人民币捌拾肆万玖仟零玖元伍角玖分，小写：¥849009.59元，其中安全文明施工费为31318.56元。 五、随机抽取时间、地点 中 （一）随机抽取公告挂网时间：2026年8月26日至2026年8月28日。 （二）报名资料递交截至时间：2026年8月31日11时00分。 （三）随机抽取开标时间：2026年8月31日11时00分。 （四）报名资料递交地点：重庆市江津区双福新区团结湖大数据智能产业园1号（科创中心）206会议室。 （五）随机抽取时间：报名资料审核结束后1个工作日内按程序随机抽取一家为中标候选单位。 （六）随机抽取地点：重庆市江津区双福新区团结湖大数据智能产业园1号（科创中心）206会议室。 六、联系方式 招标人：重庆津工工贸集团有限公司 联系人：张意 电 话：023-47523112 信息来源:https://www.chinapipe.net/project/d3080872.html cqdingjiu 2026.08.26 17:19:19 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>采购内容包括球墨铸铁井盖、球墨铸铁水篦子、HDPE双壁波纹管等，合同期限为自签订之日起一年或累计采购金额达到预算采购总价，达到任一条件即合同终止。
-https://www.chinapipe.net/project/d3079686.html</t>
+          <t>本项目为江津德感食品示范园安装燃气管道和相关设备，包括燃气管道系统、调务压系统。
+合计金额（元）：业主自筹，项目出资比例为100%。
+https://www.chinapipe.net/project/d3080872.html</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>燃气管道工程, 德感食品示范园, 江津</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>阀门产业园(管网改造)项目答疑补遗文件</t>
+          <t>西部(重庆)科学城西三镇老旧小区改造项目—东鹏周边配套(新乾路)污水管网维修工程答疑补遗文件</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -740,43 +739,44 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>管网改造</t>
+          <t>西部(重庆)科学城西三镇老旧小区改造项目—东鹏周边配套(新乾路)污水管网维修工程答疑补遗文件</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>本项目总报价最高限价为3367204.11元；安全文明施工费暂定77805.78元；本项目措施费总额报价最高限价227611.68元。</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>阀门</t>
+          <t>气囊封堵,紫外线修复,内衬钢圈修复,内衬钢套筒修复,压顶升顶复位,检查井改造</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>阀门产业园(管网改造)项目答疑补遗文件 各潜在投标人： 现对《阀门产业园（管网改造）项目》招标文件作如下答疑： 问题1：请问重庆市双业融资担保有限公司现在被人民法院列为被执行人且有1000多万股权冻结到2028年，目前 查出双业融资担保多条被执行案件，都是因为不能履行保函的见索即付，拒绝赔付。相关业主方在招标文件补 遗通知中直接将重庆双业融资担保有限公司列入担保公司回避名单，拒绝重庆双业融资担保有限公司所出具的 保函。由此可见重庆双业融资担保有限公司的信用资质、履约能力、根本无能力网是存在很大问题的。请问以重 庆双业融资担保有限公司目前的被执行和不履行投标担保责任的情况是否符合招标文件的要求？ 答：投标保函应合法合规，符合招投标行政监督部门、行业主管部门和金融监管部门的相关规定，并满足招标 文件要求。 务 问题2：任一清单的综合单价低于警戒线，就要提供说明吗？ 答：任一清单综合单价报价低于招标文件规定的对应的异常低价警戒线的，应提供报价合理性说明，并提供必 要的证明材料。 商 问题3：投标文件格式中下划线上、空格处、表格中无需要填写或无法填写内容的，是填“/”或“无”还是可以 不填(空白)，对此有无要求？ 道 答：可以填写“/”或“无”。 问题4：请问招标人是否委派业主专家参与评标吗？ 管 答：本项目由招标人按法律法规及相关规定依法组建评标委员会，不委派招标人代表参与评标。 问题5：招标人提供的工程量清单单项最高限价中金额为零的，清单综合单价报价可以为0吗？ 答：投标人的工程量清国单单项报价不得为零报价（招标人提供的工程量清单单项最高限价中金额为零的除外） 或者负数报价。 问题6：本项目是异地评标吗？ 中 答：本项目是远程异地评标。 问题7：投标人投标总报价或者部分单项报价低于招标文件规定的对应的异常低价警戒线的，投标人未提供报价 合理性说明或者提供的说明不能证明其报价合理性的，由评标委员会作否决投标处理。部分单项报价是指单项 工程的合价低于警戒线提供合理说明还是清单综合单价低于警戒线提供合理说明呢？ 答：投标总报价或任一清单综合单价报价低于招标文件规定的对应的异常低价警戒线的，应提供报价合理性说 明，并提供必要的证明材料。 问题8：投标函中的缺陷责任期可以填“达到招标文件的要求”吗？ 答：可以。 问题9：有没有人行贿专家，有的话我们就不参加了。 答：本项目面向社会公平、公正、公开招标，欢迎社会各界的监督。 问题10：招标人应当在法定时间内确定中标人。招标人或者招标投标交易场所运行服务机构应当在中标通知书发 出后 5 日内，向除中标人以外的其他投标人退还纸质投标保函正本，并书面通知相关金融机构本项目准予提前 注销纸质投标保函。具体注销事宜由投标人与金融机构协商。保函原件上需要加盖正本吗？ 答：纸质保函原件上需要加盖正本。 问题11：招标文件第八章投标文件格式中（二）承诺部分是否包含招标文件要求的所有承诺，投标人是否还需要 提供其他格式之外的其他承诺？ 答：招标文件第八章投标文件格式中（二）承诺部分包含了招标文件所要求的承诺，投标人可根据自身情况提 供格式之外的其他承诺。 问题12：现场递交纸质保函原件是否需要本项目投标人须知前附表中要求的委托代理人持授权委托书和养老保险 证明材料复印件递交吗？ 答：不需要。 网 问题13：请问投标文件制作系统软件导出的电子投标文件格式与加盖公章的招标文件PDF文件中的投标文件格式 不一致的以哪个为准？ 答：以投标文件制作系统软件导出的电子投标文件格式为准。 务 问题14：在职的已退休的注册人员，其社保局出具的养老证明已无法提供，该类人员是否可以用退休证、注册证 及在本单位注册的证明文件替代？ 答：若确认该人员已依法办理退休手续，与任何单位均不商存在全日制劳动关系，不涉及社会保险双重缴纳或劳 动关系冲突，且与投标人单位“退休返聘人员”的身份具有合法性，其从业资格有效性能保障项目履约。可同 时提供以下证明材料替代： （1）《退休证》或《退休审批表》原件扫描道件 （2）身份证原件扫描件 （3）有效的执业注册证书及在本单位的注册证明材料（如注册系统截图、注册变更记录等） 管 （4）投标单位与该人员签订的《退休返聘协议》或《劳务合同》原件扫描件 （5）该人员签署的《承诺书》，内容包括但不仅限于: 国 ① 承诺其已从[原单位名称]正式退休，退休时间为[XXXX年XX月]。 ② 承诺与原单位及任何其他单位均不存在全日制劳动关系及社保冲突。 中 ③ 承诺所提供的所有替代证明材料真实、有效，如有虚假，愿意承担由此引起的一切法律责任，包括但不限 于投标（中标）无效、列入失信名单等。 问题15：可以用自己做的材料购买协议、劳务协议、设备租赁协议作为低价说明证明材料吗？ 答：报价合理性说明提供的证明材料，须具有相关性，有效性，真实性，合法性，请各潜在投标人结合招标文 件要求，自行考虑。 问题16：现在除了没有警戒线和技术方案的低价项目评标专家不被围猎，哪个项目不围猎评标专家，请问招标人 如何保证公平？ 答：本项目面向社会公平、公正、公开招标，欢迎社会各界的监督。 问题17：投标函附录中，工期、分包和工程质量要求对应的约定内容，可以统一填写“达到招标文件要求”吗？ 答：可以。 备注：已发出的招标文件若与本次发布的答疑通知内容有不一致的地方，以本次发布的答疑通知内容为准，不 管下载与否都视为潜在投标人全部知晓有关招投标过程和全部内容。 招标人：垫江县丹香建设有限公司 招标代理机构：重庆博钰大数据科技有限公司 2026年8月24日 信息来源:https://www.chinapipe.net/project/d3079610.html cqdingjiu 2026.08.25 14:22:26 网 务 商 道 管 国 中</t>
+          <t>西部(重庆)科学城西三镇老旧小区改造项目—东鹏周边配套(新乾路)污水管网维修工程答疑补遗文件 西部（重庆）科学城西三镇老旧小区改造项目—东鹏周边配套（新乾路）污水管网维修工程答疑补遗文件 各潜在投标人： 现将“西部（重庆）科学城西三镇老旧小区改造项目—东鹏周边配套（新乾路）污水管网维修工程(二期)施工总 承包项目”的答疑、补遗如下： 网 一、答疑部分： 问题1：提问1：根据招标工程量清单内 第二章管道修复工程 2.3.2管道修复方案 ，其中W42-4-W42-3 DN400,缺 务 陷名称：破裂 ； 缺陷位置：13.7m环向0911，缺陷等级：3级，修复方案为整段修复，CIPP紫外光固化修 复；W42-5-W42-6 DN400,缺陷名称：破裂 ； 缺陷位置：18.0m环向1101；缺陷等级：3级、修复方案为整段修复， CIPP紫外光固化修复；WD-143-WD-144,DN800,缺陷名称：变形 ； 缺陷位置：4.5m环向0000，级：4级，修复方 案为整段修复，CIPP紫外光固化修复，根据规范依据：CJJ/T2102014《城镇排水管道非开挖修复更新工程技术 规程》、CJJ1812012《城镇排水管道检测与评估技术规程商》管道缺陷等级：1 级（轻微）、2 级（中等）、3 级 （严重）、4 级（重大 / 坍塌风险），其中破裂（PL）缺陷达到3 级为比较严重，必须先局部预处理（点状 / 双胀 环加固破损点位），预处理完成后方可整体紫外光固化，不能把碎块直接包在内衬里面，不能直接上 UV；缺陷 等级为4 级是重大缺陷了，优先开挖换管；局部坍塌段要切除更换，再做 UV 固化其余管段；变形（BX）缺陷， 缺陷等级4 级为重大缺陷，变形率＞30%，断面道压扁严重，整圆难度大，优先开挖更换管道，不宜 直接UV 固化。 以上请招标方变更设计。 答复：详见本次补遗。 管 问题2：本项目有无业主专家参与评标？ 答复：由招标人依法组国建评标委员会。 问题3：单位业绩为专业分包业绩是否满足本项目业绩要求？ 中 答复：不满足。 问题4：本项目属于市政工程项目，业绩要求能否改成市政工程业绩？ 答复：本项目专业性较强，对请按照比价文件提供相关业绩。 问题5：根据《中华人民共和国招标投标法》第二十四条的规定，依法必须进行招标的项目，自招标文件开始发 出之日起至投标人提交投标文件截止之日止，最短不得少于20日。这一规定确保了投标人有足够的时间来准备和 提交投标文件。请问招标人，依法公开招标的项目，发布招文到截止投标仅仅4天，是想控标吗 答复：本项目为公开比价项目且自主招标，请按照比价文件要求的时间进行投标。 问题6：图纸不全，只有局部树脂非开挖大样图呢，请补充 答复：详见本次补遗。 问题7：一个总承包合同中包含的市政排水管网业绩如果大于招标文件要求要求的金额，该业绩满足吗 答复：按照比价文件要求执行。 问题8：招标文件施工图就一张非开挖修复大样图，没有平面图和其他图纸与设计说明，无法进行现场调查及核 对工程量，请提供详细施工图纸。 网 答复：详见本次补遗。 务 问题9：本项目每项清单最高限价能否发一下 答复：详见本次补遗。 商 问题10：不公布最高限价吗 答复：详见本次补遗。 道 二、补遗部分： 管 补遗1：工程量清单以本次答疑、补遗文件发布的附件为准。 补遗2： 国 本项目总报价最高限价：3367204.11元；安全文明施工费暂定77805.78元；本项目措施费总额报价最高限 价227611.68元。 本项目总报价异常低价警戒线：2862123.49元。 中 主要单项报价异常低价警戒线具体详见下表: 计量 综合单价最高 单项报价异常低 序号 项目编码 项目名称 单位 限价(元) 价警线(元) 1 04B038 气囊封堵 管径400mm 处 919.61 781.67 2 04B039 气囊封堵 管径800mm 处 1268.58 1078.29 3 04B040 污水管网质保期满机器人CCTV电视检查、检测 m 30.77 26.15 4 04B025 8mm厚内衬钢圈修复 管径800mm m 2546.94 2164.90 5 04B023 紫外光固化修复 管径800mm m 2407.94 2046.75 6 040501004008 局部树脂固化法修复 管径800mm 环 3362.19 2857.86 7 04B041 8mm厚内衬（钢套筒）修复 管径800mm m 2562.92 2178.48 8 04B035 5mm厚内衬钢圈修复 管径400mm m 1866.82 1586.80 9 04B031 紫外光固化修复 管径400mm m 1522.56 1294.18 10 040501004010 局部树脂固化法修复 管径400mm 环 2003.1 1702.64 11 04B034 压夜升顶复位 处 878.71 746.90 12 04B042 4mm厚内衬（钢套筒）修复 管径400mm m 1799.71 1529.75 13 040204006002 检查井改造 座 1080.2 918.17 补遗3：补充大样图。 注：所有清单及图纸以本次答疑、补遗为准。以上答疑、补遗内容各潜在投标人在相关网站上注意查阅并下载； 无论查阅或下载与否,均视为已知晓本次招标的全部内容。本补遗内容与招标文件不一致时，以本补遗内容为准。 网 招标人：重庆铝产业开发投资集团有限公司 务 招标代理机构：鼎信项目管理咨询有限公司 2026年8月26日 商 信息来源:https://www.chinapipe.net/project/d3080873.html cqdingjiu 2026.08.26 17:19:19 道 管 国 中</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>管网改造
-https://www.chinapipe.net/project/d3079610.html</t>
+          <t>西部(重庆)科学城西三镇老旧小区改造项目—东鹏周边配套(新乾路)污水管网维修工程答疑补遗文件
+合计金额（元）：本项目总报价最高限价为3367204.11元；安全文明施工费暂定77805.78元；本项目措施费总额报价最高限价227611.68元。
+https://www.chinapipe.net/project/d3080873.html</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>管网改造, 阀门</t>
+          <t>西部(重庆)科学城, 老旧小区改造, 污水管网维修</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>长寿经开区沙溪新市片区污水管网建设项目(新市葛兰污水管网建设部分)一期招标计划</t>
+          <t>两江新区九曲河污水处理厂服务范围配套污水管网整治工程招标计划</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -805,50 +805,47 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>长寿区</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>新市组团内工业污水管网建设：新市组团内建成区新建工业污水管网13.13km，其中重力管总长9.51km，管径DN400-DN800，压力管道总长3.62km，管径DN160-DN400。新增加压提升泵站3座（均为埋地式泵站）：1#泵站每台提升泵站Q=156.7m/h，H=20m，22KW，3用1备；2#泵站每台提升泵站Q=63m/h，H=35m，18.5KW，2用一备；3#泵站每台提升泵站Q=47m/h，H=15m，7.5KW，2用一备。</t>
+          <t>本项目拟对两江新区礼嘉、大竹林、黄茅坪片区进行污水管网改造和修复，改造管径DN300-DN800管道长度约9.4Km；修复管径DN300-DN1000缺陷管道长度约12.8Km，箱涵整治长度约1.0km。</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>项目预算金额为2500万元人民币。</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>工业污水管网建设设备及材料，包括DN400-DN800的重力管和DN160-DN400的压力管道，以及3座埋地式加压提升泵站。</t>
+          <t>污水管网改造和修复</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>长寿经开区沙溪新市片区污水管网建设项目(新市葛兰污水管网建设部分)一期招标计划 项名目称长寿经开区沙溪新市片区污水管网建设项目（新市葛兰污水管网建设部分）一期 招法或标名（章 标人招人称盖） 重庆长寿经济技术开发区开发投资集团有限公司 项批文及号 目准件文长发改经[2025]2号 主建内 要设容（1）新市组团内工业污水管网建设：新市组团内建成区新建工业污水管网13.13km，其中重力管总长9.51km，管径DN400-DN800，压力管道总长3.62km，管径DN160-DN400。新增加压提升泵站3座（均为埋地式泵站）：1#泵站每台提升泵站Q=156.7m/h，H=20m，22KW，3用1备；2#泵站每台提升泵站Q=63m/h，H=35m，18.5KW，2用一备；3#泵站每台提升泵站Q=47m/h，H=15m，7.5KW，2用一备。组团内工业污水正常情况下通过加压提升泵站转输至沿河DN500压力管道；应急情况下工况转输至污水应急处理池。 序号 招项名 标目称招标内容 招标方式 招件发间 标计布划文 时 拟交易场所 合估额元 同金()万 预备注 招项标目 1 长经区溪市区水网设（市兰水网设分一 项 寿开沙新片污管建 新葛污管建部）期 目（（12））新新市市组组团团内、工葛业兰污组水团管监网测建设设备：建新设市：组本团次内设建计成新区建新水建质工检业测污设水备管共网计1331.套13，km其，中其新中市重组力监管测总设长备9.1551套km，，葛管兰径组D团N4监00测-D设N备80106，套压。力 具管体道以总招长标3.人62发km布，的管施径工D图N1的60工-D程N量40清0。单新、增设加计压交提底升、泵招站标3座文（件均、为招埋标地文式件泵补站遗）、：答1疑#泵、站澄每清台中提补升充泵的站全Q部=工15程6.7内m容/h为，准H=。20m，22KW，3用1备；2#泵站每台提升泵站Q=63m/h，H=35m，18.5KW，2用一备；3#泵站每台提升泵站Q=47m/h，H=15m 网 ，7.5KW，2用一备。组团内工业污水正常情况下通过加压提升泵站转输至沿河DN500压力管道；应急情况下工况转输至污水应急处理池。 公开招标 2026-09 重庆市公共资源交易中心长寿分中心 2500.00 备注本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3079604.html cqdingjiu 2026.08.25 14:22:27 务 商 道 管 国 中</t>
+          <t>两江新区九曲河污水处理厂服务范围配套污水管网整治工程招标计划 项目名称 两江新区九曲河污水处理厂服务范围配套污水管网整治工程 招标法人 或招标人 重庆市城镇排水事务中心（项目业主）、重庆水务环境控股集团管网有限公司（代理业主） 名称（盖 章） 项目批准 文件及文 网 号 主要建设 本项目拟对两江新区礼嘉、大竹林、黄茅坪片区进行污水管网改造和修复，改造管径DN300- 内容 DN800管道长度约9.4Km;修复管径DN300-DN1000缺陷管道长度约12.8Km，箱涵整治长度约1.0km。 招标方务招标文件计 拟交易 合同预估 序号 招标项目名称 招标内容 备注 式 划发布时间 场所 金额(万元) 水质水量检测服务、 两江新区九曲河 测量服务、管道内窥 商 污水处理厂服务 检测、干管内窥检测、 范围配套污水管 管路淤积、探地雷达 重庆市 招标项目 网整治工程水质 检测、排水不畅等原 公开招 公共资 1 2026-09 271.32 水量检测、工程 因的调查；管道的腐 标 源交易 道 测量、精细化排查 蚀、破损、接口错位、 中心 （内窥检测）服 淤积、结垢等运行状 务 况的探测并形成排查 报告。 管 备注 本计划表所列招标项目信息均为暂定，最终以实际招标时的信息为准 信息来源:https://www.chinapipe.net/project/d3080795.html cqdingjiu 2026.08.26 17:19:20 国 中</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>新市组团内工业污水管网建设：新市组团内建成区新建工业污水管网13.13km，其中重力管总长9.51km，管径DN400-DN800，压力管道总长3.62km，管径DN160-DN400。新增加压提升泵站3座（均为埋地式泵站）：1#泵站每台提升泵站Q=156.7m/h，H=20m，22KW，3用1备；2#泵站每台提升泵站Q=63m/h，H=35m，18.5KW，2用一备；3#泵站每台提升泵站Q=47m/h，H=15m，7.5KW，2用一备。
-https://www.chinapipe.net/project/d3079604.html</t>
+          <t>本项目拟对两江新区礼嘉、大竹林、黄茅坪片区进行污水管网改造和修复，改造管径DN300-DN800管道长度约9.4Km；修复管径DN300-DN1000缺陷管道长度约12.8Km，箱涵整治长度约1.0km。
+合计金额（元）：原文未提及
+https://www.chinapipe.net/project/d3080795.html</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>长寿经开区, 沙溪新市片区, 污水管网, 工业污水管网, 加压提升泵站, DN400-DN800, DN160-DN400, 13.13km, 3.62km, 2500万元</t>
+          <t>两江新区, 污水处理厂, 污水管网整治, 管网改造, 修复</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>关于为【涪陵区2026年珍溪镇三角村石牛山果园水肥一体化设施建设项目(可研设计)】公开选取【工程设计】机构的公告</t>
+          <t>重庆市荣昌区盘龙镇人民政府2026年9月政府采购意向-荣昌区盘龙镇高标准农田建设非耕地整改项目</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -858,7 +855,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -879,48 +876,45 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>涪陵区</t>
+          <t>荣昌区</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>该项目为直接选取项目，由采购人从报名的中介服务机构中直接选定一家中介服务机构进行项目服务。</t>
+          <t>荣昌区盘龙镇高标准农田建设非耕地整改项目包括恢复土地类整治4400.9933亩；22.输水管道（PE110000给水管1 1.2255MMPPaaΦΦ220000长度44223300mm；33.改建33.00mm宽混泥土道路22110000mm；44.新建33.00mm宽泥结石道路77006600mm；55.新建22.00mm宽混泥土生产便道22778800mm；66.土壤培肥工程4400.9933亩；77.灌溉与排水设备11套。</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>投资额为121万元人民币。</t>
+          <t>预算金额：380.54万元(人民币)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>工程设计</t>
+          <t>其他建筑工程</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>关于为【涪陵区2026年珍溪镇三角村石牛山果园水肥一体化设施建设项目(可研设计)】公开选取【工程设计】机 构的公告 我单位在重庆市网上中介超市公开选取工程设计中介服务机构，现将相关事项公告如下： 该项目为直接选取项目，由采购人从报名的中介服务机构中直接选定一家中介服务机构进行项目服务。 项目 涪陵区2026年珍溪镇三角村石牛山果园水肥一体化设施建设项目（可研设计） 名称 网 采购 重庆市涪陵区珍溪镇人民政府 人 投资 审批 否 务 项目 工程 建设 投资额（1,210,000.00元） 项目 商 规模 是否 破产 业务 道 否 服务 项目 采购 所需 管 中介 服务 事项 所需 国 服务 工程设计 类型 服务 工程设计 内容 中 中介 机构 资质（资格）要求 要求 资质 （资 格） 乙级 要求 说明 其他 要求 无 说明 服务 时限 按照合同双方自行约定 说明 服务 ￥15000.0元 金额 金额 参照涪财政发[2018]423号文件要求 说明 选取 直接选取 方式 需规 避机 构 规避 原因 选取 2026-08-28 09:00:00 （选取时间到达后不接受报名，建议中介机构至少在选取开始半小时前完成报名。） 时间 网 采购 人业 务咨 重庆市涪陵区珍溪镇人民政府（13709468227） 询电 务 话 商 道 管 国 中 网 务 商 道 采购 管 需求 书下 载 国 中 2026-08-25 信息来源:https://www.chinapipe.net/project/d3079451.html cqdingjiu 2026.08.25 14:22:27 网 务 商 道 管 国 中</t>
+          <t>重庆市荣昌区盘龙镇人民政府2026年9月政府采购意向-荣昌区盘龙镇高标准农田建设非耕地整改项目 荣昌区盘龙镇高标准农田建设非耕地整改项目 项目所在采购意向： 重庆市荣昌区盘龙镇人民政府2026年9月政府采购意向 采购单位： 重庆市荣昌区盘龙镇人民政府 采购项目名称： 荣昌区盘龙镇高标准农田建设非耕地整改项目 网 预算金额： 380.540000万元(人民币) 采购品目： 其他建筑工程 采购需求概况： 标任责 的，任 名合， 称同合 ：签同 荣订签 昌6订0日区 60内日 盘完内 龙工完 镇，工 高2， 标022 准60年2 农 61年 田2月1 建 2底月 设前底 非交前 耕付交 地，付 整逾， 改期逾 项承期 目担承 ；相担 标应相 的违应 数约违 量金约 ：。金 1；；。 标标的的目要标求：：盘盘龙龙镇镇高高标标准准农农田田建建设设；；标标的的数数量量：：11；；标标的的目目标标：：11..恢恢复复地地类类整整治治4400..9933亩亩；；22..输输水水管管道道（（PPEE110000给给水水管管 1 1..2255MMPPaaΦΦ220000长长度度44223300mm;;33..改改建建33..00mm宽宽混混泥泥土土道道路路22110000mm；；44..新新建建33..00mm宽宽泥泥结结石石道道路路77006600mm;;55..新新建建22..00mm宽宽混混泥泥土土生生产产便便道道22778800mm;;66..土土壤壤培培肥肥工工程程4400..9933亩亩;;77..灌灌溉溉与与排排水水设设备备11套套。。；；标标的的要要求求：：本本项项目目生生产产道道路路、、PPEE管管及及设设备备均均须须符符合合国国标标质质量量标标准准，，提提供供PPEE管管检检测测安安装装，，机机组组、、电电器器线线路路设设备备安安装装调调试试服服务务，，严严格格道道路路建建设设质质量量流流程程，，由由供供方方承承担担施施工工安安全全责 预计采购时间： 2026-09 务 备注： 本次公开的采购意向是本单位政府采购工作的初步安排，具体采购项目情况以相关采购公告和采购文件为准。 商 信息来源:https://www.chinapipe.net/project/d3080684.html cqdingjiu 2026.08.26 17:19:20 道 管 国 中</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>该项目为直接选取项目，由采购人从报名的中介服务机构中直接选定一家中介服务机构进行项目服务。
-https://www.chinapipe.net/project/d3079451.html</t>
+          <t>荣昌区盘龙镇高标准农田建设非耕地整改项目包括恢复土地类整治4400.9933亩；22.输水管道（PE110000给水管1 1.2255MMPPaaΦΦ220000长度44223300mm；33.改建33.00mm宽混泥土道路22110000mm；44.新建33.00mm宽泥结石道路77006600mm；55.新建22.00mm宽混泥土生产便道22778800mm；66.土壤培肥工程4400.9933亩；77.灌溉与排水设备11套。
+合计金额（元）：预算金额：380.54万元(人民币)
+https://www.chinapipe.net/project/d3080684.html</t>
         </is>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>未识别到明确匹配关键词</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>成都燃气集团股份有限公司2026年场站、撬站非埋地管道、放散管集中防腐项目变更公告</t>
+          <t>重庆高速巨能建设集团有限公司成渝高速公路改扩建LM02合同段附属材料采购公告</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -930,7 +924,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -945,50 +939,47 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>四川省</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本项目涉及场站、撬站的非埋地管道和放散管的集中防腐工作。</t>
+          <t>重庆高速巨能建设集团有限公司成渝高速公路改扩建LM02合同段附属材料采购项目</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>防腐材料</t>
+          <t>PVC带孔波纹管,PVC横向排水管,PVC排水软管,防渗土工布,透水土工布,玻纤格栅,非织造布,防裂卷材,抗裂贴,养护薄膜,养护土工布</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>成都燃气集团股份有限公司2026年场站、撬站非埋地管道、放散管集中防腐项目变更公告 公告编号：RQBGGG202608250011 本公司于2026年08月11日发布的2026年场站、撬站非埋地管道、放散管集中防腐项目公告（编 号：RQCGXY202606290035），现终止寻源，特此公告！ 网 成都燃气集团股份有限公司 2026-08-25 务 信息来源:https://www.chinapipe.net/project/d3079777.html cqdingjiu 2026.08.25 14:22:27 商 道 管 国 中</t>
+          <t>重庆高速巨能建设集团有限公司成渝高速公路改扩建LM02合同段附属材料采购公告 优选公告 重庆高速巨能建设集团有限公司成渝高速公路改扩建LM02合同段附属材料采购优选公告 根据《采购管理办法》《物资采购管理办法》等有关规定，对重庆高速巨能建设集团有限公司成渝高 速公路改扩建LM02合同段附属材料采购项目进行优选，现将本次采购有关事项通知如下： 一、项目概况 网 （一）供货期限 1000日历天，预计开始时间为2026年8月，具体时间以采购人实际需求时间为准。 务 （二）交货地点 重庆成渝高速公路改扩建LM02合同段各拌合站（重庆大足、永川、荣昌）。 商 二、项目名称：重庆高速巨能建设集团有限公司成渝高速公路改扩建 LM02 合同段附属材料采购项目； 项目编号：CGJH20260804032； 道 标包划分：1个标包； 中选人数：1名。 管 三、采购方式：公开优选 仅限于重庆高速集团物资采购平台：http://113.250.85.222:8099/merchants/login?redirect=%2F 四、优选范围 国 优选范围表 中 序号 物资名称 规格型号 单位 暂定数量 收货地址 重庆成渝高速公路改扩建 LM02合同段各拌合站 1 PVC带孔波纹管 150mm m 2000.00 （重庆大足、永川、荣昌) 2 PVC横向排水管 250mm m 14000.00 3 PVC横向排水管 50mm m 50000.00 4 PVC排水软管 150mm m 40000.00 5 防渗土工布 500g/㎡ ㎡ 340000.00 6 透水土工布 250g/㎡ ㎡ 100000.00 EGA1× 7 玻纤格栅 ㎡ 30000.00 1 (50×50) 8 非织造布 200g/㎡（1m） ㎡ 30000.00 9 防裂卷材 h≥3mm ㎡ 20000.00 10 抗裂贴 h≥3mm ㎡ 2500.00 11 养护薄膜 h≥0.1mm（2*500m） 卷 6400.00 12 养护土工布 200g/㎡ ㎡ 800000.00 备注：1、此采购量为暂定量，结算以现场到货验收合格数量为准。若实际采购量与暂定量存在偏差或因项目原 因终止采购，采购人不承担一切责任。2、采购人不组织现场考察，建议竞选人自行进行现场踏勘，竞选人可以 选择多种运输方式和多种运输线路，竞选人的综合费用不因运输方式和运输线路的变化而调整，竞选人报价时 应将此因素考虑在内。3、优选以合同签订为准，合同签订前所有费用采购人不予承担。 五、竞选人资格 （一）须具备独立法人资格，营业执照有效。经营范围具有建筑材料销售的生产商、代理商或销售商；生产商 注册资金不少于5000万元。（代理商或销售商需提供所代理生产厂家的授权书，营业执照等相关资质文件）； （二）本次采购不接受联合体参选，单位负责人为同一人或者存在控股、管理关网系的不同单位，不得同时参加 竞选，否则，相关竞选均被否决； （三）发票实行一票制，提供税率为3%的增值税专用发票（需提供一份发票截图）； 务 （四）须提供清单中任意一项以上近两年内（2024-2025）省、部级以上专业检测机构出具的带有CMA图章的产 品质量检测报告； （五）须提供清单中任意一项以上交通产品CCPC认证或铁路交通产品CRCC认证证书或ISO系列认证(或同等)证 书； 商 （六）须提供近三年(2023-2025)具备在高速或铁路项目中，单份合同同时供货含有土工布和排水管的，且合同金 额≥300万元的有效业绩2份（合同复印件加盖竞选人公章）。 道 （七）须签订质量承诺书，实行质量终身责任制； （八）竞选人必须为三年内与巨能集团无诉讼纠纷的公司，否则，相关竞选将被否决。 管 （九）竞选人必须为巨能集团集采平台内的合格供应商（状态为：可投标，由现场评选小组核查），否则视为 未参与竞选（高速集团内部单位除外）； （十）竞选人须在国家企业信用信息公示系统或信用中国中未被列入严重违法失信企业名单。 国 六、优选文件的获取 由竞选人在重庆高速集团物资采购平台（http://113.250.85.222:8099/merchants/login?redirect=%2F）下载优选文件电 子版。 中 七、竞选截止时间和地点 （一）电子版竞选文件递交 竞选人须在竞选截止时间2026年8月31日09时30分前，通过登录重庆高速集团物资采购平台 （http://113.250.85.222:8099/merchants/login?redirect=%2F），将签章完善的竞选文件扫描件（多页合并成套PDF格 式），上传至重庆高速集团物资采购平台。 逾期上传的竞选文件，平台自动拒收，线下也不接收。 为方便工作人员统计报价，竞选人须同时上传《竞选报价书》电子版（Excel或Word格式）至平台，此条件不作 为废选条件。 （二）纸质版竞选文件递交 竞选人须在竞选截止时间2026年8月31日09时30分前将签章完善且装订成册的贰份纸质版（正本壹份：鲜章文件， 且须与平台上传的电子版竞选文件一致，副本壹份）竞选文件通过现场递交（提交人需提供授权委托书并出具 身份证，否则不予接收）或邮寄方式提交采购人指定地点（以收到时间为准），逾期拒收，视为未参与竞选。 现场递交地址：重庆市两江新区回兴街道宝圣东路291号巨能集团采购供应中心；邮寄地址：重庆市两江新区回 兴街道宝圣东路291号巨能集团采购供应中心；收件人：李老师，联系电话：15823329133（须本人亲自接收）。 竞选文件须集中装入一个密封袋内，封口处粘贴封条，并在封条的封口处加盖竞选人单位公章（鲜章），“竞 选文件”封袋上写明如下内容： 优选项目名称：重庆高速巨能建设集团有限公司成渝高速公路改扩建 LM02 合同段附属材料采购 竞选人名称： 在2026年8月31日09时30分前不得开启（需加盖竞选人单位公章鲜章）。 （三）竞选人如电子版竞选文件或纸质版竞选文件（缺一项）未提交，则视为未参与竞选。 网 八、开选时间及地点：本次优选将于2026年8月31日09时30分在重庆高速巨能建设集团有限公司开选。 九、监督部门 务 重庆高速巨能建设集团有限公司成本管理部门 监督电话：023-67171350 十、优选单位 商 优选单位：重庆高速巨能建设集团有限公司 地址：重庆市两江新区服装城大道2号 道 优选人联系人：陈老师 18223944912 采购人联系人：周老师 15215170698 管 重庆高速巨能建设集团有限公司 国 2026年8月 供应商应当在投标截止时间前，通过注册供应商账号在重庆高速集团物资采购平台 中 （http://113.250.85.222:8099/merchants/login）上进行报价并将投标文件扫描上传至该平台。 信息来源:https://www.chinapipe.net/project/d3080672.html cqdingjiu 2026.08.26 17:19:20</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>本项目涉及场站、撬站的非埋地管道和放散管的集中防腐工作。
-https://www.chinapipe.net/project/d3079777.html</t>
+          <t>重庆高速巨能建设集团有限公司成渝高速公路改扩建LM02合同段附属材料采购项目
+合计金额（元）：项目详细内容无法识别
+https://www.chinapipe.net/project/d3080672.html</t>
         </is>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>未识别到明确匹配关键词</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>中国电建电建市政公司邛崃市城区污水处理厂及配套管网工程(第一批)设计-施工总承包项目新邛路及现状城市段机械顶管工程采购项目公开询比采购公告</t>
+          <t>2026年8月管材管件采购项目询比公告</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -998,7 +989,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1018,53 +1009,54 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>广安市</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>邛崃市</t>
+          <t>广安市</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>机械顶管工程采购项目</t>
+          <t>不锈钢无缝钢管、碳钢无缝钢管、弯头、等径三通、异径三通、网带颈平焊法兰、法兰盖等一批</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>机械顶管设备</t>
+          <t>管材管件</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>中国电建电建市政公司邛崃市城区污水处理厂及配套管网工程(第一批)设计-施工总承包项目新邛路及现状城市 段机械顶管工程采购项目公开询比采购公告 详见附件。 信息来源:https://www.chinapipe.net/project/d3079765.html cqdingjiu 2026.08.25 14:22:27 网 务 商 道 管 国 中</t>
+          <t>2026年8月管材管件采购项目询比公告 四川能投永立化工有限责任公司拟对“2026年8月管材管件采购项目”组织询比，欢迎符合本项目资格条件的潜 在响应人参与本项目的询比。 一、项目概况 1、项目名称：2026年8月管材管件采购项目 2、采购内容： 不锈钢 无缝钢管、碳钢无缝钢管、弯头、等径三通、异径三通、网带颈平焊法兰、法兰盖等一 批 （详见采购人要求） 3、供货期：合同签订生效后30个日历天内到货。 务 4、供货地点：甲方指定地点。 5. 标段划分：1个标段。 6、质量要求： 符合国家及行业现行合格标准且满足采购商人要求。 二、响应人参加本次询比应具备下列条件 1、一般要求： 道 （1）具有独立承担民事责任的能力； （2）具有良好的商业信誉和健全的财务会计制度； 管 （3）具有履行合同所必须的设备和专业技术能力； （4）具有依法缴纳税收和社会保障资金的良好记录； 国 （5）参加此项询比活动前三年内，在经营活动中没有重大违法记录； （6）法律、行政法规规定的其他条件； 中 2、资格要求：在中华人民共和国境内注册具有独立法人资格的合法企业。 3、业绩要求：2023年1月1日至投标截止时间具有1个已完成或正在供货或新承接的类似项目。类似项目是指:合同 金额为5万元及以上管材管件类似的供货业绩； 4、本项目不接受联合体参加询比。 5、其他要求：无。 三、询比文件发售时间及地点 1、凡有意参加本项目的响应人，请于 2026 年 8 月 27 日登录 四川能源天府阳光采购服务平台 （http://scny.tfygcgfw.com/） 参与项目报名，并按页面指示下载询比文件，采购人（或招标代理机构）不提供 文件获取的其他方式。费用以平台技术服务费为准，售后不退。 2、采购人不提供询比文件获取的其他方式。 特别提醒：响应人须按网页页面指示完成缴纳平台技术服务费并下载询比采购文件， 以完成响应本次采购活动。 四、响应文件的递交截止时间及递交地点 1、电子版响应文件递交的截止时间为 2026年 9月1日15时00 分。 超过截止时间递交的，采购人将拒收。 递交方式如下： （1）电子版由线上递交：各响应单位在递交截止时间前将加盖公章的响应文件电子版发送至邮 箱 ylhg1204@vip.163.com ，主题名为“**单位+2026年8月管材管件采购项目响应文件”，同时响应单位应对响 应文件电子版进行加密，在响应文件递交截止时间后5分钟内，响应单位联系人将电子版文件加密密码发送至采 购联系人； （2）各响应单位在递交截止时间后5个日历天内将加盖公章的响应文件纸质版邮递至采购联系人（纸质版内容须 与电子版内容保持一致） 注:响应文件应为纸质版(签字盖章后)的扫描件。 网 2、逾期递交询比响应文件，采购人不予受理。 3、专家评审以电子版文件为准。 务 五、响应文件开启时间： 同递交响应文件截止时间。 六、发布媒介： 本询比公告在四川能源天府阳光采购服务平台（http://scny.tfygcgfw.com/）上发布。 商 七、 联系方式 采购人（全称）： 四川能投永立化工有限责任公司 道 地 址： 四川省广安市前锋区新桥街道科塔大道南段198号 邮 编： 638000 管 联系人： 李先生 联系电话： 13638371097 电子邮件（E-mail）：国 707453149@qq.com 四川能投永立化工有限责任公司 2026年 8月26日 中 信息来源:https://www.chinapipe.net/project/d3081073.html cqdingjiu 2026.08.26 17:19:21</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>机械顶管工程采购项目
-https://www.chinapipe.net/project/d3079765.html</t>
+          <t>不锈钢无缝钢管、碳钢无缝钢管、弯头、等径三通、异径三通、网带颈平焊法兰、法兰盖等一批
+合计金额（元）：项目详细内容无法识别
+https://www.chinapipe.net/project/d3081073.html</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>管材, 管件, 采购项目</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>广安市前锋区凉水井水厂及管网等配套设施建设项目-管网等配套设施建设项目(一标段)(第二次)项目流标公告</t>
+          <t>苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目(一期)澄清文件</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1074,7 +1066,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1094,38 +1086,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>广安市</t>
+          <t>广元市</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>前锋区</t>
+          <t>苍溪县</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>本项目为广安市前锋区凉水井水厂及管网等配套设施建设项目的管网等配套设施建设部分，具体包括但不限于管道铺设、阀门安装等相关工程。</t>
+          <t>本项目为苍溪县嘉陵江南北侧中心城区的污水管网改造和延伸覆盖工程。</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>最高投标限价为298000元。</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>管网等配套设施</t>
+          <t>排水管道</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>广安市前锋区凉水井水厂及管网等配套设施建设项目-管网等配套设施建设项目(一标段)(第二次)项目流标公告 广安市前锋区凉水井水厂及管网等配套设施建设项目-管网等配套设施建设项目（一标段）（第二次）项目流标 公告 致各投标人： 本项目于2026年08月14日在广安市公共资源交易服务中心开标评标，因本项目评标专家未按照招标文件中规定 的评标办法进行评审，导致评标结果无效，故本项目流标。 网 务 招标人：广安鑫鸿水务有限公司 招标代理机构：中晟川建（成都）工程造价咨询有限责任公司 日期：2026年08月25日 商 信息来源:https://www.chinapipe.net/project/d3079718.html cqdingjiu 2026.08.25 14:22:29 道 管 国 中</t>
+          <t>苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目(一期)澄清文件 苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目（一期）(项目名称)监理 / 标段 补疑书（01号） 致各 潜在投标人： 1、第二章 投标人须知 投标人须知前附表 3.2.4 最高投标限价 398310元 变更为： 3.2.4 最高投标限价 298000元 2、招标文件其余内容不变更，以最新上传得招标文件为准。 苍溪县城市管网事务中心 日 期：2026年8 月26日 信息来源:https://www.chinapipe.net/project/d3081065.html cqdingjiu 2026.08.26 17:19:21 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>本项目为广安市前锋区凉水井水厂及管网等配套设施建设项目的管网等配套设施建设部分，具体包括但不限于管道铺设、阀门安装等相关工程。
-https://www.chinapipe.net/project/d3079718.html</t>
+          <t>本项目为苍溪县嘉陵江南北侧中心城区的污水管网改造和延伸覆盖工程。
+合计金额（元）：最高投标限价为298000元。
+https://www.chinapipe.net/project/d3081065.html</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -1133,14 +1126,14 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>凉水井水厂, 管网, 配套设施, 建设项目</t>
+          <t>污水管网改造, 延伸覆盖项目, 一期, 最高投标限价</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>邻水县旧城区市政雨水管道改造项目(二期)施工标段终止公告</t>
+          <t>苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目(一期)澄清文件</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1170,38 +1163,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>广安市</t>
+          <t>广元市</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>邻水县</t>
+          <t>苍溪县</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>邻水县旧城区市政雨水管道改造项目(二期)施工标段</t>
+          <t>苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目(一期)涉及污水管网的改造和延伸覆盖。</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>本项目最高投标限价为18938453.87元</t>
+          <t>投标最高限价从24931396.73元变更为22442178.76元。</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>市政雨水管道</t>
+          <t>污水管网材料</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>邻水县旧城区市政雨水管道改造项目(二期)施工标段终止公告 邻水县旧城区市政雨水管道改造项目（二期）（项目名称）施工标段 终止公告 致：各潜在投标人 1.本项目招标文件中，资格条件对公司（企业）和项目经理均做了业绩要求，根据《四川省人民政府办公厅关于 持续优化营商环境规范招标投标主体行为的实施意见》(川办规[2022]8号)第一条网第(三)项:“......对总投资3000万 元以下，采用常规通用技术标准或对技术、性能没有特殊要求的项目，鼓励招标人不将类似工程业绩作为投标、 加分、中标条件。” 本项目（本次）最高投标限价为18938453.87元，因该业绩设置不利于落实《四川省人民政府办公厅关于持续优化 务 营商环境规范招标投标主体行为的实施意见》(川办规[2022]8号)文件相关规定，为鼓励更多潜在投标人参与投标， 现取消资格条件中的公司（企业）和项目经理业绩。 2.因本项目需要更改资格条件，为保障更多的潜在投标人参与投标，现决定终止本次招标，后续招标事宜请自行 关注广安公共资源交易网。 商 3.由此带来的不便请谅解。 道 招标人：邻水县住房和城乡建设局（盖单位章） 招标代理机构：四川建交建设工程有限公司（盖单位章） 管 2026年08月24日 信息来源:https://www.chinapipe.net/project/d3079715.html 国 cqdingjiu 2026.08.25 14:22:29 中</t>
+          <t>苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目(一期)澄清文件 苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目（一期）(项目名称)施工/ 标段 补疑书（01号） 致各 潜在投标人： 1、第二章 投标人须知 投标人须知前附表 7.3.1 履约担保 投标最高限价24931396.73元。 变更为： 7.3.1 履约担保 投标最高限价22442178.76元。 2、招标控制价及招标工程量清单上传有误，现已上传最新招标控制 价和招标工程量清单。 3、招标文件其余内容不变更，以最新上传得招标文件、招标工程量清单及招标控制价为 准。 苍溪县城市管网事务中心 日 期：2026年8月26日 信息来源:https://www.chinapipe.net/project/d3081067.html cqdingjiu 2026.08.26 17:19:21 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>邻水县旧城区市政雨水管道改造项目(二期)施工标段
-https://www.chinapipe.net/project/d3079715.html</t>
+          <t>苍溪县嘉陵江南北侧中心城区污水管网改造和延伸覆盖项目(一期)涉及污水管网的改造和延伸覆盖。
+合计金额（元）：投标最高限价从24931396.73元变更为22442178.76元。
+https://www.chinapipe.net/project/d3081067.html</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1209,14 +1203,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>市政雨水管道改造, 二期, 施工标段, 最高投标限价</t>
+          <t>污水管网, 改造, 延伸覆盖, 项目, 一期, 投标最高限价</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>邻水县旧城区市政雨水管道改造项目(二期)施工施工标段招标公告</t>
+          <t>巴中市江北片区排水防涝设施建设项目施工/标段招标公告</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1246,38 +1240,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>广安市</t>
+          <t>巴中市</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>邻水县</t>
+          <t>巴中市</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>改造邻水县东环路、东邻路、古邻大道、邻洲大道、人民路、金源路、建新路城市雨水管道及设施等道路排水防涝设施。</t>
+          <t>改造江北片区雨水管网21千米，改建排水沟3.8千米，整治积水隐患点80个，增设雨水检查井525座，新建雨水口480座，分流雨污混接管网144处，安装智能监测设备80套，配备移动泵车2套，以及建相关附属配套设施。</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>项目业主为邻水县住房和城乡建设局，建设资金来自县财政资金，项目出资比例为100%。</t>
+          <t>项目业主为巴中市综合行政执法局，建设资金来自争取上级资金和地方配套，项目出资比例为100%。</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>DN400钢带增强波纹管雨水管道、DN600钢带增强波纹管雨水管道、DN800钢带增强波纹管雨水管道、DN1000钢带增强波纹管雨水管道、DN1200钢带增强波纹管雨水管道、雨水检查井、平箅式雨水口</t>
+          <t>排水管网、排水沟、雨水检查井、雨水口、雨污混接管网、智能监测设备、移动泵车及相关附属配套设施</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>邻水县旧城区市政雨水管道改造项目(二期)施工施工标段招标公告 邻水县旧城区市政雨水管道改造项目（二期）(项目名称)施工施工标段 招标公告 1. 招标条件 1.1本招标项目邻水县旧城区市政雨水管道改造项目（二期）(项目名称)已由邻水县发展和改革局(项目 审批、核准或备案机关名称)以邻发改[2024]953号（批文名称及编号）批准建设网，项目业主为邻水县住房和城乡 建设局，建设资金来自县财政资金（资金来源），项目出资比例为100%，招标人为邻水县住房和城乡建设局。 项目已具备招标条件，现对该项目的施工进行公开招标。 1.2本招标项目由邻水县发展和改革局（核准机关名称）核准（招标事项核准文号为邻发改[2024]953号）的招标 务 组织形式为委托招标（□自行招标 委托招标）。招标人选择的招标代理机构是四川建交建设工程有限公司。 2. 项目概况与招标范围 2.1建设地点：邻水县城区。 商 2.2建设内容及规模：改造邻水县东环路、东邻路、古邻大道、邻洲大道、人民路、金源路、建新路城市雨水管 道及设施等道路排水防涝设施。改造DN400钢带增强波纹管雨水管道1800米、DN600钢带增强波纹管雨水管 道5300米、DN800钢带增强波纹管雨水管道14道200米、DN1000钢带增强波纹管雨水管道8500米、DN1200钢带增强 波纹管雨水管道2220米，改造雨水检查井872座，改造易涝积水区域平箅式雨水口1744处，原平口钢筋混凝土管 改建后采用钢带增强波纹管。 2.3 计划工期：250日历天。 管 2.4本次招标范围：人民路全段，排水管改造、人行道路面拆除及恢复等，具体详见本项目（标段）工程量清单、 施工图。 2.5标段划分：施工1个国标段。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 中 3.1本次招标要求投标人须具备 3.1.1资质条件：具备独立企业法人资格，且具有建设行政主管部门颁发的市政公用工程施工总承包三级及以上资 质。 3.1.2业绩要求： □近3年（/至投标截止时间，不少于3年）（多项选择：□已完成 □已完成或新承接或正在施工）不少于1（1至3 个）个类似项目。类似项目是指:/。 无业绩要求。 3.1.3项目经理的资格要求： 项目经理（项目负责人）资格：市政公用工程(注册专业)二级及以上（级别）建造师，具有省级及以上住房城 乡建设主管部门颁发的安全生产考核合格证（B证），/（业绩要求），须为本单位人员（若为联合体投标，须为 联合体牵头人人员）。 □园林绿化工程项目经理（项目负责人）资格：（职称级别）/专业技术职称，（业绩要求）/，须为本单位人员 （若为联合体投标，须为联合体牵头人人员）。 3.2本次招标□接受不接受联合体投标。联合体投标的，应满足下列要求： /。 3.3各投标人均可就上述1(具体数量)标段投标 。 3.4本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企业、与大企业的负责人 为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体标 准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》 （工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、 存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在3000万元以下的施工项目(标段) 应勾选此项。 ） 网 4. 招标文件的获取 4.1 凡有意参加投标者，请于2026- 08- 26 开始登录：全国公共资源交易平台（四川省·广安市）（网 址：https://zhjy.gazhcs.com/）—“电子交易平台登录”—“投标登录”，通过数字证书免费下载招标资料（招标 务 文件、技术资料等）。 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 商 5.1投标文件递交的截止时间（投标截止时间，下同）为2026- 09 -16 09:30，投标人应在投标截止时间前在 线递交经投标人数字证书加密的数据电文形式投标文件。 道 5.2本项目开标实行（□见面开标；使用不见面开标系统）开标方式，关于“不见面开标系统”的流程和注意 事项，请各交易主体在广安市公共资源交易网上下载查看不见面开标系统操作指南 6. 发布公告的媒介 管 本次招标公告在《全国公共资源交易平台（四川省）》和全国公共资源交易服务平台（四川省·四川 省）、全国公共资源交易平台（四川省·广安市）(公告发布的其它媒介名称）上发布。 7.行政监督部门 国 单位名称：邻水县住房和城乡建设局 联系电话：0826-3222939 中 8. 联系方式 招标人： 邻水县住房和城乡建设局 地 址： 邻水县鼎屏镇环城路东四段199号 邮 编： 638500 联系人： 蔡老师 电 话： 18728667740 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / 招标代理机构： 四川建交建设工程有限公司 地 址： 四川省广安市华蓥市双河街道办事处红星路北段1层 邮 编： 638600 联系人： 董先生 项目负责人： 董安斌 电 话： 15681828877 传 真： / 电子邮件： / 网 网 址： / 开户银行： / 账 号： / 务 日期：2026-08-25 商 注： （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 道 （2）招标人对投标人的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不得 作为资质要求。 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工程 管 相应指标，类似项目业绩的定义应明确，用语准确无歧义。 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受投 标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 国 信息来源:https://www.chinapipe.net/project/d3079714.html 中 cqdingjiu 2026.08.25 14:22:29</t>
+          <t>巴中市江北片区排水防涝设施建设项目施工/标段招标公告 巴中市江北片区排水防涝设施建设项目 (项目名称)施工 / 标段 招标公告 1. 招标条件 网 1.1 本招标项目 巴中市江北片区排水防涝设施建设项目 (项目名称)已由 巴中市发展和改革委员 会 (项目审批、核准或备案机关名称)以 巴发改审〔2025〕46号 （批文名称及编号）批准建设 ，项目业主 为 巴中市综合行政执法局 ，建设资金来自 争取上级资金和地方配套 （资金来源），项目出资比例为 100% ，招标人为 巴中市综合行政执法局 。项目已具备招标条件，现对该项目的施工进行公开招标。 务 1.2 本招标项目由 巴中市发展和改革委员会 （核准机关名称）核准（招标事项核准文号为 巴发改审 〔2025〕46号 ）的招标组织形式为 委托招标 。 招标人选择的招标代理机构是四川诚程臣工程咨询有限公 司。 商 2. 项目概况与招标范围 道 2.1 建设地点：巴中市江北片区。 2.2 主要建设内容及规模：改造江北片区雨水管网21千米，改建排水沟3.8千米，整治积水隐患点80个，增设雨水 检查井525座，新建雨水口480座，分流雨污混接管网144处，安装智能监测设备80套，配备移动泵车2套，以及建 管 设相关附属配套设施。 2.3 招标范围：本项目工程量清单及工程量清单对应图纸所示范围内全部内容的施工。 2.4 计划工期：300日历国天。 2.5 标段划分：施工一个标段。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 中 3. 投标人资格要求 3.1 本次招标要求投标人须具备 3.1.1资质条件：（1）独立企业法人资格；（2）具有建设行政主管部门颁发的市政公用工程施工总承包三级及 以上资质；（3）施工单位须具备有效的安全生产许可证。 3.1.2业绩要求： 近年（ 2023年01月01日 至投标截止时间，不少于3年）已完成或新承接或正在施工 不少于1（1 至3个）个 类似项目。类似项目是指:合同金额不低于4000.00万元的市政公用工程施工业绩。 □ 无业绩要求。 3.1.3项目经理的资格要求 项目经理（项目负责人）资格：具备市政公用工程专业一级注册建造师(注册专业)（级别）建造师，具有省 级及以上住房城乡建设主管部门颁发的安全生产考核合格证（B证），/（业绩要求） ，须为本单位人员（若为 联合体投标，须为联合体牵头人人员）。 □ 园林绿化工程项目经理（项目负责人）资格： （职称级别）专业技术职 称， （业绩要求） ，须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.2 本次招标不接受 联合体投标。 3.3 各投标人均可就上述1(具体数量)标段投标 。 □ 3.4 本次招标仅面向中小企业发包（其中属于大企业的分支机构、与大企业的负责人为同一人的情形的企业 均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体标准以《工业和信息化部、 国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业 〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、存在特殊要求 外，我省依法必须招标的国家投资工程，招标控制价在3000万元以下的施工项目(标段) 应勾选此项。） 4. 招标文件的获取 网 4.1 凡有意参加投标者，请于 2026年08月27日 至开始登陆：巴中市政务服务和公共资源交易服务中心网站 （https://www.bzsggzy.cn）“公共资源交易平台”中“建设工程招标投标”，通过数字证书免费下载招标资料 （招标文件、技术资料等）。 务 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 商 投标文件递交的截止时间（投标截止时间，下同）为 2026年09月18日 09时00分 ，投标人应在投标截止时间前 在线递交经投标人数字证书加密的数据电文形式投标文件。 6. 发布公告的媒介 道 本次招标公告在《全国公共资源交易平台（四川省）》和《四川建设网》、《巴中市公共资源交易信息 网》(公告发布的其它媒介名称）上发布。 管 7. 行政监督部门 单位名称：巴中市住房和城乡建设局 联系电话：0827-52613国00 8. 联系方式 招 标 人：巴中市综合行政执法局 中 地 址：巴中市巴州区江北大道中段77号 邮 编：636010 联 系 人：袁先生 电 话：0827-5272300 传 真：/ 电子邮件：/ 网 址：/ 开户银行：/ 账 号：/ □ 招标代理机构： / 招标代理机构：四川诚程臣工程咨询有限公司 地 址：成都市龙泉驿区幸福大道333号华府幸福城11栋3楼 邮 编：610100 联 系 人：郑先生 项目负责人：郑先生 网 电 话：028-86703310 传 真：/ 务 电子邮件：/ 网 址：/ 商 开户银行：/ 账 号：/ 道 2026年08月26日 管 注： （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人国的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不得 作为资质要求。 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工程 相应指标，类似项目业绩的定义应明确，用语准确无歧义。类似业绩类型参照住建部总承包资质和专业资质的 中 分类标准设定，不得设定特定行业的业绩。 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受投 标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 信息来源:https://www.chinapipe.net/project/d3081064.html cqdingjiu 2026.08.26 17:19:21</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>改造邻水县东环路、东邻路、古邻大道、邻洲大道、人民路、金源路、建新路城市雨水管道及设施等道路排水防涝设施。
-https://www.chinapipe.net/project/d3079714.html</t>
+          <t>改造江北片区雨水管网21千米，改建排水沟3.8千米，整治积水隐患点80个，增设雨水检查井525座，新建雨水口480座，分流雨污混接管网144处，安装智能监测设备80套，配备移动泵车2套，以及建相关附属配套设施。
+合计金额（元）：项目业主为巴中市综合行政执法局，建设资金来自争取上级资金和地方配套，项目出资比例为100%。
+https://www.chinapipe.net/project/d3081064.html</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -1285,14 +1280,14 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>市政雨水管道改造, DN400钢带增强波纹管, DN600钢带增强波纹管, DN800钢带增强波纹管, DN1000钢带增强波纹管, DN1200钢带增强波纹管, 雨水检查井, 平箅式雨水口</t>
+          <t>排水管网, 排水沟, 雨水检查井, 雨水口, 雨污混接管网, 智能监测设备, 移动泵车</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>四川省乐山市沙湾区城北片区排水防涝综合治理项目招标计划公告</t>
+          <t>四川弘石资产管理有限公司关于中江县南片区农村供水管网智慧化提升改造项目勘察设计水利工程的招标公告</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1322,53 +1317,50 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>乐山市</t>
+          <t>德阳市</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>沙湾区</t>
+          <t>中江县</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>更新改造片区内DN600～1400雨水排放管10.5公里，同步布设智能化终端感知设备，新建一体化雨水提升泵站2座，并对配套设施进行改造。</t>
+          <t>本项目拟在中江县南片区供水问题进行提升改造，对响滩子水厂、仓山水厂周边乡镇新建DN20-DN800管网107公里，管网漏损治理80公里;进行户表改造约10万户;在响滩子水厂、仓山水厂片区范围内进行智慧水务改造，安装远程控制系统，安装无负压水泵商，安装电磁流量计，配备PE管等相关设备设施;本项目预计提升供水规模为5.5万吨/天。</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>估算总投资57957700.00元</t>
+          <t>项目业主为四川弘石资产管理有限公司，建设资金来自争取上级资金、债券资金和自筹资金（资金来源），出资比例为100%。</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>承插式钢筋混凝土管</t>
+          <t>勘察设计服务</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>四川省乐山市沙湾区城北片区排水防涝综合治理项目招标计划公告 四川省乐山市沙湾区城北片区排水防涝综合治理项目招标计划公告 招标项目 四川省乐山市沙湾区城北片区排水 项目批准文件及 乐沙发改〔2024〕318 号(乐沙发改 名称 防涝综合治理项目 文号（如有） 〔2024〕318 号) 联系人及联系方 招标人 乐山市沙湾区住房和城乡建设局 刘老师:0833-3448067 式 估算总投资 57957700.00 项目分类 市政基础设网施工程 （元） 更新改造片区内 DN600～1400 雨 水排放管 10.5 公里，同步布设智能化终端感知设备,其中：DN600 招标项目 承插式钢筋混凝土管约 3215 米、DN800 承插式钢筋混凝土管约 2538 米、DN1000 承插式钢筋混凝土 概况 管约 2213 米、DN1200 承插 式钢筋混凝土管约 1482 米、DN1400 承插式钢筋混凝土管约 1084 米，新 务 建一体化雨水提升泵站 2 座，并对配套设施进行改造。 拟招标内 序号 招标内容 投标人主要资格条件要求 预计招标时间 容 1 施工 / 2026-09-25 00:00:00 商 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3079709.html 道 cqdingjiu 2026.08.25 14:22:30 管 国 中</t>
+          <t>四川弘石资产管理有限公司关于中江县南片区农村供水管网智慧化提升改造项目勘察设计水利工程的招标公告 1 、招标条件 1.1 本招标项目 中江县南片区农村供水管网智慧化提升改造项目勘察设计 （项目名称 ） 已由中江县发展和 改革局（项目审批、核准或备案机关名称）以江发改投资[2025]312号 （批文名称及编号）批准建设，项目业 主为四川弘石资产管理有限公司 ，建设资金来自争取上级资金、债券资金和自筹资金（资金来源），出资比 例为100%，招标人为四川弘石资产管理有限公司。项目已具备招标条件，现对该项目的勘察设计进行公开招标。 1.2 本招标项目为四川省行政区域内的国家投资工程建设项目，中江县发展和改网革局 （核准机关名称）核准 （招标事项核准文号为江发改投资[2025]312号 ）的招标组织形式为 委托招标招标人选择（本招标项目在省 发展改革委指定比选网站上的项目编号为/）的招标代理机构是： 蜀熙建工有限公司 。 2、项目概况与招标范围 2.1建设地点：中江县仓山镇、永丰乡、普兴镇、联合镇、万福镇、会龙镇、太安镇、冯 务 店镇、积金镇、广福镇、白果乡、通山乡、永兴镇等。 2.2规模及投资额：本项目拟在中江县南片区供水问题进行提升改造，对响滩子水厂、仓山水厂周边乡镇新 建DN20-DN800管网107公里，管网漏损治理80公里;进行户表改造约10万户;在响滩子水厂、仓山水厂片区范围内 进行智慧水务改造，安装远程控制系统，安装无负压水泵商，安装电磁流量计，配备PE管等相关设备设施;本项目 预计提升供水规模为5.5万吨/天。 2.3勘察设计服务期限：180日历天(勘察服务期限:60日历天，设计服务期限:120日历天)。 道 2.4招标范围：（1）勘察：招标人指定范围内的全部勘察（包括初步勘察、详细勘察、工程测量及物探）及按 要求提供地勘报告并通过有关部门审查，提供的勘察成果必须符合本项目和国家、行业现行规范要求以及项目 实施阶段的相关服务工作。（2）设计：包括但不限于初步设计（含初步设计概算编制）、技施设计（含招标设 计、施工图设计），负责配合通过施工图审查并配合取得施工图审查报告或专家审查意见，配合发包人完成施 管 工报告、设计变更及后续设计配合服务及根据项目需要增加的其他设计工作。 2.5标段划分：勘察设计1个标段。 国 3 、投标人资格要求 3.1 本次招中标投标人须具有独立法人资格（独立企业法人或事业单位法人）。 3.2 资质要求： ①具备独立法人资格；②勘察单位：具备国家行政主管部门颁发的工程勘察专业类（岩土 工程（勘察））乙级及以上勘察资质；③设计单位：具备国家行政主管部门颁发的工程设计水利行业乙级及以 上资质。 3.3 业绩要求： / 3.4 本次招标接受 联合体投标。联合体投标的，应满足下列要求： （1）联合体各方均具备独立法人资格； (2)联合体成员不超过2家（含牵头人），联合体牵头人须具备国家行政主管部门颁发的工程设计水利行业乙级及 以上资质；(3)联合体各方须签订联合体协议书，明确联合体各方承担的工作和义务；(4)联合体各方不得再以自 己名义单独或参加其他联合体在本项目中投标；(5)由联合体牵头人负责本项目投标报名、缴纳投标保证金、递 交投标文件等相关事宜，牵头人进行的该行为对联合体各成员具有约束力 。 符合前述要求的即具有投标人资格。 4 、招标文件的获取 4.1 凡有意参加投标者，请于2026年08月27日00时00分00秒至2026年09月17日09时30分00秒，登录全国公共资源 交易平台（四川省.德阳市）（网址：www.dyggzy.com）， 凭CA数字证书网上报名，逾期未报名的投标企业将不 能报名及获取招标文件；未注册的企业请按全国公共资源交易平台（四川省.德阳市）（网址：www.dyggzy.com） 相关的说明完成注册并领取CA数字证书后，方可进行网上报名。 4.2 招标文件按系统要求获取，潜在投标人网上投标报名成功后，请登录全国公共资源交易平台（四川省.德阳 市）（网址：www.dyggzy.com）， 凭CA数字证书网上获取招标文件,获取招标文件时间同4.1条中的投标报名时间， 此为获取招标文件唯一途径。 4.3 招标文件供投标人下载使用（招标文件免费获取）。 5 、投标文件的递交 5.1 投标文件递交的截止时间（投标截止时间，下同）为 2026年09月17日09时30分 ，投标人应在投标截止时间 前在线递交经投标人数字证书签名制作的数据电文形式投标文件。开标地点为 德阳市政府政务服务和公共资 源交易服务中心（德阳市松花江北路8号，五洲广场东侧） 。 网 5.2逾期送达的、未送达指定地点的或者不按招标文件要求密封的投标文件，招标人予以拒收。 5.3 逾期提交的投标文件，招标人将予以拒收。 务 6 、发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省·德阳市）》和 《全国公共资源交易平台（四川 省）》 (公告发布的其它媒介名称）上发布。 商 7 、联系方式 招标人： 四川弘石资产管理有限公司 道 地址： 四川省德阳市中江县凯江镇玄武南路98号 邮编： / 管 联系人：王老师 电话： 0838-7207416 传真： / 国 电子邮件： / 网址： / 中 开户银行： / 账号： 招标代理机构： 蜀熙建工有限公司 地址：四川省眉山市东坡区裴城路359号永和苑商住小区二期3幢2层1号 邮编：/ 联系人：李老师 电话： 028-37265470 传真：/ 电子邮件： / 网址：/ 开户银行： / 账号： / 2026年08月26日 信息来源:https://www.chinapipe.net/project/d3081040.html 网 cqdingjiu 2026.08.26 17:19:21 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>更新改造片区内DN600～1400雨水排放管10.5公里，同步布设智能化终端感知设备，新建一体化雨水提升泵站2座，并对配套设施进行改造。
-https://www.chinapipe.net/project/d3079709.html</t>
+          <t>本项目拟在中江县南片区供水问题进行提升改造，对响滩子水厂、仓山水厂周边乡镇新建DN20-DN800管网107公里，管网漏损治理80公里;进行户表改造约10万户;在响滩子水厂、仓山水厂片区范围内进行智慧水务改造，安装远程控制系统，安装无负压水泵商，安装电磁流量计，配备PE管等相关设备设施;本项目预计提升供水规模为5.5万吨/天。
+合计金额（元）：项目业主为四川弘石资产管理有限公司，建设资金来自争取上级资金、债券资金和自筹资金（资金来源），出资比例为100%。
+https://www.chinapipe.net/project/d3081040.html</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>90</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>排水防涝综合治理, 承插式钢筋混凝土管, 雨水排放管</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>乐山市金口河区永和镇安全饮水改造提升工程招标计划公告</t>
+          <t>中交四航局若尔盖项目钢筋混凝土管采购招标公告</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1398,53 +1390,54 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>乐山市</t>
+          <t>阿坝藏族羌族自治州</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>金口河区</t>
+          <t>若尔盖县</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>新建加压泵站6座、供水主管道，并配备闸门井、球阀、水表等设施。</t>
+          <t>本项目包括四个子项目：1. 阿坝州若尔盖县红星镇污水处理厂建设项目；2. 若尔盖县红星镇塔哇村宜居宜业和美乡村建设项目；3. 若尔盖县红星片区老旧街区改造项目；4. 阿坝州若尔盖县红星镇市政道路基础设施建设项目。</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>估算总投资12000000.00元</t>
+          <t>资金来源：业主计量</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>供水主管道、闸门井、球阀、水表等设施</t>
+          <t>钢筋混凝土管</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>乐山市金口河区永和镇安全饮水改造提升工程招标计划公告 乐山市金口河区永和镇安全饮水改造提升工程招标计划公告 乐山市金口河区发展和改革局关于乐山市 金口河区永和镇安全饮水改造提升工程可 招标项目名 乐山市金口河区永和镇安全饮水 项目批准文件及 行性研究报告的批复、乐山市金口河区行 称 改造提升工程 文号（如有） 政审批局关于乐山市金口河区永和镇安全 饮水改造提升工程初步设计报告的批复(金 发改投资[2025]68号、金行审复[2025]43号) 网 联系人及联系方 招标人 乐山市金口河区永和镇人民政府 余老师:0833-2706406 式 估算总投资 12000000.00 项目分类 水利工程 务 （元） 招标项目概 新建加压泵站6座、供水主管道，并配备闸门井、球阀、水表等设施。详见本项目图纸及工程量 况 清单所示内容。 序号 招标内容 投标人主要资格条件要求商预计招标时间 拟招标内容 1 施工 详见本项目招标文件 2026-09-01 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 道 信息来源:https://www.chinapipe.net/project/d3079706.html cqdingjiu 2026.08.25 14:22:30 管 国 中</t>
+          <t>中交四航局若尔盖项目钢筋混凝土管采购招标公告 中交四航局若尔盖项目钢筋混凝土管采购招标公告 1.招标条件 中交第四航务工程局有限公司承建的阿坝州若尔盖县红星镇市政道路基础设施建设项目等4个打 捆项目(第二次)项目，资金来源：业主计量。该项目已具备招标条件，现对钢筋混凝土管采购进 网 行公开招标。 2.项目概况与招标内容 务 2.1 项目概况： 1.阿坝州若尔盖县红星镇污水处理厂建设项目：新建处理规模1500立方米/天的生活污水处理厂1 座，新建污水管网10.3公里及配套附属设施； 商 2.若尔盖县红星镇塔哇村宜居宜业和美乡村建设项目：新建8米宽道路约749米，护坡231立方米， 配套雨水管网1882米、给水管网1652米、电力管网2780米、通信2442米及配套附属设施； 道 3.若尔盖县红星片区老旧街区改造项目:改造若尔盖县红星片区老旧街区道路1135m，改建街角口 袋公园1处，建设公共停车场3处，滨水步道铺装改造，配套建设公厕4处及完善区域相关附属工 程； 管 4.阿坝州若尔盖县红星镇市政道路基础设施建设项目：新建市政道路4.41km及市政桥梁4座，改 建双侧人行道长2371m，宽3m，新建单侧人行步道长940m，宽2-4米，并配套相关交安工程等附 属设施。 国 2.2 招标内容： 中 （1）包件编号：不分包件。 （2）物资名称：钢筋混凝土管。 （3）数量：钢筋混凝土管13589米。 （4）交货地点：四川省若尔盖项目工地沿线。 详见招标公告附表。 3.投标人资格要求 3.1营业范围要求：在中华人民共和国境内依法注册，具有独立法人资格、具有招标物资生产或 供应经验的生产商、贸易商，并且具有合法、有效三证合一营业执照。 3.2生产能力要求：有招标物资供货的业绩（与中交集团合作的供货业绩优先） 3.3财务能力要求：投标人为一般纳税人，具有良好的资金财务状况。近三年经审计的财务报表。 3.4质量保证能力要求：投标物资生产厂、代理商和经销商拥有近两年国家认可的产品质量监督 检测机构出具的产品质量合格的检测报告，质量必须符合国家及行业现行标准的要求。须具备 三标管理体系认证证书。 3.5供货业绩要求：生产商（经销商）近三年内具有招标物资供货业绩的相关证明材料（中标通 知书复印件或供货合同复印件等）。 3.6履约信用要求：具有良好的社会信誉，近期没有在其他项目物资投标中提供虚假材料或违规 违纪处于被取消投标资格状态的投标人；最近两年内没有与骗取合同有关的犯罪或严重违法行 为而引起的诉讼和仲裁；近两年不曾在合同中严重违约或被逐；财产未被接管或冻结，企业未 网 处于禁止或取消投标状态；同时要求至少提供两份同类投标物资已供甲方或使用单位出具的投 标人履约情况证明；投标人未被纳入“信用中国”网站（www.creditchina.gov.cn）公布的失信被 执行人、企业经营异常名录、重大税收违法案件当事人名单、政府租赁严重违法失信名单（提 供查询结果截图）。 务 3.7不接受联合体投标。 3.8单位负责人为同一人或者存在控股、管理关系商的不同单位，不得同时参加本次投标，否则， 相关投标均被否决。 3.9投标人须在中交招采网（https://zjzcw.iccec.cn）注册。 道 3.9.1已在网并且已通过招标人层级供应商或已增加招标人为合作单位的供应商、上级供应商可 直接报名参与。 管 3.9.2在网平级单位供应商未增加招标人为合作单位需进行合作意向申请通过后报名参与。 3.9.3未注册中交招采网的单位需进行注册，推荐单位或合作意向单位选择招标人，审核通过后 方可报名参与。 国 3.10其他要求：自2022年8月11日起，按照《关于督促公司合作单位补充完善有关基础数据的通 知》（中交纪综函〔2022〕42号）文件要求，供应链系统内供应商需补录完善基本信息、联系人 信息、实中控主体、董监高信息，并确保信息真实有效。具体操作指南可向招标联系人索要《中 交集团供应链系统供应商信息完善帮助手册》。未按要求完善信息的供应商将无法参与投标。 4.招标文件的获取 4.1凡有意参加投标者，请于2026年8月26日16时至2026年8月31日17时（北京时间，下同），登录 中交集团供应链管理信息系统（https://zjzcw.iccec.cn）下载电子招标文件。投标人下载前应首先 将标书费汇至招标人指定账户并经招标人确认购买后，方能下载招标文件。汇款前需备注投标 项目名称、投标材料名称，并备注标书费。 4.2招标文件每套售价200 元，售后不退。投标单位通过电汇或网上转账方式支付，招标人 可提供与标书费缴纳等值的电子发票。 4.3标书费统一汇至以下账户： 中交第四航务工程局有限公司新会分公司； 统一社会信用代码：91440705770175915R； 地址：江门市新会区古井镇四航大道八号、十号、十二号； 开户行：交通银行股份有限公司北京马甸支行； 账号：01-10-000063-11。 标书费转账时，请备注：采购项目+采购方案名称+方案编码招标资料费。 4.4投标保证金：无。投标保证金通过现金或保函方式在投标截止时间前汇达。采用现金方式的， 网 必须以公对公电汇、转账等形式缴纳。 5.投标文件的递交 务 5.1投标文件递交的开始时间为2026年8月31日17时10分， 截止时间为2026年9月5日17时30分， 投标人应在截止时间前通过远程登录中交招采网（https://zjzcw.iccec.cn）递交电子投标文件。 商 5.2本次只接受电子投标文件，投标文件纸质文件经签字盖章后彩色扫描并制作成PDF格式；或 投标文件经电子签名并加盖单位章后制作成PDF格式，上传到中交招采网。逾期未上传成功的投 标文件，招标人不予受理。 道 5.3本次招标不接受纸质版投标文件。 6. 开标时间及地点 管 招标人在规定的投标截止时间2026年9月5日17时30分结束后，在中交招采网 （https://zjzcw.iccec.cn）上同步线上开标。 国 7. 电子采购交易实行有偿服务的告知 7.1收费开始时间：自2025年8月 1日起新发生的采购。 中 7.2收费对象：中标金额在100万元及以上的非豁免中标主体。 7.3豁免范围： （1）公司内部单位中标的采购项目； （2）海外采购（海外属地国、第三国采购，出口采购视同国内采购不在豁免范围）； （3）不具有竞争性的直接采购项目； （4）业主等单位要求在指定平台开展的采购项目； （5）经准入及评价中心审核确认符合豁免条件的其他情形。 7.4按照包件中标金额分档计费， 收费标准如下： （1）100万元（含）～200万元：100元/次； （2）200万元（含）～1000万元：500元/次； （3）1000万元（含）～3000万元：1000元/次； （4）3000万元（含）～1亿元：3000元/次； （5）1亿元（含）以上： 5000元/次。 7.5支付时限：中标主体需在中标结果发布后10天内完成费用缴纳，最迟应在合同签订前完成费 用缴纳。未在规定时间内完成缴费的中标主体，系统将限制签订合同，采购主体可根据需要重 新组织采购；涉事中标主体一年内发生1次的，将纳入公司重点关注名单，累计发生2次的，将 网 纳入公司“黑名单”。 7.6支付流程： 务 7.6.1通知推送：中标结果发布后，系统自动向中标主体推送缴费通知（含应缴金额及支付链 接）； 7.6.2费用查询：中标主体登录“中交招采网-服务商管理”模块查看待支付费用； 7.6.3在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； 7.6.4发票开具：支付完成后5个工作日内道，系统自动生成“技术服务费”电子发票， 中标主体可在 “中交招采网-服务管理－发票下载”模块获取。 管 8. 发布公告的媒介 本次招标公告同时在中交招采网（https://zjzcw.iccec.cn）网上发布。 国 9. 监督机构 监督人：中郑丽 地 址：四川省成都市天府新区正兴街道汉州路969号中交国际中心2921 邮 编：610000 电子邮件：zhengli8@ccccltd.cn 联系信息： 10.联系方式 项目名称：中交四航局阿坝州若尔盖县红星镇市政道路基础设施建设项目等4个打捆项目(第二 次)项目经理部 地址：四川省阿坝州若尔盖县红星镇 联系人：陈炫宇 电 话：17358633433 电子邮件:chenxuanyu1@ccccltd.cn 附件：中交集团暨中国交建合作单位黑名单和重点关注名单告知 网 中交四航局阿坝州若尔盖县红星镇市政道路基础设施建设项目等4个打捆项目(第二次)项目经理 务 部 2026年 8月 26日 商 道 附件列表 暂无数据 物资信息 管 1 钢筋混凝土排水管 300mm Ⅱ级 13% 米 2 钢筋混凝土排水管 400mm Ⅱ级 13% 米 3 钢筋混凝土排水管 500mm Ⅱ级 13% 米 国 4 钢筋混凝土排水管 600mm Ⅱ级 13% 米 5 钢筋混凝土排水管 800mm Ⅱ级 13% 米 6 钢筋混凝土排水管 1000mm Ⅱ级 13% 米 中 7 钢筋混凝土排水管 1200mm Ⅱ级 13% 米 8 混凝土检查井 1300×1300mm 高度1640mm 壁厚150mm 井筒φ700 13% 米 9 混凝土检查井 直径1500mm 高度3230mm 壁厚200 井筒φ800 13% 米 信息来源:https://www.chinapipe.net/project/d3081037.html cqdingjiu 2026.08.26 17:19:21</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>新建加压泵站6座、供水主管道，并配备闸门井、球阀、水表等设施。
-https://www.chinapipe.net/project/d3079706.html</t>
+          <t>本项目包括四个子项目：1. 阿坝州若尔盖县红星镇污水处理厂建设项目；2. 若尔盖县红星镇塔哇村宜居宜业和美乡村建设项目；3. 若尔盖县红星片区老旧街区改造项目；4. 阿坝州若尔盖县红星镇市政道路基础设施建设项目。
+合计金额（元）：资金来源：业主计量
+https://www.chinapipe.net/project/d3081037.html</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>乐山市金口河区永和镇安全饮水改造提升工程, 供水主管道, 闸门井, 球阀, 水表</t>
+          <t>钢筋混凝土管, 阿坝州, 红星镇, 市政道路基础设施建设项目</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>康定市“8.03”灾后重建土地复垦建设项目招标计划公告</t>
+          <t>南江至三台(中江)高速公路(中江境)自来水管道迁改工程设计竞价公告</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1454,7 +1447,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1474,38 +1467,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>甘孜藏族自治州</t>
+          <t>德阳市</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>康定市</t>
+          <t>中江县</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>土地复垦重建总面积41.41亩，并配套建设取水口1座、沉砂池2座、蓄水池2座、输水管道1180米、渠道785米、生产路465米及项目区公示牌1座等附属设施。</t>
+          <t>本项目为南江至三台(中江)高速公路(中江境)自来水管道迁改工程设计的招标项目。</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>估算总投资4980000.00元</t>
+          <t>原文未提及</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>土地整理工程</t>
+          <t>设计服务</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>康定市“8.03”灾后重建土地复垦建设项目招标计划公告 康定市“8.03”灾后重建土地复垦建设项目招标计划公告 项目批准文件及文号 康发改[2026]154号(康发改 招标项目名称 康定市“8.03”灾后重建土地复垦建设项目 （如有） [2026]154号) 招标人 康定市农牧农村和科技局 联系人及联系方式 杨老师:0836-2821692 估算总投资 4980000.00 项目分类 土地整理工程 （元） 网 土地复垦重建总面积41.41亩，并配套建设取水口1座、沉砂池2座、蓄水池2座、输水管道1180米、 招标项目概况 渠道785米、生产路465米及项目区公示牌1座等附属设施。 序号 招标内容 投标人主要资格条件要求 预计招标时间 拟招标内容 务 1 施工 以招标人最终发布的招标公告和招标文件为准。 2026-09-24 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3079702.html 商 cqdingjiu 2026.08.25 14:22:30 道 管 国 中</t>
+          <t>南江至三台(中江)高速公路(中江境)自来水管道迁改工程设计竞价公告 四川蜀中水务有限公司（单位）南江至三台（中江）高速公路（中江境）自来水管道迁改工程设计（中介服务 项目）将在中介服务网上交易平台进行邀请竞价，现将有关内容公告如下： 一、项目概况及要求： 项目所 中江县 在地 项目基 详情见附件内容 本情况 网 项目需 设计需求公告.docx 求材料 竞价内 按国家规定和相关技术规范开展服务工作。 务 容范围 中介服 务完成 60天 期限要 商 求 竞价价 最低限价暂无，最高限价暂无 格区间 道 二、报名时间 2026年08月26日 09:00:00 ~ 2026年08月31日 17:00:00 三、报名条件 管 经认证注册入网，取得网上竞价资格并且被委托单位邀请参与的中介机构，可参与此中介服务项目的竞价。 资质类 型及等 符合相关规定 级要求 国 经营范 围要求 因不符合上述条件参加项目报名的，由参加者自行承担相应的法律责任。 中 咨询、 现场勘 自公告之日起至2026年08月31日 17:00:00止（节假日除外）接受咨询，有需要现场勘察的请与项目委托 察的时 人联系统一安排现场勘察。 间与方 式 备注 暂无 四、选取方式 邀请竞价 五、联系方式 项目委 四川蜀中水务有限公司 托单位 项目单 位联系 张禧龙 人 联系电 18981071378 话 联系地 中江县 址 六、公告发布日期 2026年08月26日 08:55:37 免责申明：本网站是中介交易信息发布平台，所发布信息的真实性、合法性、有效性、完整性由信息发布者负 责 信息来源及报价：http://zjfw-gc.sczwfw.gov.cn/zjcsmhwz/epointzjcs/pages/defaultsp/index 网 信息来源:https://www.chinapipe.net/project/d3081029.html cqdingjiu 2026.08.26 17:19:22 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>土地复垦重建总面积41.41亩，并配套建设取水口1座、沉砂池2座、蓄水池2座、输水管道1180米、渠道785米、生产路465米及项目区公示牌1座等附属设施。
-https://www.chinapipe.net/project/d3079702.html</t>
+          <t>本项目为南江至三台(中江)高速公路(中江境)自来水管道迁改工程设计的招标项目。
+合计金额（元）：原文未提及
+https://www.chinapipe.net/project/d3081029.html</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1513,14 +1507,14 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>土地复垦, 投资额, 管道, 道路</t>
+          <t>南江至三台(中江)高速公路, 自来水管道迁改工程设计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>邻水县旧城区市政雨水管道改造项目(二期)施工招标文件预公示</t>
+          <t>中铁23局泸古高速TJ-10标项目钢筋混凝土管询价采购补遗公告</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1530,7 +1524,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1548,19 +1542,11 @@
           <t>四川省</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>广安市</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>邻水县</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>市政雨水管道改造</t>
+          <t>拟采购物资一览表中采购物资名称钢筋混凝土管，规格型号DN1400修改为DN400。</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1570,18 +1556,19 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>钢筋混凝土管</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>邻水县旧城区市政雨水管道改造项目(二期)施工招标文件预公示 详见附件。 信息来源:https://www.chinapipe.net/project/d3079700.html cqdingjiu 2026.08.25 14:22:30 网 务 商 道 管 国 中</t>
+          <t>中铁23局泸古高速TJ-10标项目钢筋混凝土管询价采购补遗公告 中铁 23 局泸古高速TJ-10标项目钢筋混凝土管询价采购 询价编号： CR23J1GS-LGTJ10-XJ-2026-012 补遗文件（ 1） 各投标人： 中铁 23 局泸古高速TJ-10标项目钢筋混凝土管询价采购 （ 询价编号： CR23J1GS-LGTJ10-XJ-2026-012 ） 补遗如下： 网 3.1拟采购物资一览表中采购物资名称钢筋混凝土管，规格型号DN1400修改为DN400。 询价 文件其他内容不变。 务 中铁二十三局集团第一工程有限公司 泸古高速 TJ-10标项目经理部 2026 年 8 月 26 日 商 信息来源:https://www.chinapipe.net/project/d3081007.html 道 cqdingjiu 2026.08.26 17:19:22 管 国 中</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>市政雨水管道改造
-https://www.chinapipe.net/project/d3079700.html</t>
+          <t>拟采购物资一览表中采购物资名称钢筋混凝土管，规格型号DN1400修改为DN400。
+合计金额（元）：原文未提及
+https://www.chinapipe.net/project/d3081007.html</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -1589,14 +1576,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>分析, 选定地区, 管材招标, 商机</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>宣汉县2026年大豆单产提升工程项目招标计划公告</t>
+          <t>盐亭县经开区清洁能源智慧供热项目设计施工总承包标段招标公告</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1606,7 +1593,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1626,53 +1613,54 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>达州市</t>
+          <t>绵阳市</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>宣汉县</t>
+          <t>盐亭县</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>项目建设大豆5万亩单产提升工程，主要实施供水泵站、首部枢纽、过滤装置、智能化控制系统和田间输配水管网等基础设施。</t>
+          <t>建设供热母管约10.76公里，备用燃气蒸汽锅炉设施，新增1套90t/h高温高压生物质循环流化床锅炉，及对管网沿线进行绿化改造。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>估算总投资25000000元</t>
+          <t>项目业主为绵阳国开能源有限公司，建设资金来自企业自筹（资金来源），项目出资比例为100%。</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>供热母管，燃气蒸汽锅炉设施，高温高压生物质循环流化床锅炉，绿化改造材料</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>宣汉县2026年大豆单产提升工程项目招标计划公告 宣汉县2026年大豆单产提升工程项目招标计划公告 项目批准文件及 招标项目名称 宣汉县2026年大豆单产提升工程项目 达市农【2026】21号 文号（如有） 联系人及联系方 网 招标人 宣汉县农业机械化推广站 朱先生；13908247848 式 估算总投资 25000000 项目分类 水利 （元） 务 项目规划建设大豆5万亩单产提升工程。主要实施供水泵站、首部枢纽、过滤装置、智能化控 招标项目概况 制系统和田间输配水管网等相关基础设施 序号 招标内容 投标人主要资格条件要求 预计招标时间 拟招标内容 1 施工 商以招标文件为准 2026-09-27 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3079696.html 道 cqdingjiu 2026.08.25 14:22:30 管 国 中</t>
+          <t>盐亭县经开区清洁能源智慧供热项目设计施工总承包标段招标公告 盐亭县经开区清洁能源智慧供热项目设计施工总承包标段 1. 招标条件 1.1本招标项目盐亭县经开区清洁能源智慧供热项目(项目名称)已由盐亭县发展和改革局(项目审批、核准或备案 机关名称)以川投资备【2602-510723-04-01-706332】FGQB-0106号（批文名称及编号）批准建设，项目业主为绵阳 国开能源有限公司，建设资金来自企业自筹（资金来源），项目出资比例为100%，招标人为绵阳国开能源有限 公司。项目已具备招标条件，现对该项目的设计施工总承包进行公开招标。 网 1.2本招标项目由盐亭县发展和改革局（核准机关名称）核准（招标事项核准文号为川投资备 【2602-510723-04-01-706332】FGQB-0106号）的招标组织形式为委托招标（□自行招标委托招标）。招标人选择 的招标代理机构是四川众禾通达工程咨询有限公司。 务 2. 项目概况与招标范围 2.1标段划分：1个标段。 商 2.2建设地点：盐亭县经开区。 2.3建设内容及规模：建设供热母管约10.76公里，备用燃气蒸汽锅炉设施，新增1套90t/h高温高压生物质循环流化 床锅炉，及对管网沿线进行绿化改造。 道 2.4工期：730日历天（包括设计、施工总工期）。 2.5招标范围：本项目的设计阶段（主要包含施工图设计及后续服务）、施工总承包直至竣工验收合格和整体移 管 交及工程缺陷责任期内的保修工作。 2.6质量标准：设计质量标准：满足相应设计现行规范要求并通过有关主管部门审查；施工要求质量标准：达到 国家现行规范及现行验收规范合格标准。 国 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 中 3.1本次招标要求投标人须具备 3.1.1资质要求：施工单位：具有国家建设行政主管部门颁发的市政公用工程施工总承包二级及以上资质和行政主 管部门颁发在有效期内的特种设备生产许可证(许可项目：压力管道安装 公用管道GB2级)；设计单位：具有建设 行政管理部门颁发的市政行业（热力工程）专业设计甲级及以上资质和行政主管部门颁发在有效期内的特种设 备生产许可证(许可项目：压力管道设计 公用管道GB2级)，施工单位须具备有效的安全生产许可证。 3.1.2业绩要求：（本项为多选） 设计业绩要求：近年（ 2023 年 01 月 01 日至投标截止时间，不少于3年）（□已完成 已完成或新承接或正在设 计）不少于1（1 至3个）个类似项目。类似项目是指:总投资不低于4000万元的市政公用工程设计业绩。 施工业绩要求：近年（ 2023 年 01 月 01 日至投标截止时间，不少于3年）（□已完成 已完成或新承接或正在施 工）不少于1（1 至3个）个类似项目。类似项目是指:单项合同金额不低于4000万元的市政公用工程施工业绩。 □无业绩要求。 3.1.3项目经理的资格要求：具有市政公用工程专业一级注册建造师□由设计负责人兼任由施工负责人兼任，无 （业绩要求） ，须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.1.4设计负责人的资格要求：具有注册公用设备工程师（动力）资格，须为投标人本单位人员。 3.1.5施工负责人（建造师，下同）的资格要求：具有市政公用工程专业(注册专业)一级（级别）建造师，具有省 级及以上住房城乡建设主管部门颁发的安全生产考核合格证（B证），须为投标人本单位人员。 3.2本次招标接受联合体投标。联合体投标的，联合体牵头人应为□设计单位施工单位，同时满足下列要求：（1） 联合体成员须具有独立法人资格，牵头人具有建设行政主管部门颁发的市政公用工程施工总承包二级及以上资 质且安全生产许可证在有效期内；（2）组成联合体的成员单位不得超过4家（含联合体牵头单位）；(3)联合体 各方应签订联合体协议书，明确联合体牵头人和各方权利义务，并由联合体各方向招标人承担连带责任；(4)组 成联合体投标应符合相关法律法规对联合体投标的有关规定，联合体各方不得再以自己名义单独或参加其他联 合体在同一工程项目中投标；（5）联合体牵头人负责本项目递交投标文件等相关事宜。 □ 3.3本次招标范围中施工部分的工作仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企 业、与大企业的负责人为同一人的情形的企业均不属于中小企业。若为联合体投网标的，本项目联合体协议书中 职责分工为承揽施工工作的所有单位均应属于中小企业）。具体标准以《工业和信息化部、国家统计局、国家 发展和改革委员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业〔2011〕300号）中的“建 筑业”划型标准为准，投标人应提供中小企业声明函。（除技术复杂、存在特殊要求外，我省依法必须招标的 国家投资工程，施工部分招标控制价在5000万元以下的，应勾选此项。） 务 4. 招标文件的获取 4.1 凡有意参加投标者，请于 2026 年 08 月 27 日开始登录：全国公共资源交易平台（四川省·绵阳市） 商 （网址：http://ggzy.my.gov.cn）-“用户注册登录”，通过数字证书免费下载招标资料（招标文件、技术资料等）。 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 道 投标文件递交的截止时间（投标截止时间，下同）为2026年09月17日09时30分，投标人应在投标截止时间前在线 递交经投标人数字证书加密的数据电文形式投标文件。 管 6. 发布公告的媒介 本次招标公告在《全国公共资源交易平台（四川省）和全国公共资源交易平台（四川省·绵阳 市）》、 / (公告发布的其它媒介名称）上发布。 国 7. 行政监督部门 单位名称：盐亭县住房和城乡建设局 中 联系电话：0816-7223721_ 8. 联系方式 招 标 人：绵阳国开能源有限公司 地 址：四川省绵阳市盐亭县经开区麻秧大桥桥头 邮 编：621600 联 系 人：李女士 电 话：0816-7226955 传 真： / 电子邮件： / 网 址： / 开户银行： / 账 号： / □招标代理机构： / 招标代理机构：四川众禾通达工程咨询有限公司 地 址：成都蛟龙港双流园区海滨广场11号楼1602室 邮 编：621000 联 系 人：曹先生 网 电 话：028-60611188 传 真： / 务 电子邮件： / 网 址： / 商 开户银行： / 账 号： / 道 2026年08月26日 注： 管 （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不得 作为资质要求。 国 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工程 相应指标，类似项目业绩的定义应明确，用语准确无歧义。 （4）招标人限定的联合体成员数量不得少于设定的资质个数。 中 （5）《招标投标法》第二十四条规定，“招标人应当确定投标人编制投标文件所需要的合理时间；但是，依法 必须进行招标的项目，自招标文件开始发出之日起至投标人提交投标文件截止之日止，最短不得少于二十 日。”期间20日的计算方法为：从招标公告发布的次日起算并以全国公共资源交易平台（四川省）审核发布的时 间为准（发布招标公告当日不算在期间内）。如某项目招标公告发布日期为2025年12月1日，期间届满的日期 是2025年12月21日，递交投标文件截止时间应该为2025年12月22日。 信息来源:https://www.chinapipe.net/project/d3080978.html cqdingjiu 2026.08.26 17:19:22</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>项目建设大豆5万亩单产提升工程，主要实施供水泵站、首部枢纽、过滤装置、智能化控制系统和田间输配水管网等基础设施。
-https://www.chinapipe.net/project/d3079696.html</t>
+          <t>建设供热母管约10.76公里，备用燃气蒸汽锅炉设施，新增1套90t/h高温高压生物质循环流化床锅炉，及对管网沿线进行绿化改造。
+合计金额（元）：项目业主为绵阳国开能源有限公司，建设资金来自企业自筹（资金来源），项目出资比例为100%。
+https://www.chinapipe.net/project/d3080978.html</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>管材招标, 清洁能源, 供热项目, 设计施工总承包</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司(宜宾分公司)无缝钢管采购询比采购公告</t>
+          <t>望丛文化园周边污水管网工程施工/标段招标公告</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1682,7 +1670,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>其他/未识别</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1702,53 +1690,54 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>宜宾市</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>珙县</t>
+          <t>郫都区</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司（宜宾分公司）无缝钢管采购询比采购公告</t>
+          <t>新建望丛文化园周边污水管网，长度约640米，管径d800，采用顶管方式施工。</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>项目业主为成都科创新城投资发展有限公司，建设资金来自国家投资-非政府投资，项目出资比例为100%。</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>无缝钢管</t>
+          <t>市政公用工程施工</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司(宜宾分公司)无缝钢管采购询比采购公告 四川华电珙县发电有限公司（宜宾分公司）无缝钢管采购询比采购公告_采购信息_中国华电集团电子商务平台 四川华电珙县发电有限公司（宜宾分公司）无缝钢管采购询比采购公告 一、采购单编号：GX-202608-007525 二、采购单名称：无缝钢管采购 三、采购代理机构：四川华电珙县发电有限公司（宜宾分公司） 四、采购方式：公开询比采购 五、采购类型：货物 六、报价方式：整单报价 七、报价截止时间：2026-08-29 23:59 八、交货时间： 2026-09-10 九、备注：技术咨询：刘洋15298178097 请下载采购文件，确定物资名称、型号、数量及要求，并点击报价清单里的《查看》，再次确认物资名称、型号、数量及要求是否与采购文件一致。如存在采购文件与报价清单《查看》里的内容不一致，请致电技术。金额交易超过5万，请联系商务签署合同，到货后，可开具发票，货到验收，合格付款。送货时提供产品相关资料（合格证、检测报告等）要盖公司鲜章的原件。请附送货清单，保包含物资名称、数量及物资编码，如无送 货清单，拒收。商务咨询杨程18783187637 十、采购清单 序号 采购人 物资名称税率 规格型号 单位数量用途 1 四川华电珙县发电有限公司（宜宾分公司）无缝钢管13%无缝钢管\φ45*11\SA-213T91公斤1,000 十一、资格条件内容： 十二、采购文件的获取 获取方式： 第一步：注册。请未注册的潜在供应商访问华电集团电子商务平台（https://www.chdtp.com），完成平台注册。服务咨询电话（08:00-20:00）：400-622-8787；平台信息审核时间为国家法定工作日的9:00-12:00；13:30-17:30。 第二步：网上报名。登录华电集团电子商务平台（https://www.chdtp.com）业务系统，点击菜单”非招采购系统“-“采购报价管理-询比采购-可参与项目”，点击“参与项目”报名，须正确填写联系人、电话等信息。 第三步：移动数字证书申请。安装移动数字证书APP(华电E盾企业版)后，请按照“移动数字证书操作指南”申请办理数字证书，在加密上传报价文件等环节须进行扫码签名，否则无法完成相关操作。（APP下载路径：安卓系统的手机终端APP需要进入“服务中心”－－资料下载－－点击“华电E盾企业版APP（安卓版)”；IOS系统的手机终端APP需要在苹果应用商店中搜索“华电E盾企业版”下载安装。移动数字证书操作指南下载路径：平台首页“服务专区”或进 入“服务中心”－－操作指南版块。)。 第四步：供应商客户端下载。登录业务系统，进入右上角工作台-右下角下载专区，下载供应商客户端和操作手册等相关文件。 十三、 报价响应文件的递交 递交方式：电子版响应文件通过供应商客户端递交至华电集团电子商务平台（https://www.chdtp.com）。 十四、异议提出渠道和方式： 供 华 应 电 商 集 或 团 者 电 其 子 他 商 利 务 害 平 关 台 系 首 人 页 对 右 本 下 招 角 标 → 项 按 目 照 的 提 公 示 告 完 内 成 容 登 有 录 异 或 议 身 的 份 ， 验 请 证 在 → 公 选 告 择 期 类 间 型 提 （ 出 非 。 招 本 标 项 投 目 诉 仅 ） 接 → 受 选 通 择 过 关 华 联 电 采 集 购 团 单 电 → 子 选 商 择 务 阶 平 段 台 → 投 上 诉 传 异 支 议 撑 系 文 统 件 提 → 出 维 的 护 异 提 议 出 ， 人 并 信 通 息 过 。 平台告知处理动态。方式如下： 网 单位名称 姓名 联系电话 中国华电集团有限公司四川分公司夏博文02862356715 十五、监督部门： 供应商或者其他利害关系人认为采购活动不符合法律法规的，可以自知道或者应当知道之日起10日内进行投诉。本项目接受仅通过华电集团电子商务平台投诉异议系统提出的投诉，并通过平台告知处理动态。方式如下： 华电集团电子商务平台首页右下角→按照提示完成登录或身份验证→选择类型（非招标投诉）→选择关联采购单→选择阶段→上传支撑文件→维护提出人信息。 单位名称 姓名 联系电话 中国华电集团有限公司四川分公司夏博文02862356715 十六、采购单位联系方式 采购机构：四川华电珙县发电有限公司（宜宾分公司） 联 系 人：杨程 联系电话：18783187637 平台注册、使用等事宜，请拨打华电电子商务平台统一客户服务电话400-622-8787进行详询。 发 布 日期：2026-08-25 务 请到中国华电集团采购平台报价，网站：http://www.chdtp.com/ 供应商服务：010-62228787转666 采购方服务：010-62228787转668 商 报名网址：https://www.chdtp.com/ 信息来源:https://www.chinapipe.net/project/d3079519.html 道 cqdingjiu 2026.08.25 14:22:31 管 国 中</t>
+          <t>望丛文化园周边污水管网工程施工/标段招标公告 望丛文化园周边污水管网工程施工/标段 招标公告 1．招标条件 网 1.1本招标项目望丛文化园周边污水管网工程施工 / 标段已由郫都区政务服务管理和行政审批局以川投资备 【2505-510124-04-01-960230】第FGQB-0214号批准建设，项目业主为成都科创新城投资发展有限公司，建设资金 来自国家投资-非政府投资，项目出资比例为100%，招标人为成都科创新城投资发展有限公司。项目已具备招标 条件，现进行公开招标。 务 1.2本招标项目由郫都区政务服务管理和行政审批局核准（招标事项核准文号为川投资备 【2505-510124-04-01-960230】第FGQB-0214号）的招标组织形式为委托招标。招标人选择的招标代理机构是中锦 军贤工程咨询集团有限公司。 商 本标段行政监督部门为郫都区水务局，采用“评定分离”方式进行评标定标。 道 2．项目概况与招标范围 2.1项目名称：望丛文化园周边污水管网工程。 管 2.2建设地点：郫都区郫筒街道。 2.3建设规模及内容：新建望丛文化园周边污水管网，长度约640米，管径d800,采用顶管方式施工。 2.4计划工期：180日历国天。 2.5招标范围：本项目施工图设计范围内的全部内容，施工直至竣工验收合格及整体移交、工程保修期内的缺陷 修复和保修工作等全部工作，具体范围详见招标工程量清单。 中 2.6质量要求：符合国家现行工程施工质量验收规范合格标准。 2.7标段划分：施工一个标段。 3．投标人资格要求 3.1 本次招标要求投标人： 3.1.1须具有 国家建设行政主管部门颁发的市政公用工程施工总承包三级或以上资质； 3.1.2信誉要求：不存在投标人须知第1.4.3项规定的限制投标的情形； 3.1.3所有投标人（无资质企业除外）应具有针对本标段的《成都市建设领域市场主体基础信息网络登记表》、 《成都市建设领域从业人员基础信息网络登记表》。 3.1.4 拟派项目经理（项目负责人）具有市政公用工程专业二级或以上注册建造师证书，须具备有效的安全生产 考核合格B证，/（业绩要求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.1.5财务要求：无财务要求； 3.1.6类似工程业绩要求： 近年（2023年01月01日至投标截止时间，不少于3年）已完成或正在施工或新承接的项目共不少于1个类似工程业 绩。 类似工程业绩是指:2023年01月01日至投标截止时间已完成或正在施工或新承接的单个合同金额不低于400万元的 市政公用工程施工业绩。 3.2本次招标不接受联合体投标。 3.3 各投标人均可就上述1个标段投标，可中标的标段数量为1个。 3.4本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东网为大企业、与大企业的负责人为 同一人的情形的企业均不属于中小企业。）。具体标准以《工业和信息化部、国家统计局、国家发展和改革委 员会、财政部关于印发中小企业划型标准规定的通知》（工信部联企业〔2011〕300号）中的“建筑业”划型标 准为准，投标人应提供中小企业声明函。 务 4．招标文件的获取 4.1凡有意参加投标者，请于2026年08月27日起，在成都市公共资源电子交易云平台(www.cdggzy.com）（以下简称 “电子交易云平台”）免费下载招标资料（招标文件及相关资料），获得“拟投标项目回执”。 商 4.2招标人 不提供 邮购招标文件服务。 5．投标文件的递交 道 5.1 投标文件递交的截止时间（投标截止时间，下同）为2026年09月17日09时30分，招标人或其委托代理机构，以 及已在投标截止时间前按规定上传投标文件的投标人，均应在开标当日投标截止时间前登录不见面开标系统 （网址：www.cdggzy.com），录入相关人员姓名、电话等基本信息。投标人未按时登录不见面开标系统，错过开 标解密时间的，由投标人自行承担不利后果。 管 5.2 投标人应在解密开始后30分钟内在线完成投标文件解密。投标文件未能在规定时间内成功解密的，视为投标 人未在规定时间内提交投标文件，由投标人自行承担责任。不见面开标项目不接受投标人现场递交光盘等形式 的投标文件，不接受投标人现场解密投标文件。 国 6．发布公告的媒介 本次招标公告在全国公共资源交易平台(四川省)、成都市公共资源电子交易云平台、郫都区人民政府门户网（网 址：http://ggzyjy.sc.gov.cn/、http://www.cdggzy.com、https://www.pidu.gov.cn/）上发布。 中 7．行政监督部门 单位名称：郫都区水务局 联系电话：028-86559595 8. 联系方式 招 标 人：成都科创新城投资发展有限公司 地 址：成都市郫都区何公路28号 邮 编：/ 联 系 人：罗先生 电 话：028-69335888 传 真：/ 电子邮件：/ 网 址：/ 开户银行：/ 账 号：/ 招标代理机构：中锦军贤工程咨询集团有限公司 网 地 址：成都市双流区东升街道龙桥路6 号 132 栋 7 楼 邮 编：/ 务 联 系 人：李先生 项目负责人：雷旭桃 商 电 话：028-83119888 传 真：/ 道 电子邮件：/ 网 址：/ 管 开户银行：/ 账 号：/ 国 信息来源:https://www.chinapipe.net/project/d3080976.html cqdingjiu 2026.08.26 17:19:22 中</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>四川华电珙县发电有限公司（宜宾分公司）无缝钢管采购询比采购公告
-https://www.chinapipe.net/project/d3079519.html</t>
+          <t>新建望丛文化园周边污水管网，长度约640米，管径d800，采用顶管方式施工。
+合计金额（元）：项目业主为成都科创新城投资发展有限公司，建设资金来自国家投资-非政府投资，项目出资比例为100%。
+https://www.chinapipe.net/project/d3080976.html</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>无缝钢管, 采购, 询比采购</t>
+          <t>污水管网工程, 排水钢管, 郫都区郫筒街道</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>中铁十一局集团第二工程有限公司通江县2025年超长期国债高标准农田建设项目经理部水泥涵管询价采购公告</t>
+          <t>四川乐山嘉州经济开发区嘉州新饮品产业园区基础设施建设项目-新建污水处理厂项目二标段施工/标段招标公告</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1758,7 +1747,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>水泥涵管</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1778,49 +1767,54 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>巴中市</t>
+          <t>乐山市</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>巴中市</t>
+          <t>乐山市</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>该项目涉及11个乡镇（街道）32个村的农田基础设施建设，包括新建和改造提升部分，主要采购水泥涵管。</t>
+          <t>新建一座1.0万m³/d污水处理厂（近期规模0.6万m³/d），建设包含粗格栅及进水泵房、细格栅及曝气沉砂池、预处理组合池、组合预缺氧AAOAO生化沉淀池、高效沉淀池、反硝化滤池消毒池及巴氏计量槽、污泥浓缩池、污泥脱水机房、加药间、鼓风机房及配电间、初雨池、管理用房、门卫等合计13个建构筑物。新建污水管网DN800，852m；DN600，5m；DN500，138m；新建压力污水管dn250，1381m；新建一体化污水泵站一座Q=2000m³/d。</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>项目资金来自2025年超长期国债，具体金额未明确。</t>
+          <t>政府投资，项目出资比例为100%，具体预算金额未提及。</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>水泥涵管</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>市政公用工程施工总承包</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>四川乐山嘉州经济开发区嘉州新饮品产业园区基础设施建设项目-新建污水处理厂项目二标段施工/标段招标公告 四川乐山嘉州经济开发区嘉州新饮品产业园区基础设施建设项目-新建污水处理厂项目二标段 (项目名称)施 工 / 标段 招标公告 1. 招标条件 网 1.1 本招标项目 四川乐山嘉州经济开发区嘉州新饮品产业园区基础设施建设项目-新建污水处理厂项目 二标段 (项目名称)已由 乐山市市中区发展和改革局 (项目审批、核准或备案机关名称)以 关于四川乐山嘉 州经济开发区嘉州新饮品产业园区基础设施建设项目可行性研究报告(代项目建议书)的批复(乐中发改政策 务 〔2025〕5 号) （批文名称及编号）批准建设 ，项目业主为 乐山市市中区城市建设投资发展集团有限公 司 ，建设资金来自 政府投资 （资金来源），项目出资比例为 100% ，招标人为 乐山市市中区城市建 设投资发展集团有限公司 。项目已具备招标条件，现对该项目的施工进行公开招标。 1.2 本招标项目由 乐山市市中区发展和改革局 （核准机商关名称）核准（招标事项核准文号为 乐中 发改政策〔2025〕5 号 ）的招标组织形式为 委托招标 。 招标人选择的招标代理机构是四川省致远建设项 目管理有限责任公司。 2. 项目概况与招标范围 道 2.1 建设地点：乐山市市中区； 管 2.2 建设规模：新建一座1.0万m3/d污水处理厂（近期规模0.6万m3/d），建设包含粗格栅及进水泵房、细格栅及曝 气沉砂池、预处理组合池、组合预缺氧AAOAO生化沉淀池、高效沉淀池、反硝化滤池消毒池及巴氏计量槽、污 泥浓缩池、污泥脱水机房、加药间、鼓风机房及配电间、初雨池、管理用房、门卫等合计13个建构筑物。新建污 水管网DN800，852m；国DN600，5m；DN500，138m；新建压力污水管dn250，1381m；新建一体化污水泵站一 座Q=2000m3/d。详见招标清单和施工设计图纸。 2.3 计划工期：270日历天； 中 2.4 招标范围：包括但不限于本工程的全部施工设计图纸及工程量清单所表达的范围（含材料、设备采购）， 以 及竣工验收合格后工程保修期内的缺陷修复和工程保修等相关工作，并对项目的质量、安全、工期、造价、环 境保护等负责。以上工作内容以实际工作内容为准。 2.5 标段划分：施工 1 个标段。 2.6 工程质量要求：符合国家、地方和行业现行施工质量验收标准，满足设计要求，达到合格标准。 （说明本次招标项目的建设地点、规模及投资额、计划工期、招标范围、标段划分及标段投资额等）。 3. 投标人资格要求 3.1 本次招标要求投标人须具备 3.1.1资质条件：（1）具有独立法人资格；（2）具备市政公用工程施工总承包三级及以上资质。 3.1.2业绩要求： 近年（ 2023年01月01日 至投标截止时间，不少于3年）已完成 不少于3（1 至3个）个类似项目。类似项目 是指:单个合同金额不少于 6500 万元的市政公用工程施工业绩。 3.1.3项目经理的资格要求 项目经理（项目负责人）资格：市政公用工程专业一级(注册专业)（级别）建造师，具有省级及以上住房城 乡建设主管部门颁发的安全生产考核合格证（B证），2023 年01 月 01 日至投标截止时间，作为项目经理（项目 负责人）已完成不少于 1 个类似项目。类似项目是指：单个合同金额不少于 6500 万元的市政公用工程施工业绩。 业绩证明材料按招标文件第八章 投标文件格式《近年完成的类似项目情况表》“注”的要求提供。项目经理 （项目负责人）以合同协议书和除发包人（总承包人）出具的证明文件以外的竣工验收证明材料为准，若合同 协议书和除发包人（总承包人）出具的证明文件以外的竣工验收证明材料无法体现招标文件要求的项目经理 （项目负责人）的，则投标人还需提供发包人（总承包人）出具的证明文件。（业绩要求） ，须为本单位人员 （若为联合体投标，须为联合体牵头人人员）。 网 3.2 本次招标不接受 联合体投标。 3.3 各投标人均可就上述1(具体数量)标段投标 。 务 □ 3.4 本次招标仅面向中小企业发包（其中属于大企业的分支机构、存在控股股东为大企业、与大企业的负责 人为同一人的情形的企业均不属于中小企业。若为联合体投标的，联合体所有单位均应属于中小企业）。具体 标准以《工业和信息化部、国家统计局、国家发展和改革委员会、财政部关于印发中小企业划型标准规定的通 知》（工信部联企业〔2011〕300号）中的“建筑业”划型标准为准，投标人应提供中小企业声明函。（除技术 商 复杂、存在特殊要求外，我省依法必须招标的国家投资工程，招标控制价在3000万元以下的施工项目(标段) 应勾 选此项。） 4. 招标文件的获取 道 4.1 凡有意参加投标者，请于 2026年08月27日 至 2026年09月02日 登陆乐山市公共资源交易服务平台官网 （http://www.lsggzy.com.cn/），在首页点击“用户登录”入口。通过数字证书免费下载招标资料（招标文件、技 术资料等）。 管 4.2 招标人不提供招标文件获取的其他方式。 5. 投标文件的递交 投标文件递交的截止时国间（投标截止时间，下同）为 2026年09月17日 09时00分 ，投标人应在截止时间前通过 乐山市公共资源交易服务平台官网（http://www.lsggzy.com.cn/），在首页点击“用户登录”入口，凭单位CFCA 数字证书登录在线递交经投标人数字证书签名制作的数据加密电子投标文件。 6. 发布公告中的媒介 本次招标公告在《全国公共资源交易平台（四川省）》和《全国公共资源交易平台（四川省?乐山市）》(公告 发布的其它媒介名称）上发布。 7. 行政监督部门 单位名称：乐山市市中区住房和城乡建设局/乐山市市中区发展和改革局 联系电话：0833-2193007/0833-2551301 8. 联系方式 招 标 人：乐山市市中区城市建设投资发展集团有限公司 地 址：乐山市市中区三苏路 1155 号 6 层 邮 编：614000 联 系 人：曹老师 电 话：0833-2277573 传 真： 电子邮件： 网 址： 开户银行： 账 号： 网 招标代理机构：四川省致远建设项目管理有限责任公司 地 址：四川省资阳市雁江区仁德西路 222 号 务 邮 编：641300 联 系 人：朱老师 商 项目负责人：邓廷林 电 话：028-26757510 道 传 真： 电子邮件： 管 网 址： 开户银行： 账 号： 国 2026年08月26日 中 注： （1）若划分标段，则填写标段序号；若划分为两个及以上标段，应分别明确各标段的具体内容、划分情况。 （2）招标人对投标人的资质要求，应是国家对投标人资质的强制性规定。不是国家规定必须具备的资质，不得 作为资质要求。 （3）招标人对投标人的类似项目业绩要求，设置的投资额、面积、长度等规模量化指标不得高于本次招标工程 相应指标，类似项目业绩的定义应明确，用语准确无歧义。类似业绩类型参照住建部总承包资质和专业资质的 分类标准设定，不得设定特定行业的业绩。 （4）招标人要求投标人需具备的资质一个项目（标段）为一个，因特殊情况需要两个以上资质的，应当接受投 标人组成联合体投标，且限定的联合体成员数量不得少于设定的资质个数。 信息来源:https://www.chinapipe.net/project/d3080973.html cqdingjiu 2026.08.26 17:19:22</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>该项目涉及11个乡镇（街道）32个村的农田基础设施建设，包括新建和改造提升部分，主要采购水泥涵管。
-https://www.chinapipe.net/project/d3079346.html</t>
+          <t>新建一座1.0万m³/d污水处理厂（近期规模0.6万m³/d），建设包含粗格栅及进水泵房、细格栅及曝气沉砂池、预处理组合池、组合预缺氧AAOAO生化沉淀池、高效沉淀池、反硝化滤池消毒池及巴氏计量槽、污泥浓缩池、污泥脱水机房、加药间、鼓风机房及配电间、初雨池、管理用房、门卫等合计13个建构筑物。新建污水管网DN800，852m；DN600，5m；DN500，138m；新建压力污水管dn250，1381m；新建一体化污水泵站一座Q=2000m³/d。
+合计金额（元）：政府投资，项目出资比例为100%，具体预算金额未提及。
+https://www.chinapipe.net/project/d3080973.html</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>未识别到明确匹配关键词</t>
+          <t>管材招标, 污水处理厂, 市政公用工程</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>云岩区中心城区供水管网改造工程—设计澄清公告</t>
+          <t>竹县国有林生态示范带建设项目(一期)招标计划公告</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1830,7 +1824,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>交通</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1845,58 +1839,55 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>云岩区</t>
-        </is>
-      </c>
+          <t>大竹县</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>本项目为云岩区中心城区供水管网改造工程的设计招标。</t>
+          <t>森林修复面积25500亩，其中现有林改培7000亩、森林抚育18500亩；林下经济建设2550亩；苗竹一体化基地300亩，林区道路53.5公里；烘干库房4个、冷库1个及冷链车1辆，灌溉水池及配套管网6座。</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>估算总投资18668.75万元</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>供水管网</t>
+          <t>生态保护修复</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>云岩区中心城区供水管网改造工程—设计澄清公告 各潜在投标人： 由贵阳市云岩区水务管理局（项目业主）、四川省川建院工程项目管理有限公司（代建单位）委托我公司代理的 “云岩区中心城区供水管网改造工程—设计招标”，现作如下澄清： 1、本项目初步设计成果文件已在全国公共资源交易平台（贵州省·贵阳市）发布，请各潜在投标人登录全国公 共资源交易平台（贵州省·贵阳市）自行下载； 网 2、其余内容不变。 特此通知。 务 贵州鹏业云通建设咨询有限公司 商 2026年08月24日 道 信息来源:https://www.chinapipe.net/project/d3079680.html cqdingjiu 2026.08.25 14:22:31 管 国 中</t>
+          <t>竹县国有林生态示范带建设项目(一期)招标计划公告 竹县国有林生态示范带建设项目（一期）招标计划公告 大竹县发展和改革局关于大竹县国有林生态示 招标项目名 大竹县国有林生态示范带建设项目 项目批准文件 范带建设项目（一期）建议书的批复、竹发改发 称 （一期） 及文号（如有） [2026]93号 网 联系人及联系 招标人 大竹县林业局 刘松；18508185091 方式 估算总投资 18668.75 项目分类 生态保护修复 （元） 务 森林修复面积25500亩，其中现有林改培7000亩、森林抚育18500亩；林下经济建设2550亩；苗竹一 招标项目概 体化基地300亩，林区道路53.5公里；烘干库房4个、冷库1个及冷链车1辆，灌溉水池及配套管网6 括 座。 商 序号 招标内容 投标人主要资格条件 预计招标时间 1 勘察设计 以招标文件为准 2026-08-31 拟招标内容 2 施工 以招标文件为准 2026-09-21 道 3 重要设备和材料 以招标文件为准 2026-09-21 4 监理 以招标文件为准 2026-09-21 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 管 标人最终发布的招标公告和招标文件为准。 附件:招标计划表.pdf 信息来源:https://www.chinapipe.net/project/d3080969.html 国 cqdingjiu 2026.08.26 17:19:23 中</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>本项目为云岩区中心城区供水管网改造工程的设计招标。
-https://www.chinapipe.net/project/d3079680.html</t>
+          <t>森林修复面积25500亩，其中现有林改培7000亩、森林抚育18500亩；林下经济建设2550亩；苗竹一体化基地300亩，林区道路53.5公里；烘干库房4个、冷库1个及冷链车1辆，灌溉水池及配套管网6座。
+合计金额（元）：估算总投资18668.75万元
+https://www.chinapipe.net/project/d3080969.html</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>中心城区, 供水管网, 改造工程, 设计招标</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>凯里市洗马河流域污水管网更新改造工程项目招标计划变更公告</t>
+          <t>安乐镇农村人饮巩固提升项目招标计划公告</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1906,7 +1897,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>水利</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1921,58 +1912,59 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>黔东南苗族侗族自治州</t>
+          <t>雅安市</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>凯里市</t>
+          <t>汉源县</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>新建及改建凯里市洗马河流域DN200-DN600的污水管共计71.362km，包括不同规格的C30球墨铸铁管和涂塑钢管；新建及改造污水检查井1763座，错混接改造160处，支墩258个；一体化污水提升泵站1座，规模2000m/d，水泵流量50m/h。</t>
+          <t>新建一座300立方米蓄水池管，在取水口新建2方引泉池1座，新建10方调节池1座，新架设13.5公里DN200 1.6MPa PE输水主管以及相应配水支管，并包含相应管道埋设固定等。</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>中央资金及县级配套资金（具体金额未明确）</t>
+          <t>总投资4300000.000000元，汉源县2026年度大中型水库移民后期扶持资金</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>C30球墨铸铁管、涂塑钢管</t>
+          <t>PE输水主管</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>凯里市洗马河流域污水管网更新改造工程项目招标计划变更公告 工程建设 凯里市洗马河流域污水管网更新改造工程 项目名称 固定资产 项目批准文件及 投资项目 2501-522601-04-01-990323 凯发改审批〔2025〕62号 文号 代码 招标人名 统一社会信用代 凯里市水务局 11522601430050251R 称 码 网 招标人委 统一社会信用代 托的代理 贵州智尚工程项目管理有限公司 91522601MAAK8EDN6U 码 机构名称 招标人联 务 苏晓宇 联系电话 18085589869 系人 投资估算 13213 资金来源 中央资金及县级配套资金 （万元） 商 新建及改建凯里市洗马河流域DN200-DN600的污水管共计71.362km，其中DN600的C30球墨铸铁 管494m，DN500的C30球墨铸铁管4705m，DN400的C30球墨铸铁管13753m，DN300的C30球墨铸铁 项目建设 管20776m，DN200的C30球墨铸铁管23452m;DN500的涂塑钢管28m，DN400的涂塑钢 内容 管7798m，DN200的涂塑钢管356m。新建及改造污水检查井1763座，错混接改造160处，支墩258个。 道 一体化污水提升泵站1座，规模2000m/d，水泵流量50m/h 序号 招标内容 预计招标时间 拟交易场所 990323804 勘察 2026-09-25 09:30:00 黔东南州公共资源交易中心 管 拟招标内 990323067 设计 2026-09-25 09:30:00 黔东南州公共资源交易中心 容 990323565 施工 2026-10-26 09:30:00 黔东南州公共资源交易中心 990323104 监理 2026-10-26 09:30:00 黔东南州公共资源交易中心 国 项目建设 贵州省-黔东南苗族侗族自治州-凯里市 地点 本项目行 政监督部中凯里市住房和城乡建设局 门 本次发布的招标计划内容是本项目招标相关工作的初步安排，仅供潜在投标人参考，后期可能存在 ★特别说 取消和变更的可能。 明 项目招标内容、时间和交易场所等内容，以最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3079678.html cqdingjiu 2026.08.25 14:22:31</t>
+          <t>安乐镇农村人饮巩固提升项目招标计划公告 安乐镇农村人饮巩固提升项目招标计划公告 项目 拟招 批准 标项 安乐镇农村人饮 文件 汉源县发展和改革局关于《安乐镇农村人饮巩固提升项目建议书》的批复 汉 目名 巩固提升项目 及文号 发改投资[2026]84号 称： （如 有）： 网 招标人 联系 （建 汉源县安乐镇人 人及 邓老师 0835-5961600 设单 民政府 联系 位）： 方式： 务 招标 联系 代理 四川省国佑招标 人及 机构 张老师 0835-2888238 代理有限公司 联系 （如 方式： 商 有）： 估算 资金 总投资 4300000.000000 汉源县2026年度大中型水库移民后期扶持资金 来源： （元）： 道 项目 水利 分类： 招标 新建一座300立方米蓄水池管，在取水口新建2方引泉池1座，新建10方调节池1座，新架设13.5公里 DN200 项目 1.6Mpa PE 输水主管以及相应配水支管，并包含相应管道埋设固定等。 概括： 拟招 招标内容 预计招标时间 拟交易场所 标内 国 施工 20260926 全国公共资源交易平台（四川省.雅安市） 容： 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以 招标人最终发布的招标公告和招标文件为准。 中 信息来源:https://www.chinapipe.net/project/d3080966.html cqdingjiu 2026.08.26 17:19:23</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>新建及改建凯里市洗马河流域DN200-DN600的污水管共计71.362km，包括不同规格的C30球墨铸铁管和涂塑钢管；新建及改造污水检查井1763座，错混接改造160处，支墩258个；一体化污水提升泵站1座，规模2000m/d，水泵流量50m/h。
-https://www.chinapipe.net/project/d3079678.html</t>
+          <t>新建一座300立方米蓄水池管，在取水口新建2方引泉池1座，新建10方调节池1座，新架设13.5公里DN200 1.6MPa PE输水主管以及相应配水支管，并包含相应管道埋设固定等。
+合计金额（元）：总投资4300000.000000元，汉源县2026年度大中型水库移民后期扶持资金
+https://www.chinapipe.net/project/d3080966.html</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>洗马河流域, 污水管网更新改造, C30球墨铸铁管, 涂塑钢管</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>中国电建水电九局习水县良村镇2026年茶园村农村饮水管材采购项目公开询比采购公告</t>
+          <t>甘孜州新龙县如龙镇集中供水工程招标计划公告</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1982,7 +1974,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>市政</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1997,58 +1989,59 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>甘孜藏族自治州</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>习水县</t>
+          <t>新龙县</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>新建泵站及上水管;新建水厂一座(600m/d);输配水管网工程:输水主管、支管总长31884m;De50PE100级 (1.0MPa)配水管3480m;安装电磁流量计9套，安装水池电子液位计9套，新建减压池一座(1m3)，新建闸阀井14座等。</t>
+          <t>新建日供水能力700立方米水厂1座，取水枢纽1座，供水管网14.75公里及配套附属设施设备等。</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>最高限价：本次报价不含税总报价不得超过171.681416万元，含税13%总报价不得超过194.00万元。</t>
+          <t>估算总投资16720000.00元</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>预制焊接坡口管、焊接内外涂塑无缝钢管、焊接内外涂塑无缝弯头、法兰闸阀、法兰止回阀、法兰流量计、法兰盘</t>
+          <t>市政基础设施工程</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>中国电建水电九局习水县良村镇2026年茶园村农村饮水管材采购项目公开询比采购公告 询比采购公告 项目编号：PC-0109-26J6-FG0307 一、采购条件 网 受中国水利水电第九工程局有限公司工程总承包公司（以下简称“采购人”）委托，中国水利水电第九工程局 有限公司工程总承包公司设备物资部（以下简称“采购机构”）以公开询比方式采购贵州省遵义市习水县良村 镇2026年茶园村农村饮水项目管材，本次询比采购后所签订合同的支付资金已落实。 务 二、项目概况、采购范围 1、工程名称：贵州省遵义市习水县良村镇2026年茶园村农村饮水项目。 商 项目概况：新建泵站及上水管;新建水厂一座(600m/d);输配水管网工程:输水主管、支管 总长31884m;De50PE100级 (1.0MPa)配水管3480m;安装电磁流量计9套，安装水池电子液位计9套 ，新建减压池一座(1m3)，新建闸阀井14座 等。 道 2、采购范围：贵州省遵义市习水县良村镇2026年茶园村农村饮水项目所需管材。 序号 物资名称 规格型号 数量 单位 备注 1预制焊接坡口 管 1 焊接内外涂塑无缝钢管 DN100内外涂塑钢管壁厚4mm（上水管） 745 米 2外壁PE（聚乙烯）、 内壁EP（环氧树脂） 1预制焊接坡口 2 焊接内外涂塑无国缝钢管 DN125内外涂塑钢管壁厚8mm 3730 米 2外壁PE（聚乙烯） 内壁EP（环氧树脂） 1预制焊接坡口 3 焊接内外涂塑无缝钢管 DN125内外涂塑钢管壁厚6mm 6175 米 2外壁PE（聚乙烯） 中 内壁EP（环氧树脂） 1预制焊接坡口 4 焊接内外涂塑无缝钢管 DN100内外涂塑钢管壁厚4mm 1188 米 2外壁PE（聚乙烯） 内壁EP（环氧树脂） 1预制焊接坡口 5 焊接内外涂塑无缝钢管 DN80内外涂塑钢管壁厚4mm 4400 米 2外壁PE（聚乙烯） 内壁EP（环氧树脂） 1预制焊接坡口 6 焊接内外涂塑无缝钢管 DN65内外涂塑钢管壁厚6mm 5100 米 2外壁PE（聚乙烯） 内壁EP（环氧树脂） 1预制焊接坡口 7 焊接内外涂塑无缝钢管 DN65内外涂塑钢管壁厚4mm 4884 米 2外壁PE（聚乙烯） 内壁EP（环氧树脂） 1预制焊接坡口 8 焊接内外涂塑无缝弯头 DN125内外涂塑钢管弯头壁厚8mm 52 个 2外壁PE（聚乙烯） 内壁EP（环氧树脂） 1预制焊接坡口 9 焊接内外涂塑无缝弯头 DN125内外涂塑钢管弯头壁厚6mm 76 个 2外壁PE（聚乙烯） 内壁EP（环氧树脂） 1预制焊接坡口 10 焊接内外涂塑无缝弯头 DN100内外涂塑钢管弯头壁厚4mm 88 个 2外壁PE（聚乙烯） 内壁EP（环氧树脂） 1预制焊接坡口 11 焊接内外涂塑无缝弯头 DN80内外涂塑钢管弯头壁厚4mm 72 个 2外壁PE（聚乙烯） 内壁EP（环氧树脂） 1预制焊接坡口 12 焊接内外涂塑无缝弯头 DN65内外涂塑钢管弯头壁厚4mm 95 个 2外壁PE（聚乙烯） 内壁EP（环氧树脂） 网 13 法兰闸阀（配垫片） DN125钢制闸阀6.0MPa 3 个 执行GB/T 12234-2019 14 法兰闸阀（配垫片） DN100钢制闸阀4.0MPa 3 个 执行GB/T 12234-2019 15 法兰止回阀（配垫片） DN125缓闭式单向止回阀(6.0MPa) 1 个 执行GB/T 12234-2019 务 16 法兰流量计（配垫片） 电磁流量计DN125 9 套 执行GB/T 12234-2019 17 法兰盘（配镀锌螺栓） DN125钢制闸阀法兰盘 3 套 执行GB/T 9124.1-2019 18 法兰盘（配镀锌螺栓） DN100钢制闸阀法兰盘 3 套 执行GB/T 9124.1-2019 商 19 法兰盘（配镀锌螺栓） DN125缓闭式单向止回阀法兰盘 1 套 执行GB/T 9124.1-2019 3、采购数量 道 （1）以上采购数量，仅供参考。最终结算量以现场签收确定的订单供货并经验收合格的数量为准。若因施工生 产等原因，致使与采购材料品种、供货数量发生较大偏差时，供应商应予以接受，且不得以此作为调价和索赔 依据。由于前期施工场地受限等因素，为保证现场材料的质量，供应商每次供货数量根据采购人需求供应，后 续供货按采购人供货计划。 管 （2）综合单价为货到工地价，包括但不限于以下费用：原材料、生产加工、装卸费、出厂检验试验费、采购保 管费、运输、过路过桥费、车辆油料费及税金、保险费、利润等各项货到现场的费用。综合单价为固定单价， 合同执行期间不予调整。 国 （3）限价要求： 最高限价：本次报价不含税总报价不得超过171.681416万元，含税13%总报价不得超过194.00万元。供应商报价总 价不得超过中最高限价，否则视为无效报价。（注：供应商应合理均衡填报各分项单价，采购人有权结合市场行 情、厂家价格信息对不平衡报价进行核查，存在明显不平衡报价的，采购人有权否决其投标。） （4）结算方式：先货后款，结算时段为供货上月16日至本月15日，供应商凭买方授权的现场验收人员签收的 《收货凭证》（一式四份）和《收货清单》（当期收货凭证的汇总），以检验合格的数量为结算数量，于本月18 日前到买方项目设备物资部办理本期《材料结算单》（双方签字盖章，一式四份，双方各两份），以及买方要 求提供的其他有关资料。 付款方式：供应商于结算后三日内，开具对应结算金额的增值税专用发票（供应商须提供发票为13%的增值税专 用发票，若因国家政策性调整税率，则按国家政策所规定的税率执行）给买方，买方在收到发票后30日内根据合 同约定支付当期结算货款80%，施工完成后经监理验收合格30日内支付至97%，剩余3%为质保金，扣除因材料质 量问题而发生的费用后，质保期满后（质保期为工程竣工验收通过后12个月）30个工作日内无息支付。 采取银行汇款、银行承兑汇票、非现金方式及资产（资产支付比例原则上不低于实际结算价款5%）等方式支付。 采购人可采取前述付款方式中的其中一种或两种方式支付合同货款，供应商的综合单价即本合同综合单价已充 分考虑了采购人采用不同付款方式对供应商的影响，供应商不得以采购方选取不同付款方式而要求采购人补偿， 且供应商需承担因承兑汇票产生的提前兑现或超期未兑现的相关费用。 若采购人因资金困难不能及时按约定时间节点支付相应货款，供应商应同意采购人延期付款，不视为采购人违 约。 4、交货时间：合同签订后供应商按买方提交的书面采购计划完成供应。 5、交货地点：贵州省遵义市习水县良村镇2026年茶园村农村饮水项目指定施工现场。 6、验收方式和计量原则： （1）数量验收:货物到现场时，首先对合格质量证明文件、合格证和试验检验报告等质保文件进行验收，数量以 每批次货物验收数量为准，验收单双方签字有效。 （2）质量验收：材料到达目的地后，供应商必须随车提供生产厂家出具的“质量出厂合格证明文件”及相关证 明资料，交采购人验证。由此造成的经济损失，全部由供应商承担； 严格执行国家GB/T28897-2021(流体输送用钢塑复合管及管件）标准，执行国家GB/T17395-2024(钢管尺寸、外形、 重量及允许偏差)标准,满足GB/T 8163-2018）《输送流体用无缝钢管》的规定，阀门管件执行GB/T 12234-2019 《石油、天然气工业用螺柱连接阀盖的钢制闸阀》标准,必须严格按照国家要求网采购选用原材料，并自行抽样检 测，合格后方能使用。供应商提供的所有涂塑钢管及管件均应按有关技术要求规定进行保护，应根据气候条件、 路况、行驶时间等情况，做好预判工作，确保安全保质送达买方指定地点。供应商保证涂塑钢管在使用前经过 严格测试，保证质量、规格和技术要求符合该产品标准，产品质量保证期内卖方严格按照三包服务有关规定执 行。如因产品质量不合格发生的一切责任和经济损失均由供应商承担。 务 对不符合本合同约定要求的货物采购人有权拒绝签收，供应商应立即将该货物全部运离现场，并在供货期限内 重新更换符合约定的货物，否则，供应商除应承担产品丢失、毁损的风险外，还应向采购人支付场地占用费， 并承担合同违约责任。 商 7、质量要求： （1）质保期1年。质量标准或要求：供应商所供产品质量必须满足国家GB/T28897-2021(流体输送用钢塑复合管 及管件）标准以及，执行国家GB/T17395-202道4(钢管尺寸、外形、重量及允许偏差)标准,满足GB/T 8163-2018） 《输送流体用无缝钢管》的规定，阀门管件执行GB/T 12234-2019《石油、天然气工业用螺柱连接阀盖的钢制闸 阀》标准等相关国家标准或行业标准，如遇国家或行业标准更新，以最新标准为准。 （2）供应商必须保证提供的物资符合国家有关环保法律法规的规定，不能对施工环境造成污染，也不能对接触 管 物资的有关人员及竣工后投入运行过程中使用人员的健康造成危害。 （3）每批发货随车附产品合格证及批量检验报告以及原材料材质证书，产品符合国家标准。采购人接货后取样 复查，如有异议立即通知供应商，经双方共同认可的检验机构进行重新检验。复检合格其一切费用由采购人承 担；复检不合格，除退国回不合格品外，其所发生一切费用均由供应商承担。 （4）供应商保证所供材料或产品必须严格遵守国家标准中的强制性规定。遇有争议时，按国家的强制性规定进 行。 中 8、实地勘察：供应商单位自行组织，并承担相关费用及风险。响应供应商应根据需要对现场交通条件等进行实 地考察，以保证报价的准确性。 三、供应商资格要求 1、供应商为生产厂家的必须是经国家工商、税务登记注册，能独立承担民事责任、具有独立法人资格的企业， 具有有效期内ISO9001质量管理体系认证证书、环境与职业健康体系认证证书，输送生活饮用水管材须提供有效的 《涉及饮用水卫生安全产品卫生许可批件》；提供CMA第三方出具覆盖本项目规格压力等级的产品型式检验报 告。 2、供应商为代理商的必须是在中国境内注册的企业法人，具有独立承担民事责任的能力，提供生产厂家针对本 项目的专项授权文件；生产厂家须全部满足上述生产厂家资格条件，并提供生产厂家全套有效证明文件（复印 件须加盖生产厂家公章）。 3、业绩要求：供应商须提供近3年（2023至今）供水输水管材同类供货业绩不少于2个（提供合同扫描件，扫描 件需清晰可辨）。 4、具有良好的银行资信和商业信誉，近三年没有处于被责令停业，财产被接管、冻结、破产状态（需提供审计 报告或财务报表、信誉中国查询等证明资料）。 5、本次采购不接受联合体报价，代理商不得与所代理生产厂家同时参与报价。 6、供应商不存在《中华人民共和国招标投标法》、《中华人民共和国招标投标法实施条例》禁止投标的情形。 四、采购文件的获取 凡有意参加的供应商，请于2026年08月31日17:00前（北京时间）在中国电建采购招标数智化平台 （https://bid.powerchina.cn/bidweb/#/login，以下简称“采购平台”）获取采购文件。 供应商注册在“中国电建阳光采购网”（网址为https://bid.powerchina.cn）右侧快捷入口，切换“新版登录”， 选择“供应商登录”进行供应商注册。 五、响应文件的递交 网 1、响应文件递交的截止时间（响应文件开启时间，下同）为2026年09月07日11时00分（北京时间），供应商应 在截止时间前通过采购平台递交电子响应文件。 （1）本次采购将通过“中国电建采购招标数智化平台”（网址为https://bid.powerchina.cn/bidweb/#/supplierLogin） 务 全程在线开展，响应文件的加密、提交、解密等流程须各响应供应商在线进行操作。响应供应商可在登录系统 后，点击左侧“CA办理”菜单，扫码下载“中招互联”在线办理移动证书制作电子响应文件，并严格按照要求 进行在线响应，因操作流程失误造成的响应失败，将由响应供应商自行承担后果。 （2）平台注册等相关问题可咨询平台客服，具体联系方商式请根据网站首页“联系电话”列表中查找相应客服经 理电话。 3.平台在线签到：本次采购在平台集中解密，各供应商无须在线签到。 道 4.响应文件在线解密：响应文件递交截止时间后，由平台统一进行集中解密。 5.响应文件递交截止时间及递交地点如有变动，采购人将及时以书面形式通过采购平台通知所有已获取采购文件 的响应供应商。 管 六、发布公告的媒介 本次询比采购公告同时在中国电建阳光采购网（http://bid.powerchina.cn)和中国招标投标公共服务平台 国 （http://www.cebpubservice.com）上发布。 七、联系方式 中 采购机构：中国水利水电第九工程局有限公司工程总承包公司设备物资部 地址：贵州省贵阳市观山湖区诚信南路501号 邮编：550081 联系人：郑工 电话：17708505676 电子邮箱：409441640@qq.com 八、提出异议的渠道和方式 电话：17708505676 电子邮箱：409441640@qq.com 九、纪检监督机构 中国水利水电第九工程局有限公司工程总承包公司纪委办公室 监督电话：17685008617 2026年08月25日 信息来源:https://www.chinapipe.net/project/d3079644.html cqdingjiu 2026.08.25 14:22:31 网 务 商 道 管 国 中</t>
+          <t>甘孜州新龙县如龙镇集中供水工程招标计划公告 甘孜州新龙县如龙镇集中供水工程招标计划公告 新龙县发展和改革局关于甘孜州新 项目批准文件及文号 龙县如龙镇集中供水工程可行性研 招标项目名称 甘孜州新龙县如龙镇集中供水工程 （如有） 究报告的批复(新发改投 〔2025〕176号) 招标人 新龙县住房和城乡建设局 联系人及联系方式 张先生:0836-8122127 网 估算总投资 16720000.00 项目分类 市政基础设施工程 （元） 招标项目概况 新建日供水能力700立方米水厂1座，取水枢纽1座，供水管网14.75公里及配套附属设施设备等。 务 序号 招标内容 投标人主要资格条件要求 预计招标时间 拟招标内容 1 施工 以招标文件为准 2026-09-27 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 商 信息来源:https://www.chinapipe.net/project/d3080965.html cqdingjiu 2026.08.26 17:19:23 道 管 国 中</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>新建泵站及上水管;新建水厂一座(600m/d);输配水管网工程:输水主管、支管总长31884m;De50PE100级 (1.0MPa)配水管3480m;安装电磁流量计9套，安装水池电子液位计9套，新建减压池一座(1m3)，新建闸阀井14座等。
-https://www.chinapipe.net/project/d3079644.html</t>
+          <t>新建日供水能力700立方米水厂1座，取水枢纽1座，供水管网14.75公里及配套附属设施设备等。
+合计金额（元）：估算总投资16720000.00元
+https://www.chinapipe.net/project/d3080965.html</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>农村饮水项目, 管材采购, 预制焊接坡口管, 焊接内外涂塑无缝钢管, 焊接内外涂塑无缝弯头, 法兰闸阀, 法兰止回阀, 电磁流量计, DN100, DN125, DN80, DN65, 6.0MPa, 4.0MPa, 贵州省遵义市习水县良村镇2026年茶园村</t>
+          <t>甘孜州, 集中供水工程, 供水管网, 市政基础设施工程</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>贵阳高新区麦架河生活污水管网提升改造项目设计施工总承包招标公告</t>
+          <t>米易县老旧小区改造及配套基础设施建设项目(三期)招标计划公告</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2073,58 +2066,59 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>攀枝花市</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>米易县</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>新建网DN500-DN800聚乙烯（改性无水磷石膏）双波峰增强排水管混凝土包封约7450米，与现有污水管网连通，采用聚乙烯（改性无水磷石膏）双波峰增强排水管混凝土包封方式改造污水管网约3000米，新增污水检查井248座。</t>
+          <t>建筑立面改造8365.5㎡，新建配套设施及环境改造4202.9㎡，硬质铺地2785.5㎡，沥青路面改造1750㎡，污水管网改造、强弱电改造（飞线下地）、完善照明设施、配套服务设施等。</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>项目总投资5670.02万元，本标段合同估算金额为约44165591元。</t>
+          <t>总投资9800000元，专项债资金及企业自筹</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>聚乙烯（改性无水磷石膏）双波峰增强排水管混凝土包封</t>
+          <t>市政管道、建筑材料、照明设备、公共服务设施</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>贵阳高新区麦架河生活污水管网提升改造项目设计施工总承包招标公告 1、招标条件 本招标项目贵阳高新区麦架河生活污水管网提升改造项目设计施工总承包已由贵阳国家高新技术产业开发区产 业发展局以 关于贵州高科城市开发集团股份有限公司“贵阳高新区麦架河生活污水管网提升改造项目”初步设 计的批复,“筑高新产项[2025]315号”批准建设，招标人（项目业主）为贵阳高科城市运营服务有限公司 （代建 单位）、贵州高科城市开发集团股份有限公司（建设单位），建设资金来自 财政 ，项目出资比例为 政府投 资：100%。 项目已具备招标条件，现对该项目进行公开招标。 2、项目概况与招标范围 2.1项目总投资：5670.02万元，本标段合同估算金额为：约44165591元（其中设计费500836元，施工费43664755 元）。 2.2建设地址：贵阳国家高新区沙文生态科技产业园。 2.3建设规模：新建网DN500-DN800聚乙烯（改性无水 磷石膏）双波峰增强排水管混凝土包封约7450米，与现有污水管网连通，采用聚乙烯（改性无水磷石膏）双波峰 增强排水管混凝土包封方式改造污水管网约3000米，新增污水检查井248座。 2.4计划工期：总工期24个月（设计 期1个月；施工期23个月）。 2.5招标范围：本项目包含苏庄大沟（海马洞小河）、斑竹大沟（大尖坡小河）等污 水管网进行改建和治理。完成本项目范围内的施工图设计和施工工作，含施工图概算或工程经济指标、施工图 务 设计及送审，并按照审核通过的施工图完成施工及采购，项目完工后由施工单位出具完整的检测报告，直至完 成竣工验收、整体移交、质量保修责任期内的缺陷修复保修等相关工作。 3、投标人资格要求 3.1项目要求申请人具备下述①、②的资质要求 ：①具备建设行政主管部门核发的市政行业（排水工程）专业乙 商 级及以上设计资质。②具备建设行政主管部门核发的市政公用工程施工总承包二级及以上资质，同时具备有效 期内的安全生产许可证，并在人员、设备、资金等方面具备相应的能力。 3.2项目负责人资格：项目负责人须具备①项目经理须具备市政公用工程专业二级及以上注册建造师资格，具备 有效的安全生产考核合格证（B类），在投标截止日前未在其他在建建设工程（含已经获得中标通知书未开工） 担任项目负责人（项目经理，包括工程总承包道中的施工项目负责人）。②施工项目负责人须具备市政公用工程 专业二级及以上注册建造师资格，具备有效的安全生产考核合格证（B类）。③设计项目负责人须具备注册公用 设备工程师（给水排水）资格。④项目经理、施工项目负责人可以为同一人，项目经理（施工项目负责人）与 设计项目负责人不可以为同一人。 3.3本次招标接受联合体投标。联合体投标的，应满足下列要求：①联合体成员不超过2家，各成员应为独立法人， 管 并提供有效期内的营业执照及资质证书。 ②联合体牵头单位须具备建设行政主管部门核发的市政公用工程施工 总承包二级及以上资质。 ③项目经理须为联合体牵头单位在职员工。 ④联合体各方必须签订联合体协议书，明 确联合体牵头单位和各方的权利义务，联合体牵头单位须代表联合体在投标、签约与履行合同中承担其义务和 法律责任。 ⑤联合体各方没有被暂停或取消投标资格或被有关部门通报在招投标过程中有违法行为。 ⑥联合体 国 各方不得再以自己名义单独或加入其他联合体在本招标项目中参加投标。 ⑦如联合体成员具有相同专业资质， 且联合体协议书有明确分工的，按其分工确定相应专业的资质等级。 ⑧联合体中标的，联合体应当共同与招标 人签订合同，就中标项目向招标人承担连带责任。 3.4各申请人均可就上述标段提出投标申请。 4、招标文中件的获取 凡有意参加投标者，请于2026年08月26日至2026年09月24日,贵阳市公共资源交易中心网站下载（系统使用咨询电 话：0851-84839750、编标工具咨询电话：0851-84839750，交易中心网址：http://ggzy.guiyang.gov.cn） 5、投标文件的递交 5.1投标文件递交的截止时间为2026年09月28日 09:30，通过贵阳市公共资源电子交易系统递交（网 址http://222.85.190.33:82/TPBidder/memberLoginForJsgc） 5.2未在贵阳市公共资源交易中心系统成功上传的电子投标文件，招标人不予受理。 6、发布公告的媒介 本次招标公告同时在全国公共资源交易平台 ( 贵州省·贵阳市)（工程建设类）、贵州省招标投标公共服务平台 上发布。 7、行政监督部门 本次招标的监督部门：贵阳市国家高新技术产业开发区建设工程招标投标办公室。 地址：贵阳市观山湖区阳关大道100号贵阳国家高新区管委会20楼。 电话：0851-84700839。 8、联系方式 招标 招标 贵阳高科城市运营服务有限公司 （代建单位）、贵州高科城市开发集团股份 贵州智聚招标造价 代理 人： 有限公司（建设单位） 咨询有限公司 机构： 李刚（项目负责 联系 联系 隋万全 人）、郭娅、刘佳 人： 人： 丽 电话： 0851-84612641 电话： 13984410692 贵阳高科城市运营服务有限公司 （代建单位）、贵州高科城市开发集团股份有限公司（建设单位） 2026年08月25日 信息来源:https://www.chinapipe.net/project/d3079633.html cqdingjiu 2026.08.25 14:22:32 网 务 商 道 管 国 中</t>
+          <t>米易县老旧小区改造及配套基础设施建设项目(三期)招标计划公告 米易县老旧小区改造及配套基础设施建设项目（三期）招标计划公告 项 米易县 目 老旧小 批 拟招 区改造 准 标项 及配套 关于米易县老旧小区改造及配套基础设施建设项目（三期）初步设计（代项目建议书、可行性研究报告）及概算的批复 文 目名 基础设 米发改审批[2026]139号 件 称： 施建设 及 项目 文 （三期） 号： 网 联 米易城 系 招标人 乡融合 人 （建 发展投 及 设单 资开发 联 邓伊婷 17780587347 务 位）： 有限公 系 司 方 式： 联 商 系 人 招标 及 代理 联 机构： 系 道 方 式： 资 估算 金 总投资 9800000 专项债资金及企业自筹 项目分类： 市政 来 （元）： 管 源： 招标 建筑立面改造8365.5㎡、新建配套设施及环境改造4202.9㎡、硬质铺地2785.5㎡、沥青路面改造1750㎡、污水管网改造、强弱电改造 项目 （飞线下地）、完善照明设施、配套服务设施等。 概括： 国 拟招 序号 招标内容 投标人主要资格条件要求 预计招标时间 拟交易场所 标内 1 设计施工总承包 以招标文件为准 20260928 攀枝花市公共资源交易服务中心 容： 信息来源:https://www.chinapipe.net/project/d3080964.html 中 cqdingjiu 2026.08.26 17:19:23</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>新建网DN500-DN800聚乙烯（改性无水磷石膏）双波峰增强排水管混凝土包封约7450米，与现有污水管网连通，采用聚乙烯（改性无水磷石膏）双波峰增强排水管混凝土包封方式改造污水管网约3000米，新增污水检查井248座。
-https://www.chinapipe.net/project/d3079633.html</t>
+          <t>建筑立面改造8365.5㎡，新建配套设施及环境改造4202.9㎡，硬质铺地2785.5㎡，沥青路面改造1750㎡，污水管网改造、强弱电改造（飞线下地）、完善照明设施、配套服务设施等。
+合计金额（元）：总投资9800000元，专项债资金及企业自筹
+https://www.chinapipe.net/project/d3080964.html</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>贵阳高新区, 麦架河, 生活污水管网, 提升改造, 设计施工总承包, 聚乙烯, 排水管, 改造</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>白云区沙文村城市棚户区改造项目雨、污管网维修整改采购公开询比公告</t>
+          <t>马边彝族自治县城中村改造项目招标计划公告</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2149,58 +2143,59 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>乐山市</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>白云区</t>
+          <t>马边彝族自治县</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>白云区沙文村城市棚户区改造项目雨、污管网维修整改采购。</t>
+          <t>本项目征拆改造实施范围约550亩，改造位于民建镇，共改造拆迁379户，涉及改造拆迁人数1543人，其中：住宅拆迁32677.43平方米，非住宅拆迁6799.68平方米。新建安置房占地面积约23.35亩，安置房套数399套，总建筑面积53545.75平方米，配套建设社区服务功能用房1189.41平方米、地下停车库11690.80平方米（停车位272个）、安置房配套道路1.5公里（含地下综合管网）及其他相关基础设施。</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>本项目采购最高限价为301669.95元(含税3%)。</t>
+          <t>估算总投资402600000.00元</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>雨、污管网</t>
+          <t>房屋建筑工程</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>白云区沙文村城市棚户区改造项目雨、污管网维修整改采购公开询比公告 普诚正华工程咨询有限公司（以下简称采购采购代理机构）受贵阳城市建设工程集团有限责任公司（以下简称 采购人）的委托，对白云区沙文村城市棚户区改造项目雨、污管网维修整改采购进行公开询比采购，资金来源 为自筹资金，欢迎符合资格要求的潜在供应商参加本次采购活动。 一、项目概况与采购范围： 1.项目名称：白云区沙文村城市棚户区改造项目雨、污管网维修整改采购 网 2.项目编号：PCZH2026ZB--177 3.项目概况：白云区沙文村城市棚户区改造项目地址位于贵阳市白云区沙文乡210国道东侧，交通较为便利。由 贵阳市城市建设投资（集团）康居房地产开发有限公司开发建设，总建筑面积：8.4万m，其中塔楼部分为5.4 务 万m、基础工程部分为1.6万m、地下室及塔楼部分建筑面积3万㎡。各建筑高度73.8米，结构形式为框剪结 构，抗震设防烈度为6度。+0.000标高为1303．.5m，设计使用年限50年。地下室为人防及停车场；地上塔楼（2 至22层）为住宅。 4.本项目采购最高限价：301669.95元(含税3%)。 商 5.工期：30日历天 6.交付地点：采购人指定地点。 道 7.采购范围：本次招标范围为白云区沙文村城市棚户区改造项目雨、污管网维修整改采购。 8.质量保证期/服务标准： 管 质量保证期：两年。 质量标准：满足现行的国家规定及行业规范和采购人要求。 国 9.采购文件解释权 本项目采购文件的最终解释权归采购人。 中 二、供应商资格要求 （一）一般资格要求 1.具有独立承担民事责任的能力：提供法人或其他组织的营业执照等证明文件；(复印件或扫描件加盖公章) 2.具有良好的商业信誉和健全的财务会计制度： 具体要求：提供2024年或2025年经第三方审计的财务报告或2026年1月至响应文件递交截止时间前任意一个月由 基本开户银行出具的资信证明；(复印件或扫描件加盖公章)； 3.具有履行合同所必需的设备和专业技术能力： 具体要求：提供具备履行合同所必需的设备和专业技术能力的证明材料或承诺函(供应商自行承诺，加盖公章)； 4.具有依法缴纳税收和社会保障资金的良好记录： 具体要求：提供缴纳所属日期为2026年1月至响应文件递交截止时间前任意一个月依法缴纳税收和社会保障资金 的有效证明材料。依法免税的，提供注册地税务机关出具的有效证明材料；依法不需缴纳社保的，提供注册地 社保机关出具的有效证明材料。(复印件或扫描件加盖公章)； 5.参加本次采购活动前三年内，在经营活动中没有违法违规记录： 提供参加采购活动前3年内在经营活动中没有重大违法记录的书面声明（格式文件详见响应文件范本，加盖公 章）； 6.法律、行政法规规定的其他条件： 供应商须承诺：2023年1月1日至响应文件递交截止时间在“信用中国”网站(https://www. creditchina.gov.cn/) 或中 国执行信息公开网(http://zxgk.court.gov.cn/)中被列入失信被执行人名单(供应商承诺未被列入失信被执行人名单， 并加盖供应商单位公章，采购人保留在上述网站复核的权利)。 7.参加本次采购活动前3年内在经营活动中未被行政或行业相关主管部门限制在全国或采购人所在地投标、承接 业务的书面声明。（格式文件详见响应文件范本） 网 （二）本项目所需特殊行业资质或要求 供应商须具备建设行政主管部门核发的施工劳务企业资质（施工劳务不分等级或建筑业企业劳务备案证书）， 务 并具备有效的安全生产许可证。(提供证书复印件加盖供应商公章)； 本项目技术负责人须具有工程类中级及以上职称。配备持证上岗的施工员1人、质量员1人、安全员1人、劳务人 员1人。 商 （三）本项目不接受联合体投标。 三、获取采购文件的时间、地点及方式： 道 1、时间：2026年08月26日09:00时至2026年08月29日17:00时。 2、获取地点： 管 （1）凡有意参加响应者，请登录贵阳市公共资源国有企业招标采购平台（https://www.ygzcfwy.net/#/）进行项目 报名和下载电子采购文件（未在该采购平台注册过的响应供应商请先注册，注册后进行实名认证，认证通过后 进行企业主体认证）。 通过企业认证后登录进国行项目报名和下载电子采购文件，（点击登录入口-登入后进入投标系统端口-项目列表- 采购项目-我要参与）。 （2）采购文件售价：0元。 中 （3）响应单位注册、报名、网上响应操作等相关业务的咨询，请直接拨打贵阳市国企招采平台技术支持联系电话 （0851-84111471）。 （4）请各供应商自行确定单位信息，如因填写错误导致投标失败的责任自负。 四、评审时间、地点： 1．响应文件递交的截止时间及评审时间：2026年08月31日14：00时。 2.递交响应文件及评审地点：贵阳市公共资源国有企业招标采购平台（https://www.ygzcfwy.net/#/）。 五、公告发布的媒介： 本次采购公告在贵阳市公共资源国有企业招标采购平台：（https://www.ygzcfwy.net/#/）、贵州省招标投标公共服 务平台、贵阳城市建设工程集团有限责任公司上发布。 六、采购人及采购代理机构的名称、地址、联系方式： 1、采购人信息 采购人名称：贵阳城市建设工程集团有限责任公司 地址：贵阳市观山湖区西南国际商贸城2一G栋 联系人：龙云丹 联系电话：19385012069/0851-859801784 2、采购代理机构信息 采购代理名称：普诚正华工程咨询有限公司 联系人：陈芊羽、王雨莲、吴晓芳 地 址：贵州省贵阳市观山湖区诚信路G03-07号麒龙中央商务大厦B1栋17楼2号 网 联系电话：18685007775 务 信息来源:https://www.chinapipe.net/project/d3079628.html cqdingjiu 2026.08.25 14:22:32 商 道 管 国 中</t>
+          <t>马边彝族自治县城中村改造项目招标计划公告 马边彝族自治县城中村改造项目招标计划公告 马边彝族自治县发展和改革局 关于《马边彝族自治县城中村 招标项目 项目批准文件及文号 马边彝族自治县城中村改造项目 改造项目可行性研究报告（代 名称 （如有） 项目建议书）》的批复(马发展 改革【2026】30号) 招标人 马边彝族自治县住房和城乡建设局 联系人及联系方式 网简老师:0833-2765625 估算总投资 402600000.00 项目分类 房屋建筑工程 （元） 本项目征拆改造实施范围约550亩，改造位于民建镇，共改造拆迁379户，涉及改造拆迁人数1543人， 务 其中：住宅拆迁32677.43平方米，非住宅拆迁6799.68平方米。新建安置房占地面积约23.35亩，安置 招标项目 房套数399套，总建筑面积53545.75平方米，配套建设社区服务功能用房1189.41平方米、地下停车 概况 库11690.80平方米（停车位272个）、安置房配套道路1.5公里（含地下综合管网）及其他相关基础设 施。 商 序号 招标内容 投标人主要资格条件要求 预计招标时间 拟招标内 1 设计施工总承包 详见招标文件 2026-11-30 00:00:00 容 2 监理 详见招标道文件 2026-11-30 00:00:00 备注：提前发布的招标计划内容仅供各方主体提前获知项目基本信息和拟招标内容，招标项目的实际信息以招 标人最终发布的招标公告和招标文件为准。 信息来源:https://www.chinapipe.net/project/d3080961.html 管 cqdingjiu 2026.08.26 17:19:23 国 中</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>白云区沙文村城市棚户区改造项目雨、污管网维修整改采购。
-https://www.chinapipe.net/project/d3079628.html</t>
+          <t>本项目征拆改造实施范围约550亩，改造位于民建镇，共改造拆迁379户，涉及改造拆迁人数1543人，其中：住宅拆迁32677.43平方米，非住宅拆迁6799.68平方米。新建安置房占地面积约23.35亩，安置房套数399套，总建筑面积53545.75平方米，配套建设社区服务功能用房1189.41平方米、地下停车库11690.80平方米（停车位272个）、安置房配套道路1.5公里（含地下综合管网）及其他相关基础设施。
+合计金额（元）：估算总投资402600000.00元
+https://www.chinapipe.net/project/d3080961.html</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>管材招标, 雨、污管网, 城市棚户区改造</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>中交一公局集团有限公司2026年8月茅台老区管网改造项目不锈钢管及管件流标公告</t>
+          <t>陵川县县城雨污分流源头治理改造及错接混接改造工程招标控制价</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2210,7 +2205,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2225,50 +2220,59 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>贵州省</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+          <t>四川省</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>晋城市</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>陵川县</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>本项目为茅台老区管网改造项目的不锈钢管及管件招标。</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>不锈钢管及管件</t>
+          <t>项目详细内容无法识别</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>中交一公局集团有限公司2026年8月茅台老区管网改造项目不锈钢管及管件流标公告 中交一公局集团有限公司2026年8月茅台老区管网改造项目不锈钢管及管件流标公告 各投标人： 中交一公局集团有限公司2026年8月茅台老区管网改造项目不锈钢管及管件招标（采购方案编号：FA00000661399） 包件1，三家参与投标供应商，因其中一家投标人未按招标文件要求及时足额提交投标保证金，符合性评审不通 过，导致有效投标人不足三家按流标处理，现对该包件进行流标。 网 特此公告 务 商 中交一公局集团有限公司茅台制酒车间（二期）管网改造老区标段项目经理 部 道 2026年8月25日 信息来源:https://www.chinapipe.net/project/d3079623.html 管 cqdingjiu 2026.08.25 14:22:32 国 中</t>
+          <t>陵川县县城雨污分流源头治理改造及错接混接改造工程招标控制价 详见附件。 信息来源:https://www.chinapipe.net/project/d3080958.html cqdingjiu 2026.08.26 17:19:24 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>本项目为茅台老区管网改造项目的不锈钢管及管件招标。
-https://www.chinapipe.net/project/d3079623.html</t>
+          <t>项目详细内容无法识别
+合计金额（元）：项目详细内容无法识别
+https://www.chinapipe.net/project/d3080958.html</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>管网改造, 不锈钢管, 管件, 招标</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>兴义市捧乍镇垛坎村蔬菜基地节水灌溉管网建设项目采购公告</t>
+          <t>叙永县水务局2026年饮水巩固提升项目抗旱管道采购竞争性磋商公告</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2278,7 +2282,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>水利</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2293,43 +2297,44 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>黔西南布依族苗族自治州</t>
+          <t>泸州市</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>兴义市</t>
+          <t>叙永县</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>新建输水主管2701m，新建输水支管（PE100DN40（0.8MPa）灌溉管道）4700m，新建闸阀井5座，新建灌桩130座。</t>
+          <t>本项目为叙永县水务局的2026年饮水巩固提升项目抗旱管道采购，预算金额为600,000.00元。</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>预算金额（元）：500000.00元 最高限价（元）：457000.00元</t>
+          <t>预算金额：600,000.00元</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>PE100DN40（0.8MPa）灌溉管道</t>
+          <t>抗旱管道</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>兴义市捧乍镇垛坎村蔬菜基地节水灌溉管网建设项目采购公告 项目概况 兴义市捧乍镇垛坎村蔬菜基地节水灌溉管网建设项目招标项目的潜在投标人应在贵州鼎冠项目管理咨询有限公司 （兴义市桔山街道新河一街）获取采购文件，并于 2026年 09月 04 日 16:00 时（北京时间）前提交响 应文件。 一、项目基本情况 项目编号： GZDG-2026（采）-008-03 网 项目名称：兴义市捧乍镇垛坎村蔬菜基地节水灌溉管网建设项目 采购方式：竞争性磋商 务 预算金额（元）：500000.00元 最高限价（元）：457000.00元 商 采购需求：新建输水主管2701m，新建输水支管（PE100DN40（0.8MPa）灌溉管道）4700m，新建闸阀井5座，新 建灌桩130座。 数量：1 项 道 简要规格描述：详见竞争性磋商文件“工程量清单及商务要求”。 合同履约期限：4个月。 管 本项目（是/否）接受联合体投标：否。 二、申请人的资格要求： 国 （1）一般资格要求 投标人符合《中华人民共和国政府采购法》第二十二条的基本规定条件，须提供政府采购法实施条例第十七条 规定资料： 中 1)具有独立承担民事责任的能力：提供法人或者其他组织的营业执照等证明文件； 2)具有良好的商业信誉和健全的财务会计制度：提供具有良好的商业信誉和健全的财务会计制度的承诺函（自行 书面承诺，格式自拟）； 3)具有依法缴纳税收和社会保障资金的良好记录：提供具有依法缴纳税收和社会保障资金的良好记录的承诺函 （自行书面承诺，格式自拟）； 4）具有履行合同所必需的设备和专业技术能力：提供具有履行合同所必需的设备和专业技术能力的承诺函（自 行书面承诺，格式自拟）； 5）参加政府采购活动前三年内，在经营活动中没有重大违法记录：提供参加政府采购活动前三年内在经营活动 中没有重大违法记录的承诺函（自行书面承诺）； 6）单位负责人为同一人或者存在直接控股、管理关系的不同投标人，不得参加同一合同项下的政府采购活动。 除单一来源采购项目外，为采购项目提供整体设计、规范编制或者项目管理、监理、检测等服务的投标人，不 得再参加该采购项目的其他采购活动（自行书面承诺，格式自拟）； 7)投标供应商须承诺：在“信用中国”网站（www.creditchina.gov.cn）、中国政府采购网（www.ccgp.gov.cn）等 渠道查询中未被列入失信被执行人名单、重大税收违法失信主体、政府采购严重违法失信行为记录名单中，如 被列入失信被执行人、重大税收违法失信主体、政府采购严重违法失信行为记录名单中的投标人取消其投标资 格，并承担由此造成的一切法律责任及后果（自行书面承诺，格式自拟）； 8)联合体投标：本项目不接受任何形式的联合体投标（自行书面承诺，格式自拟）； 9）根据中华人民共和国《政府采购促进中小企业发展管理办法》（财库〔2020〕46号）及《关于政府采购支持 监狱企业发展有关问题的通知》（财库〔2014〕68号）的精神，财政部印发通知《进一步加大政府采购支持中小 企业力度》（财库〔2022〕19号）及《黔西南州政府采购营商环境提升专项行动方案》（州财采〔2022〕2号） 的通知，本项目属于专门面向中小企业采购的项目，供应商应为中小企业，监狱企业、残疾人福利性单位视同 为小型、微型企业（供应商为中小企业的提供中小企业声明函，为监狱企业的提供属于监狱企业的证明文件， 为残疾人福利性单位的提供残疾人福利性单位声明函）。 （2）特殊资格要求： 网 (1）投标人须具备建设行政主管部门颁发的水利水电工程施工总承包贰级及以上资质。 (2）投标人须具备有效的安全生产许可证。 务 三、获取采购文件 时间：2026 年 08 月 26 日至 2026年 09 月01 日，每天上午 09:00 至 12:00，下午14:30 至 17:00 （北京时间，法定节假日除外） 商 地点：贵州鼎冠项目管理咨询有限公司（兴义市桔山街道新河一街）。 方式：有意参加竞标的投标人请持法定代表人证明书、法人身份证原件或授权委托人授权委托书、委托人身份 证原件，营业执照、资料真实性承诺函（以上道资料均需加盖单位公章及法定代表人印章）到贵州鼎冠项目管理 咨询有限公司（兴义市桔山街道新河一街）获取； 售价：300 元。 管 开户银行及账号（注：报名费收款账户） 开户单位名称：贵州鼎冠项目管理咨询有限公司 开户银行： 贵州银行股国份有限公司兴义市支行 开户账号： 090070001600023369 中 四、响应文件提交 截止时间：2026 年 09 月04 日 16:00（北京时间） 地点：贵州鼎冠项目管理咨询有限公司（兴义市桔山街道新河一街）。 五、响应文件开启 开标时间：2026 年 09 月04 日 16:00（北京时间） 地点：贵州鼎冠项目管理咨询有限公司（兴义市桔山街道新河一街）。 六、公告期限 自本公告发布之日起 5 个工作日。 七、其他补充事宜： 本项目属于专门面向中小企业采购的项目。 八、凡对本次招标提出询问，请按以下方式联系。 1 、采购人信息 名 称： 兴义市捧乍镇人民政府 地 址：兴义市捧乍镇 联 系 人：罗先生 联系方式：18286938554 2 、代理机构信息 网 名 称：贵州鼎冠项目管理咨询有限公司 地 址：兴义市桔山街道新河一街 务 项目联系人：马先生 联系电话：15685979901 商 信息来源:https://www.chinapipe.net/project/d3079626.html cqdingjiu 2026.08.25 14:22:32 道 管 国 中</t>
+          <t>叙永县水务局2026年饮水巩固提升项目抗旱管道采购竞争性磋商公告 项目概况 2026年饮水巩固提升项目抗旱管道采购的潜在供应商应在四川省政府采购一体化平台项目电子化交易系统（以下 简称“项目电子化交易系统”）获取采购文件，并于 2026年09月07日 10时30分（北京时间）前提交响应文件。 本项目通过项目电子化交易系统实行电子化采购。 一、项目基本情况 网 项目编号：N5105242026000225 项目名称：2026年饮水巩固提升项目抗旱管道采购 务 采购方式：竞争性磋商 预算金额：600,000.00元 商 采购需求：详见采购需求附件 合同履行期限： 道 采购包1：30个工作日内 管 本项目是否接受联合体参与： 采购包1：不接受联合国体投标 二、申请人的资格要求： 中 1.满足《中华人民共和国政府采购法》第二十二条规定： （1）具有独立承担民事责任的能力；（2）具有良好的商业信誉和健全的财务会计制度；（3）具有履行合同所 必需的设备和专业技术能力；（4）有依法缴纳税收和社会保障资金的良好记录；（5）参加政府采购活动前三年 内，在经营活动中没有重大违法记录。 2.落实政府采购政策需满足的资格要求： 采购包1： 本项目属于专门面向中小企业采购，提供《中小企业声明函》，残疾人福利性单位提供《残疾人福利性单位声 明函》，监狱企业提供由省级以上监狱管理局、戒毒管理局（含新疆生产建设兵团）出具的属于监狱企业的证 明文件。 3.本项目的特定资格要求： 采购包1： (1)供应商所供产品均须提供行政主管部⻔颁发有效期内的《涉及饮用水卫生安全产品卫生许可批件》复印件。。 三、获取采购文件 时间： 2026年08月26日至 2026年09月02日，每天上午 00:00:00至 12:00:00，下午 12:00:00至 23:59:59（北京时间） 途径： 项目电子化交易系统-投标（响应）管理-未获取采购文件中选择本项目获取招标文件 方式： 在线获取 网 售价： 0元 四、响应文件提交 务 截止时间： 2026年09月07日 10时30分00秒 （北京时间） 地点： 通过项目电子化交易系统-投标（响应）管理在线提交响应文件 五、开启 商 时间： 2026年09月07日 10时30分00秒 （北京时间） 地点： 通过项目电子化交易系统-开标/开启大道厅参与开启 六、公告期限 自本公告发布之日起 3 个工作日。 管 七、其他补充事宜 无。 国 八、凡对本次采购提出询问，请按以下方式联系。 中 1.采购人信息 名称： 叙永县水务局 地址： 叙永县叙永镇百花路6号纳米银园区3号楼 联系方式： 0830-6227960 2.采购代理机构信息 名称： 四川新联工程项目管理有限公司 地址： 四川省乐山市市中区柏杨中路350号CBD写字楼11楼1120号 联系方式： 0833-2408678 3.项目联系方式 项目联系人： 张先生 电话： 0833-2408678 四川新联工程项目管理有限公司 2026年08月26日 信息来源:https://www.chinapipe.net/project/d3080957.html cqdingjiu 2026.08.26 17:19:24 网 务 商 道 管 国 中</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>新建输水主管2701m，新建输水支管（PE100DN40（0.8MPa）灌溉管道）4700m，新建闸阀井5座，新建灌桩130座。
-https://www.chinapipe.net/project/d3079626.html</t>
+          <t>本项目为叙永县水务局的2026年饮水巩固提升项目抗旱管道采购，预算金额为600,000.00元。
+合计金额（元）：预算金额：600,000.00元
+https://www.chinapipe.net/project/d3080957.html</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -2337,14 +2342,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>管材, 招标, 灌溉管网</t>
+          <t>2026年, 饮水巩固提升项目, 抗旱管道采购</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FA00000677279航科物流雨水管公开直接采购公告</t>
+          <t>未来科技城卫星互联网及卫星应用片区区域性热力站项目施工/标段招标公告</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2354,7 +2359,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>房建</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2369,54 +2374,59 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>仁怀市</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>给排水管</t>
+          <t>本项目为未来科技城卫星互联网及卫星应用片区区域性热力站项目。为卫星互联网及卫星应用片区统一供能，热力站用地面积约5347平方米，建筑面积约6251平方米，包含热源塔、工艺设备布置区、高低压配电及变电室等。项目采用热源塔+水泵机组+水蓄能工艺。场外管网采用直埋敷设方式，管网敷设长度约6500米，主要建设内容包括建筑国与装饰工程、安装工程、站内工艺工程、总平工程、站外管网工程、外电工程、边坡工程等。</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>项目详细内容无法识别</t>
+          <t>项目业主为成都高新东策建设开发有限公司，建 设资金来自国家投资-非政府投资，项目出资比例为100%。</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>钢带增强聚乙烯螺旋波纹管,给水用聚乙烯(PE)管,建筑排水用硬聚氯乙烯(PVC-U)管,排水用(PVC-U)90°顺水三通,排水用(PVC-U)45°弯头</t>
+          <t>热力站项目</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>FA00000677279航科物流雨水管公开直接采购公告 公开直接采购公示 一、基本情况 采购人：武汉航科物流有限公司 采购项目名称：武汉航科物流有限公司广西事业部给排水管采购 网 采购项目内容：给排水管 二、拟采购的货物/服务情况 务 采购给排水管，规格型号见清单。 运输起点：重庆璧山重庆顾地塑胶电器有限公司 交货地点：贵州省遵义市仁怀市茅台镇茅台酒厂内 商 三、采用合作洽谈采购方式的原因及相关说明 我司投标一共六茅台酒厂排水管材料，我司以道最低报价中标，供货周期2026年8月-2026年12月。标书中要求：根 据业主方要求，螺旋波纹管推荐品牌为联塑、中财管道、顾地、金牛管业、亚通。投标阶段仅顾地向我司报价 并给与授权文件，亚通直投不做对我司报价，其他品牌未响应我司的询价单。现项目要求我司组织安排发货， 厂家生产成品需要时间，导致供货周期紧张。顾地作为大型上市公司属于集团集采品牌，质量稳定，运距最优 （场地在重庆局里项目200多公里）报价最低，符合业主茅台集团及一公局六公司品牌要求，申请向顾地科技股 管 份有限公司厂家直购。 四、拟定的供应商名称 供应商名称：顾地科技国股份有限公司 五、公示期限 本公示自发布之日起公示[3]日。如有异议，请在此期限内以书面形式向采购人反馈。 中 六、联系方式 采购联系人：丁一 联系电话：13986196940 业务联系人：王恩宏 联系电话：15827442527 监督部门联系方式：举报电话：027-52301078； 举报邮箱：hkwljiwei@wujigang.cn； 联系人：李信良 请广大供应商和社会公众予以监督，确保采购活动的公开、公平、公正。 特此公示。 采购单位：武汉航科物流有限公司 日期：2026年8月25日 物资信息 1 钢带增强聚乙烯螺旋波纹管 DN300mm 钢带增强聚丙烯（PP-HM） 13% 米 2 钢带增强聚乙烯螺旋波纹管 DN400mm 钢带增强聚丙烯（PP-HM） 13% 米 3 钢带增强聚乙烯螺旋波纹管 DN500mm 钢带增强聚丙烯（PP-HM） 13% 米 网 4 钢带增强聚乙烯螺旋波纹管 DN600mm 钢带增强聚丙烯（PP-HM） 13% 米 5 钢带增强聚乙烯螺旋波纹管 DN800mm 钢带增强聚丙烯（PP-HM） 13% 米 6 钢带增强聚乙烯螺旋波纹管 DN1000mm 钢带增强聚丙烯（PP-HM） 13% 米 务 7 钢带增强聚乙烯螺旋波纹管 DN1200mm 钢带增强聚丙烯（PP-HM） 13% 米 8 钢带增强聚乙烯螺旋波纹管 DN1400mm 钢带增强聚丙烯（PP-HM） 13% 米 9 钢带增强聚乙烯螺旋波纹管 DN1600mm 钢带增强聚丙烯（PP-HM） 13% 米 商 10 给水用聚乙烯(PE)管 500mm DE500*10mm 13% 米 11 给水用聚乙烯(PE)管 500mm DE400*10mm 13% 米 12 给水用(PE)热熔异径三通 通用mm 通用Mpa DE500*300mm 13% 个 道 13 给水用(PE)热熔异径三通 通用mm 通用Mpa DE400*300mm 13% 个 14 给水用(PE)热熔45°弯头 通用mm 通用Mpa DE500*10mm 45° 13% 个 15 给水用(PE)热熔45°弯头 通用mm 通用Mpa DE400*10mm 45° 13% 个 管 16 建筑排水用硬聚氯乙烯(PVC-U)管 160mm D160*4 13% 米 17 建筑排水用硬聚氯乙烯(PVC-U)管 200mm D200*4.9 13% 米 18 建筑排水用硬聚氯乙烯(PVC-U)管 315mm D315*7.7 13% 米 国 19 排水用(PVC-U)90°顺水三通 dn200*200mm 弹性密封圈连接 D200*160 13% 个 20 排水用(PVC-U)90°顺水三通 dn200*200mm 弹性密封圈连接 D315*160 13% 个 21 排水用(PVC-U)90°顺水三通 dn200*200mm 弹性密封圈连接 D315*200 13% 个 中 22 排水用(PVC-U)90°顺水三通 dn200*200mm 弹性密封圈连接 D160 13% 个 23 排水用(PVC-U)90°顺水三通 dn200*200mm 弹性密封圈连接 D200 13% 个 24 排水用(PVC-U)90°顺水三通 dn200*200mm 弹性密封圈连接 D315 13% 个 25 排水用(PVC-U)45°弯头 dn200mm 胶粘剂连接 D160 45° 13% 个 26 排水用(PVC-U)90°弯头 dn200mm 胶粘剂连接 D160 90° 13% 个 27 排水用(PVC-U)45°弯头 dn200mm 胶粘剂连接 D200 45° 13% 个 28 排水用(PVC-U)90°弯头 dn200mm 胶粘剂连接 D200 90° 13% 个 29 排水用(PVC-U)45°弯头 dn200mm 胶粘剂连接 D315 45° 13% 个 30 排水用(PVC-U)90°弯头 dn200mm 胶粘剂连接 D315 90° 13% 个 信息来源:https://www.chinapipe.net/project/d3079607.html cqdingjiu 2026.08.25 14:22:32</t>
+          <t>未来科技城卫星互联网及卫星应用片区区域性热力站项目施工/标段招标公告 未来科技城卫星互联网及卫星应用片区区域性热力站项目施工 / 标段 招标公告 1．招标条 件 网 1.1本招标项目未来科技城卫星互联网及卫星应用片区区域性热力站项目施工 / 标段已由成都高新区发展改革局以 川投资备【2412-510109-04-01-121690】FGQB-0864号批准建设，项目业主为成都高新东策建设开发有限公司，建 设资金来自国家投资-非政府投资，项目出资比例为100%，招标人为成都高新未来科技城建设投资有限公司。项 务 目已具备招标条件，现进行公开招标。 1.2本招标项目由成都高新区发展改革局核准（招标事项核准文号为川投资备 【2412-510109-04-01-121690】FGQB-0864号）的招标组织形式为委托招标。招标人选择的招标代理机构是四川华 通建设工程造价管理有限责任公司。 商 本标段行政监督部门为成都高新技术产业开发区公园城市建设局，采用“评定分离”方式进行评标定标。 道 2．项目概况与招标范围 2.1建设地点：成都高新区未来科技城。 管 2.2建设规模：本项目为未来科技城卫星互联网及卫星应用片区区域性热力站项目。为卫星互联网及卫星应用片 区统一供能，热力站用地面积约5347平方米，建筑面积约6251平方米，包含热源塔、工艺设备布置区、高低压配 电及变电室等。项目采用热源塔+水泵机组+水蓄能工艺。场外管网采用直埋敷设方式，管网敷设长度约6500米， 主要建设内容包括建筑国与装饰工程、安装工程、站内工艺工程、总平工程、站外管网工程、外电工程、边坡工 程等。具体建设规模以设计文件为准。 2.3计划工期：540日历天。 中 2.4招标范围：本标段施工图设计范围内的所有工作内容的施工，具体详见施工图及工程量清单。 2.5标段划分：1个标段。 2.6质量标准：达到国家现行质量合格标准。 3．投标人资格要求 3.1 本次招标要求投标人： 3.1.1须具有 ①国家建设行政主管部门颁发的建筑工程施工总承包三级及以上资质；②国家建设行政主管部门颁 发的市政公用工程施工总承包二级及以上资质； 3.1.2信誉要求：不存在投标人须知第1.4.3项规定的限制投标的情形； 3.1.3所有投标人（无资质企业除外）应具有针对本标段的《成都市建设领域市场主体基础信息网络登记表》（如 投标人为联合体，则联合体所有成员均应具有）、《成都市建设领域从业人员基础信息网络登记表》（如投标 人为联合体，则联合体所有成员均应具有）。 3.1.4 拟派项目经理（项目负责人）具有建筑工程专业二级或以上注册建造师证书，须具备有效的安全生产考核 合格B证，业绩要求：无（业绩要求），须为本单位人员（若为联合体投标，须为联合体牵头人人员）。 3.1.5财务要求：无财务要求； 3.1.6类似工程业绩要求： 近年（2023年01月01日至投标截止时间，不少于3年）已完成或正在施工或新承接的项目共不少于3个类似工程业 绩。 类似工程业绩是指:单个合同金额不低于7000万元的房屋建筑工程施工业绩（若为联合体投标，类似工程业绩由 联合体牵头人提供） 3.2本次招标接受联合体投标。 网 联合体投标的，应满足下列要求：须具有国家建设行政主管部门颁发的建筑工程施工总承包三级及以上资质的 单位作为联合体牵头人。联合体成员（含联合体牵头人）家数须不超过2家。 务 联合体需符合有关联合体投标的规定和要求，并提交了联合体协议，明确联合体牵头人和各方权利义务。 3.3 各投标人均可就上述1个标段投标，可中标的标段数量为1个。 商 4．招标文件的获取 4.1凡有意参加投标者，请于2026年08月27日起道，在成都市公共资源电子交易云平台(www.cdggzy.com）（以下简称 “电子交易云平台”）免费下载招标资料（招标文件及相关资料），获得“拟投标项目回执”。 4.2招标人 不提供 邮购招标文件服务。 管 5．投标文件的递交 5.1 投标文件递交的截止时间（投标截止时间，下同）为2026年09月21日09时30分，招标人或其委托代理机构，以 及已在投标截止时间前按规定上传投标文件的投标人，均应在开标当日投标截止时间前登录不见面开标系统 （网址：www.cdggzy.c国om），录入相关人员姓名、电话等基本信息。投标人未按时登录不见面开标系统，错过开 标解密时间的，由投标人自行承担不利后果。 5.2 投标人应在解密开始后30分钟内在线完成投标文件解密。投标文件未能在规定时间内成功解密的，视为投标 人未在规定时间内提交投标文件，由投标人自行承担责任。不见面开标项目不接受投标人现场递交光盘等形式 中 的投标文件，不接受投标人现场解密投标文件。 6．发布公告的媒介 本次招标公告在全国公共资源交易平台（四川省）（网址：http://ggzyjy.sc.gov.cn）上发布。 7．行政监督部门 单位名称：成都高新技术产业开发区公园城市建设局 联系电话：028-27280892 8. 联系方式 招 标 人：成都高新未来科技城建设投资有限公司 地 址：成都高新未来科技城大厦 邮 编：/ 联 系 人：李女士 电 话：028-27250895 传 真：/ 电子邮件：/ 网 址：/ 开户银行：/ 账 号：/ 网 招标代理机构：四川华通建设工程造价管理有限责任公司 务 地 址：成都市高新区吉泰路666号福年广场T1栋 邮 编：/ 商 联 系 人：罗女士 项目负责人：张军岐 道 电 话：028-86610077-5888 传 真：/ 管 电子邮件：/ 网 址：/ 开户银行：/ 国 账 号：/ 中 信息来源:https://www.chinapipe.net/project/d3080944.html cqdingjiu 2026.08.26 17:19:24</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>给排水管
-https://www.chinapipe.net/project/d3079607.html</t>
+          <t>本项目为未来科技城卫星互联网及卫星应用片区区域性热力站项目。为卫星互联网及卫星应用片区统一供能，热力站用地面积约5347平方米，建筑面积约6251平方米，包含热源塔、工艺设备布置区、高低压配电及变电室等。项目采用热源塔+水泵机组+水蓄能工艺。场外管网采用直埋敷设方式，管网敷设长度约6500米，主要建设内容包括建筑国与装饰工程、安装工程、站内工艺工程、总平工程、站外管网工程、外电工程、边坡工程等。
+合计金额（元）：项目业主为成都高新东策建设开发有限公司，建 设资金来自国家投资-非政府投资，项目出资比例为100%。
+https://www.chinapipe.net/project/d3080944.html</t>
         </is>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>未识别到明确匹配关键词</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>中交一公局集团有限公司2026年8月茅台管网改造老区项目不锈钢管及管件采购招标公告</t>
+          <t>W3中国核建中核华辰300MW燃料元件及含钆燃料棒生产建设工程建筑安装施工项目保温材料常规采购(第二次)采购公告</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2426,7 +2436,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>市政</t>
+          <t>房建</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2441,58 +2451,59 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>宜宾市</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>叙州区</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>贵州茅台酒股份有限公司茅台本部制酒车间（二期）管网改造老区标段项目制酒9--18车间、制酒8车间1--4号房区域排水管网改造。</t>
+          <t>中国核建中核华辰300MW燃料元件及含钆燃料棒生产建设工程建筑安装施工项目保温材料常规询比采购。</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>项目已具备招标条件，现对不锈钢管及管件进行公开招标。中标价3.77亿元。</t>
+          <t>本项目网已具备采购条件，由采购实施单位 中国核工业建设股份有限公司 组织实施采购，由采购需求单位根据采购结果签订采购合同/协议。</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>不锈钢管及管件</t>
+          <t>保温材料</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>中交一公局集团有限公司2026年8月茅台管网改造老区项目不锈钢管及管件采购招标公告 中交一公局集团有限公司2026年8月茅台管网改造老区项目不锈钢管及管件采购招标公告 1.招标条件 网 本招标项目茅台管网改造老区项目，招标人为中交一公局集团有限公司茅台制酒车间（二期）管网改造老区标 段项目经理部，招标项目资金来自业主计量款。项目已具备招标条件，现对不锈钢管及管件进行公开招标。 2.项目概况与招标范围 务 2.1 茅台管网改造老区项目项目：贵州茅台酒股份有限公司茅台本部制酒车间（二期）管网改造老区标段项目制 酒 9--18 车间、制酒 8 车间1--4 号房区域排水管网改造。主要建设内容：新增不锈钢管道单独资源化收集窖底水； 地锅水收集管更换为不锈钢管；生活污水收集管更换为涂塑钢管；新增初期雨水收集系统，将厂区初期雨水收 商 集后进入污水处理厂处理；新增微型管沟系统、视频监控系统，实现排水系统可视化管理。本工程为EPC项目， 由中交一公局集团有限公司实施。中标价3.77亿元。计划2026年12月30日完工。 项目地址：贵州省遵义市仁怀市茅台镇茅台酒厂内 道 联系人及联系电话： 项目名称 联系人 联系电话 管 茅台老区管网改造项目 刘亚鹏 13709282552 国 2.2 招标内容 本次招标采购物资的名称、数量、技术规格、交货地点、交货期等详见“物资需求一览表”。 中 物资需求一览表： 预 项 计 交 计 包 序 目 物资 量 采购数 货 供 件 规格型号 材质 备注 号 简 名称 单 量 地 货 号 称 位 点 周 期 316不 锈钢 316 1 米 DN108*4 800 GB/T14976-2025 无缝 无缝 钢管 316不 锈钢 316 2 米 DN159*4 400 GB/T14976-2025 无缝 无缝 钢管 316不 网 锈钢 316 3 米 DN219*4 20000 GB/T14976-2025 无缝 无缝 钢管 316不 务 锈钢 316 4 米 DN325*4 12000 GB/T14976-2025 无缝 无缝 钢管 316不 商 锈钢 316 5 米 DN630*6 2300 GB/T14976-2025 无缝 贵 无缝 钢管 州 省 道 无缝 316 6 个 325*219*4 50 遵 GB/T12459-2025 茅 直接 无缝 义 台 无缝 市 316 7 老 个 108*4 90EL 60 20 GB/T12459-2025 弯头 仁 无缝 区 管26 怀 管 无缝 年8 316 8 01 个 219*4 45EL 100 市 GB/T12459-2025 网 弯头 月2-026 无缝 茅 改 年12 无缝 台 316 9 造 个国219*4 90EL 400 月 GB/T12459-2025 弯头 镇 无缝 项 无缝 茅 316 10 目 个 325*4 45EL 100 GB/T12459-2025 弯头 台 无缝 酒 中无缝 316 11 个 325*4 90EL 1000 厂 GB/T12459-2025 弯头 无缝 内 无缝 316 12 个 630*6 90EL 10 GB/T12459-2025 弯头 无缝 无缝 316 13 个 219*4 110 GB/T12459-2025 三通 无缝 无缝 316 14 个 325*4 450 GB/T12459-2025 三通 无缝 无缝 316 15 个 325*219*4 100 GB/T12459-2025 三通 无缝 不锈 16 钢检 套 DN200 10 查口 不锈 316 GB/T12459-2025 含三通、盲板、法兰、螺母、螺 17 钢检 套 DN300 300 无缝 栓、四氟垫 查口 不锈 18 钢检 套 DN600 60 查口 小计 38250 注：根据业主要求，不锈钢管及管件推荐品牌：久立、武进不锈、上上、华迪钢业、永上、中钢不锈钢、盛徳 鑫泰、丰业、青山钢管、隆达、东方齐心、浙江德威、浙江博盛。若供应其他品牌需报项目申报在投标文件中 附经“贵州茅台酒股份有限公司规划建设部”同意并由项目签认的书面确认文件。 3.投标人资格要求 3.1 投标人资格条件要求 网 （1）在中华人民共和国境内依法注册，投标人具有独立法人资格、具有招标物资生产经营范围的生产商或销售 商。（个体工商户禁止参与） （2）品质档次：按照“茅台制酒车间(二期)管网改造老区标段主要材料品质档次参考表”的要求，不锈钢管及 务 管件参考品牌：浙江久立特材科技股份有限公司、江苏武进不锈股份有限公司、上上德盛集团股份有限公司、 华迪钢业集团有限公司、浙江永上特材有限公司、中钢不锈钢管业科技山西有限公司、盛德鑫泰新材料股份有 限公司、丰业集团有限公司、青山钢管有限公司、隆达钢业集团有限公司、浙江东方齐心钢业集团有限公司、 浙江德威不锈钢管业股份有限公司、浙江博盛钢业集团有限公司；需报项目申报在投标文件中附经“贵州茅台 酒股份有限公司规划建设部”同意并由项目签认的书面确商认文件。（贸易商需提供生产厂家的盖章版授权委托 书并附于投标文件中，否则视为投标无效，供货产品品牌必须与投标文件所报品牌保持一致，未经招标人同意， 严禁随意变更供货品牌。）投标人需附投标品牌对应规格型号不锈钢管生产资质证明文件（特种设备型式试验 证书）。 道 （3）送样封样要求：应业主要求，投标人需在投标截止前，将316不锈钢无缝管送至或邮寄两份样品（DN219*4、 DN325*4型号各两根，长度为0.3m）至茅台规建部进行封存，附带质量保证资料。投标人需将招标人提供的送样 证明文件附于投标文件中，逾期未送达或未附送样证明文件视为投标无效。样品必须满足招标文件的相关指标， 如投标人中标后供应材料过程中所供应材料和封存样品质量不一致或达不到招标要求文件中材料的技术质量要 管 求，招标人有权取消其中标资格。 （4）其他要求：必须是中交招采网供应商库中的合格供应商，不接受被中国交通建设集团有限公司列入限制交 易黑名单、重点关注名单的供应商。 国 3.2出口管制合规。【投标人】知晓【招标人】被美国政府列入贸易管制名单的情况，承诺在本项目中拟提供给 【招标人】的【产品/软件/技术】不受美国《出口管理条例》及美国其他相关出口管制规定的管制。【招标人】从 【投标人】获取【产品/软件/技术】的行为不会违反美国出口管制的相关规定。 中 3.3 本次招标不接受联合体投标。 3.4 单位法人代表为同一人或存在控股、管理关系的不同单位，不得同时参加本项目投标，否则相关投标文件均 视为无效。 3.5 每个投标人能参与单个包件投标。不同标段每个投标人允许中1个包件。 3.6 至投标截止时间，若投标人出现以下情况，其投标将被拒绝： （1）被省级及以上行业主管部门取消招标项目所在地的投标资格且处于有效期内； （2）被责令停业，暂扣或吊销执照，或吊销资质证书； （3）进入清算程序，或被宣告破产，或其他丧失履约能力的情形； （4）在国家企业信用信息公示系统（http://www.gsxt.gov.cn/）中被列入严重违法失信、经营异常企业名单； （5）在“信用中国”网站（http://www.creditchina.gov.cn/）中被列入严重失信主体名单。 4.招标文件的获取 4.1 凡有意参加投标者，请于2026年8月25日至2026年8月30日14时00分(北京时间，下同），登录“中交招采 网”（网址：https://zjzcw.iccec.cn）获取电子招标文件。 4.2 招标文件的获取： 免费下载 □出售，每套售价 元（采购文件中提到的货币单位除有特别说明外，均指人民币元，下同），售后不退。供 应商应于 年 月 日 时前以电汇方式缴纳招标文件费用，备注栏填写“ 标书 包件费 用”，汇款需使用投标单位的公户进行汇款，缴纳采购文件费用后，将付款凭证于 年 月 日 时 前发至邮箱 ，并致电采购联系人确认开通标书下载权限，（邮件标题栏填写“ （供应商名称） 包件 （招标名称）标书费用”）方能下载采购文件。 保证金的费用请汇入以下账户：备注：**项目**物资招标采购投标保证金（投递网多个包件可合并递交，但需注明 包件号），交纳投标保证金的银行凭证（电汇回单）扫描件必须放置投标文件中一同上传（如参与多个包件投 标电汇时应备注注明所投包件号等）。 账户名称 ：中交一公局集团有限公司 务 账户性质 ：一般账户 账 号 ：01-10-000340-01 商 开 户 行 ：交通银行北京马甸支行 4.3 已在网并且已通过招标人层级供应商或已增加招标人为合作单位的供应商、上级供应商可直接参与投标。 在网平级单位供应商未增加招标人为合作单位道需进行合作意向申请通过后参与投标。 未注册“中交招采网”的单位需先进行注册，推荐单位或合作意向单位选择招标人，审核通过后方可参与投标。 5.投标文件的递交 管 5.1 投标文件递交的截止时间（投标截止时间，下同）为2026年9月4日14时00分，投标人应在截止时间前通 过“中交招采网”递交电子投标文件。 国 5.2 逾期未完成上传的电子投标文件，“中交招采网”将予以拒收。 5.3 电子采购的供应商报价文件由线上电子报价表及附件共同组成。当电子报价表与附件内容冲突时，以线上电 子报价表的数据为准。 中 6.开标 6.1开标时间：与投标文件递交的截止时间相同。 6.2开标地点：本次招标在“中交招采网”线上开标，不举办现场开标。 7.发布公告的媒介 本次招标公告在“中交招采网”上发布。 8.评标办法 本项目评标办法采用： □本项目采购内容为一级集采目录物资，评标办法采用经评审的最低价投标法。 本项目采购内容为非一级集采目录物资，评标办法采用经评审的最低价投标法。 9.投标保证金 投标保证金的递交： （1）□不要求递交 （2）要求递交 保证金金额：收取10万元； 保证金形式：现金、银行转账、银行保函等电子保函，需公对公转账。在递交投标文件截止时间后到达指定账 户的投标保证金无效（以招标人财务统计为准）。投标人应充分考虑投标保证金在银行之间的划转所需要的时 间，以确保其在投标截止时间之前到达指定账户。未及时足额提交投标保证金的，予以废标。 供应商可采用电子投标保函替代投标保证金，具体要求及操作详见附件《关于在网物资招标采购过程中推广电子 投标保函替代投标保证金的通知》。 投标保证金的到账截止时间为：投标截止时间前。 务 保证金退还条件及信息： 1.招标人发布中标通知书及中标结果通知书后，统一开始办理退中标和未中标的投标人提交的投标保证金。 2.投标人必须按要求将打款账户一致的收款账户信息（收商款单位、账户、开户行等）发给招标人邮箱。 10.合同主要条款 10.1结算及付款方式： 道 按月办理结算，甲方在取得乙方合规的增值税专用发票后进行结算办理，于每月25日前完成财务入账工作。结算 完成后2个月内支付结算金额的60%，3个月内支付结算金额的80%，剩余20%于6个月内付清。付款方式包含50% 银行转账+50%银行产品（E信通、云信等，银行产品期限为半年期）。其中金融产品对应的贴息费由乙方承担。 管 10.2履约保证金的递交： （1）□不要求递交 国 （2）要求递交 保证金金额：按中标金额的2%，最高金额不超100万。 中 保证金形式：现金、银行转账、银行保函等电子保函，需公对公转账。 提交时间：中标人与所属项目签订合同前应提交履约担保，若投标人未按规定的时间和额度提交履约担保，招 标人可取消其中标资格或宣布其中标无效，并没收其投标保证金。办理履约担保所需费用由中标人自行承担。 履约保证金缴纳账户为“甲方”（项目承建公司）对公账户。有效期：履约担保的有效期限为合同最后一批材 料交货验收合格后三个月后由甲方审核次月返还。 11.监督机构 监督机构名称：中交一公局集团有限公司茅台制酒车间（二期）管网改造老区标段项目经理部监督部 举报电话：17767795970 举报邮箱：zjygjlgscsb@126.com 12.中标供应商平台服务费缴纳说明 为进一步提升电子采购平台服务质量，优化运营流程，保障双方合作更加顺畅高效，对参与我司采购活动并成 功中标的供应商分档收取服务费。具体费用以中标通知书中同步生成的服务费订单为准，订单将通过“中交招 采网”（网址：https://zjzcw.iccec.cn）发送，发送后10天内需完成费用缴纳。缴费过程中如有问题，请联 系4006765885中标服务费请按7咨询。 12.1收费标准 按照包件分档进行收费，收费标准按以下中标金额进行收取： （1）在100万元（含）至200万元之间的，每次收取100元； （2）在200万元（含）至1000万元之间的，每次收取500元； （3）在1000万元（含）至3000万元之间的，每次收取1000元； （4）在3000万元（含）至1亿元之间的，每次收取3000元； 网 （5）在1亿元（含）以上的，每次收取5000元。 12.2支付流程 务 （1）通知推送：中标结果发布后，系统自动推送缴费通知（含应缴金额及支付链接）； （2）费用查询：供应商登录“中交招采网-服务管理”模块查看待支付费用； 商 （3）在线支付：支持对公银行转账或在线支付，支付成功后生成电子凭证； （4）发票开具：支付完成后5个工作日内，系统自动生成“技术服务费”电子发票，供应商可在“中交招采网- 服务管理－发票下载”模块获取。 道 13.其他 / 。 管 （注：可根据项目情况简述其他需要说明的内容。） 联系信息： 国 14.联系方式 中 招 标 人：中交一公局集团有限公司茅台制酒车间（二期）管网改造老区标段项目经理部 地 址：天津市滨海新区塘沽塘汉路549号 邮 编：300450 联 系 人：温女士 电 话：022-66350320 电子邮件：zjygjlgscsb@126.com 2026年8月 信息来源:https://www.chinapipe.net/project/d3064609.html cqdingjiu 2026.08.25 14:22:33 网 务 商 道 管 国 中</t>
+          <t>W3中国核建中核华辰300MW燃料元件及含钆燃料棒生产建设工程建筑安装施工项目保温材料常规采购(第二次) 采购公告 第一章 采购公告 中国核建中核华辰300MW燃料元件及含钆燃料棒生产建设工程建筑安装施工项目保温材料常规询比采购公告 （第二次） 本次采购项目：中国核建中核华辰300MW燃料元件及含钆燃料棒生产建设工程建筑安装施工项目保温材料常规 询比采购（第二次），采购需求单位为：中核华辰建筑工程有限公司 ，本项目网已具备采购条件，由采购实施单 位 中国核工业建设股份有限公司 组织实施采购，由采购需求单位根据采购结果签订采购合同/协议。现诚邀愿意 承接该项目的潜在供应商参加本次采购活动。 1. 采购项目简介 务 1. 采购项目名称：中国核建中核华辰300MW燃料元件及含钆燃料棒生产建设工程建筑安装施工项目保 温材料常规询比采购（第二次）； 2. 采购实施单位：中国核工业建设股份有限公司 3. 采购项目资金落实情况： 已落实； 商 4. 采购方式：公开询比； 5. 成交供应商数量及份额： 1家； 1. 采购范围及相关要求 1. 采购范围：中国核建中核华辰300MW燃料元件及含钆燃料棒生产建设工程建筑安装施工项目保温材 道 料常规询比采购。 序 计量 物资名称 规格型号 材质 技术标准 数量 备注 号 单位 管 1 岩棉管壳 Φ89×50mm 110kg/m3 / GB/T 19686-2015 m3 3.87 2 岩棉管壳 Φ73×50mm 110kg/m3 / GB/T 19686-2015 m3 2.18 3 岩棉管壳 Φ48×50mm 130kg/m3 / GB/T 19686-2015 m3 3.26 国 4 岩棉管壳 Φ42×50mm 130kg/m3 / GB/T 19686-2015 m3 1.1 夹筋铝 5 箔橡塑保 Φ114.3×20mm / GB/T 17794-2021 m3 0.73 B2级 温管壳中 夹筋铝箔 6 橡塑保温 Φ89×20mm / GB/T 17794-2021 m3 0.13 B2级 管壳 夹筋铝箔 7 橡塑保温 Φ73×20mm / GB/T 17794-2021 m3 0.35 B2级 管壳 夹筋铝箔 8 橡塑保温 Φ54×20mm / GB/T 17794-2021 m 50 B2级 管壳 夹筋铝箔 9 橡塑保温 Φ48×20mm / GB/T 17794-2021 m3 1.06 B2级 管壳 夹筋铝箔 10 橡塑保温 Φ42×20mm / GB/T 17794-2021 m3 0.38 B2级 管壳 夹筋铝箔 11 橡塑保温 Φ34×20mm / GB/T 17794-2021 m3 0.22 B2级 管壳 冷轧不锈 12 δ=0.3mm 06Cr19Ni10 GB/T3280 06Cr19Ni10 GB/T3280-2015 t 0.95 钢板 DBK 250×120×40mm 陶瓷纤维+硅酸钙隔热 陶瓷纤维+硅 13 阻火包 GB 23864-2023 个 600 板+防火硅布 酸 2.2交货期：根据通知分批交付； 2.3交货地点： 四川省宜宾市叙州区高场镇中核华辰项目；进入卸货场地须遵循网特别要求，甲方现场管理要求； 甲方卸货 2.4货物质量标准或主要技术性能指标：必须符合以上采购明细中各项材料的技术标准要求。如合同执行期间有 新的标准，则自动按新标准执行。 务 1. 供应商资格要求 1. 本次资格审查为 资格后审方式 2. 供应商应依法设立且具备承担本采购项目的资质条件、能力和信誉： 商 1. 基本要求：提供有效的营业执照（或事业法人登记证）； 2. 资质要求：/； 1. 安全要求：/； 道 2. 财务要求：/； 3. 业绩要求：应答人需提供本单位近3年（自采购公告截止日往前计算至3个整年，业绩审查以合同为准，需 体现合同范围内容页、合同金额页、时间、双方盖章页等合同关键信息，若无法体现上述内容的视为未提 供）物资合同业绩、且提供的合同业绩累加总额不低于本次采购供应商自身报价金额50%规模业绩； 4. 信誉要求：应当无不良施工管记录等违法行为，且无下列不良状况或不良信用记录：①在国家企业信用信息 公示系统（www.gsxt.gov.cn）中列为严重违法失信企业名单；②在“中国执行信息公开网”网站中被列入 失信被执行人名单；③在国家税务总局（http://www.chinatax.gov.cn/）中被列入重大税收违法失信案件信息 公布栏。（应答人无需提供截图,以递交响应文件截止当日采购人查询结果为准） 5. 其他要求：①不国接受参保人数为0的供应商参与应答，应答人需提供截止应答时间近 3 个月内的员工社会 保险缴纳记录；②不接受实缴资本为0元的供应商参与应答，应答人需提供实缴资本证明材料（此项若未 提供，以递交响应文件截止当日采购人在国家企业信用信息公示系统（www.gsxt.gov.cn）查询的缴纳证明 为准）； 1. 供应商不得存在下列情形之一： 中 1. 不同供应商之间的单位负责人为同一人，或者存在直接控股、管理关系； 2. 处于被责令停产停业、暂扣或者吊销执照、暂扣或者吊销许可证、吊销资质证书状态； 3. 被本项目所在地省级以上行业主管部门依法暂停或者取消报价资格； 4. 进入清算程序，或被宣告破产，或其他丧失履约能力的情形； 5. 根据中国核工业集团供应商管理要求，被禁止参与采购活动且处于有效期； 6. 供应商处于中国核工业集团有限公司、中国核工业建设股份有限公司供应商黑名单或灰名单，且处于有效 期内； 7. 国务院国资委、国家核安全局、国家能源局、国防科工局等国家行政或行业主管部门等发布的属于严重及 以上行为情形的； 8. 近三年有骗取中标或严重违约，有经鉴定部门认定的因其产品引起的重大及以上质量事故或重大及以上安 全事故的或重大及以上环保事故的； 9. 供应商在中国核工业集团电子采购平台的报名、下载文件、报价等环节实施过程中，如出现硬件特征码 或MAC地址一致或参与项目的联系人及其联系方式一致的等异常情况时，采购实施单位将视情况决定对 硬件特征码或MAC地址出现异常或参与项目的联系人及其联系方式一致的供应商进行调查或直接采取处 理措施。采购实施单位如进行调查的，供应商有义务配合调查并按要求做出回应，如供应商未按采购实施 单位要求及时回应的，则采购实施单位有权根据已知资料和情况做出相关处理决定。 1. 本次采购不接受联合体应答。联合体应答的，应满足下列要求：/。 1. 文件的获取 1. 采购文件售价 每套采购文件售价人民币 不收取 元整，除因采购人原因导致采购终止外，售后款项不予退还。 采购实施单位收款银行名称：中国工商银行上海市分行第二营业部 开户单位：中国核工业建设股份有限公司 收款账号：1001 1907 1900 4867 917 应答供应商须在汇款单上注明：“XJD-26-15247”。（注：“摘要”栏中不要额外加汉字！若供应商银行支付系 统内无“摘要”栏，则在“备注”栏及“用途”栏同时填写XJD-26-15247）。 缴纳方式：公对公银行转账方式（不接受私人转账和其它形式缴纳）。 网 1. 发售时间 北京时间：2026年8月26日—2026年9月2日10：00 务 1. 采购文件发售方式 电子版采购文件将在中国核工业集团电子采购平台（https://www.cnncecp.com）进行发布。供应商已注册为中国 核工业集团电子采购平台会员的，可直接登录报名；其他有意向的供应商请于采购文件发售截止时间前完成在 中国核工业集团电子采购平台（https://www.cnncecp.com）商在线注册，交纳相关费用及应答保密承诺函的签署盖章 （格式见主页服务中心），报名经采购实施单位/采购代理机构（如有）审核后方可下载采购文件。中国核工业 集团电子采购平台将在发售期结束后自动关闭报名入口，未能按时完成报名、购买采购文件相关工作的供应商 不得参与项目应答。 道 因供应商未能按上述要求包括但不限于上传错误的缴费凭证、提交的报名文件不符合要求，造成无法报名、报 名错误等情况的，供应商须自行承担责任。 1. 其他事项说明 管 未购买本项目采购文件的，其应答将被拒绝，有文件证明下列情形的除外： （1）作为应答供应商的办事处或分公司代为购买采购文件的； 国 （2）购买采购文件的厂家在应答截止前因兼并、重组上市等原因导致公司名称变化的。 1. 应答文件的递交 中 递交应答文件方式：中国核工业集团电子采购平台网络递交电子版应答文件（同时须在平台上进行报价）及线 下递交纸质版应答文件（如有）。 递交应答文件地点： / 1. 递交应答文件截止时间（应答截止时间）：2026年9月2日10：00。 应答文件应按采购文件规定时间、地点递交，逾期送达的、未送达指定地点的或者不按照采购文件要求密封的 应答文件，采购实施单位将予以拒收 。 1. 应答文件开启时间和地点 采购实施单位在本项目提交应答文件截止时间 公开 开启应答文件，地点为应答文件递交地点。 1. 发布公告的媒介 本次公告在中国核工业集团电子采购平台（https://www.cnncecp.com）上发布。 1. 联系方式 采购实施单位：中国核工业建设股份有限公司 地址：上海市青浦区蟠龙路500号 联系人：赵楠 电话：17275423359 1. 其他说明 1. 本次采购活动的最终解释权在采购实施单位。 2. 供应商须遵守采购实施单位的保密规定（见保密承诺函），并遵守相关廉洁协议。 3. 对于其它公司利用本公司发布的公告信息进行诈骗的行为，本公司将不承担任何责任，并保留追究 相关责任人权利。 4. 本项目评审完成后，评审专家将按照成交候选人排序依次对拟成交供应商进行准入评审打分，满足 合格供应商准入评审要求的候选人方可被确定为成交供应商。具体网准入评审流程及材料要求详见第 二章“供应商须知前附表”第10条。请供应商在应答文件中按要求完整提供准入评审所需材料。 2. 其他需要补充的内容 若相同厂家/品牌产品的不同应答人同时参与本次应答的，仅推荐1个成交候选人资格，即通过资格审查、符合性 务 审查且报价最低的应答人获得成交候选人推荐资格。 采购实施单位：中国核工业建设股份有限公司 商 采购需求单位：中核华辰建筑工程有限公司 2026年8月26日 道 信息来源:https://www.chinapipe.net/project/d3080900.html cqdingjiu 2026.08.26 17:19:24 管 国 中</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>贵州茅台酒股份有限公司茅台本部制酒车间（二期）管网改造老区标段项目制酒9--18车间、制酒8车间1--4号房区域排水管网改造。
-https://www.chinapipe.net/project/d3064609.html</t>
+          <t>中国核建中核华辰300MW燃料元件及含钆燃料棒生产建设工程建筑安装施工项目保温材料常规询比采购。
+合计金额（元）：本项目网已具备采购条件，由采购实施单位 中国核工业建设股份有限公司 组织实施采购，由采购需求单位根据采购结果签订采购合同/协议。
+https://www.chinapipe.net/project/d3080900.html</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>茅台管网改造, 不锈钢管, 管件, 管网改造, 排水管网改造</t>
+          <t>未识别到明确匹配关键词</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>贵州图南矿业(集团)有限公司兴仁市下山镇四海煤矿钢材采购公告</t>
+          <t>自贡水务投资集团有限公司软密封蝶阀、闸阀等阀门年度采购项目采购邀请公告</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2502,7 +2513,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>其他/未识别</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2517,58 +2528,59 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>贵州省</t>
+          <t>四川省</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>黔西南布依族苗族自治州</t>
+          <t>自贡市</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>兴仁市</t>
+          <t>自流井区</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>立柱镀锌方钢管、背筋镀锌方钢管、拉杆镀锌方钢管、拉杆角铁、彩钢瓦、彩条布的采购。</t>
+          <t>采购软密封蝶阀、电动软密封蝶阀、软密封闸阀、电动软密封闸阀、伸缩器、Y型过滤器、复合式排气阀等产品。</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>原文未提及</t>
+          <t>年度采购金额预估185万元（以实际采购金额为准）。</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>立柱镀锌方钢管,背筋镀锌方钢管,拉杆镀锌方钢管,拉杆角铁,彩钢瓦,彩条布</t>
+          <t>软密封蝶阀,电动软密封蝶阀,软密封闸阀,电动软密封闸阀,伸缩器,Y型过滤器,复合式排气阀</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>贵州图南矿业(集团)有限公司兴仁市下山镇四海煤矿钢材采购公告 采购公告 一、项目名称：贵州图南矿业(集团)有限公司兴仁市下山镇四海煤矿钢材采购 二、项目编号：JZJC-20260890 三、采购方式：公开询价 网 四、购买项目概况及需求： 序 申请公司 物品编码 名称 规格型号 单位 数量 备注 号 务 贵州图南矿业(集团)有限公司 立柱镀锌 1 MKD5BE.00042 60*60*3mm 米 5530 兴仁市下山镇四海煤矿 方钢管 贵州图南矿业(集团)有限公司 背筋镀锌 2 MKD5BE.00043 商50*30*3mm 米 11060 兴仁市下山镇四海煤矿 方钢管 上述材料所 产生的费用 贵州图南矿业(集团)有限公司 拉杆镀锌 3 MKD5BE.00044 50*30*3mm 米 4793 涵盖运输、 兴仁市下山镇四海煤矿 方钢管 安装以及安 道 贵州图南矿业(集团)有限公司 4 MKD5BA.00019 拉杆角铁 40*40*4mm 米 1844 装所需的辅 兴仁市下山镇四海煤矿 材、设备和 贵州图南矿业(集团)有限公司 YX30-245-980（展 平方 人员等。 5 MKD5BA.00021 彩钢瓦 11031 兴仁市下山镇四海煤矿 开宽度1200mm) 米 管 贵州图南矿业(集团)有限公司 6 MKC10E.00003 彩条布 8mx30m 包 50 兴仁市下山镇四海煤矿 五、项目要求： 国 （1）上述材料所产生的费用涵盖运输、安装以及安装所需的辅材、设备和人员等。 六、付款方式：货到验收合格并完成安装后，供货方开具增值税专用发票30天内支付全款。 中 七、询比文件获取： 地点：贵州省兴义市梦乐城1号写字楼22楼 询比文件发布时间：2026年8月25日 询比文件获取截止时间：2026年8月27日14时30分前 获取方式：2026年8月25日在贵州招标投标公共服务平台(http://ztb.guizhou.gov.cn/#）发布采购公告；金州集团公 司采购平台(http://111.85.155.224:2243/)公开发布采购询价单，在采购平台中登录后进行下载；若是无登录账号， 需联系采购方，按采购方要求提供资料，审核通过后注册账号。 采购文件：免费获取(电子文档)。 八、询比报价截止时间： 询比报价单递交截止时间：2026年8月27日14时30分 递交地点：在金州电力集团公司采购平台上传询比报价单 九、联系方式： 采购公司：贵州黔铭物资贸易有限公司 联系人：江文欢（19985399266） 信息来源:https://www.chinapipe.net/project/d3079585.html cqdingjiu 2026.08.25 14:22:33 网 务 商 道 管 国 中</t>
+          <t>自贡水务投资集团有限公司软密封蝶阀、闸阀等阀门年度采购项目采购邀请公告 自贡水务投资集团有限公司将对软密封蝶阀、闸阀等阀门年度采购项目进行公开采购，现拟邀请符合本次采购 要求的供应商参加采购，内容如下： 一、 公告网址：自贡水务投资集团有限公司 （ https://www.zgwater.com ） 上公开发布 二、 项目名称：自贡水务投资集团有限公司软密封蝶阀、闸阀等阀门 年度采购项目 三、合同签订主体分别为：自贡水务投资集团有限公司、自贡水投建设安装工程网有限责任公司、自贡市城南水 务有限公司 四 、 年度采购金额： 年度采购金额 预估 185 万元 （ 以实际采购金额为准 ） 务 五 、合同有效期限： 1 年 六 、项目 采购 内容： 商 序号 产品名称 单位 规格 连接方式 1 软密封蝶阀 台 DN200-1200 法兰 2 电动软密封蝶阀 台 DN200-1200 法兰 道 3 软密封闸阀 台 DN65-500 法兰 4 软密封闸阀 台 DN40-80 螺纹 5 电动软密封闸阀 台 DN100-500 法兰 管 6 伸缩器 台 DN100-1200 法兰（限位） 7 Y型过滤器 台 DN80-500 法兰 8 复合式排气阀 台 DN50-300 法兰 国 七、中选年度供应商 确定方式： 采用综合评分法评审，以得分 ≥60从高到低进行排序，按得分最高原则确 定 2 家为 中选年度第一、第二供应商 。综 合得分相同的，报价低者优先；报价也相同的，技术分高者 优先。 中 八 、供应商参加本次采购活动应具备下列条件 1.供应商营业执照经营范围须包含采购内容。 2.具有独立承担民事责任能力。 3.具有良好的商业信誉和健全的财务会计制度。 